--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/673b1203f7e82b27/מסמכים/GitHub/BURSA/BURSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D1803D-9746-4C08-83A2-CD263161045D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{F8D1803D-9746-4C08-83A2-CD263161045D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E8C3EB6-52FF-4CCF-A997-CC1513EDCD59}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
   <sheets>
     <sheet name="התיק העדכני" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="100">
   <si>
     <t>MTF מחקה אינדקס תעשיה ישראל</t>
   </si>
@@ -326,6 +337,9 @@
   </si>
   <si>
     <t>מחיר 21/01/2026</t>
+  </si>
+  <si>
+    <t>מחיר 22/01/2026</t>
   </si>
 </sst>
 </file>
@@ -335,11 +349,11 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₪&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -348,7 +362,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -399,13 +413,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -799,9 +813,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא של Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -839,7 +853,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -945,7 +959,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1087,7 +1101,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1095,22 +1109,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86B4639-EF9D-4B16-B2C9-0D5E9C5EEC8B}">
-  <dimension ref="A1:BO25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BP25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="5" width="17.5703125" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="50" width="14.85546875" customWidth="1"/>
-    <col min="51" max="60" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="11" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="11.5703125" customWidth="1"/>
+    <col min="1" max="5" width="17.59765625" customWidth="1"/>
+    <col min="6" max="6" width="13.296875" customWidth="1"/>
+    <col min="7" max="7" width="11.59765625" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="51" width="14.8984375" customWidth="1"/>
+    <col min="52" max="61" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="13" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="11" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="11.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1139,181 +1153,184 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BK1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BL1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BM1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="BM1" s="12" t="s">
+      <c r="BN1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="BN1" s="12" t="s">
+      <c r="BO1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="BO1" s="12" t="s">
+      <c r="BP1" s="12" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A2" s="1">
         <v>282012</v>
       </c>
@@ -1339,12 +1356,14 @@
         <v>10700</v>
       </c>
       <c r="J2" s="13">
+        <v>10700</v>
+      </c>
+      <c r="K2" s="13">
         <v>10400</v>
       </c>
-      <c r="K2" s="13">
+      <c r="L2" s="13">
         <v>11230</v>
       </c>
-      <c r="L2" s="6"/>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
@@ -1385,11 +1404,11 @@
       <c r="AX2" s="6"/>
       <c r="AY2" s="6"/>
       <c r="AZ2" s="6"/>
-      <c r="BA2" s="33"/>
-      <c r="BB2" s="6"/>
+      <c r="BA2" s="6"/>
+      <c r="BB2" s="33"/>
       <c r="BC2" s="6"/>
-      <c r="BD2" s="33"/>
-      <c r="BE2" s="6"/>
+      <c r="BD2" s="6"/>
+      <c r="BE2" s="33"/>
       <c r="BF2" s="6"/>
       <c r="BG2" s="6"/>
       <c r="BH2" s="6"/>
@@ -1397,11 +1416,12 @@
       <c r="BJ2" s="6"/>
       <c r="BK2" s="6"/>
       <c r="BL2" s="6"/>
-      <c r="BM2" s="25"/>
+      <c r="BM2" s="6"/>
       <c r="BN2" s="25"/>
       <c r="BO2" s="25"/>
-    </row>
-    <row r="3" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BP2" s="25"/>
+    </row>
+    <row r="3" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A3" s="1">
         <v>1227552</v>
       </c>
@@ -1424,39 +1444,41 @@
         <v>46029</v>
       </c>
       <c r="G3" s="27">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H3" s="13">
         <v>1153.6300000000001</v>
       </c>
       <c r="I3" s="13">
-        <v>1316</v>
+        <v>1331</v>
       </c>
       <c r="J3" s="13">
+        <v>1331</v>
+      </c>
+      <c r="K3" s="13">
         <v>1386</v>
       </c>
-      <c r="K3" s="13">
+      <c r="L3" s="13">
         <v>1342</v>
       </c>
-      <c r="L3" s="13">
+      <c r="M3" s="13">
         <v>1250</v>
-      </c>
-      <c r="M3" s="13">
-        <v>1389</v>
       </c>
       <c r="N3" s="13">
         <v>1389</v>
       </c>
       <c r="O3" s="13">
+        <v>1389</v>
+      </c>
+      <c r="P3" s="13">
         <v>1367</v>
       </c>
-      <c r="P3" s="13">
+      <c r="Q3" s="13">
         <v>1026</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="R3" s="13">
         <v>949.1</v>
       </c>
-      <c r="R3" s="13"/>
       <c r="S3" s="13"/>
       <c r="T3" s="13"/>
       <c r="U3" s="13"/>
@@ -1472,8 +1494,8 @@
       <c r="AE3" s="13"/>
       <c r="AF3" s="13"/>
       <c r="AG3" s="13"/>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="13"/>
+      <c r="AH3" s="13"/>
+      <c r="AI3" s="14"/>
       <c r="AJ3" s="13"/>
       <c r="AK3" s="13"/>
       <c r="AL3" s="13"/>
@@ -1491,36 +1513,37 @@
       <c r="AX3" s="13"/>
       <c r="AY3" s="13"/>
       <c r="AZ3" s="13"/>
-      <c r="BA3" s="29"/>
-      <c r="BB3" s="13"/>
+      <c r="BA3" s="13"/>
+      <c r="BB3" s="29"/>
       <c r="BC3" s="13"/>
-      <c r="BD3" s="29"/>
-      <c r="BE3" s="13"/>
+      <c r="BD3" s="13"/>
+      <c r="BE3" s="29"/>
       <c r="BF3" s="13"/>
       <c r="BG3" s="13"/>
       <c r="BH3" s="13"/>
-      <c r="BI3" s="13">
-        <f>(G3*H3)/100-BO3</f>
-        <v>634.49650000000008</v>
-      </c>
+      <c r="BI3" s="13"/>
       <c r="BJ3" s="13">
+        <f>(G3*H3)/100-BP3</f>
+        <v>784.46840000000009</v>
+      </c>
+      <c r="BK3" s="13">
         <f>(G3*H3)/100</f>
-        <v>634.49650000000008</v>
-      </c>
-      <c r="BK3" s="13">
-        <f>(BJ3-BI3)</f>
+        <v>784.46840000000009</v>
+      </c>
+      <c r="BL3" s="13">
+        <f>(BK3-BJ3)</f>
         <v>0</v>
       </c>
-      <c r="BL3" s="13">
-        <f>((AZ3-H3)/H3)*100</f>
+      <c r="BM3" s="13">
+        <f>((BA3-H3)/H3)*100</f>
         <v>-100</v>
       </c>
-      <c r="BO3" s="15">
-        <f>(BM3*BN3-BM3*H3)/100</f>
+      <c r="BP3" s="15">
+        <f>(BN3*BO3-BN3*H3)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A4" s="1">
         <v>587014</v>
       </c>
@@ -1549,33 +1572,35 @@
         <v>5925</v>
       </c>
       <c r="I4" s="13">
-        <v>6060</v>
+        <v>6111</v>
       </c>
       <c r="J4" s="13">
+        <v>6111</v>
+      </c>
+      <c r="K4" s="13">
         <v>6050</v>
       </c>
-      <c r="K4" s="13">
+      <c r="L4" s="13">
         <v>6169</v>
       </c>
-      <c r="L4" s="13">
+      <c r="M4" s="13">
         <v>6300</v>
-      </c>
-      <c r="M4" s="13">
-        <v>6335</v>
       </c>
       <c r="N4" s="13">
         <v>6335</v>
       </c>
       <c r="O4" s="13">
+        <v>6335</v>
+      </c>
+      <c r="P4" s="13">
         <v>6444</v>
-      </c>
-      <c r="P4" s="13">
-        <v>5749</v>
       </c>
       <c r="Q4" s="13">
         <v>5749</v>
       </c>
-      <c r="R4" s="13"/>
+      <c r="R4" s="13">
+        <v>5749</v>
+      </c>
       <c r="S4" s="13"/>
       <c r="T4" s="13"/>
       <c r="U4" s="13"/>
@@ -1610,36 +1635,37 @@
       <c r="AX4" s="13"/>
       <c r="AY4" s="13"/>
       <c r="AZ4" s="13"/>
-      <c r="BA4" s="29"/>
-      <c r="BB4" s="13"/>
+      <c r="BA4" s="13"/>
+      <c r="BB4" s="29"/>
       <c r="BC4" s="13"/>
-      <c r="BD4" s="29"/>
-      <c r="BE4" s="13"/>
+      <c r="BD4" s="13"/>
+      <c r="BE4" s="29"/>
       <c r="BF4" s="13"/>
       <c r="BG4" s="13"/>
       <c r="BH4" s="13"/>
-      <c r="BI4" s="13">
-        <f>(G4*H4)/100-BO4</f>
+      <c r="BI4" s="13"/>
+      <c r="BJ4" s="13">
+        <f>(G4*H4)/100-BP4</f>
         <v>1185</v>
       </c>
-      <c r="BJ4" s="13">
+      <c r="BK4" s="13">
         <f>(G4*H4)/100</f>
         <v>1185</v>
       </c>
-      <c r="BK4" s="13">
-        <f>(BJ4-BI4)</f>
+      <c r="BL4" s="13">
+        <f>(BK4-BJ4)</f>
         <v>0</v>
       </c>
-      <c r="BL4" s="13">
-        <f>((AZ4-H4)/H4)*100</f>
+      <c r="BM4" s="13">
+        <f>((BA4-H4)/H4)*100</f>
         <v>-100</v>
       </c>
-      <c r="BO4" s="15">
-        <f>(BM4*BN4-BM4*H4)/100</f>
+      <c r="BP4" s="15">
+        <f>(BN4*BO4-BN4*H4)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A5" s="1">
         <v>1099787</v>
       </c>
@@ -1653,7 +1679,7 @@
       </c>
       <c r="D5" s="6" t="str">
         <f>IF(I5&lt;GEMINI!L5,"למכור בהפסד",IF(I5&gt;GEMINI!M5,"למכור ברווח","לשמור"))</f>
-        <v>למכור בהפסד</v>
+        <v>לשמור</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>67</v>
@@ -1668,63 +1694,65 @@
         <v>525.71</v>
       </c>
       <c r="I5" s="13">
+        <v>626</v>
+      </c>
+      <c r="J5" s="13">
+        <v>626</v>
+      </c>
+      <c r="K5" s="13">
         <v>595.4</v>
       </c>
-      <c r="J5" s="13">
-        <v>595.4</v>
-      </c>
-      <c r="K5" s="13">
+      <c r="L5" s="13">
         <v>667.1</v>
       </c>
-      <c r="L5" s="13">
+      <c r="M5" s="13">
         <v>651</v>
-      </c>
-      <c r="M5" s="13">
-        <v>641.1</v>
       </c>
       <c r="N5" s="13">
         <v>641.1</v>
       </c>
       <c r="O5" s="13">
+        <v>641.1</v>
+      </c>
+      <c r="P5" s="13">
         <v>607.1</v>
       </c>
-      <c r="P5" s="13">
+      <c r="Q5" s="13">
         <v>583</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="R5" s="13">
         <v>581.6</v>
       </c>
-      <c r="R5" s="13">
+      <c r="S5" s="13">
         <v>578.70000000000005</v>
       </c>
-      <c r="S5" s="13">
+      <c r="T5" s="13">
         <v>590</v>
       </c>
-      <c r="T5" s="13">
+      <c r="U5" s="13">
         <v>554.70000000000005</v>
       </c>
-      <c r="U5" s="13">
+      <c r="V5" s="13">
         <v>511.8</v>
       </c>
-      <c r="V5" s="13">
+      <c r="W5" s="13">
         <v>487</v>
       </c>
-      <c r="W5" s="13">
+      <c r="X5" s="13">
         <v>478.8</v>
       </c>
-      <c r="X5" s="13">
+      <c r="Y5" s="13">
         <v>485.5</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="Z5" s="13">
         <v>453.4</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="AA5" s="13">
         <v>426.1</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AB5" s="13">
         <v>423.2</v>
       </c>
-      <c r="AB5" s="13"/>
       <c r="AC5" s="13"/>
       <c r="AD5" s="13"/>
       <c r="AE5" s="13"/>
@@ -1749,36 +1777,37 @@
       <c r="AX5" s="13"/>
       <c r="AY5" s="13"/>
       <c r="AZ5" s="13"/>
-      <c r="BA5" s="29"/>
-      <c r="BB5" s="13"/>
+      <c r="BA5" s="13"/>
+      <c r="BB5" s="29"/>
       <c r="BC5" s="13"/>
-      <c r="BD5" s="29"/>
-      <c r="BE5" s="13"/>
+      <c r="BD5" s="13"/>
+      <c r="BE5" s="29"/>
       <c r="BF5" s="13"/>
       <c r="BG5" s="13"/>
       <c r="BH5" s="13"/>
-      <c r="BI5" s="13">
-        <f t="shared" ref="BI5:BI19" si="0">(G5*H5)/100-BO5</f>
+      <c r="BI5" s="13"/>
+      <c r="BJ5" s="13">
+        <f t="shared" ref="BJ5:BJ19" si="0">(G5*H5)/100-BP5</f>
         <v>-294.42399999999992</v>
       </c>
-      <c r="BJ5" s="13">
+      <c r="BK5" s="13">
         <f>(G5*H5)/100</f>
         <v>0</v>
       </c>
-      <c r="BK5" s="13"/>
       <c r="BL5" s="13"/>
-      <c r="BM5">
+      <c r="BM5" s="13"/>
+      <c r="BN5">
         <v>260</v>
       </c>
-      <c r="BN5">
+      <c r="BO5">
         <v>638.95000000000005</v>
       </c>
-      <c r="BO5" s="15">
-        <f>(BM5*BN5-BM5*H5)/100</f>
+      <c r="BP5" s="15">
+        <f>(BN5*BO5-BN5*H5)/100</f>
         <v>294.42399999999992</v>
       </c>
     </row>
-    <row r="6" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A6" s="2">
         <v>1166768</v>
       </c>
@@ -1807,36 +1836,38 @@
         <v>3700</v>
       </c>
       <c r="I6" s="13">
-        <v>3931</v>
+        <v>3970</v>
       </c>
       <c r="J6" s="13">
+        <v>3970</v>
+      </c>
+      <c r="K6" s="13">
         <v>3870</v>
       </c>
-      <c r="K6" s="13">
+      <c r="L6" s="13">
         <v>3805</v>
       </c>
-      <c r="L6" s="13">
+      <c r="M6" s="13">
         <v>3667</v>
-      </c>
-      <c r="M6" s="13">
-        <v>3582</v>
       </c>
       <c r="N6" s="13">
         <v>3582</v>
       </c>
       <c r="O6" s="13">
+        <v>3582</v>
+      </c>
+      <c r="P6" s="13">
         <v>3570</v>
       </c>
-      <c r="P6" s="13">
+      <c r="Q6" s="13">
         <v>3619</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="R6" s="13">
         <v>3650</v>
       </c>
-      <c r="R6" s="13">
+      <c r="S6" s="13">
         <v>3720</v>
       </c>
-      <c r="S6" s="13"/>
       <c r="T6" s="13"/>
       <c r="U6" s="13"/>
       <c r="V6" s="13"/>
@@ -1870,41 +1901,42 @@
       <c r="AX6" s="13"/>
       <c r="AY6" s="13"/>
       <c r="AZ6" s="13"/>
-      <c r="BA6" s="29"/>
-      <c r="BB6" s="13"/>
+      <c r="BA6" s="13"/>
+      <c r="BB6" s="29"/>
       <c r="BC6" s="13"/>
-      <c r="BD6" s="29"/>
-      <c r="BE6" s="13"/>
+      <c r="BD6" s="13"/>
+      <c r="BE6" s="29"/>
       <c r="BF6" s="13"/>
       <c r="BG6" s="13"/>
-      <c r="BI6" s="13">
-        <f>(G6*H6)/100-BO6</f>
+      <c r="BH6" s="13"/>
+      <c r="BJ6" s="13">
+        <f>(G6*H6)/100-BP6</f>
         <v>561.70000000000005</v>
       </c>
-      <c r="BJ6" s="13">
+      <c r="BK6" s="13">
         <f>(G6*H6)/100</f>
         <v>555</v>
       </c>
-      <c r="BK6" s="13">
-        <f t="shared" ref="BK6" si="1">(BJ6-BI6)</f>
+      <c r="BL6" s="13">
+        <f t="shared" ref="BL6" si="1">(BK6-BJ6)</f>
         <v>-6.7000000000000455</v>
       </c>
-      <c r="BL6" s="13">
-        <f>((AZ6-H6)/H6)*100</f>
+      <c r="BM6" s="13">
+        <f>((BA6-H6)/H6)*100</f>
         <v>-100</v>
       </c>
-      <c r="BM6">
+      <c r="BN6">
         <v>5</v>
       </c>
-      <c r="BN6">
+      <c r="BO6">
         <v>3566</v>
       </c>
-      <c r="BO6" s="15">
-        <f>(BM6*BN6-BM6*H6)/100</f>
+      <c r="BP6" s="15">
+        <f>(BN6*BO6-BN6*H6)/100</f>
         <v>-6.7</v>
       </c>
     </row>
-    <row r="7" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A7" s="1">
         <v>1148899</v>
       </c>
@@ -1927,69 +1959,71 @@
         <v>46010</v>
       </c>
       <c r="G7" s="27">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H7" s="13">
         <v>3585</v>
       </c>
       <c r="I7" s="13">
-        <v>3885</v>
+        <v>3913</v>
       </c>
       <c r="J7" s="13">
+        <v>3913</v>
+      </c>
+      <c r="K7" s="13">
         <v>3860</v>
       </c>
-      <c r="K7" s="13">
+      <c r="L7" s="13">
         <v>3893</v>
       </c>
-      <c r="L7" s="13">
+      <c r="M7" s="13">
         <v>3900</v>
-      </c>
-      <c r="M7" s="13">
-        <v>3842</v>
       </c>
       <c r="N7" s="13">
         <v>3842</v>
       </c>
       <c r="O7" s="13">
+        <v>3842</v>
+      </c>
+      <c r="P7" s="13">
         <v>3841</v>
       </c>
-      <c r="P7" s="13">
+      <c r="Q7" s="13">
         <v>3809</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="R7" s="13">
         <v>3810</v>
       </c>
-      <c r="R7" s="13">
+      <c r="S7" s="13">
         <v>3798</v>
       </c>
-      <c r="S7" s="13">
+      <c r="T7" s="13">
         <v>3713</v>
       </c>
-      <c r="T7" s="13">
+      <c r="U7" s="13">
         <v>3657</v>
       </c>
-      <c r="U7" s="13">
+      <c r="V7" s="13">
         <v>3592</v>
       </c>
-      <c r="V7" s="13">
+      <c r="W7" s="13">
         <v>3621</v>
       </c>
-      <c r="W7" s="13">
+      <c r="X7" s="13">
         <v>3572</v>
       </c>
-      <c r="X7" s="13">
+      <c r="Y7" s="13">
         <v>3580</v>
       </c>
-      <c r="Y7" s="13">
+      <c r="Z7" s="13">
         <v>3569</v>
       </c>
-      <c r="Z7" s="13">
+      <c r="AA7" s="13">
         <v>3659</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="AB7" s="13">
         <v>3656</v>
       </c>
-      <c r="AB7" s="13"/>
       <c r="AC7" s="13"/>
       <c r="AD7" s="13"/>
       <c r="AE7" s="13"/>
@@ -2014,27 +2048,28 @@
       <c r="AX7" s="13"/>
       <c r="AY7" s="13"/>
       <c r="AZ7" s="13"/>
-      <c r="BA7" s="29"/>
-      <c r="BB7" s="13"/>
+      <c r="BA7" s="13"/>
+      <c r="BB7" s="29"/>
       <c r="BC7" s="13"/>
-      <c r="BD7" s="29"/>
-      <c r="BE7" s="13"/>
+      <c r="BD7" s="13"/>
+      <c r="BE7" s="29"/>
       <c r="BF7" s="13"/>
       <c r="BG7" s="13"/>
       <c r="BH7" s="13"/>
-      <c r="BI7" s="13">
+      <c r="BI7" s="13"/>
+      <c r="BJ7" s="13">
         <f t="shared" si="0"/>
-        <v>3226.5</v>
-      </c>
-      <c r="BJ7" s="13">
-        <f t="shared" ref="BJ7:BJ19" si="2">(G7*H7)/100</f>
-        <v>3226.5</v>
-      </c>
-      <c r="BK7" s="13"/>
+        <v>2509.5</v>
+      </c>
+      <c r="BK7" s="13">
+        <f t="shared" ref="BK7:BK19" si="2">(G7*H7)/100</f>
+        <v>2509.5</v>
+      </c>
       <c r="BL7" s="13"/>
-      <c r="BO7" s="15"/>
-    </row>
-    <row r="8" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BM7" s="13"/>
+      <c r="BP7" s="15"/>
+    </row>
+    <row r="8" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A8" s="1">
         <v>1082379</v>
       </c>
@@ -2063,99 +2098,101 @@
         <v>37875</v>
       </c>
       <c r="I8" s="13">
-        <v>42250</v>
+        <v>41570</v>
       </c>
       <c r="J8" s="13">
+        <v>41570</v>
+      </c>
+      <c r="K8" s="13">
         <v>42050</v>
       </c>
-      <c r="K8" s="13">
+      <c r="L8" s="13">
         <v>39960</v>
       </c>
-      <c r="L8" s="13">
+      <c r="M8" s="13">
         <v>39990</v>
-      </c>
-      <c r="M8" s="13">
-        <v>38680</v>
       </c>
       <c r="N8" s="13">
         <v>38680</v>
       </c>
       <c r="O8" s="13">
+        <v>38680</v>
+      </c>
+      <c r="P8" s="13">
         <v>37770</v>
       </c>
-      <c r="P8" s="13">
+      <c r="Q8" s="13">
         <v>36330</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="R8" s="13">
         <v>38680</v>
       </c>
-      <c r="R8" s="13">
+      <c r="S8" s="13">
         <v>39090</v>
       </c>
-      <c r="S8" s="13">
+      <c r="T8" s="13">
         <v>37300</v>
       </c>
-      <c r="T8" s="13">
+      <c r="U8" s="13">
         <v>37650</v>
       </c>
-      <c r="U8" s="13">
+      <c r="V8" s="13">
         <v>37300</v>
       </c>
-      <c r="V8" s="13">
+      <c r="W8" s="13">
         <v>39450</v>
       </c>
-      <c r="W8" s="13">
+      <c r="X8" s="13">
         <v>38390</v>
       </c>
-      <c r="X8" s="13">
+      <c r="Y8" s="13">
         <v>38800</v>
       </c>
-      <c r="Y8" s="13">
+      <c r="Z8" s="13">
         <v>38510</v>
-      </c>
-      <c r="Z8" s="13">
-        <v>38970</v>
       </c>
       <c r="AA8" s="13">
         <v>38970</v>
       </c>
       <c r="AB8" s="13">
-        <v>37700</v>
+        <v>38970</v>
       </c>
       <c r="AC8" s="13">
         <v>37700</v>
       </c>
       <c r="AD8" s="13">
+        <v>37700</v>
+      </c>
+      <c r="AE8" s="13">
         <v>37750</v>
       </c>
-      <c r="AE8" s="13">
+      <c r="AF8" s="13">
         <v>38430</v>
       </c>
-      <c r="AF8" s="13">
+      <c r="AG8" s="13">
         <v>38250</v>
       </c>
-      <c r="AG8" s="13">
+      <c r="AH8" s="13">
         <v>40110</v>
       </c>
-      <c r="AH8" s="13">
+      <c r="AI8" s="13">
         <v>40820</v>
       </c>
-      <c r="AI8" s="13">
+      <c r="AJ8" s="13">
         <v>39320</v>
       </c>
-      <c r="AJ8" s="13">
+      <c r="AK8" s="13">
         <v>37800</v>
       </c>
-      <c r="AK8" s="13">
+      <c r="AL8" s="13">
         <v>36620</v>
       </c>
-      <c r="AL8" s="13">
+      <c r="AM8" s="13">
         <v>37130</v>
       </c>
-      <c r="AM8" s="13">
+      <c r="AN8" s="13">
         <v>35850</v>
       </c>
-      <c r="AN8" s="13"/>
       <c r="AO8" s="13"/>
       <c r="AP8" s="13"/>
       <c r="AQ8" s="13"/>
@@ -2168,39 +2205,40 @@
       <c r="AX8" s="13"/>
       <c r="AY8" s="13"/>
       <c r="AZ8" s="13"/>
-      <c r="BA8" s="29"/>
-      <c r="BB8" s="13"/>
+      <c r="BA8" s="13"/>
+      <c r="BB8" s="29"/>
       <c r="BC8" s="13"/>
-      <c r="BD8" s="29"/>
-      <c r="BE8" s="13"/>
+      <c r="BD8" s="13"/>
+      <c r="BE8" s="29"/>
       <c r="BF8" s="13"/>
       <c r="BG8" s="13"/>
       <c r="BH8" s="13"/>
-      <c r="BI8" s="13">
+      <c r="BI8" s="13"/>
+      <c r="BJ8" s="13">
         <f t="shared" si="0"/>
         <v>806.25</v>
       </c>
-      <c r="BJ8" s="13">
+      <c r="BK8" s="13">
         <f t="shared" si="2"/>
         <v>757.5</v>
       </c>
-      <c r="BK8" s="13">
-        <f t="shared" ref="BK8:BK11" si="3">(BJ8-BI8)</f>
+      <c r="BL8" s="13">
+        <f t="shared" ref="BL8:BL11" si="3">(BK8-BJ8)</f>
         <v>-48.75</v>
       </c>
-      <c r="BL8" s="13"/>
-      <c r="BM8">
+      <c r="BM8" s="13"/>
+      <c r="BN8">
         <v>3</v>
       </c>
-      <c r="BN8">
+      <c r="BO8">
         <v>36250</v>
       </c>
-      <c r="BO8" s="15">
-        <f>(BM8*BN8-BM8*H8)/100</f>
+      <c r="BP8" s="15">
+        <f>(BN8*BO8-BN8*H8)/100</f>
         <v>-48.75</v>
       </c>
     </row>
-    <row r="9" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A9" s="1">
         <v>629014</v>
       </c>
@@ -2229,93 +2267,95 @@
         <v>9227</v>
       </c>
       <c r="I9" s="13">
-        <v>9917</v>
+        <v>9924</v>
       </c>
       <c r="J9" s="13">
+        <v>9924</v>
+      </c>
+      <c r="K9" s="13">
         <v>9999</v>
       </c>
-      <c r="K9" s="13">
+      <c r="L9" s="13">
         <v>9962</v>
       </c>
-      <c r="L9" s="13">
+      <c r="M9" s="13">
         <v>9979</v>
-      </c>
-      <c r="M9" s="13">
-        <v>10130</v>
       </c>
       <c r="N9" s="13">
         <v>10130</v>
       </c>
       <c r="O9" s="13">
+        <v>10130</v>
+      </c>
+      <c r="P9" s="13">
         <v>10400</v>
       </c>
-      <c r="P9" s="13">
+      <c r="Q9" s="13">
         <v>10320</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="R9" s="13">
         <v>10300</v>
       </c>
-      <c r="R9" s="13">
+      <c r="S9" s="13">
         <v>10310</v>
       </c>
-      <c r="S9" s="13">
+      <c r="T9" s="13">
         <v>9672</v>
       </c>
-      <c r="T9" s="13">
+      <c r="U9" s="13">
         <v>9953</v>
       </c>
-      <c r="U9" s="13">
+      <c r="V9" s="13">
         <v>10090</v>
       </c>
-      <c r="V9" s="13">
+      <c r="W9" s="13">
         <v>10070</v>
       </c>
-      <c r="W9" s="13">
+      <c r="X9" s="13">
         <v>10030</v>
       </c>
-      <c r="X9" s="13">
+      <c r="Y9" s="13">
         <v>10120</v>
       </c>
-      <c r="Y9" s="13">
+      <c r="Z9" s="13">
         <v>10000</v>
       </c>
-      <c r="Z9" s="13">
+      <c r="AA9" s="13">
         <v>10080</v>
       </c>
-      <c r="AA9" s="13">
+      <c r="AB9" s="13">
         <v>10030</v>
-      </c>
-      <c r="AB9" s="13">
-        <v>9726</v>
       </c>
       <c r="AC9" s="13">
         <v>9726</v>
       </c>
       <c r="AD9" s="13">
+        <v>9726</v>
+      </c>
+      <c r="AE9" s="13">
         <v>9659</v>
       </c>
-      <c r="AE9" s="13">
+      <c r="AF9" s="13">
         <v>9670</v>
       </c>
-      <c r="AF9" s="13">
+      <c r="AG9" s="13">
         <v>9590</v>
       </c>
-      <c r="AG9" s="13">
+      <c r="AH9" s="13">
         <v>9588</v>
       </c>
-      <c r="AH9" s="13">
+      <c r="AI9" s="13">
         <v>9400</v>
       </c>
-      <c r="AI9" s="13">
+      <c r="AJ9" s="13">
         <v>9320</v>
       </c>
-      <c r="AJ9" s="13">
+      <c r="AK9" s="13">
         <v>9071</v>
       </c>
-      <c r="AK9" s="13">
+      <c r="AL9" s="13">
         <v>9271</v>
       </c>
-      <c r="AL9" s="13"/>
       <c r="AM9" s="13"/>
       <c r="AN9" s="13"/>
       <c r="AO9" s="13"/>
@@ -2330,33 +2370,34 @@
       <c r="AX9" s="13"/>
       <c r="AY9" s="13"/>
       <c r="AZ9" s="13"/>
-      <c r="BA9" s="29"/>
-      <c r="BB9" s="13"/>
+      <c r="BA9" s="13"/>
+      <c r="BB9" s="29"/>
       <c r="BC9" s="13"/>
-      <c r="BD9" s="29"/>
-      <c r="BE9" s="13"/>
+      <c r="BD9" s="13"/>
+      <c r="BE9" s="29"/>
       <c r="BF9" s="13"/>
       <c r="BG9" s="13"/>
       <c r="BH9" s="13"/>
-      <c r="BI9" s="13">
+      <c r="BI9" s="13"/>
+      <c r="BJ9" s="13">
         <f t="shared" si="0"/>
         <v>461.35</v>
       </c>
-      <c r="BJ9" s="13">
+      <c r="BK9" s="13">
         <f t="shared" si="2"/>
         <v>461.35</v>
       </c>
-      <c r="BK9" s="13">
+      <c r="BL9" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BL9" s="13"/>
-      <c r="BO9" s="15">
-        <f>(BM9*BN9-BM9*H9)/100</f>
+      <c r="BM9" s="13"/>
+      <c r="BP9" s="15">
+        <f>(BN9*BO9-BN9*H9)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A10" s="1">
         <v>1141464</v>
       </c>
@@ -2370,7 +2411,7 @@
       </c>
       <c r="D10" s="6" t="str">
         <f>IF(I10&lt;GEMINI!L10,"למכור בהפסד",IF(I10&gt;GEMINI!M10,"למכור ברווח","לשמור"))</f>
-        <v>למכור בהפסד</v>
+        <v>לשמור</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>39</v>
@@ -2385,175 +2426,178 @@
         <v>4834</v>
       </c>
       <c r="I10" s="13">
+        <v>5050</v>
+      </c>
+      <c r="J10" s="13">
+        <v>5050</v>
+      </c>
+      <c r="K10" s="13">
         <v>4930</v>
       </c>
-      <c r="J10" s="13">
-        <v>4930</v>
-      </c>
-      <c r="K10" s="13">
+      <c r="L10" s="13">
         <v>5150</v>
       </c>
-      <c r="L10" s="13">
+      <c r="M10" s="13">
         <v>5283</v>
-      </c>
-      <c r="M10" s="13">
-        <v>5253</v>
       </c>
       <c r="N10" s="13">
         <v>5253</v>
       </c>
       <c r="O10" s="13">
+        <v>5253</v>
+      </c>
+      <c r="P10" s="13">
         <v>5400</v>
       </c>
-      <c r="P10" s="13">
+      <c r="Q10" s="13">
         <v>5522</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="R10" s="13">
         <v>5690</v>
       </c>
-      <c r="R10" s="13">
+      <c r="S10" s="13">
         <v>5749</v>
       </c>
-      <c r="S10" s="13">
+      <c r="T10" s="13">
         <v>5840</v>
-      </c>
-      <c r="T10" s="13">
-        <v>5650</v>
       </c>
       <c r="U10" s="13">
         <v>5650</v>
       </c>
       <c r="V10" s="13">
+        <v>5650</v>
+      </c>
+      <c r="W10" s="13">
         <v>5841</v>
       </c>
-      <c r="W10" s="13">
+      <c r="X10" s="13">
         <v>5758</v>
       </c>
-      <c r="X10" s="13">
+      <c r="Y10" s="13">
         <v>5673</v>
       </c>
-      <c r="Y10" s="13">
+      <c r="Z10" s="13">
         <v>5609</v>
       </c>
-      <c r="Z10" s="13">
+      <c r="AA10" s="13">
         <v>5750</v>
       </c>
-      <c r="AA10" s="13">
+      <c r="AB10" s="13">
         <v>5841</v>
-      </c>
-      <c r="AB10" s="13">
-        <v>5564</v>
       </c>
       <c r="AC10" s="13">
         <v>5564</v>
       </c>
       <c r="AD10" s="13">
+        <v>5564</v>
+      </c>
+      <c r="AE10" s="13">
         <v>5557</v>
       </c>
-      <c r="AE10" s="13">
+      <c r="AF10" s="13">
         <v>5501</v>
       </c>
-      <c r="AF10" s="13">
+      <c r="AG10" s="13">
         <v>5250</v>
       </c>
-      <c r="AG10" s="13">
+      <c r="AH10" s="13">
         <v>5270</v>
       </c>
-      <c r="AH10" s="13">
+      <c r="AI10" s="13">
         <v>5149</v>
       </c>
-      <c r="AI10" s="13">
+      <c r="AJ10" s="13">
         <v>5092</v>
       </c>
-      <c r="AJ10" s="13">
+      <c r="AK10" s="13">
         <v>5228</v>
       </c>
-      <c r="AK10" s="13">
+      <c r="AL10" s="13">
         <v>5301</v>
       </c>
-      <c r="AL10" s="13">
+      <c r="AM10" s="13">
         <v>5159</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AN10" s="13">
         <v>5198</v>
       </c>
-      <c r="AN10" s="13">
+      <c r="AO10" s="13">
         <v>5077</v>
       </c>
-      <c r="AO10" s="13">
+      <c r="AP10" s="13">
         <v>4842</v>
       </c>
-      <c r="AP10" s="13">
+      <c r="AQ10" s="13">
         <v>5050</v>
       </c>
-      <c r="AQ10" s="13">
+      <c r="AR10" s="13">
         <v>4970</v>
       </c>
-      <c r="AR10" s="13">
+      <c r="AS10" s="13">
         <v>4880</v>
       </c>
-      <c r="AS10" s="13">
+      <c r="AT10" s="13">
         <v>4704</v>
       </c>
-      <c r="AT10" s="13">
+      <c r="AU10" s="13">
         <v>4770</v>
       </c>
-      <c r="AU10" s="13">
+      <c r="AV10" s="13">
         <v>4609</v>
       </c>
-      <c r="AV10" s="13">
+      <c r="AW10" s="13">
         <v>4674</v>
       </c>
-      <c r="AW10" s="13">
+      <c r="AX10" s="13">
         <v>4710</v>
       </c>
-      <c r="AX10" s="13">
+      <c r="AY10" s="13">
         <v>4688</v>
       </c>
-      <c r="AY10" s="13">
+      <c r="AZ10" s="13">
         <v>4900</v>
       </c>
-      <c r="AZ10" s="13">
+      <c r="BA10" s="13">
         <v>5000</v>
       </c>
-      <c r="BA10" s="29">
+      <c r="BB10" s="29">
         <v>4932</v>
       </c>
-      <c r="BB10" s="13"/>
       <c r="BC10" s="13"/>
-      <c r="BD10" s="29"/>
-      <c r="BE10" s="13"/>
+      <c r="BD10" s="13"/>
+      <c r="BE10" s="29"/>
       <c r="BF10" s="13"/>
       <c r="BG10" s="13"/>
       <c r="BH10" s="13"/>
-      <c r="BI10" s="13">
+      <c r="BI10" s="13"/>
+      <c r="BJ10" s="13">
         <f t="shared" si="0"/>
         <v>-87.859799999999964</v>
       </c>
-      <c r="BJ10" s="13">
+      <c r="BK10" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BK10" s="13">
+      <c r="BL10" s="13">
         <f t="shared" si="3"/>
         <v>87.859799999999964</v>
       </c>
-      <c r="BL10" s="13">
-        <f>((AZ10-H10)/H10)*100</f>
+      <c r="BM10" s="13">
+        <f>((BA10-H10)/H10)*100</f>
         <v>3.434009102192801</v>
       </c>
-      <c r="BM10">
+      <c r="BN10">
         <v>21</v>
       </c>
-      <c r="BN10">
+      <c r="BO10">
         <v>5252.38</v>
       </c>
-      <c r="BO10" s="15">
-        <f>(BM10*BN10-BM10*H10)/100</f>
+      <c r="BP10" s="15">
+        <f>(BN10*BO10-BN10*H10)/100</f>
         <v>87.859799999999964</v>
       </c>
     </row>
-    <row r="11" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A11" s="1">
         <v>1166974</v>
       </c>
@@ -2582,57 +2626,59 @@
         <v>901.87</v>
       </c>
       <c r="I11" s="13">
-        <v>1003</v>
+        <v>1029</v>
       </c>
       <c r="J11" s="13">
+        <v>1029</v>
+      </c>
+      <c r="K11" s="13">
         <v>993</v>
       </c>
-      <c r="K11" s="13">
+      <c r="L11" s="13">
         <v>1017</v>
       </c>
-      <c r="L11" s="13">
+      <c r="M11" s="13">
         <v>960</v>
-      </c>
-      <c r="M11" s="13">
-        <v>965</v>
       </c>
       <c r="N11" s="13">
         <v>965</v>
       </c>
       <c r="O11" s="13">
+        <v>965</v>
+      </c>
+      <c r="P11" s="13">
         <v>951.7</v>
       </c>
-      <c r="P11" s="13">
+      <c r="Q11" s="13">
         <v>946</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="R11" s="13">
         <v>869.2</v>
       </c>
-      <c r="R11" s="13">
+      <c r="S11" s="13">
         <v>865</v>
       </c>
-      <c r="S11" s="13">
+      <c r="T11" s="13">
         <v>851</v>
       </c>
-      <c r="T11" s="13">
+      <c r="U11" s="13">
         <v>829.3</v>
       </c>
-      <c r="U11" s="13">
+      <c r="V11" s="13">
         <v>830</v>
       </c>
-      <c r="V11" s="13">
+      <c r="W11" s="13">
         <v>810</v>
       </c>
-      <c r="W11" s="13">
+      <c r="X11" s="13">
         <v>812.8</v>
       </c>
-      <c r="X11" s="13">
+      <c r="Y11" s="13">
         <v>788</v>
       </c>
-      <c r="Y11" s="13">
+      <c r="Z11" s="13">
         <v>772</v>
       </c>
-      <c r="Z11" s="13"/>
       <c r="AA11" s="13"/>
       <c r="AB11" s="13"/>
       <c r="AC11" s="13"/>
@@ -2659,33 +2705,34 @@
       <c r="AX11" s="13"/>
       <c r="AY11" s="13"/>
       <c r="AZ11" s="13"/>
-      <c r="BA11" s="29"/>
-      <c r="BB11" s="13"/>
+      <c r="BA11" s="13"/>
+      <c r="BB11" s="29"/>
       <c r="BC11" s="13"/>
-      <c r="BD11" s="29"/>
-      <c r="BE11" s="13"/>
+      <c r="BD11" s="13"/>
+      <c r="BE11" s="29"/>
       <c r="BF11" s="13"/>
       <c r="BG11" s="13"/>
       <c r="BH11" s="13"/>
-      <c r="BI11" s="13">
+      <c r="BI11" s="13"/>
+      <c r="BJ11" s="13">
         <f t="shared" si="0"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BJ11" s="13">
+      <c r="BK11" s="13">
         <f t="shared" si="2"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BK11" s="13">
+      <c r="BL11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BL11" s="13"/>
-      <c r="BO11" s="15">
-        <f>(BM11*BN11-BM11*H11)/100</f>
+      <c r="BM11" s="13"/>
+      <c r="BP11" s="15">
+        <f>(BN11*BO11-BN11*H11)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A12" s="1">
         <v>1176593</v>
       </c>
@@ -2714,63 +2761,65 @@
         <v>22581.42</v>
       </c>
       <c r="I12" s="13">
-        <v>26620</v>
+        <v>26800</v>
       </c>
       <c r="J12" s="13">
+        <v>26800</v>
+      </c>
+      <c r="K12" s="13">
         <v>25950</v>
       </c>
-      <c r="K12" s="13">
+      <c r="L12" s="13">
         <v>26000</v>
       </c>
-      <c r="L12" s="13">
+      <c r="M12" s="13">
         <v>26600</v>
-      </c>
-      <c r="M12" s="13">
-        <v>24630</v>
       </c>
       <c r="N12" s="13">
         <v>24630</v>
       </c>
       <c r="O12" s="13">
+        <v>24630</v>
+      </c>
+      <c r="P12" s="13">
         <v>25230</v>
       </c>
-      <c r="P12" s="13">
+      <c r="Q12" s="13">
         <v>24700</v>
       </c>
-      <c r="Q12" s="13">
+      <c r="R12" s="13">
         <v>23780</v>
       </c>
-      <c r="R12" s="13">
+      <c r="S12" s="13">
         <v>23920</v>
       </c>
-      <c r="S12" s="13">
+      <c r="T12" s="13">
         <v>22390</v>
       </c>
-      <c r="T12" s="13">
+      <c r="U12" s="13">
         <v>23000</v>
       </c>
-      <c r="U12" s="13">
+      <c r="V12" s="13">
         <v>20990</v>
       </c>
-      <c r="V12" s="13">
+      <c r="W12" s="13">
         <v>20260</v>
       </c>
-      <c r="W12" s="13">
+      <c r="X12" s="13">
         <v>19200</v>
       </c>
-      <c r="X12" s="13">
+      <c r="Y12" s="13">
         <v>19860</v>
       </c>
-      <c r="Y12" s="13">
+      <c r="Z12" s="13">
         <v>19700</v>
       </c>
-      <c r="Z12" s="13">
+      <c r="AA12" s="13">
         <v>19430</v>
       </c>
-      <c r="AA12" s="13">
+      <c r="AB12" s="13">
         <v>19020</v>
       </c>
-      <c r="AB12" s="13"/>
       <c r="AC12" s="13"/>
       <c r="AD12" s="13"/>
       <c r="AE12" s="13"/>
@@ -2795,30 +2844,31 @@
       <c r="AX12" s="13"/>
       <c r="AY12" s="13"/>
       <c r="AZ12" s="13"/>
-      <c r="BA12" s="29"/>
-      <c r="BB12" s="13"/>
+      <c r="BA12" s="13"/>
+      <c r="BB12" s="29"/>
       <c r="BC12" s="13"/>
-      <c r="BD12" s="29"/>
-      <c r="BE12" s="13"/>
+      <c r="BD12" s="13"/>
+      <c r="BE12" s="29"/>
       <c r="BF12" s="13"/>
       <c r="BG12" s="13"/>
       <c r="BH12" s="13"/>
-      <c r="BI12" s="13">
+      <c r="BI12" s="13"/>
+      <c r="BJ12" s="13">
         <f t="shared" si="0"/>
         <v>1580.6994</v>
       </c>
-      <c r="BJ12" s="13">
+      <c r="BK12" s="13">
         <f t="shared" si="2"/>
         <v>1580.6994</v>
       </c>
-      <c r="BK12" s="13"/>
       <c r="BL12" s="13"/>
-      <c r="BO12" s="15">
-        <f t="shared" ref="BO12:BO14" si="4">(BM12*BN12-BM12*H12)/100</f>
+      <c r="BM12" s="13"/>
+      <c r="BP12" s="15">
+        <f t="shared" ref="BP12:BP14" si="4">(BN12*BO12-BN12*H12)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A13" s="1">
         <v>397018</v>
       </c>
@@ -2835,21 +2885,23 @@
         <v>46042</v>
       </c>
       <c r="G13" s="27">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="H13" s="13">
         <v>723</v>
       </c>
       <c r="I13" s="13">
-        <v>830.1</v>
+        <v>932.1</v>
       </c>
       <c r="J13" s="13">
+        <v>932.1</v>
+      </c>
+      <c r="K13" s="13">
         <v>822</v>
       </c>
-      <c r="K13" s="13">
+      <c r="L13" s="13">
         <v>790</v>
       </c>
-      <c r="L13" s="13"/>
       <c r="M13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -2890,30 +2942,31 @@
       <c r="AX13" s="13"/>
       <c r="AY13" s="13"/>
       <c r="AZ13" s="13"/>
-      <c r="BA13" s="29"/>
-      <c r="BB13" s="13"/>
+      <c r="BA13" s="13"/>
+      <c r="BB13" s="29"/>
       <c r="BC13" s="13"/>
-      <c r="BD13" s="29"/>
-      <c r="BE13" s="13"/>
+      <c r="BD13" s="13"/>
+      <c r="BE13" s="29"/>
       <c r="BF13" s="13"/>
       <c r="BG13" s="13"/>
       <c r="BH13" s="13"/>
-      <c r="BI13" s="13">
+      <c r="BI13" s="13"/>
+      <c r="BJ13" s="13">
         <f t="shared" si="0"/>
-        <v>723</v>
-      </c>
-      <c r="BJ13" s="13">
+        <v>816.99</v>
+      </c>
+      <c r="BK13" s="13">
         <f t="shared" si="2"/>
-        <v>723</v>
-      </c>
-      <c r="BK13" s="13"/>
+        <v>816.99</v>
+      </c>
       <c r="BL13" s="13"/>
-      <c r="BO13" s="15">
+      <c r="BM13" s="13"/>
+      <c r="BP13" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A14" s="1">
         <v>662577</v>
       </c>
@@ -2942,183 +2995,186 @@
         <v>7204.22</v>
       </c>
       <c r="I14" s="13">
-        <v>7722</v>
+        <v>7735</v>
       </c>
       <c r="J14" s="13">
+        <v>7735</v>
+      </c>
+      <c r="K14" s="13">
         <v>7725</v>
       </c>
-      <c r="K14" s="13">
+      <c r="L14" s="13">
         <v>7787</v>
       </c>
-      <c r="L14" s="13">
+      <c r="M14" s="13">
         <v>7955</v>
-      </c>
-      <c r="M14" s="13">
-        <v>7627</v>
       </c>
       <c r="N14" s="13">
         <v>7627</v>
       </c>
       <c r="O14" s="13">
+        <v>7627</v>
+      </c>
+      <c r="P14" s="13">
         <v>7656</v>
       </c>
-      <c r="P14" s="13">
+      <c r="Q14" s="13">
         <v>7507</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="R14" s="13">
         <v>7590</v>
       </c>
-      <c r="R14" s="13">
+      <c r="S14" s="13">
         <v>7569</v>
       </c>
-      <c r="S14" s="13">
+      <c r="T14" s="13">
         <v>7269</v>
       </c>
-      <c r="T14" s="13">
+      <c r="U14" s="13">
         <v>7444</v>
       </c>
-      <c r="U14" s="13">
+      <c r="V14" s="13">
         <v>7205</v>
       </c>
-      <c r="V14" s="13">
+      <c r="W14" s="13">
         <v>7298</v>
       </c>
-      <c r="W14" s="13">
+      <c r="X14" s="13">
         <v>7222</v>
       </c>
-      <c r="X14" s="13">
+      <c r="Y14" s="13">
         <v>7079</v>
       </c>
-      <c r="Y14" s="13">
+      <c r="Z14" s="13">
         <v>7140</v>
       </c>
-      <c r="Z14" s="13">
+      <c r="AA14" s="13">
         <v>7440</v>
       </c>
-      <c r="AA14" s="13">
+      <c r="AB14" s="13">
         <v>7530</v>
-      </c>
-      <c r="AB14" s="13">
-        <v>7535</v>
       </c>
       <c r="AC14" s="13">
         <v>7535</v>
       </c>
       <c r="AD14" s="13">
+        <v>7535</v>
+      </c>
+      <c r="AE14" s="13">
         <v>7568</v>
       </c>
-      <c r="AE14" s="13">
+      <c r="AF14" s="13">
         <v>7699</v>
       </c>
-      <c r="AF14" s="13">
+      <c r="AG14" s="13">
         <v>7638</v>
       </c>
-      <c r="AG14" s="13">
+      <c r="AH14" s="13">
         <v>7654</v>
       </c>
-      <c r="AH14" s="13">
+      <c r="AI14" s="13">
         <v>7584</v>
       </c>
-      <c r="AI14" s="13">
+      <c r="AJ14" s="13">
         <v>7479</v>
       </c>
-      <c r="AJ14" s="13">
+      <c r="AK14" s="13">
         <v>7490</v>
       </c>
-      <c r="AK14" s="13">
+      <c r="AL14" s="13">
         <v>7480</v>
       </c>
-      <c r="AL14" s="13">
+      <c r="AM14" s="13">
         <v>7270</v>
       </c>
-      <c r="AM14" s="13">
+      <c r="AN14" s="13">
         <v>7163</v>
       </c>
-      <c r="AN14" s="13">
+      <c r="AO14" s="13">
         <v>7231</v>
-      </c>
-      <c r="AO14" s="13">
-        <v>7100</v>
       </c>
       <c r="AP14" s="13">
         <v>7100</v>
       </c>
       <c r="AQ14" s="13">
+        <v>7100</v>
+      </c>
+      <c r="AR14" s="13">
         <v>7027</v>
       </c>
-      <c r="AR14" s="13">
+      <c r="AS14" s="13">
         <v>6984</v>
       </c>
-      <c r="AS14" s="13">
+      <c r="AT14" s="13">
         <v>6944</v>
       </c>
-      <c r="AT14" s="13">
+      <c r="AU14" s="13">
         <v>6924</v>
       </c>
-      <c r="AU14" s="13">
+      <c r="AV14" s="13">
         <v>6930</v>
       </c>
-      <c r="AV14" s="13">
+      <c r="AW14" s="13">
         <v>6938</v>
       </c>
-      <c r="AW14" s="13">
+      <c r="AX14" s="13">
         <v>6989</v>
       </c>
-      <c r="AX14" s="13">
+      <c r="AY14" s="13">
         <v>6871</v>
       </c>
-      <c r="AY14" s="13">
+      <c r="AZ14" s="13">
         <v>6943</v>
       </c>
-      <c r="AZ14" s="13">
+      <c r="BA14" s="13">
         <v>7040</v>
       </c>
-      <c r="BA14" s="29">
+      <c r="BB14" s="29">
         <v>6696</v>
       </c>
-      <c r="BB14" s="13">
+      <c r="BC14" s="13">
         <v>6965</v>
       </c>
-      <c r="BC14" s="13">
+      <c r="BD14" s="13">
         <v>6788</v>
       </c>
-      <c r="BD14" s="29">
+      <c r="BE14" s="29">
         <v>6696</v>
       </c>
-      <c r="BE14" s="13">
+      <c r="BF14" s="13">
         <v>6625</v>
       </c>
-      <c r="BF14" s="13">
+      <c r="BG14" s="13">
         <v>6660</v>
       </c>
-      <c r="BG14" s="13">
+      <c r="BH14" s="13">
         <v>6791</v>
       </c>
-      <c r="BH14" s="13">
+      <c r="BI14" s="13">
         <v>6610</v>
       </c>
-      <c r="BI14" s="13">
+      <c r="BJ14" s="13">
         <f t="shared" si="0"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BJ14" s="13">
+      <c r="BK14" s="13">
         <f t="shared" si="2"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BK14" s="13">
-        <f t="shared" ref="BK14" si="5">(BJ14-BI14)</f>
+      <c r="BL14" s="13">
+        <f t="shared" ref="BL14" si="5">(BK14-BJ14)</f>
         <v>0</v>
       </c>
-      <c r="BL14" s="13">
-        <f>((AZ14-H14)/H14)*100</f>
+      <c r="BM14" s="13">
+        <f>((BA14-H14)/H14)*100</f>
         <v>-2.2794972946411995</v>
       </c>
-      <c r="BO14" s="15">
+      <c r="BP14" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A15" s="1">
         <v>5137534</v>
       </c>
@@ -3132,7 +3188,7 @@
       </c>
       <c r="D15" s="6" t="str">
         <f>IF(I15&lt;GEMINI!L15,"למכור בהפסד",IF(I15&gt;GEMINI!M15,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>78</v>
@@ -3147,51 +3203,53 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
-        <v>13765.62</v>
+        <v>14385.75</v>
       </c>
       <c r="J15" s="13">
+        <v>14385.75</v>
+      </c>
+      <c r="K15" s="13">
         <v>13880</v>
       </c>
-      <c r="K15" s="13">
+      <c r="L15" s="13">
         <v>13610.62</v>
       </c>
-      <c r="L15" s="13">
+      <c r="M15" s="13">
         <v>13016</v>
       </c>
-      <c r="M15" s="13">
+      <c r="N15" s="13">
         <v>12487.37</v>
       </c>
-      <c r="N15" s="13">
+      <c r="O15" s="13">
         <v>12638.62</v>
       </c>
-      <c r="O15" s="13">
+      <c r="P15" s="13">
         <v>12533.87</v>
       </c>
-      <c r="P15" s="13">
+      <c r="Q15" s="13">
         <v>11299.5</v>
       </c>
-      <c r="Q15" s="13">
+      <c r="R15" s="13">
         <v>11193.12</v>
       </c>
-      <c r="R15" s="13">
+      <c r="S15" s="13">
         <v>11548.62</v>
       </c>
-      <c r="S15" s="13">
+      <c r="T15" s="13">
         <v>11125.62</v>
       </c>
-      <c r="T15" s="13">
+      <c r="U15" s="13">
         <v>10932.12</v>
       </c>
-      <c r="U15" s="13">
+      <c r="V15" s="13">
         <v>11095.62</v>
       </c>
-      <c r="V15" s="13">
+      <c r="W15" s="13">
         <v>10910.58</v>
       </c>
-      <c r="W15" s="13">
+      <c r="X15" s="13">
         <v>11609.37</v>
       </c>
-      <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
       <c r="Z15" s="13"/>
       <c r="AA15" s="13"/>
@@ -3201,8 +3259,8 @@
       <c r="AE15" s="13"/>
       <c r="AF15" s="13"/>
       <c r="AG15" s="13"/>
-      <c r="AH15" s="14"/>
-      <c r="AI15" s="13"/>
+      <c r="AH15" s="13"/>
+      <c r="AI15" s="14"/>
       <c r="AJ15" s="13"/>
       <c r="AK15" s="13"/>
       <c r="AL15" s="13"/>
@@ -3220,36 +3278,37 @@
       <c r="AX15" s="13"/>
       <c r="AY15" s="13"/>
       <c r="AZ15" s="13"/>
-      <c r="BA15" s="29"/>
-      <c r="BB15" s="13"/>
+      <c r="BA15" s="13"/>
+      <c r="BB15" s="29"/>
       <c r="BC15" s="13"/>
-      <c r="BD15" s="29"/>
-      <c r="BE15" s="13"/>
+      <c r="BD15" s="13"/>
+      <c r="BE15" s="29"/>
       <c r="BF15" s="13"/>
       <c r="BG15" s="13"/>
       <c r="BH15" s="13"/>
-      <c r="BI15" s="13">
+      <c r="BI15" s="13"/>
+      <c r="BJ15" s="13">
         <f t="shared" si="0"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BJ15" s="13">
+      <c r="BK15" s="13">
         <f t="shared" si="2"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BK15" s="13">
-        <f t="shared" ref="BK15:BK18" si="6">(BJ15-BI15)</f>
+      <c r="BL15" s="13">
+        <f t="shared" ref="BL15:BL18" si="6">(BK15-BJ15)</f>
         <v>0</v>
       </c>
-      <c r="BL15" s="13">
-        <f>((AZ15-H15)/H15)*100</f>
+      <c r="BM15" s="13">
+        <f>((BA15-H15)/H15)*100</f>
         <v>-100</v>
       </c>
-      <c r="BO15" s="15">
-        <f t="shared" ref="BO15:BO18" si="7">(BM15*BN15-BM15*H15)/100</f>
+      <c r="BP15" s="15">
+        <f t="shared" ref="BP15:BP18" si="7">(BN15*BO15-BN15*H15)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A16" s="1">
         <v>5135470</v>
       </c>
@@ -3278,189 +3337,192 @@
         <v>183.73</v>
       </c>
       <c r="I16" s="13">
-        <v>216.78</v>
+        <v>219.14</v>
       </c>
       <c r="J16" s="13">
+        <v>219.14</v>
+      </c>
+      <c r="K16" s="13">
         <v>219.3</v>
       </c>
-      <c r="K16" s="13">
+      <c r="L16" s="13">
         <v>222.79</v>
       </c>
-      <c r="L16" s="13">
+      <c r="M16" s="13">
         <v>221.16</v>
       </c>
-      <c r="M16" s="13">
+      <c r="N16" s="13">
         <v>220.66</v>
       </c>
-      <c r="N16" s="13">
+      <c r="O16" s="13">
         <v>222.06</v>
       </c>
-      <c r="O16" s="13">
+      <c r="P16" s="13">
         <v>218.71</v>
       </c>
-      <c r="P16" s="13">
+      <c r="Q16" s="13">
         <v>216.74</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="R16" s="13">
         <v>216.04</v>
-      </c>
-      <c r="R16" s="13">
-        <v>210.69</v>
       </c>
       <c r="S16" s="13">
         <v>210.69</v>
       </c>
       <c r="T16" s="13">
+        <v>210.69</v>
+      </c>
+      <c r="U16" s="13">
         <v>198</v>
       </c>
-      <c r="U16" s="13">
+      <c r="V16" s="13">
         <v>196.74</v>
       </c>
-      <c r="V16" s="13">
+      <c r="W16" s="13">
         <v>192.56</v>
       </c>
-      <c r="W16" s="13">
+      <c r="X16" s="13">
         <v>192.23</v>
       </c>
-      <c r="X16" s="13">
+      <c r="Y16" s="13">
         <v>191.19</v>
       </c>
-      <c r="Y16" s="13">
+      <c r="Z16" s="13">
         <v>193.62</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="AA16" s="13">
         <v>190.75</v>
       </c>
-      <c r="AA16" s="13">
+      <c r="AB16" s="13">
         <v>189.06</v>
-      </c>
-      <c r="AB16" s="13">
-        <v>182.73</v>
       </c>
       <c r="AC16" s="13">
         <v>182.73</v>
       </c>
       <c r="AD16" s="13">
+        <v>182.73</v>
+      </c>
+      <c r="AE16" s="13">
         <v>177.92</v>
       </c>
-      <c r="AE16" s="13">
+      <c r="AF16" s="13">
         <v>179.16</v>
       </c>
-      <c r="AF16" s="13">
+      <c r="AG16" s="13">
         <v>179.34</v>
-      </c>
-      <c r="AG16" s="13">
-        <v>176.5</v>
       </c>
       <c r="AH16" s="13">
         <v>176.5</v>
       </c>
       <c r="AI16" s="13">
+        <v>176.5</v>
+      </c>
+      <c r="AJ16" s="13">
         <v>175.93</v>
       </c>
-      <c r="AJ16" s="13">
+      <c r="AK16" s="13">
         <v>174.51</v>
       </c>
-      <c r="AK16" s="13">
+      <c r="AL16" s="13">
         <v>173.91</v>
       </c>
-      <c r="AL16" s="13">
+      <c r="AM16" s="13">
         <v>177.1</v>
       </c>
-      <c r="AM16" s="13">
+      <c r="AN16" s="13">
         <v>178.24</v>
       </c>
-      <c r="AN16" s="13">
+      <c r="AO16" s="13">
         <v>176.52</v>
       </c>
-      <c r="AO16" s="13">
+      <c r="AP16" s="13">
         <v>178.27</v>
       </c>
-      <c r="AP16" s="13">
+      <c r="AQ16" s="13">
         <v>175.29</v>
       </c>
-      <c r="AQ16" s="13">
+      <c r="AR16" s="13">
         <v>175.34</v>
       </c>
-      <c r="AR16" s="13">
+      <c r="AS16" s="13">
         <v>174.41</v>
       </c>
-      <c r="AS16" s="13">
+      <c r="AT16" s="13">
         <v>176.22</v>
       </c>
-      <c r="AT16" s="13">
+      <c r="AU16" s="13">
         <v>174</v>
       </c>
-      <c r="AU16" s="13">
+      <c r="AV16" s="13">
         <v>176.35</v>
       </c>
-      <c r="AV16" s="13">
+      <c r="AW16" s="13">
         <v>177.71</v>
       </c>
-      <c r="AW16" s="13">
+      <c r="AX16" s="13">
         <v>180.08</v>
       </c>
-      <c r="AX16" s="13">
+      <c r="AY16" s="13">
         <v>181.96</v>
       </c>
-      <c r="AY16" s="13">
+      <c r="AZ16" s="13">
         <v>182.9</v>
       </c>
-      <c r="AZ16" s="13">
+      <c r="BA16" s="13">
         <v>181.86</v>
       </c>
-      <c r="BA16" s="29">
+      <c r="BB16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BB16" s="13">
+      <c r="BC16" s="13">
         <v>181.07</v>
       </c>
-      <c r="BC16" s="13">
+      <c r="BD16" s="13">
         <v>182.56</v>
       </c>
-      <c r="BD16" s="29">
+      <c r="BE16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BE16" s="13">
+      <c r="BF16" s="13">
         <v>178.86</v>
       </c>
-      <c r="BF16" s="13">
+      <c r="BG16" s="13">
         <v>180.16</v>
       </c>
-      <c r="BG16" s="13">
+      <c r="BH16" s="13">
         <v>179.56</v>
       </c>
-      <c r="BH16" s="13">
+      <c r="BI16" s="13">
         <v>176.55</v>
       </c>
-      <c r="BI16" s="13">
+      <c r="BJ16" s="13">
         <f t="shared" si="0"/>
         <v>673.09559999999999</v>
       </c>
-      <c r="BJ16" s="13">
+      <c r="BK16" s="13">
         <f t="shared" si="2"/>
         <v>551.19000000000005</v>
       </c>
-      <c r="BK16" s="13">
+      <c r="BL16" s="13">
         <f t="shared" si="6"/>
         <v>-121.90559999999994</v>
       </c>
-      <c r="BL16" s="13">
-        <f>((AZ16-H16)/H16)*100</f>
+      <c r="BM16" s="13">
+        <f>((BA16-H16)/H16)*100</f>
         <v>-1.0177978555488905</v>
       </c>
-      <c r="BM16">
+      <c r="BN16">
         <v>1864</v>
       </c>
-      <c r="BN16">
+      <c r="BO16">
         <v>177.19</v>
       </c>
-      <c r="BO16" s="15">
+      <c r="BP16" s="15">
         <f t="shared" si="7"/>
         <v>-121.90559999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A17" s="1">
         <v>5134135</v>
       </c>
@@ -3489,10 +3551,10 @@
         <v>159.65</v>
       </c>
       <c r="I17" s="13">
-        <v>182.59</v>
+        <v>185.52</v>
       </c>
       <c r="J17" s="13">
-        <v>178.98</v>
+        <v>185.52</v>
       </c>
       <c r="K17" s="13">
         <v>178.98</v>
@@ -3501,7 +3563,7 @@
         <v>178.98</v>
       </c>
       <c r="M17" s="13">
-        <v>170.7</v>
+        <v>178.98</v>
       </c>
       <c r="N17" s="13">
         <v>170.7</v>
@@ -3510,10 +3572,10 @@
         <v>170.7</v>
       </c>
       <c r="P17" s="13">
+        <v>170.7</v>
+      </c>
+      <c r="Q17" s="13">
         <v>170.45</v>
-      </c>
-      <c r="Q17" s="13">
-        <v>160.84</v>
       </c>
       <c r="R17" s="13">
         <v>160.84</v>
@@ -3522,15 +3584,17 @@
         <v>160.84</v>
       </c>
       <c r="T17" s="13">
+        <v>160.84</v>
+      </c>
+      <c r="U17" s="13">
         <v>159.02000000000001</v>
-      </c>
-      <c r="U17" s="13">
-        <v>159.65</v>
       </c>
       <c r="V17" s="13">
         <v>159.65</v>
       </c>
-      <c r="W17" s="13"/>
+      <c r="W17" s="13">
+        <v>159.65</v>
+      </c>
       <c r="X17" s="13"/>
       <c r="Y17" s="13"/>
       <c r="Z17" s="13"/>
@@ -3560,36 +3624,37 @@
       <c r="AX17" s="13"/>
       <c r="AY17" s="13"/>
       <c r="AZ17" s="13"/>
-      <c r="BA17" s="29"/>
-      <c r="BB17" s="13"/>
+      <c r="BA17" s="13"/>
+      <c r="BB17" s="29"/>
       <c r="BC17" s="13"/>
-      <c r="BD17" s="29"/>
-      <c r="BE17" s="13"/>
+      <c r="BD17" s="13"/>
+      <c r="BE17" s="29"/>
       <c r="BF17" s="13"/>
       <c r="BG17" s="13"/>
       <c r="BH17" s="13"/>
-      <c r="BI17" s="13">
+      <c r="BI17" s="13"/>
+      <c r="BJ17" s="13">
         <f t="shared" si="0"/>
         <v>957.9</v>
       </c>
-      <c r="BJ17" s="13">
+      <c r="BK17" s="13">
         <f t="shared" si="2"/>
         <v>957.9</v>
       </c>
-      <c r="BK17" s="13">
-        <f t="shared" ref="BK17" si="8">(BJ17-BI17)</f>
+      <c r="BL17" s="13">
+        <f t="shared" ref="BL17" si="8">(BK17-BJ17)</f>
         <v>0</v>
       </c>
-      <c r="BL17" s="13">
-        <f>((AZ17-H17)/H17)*100</f>
+      <c r="BM17" s="13">
+        <f>((BA17-H17)/H17)*100</f>
         <v>-100</v>
       </c>
-      <c r="BO17" s="15">
+      <c r="BP17" s="15">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A18" s="1">
         <v>1168723</v>
       </c>
@@ -3618,54 +3683,56 @@
         <v>1434</v>
       </c>
       <c r="I18" s="13">
-        <v>1740</v>
+        <v>1757</v>
       </c>
       <c r="J18" s="13">
+        <v>1757</v>
+      </c>
+      <c r="K18" s="13">
         <v>1698</v>
       </c>
-      <c r="K18" s="13">
+      <c r="L18" s="13">
         <v>1694</v>
       </c>
-      <c r="L18" s="13">
+      <c r="M18" s="13">
         <v>1671</v>
-      </c>
-      <c r="M18" s="13">
-        <v>1660</v>
       </c>
       <c r="N18" s="13">
         <v>1660</v>
       </c>
       <c r="O18" s="13">
+        <v>1660</v>
+      </c>
+      <c r="P18" s="13">
         <v>1646</v>
       </c>
-      <c r="P18" s="13">
+      <c r="Q18" s="13">
         <v>1648</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="R18" s="13">
         <v>1614</v>
       </c>
-      <c r="R18" s="13">
+      <c r="S18" s="13">
         <v>1626</v>
       </c>
-      <c r="S18" s="13">
+      <c r="T18" s="13">
         <v>1587</v>
       </c>
-      <c r="T18" s="13">
+      <c r="U18" s="13">
         <v>1548</v>
       </c>
-      <c r="U18" s="13">
+      <c r="V18" s="13">
         <v>1500</v>
       </c>
-      <c r="V18" s="13">
+      <c r="W18" s="13">
         <v>1491</v>
       </c>
-      <c r="W18" s="13">
+      <c r="X18" s="13">
         <v>1444</v>
       </c>
-      <c r="X18" s="13">
+      <c r="Y18" s="13">
         <v>1431</v>
       </c>
-      <c r="Y18" s="13"/>
       <c r="Z18" s="13"/>
       <c r="AA18" s="13"/>
       <c r="AB18" s="13"/>
@@ -3691,64 +3758,65 @@
       <c r="AV18" s="13"/>
       <c r="AW18" s="13"/>
       <c r="AX18" s="13"/>
-      <c r="AY18" s="13">
-        <v>1788</v>
-      </c>
+      <c r="AY18" s="13"/>
       <c r="AZ18" s="13">
         <v>1788</v>
       </c>
-      <c r="BA18" s="29">
+      <c r="BA18" s="13">
+        <v>1788</v>
+      </c>
+      <c r="BB18" s="29">
         <v>1780</v>
       </c>
-      <c r="BB18" s="13">
+      <c r="BC18" s="13">
         <v>1814</v>
       </c>
-      <c r="BC18" s="13">
+      <c r="BD18" s="13">
         <v>1794</v>
       </c>
-      <c r="BD18" s="29">
+      <c r="BE18" s="29">
         <v>1780</v>
       </c>
-      <c r="BE18" s="13">
+      <c r="BF18" s="13">
         <v>1772</v>
       </c>
-      <c r="BF18" s="13">
+      <c r="BG18" s="13">
         <v>1798</v>
       </c>
-      <c r="BG18" s="13">
+      <c r="BH18" s="13">
         <v>1806</v>
       </c>
-      <c r="BH18" s="13">
+      <c r="BI18" s="13">
         <v>1801</v>
       </c>
-      <c r="BI18" s="13">
+      <c r="BJ18" s="13">
         <f t="shared" si="0"/>
         <v>292.79999999999995</v>
       </c>
-      <c r="BJ18" s="13">
+      <c r="BK18" s="13">
         <f t="shared" si="2"/>
         <v>645.29999999999995</v>
       </c>
-      <c r="BK18" s="13">
+      <c r="BL18" s="13">
         <f t="shared" si="6"/>
         <v>352.5</v>
       </c>
-      <c r="BL18" s="13">
-        <f>((AZ18-H18)/H18)*100</f>
+      <c r="BM18" s="13">
+        <f>((BA18-H18)/H18)*100</f>
         <v>24.686192468619247</v>
       </c>
-      <c r="BM18">
+      <c r="BN18">
         <v>100</v>
       </c>
-      <c r="BN18">
+      <c r="BO18">
         <v>1786.5</v>
       </c>
-      <c r="BO18" s="15">
+      <c r="BP18" s="15">
         <f t="shared" si="7"/>
         <v>352.5</v>
       </c>
     </row>
-    <row r="19" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A19" s="1">
         <v>1146604</v>
       </c>
@@ -3787,22 +3855,22 @@
       <c r="Q19" s="13"/>
       <c r="R19" s="13"/>
       <c r="S19" s="13"/>
-      <c r="T19" s="13">
+      <c r="T19" s="13"/>
+      <c r="U19" s="13">
         <v>6461</v>
       </c>
-      <c r="U19" s="13">
+      <c r="V19" s="13">
         <v>6503</v>
       </c>
-      <c r="V19" s="13">
+      <c r="W19" s="13">
         <v>6535</v>
       </c>
-      <c r="W19" s="13">
+      <c r="X19" s="13">
         <v>6532</v>
       </c>
-      <c r="X19" s="13">
+      <c r="Y19" s="13">
         <v>6515</v>
       </c>
-      <c r="Y19" s="13"/>
       <c r="Z19" s="13"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="13"/>
@@ -3830,33 +3898,34 @@
       <c r="AX19" s="13"/>
       <c r="AY19" s="13"/>
       <c r="AZ19" s="13"/>
-      <c r="BA19" s="29"/>
-      <c r="BB19" s="13"/>
+      <c r="BA19" s="13"/>
+      <c r="BB19" s="29"/>
       <c r="BC19" s="13"/>
-      <c r="BD19" s="29"/>
-      <c r="BE19" s="13"/>
+      <c r="BD19" s="13"/>
+      <c r="BE19" s="29"/>
       <c r="BF19" s="13"/>
       <c r="BG19" s="13"/>
       <c r="BH19" s="13"/>
-      <c r="BI19" s="13">
+      <c r="BI19" s="13"/>
+      <c r="BJ19" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BJ19" s="13">
+      <c r="BK19" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="13"/>
       <c r="BL19" s="13"/>
-      <c r="BM19">
+      <c r="BM19" s="13"/>
+      <c r="BN19">
         <v>7</v>
       </c>
-      <c r="BN19">
+      <c r="BO19">
         <v>6461</v>
       </c>
-      <c r="BO19" s="15"/>
-    </row>
-    <row r="20" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BP19" s="15"/>
+    </row>
+    <row r="20" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A20" s="1">
         <v>1144807</v>
       </c>
@@ -3888,7 +3957,9 @@
       <c r="L20" s="13">
         <v>3159</v>
       </c>
-      <c r="M20" s="13"/>
+      <c r="M20" s="13">
+        <v>3159</v>
+      </c>
       <c r="N20" s="13"/>
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
@@ -3928,28 +3999,29 @@
       <c r="AX20" s="13"/>
       <c r="AY20" s="13"/>
       <c r="AZ20" s="13"/>
-      <c r="BA20" s="29"/>
-      <c r="BB20" s="13"/>
+      <c r="BA20" s="13"/>
+      <c r="BB20" s="29"/>
       <c r="BC20" s="13"/>
-      <c r="BD20" s="29"/>
-      <c r="BE20" s="13"/>
+      <c r="BD20" s="13"/>
+      <c r="BE20" s="29"/>
       <c r="BF20" s="13"/>
       <c r="BG20" s="13"/>
       <c r="BH20" s="13"/>
-      <c r="BI20" s="13">
-        <f>(G20*H20)/100-BO20</f>
+      <c r="BI20" s="13"/>
+      <c r="BJ20" s="13">
+        <f>(G20*H20)/100-BP20</f>
         <v>0</v>
       </c>
-      <c r="BJ20" s="13">
+      <c r="BK20" s="13">
         <f>(G20*H20)/100</f>
         <v>0</v>
       </c>
-      <c r="BK20" s="13"/>
       <c r="BL20" s="13"/>
-      <c r="BO20" s="15"/>
-    </row>
-    <row r="21" spans="1:67" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:67" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BM20" s="13"/>
+      <c r="BP20" s="15"/>
+    </row>
+    <row r="21" spans="1:68" ht="14.4" thickBot="1"/>
+    <row r="22" spans="1:68" ht="45" customHeight="1" thickBot="1">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4002,11 +4074,11 @@
       <c r="AX22" s="13"/>
       <c r="AY22" s="13"/>
       <c r="AZ22" s="13"/>
-      <c r="BA22" s="29"/>
-      <c r="BB22" s="13"/>
+      <c r="BA22" s="13"/>
+      <c r="BB22" s="29"/>
       <c r="BC22" s="13"/>
-      <c r="BD22" s="29"/>
-      <c r="BE22" s="13"/>
+      <c r="BD22" s="13"/>
+      <c r="BE22" s="29"/>
       <c r="BF22" s="13"/>
       <c r="BG22" s="13"/>
       <c r="BH22" s="13"/>
@@ -4014,9 +4086,10 @@
       <c r="BJ22" s="13"/>
       <c r="BK22" s="13"/>
       <c r="BL22" s="13"/>
-      <c r="BO22" s="15"/>
-    </row>
-    <row r="23" spans="1:67" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BM22" s="13"/>
+      <c r="BP22" s="15"/>
+    </row>
+    <row r="23" spans="1:68" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4027,51 +4100,51 @@
       <c r="H23" s="13"/>
       <c r="I23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19)/100</f>
-        <v>15932.809600000001</v>
+        <v>15699.153</v>
       </c>
       <c r="J23" s="23">
         <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19)/100</f>
-        <v>15830.18</v>
+        <v>15699.153</v>
       </c>
       <c r="K23" s="23">
         <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19)/100</f>
-        <v>15847.579599999999</v>
+        <v>15345.22</v>
       </c>
       <c r="L23" s="23">
-        <f>(L3*G3+G4*L4+L5*G5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+G14*L14+L15*G15+G16*L16+L17*G17+G18*L18+G19*L19)/100</f>
-        <v>14182.84</v>
+        <f>(L2*G2+G3*L3+L4*G4+G5*L5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+L13*G13+G14*L14+L15*G15+G16*L16+G17*L17+L18*G18+G19*L19)/100</f>
+        <v>15346.1396</v>
       </c>
       <c r="M23" s="23">
         <f>(M3*G3+G4*M4+M5*G5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+G14*M14+M15*G15+G16*M16+M17*G17+G18*M18+G19*M19)/100</f>
-        <v>13920.8496</v>
+        <v>13565.34</v>
       </c>
       <c r="N23" s="23">
         <f>(N3*G3+G4*N4+N5*G5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+G14*N14+N15*G15+G16*N16+N17*G17+G18*N18+G19*N19)/100</f>
-        <v>13937.149599999999</v>
+        <v>13333.0196</v>
       </c>
       <c r="O23" s="23">
         <f>(O3*G3+G4*O4+O5*G5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+G14*O14+O15*G15+G16*O16+O17*G17+G18*O18+G19*O19)/100</f>
-        <v>13948.6896</v>
+        <v>13349.319599999999</v>
       </c>
       <c r="P23" s="23">
         <f>(P3*G3+G4*P4+P5*G5+G6*P6+G7*P7+G8*P8+G9*P9+G10*P10+G11*P11+G12*P12+G14*P14+P15*G15+G16*P16+P17*G17+G18*P18+G19*P19)/100</f>
-        <v>13407.56</v>
+        <v>13358.1996</v>
       </c>
       <c r="Q23" s="23">
         <f>(Q3*G3+G4*Q4+Q5*G5+G6*Q6+G7*Q7+G8*Q8+G9*Q9+G10*Q10+G11*Q11+G12*Q12+G14*Q14+Q15*G15+G16*Q16+Q17*G17+G18*Q18+G19*Q19)/100</f>
-        <v>13214.874599999999</v>
+        <v>12779.14</v>
       </c>
       <c r="R23" s="23">
         <f>(R3*G3+G4*R4+R5*G5+G6*R6+G7*R7+G8*R8+G9*R9+G10*R10+G11*R11+G12*R12+G14*R14+R15*G15+G16*R16+R17*G17+G18*R18+G19*R19)/100</f>
-        <v>11573.809600000001</v>
+        <v>12576.257600000001</v>
       </c>
       <c r="S23" s="23">
-        <f>(S5*G5+G6*S6+S7*G7+G8*S8+G9*S9+G10*S10+G11*S11+G12*S12+G14*S14+G20*S20+G15*S15+S16*G16+G17*S17+S18*G18+G19*S19)/100</f>
-        <v>10674.919599999999</v>
-      </c>
-      <c r="T23" s="23" t="e">
-        <f>(T5*G5+G7*T7+T8*G8+G9*T9+#REF!*#REF!+G10*T10+G11*T11+G12*T12+G14*T14+G19*T19+G20*T20+T6*G6+G15*T15+#REF!*#REF!+G16*T16+G17*T17+T18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*T3+#REF!*#REF!)/100</f>
-        <v>#REF!</v>
+        <f>(S3*G3+G4*S4+S5*G5+G6*S6+G7*S7+G8*S8+G9*S9+G10*S10+G11*S11+G12*S12+G14*S14+S15*G15+G16*S16+S17*G17+G18*S18+G19*S19)/100</f>
+        <v>10814.2096</v>
+      </c>
+      <c r="T23" s="23">
+        <f>(T5*G5+G6*T6+T7*G7+G8*T8+G9*T9+G10*T10+G11*T11+G12*T12+G14*T14+G20*T20+G15*T15+T16*G16+G17*T17+T18*G18+G19*T19)/100</f>
+        <v>9932.3195999999989</v>
       </c>
       <c r="U23" s="23" t="e">
         <f>(U5*G5+G7*U7+U8*G8+G9*U9+#REF!*#REF!+G10*U10+G11*U11+G12*U12+G14*U14+G19*U19+G20*U20+U6*G6+G15*U15+#REF!*#REF!+G16*U16+G17*U17+U18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*U3+#REF!*#REF!)/100</f>
@@ -4082,11 +4155,11 @@
         <v>#REF!</v>
       </c>
       <c r="W23" s="23" t="e">
-        <f>(W5*G5+G7*W7+W8*G8+G9*W9+#REF!*#REF!+G10*W10+G11*W11+G12*W12+G14*W14+G19*W19+G20*W20+W6*G6+G15*W15+#REF!*#REF!+G16*W16+G18*W18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*W3+#REF!*#REF!+G4*W4)/100</f>
+        <f>(W5*G5+G7*W7+W8*G8+G9*W9+#REF!*#REF!+G10*W10+G11*W11+G12*W12+G14*W14+G19*W19+G20*W20+W6*G6+G15*W15+#REF!*#REF!+G16*W16+G17*W17+W18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*W3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="X23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+X3*G3+#REF!*#REF!+G4*X4+G5*X5+G7*X7+G8*X8+G9*X9+#REF!*#REF!+G10*X10+X11*G11+G12*X12+X14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*X20+X6*G6+#REF!*#REF!+G16*X16+G18*X18+G19*X19)/100</f>
+        <f>(X5*G5+G7*X7+X8*G8+G9*X9+#REF!*#REF!+G10*X10+G11*X11+G12*X12+G14*X14+G19*X19+G20*X20+X6*G6+G15*X15+#REF!*#REF!+G16*X16+G18*X18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*X3+#REF!*#REF!+G4*X4)/100</f>
         <v>#REF!</v>
       </c>
       <c r="Y23" s="23" t="e">
@@ -4094,7 +4167,7 @@
         <v>#REF!</v>
       </c>
       <c r="Z23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+Z3*G3+#REF!*#REF!+G4*Z4+G5*Z5+Z7*G7+Z8*G8+Z9*G9+#REF!*#REF!+G10*Z10+Z11*G11+G12*Z12+Z14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*Z20+G6*Z6+#REF!*#REF!+G16*Z16+G18*Z18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+Z3*G3+#REF!*#REF!+G4*Z4+G5*Z5+G7*Z7+G8*Z8+G9*Z9+#REF!*#REF!+G10*Z10+Z11*G11+G12*Z12+Z14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*Z20+Z6*G6+#REF!*#REF!+G16*Z16+G18*Z18+G19*Z19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AA23" s="23" t="e">
@@ -4102,19 +4175,19 @@
         <v>#REF!</v>
       </c>
       <c r="AB23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AB3*G3+#REF!*#REF!+G4*AB4+G8*AB8+AB9*G9+#REF!*#REF!+AB10*G10+G11*AB11+G14*AB14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AB6+#REF!*#REF!+G16*AB16+G18*AB18+G7*AB7+G5*AB5+G12*AB12+G20*AB20)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AB3*G3+#REF!*#REF!+G4*AB4+G5*AB5+AB7*G7+AB8*G8+AB9*G9+#REF!*#REF!+G10*AB10+AB11*G11+G12*AB12+AB14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AB20+G6*AB6+#REF!*#REF!+G16*AB16+G18*AB18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AC23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AC3*G3+#REF!*#REF!+G4*AC4+G8*AC8+AC9*G9+#REF!*#REF!+AC10*G10+G11*AC11+G14*AC14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AC6+#REF!*#REF!+G16*AC16+G18*AC18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AC3*G3+#REF!*#REF!+G4*AC4+G8*AC8+AC9*G9+#REF!*#REF!+AC10*G10+G11*AC11+G14*AC14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AC6+#REF!*#REF!+G16*AC16+G18*AC18+G7*AC7+G5*AC5+G12*AC12+G20*AC20)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AD23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AD3*G3+#REF!*#REF!+G4*AD4+G8*AD8+G9*AD9+#REF!*#REF!+G10*AD10+AD11*G11+AD14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AD6*G6+#REF!*#REF!+G16*AD16+G18*AD18+G19*AD19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AD3*G3+#REF!*#REF!+G4*AD4+G8*AD8+AD9*G9+#REF!*#REF!+AD10*G10+G11*AD11+G14*AD14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AD6+#REF!*#REF!+G16*AD16+G18*AD18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AE23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AE3*G3+#REF!*#REF!+G4*AE4+G8*AE8+AE9*G9+#REF!*#REF!+AE10*G10+G11*AE11+G14*AE14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AE6+#REF!*#REF!+G16*AE16+G18*AE18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AE3*G3+#REF!*#REF!+G4*AE4+G8*AE8+G9*AE9+#REF!*#REF!+G10*AE10+AE11*G11+AE14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AE6*G6+#REF!*#REF!+G16*AE16+G18*AE18+G19*AE19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AF23" s="23" t="e">
@@ -4122,7 +4195,7 @@
         <v>#REF!</v>
       </c>
       <c r="AG23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AG3*G3+#REF!*#REF!+G4*AG4+G8*AG8+AG9*G9+AG10*G10+AG11*G11+G14*AG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AG6+#REF!*#REF!+G16*AG16+G18*AG18+G19*AG19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AG3*G3+#REF!*#REF!+G4*AG4+G8*AG8+AG9*G9+#REF!*#REF!+AG10*G10+G11*AG11+G14*AG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AG6+#REF!*#REF!+G16*AG16+G18*AG18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AH23" s="23" t="e">
@@ -4142,19 +4215,19 @@
         <v>#REF!</v>
       </c>
       <c r="AL23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AL3*G3+#REF!*#REF!+G4*AL4+G8*AL8+AL9*G9+AL10*G10+AL11*G11+G14*AL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AL6+#REF!*#REF!+G16*AL16+G18*AL18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AL3*G3+#REF!*#REF!+G4*AL4+G8*AL8+AL9*G9+AL10*G10+AL11*G11+G14*AL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AL6+#REF!*#REF!+G16*AL16+G18*AL18+G19*AL19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AM23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AM3*G3+#REF!*#REF!+G4*AM4+G8*AM8+AM10*G10+AM11*G11+G14*AM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AM6+#REF!*#REF!+G16*AM16+G18*AM18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AM3*G3+#REF!*#REF!+G4*AM4+G8*AM8+AM9*G9+AM10*G10+AM11*G11+G14*AM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AM6+#REF!*#REF!+G16*AM16+G18*AM18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AN23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+G10*AN10+AN11*G11+AN14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AN6*G6+#REF!*#REF!+G16*AN16+G18*AN18+G19*AN19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+AN10*G10+AN11*G11+G14*AN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AN6+#REF!*#REF!+G16*AN16+G18*AN18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AO23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G10*AO10+AO11*G11+AO14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AO6*G6+#REF!*#REF!+G16*AO16+G18*AO18+G19*AO19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+G10*AO10+AO11*G11+AO14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AO6*G6+#REF!*#REF!+G16*AO16+G18*AO18+G19*AO19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AP23" s="23" t="e">
@@ -4166,7 +4239,7 @@
         <v>#REF!</v>
       </c>
       <c r="AR23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AR3*G3+#REF!*#REF!+G4*AR4+G10*AR10+AR11*G11+AR14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AR6*G6+G16*AR16+G18*AR18+G19*AR19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AR3*G3+#REF!*#REF!+G4*AR4+G10*AR10+AR11*G11+AR14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AR6*G6+#REF!*#REF!+G16*AR16+G18*AR18+G19*AR19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AS23" s="23" t="e">
@@ -4194,15 +4267,15 @@
         <v>#REF!</v>
       </c>
       <c r="AY23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AY3*G3+#REF!*#REF!+G4*AY4+G10*AY10+G11*AY11+G14*AY14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AY6+AY16*G16+G18*AY18+G19*AY19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AY3*G3+#REF!*#REF!+G4*AY4+G10*AY10+AY11*G11+AY14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AY6*G6+G16*AY16+G18*AY18+G19*AY19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AZ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AZ3*G3+#REF!*#REF!+G4*AZ4+G10*AZ10+G14*AZ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AZ6+AZ16*G16+G18*AZ18+G19*AZ19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AZ3*G3+#REF!*#REF!+G4*AZ4+G10*AZ10+G11*AZ11+G14*AZ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AZ6+AZ16*G16+G18*AZ18+G19*AZ19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BA23" s="23" t="e">
-        <f>(#REF!*#REF!+BA3*G3+G4*BA4+G14*BA14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BA6+BA16*G16+G18*BA18+G19*BA19+G22*BA22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BA3*G3+#REF!*#REF!+G4*BA4+G10*BA10+G14*BA14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BA6+BA16*G16+G18*BA18+G19*BA19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BB23" s="23" t="e">
@@ -4213,16 +4286,16 @@
         <f>(#REF!*#REF!+BC3*G3+G4*BC4+G14*BC14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BC6+BC16*G16+G18*BC18+G19*BC19+G22*BC22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BD23" s="30" t="e">
+      <c r="BD23" s="23" t="e">
         <f>(#REF!*#REF!+BD3*G3+G4*BD4+G14*BD14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BD6+BD16*G16+G18*BD18+G19*BD19+G22*BD22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BE23" s="23" t="e">
+      <c r="BE23" s="30" t="e">
         <f>(#REF!*#REF!+BE3*G3+G4*BE4+G14*BE14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BE6+BE16*G16+G18*BE18+G19*BE19+G22*BE22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BF23" s="23" t="e">
-        <f>(#REF!*#REF!+BF3*G3+G14*BF14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BF6+BF16*G16+G18*BF18+G19*BF19+G22*BF22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+BF3*G3+G4*BF4+G14*BF14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BF6+BF16*G16+G18*BF18+G19*BF19+G22*BF22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BG23" s="23" t="e">
@@ -4233,15 +4306,19 @@
         <f>(#REF!*#REF!+BH3*G3+G14*BH14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BH6+BH16*G16+G18*BH18+G19*BH19+G22*BH22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BI23" s="13"/>
+      <c r="BI23" s="23" t="e">
+        <f>(#REF!*#REF!+BI3*G3+G14*BI14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BI6+BI16*G16+G18*BI18+G19*BI19+G22*BI22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <v>#REF!</v>
+      </c>
       <c r="BJ23" s="13"/>
       <c r="BK23" s="13"/>
       <c r="BL23" s="13"/>
-      <c r="BO23" s="15">
+      <c r="BM23" s="13"/>
+      <c r="BP23" s="15">
         <v>434.9</v>
       </c>
     </row>
-    <row r="24" spans="1:67" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:68" ht="44.25" customHeight="1" thickBot="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4302,29 +4379,30 @@
       <c r="BF24" s="14"/>
       <c r="BG24" s="14"/>
       <c r="BH24" s="14"/>
-      <c r="BI24" s="23">
-        <f>SUM(BI3:BI20)</f>
-        <v>13018.293100000001</v>
-      </c>
+      <c r="BI24" s="14"/>
       <c r="BJ24" s="23">
         <f>SUM(BJ3:BJ20)</f>
-        <v>13575.721300000001</v>
-      </c>
-      <c r="BK24" s="24">
-        <f>BJ24-BI24</f>
+        <v>12545.255000000001</v>
+      </c>
+      <c r="BK24" s="23">
+        <f>SUM(BK3:BK20)</f>
+        <v>13102.683200000001</v>
+      </c>
+      <c r="BL24" s="24">
+        <f>BK24-BJ24</f>
         <v>557.42820000000029</v>
       </c>
-      <c r="BL24" s="13">
-        <f>((BJ24-BI24)/BI24)*100</f>
-        <v>4.2818839283930412</v>
-      </c>
-      <c r="BO24" s="15">
-        <f>SUM(BO5:BO23)</f>
+      <c r="BM24" s="13">
+        <f>((BK24-BJ24)/BJ24)*100</f>
+        <v>4.443338935717132</v>
+      </c>
+      <c r="BP24" s="15">
+        <f>SUM(BP5:BP23)</f>
         <v>992.32819999999981</v>
       </c>
     </row>
-    <row r="25" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="BI25" s="15">
+    <row r="25" spans="1:68">
+      <c r="BJ25" s="15">
         <v>12034.32</v>
       </c>
     </row>
@@ -4382,17 +4460,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DECD697-7590-4F64-9E15-0FA62A69A078}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="7" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="1" width="17.59765625" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="7" width="17.59765625" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="10" max="10" width="9.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>11</v>
       </c>
@@ -4425,7 +4503,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -4453,7 +4531,7 @@
       <c r="L2" s="32"/>
       <c r="M2" s="32"/>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -4468,7 +4546,7 @@
       </c>
       <c r="D3" s="19">
         <f>'התיק העדכני'!G3</f>
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E3" s="16">
         <v>950</v>
@@ -4479,7 +4557,7 @@
       <c r="G3" s="17"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1316</v>
+        <v>1331</v>
       </c>
       <c r="J3" s="26"/>
       <c r="L3" s="21">
@@ -4491,7 +4569,7 @@
         <v>1273.75</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -4517,7 +4595,7 @@
       <c r="G4" s="17"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6060</v>
+        <v>6111</v>
       </c>
       <c r="J4" s="26"/>
       <c r="L4" s="21">
@@ -4529,7 +4607,7 @@
         <v>6701.5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -4554,7 +4632,7 @@
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>595.4</v>
+        <v>626</v>
       </c>
       <c r="J5" s="26"/>
       <c r="L5" s="21">
@@ -4566,7 +4644,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -4591,7 +4669,7 @@
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>3931</v>
+        <v>3970</v>
       </c>
       <c r="J6" s="26"/>
       <c r="L6" s="21">
@@ -4603,7 +4681,7 @@
         <v>4231.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -4618,7 +4696,7 @@
       </c>
       <c r="D7" s="19">
         <f>'התיק העדכני'!G7</f>
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E7" s="16">
         <v>3700</v>
@@ -4629,7 +4707,7 @@
       <c r="G7" s="18"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3885</v>
+        <v>3913</v>
       </c>
       <c r="J7" s="26"/>
       <c r="L7" s="21">
@@ -4641,7 +4719,7 @@
         <v>4253</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -4667,7 +4745,7 @@
       <c r="G8" s="18"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>42250</v>
+        <v>41570</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -4678,7 +4756,7 @@
         <v>42975</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -4704,7 +4782,7 @@
       <c r="G9" s="17"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9917</v>
+        <v>9924</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -4715,7 +4793,7 @@
         <v>11459.25</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -4741,7 +4819,7 @@
       <c r="G10" s="18"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4930</v>
+        <v>5050</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -4752,7 +4830,7 @@
         <v>6041.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -4778,7 +4856,7 @@
       <c r="G11" s="18"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1003</v>
+        <v>1029</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -4789,7 +4867,7 @@
         <v>1085.5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -4815,7 +4893,7 @@
       <c r="G12" s="18"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>26620</v>
+        <v>26800</v>
       </c>
       <c r="J12" s="26"/>
       <c r="L12" s="21">
@@ -4827,7 +4905,7 @@
         <v>27485</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -4842,20 +4920,20 @@
       </c>
       <c r="D13" s="19">
         <f>'התיק העדכני'!G13</f>
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>830.1</v>
+        <v>932.1</v>
       </c>
       <c r="J13" s="26"/>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -4881,7 +4959,7 @@
       <c r="G14" s="17"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7722</v>
+        <v>7735</v>
       </c>
       <c r="J14" s="26"/>
       <c r="L14" s="21">
@@ -4893,7 +4971,7 @@
         <v>8564.5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -4919,7 +4997,7 @@
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>13765.62</v>
+        <v>14385.75</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
@@ -4931,7 +5009,7 @@
         <v>14031.25</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -4957,7 +5035,7 @@
       <c r="G16" s="17"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216.78</v>
+        <v>219.14</v>
       </c>
       <c r="J16" s="26"/>
       <c r="L16" s="21">
@@ -4969,7 +5047,7 @@
         <v>234.5</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -4995,7 +5073,7 @@
       <c r="G17" s="17"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>182.59</v>
+        <v>185.52</v>
       </c>
       <c r="J17" s="26"/>
       <c r="L17" s="21">
@@ -5007,7 +5085,7 @@
         <v>201.25</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -5033,7 +5111,7 @@
       <c r="G18" s="18"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1740</v>
+        <v>1757</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -5044,7 +5122,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>קסם S&amp;P 500 ETF מנוטרלת מט"ח</v>
@@ -5077,7 +5155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5111,7 +5189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5145,7 +5223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5179,7 +5257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5213,7 +5291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5247,7 +5325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5281,7 +5359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5315,7 +5393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5349,7 +5427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17">
         <f>'התיק העדכני'!E20</f>
         <v>0</v>
@@ -5391,15 +5469,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7390F3B9-AE45-44AE-B4DF-D92B58EB94BD}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="7" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="7" width="17.59765625" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -5429,7 +5507,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -5456,7 +5534,7 @@
       <c r="L2" s="32"/>
       <c r="M2" s="32"/>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -5471,7 +5549,7 @@
       </c>
       <c r="D3" s="19">
         <f>'התיק העדכני'!G3</f>
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E3" s="16">
         <v>848</v>
@@ -5482,7 +5560,7 @@
       <c r="G3" s="7"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1316</v>
+        <v>1331</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
@@ -5493,7 +5571,7 @@
         <v>1273.75</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -5519,7 +5597,7 @@
       <c r="G4" s="7"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6060</v>
+        <v>6111</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+GEMINI!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
@@ -5530,7 +5608,7 @@
         <v>6701.5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -5556,7 +5634,7 @@
       <c r="G5" s="7"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>595.4</v>
+        <v>626</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
@@ -5567,7 +5645,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -5593,7 +5671,7 @@
       <c r="G6" s="7"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>3931</v>
+        <v>3970</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
@@ -5604,7 +5682,7 @@
         <v>4231.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -5619,7 +5697,7 @@
       </c>
       <c r="D7" s="19">
         <f>'התיק העדכני'!G7</f>
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E7" s="16">
         <v>3363</v>
@@ -5630,7 +5708,7 @@
       <c r="G7" s="8"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3885</v>
+        <v>3913</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+GEMINI!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
@@ -5641,7 +5719,7 @@
         <v>4253</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -5667,7 +5745,7 @@
       <c r="G8" s="8"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>42250</v>
+        <v>41570</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+GEMINI!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -5678,7 +5756,7 @@
         <v>42975</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -5704,7 +5782,7 @@
       <c r="G9" s="8"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9917</v>
+        <v>9924</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+GEMINI!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -5715,7 +5793,7 @@
         <v>11459.25</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -5741,7 +5819,7 @@
       <c r="G10" s="8"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4930</v>
+        <v>5050</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+GEMINI!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -5752,7 +5830,7 @@
         <v>6041.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -5778,7 +5856,7 @@
       <c r="G11" s="8"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1003</v>
+        <v>1029</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+GEMINI!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -5789,7 +5867,7 @@
         <v>1085.5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -5815,7 +5893,7 @@
       <c r="G12" s="8"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>26620</v>
+        <v>26800</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+GEMINI!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
@@ -5826,7 +5904,7 @@
         <v>27485</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -5841,19 +5919,19 @@
       </c>
       <c r="D13" s="19">
         <f>'התיק העדכני'!G13</f>
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>830.1</v>
+        <v>932.1</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -5879,7 +5957,7 @@
       <c r="G14" s="7"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7722</v>
+        <v>7735</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
@@ -5890,7 +5968,7 @@
         <v>8564.5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -5927,7 +6005,7 @@
         <v>14031.25</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -5953,7 +6031,7 @@
       <c r="G16" s="7"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>13765.62</v>
+        <v>14385.75</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
@@ -5964,7 +6042,7 @@
         <v>234.5</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -5990,7 +6068,7 @@
       <c r="G17" s="7"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216.78</v>
+        <v>219.14</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+GEMINI!E17+PERPLIXITY!E17+DEEPSEEK!E17)/4</f>
@@ -6001,7 +6079,7 @@
         <v>201.25</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -6027,7 +6105,7 @@
       <c r="G18" s="8"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>182.59</v>
+        <v>185.52</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+GEMINI!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -6038,7 +6116,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>קסם S&amp;P 500 ETF מנוטרלת מט"ח</v>
@@ -6060,7 +6138,7 @@
       <c r="G19" s="8"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1740</v>
+        <v>1757</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+GEMINI!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -6071,7 +6149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -6083,7 +6161,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -6095,7 +6173,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -6107,7 +6185,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -6119,7 +6197,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -6131,7 +6209,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -6143,7 +6221,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -6155,7 +6233,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -6167,7 +6245,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -6187,15 +6265,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88497C0-21A8-47C7-B959-3D6DF74EF6E2}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="6" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="6" width="17.59765625" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -6225,7 +6303,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -6256,7 +6334,7 @@
       <c r="L2" s="32"/>
       <c r="M2" s="32"/>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -6271,7 +6349,7 @@
       </c>
       <c r="D3" s="19">
         <f>'התיק העדכני'!G3</f>
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E3" s="16">
         <v>1050</v>
@@ -6282,7 +6360,7 @@
       <c r="G3" s="10"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1316</v>
+        <v>1331</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
@@ -6293,7 +6371,7 @@
         <v>1273.75</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -6319,7 +6397,7 @@
       <c r="G4" s="10"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6060</v>
+        <v>6111</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+GEMINI!E4+DEEPSEEK!E4)/4</f>
@@ -6330,7 +6408,7 @@
         <v>6701.5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -6356,7 +6434,7 @@
       <c r="G5" s="10"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>595.4</v>
+        <v>626</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
@@ -6367,7 +6445,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -6393,7 +6471,7 @@
       <c r="G6" s="10"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>3931</v>
+        <v>3970</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
@@ -6404,7 +6482,7 @@
         <v>4231.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -6419,7 +6497,7 @@
       </c>
       <c r="D7" s="19">
         <f>'התיק העדכני'!G7</f>
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E7" s="16">
         <v>3600</v>
@@ -6430,7 +6508,7 @@
       <c r="G7" s="10"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3885</v>
+        <v>3913</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+GEMINI!E7+DEEPSEEK!E7)/4</f>
@@ -6441,7 +6519,7 @@
         <v>4253</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -6466,7 +6544,7 @@
       </c>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>42250</v>
+        <v>41570</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+GEMINI!E8+DEEPSEEK!E8)/4</f>
@@ -6477,7 +6555,7 @@
         <v>42975</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -6502,7 +6580,7 @@
       </c>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9917</v>
+        <v>9924</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+GEMINI!E9+DEEPSEEK!E9)/4</f>
@@ -6513,7 +6591,7 @@
         <v>11459.25</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -6538,7 +6616,7 @@
       </c>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4930</v>
+        <v>5050</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+GEMINI!E10+DEEPSEEK!E10)/4</f>
@@ -6549,7 +6627,7 @@
         <v>6041.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -6574,7 +6652,7 @@
       </c>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1003</v>
+        <v>1029</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+GEMINI!E11+DEEPSEEK!E11)/4</f>
@@ -6585,7 +6663,7 @@
         <v>1085.5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -6611,7 +6689,7 @@
       <c r="G12" s="10"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>26620</v>
+        <v>26800</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+GEMINI!E12+DEEPSEEK!E12)/4</f>
@@ -6622,7 +6700,7 @@
         <v>27485</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -6637,7 +6715,7 @@
       </c>
       <c r="D13" s="19">
         <f>'התיק העדכני'!G13</f>
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E13" s="16">
         <v>690</v>
@@ -6648,12 +6726,12 @@
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>830.1</v>
+        <v>932.1</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -6679,7 +6757,7 @@
       <c r="G14" s="10"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7722</v>
+        <v>7735</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
@@ -6690,7 +6768,7 @@
         <v>8564.5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -6716,7 +6794,7 @@
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>13765.62</v>
+        <v>14385.75</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
@@ -6727,7 +6805,7 @@
         <v>14031.25</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -6753,7 +6831,7 @@
       <c r="G16" s="10"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216.78</v>
+        <v>219.14</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+GEMINI!E16+DEEPSEEK!E16)/4</f>
@@ -6764,7 +6842,7 @@
         <v>234.5</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -6790,7 +6868,7 @@
       <c r="G17" s="10"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>182.59</v>
+        <v>185.52</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+GEMINI!E17+DEEPSEEK!E17)/4</f>
@@ -6801,7 +6879,7 @@
         <v>201.25</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -6826,7 +6904,7 @@
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1740</v>
+        <v>1757</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
@@ -6837,7 +6915,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>קסם S&amp;P 500 ETF מנוטרלת מט"ח</v>
@@ -6869,7 +6947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -6881,7 +6959,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -6893,7 +6971,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -6905,7 +6983,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -6917,7 +6995,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -6929,7 +7007,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -6941,7 +7019,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -6953,7 +7031,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -6965,7 +7043,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -6985,16 +7063,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D354D65C-237D-4544-BBD1-8A37190947C4}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="5" width="17.5703125" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="5" width="17.59765625" customWidth="1"/>
+    <col min="6" max="6" width="20.3984375" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -7023,7 +7101,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -7050,7 +7128,7 @@
       <c r="L2" s="32"/>
       <c r="M2" s="32"/>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -7065,7 +7143,7 @@
       </c>
       <c r="D3" s="19">
         <f>'התיק העדכני'!G3</f>
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E3" s="16">
         <v>1000</v>
@@ -7076,7 +7154,7 @@
       <c r="G3" s="31"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1316</v>
+        <v>1331</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
@@ -7087,7 +7165,7 @@
         <v>1273.75</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -7112,7 +7190,7 @@
       </c>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6060</v>
+        <v>6111</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+GEMINI!E4)/4</f>
@@ -7123,7 +7201,7 @@
         <v>6701.5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -7149,7 +7227,7 @@
       <c r="G5" s="31"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>595.4</v>
+        <v>626</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
@@ -7160,7 +7238,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -7186,7 +7264,7 @@
       <c r="G6" s="31"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>3931</v>
+        <v>3970</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
@@ -7197,7 +7275,7 @@
         <v>4231.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -7212,7 +7290,7 @@
       </c>
       <c r="D7" s="19">
         <f>'התיק העדכני'!G7</f>
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E7" s="16">
         <v>3750</v>
@@ -7222,7 +7300,7 @@
       </c>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3885</v>
+        <v>3913</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+GEMINI!E7)/4</f>
@@ -7233,7 +7311,7 @@
         <v>4253</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -7259,7 +7337,7 @@
       <c r="G8" s="31"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>42250</v>
+        <v>41570</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+GEMINI!E8)/4</f>
@@ -7270,7 +7348,7 @@
         <v>42975</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -7296,7 +7374,7 @@
       <c r="G9" s="31"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9917</v>
+        <v>9924</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+GEMINI!E9)/4</f>
@@ -7307,7 +7385,7 @@
         <v>11459.25</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -7333,7 +7411,7 @@
       <c r="G10" s="31"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4930</v>
+        <v>5050</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+GEMINI!E10)/4</f>
@@ -7344,7 +7422,7 @@
         <v>6041.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -7370,7 +7448,7 @@
       <c r="G11" s="31"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1003</v>
+        <v>1029</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+GEMINI!E11)/4</f>
@@ -7381,7 +7459,7 @@
         <v>1085.5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -7407,7 +7485,7 @@
       <c r="G12" s="31"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>26620</v>
+        <v>26800</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+GEMINI!E12)/4</f>
@@ -7418,7 +7496,7 @@
         <v>27485</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -7433,19 +7511,19 @@
       </c>
       <c r="D13" s="19">
         <f>'התיק העדכני'!G13</f>
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>830.1</v>
+        <v>932.1</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -7471,7 +7549,7 @@
       <c r="G14" s="31"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7722</v>
+        <v>7735</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
@@ -7482,7 +7560,7 @@
         <v>8564.5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -7518,7 +7596,7 @@
         <v>14031.25</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -7543,7 +7621,7 @@
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>13765.62</v>
+        <v>14385.75</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
@@ -7554,7 +7632,7 @@
         <v>234.5</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -7580,7 +7658,7 @@
       <c r="G17" s="31"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216.78</v>
+        <v>219.14</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+GEMINI!E17)/4</f>
@@ -7591,7 +7669,7 @@
         <v>201.25</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -7617,7 +7695,7 @@
       <c r="G18" s="31"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>182.59</v>
+        <v>185.52</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+GEMINI!E18)/4</f>
@@ -7628,7 +7706,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>קסם S&amp;P 500 ETF מנוטרלת מט"ח</v>
@@ -7647,7 +7725,7 @@
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1740</v>
+        <v>1757</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+GEMINI!E19)/4</f>
@@ -7658,7 +7736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -7669,7 +7747,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -7681,7 +7759,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -7693,7 +7771,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -7705,7 +7783,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -7717,7 +7795,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -7729,7 +7807,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -7741,7 +7819,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -7753,7 +7831,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/673b1203f7e82b27/מסמכים/GitHub/BURSA/BURSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{F8D1803D-9746-4C08-83A2-CD263161045D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E8C3EB6-52FF-4CCF-A997-CC1513EDCD59}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{F8D1803D-9746-4C08-83A2-CD263161045D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{829E538F-0444-48DD-A7DE-CDB627698DD0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="101">
   <si>
     <t>MTF מחקה אינדקס תעשיה ישראל</t>
   </si>
@@ -340,6 +340,9 @@
   </si>
   <si>
     <t>מחיר 22/01/2026</t>
+  </si>
+  <si>
+    <t>מחיר 23/01/2026</t>
   </si>
 </sst>
 </file>
@@ -812,6 +815,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא של Office 2013 - 2022">
   <a:themeElements>
@@ -1109,22 +1116,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86B4639-EF9D-4B16-B2C9-0D5E9C5EEC8B}">
-  <dimension ref="A1:BP25"/>
+  <dimension ref="A1:BQ25"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="5" width="17.59765625" customWidth="1"/>
     <col min="6" max="6" width="13.296875" customWidth="1"/>
     <col min="7" max="7" width="11.59765625" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="51" width="14.8984375" customWidth="1"/>
-    <col min="52" max="61" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="13" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="13.09765625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="11" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="7.09765625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="11.59765625" customWidth="1"/>
+    <col min="8" max="52" width="14.8984375" customWidth="1"/>
+    <col min="53" max="62" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="13" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="11.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="1" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1153,184 +1160,187 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BK1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BL1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BM1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BN1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="BN1" s="12" t="s">
+      <c r="BO1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="BO1" s="12" t="s">
+      <c r="BP1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="BP1" s="12" t="s">
+      <c r="BQ1" s="12" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="2" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A2" s="1">
         <v>282012</v>
       </c>
@@ -1353,18 +1363,20 @@
         <v>11000</v>
       </c>
       <c r="I2" s="13">
+        <v>11000</v>
+      </c>
+      <c r="J2" s="13">
+        <v>11000</v>
+      </c>
+      <c r="K2" s="13">
         <v>10700</v>
       </c>
-      <c r="J2" s="13">
-        <v>10700</v>
-      </c>
-      <c r="K2" s="13">
+      <c r="L2" s="13">
         <v>10400</v>
       </c>
-      <c r="L2" s="13">
+      <c r="M2" s="13">
         <v>11230</v>
       </c>
-      <c r="M2" s="6"/>
       <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
@@ -1405,23 +1417,30 @@
       <c r="AY2" s="6"/>
       <c r="AZ2" s="6"/>
       <c r="BA2" s="6"/>
-      <c r="BB2" s="33"/>
-      <c r="BC2" s="6"/>
+      <c r="BB2" s="6"/>
+      <c r="BC2" s="33"/>
       <c r="BD2" s="6"/>
-      <c r="BE2" s="33"/>
-      <c r="BF2" s="6"/>
+      <c r="BE2" s="6"/>
+      <c r="BF2" s="33"/>
       <c r="BG2" s="6"/>
       <c r="BH2" s="6"/>
       <c r="BI2" s="6"/>
       <c r="BJ2" s="6"/>
-      <c r="BK2" s="6"/>
-      <c r="BL2" s="6"/>
+      <c r="BK2" s="13">
+        <f>(G2*H2)/100-BQ2</f>
+        <v>770</v>
+      </c>
+      <c r="BL2" s="13">
+        <f>(G2*H2)/100</f>
+        <v>770</v>
+      </c>
       <c r="BM2" s="6"/>
-      <c r="BN2" s="25"/>
+      <c r="BN2" s="6"/>
       <c r="BO2" s="25"/>
       <c r="BP2" s="25"/>
-    </row>
-    <row r="3" spans="1:68" ht="45" customHeight="1" thickBot="1">
+      <c r="BQ2" s="25"/>
+    </row>
+    <row r="3" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A3" s="1">
         <v>1227552</v>
       </c>
@@ -1450,36 +1469,38 @@
         <v>1153.6300000000001</v>
       </c>
       <c r="I3" s="13">
+        <v>1373</v>
+      </c>
+      <c r="J3" s="13">
+        <v>1373</v>
+      </c>
+      <c r="K3" s="13">
         <v>1331</v>
       </c>
-      <c r="J3" s="13">
-        <v>1331</v>
-      </c>
-      <c r="K3" s="13">
+      <c r="L3" s="13">
         <v>1386</v>
       </c>
-      <c r="L3" s="13">
+      <c r="M3" s="13">
         <v>1342</v>
       </c>
-      <c r="M3" s="13">
+      <c r="N3" s="13">
         <v>1250</v>
-      </c>
-      <c r="N3" s="13">
-        <v>1389</v>
       </c>
       <c r="O3" s="13">
         <v>1389</v>
       </c>
       <c r="P3" s="13">
+        <v>1389</v>
+      </c>
+      <c r="Q3" s="13">
         <v>1367</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="R3" s="13">
         <v>1026</v>
       </c>
-      <c r="R3" s="13">
+      <c r="S3" s="13">
         <v>949.1</v>
       </c>
-      <c r="S3" s="13"/>
       <c r="T3" s="13"/>
       <c r="U3" s="13"/>
       <c r="V3" s="13"/>
@@ -1495,8 +1516,8 @@
       <c r="AF3" s="13"/>
       <c r="AG3" s="13"/>
       <c r="AH3" s="13"/>
-      <c r="AI3" s="14"/>
-      <c r="AJ3" s="13"/>
+      <c r="AI3" s="13"/>
+      <c r="AJ3" s="14"/>
       <c r="AK3" s="13"/>
       <c r="AL3" s="13"/>
       <c r="AM3" s="13"/>
@@ -1514,36 +1535,37 @@
       <c r="AY3" s="13"/>
       <c r="AZ3" s="13"/>
       <c r="BA3" s="13"/>
-      <c r="BB3" s="29"/>
-      <c r="BC3" s="13"/>
+      <c r="BB3" s="13"/>
+      <c r="BC3" s="29"/>
       <c r="BD3" s="13"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="13"/>
+      <c r="BE3" s="13"/>
+      <c r="BF3" s="29"/>
       <c r="BG3" s="13"/>
       <c r="BH3" s="13"/>
       <c r="BI3" s="13"/>
-      <c r="BJ3" s="13">
-        <f>(G3*H3)/100-BP3</f>
+      <c r="BJ3" s="13"/>
+      <c r="BK3" s="13">
+        <f>(G3*H3)/100-BQ3</f>
         <v>784.46840000000009</v>
       </c>
-      <c r="BK3" s="13">
+      <c r="BL3" s="13">
         <f>(G3*H3)/100</f>
         <v>784.46840000000009</v>
       </c>
-      <c r="BL3" s="13">
-        <f>(BK3-BJ3)</f>
+      <c r="BM3" s="13">
+        <f>(BL3-BK3)</f>
         <v>0</v>
       </c>
-      <c r="BM3" s="13">
-        <f>((BA3-H3)/H3)*100</f>
+      <c r="BN3" s="13">
+        <f>((BB3-H3)/H3)*100</f>
         <v>-100</v>
       </c>
-      <c r="BP3" s="15">
-        <f>(BN3*BO3-BN3*H3)/100</f>
+      <c r="BQ3" s="15">
+        <f>(BO3*BP3-BO3*H3)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="4" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A4" s="1">
         <v>587014</v>
       </c>
@@ -1572,36 +1594,38 @@
         <v>5925</v>
       </c>
       <c r="I4" s="13">
+        <v>6680</v>
+      </c>
+      <c r="J4" s="13">
+        <v>6680</v>
+      </c>
+      <c r="K4" s="13">
         <v>6111</v>
       </c>
-      <c r="J4" s="13">
-        <v>6111</v>
-      </c>
-      <c r="K4" s="13">
+      <c r="L4" s="13">
         <v>6050</v>
       </c>
-      <c r="L4" s="13">
+      <c r="M4" s="13">
         <v>6169</v>
       </c>
-      <c r="M4" s="13">
+      <c r="N4" s="13">
         <v>6300</v>
-      </c>
-      <c r="N4" s="13">
-        <v>6335</v>
       </c>
       <c r="O4" s="13">
         <v>6335</v>
       </c>
       <c r="P4" s="13">
+        <v>6335</v>
+      </c>
+      <c r="Q4" s="13">
         <v>6444</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>5749</v>
       </c>
       <c r="R4" s="13">
         <v>5749</v>
       </c>
-      <c r="S4" s="13"/>
+      <c r="S4" s="13">
+        <v>5749</v>
+      </c>
       <c r="T4" s="13"/>
       <c r="U4" s="13"/>
       <c r="V4" s="13"/>
@@ -1636,36 +1660,37 @@
       <c r="AY4" s="13"/>
       <c r="AZ4" s="13"/>
       <c r="BA4" s="13"/>
-      <c r="BB4" s="29"/>
-      <c r="BC4" s="13"/>
+      <c r="BB4" s="13"/>
+      <c r="BC4" s="29"/>
       <c r="BD4" s="13"/>
-      <c r="BE4" s="29"/>
-      <c r="BF4" s="13"/>
+      <c r="BE4" s="13"/>
+      <c r="BF4" s="29"/>
       <c r="BG4" s="13"/>
       <c r="BH4" s="13"/>
       <c r="BI4" s="13"/>
-      <c r="BJ4" s="13">
-        <f>(G4*H4)/100-BP4</f>
+      <c r="BJ4" s="13"/>
+      <c r="BK4" s="13">
+        <f>(G4*H4)/100-BQ4</f>
         <v>1185</v>
       </c>
-      <c r="BK4" s="13">
+      <c r="BL4" s="13">
         <f>(G4*H4)/100</f>
         <v>1185</v>
       </c>
-      <c r="BL4" s="13">
-        <f>(BK4-BJ4)</f>
+      <c r="BM4" s="13">
+        <f>(BL4-BK4)</f>
         <v>0</v>
       </c>
-      <c r="BM4" s="13">
-        <f>((BA4-H4)/H4)*100</f>
+      <c r="BN4" s="13">
+        <f>((BB4-H4)/H4)*100</f>
         <v>-100</v>
       </c>
-      <c r="BP4" s="15">
-        <f>(BN4*BO4-BN4*H4)/100</f>
+      <c r="BQ4" s="15">
+        <f>(BO4*BP4-BO4*H4)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="5" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A5" s="1">
         <v>1099787</v>
       </c>
@@ -1685,75 +1710,77 @@
         <v>67</v>
       </c>
       <c r="F5" s="4">
-        <v>46010</v>
+        <v>46045</v>
       </c>
       <c r="G5" s="27">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H5" s="13">
-        <v>525.71</v>
+        <v>615</v>
       </c>
       <c r="I5" s="13">
+        <v>630.29999999999995</v>
+      </c>
+      <c r="J5" s="13">
+        <v>630.29999999999995</v>
+      </c>
+      <c r="K5" s="13">
         <v>626</v>
       </c>
-      <c r="J5" s="13">
-        <v>626</v>
-      </c>
-      <c r="K5" s="13">
+      <c r="L5" s="13">
         <v>595.4</v>
       </c>
-      <c r="L5" s="13">
+      <c r="M5" s="13">
         <v>667.1</v>
       </c>
-      <c r="M5" s="13">
+      <c r="N5" s="13">
         <v>651</v>
-      </c>
-      <c r="N5" s="13">
-        <v>641.1</v>
       </c>
       <c r="O5" s="13">
         <v>641.1</v>
       </c>
       <c r="P5" s="13">
+        <v>641.1</v>
+      </c>
+      <c r="Q5" s="13">
         <v>607.1</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="R5" s="13">
         <v>583</v>
       </c>
-      <c r="R5" s="13">
+      <c r="S5" s="13">
         <v>581.6</v>
       </c>
-      <c r="S5" s="13">
+      <c r="T5" s="13">
         <v>578.70000000000005</v>
       </c>
-      <c r="T5" s="13">
+      <c r="U5" s="13">
         <v>590</v>
       </c>
-      <c r="U5" s="13">
+      <c r="V5" s="13">
         <v>554.70000000000005</v>
       </c>
-      <c r="V5" s="13">
+      <c r="W5" s="13">
         <v>511.8</v>
       </c>
-      <c r="W5" s="13">
+      <c r="X5" s="13">
         <v>487</v>
       </c>
-      <c r="X5" s="13">
+      <c r="Y5" s="13">
         <v>478.8</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="Z5" s="13">
         <v>485.5</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="AA5" s="13">
         <v>453.4</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AB5" s="13">
         <v>426.1</v>
       </c>
-      <c r="AB5" s="13">
+      <c r="AC5" s="13">
         <v>423.2</v>
       </c>
-      <c r="AC5" s="13"/>
       <c r="AD5" s="13"/>
       <c r="AE5" s="13"/>
       <c r="AF5" s="13"/>
@@ -1778,36 +1805,28 @@
       <c r="AY5" s="13"/>
       <c r="AZ5" s="13"/>
       <c r="BA5" s="13"/>
-      <c r="BB5" s="29"/>
-      <c r="BC5" s="13"/>
+      <c r="BB5" s="13"/>
+      <c r="BC5" s="29"/>
       <c r="BD5" s="13"/>
-      <c r="BE5" s="29"/>
-      <c r="BF5" s="13"/>
+      <c r="BE5" s="13"/>
+      <c r="BF5" s="29"/>
       <c r="BG5" s="13"/>
       <c r="BH5" s="13"/>
       <c r="BI5" s="13"/>
-      <c r="BJ5" s="13">
-        <f t="shared" ref="BJ5:BJ19" si="0">(G5*H5)/100-BP5</f>
-        <v>-294.42399999999992</v>
-      </c>
+      <c r="BJ5" s="13"/>
       <c r="BK5" s="13">
+        <f t="shared" ref="BK5:BK19" si="0">(G5*H5)/100-BQ5</f>
+        <v>479.7</v>
+      </c>
+      <c r="BL5" s="13">
         <f>(G5*H5)/100</f>
-        <v>0</v>
-      </c>
-      <c r="BL5" s="13"/>
+        <v>479.7</v>
+      </c>
       <c r="BM5" s="13"/>
-      <c r="BN5">
-        <v>260</v>
-      </c>
-      <c r="BO5">
-        <v>638.95000000000005</v>
-      </c>
-      <c r="BP5" s="15">
-        <f>(BN5*BO5-BN5*H5)/100</f>
-        <v>294.42399999999992</v>
-      </c>
-    </row>
-    <row r="6" spans="1:68" ht="45" customHeight="1" thickBot="1">
+      <c r="BN5" s="13"/>
+      <c r="BQ5" s="15"/>
+    </row>
+    <row r="6" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A6" s="2">
         <v>1166768</v>
       </c>
@@ -1821,7 +1840,7 @@
       </c>
       <c r="D6" s="6" t="str">
         <f>IF(I6&lt;GEMINI!L6,"למכור בהפסד",IF(I6&gt;GEMINI!M6,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>85</v>
@@ -1836,39 +1855,41 @@
         <v>3700</v>
       </c>
       <c r="I6" s="13">
+        <v>4238</v>
+      </c>
+      <c r="J6" s="13">
+        <v>4238</v>
+      </c>
+      <c r="K6" s="13">
         <v>3970</v>
       </c>
-      <c r="J6" s="13">
-        <v>3970</v>
-      </c>
-      <c r="K6" s="13">
+      <c r="L6" s="13">
         <v>3870</v>
       </c>
-      <c r="L6" s="13">
+      <c r="M6" s="13">
         <v>3805</v>
       </c>
-      <c r="M6" s="13">
+      <c r="N6" s="13">
         <v>3667</v>
-      </c>
-      <c r="N6" s="13">
-        <v>3582</v>
       </c>
       <c r="O6" s="13">
         <v>3582</v>
       </c>
       <c r="P6" s="13">
+        <v>3582</v>
+      </c>
+      <c r="Q6" s="13">
         <v>3570</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="R6" s="13">
         <v>3619</v>
       </c>
-      <c r="R6" s="13">
+      <c r="S6" s="13">
         <v>3650</v>
       </c>
-      <c r="S6" s="13">
+      <c r="T6" s="13">
         <v>3720</v>
       </c>
-      <c r="T6" s="13"/>
       <c r="U6" s="13"/>
       <c r="V6" s="13"/>
       <c r="W6" s="13"/>
@@ -1902,41 +1923,42 @@
       <c r="AY6" s="13"/>
       <c r="AZ6" s="13"/>
       <c r="BA6" s="13"/>
-      <c r="BB6" s="29"/>
-      <c r="BC6" s="13"/>
+      <c r="BB6" s="13"/>
+      <c r="BC6" s="29"/>
       <c r="BD6" s="13"/>
-      <c r="BE6" s="29"/>
-      <c r="BF6" s="13"/>
+      <c r="BE6" s="13"/>
+      <c r="BF6" s="29"/>
       <c r="BG6" s="13"/>
       <c r="BH6" s="13"/>
-      <c r="BJ6" s="13">
-        <f>(G6*H6)/100-BP6</f>
+      <c r="BI6" s="13"/>
+      <c r="BK6" s="13">
+        <f>(G6*H6)/100-BQ6</f>
         <v>561.70000000000005</v>
       </c>
-      <c r="BK6" s="13">
+      <c r="BL6" s="13">
         <f>(G6*H6)/100</f>
         <v>555</v>
       </c>
-      <c r="BL6" s="13">
-        <f t="shared" ref="BL6" si="1">(BK6-BJ6)</f>
+      <c r="BM6" s="13">
+        <f t="shared" ref="BM6" si="1">(BL6-BK6)</f>
         <v>-6.7000000000000455</v>
       </c>
-      <c r="BM6" s="13">
-        <f>((BA6-H6)/H6)*100</f>
+      <c r="BN6" s="13">
+        <f>((BB6-H6)/H6)*100</f>
         <v>-100</v>
       </c>
-      <c r="BN6">
+      <c r="BO6">
         <v>5</v>
       </c>
-      <c r="BO6">
+      <c r="BP6">
         <v>3566</v>
       </c>
-      <c r="BP6" s="15">
-        <f>(BN6*BO6-BN6*H6)/100</f>
+      <c r="BQ6" s="15">
+        <f>(BO6*BP6-BO6*H6)/100</f>
         <v>-6.7</v>
       </c>
     </row>
-    <row r="7" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="7" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A7" s="1">
         <v>1148899</v>
       </c>
@@ -1965,66 +1987,68 @@
         <v>3585</v>
       </c>
       <c r="I7" s="13">
+        <v>3928</v>
+      </c>
+      <c r="J7" s="13">
+        <v>3928</v>
+      </c>
+      <c r="K7" s="13">
         <v>3913</v>
       </c>
-      <c r="J7" s="13">
-        <v>3913</v>
-      </c>
-      <c r="K7" s="13">
+      <c r="L7" s="13">
         <v>3860</v>
       </c>
-      <c r="L7" s="13">
+      <c r="M7" s="13">
         <v>3893</v>
       </c>
-      <c r="M7" s="13">
+      <c r="N7" s="13">
         <v>3900</v>
-      </c>
-      <c r="N7" s="13">
-        <v>3842</v>
       </c>
       <c r="O7" s="13">
         <v>3842</v>
       </c>
       <c r="P7" s="13">
+        <v>3842</v>
+      </c>
+      <c r="Q7" s="13">
         <v>3841</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="R7" s="13">
         <v>3809</v>
       </c>
-      <c r="R7" s="13">
+      <c r="S7" s="13">
         <v>3810</v>
       </c>
-      <c r="S7" s="13">
+      <c r="T7" s="13">
         <v>3798</v>
       </c>
-      <c r="T7" s="13">
+      <c r="U7" s="13">
         <v>3713</v>
       </c>
-      <c r="U7" s="13">
+      <c r="V7" s="13">
         <v>3657</v>
       </c>
-      <c r="V7" s="13">
+      <c r="W7" s="13">
         <v>3592</v>
       </c>
-      <c r="W7" s="13">
+      <c r="X7" s="13">
         <v>3621</v>
       </c>
-      <c r="X7" s="13">
+      <c r="Y7" s="13">
         <v>3572</v>
       </c>
-      <c r="Y7" s="13">
+      <c r="Z7" s="13">
         <v>3580</v>
       </c>
-      <c r="Z7" s="13">
+      <c r="AA7" s="13">
         <v>3569</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="AB7" s="13">
         <v>3659</v>
       </c>
-      <c r="AB7" s="13">
+      <c r="AC7" s="13">
         <v>3656</v>
       </c>
-      <c r="AC7" s="13"/>
       <c r="AD7" s="13"/>
       <c r="AE7" s="13"/>
       <c r="AF7" s="13"/>
@@ -2049,27 +2073,28 @@
       <c r="AY7" s="13"/>
       <c r="AZ7" s="13"/>
       <c r="BA7" s="13"/>
-      <c r="BB7" s="29"/>
-      <c r="BC7" s="13"/>
+      <c r="BB7" s="13"/>
+      <c r="BC7" s="29"/>
       <c r="BD7" s="13"/>
-      <c r="BE7" s="29"/>
-      <c r="BF7" s="13"/>
+      <c r="BE7" s="13"/>
+      <c r="BF7" s="29"/>
       <c r="BG7" s="13"/>
       <c r="BH7" s="13"/>
       <c r="BI7" s="13"/>
-      <c r="BJ7" s="13">
+      <c r="BJ7" s="13"/>
+      <c r="BK7" s="13">
         <f t="shared" si="0"/>
         <v>2509.5</v>
       </c>
-      <c r="BK7" s="13">
-        <f t="shared" ref="BK7:BK19" si="2">(G7*H7)/100</f>
+      <c r="BL7" s="13">
+        <f t="shared" ref="BL7:BL19" si="2">(G7*H7)/100</f>
         <v>2509.5</v>
       </c>
-      <c r="BL7" s="13"/>
       <c r="BM7" s="13"/>
-      <c r="BP7" s="15"/>
-    </row>
-    <row r="8" spans="1:68" ht="45" customHeight="1" thickBot="1">
+      <c r="BN7" s="13"/>
+      <c r="BQ7" s="15"/>
+    </row>
+    <row r="8" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A8" s="1">
         <v>1082379</v>
       </c>
@@ -2098,102 +2123,104 @@
         <v>37875</v>
       </c>
       <c r="I8" s="13">
+        <v>40820</v>
+      </c>
+      <c r="J8" s="13">
+        <v>40820</v>
+      </c>
+      <c r="K8" s="13">
         <v>41570</v>
       </c>
-      <c r="J8" s="13">
-        <v>41570</v>
-      </c>
-      <c r="K8" s="13">
+      <c r="L8" s="13">
         <v>42050</v>
       </c>
-      <c r="L8" s="13">
+      <c r="M8" s="13">
         <v>39960</v>
       </c>
-      <c r="M8" s="13">
+      <c r="N8" s="13">
         <v>39990</v>
-      </c>
-      <c r="N8" s="13">
-        <v>38680</v>
       </c>
       <c r="O8" s="13">
         <v>38680</v>
       </c>
       <c r="P8" s="13">
+        <v>38680</v>
+      </c>
+      <c r="Q8" s="13">
         <v>37770</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="R8" s="13">
         <v>36330</v>
       </c>
-      <c r="R8" s="13">
+      <c r="S8" s="13">
         <v>38680</v>
       </c>
-      <c r="S8" s="13">
+      <c r="T8" s="13">
         <v>39090</v>
       </c>
-      <c r="T8" s="13">
+      <c r="U8" s="13">
         <v>37300</v>
       </c>
-      <c r="U8" s="13">
+      <c r="V8" s="13">
         <v>37650</v>
       </c>
-      <c r="V8" s="13">
+      <c r="W8" s="13">
         <v>37300</v>
       </c>
-      <c r="W8" s="13">
+      <c r="X8" s="13">
         <v>39450</v>
       </c>
-      <c r="X8" s="13">
+      <c r="Y8" s="13">
         <v>38390</v>
       </c>
-      <c r="Y8" s="13">
+      <c r="Z8" s="13">
         <v>38800</v>
       </c>
-      <c r="Z8" s="13">
+      <c r="AA8" s="13">
         <v>38510</v>
-      </c>
-      <c r="AA8" s="13">
-        <v>38970</v>
       </c>
       <c r="AB8" s="13">
         <v>38970</v>
       </c>
       <c r="AC8" s="13">
-        <v>37700</v>
+        <v>38970</v>
       </c>
       <c r="AD8" s="13">
         <v>37700</v>
       </c>
       <c r="AE8" s="13">
+        <v>37700</v>
+      </c>
+      <c r="AF8" s="13">
         <v>37750</v>
       </c>
-      <c r="AF8" s="13">
+      <c r="AG8" s="13">
         <v>38430</v>
       </c>
-      <c r="AG8" s="13">
+      <c r="AH8" s="13">
         <v>38250</v>
       </c>
-      <c r="AH8" s="13">
+      <c r="AI8" s="13">
         <v>40110</v>
       </c>
-      <c r="AI8" s="13">
+      <c r="AJ8" s="13">
         <v>40820</v>
       </c>
-      <c r="AJ8" s="13">
+      <c r="AK8" s="13">
         <v>39320</v>
       </c>
-      <c r="AK8" s="13">
+      <c r="AL8" s="13">
         <v>37800</v>
       </c>
-      <c r="AL8" s="13">
+      <c r="AM8" s="13">
         <v>36620</v>
       </c>
-      <c r="AM8" s="13">
+      <c r="AN8" s="13">
         <v>37130</v>
       </c>
-      <c r="AN8" s="13">
+      <c r="AO8" s="13">
         <v>35850</v>
       </c>
-      <c r="AO8" s="13"/>
       <c r="AP8" s="13"/>
       <c r="AQ8" s="13"/>
       <c r="AR8" s="13"/>
@@ -2206,39 +2233,40 @@
       <c r="AY8" s="13"/>
       <c r="AZ8" s="13"/>
       <c r="BA8" s="13"/>
-      <c r="BB8" s="29"/>
-      <c r="BC8" s="13"/>
+      <c r="BB8" s="13"/>
+      <c r="BC8" s="29"/>
       <c r="BD8" s="13"/>
-      <c r="BE8" s="29"/>
-      <c r="BF8" s="13"/>
+      <c r="BE8" s="13"/>
+      <c r="BF8" s="29"/>
       <c r="BG8" s="13"/>
       <c r="BH8" s="13"/>
       <c r="BI8" s="13"/>
-      <c r="BJ8" s="13">
+      <c r="BJ8" s="13"/>
+      <c r="BK8" s="13">
         <f t="shared" si="0"/>
         <v>806.25</v>
       </c>
-      <c r="BK8" s="13">
+      <c r="BL8" s="13">
         <f t="shared" si="2"/>
         <v>757.5</v>
       </c>
-      <c r="BL8" s="13">
-        <f t="shared" ref="BL8:BL11" si="3">(BK8-BJ8)</f>
+      <c r="BM8" s="13">
+        <f t="shared" ref="BM8:BM11" si="3">(BL8-BK8)</f>
         <v>-48.75</v>
       </c>
-      <c r="BM8" s="13"/>
-      <c r="BN8">
+      <c r="BN8" s="13"/>
+      <c r="BO8">
         <v>3</v>
       </c>
-      <c r="BO8">
+      <c r="BP8">
         <v>36250</v>
       </c>
-      <c r="BP8" s="15">
-        <f>(BN8*BO8-BN8*H8)/100</f>
+      <c r="BQ8" s="15">
+        <f>(BO8*BP8-BO8*H8)/100</f>
         <v>-48.75</v>
       </c>
     </row>
-    <row r="9" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="9" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A9" s="1">
         <v>629014</v>
       </c>
@@ -2267,96 +2295,98 @@
         <v>9227</v>
       </c>
       <c r="I9" s="13">
+        <v>9960</v>
+      </c>
+      <c r="J9" s="13">
+        <v>9960</v>
+      </c>
+      <c r="K9" s="13">
         <v>9924</v>
       </c>
-      <c r="J9" s="13">
-        <v>9924</v>
-      </c>
-      <c r="K9" s="13">
+      <c r="L9" s="13">
         <v>9999</v>
       </c>
-      <c r="L9" s="13">
+      <c r="M9" s="13">
         <v>9962</v>
       </c>
-      <c r="M9" s="13">
+      <c r="N9" s="13">
         <v>9979</v>
-      </c>
-      <c r="N9" s="13">
-        <v>10130</v>
       </c>
       <c r="O9" s="13">
         <v>10130</v>
       </c>
       <c r="P9" s="13">
+        <v>10130</v>
+      </c>
+      <c r="Q9" s="13">
         <v>10400</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="R9" s="13">
         <v>10320</v>
       </c>
-      <c r="R9" s="13">
+      <c r="S9" s="13">
         <v>10300</v>
       </c>
-      <c r="S9" s="13">
+      <c r="T9" s="13">
         <v>10310</v>
       </c>
-      <c r="T9" s="13">
+      <c r="U9" s="13">
         <v>9672</v>
       </c>
-      <c r="U9" s="13">
+      <c r="V9" s="13">
         <v>9953</v>
       </c>
-      <c r="V9" s="13">
+      <c r="W9" s="13">
         <v>10090</v>
       </c>
-      <c r="W9" s="13">
+      <c r="X9" s="13">
         <v>10070</v>
       </c>
-      <c r="X9" s="13">
+      <c r="Y9" s="13">
         <v>10030</v>
       </c>
-      <c r="Y9" s="13">
+      <c r="Z9" s="13">
         <v>10120</v>
       </c>
-      <c r="Z9" s="13">
+      <c r="AA9" s="13">
         <v>10000</v>
       </c>
-      <c r="AA9" s="13">
+      <c r="AB9" s="13">
         <v>10080</v>
       </c>
-      <c r="AB9" s="13">
+      <c r="AC9" s="13">
         <v>10030</v>
-      </c>
-      <c r="AC9" s="13">
-        <v>9726</v>
       </c>
       <c r="AD9" s="13">
         <v>9726</v>
       </c>
       <c r="AE9" s="13">
+        <v>9726</v>
+      </c>
+      <c r="AF9" s="13">
         <v>9659</v>
       </c>
-      <c r="AF9" s="13">
+      <c r="AG9" s="13">
         <v>9670</v>
       </c>
-      <c r="AG9" s="13">
+      <c r="AH9" s="13">
         <v>9590</v>
       </c>
-      <c r="AH9" s="13">
+      <c r="AI9" s="13">
         <v>9588</v>
       </c>
-      <c r="AI9" s="13">
+      <c r="AJ9" s="13">
         <v>9400</v>
       </c>
-      <c r="AJ9" s="13">
+      <c r="AK9" s="13">
         <v>9320</v>
       </c>
-      <c r="AK9" s="13">
+      <c r="AL9" s="13">
         <v>9071</v>
       </c>
-      <c r="AL9" s="13">
+      <c r="AM9" s="13">
         <v>9271</v>
       </c>
-      <c r="AM9" s="13"/>
       <c r="AN9" s="13"/>
       <c r="AO9" s="13"/>
       <c r="AP9" s="13"/>
@@ -2371,33 +2401,34 @@
       <c r="AY9" s="13"/>
       <c r="AZ9" s="13"/>
       <c r="BA9" s="13"/>
-      <c r="BB9" s="29"/>
-      <c r="BC9" s="13"/>
+      <c r="BB9" s="13"/>
+      <c r="BC9" s="29"/>
       <c r="BD9" s="13"/>
-      <c r="BE9" s="29"/>
-      <c r="BF9" s="13"/>
+      <c r="BE9" s="13"/>
+      <c r="BF9" s="29"/>
       <c r="BG9" s="13"/>
       <c r="BH9" s="13"/>
       <c r="BI9" s="13"/>
-      <c r="BJ9" s="13">
+      <c r="BJ9" s="13"/>
+      <c r="BK9" s="13">
         <f t="shared" si="0"/>
         <v>461.35</v>
       </c>
-      <c r="BK9" s="13">
+      <c r="BL9" s="13">
         <f t="shared" si="2"/>
         <v>461.35</v>
       </c>
-      <c r="BL9" s="13">
+      <c r="BM9" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BM9" s="13"/>
-      <c r="BP9" s="15">
-        <f>(BN9*BO9-BN9*H9)/100</f>
+      <c r="BN9" s="13"/>
+      <c r="BQ9" s="15">
+        <f>(BO9*BP9-BO9*H9)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="10" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A10" s="1">
         <v>1141464</v>
       </c>
@@ -2432,172 +2463,175 @@
         <v>5050</v>
       </c>
       <c r="K10" s="13">
+        <v>5050</v>
+      </c>
+      <c r="L10" s="13">
         <v>4930</v>
       </c>
-      <c r="L10" s="13">
+      <c r="M10" s="13">
         <v>5150</v>
       </c>
-      <c r="M10" s="13">
+      <c r="N10" s="13">
         <v>5283</v>
-      </c>
-      <c r="N10" s="13">
-        <v>5253</v>
       </c>
       <c r="O10" s="13">
         <v>5253</v>
       </c>
       <c r="P10" s="13">
+        <v>5253</v>
+      </c>
+      <c r="Q10" s="13">
         <v>5400</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="R10" s="13">
         <v>5522</v>
       </c>
-      <c r="R10" s="13">
+      <c r="S10" s="13">
         <v>5690</v>
       </c>
-      <c r="S10" s="13">
+      <c r="T10" s="13">
         <v>5749</v>
       </c>
-      <c r="T10" s="13">
+      <c r="U10" s="13">
         <v>5840</v>
-      </c>
-      <c r="U10" s="13">
-        <v>5650</v>
       </c>
       <c r="V10" s="13">
         <v>5650</v>
       </c>
       <c r="W10" s="13">
+        <v>5650</v>
+      </c>
+      <c r="X10" s="13">
         <v>5841</v>
       </c>
-      <c r="X10" s="13">
+      <c r="Y10" s="13">
         <v>5758</v>
       </c>
-      <c r="Y10" s="13">
+      <c r="Z10" s="13">
         <v>5673</v>
       </c>
-      <c r="Z10" s="13">
+      <c r="AA10" s="13">
         <v>5609</v>
       </c>
-      <c r="AA10" s="13">
+      <c r="AB10" s="13">
         <v>5750</v>
       </c>
-      <c r="AB10" s="13">
+      <c r="AC10" s="13">
         <v>5841</v>
-      </c>
-      <c r="AC10" s="13">
-        <v>5564</v>
       </c>
       <c r="AD10" s="13">
         <v>5564</v>
       </c>
       <c r="AE10" s="13">
+        <v>5564</v>
+      </c>
+      <c r="AF10" s="13">
         <v>5557</v>
       </c>
-      <c r="AF10" s="13">
+      <c r="AG10" s="13">
         <v>5501</v>
       </c>
-      <c r="AG10" s="13">
+      <c r="AH10" s="13">
         <v>5250</v>
       </c>
-      <c r="AH10" s="13">
+      <c r="AI10" s="13">
         <v>5270</v>
       </c>
-      <c r="AI10" s="13">
+      <c r="AJ10" s="13">
         <v>5149</v>
       </c>
-      <c r="AJ10" s="13">
+      <c r="AK10" s="13">
         <v>5092</v>
       </c>
-      <c r="AK10" s="13">
+      <c r="AL10" s="13">
         <v>5228</v>
       </c>
-      <c r="AL10" s="13">
+      <c r="AM10" s="13">
         <v>5301</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AN10" s="13">
         <v>5159</v>
       </c>
-      <c r="AN10" s="13">
+      <c r="AO10" s="13">
         <v>5198</v>
       </c>
-      <c r="AO10" s="13">
+      <c r="AP10" s="13">
         <v>5077</v>
       </c>
-      <c r="AP10" s="13">
+      <c r="AQ10" s="13">
         <v>4842</v>
       </c>
-      <c r="AQ10" s="13">
+      <c r="AR10" s="13">
         <v>5050</v>
       </c>
-      <c r="AR10" s="13">
+      <c r="AS10" s="13">
         <v>4970</v>
       </c>
-      <c r="AS10" s="13">
+      <c r="AT10" s="13">
         <v>4880</v>
       </c>
-      <c r="AT10" s="13">
+      <c r="AU10" s="13">
         <v>4704</v>
       </c>
-      <c r="AU10" s="13">
+      <c r="AV10" s="13">
         <v>4770</v>
       </c>
-      <c r="AV10" s="13">
+      <c r="AW10" s="13">
         <v>4609</v>
       </c>
-      <c r="AW10" s="13">
+      <c r="AX10" s="13">
         <v>4674</v>
       </c>
-      <c r="AX10" s="13">
+      <c r="AY10" s="13">
         <v>4710</v>
       </c>
-      <c r="AY10" s="13">
+      <c r="AZ10" s="13">
         <v>4688</v>
       </c>
-      <c r="AZ10" s="13">
+      <c r="BA10" s="13">
         <v>4900</v>
       </c>
-      <c r="BA10" s="13">
+      <c r="BB10" s="13">
         <v>5000</v>
       </c>
-      <c r="BB10" s="29">
+      <c r="BC10" s="29">
         <v>4932</v>
       </c>
-      <c r="BC10" s="13"/>
       <c r="BD10" s="13"/>
-      <c r="BE10" s="29"/>
-      <c r="BF10" s="13"/>
+      <c r="BE10" s="13"/>
+      <c r="BF10" s="29"/>
       <c r="BG10" s="13"/>
       <c r="BH10" s="13"/>
       <c r="BI10" s="13"/>
-      <c r="BJ10" s="13">
+      <c r="BJ10" s="13"/>
+      <c r="BK10" s="13">
         <f t="shared" si="0"/>
         <v>-87.859799999999964</v>
       </c>
-      <c r="BK10" s="13">
+      <c r="BL10" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BL10" s="13">
+      <c r="BM10" s="13">
         <f t="shared" si="3"/>
         <v>87.859799999999964</v>
       </c>
-      <c r="BM10" s="13">
-        <f>((BA10-H10)/H10)*100</f>
+      <c r="BN10" s="13">
+        <f>((BB10-H10)/H10)*100</f>
         <v>3.434009102192801</v>
       </c>
-      <c r="BN10">
+      <c r="BO10">
         <v>21</v>
       </c>
-      <c r="BO10">
+      <c r="BP10">
         <v>5252.38</v>
       </c>
-      <c r="BP10" s="15">
-        <f>(BN10*BO10-BN10*H10)/100</f>
+      <c r="BQ10" s="15">
+        <f>(BO10*BP10-BO10*H10)/100</f>
         <v>87.859799999999964</v>
       </c>
     </row>
-    <row r="11" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="11" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A11" s="1">
         <v>1166974</v>
       </c>
@@ -2611,7 +2645,7 @@
       </c>
       <c r="D11" s="6" t="str">
         <f>IF(I11&lt;GEMINI!L11,"למכור בהפסד",IF(I11&gt;GEMINI!M11,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>72</v>
@@ -2626,60 +2660,62 @@
         <v>901.87</v>
       </c>
       <c r="I11" s="13">
+        <v>1109</v>
+      </c>
+      <c r="J11" s="13">
+        <v>1109</v>
+      </c>
+      <c r="K11" s="13">
         <v>1029</v>
       </c>
-      <c r="J11" s="13">
-        <v>1029</v>
-      </c>
-      <c r="K11" s="13">
+      <c r="L11" s="13">
         <v>993</v>
       </c>
-      <c r="L11" s="13">
+      <c r="M11" s="13">
         <v>1017</v>
       </c>
-      <c r="M11" s="13">
+      <c r="N11" s="13">
         <v>960</v>
-      </c>
-      <c r="N11" s="13">
-        <v>965</v>
       </c>
       <c r="O11" s="13">
         <v>965</v>
       </c>
       <c r="P11" s="13">
+        <v>965</v>
+      </c>
+      <c r="Q11" s="13">
         <v>951.7</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="R11" s="13">
         <v>946</v>
       </c>
-      <c r="R11" s="13">
+      <c r="S11" s="13">
         <v>869.2</v>
       </c>
-      <c r="S11" s="13">
+      <c r="T11" s="13">
         <v>865</v>
       </c>
-      <c r="T11" s="13">
+      <c r="U11" s="13">
         <v>851</v>
       </c>
-      <c r="U11" s="13">
+      <c r="V11" s="13">
         <v>829.3</v>
       </c>
-      <c r="V11" s="13">
+      <c r="W11" s="13">
         <v>830</v>
       </c>
-      <c r="W11" s="13">
+      <c r="X11" s="13">
         <v>810</v>
       </c>
-      <c r="X11" s="13">
+      <c r="Y11" s="13">
         <v>812.8</v>
       </c>
-      <c r="Y11" s="13">
+      <c r="Z11" s="13">
         <v>788</v>
       </c>
-      <c r="Z11" s="13">
+      <c r="AA11" s="13">
         <v>772</v>
       </c>
-      <c r="AA11" s="13"/>
       <c r="AB11" s="13"/>
       <c r="AC11" s="13"/>
       <c r="AD11" s="13"/>
@@ -2706,33 +2742,34 @@
       <c r="AY11" s="13"/>
       <c r="AZ11" s="13"/>
       <c r="BA11" s="13"/>
-      <c r="BB11" s="29"/>
-      <c r="BC11" s="13"/>
+      <c r="BB11" s="13"/>
+      <c r="BC11" s="29"/>
       <c r="BD11" s="13"/>
-      <c r="BE11" s="29"/>
-      <c r="BF11" s="13"/>
+      <c r="BE11" s="13"/>
+      <c r="BF11" s="29"/>
       <c r="BG11" s="13"/>
       <c r="BH11" s="13"/>
       <c r="BI11" s="13"/>
-      <c r="BJ11" s="13">
+      <c r="BJ11" s="13"/>
+      <c r="BK11" s="13">
         <f t="shared" si="0"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BK11" s="13">
+      <c r="BL11" s="13">
         <f t="shared" si="2"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BL11" s="13">
+      <c r="BM11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BM11" s="13"/>
-      <c r="BP11" s="15">
-        <f>(BN11*BO11-BN11*H11)/100</f>
+      <c r="BN11" s="13"/>
+      <c r="BQ11" s="15">
+        <f>(BO11*BP11-BO11*H11)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="12" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A12" s="1">
         <v>1176593</v>
       </c>
@@ -2761,66 +2798,68 @@
         <v>22581.42</v>
       </c>
       <c r="I12" s="13">
+        <v>26940</v>
+      </c>
+      <c r="J12" s="13">
+        <v>26940</v>
+      </c>
+      <c r="K12" s="13">
         <v>26800</v>
       </c>
-      <c r="J12" s="13">
-        <v>26800</v>
-      </c>
-      <c r="K12" s="13">
+      <c r="L12" s="13">
         <v>25950</v>
       </c>
-      <c r="L12" s="13">
+      <c r="M12" s="13">
         <v>26000</v>
       </c>
-      <c r="M12" s="13">
+      <c r="N12" s="13">
         <v>26600</v>
-      </c>
-      <c r="N12" s="13">
-        <v>24630</v>
       </c>
       <c r="O12" s="13">
         <v>24630</v>
       </c>
       <c r="P12" s="13">
+        <v>24630</v>
+      </c>
+      <c r="Q12" s="13">
         <v>25230</v>
       </c>
-      <c r="Q12" s="13">
+      <c r="R12" s="13">
         <v>24700</v>
       </c>
-      <c r="R12" s="13">
+      <c r="S12" s="13">
         <v>23780</v>
       </c>
-      <c r="S12" s="13">
+      <c r="T12" s="13">
         <v>23920</v>
       </c>
-      <c r="T12" s="13">
+      <c r="U12" s="13">
         <v>22390</v>
       </c>
-      <c r="U12" s="13">
+      <c r="V12" s="13">
         <v>23000</v>
       </c>
-      <c r="V12" s="13">
+      <c r="W12" s="13">
         <v>20990</v>
       </c>
-      <c r="W12" s="13">
+      <c r="X12" s="13">
         <v>20260</v>
       </c>
-      <c r="X12" s="13">
+      <c r="Y12" s="13">
         <v>19200</v>
       </c>
-      <c r="Y12" s="13">
+      <c r="Z12" s="13">
         <v>19860</v>
       </c>
-      <c r="Z12" s="13">
+      <c r="AA12" s="13">
         <v>19700</v>
       </c>
-      <c r="AA12" s="13">
+      <c r="AB12" s="13">
         <v>19430</v>
       </c>
-      <c r="AB12" s="13">
+      <c r="AC12" s="13">
         <v>19020</v>
       </c>
-      <c r="AC12" s="13"/>
       <c r="AD12" s="13"/>
       <c r="AE12" s="13"/>
       <c r="AF12" s="13"/>
@@ -2845,30 +2884,31 @@
       <c r="AY12" s="13"/>
       <c r="AZ12" s="13"/>
       <c r="BA12" s="13"/>
-      <c r="BB12" s="29"/>
-      <c r="BC12" s="13"/>
+      <c r="BB12" s="13"/>
+      <c r="BC12" s="29"/>
       <c r="BD12" s="13"/>
-      <c r="BE12" s="29"/>
-      <c r="BF12" s="13"/>
+      <c r="BE12" s="13"/>
+      <c r="BF12" s="29"/>
       <c r="BG12" s="13"/>
       <c r="BH12" s="13"/>
       <c r="BI12" s="13"/>
-      <c r="BJ12" s="13">
+      <c r="BJ12" s="13"/>
+      <c r="BK12" s="13">
         <f t="shared" si="0"/>
         <v>1580.6994</v>
       </c>
-      <c r="BK12" s="13">
+      <c r="BL12" s="13">
         <f t="shared" si="2"/>
         <v>1580.6994</v>
       </c>
-      <c r="BL12" s="13"/>
       <c r="BM12" s="13"/>
-      <c r="BP12" s="15">
-        <f t="shared" ref="BP12:BP14" si="4">(BN12*BO12-BN12*H12)/100</f>
+      <c r="BN12" s="13"/>
+      <c r="BQ12" s="15">
+        <f t="shared" ref="BQ12:BQ14" si="4">(BO12*BP12-BO12*H12)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="13" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A13" s="1">
         <v>397018</v>
       </c>
@@ -2891,18 +2931,20 @@
         <v>723</v>
       </c>
       <c r="I13" s="13">
+        <v>980</v>
+      </c>
+      <c r="J13" s="13">
+        <v>980</v>
+      </c>
+      <c r="K13" s="13">
         <v>932.1</v>
       </c>
-      <c r="J13" s="13">
-        <v>932.1</v>
-      </c>
-      <c r="K13" s="13">
+      <c r="L13" s="13">
         <v>822</v>
       </c>
-      <c r="L13" s="13">
+      <c r="M13" s="13">
         <v>790</v>
       </c>
-      <c r="M13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
@@ -2943,30 +2985,31 @@
       <c r="AY13" s="13"/>
       <c r="AZ13" s="13"/>
       <c r="BA13" s="13"/>
-      <c r="BB13" s="29"/>
-      <c r="BC13" s="13"/>
+      <c r="BB13" s="13"/>
+      <c r="BC13" s="29"/>
       <c r="BD13" s="13"/>
-      <c r="BE13" s="29"/>
-      <c r="BF13" s="13"/>
+      <c r="BE13" s="13"/>
+      <c r="BF13" s="29"/>
       <c r="BG13" s="13"/>
       <c r="BH13" s="13"/>
       <c r="BI13" s="13"/>
-      <c r="BJ13" s="13">
+      <c r="BJ13" s="13"/>
+      <c r="BK13" s="13">
         <f t="shared" si="0"/>
         <v>816.99</v>
       </c>
-      <c r="BK13" s="13">
+      <c r="BL13" s="13">
         <f t="shared" si="2"/>
         <v>816.99</v>
       </c>
-      <c r="BL13" s="13"/>
       <c r="BM13" s="13"/>
-      <c r="BP13" s="15">
+      <c r="BN13" s="13"/>
+      <c r="BQ13" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="14" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A14" s="1">
         <v>662577</v>
       </c>
@@ -2995,186 +3038,189 @@
         <v>7204.22</v>
       </c>
       <c r="I14" s="13">
+        <v>7710</v>
+      </c>
+      <c r="J14" s="13">
+        <v>7710</v>
+      </c>
+      <c r="K14" s="13">
         <v>7735</v>
       </c>
-      <c r="J14" s="13">
-        <v>7735</v>
-      </c>
-      <c r="K14" s="13">
+      <c r="L14" s="13">
         <v>7725</v>
       </c>
-      <c r="L14" s="13">
+      <c r="M14" s="13">
         <v>7787</v>
       </c>
-      <c r="M14" s="13">
+      <c r="N14" s="13">
         <v>7955</v>
-      </c>
-      <c r="N14" s="13">
-        <v>7627</v>
       </c>
       <c r="O14" s="13">
         <v>7627</v>
       </c>
       <c r="P14" s="13">
+        <v>7627</v>
+      </c>
+      <c r="Q14" s="13">
         <v>7656</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="R14" s="13">
         <v>7507</v>
       </c>
-      <c r="R14" s="13">
+      <c r="S14" s="13">
         <v>7590</v>
       </c>
-      <c r="S14" s="13">
+      <c r="T14" s="13">
         <v>7569</v>
       </c>
-      <c r="T14" s="13">
+      <c r="U14" s="13">
         <v>7269</v>
       </c>
-      <c r="U14" s="13">
+      <c r="V14" s="13">
         <v>7444</v>
       </c>
-      <c r="V14" s="13">
+      <c r="W14" s="13">
         <v>7205</v>
       </c>
-      <c r="W14" s="13">
+      <c r="X14" s="13">
         <v>7298</v>
       </c>
-      <c r="X14" s="13">
+      <c r="Y14" s="13">
         <v>7222</v>
       </c>
-      <c r="Y14" s="13">
+      <c r="Z14" s="13">
         <v>7079</v>
       </c>
-      <c r="Z14" s="13">
+      <c r="AA14" s="13">
         <v>7140</v>
       </c>
-      <c r="AA14" s="13">
+      <c r="AB14" s="13">
         <v>7440</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AC14" s="13">
         <v>7530</v>
-      </c>
-      <c r="AC14" s="13">
-        <v>7535</v>
       </c>
       <c r="AD14" s="13">
         <v>7535</v>
       </c>
       <c r="AE14" s="13">
+        <v>7535</v>
+      </c>
+      <c r="AF14" s="13">
         <v>7568</v>
       </c>
-      <c r="AF14" s="13">
+      <c r="AG14" s="13">
         <v>7699</v>
       </c>
-      <c r="AG14" s="13">
+      <c r="AH14" s="13">
         <v>7638</v>
       </c>
-      <c r="AH14" s="13">
+      <c r="AI14" s="13">
         <v>7654</v>
       </c>
-      <c r="AI14" s="13">
+      <c r="AJ14" s="13">
         <v>7584</v>
       </c>
-      <c r="AJ14" s="13">
+      <c r="AK14" s="13">
         <v>7479</v>
       </c>
-      <c r="AK14" s="13">
+      <c r="AL14" s="13">
         <v>7490</v>
       </c>
-      <c r="AL14" s="13">
+      <c r="AM14" s="13">
         <v>7480</v>
       </c>
-      <c r="AM14" s="13">
+      <c r="AN14" s="13">
         <v>7270</v>
       </c>
-      <c r="AN14" s="13">
+      <c r="AO14" s="13">
         <v>7163</v>
       </c>
-      <c r="AO14" s="13">
+      <c r="AP14" s="13">
         <v>7231</v>
-      </c>
-      <c r="AP14" s="13">
-        <v>7100</v>
       </c>
       <c r="AQ14" s="13">
         <v>7100</v>
       </c>
       <c r="AR14" s="13">
+        <v>7100</v>
+      </c>
+      <c r="AS14" s="13">
         <v>7027</v>
       </c>
-      <c r="AS14" s="13">
+      <c r="AT14" s="13">
         <v>6984</v>
       </c>
-      <c r="AT14" s="13">
+      <c r="AU14" s="13">
         <v>6944</v>
       </c>
-      <c r="AU14" s="13">
+      <c r="AV14" s="13">
         <v>6924</v>
       </c>
-      <c r="AV14" s="13">
+      <c r="AW14" s="13">
         <v>6930</v>
       </c>
-      <c r="AW14" s="13">
+      <c r="AX14" s="13">
         <v>6938</v>
       </c>
-      <c r="AX14" s="13">
+      <c r="AY14" s="13">
         <v>6989</v>
       </c>
-      <c r="AY14" s="13">
+      <c r="AZ14" s="13">
         <v>6871</v>
       </c>
-      <c r="AZ14" s="13">
+      <c r="BA14" s="13">
         <v>6943</v>
       </c>
-      <c r="BA14" s="13">
+      <c r="BB14" s="13">
         <v>7040</v>
       </c>
-      <c r="BB14" s="29">
+      <c r="BC14" s="29">
         <v>6696</v>
       </c>
-      <c r="BC14" s="13">
+      <c r="BD14" s="13">
         <v>6965</v>
       </c>
-      <c r="BD14" s="13">
+      <c r="BE14" s="13">
         <v>6788</v>
       </c>
-      <c r="BE14" s="29">
+      <c r="BF14" s="29">
         <v>6696</v>
       </c>
-      <c r="BF14" s="13">
+      <c r="BG14" s="13">
         <v>6625</v>
       </c>
-      <c r="BG14" s="13">
+      <c r="BH14" s="13">
         <v>6660</v>
       </c>
-      <c r="BH14" s="13">
+      <c r="BI14" s="13">
         <v>6791</v>
       </c>
-      <c r="BI14" s="13">
+      <c r="BJ14" s="13">
         <v>6610</v>
       </c>
-      <c r="BJ14" s="13">
+      <c r="BK14" s="13">
         <f t="shared" si="0"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BK14" s="13">
+      <c r="BL14" s="13">
         <f t="shared" si="2"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BL14" s="13">
-        <f t="shared" ref="BL14" si="5">(BK14-BJ14)</f>
+      <c r="BM14" s="13">
+        <f t="shared" ref="BM14" si="5">(BL14-BK14)</f>
         <v>0</v>
       </c>
-      <c r="BM14" s="13">
-        <f>((BA14-H14)/H14)*100</f>
+      <c r="BN14" s="13">
+        <f>((BB14-H14)/H14)*100</f>
         <v>-2.2794972946411995</v>
       </c>
-      <c r="BP14" s="15">
+      <c r="BQ14" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="15" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A15" s="1">
         <v>5137534</v>
       </c>
@@ -3203,54 +3249,56 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
+        <v>14358.25</v>
+      </c>
+      <c r="J15" s="13">
+        <v>14358.25</v>
+      </c>
+      <c r="K15" s="13">
         <v>14385.75</v>
       </c>
-      <c r="J15" s="13">
-        <v>14385.75</v>
-      </c>
-      <c r="K15" s="13">
+      <c r="L15" s="13">
         <v>13880</v>
       </c>
-      <c r="L15" s="13">
+      <c r="M15" s="13">
         <v>13610.62</v>
       </c>
-      <c r="M15" s="13">
+      <c r="N15" s="13">
         <v>13016</v>
       </c>
-      <c r="N15" s="13">
+      <c r="O15" s="13">
         <v>12487.37</v>
       </c>
-      <c r="O15" s="13">
+      <c r="P15" s="13">
         <v>12638.62</v>
       </c>
-      <c r="P15" s="13">
+      <c r="Q15" s="13">
         <v>12533.87</v>
       </c>
-      <c r="Q15" s="13">
+      <c r="R15" s="13">
         <v>11299.5</v>
       </c>
-      <c r="R15" s="13">
+      <c r="S15" s="13">
         <v>11193.12</v>
       </c>
-      <c r="S15" s="13">
+      <c r="T15" s="13">
         <v>11548.62</v>
       </c>
-      <c r="T15" s="13">
+      <c r="U15" s="13">
         <v>11125.62</v>
       </c>
-      <c r="U15" s="13">
+      <c r="V15" s="13">
         <v>10932.12</v>
       </c>
-      <c r="V15" s="13">
+      <c r="W15" s="13">
         <v>11095.62</v>
       </c>
-      <c r="W15" s="13">
+      <c r="X15" s="13">
         <v>10910.58</v>
       </c>
-      <c r="X15" s="13">
+      <c r="Y15" s="13">
         <v>11609.37</v>
       </c>
-      <c r="Y15" s="13"/>
       <c r="Z15" s="13"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="13"/>
@@ -3260,8 +3308,8 @@
       <c r="AF15" s="13"/>
       <c r="AG15" s="13"/>
       <c r="AH15" s="13"/>
-      <c r="AI15" s="14"/>
-      <c r="AJ15" s="13"/>
+      <c r="AI15" s="13"/>
+      <c r="AJ15" s="14"/>
       <c r="AK15" s="13"/>
       <c r="AL15" s="13"/>
       <c r="AM15" s="13"/>
@@ -3279,36 +3327,37 @@
       <c r="AY15" s="13"/>
       <c r="AZ15" s="13"/>
       <c r="BA15" s="13"/>
-      <c r="BB15" s="29"/>
-      <c r="BC15" s="13"/>
+      <c r="BB15" s="13"/>
+      <c r="BC15" s="29"/>
       <c r="BD15" s="13"/>
-      <c r="BE15" s="29"/>
-      <c r="BF15" s="13"/>
+      <c r="BE15" s="13"/>
+      <c r="BF15" s="29"/>
       <c r="BG15" s="13"/>
       <c r="BH15" s="13"/>
       <c r="BI15" s="13"/>
-      <c r="BJ15" s="13">
+      <c r="BJ15" s="13"/>
+      <c r="BK15" s="13">
         <f t="shared" si="0"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BK15" s="13">
+      <c r="BL15" s="13">
         <f t="shared" si="2"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BL15" s="13">
-        <f t="shared" ref="BL15:BL18" si="6">(BK15-BJ15)</f>
+      <c r="BM15" s="13">
+        <f t="shared" ref="BM15:BM18" si="6">(BL15-BK15)</f>
         <v>0</v>
       </c>
-      <c r="BM15" s="13">
-        <f>((BA15-H15)/H15)*100</f>
+      <c r="BN15" s="13">
+        <f>((BB15-H15)/H15)*100</f>
         <v>-100</v>
       </c>
-      <c r="BP15" s="15">
-        <f t="shared" ref="BP15:BP18" si="7">(BN15*BO15-BN15*H15)/100</f>
+      <c r="BQ15" s="15">
+        <f t="shared" ref="BQ15:BQ18" si="7">(BO15*BP15-BO15*H15)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="16" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A16" s="1">
         <v>5135470</v>
       </c>
@@ -3343,186 +3392,189 @@
         <v>219.14</v>
       </c>
       <c r="K16" s="13">
+        <v>219.14</v>
+      </c>
+      <c r="L16" s="13">
         <v>219.3</v>
       </c>
-      <c r="L16" s="13">
+      <c r="M16" s="13">
         <v>222.79</v>
       </c>
-      <c r="M16" s="13">
+      <c r="N16" s="13">
         <v>221.16</v>
       </c>
-      <c r="N16" s="13">
+      <c r="O16" s="13">
         <v>220.66</v>
       </c>
-      <c r="O16" s="13">
+      <c r="P16" s="13">
         <v>222.06</v>
       </c>
-      <c r="P16" s="13">
+      <c r="Q16" s="13">
         <v>218.71</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="R16" s="13">
         <v>216.74</v>
       </c>
-      <c r="R16" s="13">
+      <c r="S16" s="13">
         <v>216.04</v>
-      </c>
-      <c r="S16" s="13">
-        <v>210.69</v>
       </c>
       <c r="T16" s="13">
         <v>210.69</v>
       </c>
       <c r="U16" s="13">
+        <v>210.69</v>
+      </c>
+      <c r="V16" s="13">
         <v>198</v>
       </c>
-      <c r="V16" s="13">
+      <c r="W16" s="13">
         <v>196.74</v>
       </c>
-      <c r="W16" s="13">
+      <c r="X16" s="13">
         <v>192.56</v>
       </c>
-      <c r="X16" s="13">
+      <c r="Y16" s="13">
         <v>192.23</v>
       </c>
-      <c r="Y16" s="13">
+      <c r="Z16" s="13">
         <v>191.19</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="AA16" s="13">
         <v>193.62</v>
       </c>
-      <c r="AA16" s="13">
+      <c r="AB16" s="13">
         <v>190.75</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AC16" s="13">
         <v>189.06</v>
-      </c>
-      <c r="AC16" s="13">
-        <v>182.73</v>
       </c>
       <c r="AD16" s="13">
         <v>182.73</v>
       </c>
       <c r="AE16" s="13">
+        <v>182.73</v>
+      </c>
+      <c r="AF16" s="13">
         <v>177.92</v>
       </c>
-      <c r="AF16" s="13">
+      <c r="AG16" s="13">
         <v>179.16</v>
       </c>
-      <c r="AG16" s="13">
+      <c r="AH16" s="13">
         <v>179.34</v>
-      </c>
-      <c r="AH16" s="13">
-        <v>176.5</v>
       </c>
       <c r="AI16" s="13">
         <v>176.5</v>
       </c>
       <c r="AJ16" s="13">
+        <v>176.5</v>
+      </c>
+      <c r="AK16" s="13">
         <v>175.93</v>
       </c>
-      <c r="AK16" s="13">
+      <c r="AL16" s="13">
         <v>174.51</v>
       </c>
-      <c r="AL16" s="13">
+      <c r="AM16" s="13">
         <v>173.91</v>
       </c>
-      <c r="AM16" s="13">
+      <c r="AN16" s="13">
         <v>177.1</v>
       </c>
-      <c r="AN16" s="13">
+      <c r="AO16" s="13">
         <v>178.24</v>
       </c>
-      <c r="AO16" s="13">
+      <c r="AP16" s="13">
         <v>176.52</v>
       </c>
-      <c r="AP16" s="13">
+      <c r="AQ16" s="13">
         <v>178.27</v>
       </c>
-      <c r="AQ16" s="13">
+      <c r="AR16" s="13">
         <v>175.29</v>
       </c>
-      <c r="AR16" s="13">
+      <c r="AS16" s="13">
         <v>175.34</v>
       </c>
-      <c r="AS16" s="13">
+      <c r="AT16" s="13">
         <v>174.41</v>
       </c>
-      <c r="AT16" s="13">
+      <c r="AU16" s="13">
         <v>176.22</v>
       </c>
-      <c r="AU16" s="13">
+      <c r="AV16" s="13">
         <v>174</v>
       </c>
-      <c r="AV16" s="13">
+      <c r="AW16" s="13">
         <v>176.35</v>
       </c>
-      <c r="AW16" s="13">
+      <c r="AX16" s="13">
         <v>177.71</v>
       </c>
-      <c r="AX16" s="13">
+      <c r="AY16" s="13">
         <v>180.08</v>
       </c>
-      <c r="AY16" s="13">
+      <c r="AZ16" s="13">
         <v>181.96</v>
       </c>
-      <c r="AZ16" s="13">
+      <c r="BA16" s="13">
         <v>182.9</v>
       </c>
-      <c r="BA16" s="13">
+      <c r="BB16" s="13">
         <v>181.86</v>
       </c>
-      <c r="BB16" s="29">
+      <c r="BC16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BC16" s="13">
+      <c r="BD16" s="13">
         <v>181.07</v>
       </c>
-      <c r="BD16" s="13">
+      <c r="BE16" s="13">
         <v>182.56</v>
       </c>
-      <c r="BE16" s="29">
+      <c r="BF16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BF16" s="13">
+      <c r="BG16" s="13">
         <v>178.86</v>
       </c>
-      <c r="BG16" s="13">
+      <c r="BH16" s="13">
         <v>180.16</v>
       </c>
-      <c r="BH16" s="13">
+      <c r="BI16" s="13">
         <v>179.56</v>
       </c>
-      <c r="BI16" s="13">
+      <c r="BJ16" s="13">
         <v>176.55</v>
       </c>
-      <c r="BJ16" s="13">
+      <c r="BK16" s="13">
         <f t="shared" si="0"/>
         <v>673.09559999999999</v>
       </c>
-      <c r="BK16" s="13">
+      <c r="BL16" s="13">
         <f t="shared" si="2"/>
         <v>551.19000000000005</v>
       </c>
-      <c r="BL16" s="13">
+      <c r="BM16" s="13">
         <f t="shared" si="6"/>
         <v>-121.90559999999994</v>
       </c>
-      <c r="BM16" s="13">
-        <f>((BA16-H16)/H16)*100</f>
+      <c r="BN16" s="13">
+        <f>((BB16-H16)/H16)*100</f>
         <v>-1.0177978555488905</v>
       </c>
-      <c r="BN16">
+      <c r="BO16">
         <v>1864</v>
       </c>
-      <c r="BO16">
+      <c r="BP16">
         <v>177.19</v>
       </c>
-      <c r="BP16" s="15">
+      <c r="BQ16" s="15">
         <f t="shared" si="7"/>
         <v>-121.90559999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="17" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A17" s="1">
         <v>5134135</v>
       </c>
@@ -3557,7 +3609,7 @@
         <v>185.52</v>
       </c>
       <c r="K17" s="13">
-        <v>178.98</v>
+        <v>185.52</v>
       </c>
       <c r="L17" s="13">
         <v>178.98</v>
@@ -3566,7 +3618,7 @@
         <v>178.98</v>
       </c>
       <c r="N17" s="13">
-        <v>170.7</v>
+        <v>178.98</v>
       </c>
       <c r="O17" s="13">
         <v>170.7</v>
@@ -3575,10 +3627,10 @@
         <v>170.7</v>
       </c>
       <c r="Q17" s="13">
+        <v>170.7</v>
+      </c>
+      <c r="R17" s="13">
         <v>170.45</v>
-      </c>
-      <c r="R17" s="13">
-        <v>160.84</v>
       </c>
       <c r="S17" s="13">
         <v>160.84</v>
@@ -3587,15 +3639,17 @@
         <v>160.84</v>
       </c>
       <c r="U17" s="13">
+        <v>160.84</v>
+      </c>
+      <c r="V17" s="13">
         <v>159.02000000000001</v>
-      </c>
-      <c r="V17" s="13">
-        <v>159.65</v>
       </c>
       <c r="W17" s="13">
         <v>159.65</v>
       </c>
-      <c r="X17" s="13"/>
+      <c r="X17" s="13">
+        <v>159.65</v>
+      </c>
       <c r="Y17" s="13"/>
       <c r="Z17" s="13"/>
       <c r="AA17" s="13"/>
@@ -3625,36 +3679,37 @@
       <c r="AY17" s="13"/>
       <c r="AZ17" s="13"/>
       <c r="BA17" s="13"/>
-      <c r="BB17" s="29"/>
-      <c r="BC17" s="13"/>
+      <c r="BB17" s="13"/>
+      <c r="BC17" s="29"/>
       <c r="BD17" s="13"/>
-      <c r="BE17" s="29"/>
-      <c r="BF17" s="13"/>
+      <c r="BE17" s="13"/>
+      <c r="BF17" s="29"/>
       <c r="BG17" s="13"/>
       <c r="BH17" s="13"/>
       <c r="BI17" s="13"/>
-      <c r="BJ17" s="13">
+      <c r="BJ17" s="13"/>
+      <c r="BK17" s="13">
         <f t="shared" si="0"/>
         <v>957.9</v>
       </c>
-      <c r="BK17" s="13">
+      <c r="BL17" s="13">
         <f t="shared" si="2"/>
         <v>957.9</v>
       </c>
-      <c r="BL17" s="13">
-        <f t="shared" ref="BL17" si="8">(BK17-BJ17)</f>
+      <c r="BM17" s="13">
+        <f t="shared" ref="BM17" si="8">(BL17-BK17)</f>
         <v>0</v>
       </c>
-      <c r="BM17" s="13">
-        <f>((BA17-H17)/H17)*100</f>
+      <c r="BN17" s="13">
+        <f>((BB17-H17)/H17)*100</f>
         <v>-100</v>
       </c>
-      <c r="BP17" s="15">
+      <c r="BQ17" s="15">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="18" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A18" s="1">
         <v>1168723</v>
       </c>
@@ -3683,57 +3738,59 @@
         <v>1434</v>
       </c>
       <c r="I18" s="13">
+        <v>1799</v>
+      </c>
+      <c r="J18" s="13">
+        <v>1799</v>
+      </c>
+      <c r="K18" s="13">
         <v>1757</v>
       </c>
-      <c r="J18" s="13">
-        <v>1757</v>
-      </c>
-      <c r="K18" s="13">
+      <c r="L18" s="13">
         <v>1698</v>
       </c>
-      <c r="L18" s="13">
+      <c r="M18" s="13">
         <v>1694</v>
       </c>
-      <c r="M18" s="13">
+      <c r="N18" s="13">
         <v>1671</v>
-      </c>
-      <c r="N18" s="13">
-        <v>1660</v>
       </c>
       <c r="O18" s="13">
         <v>1660</v>
       </c>
       <c r="P18" s="13">
+        <v>1660</v>
+      </c>
+      <c r="Q18" s="13">
         <v>1646</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="R18" s="13">
         <v>1648</v>
       </c>
-      <c r="R18" s="13">
+      <c r="S18" s="13">
         <v>1614</v>
       </c>
-      <c r="S18" s="13">
+      <c r="T18" s="13">
         <v>1626</v>
       </c>
-      <c r="T18" s="13">
+      <c r="U18" s="13">
         <v>1587</v>
       </c>
-      <c r="U18" s="13">
+      <c r="V18" s="13">
         <v>1548</v>
       </c>
-      <c r="V18" s="13">
+      <c r="W18" s="13">
         <v>1500</v>
       </c>
-      <c r="W18" s="13">
+      <c r="X18" s="13">
         <v>1491</v>
       </c>
-      <c r="X18" s="13">
+      <c r="Y18" s="13">
         <v>1444</v>
       </c>
-      <c r="Y18" s="13">
+      <c r="Z18" s="13">
         <v>1431</v>
       </c>
-      <c r="Z18" s="13"/>
       <c r="AA18" s="13"/>
       <c r="AB18" s="13"/>
       <c r="AC18" s="13"/>
@@ -3759,64 +3816,65 @@
       <c r="AW18" s="13"/>
       <c r="AX18" s="13"/>
       <c r="AY18" s="13"/>
-      <c r="AZ18" s="13">
-        <v>1788</v>
-      </c>
+      <c r="AZ18" s="13"/>
       <c r="BA18" s="13">
         <v>1788</v>
       </c>
-      <c r="BB18" s="29">
+      <c r="BB18" s="13">
+        <v>1788</v>
+      </c>
+      <c r="BC18" s="29">
         <v>1780</v>
       </c>
-      <c r="BC18" s="13">
+      <c r="BD18" s="13">
         <v>1814</v>
       </c>
-      <c r="BD18" s="13">
+      <c r="BE18" s="13">
         <v>1794</v>
       </c>
-      <c r="BE18" s="29">
+      <c r="BF18" s="29">
         <v>1780</v>
       </c>
-      <c r="BF18" s="13">
+      <c r="BG18" s="13">
         <v>1772</v>
       </c>
-      <c r="BG18" s="13">
+      <c r="BH18" s="13">
         <v>1798</v>
       </c>
-      <c r="BH18" s="13">
+      <c r="BI18" s="13">
         <v>1806</v>
       </c>
-      <c r="BI18" s="13">
+      <c r="BJ18" s="13">
         <v>1801</v>
       </c>
-      <c r="BJ18" s="13">
+      <c r="BK18" s="13">
         <f t="shared" si="0"/>
         <v>292.79999999999995</v>
       </c>
-      <c r="BK18" s="13">
+      <c r="BL18" s="13">
         <f t="shared" si="2"/>
         <v>645.29999999999995</v>
       </c>
-      <c r="BL18" s="13">
+      <c r="BM18" s="13">
         <f t="shared" si="6"/>
         <v>352.5</v>
       </c>
-      <c r="BM18" s="13">
-        <f>((BA18-H18)/H18)*100</f>
+      <c r="BN18" s="13">
+        <f>((BB18-H18)/H18)*100</f>
         <v>24.686192468619247</v>
       </c>
-      <c r="BN18">
+      <c r="BO18">
         <v>100</v>
       </c>
-      <c r="BO18">
+      <c r="BP18">
         <v>1786.5</v>
       </c>
-      <c r="BP18" s="15">
+      <c r="BQ18" s="15">
         <f t="shared" si="7"/>
         <v>352.5</v>
       </c>
     </row>
-    <row r="19" spans="1:68" ht="45" customHeight="1" thickBot="1">
+    <row r="19" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A19" s="1">
         <v>1146604</v>
       </c>
@@ -3856,22 +3914,22 @@
       <c r="R19" s="13"/>
       <c r="S19" s="13"/>
       <c r="T19" s="13"/>
-      <c r="U19" s="13">
+      <c r="U19" s="13"/>
+      <c r="V19" s="13">
         <v>6461</v>
       </c>
-      <c r="V19" s="13">
+      <c r="W19" s="13">
         <v>6503</v>
       </c>
-      <c r="W19" s="13">
+      <c r="X19" s="13">
         <v>6535</v>
       </c>
-      <c r="X19" s="13">
+      <c r="Y19" s="13">
         <v>6532</v>
       </c>
-      <c r="Y19" s="13">
+      <c r="Z19" s="13">
         <v>6515</v>
       </c>
-      <c r="Z19" s="13"/>
       <c r="AA19" s="13"/>
       <c r="AB19" s="13"/>
       <c r="AC19" s="13"/>
@@ -3899,33 +3957,34 @@
       <c r="AY19" s="13"/>
       <c r="AZ19" s="13"/>
       <c r="BA19" s="13"/>
-      <c r="BB19" s="29"/>
-      <c r="BC19" s="13"/>
+      <c r="BB19" s="13"/>
+      <c r="BC19" s="29"/>
       <c r="BD19" s="13"/>
-      <c r="BE19" s="29"/>
-      <c r="BF19" s="13"/>
+      <c r="BE19" s="13"/>
+      <c r="BF19" s="29"/>
       <c r="BG19" s="13"/>
       <c r="BH19" s="13"/>
       <c r="BI19" s="13"/>
-      <c r="BJ19" s="13">
+      <c r="BJ19" s="13"/>
+      <c r="BK19" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BK19" s="13">
+      <c r="BL19" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BL19" s="13"/>
       <c r="BM19" s="13"/>
-      <c r="BN19">
+      <c r="BN19" s="13"/>
+      <c r="BO19">
         <v>7</v>
       </c>
-      <c r="BO19">
+      <c r="BP19">
         <v>6461</v>
       </c>
-      <c r="BP19" s="15"/>
-    </row>
-    <row r="20" spans="1:68" ht="45" customHeight="1" thickBot="1">
+      <c r="BQ19" s="15"/>
+    </row>
+    <row r="20" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A20" s="1">
         <v>1144807</v>
       </c>
@@ -3960,7 +4019,9 @@
       <c r="M20" s="13">
         <v>3159</v>
       </c>
-      <c r="N20" s="13"/>
+      <c r="N20" s="13">
+        <v>3159</v>
+      </c>
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
@@ -4000,28 +4061,29 @@
       <c r="AY20" s="13"/>
       <c r="AZ20" s="13"/>
       <c r="BA20" s="13"/>
-      <c r="BB20" s="29"/>
-      <c r="BC20" s="13"/>
+      <c r="BB20" s="13"/>
+      <c r="BC20" s="29"/>
       <c r="BD20" s="13"/>
-      <c r="BE20" s="29"/>
-      <c r="BF20" s="13"/>
+      <c r="BE20" s="13"/>
+      <c r="BF20" s="29"/>
       <c r="BG20" s="13"/>
       <c r="BH20" s="13"/>
       <c r="BI20" s="13"/>
-      <c r="BJ20" s="13">
-        <f>(G20*H20)/100-BP20</f>
+      <c r="BJ20" s="13"/>
+      <c r="BK20" s="13">
+        <f>(G20*H20)/100-BQ20</f>
         <v>0</v>
       </c>
-      <c r="BK20" s="13">
+      <c r="BL20" s="13">
         <f>(G20*H20)/100</f>
         <v>0</v>
       </c>
-      <c r="BL20" s="13"/>
       <c r="BM20" s="13"/>
-      <c r="BP20" s="15"/>
-    </row>
-    <row r="21" spans="1:68" ht="14.4" thickBot="1"/>
-    <row r="22" spans="1:68" ht="45" customHeight="1" thickBot="1">
+      <c r="BN20" s="13"/>
+      <c r="BQ20" s="15"/>
+    </row>
+    <row r="21" spans="1:69" ht="14.4" thickBot="1"/>
+    <row r="22" spans="1:69" ht="45" customHeight="1" thickBot="1">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4075,11 +4137,11 @@
       <c r="AY22" s="13"/>
       <c r="AZ22" s="13"/>
       <c r="BA22" s="13"/>
-      <c r="BB22" s="29"/>
-      <c r="BC22" s="13"/>
+      <c r="BB22" s="13"/>
+      <c r="BC22" s="29"/>
       <c r="BD22" s="13"/>
-      <c r="BE22" s="29"/>
-      <c r="BF22" s="13"/>
+      <c r="BE22" s="13"/>
+      <c r="BF22" s="29"/>
       <c r="BG22" s="13"/>
       <c r="BH22" s="13"/>
       <c r="BI22" s="13"/>
@@ -4087,9 +4149,10 @@
       <c r="BK22" s="13"/>
       <c r="BL22" s="13"/>
       <c r="BM22" s="13"/>
-      <c r="BP22" s="15"/>
-    </row>
-    <row r="23" spans="1:68" ht="54.9" customHeight="1" thickBot="1">
+      <c r="BN22" s="13"/>
+      <c r="BQ22" s="15"/>
+    </row>
+    <row r="23" spans="1:69" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4100,55 +4163,55 @@
       <c r="H23" s="13"/>
       <c r="I23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19)/100</f>
-        <v>15699.153</v>
+        <v>16534.023999999998</v>
       </c>
       <c r="J23" s="23">
-        <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19)/100</f>
-        <v>15699.153</v>
+        <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19)/100</f>
+        <v>16534.023999999998</v>
       </c>
       <c r="K23" s="23">
         <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19)/100</f>
-        <v>15345.22</v>
+        <v>16187.433000000001</v>
       </c>
       <c r="L23" s="23">
         <f>(L2*G2+G3*L3+L4*G4+G5*L5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+L13*G13+G14*L14+L15*G15+G16*L16+G17*L17+L18*G18+G19*L19)/100</f>
-        <v>15346.1396</v>
+        <v>15809.632</v>
       </c>
       <c r="M23" s="23">
-        <f>(M3*G3+G4*M4+M5*G5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+G14*M14+M15*G15+G16*M16+M17*G17+G18*M18+G19*M19)/100</f>
-        <v>13565.34</v>
+        <f>(M2*G2+G3*M3+M4*G4+G5*M5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+M13*G13+G14*M14+M15*G15+G16*M16+G17*M17+M18*G18+G19*M19)/100</f>
+        <v>15866.4776</v>
       </c>
       <c r="N23" s="23">
         <f>(N3*G3+G4*N4+N5*G5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+G14*N14+N15*G15+G16*N16+N17*G17+G18*N18+G19*N19)/100</f>
-        <v>13333.0196</v>
+        <v>14073.12</v>
       </c>
       <c r="O23" s="23">
         <f>(O3*G3+G4*O4+O5*G5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+G14*O14+O15*G15+G16*O16+O17*G17+G18*O18+G19*O19)/100</f>
-        <v>13349.319599999999</v>
+        <v>13833.077600000001</v>
       </c>
       <c r="P23" s="23">
         <f>(P3*G3+G4*P4+P5*G5+G6*P6+G7*P7+G8*P8+G9*P9+G10*P10+G11*P11+G12*P12+G14*P14+P15*G15+G16*P16+P17*G17+G18*P18+G19*P19)/100</f>
-        <v>13358.1996</v>
+        <v>13849.3776</v>
       </c>
       <c r="Q23" s="23">
         <f>(Q3*G3+G4*Q4+Q5*G5+G6*Q6+G7*Q7+G8*Q8+G9*Q9+G10*Q10+G11*Q11+G12*Q12+G14*Q14+Q15*G15+G16*Q16+Q17*G17+G18*Q18+G19*Q19)/100</f>
-        <v>12779.14</v>
+        <v>13831.7376</v>
       </c>
       <c r="R23" s="23">
         <f>(R3*G3+G4*R4+R5*G5+G6*R6+G7*R7+G8*R8+G9*R9+G10*R10+G11*R11+G12*R12+G14*R14+R15*G15+G16*R16+R17*G17+G18*R18+G19*R19)/100</f>
-        <v>12576.257600000001</v>
+        <v>13233.88</v>
       </c>
       <c r="S23" s="23">
         <f>(S3*G3+G4*S4+S5*G5+G6*S6+G7*S7+G8*S8+G9*S9+G10*S10+G11*S11+G12*S12+G14*S14+S15*G15+G16*S16+S17*G17+G18*S18+G19*S19)/100</f>
-        <v>10814.2096</v>
+        <v>13029.9056</v>
       </c>
       <c r="T23" s="23">
-        <f>(T5*G5+G6*T6+T7*G7+G8*T8+G9*T9+G10*T10+G11*T11+G12*T12+G14*T14+G20*T20+G15*T15+T16*G16+G17*T17+T18*G18+G19*T19)/100</f>
-        <v>9932.3195999999989</v>
-      </c>
-      <c r="U23" s="23" t="e">
-        <f>(U5*G5+G7*U7+U8*G8+G9*U9+#REF!*#REF!+G10*U10+G11*U11+G12*U12+G14*U14+G19*U19+G20*U20+U6*G6+G15*U15+#REF!*#REF!+G16*U16+G17*U17+U18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*U3+#REF!*#REF!)/100</f>
-        <v>#REF!</v>
+        <f>(T3*G3+G4*T4+T5*G5+G6*T6+G7*T7+G8*T8+G9*T9+G10*T10+G11*T11+G12*T12+G14*T14+T15*G15+G16*T16+T17*G17+G18*T18+G19*T19)/100</f>
+        <v>11265.595600000001</v>
+      </c>
+      <c r="U23" s="23">
+        <f>(U5*G5+G6*U6+U7*G7+G8*U8+G9*U9+G10*U10+G11*U11+G12*U12+G14*U14+G20*U20+G15*U15+U16*G16+G17*U17+U18*G18+G19*U19)/100</f>
+        <v>10392.5196</v>
       </c>
       <c r="V23" s="23" t="e">
         <f>(V5*G5+G7*V7+V8*G8+G9*V9+#REF!*#REF!+G10*V10+G11*V11+G12*V12+G14*V14+G19*V19+G20*V20+V6*G6+G15*V15+#REF!*#REF!+G16*V16+G17*V17+V18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*V3+#REF!*#REF!)/100</f>
@@ -4159,11 +4222,11 @@
         <v>#REF!</v>
       </c>
       <c r="X23" s="23" t="e">
-        <f>(X5*G5+G7*X7+X8*G8+G9*X9+#REF!*#REF!+G10*X10+G11*X11+G12*X12+G14*X14+G19*X19+G20*X20+X6*G6+G15*X15+#REF!*#REF!+G16*X16+G18*X18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*X3+#REF!*#REF!+G4*X4)/100</f>
+        <f>(X5*G5+G7*X7+X8*G8+G9*X9+#REF!*#REF!+G10*X10+G11*X11+G12*X12+G14*X14+G19*X19+G20*X20+X6*G6+G15*X15+#REF!*#REF!+G16*X16+G17*X17+X18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*X3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="Y23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+Y3*G3+#REF!*#REF!+G4*Y4+G5*Y5+G7*Y7+G8*Y8+G9*Y9+#REF!*#REF!+G10*Y10+Y11*G11+G12*Y12+Y14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*Y20+Y6*G6+#REF!*#REF!+G16*Y16+G18*Y18+G19*Y19)/100</f>
+        <f>(Y5*G5+G7*Y7+Y8*G8+G9*Y9+#REF!*#REF!+G10*Y10+G11*Y11+G12*Y12+G14*Y14+G19*Y19+G20*Y20+Y6*G6+G15*Y15+#REF!*#REF!+G16*Y16+G18*Y18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*Y3+#REF!*#REF!+G4*Y4)/100</f>
         <v>#REF!</v>
       </c>
       <c r="Z23" s="23" t="e">
@@ -4171,7 +4234,7 @@
         <v>#REF!</v>
       </c>
       <c r="AA23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AA3*G3+#REF!*#REF!+G4*AA4+G5*AA5+AA7*G7+AA8*G8+AA9*G9+#REF!*#REF!+G10*AA10+AA11*G11+G12*AA12+AA14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AA20+G6*AA6+#REF!*#REF!+G16*AA16+G18*AA18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AA3*G3+#REF!*#REF!+G4*AA4+G5*AA5+G7*AA7+G8*AA8+G9*AA9+#REF!*#REF!+G10*AA10+AA11*G11+G12*AA12+AA14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AA20+AA6*G6+#REF!*#REF!+G16*AA16+G18*AA18+G19*AA19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AB23" s="23" t="e">
@@ -4179,19 +4242,19 @@
         <v>#REF!</v>
       </c>
       <c r="AC23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AC3*G3+#REF!*#REF!+G4*AC4+G8*AC8+AC9*G9+#REF!*#REF!+AC10*G10+G11*AC11+G14*AC14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AC6+#REF!*#REF!+G16*AC16+G18*AC18+G7*AC7+G5*AC5+G12*AC12+G20*AC20)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AC3*G3+#REF!*#REF!+G4*AC4+G5*AC5+AC7*G7+AC8*G8+AC9*G9+#REF!*#REF!+G10*AC10+AC11*G11+G12*AC12+AC14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AC20+G6*AC6+#REF!*#REF!+G16*AC16+G18*AC18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AD23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AD3*G3+#REF!*#REF!+G4*AD4+G8*AD8+AD9*G9+#REF!*#REF!+AD10*G10+G11*AD11+G14*AD14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AD6+#REF!*#REF!+G16*AD16+G18*AD18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AD3*G3+#REF!*#REF!+G4*AD4+G8*AD8+AD9*G9+#REF!*#REF!+AD10*G10+G11*AD11+G14*AD14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AD6+#REF!*#REF!+G16*AD16+G18*AD18+G7*AD7+G5*AD5+G12*AD12+G20*AD20)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AE23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AE3*G3+#REF!*#REF!+G4*AE4+G8*AE8+G9*AE9+#REF!*#REF!+G10*AE10+AE11*G11+AE14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AE6*G6+#REF!*#REF!+G16*AE16+G18*AE18+G19*AE19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AE3*G3+#REF!*#REF!+G4*AE4+G8*AE8+AE9*G9+#REF!*#REF!+AE10*G10+G11*AE11+G14*AE14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AE6+#REF!*#REF!+G16*AE16+G18*AE18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AF23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AF3*G3+#REF!*#REF!+G4*AF4+G8*AF8+AF9*G9+#REF!*#REF!+AF10*G10+G11*AF11+G14*AF14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AF6+#REF!*#REF!+G16*AF16+G18*AF18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AF3*G3+#REF!*#REF!+G4*AF4+G8*AF8+G9*AF9+#REF!*#REF!+G10*AF10+AF11*G11+AF14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AF6*G6+#REF!*#REF!+G16*AF16+G18*AF18+G19*AF19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AG23" s="23" t="e">
@@ -4199,7 +4262,7 @@
         <v>#REF!</v>
       </c>
       <c r="AH23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AH3*G3+#REF!*#REF!+G4*AH4+G8*AH8+AH9*G9+AH10*G10+AH11*G11+G14*AH14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AH6+#REF!*#REF!+G16*AH16+G18*AH18+G19*AH19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AH3*G3+#REF!*#REF!+G4*AH4+G8*AH8+AH9*G9+#REF!*#REF!+AH10*G10+G11*AH11+G14*AH14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AH6+#REF!*#REF!+G16*AH16+G18*AH18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AI23" s="23" t="e">
@@ -4219,19 +4282,19 @@
         <v>#REF!</v>
       </c>
       <c r="AM23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AM3*G3+#REF!*#REF!+G4*AM4+G8*AM8+AM9*G9+AM10*G10+AM11*G11+G14*AM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AM6+#REF!*#REF!+G16*AM16+G18*AM18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AM3*G3+#REF!*#REF!+G4*AM4+G8*AM8+AM9*G9+AM10*G10+AM11*G11+G14*AM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AM6+#REF!*#REF!+G16*AM16+G18*AM18+G19*AM19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AN23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+AN10*G10+AN11*G11+G14*AN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AN6+#REF!*#REF!+G16*AN16+G18*AN18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+AN9*G9+AN10*G10+AN11*G11+G14*AN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AN6+#REF!*#REF!+G16*AN16+G18*AN18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AO23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+G10*AO10+AO11*G11+AO14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AO6*G6+#REF!*#REF!+G16*AO16+G18*AO18+G19*AO19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+AO10*G10+AO11*G11+G14*AO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AO6+#REF!*#REF!+G16*AO16+G18*AO18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AP23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G10*AP10+AP11*G11+AP14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AP6*G6+#REF!*#REF!+G16*AP16+G18*AP18+G19*AP19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+G10*AP10+AP11*G11+AP14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AP6*G6+#REF!*#REF!+G16*AP16+G18*AP18+G19*AP19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AQ23" s="23" t="e">
@@ -4243,7 +4306,7 @@
         <v>#REF!</v>
       </c>
       <c r="AS23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AS3*G3+#REF!*#REF!+G4*AS4+G10*AS10+AS11*G11+AS14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AS6*G6+G16*AS16+G18*AS18+G19*AS19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AS3*G3+#REF!*#REF!+G4*AS4+G10*AS10+AS11*G11+AS14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AS6*G6+#REF!*#REF!+G16*AS16+G18*AS18+G19*AS19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AT23" s="23" t="e">
@@ -4271,15 +4334,15 @@
         <v>#REF!</v>
       </c>
       <c r="AZ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AZ3*G3+#REF!*#REF!+G4*AZ4+G10*AZ10+G11*AZ11+G14*AZ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AZ6+AZ16*G16+G18*AZ18+G19*AZ19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AZ3*G3+#REF!*#REF!+G4*AZ4+G10*AZ10+AZ11*G11+AZ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AZ6*G6+G16*AZ16+G18*AZ18+G19*AZ19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BA23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BA3*G3+#REF!*#REF!+G4*BA4+G10*BA10+G14*BA14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BA6+BA16*G16+G18*BA18+G19*BA19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BA3*G3+#REF!*#REF!+G4*BA4+G10*BA10+G11*BA11+G14*BA14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BA6+BA16*G16+G18*BA18+G19*BA19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BB23" s="23" t="e">
-        <f>(#REF!*#REF!+BB3*G3+G4*BB4+G14*BB14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BB6+BB16*G16+G18*BB18+G19*BB19+G22*BB22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BB3*G3+#REF!*#REF!+G4*BB4+G10*BB10+G14*BB14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BB6+BB16*G16+G18*BB18+G19*BB19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BC23" s="23" t="e">
@@ -4290,16 +4353,16 @@
         <f>(#REF!*#REF!+BD3*G3+G4*BD4+G14*BD14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BD6+BD16*G16+G18*BD18+G19*BD19+G22*BD22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BE23" s="30" t="e">
+      <c r="BE23" s="23" t="e">
         <f>(#REF!*#REF!+BE3*G3+G4*BE4+G14*BE14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BE6+BE16*G16+G18*BE18+G19*BE19+G22*BE22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BF23" s="23" t="e">
+      <c r="BF23" s="30" t="e">
         <f>(#REF!*#REF!+BF3*G3+G4*BF4+G14*BF14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BF6+BF16*G16+G18*BF18+G19*BF19+G22*BF22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BG23" s="23" t="e">
-        <f>(#REF!*#REF!+BG3*G3+G14*BG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BG6+BG16*G16+G18*BG18+G19*BG19+G22*BG22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+BG3*G3+G4*BG4+G14*BG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BG6+BG16*G16+G18*BG18+G19*BG19+G22*BG22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BH23" s="23" t="e">
@@ -4310,15 +4373,20 @@
         <f>(#REF!*#REF!+BI3*G3+G14*BI14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BI6+BI16*G16+G18*BI18+G19*BI19+G22*BI22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BJ23" s="13"/>
+      <c r="BJ23" s="23" t="e">
+        <f>(#REF!*#REF!+BJ3*G3+G14*BJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BJ6+BJ16*G16+G18*BJ18+G19*BJ19+G22*BJ22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <v>#REF!</v>
+      </c>
       <c r="BK23" s="13"/>
       <c r="BL23" s="13"/>
       <c r="BM23" s="13"/>
-      <c r="BP23" s="15">
-        <v>434.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:68" ht="44.25" customHeight="1" thickBot="1">
+      <c r="BN23" s="13"/>
+      <c r="BQ23" s="15">
+        <f>434.9+62.57</f>
+        <v>497.46999999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:69" ht="44.25" customHeight="1" thickBot="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4380,29 +4448,30 @@
       <c r="BG24" s="14"/>
       <c r="BH24" s="14"/>
       <c r="BI24" s="14"/>
-      <c r="BJ24" s="23">
-        <f>SUM(BJ3:BJ20)</f>
-        <v>12545.255000000001</v>
-      </c>
+      <c r="BJ24" s="14"/>
       <c r="BK24" s="23">
-        <f>SUM(BK3:BK20)</f>
-        <v>13102.683200000001</v>
-      </c>
-      <c r="BL24" s="24">
-        <f>BK24-BJ24</f>
-        <v>557.42820000000029</v>
-      </c>
-      <c r="BM24" s="13">
-        <f>((BK24-BJ24)/BJ24)*100</f>
-        <v>4.443338935717132</v>
-      </c>
-      <c r="BP24" s="15">
-        <f>SUM(BP5:BP23)</f>
-        <v>992.32819999999981</v>
-      </c>
-    </row>
-    <row r="25" spans="1:68">
-      <c r="BJ25" s="15">
+        <f>SUM(BK2:BK20)</f>
+        <v>14089.379000000001</v>
+      </c>
+      <c r="BL24" s="23">
+        <f>SUM(BL2:BL20)</f>
+        <v>14352.3832</v>
+      </c>
+      <c r="BM24" s="24">
+        <f>BL24-BK24</f>
+        <v>263.0041999999994</v>
+      </c>
+      <c r="BN24" s="13">
+        <f>((BL24-BK24)/BK24)*100</f>
+        <v>1.8666841171637119</v>
+      </c>
+      <c r="BQ24" s="15">
+        <f>SUM(BQ5:BQ23)</f>
+        <v>760.47419999999988</v>
+      </c>
+    </row>
+    <row r="25" spans="1:69">
+      <c r="BK25" s="15">
         <v>12034.32</v>
       </c>
     </row>
@@ -4525,7 +4594,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>10700</v>
+        <v>11000</v>
       </c>
       <c r="J2" s="25"/>
       <c r="L2" s="32"/>
@@ -4557,7 +4626,7 @@
       <c r="G3" s="17"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1331</v>
+        <v>1373</v>
       </c>
       <c r="J3" s="26"/>
       <c r="L3" s="21">
@@ -4595,7 +4664,7 @@
       <c r="G4" s="17"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6111</v>
+        <v>6680</v>
       </c>
       <c r="J4" s="26"/>
       <c r="L4" s="21">
@@ -4618,11 +4687,11 @@
       </c>
       <c r="C5" s="18">
         <f>'התיק העדכני'!H5</f>
-        <v>525.71</v>
+        <v>615</v>
       </c>
       <c r="D5" s="19">
         <f>'התיק העדכני'!G5</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="E5" s="16">
         <v>650</v>
@@ -4632,7 +4701,7 @@
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>626</v>
+        <v>630.29999999999995</v>
       </c>
       <c r="J5" s="26"/>
       <c r="L5" s="21">
@@ -4669,7 +4738,7 @@
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>3970</v>
+        <v>4238</v>
       </c>
       <c r="J6" s="26"/>
       <c r="L6" s="21">
@@ -4707,7 +4776,7 @@
       <c r="G7" s="18"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3913</v>
+        <v>3928</v>
       </c>
       <c r="J7" s="26"/>
       <c r="L7" s="21">
@@ -4745,7 +4814,7 @@
       <c r="G8" s="18"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>41570</v>
+        <v>40820</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -4782,7 +4851,7 @@
       <c r="G9" s="17"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9924</v>
+        <v>9960</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -4856,7 +4925,7 @@
       <c r="G11" s="18"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1029</v>
+        <v>1109</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -4893,7 +4962,7 @@
       <c r="G12" s="18"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>26800</v>
+        <v>26940</v>
       </c>
       <c r="J12" s="26"/>
       <c r="L12" s="21">
@@ -4927,7 +4996,7 @@
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>932.1</v>
+        <v>980</v>
       </c>
       <c r="J13" s="26"/>
       <c r="L13" s="21"/>
@@ -4959,7 +5028,7 @@
       <c r="G14" s="17"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7735</v>
+        <v>7710</v>
       </c>
       <c r="J14" s="26"/>
       <c r="L14" s="21">
@@ -4997,7 +5066,7 @@
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14385.75</v>
+        <v>14358.25</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
@@ -5111,7 +5180,7 @@
       <c r="G18" s="18"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1757</v>
+        <v>1799</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -5529,7 +5598,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>10700</v>
+        <v>11000</v>
       </c>
       <c r="L2" s="32"/>
       <c r="M2" s="32"/>
@@ -5560,7 +5629,7 @@
       <c r="G3" s="7"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1331</v>
+        <v>1373</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
@@ -5597,7 +5666,7 @@
       <c r="G4" s="7"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6111</v>
+        <v>6680</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+GEMINI!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
@@ -5619,11 +5688,11 @@
       </c>
       <c r="C5" s="18">
         <f>'התיק העדכני'!H5</f>
-        <v>525.71</v>
+        <v>615</v>
       </c>
       <c r="D5" s="19">
         <f>'התיק העדכני'!G5</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="E5" s="16">
         <v>454</v>
@@ -5634,7 +5703,7 @@
       <c r="G5" s="7"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>626</v>
+        <v>630.29999999999995</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
@@ -5671,7 +5740,7 @@
       <c r="G6" s="7"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>3970</v>
+        <v>4238</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
@@ -5708,7 +5777,7 @@
       <c r="G7" s="8"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3913</v>
+        <v>3928</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+GEMINI!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
@@ -5745,7 +5814,7 @@
       <c r="G8" s="8"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>41570</v>
+        <v>40820</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+GEMINI!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -5782,7 +5851,7 @@
       <c r="G9" s="8"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9924</v>
+        <v>9960</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+GEMINI!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -5856,7 +5925,7 @@
       <c r="G11" s="8"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1029</v>
+        <v>1109</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+GEMINI!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -5893,7 +5962,7 @@
       <c r="G12" s="8"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>26800</v>
+        <v>26940</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+GEMINI!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
@@ -5926,7 +5995,7 @@
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>932.1</v>
+        <v>980</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
@@ -5957,7 +6026,7 @@
       <c r="G14" s="7"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7735</v>
+        <v>7710</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
@@ -6031,7 +6100,7 @@
       <c r="G16" s="7"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14385.75</v>
+        <v>14358.25</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
@@ -6138,7 +6207,7 @@
       <c r="G19" s="8"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1757</v>
+        <v>1799</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+GEMINI!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -6329,7 +6398,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>10700</v>
+        <v>11000</v>
       </c>
       <c r="L2" s="32"/>
       <c r="M2" s="32"/>
@@ -6360,7 +6429,7 @@
       <c r="G3" s="10"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1331</v>
+        <v>1373</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
@@ -6397,7 +6466,7 @@
       <c r="G4" s="10"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6111</v>
+        <v>6680</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+GEMINI!E4+DEEPSEEK!E4)/4</f>
@@ -6419,11 +6488,11 @@
       </c>
       <c r="C5" s="18">
         <f>'התיק העדכני'!H5</f>
-        <v>525.71</v>
+        <v>615</v>
       </c>
       <c r="D5" s="19">
         <f>'התיק העדכני'!G5</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="E5" s="16">
         <v>650</v>
@@ -6434,7 +6503,7 @@
       <c r="G5" s="10"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>626</v>
+        <v>630.29999999999995</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
@@ -6471,7 +6540,7 @@
       <c r="G6" s="10"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>3970</v>
+        <v>4238</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
@@ -6508,7 +6577,7 @@
       <c r="G7" s="10"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3913</v>
+        <v>3928</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+GEMINI!E7+DEEPSEEK!E7)/4</f>
@@ -6544,7 +6613,7 @@
       </c>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>41570</v>
+        <v>40820</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+GEMINI!E8+DEEPSEEK!E8)/4</f>
@@ -6580,7 +6649,7 @@
       </c>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9924</v>
+        <v>9960</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+GEMINI!E9+DEEPSEEK!E9)/4</f>
@@ -6652,7 +6721,7 @@
       </c>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1029</v>
+        <v>1109</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+GEMINI!E11+DEEPSEEK!E11)/4</f>
@@ -6689,7 +6758,7 @@
       <c r="G12" s="10"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>26800</v>
+        <v>26940</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+GEMINI!E12+DEEPSEEK!E12)/4</f>
@@ -6726,7 +6795,7 @@
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>932.1</v>
+        <v>980</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
@@ -6757,7 +6826,7 @@
       <c r="G14" s="10"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7735</v>
+        <v>7710</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
@@ -6794,7 +6863,7 @@
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14385.75</v>
+        <v>14358.25</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
@@ -6904,7 +6973,7 @@
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1757</v>
+        <v>1799</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
@@ -7123,7 +7192,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>10700</v>
+        <v>11000</v>
       </c>
       <c r="L2" s="32"/>
       <c r="M2" s="32"/>
@@ -7154,7 +7223,7 @@
       <c r="G3" s="31"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1331</v>
+        <v>1373</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
@@ -7190,7 +7259,7 @@
       </c>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6111</v>
+        <v>6680</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+GEMINI!E4)/4</f>
@@ -7212,11 +7281,11 @@
       </c>
       <c r="C5" s="18">
         <f>'התיק העדכני'!H5</f>
-        <v>525.71</v>
+        <v>615</v>
       </c>
       <c r="D5" s="19">
         <f>'התיק העדכני'!G5</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="E5" s="16">
         <v>650</v>
@@ -7227,7 +7296,7 @@
       <c r="G5" s="31"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>626</v>
+        <v>630.29999999999995</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
@@ -7264,7 +7333,7 @@
       <c r="G6" s="31"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>3970</v>
+        <v>4238</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
@@ -7300,7 +7369,7 @@
       </c>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3913</v>
+        <v>3928</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+GEMINI!E7)/4</f>
@@ -7337,7 +7406,7 @@
       <c r="G8" s="31"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>41570</v>
+        <v>40820</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+GEMINI!E8)/4</f>
@@ -7374,7 +7443,7 @@
       <c r="G9" s="31"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9924</v>
+        <v>9960</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+GEMINI!E9)/4</f>
@@ -7448,7 +7517,7 @@
       <c r="G11" s="31"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1029</v>
+        <v>1109</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+GEMINI!E11)/4</f>
@@ -7485,7 +7554,7 @@
       <c r="G12" s="31"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>26800</v>
+        <v>26940</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+GEMINI!E12)/4</f>
@@ -7518,7 +7587,7 @@
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>932.1</v>
+        <v>980</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
@@ -7549,7 +7618,7 @@
       <c r="G14" s="31"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7735</v>
+        <v>7710</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
@@ -7621,7 +7690,7 @@
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14385.75</v>
+        <v>14358.25</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
@@ -7725,7 +7794,7 @@
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1757</v>
+        <v>1799</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+GEMINI!E19)/4</f>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/673b1203f7e82b27/מסמכים/GitHub/BURSA/BURSA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\BURSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{F8D1803D-9746-4C08-83A2-CD263161045D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{829E538F-0444-48DD-A7DE-CDB627698DD0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239AB4EA-ED33-48B4-A1C0-B7D57BA9AFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
   <sheets>
     <sheet name="התיק העדכני" sheetId="1" r:id="rId1"/>
@@ -24,17 +24,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -352,11 +341,11 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₪&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -365,7 +354,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -416,13 +405,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -558,7 +547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -647,9 +636,6 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -820,9 +806,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא של Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -860,7 +846,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -966,7 +952,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1108,7 +1094,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1117,21 +1103,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86B4639-EF9D-4B16-B2C9-0D5E9C5EEC8B}">
   <dimension ref="A1:BQ25"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="17.59765625" customWidth="1"/>
-    <col min="6" max="6" width="13.296875" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="52" width="14.8984375" customWidth="1"/>
-    <col min="53" max="62" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="5" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="52" width="14.85546875" customWidth="1"/>
+    <col min="53" max="62" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="63" max="63" width="13" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="11" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="7.09765625" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="11.59765625" customWidth="1"/>
+    <col min="66" max="66" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="1" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1340,15 +1326,21 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="2" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>282012</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
+      <c r="B2" s="17">
+        <f>GEMINI!L2</f>
+        <v>10550</v>
+      </c>
+      <c r="C2" s="17">
+        <f>GEMINI!M2</f>
+        <v>12350</v>
+      </c>
       <c r="D2" s="6" t="str">
         <f>IF(I2&lt;GEMINI!L2,"למכור בהפסד",IF(I2&gt;GEMINI!M2,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>95</v>
@@ -1418,10 +1410,10 @@
       <c r="AZ2" s="6"/>
       <c r="BA2" s="6"/>
       <c r="BB2" s="6"/>
-      <c r="BC2" s="33"/>
+      <c r="BC2" s="32"/>
       <c r="BD2" s="6"/>
       <c r="BE2" s="6"/>
-      <c r="BF2" s="33"/>
+      <c r="BF2" s="32"/>
       <c r="BG2" s="6"/>
       <c r="BH2" s="6"/>
       <c r="BI2" s="6"/>
@@ -1440,17 +1432,17 @@
       <c r="BP2" s="25"/>
       <c r="BQ2" s="25"/>
     </row>
-    <row r="3" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="3" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1227552</v>
       </c>
       <c r="B3" s="17">
         <f>GEMINI!L3</f>
-        <v>962</v>
+        <v>1098</v>
       </c>
       <c r="C3" s="17">
         <f>GEMINI!M3</f>
-        <v>1273.75</v>
+        <v>1368.25</v>
       </c>
       <c r="D3" s="6" t="str">
         <f>IF(I3&lt;GEMINI!L3,"למכור בהפסד",IF(I3&gt;GEMINI!M3,"למכור ברווח","לשמור"))</f>
@@ -1565,17 +1557,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="4" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>587014</v>
       </c>
       <c r="B4" s="17">
         <f>GEMINI!L4</f>
-        <v>5621</v>
+        <v>6030.25</v>
       </c>
       <c r="C4" s="17">
         <f>GEMINI!M4</f>
-        <v>6701.5</v>
+        <v>6975.25</v>
       </c>
       <c r="D4" s="6" t="str">
         <f>IF(I4&lt;GEMINI!L4,"למכור בהפסד",IF(I4&gt;GEMINI!M4,"למכור ברווח","לשמור"))</f>
@@ -1690,17 +1682,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="5" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1099787</v>
       </c>
       <c r="B5" s="17">
         <f>GEMINI!L5</f>
-        <v>601</v>
+        <v>607.75</v>
       </c>
       <c r="C5" s="17">
         <f>GEMINI!M5</f>
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="D5" s="6" t="str">
         <f>IF(I5&lt;GEMINI!L5,"למכור בהפסד",IF(I5&gt;GEMINI!M5,"למכור ברווח","לשמור"))</f>
@@ -1826,21 +1818,21 @@
       <c r="BN5" s="13"/>
       <c r="BQ5" s="15"/>
     </row>
-    <row r="6" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="6" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1166768</v>
       </c>
       <c r="B6" s="17">
         <f>GEMINI!L6</f>
-        <v>3340.25</v>
+        <v>3560</v>
       </c>
       <c r="C6" s="17">
         <f>GEMINI!M6</f>
-        <v>4231.75</v>
+        <v>4332.75</v>
       </c>
       <c r="D6" s="6" t="str">
         <f>IF(I6&lt;GEMINI!L6,"למכור בהפסד",IF(I6&gt;GEMINI!M6,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>85</v>
@@ -1958,17 +1950,17 @@
         <v>-6.7</v>
       </c>
     </row>
-    <row r="7" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="7" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1148899</v>
       </c>
       <c r="B7" s="17">
         <f>GEMINI!L7</f>
-        <v>3603.25</v>
+        <v>3663.25</v>
       </c>
       <c r="C7" s="17">
         <f>GEMINI!M7</f>
-        <v>4253</v>
+        <v>4213.25</v>
       </c>
       <c r="D7" s="6" t="str">
         <f>IF(I7&lt;GEMINI!L7,"למכור בהפסד",IF(I7&gt;GEMINI!M7,"למכור ברווח","לשמור"))</f>
@@ -2094,17 +2086,17 @@
       <c r="BN7" s="13"/>
       <c r="BQ7" s="15"/>
     </row>
-    <row r="8" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="8" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1082379</v>
       </c>
       <c r="B8" s="17">
         <f>GEMINI!L8</f>
-        <v>36536.25</v>
+        <v>37884</v>
       </c>
       <c r="C8" s="17">
         <f>GEMINI!M8</f>
-        <v>42975</v>
+        <v>43218.75</v>
       </c>
       <c r="D8" s="6" t="str">
         <f>IF(I8&lt;GEMINI!L8,"למכור בהפסד",IF(I8&gt;GEMINI!M8,"למכור ברווח","לשמור"))</f>
@@ -2266,17 +2258,17 @@
         <v>-48.75</v>
       </c>
     </row>
-    <row r="9" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="9" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>629014</v>
       </c>
       <c r="B9" s="17">
         <f>GEMINI!L9</f>
-        <v>9327.5</v>
+        <v>9481.75</v>
       </c>
       <c r="C9" s="17">
         <f>GEMINI!M9</f>
-        <v>11459.25</v>
+        <v>11139.75</v>
       </c>
       <c r="D9" s="6" t="str">
         <f>IF(I9&lt;GEMINI!L9,"למכור בהפסד",IF(I9&gt;GEMINI!M9,"למכור ברווח","לשמור"))</f>
@@ -2428,7 +2420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="10" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1141464</v>
       </c>
@@ -2438,7 +2430,7 @@
       </c>
       <c r="C10" s="17">
         <f>GEMINI!M10</f>
-        <v>6041.5</v>
+        <v>6091.5</v>
       </c>
       <c r="D10" s="6" t="str">
         <f>IF(I10&lt;GEMINI!L10,"למכור בהפסד",IF(I10&gt;GEMINI!M10,"למכור ברווח","לשמור"))</f>
@@ -2631,21 +2623,21 @@
         <v>87.859799999999964</v>
       </c>
     </row>
-    <row r="11" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="11" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1166974</v>
       </c>
       <c r="B11" s="17">
         <f>GEMINI!L11</f>
-        <v>863.5</v>
+        <v>940.75</v>
       </c>
       <c r="C11" s="17">
         <f>GEMINI!M11</f>
-        <v>1085.5</v>
+        <v>1146.25</v>
       </c>
       <c r="D11" s="6" t="str">
         <f>IF(I11&lt;GEMINI!L11,"למכור בהפסד",IF(I11&gt;GEMINI!M11,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>72</v>
@@ -2769,17 +2761,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="12" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1176593</v>
       </c>
       <c r="B12" s="17">
         <f>GEMINI!L12</f>
-        <v>22573</v>
+        <v>23843.25</v>
       </c>
       <c r="C12" s="17">
         <f>GEMINI!M12</f>
-        <v>27485</v>
+        <v>28496.25</v>
       </c>
       <c r="D12" s="6" t="str">
         <f>IF(I12&lt;GEMINI!L12,"למכור בהפסד",IF(I12&gt;GEMINI!M12,"למכור ברווח","לשמור"))</f>
@@ -2908,15 +2900,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="13" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>397018</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
+      <c r="B13" s="17">
+        <f>GEMINI!L13</f>
+        <v>890</v>
+      </c>
+      <c r="C13" s="17">
+        <f>GEMINI!M13</f>
+        <v>1125</v>
+      </c>
       <c r="D13" s="6" t="str">
         <f>IF(I13&lt;GEMINI!L13,"למכור בהפסד",IF(I13&gt;GEMINI!M13,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>96</v>
@@ -3009,17 +3007,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="14" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>662577</v>
       </c>
       <c r="B14" s="17">
         <f>GEMINI!L14</f>
-        <v>7260.5</v>
+        <v>7315</v>
       </c>
       <c r="C14" s="17">
         <f>GEMINI!M14</f>
-        <v>8564.5</v>
+        <v>8391</v>
       </c>
       <c r="D14" s="6" t="str">
         <f>IF(I14&lt;GEMINI!L14,"למכור בהפסד",IF(I14&gt;GEMINI!M14,"למכור ברווח","לשמור"))</f>
@@ -3220,21 +3218,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="15" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>5137534</v>
       </c>
       <c r="B15" s="17">
         <f>GEMINI!L15</f>
-        <v>11369.25</v>
+        <v>12492.25</v>
       </c>
       <c r="C15" s="17">
         <f>GEMINI!M15</f>
-        <v>14031.25</v>
+        <v>15132.75</v>
       </c>
       <c r="D15" s="6" t="str">
         <f>IF(I15&lt;GEMINI!L15,"למכור בהפסד",IF(I15&gt;GEMINI!M15,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>78</v>
@@ -3249,7 +3247,7 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
-        <v>14358.25</v>
+        <v>14790.87</v>
       </c>
       <c r="J15" s="13">
         <v>14358.25</v>
@@ -3357,17 +3355,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="16" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>5135470</v>
       </c>
       <c r="B16" s="17">
         <f>GEMINI!L16</f>
-        <v>186.25</v>
+        <v>198.5</v>
       </c>
       <c r="C16" s="17">
         <f>GEMINI!M16</f>
-        <v>234.5</v>
+        <v>239.75</v>
       </c>
       <c r="D16" s="6" t="str">
         <f>IF(I16&lt;GEMINI!L16,"למכור בהפסד",IF(I16&gt;GEMINI!M16,"למכור ברווח","לשמור"))</f>
@@ -3574,17 +3572,17 @@
         <v>-121.90559999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="17" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>5134135</v>
       </c>
       <c r="B17" s="17">
         <f>GEMINI!L17</f>
-        <v>161.5</v>
+        <v>170</v>
       </c>
       <c r="C17" s="17">
         <f>GEMINI!M17</f>
-        <v>201.25</v>
+        <v>204</v>
       </c>
       <c r="D17" s="6" t="str">
         <f>IF(I17&lt;GEMINI!L17,"למכור בהפסד",IF(I17&gt;GEMINI!M17,"למכור ברווח","לשמור"))</f>
@@ -3709,17 +3707,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="18" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1168723</v>
       </c>
       <c r="B18" s="17">
         <f>GEMINI!L18</f>
-        <v>1455.5</v>
+        <v>1608.75</v>
       </c>
       <c r="C18" s="17">
         <f>GEMINI!M18</f>
-        <v>1863</v>
+        <v>1928.25</v>
       </c>
       <c r="D18" s="6" t="str">
         <f>IF(I18&lt;GEMINI!L18,"למכור בהפסד",IF(I18&gt;GEMINI!M18,"למכור ברווח","לשמור"))</f>
@@ -3874,7 +3872,7 @@
         <v>352.5</v>
       </c>
     </row>
-    <row r="19" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="19" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1146604</v>
       </c>
@@ -3984,17 +3982,17 @@
       </c>
       <c r="BQ19" s="15"/>
     </row>
-    <row r="20" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="20" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1144807</v>
       </c>
       <c r="B20" s="17">
         <f>GEMINI!L12</f>
-        <v>22573</v>
+        <v>23843.25</v>
       </c>
       <c r="C20" s="17">
         <f>GEMINI!M12</f>
-        <v>27485</v>
+        <v>28496.25</v>
       </c>
       <c r="D20" s="6" t="str">
         <f>IF(I20&lt;GEMINI!L12,"למכור בהפסד",IF(I20&gt;GEMINI!M12,"למכור ברווח","לשמור"))</f>
@@ -4082,8 +4080,8 @@
       <c r="BN20" s="13"/>
       <c r="BQ20" s="15"/>
     </row>
-    <row r="21" spans="1:69" ht="14.4" thickBot="1"/>
-    <row r="22" spans="1:69" ht="45" customHeight="1" thickBot="1">
+    <row r="21" spans="1:69" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4152,7 +4150,7 @@
       <c r="BN22" s="13"/>
       <c r="BQ22" s="15"/>
     </row>
-    <row r="23" spans="1:69" ht="54.9" customHeight="1" thickBot="1">
+    <row r="23" spans="1:69" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4163,11 +4161,11 @@
       <c r="H23" s="13"/>
       <c r="I23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19)/100</f>
-        <v>16534.023999999998</v>
+        <v>16568.633599999997</v>
       </c>
       <c r="J23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19)/100</f>
-        <v>16534.023999999998</v>
+        <v>16568.633599999997</v>
       </c>
       <c r="K23" s="23">
         <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19)/100</f>
@@ -4386,7 +4384,7 @@
         <v>497.46999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:69" ht="44.25" customHeight="1" thickBot="1">
+    <row r="24" spans="1:69" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4470,7 +4468,7 @@
         <v>760.47419999999988</v>
       </c>
     </row>
-    <row r="25" spans="1:69">
+    <row r="25" spans="1:69" x14ac:dyDescent="0.25">
       <c r="BK25" s="15">
         <v>12034.32</v>
       </c>
@@ -4529,17 +4527,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DECD697-7590-4F64-9E15-0FA62A69A078}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.59765625" customWidth="1"/>
-    <col min="2" max="2" width="17.59765625" style="20" customWidth="1"/>
-    <col min="3" max="7" width="17.59765625" customWidth="1"/>
-    <col min="9" max="9" width="17.59765625" customWidth="1"/>
-    <col min="10" max="10" width="9.59765625" customWidth="1"/>
-    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="20" customWidth="1"/>
+    <col min="3" max="7" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>11</v>
       </c>
@@ -4572,7 +4570,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -4589,18 +4587,28 @@
         <f>'התיק העדכני'!G2</f>
         <v>7</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="E2" s="17">
+        <v>10800</v>
+      </c>
+      <c r="F2" s="17">
+        <v>13000</v>
+      </c>
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
         <v>11000</v>
       </c>
       <c r="J2" s="25"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-    </row>
-    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+      <c r="L2" s="21">
+        <f>(E2+CHATGPT!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
+        <v>10550</v>
+      </c>
+      <c r="M2" s="21">
+        <f>(F2+CHATGPT!F2+PERPLIXITY!F2+DEEPSEEK!F2)/4</f>
+        <v>12350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -4621,7 +4629,7 @@
         <v>950</v>
       </c>
       <c r="F3" s="16">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="G3" s="17"/>
       <c r="I3" s="13">
@@ -4631,14 +4639,14 @@
       <c r="J3" s="26"/>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
-        <v>962</v>
+        <v>1098</v>
       </c>
       <c r="M3" s="21">
         <f>(F3+CHATGPT!F3+PERPLIXITY!F3+DEEPSEEK!F3)/4</f>
-        <v>1273.75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>1368.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -4656,10 +4664,10 @@
         <v>20</v>
       </c>
       <c r="E4" s="16">
-        <v>5925</v>
+        <v>5950</v>
       </c>
       <c r="F4" s="16">
-        <v>6600</v>
+        <v>6800</v>
       </c>
       <c r="G4" s="17"/>
       <c r="I4" s="13">
@@ -4669,14 +4677,14 @@
       <c r="J4" s="26"/>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
-        <v>5621</v>
+        <v>6030.25</v>
       </c>
       <c r="M4" s="21">
         <f>(F4+CHATGPT!F4+PERPLIXITY!F4+DEEPSEEK!F4)/4</f>
-        <v>6701.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>6975.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -4697,7 +4705,7 @@
         <v>650</v>
       </c>
       <c r="F5" s="16">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
@@ -4706,14 +4714,14 @@
       <c r="J5" s="26"/>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
-        <v>601</v>
+        <v>607.75</v>
       </c>
       <c r="M5" s="21">
         <f>(F5+CHATGPT!F5+PERPLIXITY!F5+DEEPSEEK!F5)/4</f>
-        <v>772</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -4734,7 +4742,7 @@
         <v>3300</v>
       </c>
       <c r="F6" s="16">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
@@ -4743,14 +4751,14 @@
       <c r="J6" s="26"/>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
-        <v>3340.25</v>
+        <v>3560</v>
       </c>
       <c r="M6" s="21">
         <f>(F6+CHATGPT!F6+PERPLIXITY!F6+DEEPSEEK!F6)/4</f>
-        <v>4231.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>4332.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -4768,10 +4776,10 @@
         <v>70</v>
       </c>
       <c r="E7" s="16">
-        <v>3700</v>
+        <v>3750</v>
       </c>
       <c r="F7" s="16">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="G7" s="18"/>
       <c r="I7" s="13">
@@ -4781,14 +4789,14 @@
       <c r="J7" s="26"/>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
-        <v>3603.25</v>
+        <v>3663.25</v>
       </c>
       <c r="M7" s="21">
         <f>(F7+CHATGPT!F7+PERPLIXITY!F7+DEEPSEEK!F7)/4</f>
-        <v>4253</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>4213.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -4806,10 +4814,10 @@
         <v>2</v>
       </c>
       <c r="E8" s="16">
-        <v>37875</v>
+        <v>38000</v>
       </c>
       <c r="F8" s="16">
-        <v>42000</v>
+        <v>44000</v>
       </c>
       <c r="G8" s="18"/>
       <c r="I8" s="13">
@@ -4818,14 +4826,14 @@
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
-        <v>36536.25</v>
+        <v>37884</v>
       </c>
       <c r="M8" s="21">
         <f>(F8+CHATGPT!F8+PERPLIXITY!F8+DEEPSEEK!F8)/4</f>
-        <v>42975</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>43218.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -4846,7 +4854,7 @@
         <v>9700</v>
       </c>
       <c r="F9" s="16">
-        <v>11000</v>
+        <v>11500</v>
       </c>
       <c r="G9" s="17"/>
       <c r="I9" s="13">
@@ -4855,14 +4863,14 @@
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
-        <v>9327.5</v>
+        <v>9481.75</v>
       </c>
       <c r="M9" s="21">
         <f>(F9+CHATGPT!F9+PERPLIXITY!F9+DEEPSEEK!F9)/4</f>
-        <v>11459.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>11139.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -4883,7 +4891,7 @@
         <v>5150</v>
       </c>
       <c r="F10" s="16">
-        <v>5800</v>
+        <v>6000</v>
       </c>
       <c r="G10" s="18"/>
       <c r="I10" s="13">
@@ -4896,10 +4904,10 @@
       </c>
       <c r="M10" s="21">
         <f>(F10+CHATGPT!F10+PERPLIXITY!F10+DEEPSEEK!F10)/4</f>
-        <v>6041.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>6091.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -4917,10 +4925,10 @@
         <v>80</v>
       </c>
       <c r="E11" s="16">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="F11" s="16">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="G11" s="18"/>
       <c r="I11" s="13">
@@ -4929,14 +4937,14 @@
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
-        <v>863.5</v>
+        <v>940.75</v>
       </c>
       <c r="M11" s="21">
         <f>(F11+CHATGPT!F11+PERPLIXITY!F11+DEEPSEEK!F11)/4</f>
-        <v>1085.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>1146.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -4957,7 +4965,7 @@
         <v>23800</v>
       </c>
       <c r="F12" s="16">
-        <v>27000</v>
+        <v>28000</v>
       </c>
       <c r="G12" s="18"/>
       <c r="I12" s="13">
@@ -4967,14 +4975,14 @@
       <c r="J12" s="26"/>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
-        <v>22573</v>
+        <v>23843.25</v>
       </c>
       <c r="M12" s="21">
         <f>(F12+CHATGPT!F12+PERPLIXITY!F12+DEEPSEEK!F12)/4</f>
-        <v>27485</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>28496.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -4991,18 +4999,28 @@
         <f>'התיק העדכני'!G13</f>
         <v>113</v>
       </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="E13" s="16">
+        <v>890</v>
+      </c>
+      <c r="F13" s="16">
+        <v>1200</v>
+      </c>
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
         <v>980</v>
       </c>
       <c r="J13" s="26"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-    </row>
-    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+      <c r="L13" s="21">
+        <f>(E13+CHATGPT!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
+        <v>890</v>
+      </c>
+      <c r="M13" s="21">
+        <f>(F13+CHATGPT!F13+PERPLIXITY!F13+DEEPSEEK!F13)/4</f>
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -5023,7 +5041,7 @@
         <v>7600</v>
       </c>
       <c r="F14" s="16">
-        <v>8400</v>
+        <v>8500</v>
       </c>
       <c r="G14" s="17"/>
       <c r="I14" s="13">
@@ -5033,14 +5051,14 @@
       <c r="J14" s="26"/>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
-        <v>7260.5</v>
+        <v>7315</v>
       </c>
       <c r="M14" s="21">
         <f>(F14+CHATGPT!F14+PERPLIXITY!F14+DEEPSEEK!F14)/4</f>
-        <v>8564.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>8391</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -5058,27 +5076,27 @@
         <v>8</v>
       </c>
       <c r="E15" s="16">
-        <v>12200</v>
+        <v>12300</v>
       </c>
       <c r="F15" s="16">
-        <v>14000</v>
+        <v>14500</v>
       </c>
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14358.25</v>
+        <v>14790.87</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
-        <v>11369.25</v>
+        <v>12492.25</v>
       </c>
       <c r="M15" s="21">
         <f>(F15+CHATGPT!F15+PERPLIXITY!F15+DEEPSEEK!F15)/4</f>
-        <v>14031.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>15132.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -5099,7 +5117,7 @@
         <v>205</v>
       </c>
       <c r="F16" s="16">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="G16" s="17"/>
       <c r="I16" s="13">
@@ -5109,14 +5127,14 @@
       <c r="J16" s="26"/>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
-        <v>186.25</v>
+        <v>198.5</v>
       </c>
       <c r="M16" s="21">
         <f>(F16+CHATGPT!F16+PERPLIXITY!F16+DEEPSEEK!F16)/4</f>
-        <v>234.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>239.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -5134,10 +5152,10 @@
         <v>600</v>
       </c>
       <c r="E17" s="16">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="F17" s="16">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="G17" s="17"/>
       <c r="I17" s="13">
@@ -5147,14 +5165,14 @@
       <c r="J17" s="26"/>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+DEEPSEEK!E17)/4</f>
-        <v>161.5</v>
+        <v>170</v>
       </c>
       <c r="M17" s="21">
         <f>(F17+CHATGPT!F17+PERPLIXITY!F17+DEEPSEEK!F17)/4</f>
-        <v>201.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -5172,10 +5190,10 @@
         <v>45</v>
       </c>
       <c r="E18" s="16">
-        <v>1580</v>
+        <v>1650</v>
       </c>
       <c r="F18" s="16">
-        <v>1850</v>
+        <v>2000</v>
       </c>
       <c r="G18" s="18"/>
       <c r="I18" s="13">
@@ -5184,14 +5202,14 @@
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
-        <v>1455.5</v>
+        <v>1608.75</v>
       </c>
       <c r="M18" s="21">
         <f>(F18+CHATGPT!F18+PERPLIXITY!F18+DEEPSEEK!F18)/4</f>
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>1928.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>קסם S&amp;P 500 ETF מנוטרלת מט"ח</v>
@@ -5224,7 +5242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5258,7 +5276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5292,7 +5310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5326,7 +5344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5360,7 +5378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5394,7 +5412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5428,7 +5446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5462,7 +5480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5496,7 +5514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17">
         <f>'התיק העדכני'!E20</f>
         <v>0</v>
@@ -5538,15 +5556,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7390F3B9-AE45-44AE-B4DF-D92B58EB94BD}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
-    <col min="3" max="7" width="17.59765625" customWidth="1"/>
-    <col min="9" max="9" width="17.59765625" customWidth="1"/>
-    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
+    <col min="3" max="7" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -5576,7 +5594,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -5593,17 +5611,27 @@
         <f>'התיק העדכני'!G2</f>
         <v>7</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="E2" s="17">
+        <v>10500</v>
+      </c>
+      <c r="F2" s="17">
+        <v>12500</v>
+      </c>
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
         <v>11000</v>
       </c>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-    </row>
-    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+      <c r="L2" s="21">
+        <f>(E2+GEMINI!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
+        <v>10550</v>
+      </c>
+      <c r="M2" s="21">
+        <f>(F2+GEMINI!F2+PERPLIXITY!F2+DEEPSEEK!F2)/4</f>
+        <v>12350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -5621,10 +5649,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="16">
-        <v>848</v>
+        <v>962</v>
       </c>
       <c r="F3" s="16">
-        <v>1170</v>
+        <v>1273</v>
       </c>
       <c r="G3" s="7"/>
       <c r="I3" s="13">
@@ -5633,14 +5661,14 @@
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
-        <v>962</v>
+        <v>1098</v>
       </c>
       <c r="M3" s="21">
         <f>(F3+GEMINI!F3+PERPLIXITY!F3+DEEPSEEK!F3)/4</f>
-        <v>1273.75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>1368.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -5658,10 +5686,10 @@
         <v>20</v>
       </c>
       <c r="E4" s="16">
-        <v>5059</v>
+        <v>5621</v>
       </c>
       <c r="F4" s="16">
-        <v>6806</v>
+        <v>6701</v>
       </c>
       <c r="G4" s="7"/>
       <c r="I4" s="13">
@@ -5670,14 +5698,14 @@
       </c>
       <c r="L4" s="21">
         <f>(E4+GEMINI!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
-        <v>5621</v>
+        <v>6030.25</v>
       </c>
       <c r="M4" s="21">
         <f>(F4+GEMINI!F4+PERPLIXITY!F4+DEEPSEEK!F4)/4</f>
-        <v>6701.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>6975.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -5695,10 +5723,10 @@
         <v>78</v>
       </c>
       <c r="E5" s="16">
-        <v>454</v>
+        <v>601</v>
       </c>
       <c r="F5" s="16">
-        <v>633</v>
+        <v>772</v>
       </c>
       <c r="G5" s="7"/>
       <c r="I5" s="13">
@@ -5707,14 +5735,14 @@
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
-        <v>601</v>
+        <v>607.75</v>
       </c>
       <c r="M5" s="21">
         <f>(F5+GEMINI!F5+PERPLIXITY!F5+DEEPSEEK!F5)/4</f>
-        <v>772</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -5732,10 +5760,10 @@
         <v>15</v>
       </c>
       <c r="E6" s="16">
-        <v>3311</v>
+        <v>3340</v>
       </c>
       <c r="F6" s="16">
-        <v>4377</v>
+        <v>4231</v>
       </c>
       <c r="G6" s="7"/>
       <c r="I6" s="13">
@@ -5744,14 +5772,14 @@
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
-        <v>3340.25</v>
+        <v>3560</v>
       </c>
       <c r="M6" s="21">
         <f>(F6+GEMINI!F6+PERPLIXITY!F6+DEEPSEEK!F6)/4</f>
-        <v>4231.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>4332.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -5769,10 +5797,10 @@
         <v>70</v>
       </c>
       <c r="E7" s="16">
-        <v>3363</v>
+        <v>3603</v>
       </c>
       <c r="F7" s="16">
-        <v>4312</v>
+        <v>4253</v>
       </c>
       <c r="G7" s="8"/>
       <c r="I7" s="13">
@@ -5781,14 +5809,14 @@
       </c>
       <c r="L7" s="21">
         <f>(E7+GEMINI!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
-        <v>3603.25</v>
+        <v>3663.25</v>
       </c>
       <c r="M7" s="21">
         <f>(F7+GEMINI!F7+PERPLIXITY!F7+DEEPSEEK!F7)/4</f>
-        <v>4253</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>4213.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -5806,10 +5834,10 @@
         <v>2</v>
       </c>
       <c r="E8" s="16">
-        <v>34770</v>
+        <v>36536</v>
       </c>
       <c r="F8" s="16">
-        <v>44400</v>
+        <v>42875</v>
       </c>
       <c r="G8" s="8"/>
       <c r="I8" s="13">
@@ -5818,14 +5846,14 @@
       </c>
       <c r="L8" s="21">
         <f>(E8+GEMINI!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
-        <v>36536.25</v>
+        <v>37884</v>
       </c>
       <c r="M8" s="21">
         <f>(F8+GEMINI!F8+PERPLIXITY!F8+DEEPSEEK!F8)/4</f>
-        <v>42975</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>43218.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -5843,10 +5871,10 @@
         <v>5</v>
       </c>
       <c r="E9" s="16">
-        <v>8610</v>
+        <v>9327</v>
       </c>
       <c r="F9" s="16">
-        <v>11837</v>
+        <v>11459</v>
       </c>
       <c r="G9" s="8"/>
       <c r="I9" s="13">
@@ -5855,14 +5883,14 @@
       </c>
       <c r="L9" s="21">
         <f>(E9+GEMINI!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
-        <v>9327.5</v>
+        <v>9481.75</v>
       </c>
       <c r="M9" s="21">
         <f>(F9+GEMINI!F9+PERPLIXITY!F9+DEEPSEEK!F9)/4</f>
-        <v>11459.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>11139.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -5896,10 +5924,10 @@
       </c>
       <c r="M10" s="21">
         <f>(F10+GEMINI!F10+PERPLIXITY!F10+DEEPSEEK!F10)/4</f>
-        <v>6041.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>6091.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -5917,10 +5945,10 @@
         <v>80</v>
       </c>
       <c r="E11" s="16">
-        <v>729</v>
+        <v>863</v>
       </c>
       <c r="F11" s="16">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="G11" s="8"/>
       <c r="I11" s="13">
@@ -5929,14 +5957,14 @@
       </c>
       <c r="L11" s="21">
         <f>(E11+GEMINI!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
-        <v>863.5</v>
+        <v>940.75</v>
       </c>
       <c r="M11" s="21">
         <f>(F11+GEMINI!F11+PERPLIXITY!F11+DEEPSEEK!F11)/4</f>
-        <v>1085.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>1146.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -5954,10 +5982,10 @@
         <v>7</v>
       </c>
       <c r="E12" s="16">
-        <v>19992</v>
+        <v>22573</v>
       </c>
       <c r="F12" s="16">
-        <v>26940</v>
+        <v>27485</v>
       </c>
       <c r="G12" s="8"/>
       <c r="I12" s="13">
@@ -5966,14 +5994,14 @@
       </c>
       <c r="L12" s="21">
         <f>(E12+GEMINI!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
-        <v>22573</v>
+        <v>23843.25</v>
       </c>
       <c r="M12" s="21">
         <f>(F12+GEMINI!F12+PERPLIXITY!F12+DEEPSEEK!F12)/4</f>
-        <v>27485</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>28496.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -5990,17 +6018,27 @@
         <f>'התיק העדכני'!G13</f>
         <v>113</v>
       </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="E13" s="16">
+        <v>890</v>
+      </c>
+      <c r="F13" s="16">
+        <v>1120</v>
+      </c>
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
         <v>980</v>
       </c>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-    </row>
-    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+      <c r="L13" s="21">
+        <f>(E13+GEMINI!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
+        <v>890</v>
+      </c>
+      <c r="M13" s="21">
+        <f>(F13+GEMINI!F13+PERPLIXITY!F13+DEEPSEEK!F13)/4</f>
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -6018,10 +6056,10 @@
         <v>9</v>
       </c>
       <c r="E14" s="16">
-        <v>6642</v>
+        <v>7260</v>
       </c>
       <c r="F14" s="16">
-        <v>8258</v>
+        <v>8564</v>
       </c>
       <c r="G14" s="7"/>
       <c r="I14" s="13">
@@ -6030,14 +6068,14 @@
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
-        <v>7260.5</v>
+        <v>7315</v>
       </c>
       <c r="M14" s="21">
         <f>(F14+GEMINI!F14+PERPLIXITY!F14+DEEPSEEK!F14)/4</f>
-        <v>8564.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>8391</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -6055,26 +6093,26 @@
         <v>8</v>
       </c>
       <c r="E15" s="16">
-        <v>10477</v>
+        <v>11369</v>
       </c>
       <c r="F15" s="16">
-        <v>13925</v>
+        <v>14031</v>
       </c>
       <c r="G15" s="7"/>
       <c r="I15" s="13">
-        <f>'התיק העדכני'!I20</f>
-        <v>3159</v>
+        <f>'התיק העדכני'!I15</f>
+        <v>14790.87</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+GEMINI!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
-        <v>11369.25</v>
+        <v>12492.25</v>
       </c>
       <c r="M15" s="21">
         <f>(F15+GEMINI!F15+PERPLIXITY!F15+DEEPSEEK!F15)/4</f>
-        <v>14031.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>15132.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -6092,26 +6130,26 @@
         <v>300</v>
       </c>
       <c r="E16" s="16">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="F16" s="16">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="G16" s="7"/>
       <c r="I16" s="13">
-        <f>'התיק העדכני'!I15</f>
-        <v>14358.25</v>
+        <f>'התיק העדכני'!I16</f>
+        <v>219.14</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
-        <v>186.25</v>
+        <v>198.5</v>
       </c>
       <c r="M16" s="21">
         <f>(F16+GEMINI!F16+PERPLIXITY!F16+DEEPSEEK!F16)/4</f>
-        <v>234.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>239.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -6129,26 +6167,26 @@
         <v>600</v>
       </c>
       <c r="E17" s="16">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="F17" s="16">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="G17" s="7"/>
       <c r="I17" s="13">
-        <f>'התיק העדכני'!I16</f>
-        <v>219.14</v>
+        <f>'התיק העדכני'!I17</f>
+        <v>185.52</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+GEMINI!E17+PERPLIXITY!E17+DEEPSEEK!E17)/4</f>
-        <v>161.5</v>
+        <v>170</v>
       </c>
       <c r="M17" s="21">
         <f>(F17+GEMINI!F17+PERPLIXITY!F17+DEEPSEEK!F17)/4</f>
-        <v>201.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -6166,26 +6204,26 @@
         <v>45</v>
       </c>
       <c r="E18" s="16">
-        <v>1342</v>
+        <v>1455</v>
       </c>
       <c r="F18" s="16">
-        <v>1852</v>
+        <v>1863</v>
       </c>
       <c r="G18" s="8"/>
       <c r="I18" s="13">
-        <f>'התיק העדכני'!I17</f>
-        <v>185.52</v>
+        <f>'התיק העדכני'!I18</f>
+        <v>1799</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+GEMINI!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
-        <v>1455.5</v>
+        <v>1608.75</v>
       </c>
       <c r="M18" s="21">
         <f>(F18+GEMINI!F18+PERPLIXITY!F18+DEEPSEEK!F18)/4</f>
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>1928.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>קסם S&amp;P 500 ETF מנוטרלת מט"ח</v>
@@ -6206,8 +6244,8 @@
       <c r="F19" s="16"/>
       <c r="G19" s="8"/>
       <c r="I19" s="13">
-        <f>'התיק העדכני'!I18</f>
-        <v>1799</v>
+        <f>'התיק העדכני'!I19</f>
+        <v>0</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+GEMINI!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -6218,7 +6256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -6230,7 +6268,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -6242,7 +6280,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -6254,7 +6292,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -6266,7 +6304,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -6278,7 +6316,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -6290,7 +6328,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -6302,7 +6340,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -6314,7 +6352,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -6334,15 +6372,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88497C0-21A8-47C7-B959-3D6DF74EF6E2}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
-    <col min="3" max="6" width="17.59765625" customWidth="1"/>
-    <col min="9" max="9" width="17.59765625" customWidth="1"/>
-    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
+    <col min="3" max="6" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -6372,7 +6410,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -6393,17 +6431,23 @@
         <v>10500</v>
       </c>
       <c r="F2" s="17">
-        <v>11500</v>
+        <v>12100</v>
       </c>
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
         <v>11000</v>
       </c>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-    </row>
-    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+      <c r="L2" s="21">
+        <f>(E2+CHATGPT!E2+GEMINI!E2+DEEPSEEK!E2)/4</f>
+        <v>10550</v>
+      </c>
+      <c r="M2" s="21">
+        <f>(F2+CHATGPT!F2+GEMINI!F2+DEEPSEEK!F2)/4</f>
+        <v>12350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -6421,10 +6465,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="16">
-        <v>1050</v>
+        <v>1200</v>
       </c>
       <c r="F3" s="16">
-        <v>1375</v>
+        <v>1500</v>
       </c>
       <c r="G3" s="10"/>
       <c r="I3" s="13">
@@ -6433,14 +6477,14 @@
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
-        <v>962</v>
+        <v>1098</v>
       </c>
       <c r="M3" s="21">
         <f>(F3+CHATGPT!F3+GEMINI!F3+DEEPSEEK!F3)/4</f>
-        <v>1273.75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>1368.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -6458,10 +6502,10 @@
         <v>20</v>
       </c>
       <c r="E4" s="16">
-        <v>5700</v>
+        <v>6200</v>
       </c>
       <c r="F4" s="16">
-        <v>6700</v>
+        <v>7200</v>
       </c>
       <c r="G4" s="10"/>
       <c r="I4" s="13">
@@ -6470,14 +6514,14 @@
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+GEMINI!E4+DEEPSEEK!E4)/4</f>
-        <v>5621</v>
+        <v>6030.25</v>
       </c>
       <c r="M4" s="21">
         <f>(F4+CHATGPT!F4+GEMINI!F4+DEEPSEEK!F4)/4</f>
-        <v>6701.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>6975.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -6495,10 +6539,10 @@
         <v>78</v>
       </c>
       <c r="E5" s="16">
-        <v>650</v>
+        <v>585</v>
       </c>
       <c r="F5" s="16">
-        <v>805</v>
+        <v>720</v>
       </c>
       <c r="G5" s="10"/>
       <c r="I5" s="13">
@@ -6507,14 +6551,14 @@
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
-        <v>601</v>
+        <v>607.75</v>
       </c>
       <c r="M5" s="21">
         <f>(F5+CHATGPT!F5+GEMINI!F5+DEEPSEEK!F5)/4</f>
-        <v>772</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -6532,10 +6576,10 @@
         <v>15</v>
       </c>
       <c r="E6" s="16">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="F6" s="16">
-        <v>4050</v>
+        <v>4400</v>
       </c>
       <c r="G6" s="10"/>
       <c r="I6" s="13">
@@ -6544,14 +6588,14 @@
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
-        <v>3340.25</v>
+        <v>3560</v>
       </c>
       <c r="M6" s="21">
         <f>(F6+CHATGPT!F6+GEMINI!F6+DEEPSEEK!F6)/4</f>
-        <v>4231.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>4332.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -6569,7 +6613,7 @@
         <v>70</v>
       </c>
       <c r="E7" s="16">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="F7" s="16">
         <v>4200</v>
@@ -6581,14 +6625,14 @@
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+GEMINI!E7+DEEPSEEK!E7)/4</f>
-        <v>3603.25</v>
+        <v>3663.25</v>
       </c>
       <c r="M7" s="21">
         <f>(F7+CHATGPT!F7+GEMINI!F7+DEEPSEEK!F7)/4</f>
-        <v>4253</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>4213.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -6606,10 +6650,10 @@
         <v>2</v>
       </c>
       <c r="E8" s="16">
-        <v>36500</v>
+        <v>38000</v>
       </c>
       <c r="F8" s="16">
-        <v>42000</v>
+        <v>43000</v>
       </c>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
@@ -6617,14 +6661,14 @@
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+GEMINI!E8+DEEPSEEK!E8)/4</f>
-        <v>36536.25</v>
+        <v>37884</v>
       </c>
       <c r="M8" s="21">
         <f>(F8+CHATGPT!F8+GEMINI!F8+DEEPSEEK!F8)/4</f>
-        <v>42975</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>43218.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -6642,10 +6686,10 @@
         <v>5</v>
       </c>
       <c r="E9" s="16">
-        <v>9500</v>
+        <v>9400</v>
       </c>
       <c r="F9" s="16">
-        <v>11500</v>
+        <v>11000</v>
       </c>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
@@ -6653,14 +6697,14 @@
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+GEMINI!E9+DEEPSEEK!E9)/4</f>
-        <v>9327.5</v>
+        <v>9481.75</v>
       </c>
       <c r="M9" s="21">
         <f>(F9+CHATGPT!F9+GEMINI!F9+DEEPSEEK!F9)/4</f>
-        <v>11459.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>11139.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -6693,10 +6737,10 @@
       </c>
       <c r="M10" s="21">
         <f>(F10+CHATGPT!F10+GEMINI!F10+DEEPSEEK!F10)/4</f>
-        <v>6041.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>6091.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -6714,10 +6758,10 @@
         <v>80</v>
       </c>
       <c r="E11" s="16">
-        <v>920</v>
+        <v>950</v>
       </c>
       <c r="F11" s="16">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
@@ -6725,14 +6769,14 @@
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+GEMINI!E11+DEEPSEEK!E11)/4</f>
-        <v>863.5</v>
+        <v>940.75</v>
       </c>
       <c r="M11" s="21">
         <f>(F11+CHATGPT!F11+GEMINI!F11+DEEPSEEK!F11)/4</f>
-        <v>1085.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>1146.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -6750,10 +6794,10 @@
         <v>7</v>
       </c>
       <c r="E12" s="16">
-        <v>23500</v>
+        <v>24000</v>
       </c>
       <c r="F12" s="16">
-        <v>28000</v>
+        <v>29000</v>
       </c>
       <c r="G12" s="10"/>
       <c r="I12" s="13">
@@ -6762,14 +6806,14 @@
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+GEMINI!E12+DEEPSEEK!E12)/4</f>
-        <v>22573</v>
+        <v>23843.25</v>
       </c>
       <c r="M12" s="21">
         <f>(F12+CHATGPT!F12+GEMINI!F12+DEEPSEEK!F12)/4</f>
-        <v>27485</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>28496.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -6787,20 +6831,26 @@
         <v>113</v>
       </c>
       <c r="E13" s="16">
-        <v>690</v>
+        <v>880</v>
       </c>
       <c r="F13" s="16">
-        <v>780</v>
+        <v>1100</v>
       </c>
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
         <v>980</v>
       </c>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-    </row>
-    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+      <c r="L13" s="21">
+        <f>(E13+CHATGPT!E13+GEMINI!E13+DEEPSEEK!E13)/4</f>
+        <v>890</v>
+      </c>
+      <c r="M13" s="21">
+        <f>(F13+CHATGPT!F13+GEMINI!F13+DEEPSEEK!F13)/4</f>
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -6818,10 +6868,10 @@
         <v>9</v>
       </c>
       <c r="E14" s="16">
-        <v>7400</v>
+        <v>7000</v>
       </c>
       <c r="F14" s="16">
-        <v>8600</v>
+        <v>8300</v>
       </c>
       <c r="G14" s="10"/>
       <c r="I14" s="13">
@@ -6830,14 +6880,14 @@
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
-        <v>7260.5</v>
+        <v>7315</v>
       </c>
       <c r="M14" s="21">
         <f>(F14+CHATGPT!F14+GEMINI!F14+DEEPSEEK!F14)/4</f>
-        <v>8564.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>8391</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -6855,26 +6905,26 @@
         <v>8</v>
       </c>
       <c r="E15" s="16">
-        <v>10800</v>
+        <v>12500</v>
       </c>
       <c r="F15" s="16">
-        <v>13700</v>
+        <v>16000</v>
       </c>
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14358.25</v>
+        <v>14790.87</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
-        <v>11369.25</v>
+        <v>12492.25</v>
       </c>
       <c r="M15" s="21">
         <f>(F15+CHATGPT!F15+GEMINI!F15+DEEPSEEK!F15)/4</f>
-        <v>14031.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>15132.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -6892,10 +6942,10 @@
         <v>300</v>
       </c>
       <c r="E16" s="16">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="F16" s="16">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="G16" s="10"/>
       <c r="I16" s="13">
@@ -6904,14 +6954,14 @@
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+GEMINI!E16+DEEPSEEK!E16)/4</f>
-        <v>186.25</v>
+        <v>198.5</v>
       </c>
       <c r="M16" s="21">
         <f>(F16+CHATGPT!F16+GEMINI!F16+DEEPSEEK!F16)/4</f>
-        <v>234.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>239.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -6929,10 +6979,10 @@
         <v>600</v>
       </c>
       <c r="E17" s="16">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="F17" s="16">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G17" s="10"/>
       <c r="I17" s="13">
@@ -6941,14 +6991,14 @@
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+GEMINI!E17+DEEPSEEK!E17)/4</f>
-        <v>161.5</v>
+        <v>170</v>
       </c>
       <c r="M17" s="21">
         <f>(F17+CHATGPT!F17+GEMINI!F17+DEEPSEEK!F17)/4</f>
-        <v>201.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -6966,10 +7016,10 @@
         <v>45</v>
       </c>
       <c r="E18" s="16">
-        <v>1350</v>
+        <v>1650</v>
       </c>
       <c r="F18" s="16">
-        <v>1850</v>
+        <v>1900</v>
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
@@ -6977,14 +7027,14 @@
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
-        <v>1455.5</v>
+        <v>1608.75</v>
       </c>
       <c r="M18" s="21">
         <f>(F18+CHATGPT!F18+GEMINI!F18+DEEPSEEK!F18)/4</f>
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>1928.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>קסם S&amp;P 500 ETF מנוטרלת מט"ח</v>
@@ -7016,7 +7066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -7028,7 +7078,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -7040,7 +7090,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -7052,7 +7102,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -7064,7 +7114,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -7076,7 +7126,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -7088,7 +7138,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -7100,7 +7150,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -7112,7 +7162,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -7132,16 +7182,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D354D65C-237D-4544-BBD1-8A37190947C4}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
-    <col min="3" max="5" width="17.59765625" customWidth="1"/>
-    <col min="6" max="6" width="20.3984375" customWidth="1"/>
-    <col min="9" max="9" width="17.59765625" customWidth="1"/>
-    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
+    <col min="3" max="5" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -7170,7 +7220,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -7187,17 +7237,27 @@
         <f>'התיק העדכני'!G2</f>
         <v>7</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="E2" s="17">
+        <v>10400</v>
+      </c>
+      <c r="F2" s="17">
+        <v>11800</v>
+      </c>
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
         <v>11000</v>
       </c>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-    </row>
-    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+      <c r="L2" s="21">
+        <f>(E2+CHATGPT!E2+PERPLIXITY!E2+GEMINI!E2)/4</f>
+        <v>10550</v>
+      </c>
+      <c r="M2" s="21">
+        <f>(F2+CHATGPT!F2+PERPLIXITY!F2+GEMINI!F2)/4</f>
+        <v>12350</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -7215,10 +7275,10 @@
         <v>68</v>
       </c>
       <c r="E3" s="16">
-        <v>1000</v>
+        <v>1280</v>
       </c>
       <c r="F3" s="16">
-        <v>1350</v>
+        <v>1450</v>
       </c>
       <c r="G3" s="31"/>
       <c r="I3" s="13">
@@ -7227,14 +7287,14 @@
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
-        <v>962</v>
+        <v>1098</v>
       </c>
       <c r="M3" s="21">
         <f>(F3+CHATGPT!F3+PERPLIXITY!F3+GEMINI!F3)/4</f>
-        <v>1273.75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>1368.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -7252,10 +7312,10 @@
         <v>20</v>
       </c>
       <c r="E4" s="16">
-        <v>5800</v>
+        <v>6350</v>
       </c>
       <c r="F4" s="16">
-        <v>6700</v>
+        <v>7200</v>
       </c>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
@@ -7263,14 +7323,14 @@
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+GEMINI!E4)/4</f>
-        <v>5621</v>
+        <v>6030.25</v>
       </c>
       <c r="M4" s="21">
         <f>(F4+CHATGPT!F4+PERPLIXITY!F4+GEMINI!F4)/4</f>
-        <v>6701.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>6975.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -7288,10 +7348,10 @@
         <v>78</v>
       </c>
       <c r="E5" s="16">
-        <v>650</v>
+        <v>595</v>
       </c>
       <c r="F5" s="16">
-        <v>850</v>
+        <v>730</v>
       </c>
       <c r="G5" s="31"/>
       <c r="I5" s="13">
@@ -7300,14 +7360,14 @@
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
-        <v>601</v>
+        <v>607.75</v>
       </c>
       <c r="M5" s="21">
         <f>(F5+CHATGPT!F5+PERPLIXITY!F5+GEMINI!F5)/4</f>
-        <v>772</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -7325,10 +7385,10 @@
         <v>15</v>
       </c>
       <c r="E6" s="16">
-        <v>3450</v>
+        <v>4000</v>
       </c>
       <c r="F6" s="16">
-        <v>4100</v>
+        <v>4500</v>
       </c>
       <c r="G6" s="31"/>
       <c r="I6" s="13">
@@ -7337,14 +7397,14 @@
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
-        <v>3340.25</v>
+        <v>3560</v>
       </c>
       <c r="M6" s="21">
         <f>(F6+CHATGPT!F6+PERPLIXITY!F6+GEMINI!F6)/4</f>
-        <v>4231.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>4332.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -7362,10 +7422,10 @@
         <v>70</v>
       </c>
       <c r="E7" s="16">
-        <v>3750</v>
+        <v>3800</v>
       </c>
       <c r="F7" s="16">
-        <v>4300</v>
+        <v>4100</v>
       </c>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
@@ -7373,14 +7433,14 @@
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+GEMINI!E7)/4</f>
-        <v>3603.25</v>
+        <v>3663.25</v>
       </c>
       <c r="M7" s="21">
         <f>(F7+CHATGPT!F7+PERPLIXITY!F7+GEMINI!F7)/4</f>
-        <v>4253</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>4213.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -7398,10 +7458,10 @@
         <v>2</v>
       </c>
       <c r="E8" s="16">
-        <v>37000</v>
+        <v>39000</v>
       </c>
       <c r="F8" s="16">
-        <v>43500</v>
+        <v>43000</v>
       </c>
       <c r="G8" s="31"/>
       <c r="I8" s="13">
@@ -7410,14 +7470,14 @@
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+GEMINI!E8)/4</f>
-        <v>36536.25</v>
+        <v>37884</v>
       </c>
       <c r="M8" s="21">
         <f>(F8+CHATGPT!F8+PERPLIXITY!F8+GEMINI!F8)/4</f>
-        <v>42975</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>43218.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -7438,7 +7498,7 @@
         <v>9500</v>
       </c>
       <c r="F9" s="16">
-        <v>11500</v>
+        <v>10600</v>
       </c>
       <c r="G9" s="31"/>
       <c r="I9" s="13">
@@ -7447,14 +7507,14 @@
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+GEMINI!E9)/4</f>
-        <v>9327.5</v>
+        <v>9481.75</v>
       </c>
       <c r="M9" s="21">
         <f>(F9+CHATGPT!F9+PERPLIXITY!F9+GEMINI!F9)/4</f>
-        <v>11459.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>11139.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -7488,10 +7548,10 @@
       </c>
       <c r="M10" s="21">
         <f>(F10+CHATGPT!F10+PERPLIXITY!F10+GEMINI!F10)/4</f>
-        <v>6041.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>6091.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -7509,10 +7569,10 @@
         <v>80</v>
       </c>
       <c r="E11" s="16">
-        <v>900</v>
+        <v>1040</v>
       </c>
       <c r="F11" s="16">
-        <v>1150</v>
+        <v>1200</v>
       </c>
       <c r="G11" s="31"/>
       <c r="I11" s="13">
@@ -7521,14 +7581,14 @@
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+GEMINI!E11)/4</f>
-        <v>863.5</v>
+        <v>940.75</v>
       </c>
       <c r="M11" s="21">
         <f>(F11+CHATGPT!F11+PERPLIXITY!F11+GEMINI!F11)/4</f>
-        <v>1085.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>1146.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -7546,10 +7606,10 @@
         <v>7</v>
       </c>
       <c r="E12" s="16">
-        <v>23000</v>
+        <v>25000</v>
       </c>
       <c r="F12" s="16">
-        <v>28000</v>
+        <v>29500</v>
       </c>
       <c r="G12" s="31"/>
       <c r="I12" s="13">
@@ -7558,14 +7618,14 @@
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+GEMINI!E12)/4</f>
-        <v>22573</v>
+        <v>23843.25</v>
       </c>
       <c r="M12" s="21">
         <f>(F12+CHATGPT!F12+PERPLIXITY!F12+GEMINI!F12)/4</f>
-        <v>27485</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>28496.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -7582,8 +7642,12 @@
         <f>'התיק העדכני'!G13</f>
         <v>113</v>
       </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+      <c r="E13" s="16">
+        <v>900</v>
+      </c>
+      <c r="F13" s="16">
+        <v>1080</v>
+      </c>
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
@@ -7592,7 +7656,7 @@
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
     </row>
-    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -7613,7 +7677,7 @@
         <v>7400</v>
       </c>
       <c r="F14" s="16">
-        <v>9000</v>
+        <v>8200</v>
       </c>
       <c r="G14" s="31"/>
       <c r="I14" s="13">
@@ -7622,14 +7686,14 @@
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
-        <v>7260.5</v>
+        <v>7315</v>
       </c>
       <c r="M14" s="21">
         <f>(F14+CHATGPT!F14+PERPLIXITY!F14+GEMINI!F14)/4</f>
-        <v>8564.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>8391</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -7647,10 +7711,10 @@
         <v>8</v>
       </c>
       <c r="E15" s="16">
-        <v>12000</v>
+        <v>13800</v>
       </c>
       <c r="F15" s="16">
-        <v>14500</v>
+        <v>16000</v>
       </c>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I20</f>
@@ -7658,14 +7722,14 @@
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+PERPLIXITY!E15+GEMINI!E15)/4</f>
-        <v>11369.25</v>
+        <v>12492.25</v>
       </c>
       <c r="M15" s="21">
         <f>(F15+CHATGPT!F15+PERPLIXITY!F15+GEMINI!F15)/4</f>
-        <v>14031.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>15132.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -7683,25 +7747,25 @@
         <v>300</v>
       </c>
       <c r="E16" s="16">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F16" s="16">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14358.25</v>
+        <v>14790.87</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
-        <v>186.25</v>
+        <v>198.5</v>
       </c>
       <c r="M16" s="21">
         <f>(F16+CHATGPT!F16+PERPLIXITY!F16+GEMINI!F16)/4</f>
-        <v>234.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>239.75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -7719,7 +7783,7 @@
         <v>600</v>
       </c>
       <c r="E17" s="16">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F17" s="16">
         <v>200</v>
@@ -7731,14 +7795,14 @@
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+GEMINI!E17)/4</f>
-        <v>161.5</v>
+        <v>170</v>
       </c>
       <c r="M17" s="21">
         <f>(F17+CHATGPT!F17+PERPLIXITY!F17+GEMINI!F17)/4</f>
-        <v>201.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -7756,10 +7820,10 @@
         <v>45</v>
       </c>
       <c r="E18" s="16">
-        <v>1550</v>
+        <v>1680</v>
       </c>
       <c r="F18" s="16">
-        <v>1900</v>
+        <v>1950</v>
       </c>
       <c r="G18" s="31"/>
       <c r="I18" s="13">
@@ -7768,14 +7832,14 @@
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+GEMINI!E18)/4</f>
-        <v>1455.5</v>
+        <v>1608.75</v>
       </c>
       <c r="M18" s="21">
         <f>(F18+CHATGPT!F18+PERPLIXITY!F18+GEMINI!F18)/4</f>
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+        <v>1928.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>קסם S&amp;P 500 ETF מנוטרלת מט"ח</v>
@@ -7805,7 +7869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -7816,7 +7880,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -7828,7 +7892,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -7840,7 +7904,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -7852,7 +7916,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -7864,7 +7928,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -7876,7 +7940,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -7888,7 +7952,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -7900,7 +7964,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\BURSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239AB4EA-ED33-48B4-A1C0-B7D57BA9AFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCFDDED-F4DE-41A7-B300-EC97C54377E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="102">
   <si>
     <t>MTF מחקה אינדקס תעשיה ישראל</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>מחיר 23/01/2026</t>
+  </si>
+  <si>
+    <t>מחיר 26/01/2026</t>
   </si>
 </sst>
 </file>
@@ -1102,22 +1105,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86B4639-EF9D-4B16-B2C9-0D5E9C5EEC8B}">
-  <dimension ref="A1:BQ25"/>
+  <dimension ref="A1:BR25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="17.5703125" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="52" width="14.85546875" customWidth="1"/>
-    <col min="53" max="62" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="13" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="11.5703125" customWidth="1"/>
+    <col min="8" max="53" width="14.85546875" customWidth="1"/>
+    <col min="54" max="63" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="11" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1146,187 +1149,190 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BK1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BL1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BM1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BN1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BO1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="BO1" s="12" t="s">
+      <c r="BP1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="BP1" s="12" t="s">
+      <c r="BQ1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="BQ1" s="12" t="s">
+      <c r="BR1" s="12" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>282012</v>
       </c>
@@ -1355,21 +1361,23 @@
         <v>11000</v>
       </c>
       <c r="I2" s="13">
+        <v>11360</v>
+      </c>
+      <c r="J2" s="13">
+        <v>11360</v>
+      </c>
+      <c r="K2" s="13">
         <v>11000</v>
       </c>
-      <c r="J2" s="13">
-        <v>11000</v>
-      </c>
-      <c r="K2" s="13">
+      <c r="L2" s="13">
         <v>10700</v>
       </c>
-      <c r="L2" s="13">
+      <c r="M2" s="13">
         <v>10400</v>
       </c>
-      <c r="M2" s="13">
+      <c r="N2" s="13">
         <v>11230</v>
       </c>
-      <c r="N2" s="6"/>
       <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
@@ -1410,29 +1418,30 @@
       <c r="AZ2" s="6"/>
       <c r="BA2" s="6"/>
       <c r="BB2" s="6"/>
-      <c r="BC2" s="32"/>
-      <c r="BD2" s="6"/>
+      <c r="BC2" s="6"/>
+      <c r="BD2" s="32"/>
       <c r="BE2" s="6"/>
-      <c r="BF2" s="32"/>
-      <c r="BG2" s="6"/>
+      <c r="BF2" s="6"/>
+      <c r="BG2" s="32"/>
       <c r="BH2" s="6"/>
       <c r="BI2" s="6"/>
       <c r="BJ2" s="6"/>
-      <c r="BK2" s="13">
-        <f>(G2*H2)/100-BQ2</f>
+      <c r="BK2" s="6"/>
+      <c r="BL2" s="13">
+        <f>(G2*H2)/100-BR2</f>
         <v>770</v>
       </c>
-      <c r="BL2" s="13">
+      <c r="BM2" s="13">
         <f>(G2*H2)/100</f>
         <v>770</v>
       </c>
-      <c r="BM2" s="6"/>
       <c r="BN2" s="6"/>
-      <c r="BO2" s="25"/>
+      <c r="BO2" s="6"/>
       <c r="BP2" s="25"/>
       <c r="BQ2" s="25"/>
-    </row>
-    <row r="3" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BR2" s="25"/>
+    </row>
+    <row r="3" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1227552</v>
       </c>
@@ -1446,7 +1455,7 @@
       </c>
       <c r="D3" s="6" t="str">
         <f>IF(I3&lt;GEMINI!L3,"למכור בהפסד",IF(I3&gt;GEMINI!M3,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>88</v>
@@ -1461,39 +1470,41 @@
         <v>1153.6300000000001</v>
       </c>
       <c r="I3" s="13">
+        <v>1348</v>
+      </c>
+      <c r="J3" s="13">
+        <v>1348</v>
+      </c>
+      <c r="K3" s="13">
         <v>1373</v>
       </c>
-      <c r="J3" s="13">
-        <v>1373</v>
-      </c>
-      <c r="K3" s="13">
+      <c r="L3" s="13">
         <v>1331</v>
       </c>
-      <c r="L3" s="13">
+      <c r="M3" s="13">
         <v>1386</v>
       </c>
-      <c r="M3" s="13">
+      <c r="N3" s="13">
         <v>1342</v>
       </c>
-      <c r="N3" s="13">
+      <c r="O3" s="13">
         <v>1250</v>
-      </c>
-      <c r="O3" s="13">
-        <v>1389</v>
       </c>
       <c r="P3" s="13">
         <v>1389</v>
       </c>
       <c r="Q3" s="13">
+        <v>1389</v>
+      </c>
+      <c r="R3" s="13">
         <v>1367</v>
       </c>
-      <c r="R3" s="13">
+      <c r="S3" s="13">
         <v>1026</v>
       </c>
-      <c r="S3" s="13">
+      <c r="T3" s="13">
         <v>949.1</v>
       </c>
-      <c r="T3" s="13"/>
       <c r="U3" s="13"/>
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
@@ -1509,8 +1520,8 @@
       <c r="AG3" s="13"/>
       <c r="AH3" s="13"/>
       <c r="AI3" s="13"/>
-      <c r="AJ3" s="14"/>
-      <c r="AK3" s="13"/>
+      <c r="AJ3" s="13"/>
+      <c r="AK3" s="14"/>
       <c r="AL3" s="13"/>
       <c r="AM3" s="13"/>
       <c r="AN3" s="13"/>
@@ -1528,36 +1539,37 @@
       <c r="AZ3" s="13"/>
       <c r="BA3" s="13"/>
       <c r="BB3" s="13"/>
-      <c r="BC3" s="29"/>
-      <c r="BD3" s="13"/>
+      <c r="BC3" s="13"/>
+      <c r="BD3" s="29"/>
       <c r="BE3" s="13"/>
-      <c r="BF3" s="29"/>
-      <c r="BG3" s="13"/>
+      <c r="BF3" s="13"/>
+      <c r="BG3" s="29"/>
       <c r="BH3" s="13"/>
       <c r="BI3" s="13"/>
       <c r="BJ3" s="13"/>
-      <c r="BK3" s="13">
-        <f>(G3*H3)/100-BQ3</f>
+      <c r="BK3" s="13"/>
+      <c r="BL3" s="13">
+        <f>(G3*H3)/100-BR3</f>
         <v>784.46840000000009</v>
       </c>
-      <c r="BL3" s="13">
+      <c r="BM3" s="13">
         <f>(G3*H3)/100</f>
         <v>784.46840000000009</v>
       </c>
-      <c r="BM3" s="13">
-        <f>(BL3-BK3)</f>
+      <c r="BN3" s="13">
+        <f>(BM3-BL3)</f>
         <v>0</v>
       </c>
-      <c r="BN3" s="13">
-        <f>((BB3-H3)/H3)*100</f>
+      <c r="BO3" s="13">
+        <f>((BC3-H3)/H3)*100</f>
         <v>-100</v>
       </c>
-      <c r="BQ3" s="15">
-        <f>(BO3*BP3-BO3*H3)/100</f>
+      <c r="BR3" s="15">
+        <f>(BP3*BQ3-BP3*H3)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>587014</v>
       </c>
@@ -1571,7 +1583,7 @@
       </c>
       <c r="D4" s="6" t="str">
         <f>IF(I4&lt;GEMINI!L4,"למכור בהפסד",IF(I4&gt;GEMINI!M4,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>33</v>
@@ -1586,39 +1598,41 @@
         <v>5925</v>
       </c>
       <c r="I4" s="13">
+        <v>6979</v>
+      </c>
+      <c r="J4" s="13">
+        <v>6979</v>
+      </c>
+      <c r="K4" s="13">
         <v>6680</v>
       </c>
-      <c r="J4" s="13">
-        <v>6680</v>
-      </c>
-      <c r="K4" s="13">
+      <c r="L4" s="13">
         <v>6111</v>
       </c>
-      <c r="L4" s="13">
+      <c r="M4" s="13">
         <v>6050</v>
       </c>
-      <c r="M4" s="13">
+      <c r="N4" s="13">
         <v>6169</v>
       </c>
-      <c r="N4" s="13">
+      <c r="O4" s="13">
         <v>6300</v>
-      </c>
-      <c r="O4" s="13">
-        <v>6335</v>
       </c>
       <c r="P4" s="13">
         <v>6335</v>
       </c>
       <c r="Q4" s="13">
+        <v>6335</v>
+      </c>
+      <c r="R4" s="13">
         <v>6444</v>
-      </c>
-      <c r="R4" s="13">
-        <v>5749</v>
       </c>
       <c r="S4" s="13">
         <v>5749</v>
       </c>
-      <c r="T4" s="13"/>
+      <c r="T4" s="13">
+        <v>5749</v>
+      </c>
       <c r="U4" s="13"/>
       <c r="V4" s="13"/>
       <c r="W4" s="13"/>
@@ -1653,36 +1667,37 @@
       <c r="AZ4" s="13"/>
       <c r="BA4" s="13"/>
       <c r="BB4" s="13"/>
-      <c r="BC4" s="29"/>
-      <c r="BD4" s="13"/>
+      <c r="BC4" s="13"/>
+      <c r="BD4" s="29"/>
       <c r="BE4" s="13"/>
-      <c r="BF4" s="29"/>
-      <c r="BG4" s="13"/>
+      <c r="BF4" s="13"/>
+      <c r="BG4" s="29"/>
       <c r="BH4" s="13"/>
       <c r="BI4" s="13"/>
       <c r="BJ4" s="13"/>
-      <c r="BK4" s="13">
-        <f>(G4*H4)/100-BQ4</f>
+      <c r="BK4" s="13"/>
+      <c r="BL4" s="13">
+        <f>(G4*H4)/100-BR4</f>
         <v>1185</v>
       </c>
-      <c r="BL4" s="13">
+      <c r="BM4" s="13">
         <f>(G4*H4)/100</f>
         <v>1185</v>
       </c>
-      <c r="BM4" s="13">
-        <f>(BL4-BK4)</f>
+      <c r="BN4" s="13">
+        <f>(BM4-BL4)</f>
         <v>0</v>
       </c>
-      <c r="BN4" s="13">
-        <f>((BB4-H4)/H4)*100</f>
+      <c r="BO4" s="13">
+        <f>((BC4-H4)/H4)*100</f>
         <v>-100</v>
       </c>
-      <c r="BQ4" s="15">
-        <f>(BO4*BP4-BO4*H4)/100</f>
+      <c r="BR4" s="15">
+        <f>(BP4*BQ4-BP4*H4)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1099787</v>
       </c>
@@ -1711,69 +1726,71 @@
         <v>615</v>
       </c>
       <c r="I5" s="13">
+        <v>638.29999999999995</v>
+      </c>
+      <c r="J5" s="13">
+        <v>638.29999999999995</v>
+      </c>
+      <c r="K5" s="13">
         <v>630.29999999999995</v>
       </c>
-      <c r="J5" s="13">
-        <v>630.29999999999995</v>
-      </c>
-      <c r="K5" s="13">
+      <c r="L5" s="13">
         <v>626</v>
       </c>
-      <c r="L5" s="13">
+      <c r="M5" s="13">
         <v>595.4</v>
       </c>
-      <c r="M5" s="13">
+      <c r="N5" s="13">
         <v>667.1</v>
       </c>
-      <c r="N5" s="13">
+      <c r="O5" s="13">
         <v>651</v>
-      </c>
-      <c r="O5" s="13">
-        <v>641.1</v>
       </c>
       <c r="P5" s="13">
         <v>641.1</v>
       </c>
       <c r="Q5" s="13">
+        <v>641.1</v>
+      </c>
+      <c r="R5" s="13">
         <v>607.1</v>
       </c>
-      <c r="R5" s="13">
+      <c r="S5" s="13">
         <v>583</v>
       </c>
-      <c r="S5" s="13">
+      <c r="T5" s="13">
         <v>581.6</v>
       </c>
-      <c r="T5" s="13">
+      <c r="U5" s="13">
         <v>578.70000000000005</v>
       </c>
-      <c r="U5" s="13">
+      <c r="V5" s="13">
         <v>590</v>
       </c>
-      <c r="V5" s="13">
+      <c r="W5" s="13">
         <v>554.70000000000005</v>
       </c>
-      <c r="W5" s="13">
+      <c r="X5" s="13">
         <v>511.8</v>
       </c>
-      <c r="X5" s="13">
+      <c r="Y5" s="13">
         <v>487</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="Z5" s="13">
         <v>478.8</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="AA5" s="13">
         <v>485.5</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AB5" s="13">
         <v>453.4</v>
       </c>
-      <c r="AB5" s="13">
+      <c r="AC5" s="13">
         <v>426.1</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AD5" s="13">
         <v>423.2</v>
       </c>
-      <c r="AD5" s="13"/>
       <c r="AE5" s="13"/>
       <c r="AF5" s="13"/>
       <c r="AG5" s="13"/>
@@ -1798,27 +1815,28 @@
       <c r="AZ5" s="13"/>
       <c r="BA5" s="13"/>
       <c r="BB5" s="13"/>
-      <c r="BC5" s="29"/>
-      <c r="BD5" s="13"/>
+      <c r="BC5" s="13"/>
+      <c r="BD5" s="29"/>
       <c r="BE5" s="13"/>
-      <c r="BF5" s="29"/>
-      <c r="BG5" s="13"/>
+      <c r="BF5" s="13"/>
+      <c r="BG5" s="29"/>
       <c r="BH5" s="13"/>
       <c r="BI5" s="13"/>
       <c r="BJ5" s="13"/>
-      <c r="BK5" s="13">
-        <f t="shared" ref="BK5:BK19" si="0">(G5*H5)/100-BQ5</f>
+      <c r="BK5" s="13"/>
+      <c r="BL5" s="13">
+        <f t="shared" ref="BL5:BL19" si="0">(G5*H5)/100-BR5</f>
         <v>479.7</v>
       </c>
-      <c r="BL5" s="13">
+      <c r="BM5" s="13">
         <f>(G5*H5)/100</f>
         <v>479.7</v>
       </c>
-      <c r="BM5" s="13"/>
       <c r="BN5" s="13"/>
-      <c r="BQ5" s="15"/>
-    </row>
-    <row r="6" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BO5" s="13"/>
+      <c r="BR5" s="15"/>
+    </row>
+    <row r="6" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1166768</v>
       </c>
@@ -1832,7 +1850,7 @@
       </c>
       <c r="D6" s="6" t="str">
         <f>IF(I6&lt;GEMINI!L6,"למכור בהפסד",IF(I6&gt;GEMINI!M6,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>85</v>
@@ -1847,42 +1865,44 @@
         <v>3700</v>
       </c>
       <c r="I6" s="13">
+        <v>4450</v>
+      </c>
+      <c r="J6" s="13">
+        <v>4450</v>
+      </c>
+      <c r="K6" s="13">
         <v>4238</v>
       </c>
-      <c r="J6" s="13">
-        <v>4238</v>
-      </c>
-      <c r="K6" s="13">
+      <c r="L6" s="13">
         <v>3970</v>
       </c>
-      <c r="L6" s="13">
+      <c r="M6" s="13">
         <v>3870</v>
       </c>
-      <c r="M6" s="13">
+      <c r="N6" s="13">
         <v>3805</v>
       </c>
-      <c r="N6" s="13">
+      <c r="O6" s="13">
         <v>3667</v>
-      </c>
-      <c r="O6" s="13">
-        <v>3582</v>
       </c>
       <c r="P6" s="13">
         <v>3582</v>
       </c>
       <c r="Q6" s="13">
+        <v>3582</v>
+      </c>
+      <c r="R6" s="13">
         <v>3570</v>
       </c>
-      <c r="R6" s="13">
+      <c r="S6" s="13">
         <v>3619</v>
       </c>
-      <c r="S6" s="13">
+      <c r="T6" s="13">
         <v>3650</v>
       </c>
-      <c r="T6" s="13">
+      <c r="U6" s="13">
         <v>3720</v>
       </c>
-      <c r="U6" s="13"/>
       <c r="V6" s="13"/>
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
@@ -1916,41 +1936,42 @@
       <c r="AZ6" s="13"/>
       <c r="BA6" s="13"/>
       <c r="BB6" s="13"/>
-      <c r="BC6" s="29"/>
-      <c r="BD6" s="13"/>
+      <c r="BC6" s="13"/>
+      <c r="BD6" s="29"/>
       <c r="BE6" s="13"/>
-      <c r="BF6" s="29"/>
-      <c r="BG6" s="13"/>
+      <c r="BF6" s="13"/>
+      <c r="BG6" s="29"/>
       <c r="BH6" s="13"/>
       <c r="BI6" s="13"/>
-      <c r="BK6" s="13">
-        <f>(G6*H6)/100-BQ6</f>
+      <c r="BJ6" s="13"/>
+      <c r="BL6" s="13">
+        <f>(G6*H6)/100-BR6</f>
         <v>561.70000000000005</v>
       </c>
-      <c r="BL6" s="13">
+      <c r="BM6" s="13">
         <f>(G6*H6)/100</f>
         <v>555</v>
       </c>
-      <c r="BM6" s="13">
-        <f t="shared" ref="BM6" si="1">(BL6-BK6)</f>
+      <c r="BN6" s="13">
+        <f t="shared" ref="BN6" si="1">(BM6-BL6)</f>
         <v>-6.7000000000000455</v>
       </c>
-      <c r="BN6" s="13">
-        <f>((BB6-H6)/H6)*100</f>
+      <c r="BO6" s="13">
+        <f>((BC6-H6)/H6)*100</f>
         <v>-100</v>
       </c>
-      <c r="BO6">
+      <c r="BP6">
         <v>5</v>
       </c>
-      <c r="BP6">
+      <c r="BQ6">
         <v>3566</v>
       </c>
-      <c r="BQ6" s="15">
-        <f>(BO6*BP6-BO6*H6)/100</f>
+      <c r="BR6" s="15">
+        <f>(BP6*BQ6-BP6*H6)/100</f>
         <v>-6.7</v>
       </c>
     </row>
-    <row r="7" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1148899</v>
       </c>
@@ -1979,69 +2000,71 @@
         <v>3585</v>
       </c>
       <c r="I7" s="13">
+        <v>3943</v>
+      </c>
+      <c r="J7" s="13">
+        <v>3943</v>
+      </c>
+      <c r="K7" s="13">
         <v>3928</v>
       </c>
-      <c r="J7" s="13">
-        <v>3928</v>
-      </c>
-      <c r="K7" s="13">
+      <c r="L7" s="13">
         <v>3913</v>
       </c>
-      <c r="L7" s="13">
+      <c r="M7" s="13">
         <v>3860</v>
       </c>
-      <c r="M7" s="13">
+      <c r="N7" s="13">
         <v>3893</v>
       </c>
-      <c r="N7" s="13">
+      <c r="O7" s="13">
         <v>3900</v>
-      </c>
-      <c r="O7" s="13">
-        <v>3842</v>
       </c>
       <c r="P7" s="13">
         <v>3842</v>
       </c>
       <c r="Q7" s="13">
+        <v>3842</v>
+      </c>
+      <c r="R7" s="13">
         <v>3841</v>
       </c>
-      <c r="R7" s="13">
+      <c r="S7" s="13">
         <v>3809</v>
       </c>
-      <c r="S7" s="13">
+      <c r="T7" s="13">
         <v>3810</v>
       </c>
-      <c r="T7" s="13">
+      <c r="U7" s="13">
         <v>3798</v>
       </c>
-      <c r="U7" s="13">
+      <c r="V7" s="13">
         <v>3713</v>
       </c>
-      <c r="V7" s="13">
+      <c r="W7" s="13">
         <v>3657</v>
       </c>
-      <c r="W7" s="13">
+      <c r="X7" s="13">
         <v>3592</v>
       </c>
-      <c r="X7" s="13">
+      <c r="Y7" s="13">
         <v>3621</v>
       </c>
-      <c r="Y7" s="13">
+      <c r="Z7" s="13">
         <v>3572</v>
       </c>
-      <c r="Z7" s="13">
+      <c r="AA7" s="13">
         <v>3580</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="AB7" s="13">
         <v>3569</v>
       </c>
-      <c r="AB7" s="13">
+      <c r="AC7" s="13">
         <v>3659</v>
       </c>
-      <c r="AC7" s="13">
+      <c r="AD7" s="13">
         <v>3656</v>
       </c>
-      <c r="AD7" s="13"/>
       <c r="AE7" s="13"/>
       <c r="AF7" s="13"/>
       <c r="AG7" s="13"/>
@@ -2066,27 +2089,28 @@
       <c r="AZ7" s="13"/>
       <c r="BA7" s="13"/>
       <c r="BB7" s="13"/>
-      <c r="BC7" s="29"/>
-      <c r="BD7" s="13"/>
+      <c r="BC7" s="13"/>
+      <c r="BD7" s="29"/>
       <c r="BE7" s="13"/>
-      <c r="BF7" s="29"/>
-      <c r="BG7" s="13"/>
+      <c r="BF7" s="13"/>
+      <c r="BG7" s="29"/>
       <c r="BH7" s="13"/>
       <c r="BI7" s="13"/>
       <c r="BJ7" s="13"/>
-      <c r="BK7" s="13">
+      <c r="BK7" s="13"/>
+      <c r="BL7" s="13">
         <f t="shared" si="0"/>
         <v>2509.5</v>
       </c>
-      <c r="BL7" s="13">
-        <f t="shared" ref="BL7:BL19" si="2">(G7*H7)/100</f>
+      <c r="BM7" s="13">
+        <f t="shared" ref="BM7:BM19" si="2">(G7*H7)/100</f>
         <v>2509.5</v>
       </c>
-      <c r="BM7" s="13"/>
       <c r="BN7" s="13"/>
-      <c r="BQ7" s="15"/>
-    </row>
-    <row r="8" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BO7" s="13"/>
+      <c r="BR7" s="15"/>
+    </row>
+    <row r="8" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1082379</v>
       </c>
@@ -2115,105 +2139,107 @@
         <v>37875</v>
       </c>
       <c r="I8" s="13">
+        <v>40790</v>
+      </c>
+      <c r="J8" s="13">
+        <v>40790</v>
+      </c>
+      <c r="K8" s="13">
         <v>40820</v>
       </c>
-      <c r="J8" s="13">
-        <v>40820</v>
-      </c>
-      <c r="K8" s="13">
+      <c r="L8" s="13">
         <v>41570</v>
       </c>
-      <c r="L8" s="13">
+      <c r="M8" s="13">
         <v>42050</v>
       </c>
-      <c r="M8" s="13">
+      <c r="N8" s="13">
         <v>39960</v>
       </c>
-      <c r="N8" s="13">
+      <c r="O8" s="13">
         <v>39990</v>
-      </c>
-      <c r="O8" s="13">
-        <v>38680</v>
       </c>
       <c r="P8" s="13">
         <v>38680</v>
       </c>
       <c r="Q8" s="13">
+        <v>38680</v>
+      </c>
+      <c r="R8" s="13">
         <v>37770</v>
       </c>
-      <c r="R8" s="13">
+      <c r="S8" s="13">
         <v>36330</v>
       </c>
-      <c r="S8" s="13">
+      <c r="T8" s="13">
         <v>38680</v>
       </c>
-      <c r="T8" s="13">
+      <c r="U8" s="13">
         <v>39090</v>
       </c>
-      <c r="U8" s="13">
+      <c r="V8" s="13">
         <v>37300</v>
       </c>
-      <c r="V8" s="13">
+      <c r="W8" s="13">
         <v>37650</v>
       </c>
-      <c r="W8" s="13">
+      <c r="X8" s="13">
         <v>37300</v>
       </c>
-      <c r="X8" s="13">
+      <c r="Y8" s="13">
         <v>39450</v>
       </c>
-      <c r="Y8" s="13">
+      <c r="Z8" s="13">
         <v>38390</v>
       </c>
-      <c r="Z8" s="13">
+      <c r="AA8" s="13">
         <v>38800</v>
       </c>
-      <c r="AA8" s="13">
+      <c r="AB8" s="13">
         <v>38510</v>
-      </c>
-      <c r="AB8" s="13">
-        <v>38970</v>
       </c>
       <c r="AC8" s="13">
         <v>38970</v>
       </c>
       <c r="AD8" s="13">
-        <v>37700</v>
+        <v>38970</v>
       </c>
       <c r="AE8" s="13">
         <v>37700</v>
       </c>
       <c r="AF8" s="13">
+        <v>37700</v>
+      </c>
+      <c r="AG8" s="13">
         <v>37750</v>
       </c>
-      <c r="AG8" s="13">
+      <c r="AH8" s="13">
         <v>38430</v>
       </c>
-      <c r="AH8" s="13">
+      <c r="AI8" s="13">
         <v>38250</v>
       </c>
-      <c r="AI8" s="13">
+      <c r="AJ8" s="13">
         <v>40110</v>
       </c>
-      <c r="AJ8" s="13">
+      <c r="AK8" s="13">
         <v>40820</v>
       </c>
-      <c r="AK8" s="13">
+      <c r="AL8" s="13">
         <v>39320</v>
       </c>
-      <c r="AL8" s="13">
+      <c r="AM8" s="13">
         <v>37800</v>
       </c>
-      <c r="AM8" s="13">
+      <c r="AN8" s="13">
         <v>36620</v>
       </c>
-      <c r="AN8" s="13">
+      <c r="AO8" s="13">
         <v>37130</v>
       </c>
-      <c r="AO8" s="13">
+      <c r="AP8" s="13">
         <v>35850</v>
       </c>
-      <c r="AP8" s="13"/>
       <c r="AQ8" s="13"/>
       <c r="AR8" s="13"/>
       <c r="AS8" s="13"/>
@@ -2226,39 +2252,40 @@
       <c r="AZ8" s="13"/>
       <c r="BA8" s="13"/>
       <c r="BB8" s="13"/>
-      <c r="BC8" s="29"/>
-      <c r="BD8" s="13"/>
+      <c r="BC8" s="13"/>
+      <c r="BD8" s="29"/>
       <c r="BE8" s="13"/>
-      <c r="BF8" s="29"/>
-      <c r="BG8" s="13"/>
+      <c r="BF8" s="13"/>
+      <c r="BG8" s="29"/>
       <c r="BH8" s="13"/>
       <c r="BI8" s="13"/>
       <c r="BJ8" s="13"/>
-      <c r="BK8" s="13">
+      <c r="BK8" s="13"/>
+      <c r="BL8" s="13">
         <f t="shared" si="0"/>
         <v>806.25</v>
       </c>
-      <c r="BL8" s="13">
+      <c r="BM8" s="13">
         <f t="shared" si="2"/>
         <v>757.5</v>
       </c>
-      <c r="BM8" s="13">
-        <f t="shared" ref="BM8:BM11" si="3">(BL8-BK8)</f>
+      <c r="BN8" s="13">
+        <f t="shared" ref="BN8:BN11" si="3">(BM8-BL8)</f>
         <v>-48.75</v>
       </c>
-      <c r="BN8" s="13"/>
-      <c r="BO8">
+      <c r="BO8" s="13"/>
+      <c r="BP8">
         <v>3</v>
       </c>
-      <c r="BP8">
+      <c r="BQ8">
         <v>36250</v>
       </c>
-      <c r="BQ8" s="15">
-        <f>(BO8*BP8-BO8*H8)/100</f>
+      <c r="BR8" s="15">
+        <f>(BP8*BQ8-BP8*H8)/100</f>
         <v>-48.75</v>
       </c>
     </row>
-    <row r="9" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>629014</v>
       </c>
@@ -2281,105 +2308,107 @@
         <v>45998</v>
       </c>
       <c r="G9" s="27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H9" s="13">
         <v>9227</v>
       </c>
       <c r="I9" s="13">
+        <v>9910</v>
+      </c>
+      <c r="J9" s="13">
+        <v>9910</v>
+      </c>
+      <c r="K9" s="13">
         <v>9960</v>
       </c>
-      <c r="J9" s="13">
-        <v>9960</v>
-      </c>
-      <c r="K9" s="13">
+      <c r="L9" s="13">
         <v>9924</v>
       </c>
-      <c r="L9" s="13">
+      <c r="M9" s="13">
         <v>9999</v>
       </c>
-      <c r="M9" s="13">
+      <c r="N9" s="13">
         <v>9962</v>
       </c>
-      <c r="N9" s="13">
+      <c r="O9" s="13">
         <v>9979</v>
-      </c>
-      <c r="O9" s="13">
-        <v>10130</v>
       </c>
       <c r="P9" s="13">
         <v>10130</v>
       </c>
       <c r="Q9" s="13">
+        <v>10130</v>
+      </c>
+      <c r="R9" s="13">
         <v>10400</v>
       </c>
-      <c r="R9" s="13">
+      <c r="S9" s="13">
         <v>10320</v>
       </c>
-      <c r="S9" s="13">
+      <c r="T9" s="13">
         <v>10300</v>
       </c>
-      <c r="T9" s="13">
+      <c r="U9" s="13">
         <v>10310</v>
       </c>
-      <c r="U9" s="13">
+      <c r="V9" s="13">
         <v>9672</v>
       </c>
-      <c r="V9" s="13">
+      <c r="W9" s="13">
         <v>9953</v>
       </c>
-      <c r="W9" s="13">
+      <c r="X9" s="13">
         <v>10090</v>
       </c>
-      <c r="X9" s="13">
+      <c r="Y9" s="13">
         <v>10070</v>
       </c>
-      <c r="Y9" s="13">
+      <c r="Z9" s="13">
         <v>10030</v>
       </c>
-      <c r="Z9" s="13">
+      <c r="AA9" s="13">
         <v>10120</v>
       </c>
-      <c r="AA9" s="13">
+      <c r="AB9" s="13">
         <v>10000</v>
       </c>
-      <c r="AB9" s="13">
+      <c r="AC9" s="13">
         <v>10080</v>
       </c>
-      <c r="AC9" s="13">
+      <c r="AD9" s="13">
         <v>10030</v>
-      </c>
-      <c r="AD9" s="13">
-        <v>9726</v>
       </c>
       <c r="AE9" s="13">
         <v>9726</v>
       </c>
       <c r="AF9" s="13">
+        <v>9726</v>
+      </c>
+      <c r="AG9" s="13">
         <v>9659</v>
       </c>
-      <c r="AG9" s="13">
+      <c r="AH9" s="13">
         <v>9670</v>
       </c>
-      <c r="AH9" s="13">
+      <c r="AI9" s="13">
         <v>9590</v>
       </c>
-      <c r="AI9" s="13">
+      <c r="AJ9" s="13">
         <v>9588</v>
       </c>
-      <c r="AJ9" s="13">
+      <c r="AK9" s="13">
         <v>9400</v>
       </c>
-      <c r="AK9" s="13">
+      <c r="AL9" s="13">
         <v>9320</v>
       </c>
-      <c r="AL9" s="13">
+      <c r="AM9" s="13">
         <v>9071</v>
       </c>
-      <c r="AM9" s="13">
+      <c r="AN9" s="13">
         <v>9271</v>
       </c>
-      <c r="AN9" s="13"/>
       <c r="AO9" s="13"/>
       <c r="AP9" s="13"/>
       <c r="AQ9" s="13"/>
@@ -2394,33 +2423,40 @@
       <c r="AZ9" s="13"/>
       <c r="BA9" s="13"/>
       <c r="BB9" s="13"/>
-      <c r="BC9" s="29"/>
-      <c r="BD9" s="13"/>
+      <c r="BC9" s="13"/>
+      <c r="BD9" s="29"/>
       <c r="BE9" s="13"/>
-      <c r="BF9" s="29"/>
-      <c r="BG9" s="13"/>
+      <c r="BF9" s="13"/>
+      <c r="BG9" s="29"/>
       <c r="BH9" s="13"/>
       <c r="BI9" s="13"/>
       <c r="BJ9" s="13"/>
-      <c r="BK9" s="13">
+      <c r="BK9" s="13"/>
+      <c r="BL9" s="13">
         <f t="shared" si="0"/>
-        <v>461.35</v>
-      </c>
-      <c r="BL9" s="13">
+        <v>-38.65</v>
+      </c>
+      <c r="BM9" s="13">
         <f t="shared" si="2"/>
-        <v>461.35</v>
-      </c>
-      <c r="BM9" s="13">
+        <v>0</v>
+      </c>
+      <c r="BN9" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="BN9" s="13"/>
-      <c r="BQ9" s="15">
-        <f>(BO9*BP9-BO9*H9)/100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>38.65</v>
+      </c>
+      <c r="BO9" s="13"/>
+      <c r="BP9">
+        <v>5</v>
+      </c>
+      <c r="BQ9">
+        <v>10000</v>
+      </c>
+      <c r="BR9" s="15">
+        <f>(BP9*BQ9-BP9*H9)/100</f>
+        <v>38.65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1141464</v>
       </c>
@@ -2449,181 +2485,184 @@
         <v>4834</v>
       </c>
       <c r="I10" s="13">
-        <v>5050</v>
+        <v>5013</v>
       </c>
       <c r="J10" s="13">
-        <v>5050</v>
+        <v>5013</v>
       </c>
       <c r="K10" s="13">
         <v>5050</v>
       </c>
       <c r="L10" s="13">
+        <v>5050</v>
+      </c>
+      <c r="M10" s="13">
         <v>4930</v>
       </c>
-      <c r="M10" s="13">
+      <c r="N10" s="13">
         <v>5150</v>
       </c>
-      <c r="N10" s="13">
+      <c r="O10" s="13">
         <v>5283</v>
-      </c>
-      <c r="O10" s="13">
-        <v>5253</v>
       </c>
       <c r="P10" s="13">
         <v>5253</v>
       </c>
       <c r="Q10" s="13">
+        <v>5253</v>
+      </c>
+      <c r="R10" s="13">
         <v>5400</v>
       </c>
-      <c r="R10" s="13">
+      <c r="S10" s="13">
         <v>5522</v>
       </c>
-      <c r="S10" s="13">
+      <c r="T10" s="13">
         <v>5690</v>
       </c>
-      <c r="T10" s="13">
+      <c r="U10" s="13">
         <v>5749</v>
       </c>
-      <c r="U10" s="13">
+      <c r="V10" s="13">
         <v>5840</v>
-      </c>
-      <c r="V10" s="13">
-        <v>5650</v>
       </c>
       <c r="W10" s="13">
         <v>5650</v>
       </c>
       <c r="X10" s="13">
+        <v>5650</v>
+      </c>
+      <c r="Y10" s="13">
         <v>5841</v>
       </c>
-      <c r="Y10" s="13">
+      <c r="Z10" s="13">
         <v>5758</v>
       </c>
-      <c r="Z10" s="13">
+      <c r="AA10" s="13">
         <v>5673</v>
       </c>
-      <c r="AA10" s="13">
+      <c r="AB10" s="13">
         <v>5609</v>
       </c>
-      <c r="AB10" s="13">
+      <c r="AC10" s="13">
         <v>5750</v>
       </c>
-      <c r="AC10" s="13">
+      <c r="AD10" s="13">
         <v>5841</v>
-      </c>
-      <c r="AD10" s="13">
-        <v>5564</v>
       </c>
       <c r="AE10" s="13">
         <v>5564</v>
       </c>
       <c r="AF10" s="13">
+        <v>5564</v>
+      </c>
+      <c r="AG10" s="13">
         <v>5557</v>
       </c>
-      <c r="AG10" s="13">
+      <c r="AH10" s="13">
         <v>5501</v>
       </c>
-      <c r="AH10" s="13">
+      <c r="AI10" s="13">
         <v>5250</v>
       </c>
-      <c r="AI10" s="13">
+      <c r="AJ10" s="13">
         <v>5270</v>
       </c>
-      <c r="AJ10" s="13">
+      <c r="AK10" s="13">
         <v>5149</v>
       </c>
-      <c r="AK10" s="13">
+      <c r="AL10" s="13">
         <v>5092</v>
       </c>
-      <c r="AL10" s="13">
+      <c r="AM10" s="13">
         <v>5228</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AN10" s="13">
         <v>5301</v>
       </c>
-      <c r="AN10" s="13">
+      <c r="AO10" s="13">
         <v>5159</v>
       </c>
-      <c r="AO10" s="13">
+      <c r="AP10" s="13">
         <v>5198</v>
       </c>
-      <c r="AP10" s="13">
+      <c r="AQ10" s="13">
         <v>5077</v>
       </c>
-      <c r="AQ10" s="13">
+      <c r="AR10" s="13">
         <v>4842</v>
       </c>
-      <c r="AR10" s="13">
+      <c r="AS10" s="13">
         <v>5050</v>
       </c>
-      <c r="AS10" s="13">
+      <c r="AT10" s="13">
         <v>4970</v>
       </c>
-      <c r="AT10" s="13">
+      <c r="AU10" s="13">
         <v>4880</v>
       </c>
-      <c r="AU10" s="13">
+      <c r="AV10" s="13">
         <v>4704</v>
       </c>
-      <c r="AV10" s="13">
+      <c r="AW10" s="13">
         <v>4770</v>
       </c>
-      <c r="AW10" s="13">
+      <c r="AX10" s="13">
         <v>4609</v>
       </c>
-      <c r="AX10" s="13">
+      <c r="AY10" s="13">
         <v>4674</v>
       </c>
-      <c r="AY10" s="13">
+      <c r="AZ10" s="13">
         <v>4710</v>
       </c>
-      <c r="AZ10" s="13">
+      <c r="BA10" s="13">
         <v>4688</v>
       </c>
-      <c r="BA10" s="13">
+      <c r="BB10" s="13">
         <v>4900</v>
       </c>
-      <c r="BB10" s="13">
+      <c r="BC10" s="13">
         <v>5000</v>
       </c>
-      <c r="BC10" s="29">
+      <c r="BD10" s="29">
         <v>4932</v>
       </c>
-      <c r="BD10" s="13"/>
       <c r="BE10" s="13"/>
-      <c r="BF10" s="29"/>
-      <c r="BG10" s="13"/>
+      <c r="BF10" s="13"/>
+      <c r="BG10" s="29"/>
       <c r="BH10" s="13"/>
       <c r="BI10" s="13"/>
       <c r="BJ10" s="13"/>
-      <c r="BK10" s="13">
+      <c r="BK10" s="13"/>
+      <c r="BL10" s="13">
         <f t="shared" si="0"/>
         <v>-87.859799999999964</v>
       </c>
-      <c r="BL10" s="13">
+      <c r="BM10" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BM10" s="13">
+      <c r="BN10" s="13">
         <f t="shared" si="3"/>
         <v>87.859799999999964</v>
       </c>
-      <c r="BN10" s="13">
-        <f>((BB10-H10)/H10)*100</f>
+      <c r="BO10" s="13">
+        <f>((BC10-H10)/H10)*100</f>
         <v>3.434009102192801</v>
       </c>
-      <c r="BO10">
+      <c r="BP10">
         <v>21</v>
       </c>
-      <c r="BP10">
+      <c r="BQ10">
         <v>5252.38</v>
       </c>
-      <c r="BQ10" s="15">
-        <f>(BO10*BP10-BO10*H10)/100</f>
+      <c r="BR10" s="15">
+        <f>(BP10*BQ10-BP10*H10)/100</f>
         <v>87.859799999999964</v>
       </c>
     </row>
-    <row r="11" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1166974</v>
       </c>
@@ -2637,7 +2676,7 @@
       </c>
       <c r="D11" s="6" t="str">
         <f>IF(I11&lt;GEMINI!L11,"למכור בהפסד",IF(I11&gt;GEMINI!M11,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>72</v>
@@ -2652,63 +2691,65 @@
         <v>901.87</v>
       </c>
       <c r="I11" s="13">
+        <v>1162</v>
+      </c>
+      <c r="J11" s="13">
+        <v>1162</v>
+      </c>
+      <c r="K11" s="13">
         <v>1109</v>
       </c>
-      <c r="J11" s="13">
-        <v>1109</v>
-      </c>
-      <c r="K11" s="13">
+      <c r="L11" s="13">
         <v>1029</v>
       </c>
-      <c r="L11" s="13">
+      <c r="M11" s="13">
         <v>993</v>
       </c>
-      <c r="M11" s="13">
+      <c r="N11" s="13">
         <v>1017</v>
       </c>
-      <c r="N11" s="13">
+      <c r="O11" s="13">
         <v>960</v>
-      </c>
-      <c r="O11" s="13">
-        <v>965</v>
       </c>
       <c r="P11" s="13">
         <v>965</v>
       </c>
       <c r="Q11" s="13">
+        <v>965</v>
+      </c>
+      <c r="R11" s="13">
         <v>951.7</v>
       </c>
-      <c r="R11" s="13">
+      <c r="S11" s="13">
         <v>946</v>
       </c>
-      <c r="S11" s="13">
+      <c r="T11" s="13">
         <v>869.2</v>
       </c>
-      <c r="T11" s="13">
+      <c r="U11" s="13">
         <v>865</v>
       </c>
-      <c r="U11" s="13">
+      <c r="V11" s="13">
         <v>851</v>
       </c>
-      <c r="V11" s="13">
+      <c r="W11" s="13">
         <v>829.3</v>
       </c>
-      <c r="W11" s="13">
+      <c r="X11" s="13">
         <v>830</v>
       </c>
-      <c r="X11" s="13">
+      <c r="Y11" s="13">
         <v>810</v>
       </c>
-      <c r="Y11" s="13">
+      <c r="Z11" s="13">
         <v>812.8</v>
       </c>
-      <c r="Z11" s="13">
+      <c r="AA11" s="13">
         <v>788</v>
       </c>
-      <c r="AA11" s="13">
+      <c r="AB11" s="13">
         <v>772</v>
       </c>
-      <c r="AB11" s="13"/>
       <c r="AC11" s="13"/>
       <c r="AD11" s="13"/>
       <c r="AE11" s="13"/>
@@ -2735,33 +2776,34 @@
       <c r="AZ11" s="13"/>
       <c r="BA11" s="13"/>
       <c r="BB11" s="13"/>
-      <c r="BC11" s="29"/>
-      <c r="BD11" s="13"/>
+      <c r="BC11" s="13"/>
+      <c r="BD11" s="29"/>
       <c r="BE11" s="13"/>
-      <c r="BF11" s="29"/>
-      <c r="BG11" s="13"/>
+      <c r="BF11" s="13"/>
+      <c r="BG11" s="29"/>
       <c r="BH11" s="13"/>
       <c r="BI11" s="13"/>
       <c r="BJ11" s="13"/>
-      <c r="BK11" s="13">
+      <c r="BK11" s="13"/>
+      <c r="BL11" s="13">
         <f t="shared" si="0"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BL11" s="13">
+      <c r="BM11" s="13">
         <f t="shared" si="2"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BM11" s="13">
+      <c r="BN11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BN11" s="13"/>
-      <c r="BQ11" s="15">
-        <f>(BO11*BP11-BO11*H11)/100</f>
+      <c r="BO11" s="13"/>
+      <c r="BR11" s="15">
+        <f>(BP11*BQ11-BP11*H11)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1176593</v>
       </c>
@@ -2790,69 +2832,71 @@
         <v>22581.42</v>
       </c>
       <c r="I12" s="13">
+        <v>27450</v>
+      </c>
+      <c r="J12" s="13">
+        <v>27450</v>
+      </c>
+      <c r="K12" s="13">
         <v>26940</v>
       </c>
-      <c r="J12" s="13">
-        <v>26940</v>
-      </c>
-      <c r="K12" s="13">
+      <c r="L12" s="13">
         <v>26800</v>
       </c>
-      <c r="L12" s="13">
+      <c r="M12" s="13">
         <v>25950</v>
       </c>
-      <c r="M12" s="13">
+      <c r="N12" s="13">
         <v>26000</v>
       </c>
-      <c r="N12" s="13">
+      <c r="O12" s="13">
         <v>26600</v>
-      </c>
-      <c r="O12" s="13">
-        <v>24630</v>
       </c>
       <c r="P12" s="13">
         <v>24630</v>
       </c>
       <c r="Q12" s="13">
+        <v>24630</v>
+      </c>
+      <c r="R12" s="13">
         <v>25230</v>
       </c>
-      <c r="R12" s="13">
+      <c r="S12" s="13">
         <v>24700</v>
       </c>
-      <c r="S12" s="13">
+      <c r="T12" s="13">
         <v>23780</v>
       </c>
-      <c r="T12" s="13">
+      <c r="U12" s="13">
         <v>23920</v>
       </c>
-      <c r="U12" s="13">
+      <c r="V12" s="13">
         <v>22390</v>
       </c>
-      <c r="V12" s="13">
+      <c r="W12" s="13">
         <v>23000</v>
       </c>
-      <c r="W12" s="13">
+      <c r="X12" s="13">
         <v>20990</v>
       </c>
-      <c r="X12" s="13">
+      <c r="Y12" s="13">
         <v>20260</v>
       </c>
-      <c r="Y12" s="13">
+      <c r="Z12" s="13">
         <v>19200</v>
       </c>
-      <c r="Z12" s="13">
+      <c r="AA12" s="13">
         <v>19860</v>
       </c>
-      <c r="AA12" s="13">
+      <c r="AB12" s="13">
         <v>19700</v>
       </c>
-      <c r="AB12" s="13">
+      <c r="AC12" s="13">
         <v>19430</v>
       </c>
-      <c r="AC12" s="13">
+      <c r="AD12" s="13">
         <v>19020</v>
       </c>
-      <c r="AD12" s="13"/>
       <c r="AE12" s="13"/>
       <c r="AF12" s="13"/>
       <c r="AG12" s="13"/>
@@ -2877,30 +2921,31 @@
       <c r="AZ12" s="13"/>
       <c r="BA12" s="13"/>
       <c r="BB12" s="13"/>
-      <c r="BC12" s="29"/>
-      <c r="BD12" s="13"/>
+      <c r="BC12" s="13"/>
+      <c r="BD12" s="29"/>
       <c r="BE12" s="13"/>
-      <c r="BF12" s="29"/>
-      <c r="BG12" s="13"/>
+      <c r="BF12" s="13"/>
+      <c r="BG12" s="29"/>
       <c r="BH12" s="13"/>
       <c r="BI12" s="13"/>
       <c r="BJ12" s="13"/>
-      <c r="BK12" s="13">
+      <c r="BK12" s="13"/>
+      <c r="BL12" s="13">
         <f t="shared" si="0"/>
         <v>1580.6994</v>
       </c>
-      <c r="BL12" s="13">
+      <c r="BM12" s="13">
         <f t="shared" si="2"/>
         <v>1580.6994</v>
       </c>
-      <c r="BM12" s="13"/>
       <c r="BN12" s="13"/>
-      <c r="BQ12" s="15">
-        <f t="shared" ref="BQ12:BQ14" si="4">(BO12*BP12-BO12*H12)/100</f>
+      <c r="BO12" s="13"/>
+      <c r="BR12" s="15">
+        <f t="shared" ref="BR12:BR14" si="4">(BP12*BQ12-BP12*H12)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>397018</v>
       </c>
@@ -2929,21 +2974,23 @@
         <v>723</v>
       </c>
       <c r="I13" s="13">
+        <v>1100</v>
+      </c>
+      <c r="J13" s="13">
+        <v>1100</v>
+      </c>
+      <c r="K13" s="13">
         <v>980</v>
       </c>
-      <c r="J13" s="13">
-        <v>980</v>
-      </c>
-      <c r="K13" s="13">
+      <c r="L13" s="13">
         <v>932.1</v>
       </c>
-      <c r="L13" s="13">
+      <c r="M13" s="13">
         <v>822</v>
       </c>
-      <c r="M13" s="13">
+      <c r="N13" s="13">
         <v>790</v>
       </c>
-      <c r="N13" s="13"/>
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
@@ -2984,30 +3031,31 @@
       <c r="AZ13" s="13"/>
       <c r="BA13" s="13"/>
       <c r="BB13" s="13"/>
-      <c r="BC13" s="29"/>
-      <c r="BD13" s="13"/>
+      <c r="BC13" s="13"/>
+      <c r="BD13" s="29"/>
       <c r="BE13" s="13"/>
-      <c r="BF13" s="29"/>
-      <c r="BG13" s="13"/>
+      <c r="BF13" s="13"/>
+      <c r="BG13" s="29"/>
       <c r="BH13" s="13"/>
       <c r="BI13" s="13"/>
       <c r="BJ13" s="13"/>
-      <c r="BK13" s="13">
+      <c r="BK13" s="13"/>
+      <c r="BL13" s="13">
         <f t="shared" si="0"/>
         <v>816.99</v>
       </c>
-      <c r="BL13" s="13">
+      <c r="BM13" s="13">
         <f t="shared" si="2"/>
         <v>816.99</v>
       </c>
-      <c r="BM13" s="13"/>
       <c r="BN13" s="13"/>
-      <c r="BQ13" s="15">
+      <c r="BO13" s="13"/>
+      <c r="BR13" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>662577</v>
       </c>
@@ -3036,189 +3084,192 @@
         <v>7204.22</v>
       </c>
       <c r="I14" s="13">
+        <v>7810</v>
+      </c>
+      <c r="J14" s="13">
+        <v>7810</v>
+      </c>
+      <c r="K14" s="13">
         <v>7710</v>
       </c>
-      <c r="J14" s="13">
-        <v>7710</v>
-      </c>
-      <c r="K14" s="13">
+      <c r="L14" s="13">
         <v>7735</v>
       </c>
-      <c r="L14" s="13">
+      <c r="M14" s="13">
         <v>7725</v>
       </c>
-      <c r="M14" s="13">
+      <c r="N14" s="13">
         <v>7787</v>
       </c>
-      <c r="N14" s="13">
+      <c r="O14" s="13">
         <v>7955</v>
-      </c>
-      <c r="O14" s="13">
-        <v>7627</v>
       </c>
       <c r="P14" s="13">
         <v>7627</v>
       </c>
       <c r="Q14" s="13">
+        <v>7627</v>
+      </c>
+      <c r="R14" s="13">
         <v>7656</v>
       </c>
-      <c r="R14" s="13">
+      <c r="S14" s="13">
         <v>7507</v>
       </c>
-      <c r="S14" s="13">
+      <c r="T14" s="13">
         <v>7590</v>
       </c>
-      <c r="T14" s="13">
+      <c r="U14" s="13">
         <v>7569</v>
       </c>
-      <c r="U14" s="13">
+      <c r="V14" s="13">
         <v>7269</v>
       </c>
-      <c r="V14" s="13">
+      <c r="W14" s="13">
         <v>7444</v>
       </c>
-      <c r="W14" s="13">
+      <c r="X14" s="13">
         <v>7205</v>
       </c>
-      <c r="X14" s="13">
+      <c r="Y14" s="13">
         <v>7298</v>
       </c>
-      <c r="Y14" s="13">
+      <c r="Z14" s="13">
         <v>7222</v>
       </c>
-      <c r="Z14" s="13">
+      <c r="AA14" s="13">
         <v>7079</v>
       </c>
-      <c r="AA14" s="13">
+      <c r="AB14" s="13">
         <v>7140</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AC14" s="13">
         <v>7440</v>
       </c>
-      <c r="AC14" s="13">
+      <c r="AD14" s="13">
         <v>7530</v>
-      </c>
-      <c r="AD14" s="13">
-        <v>7535</v>
       </c>
       <c r="AE14" s="13">
         <v>7535</v>
       </c>
       <c r="AF14" s="13">
+        <v>7535</v>
+      </c>
+      <c r="AG14" s="13">
         <v>7568</v>
       </c>
-      <c r="AG14" s="13">
+      <c r="AH14" s="13">
         <v>7699</v>
       </c>
-      <c r="AH14" s="13">
+      <c r="AI14" s="13">
         <v>7638</v>
       </c>
-      <c r="AI14" s="13">
+      <c r="AJ14" s="13">
         <v>7654</v>
       </c>
-      <c r="AJ14" s="13">
+      <c r="AK14" s="13">
         <v>7584</v>
       </c>
-      <c r="AK14" s="13">
+      <c r="AL14" s="13">
         <v>7479</v>
       </c>
-      <c r="AL14" s="13">
+      <c r="AM14" s="13">
         <v>7490</v>
       </c>
-      <c r="AM14" s="13">
+      <c r="AN14" s="13">
         <v>7480</v>
       </c>
-      <c r="AN14" s="13">
+      <c r="AO14" s="13">
         <v>7270</v>
       </c>
-      <c r="AO14" s="13">
+      <c r="AP14" s="13">
         <v>7163</v>
       </c>
-      <c r="AP14" s="13">
+      <c r="AQ14" s="13">
         <v>7231</v>
-      </c>
-      <c r="AQ14" s="13">
-        <v>7100</v>
       </c>
       <c r="AR14" s="13">
         <v>7100</v>
       </c>
       <c r="AS14" s="13">
+        <v>7100</v>
+      </c>
+      <c r="AT14" s="13">
         <v>7027</v>
       </c>
-      <c r="AT14" s="13">
+      <c r="AU14" s="13">
         <v>6984</v>
       </c>
-      <c r="AU14" s="13">
+      <c r="AV14" s="13">
         <v>6944</v>
       </c>
-      <c r="AV14" s="13">
+      <c r="AW14" s="13">
         <v>6924</v>
       </c>
-      <c r="AW14" s="13">
+      <c r="AX14" s="13">
         <v>6930</v>
       </c>
-      <c r="AX14" s="13">
+      <c r="AY14" s="13">
         <v>6938</v>
       </c>
-      <c r="AY14" s="13">
+      <c r="AZ14" s="13">
         <v>6989</v>
       </c>
-      <c r="AZ14" s="13">
+      <c r="BA14" s="13">
         <v>6871</v>
       </c>
-      <c r="BA14" s="13">
+      <c r="BB14" s="13">
         <v>6943</v>
       </c>
-      <c r="BB14" s="13">
+      <c r="BC14" s="13">
         <v>7040</v>
       </c>
-      <c r="BC14" s="29">
+      <c r="BD14" s="29">
         <v>6696</v>
       </c>
-      <c r="BD14" s="13">
+      <c r="BE14" s="13">
         <v>6965</v>
       </c>
-      <c r="BE14" s="13">
+      <c r="BF14" s="13">
         <v>6788</v>
       </c>
-      <c r="BF14" s="29">
+      <c r="BG14" s="29">
         <v>6696</v>
       </c>
-      <c r="BG14" s="13">
+      <c r="BH14" s="13">
         <v>6625</v>
       </c>
-      <c r="BH14" s="13">
+      <c r="BI14" s="13">
         <v>6660</v>
       </c>
-      <c r="BI14" s="13">
+      <c r="BJ14" s="13">
         <v>6791</v>
       </c>
-      <c r="BJ14" s="13">
+      <c r="BK14" s="13">
         <v>6610</v>
       </c>
-      <c r="BK14" s="13">
+      <c r="BL14" s="13">
         <f t="shared" si="0"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BL14" s="13">
+      <c r="BM14" s="13">
         <f t="shared" si="2"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BM14" s="13">
-        <f t="shared" ref="BM14" si="5">(BL14-BK14)</f>
+      <c r="BN14" s="13">
+        <f t="shared" ref="BN14" si="5">(BM14-BL14)</f>
         <v>0</v>
       </c>
-      <c r="BN14" s="13">
-        <f>((BB14-H14)/H14)*100</f>
+      <c r="BO14" s="13">
+        <f>((BC14-H14)/H14)*100</f>
         <v>-2.2794972946411995</v>
       </c>
-      <c r="BQ14" s="15">
+      <c r="BR14" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>5137534</v>
       </c>
@@ -3232,7 +3283,7 @@
       </c>
       <c r="D15" s="6" t="str">
         <f>IF(I15&lt;GEMINI!L15,"למכור בהפסד",IF(I15&gt;GEMINI!M15,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>78</v>
@@ -3247,57 +3298,59 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
-        <v>14790.87</v>
+        <v>15528.12</v>
       </c>
       <c r="J15" s="13">
+        <v>15528.12</v>
+      </c>
+      <c r="K15" s="13">
         <v>14358.25</v>
       </c>
-      <c r="K15" s="13">
+      <c r="L15" s="13">
         <v>14385.75</v>
       </c>
-      <c r="L15" s="13">
+      <c r="M15" s="13">
         <v>13880</v>
       </c>
-      <c r="M15" s="13">
+      <c r="N15" s="13">
         <v>13610.62</v>
       </c>
-      <c r="N15" s="13">
+      <c r="O15" s="13">
         <v>13016</v>
       </c>
-      <c r="O15" s="13">
+      <c r="P15" s="13">
         <v>12487.37</v>
       </c>
-      <c r="P15" s="13">
+      <c r="Q15" s="13">
         <v>12638.62</v>
       </c>
-      <c r="Q15" s="13">
+      <c r="R15" s="13">
         <v>12533.87</v>
       </c>
-      <c r="R15" s="13">
+      <c r="S15" s="13">
         <v>11299.5</v>
       </c>
-      <c r="S15" s="13">
+      <c r="T15" s="13">
         <v>11193.12</v>
       </c>
-      <c r="T15" s="13">
+      <c r="U15" s="13">
         <v>11548.62</v>
       </c>
-      <c r="U15" s="13">
+      <c r="V15" s="13">
         <v>11125.62</v>
       </c>
-      <c r="V15" s="13">
+      <c r="W15" s="13">
         <v>10932.12</v>
       </c>
-      <c r="W15" s="13">
+      <c r="X15" s="13">
         <v>11095.62</v>
       </c>
-      <c r="X15" s="13">
+      <c r="Y15" s="13">
         <v>10910.58</v>
       </c>
-      <c r="Y15" s="13">
+      <c r="Z15" s="13">
         <v>11609.37</v>
       </c>
-      <c r="Z15" s="13"/>
       <c r="AA15" s="13"/>
       <c r="AB15" s="13"/>
       <c r="AC15" s="13"/>
@@ -3307,8 +3360,8 @@
       <c r="AG15" s="13"/>
       <c r="AH15" s="13"/>
       <c r="AI15" s="13"/>
-      <c r="AJ15" s="14"/>
-      <c r="AK15" s="13"/>
+      <c r="AJ15" s="13"/>
+      <c r="AK15" s="14"/>
       <c r="AL15" s="13"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="13"/>
@@ -3326,36 +3379,37 @@
       <c r="AZ15" s="13"/>
       <c r="BA15" s="13"/>
       <c r="BB15" s="13"/>
-      <c r="BC15" s="29"/>
-      <c r="BD15" s="13"/>
+      <c r="BC15" s="13"/>
+      <c r="BD15" s="29"/>
       <c r="BE15" s="13"/>
-      <c r="BF15" s="29"/>
-      <c r="BG15" s="13"/>
+      <c r="BF15" s="13"/>
+      <c r="BG15" s="29"/>
       <c r="BH15" s="13"/>
       <c r="BI15" s="13"/>
       <c r="BJ15" s="13"/>
-      <c r="BK15" s="13">
+      <c r="BK15" s="13"/>
+      <c r="BL15" s="13">
         <f t="shared" si="0"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BL15" s="13">
+      <c r="BM15" s="13">
         <f t="shared" si="2"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BM15" s="13">
-        <f t="shared" ref="BM15:BM18" si="6">(BL15-BK15)</f>
+      <c r="BN15" s="13">
+        <f t="shared" ref="BN15:BN18" si="6">(BM15-BL15)</f>
         <v>0</v>
       </c>
-      <c r="BN15" s="13">
-        <f>((BB15-H15)/H15)*100</f>
+      <c r="BO15" s="13">
+        <f>((BC15-H15)/H15)*100</f>
         <v>-100</v>
       </c>
-      <c r="BQ15" s="15">
-        <f t="shared" ref="BQ15:BQ18" si="7">(BO15*BP15-BO15*H15)/100</f>
+      <c r="BR15" s="15">
+        <f t="shared" ref="BR15:BR18" si="7">(BP15*BQ15-BP15*H15)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>5135470</v>
       </c>
@@ -3384,195 +3438,198 @@
         <v>183.73</v>
       </c>
       <c r="I16" s="13">
-        <v>219.14</v>
+        <v>223.25</v>
       </c>
       <c r="J16" s="13">
-        <v>219.14</v>
+        <v>223.25</v>
       </c>
       <c r="K16" s="13">
         <v>219.14</v>
       </c>
       <c r="L16" s="13">
+        <v>219.14</v>
+      </c>
+      <c r="M16" s="13">
         <v>219.3</v>
       </c>
-      <c r="M16" s="13">
+      <c r="N16" s="13">
         <v>222.79</v>
       </c>
-      <c r="N16" s="13">
+      <c r="O16" s="13">
         <v>221.16</v>
       </c>
-      <c r="O16" s="13">
+      <c r="P16" s="13">
         <v>220.66</v>
       </c>
-      <c r="P16" s="13">
+      <c r="Q16" s="13">
         <v>222.06</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="R16" s="13">
         <v>218.71</v>
       </c>
-      <c r="R16" s="13">
+      <c r="S16" s="13">
         <v>216.74</v>
       </c>
-      <c r="S16" s="13">
+      <c r="T16" s="13">
         <v>216.04</v>
-      </c>
-      <c r="T16" s="13">
-        <v>210.69</v>
       </c>
       <c r="U16" s="13">
         <v>210.69</v>
       </c>
       <c r="V16" s="13">
+        <v>210.69</v>
+      </c>
+      <c r="W16" s="13">
         <v>198</v>
       </c>
-      <c r="W16" s="13">
+      <c r="X16" s="13">
         <v>196.74</v>
       </c>
-      <c r="X16" s="13">
+      <c r="Y16" s="13">
         <v>192.56</v>
       </c>
-      <c r="Y16" s="13">
+      <c r="Z16" s="13">
         <v>192.23</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="AA16" s="13">
         <v>191.19</v>
       </c>
-      <c r="AA16" s="13">
+      <c r="AB16" s="13">
         <v>193.62</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AC16" s="13">
         <v>190.75</v>
       </c>
-      <c r="AC16" s="13">
+      <c r="AD16" s="13">
         <v>189.06</v>
-      </c>
-      <c r="AD16" s="13">
-        <v>182.73</v>
       </c>
       <c r="AE16" s="13">
         <v>182.73</v>
       </c>
       <c r="AF16" s="13">
+        <v>182.73</v>
+      </c>
+      <c r="AG16" s="13">
         <v>177.92</v>
       </c>
-      <c r="AG16" s="13">
+      <c r="AH16" s="13">
         <v>179.16</v>
       </c>
-      <c r="AH16" s="13">
+      <c r="AI16" s="13">
         <v>179.34</v>
-      </c>
-      <c r="AI16" s="13">
-        <v>176.5</v>
       </c>
       <c r="AJ16" s="13">
         <v>176.5</v>
       </c>
       <c r="AK16" s="13">
+        <v>176.5</v>
+      </c>
+      <c r="AL16" s="13">
         <v>175.93</v>
       </c>
-      <c r="AL16" s="13">
+      <c r="AM16" s="13">
         <v>174.51</v>
       </c>
-      <c r="AM16" s="13">
+      <c r="AN16" s="13">
         <v>173.91</v>
       </c>
-      <c r="AN16" s="13">
+      <c r="AO16" s="13">
         <v>177.1</v>
       </c>
-      <c r="AO16" s="13">
+      <c r="AP16" s="13">
         <v>178.24</v>
       </c>
-      <c r="AP16" s="13">
+      <c r="AQ16" s="13">
         <v>176.52</v>
       </c>
-      <c r="AQ16" s="13">
+      <c r="AR16" s="13">
         <v>178.27</v>
       </c>
-      <c r="AR16" s="13">
+      <c r="AS16" s="13">
         <v>175.29</v>
       </c>
-      <c r="AS16" s="13">
+      <c r="AT16" s="13">
         <v>175.34</v>
       </c>
-      <c r="AT16" s="13">
+      <c r="AU16" s="13">
         <v>174.41</v>
       </c>
-      <c r="AU16" s="13">
+      <c r="AV16" s="13">
         <v>176.22</v>
       </c>
-      <c r="AV16" s="13">
+      <c r="AW16" s="13">
         <v>174</v>
       </c>
-      <c r="AW16" s="13">
+      <c r="AX16" s="13">
         <v>176.35</v>
       </c>
-      <c r="AX16" s="13">
+      <c r="AY16" s="13">
         <v>177.71</v>
       </c>
-      <c r="AY16" s="13">
+      <c r="AZ16" s="13">
         <v>180.08</v>
       </c>
-      <c r="AZ16" s="13">
+      <c r="BA16" s="13">
         <v>181.96</v>
       </c>
-      <c r="BA16" s="13">
+      <c r="BB16" s="13">
         <v>182.9</v>
       </c>
-      <c r="BB16" s="13">
+      <c r="BC16" s="13">
         <v>181.86</v>
       </c>
-      <c r="BC16" s="29">
+      <c r="BD16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BD16" s="13">
+      <c r="BE16" s="13">
         <v>181.07</v>
       </c>
-      <c r="BE16" s="13">
+      <c r="BF16" s="13">
         <v>182.56</v>
       </c>
-      <c r="BF16" s="29">
+      <c r="BG16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BG16" s="13">
+      <c r="BH16" s="13">
         <v>178.86</v>
       </c>
-      <c r="BH16" s="13">
+      <c r="BI16" s="13">
         <v>180.16</v>
       </c>
-      <c r="BI16" s="13">
+      <c r="BJ16" s="13">
         <v>179.56</v>
       </c>
-      <c r="BJ16" s="13">
+      <c r="BK16" s="13">
         <v>176.55</v>
       </c>
-      <c r="BK16" s="13">
+      <c r="BL16" s="13">
         <f t="shared" si="0"/>
         <v>673.09559999999999</v>
       </c>
-      <c r="BL16" s="13">
+      <c r="BM16" s="13">
         <f t="shared" si="2"/>
         <v>551.19000000000005</v>
       </c>
-      <c r="BM16" s="13">
+      <c r="BN16" s="13">
         <f t="shared" si="6"/>
         <v>-121.90559999999994</v>
       </c>
-      <c r="BN16" s="13">
-        <f>((BB16-H16)/H16)*100</f>
+      <c r="BO16" s="13">
+        <f>((BC16-H16)/H16)*100</f>
         <v>-1.0177978555488905</v>
       </c>
-      <c r="BO16">
+      <c r="BP16">
         <v>1864</v>
       </c>
-      <c r="BP16">
+      <c r="BQ16">
         <v>177.19</v>
       </c>
-      <c r="BQ16" s="15">
+      <c r="BR16" s="15">
         <f t="shared" si="7"/>
         <v>-121.90559999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>5134135</v>
       </c>
@@ -3601,16 +3658,16 @@
         <v>159.65</v>
       </c>
       <c r="I17" s="13">
-        <v>185.52</v>
+        <v>189.51</v>
       </c>
       <c r="J17" s="13">
-        <v>185.52</v>
+        <v>189.51</v>
       </c>
       <c r="K17" s="13">
         <v>185.52</v>
       </c>
       <c r="L17" s="13">
-        <v>178.98</v>
+        <v>185.52</v>
       </c>
       <c r="M17" s="13">
         <v>178.98</v>
@@ -3619,7 +3676,7 @@
         <v>178.98</v>
       </c>
       <c r="O17" s="13">
-        <v>170.7</v>
+        <v>178.98</v>
       </c>
       <c r="P17" s="13">
         <v>170.7</v>
@@ -3628,10 +3685,10 @@
         <v>170.7</v>
       </c>
       <c r="R17" s="13">
+        <v>170.7</v>
+      </c>
+      <c r="S17" s="13">
         <v>170.45</v>
-      </c>
-      <c r="S17" s="13">
-        <v>160.84</v>
       </c>
       <c r="T17" s="13">
         <v>160.84</v>
@@ -3640,15 +3697,17 @@
         <v>160.84</v>
       </c>
       <c r="V17" s="13">
+        <v>160.84</v>
+      </c>
+      <c r="W17" s="13">
         <v>159.02000000000001</v>
-      </c>
-      <c r="W17" s="13">
-        <v>159.65</v>
       </c>
       <c r="X17" s="13">
         <v>159.65</v>
       </c>
-      <c r="Y17" s="13"/>
+      <c r="Y17" s="13">
+        <v>159.65</v>
+      </c>
       <c r="Z17" s="13"/>
       <c r="AA17" s="13"/>
       <c r="AB17" s="13"/>
@@ -3678,36 +3737,37 @@
       <c r="AZ17" s="13"/>
       <c r="BA17" s="13"/>
       <c r="BB17" s="13"/>
-      <c r="BC17" s="29"/>
-      <c r="BD17" s="13"/>
+      <c r="BC17" s="13"/>
+      <c r="BD17" s="29"/>
       <c r="BE17" s="13"/>
-      <c r="BF17" s="29"/>
-      <c r="BG17" s="13"/>
+      <c r="BF17" s="13"/>
+      <c r="BG17" s="29"/>
       <c r="BH17" s="13"/>
       <c r="BI17" s="13"/>
       <c r="BJ17" s="13"/>
-      <c r="BK17" s="13">
+      <c r="BK17" s="13"/>
+      <c r="BL17" s="13">
         <f t="shared" si="0"/>
         <v>957.9</v>
       </c>
-      <c r="BL17" s="13">
+      <c r="BM17" s="13">
         <f t="shared" si="2"/>
         <v>957.9</v>
       </c>
-      <c r="BM17" s="13">
-        <f t="shared" ref="BM17" si="8">(BL17-BK17)</f>
+      <c r="BN17" s="13">
+        <f t="shared" ref="BN17" si="8">(BM17-BL17)</f>
         <v>0</v>
       </c>
-      <c r="BN17" s="13">
-        <f>((BB17-H17)/H17)*100</f>
+      <c r="BO17" s="13">
+        <f>((BC17-H17)/H17)*100</f>
         <v>-100</v>
       </c>
-      <c r="BQ17" s="15">
+      <c r="BR17" s="15">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1168723</v>
       </c>
@@ -3736,60 +3796,62 @@
         <v>1434</v>
       </c>
       <c r="I18" s="13">
+        <v>1831</v>
+      </c>
+      <c r="J18" s="13">
+        <v>1831</v>
+      </c>
+      <c r="K18" s="13">
         <v>1799</v>
       </c>
-      <c r="J18" s="13">
-        <v>1799</v>
-      </c>
-      <c r="K18" s="13">
+      <c r="L18" s="13">
         <v>1757</v>
       </c>
-      <c r="L18" s="13">
+      <c r="M18" s="13">
         <v>1698</v>
       </c>
-      <c r="M18" s="13">
+      <c r="N18" s="13">
         <v>1694</v>
       </c>
-      <c r="N18" s="13">
+      <c r="O18" s="13">
         <v>1671</v>
-      </c>
-      <c r="O18" s="13">
-        <v>1660</v>
       </c>
       <c r="P18" s="13">
         <v>1660</v>
       </c>
       <c r="Q18" s="13">
+        <v>1660</v>
+      </c>
+      <c r="R18" s="13">
         <v>1646</v>
       </c>
-      <c r="R18" s="13">
+      <c r="S18" s="13">
         <v>1648</v>
       </c>
-      <c r="S18" s="13">
+      <c r="T18" s="13">
         <v>1614</v>
       </c>
-      <c r="T18" s="13">
+      <c r="U18" s="13">
         <v>1626</v>
       </c>
-      <c r="U18" s="13">
+      <c r="V18" s="13">
         <v>1587</v>
       </c>
-      <c r="V18" s="13">
+      <c r="W18" s="13">
         <v>1548</v>
       </c>
-      <c r="W18" s="13">
+      <c r="X18" s="13">
         <v>1500</v>
       </c>
-      <c r="X18" s="13">
+      <c r="Y18" s="13">
         <v>1491</v>
       </c>
-      <c r="Y18" s="13">
+      <c r="Z18" s="13">
         <v>1444</v>
       </c>
-      <c r="Z18" s="13">
+      <c r="AA18" s="13">
         <v>1431</v>
       </c>
-      <c r="AA18" s="13"/>
       <c r="AB18" s="13"/>
       <c r="AC18" s="13"/>
       <c r="AD18" s="13"/>
@@ -3815,64 +3877,65 @@
       <c r="AX18" s="13"/>
       <c r="AY18" s="13"/>
       <c r="AZ18" s="13"/>
-      <c r="BA18" s="13">
-        <v>1788</v>
-      </c>
+      <c r="BA18" s="13"/>
       <c r="BB18" s="13">
         <v>1788</v>
       </c>
-      <c r="BC18" s="29">
+      <c r="BC18" s="13">
+        <v>1788</v>
+      </c>
+      <c r="BD18" s="29">
         <v>1780</v>
       </c>
-      <c r="BD18" s="13">
+      <c r="BE18" s="13">
         <v>1814</v>
       </c>
-      <c r="BE18" s="13">
+      <c r="BF18" s="13">
         <v>1794</v>
       </c>
-      <c r="BF18" s="29">
+      <c r="BG18" s="29">
         <v>1780</v>
       </c>
-      <c r="BG18" s="13">
+      <c r="BH18" s="13">
         <v>1772</v>
       </c>
-      <c r="BH18" s="13">
+      <c r="BI18" s="13">
         <v>1798</v>
       </c>
-      <c r="BI18" s="13">
+      <c r="BJ18" s="13">
         <v>1806</v>
       </c>
-      <c r="BJ18" s="13">
+      <c r="BK18" s="13">
         <v>1801</v>
       </c>
-      <c r="BK18" s="13">
+      <c r="BL18" s="13">
         <f t="shared" si="0"/>
         <v>292.79999999999995</v>
       </c>
-      <c r="BL18" s="13">
+      <c r="BM18" s="13">
         <f t="shared" si="2"/>
         <v>645.29999999999995</v>
       </c>
-      <c r="BM18" s="13">
+      <c r="BN18" s="13">
         <f t="shared" si="6"/>
         <v>352.5</v>
       </c>
-      <c r="BN18" s="13">
-        <f>((BB18-H18)/H18)*100</f>
+      <c r="BO18" s="13">
+        <f>((BC18-H18)/H18)*100</f>
         <v>24.686192468619247</v>
       </c>
-      <c r="BO18">
+      <c r="BP18">
         <v>100</v>
       </c>
-      <c r="BP18">
+      <c r="BQ18">
         <v>1786.5</v>
       </c>
-      <c r="BQ18" s="15">
+      <c r="BR18" s="15">
         <f t="shared" si="7"/>
         <v>352.5</v>
       </c>
     </row>
-    <row r="19" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1146604</v>
       </c>
@@ -3913,22 +3976,22 @@
       <c r="S19" s="13"/>
       <c r="T19" s="13"/>
       <c r="U19" s="13"/>
-      <c r="V19" s="13">
+      <c r="V19" s="13"/>
+      <c r="W19" s="13">
         <v>6461</v>
       </c>
-      <c r="W19" s="13">
+      <c r="X19" s="13">
         <v>6503</v>
       </c>
-      <c r="X19" s="13">
+      <c r="Y19" s="13">
         <v>6535</v>
       </c>
-      <c r="Y19" s="13">
+      <c r="Z19" s="13">
         <v>6532</v>
       </c>
-      <c r="Z19" s="13">
+      <c r="AA19" s="13">
         <v>6515</v>
       </c>
-      <c r="AA19" s="13"/>
       <c r="AB19" s="13"/>
       <c r="AC19" s="13"/>
       <c r="AD19" s="13"/>
@@ -3956,33 +4019,34 @@
       <c r="AZ19" s="13"/>
       <c r="BA19" s="13"/>
       <c r="BB19" s="13"/>
-      <c r="BC19" s="29"/>
-      <c r="BD19" s="13"/>
+      <c r="BC19" s="13"/>
+      <c r="BD19" s="29"/>
       <c r="BE19" s="13"/>
-      <c r="BF19" s="29"/>
-      <c r="BG19" s="13"/>
+      <c r="BF19" s="13"/>
+      <c r="BG19" s="29"/>
       <c r="BH19" s="13"/>
       <c r="BI19" s="13"/>
       <c r="BJ19" s="13"/>
-      <c r="BK19" s="13">
+      <c r="BK19" s="13"/>
+      <c r="BL19" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BL19" s="13">
+      <c r="BM19" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BM19" s="13"/>
       <c r="BN19" s="13"/>
-      <c r="BO19">
+      <c r="BO19" s="13"/>
+      <c r="BP19">
         <v>7</v>
       </c>
-      <c r="BP19">
+      <c r="BQ19">
         <v>6461</v>
       </c>
-      <c r="BQ19" s="15"/>
-    </row>
-    <row r="20" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BR19" s="15"/>
+    </row>
+    <row r="20" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1144807</v>
       </c>
@@ -4020,7 +4084,9 @@
       <c r="N20" s="13">
         <v>3159</v>
       </c>
-      <c r="O20" s="13"/>
+      <c r="O20" s="13">
+        <v>3159</v>
+      </c>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
@@ -4060,28 +4126,29 @@
       <c r="AZ20" s="13"/>
       <c r="BA20" s="13"/>
       <c r="BB20" s="13"/>
-      <c r="BC20" s="29"/>
-      <c r="BD20" s="13"/>
+      <c r="BC20" s="13"/>
+      <c r="BD20" s="29"/>
       <c r="BE20" s="13"/>
-      <c r="BF20" s="29"/>
-      <c r="BG20" s="13"/>
+      <c r="BF20" s="13"/>
+      <c r="BG20" s="29"/>
       <c r="BH20" s="13"/>
       <c r="BI20" s="13"/>
       <c r="BJ20" s="13"/>
-      <c r="BK20" s="13">
-        <f>(G20*H20)/100-BQ20</f>
+      <c r="BK20" s="13"/>
+      <c r="BL20" s="13">
+        <f>(G20*H20)/100-BR20</f>
         <v>0</v>
       </c>
-      <c r="BL20" s="13">
+      <c r="BM20" s="13">
         <f>(G20*H20)/100</f>
         <v>0</v>
       </c>
-      <c r="BM20" s="13"/>
       <c r="BN20" s="13"/>
-      <c r="BQ20" s="15"/>
-    </row>
-    <row r="21" spans="1:69" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:69" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BO20" s="13"/>
+      <c r="BR20" s="15"/>
+    </row>
+    <row r="21" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4136,11 +4203,11 @@
       <c r="AZ22" s="13"/>
       <c r="BA22" s="13"/>
       <c r="BB22" s="13"/>
-      <c r="BC22" s="29"/>
-      <c r="BD22" s="13"/>
+      <c r="BC22" s="13"/>
+      <c r="BD22" s="29"/>
       <c r="BE22" s="13"/>
-      <c r="BF22" s="29"/>
-      <c r="BG22" s="13"/>
+      <c r="BF22" s="13"/>
+      <c r="BG22" s="29"/>
       <c r="BH22" s="13"/>
       <c r="BI22" s="13"/>
       <c r="BJ22" s="13"/>
@@ -4148,9 +4215,10 @@
       <c r="BL22" s="13"/>
       <c r="BM22" s="13"/>
       <c r="BN22" s="13"/>
-      <c r="BQ22" s="15"/>
-    </row>
-    <row r="23" spans="1:69" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BO22" s="13"/>
+      <c r="BR22" s="15"/>
+    </row>
+    <row r="23" spans="1:70" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4161,59 +4229,59 @@
       <c r="H23" s="13"/>
       <c r="I23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19)/100</f>
-        <v>16568.633599999997</v>
+        <v>16518.923599999998</v>
       </c>
       <c r="J23" s="23">
-        <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19)/100</f>
-        <v>16568.633599999997</v>
+        <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19)/100</f>
+        <v>16518.923599999998</v>
       </c>
       <c r="K23" s="23">
         <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19)/100</f>
-        <v>16187.433000000001</v>
+        <v>16036.023999999999</v>
       </c>
       <c r="L23" s="23">
         <f>(L2*G2+G3*L3+L4*G4+G5*L5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+L13*G13+G14*L14+L15*G15+G16*L16+G17*L17+L18*G18+G19*L19)/100</f>
-        <v>15809.632</v>
+        <v>15691.233</v>
       </c>
       <c r="M23" s="23">
         <f>(M2*G2+G3*M3+M4*G4+G5*M5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+M13*G13+G14*M14+M15*G15+G16*M16+G17*M17+M18*G18+G19*M19)/100</f>
-        <v>15866.4776</v>
+        <v>15309.681999999999</v>
       </c>
       <c r="N23" s="23">
-        <f>(N3*G3+G4*N4+N5*G5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+G14*N14+N15*G15+G16*N16+N17*G17+G18*N18+G19*N19)/100</f>
-        <v>14073.12</v>
+        <f>(N2*G2+G3*N3+N4*G4+G5*N5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+N13*G13+G14*N14+N15*G15+G16*N16+G17*N17+N18*G18+G19*N19)/100</f>
+        <v>15368.3776</v>
       </c>
       <c r="O23" s="23">
         <f>(O3*G3+G4*O4+O5*G5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+G14*O14+O15*G15+G16*O16+O17*G17+G18*O18+G19*O19)/100</f>
-        <v>13833.077600000001</v>
+        <v>13574.17</v>
       </c>
       <c r="P23" s="23">
         <f>(P3*G3+G4*P4+P5*G5+G6*P6+G7*P7+G8*P8+G9*P9+G10*P10+G11*P11+G12*P12+G14*P14+P15*G15+G16*P16+P17*G17+G18*P18+G19*P19)/100</f>
-        <v>13849.3776</v>
+        <v>13326.577600000001</v>
       </c>
       <c r="Q23" s="23">
         <f>(Q3*G3+G4*Q4+Q5*G5+G6*Q6+G7*Q7+G8*Q8+G9*Q9+G10*Q10+G11*Q11+G12*Q12+G14*Q14+Q15*G15+G16*Q16+Q17*G17+G18*Q18+G19*Q19)/100</f>
-        <v>13831.7376</v>
+        <v>13342.8776</v>
       </c>
       <c r="R23" s="23">
         <f>(R3*G3+G4*R4+R5*G5+G6*R6+G7*R7+G8*R8+G9*R9+G10*R10+G11*R11+G12*R12+G14*R14+R15*G15+G16*R16+R17*G17+G18*R18+G19*R19)/100</f>
-        <v>13233.88</v>
+        <v>13311.7376</v>
       </c>
       <c r="S23" s="23">
         <f>(S3*G3+G4*S4+S5*G5+G6*S6+G7*S7+G8*S8+G9*S9+G10*S10+G11*S11+G12*S12+G14*S14+S15*G15+G16*S16+S17*G17+G18*S18+G19*S19)/100</f>
-        <v>13029.9056</v>
+        <v>12717.88</v>
       </c>
       <c r="T23" s="23">
         <f>(T3*G3+G4*T4+T5*G5+G6*T6+G7*T7+G8*T8+G9*T9+G10*T10+G11*T11+G12*T12+G14*T14+T15*G15+G16*T16+T17*G17+G18*T18+G19*T19)/100</f>
-        <v>11265.595600000001</v>
+        <v>12514.9056</v>
       </c>
       <c r="U23" s="23">
-        <f>(U5*G5+G6*U6+U7*G7+G8*U8+G9*U9+G10*U10+G11*U11+G12*U12+G14*U14+G20*U20+G15*U15+U16*G16+G17*U17+U18*G18+G19*U19)/100</f>
-        <v>10392.5196</v>
-      </c>
-      <c r="V23" s="23" t="e">
-        <f>(V5*G5+G7*V7+V8*G8+G9*V9+#REF!*#REF!+G10*V10+G11*V11+G12*V12+G14*V14+G19*V19+G20*V20+V6*G6+G15*V15+#REF!*#REF!+G16*V16+G17*V17+V18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*V3+#REF!*#REF!)/100</f>
-        <v>#REF!</v>
+        <f>(U3*G3+G4*U4+U5*G5+G6*U6+G7*U7+G8*U8+G9*U9+G10*U10+G11*U11+G12*U12+G14*U14+U15*G15+G16*U16+U17*G17+G18*U18+G19*U19)/100</f>
+        <v>10750.095600000001</v>
+      </c>
+      <c r="V23" s="23">
+        <f>(V5*G5+G6*V6+V7*G7+G8*V8+G9*V9+G10*V10+G11*V11+G12*V12+G14*V14+G20*V20+G15*V15+V16*G16+G17*V17+V18*G18+G19*V19)/100</f>
+        <v>9908.9195999999993</v>
       </c>
       <c r="W23" s="23" t="e">
         <f>(W5*G5+G7*W7+W8*G8+G9*W9+#REF!*#REF!+G10*W10+G11*W11+G12*W12+G14*W14+G19*W19+G20*W20+W6*G6+G15*W15+#REF!*#REF!+G16*W16+G17*W17+W18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*W3+#REF!*#REF!)/100</f>
@@ -4224,11 +4292,11 @@
         <v>#REF!</v>
       </c>
       <c r="Y23" s="23" t="e">
-        <f>(Y5*G5+G7*Y7+Y8*G8+G9*Y9+#REF!*#REF!+G10*Y10+G11*Y11+G12*Y12+G14*Y14+G19*Y19+G20*Y20+Y6*G6+G15*Y15+#REF!*#REF!+G16*Y16+G18*Y18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*Y3+#REF!*#REF!+G4*Y4)/100</f>
+        <f>(Y5*G5+G7*Y7+Y8*G8+G9*Y9+#REF!*#REF!+G10*Y10+G11*Y11+G12*Y12+G14*Y14+G19*Y19+G20*Y20+Y6*G6+G15*Y15+#REF!*#REF!+G16*Y16+G17*Y17+Y18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*Y3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="Z23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+Z3*G3+#REF!*#REF!+G4*Z4+G5*Z5+G7*Z7+G8*Z8+G9*Z9+#REF!*#REF!+G10*Z10+Z11*G11+G12*Z12+Z14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*Z20+Z6*G6+#REF!*#REF!+G16*Z16+G18*Z18+G19*Z19)/100</f>
+        <f>(Z5*G5+G7*Z7+Z8*G8+G9*Z9+#REF!*#REF!+G10*Z10+G11*Z11+G12*Z12+G14*Z14+G19*Z19+G20*Z20+Z6*G6+G15*Z15+#REF!*#REF!+G16*Z16+G18*Z18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*Z3+#REF!*#REF!+G4*Z4)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AA23" s="23" t="e">
@@ -4236,7 +4304,7 @@
         <v>#REF!</v>
       </c>
       <c r="AB23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AB3*G3+#REF!*#REF!+G4*AB4+G5*AB5+AB7*G7+AB8*G8+AB9*G9+#REF!*#REF!+G10*AB10+AB11*G11+G12*AB12+AB14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AB20+G6*AB6+#REF!*#REF!+G16*AB16+G18*AB18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AB3*G3+#REF!*#REF!+G4*AB4+G5*AB5+G7*AB7+G8*AB8+G9*AB9+#REF!*#REF!+G10*AB10+AB11*G11+G12*AB12+AB14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AB20+AB6*G6+#REF!*#REF!+G16*AB16+G18*AB18+G19*AB19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AC23" s="23" t="e">
@@ -4244,19 +4312,19 @@
         <v>#REF!</v>
       </c>
       <c r="AD23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AD3*G3+#REF!*#REF!+G4*AD4+G8*AD8+AD9*G9+#REF!*#REF!+AD10*G10+G11*AD11+G14*AD14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AD6+#REF!*#REF!+G16*AD16+G18*AD18+G7*AD7+G5*AD5+G12*AD12+G20*AD20)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AD3*G3+#REF!*#REF!+G4*AD4+G5*AD5+AD7*G7+AD8*G8+AD9*G9+#REF!*#REF!+G10*AD10+AD11*G11+G12*AD12+AD14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AD20+G6*AD6+#REF!*#REF!+G16*AD16+G18*AD18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AE23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AE3*G3+#REF!*#REF!+G4*AE4+G8*AE8+AE9*G9+#REF!*#REF!+AE10*G10+G11*AE11+G14*AE14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AE6+#REF!*#REF!+G16*AE16+G18*AE18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AE3*G3+#REF!*#REF!+G4*AE4+G8*AE8+AE9*G9+#REF!*#REF!+AE10*G10+G11*AE11+G14*AE14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AE6+#REF!*#REF!+G16*AE16+G18*AE18+G7*AE7+G5*AE5+G12*AE12+G20*AE20)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AF23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AF3*G3+#REF!*#REF!+G4*AF4+G8*AF8+G9*AF9+#REF!*#REF!+G10*AF10+AF11*G11+AF14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AF6*G6+#REF!*#REF!+G16*AF16+G18*AF18+G19*AF19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AF3*G3+#REF!*#REF!+G4*AF4+G8*AF8+AF9*G9+#REF!*#REF!+AF10*G10+G11*AF11+G14*AF14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AF6+#REF!*#REF!+G16*AF16+G18*AF18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AG23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AG3*G3+#REF!*#REF!+G4*AG4+G8*AG8+AG9*G9+#REF!*#REF!+AG10*G10+G11*AG11+G14*AG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AG6+#REF!*#REF!+G16*AG16+G18*AG18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AG3*G3+#REF!*#REF!+G4*AG4+G8*AG8+G9*AG9+#REF!*#REF!+G10*AG10+AG11*G11+AG14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AG6*G6+#REF!*#REF!+G16*AG16+G18*AG18+G19*AG19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AH23" s="23" t="e">
@@ -4264,7 +4332,7 @@
         <v>#REF!</v>
       </c>
       <c r="AI23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AI3*G3+#REF!*#REF!+G4*AI4+G8*AI8+AI9*G9+AI10*G10+AI11*G11+G14*AI14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AI6+#REF!*#REF!+G16*AI16+G18*AI18+G19*AI19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AI3*G3+#REF!*#REF!+G4*AI4+G8*AI8+AI9*G9+#REF!*#REF!+AI10*G10+G11*AI11+G14*AI14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AI6+#REF!*#REF!+G16*AI16+G18*AI18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AJ23" s="23" t="e">
@@ -4284,19 +4352,19 @@
         <v>#REF!</v>
       </c>
       <c r="AN23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+AN9*G9+AN10*G10+AN11*G11+G14*AN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AN6+#REF!*#REF!+G16*AN16+G18*AN18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+AN9*G9+AN10*G10+AN11*G11+G14*AN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AN6+#REF!*#REF!+G16*AN16+G18*AN18+G19*AN19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AO23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+AO10*G10+AO11*G11+G14*AO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AO6+#REF!*#REF!+G16*AO16+G18*AO18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+AO9*G9+AO10*G10+AO11*G11+G14*AO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AO6+#REF!*#REF!+G16*AO16+G18*AO18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AP23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+G10*AP10+AP11*G11+AP14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AP6*G6+#REF!*#REF!+G16*AP16+G18*AP18+G19*AP19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+AP10*G10+AP11*G11+G14*AP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AP6+#REF!*#REF!+G16*AP16+G18*AP18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AQ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AQ3*G3+#REF!*#REF!+G4*AQ4+G10*AQ10+AQ11*G11+AQ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AQ6*G6+#REF!*#REF!+G16*AQ16+G18*AQ18+G19*AQ19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AQ3*G3+#REF!*#REF!+G4*AQ4+G8*AQ8+G10*AQ10+AQ11*G11+AQ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AQ6*G6+#REF!*#REF!+G16*AQ16+G18*AQ18+G19*AQ19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AR23" s="23" t="e">
@@ -4308,7 +4376,7 @@
         <v>#REF!</v>
       </c>
       <c r="AT23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AT3*G3+#REF!*#REF!+G4*AT4+G10*AT10+AT11*G11+AT14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AT6*G6+G16*AT16+G18*AT18+G19*AT19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AT3*G3+#REF!*#REF!+G4*AT4+G10*AT10+AT11*G11+AT14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AT6*G6+#REF!*#REF!+G16*AT16+G18*AT18+G19*AT19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AU23" s="23" t="e">
@@ -4336,15 +4404,15 @@
         <v>#REF!</v>
       </c>
       <c r="BA23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BA3*G3+#REF!*#REF!+G4*BA4+G10*BA10+G11*BA11+G14*BA14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BA6+BA16*G16+G18*BA18+G19*BA19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BA3*G3+#REF!*#REF!+G4*BA4+G10*BA10+BA11*G11+BA14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BA6*G6+G16*BA16+G18*BA18+G19*BA19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BB23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BB3*G3+#REF!*#REF!+G4*BB4+G10*BB10+G14*BB14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BB6+BB16*G16+G18*BB18+G19*BB19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BB3*G3+#REF!*#REF!+G4*BB4+G10*BB10+G11*BB11+G14*BB14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BB6+BB16*G16+G18*BB18+G19*BB19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BC23" s="23" t="e">
-        <f>(#REF!*#REF!+BC3*G3+G4*BC4+G14*BC14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BC6+BC16*G16+G18*BC18+G19*BC19+G22*BC22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BC3*G3+#REF!*#REF!+G4*BC4+G10*BC10+G14*BC14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BC6+BC16*G16+G18*BC18+G19*BC19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BD23" s="23" t="e">
@@ -4355,16 +4423,16 @@
         <f>(#REF!*#REF!+BE3*G3+G4*BE4+G14*BE14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BE6+BE16*G16+G18*BE18+G19*BE19+G22*BE22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BF23" s="30" t="e">
+      <c r="BF23" s="23" t="e">
         <f>(#REF!*#REF!+BF3*G3+G4*BF4+G14*BF14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BF6+BF16*G16+G18*BF18+G19*BF19+G22*BF22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BG23" s="23" t="e">
+      <c r="BG23" s="30" t="e">
         <f>(#REF!*#REF!+BG3*G3+G4*BG4+G14*BG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BG6+BG16*G16+G18*BG18+G19*BG19+G22*BG22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BH23" s="23" t="e">
-        <f>(#REF!*#REF!+BH3*G3+G14*BH14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BH6+BH16*G16+G18*BH18+G19*BH19+G22*BH22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+BH3*G3+G4*BH4+G14*BH14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BH6+BH16*G16+G18*BH18+G19*BH19+G22*BH22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BI23" s="23" t="e">
@@ -4375,16 +4443,20 @@
         <f>(#REF!*#REF!+BJ3*G3+G14*BJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BJ6+BJ16*G16+G18*BJ18+G19*BJ19+G22*BJ22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BK23" s="13"/>
+      <c r="BK23" s="23" t="e">
+        <f>(#REF!*#REF!+BK3*G3+G14*BK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BK6+BK16*G16+G18*BK18+G19*BK19+G22*BK22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <v>#REF!</v>
+      </c>
       <c r="BL23" s="13"/>
       <c r="BM23" s="13"/>
       <c r="BN23" s="13"/>
-      <c r="BQ23" s="15">
+      <c r="BO23" s="13"/>
+      <c r="BR23" s="15">
         <f>434.9+62.57</f>
         <v>497.46999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:69" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:70" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4447,29 +4519,30 @@
       <c r="BH24" s="14"/>
       <c r="BI24" s="14"/>
       <c r="BJ24" s="14"/>
-      <c r="BK24" s="23">
-        <f>SUM(BK2:BK20)</f>
-        <v>14089.379000000001</v>
-      </c>
+      <c r="BK24" s="14"/>
       <c r="BL24" s="23">
         <f>SUM(BL2:BL20)</f>
-        <v>14352.3832</v>
-      </c>
-      <c r="BM24" s="24">
-        <f>BL24-BK24</f>
-        <v>263.0041999999994</v>
-      </c>
-      <c r="BN24" s="13">
-        <f>((BL24-BK24)/BK24)*100</f>
-        <v>1.8666841171637119</v>
-      </c>
-      <c r="BQ24" s="15">
-        <f>SUM(BQ5:BQ23)</f>
-        <v>760.47419999999988</v>
-      </c>
-    </row>
-    <row r="25" spans="1:69" x14ac:dyDescent="0.25">
-      <c r="BK25" s="15">
+        <v>13589.379000000001</v>
+      </c>
+      <c r="BM24" s="23">
+        <f>SUM(BM2:BM20)</f>
+        <v>13891.033200000002</v>
+      </c>
+      <c r="BN24" s="24">
+        <f>BM24-BL24</f>
+        <v>301.65420000000086</v>
+      </c>
+      <c r="BO24" s="13">
+        <f>((BM24-BL24)/BL24)*100</f>
+        <v>2.2197791378104976</v>
+      </c>
+      <c r="BR24" s="15">
+        <f>SUM(BR5:BR23)</f>
+        <v>799.12419999999997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:70" x14ac:dyDescent="0.25">
+      <c r="BL25" s="15">
         <v>12034.32</v>
       </c>
     </row>
@@ -4596,7 +4669,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>11000</v>
+        <v>11360</v>
       </c>
       <c r="J2" s="25"/>
       <c r="L2" s="21">
@@ -4634,7 +4707,7 @@
       <c r="G3" s="17"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1373</v>
+        <v>1348</v>
       </c>
       <c r="J3" s="26"/>
       <c r="L3" s="21">
@@ -4672,7 +4745,7 @@
       <c r="G4" s="17"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6680</v>
+        <v>6979</v>
       </c>
       <c r="J4" s="26"/>
       <c r="L4" s="21">
@@ -4709,7 +4782,7 @@
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>630.29999999999995</v>
+        <v>638.29999999999995</v>
       </c>
       <c r="J5" s="26"/>
       <c r="L5" s="21">
@@ -4746,7 +4819,7 @@
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4238</v>
+        <v>4450</v>
       </c>
       <c r="J6" s="26"/>
       <c r="L6" s="21">
@@ -4784,7 +4857,7 @@
       <c r="G7" s="18"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3928</v>
+        <v>3943</v>
       </c>
       <c r="J7" s="26"/>
       <c r="L7" s="21">
@@ -4822,7 +4895,7 @@
       <c r="G8" s="18"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40820</v>
+        <v>40790</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -4848,7 +4921,7 @@
       </c>
       <c r="D9" s="19">
         <f>'התיק העדכני'!G9</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" s="16">
         <v>9700</v>
@@ -4859,7 +4932,7 @@
       <c r="G9" s="17"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9960</v>
+        <v>9910</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -4896,7 +4969,7 @@
       <c r="G10" s="18"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5050</v>
+        <v>5013</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -4933,7 +5006,7 @@
       <c r="G11" s="18"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1109</v>
+        <v>1162</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -4970,7 +5043,7 @@
       <c r="G12" s="18"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>26940</v>
+        <v>27450</v>
       </c>
       <c r="J12" s="26"/>
       <c r="L12" s="21">
@@ -5008,7 +5081,7 @@
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>980</v>
+        <v>1100</v>
       </c>
       <c r="J13" s="26"/>
       <c r="L13" s="21">
@@ -5046,7 +5119,7 @@
       <c r="G14" s="17"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7710</v>
+        <v>7810</v>
       </c>
       <c r="J14" s="26"/>
       <c r="L14" s="21">
@@ -5084,7 +5157,7 @@
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14790.87</v>
+        <v>15528.12</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
@@ -5122,7 +5195,7 @@
       <c r="G16" s="17"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>219.14</v>
+        <v>223.25</v>
       </c>
       <c r="J16" s="26"/>
       <c r="L16" s="21">
@@ -5160,7 +5233,7 @@
       <c r="G17" s="17"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>185.52</v>
+        <v>189.51</v>
       </c>
       <c r="J17" s="26"/>
       <c r="L17" s="21">
@@ -5198,7 +5271,7 @@
       <c r="G18" s="18"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1799</v>
+        <v>1831</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -5620,7 +5693,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>11000</v>
+        <v>11360</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+GEMINI!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
@@ -5657,7 +5730,7 @@
       <c r="G3" s="7"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1373</v>
+        <v>1348</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
@@ -5694,7 +5767,7 @@
       <c r="G4" s="7"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6680</v>
+        <v>6979</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+GEMINI!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
@@ -5731,7 +5804,7 @@
       <c r="G5" s="7"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>630.29999999999995</v>
+        <v>638.29999999999995</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
@@ -5768,7 +5841,7 @@
       <c r="G6" s="7"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4238</v>
+        <v>4450</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
@@ -5805,7 +5878,7 @@
       <c r="G7" s="8"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3928</v>
+        <v>3943</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+GEMINI!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
@@ -5842,7 +5915,7 @@
       <c r="G8" s="8"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40820</v>
+        <v>40790</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+GEMINI!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -5868,7 +5941,7 @@
       </c>
       <c r="D9" s="19">
         <f>'התיק העדכני'!G9</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" s="16">
         <v>9327</v>
@@ -5879,7 +5952,7 @@
       <c r="G9" s="8"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9960</v>
+        <v>9910</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+GEMINI!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -5916,7 +5989,7 @@
       <c r="G10" s="8"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5050</v>
+        <v>5013</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+GEMINI!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -5953,7 +6026,7 @@
       <c r="G11" s="8"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1109</v>
+        <v>1162</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+GEMINI!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -5990,7 +6063,7 @@
       <c r="G12" s="8"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>26940</v>
+        <v>27450</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+GEMINI!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
@@ -6027,7 +6100,7 @@
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>980</v>
+        <v>1100</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+GEMINI!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
@@ -6064,7 +6137,7 @@
       <c r="G14" s="7"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7710</v>
+        <v>7810</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
@@ -6101,7 +6174,7 @@
       <c r="G15" s="7"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14790.87</v>
+        <v>15528.12</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+GEMINI!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
@@ -6138,7 +6211,7 @@
       <c r="G16" s="7"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>219.14</v>
+        <v>223.25</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
@@ -6175,7 +6248,7 @@
       <c r="G17" s="7"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>185.52</v>
+        <v>189.51</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+GEMINI!E17+PERPLIXITY!E17+DEEPSEEK!E17)/4</f>
@@ -6212,7 +6285,7 @@
       <c r="G18" s="8"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1799</v>
+        <v>1831</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+GEMINI!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -6436,7 +6509,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>11000</v>
+        <v>11360</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+GEMINI!E2+DEEPSEEK!E2)/4</f>
@@ -6473,7 +6546,7 @@
       <c r="G3" s="10"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1373</v>
+        <v>1348</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
@@ -6510,7 +6583,7 @@
       <c r="G4" s="10"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6680</v>
+        <v>6979</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+GEMINI!E4+DEEPSEEK!E4)/4</f>
@@ -6547,7 +6620,7 @@
       <c r="G5" s="10"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>630.29999999999995</v>
+        <v>638.29999999999995</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
@@ -6584,7 +6657,7 @@
       <c r="G6" s="10"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4238</v>
+        <v>4450</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
@@ -6621,7 +6694,7 @@
       <c r="G7" s="10"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3928</v>
+        <v>3943</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+GEMINI!E7+DEEPSEEK!E7)/4</f>
@@ -6657,7 +6730,7 @@
       </c>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40820</v>
+        <v>40790</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+GEMINI!E8+DEEPSEEK!E8)/4</f>
@@ -6683,7 +6756,7 @@
       </c>
       <c r="D9" s="19">
         <f>'התיק העדכני'!G9</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" s="16">
         <v>9400</v>
@@ -6693,7 +6766,7 @@
       </c>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9960</v>
+        <v>9910</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+GEMINI!E9+DEEPSEEK!E9)/4</f>
@@ -6729,7 +6802,7 @@
       </c>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5050</v>
+        <v>5013</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+GEMINI!E10+DEEPSEEK!E10)/4</f>
@@ -6765,7 +6838,7 @@
       </c>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1109</v>
+        <v>1162</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+GEMINI!E11+DEEPSEEK!E11)/4</f>
@@ -6802,7 +6875,7 @@
       <c r="G12" s="10"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>26940</v>
+        <v>27450</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+GEMINI!E12+DEEPSEEK!E12)/4</f>
@@ -6839,7 +6912,7 @@
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>980</v>
+        <v>1100</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+CHATGPT!E13+GEMINI!E13+DEEPSEEK!E13)/4</f>
@@ -6876,7 +6949,7 @@
       <c r="G14" s="10"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7710</v>
+        <v>7810</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
@@ -6913,7 +6986,7 @@
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14790.87</v>
+        <v>15528.12</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
@@ -6950,7 +7023,7 @@
       <c r="G16" s="10"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>219.14</v>
+        <v>223.25</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+GEMINI!E16+DEEPSEEK!E16)/4</f>
@@ -6987,7 +7060,7 @@
       <c r="G17" s="10"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>185.52</v>
+        <v>189.51</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+GEMINI!E17+DEEPSEEK!E17)/4</f>
@@ -7023,7 +7096,7 @@
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1799</v>
+        <v>1831</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
@@ -7246,7 +7319,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>11000</v>
+        <v>11360</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+PERPLIXITY!E2+GEMINI!E2)/4</f>
@@ -7283,7 +7356,7 @@
       <c r="G3" s="31"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1373</v>
+        <v>1348</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
@@ -7319,7 +7392,7 @@
       </c>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6680</v>
+        <v>6979</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+GEMINI!E4)/4</f>
@@ -7356,7 +7429,7 @@
       <c r="G5" s="31"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>630.29999999999995</v>
+        <v>638.29999999999995</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
@@ -7393,7 +7466,7 @@
       <c r="G6" s="31"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4238</v>
+        <v>4450</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
@@ -7429,7 +7502,7 @@
       </c>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3928</v>
+        <v>3943</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+GEMINI!E7)/4</f>
@@ -7466,7 +7539,7 @@
       <c r="G8" s="31"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40820</v>
+        <v>40790</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+GEMINI!E8)/4</f>
@@ -7492,7 +7565,7 @@
       </c>
       <c r="D9" s="19">
         <f>'התיק העדכני'!G9</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" s="16">
         <v>9500</v>
@@ -7503,7 +7576,7 @@
       <c r="G9" s="31"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9960</v>
+        <v>9910</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+GEMINI!E9)/4</f>
@@ -7540,7 +7613,7 @@
       <c r="G10" s="31"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5050</v>
+        <v>5013</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+GEMINI!E10)/4</f>
@@ -7577,7 +7650,7 @@
       <c r="G11" s="31"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1109</v>
+        <v>1162</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+GEMINI!E11)/4</f>
@@ -7614,7 +7687,7 @@
       <c r="G12" s="31"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>26940</v>
+        <v>27450</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+GEMINI!E12)/4</f>
@@ -7651,7 +7724,7 @@
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>980</v>
+        <v>1100</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
@@ -7682,7 +7755,7 @@
       <c r="G14" s="31"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7710</v>
+        <v>7810</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
@@ -7754,7 +7827,7 @@
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14790.87</v>
+        <v>15528.12</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
@@ -7791,7 +7864,7 @@
       <c r="G17" s="31"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>219.14</v>
+        <v>223.25</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+GEMINI!E17)/4</f>
@@ -7828,7 +7901,7 @@
       <c r="G18" s="31"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>185.52</v>
+        <v>189.51</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+GEMINI!E18)/4</f>
@@ -7858,7 +7931,7 @@
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1799</v>
+        <v>1831</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+GEMINI!E19)/4</f>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\BURSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCFDDED-F4DE-41A7-B300-EC97C54377E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA15407-37F8-4B9E-9201-4F65EAE5B6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="103">
   <si>
     <t>MTF מחקה אינדקס תעשיה ישראל</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>מחיר 26/01/2026</t>
+  </si>
+  <si>
+    <t>מחיר 27/01/2026</t>
   </si>
 </sst>
 </file>
@@ -1105,22 +1108,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86B4639-EF9D-4B16-B2C9-0D5E9C5EEC8B}">
-  <dimension ref="A1:BR25"/>
+  <dimension ref="A1:BS25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="17.5703125" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="53" width="14.85546875" customWidth="1"/>
-    <col min="54" max="63" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="13" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="11" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.5703125" customWidth="1"/>
+    <col min="8" max="54" width="14.85546875" customWidth="1"/>
+    <col min="55" max="64" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="13" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="11" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1149,190 +1152,193 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BK1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BL1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BM1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BN1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BO1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BO1" s="6" t="s">
+      <c r="BP1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="BP1" s="12" t="s">
+      <c r="BQ1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="BQ1" s="12" t="s">
+      <c r="BR1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="BR1" s="12" t="s">
+      <c r="BS1" s="12" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>282012</v>
       </c>
@@ -1361,24 +1367,26 @@
         <v>11000</v>
       </c>
       <c r="I2" s="13">
+        <v>11840</v>
+      </c>
+      <c r="J2" s="13">
+        <v>11400</v>
+      </c>
+      <c r="K2" s="13">
         <v>11360</v>
       </c>
-      <c r="J2" s="13">
-        <v>11360</v>
-      </c>
-      <c r="K2" s="13">
+      <c r="L2" s="13">
         <v>11000</v>
       </c>
-      <c r="L2" s="13">
+      <c r="M2" s="13">
         <v>10700</v>
       </c>
-      <c r="M2" s="13">
+      <c r="N2" s="13">
         <v>10400</v>
       </c>
-      <c r="N2" s="13">
+      <c r="O2" s="13">
         <v>11230</v>
       </c>
-      <c r="O2" s="6"/>
       <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
@@ -1419,29 +1427,30 @@
       <c r="BA2" s="6"/>
       <c r="BB2" s="6"/>
       <c r="BC2" s="6"/>
-      <c r="BD2" s="32"/>
-      <c r="BE2" s="6"/>
+      <c r="BD2" s="6"/>
+      <c r="BE2" s="32"/>
       <c r="BF2" s="6"/>
-      <c r="BG2" s="32"/>
-      <c r="BH2" s="6"/>
+      <c r="BG2" s="6"/>
+      <c r="BH2" s="32"/>
       <c r="BI2" s="6"/>
       <c r="BJ2" s="6"/>
       <c r="BK2" s="6"/>
-      <c r="BL2" s="13">
-        <f>(G2*H2)/100-BR2</f>
+      <c r="BL2" s="6"/>
+      <c r="BM2" s="13">
+        <f>(G2*H2)/100-BS2</f>
         <v>770</v>
       </c>
-      <c r="BM2" s="13">
+      <c r="BN2" s="13">
         <f>(G2*H2)/100</f>
         <v>770</v>
       </c>
-      <c r="BN2" s="6"/>
       <c r="BO2" s="6"/>
-      <c r="BP2" s="25"/>
+      <c r="BP2" s="6"/>
       <c r="BQ2" s="25"/>
       <c r="BR2" s="25"/>
-    </row>
-    <row r="3" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BS2" s="25"/>
+    </row>
+    <row r="3" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1227552</v>
       </c>
@@ -1455,7 +1464,7 @@
       </c>
       <c r="D3" s="6" t="str">
         <f>IF(I3&lt;GEMINI!L3,"למכור בהפסד",IF(I3&gt;GEMINI!M3,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>88</v>
@@ -1470,42 +1479,44 @@
         <v>1153.6300000000001</v>
       </c>
       <c r="I3" s="13">
+        <v>1500</v>
+      </c>
+      <c r="J3" s="13">
+        <v>1424</v>
+      </c>
+      <c r="K3" s="13">
         <v>1348</v>
       </c>
-      <c r="J3" s="13">
-        <v>1348</v>
-      </c>
-      <c r="K3" s="13">
+      <c r="L3" s="13">
         <v>1373</v>
       </c>
-      <c r="L3" s="13">
+      <c r="M3" s="13">
         <v>1331</v>
       </c>
-      <c r="M3" s="13">
+      <c r="N3" s="13">
         <v>1386</v>
       </c>
-      <c r="N3" s="13">
+      <c r="O3" s="13">
         <v>1342</v>
       </c>
-      <c r="O3" s="13">
+      <c r="P3" s="13">
         <v>1250</v>
-      </c>
-      <c r="P3" s="13">
-        <v>1389</v>
       </c>
       <c r="Q3" s="13">
         <v>1389</v>
       </c>
       <c r="R3" s="13">
+        <v>1389</v>
+      </c>
+      <c r="S3" s="13">
         <v>1367</v>
       </c>
-      <c r="S3" s="13">
+      <c r="T3" s="13">
         <v>1026</v>
       </c>
-      <c r="T3" s="13">
+      <c r="U3" s="13">
         <v>949.1</v>
       </c>
-      <c r="U3" s="13"/>
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
@@ -1521,8 +1532,8 @@
       <c r="AH3" s="13"/>
       <c r="AI3" s="13"/>
       <c r="AJ3" s="13"/>
-      <c r="AK3" s="14"/>
-      <c r="AL3" s="13"/>
+      <c r="AK3" s="13"/>
+      <c r="AL3" s="14"/>
       <c r="AM3" s="13"/>
       <c r="AN3" s="13"/>
       <c r="AO3" s="13"/>
@@ -1540,36 +1551,37 @@
       <c r="BA3" s="13"/>
       <c r="BB3" s="13"/>
       <c r="BC3" s="13"/>
-      <c r="BD3" s="29"/>
-      <c r="BE3" s="13"/>
+      <c r="BD3" s="13"/>
+      <c r="BE3" s="29"/>
       <c r="BF3" s="13"/>
-      <c r="BG3" s="29"/>
-      <c r="BH3" s="13"/>
+      <c r="BG3" s="13"/>
+      <c r="BH3" s="29"/>
       <c r="BI3" s="13"/>
       <c r="BJ3" s="13"/>
       <c r="BK3" s="13"/>
-      <c r="BL3" s="13">
-        <f>(G3*H3)/100-BR3</f>
+      <c r="BL3" s="13"/>
+      <c r="BM3" s="13">
+        <f>(G3*H3)/100-BS3</f>
         <v>784.46840000000009</v>
       </c>
-      <c r="BM3" s="13">
+      <c r="BN3" s="13">
         <f>(G3*H3)/100</f>
         <v>784.46840000000009</v>
       </c>
-      <c r="BN3" s="13">
-        <f>(BM3-BL3)</f>
+      <c r="BO3" s="13">
+        <f>(BN3-BM3)</f>
         <v>0</v>
       </c>
-      <c r="BO3" s="13">
-        <f>((BC3-H3)/H3)*100</f>
+      <c r="BP3" s="13">
+        <f>((BD3-H3)/H3)*100</f>
         <v>-100</v>
       </c>
-      <c r="BR3" s="15">
-        <f>(BP3*BQ3-BP3*H3)/100</f>
+      <c r="BS3" s="15">
+        <f>(BQ3*BR3-BQ3*H3)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>587014</v>
       </c>
@@ -1598,42 +1610,44 @@
         <v>5925</v>
       </c>
       <c r="I4" s="13">
+        <v>7120</v>
+      </c>
+      <c r="J4" s="13">
+        <v>7048</v>
+      </c>
+      <c r="K4" s="13">
         <v>6979</v>
       </c>
-      <c r="J4" s="13">
-        <v>6979</v>
-      </c>
-      <c r="K4" s="13">
+      <c r="L4" s="13">
         <v>6680</v>
       </c>
-      <c r="L4" s="13">
+      <c r="M4" s="13">
         <v>6111</v>
       </c>
-      <c r="M4" s="13">
+      <c r="N4" s="13">
         <v>6050</v>
       </c>
-      <c r="N4" s="13">
+      <c r="O4" s="13">
         <v>6169</v>
       </c>
-      <c r="O4" s="13">
+      <c r="P4" s="13">
         <v>6300</v>
-      </c>
-      <c r="P4" s="13">
-        <v>6335</v>
       </c>
       <c r="Q4" s="13">
         <v>6335</v>
       </c>
       <c r="R4" s="13">
+        <v>6335</v>
+      </c>
+      <c r="S4" s="13">
         <v>6444</v>
-      </c>
-      <c r="S4" s="13">
-        <v>5749</v>
       </c>
       <c r="T4" s="13">
         <v>5749</v>
       </c>
-      <c r="U4" s="13"/>
+      <c r="U4" s="13">
+        <v>5749</v>
+      </c>
       <c r="V4" s="13"/>
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
@@ -1668,36 +1682,37 @@
       <c r="BA4" s="13"/>
       <c r="BB4" s="13"/>
       <c r="BC4" s="13"/>
-      <c r="BD4" s="29"/>
-      <c r="BE4" s="13"/>
+      <c r="BD4" s="13"/>
+      <c r="BE4" s="29"/>
       <c r="BF4" s="13"/>
-      <c r="BG4" s="29"/>
-      <c r="BH4" s="13"/>
+      <c r="BG4" s="13"/>
+      <c r="BH4" s="29"/>
       <c r="BI4" s="13"/>
       <c r="BJ4" s="13"/>
       <c r="BK4" s="13"/>
-      <c r="BL4" s="13">
-        <f>(G4*H4)/100-BR4</f>
+      <c r="BL4" s="13"/>
+      <c r="BM4" s="13">
+        <f>(G4*H4)/100-BS4</f>
         <v>1185</v>
       </c>
-      <c r="BM4" s="13">
+      <c r="BN4" s="13">
         <f>(G4*H4)/100</f>
         <v>1185</v>
       </c>
-      <c r="BN4" s="13">
-        <f>(BM4-BL4)</f>
+      <c r="BO4" s="13">
+        <f>(BN4-BM4)</f>
         <v>0</v>
       </c>
-      <c r="BO4" s="13">
-        <f>((BC4-H4)/H4)*100</f>
+      <c r="BP4" s="13">
+        <f>((BD4-H4)/H4)*100</f>
         <v>-100</v>
       </c>
-      <c r="BR4" s="15">
-        <f>(BP4*BQ4-BP4*H4)/100</f>
+      <c r="BS4" s="15">
+        <f>(BQ4*BR4-BQ4*H4)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1099787</v>
       </c>
@@ -1711,7 +1726,7 @@
       </c>
       <c r="D5" s="6" t="str">
         <f>IF(I5&lt;GEMINI!L5,"למכור בהפסד",IF(I5&gt;GEMINI!M5,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור בהפסד</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>67</v>
@@ -1720,78 +1735,80 @@
         <v>46045</v>
       </c>
       <c r="G5" s="27">
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="H5" s="13">
-        <v>615</v>
+        <v>617.53</v>
       </c>
       <c r="I5" s="13">
+        <v>575.70000000000005</v>
+      </c>
+      <c r="J5" s="13">
+        <v>612.6</v>
+      </c>
+      <c r="K5" s="13">
         <v>638.29999999999995</v>
       </c>
-      <c r="J5" s="13">
-        <v>638.29999999999995</v>
-      </c>
-      <c r="K5" s="13">
+      <c r="L5" s="13">
         <v>630.29999999999995</v>
       </c>
-      <c r="L5" s="13">
+      <c r="M5" s="13">
         <v>626</v>
       </c>
-      <c r="M5" s="13">
+      <c r="N5" s="13">
         <v>595.4</v>
       </c>
-      <c r="N5" s="13">
+      <c r="O5" s="13">
         <v>667.1</v>
       </c>
-      <c r="O5" s="13">
+      <c r="P5" s="13">
         <v>651</v>
-      </c>
-      <c r="P5" s="13">
-        <v>641.1</v>
       </c>
       <c r="Q5" s="13">
         <v>641.1</v>
       </c>
       <c r="R5" s="13">
+        <v>641.1</v>
+      </c>
+      <c r="S5" s="13">
         <v>607.1</v>
       </c>
-      <c r="S5" s="13">
+      <c r="T5" s="13">
         <v>583</v>
       </c>
-      <c r="T5" s="13">
+      <c r="U5" s="13">
         <v>581.6</v>
       </c>
-      <c r="U5" s="13">
+      <c r="V5" s="13">
         <v>578.70000000000005</v>
       </c>
-      <c r="V5" s="13">
+      <c r="W5" s="13">
         <v>590</v>
       </c>
-      <c r="W5" s="13">
+      <c r="X5" s="13">
         <v>554.70000000000005</v>
       </c>
-      <c r="X5" s="13">
+      <c r="Y5" s="13">
         <v>511.8</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="Z5" s="13">
         <v>487</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="AA5" s="13">
         <v>478.8</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AB5" s="13">
         <v>485.5</v>
       </c>
-      <c r="AB5" s="13">
+      <c r="AC5" s="13">
         <v>453.4</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AD5" s="13">
         <v>426.1</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AE5" s="13">
         <v>423.2</v>
       </c>
-      <c r="AE5" s="13"/>
       <c r="AF5" s="13"/>
       <c r="AG5" s="13"/>
       <c r="AH5" s="13"/>
@@ -1816,27 +1833,28 @@
       <c r="BA5" s="13"/>
       <c r="BB5" s="13"/>
       <c r="BC5" s="13"/>
-      <c r="BD5" s="29"/>
-      <c r="BE5" s="13"/>
+      <c r="BD5" s="13"/>
+      <c r="BE5" s="29"/>
       <c r="BF5" s="13"/>
-      <c r="BG5" s="29"/>
-      <c r="BH5" s="13"/>
+      <c r="BG5" s="13"/>
+      <c r="BH5" s="29"/>
       <c r="BI5" s="13"/>
       <c r="BJ5" s="13"/>
       <c r="BK5" s="13"/>
-      <c r="BL5" s="13">
-        <f t="shared" ref="BL5:BL19" si="0">(G5*H5)/100-BR5</f>
-        <v>479.7</v>
-      </c>
+      <c r="BL5" s="13"/>
       <c r="BM5" s="13">
+        <f t="shared" ref="BM5:BM19" si="0">(G5*H5)/100-BS5</f>
+        <v>975.6973999999999</v>
+      </c>
+      <c r="BN5" s="13">
         <f>(G5*H5)/100</f>
-        <v>479.7</v>
-      </c>
-      <c r="BN5" s="13"/>
+        <v>975.6973999999999</v>
+      </c>
       <c r="BO5" s="13"/>
-      <c r="BR5" s="15"/>
-    </row>
-    <row r="6" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BP5" s="13"/>
+      <c r="BS5" s="15"/>
+    </row>
+    <row r="6" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1166768</v>
       </c>
@@ -1865,45 +1883,47 @@
         <v>3700</v>
       </c>
       <c r="I6" s="13">
+        <v>4424</v>
+      </c>
+      <c r="J6" s="13">
+        <v>4412</v>
+      </c>
+      <c r="K6" s="13">
         <v>4450</v>
       </c>
-      <c r="J6" s="13">
-        <v>4450</v>
-      </c>
-      <c r="K6" s="13">
+      <c r="L6" s="13">
         <v>4238</v>
       </c>
-      <c r="L6" s="13">
+      <c r="M6" s="13">
         <v>3970</v>
       </c>
-      <c r="M6" s="13">
+      <c r="N6" s="13">
         <v>3870</v>
       </c>
-      <c r="N6" s="13">
+      <c r="O6" s="13">
         <v>3805</v>
       </c>
-      <c r="O6" s="13">
+      <c r="P6" s="13">
         <v>3667</v>
-      </c>
-      <c r="P6" s="13">
-        <v>3582</v>
       </c>
       <c r="Q6" s="13">
         <v>3582</v>
       </c>
       <c r="R6" s="13">
+        <v>3582</v>
+      </c>
+      <c r="S6" s="13">
         <v>3570</v>
       </c>
-      <c r="S6" s="13">
+      <c r="T6" s="13">
         <v>3619</v>
       </c>
-      <c r="T6" s="13">
+      <c r="U6" s="13">
         <v>3650</v>
       </c>
-      <c r="U6" s="13">
+      <c r="V6" s="13">
         <v>3720</v>
       </c>
-      <c r="V6" s="13"/>
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
@@ -1937,41 +1957,42 @@
       <c r="BA6" s="13"/>
       <c r="BB6" s="13"/>
       <c r="BC6" s="13"/>
-      <c r="BD6" s="29"/>
-      <c r="BE6" s="13"/>
+      <c r="BD6" s="13"/>
+      <c r="BE6" s="29"/>
       <c r="BF6" s="13"/>
-      <c r="BG6" s="29"/>
-      <c r="BH6" s="13"/>
+      <c r="BG6" s="13"/>
+      <c r="BH6" s="29"/>
       <c r="BI6" s="13"/>
       <c r="BJ6" s="13"/>
-      <c r="BL6" s="13">
-        <f>(G6*H6)/100-BR6</f>
+      <c r="BK6" s="13"/>
+      <c r="BM6" s="13">
+        <f>(G6*H6)/100-BS6</f>
         <v>561.70000000000005</v>
       </c>
-      <c r="BM6" s="13">
+      <c r="BN6" s="13">
         <f>(G6*H6)/100</f>
         <v>555</v>
       </c>
-      <c r="BN6" s="13">
-        <f t="shared" ref="BN6" si="1">(BM6-BL6)</f>
+      <c r="BO6" s="13">
+        <f t="shared" ref="BO6" si="1">(BN6-BM6)</f>
         <v>-6.7000000000000455</v>
       </c>
-      <c r="BO6" s="13">
-        <f>((BC6-H6)/H6)*100</f>
+      <c r="BP6" s="13">
+        <f>((BD6-H6)/H6)*100</f>
         <v>-100</v>
       </c>
-      <c r="BP6">
+      <c r="BQ6">
         <v>5</v>
       </c>
-      <c r="BQ6">
+      <c r="BR6">
         <v>3566</v>
       </c>
-      <c r="BR6" s="15">
-        <f>(BP6*BQ6-BP6*H6)/100</f>
+      <c r="BS6" s="15">
+        <f>(BQ6*BR6-BQ6*H6)/100</f>
         <v>-6.7</v>
       </c>
     </row>
-    <row r="7" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1148899</v>
       </c>
@@ -2000,72 +2021,74 @@
         <v>3585</v>
       </c>
       <c r="I7" s="13">
+        <v>3932</v>
+      </c>
+      <c r="J7" s="13">
+        <v>3949</v>
+      </c>
+      <c r="K7" s="13">
         <v>3943</v>
       </c>
-      <c r="J7" s="13">
-        <v>3943</v>
-      </c>
-      <c r="K7" s="13">
+      <c r="L7" s="13">
         <v>3928</v>
       </c>
-      <c r="L7" s="13">
+      <c r="M7" s="13">
         <v>3913</v>
       </c>
-      <c r="M7" s="13">
+      <c r="N7" s="13">
         <v>3860</v>
       </c>
-      <c r="N7" s="13">
+      <c r="O7" s="13">
         <v>3893</v>
       </c>
-      <c r="O7" s="13">
+      <c r="P7" s="13">
         <v>3900</v>
-      </c>
-      <c r="P7" s="13">
-        <v>3842</v>
       </c>
       <c r="Q7" s="13">
         <v>3842</v>
       </c>
       <c r="R7" s="13">
+        <v>3842</v>
+      </c>
+      <c r="S7" s="13">
         <v>3841</v>
       </c>
-      <c r="S7" s="13">
+      <c r="T7" s="13">
         <v>3809</v>
       </c>
-      <c r="T7" s="13">
+      <c r="U7" s="13">
         <v>3810</v>
       </c>
-      <c r="U7" s="13">
+      <c r="V7" s="13">
         <v>3798</v>
       </c>
-      <c r="V7" s="13">
+      <c r="W7" s="13">
         <v>3713</v>
       </c>
-      <c r="W7" s="13">
+      <c r="X7" s="13">
         <v>3657</v>
       </c>
-      <c r="X7" s="13">
+      <c r="Y7" s="13">
         <v>3592</v>
       </c>
-      <c r="Y7" s="13">
+      <c r="Z7" s="13">
         <v>3621</v>
       </c>
-      <c r="Z7" s="13">
+      <c r="AA7" s="13">
         <v>3572</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="AB7" s="13">
         <v>3580</v>
       </c>
-      <c r="AB7" s="13">
+      <c r="AC7" s="13">
         <v>3569</v>
       </c>
-      <c r="AC7" s="13">
+      <c r="AD7" s="13">
         <v>3659</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AE7" s="13">
         <v>3656</v>
       </c>
-      <c r="AE7" s="13"/>
       <c r="AF7" s="13"/>
       <c r="AG7" s="13"/>
       <c r="AH7" s="13"/>
@@ -2090,27 +2113,28 @@
       <c r="BA7" s="13"/>
       <c r="BB7" s="13"/>
       <c r="BC7" s="13"/>
-      <c r="BD7" s="29"/>
-      <c r="BE7" s="13"/>
+      <c r="BD7" s="13"/>
+      <c r="BE7" s="29"/>
       <c r="BF7" s="13"/>
-      <c r="BG7" s="29"/>
-      <c r="BH7" s="13"/>
+      <c r="BG7" s="13"/>
+      <c r="BH7" s="29"/>
       <c r="BI7" s="13"/>
       <c r="BJ7" s="13"/>
       <c r="BK7" s="13"/>
-      <c r="BL7" s="13">
+      <c r="BL7" s="13"/>
+      <c r="BM7" s="13">
         <f t="shared" si="0"/>
         <v>2509.5</v>
       </c>
-      <c r="BM7" s="13">
-        <f t="shared" ref="BM7:BM19" si="2">(G7*H7)/100</f>
+      <c r="BN7" s="13">
+        <f t="shared" ref="BN7:BN19" si="2">(G7*H7)/100</f>
         <v>2509.5</v>
       </c>
-      <c r="BN7" s="13"/>
       <c r="BO7" s="13"/>
-      <c r="BR7" s="15"/>
-    </row>
-    <row r="8" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BP7" s="13"/>
+      <c r="BS7" s="15"/>
+    </row>
+    <row r="8" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1082379</v>
       </c>
@@ -2139,108 +2163,110 @@
         <v>37875</v>
       </c>
       <c r="I8" s="13">
+        <v>40750</v>
+      </c>
+      <c r="J8" s="13">
+        <v>40900</v>
+      </c>
+      <c r="K8" s="13">
         <v>40790</v>
       </c>
-      <c r="J8" s="13">
-        <v>40790</v>
-      </c>
-      <c r="K8" s="13">
+      <c r="L8" s="13">
         <v>40820</v>
       </c>
-      <c r="L8" s="13">
+      <c r="M8" s="13">
         <v>41570</v>
       </c>
-      <c r="M8" s="13">
+      <c r="N8" s="13">
         <v>42050</v>
       </c>
-      <c r="N8" s="13">
+      <c r="O8" s="13">
         <v>39960</v>
       </c>
-      <c r="O8" s="13">
+      <c r="P8" s="13">
         <v>39990</v>
-      </c>
-      <c r="P8" s="13">
-        <v>38680</v>
       </c>
       <c r="Q8" s="13">
         <v>38680</v>
       </c>
       <c r="R8" s="13">
+        <v>38680</v>
+      </c>
+      <c r="S8" s="13">
         <v>37770</v>
       </c>
-      <c r="S8" s="13">
+      <c r="T8" s="13">
         <v>36330</v>
       </c>
-      <c r="T8" s="13">
+      <c r="U8" s="13">
         <v>38680</v>
       </c>
-      <c r="U8" s="13">
+      <c r="V8" s="13">
         <v>39090</v>
       </c>
-      <c r="V8" s="13">
+      <c r="W8" s="13">
         <v>37300</v>
       </c>
-      <c r="W8" s="13">
+      <c r="X8" s="13">
         <v>37650</v>
       </c>
-      <c r="X8" s="13">
+      <c r="Y8" s="13">
         <v>37300</v>
       </c>
-      <c r="Y8" s="13">
+      <c r="Z8" s="13">
         <v>39450</v>
       </c>
-      <c r="Z8" s="13">
+      <c r="AA8" s="13">
         <v>38390</v>
       </c>
-      <c r="AA8" s="13">
+      <c r="AB8" s="13">
         <v>38800</v>
       </c>
-      <c r="AB8" s="13">
+      <c r="AC8" s="13">
         <v>38510</v>
-      </c>
-      <c r="AC8" s="13">
-        <v>38970</v>
       </c>
       <c r="AD8" s="13">
         <v>38970</v>
       </c>
       <c r="AE8" s="13">
-        <v>37700</v>
+        <v>38970</v>
       </c>
       <c r="AF8" s="13">
         <v>37700</v>
       </c>
       <c r="AG8" s="13">
+        <v>37700</v>
+      </c>
+      <c r="AH8" s="13">
         <v>37750</v>
       </c>
-      <c r="AH8" s="13">
+      <c r="AI8" s="13">
         <v>38430</v>
       </c>
-      <c r="AI8" s="13">
+      <c r="AJ8" s="13">
         <v>38250</v>
       </c>
-      <c r="AJ8" s="13">
+      <c r="AK8" s="13">
         <v>40110</v>
       </c>
-      <c r="AK8" s="13">
+      <c r="AL8" s="13">
         <v>40820</v>
       </c>
-      <c r="AL8" s="13">
+      <c r="AM8" s="13">
         <v>39320</v>
       </c>
-      <c r="AM8" s="13">
+      <c r="AN8" s="13">
         <v>37800</v>
       </c>
-      <c r="AN8" s="13">
+      <c r="AO8" s="13">
         <v>36620</v>
       </c>
-      <c r="AO8" s="13">
+      <c r="AP8" s="13">
         <v>37130</v>
       </c>
-      <c r="AP8" s="13">
+      <c r="AQ8" s="13">
         <v>35850</v>
       </c>
-      <c r="AQ8" s="13"/>
       <c r="AR8" s="13"/>
       <c r="AS8" s="13"/>
       <c r="AT8" s="13"/>
@@ -2253,39 +2279,40 @@
       <c r="BA8" s="13"/>
       <c r="BB8" s="13"/>
       <c r="BC8" s="13"/>
-      <c r="BD8" s="29"/>
-      <c r="BE8" s="13"/>
+      <c r="BD8" s="13"/>
+      <c r="BE8" s="29"/>
       <c r="BF8" s="13"/>
-      <c r="BG8" s="29"/>
-      <c r="BH8" s="13"/>
+      <c r="BG8" s="13"/>
+      <c r="BH8" s="29"/>
       <c r="BI8" s="13"/>
       <c r="BJ8" s="13"/>
       <c r="BK8" s="13"/>
-      <c r="BL8" s="13">
+      <c r="BL8" s="13"/>
+      <c r="BM8" s="13">
         <f t="shared" si="0"/>
         <v>806.25</v>
       </c>
-      <c r="BM8" s="13">
+      <c r="BN8" s="13">
         <f t="shared" si="2"/>
         <v>757.5</v>
       </c>
-      <c r="BN8" s="13">
-        <f t="shared" ref="BN8:BN11" si="3">(BM8-BL8)</f>
+      <c r="BO8" s="13">
+        <f t="shared" ref="BO8:BO11" si="3">(BN8-BM8)</f>
         <v>-48.75</v>
       </c>
-      <c r="BO8" s="13"/>
-      <c r="BP8">
+      <c r="BP8" s="13"/>
+      <c r="BQ8">
         <v>3</v>
       </c>
-      <c r="BQ8">
+      <c r="BR8">
         <v>36250</v>
       </c>
-      <c r="BR8" s="15">
-        <f>(BP8*BQ8-BP8*H8)/100</f>
+      <c r="BS8" s="15">
+        <f>(BQ8*BR8-BQ8*H8)/100</f>
         <v>-48.75</v>
       </c>
     </row>
-    <row r="9" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>629014</v>
       </c>
@@ -2314,102 +2341,104 @@
         <v>9227</v>
       </c>
       <c r="I9" s="13">
+        <v>9891</v>
+      </c>
+      <c r="J9" s="13">
+        <v>9956</v>
+      </c>
+      <c r="K9" s="13">
         <v>9910</v>
       </c>
-      <c r="J9" s="13">
-        <v>9910</v>
-      </c>
-      <c r="K9" s="13">
+      <c r="L9" s="13">
         <v>9960</v>
       </c>
-      <c r="L9" s="13">
+      <c r="M9" s="13">
         <v>9924</v>
       </c>
-      <c r="M9" s="13">
+      <c r="N9" s="13">
         <v>9999</v>
       </c>
-      <c r="N9" s="13">
+      <c r="O9" s="13">
         <v>9962</v>
       </c>
-      <c r="O9" s="13">
+      <c r="P9" s="13">
         <v>9979</v>
-      </c>
-      <c r="P9" s="13">
-        <v>10130</v>
       </c>
       <c r="Q9" s="13">
         <v>10130</v>
       </c>
       <c r="R9" s="13">
+        <v>10130</v>
+      </c>
+      <c r="S9" s="13">
         <v>10400</v>
       </c>
-      <c r="S9" s="13">
+      <c r="T9" s="13">
         <v>10320</v>
       </c>
-      <c r="T9" s="13">
+      <c r="U9" s="13">
         <v>10300</v>
       </c>
-      <c r="U9" s="13">
+      <c r="V9" s="13">
         <v>10310</v>
       </c>
-      <c r="V9" s="13">
+      <c r="W9" s="13">
         <v>9672</v>
       </c>
-      <c r="W9" s="13">
+      <c r="X9" s="13">
         <v>9953</v>
       </c>
-      <c r="X9" s="13">
+      <c r="Y9" s="13">
         <v>10090</v>
       </c>
-      <c r="Y9" s="13">
+      <c r="Z9" s="13">
         <v>10070</v>
       </c>
-      <c r="Z9" s="13">
+      <c r="AA9" s="13">
         <v>10030</v>
       </c>
-      <c r="AA9" s="13">
+      <c r="AB9" s="13">
         <v>10120</v>
       </c>
-      <c r="AB9" s="13">
+      <c r="AC9" s="13">
         <v>10000</v>
       </c>
-      <c r="AC9" s="13">
+      <c r="AD9" s="13">
         <v>10080</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AE9" s="13">
         <v>10030</v>
-      </c>
-      <c r="AE9" s="13">
-        <v>9726</v>
       </c>
       <c r="AF9" s="13">
         <v>9726</v>
       </c>
       <c r="AG9" s="13">
+        <v>9726</v>
+      </c>
+      <c r="AH9" s="13">
         <v>9659</v>
       </c>
-      <c r="AH9" s="13">
+      <c r="AI9" s="13">
         <v>9670</v>
       </c>
-      <c r="AI9" s="13">
+      <c r="AJ9" s="13">
         <v>9590</v>
       </c>
-      <c r="AJ9" s="13">
+      <c r="AK9" s="13">
         <v>9588</v>
       </c>
-      <c r="AK9" s="13">
+      <c r="AL9" s="13">
         <v>9400</v>
       </c>
-      <c r="AL9" s="13">
+      <c r="AM9" s="13">
         <v>9320</v>
       </c>
-      <c r="AM9" s="13">
+      <c r="AN9" s="13">
         <v>9071</v>
       </c>
-      <c r="AN9" s="13">
+      <c r="AO9" s="13">
         <v>9271</v>
       </c>
-      <c r="AO9" s="13"/>
       <c r="AP9" s="13"/>
       <c r="AQ9" s="13"/>
       <c r="AR9" s="13"/>
@@ -2424,39 +2453,40 @@
       <c r="BA9" s="13"/>
       <c r="BB9" s="13"/>
       <c r="BC9" s="13"/>
-      <c r="BD9" s="29"/>
-      <c r="BE9" s="13"/>
+      <c r="BD9" s="13"/>
+      <c r="BE9" s="29"/>
       <c r="BF9" s="13"/>
-      <c r="BG9" s="29"/>
-      <c r="BH9" s="13"/>
+      <c r="BG9" s="13"/>
+      <c r="BH9" s="29"/>
       <c r="BI9" s="13"/>
       <c r="BJ9" s="13"/>
       <c r="BK9" s="13"/>
-      <c r="BL9" s="13">
+      <c r="BL9" s="13"/>
+      <c r="BM9" s="13">
         <f t="shared" si="0"/>
         <v>-38.65</v>
       </c>
-      <c r="BM9" s="13">
+      <c r="BN9" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BN9" s="13">
+      <c r="BO9" s="13">
         <f t="shared" si="3"/>
         <v>38.65</v>
       </c>
-      <c r="BO9" s="13"/>
-      <c r="BP9">
+      <c r="BP9" s="13"/>
+      <c r="BQ9">
         <v>5</v>
       </c>
-      <c r="BQ9">
+      <c r="BR9">
         <v>10000</v>
       </c>
-      <c r="BR9" s="15">
-        <f>(BP9*BQ9-BP9*H9)/100</f>
+      <c r="BS9" s="15">
+        <f>(BQ9*BR9-BQ9*H9)/100</f>
         <v>38.65</v>
       </c>
     </row>
-    <row r="10" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1141464</v>
       </c>
@@ -2470,7 +2500,7 @@
       </c>
       <c r="D10" s="6" t="str">
         <f>IF(I10&lt;GEMINI!L10,"למכור בהפסד",IF(I10&gt;GEMINI!M10,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור בהפסד</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>39</v>
@@ -2485,184 +2515,187 @@
         <v>4834</v>
       </c>
       <c r="I10" s="13">
+        <v>4821</v>
+      </c>
+      <c r="J10" s="13">
+        <v>4925</v>
+      </c>
+      <c r="K10" s="13">
         <v>5013</v>
-      </c>
-      <c r="J10" s="13">
-        <v>5013</v>
-      </c>
-      <c r="K10" s="13">
-        <v>5050</v>
       </c>
       <c r="L10" s="13">
         <v>5050</v>
       </c>
       <c r="M10" s="13">
+        <v>5050</v>
+      </c>
+      <c r="N10" s="13">
         <v>4930</v>
       </c>
-      <c r="N10" s="13">
+      <c r="O10" s="13">
         <v>5150</v>
       </c>
-      <c r="O10" s="13">
+      <c r="P10" s="13">
         <v>5283</v>
-      </c>
-      <c r="P10" s="13">
-        <v>5253</v>
       </c>
       <c r="Q10" s="13">
         <v>5253</v>
       </c>
       <c r="R10" s="13">
+        <v>5253</v>
+      </c>
+      <c r="S10" s="13">
         <v>5400</v>
       </c>
-      <c r="S10" s="13">
+      <c r="T10" s="13">
         <v>5522</v>
       </c>
-      <c r="T10" s="13">
+      <c r="U10" s="13">
         <v>5690</v>
       </c>
-      <c r="U10" s="13">
+      <c r="V10" s="13">
         <v>5749</v>
       </c>
-      <c r="V10" s="13">
+      <c r="W10" s="13">
         <v>5840</v>
-      </c>
-      <c r="W10" s="13">
-        <v>5650</v>
       </c>
       <c r="X10" s="13">
         <v>5650</v>
       </c>
       <c r="Y10" s="13">
+        <v>5650</v>
+      </c>
+      <c r="Z10" s="13">
         <v>5841</v>
       </c>
-      <c r="Z10" s="13">
+      <c r="AA10" s="13">
         <v>5758</v>
       </c>
-      <c r="AA10" s="13">
+      <c r="AB10" s="13">
         <v>5673</v>
       </c>
-      <c r="AB10" s="13">
+      <c r="AC10" s="13">
         <v>5609</v>
       </c>
-      <c r="AC10" s="13">
+      <c r="AD10" s="13">
         <v>5750</v>
       </c>
-      <c r="AD10" s="13">
+      <c r="AE10" s="13">
         <v>5841</v>
-      </c>
-      <c r="AE10" s="13">
-        <v>5564</v>
       </c>
       <c r="AF10" s="13">
         <v>5564</v>
       </c>
       <c r="AG10" s="13">
+        <v>5564</v>
+      </c>
+      <c r="AH10" s="13">
         <v>5557</v>
       </c>
-      <c r="AH10" s="13">
+      <c r="AI10" s="13">
         <v>5501</v>
       </c>
-      <c r="AI10" s="13">
+      <c r="AJ10" s="13">
         <v>5250</v>
       </c>
-      <c r="AJ10" s="13">
+      <c r="AK10" s="13">
         <v>5270</v>
       </c>
-      <c r="AK10" s="13">
+      <c r="AL10" s="13">
         <v>5149</v>
       </c>
-      <c r="AL10" s="13">
+      <c r="AM10" s="13">
         <v>5092</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AN10" s="13">
         <v>5228</v>
       </c>
-      <c r="AN10" s="13">
+      <c r="AO10" s="13">
         <v>5301</v>
       </c>
-      <c r="AO10" s="13">
+      <c r="AP10" s="13">
         <v>5159</v>
       </c>
-      <c r="AP10" s="13">
+      <c r="AQ10" s="13">
         <v>5198</v>
       </c>
-      <c r="AQ10" s="13">
+      <c r="AR10" s="13">
         <v>5077</v>
       </c>
-      <c r="AR10" s="13">
+      <c r="AS10" s="13">
         <v>4842</v>
       </c>
-      <c r="AS10" s="13">
+      <c r="AT10" s="13">
         <v>5050</v>
       </c>
-      <c r="AT10" s="13">
+      <c r="AU10" s="13">
         <v>4970</v>
       </c>
-      <c r="AU10" s="13">
+      <c r="AV10" s="13">
         <v>4880</v>
       </c>
-      <c r="AV10" s="13">
+      <c r="AW10" s="13">
         <v>4704</v>
       </c>
-      <c r="AW10" s="13">
+      <c r="AX10" s="13">
         <v>4770</v>
       </c>
-      <c r="AX10" s="13">
+      <c r="AY10" s="13">
         <v>4609</v>
       </c>
-      <c r="AY10" s="13">
+      <c r="AZ10" s="13">
         <v>4674</v>
       </c>
-      <c r="AZ10" s="13">
+      <c r="BA10" s="13">
         <v>4710</v>
       </c>
-      <c r="BA10" s="13">
+      <c r="BB10" s="13">
         <v>4688</v>
       </c>
-      <c r="BB10" s="13">
+      <c r="BC10" s="13">
         <v>4900</v>
       </c>
-      <c r="BC10" s="13">
+      <c r="BD10" s="13">
         <v>5000</v>
       </c>
-      <c r="BD10" s="29">
+      <c r="BE10" s="29">
         <v>4932</v>
       </c>
-      <c r="BE10" s="13"/>
       <c r="BF10" s="13"/>
-      <c r="BG10" s="29"/>
-      <c r="BH10" s="13"/>
+      <c r="BG10" s="13"/>
+      <c r="BH10" s="29"/>
       <c r="BI10" s="13"/>
       <c r="BJ10" s="13"/>
       <c r="BK10" s="13"/>
-      <c r="BL10" s="13">
+      <c r="BL10" s="13"/>
+      <c r="BM10" s="13">
         <f t="shared" si="0"/>
         <v>-87.859799999999964</v>
       </c>
-      <c r="BM10" s="13">
+      <c r="BN10" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BN10" s="13">
+      <c r="BO10" s="13">
         <f t="shared" si="3"/>
         <v>87.859799999999964</v>
       </c>
-      <c r="BO10" s="13">
-        <f>((BC10-H10)/H10)*100</f>
+      <c r="BP10" s="13">
+        <f>((BD10-H10)/H10)*100</f>
         <v>3.434009102192801</v>
       </c>
-      <c r="BP10">
+      <c r="BQ10">
         <v>21</v>
       </c>
-      <c r="BQ10">
+      <c r="BR10">
         <v>5252.38</v>
       </c>
-      <c r="BR10" s="15">
-        <f>(BP10*BQ10-BP10*H10)/100</f>
+      <c r="BS10" s="15">
+        <f>(BQ10*BR10-BQ10*H10)/100</f>
         <v>87.859799999999964</v>
       </c>
     </row>
-    <row r="11" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1166974</v>
       </c>
@@ -2676,7 +2709,7 @@
       </c>
       <c r="D11" s="6" t="str">
         <f>IF(I11&lt;GEMINI!L11,"למכור בהפסד",IF(I11&gt;GEMINI!M11,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>72</v>
@@ -2691,66 +2724,68 @@
         <v>901.87</v>
       </c>
       <c r="I11" s="13">
+        <v>1090</v>
+      </c>
+      <c r="J11" s="13">
+        <v>1144</v>
+      </c>
+      <c r="K11" s="13">
         <v>1162</v>
       </c>
-      <c r="J11" s="13">
-        <v>1162</v>
-      </c>
-      <c r="K11" s="13">
+      <c r="L11" s="13">
         <v>1109</v>
       </c>
-      <c r="L11" s="13">
+      <c r="M11" s="13">
         <v>1029</v>
       </c>
-      <c r="M11" s="13">
+      <c r="N11" s="13">
         <v>993</v>
       </c>
-      <c r="N11" s="13">
+      <c r="O11" s="13">
         <v>1017</v>
       </c>
-      <c r="O11" s="13">
+      <c r="P11" s="13">
         <v>960</v>
-      </c>
-      <c r="P11" s="13">
-        <v>965</v>
       </c>
       <c r="Q11" s="13">
         <v>965</v>
       </c>
       <c r="R11" s="13">
+        <v>965</v>
+      </c>
+      <c r="S11" s="13">
         <v>951.7</v>
       </c>
-      <c r="S11" s="13">
+      <c r="T11" s="13">
         <v>946</v>
       </c>
-      <c r="T11" s="13">
+      <c r="U11" s="13">
         <v>869.2</v>
       </c>
-      <c r="U11" s="13">
+      <c r="V11" s="13">
         <v>865</v>
       </c>
-      <c r="V11" s="13">
+      <c r="W11" s="13">
         <v>851</v>
       </c>
-      <c r="W11" s="13">
+      <c r="X11" s="13">
         <v>829.3</v>
       </c>
-      <c r="X11" s="13">
+      <c r="Y11" s="13">
         <v>830</v>
       </c>
-      <c r="Y11" s="13">
+      <c r="Z11" s="13">
         <v>810</v>
       </c>
-      <c r="Z11" s="13">
+      <c r="AA11" s="13">
         <v>812.8</v>
       </c>
-      <c r="AA11" s="13">
+      <c r="AB11" s="13">
         <v>788</v>
       </c>
-      <c r="AB11" s="13">
+      <c r="AC11" s="13">
         <v>772</v>
       </c>
-      <c r="AC11" s="13"/>
       <c r="AD11" s="13"/>
       <c r="AE11" s="13"/>
       <c r="AF11" s="13"/>
@@ -2777,33 +2812,34 @@
       <c r="BA11" s="13"/>
       <c r="BB11" s="13"/>
       <c r="BC11" s="13"/>
-      <c r="BD11" s="29"/>
-      <c r="BE11" s="13"/>
+      <c r="BD11" s="13"/>
+      <c r="BE11" s="29"/>
       <c r="BF11" s="13"/>
-      <c r="BG11" s="29"/>
-      <c r="BH11" s="13"/>
+      <c r="BG11" s="13"/>
+      <c r="BH11" s="29"/>
       <c r="BI11" s="13"/>
       <c r="BJ11" s="13"/>
       <c r="BK11" s="13"/>
-      <c r="BL11" s="13">
+      <c r="BL11" s="13"/>
+      <c r="BM11" s="13">
         <f t="shared" si="0"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BM11" s="13">
+      <c r="BN11" s="13">
         <f t="shared" si="2"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BN11" s="13">
+      <c r="BO11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BO11" s="13"/>
-      <c r="BR11" s="15">
-        <f>(BP11*BQ11-BP11*H11)/100</f>
+      <c r="BP11" s="13"/>
+      <c r="BS11" s="15">
+        <f>(BQ11*BR11-BQ11*H11)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1176593</v>
       </c>
@@ -2817,7 +2853,7 @@
       </c>
       <c r="D12" s="6" t="str">
         <f>IF(I12&lt;GEMINI!L12,"למכור בהפסד",IF(I12&gt;GEMINI!M12,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>68</v>
@@ -2832,72 +2868,74 @@
         <v>22581.42</v>
       </c>
       <c r="I12" s="13">
+        <v>30500</v>
+      </c>
+      <c r="J12" s="13">
+        <v>28850</v>
+      </c>
+      <c r="K12" s="13">
         <v>27450</v>
       </c>
-      <c r="J12" s="13">
-        <v>27450</v>
-      </c>
-      <c r="K12" s="13">
+      <c r="L12" s="13">
         <v>26940</v>
       </c>
-      <c r="L12" s="13">
+      <c r="M12" s="13">
         <v>26800</v>
       </c>
-      <c r="M12" s="13">
+      <c r="N12" s="13">
         <v>25950</v>
       </c>
-      <c r="N12" s="13">
+      <c r="O12" s="13">
         <v>26000</v>
       </c>
-      <c r="O12" s="13">
+      <c r="P12" s="13">
         <v>26600</v>
-      </c>
-      <c r="P12" s="13">
-        <v>24630</v>
       </c>
       <c r="Q12" s="13">
         <v>24630</v>
       </c>
       <c r="R12" s="13">
+        <v>24630</v>
+      </c>
+      <c r="S12" s="13">
         <v>25230</v>
       </c>
-      <c r="S12" s="13">
+      <c r="T12" s="13">
         <v>24700</v>
       </c>
-      <c r="T12" s="13">
+      <c r="U12" s="13">
         <v>23780</v>
       </c>
-      <c r="U12" s="13">
+      <c r="V12" s="13">
         <v>23920</v>
       </c>
-      <c r="V12" s="13">
+      <c r="W12" s="13">
         <v>22390</v>
       </c>
-      <c r="W12" s="13">
+      <c r="X12" s="13">
         <v>23000</v>
       </c>
-      <c r="X12" s="13">
+      <c r="Y12" s="13">
         <v>20990</v>
       </c>
-      <c r="Y12" s="13">
+      <c r="Z12" s="13">
         <v>20260</v>
       </c>
-      <c r="Z12" s="13">
+      <c r="AA12" s="13">
         <v>19200</v>
       </c>
-      <c r="AA12" s="13">
+      <c r="AB12" s="13">
         <v>19860</v>
       </c>
-      <c r="AB12" s="13">
+      <c r="AC12" s="13">
         <v>19700</v>
       </c>
-      <c r="AC12" s="13">
+      <c r="AD12" s="13">
         <v>19430</v>
       </c>
-      <c r="AD12" s="13">
+      <c r="AE12" s="13">
         <v>19020</v>
       </c>
-      <c r="AE12" s="13"/>
       <c r="AF12" s="13"/>
       <c r="AG12" s="13"/>
       <c r="AH12" s="13"/>
@@ -2922,30 +2960,31 @@
       <c r="BA12" s="13"/>
       <c r="BB12" s="13"/>
       <c r="BC12" s="13"/>
-      <c r="BD12" s="29"/>
-      <c r="BE12" s="13"/>
+      <c r="BD12" s="13"/>
+      <c r="BE12" s="29"/>
       <c r="BF12" s="13"/>
-      <c r="BG12" s="29"/>
-      <c r="BH12" s="13"/>
+      <c r="BG12" s="13"/>
+      <c r="BH12" s="29"/>
       <c r="BI12" s="13"/>
       <c r="BJ12" s="13"/>
       <c r="BK12" s="13"/>
-      <c r="BL12" s="13">
+      <c r="BL12" s="13"/>
+      <c r="BM12" s="13">
         <f t="shared" si="0"/>
         <v>1580.6994</v>
       </c>
-      <c r="BM12" s="13">
+      <c r="BN12" s="13">
         <f t="shared" si="2"/>
         <v>1580.6994</v>
       </c>
-      <c r="BN12" s="13"/>
       <c r="BO12" s="13"/>
-      <c r="BR12" s="15">
-        <f t="shared" ref="BR12:BR14" si="4">(BP12*BQ12-BP12*H12)/100</f>
+      <c r="BP12" s="13"/>
+      <c r="BS12" s="15">
+        <f t="shared" ref="BS12:BS14" si="4">(BQ12*BR12-BQ12*H12)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>397018</v>
       </c>
@@ -2959,7 +2998,7 @@
       </c>
       <c r="D13" s="6" t="str">
         <f>IF(I13&lt;GEMINI!L13,"למכור בהפסד",IF(I13&gt;GEMINI!M13,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>96</v>
@@ -2974,24 +3013,26 @@
         <v>723</v>
       </c>
       <c r="I13" s="13">
+        <v>1490</v>
+      </c>
+      <c r="J13" s="13">
+        <v>1210</v>
+      </c>
+      <c r="K13" s="13">
         <v>1100</v>
       </c>
-      <c r="J13" s="13">
-        <v>1100</v>
-      </c>
-      <c r="K13" s="13">
+      <c r="L13" s="13">
         <v>980</v>
       </c>
-      <c r="L13" s="13">
+      <c r="M13" s="13">
         <v>932.1</v>
       </c>
-      <c r="M13" s="13">
+      <c r="N13" s="13">
         <v>822</v>
       </c>
-      <c r="N13" s="13">
+      <c r="O13" s="13">
         <v>790</v>
       </c>
-      <c r="O13" s="13"/>
       <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
       <c r="R13" s="13"/>
@@ -3032,30 +3073,31 @@
       <c r="BA13" s="13"/>
       <c r="BB13" s="13"/>
       <c r="BC13" s="13"/>
-      <c r="BD13" s="29"/>
-      <c r="BE13" s="13"/>
+      <c r="BD13" s="13"/>
+      <c r="BE13" s="29"/>
       <c r="BF13" s="13"/>
-      <c r="BG13" s="29"/>
-      <c r="BH13" s="13"/>
+      <c r="BG13" s="13"/>
+      <c r="BH13" s="29"/>
       <c r="BI13" s="13"/>
       <c r="BJ13" s="13"/>
       <c r="BK13" s="13"/>
-      <c r="BL13" s="13">
+      <c r="BL13" s="13"/>
+      <c r="BM13" s="13">
         <f t="shared" si="0"/>
         <v>816.99</v>
       </c>
-      <c r="BM13" s="13">
+      <c r="BN13" s="13">
         <f t="shared" si="2"/>
         <v>816.99</v>
       </c>
-      <c r="BN13" s="13"/>
       <c r="BO13" s="13"/>
-      <c r="BR13" s="15">
+      <c r="BP13" s="13"/>
+      <c r="BS13" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>662577</v>
       </c>
@@ -3084,192 +3126,195 @@
         <v>7204.22</v>
       </c>
       <c r="I14" s="13">
+        <v>7676</v>
+      </c>
+      <c r="J14" s="13">
+        <v>7844</v>
+      </c>
+      <c r="K14" s="13">
         <v>7810</v>
       </c>
-      <c r="J14" s="13">
-        <v>7810</v>
-      </c>
-      <c r="K14" s="13">
+      <c r="L14" s="13">
         <v>7710</v>
       </c>
-      <c r="L14" s="13">
+      <c r="M14" s="13">
         <v>7735</v>
       </c>
-      <c r="M14" s="13">
+      <c r="N14" s="13">
         <v>7725</v>
       </c>
-      <c r="N14" s="13">
+      <c r="O14" s="13">
         <v>7787</v>
       </c>
-      <c r="O14" s="13">
+      <c r="P14" s="13">
         <v>7955</v>
-      </c>
-      <c r="P14" s="13">
-        <v>7627</v>
       </c>
       <c r="Q14" s="13">
         <v>7627</v>
       </c>
       <c r="R14" s="13">
+        <v>7627</v>
+      </c>
+      <c r="S14" s="13">
         <v>7656</v>
       </c>
-      <c r="S14" s="13">
+      <c r="T14" s="13">
         <v>7507</v>
       </c>
-      <c r="T14" s="13">
+      <c r="U14" s="13">
         <v>7590</v>
       </c>
-      <c r="U14" s="13">
+      <c r="V14" s="13">
         <v>7569</v>
       </c>
-      <c r="V14" s="13">
+      <c r="W14" s="13">
         <v>7269</v>
       </c>
-      <c r="W14" s="13">
+      <c r="X14" s="13">
         <v>7444</v>
       </c>
-      <c r="X14" s="13">
+      <c r="Y14" s="13">
         <v>7205</v>
       </c>
-      <c r="Y14" s="13">
+      <c r="Z14" s="13">
         <v>7298</v>
       </c>
-      <c r="Z14" s="13">
+      <c r="AA14" s="13">
         <v>7222</v>
       </c>
-      <c r="AA14" s="13">
+      <c r="AB14" s="13">
         <v>7079</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AC14" s="13">
         <v>7140</v>
       </c>
-      <c r="AC14" s="13">
+      <c r="AD14" s="13">
         <v>7440</v>
       </c>
-      <c r="AD14" s="13">
+      <c r="AE14" s="13">
         <v>7530</v>
-      </c>
-      <c r="AE14" s="13">
-        <v>7535</v>
       </c>
       <c r="AF14" s="13">
         <v>7535</v>
       </c>
       <c r="AG14" s="13">
+        <v>7535</v>
+      </c>
+      <c r="AH14" s="13">
         <v>7568</v>
       </c>
-      <c r="AH14" s="13">
+      <c r="AI14" s="13">
         <v>7699</v>
       </c>
-      <c r="AI14" s="13">
+      <c r="AJ14" s="13">
         <v>7638</v>
       </c>
-      <c r="AJ14" s="13">
+      <c r="AK14" s="13">
         <v>7654</v>
       </c>
-      <c r="AK14" s="13">
+      <c r="AL14" s="13">
         <v>7584</v>
       </c>
-      <c r="AL14" s="13">
+      <c r="AM14" s="13">
         <v>7479</v>
       </c>
-      <c r="AM14" s="13">
+      <c r="AN14" s="13">
         <v>7490</v>
       </c>
-      <c r="AN14" s="13">
+      <c r="AO14" s="13">
         <v>7480</v>
       </c>
-      <c r="AO14" s="13">
+      <c r="AP14" s="13">
         <v>7270</v>
       </c>
-      <c r="AP14" s="13">
+      <c r="AQ14" s="13">
         <v>7163</v>
       </c>
-      <c r="AQ14" s="13">
+      <c r="AR14" s="13">
         <v>7231</v>
-      </c>
-      <c r="AR14" s="13">
-        <v>7100</v>
       </c>
       <c r="AS14" s="13">
         <v>7100</v>
       </c>
       <c r="AT14" s="13">
+        <v>7100</v>
+      </c>
+      <c r="AU14" s="13">
         <v>7027</v>
       </c>
-      <c r="AU14" s="13">
+      <c r="AV14" s="13">
         <v>6984</v>
       </c>
-      <c r="AV14" s="13">
+      <c r="AW14" s="13">
         <v>6944</v>
       </c>
-      <c r="AW14" s="13">
+      <c r="AX14" s="13">
         <v>6924</v>
       </c>
-      <c r="AX14" s="13">
+      <c r="AY14" s="13">
         <v>6930</v>
       </c>
-      <c r="AY14" s="13">
+      <c r="AZ14" s="13">
         <v>6938</v>
       </c>
-      <c r="AZ14" s="13">
+      <c r="BA14" s="13">
         <v>6989</v>
       </c>
-      <c r="BA14" s="13">
+      <c r="BB14" s="13">
         <v>6871</v>
       </c>
-      <c r="BB14" s="13">
+      <c r="BC14" s="13">
         <v>6943</v>
       </c>
-      <c r="BC14" s="13">
+      <c r="BD14" s="13">
         <v>7040</v>
       </c>
-      <c r="BD14" s="29">
+      <c r="BE14" s="29">
         <v>6696</v>
       </c>
-      <c r="BE14" s="13">
+      <c r="BF14" s="13">
         <v>6965</v>
       </c>
-      <c r="BF14" s="13">
+      <c r="BG14" s="13">
         <v>6788</v>
       </c>
-      <c r="BG14" s="29">
+      <c r="BH14" s="29">
         <v>6696</v>
       </c>
-      <c r="BH14" s="13">
+      <c r="BI14" s="13">
         <v>6625</v>
       </c>
-      <c r="BI14" s="13">
+      <c r="BJ14" s="13">
         <v>6660</v>
       </c>
-      <c r="BJ14" s="13">
+      <c r="BK14" s="13">
         <v>6791</v>
       </c>
-      <c r="BK14" s="13">
+      <c r="BL14" s="13">
         <v>6610</v>
       </c>
-      <c r="BL14" s="13">
+      <c r="BM14" s="13">
         <f t="shared" si="0"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BM14" s="13">
+      <c r="BN14" s="13">
         <f t="shared" si="2"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BN14" s="13">
-        <f t="shared" ref="BN14" si="5">(BM14-BL14)</f>
+      <c r="BO14" s="13">
+        <f t="shared" ref="BO14" si="5">(BN14-BM14)</f>
         <v>0</v>
       </c>
-      <c r="BO14" s="13">
-        <f>((BC14-H14)/H14)*100</f>
+      <c r="BP14" s="13">
+        <f>((BD14-H14)/H14)*100</f>
         <v>-2.2794972946411995</v>
       </c>
-      <c r="BR14" s="15">
+      <c r="BS14" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>5137534</v>
       </c>
@@ -3283,7 +3328,7 @@
       </c>
       <c r="D15" s="6" t="str">
         <f>IF(I15&lt;GEMINI!L15,"למכור בהפסד",IF(I15&gt;GEMINI!M15,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>78</v>
@@ -3298,60 +3343,62 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
+        <v>14583.37</v>
+      </c>
+      <c r="J15" s="13">
+        <v>13968</v>
+      </c>
+      <c r="K15" s="13">
         <v>15528.12</v>
       </c>
-      <c r="J15" s="13">
-        <v>15528.12</v>
-      </c>
-      <c r="K15" s="13">
+      <c r="L15" s="13">
         <v>14358.25</v>
       </c>
-      <c r="L15" s="13">
+      <c r="M15" s="13">
         <v>14385.75</v>
       </c>
-      <c r="M15" s="13">
+      <c r="N15" s="13">
         <v>13880</v>
       </c>
-      <c r="N15" s="13">
+      <c r="O15" s="13">
         <v>13610.62</v>
       </c>
-      <c r="O15" s="13">
+      <c r="P15" s="13">
         <v>13016</v>
       </c>
-      <c r="P15" s="13">
+      <c r="Q15" s="13">
         <v>12487.37</v>
       </c>
-      <c r="Q15" s="13">
+      <c r="R15" s="13">
         <v>12638.62</v>
       </c>
-      <c r="R15" s="13">
+      <c r="S15" s="13">
         <v>12533.87</v>
       </c>
-      <c r="S15" s="13">
+      <c r="T15" s="13">
         <v>11299.5</v>
       </c>
-      <c r="T15" s="13">
+      <c r="U15" s="13">
         <v>11193.12</v>
       </c>
-      <c r="U15" s="13">
+      <c r="V15" s="13">
         <v>11548.62</v>
       </c>
-      <c r="V15" s="13">
+      <c r="W15" s="13">
         <v>11125.62</v>
       </c>
-      <c r="W15" s="13">
+      <c r="X15" s="13">
         <v>10932.12</v>
       </c>
-      <c r="X15" s="13">
+      <c r="Y15" s="13">
         <v>11095.62</v>
       </c>
-      <c r="Y15" s="13">
+      <c r="Z15" s="13">
         <v>10910.58</v>
       </c>
-      <c r="Z15" s="13">
+      <c r="AA15" s="13">
         <v>11609.37</v>
       </c>
-      <c r="AA15" s="13"/>
       <c r="AB15" s="13"/>
       <c r="AC15" s="13"/>
       <c r="AD15" s="13"/>
@@ -3361,8 +3408,8 @@
       <c r="AH15" s="13"/>
       <c r="AI15" s="13"/>
       <c r="AJ15" s="13"/>
-      <c r="AK15" s="14"/>
-      <c r="AL15" s="13"/>
+      <c r="AK15" s="13"/>
+      <c r="AL15" s="14"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="13"/>
       <c r="AO15" s="13"/>
@@ -3380,36 +3427,37 @@
       <c r="BA15" s="13"/>
       <c r="BB15" s="13"/>
       <c r="BC15" s="13"/>
-      <c r="BD15" s="29"/>
-      <c r="BE15" s="13"/>
+      <c r="BD15" s="13"/>
+      <c r="BE15" s="29"/>
       <c r="BF15" s="13"/>
-      <c r="BG15" s="29"/>
-      <c r="BH15" s="13"/>
+      <c r="BG15" s="13"/>
+      <c r="BH15" s="29"/>
       <c r="BI15" s="13"/>
       <c r="BJ15" s="13"/>
       <c r="BK15" s="13"/>
-      <c r="BL15" s="13">
+      <c r="BL15" s="13"/>
+      <c r="BM15" s="13">
         <f t="shared" si="0"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BM15" s="13">
+      <c r="BN15" s="13">
         <f t="shared" si="2"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BN15" s="13">
-        <f t="shared" ref="BN15:BN18" si="6">(BM15-BL15)</f>
+      <c r="BO15" s="13">
+        <f t="shared" ref="BO15:BO18" si="6">(BN15-BM15)</f>
         <v>0</v>
       </c>
-      <c r="BO15" s="13">
-        <f>((BC15-H15)/H15)*100</f>
+      <c r="BP15" s="13">
+        <f>((BD15-H15)/H15)*100</f>
         <v>-100</v>
       </c>
-      <c r="BR15" s="15">
-        <f t="shared" ref="BR15:BR18" si="7">(BP15*BQ15-BP15*H15)/100</f>
+      <c r="BS15" s="15">
+        <f t="shared" ref="BS15:BS18" si="7">(BQ15*BR15-BQ15*H15)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>5135470</v>
       </c>
@@ -3438,198 +3486,201 @@
         <v>183.73</v>
       </c>
       <c r="I16" s="13">
+        <v>226.96</v>
+      </c>
+      <c r="J16" s="13">
+        <v>225.24</v>
+      </c>
+      <c r="K16" s="13">
         <v>223.25</v>
-      </c>
-      <c r="J16" s="13">
-        <v>223.25</v>
-      </c>
-      <c r="K16" s="13">
-        <v>219.14</v>
       </c>
       <c r="L16" s="13">
         <v>219.14</v>
       </c>
       <c r="M16" s="13">
+        <v>219.14</v>
+      </c>
+      <c r="N16" s="13">
         <v>219.3</v>
       </c>
-      <c r="N16" s="13">
+      <c r="O16" s="13">
         <v>222.79</v>
       </c>
-      <c r="O16" s="13">
+      <c r="P16" s="13">
         <v>221.16</v>
       </c>
-      <c r="P16" s="13">
+      <c r="Q16" s="13">
         <v>220.66</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="R16" s="13">
         <v>222.06</v>
       </c>
-      <c r="R16" s="13">
+      <c r="S16" s="13">
         <v>218.71</v>
       </c>
-      <c r="S16" s="13">
+      <c r="T16" s="13">
         <v>216.74</v>
       </c>
-      <c r="T16" s="13">
+      <c r="U16" s="13">
         <v>216.04</v>
-      </c>
-      <c r="U16" s="13">
-        <v>210.69</v>
       </c>
       <c r="V16" s="13">
         <v>210.69</v>
       </c>
       <c r="W16" s="13">
+        <v>210.69</v>
+      </c>
+      <c r="X16" s="13">
         <v>198</v>
       </c>
-      <c r="X16" s="13">
+      <c r="Y16" s="13">
         <v>196.74</v>
       </c>
-      <c r="Y16" s="13">
+      <c r="Z16" s="13">
         <v>192.56</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="AA16" s="13">
         <v>192.23</v>
       </c>
-      <c r="AA16" s="13">
+      <c r="AB16" s="13">
         <v>191.19</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AC16" s="13">
         <v>193.62</v>
       </c>
-      <c r="AC16" s="13">
+      <c r="AD16" s="13">
         <v>190.75</v>
       </c>
-      <c r="AD16" s="13">
+      <c r="AE16" s="13">
         <v>189.06</v>
-      </c>
-      <c r="AE16" s="13">
-        <v>182.73</v>
       </c>
       <c r="AF16" s="13">
         <v>182.73</v>
       </c>
       <c r="AG16" s="13">
+        <v>182.73</v>
+      </c>
+      <c r="AH16" s="13">
         <v>177.92</v>
       </c>
-      <c r="AH16" s="13">
+      <c r="AI16" s="13">
         <v>179.16</v>
       </c>
-      <c r="AI16" s="13">
+      <c r="AJ16" s="13">
         <v>179.34</v>
-      </c>
-      <c r="AJ16" s="13">
-        <v>176.5</v>
       </c>
       <c r="AK16" s="13">
         <v>176.5</v>
       </c>
       <c r="AL16" s="13">
+        <v>176.5</v>
+      </c>
+      <c r="AM16" s="13">
         <v>175.93</v>
       </c>
-      <c r="AM16" s="13">
+      <c r="AN16" s="13">
         <v>174.51</v>
       </c>
-      <c r="AN16" s="13">
+      <c r="AO16" s="13">
         <v>173.91</v>
       </c>
-      <c r="AO16" s="13">
+      <c r="AP16" s="13">
         <v>177.1</v>
       </c>
-      <c r="AP16" s="13">
+      <c r="AQ16" s="13">
         <v>178.24</v>
       </c>
-      <c r="AQ16" s="13">
+      <c r="AR16" s="13">
         <v>176.52</v>
       </c>
-      <c r="AR16" s="13">
+      <c r="AS16" s="13">
         <v>178.27</v>
       </c>
-      <c r="AS16" s="13">
+      <c r="AT16" s="13">
         <v>175.29</v>
       </c>
-      <c r="AT16" s="13">
+      <c r="AU16" s="13">
         <v>175.34</v>
       </c>
-      <c r="AU16" s="13">
+      <c r="AV16" s="13">
         <v>174.41</v>
       </c>
-      <c r="AV16" s="13">
+      <c r="AW16" s="13">
         <v>176.22</v>
       </c>
-      <c r="AW16" s="13">
+      <c r="AX16" s="13">
         <v>174</v>
       </c>
-      <c r="AX16" s="13">
+      <c r="AY16" s="13">
         <v>176.35</v>
       </c>
-      <c r="AY16" s="13">
+      <c r="AZ16" s="13">
         <v>177.71</v>
       </c>
-      <c r="AZ16" s="13">
+      <c r="BA16" s="13">
         <v>180.08</v>
       </c>
-      <c r="BA16" s="13">
+      <c r="BB16" s="13">
         <v>181.96</v>
       </c>
-      <c r="BB16" s="13">
+      <c r="BC16" s="13">
         <v>182.9</v>
       </c>
-      <c r="BC16" s="13">
+      <c r="BD16" s="13">
         <v>181.86</v>
       </c>
-      <c r="BD16" s="29">
+      <c r="BE16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BE16" s="13">
+      <c r="BF16" s="13">
         <v>181.07</v>
       </c>
-      <c r="BF16" s="13">
+      <c r="BG16" s="13">
         <v>182.56</v>
       </c>
-      <c r="BG16" s="29">
+      <c r="BH16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BH16" s="13">
+      <c r="BI16" s="13">
         <v>178.86</v>
       </c>
-      <c r="BI16" s="13">
+      <c r="BJ16" s="13">
         <v>180.16</v>
       </c>
-      <c r="BJ16" s="13">
+      <c r="BK16" s="13">
         <v>179.56</v>
       </c>
-      <c r="BK16" s="13">
+      <c r="BL16" s="13">
         <v>176.55</v>
       </c>
-      <c r="BL16" s="13">
+      <c r="BM16" s="13">
         <f t="shared" si="0"/>
         <v>673.09559999999999</v>
       </c>
-      <c r="BM16" s="13">
+      <c r="BN16" s="13">
         <f t="shared" si="2"/>
         <v>551.19000000000005</v>
       </c>
-      <c r="BN16" s="13">
+      <c r="BO16" s="13">
         <f t="shared" si="6"/>
         <v>-121.90559999999994</v>
       </c>
-      <c r="BO16" s="13">
-        <f>((BC16-H16)/H16)*100</f>
+      <c r="BP16" s="13">
+        <f>((BD16-H16)/H16)*100</f>
         <v>-1.0177978555488905</v>
       </c>
-      <c r="BP16">
+      <c r="BQ16">
         <v>1864</v>
       </c>
-      <c r="BQ16">
+      <c r="BR16">
         <v>177.19</v>
       </c>
-      <c r="BR16" s="15">
+      <c r="BS16" s="15">
         <f t="shared" si="7"/>
         <v>-121.90559999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>5134135</v>
       </c>
@@ -3664,13 +3715,13 @@
         <v>189.51</v>
       </c>
       <c r="K17" s="13">
-        <v>185.52</v>
+        <v>189.51</v>
       </c>
       <c r="L17" s="13">
         <v>185.52</v>
       </c>
       <c r="M17" s="13">
-        <v>178.98</v>
+        <v>185.52</v>
       </c>
       <c r="N17" s="13">
         <v>178.98</v>
@@ -3679,7 +3730,7 @@
         <v>178.98</v>
       </c>
       <c r="P17" s="13">
-        <v>170.7</v>
+        <v>178.98</v>
       </c>
       <c r="Q17" s="13">
         <v>170.7</v>
@@ -3688,10 +3739,10 @@
         <v>170.7</v>
       </c>
       <c r="S17" s="13">
+        <v>170.7</v>
+      </c>
+      <c r="T17" s="13">
         <v>170.45</v>
-      </c>
-      <c r="T17" s="13">
-        <v>160.84</v>
       </c>
       <c r="U17" s="13">
         <v>160.84</v>
@@ -3700,15 +3751,17 @@
         <v>160.84</v>
       </c>
       <c r="W17" s="13">
+        <v>160.84</v>
+      </c>
+      <c r="X17" s="13">
         <v>159.02000000000001</v>
-      </c>
-      <c r="X17" s="13">
-        <v>159.65</v>
       </c>
       <c r="Y17" s="13">
         <v>159.65</v>
       </c>
-      <c r="Z17" s="13"/>
+      <c r="Z17" s="13">
+        <v>159.65</v>
+      </c>
       <c r="AA17" s="13"/>
       <c r="AB17" s="13"/>
       <c r="AC17" s="13"/>
@@ -3738,36 +3791,37 @@
       <c r="BA17" s="13"/>
       <c r="BB17" s="13"/>
       <c r="BC17" s="13"/>
-      <c r="BD17" s="29"/>
-      <c r="BE17" s="13"/>
+      <c r="BD17" s="13"/>
+      <c r="BE17" s="29"/>
       <c r="BF17" s="13"/>
-      <c r="BG17" s="29"/>
-      <c r="BH17" s="13"/>
+      <c r="BG17" s="13"/>
+      <c r="BH17" s="29"/>
       <c r="BI17" s="13"/>
       <c r="BJ17" s="13"/>
       <c r="BK17" s="13"/>
-      <c r="BL17" s="13">
+      <c r="BL17" s="13"/>
+      <c r="BM17" s="13">
         <f t="shared" si="0"/>
         <v>957.9</v>
       </c>
-      <c r="BM17" s="13">
+      <c r="BN17" s="13">
         <f t="shared" si="2"/>
         <v>957.9</v>
       </c>
-      <c r="BN17" s="13">
-        <f t="shared" ref="BN17" si="8">(BM17-BL17)</f>
+      <c r="BO17" s="13">
+        <f t="shared" ref="BO17" si="8">(BN17-BM17)</f>
         <v>0</v>
       </c>
-      <c r="BO17" s="13">
-        <f>((BC17-H17)/H17)*100</f>
+      <c r="BP17" s="13">
+        <f>((BD17-H17)/H17)*100</f>
         <v>-100</v>
       </c>
-      <c r="BR17" s="15">
+      <c r="BS17" s="15">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1168723</v>
       </c>
@@ -3796,63 +3850,65 @@
         <v>1434</v>
       </c>
       <c r="I18" s="13">
+        <v>1811</v>
+      </c>
+      <c r="J18" s="13">
+        <v>1825</v>
+      </c>
+      <c r="K18" s="13">
         <v>1831</v>
       </c>
-      <c r="J18" s="13">
-        <v>1831</v>
-      </c>
-      <c r="K18" s="13">
+      <c r="L18" s="13">
         <v>1799</v>
       </c>
-      <c r="L18" s="13">
+      <c r="M18" s="13">
         <v>1757</v>
       </c>
-      <c r="M18" s="13">
+      <c r="N18" s="13">
         <v>1698</v>
       </c>
-      <c r="N18" s="13">
+      <c r="O18" s="13">
         <v>1694</v>
       </c>
-      <c r="O18" s="13">
+      <c r="P18" s="13">
         <v>1671</v>
-      </c>
-      <c r="P18" s="13">
-        <v>1660</v>
       </c>
       <c r="Q18" s="13">
         <v>1660</v>
       </c>
       <c r="R18" s="13">
+        <v>1660</v>
+      </c>
+      <c r="S18" s="13">
         <v>1646</v>
       </c>
-      <c r="S18" s="13">
+      <c r="T18" s="13">
         <v>1648</v>
       </c>
-      <c r="T18" s="13">
+      <c r="U18" s="13">
         <v>1614</v>
       </c>
-      <c r="U18" s="13">
+      <c r="V18" s="13">
         <v>1626</v>
       </c>
-      <c r="V18" s="13">
+      <c r="W18" s="13">
         <v>1587</v>
       </c>
-      <c r="W18" s="13">
+      <c r="X18" s="13">
         <v>1548</v>
       </c>
-      <c r="X18" s="13">
+      <c r="Y18" s="13">
         <v>1500</v>
       </c>
-      <c r="Y18" s="13">
+      <c r="Z18" s="13">
         <v>1491</v>
       </c>
-      <c r="Z18" s="13">
+      <c r="AA18" s="13">
         <v>1444</v>
       </c>
-      <c r="AA18" s="13">
+      <c r="AB18" s="13">
         <v>1431</v>
       </c>
-      <c r="AB18" s="13"/>
       <c r="AC18" s="13"/>
       <c r="AD18" s="13"/>
       <c r="AE18" s="13"/>
@@ -3878,64 +3934,65 @@
       <c r="AY18" s="13"/>
       <c r="AZ18" s="13"/>
       <c r="BA18" s="13"/>
-      <c r="BB18" s="13">
-        <v>1788</v>
-      </c>
+      <c r="BB18" s="13"/>
       <c r="BC18" s="13">
         <v>1788</v>
       </c>
-      <c r="BD18" s="29">
+      <c r="BD18" s="13">
+        <v>1788</v>
+      </c>
+      <c r="BE18" s="29">
         <v>1780</v>
       </c>
-      <c r="BE18" s="13">
+      <c r="BF18" s="13">
         <v>1814</v>
       </c>
-      <c r="BF18" s="13">
+      <c r="BG18" s="13">
         <v>1794</v>
       </c>
-      <c r="BG18" s="29">
+      <c r="BH18" s="29">
         <v>1780</v>
       </c>
-      <c r="BH18" s="13">
+      <c r="BI18" s="13">
         <v>1772</v>
       </c>
-      <c r="BI18" s="13">
+      <c r="BJ18" s="13">
         <v>1798</v>
       </c>
-      <c r="BJ18" s="13">
+      <c r="BK18" s="13">
         <v>1806</v>
       </c>
-      <c r="BK18" s="13">
+      <c r="BL18" s="13">
         <v>1801</v>
       </c>
-      <c r="BL18" s="13">
+      <c r="BM18" s="13">
         <f t="shared" si="0"/>
         <v>292.79999999999995</v>
       </c>
-      <c r="BM18" s="13">
+      <c r="BN18" s="13">
         <f t="shared" si="2"/>
         <v>645.29999999999995</v>
       </c>
-      <c r="BN18" s="13">
+      <c r="BO18" s="13">
         <f t="shared" si="6"/>
         <v>352.5</v>
       </c>
-      <c r="BO18" s="13">
-        <f>((BC18-H18)/H18)*100</f>
+      <c r="BP18" s="13">
+        <f>((BD18-H18)/H18)*100</f>
         <v>24.686192468619247</v>
       </c>
-      <c r="BP18">
+      <c r="BQ18">
         <v>100</v>
       </c>
-      <c r="BQ18">
+      <c r="BR18">
         <v>1786.5</v>
       </c>
-      <c r="BR18" s="15">
+      <c r="BS18" s="15">
         <f t="shared" si="7"/>
         <v>352.5</v>
       </c>
     </row>
-    <row r="19" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1146604</v>
       </c>
@@ -3977,22 +4034,22 @@
       <c r="T19" s="13"/>
       <c r="U19" s="13"/>
       <c r="V19" s="13"/>
-      <c r="W19" s="13">
+      <c r="W19" s="13"/>
+      <c r="X19" s="13">
         <v>6461</v>
       </c>
-      <c r="X19" s="13">
+      <c r="Y19" s="13">
         <v>6503</v>
       </c>
-      <c r="Y19" s="13">
+      <c r="Z19" s="13">
         <v>6535</v>
       </c>
-      <c r="Z19" s="13">
+      <c r="AA19" s="13">
         <v>6532</v>
       </c>
-      <c r="AA19" s="13">
+      <c r="AB19" s="13">
         <v>6515</v>
       </c>
-      <c r="AB19" s="13"/>
       <c r="AC19" s="13"/>
       <c r="AD19" s="13"/>
       <c r="AE19" s="13"/>
@@ -4020,33 +4077,34 @@
       <c r="BA19" s="13"/>
       <c r="BB19" s="13"/>
       <c r="BC19" s="13"/>
-      <c r="BD19" s="29"/>
-      <c r="BE19" s="13"/>
+      <c r="BD19" s="13"/>
+      <c r="BE19" s="29"/>
       <c r="BF19" s="13"/>
-      <c r="BG19" s="29"/>
-      <c r="BH19" s="13"/>
+      <c r="BG19" s="13"/>
+      <c r="BH19" s="29"/>
       <c r="BI19" s="13"/>
       <c r="BJ19" s="13"/>
       <c r="BK19" s="13"/>
-      <c r="BL19" s="13">
+      <c r="BL19" s="13"/>
+      <c r="BM19" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BM19" s="13">
+      <c r="BN19" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BN19" s="13"/>
       <c r="BO19" s="13"/>
-      <c r="BP19">
+      <c r="BP19" s="13"/>
+      <c r="BQ19">
         <v>7</v>
       </c>
-      <c r="BQ19">
+      <c r="BR19">
         <v>6461</v>
       </c>
-      <c r="BR19" s="15"/>
-    </row>
-    <row r="20" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BS19" s="15"/>
+    </row>
+    <row r="20" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1144807</v>
       </c>
@@ -4087,7 +4145,9 @@
       <c r="O20" s="13">
         <v>3159</v>
       </c>
-      <c r="P20" s="13"/>
+      <c r="P20" s="13">
+        <v>3159</v>
+      </c>
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
       <c r="S20" s="13"/>
@@ -4127,28 +4187,29 @@
       <c r="BA20" s="13"/>
       <c r="BB20" s="13"/>
       <c r="BC20" s="13"/>
-      <c r="BD20" s="29"/>
-      <c r="BE20" s="13"/>
+      <c r="BD20" s="13"/>
+      <c r="BE20" s="29"/>
       <c r="BF20" s="13"/>
-      <c r="BG20" s="29"/>
-      <c r="BH20" s="13"/>
+      <c r="BG20" s="13"/>
+      <c r="BH20" s="29"/>
       <c r="BI20" s="13"/>
       <c r="BJ20" s="13"/>
       <c r="BK20" s="13"/>
-      <c r="BL20" s="13">
-        <f>(G20*H20)/100-BR20</f>
+      <c r="BL20" s="13"/>
+      <c r="BM20" s="13">
+        <f>(G20*H20)/100-BS20</f>
         <v>0</v>
       </c>
-      <c r="BM20" s="13">
+      <c r="BN20" s="13">
         <f>(G20*H20)/100</f>
         <v>0</v>
       </c>
-      <c r="BN20" s="13"/>
       <c r="BO20" s="13"/>
-      <c r="BR20" s="15"/>
-    </row>
-    <row r="21" spans="1:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:70" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BP20" s="13"/>
+      <c r="BS20" s="15"/>
+    </row>
+    <row r="21" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4204,11 +4265,11 @@
       <c r="BA22" s="13"/>
       <c r="BB22" s="13"/>
       <c r="BC22" s="13"/>
-      <c r="BD22" s="29"/>
-      <c r="BE22" s="13"/>
+      <c r="BD22" s="13"/>
+      <c r="BE22" s="29"/>
       <c r="BF22" s="13"/>
-      <c r="BG22" s="29"/>
-      <c r="BH22" s="13"/>
+      <c r="BG22" s="13"/>
+      <c r="BH22" s="29"/>
       <c r="BI22" s="13"/>
       <c r="BJ22" s="13"/>
       <c r="BK22" s="13"/>
@@ -4216,9 +4277,10 @@
       <c r="BM22" s="13"/>
       <c r="BN22" s="13"/>
       <c r="BO22" s="13"/>
-      <c r="BR22" s="15"/>
-    </row>
-    <row r="23" spans="1:70" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BP22" s="13"/>
+      <c r="BS22" s="15"/>
+    </row>
+    <row r="23" spans="1:71" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4229,63 +4291,63 @@
       <c r="H23" s="13"/>
       <c r="I23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19)/100</f>
-        <v>16518.923599999998</v>
+        <v>17594.5056</v>
       </c>
       <c r="J23" s="23">
         <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19)/100</f>
-        <v>16518.923599999998</v>
+        <v>17147.358</v>
       </c>
       <c r="K23" s="23">
         <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19)/100</f>
-        <v>16036.023999999999</v>
+        <v>17029.563599999998</v>
       </c>
       <c r="L23" s="23">
         <f>(L2*G2+G3*L3+L4*G4+G5*L5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+L13*G13+G14*L14+L15*G15+G16*L16+G17*L17+L18*G18+G19*L19)/100</f>
-        <v>15691.233</v>
+        <v>16540.263999999999</v>
       </c>
       <c r="M23" s="23">
         <f>(M2*G2+G3*M3+M4*G4+G5*M5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+M13*G13+G14*M14+M15*G15+G16*M16+G17*M17+M18*G18+G19*M19)/100</f>
-        <v>15309.681999999999</v>
+        <v>16192.033000000001</v>
       </c>
       <c r="N23" s="23">
         <f>(N2*G2+G3*N3+N4*G4+G5*N5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+N13*G13+G14*N14+N15*G15+G16*N16+G17*N17+N18*G18+G19*N19)/100</f>
-        <v>15368.3776</v>
+        <v>15786.002</v>
       </c>
       <c r="O23" s="23">
-        <f>(O3*G3+G4*O4+O5*G5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+G14*O14+O15*G15+G16*O16+O17*G17+G18*O18+G19*O19)/100</f>
-        <v>13574.17</v>
+        <f>(O2*G2+G3*O3+O4*G4+G5*O5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+O13*G13+G14*O14+O15*G15+G16*O16+G17*O17+O18*G18+G19*O19)/100</f>
+        <v>15902.0576</v>
       </c>
       <c r="P23" s="23">
         <f>(P3*G3+G4*P4+P5*G5+G6*P6+G7*P7+G8*P8+G9*P9+G10*P10+G11*P11+G12*P12+G14*P14+P15*G15+G16*P16+P17*G17+G18*P18+G19*P19)/100</f>
-        <v>13326.577600000001</v>
+        <v>14094.97</v>
       </c>
       <c r="Q23" s="23">
         <f>(Q3*G3+G4*Q4+Q5*G5+G6*Q6+G7*Q7+G8*Q8+G9*Q9+G10*Q10+G11*Q11+G12*Q12+G14*Q14+Q15*G15+G16*Q16+Q17*G17+G18*Q18+G19*Q19)/100</f>
-        <v>13342.8776</v>
+        <v>13839.4576</v>
       </c>
       <c r="R23" s="23">
         <f>(R3*G3+G4*R4+R5*G5+G6*R6+G7*R7+G8*R8+G9*R9+G10*R10+G11*R11+G12*R12+G14*R14+R15*G15+G16*R16+R17*G17+G18*R18+G19*R19)/100</f>
-        <v>13311.7376</v>
+        <v>13855.757600000001</v>
       </c>
       <c r="S23" s="23">
         <f>(S3*G3+G4*S4+S5*G5+G6*S6+G7*S7+G8*S8+G9*S9+G10*S10+G11*S11+G12*S12+G14*S14+S15*G15+G16*S16+S17*G17+G18*S18+G19*S19)/100</f>
-        <v>12717.88</v>
+        <v>13797.417600000001</v>
       </c>
       <c r="T23" s="23">
         <f>(T3*G3+G4*T4+T5*G5+G6*T6+G7*T7+G8*T8+G9*T9+G10*T10+G11*T11+G12*T12+G14*T14+T15*G15+G16*T16+T17*G17+G18*T18+G19*T19)/100</f>
-        <v>12514.9056</v>
+        <v>13184.28</v>
       </c>
       <c r="U23" s="23">
         <f>(U3*G3+G4*U4+U5*G5+G6*U6+G7*U7+G8*U8+G9*U9+G10*U10+G11*U11+G12*U12+G14*U14+U15*G15+G16*U16+U17*G17+G18*U18+G19*U19)/100</f>
-        <v>10750.095600000001</v>
+        <v>12980.185600000001</v>
       </c>
       <c r="V23" s="23">
-        <f>(V5*G5+G6*V6+V7*G7+G8*V8+G9*V9+G10*V10+G11*V11+G12*V12+G14*V14+G20*V20+G15*V15+V16*G16+G17*V17+V18*G18+G19*V19)/100</f>
-        <v>9908.9195999999993</v>
-      </c>
-      <c r="W23" s="23" t="e">
-        <f>(W5*G5+G7*W7+W8*G8+G9*W9+#REF!*#REF!+G10*W10+G11*W11+G12*W12+G14*W14+G19*W19+G20*W20+W6*G6+G15*W15+#REF!*#REF!+G16*W16+G17*W17+W18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*W3+#REF!*#REF!)/100</f>
-        <v>#REF!</v>
+        <f>(V3*G3+G4*V4+V5*G5+G6*V6+G7*V7+G8*V8+G9*V9+G10*V10+G11*V11+G12*V12+G14*V14+V15*G15+G16*V16+V17*G17+G18*V18+G19*V19)/100</f>
+        <v>11213.0556</v>
+      </c>
+      <c r="W23" s="23">
+        <f>(W5*G5+G6*W6+W7*G7+G8*W8+G9*W9+G10*W10+G11*W11+G12*W12+G14*W14+G20*W20+G15*W15+W16*G16+G17*W17+W18*G18+G19*W19)/100</f>
+        <v>10380.919599999999</v>
       </c>
       <c r="X23" s="23" t="e">
         <f>(X5*G5+G7*X7+X8*G8+G9*X9+#REF!*#REF!+G10*X10+G11*X11+G12*X12+G14*X14+G19*X19+G20*X20+X6*G6+G15*X15+#REF!*#REF!+G16*X16+G17*X17+X18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*X3+#REF!*#REF!)/100</f>
@@ -4296,11 +4358,11 @@
         <v>#REF!</v>
       </c>
       <c r="Z23" s="23" t="e">
-        <f>(Z5*G5+G7*Z7+Z8*G8+G9*Z9+#REF!*#REF!+G10*Z10+G11*Z11+G12*Z12+G14*Z14+G19*Z19+G20*Z20+Z6*G6+G15*Z15+#REF!*#REF!+G16*Z16+G18*Z18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*Z3+#REF!*#REF!+G4*Z4)/100</f>
+        <f>(Z5*G5+G7*Z7+Z8*G8+G9*Z9+#REF!*#REF!+G10*Z10+G11*Z11+G12*Z12+G14*Z14+G19*Z19+G20*Z20+Z6*G6+G15*Z15+#REF!*#REF!+G16*Z16+G17*Z17+Z18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*Z3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AA23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AA3*G3+#REF!*#REF!+G4*AA4+G5*AA5+G7*AA7+G8*AA8+G9*AA9+#REF!*#REF!+G10*AA10+AA11*G11+G12*AA12+AA14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AA20+AA6*G6+#REF!*#REF!+G16*AA16+G18*AA18+G19*AA19)/100</f>
+        <f>(AA5*G5+G7*AA7+AA8*G8+G9*AA9+#REF!*#REF!+G10*AA10+G11*AA11+G12*AA12+G14*AA14+G19*AA19+G20*AA20+AA6*G6+G15*AA15+#REF!*#REF!+G16*AA16+G18*AA18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AA3+#REF!*#REF!+G4*AA4)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AB23" s="23" t="e">
@@ -4308,7 +4370,7 @@
         <v>#REF!</v>
       </c>
       <c r="AC23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AC3*G3+#REF!*#REF!+G4*AC4+G5*AC5+AC7*G7+AC8*G8+AC9*G9+#REF!*#REF!+G10*AC10+AC11*G11+G12*AC12+AC14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AC20+G6*AC6+#REF!*#REF!+G16*AC16+G18*AC18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AC3*G3+#REF!*#REF!+G4*AC4+G5*AC5+G7*AC7+G8*AC8+G9*AC9+#REF!*#REF!+G10*AC10+AC11*G11+G12*AC12+AC14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AC20+AC6*G6+#REF!*#REF!+G16*AC16+G18*AC18+G19*AC19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AD23" s="23" t="e">
@@ -4316,19 +4378,19 @@
         <v>#REF!</v>
       </c>
       <c r="AE23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AE3*G3+#REF!*#REF!+G4*AE4+G8*AE8+AE9*G9+#REF!*#REF!+AE10*G10+G11*AE11+G14*AE14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AE6+#REF!*#REF!+G16*AE16+G18*AE18+G7*AE7+G5*AE5+G12*AE12+G20*AE20)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AE3*G3+#REF!*#REF!+G4*AE4+G5*AE5+AE7*G7+AE8*G8+AE9*G9+#REF!*#REF!+G10*AE10+AE11*G11+G12*AE12+AE14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AE20+G6*AE6+#REF!*#REF!+G16*AE16+G18*AE18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AF23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AF3*G3+#REF!*#REF!+G4*AF4+G8*AF8+AF9*G9+#REF!*#REF!+AF10*G10+G11*AF11+G14*AF14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AF6+#REF!*#REF!+G16*AF16+G18*AF18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AF3*G3+#REF!*#REF!+G4*AF4+G8*AF8+AF9*G9+#REF!*#REF!+AF10*G10+G11*AF11+G14*AF14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AF6+#REF!*#REF!+G16*AF16+G18*AF18+G7*AF7+G5*AF5+G12*AF12+G20*AF20)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AG23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AG3*G3+#REF!*#REF!+G4*AG4+G8*AG8+G9*AG9+#REF!*#REF!+G10*AG10+AG11*G11+AG14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AG6*G6+#REF!*#REF!+G16*AG16+G18*AG18+G19*AG19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AG3*G3+#REF!*#REF!+G4*AG4+G8*AG8+AG9*G9+#REF!*#REF!+AG10*G10+G11*AG11+G14*AG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AG6+#REF!*#REF!+G16*AG16+G18*AG18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AH23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AH3*G3+#REF!*#REF!+G4*AH4+G8*AH8+AH9*G9+#REF!*#REF!+AH10*G10+G11*AH11+G14*AH14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AH6+#REF!*#REF!+G16*AH16+G18*AH18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AH3*G3+#REF!*#REF!+G4*AH4+G8*AH8+G9*AH9+#REF!*#REF!+G10*AH10+AH11*G11+AH14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AH6*G6+#REF!*#REF!+G16*AH16+G18*AH18+G19*AH19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AI23" s="23" t="e">
@@ -4336,7 +4398,7 @@
         <v>#REF!</v>
       </c>
       <c r="AJ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AJ3*G3+#REF!*#REF!+G4*AJ4+G8*AJ8+AJ9*G9+AJ10*G10+AJ11*G11+G14*AJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AJ6+#REF!*#REF!+G16*AJ16+G18*AJ18+G19*AJ19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AJ3*G3+#REF!*#REF!+G4*AJ4+G8*AJ8+AJ9*G9+#REF!*#REF!+AJ10*G10+G11*AJ11+G14*AJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AJ6+#REF!*#REF!+G16*AJ16+G18*AJ18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AK23" s="23" t="e">
@@ -4356,19 +4418,19 @@
         <v>#REF!</v>
       </c>
       <c r="AO23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+AO9*G9+AO10*G10+AO11*G11+G14*AO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AO6+#REF!*#REF!+G16*AO16+G18*AO18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+AO9*G9+AO10*G10+AO11*G11+G14*AO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AO6+#REF!*#REF!+G16*AO16+G18*AO18+G19*AO19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AP23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+AP10*G10+AP11*G11+G14*AP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AP6+#REF!*#REF!+G16*AP16+G18*AP18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+AP9*G9+AP10*G10+AP11*G11+G14*AP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AP6+#REF!*#REF!+G16*AP16+G18*AP18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AQ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AQ3*G3+#REF!*#REF!+G4*AQ4+G8*AQ8+G10*AQ10+AQ11*G11+AQ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AQ6*G6+#REF!*#REF!+G16*AQ16+G18*AQ18+G19*AQ19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AQ3*G3+#REF!*#REF!+G4*AQ4+G8*AQ8+AQ10*G10+AQ11*G11+G14*AQ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AQ6+#REF!*#REF!+G16*AQ16+G18*AQ18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AR23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AR3*G3+#REF!*#REF!+G4*AR4+G10*AR10+AR11*G11+AR14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AR6*G6+#REF!*#REF!+G16*AR16+G18*AR18+G19*AR19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AR3*G3+#REF!*#REF!+G4*AR4+G8*AR8+G10*AR10+AR11*G11+AR14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AR6*G6+#REF!*#REF!+G16*AR16+G18*AR18+G19*AR19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AS23" s="23" t="e">
@@ -4380,7 +4442,7 @@
         <v>#REF!</v>
       </c>
       <c r="AU23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AU3*G3+#REF!*#REF!+G4*AU4+G10*AU10+AU11*G11+AU14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AU6*G6+G16*AU16+G18*AU18+G19*AU19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AU3*G3+#REF!*#REF!+G4*AU4+G10*AU10+AU11*G11+AU14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AU6*G6+#REF!*#REF!+G16*AU16+G18*AU18+G19*AU19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AV23" s="23" t="e">
@@ -4408,15 +4470,15 @@
         <v>#REF!</v>
       </c>
       <c r="BB23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BB3*G3+#REF!*#REF!+G4*BB4+G10*BB10+G11*BB11+G14*BB14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BB6+BB16*G16+G18*BB18+G19*BB19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BB3*G3+#REF!*#REF!+G4*BB4+G10*BB10+BB11*G11+BB14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BB6*G6+G16*BB16+G18*BB18+G19*BB19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BC23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BC3*G3+#REF!*#REF!+G4*BC4+G10*BC10+G14*BC14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BC6+BC16*G16+G18*BC18+G19*BC19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BC3*G3+#REF!*#REF!+G4*BC4+G10*BC10+G11*BC11+G14*BC14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BC6+BC16*G16+G18*BC18+G19*BC19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BD23" s="23" t="e">
-        <f>(#REF!*#REF!+BD3*G3+G4*BD4+G14*BD14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BD6+BD16*G16+G18*BD18+G19*BD19+G22*BD22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BD3*G3+#REF!*#REF!+G4*BD4+G10*BD10+G14*BD14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BD6+BD16*G16+G18*BD18+G19*BD19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BE23" s="23" t="e">
@@ -4427,16 +4489,16 @@
         <f>(#REF!*#REF!+BF3*G3+G4*BF4+G14*BF14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BF6+BF16*G16+G18*BF18+G19*BF19+G22*BF22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BG23" s="30" t="e">
+      <c r="BG23" s="23" t="e">
         <f>(#REF!*#REF!+BG3*G3+G4*BG4+G14*BG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BG6+BG16*G16+G18*BG18+G19*BG19+G22*BG22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BH23" s="23" t="e">
+      <c r="BH23" s="30" t="e">
         <f>(#REF!*#REF!+BH3*G3+G4*BH4+G14*BH14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BH6+BH16*G16+G18*BH18+G19*BH19+G22*BH22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BI23" s="23" t="e">
-        <f>(#REF!*#REF!+BI3*G3+G14*BI14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BI6+BI16*G16+G18*BI18+G19*BI19+G22*BI22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+BI3*G3+G4*BI4+G14*BI14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BI6+BI16*G16+G18*BI18+G19*BI19+G22*BI22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BJ23" s="23" t="e">
@@ -4447,16 +4509,20 @@
         <f>(#REF!*#REF!+BK3*G3+G14*BK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BK6+BK16*G16+G18*BK18+G19*BK19+G22*BK22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BL23" s="13"/>
+      <c r="BL23" s="23" t="e">
+        <f>(#REF!*#REF!+BL3*G3+G14*BL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BL6+BL16*G16+G18*BL18+G19*BL19+G22*BL22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <v>#REF!</v>
+      </c>
       <c r="BM23" s="13"/>
       <c r="BN23" s="13"/>
       <c r="BO23" s="13"/>
-      <c r="BR23" s="15">
+      <c r="BP23" s="13"/>
+      <c r="BS23" s="15">
         <f>434.9+62.57</f>
         <v>497.46999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:70" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:71" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4520,29 +4586,30 @@
       <c r="BI24" s="14"/>
       <c r="BJ24" s="14"/>
       <c r="BK24" s="14"/>
-      <c r="BL24" s="23">
-        <f>SUM(BL2:BL20)</f>
-        <v>13589.379000000001</v>
-      </c>
+      <c r="BL24" s="14"/>
       <c r="BM24" s="23">
         <f>SUM(BM2:BM20)</f>
-        <v>13891.033200000002</v>
-      </c>
-      <c r="BN24" s="24">
-        <f>BM24-BL24</f>
+        <v>14085.376400000001</v>
+      </c>
+      <c r="BN24" s="23">
+        <f>SUM(BN2:BN20)</f>
+        <v>14387.030600000002</v>
+      </c>
+      <c r="BO24" s="24">
+        <f>BN24-BM24</f>
         <v>301.65420000000086</v>
       </c>
-      <c r="BO24" s="13">
-        <f>((BM24-BL24)/BL24)*100</f>
-        <v>2.2197791378104976</v>
-      </c>
-      <c r="BR24" s="15">
-        <f>SUM(BR5:BR23)</f>
+      <c r="BP24" s="13">
+        <f>((BN24-BM24)/BM24)*100</f>
+        <v>2.1416126302453717</v>
+      </c>
+      <c r="BS24" s="15">
+        <f>SUM(BS5:BS23)</f>
         <v>799.12419999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="BL25" s="15">
+    <row r="25" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="BM25" s="15">
         <v>12034.32</v>
       </c>
     </row>
@@ -4669,7 +4736,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>11360</v>
+        <v>11840</v>
       </c>
       <c r="J2" s="25"/>
       <c r="L2" s="21">
@@ -4707,7 +4774,7 @@
       <c r="G3" s="17"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1348</v>
+        <v>1500</v>
       </c>
       <c r="J3" s="26"/>
       <c r="L3" s="21">
@@ -4745,7 +4812,7 @@
       <c r="G4" s="17"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6979</v>
+        <v>7120</v>
       </c>
       <c r="J4" s="26"/>
       <c r="L4" s="21">
@@ -4768,11 +4835,11 @@
       </c>
       <c r="C5" s="18">
         <f>'התיק העדכני'!H5</f>
-        <v>615</v>
+        <v>617.53</v>
       </c>
       <c r="D5" s="19">
         <f>'התיק העדכני'!G5</f>
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="E5" s="16">
         <v>650</v>
@@ -4782,7 +4849,7 @@
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>638.29999999999995</v>
+        <v>575.70000000000005</v>
       </c>
       <c r="J5" s="26"/>
       <c r="L5" s="21">
@@ -4819,7 +4886,7 @@
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4450</v>
+        <v>4424</v>
       </c>
       <c r="J6" s="26"/>
       <c r="L6" s="21">
@@ -4857,7 +4924,7 @@
       <c r="G7" s="18"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3943</v>
+        <v>3932</v>
       </c>
       <c r="J7" s="26"/>
       <c r="L7" s="21">
@@ -4895,7 +4962,7 @@
       <c r="G8" s="18"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40790</v>
+        <v>40750</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -4932,7 +4999,7 @@
       <c r="G9" s="17"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9910</v>
+        <v>9891</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -4969,7 +5036,7 @@
       <c r="G10" s="18"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5013</v>
+        <v>4821</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -5006,7 +5073,7 @@
       <c r="G11" s="18"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1162</v>
+        <v>1090</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -5043,7 +5110,7 @@
       <c r="G12" s="18"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>27450</v>
+        <v>30500</v>
       </c>
       <c r="J12" s="26"/>
       <c r="L12" s="21">
@@ -5081,7 +5148,7 @@
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1100</v>
+        <v>1490</v>
       </c>
       <c r="J13" s="26"/>
       <c r="L13" s="21">
@@ -5119,7 +5186,7 @@
       <c r="G14" s="17"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7810</v>
+        <v>7676</v>
       </c>
       <c r="J14" s="26"/>
       <c r="L14" s="21">
@@ -5157,7 +5224,7 @@
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>15528.12</v>
+        <v>14583.37</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
@@ -5195,7 +5262,7 @@
       <c r="G16" s="17"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>223.25</v>
+        <v>226.96</v>
       </c>
       <c r="J16" s="26"/>
       <c r="L16" s="21">
@@ -5271,7 +5338,7 @@
       <c r="G18" s="18"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1831</v>
+        <v>1811</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -5693,7 +5760,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>11360</v>
+        <v>11840</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+GEMINI!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
@@ -5730,7 +5797,7 @@
       <c r="G3" s="7"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1348</v>
+        <v>1500</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
@@ -5767,7 +5834,7 @@
       <c r="G4" s="7"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6979</v>
+        <v>7120</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+GEMINI!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
@@ -5789,11 +5856,11 @@
       </c>
       <c r="C5" s="18">
         <f>'התיק העדכני'!H5</f>
-        <v>615</v>
+        <v>617.53</v>
       </c>
       <c r="D5" s="19">
         <f>'התיק העדכני'!G5</f>
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="E5" s="16">
         <v>601</v>
@@ -5804,7 +5871,7 @@
       <c r="G5" s="7"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>638.29999999999995</v>
+        <v>575.70000000000005</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
@@ -5841,7 +5908,7 @@
       <c r="G6" s="7"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4450</v>
+        <v>4424</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
@@ -5878,7 +5945,7 @@
       <c r="G7" s="8"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3943</v>
+        <v>3932</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+GEMINI!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
@@ -5915,7 +5982,7 @@
       <c r="G8" s="8"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40790</v>
+        <v>40750</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+GEMINI!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -5952,7 +6019,7 @@
       <c r="G9" s="8"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9910</v>
+        <v>9891</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+GEMINI!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -5989,7 +6056,7 @@
       <c r="G10" s="8"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5013</v>
+        <v>4821</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+GEMINI!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -6026,7 +6093,7 @@
       <c r="G11" s="8"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1162</v>
+        <v>1090</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+GEMINI!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -6063,7 +6130,7 @@
       <c r="G12" s="8"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>27450</v>
+        <v>30500</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+GEMINI!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
@@ -6100,7 +6167,7 @@
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1100</v>
+        <v>1490</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+GEMINI!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
@@ -6137,7 +6204,7 @@
       <c r="G14" s="7"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7810</v>
+        <v>7676</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
@@ -6174,7 +6241,7 @@
       <c r="G15" s="7"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>15528.12</v>
+        <v>14583.37</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+GEMINI!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
@@ -6211,7 +6278,7 @@
       <c r="G16" s="7"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>223.25</v>
+        <v>226.96</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
@@ -6285,7 +6352,7 @@
       <c r="G18" s="8"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1831</v>
+        <v>1811</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+GEMINI!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -6509,7 +6576,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>11360</v>
+        <v>11840</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+GEMINI!E2+DEEPSEEK!E2)/4</f>
@@ -6546,7 +6613,7 @@
       <c r="G3" s="10"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1348</v>
+        <v>1500</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
@@ -6583,7 +6650,7 @@
       <c r="G4" s="10"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6979</v>
+        <v>7120</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+GEMINI!E4+DEEPSEEK!E4)/4</f>
@@ -6605,11 +6672,11 @@
       </c>
       <c r="C5" s="18">
         <f>'התיק העדכני'!H5</f>
-        <v>615</v>
+        <v>617.53</v>
       </c>
       <c r="D5" s="19">
         <f>'התיק העדכני'!G5</f>
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="E5" s="16">
         <v>585</v>
@@ -6620,7 +6687,7 @@
       <c r="G5" s="10"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>638.29999999999995</v>
+        <v>575.70000000000005</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
@@ -6657,7 +6724,7 @@
       <c r="G6" s="10"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4450</v>
+        <v>4424</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
@@ -6694,7 +6761,7 @@
       <c r="G7" s="10"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3943</v>
+        <v>3932</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+GEMINI!E7+DEEPSEEK!E7)/4</f>
@@ -6730,7 +6797,7 @@
       </c>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40790</v>
+        <v>40750</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+GEMINI!E8+DEEPSEEK!E8)/4</f>
@@ -6766,7 +6833,7 @@
       </c>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9910</v>
+        <v>9891</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+GEMINI!E9+DEEPSEEK!E9)/4</f>
@@ -6802,7 +6869,7 @@
       </c>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5013</v>
+        <v>4821</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+GEMINI!E10+DEEPSEEK!E10)/4</f>
@@ -6838,7 +6905,7 @@
       </c>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1162</v>
+        <v>1090</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+GEMINI!E11+DEEPSEEK!E11)/4</f>
@@ -6875,7 +6942,7 @@
       <c r="G12" s="10"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>27450</v>
+        <v>30500</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+GEMINI!E12+DEEPSEEK!E12)/4</f>
@@ -6912,7 +6979,7 @@
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1100</v>
+        <v>1490</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+CHATGPT!E13+GEMINI!E13+DEEPSEEK!E13)/4</f>
@@ -6949,7 +7016,7 @@
       <c r="G14" s="10"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7810</v>
+        <v>7676</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
@@ -6986,7 +7053,7 @@
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>15528.12</v>
+        <v>14583.37</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
@@ -7023,7 +7090,7 @@
       <c r="G16" s="10"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>223.25</v>
+        <v>226.96</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+GEMINI!E16+DEEPSEEK!E16)/4</f>
@@ -7096,7 +7163,7 @@
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1831</v>
+        <v>1811</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
@@ -7319,7 +7386,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>11360</v>
+        <v>11840</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+PERPLIXITY!E2+GEMINI!E2)/4</f>
@@ -7356,7 +7423,7 @@
       <c r="G3" s="31"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1348</v>
+        <v>1500</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
@@ -7392,7 +7459,7 @@
       </c>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6979</v>
+        <v>7120</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+GEMINI!E4)/4</f>
@@ -7414,11 +7481,11 @@
       </c>
       <c r="C5" s="18">
         <f>'התיק העדכני'!H5</f>
-        <v>615</v>
+        <v>617.53</v>
       </c>
       <c r="D5" s="19">
         <f>'התיק העדכני'!G5</f>
-        <v>78</v>
+        <v>158</v>
       </c>
       <c r="E5" s="16">
         <v>595</v>
@@ -7429,7 +7496,7 @@
       <c r="G5" s="31"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>638.29999999999995</v>
+        <v>575.70000000000005</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
@@ -7466,7 +7533,7 @@
       <c r="G6" s="31"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4450</v>
+        <v>4424</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
@@ -7502,7 +7569,7 @@
       </c>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3943</v>
+        <v>3932</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+GEMINI!E7)/4</f>
@@ -7539,7 +7606,7 @@
       <c r="G8" s="31"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40790</v>
+        <v>40750</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+GEMINI!E8)/4</f>
@@ -7576,7 +7643,7 @@
       <c r="G9" s="31"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9910</v>
+        <v>9891</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+GEMINI!E9)/4</f>
@@ -7613,7 +7680,7 @@
       <c r="G10" s="31"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5013</v>
+        <v>4821</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+GEMINI!E10)/4</f>
@@ -7650,7 +7717,7 @@
       <c r="G11" s="31"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1162</v>
+        <v>1090</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+GEMINI!E11)/4</f>
@@ -7687,7 +7754,7 @@
       <c r="G12" s="31"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>27450</v>
+        <v>30500</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+GEMINI!E12)/4</f>
@@ -7724,7 +7791,7 @@
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1100</v>
+        <v>1490</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
@@ -7755,7 +7822,7 @@
       <c r="G14" s="31"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7810</v>
+        <v>7676</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
@@ -7827,7 +7894,7 @@
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>15528.12</v>
+        <v>14583.37</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
@@ -7864,7 +7931,7 @@
       <c r="G17" s="31"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>223.25</v>
+        <v>226.96</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+GEMINI!E17)/4</f>
@@ -7931,7 +7998,7 @@
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1831</v>
+        <v>1811</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+GEMINI!E19)/4</f>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\BURSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA15407-37F8-4B9E-9201-4F65EAE5B6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F48523D-468C-42AF-BD2E-4B36F92ADF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="104">
   <si>
     <t>MTF מחקה אינדקס תעשיה ישראל</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>מחיר 27/01/2026</t>
+  </si>
+  <si>
+    <t>מחיר 28/01/2026</t>
   </si>
 </sst>
 </file>
@@ -1108,22 +1111,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86B4639-EF9D-4B16-B2C9-0D5E9C5EEC8B}">
-  <dimension ref="A1:BS25"/>
+  <dimension ref="A1:BT25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="17.5703125" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="54" width="14.85546875" customWidth="1"/>
-    <col min="55" max="64" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="13" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="11" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="11.5703125" customWidth="1"/>
+    <col min="8" max="55" width="14.85546875" customWidth="1"/>
+    <col min="56" max="65" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="13" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="11" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1152,193 +1155,196 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BK1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BL1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BM1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BN1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BO1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="BO1" s="6" t="s">
+      <c r="BP1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BP1" s="6" t="s">
+      <c r="BQ1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="BQ1" s="12" t="s">
+      <c r="BR1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="BR1" s="12" t="s">
+      <c r="BS1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="BS1" s="12" t="s">
+      <c r="BT1" s="12" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>282012</v>
       </c>
@@ -1367,27 +1373,29 @@
         <v>11000</v>
       </c>
       <c r="I2" s="13">
+        <v>12130</v>
+      </c>
+      <c r="J2" s="13">
         <v>11840</v>
       </c>
-      <c r="J2" s="13">
+      <c r="K2" s="13">
         <v>11400</v>
       </c>
-      <c r="K2" s="13">
+      <c r="L2" s="13">
         <v>11360</v>
       </c>
-      <c r="L2" s="13">
+      <c r="M2" s="13">
         <v>11000</v>
       </c>
-      <c r="M2" s="13">
+      <c r="N2" s="13">
         <v>10700</v>
       </c>
-      <c r="N2" s="13">
+      <c r="O2" s="13">
         <v>10400</v>
       </c>
-      <c r="O2" s="13">
+      <c r="P2" s="13">
         <v>11230</v>
       </c>
-      <c r="P2" s="6"/>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
@@ -1428,29 +1436,30 @@
       <c r="BB2" s="6"/>
       <c r="BC2" s="6"/>
       <c r="BD2" s="6"/>
-      <c r="BE2" s="32"/>
-      <c r="BF2" s="6"/>
+      <c r="BE2" s="6"/>
+      <c r="BF2" s="32"/>
       <c r="BG2" s="6"/>
-      <c r="BH2" s="32"/>
-      <c r="BI2" s="6"/>
+      <c r="BH2" s="6"/>
+      <c r="BI2" s="32"/>
       <c r="BJ2" s="6"/>
       <c r="BK2" s="6"/>
       <c r="BL2" s="6"/>
-      <c r="BM2" s="13">
-        <f>(G2*H2)/100-BS2</f>
+      <c r="BM2" s="6"/>
+      <c r="BN2" s="13">
+        <f>(G2*H2)/100-BT2</f>
         <v>770</v>
       </c>
-      <c r="BN2" s="13">
+      <c r="BO2" s="13">
         <f>(G2*H2)/100</f>
         <v>770</v>
       </c>
-      <c r="BO2" s="6"/>
       <c r="BP2" s="6"/>
-      <c r="BQ2" s="25"/>
+      <c r="BQ2" s="6"/>
       <c r="BR2" s="25"/>
       <c r="BS2" s="25"/>
-    </row>
-    <row r="3" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT2" s="25"/>
+    </row>
+    <row r="3" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1227552</v>
       </c>
@@ -1479,45 +1488,47 @@
         <v>1153.6300000000001</v>
       </c>
       <c r="I3" s="13">
+        <v>1556</v>
+      </c>
+      <c r="J3" s="13">
         <v>1500</v>
       </c>
-      <c r="J3" s="13">
+      <c r="K3" s="13">
         <v>1424</v>
       </c>
-      <c r="K3" s="13">
+      <c r="L3" s="13">
         <v>1348</v>
       </c>
-      <c r="L3" s="13">
+      <c r="M3" s="13">
         <v>1373</v>
       </c>
-      <c r="M3" s="13">
+      <c r="N3" s="13">
         <v>1331</v>
       </c>
-      <c r="N3" s="13">
+      <c r="O3" s="13">
         <v>1386</v>
       </c>
-      <c r="O3" s="13">
+      <c r="P3" s="13">
         <v>1342</v>
       </c>
-      <c r="P3" s="13">
+      <c r="Q3" s="13">
         <v>1250</v>
-      </c>
-      <c r="Q3" s="13">
-        <v>1389</v>
       </c>
       <c r="R3" s="13">
         <v>1389</v>
       </c>
       <c r="S3" s="13">
+        <v>1389</v>
+      </c>
+      <c r="T3" s="13">
         <v>1367</v>
       </c>
-      <c r="T3" s="13">
+      <c r="U3" s="13">
         <v>1026</v>
       </c>
-      <c r="U3" s="13">
+      <c r="V3" s="13">
         <v>949.1</v>
       </c>
-      <c r="V3" s="13"/>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
@@ -1533,8 +1544,8 @@
       <c r="AI3" s="13"/>
       <c r="AJ3" s="13"/>
       <c r="AK3" s="13"/>
-      <c r="AL3" s="14"/>
-      <c r="AM3" s="13"/>
+      <c r="AL3" s="13"/>
+      <c r="AM3" s="14"/>
       <c r="AN3" s="13"/>
       <c r="AO3" s="13"/>
       <c r="AP3" s="13"/>
@@ -1552,36 +1563,37 @@
       <c r="BB3" s="13"/>
       <c r="BC3" s="13"/>
       <c r="BD3" s="13"/>
-      <c r="BE3" s="29"/>
-      <c r="BF3" s="13"/>
+      <c r="BE3" s="13"/>
+      <c r="BF3" s="29"/>
       <c r="BG3" s="13"/>
-      <c r="BH3" s="29"/>
-      <c r="BI3" s="13"/>
+      <c r="BH3" s="13"/>
+      <c r="BI3" s="29"/>
       <c r="BJ3" s="13"/>
       <c r="BK3" s="13"/>
       <c r="BL3" s="13"/>
-      <c r="BM3" s="13">
-        <f>(G3*H3)/100-BS3</f>
+      <c r="BM3" s="13"/>
+      <c r="BN3" s="13">
+        <f>(G3*H3)/100-BT3</f>
         <v>784.46840000000009</v>
       </c>
-      <c r="BN3" s="13">
+      <c r="BO3" s="13">
         <f>(G3*H3)/100</f>
         <v>784.46840000000009</v>
       </c>
-      <c r="BO3" s="13">
-        <f>(BN3-BM3)</f>
+      <c r="BP3" s="13">
+        <f>(BO3-BN3)</f>
         <v>0</v>
       </c>
-      <c r="BP3" s="13">
-        <f>((BD3-H3)/H3)*100</f>
+      <c r="BQ3" s="13">
+        <f>((BE3-H3)/H3)*100</f>
         <v>-100</v>
       </c>
-      <c r="BS3" s="15">
-        <f>(BQ3*BR3-BQ3*H3)/100</f>
+      <c r="BT3" s="15">
+        <f>(BR3*BS3-BR3*H3)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>587014</v>
       </c>
@@ -1610,45 +1622,47 @@
         <v>5925</v>
       </c>
       <c r="I4" s="13">
+        <v>7252</v>
+      </c>
+      <c r="J4" s="13">
         <v>7120</v>
       </c>
-      <c r="J4" s="13">
+      <c r="K4" s="13">
         <v>7048</v>
       </c>
-      <c r="K4" s="13">
+      <c r="L4" s="13">
         <v>6979</v>
       </c>
-      <c r="L4" s="13">
+      <c r="M4" s="13">
         <v>6680</v>
       </c>
-      <c r="M4" s="13">
+      <c r="N4" s="13">
         <v>6111</v>
       </c>
-      <c r="N4" s="13">
+      <c r="O4" s="13">
         <v>6050</v>
       </c>
-      <c r="O4" s="13">
+      <c r="P4" s="13">
         <v>6169</v>
       </c>
-      <c r="P4" s="13">
+      <c r="Q4" s="13">
         <v>6300</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>6335</v>
       </c>
       <c r="R4" s="13">
         <v>6335</v>
       </c>
       <c r="S4" s="13">
+        <v>6335</v>
+      </c>
+      <c r="T4" s="13">
         <v>6444</v>
-      </c>
-      <c r="T4" s="13">
-        <v>5749</v>
       </c>
       <c r="U4" s="13">
         <v>5749</v>
       </c>
-      <c r="V4" s="13"/>
+      <c r="V4" s="13">
+        <v>5749</v>
+      </c>
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
@@ -1683,36 +1697,37 @@
       <c r="BB4" s="13"/>
       <c r="BC4" s="13"/>
       <c r="BD4" s="13"/>
-      <c r="BE4" s="29"/>
-      <c r="BF4" s="13"/>
+      <c r="BE4" s="13"/>
+      <c r="BF4" s="29"/>
       <c r="BG4" s="13"/>
-      <c r="BH4" s="29"/>
-      <c r="BI4" s="13"/>
+      <c r="BH4" s="13"/>
+      <c r="BI4" s="29"/>
       <c r="BJ4" s="13"/>
       <c r="BK4" s="13"/>
       <c r="BL4" s="13"/>
-      <c r="BM4" s="13">
-        <f>(G4*H4)/100-BS4</f>
+      <c r="BM4" s="13"/>
+      <c r="BN4" s="13">
+        <f>(G4*H4)/100-BT4</f>
         <v>1185</v>
       </c>
-      <c r="BN4" s="13">
+      <c r="BO4" s="13">
         <f>(G4*H4)/100</f>
         <v>1185</v>
       </c>
-      <c r="BO4" s="13">
-        <f>(BN4-BM4)</f>
+      <c r="BP4" s="13">
+        <f>(BO4-BN4)</f>
         <v>0</v>
       </c>
-      <c r="BP4" s="13">
-        <f>((BD4-H4)/H4)*100</f>
+      <c r="BQ4" s="13">
+        <f>((BE4-H4)/H4)*100</f>
         <v>-100</v>
       </c>
-      <c r="BS4" s="15">
-        <f>(BQ4*BR4-BQ4*H4)/100</f>
+      <c r="BT4" s="15">
+        <f>(BR4*BS4-BR4*H4)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1099787</v>
       </c>
@@ -1741,75 +1756,77 @@
         <v>617.53</v>
       </c>
       <c r="I5" s="13">
+        <v>570</v>
+      </c>
+      <c r="J5" s="13">
         <v>575.70000000000005</v>
       </c>
-      <c r="J5" s="13">
+      <c r="K5" s="13">
         <v>612.6</v>
       </c>
-      <c r="K5" s="13">
+      <c r="L5" s="13">
         <v>638.29999999999995</v>
       </c>
-      <c r="L5" s="13">
+      <c r="M5" s="13">
         <v>630.29999999999995</v>
       </c>
-      <c r="M5" s="13">
+      <c r="N5" s="13">
         <v>626</v>
       </c>
-      <c r="N5" s="13">
+      <c r="O5" s="13">
         <v>595.4</v>
       </c>
-      <c r="O5" s="13">
+      <c r="P5" s="13">
         <v>667.1</v>
       </c>
-      <c r="P5" s="13">
+      <c r="Q5" s="13">
         <v>651</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>641.1</v>
       </c>
       <c r="R5" s="13">
         <v>641.1</v>
       </c>
       <c r="S5" s="13">
+        <v>641.1</v>
+      </c>
+      <c r="T5" s="13">
         <v>607.1</v>
       </c>
-      <c r="T5" s="13">
+      <c r="U5" s="13">
         <v>583</v>
       </c>
-      <c r="U5" s="13">
+      <c r="V5" s="13">
         <v>581.6</v>
       </c>
-      <c r="V5" s="13">
+      <c r="W5" s="13">
         <v>578.70000000000005</v>
       </c>
-      <c r="W5" s="13">
+      <c r="X5" s="13">
         <v>590</v>
       </c>
-      <c r="X5" s="13">
+      <c r="Y5" s="13">
         <v>554.70000000000005</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="Z5" s="13">
         <v>511.8</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="AA5" s="13">
         <v>487</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AB5" s="13">
         <v>478.8</v>
       </c>
-      <c r="AB5" s="13">
+      <c r="AC5" s="13">
         <v>485.5</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AD5" s="13">
         <v>453.4</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AE5" s="13">
         <v>426.1</v>
       </c>
-      <c r="AE5" s="13">
+      <c r="AF5" s="13">
         <v>423.2</v>
       </c>
-      <c r="AF5" s="13"/>
       <c r="AG5" s="13"/>
       <c r="AH5" s="13"/>
       <c r="AI5" s="13"/>
@@ -1834,27 +1851,28 @@
       <c r="BB5" s="13"/>
       <c r="BC5" s="13"/>
       <c r="BD5" s="13"/>
-      <c r="BE5" s="29"/>
-      <c r="BF5" s="13"/>
+      <c r="BE5" s="13"/>
+      <c r="BF5" s="29"/>
       <c r="BG5" s="13"/>
-      <c r="BH5" s="29"/>
-      <c r="BI5" s="13"/>
+      <c r="BH5" s="13"/>
+      <c r="BI5" s="29"/>
       <c r="BJ5" s="13"/>
       <c r="BK5" s="13"/>
       <c r="BL5" s="13"/>
-      <c r="BM5" s="13">
-        <f t="shared" ref="BM5:BM19" si="0">(G5*H5)/100-BS5</f>
+      <c r="BM5" s="13"/>
+      <c r="BN5" s="13">
+        <f t="shared" ref="BN5:BN19" si="0">(G5*H5)/100-BT5</f>
         <v>975.6973999999999</v>
       </c>
-      <c r="BN5" s="13">
+      <c r="BO5" s="13">
         <f>(G5*H5)/100</f>
         <v>975.6973999999999</v>
       </c>
-      <c r="BO5" s="13"/>
       <c r="BP5" s="13"/>
-      <c r="BS5" s="15"/>
-    </row>
-    <row r="6" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BQ5" s="13"/>
+      <c r="BT5" s="15"/>
+    </row>
+    <row r="6" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1166768</v>
       </c>
@@ -1883,48 +1901,50 @@
         <v>3700</v>
       </c>
       <c r="I6" s="13">
+        <v>4500</v>
+      </c>
+      <c r="J6" s="13">
         <v>4424</v>
       </c>
-      <c r="J6" s="13">
+      <c r="K6" s="13">
         <v>4412</v>
       </c>
-      <c r="K6" s="13">
+      <c r="L6" s="13">
         <v>4450</v>
       </c>
-      <c r="L6" s="13">
+      <c r="M6" s="13">
         <v>4238</v>
       </c>
-      <c r="M6" s="13">
+      <c r="N6" s="13">
         <v>3970</v>
       </c>
-      <c r="N6" s="13">
+      <c r="O6" s="13">
         <v>3870</v>
       </c>
-      <c r="O6" s="13">
+      <c r="P6" s="13">
         <v>3805</v>
       </c>
-      <c r="P6" s="13">
+      <c r="Q6" s="13">
         <v>3667</v>
-      </c>
-      <c r="Q6" s="13">
-        <v>3582</v>
       </c>
       <c r="R6" s="13">
         <v>3582</v>
       </c>
       <c r="S6" s="13">
+        <v>3582</v>
+      </c>
+      <c r="T6" s="13">
         <v>3570</v>
       </c>
-      <c r="T6" s="13">
+      <c r="U6" s="13">
         <v>3619</v>
       </c>
-      <c r="U6" s="13">
+      <c r="V6" s="13">
         <v>3650</v>
       </c>
-      <c r="V6" s="13">
+      <c r="W6" s="13">
         <v>3720</v>
       </c>
-      <c r="W6" s="13"/>
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
       <c r="Z6" s="13"/>
@@ -1958,41 +1978,42 @@
       <c r="BB6" s="13"/>
       <c r="BC6" s="13"/>
       <c r="BD6" s="13"/>
-      <c r="BE6" s="29"/>
-      <c r="BF6" s="13"/>
+      <c r="BE6" s="13"/>
+      <c r="BF6" s="29"/>
       <c r="BG6" s="13"/>
-      <c r="BH6" s="29"/>
-      <c r="BI6" s="13"/>
+      <c r="BH6" s="13"/>
+      <c r="BI6" s="29"/>
       <c r="BJ6" s="13"/>
       <c r="BK6" s="13"/>
-      <c r="BM6" s="13">
-        <f>(G6*H6)/100-BS6</f>
+      <c r="BL6" s="13"/>
+      <c r="BN6" s="13">
+        <f>(G6*H6)/100-BT6</f>
         <v>561.70000000000005</v>
       </c>
-      <c r="BN6" s="13">
+      <c r="BO6" s="13">
         <f>(G6*H6)/100</f>
         <v>555</v>
       </c>
-      <c r="BO6" s="13">
-        <f t="shared" ref="BO6" si="1">(BN6-BM6)</f>
+      <c r="BP6" s="13">
+        <f t="shared" ref="BP6" si="1">(BO6-BN6)</f>
         <v>-6.7000000000000455</v>
       </c>
-      <c r="BP6" s="13">
-        <f>((BD6-H6)/H6)*100</f>
+      <c r="BQ6" s="13">
+        <f>((BE6-H6)/H6)*100</f>
         <v>-100</v>
       </c>
-      <c r="BQ6">
+      <c r="BR6">
         <v>5</v>
       </c>
-      <c r="BR6">
+      <c r="BS6">
         <v>3566</v>
       </c>
-      <c r="BS6" s="15">
-        <f>(BQ6*BR6-BQ6*H6)/100</f>
+      <c r="BT6" s="15">
+        <f>(BR6*BS6-BR6*H6)/100</f>
         <v>-6.7</v>
       </c>
     </row>
-    <row r="7" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1148899</v>
       </c>
@@ -2021,75 +2042,77 @@
         <v>3585</v>
       </c>
       <c r="I7" s="13">
+        <v>3954</v>
+      </c>
+      <c r="J7" s="13">
         <v>3932</v>
       </c>
-      <c r="J7" s="13">
+      <c r="K7" s="13">
         <v>3949</v>
       </c>
-      <c r="K7" s="13">
+      <c r="L7" s="13">
         <v>3943</v>
       </c>
-      <c r="L7" s="13">
+      <c r="M7" s="13">
         <v>3928</v>
       </c>
-      <c r="M7" s="13">
+      <c r="N7" s="13">
         <v>3913</v>
       </c>
-      <c r="N7" s="13">
+      <c r="O7" s="13">
         <v>3860</v>
       </c>
-      <c r="O7" s="13">
+      <c r="P7" s="13">
         <v>3893</v>
       </c>
-      <c r="P7" s="13">
+      <c r="Q7" s="13">
         <v>3900</v>
-      </c>
-      <c r="Q7" s="13">
-        <v>3842</v>
       </c>
       <c r="R7" s="13">
         <v>3842</v>
       </c>
       <c r="S7" s="13">
+        <v>3842</v>
+      </c>
+      <c r="T7" s="13">
         <v>3841</v>
       </c>
-      <c r="T7" s="13">
+      <c r="U7" s="13">
         <v>3809</v>
       </c>
-      <c r="U7" s="13">
+      <c r="V7" s="13">
         <v>3810</v>
       </c>
-      <c r="V7" s="13">
+      <c r="W7" s="13">
         <v>3798</v>
       </c>
-      <c r="W7" s="13">
+      <c r="X7" s="13">
         <v>3713</v>
       </c>
-      <c r="X7" s="13">
+      <c r="Y7" s="13">
         <v>3657</v>
       </c>
-      <c r="Y7" s="13">
+      <c r="Z7" s="13">
         <v>3592</v>
       </c>
-      <c r="Z7" s="13">
+      <c r="AA7" s="13">
         <v>3621</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="AB7" s="13">
         <v>3572</v>
       </c>
-      <c r="AB7" s="13">
+      <c r="AC7" s="13">
         <v>3580</v>
       </c>
-      <c r="AC7" s="13">
+      <c r="AD7" s="13">
         <v>3569</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AE7" s="13">
         <v>3659</v>
       </c>
-      <c r="AE7" s="13">
+      <c r="AF7" s="13">
         <v>3656</v>
       </c>
-      <c r="AF7" s="13"/>
       <c r="AG7" s="13"/>
       <c r="AH7" s="13"/>
       <c r="AI7" s="13"/>
@@ -2114,27 +2137,28 @@
       <c r="BB7" s="13"/>
       <c r="BC7" s="13"/>
       <c r="BD7" s="13"/>
-      <c r="BE7" s="29"/>
-      <c r="BF7" s="13"/>
+      <c r="BE7" s="13"/>
+      <c r="BF7" s="29"/>
       <c r="BG7" s="13"/>
-      <c r="BH7" s="29"/>
-      <c r="BI7" s="13"/>
+      <c r="BH7" s="13"/>
+      <c r="BI7" s="29"/>
       <c r="BJ7" s="13"/>
       <c r="BK7" s="13"/>
       <c r="BL7" s="13"/>
-      <c r="BM7" s="13">
+      <c r="BM7" s="13"/>
+      <c r="BN7" s="13">
         <f t="shared" si="0"/>
         <v>2509.5</v>
       </c>
-      <c r="BN7" s="13">
-        <f t="shared" ref="BN7:BN19" si="2">(G7*H7)/100</f>
+      <c r="BO7" s="13">
+        <f t="shared" ref="BO7:BO19" si="2">(G7*H7)/100</f>
         <v>2509.5</v>
       </c>
-      <c r="BO7" s="13"/>
       <c r="BP7" s="13"/>
-      <c r="BS7" s="15"/>
-    </row>
-    <row r="8" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BQ7" s="13"/>
+      <c r="BT7" s="15"/>
+    </row>
+    <row r="8" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1082379</v>
       </c>
@@ -2148,7 +2172,7 @@
       </c>
       <c r="D8" s="6" t="str">
         <f>IF(I8&lt;GEMINI!L8,"למכור בהפסד",IF(I8&gt;GEMINI!M8,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>52</v>
@@ -2163,111 +2187,113 @@
         <v>37875</v>
       </c>
       <c r="I8" s="13">
+        <v>43490</v>
+      </c>
+      <c r="J8" s="13">
         <v>40750</v>
       </c>
-      <c r="J8" s="13">
+      <c r="K8" s="13">
         <v>40900</v>
       </c>
-      <c r="K8" s="13">
+      <c r="L8" s="13">
         <v>40790</v>
       </c>
-      <c r="L8" s="13">
+      <c r="M8" s="13">
         <v>40820</v>
       </c>
-      <c r="M8" s="13">
+      <c r="N8" s="13">
         <v>41570</v>
       </c>
-      <c r="N8" s="13">
+      <c r="O8" s="13">
         <v>42050</v>
       </c>
-      <c r="O8" s="13">
+      <c r="P8" s="13">
         <v>39960</v>
       </c>
-      <c r="P8" s="13">
+      <c r="Q8" s="13">
         <v>39990</v>
-      </c>
-      <c r="Q8" s="13">
-        <v>38680</v>
       </c>
       <c r="R8" s="13">
         <v>38680</v>
       </c>
       <c r="S8" s="13">
+        <v>38680</v>
+      </c>
+      <c r="T8" s="13">
         <v>37770</v>
       </c>
-      <c r="T8" s="13">
+      <c r="U8" s="13">
         <v>36330</v>
       </c>
-      <c r="U8" s="13">
+      <c r="V8" s="13">
         <v>38680</v>
       </c>
-      <c r="V8" s="13">
+      <c r="W8" s="13">
         <v>39090</v>
       </c>
-      <c r="W8" s="13">
+      <c r="X8" s="13">
         <v>37300</v>
       </c>
-      <c r="X8" s="13">
+      <c r="Y8" s="13">
         <v>37650</v>
       </c>
-      <c r="Y8" s="13">
+      <c r="Z8" s="13">
         <v>37300</v>
       </c>
-      <c r="Z8" s="13">
+      <c r="AA8" s="13">
         <v>39450</v>
       </c>
-      <c r="AA8" s="13">
+      <c r="AB8" s="13">
         <v>38390</v>
       </c>
-      <c r="AB8" s="13">
+      <c r="AC8" s="13">
         <v>38800</v>
       </c>
-      <c r="AC8" s="13">
+      <c r="AD8" s="13">
         <v>38510</v>
-      </c>
-      <c r="AD8" s="13">
-        <v>38970</v>
       </c>
       <c r="AE8" s="13">
         <v>38970</v>
       </c>
       <c r="AF8" s="13">
-        <v>37700</v>
+        <v>38970</v>
       </c>
       <c r="AG8" s="13">
         <v>37700</v>
       </c>
       <c r="AH8" s="13">
+        <v>37700</v>
+      </c>
+      <c r="AI8" s="13">
         <v>37750</v>
       </c>
-      <c r="AI8" s="13">
+      <c r="AJ8" s="13">
         <v>38430</v>
       </c>
-      <c r="AJ8" s="13">
+      <c r="AK8" s="13">
         <v>38250</v>
       </c>
-      <c r="AK8" s="13">
+      <c r="AL8" s="13">
         <v>40110</v>
       </c>
-      <c r="AL8" s="13">
+      <c r="AM8" s="13">
         <v>40820</v>
       </c>
-      <c r="AM8" s="13">
+      <c r="AN8" s="13">
         <v>39320</v>
       </c>
-      <c r="AN8" s="13">
+      <c r="AO8" s="13">
         <v>37800</v>
       </c>
-      <c r="AO8" s="13">
+      <c r="AP8" s="13">
         <v>36620</v>
       </c>
-      <c r="AP8" s="13">
+      <c r="AQ8" s="13">
         <v>37130</v>
       </c>
-      <c r="AQ8" s="13">
+      <c r="AR8" s="13">
         <v>35850</v>
       </c>
-      <c r="AR8" s="13"/>
       <c r="AS8" s="13"/>
       <c r="AT8" s="13"/>
       <c r="AU8" s="13"/>
@@ -2280,39 +2306,40 @@
       <c r="BB8" s="13"/>
       <c r="BC8" s="13"/>
       <c r="BD8" s="13"/>
-      <c r="BE8" s="29"/>
-      <c r="BF8" s="13"/>
+      <c r="BE8" s="13"/>
+      <c r="BF8" s="29"/>
       <c r="BG8" s="13"/>
-      <c r="BH8" s="29"/>
-      <c r="BI8" s="13"/>
+      <c r="BH8" s="13"/>
+      <c r="BI8" s="29"/>
       <c r="BJ8" s="13"/>
       <c r="BK8" s="13"/>
       <c r="BL8" s="13"/>
-      <c r="BM8" s="13">
+      <c r="BM8" s="13"/>
+      <c r="BN8" s="13">
         <f t="shared" si="0"/>
         <v>806.25</v>
       </c>
-      <c r="BN8" s="13">
+      <c r="BO8" s="13">
         <f t="shared" si="2"/>
         <v>757.5</v>
       </c>
-      <c r="BO8" s="13">
-        <f t="shared" ref="BO8:BO11" si="3">(BN8-BM8)</f>
+      <c r="BP8" s="13">
+        <f t="shared" ref="BP8:BP11" si="3">(BO8-BN8)</f>
         <v>-48.75</v>
       </c>
-      <c r="BP8" s="13"/>
-      <c r="BQ8">
+      <c r="BQ8" s="13"/>
+      <c r="BR8">
         <v>3</v>
       </c>
-      <c r="BR8">
+      <c r="BS8">
         <v>36250</v>
       </c>
-      <c r="BS8" s="15">
-        <f>(BQ8*BR8-BQ8*H8)/100</f>
+      <c r="BT8" s="15">
+        <f>(BR8*BS8-BR8*H8)/100</f>
         <v>-48.75</v>
       </c>
     </row>
-    <row r="9" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>629014</v>
       </c>
@@ -2341,105 +2368,107 @@
         <v>9227</v>
       </c>
       <c r="I9" s="13">
+        <v>10240</v>
+      </c>
+      <c r="J9" s="13">
         <v>9891</v>
       </c>
-      <c r="J9" s="13">
+      <c r="K9" s="13">
         <v>9956</v>
       </c>
-      <c r="K9" s="13">
+      <c r="L9" s="13">
         <v>9910</v>
       </c>
-      <c r="L9" s="13">
+      <c r="M9" s="13">
         <v>9960</v>
       </c>
-      <c r="M9" s="13">
+      <c r="N9" s="13">
         <v>9924</v>
       </c>
-      <c r="N9" s="13">
+      <c r="O9" s="13">
         <v>9999</v>
       </c>
-      <c r="O9" s="13">
+      <c r="P9" s="13">
         <v>9962</v>
       </c>
-      <c r="P9" s="13">
+      <c r="Q9" s="13">
         <v>9979</v>
-      </c>
-      <c r="Q9" s="13">
-        <v>10130</v>
       </c>
       <c r="R9" s="13">
         <v>10130</v>
       </c>
       <c r="S9" s="13">
+        <v>10130</v>
+      </c>
+      <c r="T9" s="13">
         <v>10400</v>
       </c>
-      <c r="T9" s="13">
+      <c r="U9" s="13">
         <v>10320</v>
       </c>
-      <c r="U9" s="13">
+      <c r="V9" s="13">
         <v>10300</v>
       </c>
-      <c r="V9" s="13">
+      <c r="W9" s="13">
         <v>10310</v>
       </c>
-      <c r="W9" s="13">
+      <c r="X9" s="13">
         <v>9672</v>
       </c>
-      <c r="X9" s="13">
+      <c r="Y9" s="13">
         <v>9953</v>
       </c>
-      <c r="Y9" s="13">
+      <c r="Z9" s="13">
         <v>10090</v>
       </c>
-      <c r="Z9" s="13">
+      <c r="AA9" s="13">
         <v>10070</v>
       </c>
-      <c r="AA9" s="13">
+      <c r="AB9" s="13">
         <v>10030</v>
       </c>
-      <c r="AB9" s="13">
+      <c r="AC9" s="13">
         <v>10120</v>
       </c>
-      <c r="AC9" s="13">
+      <c r="AD9" s="13">
         <v>10000</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AE9" s="13">
         <v>10080</v>
       </c>
-      <c r="AE9" s="13">
+      <c r="AF9" s="13">
         <v>10030</v>
-      </c>
-      <c r="AF9" s="13">
-        <v>9726</v>
       </c>
       <c r="AG9" s="13">
         <v>9726</v>
       </c>
       <c r="AH9" s="13">
+        <v>9726</v>
+      </c>
+      <c r="AI9" s="13">
         <v>9659</v>
       </c>
-      <c r="AI9" s="13">
+      <c r="AJ9" s="13">
         <v>9670</v>
       </c>
-      <c r="AJ9" s="13">
+      <c r="AK9" s="13">
         <v>9590</v>
       </c>
-      <c r="AK9" s="13">
+      <c r="AL9" s="13">
         <v>9588</v>
       </c>
-      <c r="AL9" s="13">
+      <c r="AM9" s="13">
         <v>9400</v>
       </c>
-      <c r="AM9" s="13">
+      <c r="AN9" s="13">
         <v>9320</v>
       </c>
-      <c r="AN9" s="13">
+      <c r="AO9" s="13">
         <v>9071</v>
       </c>
-      <c r="AO9" s="13">
+      <c r="AP9" s="13">
         <v>9271</v>
       </c>
-      <c r="AP9" s="13"/>
       <c r="AQ9" s="13"/>
       <c r="AR9" s="13"/>
       <c r="AS9" s="13"/>
@@ -2454,39 +2483,40 @@
       <c r="BB9" s="13"/>
       <c r="BC9" s="13"/>
       <c r="BD9" s="13"/>
-      <c r="BE9" s="29"/>
-      <c r="BF9" s="13"/>
+      <c r="BE9" s="13"/>
+      <c r="BF9" s="29"/>
       <c r="BG9" s="13"/>
-      <c r="BH9" s="29"/>
-      <c r="BI9" s="13"/>
+      <c r="BH9" s="13"/>
+      <c r="BI9" s="29"/>
       <c r="BJ9" s="13"/>
       <c r="BK9" s="13"/>
       <c r="BL9" s="13"/>
-      <c r="BM9" s="13">
+      <c r="BM9" s="13"/>
+      <c r="BN9" s="13">
         <f t="shared" si="0"/>
         <v>-38.65</v>
       </c>
-      <c r="BN9" s="13">
+      <c r="BO9" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BO9" s="13">
+      <c r="BP9" s="13">
         <f t="shared" si="3"/>
         <v>38.65</v>
       </c>
-      <c r="BP9" s="13"/>
-      <c r="BQ9">
+      <c r="BQ9" s="13"/>
+      <c r="BR9">
         <v>5</v>
       </c>
-      <c r="BR9">
+      <c r="BS9">
         <v>10000</v>
       </c>
-      <c r="BS9" s="15">
-        <f>(BQ9*BR9-BQ9*H9)/100</f>
+      <c r="BT9" s="15">
+        <f>(BR9*BS9-BR9*H9)/100</f>
         <v>38.65</v>
       </c>
     </row>
-    <row r="10" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1141464</v>
       </c>
@@ -2515,187 +2545,190 @@
         <v>4834</v>
       </c>
       <c r="I10" s="13">
+        <v>4849</v>
+      </c>
+      <c r="J10" s="13">
         <v>4821</v>
       </c>
-      <c r="J10" s="13">
+      <c r="K10" s="13">
         <v>4925</v>
       </c>
-      <c r="K10" s="13">
+      <c r="L10" s="13">
         <v>5013</v>
-      </c>
-      <c r="L10" s="13">
-        <v>5050</v>
       </c>
       <c r="M10" s="13">
         <v>5050</v>
       </c>
       <c r="N10" s="13">
+        <v>5050</v>
+      </c>
+      <c r="O10" s="13">
         <v>4930</v>
       </c>
-      <c r="O10" s="13">
+      <c r="P10" s="13">
         <v>5150</v>
       </c>
-      <c r="P10" s="13">
+      <c r="Q10" s="13">
         <v>5283</v>
-      </c>
-      <c r="Q10" s="13">
-        <v>5253</v>
       </c>
       <c r="R10" s="13">
         <v>5253</v>
       </c>
       <c r="S10" s="13">
+        <v>5253</v>
+      </c>
+      <c r="T10" s="13">
         <v>5400</v>
       </c>
-      <c r="T10" s="13">
+      <c r="U10" s="13">
         <v>5522</v>
       </c>
-      <c r="U10" s="13">
+      <c r="V10" s="13">
         <v>5690</v>
       </c>
-      <c r="V10" s="13">
+      <c r="W10" s="13">
         <v>5749</v>
       </c>
-      <c r="W10" s="13">
+      <c r="X10" s="13">
         <v>5840</v>
-      </c>
-      <c r="X10" s="13">
-        <v>5650</v>
       </c>
       <c r="Y10" s="13">
         <v>5650</v>
       </c>
       <c r="Z10" s="13">
+        <v>5650</v>
+      </c>
+      <c r="AA10" s="13">
         <v>5841</v>
       </c>
-      <c r="AA10" s="13">
+      <c r="AB10" s="13">
         <v>5758</v>
       </c>
-      <c r="AB10" s="13">
+      <c r="AC10" s="13">
         <v>5673</v>
       </c>
-      <c r="AC10" s="13">
+      <c r="AD10" s="13">
         <v>5609</v>
       </c>
-      <c r="AD10" s="13">
+      <c r="AE10" s="13">
         <v>5750</v>
       </c>
-      <c r="AE10" s="13">
+      <c r="AF10" s="13">
         <v>5841</v>
-      </c>
-      <c r="AF10" s="13">
-        <v>5564</v>
       </c>
       <c r="AG10" s="13">
         <v>5564</v>
       </c>
       <c r="AH10" s="13">
+        <v>5564</v>
+      </c>
+      <c r="AI10" s="13">
         <v>5557</v>
       </c>
-      <c r="AI10" s="13">
+      <c r="AJ10" s="13">
         <v>5501</v>
       </c>
-      <c r="AJ10" s="13">
+      <c r="AK10" s="13">
         <v>5250</v>
       </c>
-      <c r="AK10" s="13">
+      <c r="AL10" s="13">
         <v>5270</v>
       </c>
-      <c r="AL10" s="13">
+      <c r="AM10" s="13">
         <v>5149</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AN10" s="13">
         <v>5092</v>
       </c>
-      <c r="AN10" s="13">
+      <c r="AO10" s="13">
         <v>5228</v>
       </c>
-      <c r="AO10" s="13">
+      <c r="AP10" s="13">
         <v>5301</v>
       </c>
-      <c r="AP10" s="13">
+      <c r="AQ10" s="13">
         <v>5159</v>
       </c>
-      <c r="AQ10" s="13">
+      <c r="AR10" s="13">
         <v>5198</v>
       </c>
-      <c r="AR10" s="13">
+      <c r="AS10" s="13">
         <v>5077</v>
       </c>
-      <c r="AS10" s="13">
+      <c r="AT10" s="13">
         <v>4842</v>
       </c>
-      <c r="AT10" s="13">
+      <c r="AU10" s="13">
         <v>5050</v>
       </c>
-      <c r="AU10" s="13">
+      <c r="AV10" s="13">
         <v>4970</v>
       </c>
-      <c r="AV10" s="13">
+      <c r="AW10" s="13">
         <v>4880</v>
       </c>
-      <c r="AW10" s="13">
+      <c r="AX10" s="13">
         <v>4704</v>
       </c>
-      <c r="AX10" s="13">
+      <c r="AY10" s="13">
         <v>4770</v>
       </c>
-      <c r="AY10" s="13">
+      <c r="AZ10" s="13">
         <v>4609</v>
       </c>
-      <c r="AZ10" s="13">
+      <c r="BA10" s="13">
         <v>4674</v>
       </c>
-      <c r="BA10" s="13">
+      <c r="BB10" s="13">
         <v>4710</v>
       </c>
-      <c r="BB10" s="13">
+      <c r="BC10" s="13">
         <v>4688</v>
       </c>
-      <c r="BC10" s="13">
+      <c r="BD10" s="13">
         <v>4900</v>
       </c>
-      <c r="BD10" s="13">
+      <c r="BE10" s="13">
         <v>5000</v>
       </c>
-      <c r="BE10" s="29">
+      <c r="BF10" s="29">
         <v>4932</v>
       </c>
-      <c r="BF10" s="13"/>
       <c r="BG10" s="13"/>
-      <c r="BH10" s="29"/>
-      <c r="BI10" s="13"/>
+      <c r="BH10" s="13"/>
+      <c r="BI10" s="29"/>
       <c r="BJ10" s="13"/>
       <c r="BK10" s="13"/>
       <c r="BL10" s="13"/>
-      <c r="BM10" s="13">
+      <c r="BM10" s="13"/>
+      <c r="BN10" s="13">
         <f t="shared" si="0"/>
         <v>-87.859799999999964</v>
       </c>
-      <c r="BN10" s="13">
+      <c r="BO10" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BO10" s="13">
+      <c r="BP10" s="13">
         <f t="shared" si="3"/>
         <v>87.859799999999964</v>
       </c>
-      <c r="BP10" s="13">
-        <f>((BD10-H10)/H10)*100</f>
+      <c r="BQ10" s="13">
+        <f>((BE10-H10)/H10)*100</f>
         <v>3.434009102192801</v>
       </c>
-      <c r="BQ10">
+      <c r="BR10">
         <v>21</v>
       </c>
-      <c r="BR10">
+      <c r="BS10">
         <v>5252.38</v>
       </c>
-      <c r="BS10" s="15">
-        <f>(BQ10*BR10-BQ10*H10)/100</f>
+      <c r="BT10" s="15">
+        <f>(BR10*BS10-BR10*H10)/100</f>
         <v>87.859799999999964</v>
       </c>
     </row>
-    <row r="11" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1166974</v>
       </c>
@@ -2724,69 +2757,71 @@
         <v>901.87</v>
       </c>
       <c r="I11" s="13">
+        <v>1109</v>
+      </c>
+      <c r="J11" s="13">
         <v>1090</v>
       </c>
-      <c r="J11" s="13">
+      <c r="K11" s="13">
         <v>1144</v>
       </c>
-      <c r="K11" s="13">
+      <c r="L11" s="13">
         <v>1162</v>
       </c>
-      <c r="L11" s="13">
+      <c r="M11" s="13">
         <v>1109</v>
       </c>
-      <c r="M11" s="13">
+      <c r="N11" s="13">
         <v>1029</v>
       </c>
-      <c r="N11" s="13">
+      <c r="O11" s="13">
         <v>993</v>
       </c>
-      <c r="O11" s="13">
+      <c r="P11" s="13">
         <v>1017</v>
       </c>
-      <c r="P11" s="13">
+      <c r="Q11" s="13">
         <v>960</v>
-      </c>
-      <c r="Q11" s="13">
-        <v>965</v>
       </c>
       <c r="R11" s="13">
         <v>965</v>
       </c>
       <c r="S11" s="13">
+        <v>965</v>
+      </c>
+      <c r="T11" s="13">
         <v>951.7</v>
       </c>
-      <c r="T11" s="13">
+      <c r="U11" s="13">
         <v>946</v>
       </c>
-      <c r="U11" s="13">
+      <c r="V11" s="13">
         <v>869.2</v>
       </c>
-      <c r="V11" s="13">
+      <c r="W11" s="13">
         <v>865</v>
       </c>
-      <c r="W11" s="13">
+      <c r="X11" s="13">
         <v>851</v>
       </c>
-      <c r="X11" s="13">
+      <c r="Y11" s="13">
         <v>829.3</v>
       </c>
-      <c r="Y11" s="13">
+      <c r="Z11" s="13">
         <v>830</v>
       </c>
-      <c r="Z11" s="13">
+      <c r="AA11" s="13">
         <v>810</v>
       </c>
-      <c r="AA11" s="13">
+      <c r="AB11" s="13">
         <v>812.8</v>
       </c>
-      <c r="AB11" s="13">
+      <c r="AC11" s="13">
         <v>788</v>
       </c>
-      <c r="AC11" s="13">
+      <c r="AD11" s="13">
         <v>772</v>
       </c>
-      <c r="AD11" s="13"/>
       <c r="AE11" s="13"/>
       <c r="AF11" s="13"/>
       <c r="AG11" s="13"/>
@@ -2813,33 +2848,34 @@
       <c r="BB11" s="13"/>
       <c r="BC11" s="13"/>
       <c r="BD11" s="13"/>
-      <c r="BE11" s="29"/>
-      <c r="BF11" s="13"/>
+      <c r="BE11" s="13"/>
+      <c r="BF11" s="29"/>
       <c r="BG11" s="13"/>
-      <c r="BH11" s="29"/>
-      <c r="BI11" s="13"/>
+      <c r="BH11" s="13"/>
+      <c r="BI11" s="29"/>
       <c r="BJ11" s="13"/>
       <c r="BK11" s="13"/>
       <c r="BL11" s="13"/>
-      <c r="BM11" s="13">
+      <c r="BM11" s="13"/>
+      <c r="BN11" s="13">
         <f t="shared" si="0"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BN11" s="13">
+      <c r="BO11" s="13">
         <f t="shared" si="2"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BO11" s="13">
+      <c r="BP11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BP11" s="13"/>
-      <c r="BS11" s="15">
-        <f>(BQ11*BR11-BQ11*H11)/100</f>
+      <c r="BQ11" s="13"/>
+      <c r="BT11" s="15">
+        <f>(BR11*BS11-BR11*H11)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1176593</v>
       </c>
@@ -2868,75 +2904,77 @@
         <v>22581.42</v>
       </c>
       <c r="I12" s="13">
+        <v>30100</v>
+      </c>
+      <c r="J12" s="13">
         <v>30500</v>
       </c>
-      <c r="J12" s="13">
+      <c r="K12" s="13">
         <v>28850</v>
       </c>
-      <c r="K12" s="13">
+      <c r="L12" s="13">
         <v>27450</v>
       </c>
-      <c r="L12" s="13">
+      <c r="M12" s="13">
         <v>26940</v>
       </c>
-      <c r="M12" s="13">
+      <c r="N12" s="13">
         <v>26800</v>
       </c>
-      <c r="N12" s="13">
+      <c r="O12" s="13">
         <v>25950</v>
       </c>
-      <c r="O12" s="13">
+      <c r="P12" s="13">
         <v>26000</v>
       </c>
-      <c r="P12" s="13">
+      <c r="Q12" s="13">
         <v>26600</v>
-      </c>
-      <c r="Q12" s="13">
-        <v>24630</v>
       </c>
       <c r="R12" s="13">
         <v>24630</v>
       </c>
       <c r="S12" s="13">
+        <v>24630</v>
+      </c>
+      <c r="T12" s="13">
         <v>25230</v>
       </c>
-      <c r="T12" s="13">
+      <c r="U12" s="13">
         <v>24700</v>
       </c>
-      <c r="U12" s="13">
+      <c r="V12" s="13">
         <v>23780</v>
       </c>
-      <c r="V12" s="13">
+      <c r="W12" s="13">
         <v>23920</v>
       </c>
-      <c r="W12" s="13">
+      <c r="X12" s="13">
         <v>22390</v>
       </c>
-      <c r="X12" s="13">
+      <c r="Y12" s="13">
         <v>23000</v>
       </c>
-      <c r="Y12" s="13">
+      <c r="Z12" s="13">
         <v>20990</v>
       </c>
-      <c r="Z12" s="13">
+      <c r="AA12" s="13">
         <v>20260</v>
       </c>
-      <c r="AA12" s="13">
+      <c r="AB12" s="13">
         <v>19200</v>
       </c>
-      <c r="AB12" s="13">
+      <c r="AC12" s="13">
         <v>19860</v>
       </c>
-      <c r="AC12" s="13">
+      <c r="AD12" s="13">
         <v>19700</v>
       </c>
-      <c r="AD12" s="13">
+      <c r="AE12" s="13">
         <v>19430</v>
       </c>
-      <c r="AE12" s="13">
+      <c r="AF12" s="13">
         <v>19020</v>
       </c>
-      <c r="AF12" s="13"/>
       <c r="AG12" s="13"/>
       <c r="AH12" s="13"/>
       <c r="AI12" s="13"/>
@@ -2961,30 +2999,31 @@
       <c r="BB12" s="13"/>
       <c r="BC12" s="13"/>
       <c r="BD12" s="13"/>
-      <c r="BE12" s="29"/>
-      <c r="BF12" s="13"/>
+      <c r="BE12" s="13"/>
+      <c r="BF12" s="29"/>
       <c r="BG12" s="13"/>
-      <c r="BH12" s="29"/>
-      <c r="BI12" s="13"/>
+      <c r="BH12" s="13"/>
+      <c r="BI12" s="29"/>
       <c r="BJ12" s="13"/>
       <c r="BK12" s="13"/>
       <c r="BL12" s="13"/>
-      <c r="BM12" s="13">
+      <c r="BM12" s="13"/>
+      <c r="BN12" s="13">
         <f t="shared" si="0"/>
         <v>1580.6994</v>
       </c>
-      <c r="BN12" s="13">
+      <c r="BO12" s="13">
         <f t="shared" si="2"/>
         <v>1580.6994</v>
       </c>
-      <c r="BO12" s="13"/>
       <c r="BP12" s="13"/>
-      <c r="BS12" s="15">
-        <f t="shared" ref="BS12:BS14" si="4">(BQ12*BR12-BQ12*H12)/100</f>
+      <c r="BQ12" s="13"/>
+      <c r="BT12" s="15">
+        <f t="shared" ref="BT12:BT14" si="4">(BR12*BS12-BR12*H12)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>397018</v>
       </c>
@@ -2998,7 +3037,7 @@
       </c>
       <c r="D13" s="6" t="str">
         <f>IF(I13&lt;GEMINI!L13,"למכור בהפסד",IF(I13&gt;GEMINI!M13,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>למכור בהפסד</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>96</v>
@@ -3006,34 +3045,32 @@
       <c r="F13" s="4">
         <v>46042</v>
       </c>
-      <c r="G13" s="27">
-        <v>113</v>
-      </c>
+      <c r="G13" s="27"/>
       <c r="H13" s="13">
         <v>723</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="13"/>
+      <c r="J13" s="13">
         <v>1490</v>
       </c>
-      <c r="J13" s="13">
+      <c r="K13" s="13">
         <v>1210</v>
       </c>
-      <c r="K13" s="13">
+      <c r="L13" s="13">
         <v>1100</v>
       </c>
-      <c r="L13" s="13">
+      <c r="M13" s="13">
         <v>980</v>
       </c>
-      <c r="M13" s="13">
+      <c r="N13" s="13">
         <v>932.1</v>
       </c>
-      <c r="N13" s="13">
+      <c r="O13" s="13">
         <v>822</v>
       </c>
-      <c r="O13" s="13">
+      <c r="P13" s="13">
         <v>790</v>
       </c>
-      <c r="P13" s="13"/>
       <c r="Q13" s="13"/>
       <c r="R13" s="13"/>
       <c r="S13" s="13"/>
@@ -3074,30 +3111,31 @@
       <c r="BB13" s="13"/>
       <c r="BC13" s="13"/>
       <c r="BD13" s="13"/>
-      <c r="BE13" s="29"/>
-      <c r="BF13" s="13"/>
+      <c r="BE13" s="13"/>
+      <c r="BF13" s="29"/>
       <c r="BG13" s="13"/>
-      <c r="BH13" s="29"/>
-      <c r="BI13" s="13"/>
+      <c r="BH13" s="13"/>
+      <c r="BI13" s="29"/>
       <c r="BJ13" s="13"/>
       <c r="BK13" s="13"/>
       <c r="BL13" s="13"/>
-      <c r="BM13" s="13">
+      <c r="BM13" s="13"/>
+      <c r="BN13" s="13">
         <f t="shared" si="0"/>
-        <v>816.99</v>
-      </c>
-      <c r="BN13" s="13">
+        <v>0</v>
+      </c>
+      <c r="BO13" s="13">
         <f t="shared" si="2"/>
-        <v>816.99</v>
-      </c>
-      <c r="BO13" s="13"/>
+        <v>0</v>
+      </c>
       <c r="BP13" s="13"/>
-      <c r="BS13" s="15">
+      <c r="BQ13" s="13"/>
+      <c r="BT13" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>662577</v>
       </c>
@@ -3126,195 +3164,198 @@
         <v>7204.22</v>
       </c>
       <c r="I14" s="13">
+        <v>7672</v>
+      </c>
+      <c r="J14" s="13">
         <v>7676</v>
       </c>
-      <c r="J14" s="13">
+      <c r="K14" s="13">
         <v>7844</v>
       </c>
-      <c r="K14" s="13">
+      <c r="L14" s="13">
         <v>7810</v>
       </c>
-      <c r="L14" s="13">
+      <c r="M14" s="13">
         <v>7710</v>
       </c>
-      <c r="M14" s="13">
+      <c r="N14" s="13">
         <v>7735</v>
       </c>
-      <c r="N14" s="13">
+      <c r="O14" s="13">
         <v>7725</v>
       </c>
-      <c r="O14" s="13">
+      <c r="P14" s="13">
         <v>7787</v>
       </c>
-      <c r="P14" s="13">
+      <c r="Q14" s="13">
         <v>7955</v>
-      </c>
-      <c r="Q14" s="13">
-        <v>7627</v>
       </c>
       <c r="R14" s="13">
         <v>7627</v>
       </c>
       <c r="S14" s="13">
+        <v>7627</v>
+      </c>
+      <c r="T14" s="13">
         <v>7656</v>
       </c>
-      <c r="T14" s="13">
+      <c r="U14" s="13">
         <v>7507</v>
       </c>
-      <c r="U14" s="13">
+      <c r="V14" s="13">
         <v>7590</v>
       </c>
-      <c r="V14" s="13">
+      <c r="W14" s="13">
         <v>7569</v>
       </c>
-      <c r="W14" s="13">
+      <c r="X14" s="13">
         <v>7269</v>
       </c>
-      <c r="X14" s="13">
+      <c r="Y14" s="13">
         <v>7444</v>
       </c>
-      <c r="Y14" s="13">
+      <c r="Z14" s="13">
         <v>7205</v>
       </c>
-      <c r="Z14" s="13">
+      <c r="AA14" s="13">
         <v>7298</v>
       </c>
-      <c r="AA14" s="13">
+      <c r="AB14" s="13">
         <v>7222</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AC14" s="13">
         <v>7079</v>
       </c>
-      <c r="AC14" s="13">
+      <c r="AD14" s="13">
         <v>7140</v>
       </c>
-      <c r="AD14" s="13">
+      <c r="AE14" s="13">
         <v>7440</v>
       </c>
-      <c r="AE14" s="13">
+      <c r="AF14" s="13">
         <v>7530</v>
-      </c>
-      <c r="AF14" s="13">
-        <v>7535</v>
       </c>
       <c r="AG14" s="13">
         <v>7535</v>
       </c>
       <c r="AH14" s="13">
+        <v>7535</v>
+      </c>
+      <c r="AI14" s="13">
         <v>7568</v>
       </c>
-      <c r="AI14" s="13">
+      <c r="AJ14" s="13">
         <v>7699</v>
       </c>
-      <c r="AJ14" s="13">
+      <c r="AK14" s="13">
         <v>7638</v>
       </c>
-      <c r="AK14" s="13">
+      <c r="AL14" s="13">
         <v>7654</v>
       </c>
-      <c r="AL14" s="13">
+      <c r="AM14" s="13">
         <v>7584</v>
       </c>
-      <c r="AM14" s="13">
+      <c r="AN14" s="13">
         <v>7479</v>
       </c>
-      <c r="AN14" s="13">
+      <c r="AO14" s="13">
         <v>7490</v>
       </c>
-      <c r="AO14" s="13">
+      <c r="AP14" s="13">
         <v>7480</v>
       </c>
-      <c r="AP14" s="13">
+      <c r="AQ14" s="13">
         <v>7270</v>
       </c>
-      <c r="AQ14" s="13">
+      <c r="AR14" s="13">
         <v>7163</v>
       </c>
-      <c r="AR14" s="13">
+      <c r="AS14" s="13">
         <v>7231</v>
-      </c>
-      <c r="AS14" s="13">
-        <v>7100</v>
       </c>
       <c r="AT14" s="13">
         <v>7100</v>
       </c>
       <c r="AU14" s="13">
+        <v>7100</v>
+      </c>
+      <c r="AV14" s="13">
         <v>7027</v>
       </c>
-      <c r="AV14" s="13">
+      <c r="AW14" s="13">
         <v>6984</v>
       </c>
-      <c r="AW14" s="13">
+      <c r="AX14" s="13">
         <v>6944</v>
       </c>
-      <c r="AX14" s="13">
+      <c r="AY14" s="13">
         <v>6924</v>
       </c>
-      <c r="AY14" s="13">
+      <c r="AZ14" s="13">
         <v>6930</v>
       </c>
-      <c r="AZ14" s="13">
+      <c r="BA14" s="13">
         <v>6938</v>
       </c>
-      <c r="BA14" s="13">
+      <c r="BB14" s="13">
         <v>6989</v>
       </c>
-      <c r="BB14" s="13">
+      <c r="BC14" s="13">
         <v>6871</v>
       </c>
-      <c r="BC14" s="13">
+      <c r="BD14" s="13">
         <v>6943</v>
       </c>
-      <c r="BD14" s="13">
+      <c r="BE14" s="13">
         <v>7040</v>
       </c>
-      <c r="BE14" s="29">
+      <c r="BF14" s="29">
         <v>6696</v>
       </c>
-      <c r="BF14" s="13">
+      <c r="BG14" s="13">
         <v>6965</v>
       </c>
-      <c r="BG14" s="13">
+      <c r="BH14" s="13">
         <v>6788</v>
       </c>
-      <c r="BH14" s="29">
+      <c r="BI14" s="29">
         <v>6696</v>
       </c>
-      <c r="BI14" s="13">
+      <c r="BJ14" s="13">
         <v>6625</v>
       </c>
-      <c r="BJ14" s="13">
+      <c r="BK14" s="13">
         <v>6660</v>
       </c>
-      <c r="BK14" s="13">
+      <c r="BL14" s="13">
         <v>6791</v>
       </c>
-      <c r="BL14" s="13">
+      <c r="BM14" s="13">
         <v>6610</v>
       </c>
-      <c r="BM14" s="13">
+      <c r="BN14" s="13">
         <f t="shared" si="0"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BN14" s="13">
+      <c r="BO14" s="13">
         <f t="shared" si="2"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BO14" s="13">
-        <f t="shared" ref="BO14" si="5">(BN14-BM14)</f>
+      <c r="BP14" s="13">
+        <f t="shared" ref="BP14" si="5">(BO14-BN14)</f>
         <v>0</v>
       </c>
-      <c r="BP14" s="13">
-        <f>((BD14-H14)/H14)*100</f>
+      <c r="BQ14" s="13">
+        <f>((BE14-H14)/H14)*100</f>
         <v>-2.2794972946411995</v>
       </c>
-      <c r="BS14" s="15">
+      <c r="BT14" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>5137534</v>
       </c>
@@ -3343,63 +3384,65 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
-        <v>14583.37</v>
+        <v>14679.12</v>
       </c>
       <c r="J15" s="13">
+        <v>14679.12</v>
+      </c>
+      <c r="K15" s="13">
         <v>13968</v>
       </c>
-      <c r="K15" s="13">
+      <c r="L15" s="13">
         <v>15528.12</v>
       </c>
-      <c r="L15" s="13">
+      <c r="M15" s="13">
         <v>14358.25</v>
       </c>
-      <c r="M15" s="13">
+      <c r="N15" s="13">
         <v>14385.75</v>
       </c>
-      <c r="N15" s="13">
+      <c r="O15" s="13">
         <v>13880</v>
       </c>
-      <c r="O15" s="13">
+      <c r="P15" s="13">
         <v>13610.62</v>
       </c>
-      <c r="P15" s="13">
+      <c r="Q15" s="13">
         <v>13016</v>
       </c>
-      <c r="Q15" s="13">
+      <c r="R15" s="13">
         <v>12487.37</v>
       </c>
-      <c r="R15" s="13">
+      <c r="S15" s="13">
         <v>12638.62</v>
       </c>
-      <c r="S15" s="13">
+      <c r="T15" s="13">
         <v>12533.87</v>
       </c>
-      <c r="T15" s="13">
+      <c r="U15" s="13">
         <v>11299.5</v>
       </c>
-      <c r="U15" s="13">
+      <c r="V15" s="13">
         <v>11193.12</v>
       </c>
-      <c r="V15" s="13">
+      <c r="W15" s="13">
         <v>11548.62</v>
       </c>
-      <c r="W15" s="13">
+      <c r="X15" s="13">
         <v>11125.62</v>
       </c>
-      <c r="X15" s="13">
+      <c r="Y15" s="13">
         <v>10932.12</v>
       </c>
-      <c r="Y15" s="13">
+      <c r="Z15" s="13">
         <v>11095.62</v>
       </c>
-      <c r="Z15" s="13">
+      <c r="AA15" s="13">
         <v>10910.58</v>
       </c>
-      <c r="AA15" s="13">
+      <c r="AB15" s="13">
         <v>11609.37</v>
       </c>
-      <c r="AB15" s="13"/>
       <c r="AC15" s="13"/>
       <c r="AD15" s="13"/>
       <c r="AE15" s="13"/>
@@ -3409,8 +3452,8 @@
       <c r="AI15" s="13"/>
       <c r="AJ15" s="13"/>
       <c r="AK15" s="13"/>
-      <c r="AL15" s="14"/>
-      <c r="AM15" s="13"/>
+      <c r="AL15" s="13"/>
+      <c r="AM15" s="14"/>
       <c r="AN15" s="13"/>
       <c r="AO15" s="13"/>
       <c r="AP15" s="13"/>
@@ -3428,36 +3471,37 @@
       <c r="BB15" s="13"/>
       <c r="BC15" s="13"/>
       <c r="BD15" s="13"/>
-      <c r="BE15" s="29"/>
-      <c r="BF15" s="13"/>
+      <c r="BE15" s="13"/>
+      <c r="BF15" s="29"/>
       <c r="BG15" s="13"/>
-      <c r="BH15" s="29"/>
-      <c r="BI15" s="13"/>
+      <c r="BH15" s="13"/>
+      <c r="BI15" s="29"/>
       <c r="BJ15" s="13"/>
       <c r="BK15" s="13"/>
       <c r="BL15" s="13"/>
-      <c r="BM15" s="13">
+      <c r="BM15" s="13"/>
+      <c r="BN15" s="13">
         <f t="shared" si="0"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BN15" s="13">
+      <c r="BO15" s="13">
         <f t="shared" si="2"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BO15" s="13">
-        <f t="shared" ref="BO15:BO18" si="6">(BN15-BM15)</f>
+      <c r="BP15" s="13">
+        <f t="shared" ref="BP15:BP18" si="6">(BO15-BN15)</f>
         <v>0</v>
       </c>
-      <c r="BP15" s="13">
-        <f>((BD15-H15)/H15)*100</f>
+      <c r="BQ15" s="13">
+        <f>((BE15-H15)/H15)*100</f>
         <v>-100</v>
       </c>
-      <c r="BS15" s="15">
-        <f t="shared" ref="BS15:BS18" si="7">(BQ15*BR15-BQ15*H15)/100</f>
+      <c r="BT15" s="15">
+        <f t="shared" ref="BT15:BT18" si="7">(BR15*BS15-BR15*H15)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>5135470</v>
       </c>
@@ -3486,201 +3530,204 @@
         <v>183.73</v>
       </c>
       <c r="I16" s="13">
+        <v>227.54</v>
+      </c>
+      <c r="J16" s="13">
         <v>226.96</v>
       </c>
-      <c r="J16" s="13">
+      <c r="K16" s="13">
         <v>225.24</v>
       </c>
-      <c r="K16" s="13">
+      <c r="L16" s="13">
         <v>223.25</v>
-      </c>
-      <c r="L16" s="13">
-        <v>219.14</v>
       </c>
       <c r="M16" s="13">
         <v>219.14</v>
       </c>
       <c r="N16" s="13">
+        <v>219.14</v>
+      </c>
+      <c r="O16" s="13">
         <v>219.3</v>
       </c>
-      <c r="O16" s="13">
+      <c r="P16" s="13">
         <v>222.79</v>
       </c>
-      <c r="P16" s="13">
+      <c r="Q16" s="13">
         <v>221.16</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="R16" s="13">
         <v>220.66</v>
       </c>
-      <c r="R16" s="13">
+      <c r="S16" s="13">
         <v>222.06</v>
       </c>
-      <c r="S16" s="13">
+      <c r="T16" s="13">
         <v>218.71</v>
       </c>
-      <c r="T16" s="13">
+      <c r="U16" s="13">
         <v>216.74</v>
       </c>
-      <c r="U16" s="13">
+      <c r="V16" s="13">
         <v>216.04</v>
-      </c>
-      <c r="V16" s="13">
-        <v>210.69</v>
       </c>
       <c r="W16" s="13">
         <v>210.69</v>
       </c>
       <c r="X16" s="13">
+        <v>210.69</v>
+      </c>
+      <c r="Y16" s="13">
         <v>198</v>
       </c>
-      <c r="Y16" s="13">
+      <c r="Z16" s="13">
         <v>196.74</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="AA16" s="13">
         <v>192.56</v>
       </c>
-      <c r="AA16" s="13">
+      <c r="AB16" s="13">
         <v>192.23</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AC16" s="13">
         <v>191.19</v>
       </c>
-      <c r="AC16" s="13">
+      <c r="AD16" s="13">
         <v>193.62</v>
       </c>
-      <c r="AD16" s="13">
+      <c r="AE16" s="13">
         <v>190.75</v>
       </c>
-      <c r="AE16" s="13">
+      <c r="AF16" s="13">
         <v>189.06</v>
-      </c>
-      <c r="AF16" s="13">
-        <v>182.73</v>
       </c>
       <c r="AG16" s="13">
         <v>182.73</v>
       </c>
       <c r="AH16" s="13">
+        <v>182.73</v>
+      </c>
+      <c r="AI16" s="13">
         <v>177.92</v>
       </c>
-      <c r="AI16" s="13">
+      <c r="AJ16" s="13">
         <v>179.16</v>
       </c>
-      <c r="AJ16" s="13">
+      <c r="AK16" s="13">
         <v>179.34</v>
-      </c>
-      <c r="AK16" s="13">
-        <v>176.5</v>
       </c>
       <c r="AL16" s="13">
         <v>176.5</v>
       </c>
       <c r="AM16" s="13">
+        <v>176.5</v>
+      </c>
+      <c r="AN16" s="13">
         <v>175.93</v>
       </c>
-      <c r="AN16" s="13">
+      <c r="AO16" s="13">
         <v>174.51</v>
       </c>
-      <c r="AO16" s="13">
+      <c r="AP16" s="13">
         <v>173.91</v>
       </c>
-      <c r="AP16" s="13">
+      <c r="AQ16" s="13">
         <v>177.1</v>
       </c>
-      <c r="AQ16" s="13">
+      <c r="AR16" s="13">
         <v>178.24</v>
       </c>
-      <c r="AR16" s="13">
+      <c r="AS16" s="13">
         <v>176.52</v>
       </c>
-      <c r="AS16" s="13">
+      <c r="AT16" s="13">
         <v>178.27</v>
       </c>
-      <c r="AT16" s="13">
+      <c r="AU16" s="13">
         <v>175.29</v>
       </c>
-      <c r="AU16" s="13">
+      <c r="AV16" s="13">
         <v>175.34</v>
       </c>
-      <c r="AV16" s="13">
+      <c r="AW16" s="13">
         <v>174.41</v>
       </c>
-      <c r="AW16" s="13">
+      <c r="AX16" s="13">
         <v>176.22</v>
       </c>
-      <c r="AX16" s="13">
+      <c r="AY16" s="13">
         <v>174</v>
       </c>
-      <c r="AY16" s="13">
+      <c r="AZ16" s="13">
         <v>176.35</v>
       </c>
-      <c r="AZ16" s="13">
+      <c r="BA16" s="13">
         <v>177.71</v>
       </c>
-      <c r="BA16" s="13">
+      <c r="BB16" s="13">
         <v>180.08</v>
       </c>
-      <c r="BB16" s="13">
+      <c r="BC16" s="13">
         <v>181.96</v>
       </c>
-      <c r="BC16" s="13">
+      <c r="BD16" s="13">
         <v>182.9</v>
       </c>
-      <c r="BD16" s="13">
+      <c r="BE16" s="13">
         <v>181.86</v>
       </c>
-      <c r="BE16" s="29">
+      <c r="BF16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BF16" s="13">
+      <c r="BG16" s="13">
         <v>181.07</v>
       </c>
-      <c r="BG16" s="13">
+      <c r="BH16" s="13">
         <v>182.56</v>
       </c>
-      <c r="BH16" s="29">
+      <c r="BI16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BI16" s="13">
+      <c r="BJ16" s="13">
         <v>178.86</v>
       </c>
-      <c r="BJ16" s="13">
+      <c r="BK16" s="13">
         <v>180.16</v>
       </c>
-      <c r="BK16" s="13">
+      <c r="BL16" s="13">
         <v>179.56</v>
       </c>
-      <c r="BL16" s="13">
+      <c r="BM16" s="13">
         <v>176.55</v>
       </c>
-      <c r="BM16" s="13">
+      <c r="BN16" s="13">
         <f t="shared" si="0"/>
         <v>673.09559999999999</v>
       </c>
-      <c r="BN16" s="13">
+      <c r="BO16" s="13">
         <f t="shared" si="2"/>
         <v>551.19000000000005</v>
       </c>
-      <c r="BO16" s="13">
+      <c r="BP16" s="13">
         <f t="shared" si="6"/>
         <v>-121.90559999999994</v>
       </c>
-      <c r="BP16" s="13">
-        <f>((BD16-H16)/H16)*100</f>
+      <c r="BQ16" s="13">
+        <f>((BE16-H16)/H16)*100</f>
         <v>-1.0177978555488905</v>
       </c>
-      <c r="BQ16">
+      <c r="BR16">
         <v>1864</v>
       </c>
-      <c r="BR16">
+      <c r="BS16">
         <v>177.19</v>
       </c>
-      <c r="BS16" s="15">
+      <c r="BT16" s="15">
         <f t="shared" si="7"/>
         <v>-121.90559999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>5134135</v>
       </c>
@@ -3709,7 +3756,7 @@
         <v>159.65</v>
       </c>
       <c r="I17" s="13">
-        <v>189.51</v>
+        <v>194.88</v>
       </c>
       <c r="J17" s="13">
         <v>189.51</v>
@@ -3718,13 +3765,13 @@
         <v>189.51</v>
       </c>
       <c r="L17" s="13">
-        <v>185.52</v>
+        <v>189.51</v>
       </c>
       <c r="M17" s="13">
         <v>185.52</v>
       </c>
       <c r="N17" s="13">
-        <v>178.98</v>
+        <v>185.52</v>
       </c>
       <c r="O17" s="13">
         <v>178.98</v>
@@ -3733,7 +3780,7 @@
         <v>178.98</v>
       </c>
       <c r="Q17" s="13">
-        <v>170.7</v>
+        <v>178.98</v>
       </c>
       <c r="R17" s="13">
         <v>170.7</v>
@@ -3742,10 +3789,10 @@
         <v>170.7</v>
       </c>
       <c r="T17" s="13">
+        <v>170.7</v>
+      </c>
+      <c r="U17" s="13">
         <v>170.45</v>
-      </c>
-      <c r="U17" s="13">
-        <v>160.84</v>
       </c>
       <c r="V17" s="13">
         <v>160.84</v>
@@ -3754,15 +3801,17 @@
         <v>160.84</v>
       </c>
       <c r="X17" s="13">
+        <v>160.84</v>
+      </c>
+      <c r="Y17" s="13">
         <v>159.02000000000001</v>
-      </c>
-      <c r="Y17" s="13">
-        <v>159.65</v>
       </c>
       <c r="Z17" s="13">
         <v>159.65</v>
       </c>
-      <c r="AA17" s="13"/>
+      <c r="AA17" s="13">
+        <v>159.65</v>
+      </c>
       <c r="AB17" s="13"/>
       <c r="AC17" s="13"/>
       <c r="AD17" s="13"/>
@@ -3792,36 +3841,37 @@
       <c r="BB17" s="13"/>
       <c r="BC17" s="13"/>
       <c r="BD17" s="13"/>
-      <c r="BE17" s="29"/>
-      <c r="BF17" s="13"/>
+      <c r="BE17" s="13"/>
+      <c r="BF17" s="29"/>
       <c r="BG17" s="13"/>
-      <c r="BH17" s="29"/>
-      <c r="BI17" s="13"/>
+      <c r="BH17" s="13"/>
+      <c r="BI17" s="29"/>
       <c r="BJ17" s="13"/>
       <c r="BK17" s="13"/>
       <c r="BL17" s="13"/>
-      <c r="BM17" s="13">
+      <c r="BM17" s="13"/>
+      <c r="BN17" s="13">
         <f t="shared" si="0"/>
         <v>957.9</v>
       </c>
-      <c r="BN17" s="13">
+      <c r="BO17" s="13">
         <f t="shared" si="2"/>
         <v>957.9</v>
       </c>
-      <c r="BO17" s="13">
-        <f t="shared" ref="BO17" si="8">(BN17-BM17)</f>
+      <c r="BP17" s="13">
+        <f t="shared" ref="BP17" si="8">(BO17-BN17)</f>
         <v>0</v>
       </c>
-      <c r="BP17" s="13">
-        <f>((BD17-H17)/H17)*100</f>
+      <c r="BQ17" s="13">
+        <f>((BE17-H17)/H17)*100</f>
         <v>-100</v>
       </c>
-      <c r="BS17" s="15">
+      <c r="BT17" s="15">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1168723</v>
       </c>
@@ -3850,66 +3900,68 @@
         <v>1434</v>
       </c>
       <c r="I18" s="13">
+        <v>1828</v>
+      </c>
+      <c r="J18" s="13">
         <v>1811</v>
       </c>
-      <c r="J18" s="13">
+      <c r="K18" s="13">
         <v>1825</v>
       </c>
-      <c r="K18" s="13">
+      <c r="L18" s="13">
         <v>1831</v>
       </c>
-      <c r="L18" s="13">
+      <c r="M18" s="13">
         <v>1799</v>
       </c>
-      <c r="M18" s="13">
+      <c r="N18" s="13">
         <v>1757</v>
       </c>
-      <c r="N18" s="13">
+      <c r="O18" s="13">
         <v>1698</v>
       </c>
-      <c r="O18" s="13">
+      <c r="P18" s="13">
         <v>1694</v>
       </c>
-      <c r="P18" s="13">
+      <c r="Q18" s="13">
         <v>1671</v>
-      </c>
-      <c r="Q18" s="13">
-        <v>1660</v>
       </c>
       <c r="R18" s="13">
         <v>1660</v>
       </c>
       <c r="S18" s="13">
+        <v>1660</v>
+      </c>
+      <c r="T18" s="13">
         <v>1646</v>
       </c>
-      <c r="T18" s="13">
+      <c r="U18" s="13">
         <v>1648</v>
       </c>
-      <c r="U18" s="13">
+      <c r="V18" s="13">
         <v>1614</v>
       </c>
-      <c r="V18" s="13">
+      <c r="W18" s="13">
         <v>1626</v>
       </c>
-      <c r="W18" s="13">
+      <c r="X18" s="13">
         <v>1587</v>
       </c>
-      <c r="X18" s="13">
+      <c r="Y18" s="13">
         <v>1548</v>
       </c>
-      <c r="Y18" s="13">
+      <c r="Z18" s="13">
         <v>1500</v>
       </c>
-      <c r="Z18" s="13">
+      <c r="AA18" s="13">
         <v>1491</v>
       </c>
-      <c r="AA18" s="13">
+      <c r="AB18" s="13">
         <v>1444</v>
       </c>
-      <c r="AB18" s="13">
+      <c r="AC18" s="13">
         <v>1431</v>
       </c>
-      <c r="AC18" s="13"/>
       <c r="AD18" s="13"/>
       <c r="AE18" s="13"/>
       <c r="AF18" s="13"/>
@@ -3935,64 +3987,65 @@
       <c r="AZ18" s="13"/>
       <c r="BA18" s="13"/>
       <c r="BB18" s="13"/>
-      <c r="BC18" s="13">
-        <v>1788</v>
-      </c>
+      <c r="BC18" s="13"/>
       <c r="BD18" s="13">
         <v>1788</v>
       </c>
-      <c r="BE18" s="29">
+      <c r="BE18" s="13">
+        <v>1788</v>
+      </c>
+      <c r="BF18" s="29">
         <v>1780</v>
       </c>
-      <c r="BF18" s="13">
+      <c r="BG18" s="13">
         <v>1814</v>
       </c>
-      <c r="BG18" s="13">
+      <c r="BH18" s="13">
         <v>1794</v>
       </c>
-      <c r="BH18" s="29">
+      <c r="BI18" s="29">
         <v>1780</v>
       </c>
-      <c r="BI18" s="13">
+      <c r="BJ18" s="13">
         <v>1772</v>
       </c>
-      <c r="BJ18" s="13">
+      <c r="BK18" s="13">
         <v>1798</v>
       </c>
-      <c r="BK18" s="13">
+      <c r="BL18" s="13">
         <v>1806</v>
       </c>
-      <c r="BL18" s="13">
+      <c r="BM18" s="13">
         <v>1801</v>
       </c>
-      <c r="BM18" s="13">
+      <c r="BN18" s="13">
         <f t="shared" si="0"/>
         <v>292.79999999999995</v>
       </c>
-      <c r="BN18" s="13">
+      <c r="BO18" s="13">
         <f t="shared" si="2"/>
         <v>645.29999999999995</v>
       </c>
-      <c r="BO18" s="13">
+      <c r="BP18" s="13">
         <f t="shared" si="6"/>
         <v>352.5</v>
       </c>
-      <c r="BP18" s="13">
-        <f>((BD18-H18)/H18)*100</f>
+      <c r="BQ18" s="13">
+        <f>((BE18-H18)/H18)*100</f>
         <v>24.686192468619247</v>
       </c>
-      <c r="BQ18">
+      <c r="BR18">
         <v>100</v>
       </c>
-      <c r="BR18">
+      <c r="BS18">
         <v>1786.5</v>
       </c>
-      <c r="BS18" s="15">
+      <c r="BT18" s="15">
         <f t="shared" si="7"/>
         <v>352.5</v>
       </c>
     </row>
-    <row r="19" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1146604</v>
       </c>
@@ -4035,22 +4088,22 @@
       <c r="U19" s="13"/>
       <c r="V19" s="13"/>
       <c r="W19" s="13"/>
-      <c r="X19" s="13">
+      <c r="X19" s="13"/>
+      <c r="Y19" s="13">
         <v>6461</v>
       </c>
-      <c r="Y19" s="13">
+      <c r="Z19" s="13">
         <v>6503</v>
       </c>
-      <c r="Z19" s="13">
+      <c r="AA19" s="13">
         <v>6535</v>
       </c>
-      <c r="AA19" s="13">
+      <c r="AB19" s="13">
         <v>6532</v>
       </c>
-      <c r="AB19" s="13">
+      <c r="AC19" s="13">
         <v>6515</v>
       </c>
-      <c r="AC19" s="13"/>
       <c r="AD19" s="13"/>
       <c r="AE19" s="13"/>
       <c r="AF19" s="13"/>
@@ -4078,33 +4131,34 @@
       <c r="BB19" s="13"/>
       <c r="BC19" s="13"/>
       <c r="BD19" s="13"/>
-      <c r="BE19" s="29"/>
-      <c r="BF19" s="13"/>
+      <c r="BE19" s="13"/>
+      <c r="BF19" s="29"/>
       <c r="BG19" s="13"/>
-      <c r="BH19" s="29"/>
-      <c r="BI19" s="13"/>
+      <c r="BH19" s="13"/>
+      <c r="BI19" s="29"/>
       <c r="BJ19" s="13"/>
       <c r="BK19" s="13"/>
       <c r="BL19" s="13"/>
-      <c r="BM19" s="13">
+      <c r="BM19" s="13"/>
+      <c r="BN19" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BN19" s="13">
+      <c r="BO19" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BO19" s="13"/>
       <c r="BP19" s="13"/>
-      <c r="BQ19">
+      <c r="BQ19" s="13"/>
+      <c r="BR19">
         <v>7</v>
       </c>
-      <c r="BR19">
+      <c r="BS19">
         <v>6461</v>
       </c>
-      <c r="BS19" s="15"/>
-    </row>
-    <row r="20" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT19" s="15"/>
+    </row>
+    <row r="20" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1144807</v>
       </c>
@@ -4148,7 +4202,9 @@
       <c r="P20" s="13">
         <v>3159</v>
       </c>
-      <c r="Q20" s="13"/>
+      <c r="Q20" s="13">
+        <v>3159</v>
+      </c>
       <c r="R20" s="13"/>
       <c r="S20" s="13"/>
       <c r="T20" s="13"/>
@@ -4188,28 +4244,29 @@
       <c r="BB20" s="13"/>
       <c r="BC20" s="13"/>
       <c r="BD20" s="13"/>
-      <c r="BE20" s="29"/>
-      <c r="BF20" s="13"/>
+      <c r="BE20" s="13"/>
+      <c r="BF20" s="29"/>
       <c r="BG20" s="13"/>
-      <c r="BH20" s="29"/>
-      <c r="BI20" s="13"/>
+      <c r="BH20" s="13"/>
+      <c r="BI20" s="29"/>
       <c r="BJ20" s="13"/>
       <c r="BK20" s="13"/>
       <c r="BL20" s="13"/>
-      <c r="BM20" s="13">
-        <f>(G20*H20)/100-BS20</f>
+      <c r="BM20" s="13"/>
+      <c r="BN20" s="13">
+        <f>(G20*H20)/100-BT20</f>
         <v>0</v>
       </c>
-      <c r="BN20" s="13">
+      <c r="BO20" s="13">
         <f>(G20*H20)/100</f>
         <v>0</v>
       </c>
-      <c r="BO20" s="13"/>
       <c r="BP20" s="13"/>
-      <c r="BS20" s="15"/>
-    </row>
-    <row r="21" spans="1:71" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:71" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BQ20" s="13"/>
+      <c r="BT20" s="15"/>
+    </row>
+    <row r="21" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4266,11 +4323,11 @@
       <c r="BB22" s="13"/>
       <c r="BC22" s="13"/>
       <c r="BD22" s="13"/>
-      <c r="BE22" s="29"/>
-      <c r="BF22" s="13"/>
+      <c r="BE22" s="13"/>
+      <c r="BF22" s="29"/>
       <c r="BG22" s="13"/>
-      <c r="BH22" s="29"/>
-      <c r="BI22" s="13"/>
+      <c r="BH22" s="13"/>
+      <c r="BI22" s="29"/>
       <c r="BJ22" s="13"/>
       <c r="BK22" s="13"/>
       <c r="BL22" s="13"/>
@@ -4278,9 +4335,10 @@
       <c r="BN22" s="13"/>
       <c r="BO22" s="13"/>
       <c r="BP22" s="13"/>
-      <c r="BS22" s="15"/>
-    </row>
-    <row r="23" spans="1:71" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BQ22" s="13"/>
+      <c r="BT22" s="15"/>
+    </row>
+    <row r="23" spans="1:72" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4291,67 +4349,67 @@
       <c r="H23" s="13"/>
       <c r="I23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19)/100</f>
-        <v>17594.5056</v>
+        <v>16104.2896</v>
       </c>
       <c r="J23" s="23">
         <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19)/100</f>
-        <v>17147.358</v>
+        <v>15918.465600000001</v>
       </c>
       <c r="K23" s="23">
         <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19)/100</f>
-        <v>17029.563599999998</v>
+        <v>15780.058000000001</v>
       </c>
       <c r="L23" s="23">
         <f>(L2*G2+G3*L3+L4*G4+G5*L5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+L13*G13+G14*L14+L15*G15+G16*L16+G17*L17+L18*G18+G19*L19)/100</f>
-        <v>16540.263999999999</v>
+        <v>15786.563599999999</v>
       </c>
       <c r="M23" s="23">
         <f>(M2*G2+G3*M3+M4*G4+G5*M5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+M13*G13+G14*M14+M15*G15+G16*M16+G17*M17+M18*G18+G19*M19)/100</f>
-        <v>16192.033000000001</v>
+        <v>15432.864</v>
       </c>
       <c r="N23" s="23">
         <f>(N2*G2+G3*N3+N4*G4+G5*N5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+N13*G13+G14*N14+N15*G15+G16*N16+G17*N17+N18*G18+G19*N19)/100</f>
-        <v>15786.002</v>
+        <v>15138.76</v>
       </c>
       <c r="O23" s="23">
         <f>(O2*G2+G3*O3+O4*G4+G5*O5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+O13*G13+G14*O14+O15*G15+G16*O16+G17*O17+O18*G18+G19*O19)/100</f>
-        <v>15902.0576</v>
+        <v>14857.142</v>
       </c>
       <c r="P23" s="23">
-        <f>(P3*G3+G4*P4+P5*G5+G6*P6+G7*P7+G8*P8+G9*P9+G10*P10+G11*P11+G12*P12+G14*P14+P15*G15+G16*P16+P17*G17+G18*P18+G19*P19)/100</f>
-        <v>14094.97</v>
+        <f>(P2*G2+G3*P3+P4*G4+G5*P5+G6*P6+G7*P7+G8*P8+G9*P9+G10*P10+G11*P11+G12*P12+P13*G13+G14*P14+P15*G15+G16*P16+G17*P17+P18*G18+G19*P19)/100</f>
+        <v>15009.357599999999</v>
       </c>
       <c r="Q23" s="23">
         <f>(Q3*G3+G4*Q4+Q5*G5+G6*Q6+G7*Q7+G8*Q8+G9*Q9+G10*Q10+G11*Q11+G12*Q12+G14*Q14+Q15*G15+G16*Q16+Q17*G17+G18*Q18+G19*Q19)/100</f>
-        <v>13839.4576</v>
+        <v>14094.97</v>
       </c>
       <c r="R23" s="23">
         <f>(R3*G3+G4*R4+R5*G5+G6*R6+G7*R7+G8*R8+G9*R9+G10*R10+G11*R11+G12*R12+G14*R14+R15*G15+G16*R16+R17*G17+G18*R18+G19*R19)/100</f>
-        <v>13855.757600000001</v>
+        <v>13839.4576</v>
       </c>
       <c r="S23" s="23">
         <f>(S3*G3+G4*S4+S5*G5+G6*S6+G7*S7+G8*S8+G9*S9+G10*S10+G11*S11+G12*S12+G14*S14+S15*G15+G16*S16+S17*G17+G18*S18+G19*S19)/100</f>
-        <v>13797.417600000001</v>
+        <v>13855.757600000001</v>
       </c>
       <c r="T23" s="23">
         <f>(T3*G3+G4*T4+T5*G5+G6*T6+G7*T7+G8*T8+G9*T9+G10*T10+G11*T11+G12*T12+G14*T14+T15*G15+G16*T16+T17*G17+G18*T18+G19*T19)/100</f>
-        <v>13184.28</v>
+        <v>13797.417600000001</v>
       </c>
       <c r="U23" s="23">
         <f>(U3*G3+G4*U4+U5*G5+G6*U6+G7*U7+G8*U8+G9*U9+G10*U10+G11*U11+G12*U12+G14*U14+U15*G15+G16*U16+U17*G17+G18*U18+G19*U19)/100</f>
-        <v>12980.185600000001</v>
+        <v>13184.28</v>
       </c>
       <c r="V23" s="23">
         <f>(V3*G3+G4*V4+V5*G5+G6*V6+G7*V7+G8*V8+G9*V9+G10*V10+G11*V11+G12*V12+G14*V14+V15*G15+G16*V16+V17*G17+G18*V18+G19*V19)/100</f>
+        <v>12980.185600000001</v>
+      </c>
+      <c r="W23" s="23">
+        <f>(W3*G3+G4*W4+W5*G5+G6*W6+G7*W7+G8*W8+G9*W9+G10*W10+G11*W11+G12*W12+G14*W14+W15*G15+G16*W16+W17*G17+G18*W18+G19*W19)/100</f>
         <v>11213.0556</v>
       </c>
-      <c r="W23" s="23">
-        <f>(W5*G5+G6*W6+W7*G7+G8*W8+G9*W9+G10*W10+G11*W11+G12*W12+G14*W14+G20*W20+G15*W15+W16*G16+G17*W17+W18*G18+G19*W19)/100</f>
+      <c r="X23" s="23">
+        <f>(X5*G5+G6*X6+X7*G7+G8*X8+G9*X9+G10*X10+G11*X11+G12*X12+G14*X14+G20*X20+G15*X15+X16*G16+G17*X17+X18*G18+G19*X19)/100</f>
         <v>10380.919599999999</v>
-      </c>
-      <c r="X23" s="23" t="e">
-        <f>(X5*G5+G7*X7+X8*G8+G9*X9+#REF!*#REF!+G10*X10+G11*X11+G12*X12+G14*X14+G19*X19+G20*X20+X6*G6+G15*X15+#REF!*#REF!+G16*X16+G17*X17+X18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*X3+#REF!*#REF!)/100</f>
-        <v>#REF!</v>
       </c>
       <c r="Y23" s="23" t="e">
         <f>(Y5*G5+G7*Y7+Y8*G8+G9*Y9+#REF!*#REF!+G10*Y10+G11*Y11+G12*Y12+G14*Y14+G19*Y19+G20*Y20+Y6*G6+G15*Y15+#REF!*#REF!+G16*Y16+G17*Y17+Y18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*Y3+#REF!*#REF!)/100</f>
@@ -4362,11 +4420,11 @@
         <v>#REF!</v>
       </c>
       <c r="AA23" s="23" t="e">
-        <f>(AA5*G5+G7*AA7+AA8*G8+G9*AA9+#REF!*#REF!+G10*AA10+G11*AA11+G12*AA12+G14*AA14+G19*AA19+G20*AA20+AA6*G6+G15*AA15+#REF!*#REF!+G16*AA16+G18*AA18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AA3+#REF!*#REF!+G4*AA4)/100</f>
+        <f>(AA5*G5+G7*AA7+AA8*G8+G9*AA9+#REF!*#REF!+G10*AA10+G11*AA11+G12*AA12+G14*AA14+G19*AA19+G20*AA20+AA6*G6+G15*AA15+#REF!*#REF!+G16*AA16+G17*AA17+AA18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AA3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AB23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AB3*G3+#REF!*#REF!+G4*AB4+G5*AB5+G7*AB7+G8*AB8+G9*AB9+#REF!*#REF!+G10*AB10+AB11*G11+G12*AB12+AB14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AB20+AB6*G6+#REF!*#REF!+G16*AB16+G18*AB18+G19*AB19)/100</f>
+        <f>(AB5*G5+G7*AB7+AB8*G8+G9*AB9+#REF!*#REF!+G10*AB10+G11*AB11+G12*AB12+G14*AB14+G19*AB19+G20*AB20+AB6*G6+G15*AB15+#REF!*#REF!+G16*AB16+G18*AB18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AB3+#REF!*#REF!+G4*AB4)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AC23" s="23" t="e">
@@ -4374,7 +4432,7 @@
         <v>#REF!</v>
       </c>
       <c r="AD23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AD3*G3+#REF!*#REF!+G4*AD4+G5*AD5+AD7*G7+AD8*G8+AD9*G9+#REF!*#REF!+G10*AD10+AD11*G11+G12*AD12+AD14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AD20+G6*AD6+#REF!*#REF!+G16*AD16+G18*AD18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AD3*G3+#REF!*#REF!+G4*AD4+G5*AD5+G7*AD7+G8*AD8+G9*AD9+#REF!*#REF!+G10*AD10+AD11*G11+G12*AD12+AD14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AD20+AD6*G6+#REF!*#REF!+G16*AD16+G18*AD18+G19*AD19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AE23" s="23" t="e">
@@ -4382,19 +4440,19 @@
         <v>#REF!</v>
       </c>
       <c r="AF23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AF3*G3+#REF!*#REF!+G4*AF4+G8*AF8+AF9*G9+#REF!*#REF!+AF10*G10+G11*AF11+G14*AF14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AF6+#REF!*#REF!+G16*AF16+G18*AF18+G7*AF7+G5*AF5+G12*AF12+G20*AF20)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AF3*G3+#REF!*#REF!+G4*AF4+G5*AF5+AF7*G7+AF8*G8+AF9*G9+#REF!*#REF!+G10*AF10+AF11*G11+G12*AF12+AF14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AF20+G6*AF6+#REF!*#REF!+G16*AF16+G18*AF18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AG23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AG3*G3+#REF!*#REF!+G4*AG4+G8*AG8+AG9*G9+#REF!*#REF!+AG10*G10+G11*AG11+G14*AG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AG6+#REF!*#REF!+G16*AG16+G18*AG18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AG3*G3+#REF!*#REF!+G4*AG4+G8*AG8+AG9*G9+#REF!*#REF!+AG10*G10+G11*AG11+G14*AG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AG6+#REF!*#REF!+G16*AG16+G18*AG18+G7*AG7+G5*AG5+G12*AG12+G20*AG20)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AH23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AH3*G3+#REF!*#REF!+G4*AH4+G8*AH8+G9*AH9+#REF!*#REF!+G10*AH10+AH11*G11+AH14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AH6*G6+#REF!*#REF!+G16*AH16+G18*AH18+G19*AH19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AH3*G3+#REF!*#REF!+G4*AH4+G8*AH8+AH9*G9+#REF!*#REF!+AH10*G10+G11*AH11+G14*AH14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AH6+#REF!*#REF!+G16*AH16+G18*AH18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AI23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AI3*G3+#REF!*#REF!+G4*AI4+G8*AI8+AI9*G9+#REF!*#REF!+AI10*G10+G11*AI11+G14*AI14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AI6+#REF!*#REF!+G16*AI16+G18*AI18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AI3*G3+#REF!*#REF!+G4*AI4+G8*AI8+G9*AI9+#REF!*#REF!+G10*AI10+AI11*G11+AI14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AI6*G6+#REF!*#REF!+G16*AI16+G18*AI18+G19*AI19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AJ23" s="23" t="e">
@@ -4402,7 +4460,7 @@
         <v>#REF!</v>
       </c>
       <c r="AK23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AK3*G3+#REF!*#REF!+G4*AK4+G8*AK8+AK9*G9+AK10*G10+AK11*G11+G14*AK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AK6+#REF!*#REF!+G16*AK16+G18*AK18+G19*AK19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AK3*G3+#REF!*#REF!+G4*AK4+G8*AK8+AK9*G9+#REF!*#REF!+AK10*G10+G11*AK11+G14*AK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AK6+#REF!*#REF!+G16*AK16+G18*AK18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AL23" s="23" t="e">
@@ -4422,19 +4480,19 @@
         <v>#REF!</v>
       </c>
       <c r="AP23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+AP9*G9+AP10*G10+AP11*G11+G14*AP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AP6+#REF!*#REF!+G16*AP16+G18*AP18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+AP9*G9+AP10*G10+AP11*G11+G14*AP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AP6+#REF!*#REF!+G16*AP16+G18*AP18+G19*AP19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AQ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AQ3*G3+#REF!*#REF!+G4*AQ4+G8*AQ8+AQ10*G10+AQ11*G11+G14*AQ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AQ6+#REF!*#REF!+G16*AQ16+G18*AQ18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AQ3*G3+#REF!*#REF!+G4*AQ4+G8*AQ8+AQ9*G9+AQ10*G10+AQ11*G11+G14*AQ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AQ6+#REF!*#REF!+G16*AQ16+G18*AQ18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AR23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AR3*G3+#REF!*#REF!+G4*AR4+G8*AR8+G10*AR10+AR11*G11+AR14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AR6*G6+#REF!*#REF!+G16*AR16+G18*AR18+G19*AR19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AR3*G3+#REF!*#REF!+G4*AR4+G8*AR8+AR10*G10+AR11*G11+G14*AR14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AR6+#REF!*#REF!+G16*AR16+G18*AR18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AS23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AS3*G3+#REF!*#REF!+G4*AS4+G10*AS10+AS11*G11+AS14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AS6*G6+#REF!*#REF!+G16*AS16+G18*AS18+G19*AS19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AS3*G3+#REF!*#REF!+G4*AS4+G8*AS8+G10*AS10+AS11*G11+AS14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AS6*G6+#REF!*#REF!+G16*AS16+G18*AS18+G19*AS19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AT23" s="23" t="e">
@@ -4446,7 +4504,7 @@
         <v>#REF!</v>
       </c>
       <c r="AV23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AV3*G3+#REF!*#REF!+G4*AV4+G10*AV10+AV11*G11+AV14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AV6*G6+G16*AV16+G18*AV18+G19*AV19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AV3*G3+#REF!*#REF!+G4*AV4+G10*AV10+AV11*G11+AV14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AV6*G6+#REF!*#REF!+G16*AV16+G18*AV18+G19*AV19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AW23" s="23" t="e">
@@ -4474,15 +4532,15 @@
         <v>#REF!</v>
       </c>
       <c r="BC23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BC3*G3+#REF!*#REF!+G4*BC4+G10*BC10+G11*BC11+G14*BC14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BC6+BC16*G16+G18*BC18+G19*BC19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BC3*G3+#REF!*#REF!+G4*BC4+G10*BC10+BC11*G11+BC14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BC6*G6+G16*BC16+G18*BC18+G19*BC19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BD23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BD3*G3+#REF!*#REF!+G4*BD4+G10*BD10+G14*BD14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BD6+BD16*G16+G18*BD18+G19*BD19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BD3*G3+#REF!*#REF!+G4*BD4+G10*BD10+G11*BD11+G14*BD14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BD6+BD16*G16+G18*BD18+G19*BD19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BE23" s="23" t="e">
-        <f>(#REF!*#REF!+BE3*G3+G4*BE4+G14*BE14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BE6+BE16*G16+G18*BE18+G19*BE19+G22*BE22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BE3*G3+#REF!*#REF!+G4*BE4+G10*BE10+G14*BE14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BE6+BE16*G16+G18*BE18+G19*BE19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BF23" s="23" t="e">
@@ -4493,16 +4551,16 @@
         <f>(#REF!*#REF!+BG3*G3+G4*BG4+G14*BG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BG6+BG16*G16+G18*BG18+G19*BG19+G22*BG22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BH23" s="30" t="e">
+      <c r="BH23" s="23" t="e">
         <f>(#REF!*#REF!+BH3*G3+G4*BH4+G14*BH14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BH6+BH16*G16+G18*BH18+G19*BH19+G22*BH22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BI23" s="23" t="e">
+      <c r="BI23" s="30" t="e">
         <f>(#REF!*#REF!+BI3*G3+G4*BI4+G14*BI14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BI6+BI16*G16+G18*BI18+G19*BI19+G22*BI22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BJ23" s="23" t="e">
-        <f>(#REF!*#REF!+BJ3*G3+G14*BJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BJ6+BJ16*G16+G18*BJ18+G19*BJ19+G22*BJ22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+BJ3*G3+G4*BJ4+G14*BJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BJ6+BJ16*G16+G18*BJ18+G19*BJ19+G22*BJ22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BK23" s="23" t="e">
@@ -4513,16 +4571,19 @@
         <f>(#REF!*#REF!+BL3*G3+G14*BL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BL6+BL16*G16+G18*BL18+G19*BL19+G22*BL22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BM23" s="13"/>
+      <c r="BM23" s="23" t="e">
+        <f>(#REF!*#REF!+BM3*G3+G14*BM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BM6+BM16*G16+G18*BM18+G19*BM19+G22*BM22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <v>#REF!</v>
+      </c>
       <c r="BN23" s="13"/>
       <c r="BO23" s="13"/>
       <c r="BP23" s="13"/>
-      <c r="BS23" s="15">
-        <f>434.9+62.57</f>
-        <v>497.46999999999997</v>
-      </c>
-    </row>
-    <row r="24" spans="1:71" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BQ23" s="13"/>
+      <c r="BT23" s="15">
+        <v>1149.48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:72" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4587,29 +4648,30 @@
       <c r="BJ24" s="14"/>
       <c r="BK24" s="14"/>
       <c r="BL24" s="14"/>
-      <c r="BM24" s="23">
-        <f>SUM(BM2:BM20)</f>
-        <v>14085.376400000001</v>
-      </c>
+      <c r="BM24" s="14"/>
       <c r="BN24" s="23">
         <f>SUM(BN2:BN20)</f>
-        <v>14387.030600000002</v>
-      </c>
-      <c r="BO24" s="24">
-        <f>BN24-BM24</f>
+        <v>13268.386400000001</v>
+      </c>
+      <c r="BO24" s="23">
+        <f>SUM(BO2:BO20)</f>
+        <v>13570.040600000002</v>
+      </c>
+      <c r="BP24" s="24">
+        <f>BO24-BN24</f>
         <v>301.65420000000086</v>
       </c>
-      <c r="BP24" s="13">
-        <f>((BN24-BM24)/BM24)*100</f>
-        <v>2.1416126302453717</v>
-      </c>
-      <c r="BS24" s="15">
-        <f>SUM(BS5:BS23)</f>
-        <v>799.12419999999997</v>
-      </c>
-    </row>
-    <row r="25" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="BM25" s="15">
+      <c r="BQ24" s="13">
+        <f>((BO24-BN24)/BN24)*100</f>
+        <v>2.2734806698122751</v>
+      </c>
+      <c r="BT24" s="15">
+        <f>SUM(BT5:BT23)</f>
+        <v>1451.1342</v>
+      </c>
+    </row>
+    <row r="25" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="BN25" s="15">
         <v>12034.32</v>
       </c>
     </row>
@@ -4736,7 +4798,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>11840</v>
+        <v>12130</v>
       </c>
       <c r="J2" s="25"/>
       <c r="L2" s="21">
@@ -4774,7 +4836,7 @@
       <c r="G3" s="17"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1500</v>
+        <v>1556</v>
       </c>
       <c r="J3" s="26"/>
       <c r="L3" s="21">
@@ -4812,7 +4874,7 @@
       <c r="G4" s="17"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>7120</v>
+        <v>7252</v>
       </c>
       <c r="J4" s="26"/>
       <c r="L4" s="21">
@@ -4849,7 +4911,7 @@
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>575.70000000000005</v>
+        <v>570</v>
       </c>
       <c r="J5" s="26"/>
       <c r="L5" s="21">
@@ -4886,7 +4948,7 @@
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4424</v>
+        <v>4500</v>
       </c>
       <c r="J6" s="26"/>
       <c r="L6" s="21">
@@ -4924,7 +4986,7 @@
       <c r="G7" s="18"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3932</v>
+        <v>3954</v>
       </c>
       <c r="J7" s="26"/>
       <c r="L7" s="21">
@@ -4962,7 +5024,7 @@
       <c r="G8" s="18"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40750</v>
+        <v>43490</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -4999,7 +5061,7 @@
       <c r="G9" s="17"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9891</v>
+        <v>10240</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -5036,7 +5098,7 @@
       <c r="G10" s="18"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4821</v>
+        <v>4849</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -5073,7 +5135,7 @@
       <c r="G11" s="18"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1090</v>
+        <v>1109</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -5110,7 +5172,7 @@
       <c r="G12" s="18"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>30500</v>
+        <v>30100</v>
       </c>
       <c r="J12" s="26"/>
       <c r="L12" s="21">
@@ -5137,7 +5199,7 @@
       </c>
       <c r="D13" s="19">
         <f>'התיק העדכני'!G13</f>
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="E13" s="16">
         <v>890</v>
@@ -5148,7 +5210,7 @@
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1490</v>
+        <v>0</v>
       </c>
       <c r="J13" s="26"/>
       <c r="L13" s="21">
@@ -5186,7 +5248,7 @@
       <c r="G14" s="17"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7676</v>
+        <v>7672</v>
       </c>
       <c r="J14" s="26"/>
       <c r="L14" s="21">
@@ -5224,7 +5286,7 @@
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14583.37</v>
+        <v>14679.12</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
@@ -5262,7 +5324,7 @@
       <c r="G16" s="17"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>226.96</v>
+        <v>227.54</v>
       </c>
       <c r="J16" s="26"/>
       <c r="L16" s="21">
@@ -5300,7 +5362,7 @@
       <c r="G17" s="17"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>189.51</v>
+        <v>194.88</v>
       </c>
       <c r="J17" s="26"/>
       <c r="L17" s="21">
@@ -5338,7 +5400,7 @@
       <c r="G18" s="18"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1811</v>
+        <v>1828</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -5760,7 +5822,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>11840</v>
+        <v>12130</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+GEMINI!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
@@ -5797,7 +5859,7 @@
       <c r="G3" s="7"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1500</v>
+        <v>1556</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
@@ -5834,7 +5896,7 @@
       <c r="G4" s="7"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>7120</v>
+        <v>7252</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+GEMINI!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
@@ -5871,7 +5933,7 @@
       <c r="G5" s="7"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>575.70000000000005</v>
+        <v>570</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
@@ -5908,7 +5970,7 @@
       <c r="G6" s="7"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4424</v>
+        <v>4500</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
@@ -5945,7 +6007,7 @@
       <c r="G7" s="8"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3932</v>
+        <v>3954</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+GEMINI!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
@@ -5982,7 +6044,7 @@
       <c r="G8" s="8"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40750</v>
+        <v>43490</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+GEMINI!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -6019,7 +6081,7 @@
       <c r="G9" s="8"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9891</v>
+        <v>10240</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+GEMINI!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -6056,7 +6118,7 @@
       <c r="G10" s="8"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4821</v>
+        <v>4849</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+GEMINI!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -6093,7 +6155,7 @@
       <c r="G11" s="8"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1090</v>
+        <v>1109</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+GEMINI!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -6130,7 +6192,7 @@
       <c r="G12" s="8"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>30500</v>
+        <v>30100</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+GEMINI!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
@@ -6156,7 +6218,7 @@
       </c>
       <c r="D13" s="19">
         <f>'התיק העדכני'!G13</f>
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="E13" s="16">
         <v>890</v>
@@ -6167,7 +6229,7 @@
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1490</v>
+        <v>0</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+GEMINI!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
@@ -6204,7 +6266,7 @@
       <c r="G14" s="7"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7676</v>
+        <v>7672</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
@@ -6241,7 +6303,7 @@
       <c r="G15" s="7"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14583.37</v>
+        <v>14679.12</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+GEMINI!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
@@ -6278,7 +6340,7 @@
       <c r="G16" s="7"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>226.96</v>
+        <v>227.54</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
@@ -6315,7 +6377,7 @@
       <c r="G17" s="7"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>189.51</v>
+        <v>194.88</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+GEMINI!E17+PERPLIXITY!E17+DEEPSEEK!E17)/4</f>
@@ -6352,7 +6414,7 @@
       <c r="G18" s="8"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1811</v>
+        <v>1828</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+GEMINI!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -6576,7 +6638,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>11840</v>
+        <v>12130</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+GEMINI!E2+DEEPSEEK!E2)/4</f>
@@ -6613,7 +6675,7 @@
       <c r="G3" s="10"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1500</v>
+        <v>1556</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
@@ -6650,7 +6712,7 @@
       <c r="G4" s="10"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>7120</v>
+        <v>7252</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+GEMINI!E4+DEEPSEEK!E4)/4</f>
@@ -6687,7 +6749,7 @@
       <c r="G5" s="10"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>575.70000000000005</v>
+        <v>570</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
@@ -6724,7 +6786,7 @@
       <c r="G6" s="10"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4424</v>
+        <v>4500</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
@@ -6761,7 +6823,7 @@
       <c r="G7" s="10"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3932</v>
+        <v>3954</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+GEMINI!E7+DEEPSEEK!E7)/4</f>
@@ -6797,7 +6859,7 @@
       </c>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40750</v>
+        <v>43490</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+GEMINI!E8+DEEPSEEK!E8)/4</f>
@@ -6833,7 +6895,7 @@
       </c>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9891</v>
+        <v>10240</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+GEMINI!E9+DEEPSEEK!E9)/4</f>
@@ -6869,7 +6931,7 @@
       </c>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4821</v>
+        <v>4849</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+GEMINI!E10+DEEPSEEK!E10)/4</f>
@@ -6905,7 +6967,7 @@
       </c>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1090</v>
+        <v>1109</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+GEMINI!E11+DEEPSEEK!E11)/4</f>
@@ -6942,7 +7004,7 @@
       <c r="G12" s="10"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>30500</v>
+        <v>30100</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+GEMINI!E12+DEEPSEEK!E12)/4</f>
@@ -6968,7 +7030,7 @@
       </c>
       <c r="D13" s="19">
         <f>'התיק העדכני'!G13</f>
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="E13" s="16">
         <v>880</v>
@@ -6979,7 +7041,7 @@
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1490</v>
+        <v>0</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+CHATGPT!E13+GEMINI!E13+DEEPSEEK!E13)/4</f>
@@ -7016,7 +7078,7 @@
       <c r="G14" s="10"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7676</v>
+        <v>7672</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
@@ -7053,7 +7115,7 @@
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14583.37</v>
+        <v>14679.12</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
@@ -7090,7 +7152,7 @@
       <c r="G16" s="10"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>226.96</v>
+        <v>227.54</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+GEMINI!E16+DEEPSEEK!E16)/4</f>
@@ -7127,7 +7189,7 @@
       <c r="G17" s="10"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>189.51</v>
+        <v>194.88</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+GEMINI!E17+DEEPSEEK!E17)/4</f>
@@ -7163,7 +7225,7 @@
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1811</v>
+        <v>1828</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
@@ -7386,7 +7448,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>11840</v>
+        <v>12130</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+PERPLIXITY!E2+GEMINI!E2)/4</f>
@@ -7423,7 +7485,7 @@
       <c r="G3" s="31"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1500</v>
+        <v>1556</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
@@ -7459,7 +7521,7 @@
       </c>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>7120</v>
+        <v>7252</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+GEMINI!E4)/4</f>
@@ -7496,7 +7558,7 @@
       <c r="G5" s="31"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>575.70000000000005</v>
+        <v>570</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
@@ -7533,7 +7595,7 @@
       <c r="G6" s="31"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4424</v>
+        <v>4500</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
@@ -7569,7 +7631,7 @@
       </c>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3932</v>
+        <v>3954</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+GEMINI!E7)/4</f>
@@ -7606,7 +7668,7 @@
       <c r="G8" s="31"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40750</v>
+        <v>43490</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+GEMINI!E8)/4</f>
@@ -7643,7 +7705,7 @@
       <c r="G9" s="31"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>9891</v>
+        <v>10240</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+GEMINI!E9)/4</f>
@@ -7680,7 +7742,7 @@
       <c r="G10" s="31"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4821</v>
+        <v>4849</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+GEMINI!E10)/4</f>
@@ -7717,7 +7779,7 @@
       <c r="G11" s="31"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1090</v>
+        <v>1109</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+GEMINI!E11)/4</f>
@@ -7754,7 +7816,7 @@
       <c r="G12" s="31"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>30500</v>
+        <v>30100</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+GEMINI!E12)/4</f>
@@ -7780,7 +7842,7 @@
       </c>
       <c r="D13" s="19">
         <f>'התיק העדכני'!G13</f>
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="E13" s="16">
         <v>900</v>
@@ -7791,7 +7853,7 @@
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1490</v>
+        <v>0</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
@@ -7822,7 +7884,7 @@
       <c r="G14" s="31"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7676</v>
+        <v>7672</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
@@ -7894,7 +7956,7 @@
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14583.37</v>
+        <v>14679.12</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
@@ -7931,7 +7993,7 @@
       <c r="G17" s="31"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>226.96</v>
+        <v>227.54</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+GEMINI!E17)/4</f>
@@ -7968,7 +8030,7 @@
       <c r="G18" s="31"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>189.51</v>
+        <v>194.88</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+GEMINI!E18)/4</f>
@@ -7998,7 +8060,7 @@
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1811</v>
+        <v>1828</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+GEMINI!E19)/4</f>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\BURSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F48523D-468C-42AF-BD2E-4B36F92ADF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7059A00D-7C74-481A-8733-26E1BFF3D335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="105">
   <si>
     <t>MTF מחקה אינדקס תעשיה ישראל</t>
   </si>
@@ -256,9 +256,6 @@
     <t>מחיר 25/12/2025</t>
   </si>
   <si>
-    <t>קסם S&amp;P 500 ETF מנוטרלת מט"ח</t>
-  </si>
-  <si>
     <t>MTF סל אינדקס אנרגיה מתחדשת</t>
   </si>
   <si>
@@ -341,6 +338,12 @@
   </si>
   <si>
     <t>מחיר 28/01/2026</t>
+  </si>
+  <si>
+    <t>סטורג' דרופ</t>
+  </si>
+  <si>
+    <t>מחיר 30/01/2026</t>
   </si>
 </sst>
 </file>
@@ -1111,22 +1114,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86B4639-EF9D-4B16-B2C9-0D5E9C5EEC8B}">
-  <dimension ref="A1:BT25"/>
+  <dimension ref="A1:BV25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="17.5703125" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="55" width="14.85546875" customWidth="1"/>
-    <col min="56" max="65" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="13" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="11" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="11.5703125" customWidth="1"/>
+    <col min="8" max="57" width="14.85546875" customWidth="1"/>
+    <col min="58" max="67" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="13" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="11" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1155,196 +1158,199 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="K1" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="Q1" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="R1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="S1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="W1" s="6" t="s">
-        <v>87</v>
-      </c>
       <c r="X1" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI1" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AK1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AL1" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AN1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO1" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AP1" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AQ1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AR1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="AT1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU1" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AV1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AW1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AX1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AZ1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="BA1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="BB1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="BC1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="BD1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="BE1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="BF1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="BG1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="BH1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="BI1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="BJ1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="BK1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="BL1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="BM1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="BN1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="BO1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="BP1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="BQ1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="BR1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="BS1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="BT1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="BU1" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="BV1" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="Z1" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA1" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB1" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC1" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD1" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE1" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF1" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="AG1" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="AH1" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="AI1" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ1" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="AK1" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="AL1" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="AM1" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="AN1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="AO1" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="AP1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="AQ1" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AR1" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AS1" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="AT1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="AU1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="AV1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AW1" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AY1" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="AZ1" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="BA1" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="BB1" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="BC1" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="BD1" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="BE1" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="BF1" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="BG1" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="BH1" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="BI1" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="BJ1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="BK1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="BL1" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="BM1" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="BN1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="BO1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="BP1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="BQ1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="BR1" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="BS1" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="BT1" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>282012</v>
       </c>
@@ -1358,10 +1364,10 @@
       </c>
       <c r="D2" s="6" t="str">
         <f>IF(I2&lt;GEMINI!L2,"למכור בהפסד",IF(I2&gt;GEMINI!M2,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור בהפסד</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F2" s="4">
         <v>46042</v>
@@ -1373,31 +1379,35 @@
         <v>11000</v>
       </c>
       <c r="I2" s="13">
+        <v>9981</v>
+      </c>
+      <c r="J2" s="13">
+        <v>9981</v>
+      </c>
+      <c r="K2" s="13">
         <v>12130</v>
       </c>
-      <c r="J2" s="13">
+      <c r="L2" s="13">
         <v>11840</v>
       </c>
-      <c r="K2" s="13">
+      <c r="M2" s="13">
         <v>11400</v>
       </c>
-      <c r="L2" s="13">
+      <c r="N2" s="13">
         <v>11360</v>
       </c>
-      <c r="M2" s="13">
+      <c r="O2" s="13">
         <v>11000</v>
       </c>
-      <c r="N2" s="13">
+      <c r="P2" s="13">
         <v>10700</v>
       </c>
-      <c r="O2" s="13">
+      <c r="Q2" s="13">
         <v>10400</v>
       </c>
-      <c r="P2" s="13">
+      <c r="R2" s="13">
         <v>11230</v>
       </c>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
       <c r="S2" s="6"/>
       <c r="T2" s="6"/>
       <c r="U2" s="6"/>
@@ -1437,29 +1447,31 @@
       <c r="BC2" s="6"/>
       <c r="BD2" s="6"/>
       <c r="BE2" s="6"/>
-      <c r="BF2" s="32"/>
+      <c r="BF2" s="6"/>
       <c r="BG2" s="6"/>
-      <c r="BH2" s="6"/>
-      <c r="BI2" s="32"/>
+      <c r="BH2" s="32"/>
+      <c r="BI2" s="6"/>
       <c r="BJ2" s="6"/>
-      <c r="BK2" s="6"/>
+      <c r="BK2" s="32"/>
       <c r="BL2" s="6"/>
       <c r="BM2" s="6"/>
-      <c r="BN2" s="13">
-        <f>(G2*H2)/100-BT2</f>
+      <c r="BN2" s="6"/>
+      <c r="BO2" s="6"/>
+      <c r="BP2" s="13">
+        <f>(G2*H2)/100-BV2</f>
         <v>770</v>
       </c>
-      <c r="BO2" s="13">
+      <c r="BQ2" s="13">
         <f>(G2*H2)/100</f>
         <v>770</v>
       </c>
-      <c r="BP2" s="6"/>
-      <c r="BQ2" s="6"/>
-      <c r="BR2" s="25"/>
-      <c r="BS2" s="25"/>
+      <c r="BR2" s="6"/>
+      <c r="BS2" s="6"/>
       <c r="BT2" s="25"/>
-    </row>
-    <row r="3" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BU2" s="25"/>
+      <c r="BV2" s="25"/>
+    </row>
+    <row r="3" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1227552</v>
       </c>
@@ -1473,64 +1485,68 @@
       </c>
       <c r="D3" s="6" t="str">
         <f>IF(I3&lt;GEMINI!L3,"למכור בהפסד",IF(I3&gt;GEMINI!M3,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F3" s="4">
         <v>46029</v>
       </c>
       <c r="G3" s="27">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H3" s="13">
         <v>1153.6300000000001</v>
       </c>
       <c r="I3" s="13">
-        <v>1556</v>
+        <v>1311</v>
       </c>
       <c r="J3" s="13">
+        <v>1311</v>
+      </c>
+      <c r="K3" s="13">
+        <v>1340</v>
+      </c>
+      <c r="L3" s="13">
         <v>1500</v>
       </c>
-      <c r="K3" s="13">
+      <c r="M3" s="13">
         <v>1424</v>
       </c>
-      <c r="L3" s="13">
+      <c r="N3" s="13">
         <v>1348</v>
       </c>
-      <c r="M3" s="13">
+      <c r="O3" s="13">
         <v>1373</v>
       </c>
-      <c r="N3" s="13">
+      <c r="P3" s="13">
         <v>1331</v>
       </c>
-      <c r="O3" s="13">
+      <c r="Q3" s="13">
         <v>1386</v>
       </c>
-      <c r="P3" s="13">
+      <c r="R3" s="13">
         <v>1342</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="S3" s="13">
         <v>1250</v>
       </c>
-      <c r="R3" s="13">
+      <c r="T3" s="13">
         <v>1389</v>
       </c>
-      <c r="S3" s="13">
+      <c r="U3" s="13">
         <v>1389</v>
       </c>
-      <c r="T3" s="13">
+      <c r="V3" s="13">
         <v>1367</v>
       </c>
-      <c r="U3" s="13">
+      <c r="W3" s="13">
         <v>1026</v>
       </c>
-      <c r="V3" s="13">
+      <c r="X3" s="13">
         <v>949.1</v>
       </c>
-      <c r="W3" s="13"/>
-      <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
       <c r="Z3" s="13"/>
       <c r="AA3" s="13"/>
@@ -1545,9 +1561,9 @@
       <c r="AJ3" s="13"/>
       <c r="AK3" s="13"/>
       <c r="AL3" s="13"/>
-      <c r="AM3" s="14"/>
+      <c r="AM3" s="13"/>
       <c r="AN3" s="13"/>
-      <c r="AO3" s="13"/>
+      <c r="AO3" s="14"/>
       <c r="AP3" s="13"/>
       <c r="AQ3" s="13"/>
       <c r="AR3" s="13"/>
@@ -1564,36 +1580,44 @@
       <c r="BC3" s="13"/>
       <c r="BD3" s="13"/>
       <c r="BE3" s="13"/>
-      <c r="BF3" s="29"/>
+      <c r="BF3" s="13"/>
       <c r="BG3" s="13"/>
-      <c r="BH3" s="13"/>
-      <c r="BI3" s="29"/>
+      <c r="BH3" s="29"/>
+      <c r="BI3" s="13"/>
       <c r="BJ3" s="13"/>
-      <c r="BK3" s="13"/>
+      <c r="BK3" s="29"/>
       <c r="BL3" s="13"/>
       <c r="BM3" s="13"/>
-      <c r="BN3" s="13">
-        <f>(G3*H3)/100-BT3</f>
-        <v>784.46840000000009</v>
-      </c>
-      <c r="BO3" s="13">
+      <c r="BN3" s="13"/>
+      <c r="BO3" s="13"/>
+      <c r="BP3" s="13">
+        <f>(G3*H3)/100-BV3</f>
+        <v>-126.73159999999989</v>
+      </c>
+      <c r="BQ3" s="13">
         <f>(G3*H3)/100</f>
-        <v>784.46840000000009</v>
-      </c>
-      <c r="BP3" s="13">
-        <f>(BO3-BN3)</f>
         <v>0</v>
       </c>
-      <c r="BQ3" s="13">
-        <f>((BE3-H3)/H3)*100</f>
+      <c r="BR3" s="13">
+        <f>(BQ3-BP3)</f>
+        <v>126.73159999999989</v>
+      </c>
+      <c r="BS3" s="13">
+        <f>((BG3-H3)/H3)*100</f>
         <v>-100</v>
       </c>
-      <c r="BT3" s="15">
-        <f>(BR3*BS3-BR3*H3)/100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT3">
+        <v>68</v>
+      </c>
+      <c r="BU3">
+        <v>1340</v>
+      </c>
+      <c r="BV3" s="15">
+        <f>(BT3*BU3-BT3*H3)/100</f>
+        <v>126.73159999999989</v>
+      </c>
+    </row>
+    <row r="4" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>587014</v>
       </c>
@@ -1607,7 +1631,7 @@
       </c>
       <c r="D4" s="6" t="str">
         <f>IF(I4&lt;GEMINI!L4,"למכור בהפסד",IF(I4&gt;GEMINI!M4,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>33</v>
@@ -1622,49 +1646,53 @@
         <v>5925</v>
       </c>
       <c r="I4" s="13">
+        <v>6140</v>
+      </c>
+      <c r="J4" s="13">
+        <v>6140</v>
+      </c>
+      <c r="K4" s="13">
         <v>7252</v>
       </c>
-      <c r="J4" s="13">
+      <c r="L4" s="13">
         <v>7120</v>
       </c>
-      <c r="K4" s="13">
+      <c r="M4" s="13">
         <v>7048</v>
       </c>
-      <c r="L4" s="13">
+      <c r="N4" s="13">
         <v>6979</v>
       </c>
-      <c r="M4" s="13">
+      <c r="O4" s="13">
         <v>6680</v>
       </c>
-      <c r="N4" s="13">
+      <c r="P4" s="13">
         <v>6111</v>
       </c>
-      <c r="O4" s="13">
+      <c r="Q4" s="13">
         <v>6050</v>
       </c>
-      <c r="P4" s="13">
+      <c r="R4" s="13">
         <v>6169</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="S4" s="13">
         <v>6300</v>
       </c>
-      <c r="R4" s="13">
+      <c r="T4" s="13">
         <v>6335</v>
       </c>
-      <c r="S4" s="13">
+      <c r="U4" s="13">
         <v>6335</v>
       </c>
-      <c r="T4" s="13">
+      <c r="V4" s="13">
         <v>6444</v>
       </c>
-      <c r="U4" s="13">
+      <c r="W4" s="13">
         <v>5749</v>
       </c>
-      <c r="V4" s="13">
+      <c r="X4" s="13">
         <v>5749</v>
       </c>
-      <c r="W4" s="13"/>
-      <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
@@ -1698,36 +1726,38 @@
       <c r="BC4" s="13"/>
       <c r="BD4" s="13"/>
       <c r="BE4" s="13"/>
-      <c r="BF4" s="29"/>
+      <c r="BF4" s="13"/>
       <c r="BG4" s="13"/>
-      <c r="BH4" s="13"/>
-      <c r="BI4" s="29"/>
+      <c r="BH4" s="29"/>
+      <c r="BI4" s="13"/>
       <c r="BJ4" s="13"/>
-      <c r="BK4" s="13"/>
+      <c r="BK4" s="29"/>
       <c r="BL4" s="13"/>
       <c r="BM4" s="13"/>
-      <c r="BN4" s="13">
-        <f>(G4*H4)/100-BT4</f>
+      <c r="BN4" s="13"/>
+      <c r="BO4" s="13"/>
+      <c r="BP4" s="13">
+        <f>(G4*H4)/100-BV4</f>
         <v>1185</v>
       </c>
-      <c r="BO4" s="13">
+      <c r="BQ4" s="13">
         <f>(G4*H4)/100</f>
         <v>1185</v>
       </c>
-      <c r="BP4" s="13">
-        <f>(BO4-BN4)</f>
+      <c r="BR4" s="13">
+        <f>(BQ4-BP4)</f>
         <v>0</v>
       </c>
-      <c r="BQ4" s="13">
-        <f>((BE4-H4)/H4)*100</f>
+      <c r="BS4" s="13">
+        <f>((BG4-H4)/H4)*100</f>
         <v>-100</v>
       </c>
-      <c r="BT4" s="15">
-        <f>(BR4*BS4-BR4*H4)/100</f>
+      <c r="BV4" s="15">
+        <f>(BT4*BU4-BT4*H4)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1099787</v>
       </c>
@@ -1756,79 +1786,83 @@
         <v>617.53</v>
       </c>
       <c r="I5" s="13">
+        <v>559</v>
+      </c>
+      <c r="J5" s="13">
+        <v>559</v>
+      </c>
+      <c r="K5" s="13">
         <v>570</v>
       </c>
-      <c r="J5" s="13">
+      <c r="L5" s="13">
         <v>575.70000000000005</v>
       </c>
-      <c r="K5" s="13">
+      <c r="M5" s="13">
         <v>612.6</v>
       </c>
-      <c r="L5" s="13">
+      <c r="N5" s="13">
         <v>638.29999999999995</v>
       </c>
-      <c r="M5" s="13">
+      <c r="O5" s="13">
         <v>630.29999999999995</v>
       </c>
-      <c r="N5" s="13">
+      <c r="P5" s="13">
         <v>626</v>
       </c>
-      <c r="O5" s="13">
+      <c r="Q5" s="13">
         <v>595.4</v>
       </c>
-      <c r="P5" s="13">
+      <c r="R5" s="13">
         <v>667.1</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="S5" s="13">
         <v>651</v>
       </c>
-      <c r="R5" s="13">
+      <c r="T5" s="13">
         <v>641.1</v>
       </c>
-      <c r="S5" s="13">
+      <c r="U5" s="13">
         <v>641.1</v>
       </c>
-      <c r="T5" s="13">
+      <c r="V5" s="13">
         <v>607.1</v>
       </c>
-      <c r="U5" s="13">
+      <c r="W5" s="13">
         <v>583</v>
       </c>
-      <c r="V5" s="13">
+      <c r="X5" s="13">
         <v>581.6</v>
       </c>
-      <c r="W5" s="13">
+      <c r="Y5" s="13">
         <v>578.70000000000005</v>
       </c>
-      <c r="X5" s="13">
+      <c r="Z5" s="13">
         <v>590</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="AA5" s="13">
         <v>554.70000000000005</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="AB5" s="13">
         <v>511.8</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AC5" s="13">
         <v>487</v>
       </c>
-      <c r="AB5" s="13">
+      <c r="AD5" s="13">
         <v>478.8</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AE5" s="13">
         <v>485.5</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AF5" s="13">
         <v>453.4</v>
       </c>
-      <c r="AE5" s="13">
+      <c r="AG5" s="13">
         <v>426.1</v>
       </c>
-      <c r="AF5" s="13">
+      <c r="AH5" s="13">
         <v>423.2</v>
       </c>
-      <c r="AG5" s="13"/>
-      <c r="AH5" s="13"/>
       <c r="AI5" s="13"/>
       <c r="AJ5" s="13"/>
       <c r="AK5" s="13"/>
@@ -1852,27 +1886,29 @@
       <c r="BC5" s="13"/>
       <c r="BD5" s="13"/>
       <c r="BE5" s="13"/>
-      <c r="BF5" s="29"/>
+      <c r="BF5" s="13"/>
       <c r="BG5" s="13"/>
-      <c r="BH5" s="13"/>
-      <c r="BI5" s="29"/>
+      <c r="BH5" s="29"/>
+      <c r="BI5" s="13"/>
       <c r="BJ5" s="13"/>
-      <c r="BK5" s="13"/>
+      <c r="BK5" s="29"/>
       <c r="BL5" s="13"/>
       <c r="BM5" s="13"/>
-      <c r="BN5" s="13">
-        <f t="shared" ref="BN5:BN19" si="0">(G5*H5)/100-BT5</f>
+      <c r="BN5" s="13"/>
+      <c r="BO5" s="13"/>
+      <c r="BP5" s="13">
+        <f t="shared" ref="BP5:BP19" si="0">(G5*H5)/100-BV5</f>
         <v>975.6973999999999</v>
       </c>
-      <c r="BO5" s="13">
+      <c r="BQ5" s="13">
         <f>(G5*H5)/100</f>
         <v>975.6973999999999</v>
       </c>
-      <c r="BP5" s="13"/>
-      <c r="BQ5" s="13"/>
-      <c r="BT5" s="15"/>
-    </row>
-    <row r="6" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BR5" s="13"/>
+      <c r="BS5" s="13"/>
+      <c r="BV5" s="15"/>
+    </row>
+    <row r="6" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1166768</v>
       </c>
@@ -1889,64 +1925,68 @@
         <v>למכור ברווח</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F6" s="4">
         <v>46028</v>
       </c>
       <c r="G6" s="27">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H6" s="13">
-        <v>3700</v>
+        <v>4040</v>
       </c>
       <c r="I6" s="13">
+        <v>4355</v>
+      </c>
+      <c r="J6" s="13">
+        <v>4355</v>
+      </c>
+      <c r="K6" s="13">
         <v>4500</v>
       </c>
-      <c r="J6" s="13">
+      <c r="L6" s="13">
         <v>4424</v>
       </c>
-      <c r="K6" s="13">
+      <c r="M6" s="13">
         <v>4412</v>
       </c>
-      <c r="L6" s="13">
+      <c r="N6" s="13">
         <v>4450</v>
       </c>
-      <c r="M6" s="13">
+      <c r="O6" s="13">
         <v>4238</v>
       </c>
-      <c r="N6" s="13">
+      <c r="P6" s="13">
         <v>3970</v>
       </c>
-      <c r="O6" s="13">
+      <c r="Q6" s="13">
         <v>3870</v>
       </c>
-      <c r="P6" s="13">
+      <c r="R6" s="13">
         <v>3805</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="S6" s="13">
         <v>3667</v>
       </c>
-      <c r="R6" s="13">
+      <c r="T6" s="13">
         <v>3582</v>
       </c>
-      <c r="S6" s="13">
+      <c r="U6" s="13">
         <v>3582</v>
       </c>
-      <c r="T6" s="13">
+      <c r="V6" s="13">
         <v>3570</v>
       </c>
-      <c r="U6" s="13">
+      <c r="W6" s="13">
         <v>3619</v>
       </c>
-      <c r="V6" s="13">
+      <c r="X6" s="13">
         <v>3650</v>
       </c>
-      <c r="W6" s="13">
+      <c r="Y6" s="13">
         <v>3720</v>
       </c>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
       <c r="Z6" s="13"/>
       <c r="AA6" s="13"/>
       <c r="AB6" s="13"/>
@@ -1979,41 +2019,43 @@
       <c r="BC6" s="13"/>
       <c r="BD6" s="13"/>
       <c r="BE6" s="13"/>
-      <c r="BF6" s="29"/>
+      <c r="BF6" s="13"/>
       <c r="BG6" s="13"/>
-      <c r="BH6" s="13"/>
-      <c r="BI6" s="29"/>
+      <c r="BH6" s="29"/>
+      <c r="BI6" s="13"/>
       <c r="BJ6" s="13"/>
-      <c r="BK6" s="13"/>
+      <c r="BK6" s="29"/>
       <c r="BL6" s="13"/>
-      <c r="BN6" s="13">
-        <f>(G6*H6)/100-BT6</f>
-        <v>561.70000000000005</v>
-      </c>
-      <c r="BO6" s="13">
+      <c r="BM6" s="13"/>
+      <c r="BN6" s="13"/>
+      <c r="BP6" s="13">
+        <f>(G6*H6)/100-BV6</f>
+        <v>1033.7</v>
+      </c>
+      <c r="BQ6" s="13">
         <f>(G6*H6)/100</f>
-        <v>555</v>
-      </c>
-      <c r="BP6" s="13">
-        <f t="shared" ref="BP6" si="1">(BO6-BN6)</f>
-        <v>-6.7000000000000455</v>
-      </c>
-      <c r="BQ6" s="13">
-        <f>((BE6-H6)/H6)*100</f>
+        <v>1010</v>
+      </c>
+      <c r="BR6" s="13">
+        <f t="shared" ref="BR6" si="1">(BQ6-BP6)</f>
+        <v>-23.700000000000045</v>
+      </c>
+      <c r="BS6" s="13">
+        <f>((BG6-H6)/H6)*100</f>
         <v>-100</v>
       </c>
-      <c r="BR6">
+      <c r="BT6">
         <v>5</v>
       </c>
-      <c r="BS6">
+      <c r="BU6">
         <v>3566</v>
       </c>
-      <c r="BT6" s="15">
-        <f>(BR6*BS6-BR6*H6)/100</f>
-        <v>-6.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BV6" s="15">
+        <f>(BT6*BU6-BT6*H6)/100</f>
+        <v>-23.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1148899</v>
       </c>
@@ -2042,79 +2084,83 @@
         <v>3585</v>
       </c>
       <c r="I7" s="13">
+        <v>3916</v>
+      </c>
+      <c r="J7" s="13">
+        <v>3916</v>
+      </c>
+      <c r="K7" s="13">
         <v>3954</v>
       </c>
-      <c r="J7" s="13">
+      <c r="L7" s="13">
         <v>3932</v>
       </c>
-      <c r="K7" s="13">
+      <c r="M7" s="13">
         <v>3949</v>
       </c>
-      <c r="L7" s="13">
+      <c r="N7" s="13">
         <v>3943</v>
       </c>
-      <c r="M7" s="13">
+      <c r="O7" s="13">
         <v>3928</v>
       </c>
-      <c r="N7" s="13">
+      <c r="P7" s="13">
         <v>3913</v>
       </c>
-      <c r="O7" s="13">
+      <c r="Q7" s="13">
         <v>3860</v>
       </c>
-      <c r="P7" s="13">
+      <c r="R7" s="13">
         <v>3893</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="S7" s="13">
         <v>3900</v>
       </c>
-      <c r="R7" s="13">
+      <c r="T7" s="13">
         <v>3842</v>
       </c>
-      <c r="S7" s="13">
+      <c r="U7" s="13">
         <v>3842</v>
       </c>
-      <c r="T7" s="13">
+      <c r="V7" s="13">
         <v>3841</v>
       </c>
-      <c r="U7" s="13">
+      <c r="W7" s="13">
         <v>3809</v>
       </c>
-      <c r="V7" s="13">
+      <c r="X7" s="13">
         <v>3810</v>
       </c>
-      <c r="W7" s="13">
+      <c r="Y7" s="13">
         <v>3798</v>
       </c>
-      <c r="X7" s="13">
+      <c r="Z7" s="13">
         <v>3713</v>
       </c>
-      <c r="Y7" s="13">
+      <c r="AA7" s="13">
         <v>3657</v>
       </c>
-      <c r="Z7" s="13">
+      <c r="AB7" s="13">
         <v>3592</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="AC7" s="13">
         <v>3621</v>
       </c>
-      <c r="AB7" s="13">
+      <c r="AD7" s="13">
         <v>3572</v>
       </c>
-      <c r="AC7" s="13">
+      <c r="AE7" s="13">
         <v>3580</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AF7" s="13">
         <v>3569</v>
       </c>
-      <c r="AE7" s="13">
+      <c r="AG7" s="13">
         <v>3659</v>
       </c>
-      <c r="AF7" s="13">
+      <c r="AH7" s="13">
         <v>3656</v>
       </c>
-      <c r="AG7" s="13"/>
-      <c r="AH7" s="13"/>
       <c r="AI7" s="13"/>
       <c r="AJ7" s="13"/>
       <c r="AK7" s="13"/>
@@ -2138,27 +2184,29 @@
       <c r="BC7" s="13"/>
       <c r="BD7" s="13"/>
       <c r="BE7" s="13"/>
-      <c r="BF7" s="29"/>
+      <c r="BF7" s="13"/>
       <c r="BG7" s="13"/>
-      <c r="BH7" s="13"/>
-      <c r="BI7" s="29"/>
+      <c r="BH7" s="29"/>
+      <c r="BI7" s="13"/>
       <c r="BJ7" s="13"/>
-      <c r="BK7" s="13"/>
+      <c r="BK7" s="29"/>
       <c r="BL7" s="13"/>
       <c r="BM7" s="13"/>
-      <c r="BN7" s="13">
+      <c r="BN7" s="13"/>
+      <c r="BO7" s="13"/>
+      <c r="BP7" s="13">
         <f t="shared" si="0"/>
         <v>2509.5</v>
       </c>
-      <c r="BO7" s="13">
-        <f t="shared" ref="BO7:BO19" si="2">(G7*H7)/100</f>
+      <c r="BQ7" s="13">
+        <f t="shared" ref="BQ7:BQ19" si="2">(G7*H7)/100</f>
         <v>2509.5</v>
       </c>
-      <c r="BP7" s="13"/>
-      <c r="BQ7" s="13"/>
-      <c r="BT7" s="15"/>
-    </row>
-    <row r="8" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BR7" s="13"/>
+      <c r="BS7" s="13"/>
+      <c r="BV7" s="15"/>
+    </row>
+    <row r="8" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1082379</v>
       </c>
@@ -2172,7 +2220,7 @@
       </c>
       <c r="D8" s="6" t="str">
         <f>IF(I8&lt;GEMINI!L8,"למכור בהפסד",IF(I8&gt;GEMINI!M8,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>52</v>
@@ -2187,115 +2235,119 @@
         <v>37875</v>
       </c>
       <c r="I8" s="13">
+        <v>42140</v>
+      </c>
+      <c r="J8" s="13">
+        <v>42140</v>
+      </c>
+      <c r="K8" s="13">
         <v>43490</v>
       </c>
-      <c r="J8" s="13">
+      <c r="L8" s="13">
         <v>40750</v>
       </c>
-      <c r="K8" s="13">
+      <c r="M8" s="13">
         <v>40900</v>
       </c>
-      <c r="L8" s="13">
+      <c r="N8" s="13">
         <v>40790</v>
       </c>
-      <c r="M8" s="13">
+      <c r="O8" s="13">
         <v>40820</v>
       </c>
-      <c r="N8" s="13">
+      <c r="P8" s="13">
         <v>41570</v>
       </c>
-      <c r="O8" s="13">
+      <c r="Q8" s="13">
         <v>42050</v>
       </c>
-      <c r="P8" s="13">
+      <c r="R8" s="13">
         <v>39960</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="S8" s="13">
         <v>39990</v>
       </c>
-      <c r="R8" s="13">
+      <c r="T8" s="13">
         <v>38680</v>
       </c>
-      <c r="S8" s="13">
+      <c r="U8" s="13">
         <v>38680</v>
       </c>
-      <c r="T8" s="13">
+      <c r="V8" s="13">
         <v>37770</v>
       </c>
-      <c r="U8" s="13">
+      <c r="W8" s="13">
         <v>36330</v>
       </c>
-      <c r="V8" s="13">
+      <c r="X8" s="13">
         <v>38680</v>
       </c>
-      <c r="W8" s="13">
+      <c r="Y8" s="13">
         <v>39090</v>
-      </c>
-      <c r="X8" s="13">
-        <v>37300</v>
-      </c>
-      <c r="Y8" s="13">
-        <v>37650</v>
       </c>
       <c r="Z8" s="13">
         <v>37300</v>
       </c>
       <c r="AA8" s="13">
+        <v>37650</v>
+      </c>
+      <c r="AB8" s="13">
+        <v>37300</v>
+      </c>
+      <c r="AC8" s="13">
         <v>39450</v>
       </c>
-      <c r="AB8" s="13">
+      <c r="AD8" s="13">
         <v>38390</v>
       </c>
-      <c r="AC8" s="13">
+      <c r="AE8" s="13">
         <v>38800</v>
       </c>
-      <c r="AD8" s="13">
+      <c r="AF8" s="13">
         <v>38510</v>
       </c>
-      <c r="AE8" s="13">
+      <c r="AG8" s="13">
         <v>38970</v>
       </c>
-      <c r="AF8" s="13">
+      <c r="AH8" s="13">
         <v>38970</v>
       </c>
-      <c r="AG8" s="13">
+      <c r="AI8" s="13">
         <v>37700</v>
       </c>
-      <c r="AH8" s="13">
+      <c r="AJ8" s="13">
         <v>37700</v>
       </c>
-      <c r="AI8" s="13">
+      <c r="AK8" s="13">
         <v>37750</v>
       </c>
-      <c r="AJ8" s="13">
+      <c r="AL8" s="13">
         <v>38430</v>
       </c>
-      <c r="AK8" s="13">
+      <c r="AM8" s="13">
         <v>38250</v>
       </c>
-      <c r="AL8" s="13">
+      <c r="AN8" s="13">
         <v>40110</v>
       </c>
-      <c r="AM8" s="13">
+      <c r="AO8" s="13">
         <v>40820</v>
       </c>
-      <c r="AN8" s="13">
+      <c r="AP8" s="13">
         <v>39320</v>
       </c>
-      <c r="AO8" s="13">
+      <c r="AQ8" s="13">
         <v>37800</v>
       </c>
-      <c r="AP8" s="13">
+      <c r="AR8" s="13">
         <v>36620</v>
       </c>
-      <c r="AQ8" s="13">
+      <c r="AS8" s="13">
         <v>37130</v>
       </c>
-      <c r="AR8" s="13">
+      <c r="AT8" s="13">
         <v>35850</v>
       </c>
-      <c r="AS8" s="13"/>
-      <c r="AT8" s="13"/>
       <c r="AU8" s="13"/>
       <c r="AV8" s="13"/>
       <c r="AW8" s="13"/>
@@ -2307,39 +2359,41 @@
       <c r="BC8" s="13"/>
       <c r="BD8" s="13"/>
       <c r="BE8" s="13"/>
-      <c r="BF8" s="29"/>
+      <c r="BF8" s="13"/>
       <c r="BG8" s="13"/>
-      <c r="BH8" s="13"/>
-      <c r="BI8" s="29"/>
+      <c r="BH8" s="29"/>
+      <c r="BI8" s="13"/>
       <c r="BJ8" s="13"/>
-      <c r="BK8" s="13"/>
+      <c r="BK8" s="29"/>
       <c r="BL8" s="13"/>
       <c r="BM8" s="13"/>
-      <c r="BN8" s="13">
+      <c r="BN8" s="13"/>
+      <c r="BO8" s="13"/>
+      <c r="BP8" s="13">
         <f t="shared" si="0"/>
         <v>806.25</v>
       </c>
-      <c r="BO8" s="13">
+      <c r="BQ8" s="13">
         <f t="shared" si="2"/>
         <v>757.5</v>
       </c>
-      <c r="BP8" s="13">
-        <f t="shared" ref="BP8:BP11" si="3">(BO8-BN8)</f>
+      <c r="BR8" s="13">
+        <f t="shared" ref="BR8:BR11" si="3">(BQ8-BP8)</f>
         <v>-48.75</v>
       </c>
-      <c r="BQ8" s="13"/>
-      <c r="BR8">
+      <c r="BS8" s="13"/>
+      <c r="BT8">
         <v>3</v>
       </c>
-      <c r="BS8">
+      <c r="BU8">
         <v>36250</v>
       </c>
-      <c r="BT8" s="15">
-        <f>(BR8*BS8-BR8*H8)/100</f>
+      <c r="BV8" s="15">
+        <f>(BT8*BU8-BT8*H8)/100</f>
         <v>-48.75</v>
       </c>
     </row>
-    <row r="9" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>629014</v>
       </c>
@@ -2368,109 +2422,113 @@
         <v>9227</v>
       </c>
       <c r="I9" s="13">
+        <v>10100</v>
+      </c>
+      <c r="J9" s="13">
+        <v>10100</v>
+      </c>
+      <c r="K9" s="13">
         <v>10240</v>
       </c>
-      <c r="J9" s="13">
+      <c r="L9" s="13">
         <v>9891</v>
       </c>
-      <c r="K9" s="13">
+      <c r="M9" s="13">
         <v>9956</v>
       </c>
-      <c r="L9" s="13">
+      <c r="N9" s="13">
         <v>9910</v>
       </c>
-      <c r="M9" s="13">
+      <c r="O9" s="13">
         <v>9960</v>
       </c>
-      <c r="N9" s="13">
+      <c r="P9" s="13">
         <v>9924</v>
       </c>
-      <c r="O9" s="13">
+      <c r="Q9" s="13">
         <v>9999</v>
       </c>
-      <c r="P9" s="13">
+      <c r="R9" s="13">
         <v>9962</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="S9" s="13">
         <v>9979</v>
       </c>
-      <c r="R9" s="13">
+      <c r="T9" s="13">
         <v>10130</v>
       </c>
-      <c r="S9" s="13">
+      <c r="U9" s="13">
         <v>10130</v>
       </c>
-      <c r="T9" s="13">
+      <c r="V9" s="13">
         <v>10400</v>
       </c>
-      <c r="U9" s="13">
+      <c r="W9" s="13">
         <v>10320</v>
       </c>
-      <c r="V9" s="13">
+      <c r="X9" s="13">
         <v>10300</v>
       </c>
-      <c r="W9" s="13">
+      <c r="Y9" s="13">
         <v>10310</v>
       </c>
-      <c r="X9" s="13">
+      <c r="Z9" s="13">
         <v>9672</v>
       </c>
-      <c r="Y9" s="13">
+      <c r="AA9" s="13">
         <v>9953</v>
       </c>
-      <c r="Z9" s="13">
+      <c r="AB9" s="13">
         <v>10090</v>
       </c>
-      <c r="AA9" s="13">
+      <c r="AC9" s="13">
         <v>10070</v>
       </c>
-      <c r="AB9" s="13">
+      <c r="AD9" s="13">
         <v>10030</v>
       </c>
-      <c r="AC9" s="13">
+      <c r="AE9" s="13">
         <v>10120</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AF9" s="13">
         <v>10000</v>
       </c>
-      <c r="AE9" s="13">
+      <c r="AG9" s="13">
         <v>10080</v>
       </c>
-      <c r="AF9" s="13">
+      <c r="AH9" s="13">
         <v>10030</v>
       </c>
-      <c r="AG9" s="13">
+      <c r="AI9" s="13">
         <v>9726</v>
       </c>
-      <c r="AH9" s="13">
+      <c r="AJ9" s="13">
         <v>9726</v>
       </c>
-      <c r="AI9" s="13">
+      <c r="AK9" s="13">
         <v>9659</v>
       </c>
-      <c r="AJ9" s="13">
+      <c r="AL9" s="13">
         <v>9670</v>
       </c>
-      <c r="AK9" s="13">
+      <c r="AM9" s="13">
         <v>9590</v>
       </c>
-      <c r="AL9" s="13">
+      <c r="AN9" s="13">
         <v>9588</v>
       </c>
-      <c r="AM9" s="13">
+      <c r="AO9" s="13">
         <v>9400</v>
       </c>
-      <c r="AN9" s="13">
+      <c r="AP9" s="13">
         <v>9320</v>
       </c>
-      <c r="AO9" s="13">
+      <c r="AQ9" s="13">
         <v>9071</v>
       </c>
-      <c r="AP9" s="13">
+      <c r="AR9" s="13">
         <v>9271</v>
       </c>
-      <c r="AQ9" s="13"/>
-      <c r="AR9" s="13"/>
       <c r="AS9" s="13"/>
       <c r="AT9" s="13"/>
       <c r="AU9" s="13"/>
@@ -2484,39 +2542,41 @@
       <c r="BC9" s="13"/>
       <c r="BD9" s="13"/>
       <c r="BE9" s="13"/>
-      <c r="BF9" s="29"/>
+      <c r="BF9" s="13"/>
       <c r="BG9" s="13"/>
-      <c r="BH9" s="13"/>
-      <c r="BI9" s="29"/>
+      <c r="BH9" s="29"/>
+      <c r="BI9" s="13"/>
       <c r="BJ9" s="13"/>
-      <c r="BK9" s="13"/>
+      <c r="BK9" s="29"/>
       <c r="BL9" s="13"/>
       <c r="BM9" s="13"/>
-      <c r="BN9" s="13">
+      <c r="BN9" s="13"/>
+      <c r="BO9" s="13"/>
+      <c r="BP9" s="13">
         <f t="shared" si="0"/>
         <v>-38.65</v>
       </c>
-      <c r="BO9" s="13">
+      <c r="BQ9" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BP9" s="13">
+      <c r="BR9" s="13">
         <f t="shared" si="3"/>
         <v>38.65</v>
       </c>
-      <c r="BQ9" s="13"/>
-      <c r="BR9">
+      <c r="BS9" s="13"/>
+      <c r="BT9">
         <v>5</v>
       </c>
-      <c r="BS9">
+      <c r="BU9">
         <v>10000</v>
       </c>
-      <c r="BT9" s="15">
-        <f>(BR9*BS9-BR9*H9)/100</f>
+      <c r="BV9" s="15">
+        <f>(BT9*BU9-BT9*H9)/100</f>
         <v>38.65</v>
       </c>
     </row>
-    <row r="10" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1141464</v>
       </c>
@@ -2545,190 +2605,196 @@
         <v>4834</v>
       </c>
       <c r="I10" s="13">
+        <v>4809</v>
+      </c>
+      <c r="J10" s="13">
+        <v>4809</v>
+      </c>
+      <c r="K10" s="13">
         <v>4849</v>
       </c>
-      <c r="J10" s="13">
+      <c r="L10" s="13">
         <v>4821</v>
       </c>
-      <c r="K10" s="13">
+      <c r="M10" s="13">
         <v>4925</v>
       </c>
-      <c r="L10" s="13">
+      <c r="N10" s="13">
         <v>5013</v>
       </c>
-      <c r="M10" s="13">
+      <c r="O10" s="13">
         <v>5050</v>
       </c>
-      <c r="N10" s="13">
+      <c r="P10" s="13">
         <v>5050</v>
       </c>
-      <c r="O10" s="13">
+      <c r="Q10" s="13">
         <v>4930</v>
       </c>
-      <c r="P10" s="13">
+      <c r="R10" s="13">
         <v>5150</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="S10" s="13">
         <v>5283</v>
       </c>
-      <c r="R10" s="13">
+      <c r="T10" s="13">
         <v>5253</v>
       </c>
-      <c r="S10" s="13">
+      <c r="U10" s="13">
         <v>5253</v>
       </c>
-      <c r="T10" s="13">
+      <c r="V10" s="13">
         <v>5400</v>
       </c>
-      <c r="U10" s="13">
+      <c r="W10" s="13">
         <v>5522</v>
       </c>
-      <c r="V10" s="13">
+      <c r="X10" s="13">
         <v>5690</v>
       </c>
-      <c r="W10" s="13">
+      <c r="Y10" s="13">
         <v>5749</v>
       </c>
-      <c r="X10" s="13">
+      <c r="Z10" s="13">
         <v>5840</v>
       </c>
-      <c r="Y10" s="13">
+      <c r="AA10" s="13">
         <v>5650</v>
       </c>
-      <c r="Z10" s="13">
+      <c r="AB10" s="13">
         <v>5650</v>
       </c>
-      <c r="AA10" s="13">
+      <c r="AC10" s="13">
         <v>5841</v>
       </c>
-      <c r="AB10" s="13">
+      <c r="AD10" s="13">
         <v>5758</v>
       </c>
-      <c r="AC10" s="13">
+      <c r="AE10" s="13">
         <v>5673</v>
       </c>
-      <c r="AD10" s="13">
+      <c r="AF10" s="13">
         <v>5609</v>
       </c>
-      <c r="AE10" s="13">
+      <c r="AG10" s="13">
         <v>5750</v>
       </c>
-      <c r="AF10" s="13">
+      <c r="AH10" s="13">
         <v>5841</v>
       </c>
-      <c r="AG10" s="13">
+      <c r="AI10" s="13">
         <v>5564</v>
       </c>
-      <c r="AH10" s="13">
+      <c r="AJ10" s="13">
         <v>5564</v>
       </c>
-      <c r="AI10" s="13">
+      <c r="AK10" s="13">
         <v>5557</v>
       </c>
-      <c r="AJ10" s="13">
+      <c r="AL10" s="13">
         <v>5501</v>
       </c>
-      <c r="AK10" s="13">
+      <c r="AM10" s="13">
         <v>5250</v>
       </c>
-      <c r="AL10" s="13">
+      <c r="AN10" s="13">
         <v>5270</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AO10" s="13">
         <v>5149</v>
       </c>
-      <c r="AN10" s="13">
+      <c r="AP10" s="13">
         <v>5092</v>
       </c>
-      <c r="AO10" s="13">
+      <c r="AQ10" s="13">
         <v>5228</v>
       </c>
-      <c r="AP10" s="13">
+      <c r="AR10" s="13">
         <v>5301</v>
       </c>
-      <c r="AQ10" s="13">
+      <c r="AS10" s="13">
         <v>5159</v>
       </c>
-      <c r="AR10" s="13">
+      <c r="AT10" s="13">
         <v>5198</v>
       </c>
-      <c r="AS10" s="13">
+      <c r="AU10" s="13">
         <v>5077</v>
       </c>
-      <c r="AT10" s="13">
+      <c r="AV10" s="13">
         <v>4842</v>
       </c>
-      <c r="AU10" s="13">
+      <c r="AW10" s="13">
         <v>5050</v>
       </c>
-      <c r="AV10" s="13">
+      <c r="AX10" s="13">
         <v>4970</v>
       </c>
-      <c r="AW10" s="13">
+      <c r="AY10" s="13">
         <v>4880</v>
       </c>
-      <c r="AX10" s="13">
+      <c r="AZ10" s="13">
         <v>4704</v>
       </c>
-      <c r="AY10" s="13">
+      <c r="BA10" s="13">
         <v>4770</v>
       </c>
-      <c r="AZ10" s="13">
+      <c r="BB10" s="13">
         <v>4609</v>
       </c>
-      <c r="BA10" s="13">
+      <c r="BC10" s="13">
         <v>4674</v>
       </c>
-      <c r="BB10" s="13">
+      <c r="BD10" s="13">
         <v>4710</v>
       </c>
-      <c r="BC10" s="13">
+      <c r="BE10" s="13">
         <v>4688</v>
       </c>
-      <c r="BD10" s="13">
+      <c r="BF10" s="13">
         <v>4900</v>
       </c>
-      <c r="BE10" s="13">
+      <c r="BG10" s="13">
         <v>5000</v>
       </c>
-      <c r="BF10" s="29">
+      <c r="BH10" s="29">
         <v>4932</v>
       </c>
-      <c r="BG10" s="13"/>
-      <c r="BH10" s="13"/>
-      <c r="BI10" s="29"/>
+      <c r="BI10" s="13"/>
       <c r="BJ10" s="13"/>
-      <c r="BK10" s="13"/>
+      <c r="BK10" s="29"/>
       <c r="BL10" s="13"/>
       <c r="BM10" s="13"/>
-      <c r="BN10" s="13">
+      <c r="BN10" s="13"/>
+      <c r="BO10" s="13"/>
+      <c r="BP10" s="13">
         <f t="shared" si="0"/>
         <v>-87.859799999999964</v>
       </c>
-      <c r="BO10" s="13">
+      <c r="BQ10" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BP10" s="13">
+      <c r="BR10" s="13">
         <f t="shared" si="3"/>
         <v>87.859799999999964</v>
       </c>
-      <c r="BQ10" s="13">
-        <f>((BE10-H10)/H10)*100</f>
+      <c r="BS10" s="13">
+        <f>((BG10-H10)/H10)*100</f>
         <v>3.434009102192801</v>
       </c>
-      <c r="BR10">
+      <c r="BT10">
         <v>21</v>
       </c>
-      <c r="BS10">
+      <c r="BU10">
         <v>5252.38</v>
       </c>
-      <c r="BT10" s="15">
-        <f>(BR10*BS10-BR10*H10)/100</f>
+      <c r="BV10" s="15">
+        <f>(BT10*BU10-BT10*H10)/100</f>
         <v>87.859799999999964</v>
       </c>
     </row>
-    <row r="11" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1166974</v>
       </c>
@@ -2757,73 +2823,77 @@
         <v>901.87</v>
       </c>
       <c r="I11" s="13">
+        <v>1075</v>
+      </c>
+      <c r="J11" s="13">
+        <v>1075</v>
+      </c>
+      <c r="K11" s="13">
         <v>1109</v>
       </c>
-      <c r="J11" s="13">
+      <c r="L11" s="13">
         <v>1090</v>
       </c>
-      <c r="K11" s="13">
+      <c r="M11" s="13">
         <v>1144</v>
       </c>
-      <c r="L11" s="13">
+      <c r="N11" s="13">
         <v>1162</v>
       </c>
-      <c r="M11" s="13">
+      <c r="O11" s="13">
         <v>1109</v>
       </c>
-      <c r="N11" s="13">
+      <c r="P11" s="13">
         <v>1029</v>
       </c>
-      <c r="O11" s="13">
+      <c r="Q11" s="13">
         <v>993</v>
       </c>
-      <c r="P11" s="13">
+      <c r="R11" s="13">
         <v>1017</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="S11" s="13">
         <v>960</v>
       </c>
-      <c r="R11" s="13">
+      <c r="T11" s="13">
         <v>965</v>
       </c>
-      <c r="S11" s="13">
+      <c r="U11" s="13">
         <v>965</v>
       </c>
-      <c r="T11" s="13">
+      <c r="V11" s="13">
         <v>951.7</v>
       </c>
-      <c r="U11" s="13">
+      <c r="W11" s="13">
         <v>946</v>
       </c>
-      <c r="V11" s="13">
+      <c r="X11" s="13">
         <v>869.2</v>
       </c>
-      <c r="W11" s="13">
+      <c r="Y11" s="13">
         <v>865</v>
       </c>
-      <c r="X11" s="13">
+      <c r="Z11" s="13">
         <v>851</v>
       </c>
-      <c r="Y11" s="13">
+      <c r="AA11" s="13">
         <v>829.3</v>
       </c>
-      <c r="Z11" s="13">
+      <c r="AB11" s="13">
         <v>830</v>
       </c>
-      <c r="AA11" s="13">
+      <c r="AC11" s="13">
         <v>810</v>
       </c>
-      <c r="AB11" s="13">
+      <c r="AD11" s="13">
         <v>812.8</v>
       </c>
-      <c r="AC11" s="13">
+      <c r="AE11" s="13">
         <v>788</v>
       </c>
-      <c r="AD11" s="13">
+      <c r="AF11" s="13">
         <v>772</v>
       </c>
-      <c r="AE11" s="13"/>
-      <c r="AF11" s="13"/>
       <c r="AG11" s="13"/>
       <c r="AH11" s="13"/>
       <c r="AI11" s="13"/>
@@ -2849,33 +2919,35 @@
       <c r="BC11" s="13"/>
       <c r="BD11" s="13"/>
       <c r="BE11" s="13"/>
-      <c r="BF11" s="29"/>
+      <c r="BF11" s="13"/>
       <c r="BG11" s="13"/>
-      <c r="BH11" s="13"/>
-      <c r="BI11" s="29"/>
+      <c r="BH11" s="29"/>
+      <c r="BI11" s="13"/>
       <c r="BJ11" s="13"/>
-      <c r="BK11" s="13"/>
+      <c r="BK11" s="29"/>
       <c r="BL11" s="13"/>
       <c r="BM11" s="13"/>
-      <c r="BN11" s="13">
+      <c r="BN11" s="13"/>
+      <c r="BO11" s="13"/>
+      <c r="BP11" s="13">
         <f t="shared" si="0"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BO11" s="13">
+      <c r="BQ11" s="13">
         <f t="shared" si="2"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BP11" s="13">
+      <c r="BR11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BQ11" s="13"/>
-      <c r="BT11" s="15">
-        <f>(BR11*BS11-BR11*H11)/100</f>
+      <c r="BS11" s="13"/>
+      <c r="BV11" s="15">
+        <f>(BT11*BU11-BT11*H11)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1176593</v>
       </c>
@@ -2889,7 +2961,7 @@
       </c>
       <c r="D12" s="6" t="str">
         <f>IF(I12&lt;GEMINI!L12,"למכור בהפסד",IF(I12&gt;GEMINI!M12,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>68</v>
@@ -2898,85 +2970,89 @@
         <v>46013</v>
       </c>
       <c r="G12" s="27">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H12" s="13">
         <v>22581.42</v>
       </c>
       <c r="I12" s="13">
+        <v>27890</v>
+      </c>
+      <c r="J12" s="13">
+        <v>27890</v>
+      </c>
+      <c r="K12" s="13">
         <v>30100</v>
       </c>
-      <c r="J12" s="13">
+      <c r="L12" s="13">
         <v>30500</v>
       </c>
-      <c r="K12" s="13">
+      <c r="M12" s="13">
         <v>28850</v>
       </c>
-      <c r="L12" s="13">
+      <c r="N12" s="13">
         <v>27450</v>
       </c>
-      <c r="M12" s="13">
+      <c r="O12" s="13">
         <v>26940</v>
       </c>
-      <c r="N12" s="13">
+      <c r="P12" s="13">
         <v>26800</v>
       </c>
-      <c r="O12" s="13">
+      <c r="Q12" s="13">
         <v>25950</v>
       </c>
-      <c r="P12" s="13">
+      <c r="R12" s="13">
         <v>26000</v>
       </c>
-      <c r="Q12" s="13">
+      <c r="S12" s="13">
         <v>26600</v>
       </c>
-      <c r="R12" s="13">
+      <c r="T12" s="13">
         <v>24630</v>
       </c>
-      <c r="S12" s="13">
+      <c r="U12" s="13">
         <v>24630</v>
       </c>
-      <c r="T12" s="13">
+      <c r="V12" s="13">
         <v>25230</v>
       </c>
-      <c r="U12" s="13">
+      <c r="W12" s="13">
         <v>24700</v>
       </c>
-      <c r="V12" s="13">
+      <c r="X12" s="13">
         <v>23780</v>
       </c>
-      <c r="W12" s="13">
+      <c r="Y12" s="13">
         <v>23920</v>
       </c>
-      <c r="X12" s="13">
+      <c r="Z12" s="13">
         <v>22390</v>
       </c>
-      <c r="Y12" s="13">
+      <c r="AA12" s="13">
         <v>23000</v>
       </c>
-      <c r="Z12" s="13">
+      <c r="AB12" s="13">
         <v>20990</v>
       </c>
-      <c r="AA12" s="13">
+      <c r="AC12" s="13">
         <v>20260</v>
       </c>
-      <c r="AB12" s="13">
+      <c r="AD12" s="13">
         <v>19200</v>
       </c>
-      <c r="AC12" s="13">
+      <c r="AE12" s="13">
         <v>19860</v>
       </c>
-      <c r="AD12" s="13">
+      <c r="AF12" s="13">
         <v>19700</v>
       </c>
-      <c r="AE12" s="13">
+      <c r="AG12" s="13">
         <v>19430</v>
       </c>
-      <c r="AF12" s="13">
+      <c r="AH12" s="13">
         <v>19020</v>
       </c>
-      <c r="AG12" s="13"/>
-      <c r="AH12" s="13"/>
       <c r="AI12" s="13"/>
       <c r="AJ12" s="13"/>
       <c r="AK12" s="13"/>
@@ -3000,30 +3076,38 @@
       <c r="BC12" s="13"/>
       <c r="BD12" s="13"/>
       <c r="BE12" s="13"/>
-      <c r="BF12" s="29"/>
+      <c r="BF12" s="13"/>
       <c r="BG12" s="13"/>
-      <c r="BH12" s="13"/>
-      <c r="BI12" s="29"/>
+      <c r="BH12" s="29"/>
+      <c r="BI12" s="13"/>
       <c r="BJ12" s="13"/>
-      <c r="BK12" s="13"/>
+      <c r="BK12" s="29"/>
       <c r="BL12" s="13"/>
       <c r="BM12" s="13"/>
-      <c r="BN12" s="13">
+      <c r="BN12" s="13"/>
+      <c r="BO12" s="13"/>
+      <c r="BP12" s="13">
         <f t="shared" si="0"/>
-        <v>1580.6994</v>
-      </c>
-      <c r="BO12" s="13">
+        <v>-331.70059999999995</v>
+      </c>
+      <c r="BQ12" s="13">
         <f t="shared" si="2"/>
-        <v>1580.6994</v>
-      </c>
-      <c r="BP12" s="13"/>
-      <c r="BQ12" s="13"/>
-      <c r="BT12" s="15">
-        <f t="shared" ref="BT12:BT14" si="4">(BR12*BS12-BR12*H12)/100</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BR12" s="13"/>
+      <c r="BS12" s="13"/>
+      <c r="BT12">
+        <v>7</v>
+      </c>
+      <c r="BU12">
+        <v>27320</v>
+      </c>
+      <c r="BV12" s="15">
+        <f t="shared" ref="BV12:BV14" si="4">(BT12*BU12-BT12*H12)/100</f>
+        <v>331.70059999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>397018</v>
       </c>
@@ -3037,10 +3121,10 @@
       </c>
       <c r="D13" s="6" t="str">
         <f>IF(I13&lt;GEMINI!L13,"למכור בהפסד",IF(I13&gt;GEMINI!M13,"למכור ברווח","לשמור"))</f>
-        <v>למכור בהפסד</v>
+        <v>לשמור</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F13" s="4">
         <v>46042</v>
@@ -3049,30 +3133,34 @@
       <c r="H13" s="13">
         <v>723</v>
       </c>
-      <c r="I13" s="13"/>
+      <c r="I13" s="13">
+        <v>900</v>
+      </c>
       <c r="J13" s="13">
+        <v>900</v>
+      </c>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13">
         <v>1490</v>
       </c>
-      <c r="K13" s="13">
+      <c r="M13" s="13">
         <v>1210</v>
       </c>
-      <c r="L13" s="13">
+      <c r="N13" s="13">
         <v>1100</v>
       </c>
-      <c r="M13" s="13">
+      <c r="O13" s="13">
         <v>980</v>
       </c>
-      <c r="N13" s="13">
+      <c r="P13" s="13">
         <v>932.1</v>
       </c>
-      <c r="O13" s="13">
+      <c r="Q13" s="13">
         <v>822</v>
       </c>
-      <c r="P13" s="13">
+      <c r="R13" s="13">
         <v>790</v>
       </c>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
       <c r="S13" s="13"/>
       <c r="T13" s="13"/>
       <c r="U13" s="13"/>
@@ -3112,30 +3200,32 @@
       <c r="BC13" s="13"/>
       <c r="BD13" s="13"/>
       <c r="BE13" s="13"/>
-      <c r="BF13" s="29"/>
+      <c r="BF13" s="13"/>
       <c r="BG13" s="13"/>
-      <c r="BH13" s="13"/>
-      <c r="BI13" s="29"/>
+      <c r="BH13" s="29"/>
+      <c r="BI13" s="13"/>
       <c r="BJ13" s="13"/>
-      <c r="BK13" s="13"/>
+      <c r="BK13" s="29"/>
       <c r="BL13" s="13"/>
       <c r="BM13" s="13"/>
-      <c r="BN13" s="13">
+      <c r="BN13" s="13"/>
+      <c r="BO13" s="13"/>
+      <c r="BP13" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BO13" s="13">
+      <c r="BQ13" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BP13" s="13"/>
-      <c r="BQ13" s="13"/>
-      <c r="BT13" s="15">
+      <c r="BR13" s="13"/>
+      <c r="BS13" s="13"/>
+      <c r="BV13" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>662577</v>
       </c>
@@ -3164,198 +3254,204 @@
         <v>7204.22</v>
       </c>
       <c r="I14" s="13">
+        <v>7687</v>
+      </c>
+      <c r="J14" s="13">
+        <v>7687</v>
+      </c>
+      <c r="K14" s="13">
         <v>7672</v>
       </c>
-      <c r="J14" s="13">
+      <c r="L14" s="13">
         <v>7676</v>
       </c>
-      <c r="K14" s="13">
+      <c r="M14" s="13">
         <v>7844</v>
       </c>
-      <c r="L14" s="13">
+      <c r="N14" s="13">
         <v>7810</v>
       </c>
-      <c r="M14" s="13">
+      <c r="O14" s="13">
         <v>7710</v>
       </c>
-      <c r="N14" s="13">
+      <c r="P14" s="13">
         <v>7735</v>
       </c>
-      <c r="O14" s="13">
+      <c r="Q14" s="13">
         <v>7725</v>
       </c>
-      <c r="P14" s="13">
+      <c r="R14" s="13">
         <v>7787</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="S14" s="13">
         <v>7955</v>
       </c>
-      <c r="R14" s="13">
+      <c r="T14" s="13">
         <v>7627</v>
       </c>
-      <c r="S14" s="13">
+      <c r="U14" s="13">
         <v>7627</v>
       </c>
-      <c r="T14" s="13">
+      <c r="V14" s="13">
         <v>7656</v>
       </c>
-      <c r="U14" s="13">
+      <c r="W14" s="13">
         <v>7507</v>
       </c>
-      <c r="V14" s="13">
+      <c r="X14" s="13">
         <v>7590</v>
       </c>
-      <c r="W14" s="13">
+      <c r="Y14" s="13">
         <v>7569</v>
       </c>
-      <c r="X14" s="13">
+      <c r="Z14" s="13">
         <v>7269</v>
       </c>
-      <c r="Y14" s="13">
+      <c r="AA14" s="13">
         <v>7444</v>
       </c>
-      <c r="Z14" s="13">
+      <c r="AB14" s="13">
         <v>7205</v>
       </c>
-      <c r="AA14" s="13">
+      <c r="AC14" s="13">
         <v>7298</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AD14" s="13">
         <v>7222</v>
       </c>
-      <c r="AC14" s="13">
+      <c r="AE14" s="13">
         <v>7079</v>
       </c>
-      <c r="AD14" s="13">
+      <c r="AF14" s="13">
         <v>7140</v>
       </c>
-      <c r="AE14" s="13">
+      <c r="AG14" s="13">
         <v>7440</v>
       </c>
-      <c r="AF14" s="13">
+      <c r="AH14" s="13">
         <v>7530</v>
       </c>
-      <c r="AG14" s="13">
+      <c r="AI14" s="13">
         <v>7535</v>
       </c>
-      <c r="AH14" s="13">
+      <c r="AJ14" s="13">
         <v>7535</v>
       </c>
-      <c r="AI14" s="13">
+      <c r="AK14" s="13">
         <v>7568</v>
       </c>
-      <c r="AJ14" s="13">
+      <c r="AL14" s="13">
         <v>7699</v>
       </c>
-      <c r="AK14" s="13">
+      <c r="AM14" s="13">
         <v>7638</v>
       </c>
-      <c r="AL14" s="13">
+      <c r="AN14" s="13">
         <v>7654</v>
       </c>
-      <c r="AM14" s="13">
+      <c r="AO14" s="13">
         <v>7584</v>
       </c>
-      <c r="AN14" s="13">
+      <c r="AP14" s="13">
         <v>7479</v>
       </c>
-      <c r="AO14" s="13">
+      <c r="AQ14" s="13">
         <v>7490</v>
       </c>
-      <c r="AP14" s="13">
+      <c r="AR14" s="13">
         <v>7480</v>
       </c>
-      <c r="AQ14" s="13">
+      <c r="AS14" s="13">
         <v>7270</v>
       </c>
-      <c r="AR14" s="13">
+      <c r="AT14" s="13">
         <v>7163</v>
       </c>
-      <c r="AS14" s="13">
+      <c r="AU14" s="13">
         <v>7231</v>
       </c>
-      <c r="AT14" s="13">
+      <c r="AV14" s="13">
         <v>7100</v>
       </c>
-      <c r="AU14" s="13">
+      <c r="AW14" s="13">
         <v>7100</v>
       </c>
-      <c r="AV14" s="13">
+      <c r="AX14" s="13">
         <v>7027</v>
       </c>
-      <c r="AW14" s="13">
+      <c r="AY14" s="13">
         <v>6984</v>
       </c>
-      <c r="AX14" s="13">
+      <c r="AZ14" s="13">
         <v>6944</v>
       </c>
-      <c r="AY14" s="13">
+      <c r="BA14" s="13">
         <v>6924</v>
       </c>
-      <c r="AZ14" s="13">
+      <c r="BB14" s="13">
         <v>6930</v>
       </c>
-      <c r="BA14" s="13">
+      <c r="BC14" s="13">
         <v>6938</v>
       </c>
-      <c r="BB14" s="13">
+      <c r="BD14" s="13">
         <v>6989</v>
       </c>
-      <c r="BC14" s="13">
+      <c r="BE14" s="13">
         <v>6871</v>
       </c>
-      <c r="BD14" s="13">
+      <c r="BF14" s="13">
         <v>6943</v>
       </c>
-      <c r="BE14" s="13">
+      <c r="BG14" s="13">
         <v>7040</v>
       </c>
-      <c r="BF14" s="29">
+      <c r="BH14" s="29">
         <v>6696</v>
       </c>
-      <c r="BG14" s="13">
+      <c r="BI14" s="13">
         <v>6965</v>
       </c>
-      <c r="BH14" s="13">
+      <c r="BJ14" s="13">
         <v>6788</v>
       </c>
-      <c r="BI14" s="29">
+      <c r="BK14" s="29">
         <v>6696</v>
       </c>
-      <c r="BJ14" s="13">
+      <c r="BL14" s="13">
         <v>6625</v>
       </c>
-      <c r="BK14" s="13">
+      <c r="BM14" s="13">
         <v>6660</v>
       </c>
-      <c r="BL14" s="13">
+      <c r="BN14" s="13">
         <v>6791</v>
       </c>
-      <c r="BM14" s="13">
+      <c r="BO14" s="13">
         <v>6610</v>
       </c>
-      <c r="BN14" s="13">
+      <c r="BP14" s="13">
         <f t="shared" si="0"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BO14" s="13">
+      <c r="BQ14" s="13">
         <f t="shared" si="2"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BP14" s="13">
-        <f t="shared" ref="BP14" si="5">(BO14-BN14)</f>
+      <c r="BR14" s="13">
+        <f t="shared" ref="BR14" si="5">(BQ14-BP14)</f>
         <v>0</v>
       </c>
-      <c r="BQ14" s="13">
-        <f>((BE14-H14)/H14)*100</f>
+      <c r="BS14" s="13">
+        <f>((BG14-H14)/H14)*100</f>
         <v>-2.2794972946411995</v>
       </c>
-      <c r="BT14" s="15">
+      <c r="BV14" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>5137534</v>
       </c>
@@ -3369,10 +3465,10 @@
       </c>
       <c r="D15" s="6" t="str">
         <f>IF(I15&lt;GEMINI!L15,"למכור בהפסד",IF(I15&gt;GEMINI!M15,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור בהפסד</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F15" s="28">
         <v>46020</v>
@@ -3384,67 +3480,71 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
+        <v>11946.75</v>
+      </c>
+      <c r="J15" s="13">
+        <v>11946.75</v>
+      </c>
+      <c r="K15" s="13">
         <v>14679.12</v>
       </c>
-      <c r="J15" s="13">
+      <c r="L15" s="13">
         <v>14679.12</v>
       </c>
-      <c r="K15" s="13">
+      <c r="M15" s="13">
         <v>13968</v>
       </c>
-      <c r="L15" s="13">
+      <c r="N15" s="13">
         <v>15528.12</v>
       </c>
-      <c r="M15" s="13">
+      <c r="O15" s="13">
         <v>14358.25</v>
       </c>
-      <c r="N15" s="13">
+      <c r="P15" s="13">
         <v>14385.75</v>
       </c>
-      <c r="O15" s="13">
+      <c r="Q15" s="13">
         <v>13880</v>
       </c>
-      <c r="P15" s="13">
+      <c r="R15" s="13">
         <v>13610.62</v>
       </c>
-      <c r="Q15" s="13">
+      <c r="S15" s="13">
         <v>13016</v>
       </c>
-      <c r="R15" s="13">
+      <c r="T15" s="13">
         <v>12487.37</v>
       </c>
-      <c r="S15" s="13">
+      <c r="U15" s="13">
         <v>12638.62</v>
       </c>
-      <c r="T15" s="13">
+      <c r="V15" s="13">
         <v>12533.87</v>
       </c>
-      <c r="U15" s="13">
+      <c r="W15" s="13">
         <v>11299.5</v>
       </c>
-      <c r="V15" s="13">
+      <c r="X15" s="13">
         <v>11193.12</v>
       </c>
-      <c r="W15" s="13">
+      <c r="Y15" s="13">
         <v>11548.62</v>
       </c>
-      <c r="X15" s="13">
+      <c r="Z15" s="13">
         <v>11125.62</v>
       </c>
-      <c r="Y15" s="13">
+      <c r="AA15" s="13">
         <v>10932.12</v>
       </c>
-      <c r="Z15" s="13">
+      <c r="AB15" s="13">
         <v>11095.62</v>
       </c>
-      <c r="AA15" s="13">
+      <c r="AC15" s="13">
         <v>10910.58</v>
       </c>
-      <c r="AB15" s="13">
+      <c r="AD15" s="13">
         <v>11609.37</v>
       </c>
-      <c r="AC15" s="13"/>
-      <c r="AD15" s="13"/>
       <c r="AE15" s="13"/>
       <c r="AF15" s="13"/>
       <c r="AG15" s="13"/>
@@ -3453,9 +3553,9 @@
       <c r="AJ15" s="13"/>
       <c r="AK15" s="13"/>
       <c r="AL15" s="13"/>
-      <c r="AM15" s="14"/>
+      <c r="AM15" s="13"/>
       <c r="AN15" s="13"/>
-      <c r="AO15" s="13"/>
+      <c r="AO15" s="14"/>
       <c r="AP15" s="13"/>
       <c r="AQ15" s="13"/>
       <c r="AR15" s="13"/>
@@ -3472,36 +3572,38 @@
       <c r="BC15" s="13"/>
       <c r="BD15" s="13"/>
       <c r="BE15" s="13"/>
-      <c r="BF15" s="29"/>
+      <c r="BF15" s="13"/>
       <c r="BG15" s="13"/>
-      <c r="BH15" s="13"/>
-      <c r="BI15" s="29"/>
+      <c r="BH15" s="29"/>
+      <c r="BI15" s="13"/>
       <c r="BJ15" s="13"/>
-      <c r="BK15" s="13"/>
+      <c r="BK15" s="29"/>
       <c r="BL15" s="13"/>
       <c r="BM15" s="13"/>
-      <c r="BN15" s="13">
+      <c r="BN15" s="13"/>
+      <c r="BO15" s="13"/>
+      <c r="BP15" s="13">
         <f t="shared" si="0"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BO15" s="13">
+      <c r="BQ15" s="13">
         <f t="shared" si="2"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BP15" s="13">
-        <f t="shared" ref="BP15:BP18" si="6">(BO15-BN15)</f>
+      <c r="BR15" s="13">
+        <f t="shared" ref="BR15:BR18" si="6">(BQ15-BP15)</f>
         <v>0</v>
       </c>
-      <c r="BQ15" s="13">
-        <f>((BE15-H15)/H15)*100</f>
+      <c r="BS15" s="13">
+        <f>((BG15-H15)/H15)*100</f>
         <v>-100</v>
       </c>
-      <c r="BT15" s="15">
-        <f t="shared" ref="BT15:BT18" si="7">(BR15*BS15-BR15*H15)/100</f>
+      <c r="BV15" s="15">
+        <f t="shared" ref="BV15:BV18" si="7">(BT15*BU15-BT15*H15)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>5135470</v>
       </c>
@@ -3524,210 +3626,216 @@
         <v>45910</v>
       </c>
       <c r="G16" s="27">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H16" s="13">
-        <v>183.73</v>
+        <v>199.49</v>
       </c>
       <c r="I16" s="13">
+        <v>223.13</v>
+      </c>
+      <c r="J16" s="13">
+        <v>223.13</v>
+      </c>
+      <c r="K16" s="13">
         <v>227.54</v>
       </c>
-      <c r="J16" s="13">
+      <c r="L16" s="13">
         <v>226.96</v>
       </c>
-      <c r="K16" s="13">
+      <c r="M16" s="13">
         <v>225.24</v>
       </c>
-      <c r="L16" s="13">
+      <c r="N16" s="13">
         <v>223.25</v>
       </c>
-      <c r="M16" s="13">
+      <c r="O16" s="13">
         <v>219.14</v>
       </c>
-      <c r="N16" s="13">
+      <c r="P16" s="13">
         <v>219.14</v>
       </c>
-      <c r="O16" s="13">
+      <c r="Q16" s="13">
         <v>219.3</v>
       </c>
-      <c r="P16" s="13">
+      <c r="R16" s="13">
         <v>222.79</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="S16" s="13">
         <v>221.16</v>
       </c>
-      <c r="R16" s="13">
+      <c r="T16" s="13">
         <v>220.66</v>
       </c>
-      <c r="S16" s="13">
+      <c r="U16" s="13">
         <v>222.06</v>
       </c>
-      <c r="T16" s="13">
+      <c r="V16" s="13">
         <v>218.71</v>
       </c>
-      <c r="U16" s="13">
+      <c r="W16" s="13">
         <v>216.74</v>
       </c>
-      <c r="V16" s="13">
+      <c r="X16" s="13">
         <v>216.04</v>
       </c>
-      <c r="W16" s="13">
+      <c r="Y16" s="13">
         <v>210.69</v>
       </c>
-      <c r="X16" s="13">
+      <c r="Z16" s="13">
         <v>210.69</v>
       </c>
-      <c r="Y16" s="13">
+      <c r="AA16" s="13">
         <v>198</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="AB16" s="13">
         <v>196.74</v>
       </c>
-      <c r="AA16" s="13">
+      <c r="AC16" s="13">
         <v>192.56</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AD16" s="13">
         <v>192.23</v>
       </c>
-      <c r="AC16" s="13">
+      <c r="AE16" s="13">
         <v>191.19</v>
       </c>
-      <c r="AD16" s="13">
+      <c r="AF16" s="13">
         <v>193.62</v>
       </c>
-      <c r="AE16" s="13">
+      <c r="AG16" s="13">
         <v>190.75</v>
       </c>
-      <c r="AF16" s="13">
+      <c r="AH16" s="13">
         <v>189.06</v>
       </c>
-      <c r="AG16" s="13">
+      <c r="AI16" s="13">
         <v>182.73</v>
       </c>
-      <c r="AH16" s="13">
+      <c r="AJ16" s="13">
         <v>182.73</v>
       </c>
-      <c r="AI16" s="13">
+      <c r="AK16" s="13">
         <v>177.92</v>
       </c>
-      <c r="AJ16" s="13">
+      <c r="AL16" s="13">
         <v>179.16</v>
       </c>
-      <c r="AK16" s="13">
+      <c r="AM16" s="13">
         <v>179.34</v>
       </c>
-      <c r="AL16" s="13">
+      <c r="AN16" s="13">
         <v>176.5</v>
       </c>
-      <c r="AM16" s="13">
+      <c r="AO16" s="13">
         <v>176.5</v>
       </c>
-      <c r="AN16" s="13">
+      <c r="AP16" s="13">
         <v>175.93</v>
       </c>
-      <c r="AO16" s="13">
+      <c r="AQ16" s="13">
         <v>174.51</v>
       </c>
-      <c r="AP16" s="13">
+      <c r="AR16" s="13">
         <v>173.91</v>
       </c>
-      <c r="AQ16" s="13">
+      <c r="AS16" s="13">
         <v>177.1</v>
       </c>
-      <c r="AR16" s="13">
+      <c r="AT16" s="13">
         <v>178.24</v>
       </c>
-      <c r="AS16" s="13">
+      <c r="AU16" s="13">
         <v>176.52</v>
       </c>
-      <c r="AT16" s="13">
+      <c r="AV16" s="13">
         <v>178.27</v>
       </c>
-      <c r="AU16" s="13">
+      <c r="AW16" s="13">
         <v>175.29</v>
       </c>
-      <c r="AV16" s="13">
+      <c r="AX16" s="13">
         <v>175.34</v>
       </c>
-      <c r="AW16" s="13">
+      <c r="AY16" s="13">
         <v>174.41</v>
       </c>
-      <c r="AX16" s="13">
+      <c r="AZ16" s="13">
         <v>176.22</v>
       </c>
-      <c r="AY16" s="13">
+      <c r="BA16" s="13">
         <v>174</v>
       </c>
-      <c r="AZ16" s="13">
+      <c r="BB16" s="13">
         <v>176.35</v>
       </c>
-      <c r="BA16" s="13">
+      <c r="BC16" s="13">
         <v>177.71</v>
       </c>
-      <c r="BB16" s="13">
+      <c r="BD16" s="13">
         <v>180.08</v>
       </c>
-      <c r="BC16" s="13">
+      <c r="BE16" s="13">
         <v>181.96</v>
       </c>
-      <c r="BD16" s="13">
+      <c r="BF16" s="13">
         <v>182.9</v>
       </c>
-      <c r="BE16" s="13">
+      <c r="BG16" s="13">
         <v>181.86</v>
       </c>
-      <c r="BF16" s="29">
+      <c r="BH16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BG16" s="13">
+      <c r="BI16" s="13">
         <v>181.07</v>
       </c>
-      <c r="BH16" s="13">
+      <c r="BJ16" s="13">
         <v>182.56</v>
       </c>
-      <c r="BI16" s="29">
+      <c r="BK16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BJ16" s="13">
+      <c r="BL16" s="13">
         <v>178.86</v>
       </c>
-      <c r="BK16" s="13">
+      <c r="BM16" s="13">
         <v>180.16</v>
       </c>
-      <c r="BL16" s="13">
+      <c r="BN16" s="13">
         <v>179.56</v>
       </c>
-      <c r="BM16" s="13">
+      <c r="BO16" s="13">
         <v>176.55</v>
       </c>
-      <c r="BN16" s="13">
+      <c r="BP16" s="13">
         <f t="shared" si="0"/>
-        <v>673.09559999999999</v>
-      </c>
-      <c r="BO16" s="13">
+        <v>1413.1220000000008</v>
+      </c>
+      <c r="BQ16" s="13">
         <f t="shared" si="2"/>
-        <v>551.19000000000005</v>
-      </c>
-      <c r="BP16" s="13">
+        <v>997.45</v>
+      </c>
+      <c r="BR16" s="13">
         <f t="shared" si="6"/>
-        <v>-121.90559999999994</v>
-      </c>
-      <c r="BQ16" s="13">
-        <f>((BE16-H16)/H16)*100</f>
-        <v>-1.0177978555488905</v>
-      </c>
-      <c r="BR16">
+        <v>-415.67200000000071</v>
+      </c>
+      <c r="BS16" s="13">
+        <f>((BG16-H16)/H16)*100</f>
+        <v>-8.8375357160759904</v>
+      </c>
+      <c r="BT16">
         <v>1864</v>
       </c>
-      <c r="BS16">
+      <c r="BU16">
         <v>177.19</v>
       </c>
-      <c r="BT16" s="15">
+      <c r="BV16" s="15">
         <f t="shared" si="7"/>
-        <v>-121.90559999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>-415.67200000000071</v>
+      </c>
+    </row>
+    <row r="17" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>5134135</v>
       </c>
@@ -3744,7 +3852,7 @@
         <v>לשמור</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F17" s="4">
         <v>46021</v>
@@ -3756,64 +3864,68 @@
         <v>159.65</v>
       </c>
       <c r="I17" s="13">
+        <v>199.37</v>
+      </c>
+      <c r="J17" s="13">
+        <v>199.37</v>
+      </c>
+      <c r="K17" s="13">
         <v>194.88</v>
-      </c>
-      <c r="J17" s="13">
-        <v>189.51</v>
-      </c>
-      <c r="K17" s="13">
-        <v>189.51</v>
       </c>
       <c r="L17" s="13">
         <v>189.51</v>
       </c>
       <c r="M17" s="13">
+        <v>189.51</v>
+      </c>
+      <c r="N17" s="13">
+        <v>189.51</v>
+      </c>
+      <c r="O17" s="13">
         <v>185.52</v>
       </c>
-      <c r="N17" s="13">
+      <c r="P17" s="13">
         <v>185.52</v>
-      </c>
-      <c r="O17" s="13">
-        <v>178.98</v>
-      </c>
-      <c r="P17" s="13">
-        <v>178.98</v>
       </c>
       <c r="Q17" s="13">
         <v>178.98</v>
       </c>
       <c r="R17" s="13">
-        <v>170.7</v>
+        <v>178.98</v>
       </c>
       <c r="S17" s="13">
-        <v>170.7</v>
+        <v>178.98</v>
       </c>
       <c r="T17" s="13">
         <v>170.7</v>
       </c>
       <c r="U17" s="13">
+        <v>170.7</v>
+      </c>
+      <c r="V17" s="13">
+        <v>170.7</v>
+      </c>
+      <c r="W17" s="13">
         <v>170.45</v>
-      </c>
-      <c r="V17" s="13">
-        <v>160.84</v>
-      </c>
-      <c r="W17" s="13">
-        <v>160.84</v>
       </c>
       <c r="X17" s="13">
         <v>160.84</v>
       </c>
       <c r="Y17" s="13">
+        <v>160.84</v>
+      </c>
+      <c r="Z17" s="13">
+        <v>160.84</v>
+      </c>
+      <c r="AA17" s="13">
         <v>159.02000000000001</v>
       </c>
-      <c r="Z17" s="13">
+      <c r="AB17" s="13">
         <v>159.65</v>
       </c>
-      <c r="AA17" s="13">
+      <c r="AC17" s="13">
         <v>159.65</v>
       </c>
-      <c r="AB17" s="13"/>
-      <c r="AC17" s="13"/>
       <c r="AD17" s="13"/>
       <c r="AE17" s="13"/>
       <c r="AF17" s="13"/>
@@ -3842,36 +3954,38 @@
       <c r="BC17" s="13"/>
       <c r="BD17" s="13"/>
       <c r="BE17" s="13"/>
-      <c r="BF17" s="29"/>
+      <c r="BF17" s="13"/>
       <c r="BG17" s="13"/>
-      <c r="BH17" s="13"/>
-      <c r="BI17" s="29"/>
+      <c r="BH17" s="29"/>
+      <c r="BI17" s="13"/>
       <c r="BJ17" s="13"/>
-      <c r="BK17" s="13"/>
+      <c r="BK17" s="29"/>
       <c r="BL17" s="13"/>
       <c r="BM17" s="13"/>
-      <c r="BN17" s="13">
+      <c r="BN17" s="13"/>
+      <c r="BO17" s="13"/>
+      <c r="BP17" s="13">
         <f t="shared" si="0"/>
         <v>957.9</v>
       </c>
-      <c r="BO17" s="13">
+      <c r="BQ17" s="13">
         <f t="shared" si="2"/>
         <v>957.9</v>
       </c>
-      <c r="BP17" s="13">
-        <f t="shared" ref="BP17" si="8">(BO17-BN17)</f>
+      <c r="BR17" s="13">
+        <f t="shared" ref="BR17" si="8">(BQ17-BP17)</f>
         <v>0</v>
       </c>
-      <c r="BQ17" s="13">
-        <f>((BE17-H17)/H17)*100</f>
+      <c r="BS17" s="13">
+        <f>((BG17-H17)/H17)*100</f>
         <v>-100</v>
       </c>
-      <c r="BT17" s="15">
+      <c r="BV17" s="15">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1168723</v>
       </c>
@@ -3888,7 +4002,7 @@
         <v>לשמור</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F18" s="4">
         <v>46019</v>
@@ -3900,70 +4014,74 @@
         <v>1434</v>
       </c>
       <c r="I18" s="13">
+        <v>1785</v>
+      </c>
+      <c r="J18" s="13">
+        <v>1785</v>
+      </c>
+      <c r="K18" s="13">
         <v>1828</v>
       </c>
-      <c r="J18" s="13">
+      <c r="L18" s="13">
         <v>1811</v>
       </c>
-      <c r="K18" s="13">
+      <c r="M18" s="13">
         <v>1825</v>
       </c>
-      <c r="L18" s="13">
+      <c r="N18" s="13">
         <v>1831</v>
       </c>
-      <c r="M18" s="13">
+      <c r="O18" s="13">
         <v>1799</v>
       </c>
-      <c r="N18" s="13">
+      <c r="P18" s="13">
         <v>1757</v>
       </c>
-      <c r="O18" s="13">
+      <c r="Q18" s="13">
         <v>1698</v>
       </c>
-      <c r="P18" s="13">
+      <c r="R18" s="13">
         <v>1694</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="S18" s="13">
         <v>1671</v>
       </c>
-      <c r="R18" s="13">
+      <c r="T18" s="13">
         <v>1660</v>
       </c>
-      <c r="S18" s="13">
+      <c r="U18" s="13">
         <v>1660</v>
       </c>
-      <c r="T18" s="13">
+      <c r="V18" s="13">
         <v>1646</v>
       </c>
-      <c r="U18" s="13">
+      <c r="W18" s="13">
         <v>1648</v>
       </c>
-      <c r="V18" s="13">
+      <c r="X18" s="13">
         <v>1614</v>
       </c>
-      <c r="W18" s="13">
+      <c r="Y18" s="13">
         <v>1626</v>
       </c>
-      <c r="X18" s="13">
+      <c r="Z18" s="13">
         <v>1587</v>
       </c>
-      <c r="Y18" s="13">
+      <c r="AA18" s="13">
         <v>1548</v>
       </c>
-      <c r="Z18" s="13">
+      <c r="AB18" s="13">
         <v>1500</v>
       </c>
-      <c r="AA18" s="13">
+      <c r="AC18" s="13">
         <v>1491</v>
       </c>
-      <c r="AB18" s="13">
+      <c r="AD18" s="13">
         <v>1444</v>
       </c>
-      <c r="AC18" s="13">
+      <c r="AE18" s="13">
         <v>1431</v>
       </c>
-      <c r="AD18" s="13"/>
-      <c r="AE18" s="13"/>
       <c r="AF18" s="13"/>
       <c r="AG18" s="13"/>
       <c r="AH18" s="13"/>
@@ -3988,66 +4106,68 @@
       <c r="BA18" s="13"/>
       <c r="BB18" s="13"/>
       <c r="BC18" s="13"/>
-      <c r="BD18" s="13">
+      <c r="BD18" s="13"/>
+      <c r="BE18" s="13"/>
+      <c r="BF18" s="13">
         <v>1788</v>
       </c>
-      <c r="BE18" s="13">
+      <c r="BG18" s="13">
         <v>1788</v>
       </c>
-      <c r="BF18" s="29">
+      <c r="BH18" s="29">
         <v>1780</v>
       </c>
-      <c r="BG18" s="13">
+      <c r="BI18" s="13">
         <v>1814</v>
       </c>
-      <c r="BH18" s="13">
+      <c r="BJ18" s="13">
         <v>1794</v>
       </c>
-      <c r="BI18" s="29">
+      <c r="BK18" s="29">
         <v>1780</v>
       </c>
-      <c r="BJ18" s="13">
+      <c r="BL18" s="13">
         <v>1772</v>
       </c>
-      <c r="BK18" s="13">
+      <c r="BM18" s="13">
         <v>1798</v>
       </c>
-      <c r="BL18" s="13">
+      <c r="BN18" s="13">
         <v>1806</v>
       </c>
-      <c r="BM18" s="13">
+      <c r="BO18" s="13">
         <v>1801</v>
       </c>
-      <c r="BN18" s="13">
+      <c r="BP18" s="13">
         <f t="shared" si="0"/>
         <v>292.79999999999995</v>
       </c>
-      <c r="BO18" s="13">
+      <c r="BQ18" s="13">
         <f t="shared" si="2"/>
         <v>645.29999999999995</v>
       </c>
-      <c r="BP18" s="13">
+      <c r="BR18" s="13">
         <f t="shared" si="6"/>
         <v>352.5</v>
       </c>
-      <c r="BQ18" s="13">
-        <f>((BE18-H18)/H18)*100</f>
+      <c r="BS18" s="13">
+        <f>((BG18-H18)/H18)*100</f>
         <v>24.686192468619247</v>
       </c>
-      <c r="BR18">
+      <c r="BT18">
         <v>100</v>
       </c>
-      <c r="BS18">
+      <c r="BU18">
         <v>1786.5</v>
       </c>
-      <c r="BT18" s="15">
+      <c r="BV18" s="15">
         <f t="shared" si="7"/>
         <v>352.5</v>
       </c>
     </row>
-    <row r="19" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <v>1146604</v>
+        <v>1122654</v>
       </c>
       <c r="B19" s="17">
         <f>GEMINI!L19</f>
@@ -4059,22 +4179,26 @@
       </c>
       <c r="D19" s="6" t="str">
         <f>IF(I19&lt;GEMINI!L19,"למכור בהפסד",IF(I19&gt;GEMINI!M19,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="F19" s="4">
-        <v>46016</v>
+        <v>46052</v>
       </c>
       <c r="G19" s="27">
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="H19" s="13">
-        <v>6548</v>
-      </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
+        <v>110</v>
+      </c>
+      <c r="I19" s="13">
+        <v>132.6</v>
+      </c>
+      <c r="J19" s="13">
+        <v>132.6</v>
+      </c>
       <c r="K19" s="13"/>
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
@@ -4089,23 +4213,23 @@
       <c r="V19" s="13"/>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
-      <c r="Y19" s="13">
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="13">
         <v>6461</v>
       </c>
-      <c r="Z19" s="13">
+      <c r="AB19" s="13">
         <v>6503</v>
       </c>
-      <c r="AA19" s="13">
+      <c r="AC19" s="13">
         <v>6535</v>
       </c>
-      <c r="AB19" s="13">
+      <c r="AD19" s="13">
         <v>6532</v>
       </c>
-      <c r="AC19" s="13">
+      <c r="AE19" s="13">
         <v>6515</v>
       </c>
-      <c r="AD19" s="13"/>
-      <c r="AE19" s="13"/>
       <c r="AF19" s="13"/>
       <c r="AG19" s="13"/>
       <c r="AH19" s="13"/>
@@ -4132,33 +4256,35 @@
       <c r="BC19" s="13"/>
       <c r="BD19" s="13"/>
       <c r="BE19" s="13"/>
-      <c r="BF19" s="29"/>
+      <c r="BF19" s="13"/>
       <c r="BG19" s="13"/>
-      <c r="BH19" s="13"/>
-      <c r="BI19" s="29"/>
+      <c r="BH19" s="29"/>
+      <c r="BI19" s="13"/>
       <c r="BJ19" s="13"/>
-      <c r="BK19" s="13"/>
+      <c r="BK19" s="29"/>
       <c r="BL19" s="13"/>
       <c r="BM19" s="13"/>
-      <c r="BN19" s="13">
+      <c r="BN19" s="13"/>
+      <c r="BO19" s="13"/>
+      <c r="BP19" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BO19" s="13">
+        <v>517</v>
+      </c>
+      <c r="BQ19" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="BP19" s="13"/>
-      <c r="BQ19" s="13"/>
-      <c r="BR19">
+        <v>517</v>
+      </c>
+      <c r="BR19" s="13"/>
+      <c r="BS19" s="13"/>
+      <c r="BT19">
         <v>7</v>
       </c>
-      <c r="BS19">
+      <c r="BU19">
         <v>6461</v>
       </c>
-      <c r="BT19" s="15"/>
-    </row>
-    <row r="20" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BV19" s="15"/>
+    </row>
+    <row r="20" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1144807</v>
       </c>
@@ -4178,33 +4304,15 @@
       <c r="F20" s="28"/>
       <c r="G20" s="27"/>
       <c r="H20" s="13"/>
-      <c r="I20" s="13">
-        <v>3159</v>
-      </c>
-      <c r="J20" s="13">
-        <v>3159</v>
-      </c>
-      <c r="K20" s="13">
-        <v>3159</v>
-      </c>
-      <c r="L20" s="13">
-        <v>3159</v>
-      </c>
-      <c r="M20" s="13">
-        <v>3159</v>
-      </c>
-      <c r="N20" s="13">
-        <v>3159</v>
-      </c>
-      <c r="O20" s="13">
-        <v>3159</v>
-      </c>
-      <c r="P20" s="13">
-        <v>3159</v>
-      </c>
-      <c r="Q20" s="13">
-        <v>3159</v>
-      </c>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
       <c r="S20" s="13"/>
       <c r="T20" s="13"/>
@@ -4245,28 +4353,30 @@
       <c r="BC20" s="13"/>
       <c r="BD20" s="13"/>
       <c r="BE20" s="13"/>
-      <c r="BF20" s="29"/>
+      <c r="BF20" s="13"/>
       <c r="BG20" s="13"/>
-      <c r="BH20" s="13"/>
-      <c r="BI20" s="29"/>
+      <c r="BH20" s="29"/>
+      <c r="BI20" s="13"/>
       <c r="BJ20" s="13"/>
-      <c r="BK20" s="13"/>
+      <c r="BK20" s="29"/>
       <c r="BL20" s="13"/>
       <c r="BM20" s="13"/>
-      <c r="BN20" s="13">
-        <f>(G20*H20)/100-BT20</f>
+      <c r="BN20" s="13"/>
+      <c r="BO20" s="13"/>
+      <c r="BP20" s="13">
+        <f>(G20*H20)/100-BV20</f>
         <v>0</v>
       </c>
-      <c r="BO20" s="13">
+      <c r="BQ20" s="13">
         <f>(G20*H20)/100</f>
         <v>0</v>
       </c>
-      <c r="BP20" s="13"/>
-      <c r="BQ20" s="13"/>
-      <c r="BT20" s="15"/>
-    </row>
-    <row r="21" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:72" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BR20" s="13"/>
+      <c r="BS20" s="13"/>
+      <c r="BV20" s="15"/>
+    </row>
+    <row r="21" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4324,21 +4434,23 @@
       <c r="BC22" s="13"/>
       <c r="BD22" s="13"/>
       <c r="BE22" s="13"/>
-      <c r="BF22" s="29"/>
+      <c r="BF22" s="13"/>
       <c r="BG22" s="13"/>
-      <c r="BH22" s="13"/>
-      <c r="BI22" s="29"/>
+      <c r="BH22" s="29"/>
+      <c r="BI22" s="13"/>
       <c r="BJ22" s="13"/>
-      <c r="BK22" s="13"/>
+      <c r="BK22" s="29"/>
       <c r="BL22" s="13"/>
       <c r="BM22" s="13"/>
       <c r="BN22" s="13"/>
       <c r="BO22" s="13"/>
       <c r="BP22" s="13"/>
       <c r="BQ22" s="13"/>
-      <c r="BT22" s="15"/>
-    </row>
-    <row r="23" spans="1:72" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BR22" s="13"/>
+      <c r="BS22" s="13"/>
+      <c r="BV22" s="15"/>
+    </row>
+    <row r="23" spans="1:74" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4349,110 +4461,110 @@
       <c r="H23" s="13"/>
       <c r="I23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19)/100</f>
-        <v>16104.2896</v>
+        <v>13728.55</v>
       </c>
       <c r="J23" s="23">
         <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19)/100</f>
-        <v>15918.465600000001</v>
+        <v>13728.55</v>
       </c>
       <c r="K23" s="23">
         <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19)/100</f>
-        <v>15780.058000000001</v>
+        <v>13844.2896</v>
       </c>
       <c r="L23" s="23">
         <f>(L2*G2+G3*L3+L4*G4+G5*L5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+L13*G13+G14*L14+L15*G15+G16*L16+G17*L17+L18*G18+G19*L19)/100</f>
-        <v>15786.563599999999</v>
+        <v>13659.785600000001</v>
       </c>
       <c r="M23" s="23">
         <f>(M2*G2+G3*M3+M4*G4+G5*M5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+M13*G13+G14*M14+M15*G15+G16*M16+G17*M17+M18*G18+G19*M19)/100</f>
-        <v>15432.864</v>
+        <v>13683.918</v>
       </c>
       <c r="N23" s="23">
         <f>(N2*G2+G3*N3+N4*G4+G5*N5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+N13*G13+G14*N14+N15*G15+G16*N16+G17*N17+N18*G18+G19*N19)/100</f>
-        <v>15138.76</v>
+        <v>13839.923600000002</v>
       </c>
       <c r="O23" s="23">
         <f>(O2*G2+G3*O3+O4*G4+G5*O5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+O13*G13+G14*O14+O15*G15+G16*O16+G17*O17+O18*G18+G19*O19)/100</f>
-        <v>14857.142</v>
+        <v>13475.503999999999</v>
       </c>
       <c r="P23" s="23">
         <f>(P2*G2+G3*P3+P4*G4+G5*P5+G6*P6+G7*P7+G8*P8+G9*P9+G10*P10+G11*P11+G12*P12+P13*G13+G14*P14+P15*G15+G16*P16+G17*P17+P18*G18+G19*P19)/100</f>
-        <v>15009.357599999999</v>
+        <v>13192.96</v>
       </c>
       <c r="Q23" s="23">
-        <f>(Q3*G3+G4*Q4+Q5*G5+G6*Q6+G7*Q7+G8*Q8+G9*Q9+G10*Q10+G11*Q11+G12*Q12+G14*Q14+Q15*G15+G16*Q16+Q17*G17+G18*Q18+G19*Q19)/100</f>
-        <v>14094.97</v>
+        <f>(Q2*G2+G3*Q3+Q4*G4+G5*Q5+G6*Q6+G7*Q7+G8*Q8+G9*Q9+G10*Q10+G11*Q11+G12*Q12+Q13*G13+G14*Q14+Q15*G15+G16*Q16+G17*Q17+Q18*G18+G19*Q19)/100</f>
+        <v>12923.761999999999</v>
       </c>
       <c r="R23" s="23">
-        <f>(R3*G3+G4*R4+R5*G5+G6*R6+G7*R7+G8*R8+G9*R9+G10*R10+G11*R11+G12*R12+G14*R14+R15*G15+G16*R16+R17*G17+G18*R18+G19*R19)/100</f>
-        <v>13839.4576</v>
+        <f>(R2*G2+G3*R3+R4*G4+G5*R5+G6*R6+G7*R7+G8*R8+G9*R9+G10*R10+G11*R11+G12*R12+R13*G13+G14*R14+R15*G15+G16*R16+G17*R17+R18*G18+G19*R19)/100</f>
+        <v>13102.8776</v>
       </c>
       <c r="S23" s="23">
         <f>(S3*G3+G4*S4+S5*G5+G6*S6+G7*S7+G8*S8+G9*S9+G10*S10+G11*S11+G12*S12+G14*S14+S15*G15+G16*S16+S17*G17+G18*S18+G19*S19)/100</f>
-        <v>13855.757600000001</v>
+        <v>12191.99</v>
       </c>
       <c r="T23" s="23">
         <f>(T3*G3+G4*T4+T5*G5+G6*T6+G7*T7+G8*T8+G9*T9+G10*T10+G11*T11+G12*T12+G14*T14+T15*G15+G16*T16+T17*G17+G18*T18+G19*T19)/100</f>
-        <v>13797.417600000001</v>
+        <v>11970.357599999999</v>
       </c>
       <c r="U23" s="23">
         <f>(U3*G3+G4*U4+U5*G5+G6*U6+G7*U7+G8*U8+G9*U9+G10*U10+G11*U11+G12*U12+G14*U14+U15*G15+G16*U16+U17*G17+G18*U18+G19*U19)/100</f>
-        <v>13184.28</v>
+        <v>11989.4576</v>
       </c>
       <c r="V23" s="23">
         <f>(V3*G3+G4*V4+V5*G5+G6*V6+G7*V7+G8*V8+G9*V9+G10*V10+G11*V11+G12*V12+G14*V14+V15*G15+G16*V16+V17*G17+G18*V18+G19*V19)/100</f>
-        <v>12980.185600000001</v>
+        <v>11896.177600000001</v>
       </c>
       <c r="W23" s="23">
         <f>(W3*G3+G4*W4+W5*G5+G6*W6+G7*W7+G8*W8+G9*W9+G10*W10+G11*W11+G12*W12+G14*W14+W15*G15+G16*W16+W17*G17+G18*W18+G19*W19)/100</f>
-        <v>11213.0556</v>
+        <v>11552.98</v>
       </c>
       <c r="X23" s="23">
-        <f>(X5*G5+G6*X6+X7*G7+G8*X8+G9*X9+G10*X10+G11*X11+G12*X12+G14*X14+G20*X20+G15*X15+X16*G16+G17*X17+X18*G18+G19*X19)/100</f>
-        <v>10380.919599999999</v>
-      </c>
-      <c r="Y23" s="23" t="e">
-        <f>(Y5*G5+G7*Y7+Y8*G8+G9*Y9+#REF!*#REF!+G10*Y10+G11*Y11+G12*Y12+G14*Y14+G19*Y19+G20*Y20+Y6*G6+G15*Y15+#REF!*#REF!+G16*Y16+G17*Y17+Y18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*Y3+#REF!*#REF!)/100</f>
-        <v>#REF!</v>
-      </c>
-      <c r="Z23" s="23" t="e">
-        <f>(Z5*G5+G7*Z7+Z8*G8+G9*Z9+#REF!*#REF!+G10*Z10+G11*Z11+G12*Z12+G14*Z14+G19*Z19+G20*Z20+Z6*G6+G15*Z15+#REF!*#REF!+G16*Z16+G17*Z17+Z18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*Z3+#REF!*#REF!)/100</f>
-        <v>#REF!</v>
+        <f>(X3*G3+G4*X4+X5*G5+G6*X6+G7*X7+G8*X8+G9*X9+G10*X10+G11*X11+G12*X12+G14*X14+X15*G15+G16*X16+X17*G17+G18*X18+G19*X19)/100</f>
+        <v>11467.277599999999</v>
+      </c>
+      <c r="Y23" s="23">
+        <f>(Y3*G3+G4*Y4+Y5*G5+G6*Y6+G7*Y7+G8*Y8+G9*Y9+G10*Y10+G11*Y11+G12*Y12+G14*Y14+Y15*G15+G16*Y16+Y17*G17+G18*Y18+G19*Y19)/100</f>
+        <v>10332.035599999999</v>
+      </c>
+      <c r="Z23" s="23">
+        <f>(Z5*G5+G6*Z6+Z7*G7+G8*Z8+G9*Z9+G10*Z10+G11*Z11+G12*Z12+G14*Z14+G20*Z20+G15*Z15+Z16*G16+G17*Z17+Z18*G18+G19*Z19)/100</f>
+        <v>9234.9995999999992</v>
       </c>
       <c r="AA23" s="23" t="e">
         <f>(AA5*G5+G7*AA7+AA8*G8+G9*AA9+#REF!*#REF!+G10*AA10+G11*AA11+G12*AA12+G14*AA14+G19*AA19+G20*AA20+AA6*G6+G15*AA15+#REF!*#REF!+G16*AA16+G17*AA17+AA18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AA3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AB23" s="23" t="e">
-        <f>(AB5*G5+G7*AB7+AB8*G8+G9*AB9+#REF!*#REF!+G10*AB10+G11*AB11+G12*AB12+G14*AB14+G19*AB19+G20*AB20+AB6*G6+G15*AB15+#REF!*#REF!+G16*AB16+G18*AB18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AB3+#REF!*#REF!+G4*AB4)/100</f>
+        <f>(AB5*G5+G7*AB7+AB8*G8+G9*AB9+#REF!*#REF!+G10*AB10+G11*AB11+G12*AB12+G14*AB14+G19*AB19+G20*AB20+AB6*G6+G15*AB15+#REF!*#REF!+G16*AB16+G17*AB17+AB18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AB3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AC23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AC3*G3+#REF!*#REF!+G4*AC4+G5*AC5+G7*AC7+G8*AC8+G9*AC9+#REF!*#REF!+G10*AC10+AC11*G11+G12*AC12+AC14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AC20+AC6*G6+#REF!*#REF!+G16*AC16+G18*AC18+G19*AC19)/100</f>
+        <f>(AC5*G5+G7*AC7+AC8*G8+G9*AC9+#REF!*#REF!+G10*AC10+G11*AC11+G12*AC12+G14*AC14+G19*AC19+G20*AC20+AC6*G6+G15*AC15+#REF!*#REF!+G16*AC16+G17*AC17+AC18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AC3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AD23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AD3*G3+#REF!*#REF!+G4*AD4+G5*AD5+G7*AD7+G8*AD8+G9*AD9+#REF!*#REF!+G10*AD10+AD11*G11+G12*AD12+AD14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AD20+AD6*G6+#REF!*#REF!+G16*AD16+G18*AD18+G19*AD19)/100</f>
+        <f>(AD5*G5+G7*AD7+AD8*G8+G9*AD9+#REF!*#REF!+G10*AD10+G11*AD11+G12*AD12+G14*AD14+G19*AD19+G20*AD20+AD6*G6+G15*AD15+#REF!*#REF!+G16*AD16+G18*AD18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AD3+#REF!*#REF!+G4*AD4)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AE23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AE3*G3+#REF!*#REF!+G4*AE4+G5*AE5+AE7*G7+AE8*G8+AE9*G9+#REF!*#REF!+G10*AE10+AE11*G11+G12*AE12+AE14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AE20+G6*AE6+#REF!*#REF!+G16*AE16+G18*AE18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AE3*G3+#REF!*#REF!+G4*AE4+G5*AE5+G7*AE7+G8*AE8+G9*AE9+#REF!*#REF!+G10*AE10+AE11*G11+G12*AE12+AE14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AE20+AE6*G6+#REF!*#REF!+G16*AE16+G18*AE18+G19*AE19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AF23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AF3*G3+#REF!*#REF!+G4*AF4+G5*AF5+AF7*G7+AF8*G8+AF9*G9+#REF!*#REF!+G10*AF10+AF11*G11+G12*AF12+AF14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AF20+G6*AF6+#REF!*#REF!+G16*AF16+G18*AF18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AF3*G3+#REF!*#REF!+G4*AF4+G5*AF5+G7*AF7+G8*AF8+G9*AF9+#REF!*#REF!+G10*AF10+AF11*G11+G12*AF12+AF14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AF20+AF6*G6+#REF!*#REF!+G16*AF16+G18*AF18+G19*AF19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AG23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AG3*G3+#REF!*#REF!+G4*AG4+G8*AG8+AG9*G9+#REF!*#REF!+AG10*G10+G11*AG11+G14*AG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AG6+#REF!*#REF!+G16*AG16+G18*AG18+G7*AG7+G5*AG5+G12*AG12+G20*AG20)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AG3*G3+#REF!*#REF!+G4*AG4+G5*AG5+AG7*G7+AG8*G8+AG9*G9+#REF!*#REF!+G10*AG10+AG11*G11+G12*AG12+AG14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AG20+G6*AG6+#REF!*#REF!+G16*AG16+G18*AG18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AH23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AH3*G3+#REF!*#REF!+G4*AH4+G8*AH8+AH9*G9+#REF!*#REF!+AH10*G10+G11*AH11+G14*AH14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AH6+#REF!*#REF!+G16*AH16+G18*AH18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AH3*G3+#REF!*#REF!+G4*AH4+G5*AH5+AH7*G7+AH8*G8+AH9*G9+#REF!*#REF!+G10*AH10+AH11*G11+G12*AH12+AH14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AH20+G6*AH6+#REF!*#REF!+G16*AH16+G18*AH18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AI23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AI3*G3+#REF!*#REF!+G4*AI4+G8*AI8+G9*AI9+#REF!*#REF!+G10*AI10+AI11*G11+AI14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AI6*G6+#REF!*#REF!+G16*AI16+G18*AI18+G19*AI19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AI3*G3+#REF!*#REF!+G4*AI4+G8*AI8+AI9*G9+#REF!*#REF!+AI10*G10+G11*AI11+G14*AI14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AI6+#REF!*#REF!+G16*AI16+G18*AI18+G7*AI7+G5*AI5+G12*AI12+G20*AI20)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AJ23" s="23" t="e">
@@ -4460,15 +4572,15 @@
         <v>#REF!</v>
       </c>
       <c r="AK23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AK3*G3+#REF!*#REF!+G4*AK4+G8*AK8+AK9*G9+#REF!*#REF!+AK10*G10+G11*AK11+G14*AK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AK6+#REF!*#REF!+G16*AK16+G18*AK18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AK3*G3+#REF!*#REF!+G4*AK4+G8*AK8+G9*AK9+#REF!*#REF!+G10*AK10+AK11*G11+AK14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AK6*G6+#REF!*#REF!+G16*AK16+G18*AK18+G19*AK19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AL23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AL3*G3+#REF!*#REF!+G4*AL4+G8*AL8+AL9*G9+AL10*G10+AL11*G11+G14*AL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AL6+#REF!*#REF!+G16*AL16+G18*AL18+G19*AL19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AL3*G3+#REF!*#REF!+G4*AL4+G8*AL8+AL9*G9+#REF!*#REF!+AL10*G10+G11*AL11+G14*AL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AL6+#REF!*#REF!+G16*AL16+G18*AL18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AM23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AM3*G3+#REF!*#REF!+G4*AM4+G8*AM8+AM9*G9+AM10*G10+AM11*G11+G14*AM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AM6+#REF!*#REF!+G16*AM16+G18*AM18+G19*AM19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AM3*G3+#REF!*#REF!+G4*AM4+G8*AM8+AM9*G9+#REF!*#REF!+AM10*G10+G11*AM11+G14*AM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AM6+#REF!*#REF!+G16*AM16+G18*AM18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AN23" s="23" t="e">
@@ -4484,23 +4596,23 @@
         <v>#REF!</v>
       </c>
       <c r="AQ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AQ3*G3+#REF!*#REF!+G4*AQ4+G8*AQ8+AQ9*G9+AQ10*G10+AQ11*G11+G14*AQ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AQ6+#REF!*#REF!+G16*AQ16+G18*AQ18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AQ3*G3+#REF!*#REF!+G4*AQ4+G8*AQ8+AQ9*G9+AQ10*G10+AQ11*G11+G14*AQ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AQ6+#REF!*#REF!+G16*AQ16+G18*AQ18+G19*AQ19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AR23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AR3*G3+#REF!*#REF!+G4*AR4+G8*AR8+AR10*G10+AR11*G11+G14*AR14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AR6+#REF!*#REF!+G16*AR16+G18*AR18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AR3*G3+#REF!*#REF!+G4*AR4+G8*AR8+AR9*G9+AR10*G10+AR11*G11+G14*AR14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AR6+#REF!*#REF!+G16*AR16+G18*AR18+G19*AR19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AS23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AS3*G3+#REF!*#REF!+G4*AS4+G8*AS8+G10*AS10+AS11*G11+AS14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AS6*G6+#REF!*#REF!+G16*AS16+G18*AS18+G19*AS19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AS3*G3+#REF!*#REF!+G4*AS4+G8*AS8+AS9*G9+AS10*G10+AS11*G11+G14*AS14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AS6+#REF!*#REF!+G16*AS16+G18*AS18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AT23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AT3*G3+#REF!*#REF!+G4*AT4+G10*AT10+AT11*G11+AT14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AT6*G6+#REF!*#REF!+G16*AT16+G18*AT18+G19*AT19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AT3*G3+#REF!*#REF!+G4*AT4+G8*AT8+AT10*G10+AT11*G11+G14*AT14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AT6+#REF!*#REF!+G16*AT16+G18*AT18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AU23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AU3*G3+#REF!*#REF!+G4*AU4+G10*AU10+AU11*G11+AU14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AU6*G6+#REF!*#REF!+G16*AU16+G18*AU18+G19*AU19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AU3*G3+#REF!*#REF!+G4*AU4+G8*AU8+G10*AU10+AU11*G11+AU14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AU6*G6+#REF!*#REF!+G16*AU16+G18*AU18+G19*AU19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AV23" s="23" t="e">
@@ -4508,11 +4620,11 @@
         <v>#REF!</v>
       </c>
       <c r="AW23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AW3*G3+#REF!*#REF!+G4*AW4+G10*AW10+AW11*G11+AW14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AW6*G6+G16*AW16+G18*AW18+G19*AW19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AW3*G3+#REF!*#REF!+G4*AW4+G10*AW10+AW11*G11+AW14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AW6*G6+#REF!*#REF!+G16*AW16+G18*AW18+G19*AW19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AX23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AX3*G3+#REF!*#REF!+G4*AX4+G10*AX10+AX11*G11+AX14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AX6*G6+G16*AX16+G18*AX18+G19*AX19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AX3*G3+#REF!*#REF!+G4*AX4+G10*AX10+AX11*G11+AX14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AX6*G6+#REF!*#REF!+G16*AX16+G18*AX18+G19*AX19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AY23" s="23" t="e">
@@ -4536,26 +4648,26 @@
         <v>#REF!</v>
       </c>
       <c r="BD23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BD3*G3+#REF!*#REF!+G4*BD4+G10*BD10+G11*BD11+G14*BD14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BD6+BD16*G16+G18*BD18+G19*BD19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BD3*G3+#REF!*#REF!+G4*BD4+G10*BD10+BD11*G11+BD14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BD6*G6+G16*BD16+G18*BD18+G19*BD19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BE23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BE3*G3+#REF!*#REF!+G4*BE4+G10*BE10+G14*BE14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BE6+BE16*G16+G18*BE18+G19*BE19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BE3*G3+#REF!*#REF!+G4*BE4+G10*BE10+BE11*G11+BE14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BE6*G6+G16*BE16+G18*BE18+G19*BE19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BF23" s="23" t="e">
-        <f>(#REF!*#REF!+BF3*G3+G4*BF4+G14*BF14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BF6+BF16*G16+G18*BF18+G19*BF19+G22*BF22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BF3*G3+#REF!*#REF!+G4*BF4+G10*BF10+G11*BF11+G14*BF14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BF6+BF16*G16+G18*BF18+G19*BF19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BG23" s="23" t="e">
-        <f>(#REF!*#REF!+BG3*G3+G4*BG4+G14*BG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BG6+BG16*G16+G18*BG18+G19*BG19+G22*BG22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BG3*G3+#REF!*#REF!+G4*BG4+G10*BG10+G14*BG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BG6+BG16*G16+G18*BG18+G19*BG19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BH23" s="23" t="e">
         <f>(#REF!*#REF!+BH3*G3+G4*BH4+G14*BH14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BH6+BH16*G16+G18*BH18+G19*BH19+G22*BH22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BI23" s="30" t="e">
+      <c r="BI23" s="23" t="e">
         <f>(#REF!*#REF!+BI3*G3+G4*BI4+G14*BI14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BI6+BI16*G16+G18*BI18+G19*BI19+G22*BI22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
@@ -4563,27 +4675,35 @@
         <f>(#REF!*#REF!+BJ3*G3+G4*BJ4+G14*BJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BJ6+BJ16*G16+G18*BJ18+G19*BJ19+G22*BJ22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BK23" s="23" t="e">
-        <f>(#REF!*#REF!+BK3*G3+G14*BK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BK6+BK16*G16+G18*BK18+G19*BK19+G22*BK22+#REF!*#REF!+#REF!*#REF!)/100</f>
+      <c r="BK23" s="30" t="e">
+        <f>(#REF!*#REF!+BK3*G3+G4*BK4+G14*BK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BK6+BK16*G16+G18*BK18+G19*BK19+G22*BK22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BL23" s="23" t="e">
-        <f>(#REF!*#REF!+BL3*G3+G14*BL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BL6+BL16*G16+G18*BL18+G19*BL19+G22*BL22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+BL3*G3+G4*BL4+G14*BL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BL6+BL16*G16+G18*BL18+G19*BL19+G22*BL22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BM23" s="23" t="e">
         <f>(#REF!*#REF!+BM3*G3+G14*BM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BM6+BM16*G16+G18*BM18+G19*BM19+G22*BM22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BN23" s="13"/>
-      <c r="BO23" s="13"/>
+      <c r="BN23" s="23" t="e">
+        <f>(#REF!*#REF!+BN3*G3+G14*BN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BN6+BN16*G16+G18*BN18+G19*BN19+G22*BN22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BO23" s="23" t="e">
+        <f>(#REF!*#REF!+BO3*G3+G14*BO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BO6+BO16*G16+G18*BO18+G19*BO19+G22*BO22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <v>#REF!</v>
+      </c>
       <c r="BP23" s="13"/>
       <c r="BQ23" s="13"/>
-      <c r="BT23" s="15">
+      <c r="BR23" s="13"/>
+      <c r="BS23" s="13"/>
+      <c r="BV23" s="15">
         <v>1149.48</v>
       </c>
     </row>
-    <row r="24" spans="1:72" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:74" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4649,29 +4769,31 @@
       <c r="BK24" s="14"/>
       <c r="BL24" s="14"/>
       <c r="BM24" s="14"/>
-      <c r="BN24" s="23">
-        <f>SUM(BN2:BN20)</f>
-        <v>13268.386400000001</v>
-      </c>
-      <c r="BO24" s="23">
-        <f>SUM(BO2:BO20)</f>
-        <v>13570.040600000002</v>
-      </c>
-      <c r="BP24" s="24">
-        <f>BO24-BN24</f>
-        <v>301.65420000000086</v>
-      </c>
-      <c r="BQ24" s="13">
-        <f>((BO24-BN24)/BN24)*100</f>
-        <v>2.2734806698122751</v>
-      </c>
-      <c r="BT24" s="15">
-        <f>SUM(BT5:BT23)</f>
-        <v>1451.1342</v>
-      </c>
-    </row>
-    <row r="25" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="BN25" s="15">
+      <c r="BN24" s="14"/>
+      <c r="BO24" s="14"/>
+      <c r="BP24" s="23">
+        <f>SUM(BP2:BP20)</f>
+        <v>12173.8128</v>
+      </c>
+      <c r="BQ24" s="23">
+        <f>SUM(BQ2:BQ20)</f>
+        <v>12623.132800000001</v>
+      </c>
+      <c r="BR24" s="24">
+        <f>BQ24-BP24</f>
+        <v>449.32000000000153</v>
+      </c>
+      <c r="BS24" s="13">
+        <f>((BQ24-BP24)/BP24)*100</f>
+        <v>3.690873248847736</v>
+      </c>
+      <c r="BV24" s="15">
+        <f>SUM(BV5:BV23)</f>
+        <v>1472.0683999999992</v>
+      </c>
+    </row>
+    <row r="25" spans="1:74" x14ac:dyDescent="0.25">
+      <c r="BP25" s="15">
         <v>12034.32</v>
       </c>
     </row>
@@ -4798,7 +4920,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>12130</v>
+        <v>9981</v>
       </c>
       <c r="J2" s="25"/>
       <c r="L2" s="21">
@@ -4825,7 +4947,7 @@
       </c>
       <c r="D3" s="19">
         <f>'התיק העדכני'!G3</f>
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E3" s="16">
         <v>950</v>
@@ -4836,7 +4958,7 @@
       <c r="G3" s="17"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1556</v>
+        <v>1311</v>
       </c>
       <c r="J3" s="26"/>
       <c r="L3" s="21">
@@ -4874,7 +4996,7 @@
       <c r="G4" s="17"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>7252</v>
+        <v>6140</v>
       </c>
       <c r="J4" s="26"/>
       <c r="L4" s="21">
@@ -4911,7 +5033,7 @@
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="J5" s="26"/>
       <c r="L5" s="21">
@@ -4934,11 +5056,11 @@
       </c>
       <c r="C6" s="18">
         <f>'התיק העדכני'!H6</f>
-        <v>3700</v>
+        <v>4040</v>
       </c>
       <c r="D6" s="19">
         <f>'התיק העדכני'!G6</f>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E6" s="16">
         <v>3300</v>
@@ -4948,7 +5070,7 @@
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4500</v>
+        <v>4355</v>
       </c>
       <c r="J6" s="26"/>
       <c r="L6" s="21">
@@ -4986,7 +5108,7 @@
       <c r="G7" s="18"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3954</v>
+        <v>3916</v>
       </c>
       <c r="J7" s="26"/>
       <c r="L7" s="21">
@@ -5024,7 +5146,7 @@
       <c r="G8" s="18"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>43490</v>
+        <v>42140</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -5061,7 +5183,7 @@
       <c r="G9" s="17"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10240</v>
+        <v>10100</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -5098,7 +5220,7 @@
       <c r="G10" s="18"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4849</v>
+        <v>4809</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -5135,7 +5257,7 @@
       <c r="G11" s="18"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1109</v>
+        <v>1075</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -5161,7 +5283,7 @@
       </c>
       <c r="D12" s="19">
         <f>'התיק העדכני'!G12</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E12" s="16">
         <v>23800</v>
@@ -5172,7 +5294,7 @@
       <c r="G12" s="18"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>30100</v>
+        <v>27890</v>
       </c>
       <c r="J12" s="26"/>
       <c r="L12" s="21">
@@ -5210,7 +5332,7 @@
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J13" s="26"/>
       <c r="L13" s="21">
@@ -5248,7 +5370,7 @@
       <c r="G14" s="17"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7672</v>
+        <v>7687</v>
       </c>
       <c r="J14" s="26"/>
       <c r="L14" s="21">
@@ -5286,7 +5408,7 @@
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14679.12</v>
+        <v>11946.75</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
@@ -5309,11 +5431,11 @@
       </c>
       <c r="C16" s="18">
         <f>'התיק העדכני'!H16</f>
-        <v>183.73</v>
+        <v>199.49</v>
       </c>
       <c r="D16" s="19">
         <f>'התיק העדכני'!G16</f>
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E16" s="16">
         <v>205</v>
@@ -5324,7 +5446,7 @@
       <c r="G16" s="17"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>227.54</v>
+        <v>223.13</v>
       </c>
       <c r="J16" s="26"/>
       <c r="L16" s="21">
@@ -5362,7 +5484,7 @@
       <c r="G17" s="17"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>194.88</v>
+        <v>199.37</v>
       </c>
       <c r="J17" s="26"/>
       <c r="L17" s="21">
@@ -5400,7 +5522,7 @@
       <c r="G18" s="18"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1828</v>
+        <v>1785</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -5414,26 +5536,26 @@
     <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
-        <v>קסם S&amp;P 500 ETF מנוטרלת מט"ח</v>
+        <v>סטורג' דרופ</v>
       </c>
       <c r="B19" s="17">
         <f>'התיק העדכני'!A19</f>
-        <v>1146604</v>
+        <v>1122654</v>
       </c>
       <c r="C19" s="18">
         <f>'התיק העדכני'!H19</f>
-        <v>6548</v>
+        <v>110</v>
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
       <c r="G19" s="18"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>0</v>
+        <v>132.6</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -5738,7 +5860,7 @@
       <c r="G28" s="19"/>
       <c r="I28" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>3159</v>
+        <v>0</v>
       </c>
       <c r="J28" s="26"/>
       <c r="L28" s="21">
@@ -5822,7 +5944,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>12130</v>
+        <v>9981</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+GEMINI!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
@@ -5848,7 +5970,7 @@
       </c>
       <c r="D3" s="19">
         <f>'התיק העדכני'!G3</f>
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E3" s="16">
         <v>962</v>
@@ -5859,7 +5981,7 @@
       <c r="G3" s="7"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1556</v>
+        <v>1311</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
@@ -5896,7 +6018,7 @@
       <c r="G4" s="7"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>7252</v>
+        <v>6140</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+GEMINI!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
@@ -5933,7 +6055,7 @@
       <c r="G5" s="7"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
@@ -5955,11 +6077,11 @@
       </c>
       <c r="C6" s="18">
         <f>'התיק העדכני'!H6</f>
-        <v>3700</v>
+        <v>4040</v>
       </c>
       <c r="D6" s="19">
         <f>'התיק העדכני'!G6</f>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E6" s="16">
         <v>3340</v>
@@ -5970,7 +6092,7 @@
       <c r="G6" s="7"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4500</v>
+        <v>4355</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
@@ -6007,7 +6129,7 @@
       <c r="G7" s="8"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3954</v>
+        <v>3916</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+GEMINI!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
@@ -6044,7 +6166,7 @@
       <c r="G8" s="8"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>43490</v>
+        <v>42140</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+GEMINI!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -6081,7 +6203,7 @@
       <c r="G9" s="8"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10240</v>
+        <v>10100</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+GEMINI!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -6118,7 +6240,7 @@
       <c r="G10" s="8"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4849</v>
+        <v>4809</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+GEMINI!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -6155,7 +6277,7 @@
       <c r="G11" s="8"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1109</v>
+        <v>1075</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+GEMINI!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -6181,7 +6303,7 @@
       </c>
       <c r="D12" s="19">
         <f>'התיק העדכני'!G12</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E12" s="16">
         <v>22573</v>
@@ -6192,7 +6314,7 @@
       <c r="G12" s="8"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>30100</v>
+        <v>27890</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+GEMINI!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
@@ -6229,7 +6351,7 @@
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+GEMINI!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
@@ -6266,7 +6388,7 @@
       <c r="G14" s="7"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7672</v>
+        <v>7687</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
@@ -6303,7 +6425,7 @@
       <c r="G15" s="7"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14679.12</v>
+        <v>11946.75</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+GEMINI!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
@@ -6325,11 +6447,11 @@
       </c>
       <c r="C16" s="18">
         <f>'התיק העדכני'!H16</f>
-        <v>183.73</v>
+        <v>199.49</v>
       </c>
       <c r="D16" s="19">
         <f>'התיק העדכני'!G16</f>
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E16" s="16">
         <v>186</v>
@@ -6340,7 +6462,7 @@
       <c r="G16" s="7"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>227.54</v>
+        <v>223.13</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
@@ -6377,7 +6499,7 @@
       <c r="G17" s="7"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>194.88</v>
+        <v>199.37</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+GEMINI!E17+PERPLIXITY!E17+DEEPSEEK!E17)/4</f>
@@ -6414,7 +6536,7 @@
       <c r="G18" s="8"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1828</v>
+        <v>1785</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+GEMINI!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -6428,26 +6550,26 @@
     <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
-        <v>קסם S&amp;P 500 ETF מנוטרלת מט"ח</v>
+        <v>סטורג' דרופ</v>
       </c>
       <c r="B19" s="17">
         <f>'התיק העדכני'!A19</f>
-        <v>1146604</v>
+        <v>1122654</v>
       </c>
       <c r="C19" s="18">
         <f>'התיק העדכני'!H19</f>
-        <v>6548</v>
+        <v>110</v>
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
       <c r="G19" s="8"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>0</v>
+        <v>132.6</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+GEMINI!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -6638,7 +6760,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>12130</v>
+        <v>9981</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+GEMINI!E2+DEEPSEEK!E2)/4</f>
@@ -6664,7 +6786,7 @@
       </c>
       <c r="D3" s="19">
         <f>'התיק העדכני'!G3</f>
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E3" s="16">
         <v>1200</v>
@@ -6675,7 +6797,7 @@
       <c r="G3" s="10"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1556</v>
+        <v>1311</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
@@ -6712,7 +6834,7 @@
       <c r="G4" s="10"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>7252</v>
+        <v>6140</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+GEMINI!E4+DEEPSEEK!E4)/4</f>
@@ -6749,7 +6871,7 @@
       <c r="G5" s="10"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
@@ -6771,11 +6893,11 @@
       </c>
       <c r="C6" s="18">
         <f>'התיק העדכני'!H6</f>
-        <v>3700</v>
+        <v>4040</v>
       </c>
       <c r="D6" s="19">
         <f>'התיק העדכני'!G6</f>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E6" s="16">
         <v>3600</v>
@@ -6786,7 +6908,7 @@
       <c r="G6" s="10"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4500</v>
+        <v>4355</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
@@ -6823,7 +6945,7 @@
       <c r="G7" s="10"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3954</v>
+        <v>3916</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+GEMINI!E7+DEEPSEEK!E7)/4</f>
@@ -6859,7 +6981,7 @@
       </c>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>43490</v>
+        <v>42140</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+GEMINI!E8+DEEPSEEK!E8)/4</f>
@@ -6895,7 +7017,7 @@
       </c>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10240</v>
+        <v>10100</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+GEMINI!E9+DEEPSEEK!E9)/4</f>
@@ -6931,7 +7053,7 @@
       </c>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4849</v>
+        <v>4809</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+GEMINI!E10+DEEPSEEK!E10)/4</f>
@@ -6967,7 +7089,7 @@
       </c>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1109</v>
+        <v>1075</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+GEMINI!E11+DEEPSEEK!E11)/4</f>
@@ -6993,7 +7115,7 @@
       </c>
       <c r="D12" s="19">
         <f>'התיק העדכני'!G12</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E12" s="16">
         <v>24000</v>
@@ -7004,7 +7126,7 @@
       <c r="G12" s="10"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>30100</v>
+        <v>27890</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+GEMINI!E12+DEEPSEEK!E12)/4</f>
@@ -7041,7 +7163,7 @@
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+CHATGPT!E13+GEMINI!E13+DEEPSEEK!E13)/4</f>
@@ -7078,7 +7200,7 @@
       <c r="G14" s="10"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7672</v>
+        <v>7687</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
@@ -7115,7 +7237,7 @@
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14679.12</v>
+        <v>11946.75</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
@@ -7137,11 +7259,11 @@
       </c>
       <c r="C16" s="18">
         <f>'התיק העדכני'!H16</f>
-        <v>183.73</v>
+        <v>199.49</v>
       </c>
       <c r="D16" s="19">
         <f>'התיק העדכני'!G16</f>
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E16" s="16">
         <v>195</v>
@@ -7152,7 +7274,7 @@
       <c r="G16" s="10"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>227.54</v>
+        <v>223.13</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+GEMINI!E16+DEEPSEEK!E16)/4</f>
@@ -7189,7 +7311,7 @@
       <c r="G17" s="10"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>194.88</v>
+        <v>199.37</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+GEMINI!E17+DEEPSEEK!E17)/4</f>
@@ -7225,7 +7347,7 @@
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1828</v>
+        <v>1785</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
@@ -7239,25 +7361,25 @@
     <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
-        <v>קסם S&amp;P 500 ETF מנוטרלת מט"ח</v>
+        <v>סטורג' דרופ</v>
       </c>
       <c r="B19" s="17">
         <f>'התיק העדכני'!A19</f>
-        <v>1146604</v>
+        <v>1122654</v>
       </c>
       <c r="C19" s="18">
         <f>'התיק העדכני'!H19</f>
-        <v>6548</v>
+        <v>110</v>
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>0</v>
+        <v>132.6</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+GEMINI!E19+DEEPSEEK!E19)/4</f>
@@ -7448,7 +7570,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>12130</v>
+        <v>9981</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+PERPLIXITY!E2+GEMINI!E2)/4</f>
@@ -7474,7 +7596,7 @@
       </c>
       <c r="D3" s="19">
         <f>'התיק העדכני'!G3</f>
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E3" s="16">
         <v>1280</v>
@@ -7485,7 +7607,7 @@
       <c r="G3" s="31"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1556</v>
+        <v>1311</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
@@ -7521,7 +7643,7 @@
       </c>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>7252</v>
+        <v>6140</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+GEMINI!E4)/4</f>
@@ -7558,7 +7680,7 @@
       <c r="G5" s="31"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
@@ -7580,11 +7702,11 @@
       </c>
       <c r="C6" s="18">
         <f>'התיק העדכני'!H6</f>
-        <v>3700</v>
+        <v>4040</v>
       </c>
       <c r="D6" s="19">
         <f>'התיק העדכני'!G6</f>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E6" s="16">
         <v>4000</v>
@@ -7595,7 +7717,7 @@
       <c r="G6" s="31"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4500</v>
+        <v>4355</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
@@ -7631,7 +7753,7 @@
       </c>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3954</v>
+        <v>3916</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+GEMINI!E7)/4</f>
@@ -7668,7 +7790,7 @@
       <c r="G8" s="31"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>43490</v>
+        <v>42140</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+GEMINI!E8)/4</f>
@@ -7705,7 +7827,7 @@
       <c r="G9" s="31"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10240</v>
+        <v>10100</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+GEMINI!E9)/4</f>
@@ -7742,7 +7864,7 @@
       <c r="G10" s="31"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4849</v>
+        <v>4809</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+GEMINI!E10)/4</f>
@@ -7779,7 +7901,7 @@
       <c r="G11" s="31"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1109</v>
+        <v>1075</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+GEMINI!E11)/4</f>
@@ -7805,7 +7927,7 @@
       </c>
       <c r="D12" s="19">
         <f>'התיק העדכני'!G12</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E12" s="16">
         <v>25000</v>
@@ -7816,7 +7938,7 @@
       <c r="G12" s="31"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>30100</v>
+        <v>27890</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+GEMINI!E12)/4</f>
@@ -7853,7 +7975,7 @@
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
@@ -7884,7 +8006,7 @@
       <c r="G14" s="31"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7672</v>
+        <v>7687</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
@@ -7920,7 +8042,7 @@
       </c>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>3159</v>
+        <v>0</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+PERPLIXITY!E15+GEMINI!E15)/4</f>
@@ -7942,11 +8064,11 @@
       </c>
       <c r="C16" s="18">
         <f>'התיק העדכני'!H16</f>
-        <v>183.73</v>
+        <v>199.49</v>
       </c>
       <c r="D16" s="19">
         <f>'התיק העדכני'!G16</f>
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E16" s="16">
         <v>208</v>
@@ -7956,7 +8078,7 @@
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>14679.12</v>
+        <v>11946.75</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
@@ -7993,7 +8115,7 @@
       <c r="G17" s="31"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>227.54</v>
+        <v>223.13</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+GEMINI!E17)/4</f>
@@ -8030,7 +8152,7 @@
       <c r="G18" s="31"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>194.88</v>
+        <v>199.37</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+GEMINI!E18)/4</f>
@@ -8044,23 +8166,23 @@
     <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
-        <v>קסם S&amp;P 500 ETF מנוטרלת מט"ח</v>
+        <v>סטורג' דרופ</v>
       </c>
       <c r="B19" s="17">
         <f>'התיק העדכני'!A19</f>
-        <v>1146604</v>
+        <v>1122654</v>
       </c>
       <c r="C19" s="18">
         <f>'התיק העדכני'!H19</f>
-        <v>6548</v>
+        <v>110</v>
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
-        <v>0</v>
+        <v>470</v>
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1828</v>
+        <v>1785</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+GEMINI!E19)/4</f>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\BURSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7059A00D-7C74-481A-8733-26E1BFF3D335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB1D6B3-6D51-49E5-82E7-092D73AC6EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="108">
   <si>
     <t>MTF מחקה אינדקס תעשיה ישראל</t>
   </si>
@@ -344,6 +344,15 @@
   </si>
   <si>
     <t>מחיר 30/01/2026</t>
+  </si>
+  <si>
+    <t>מחיר 29/01/2026</t>
+  </si>
+  <si>
+    <t>מחיר 02/02/2026</t>
+  </si>
+  <si>
+    <t>אירודרום קבוצה</t>
   </si>
 </sst>
 </file>
@@ -1114,22 +1123,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86B4639-EF9D-4B16-B2C9-0D5E9C5EEC8B}">
-  <dimension ref="A1:BV25"/>
+  <dimension ref="A1:BW25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="17.5703125" customWidth="1"/>
     <col min="6" max="6" width="13.28515625" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="57" width="14.85546875" customWidth="1"/>
-    <col min="58" max="67" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="13" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="11.5703125" customWidth="1"/>
+    <col min="8" max="58" width="14.85546875" customWidth="1"/>
+    <col min="59" max="68" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="13" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="11" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1158,199 +1167,205 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>104</v>
       </c>
       <c r="L1" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BK1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BL1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BM1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BN1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BO1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BO1" s="6" t="s">
+      <c r="BP1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="BP1" s="6" t="s">
+      <c r="BQ1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="BQ1" s="6" t="s">
+      <c r="BR1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="BR1" s="6" t="s">
+      <c r="BS1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BS1" s="6" t="s">
+      <c r="BT1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="BT1" s="12" t="s">
+      <c r="BU1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="BU1" s="12" t="s">
+      <c r="BV1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="BV1" s="12" t="s">
+      <c r="BW1" s="12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>282012</v>
       </c>
@@ -1379,36 +1394,38 @@
         <v>11000</v>
       </c>
       <c r="I2" s="13">
+        <v>9787</v>
+      </c>
+      <c r="J2" s="13">
+        <v>9650</v>
+      </c>
+      <c r="K2" s="13">
         <v>9981</v>
       </c>
-      <c r="J2" s="13">
-        <v>9981</v>
-      </c>
-      <c r="K2" s="13">
+      <c r="L2" s="13">
         <v>12130</v>
       </c>
-      <c r="L2" s="13">
+      <c r="M2" s="13">
         <v>11840</v>
       </c>
-      <c r="M2" s="13">
+      <c r="N2" s="13">
         <v>11400</v>
       </c>
-      <c r="N2" s="13">
+      <c r="O2" s="13">
         <v>11360</v>
       </c>
-      <c r="O2" s="13">
+      <c r="P2" s="13">
         <v>11000</v>
       </c>
-      <c r="P2" s="13">
+      <c r="Q2" s="13">
         <v>10700</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="R2" s="13">
         <v>10400</v>
       </c>
-      <c r="R2" s="13">
+      <c r="S2" s="13">
         <v>11230</v>
       </c>
-      <c r="S2" s="6"/>
       <c r="T2" s="6"/>
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
@@ -1449,29 +1466,30 @@
       <c r="BE2" s="6"/>
       <c r="BF2" s="6"/>
       <c r="BG2" s="6"/>
-      <c r="BH2" s="32"/>
-      <c r="BI2" s="6"/>
+      <c r="BH2" s="6"/>
+      <c r="BI2" s="32"/>
       <c r="BJ2" s="6"/>
-      <c r="BK2" s="32"/>
-      <c r="BL2" s="6"/>
+      <c r="BK2" s="6"/>
+      <c r="BL2" s="32"/>
       <c r="BM2" s="6"/>
       <c r="BN2" s="6"/>
       <c r="BO2" s="6"/>
-      <c r="BP2" s="13">
-        <f>(G2*H2)/100-BV2</f>
+      <c r="BP2" s="6"/>
+      <c r="BQ2" s="13">
+        <f>(G2*H2)/100-BW2</f>
         <v>770</v>
       </c>
-      <c r="BQ2" s="13">
+      <c r="BR2" s="13">
         <f>(G2*H2)/100</f>
         <v>770</v>
       </c>
-      <c r="BR2" s="6"/>
       <c r="BS2" s="6"/>
-      <c r="BT2" s="25"/>
+      <c r="BT2" s="6"/>
       <c r="BU2" s="25"/>
       <c r="BV2" s="25"/>
-    </row>
-    <row r="3" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BW2" s="25"/>
+    </row>
+    <row r="3" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1227552</v>
       </c>
@@ -1500,54 +1518,56 @@
         <v>1153.6300000000001</v>
       </c>
       <c r="I3" s="13">
-        <v>1311</v>
+        <v>1245</v>
       </c>
       <c r="J3" s="13">
         <v>1311</v>
       </c>
       <c r="K3" s="13">
+        <v>1311</v>
+      </c>
+      <c r="L3" s="13">
         <v>1340</v>
       </c>
-      <c r="L3" s="13">
+      <c r="M3" s="13">
         <v>1500</v>
       </c>
-      <c r="M3" s="13">
+      <c r="N3" s="13">
         <v>1424</v>
       </c>
-      <c r="N3" s="13">
+      <c r="O3" s="13">
         <v>1348</v>
       </c>
-      <c r="O3" s="13">
+      <c r="P3" s="13">
         <v>1373</v>
       </c>
-      <c r="P3" s="13">
+      <c r="Q3" s="13">
         <v>1331</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="R3" s="13">
         <v>1386</v>
       </c>
-      <c r="R3" s="13">
+      <c r="S3" s="13">
         <v>1342</v>
       </c>
-      <c r="S3" s="13">
+      <c r="T3" s="13">
         <v>1250</v>
-      </c>
-      <c r="T3" s="13">
-        <v>1389</v>
       </c>
       <c r="U3" s="13">
         <v>1389</v>
       </c>
       <c r="V3" s="13">
+        <v>1389</v>
+      </c>
+      <c r="W3" s="13">
         <v>1367</v>
       </c>
-      <c r="W3" s="13">
+      <c r="X3" s="13">
         <v>1026</v>
       </c>
-      <c r="X3" s="13">
+      <c r="Y3" s="13">
         <v>949.1</v>
       </c>
-      <c r="Y3" s="13"/>
       <c r="Z3" s="13"/>
       <c r="AA3" s="13"/>
       <c r="AB3" s="13"/>
@@ -1563,8 +1583,8 @@
       <c r="AL3" s="13"/>
       <c r="AM3" s="13"/>
       <c r="AN3" s="13"/>
-      <c r="AO3" s="14"/>
-      <c r="AP3" s="13"/>
+      <c r="AO3" s="13"/>
+      <c r="AP3" s="14"/>
       <c r="AQ3" s="13"/>
       <c r="AR3" s="13"/>
       <c r="AS3" s="13"/>
@@ -1582,42 +1602,43 @@
       <c r="BE3" s="13"/>
       <c r="BF3" s="13"/>
       <c r="BG3" s="13"/>
-      <c r="BH3" s="29"/>
-      <c r="BI3" s="13"/>
+      <c r="BH3" s="13"/>
+      <c r="BI3" s="29"/>
       <c r="BJ3" s="13"/>
-      <c r="BK3" s="29"/>
-      <c r="BL3" s="13"/>
+      <c r="BK3" s="13"/>
+      <c r="BL3" s="29"/>
       <c r="BM3" s="13"/>
       <c r="BN3" s="13"/>
       <c r="BO3" s="13"/>
-      <c r="BP3" s="13">
-        <f>(G3*H3)/100-BV3</f>
+      <c r="BP3" s="13"/>
+      <c r="BQ3" s="13">
+        <f>(G3*H3)/100-BW3</f>
         <v>-126.73159999999989</v>
       </c>
-      <c r="BQ3" s="13">
+      <c r="BR3" s="13">
         <f>(G3*H3)/100</f>
         <v>0</v>
       </c>
-      <c r="BR3" s="13">
-        <f>(BQ3-BP3)</f>
+      <c r="BS3" s="13">
+        <f>(BR3-BQ3)</f>
         <v>126.73159999999989</v>
       </c>
-      <c r="BS3" s="13">
-        <f>((BG3-H3)/H3)*100</f>
+      <c r="BT3" s="13">
+        <f>((BH3-H3)/H3)*100</f>
         <v>-100</v>
       </c>
-      <c r="BT3">
+      <c r="BU3">
         <v>68</v>
       </c>
-      <c r="BU3">
+      <c r="BV3">
         <v>1340</v>
       </c>
-      <c r="BV3" s="15">
-        <f>(BT3*BU3-BT3*H3)/100</f>
+      <c r="BW3" s="15">
+        <f>(BU3*BV3-BU3*H3)/100</f>
         <v>126.73159999999989</v>
       </c>
     </row>
-    <row r="4" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>587014</v>
       </c>
@@ -1646,54 +1667,56 @@
         <v>5925</v>
       </c>
       <c r="I4" s="13">
+        <v>6295</v>
+      </c>
+      <c r="J4" s="13">
+        <v>6370</v>
+      </c>
+      <c r="K4" s="13">
         <v>6140</v>
       </c>
-      <c r="J4" s="13">
-        <v>6140</v>
-      </c>
-      <c r="K4" s="13">
+      <c r="L4" s="13">
         <v>7252</v>
       </c>
-      <c r="L4" s="13">
+      <c r="M4" s="13">
         <v>7120</v>
       </c>
-      <c r="M4" s="13">
+      <c r="N4" s="13">
         <v>7048</v>
       </c>
-      <c r="N4" s="13">
+      <c r="O4" s="13">
         <v>6979</v>
       </c>
-      <c r="O4" s="13">
+      <c r="P4" s="13">
         <v>6680</v>
       </c>
-      <c r="P4" s="13">
+      <c r="Q4" s="13">
         <v>6111</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="R4" s="13">
         <v>6050</v>
       </c>
-      <c r="R4" s="13">
+      <c r="S4" s="13">
         <v>6169</v>
       </c>
-      <c r="S4" s="13">
+      <c r="T4" s="13">
         <v>6300</v>
-      </c>
-      <c r="T4" s="13">
-        <v>6335</v>
       </c>
       <c r="U4" s="13">
         <v>6335</v>
       </c>
       <c r="V4" s="13">
+        <v>6335</v>
+      </c>
+      <c r="W4" s="13">
         <v>6444</v>
-      </c>
-      <c r="W4" s="13">
-        <v>5749</v>
       </c>
       <c r="X4" s="13">
         <v>5749</v>
       </c>
-      <c r="Y4" s="13"/>
+      <c r="Y4" s="13">
+        <v>5749</v>
+      </c>
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
       <c r="AB4" s="13"/>
@@ -1728,36 +1751,37 @@
       <c r="BE4" s="13"/>
       <c r="BF4" s="13"/>
       <c r="BG4" s="13"/>
-      <c r="BH4" s="29"/>
-      <c r="BI4" s="13"/>
+      <c r="BH4" s="13"/>
+      <c r="BI4" s="29"/>
       <c r="BJ4" s="13"/>
-      <c r="BK4" s="29"/>
-      <c r="BL4" s="13"/>
+      <c r="BK4" s="13"/>
+      <c r="BL4" s="29"/>
       <c r="BM4" s="13"/>
       <c r="BN4" s="13"/>
       <c r="BO4" s="13"/>
-      <c r="BP4" s="13">
-        <f>(G4*H4)/100-BV4</f>
+      <c r="BP4" s="13"/>
+      <c r="BQ4" s="13">
+        <f>(G4*H4)/100-BW4</f>
         <v>1185</v>
       </c>
-      <c r="BQ4" s="13">
+      <c r="BR4" s="13">
         <f>(G4*H4)/100</f>
         <v>1185</v>
       </c>
-      <c r="BR4" s="13">
-        <f>(BQ4-BP4)</f>
+      <c r="BS4" s="13">
+        <f>(BR4-BQ4)</f>
         <v>0</v>
       </c>
-      <c r="BS4" s="13">
-        <f>((BG4-H4)/H4)*100</f>
+      <c r="BT4" s="13">
+        <f>((BH4-H4)/H4)*100</f>
         <v>-100</v>
       </c>
-      <c r="BV4" s="15">
-        <f>(BT4*BU4-BT4*H4)/100</f>
+      <c r="BW4" s="15">
+        <f>(BU4*BV4-BU4*H4)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1099787</v>
       </c>
@@ -1786,84 +1810,86 @@
         <v>617.53</v>
       </c>
       <c r="I5" s="13">
+        <v>587.5</v>
+      </c>
+      <c r="J5" s="13">
+        <v>577.9</v>
+      </c>
+      <c r="K5" s="13">
         <v>559</v>
       </c>
-      <c r="J5" s="13">
-        <v>559</v>
-      </c>
-      <c r="K5" s="13">
+      <c r="L5" s="13">
         <v>570</v>
       </c>
-      <c r="L5" s="13">
+      <c r="M5" s="13">
         <v>575.70000000000005</v>
       </c>
-      <c r="M5" s="13">
+      <c r="N5" s="13">
         <v>612.6</v>
       </c>
-      <c r="N5" s="13">
+      <c r="O5" s="13">
         <v>638.29999999999995</v>
       </c>
-      <c r="O5" s="13">
+      <c r="P5" s="13">
         <v>630.29999999999995</v>
       </c>
-      <c r="P5" s="13">
+      <c r="Q5" s="13">
         <v>626</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="R5" s="13">
         <v>595.4</v>
       </c>
-      <c r="R5" s="13">
+      <c r="S5" s="13">
         <v>667.1</v>
       </c>
-      <c r="S5" s="13">
+      <c r="T5" s="13">
         <v>651</v>
-      </c>
-      <c r="T5" s="13">
-        <v>641.1</v>
       </c>
       <c r="U5" s="13">
         <v>641.1</v>
       </c>
       <c r="V5" s="13">
+        <v>641.1</v>
+      </c>
+      <c r="W5" s="13">
         <v>607.1</v>
       </c>
-      <c r="W5" s="13">
+      <c r="X5" s="13">
         <v>583</v>
       </c>
-      <c r="X5" s="13">
+      <c r="Y5" s="13">
         <v>581.6</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="Z5" s="13">
         <v>578.70000000000005</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="AA5" s="13">
         <v>590</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AB5" s="13">
         <v>554.70000000000005</v>
       </c>
-      <c r="AB5" s="13">
+      <c r="AC5" s="13">
         <v>511.8</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AD5" s="13">
         <v>487</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AE5" s="13">
         <v>478.8</v>
       </c>
-      <c r="AE5" s="13">
+      <c r="AF5" s="13">
         <v>485.5</v>
       </c>
-      <c r="AF5" s="13">
+      <c r="AG5" s="13">
         <v>453.4</v>
       </c>
-      <c r="AG5" s="13">
+      <c r="AH5" s="13">
         <v>426.1</v>
       </c>
-      <c r="AH5" s="13">
+      <c r="AI5" s="13">
         <v>423.2</v>
       </c>
-      <c r="AI5" s="13"/>
       <c r="AJ5" s="13"/>
       <c r="AK5" s="13"/>
       <c r="AL5" s="13"/>
@@ -1888,27 +1914,28 @@
       <c r="BE5" s="13"/>
       <c r="BF5" s="13"/>
       <c r="BG5" s="13"/>
-      <c r="BH5" s="29"/>
-      <c r="BI5" s="13"/>
+      <c r="BH5" s="13"/>
+      <c r="BI5" s="29"/>
       <c r="BJ5" s="13"/>
-      <c r="BK5" s="29"/>
-      <c r="BL5" s="13"/>
+      <c r="BK5" s="13"/>
+      <c r="BL5" s="29"/>
       <c r="BM5" s="13"/>
       <c r="BN5" s="13"/>
       <c r="BO5" s="13"/>
-      <c r="BP5" s="13">
-        <f t="shared" ref="BP5:BP19" si="0">(G5*H5)/100-BV5</f>
+      <c r="BP5" s="13"/>
+      <c r="BQ5" s="13">
+        <f t="shared" ref="BQ5:BQ19" si="0">(G5*H5)/100-BW5</f>
         <v>975.6973999999999</v>
       </c>
-      <c r="BQ5" s="13">
+      <c r="BR5" s="13">
         <f>(G5*H5)/100</f>
         <v>975.6973999999999</v>
       </c>
-      <c r="BR5" s="13"/>
       <c r="BS5" s="13"/>
-      <c r="BV5" s="15"/>
-    </row>
-    <row r="6" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT5" s="13"/>
+      <c r="BW5" s="15"/>
+    </row>
+    <row r="6" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1166768</v>
       </c>
@@ -1937,57 +1964,59 @@
         <v>4040</v>
       </c>
       <c r="I6" s="13">
+        <v>4740</v>
+      </c>
+      <c r="J6" s="13">
+        <v>4350</v>
+      </c>
+      <c r="K6" s="13">
         <v>4355</v>
       </c>
-      <c r="J6" s="13">
-        <v>4355</v>
-      </c>
-      <c r="K6" s="13">
+      <c r="L6" s="13">
         <v>4500</v>
       </c>
-      <c r="L6" s="13">
+      <c r="M6" s="13">
         <v>4424</v>
       </c>
-      <c r="M6" s="13">
+      <c r="N6" s="13">
         <v>4412</v>
       </c>
-      <c r="N6" s="13">
+      <c r="O6" s="13">
         <v>4450</v>
       </c>
-      <c r="O6" s="13">
+      <c r="P6" s="13">
         <v>4238</v>
       </c>
-      <c r="P6" s="13">
+      <c r="Q6" s="13">
         <v>3970</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="R6" s="13">
         <v>3870</v>
       </c>
-      <c r="R6" s="13">
+      <c r="S6" s="13">
         <v>3805</v>
       </c>
-      <c r="S6" s="13">
+      <c r="T6" s="13">
         <v>3667</v>
-      </c>
-      <c r="T6" s="13">
-        <v>3582</v>
       </c>
       <c r="U6" s="13">
         <v>3582</v>
       </c>
       <c r="V6" s="13">
+        <v>3582</v>
+      </c>
+      <c r="W6" s="13">
         <v>3570</v>
       </c>
-      <c r="W6" s="13">
+      <c r="X6" s="13">
         <v>3619</v>
       </c>
-      <c r="X6" s="13">
+      <c r="Y6" s="13">
         <v>3650</v>
       </c>
-      <c r="Y6" s="13">
+      <c r="Z6" s="13">
         <v>3720</v>
       </c>
-      <c r="Z6" s="13"/>
       <c r="AA6" s="13"/>
       <c r="AB6" s="13"/>
       <c r="AC6" s="13"/>
@@ -2021,41 +2050,42 @@
       <c r="BE6" s="13"/>
       <c r="BF6" s="13"/>
       <c r="BG6" s="13"/>
-      <c r="BH6" s="29"/>
-      <c r="BI6" s="13"/>
+      <c r="BH6" s="13"/>
+      <c r="BI6" s="29"/>
       <c r="BJ6" s="13"/>
-      <c r="BK6" s="29"/>
-      <c r="BL6" s="13"/>
+      <c r="BK6" s="13"/>
+      <c r="BL6" s="29"/>
       <c r="BM6" s="13"/>
       <c r="BN6" s="13"/>
-      <c r="BP6" s="13">
-        <f>(G6*H6)/100-BV6</f>
+      <c r="BO6" s="13"/>
+      <c r="BQ6" s="13">
+        <f>(G6*H6)/100-BW6</f>
         <v>1033.7</v>
       </c>
-      <c r="BQ6" s="13">
+      <c r="BR6" s="13">
         <f>(G6*H6)/100</f>
         <v>1010</v>
       </c>
-      <c r="BR6" s="13">
-        <f t="shared" ref="BR6" si="1">(BQ6-BP6)</f>
+      <c r="BS6" s="13">
+        <f t="shared" ref="BS6" si="1">(BR6-BQ6)</f>
         <v>-23.700000000000045</v>
       </c>
-      <c r="BS6" s="13">
-        <f>((BG6-H6)/H6)*100</f>
+      <c r="BT6" s="13">
+        <f>((BH6-H6)/H6)*100</f>
         <v>-100</v>
       </c>
-      <c r="BT6">
+      <c r="BU6">
         <v>5</v>
       </c>
-      <c r="BU6">
+      <c r="BV6">
         <v>3566</v>
       </c>
-      <c r="BV6" s="15">
-        <f>(BT6*BU6-BT6*H6)/100</f>
+      <c r="BW6" s="15">
+        <f>(BU6*BV6-BU6*H6)/100</f>
         <v>-23.7</v>
       </c>
     </row>
-    <row r="7" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1148899</v>
       </c>
@@ -2084,84 +2114,86 @@
         <v>3585</v>
       </c>
       <c r="I7" s="13">
+        <v>4033</v>
+      </c>
+      <c r="J7" s="13">
+        <v>3988</v>
+      </c>
+      <c r="K7" s="13">
         <v>3916</v>
       </c>
-      <c r="J7" s="13">
-        <v>3916</v>
-      </c>
-      <c r="K7" s="13">
+      <c r="L7" s="13">
         <v>3954</v>
       </c>
-      <c r="L7" s="13">
+      <c r="M7" s="13">
         <v>3932</v>
       </c>
-      <c r="M7" s="13">
+      <c r="N7" s="13">
         <v>3949</v>
       </c>
-      <c r="N7" s="13">
+      <c r="O7" s="13">
         <v>3943</v>
       </c>
-      <c r="O7" s="13">
+      <c r="P7" s="13">
         <v>3928</v>
       </c>
-      <c r="P7" s="13">
+      <c r="Q7" s="13">
         <v>3913</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="R7" s="13">
         <v>3860</v>
       </c>
-      <c r="R7" s="13">
+      <c r="S7" s="13">
         <v>3893</v>
       </c>
-      <c r="S7" s="13">
+      <c r="T7" s="13">
         <v>3900</v>
-      </c>
-      <c r="T7" s="13">
-        <v>3842</v>
       </c>
       <c r="U7" s="13">
         <v>3842</v>
       </c>
       <c r="V7" s="13">
+        <v>3842</v>
+      </c>
+      <c r="W7" s="13">
         <v>3841</v>
       </c>
-      <c r="W7" s="13">
+      <c r="X7" s="13">
         <v>3809</v>
       </c>
-      <c r="X7" s="13">
+      <c r="Y7" s="13">
         <v>3810</v>
       </c>
-      <c r="Y7" s="13">
+      <c r="Z7" s="13">
         <v>3798</v>
       </c>
-      <c r="Z7" s="13">
+      <c r="AA7" s="13">
         <v>3713</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="AB7" s="13">
         <v>3657</v>
       </c>
-      <c r="AB7" s="13">
+      <c r="AC7" s="13">
         <v>3592</v>
       </c>
-      <c r="AC7" s="13">
+      <c r="AD7" s="13">
         <v>3621</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AE7" s="13">
         <v>3572</v>
       </c>
-      <c r="AE7" s="13">
+      <c r="AF7" s="13">
         <v>3580</v>
       </c>
-      <c r="AF7" s="13">
+      <c r="AG7" s="13">
         <v>3569</v>
       </c>
-      <c r="AG7" s="13">
+      <c r="AH7" s="13">
         <v>3659</v>
       </c>
-      <c r="AH7" s="13">
+      <c r="AI7" s="13">
         <v>3656</v>
       </c>
-      <c r="AI7" s="13"/>
       <c r="AJ7" s="13"/>
       <c r="AK7" s="13"/>
       <c r="AL7" s="13"/>
@@ -2186,27 +2218,28 @@
       <c r="BE7" s="13"/>
       <c r="BF7" s="13"/>
       <c r="BG7" s="13"/>
-      <c r="BH7" s="29"/>
-      <c r="BI7" s="13"/>
+      <c r="BH7" s="13"/>
+      <c r="BI7" s="29"/>
       <c r="BJ7" s="13"/>
-      <c r="BK7" s="29"/>
-      <c r="BL7" s="13"/>
+      <c r="BK7" s="13"/>
+      <c r="BL7" s="29"/>
       <c r="BM7" s="13"/>
       <c r="BN7" s="13"/>
       <c r="BO7" s="13"/>
-      <c r="BP7" s="13">
+      <c r="BP7" s="13"/>
+      <c r="BQ7" s="13">
         <f t="shared" si="0"/>
         <v>2509.5</v>
       </c>
-      <c r="BQ7" s="13">
-        <f t="shared" ref="BQ7:BQ19" si="2">(G7*H7)/100</f>
+      <c r="BR7" s="13">
+        <f t="shared" ref="BR7:BR19" si="2">(G7*H7)/100</f>
         <v>2509.5</v>
       </c>
-      <c r="BR7" s="13"/>
       <c r="BS7" s="13"/>
-      <c r="BV7" s="15"/>
-    </row>
-    <row r="8" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT7" s="13"/>
+      <c r="BW7" s="15"/>
+    </row>
+    <row r="8" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1082379</v>
       </c>
@@ -2220,7 +2253,7 @@
       </c>
       <c r="D8" s="6" t="str">
         <f>IF(I8&lt;GEMINI!L8,"למכור בהפסד",IF(I8&gt;GEMINI!M8,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>52</v>
@@ -2235,120 +2268,122 @@
         <v>37875</v>
       </c>
       <c r="I8" s="13">
+        <v>43640</v>
+      </c>
+      <c r="J8" s="13">
+        <v>42700</v>
+      </c>
+      <c r="K8" s="13">
         <v>42140</v>
       </c>
-      <c r="J8" s="13">
-        <v>42140</v>
-      </c>
-      <c r="K8" s="13">
+      <c r="L8" s="13">
         <v>43490</v>
       </c>
-      <c r="L8" s="13">
+      <c r="M8" s="13">
         <v>40750</v>
       </c>
-      <c r="M8" s="13">
+      <c r="N8" s="13">
         <v>40900</v>
       </c>
-      <c r="N8" s="13">
+      <c r="O8" s="13">
         <v>40790</v>
       </c>
-      <c r="O8" s="13">
+      <c r="P8" s="13">
         <v>40820</v>
       </c>
-      <c r="P8" s="13">
+      <c r="Q8" s="13">
         <v>41570</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="R8" s="13">
         <v>42050</v>
       </c>
-      <c r="R8" s="13">
+      <c r="S8" s="13">
         <v>39960</v>
       </c>
-      <c r="S8" s="13">
+      <c r="T8" s="13">
         <v>39990</v>
-      </c>
-      <c r="T8" s="13">
-        <v>38680</v>
       </c>
       <c r="U8" s="13">
         <v>38680</v>
       </c>
       <c r="V8" s="13">
+        <v>38680</v>
+      </c>
+      <c r="W8" s="13">
         <v>37770</v>
       </c>
-      <c r="W8" s="13">
+      <c r="X8" s="13">
         <v>36330</v>
       </c>
-      <c r="X8" s="13">
+      <c r="Y8" s="13">
         <v>38680</v>
       </c>
-      <c r="Y8" s="13">
+      <c r="Z8" s="13">
         <v>39090</v>
       </c>
-      <c r="Z8" s="13">
+      <c r="AA8" s="13">
         <v>37300</v>
       </c>
-      <c r="AA8" s="13">
+      <c r="AB8" s="13">
         <v>37650</v>
       </c>
-      <c r="AB8" s="13">
+      <c r="AC8" s="13">
         <v>37300</v>
       </c>
-      <c r="AC8" s="13">
+      <c r="AD8" s="13">
         <v>39450</v>
       </c>
-      <c r="AD8" s="13">
+      <c r="AE8" s="13">
         <v>38390</v>
       </c>
-      <c r="AE8" s="13">
+      <c r="AF8" s="13">
         <v>38800</v>
       </c>
-      <c r="AF8" s="13">
+      <c r="AG8" s="13">
         <v>38510</v>
-      </c>
-      <c r="AG8" s="13">
-        <v>38970</v>
       </c>
       <c r="AH8" s="13">
         <v>38970</v>
       </c>
       <c r="AI8" s="13">
-        <v>37700</v>
+        <v>38970</v>
       </c>
       <c r="AJ8" s="13">
         <v>37700</v>
       </c>
       <c r="AK8" s="13">
+        <v>37700</v>
+      </c>
+      <c r="AL8" s="13">
         <v>37750</v>
       </c>
-      <c r="AL8" s="13">
+      <c r="AM8" s="13">
         <v>38430</v>
       </c>
-      <c r="AM8" s="13">
+      <c r="AN8" s="13">
         <v>38250</v>
       </c>
-      <c r="AN8" s="13">
+      <c r="AO8" s="13">
         <v>40110</v>
       </c>
-      <c r="AO8" s="13">
+      <c r="AP8" s="13">
         <v>40820</v>
       </c>
-      <c r="AP8" s="13">
+      <c r="AQ8" s="13">
         <v>39320</v>
       </c>
-      <c r="AQ8" s="13">
+      <c r="AR8" s="13">
         <v>37800</v>
       </c>
-      <c r="AR8" s="13">
+      <c r="AS8" s="13">
         <v>36620</v>
       </c>
-      <c r="AS8" s="13">
+      <c r="AT8" s="13">
         <v>37130</v>
       </c>
-      <c r="AT8" s="13">
+      <c r="AU8" s="13">
         <v>35850</v>
       </c>
-      <c r="AU8" s="13"/>
       <c r="AV8" s="13"/>
       <c r="AW8" s="13"/>
       <c r="AX8" s="13"/>
@@ -2361,39 +2396,40 @@
       <c r="BE8" s="13"/>
       <c r="BF8" s="13"/>
       <c r="BG8" s="13"/>
-      <c r="BH8" s="29"/>
-      <c r="BI8" s="13"/>
+      <c r="BH8" s="13"/>
+      <c r="BI8" s="29"/>
       <c r="BJ8" s="13"/>
-      <c r="BK8" s="29"/>
-      <c r="BL8" s="13"/>
+      <c r="BK8" s="13"/>
+      <c r="BL8" s="29"/>
       <c r="BM8" s="13"/>
       <c r="BN8" s="13"/>
       <c r="BO8" s="13"/>
-      <c r="BP8" s="13">
+      <c r="BP8" s="13"/>
+      <c r="BQ8" s="13">
         <f t="shared" si="0"/>
         <v>806.25</v>
       </c>
-      <c r="BQ8" s="13">
+      <c r="BR8" s="13">
         <f t="shared" si="2"/>
         <v>757.5</v>
       </c>
-      <c r="BR8" s="13">
-        <f t="shared" ref="BR8:BR11" si="3">(BQ8-BP8)</f>
+      <c r="BS8" s="13">
+        <f t="shared" ref="BS8:BS11" si="3">(BR8-BQ8)</f>
         <v>-48.75</v>
       </c>
-      <c r="BS8" s="13"/>
-      <c r="BT8">
+      <c r="BT8" s="13"/>
+      <c r="BU8">
         <v>3</v>
       </c>
-      <c r="BU8">
+      <c r="BV8">
         <v>36250</v>
       </c>
-      <c r="BV8" s="15">
-        <f>(BT8*BU8-BT8*H8)/100</f>
+      <c r="BW8" s="15">
+        <f>(BU8*BV8-BU8*H8)/100</f>
         <v>-48.75</v>
       </c>
     </row>
-    <row r="9" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>629014</v>
       </c>
@@ -2422,114 +2458,116 @@
         <v>9227</v>
       </c>
       <c r="I9" s="13">
-        <v>10100</v>
+        <v>11020</v>
       </c>
       <c r="J9" s="13">
         <v>10100</v>
       </c>
       <c r="K9" s="13">
+        <v>10100</v>
+      </c>
+      <c r="L9" s="13">
         <v>10240</v>
       </c>
-      <c r="L9" s="13">
+      <c r="M9" s="13">
         <v>9891</v>
       </c>
-      <c r="M9" s="13">
+      <c r="N9" s="13">
         <v>9956</v>
       </c>
-      <c r="N9" s="13">
+      <c r="O9" s="13">
         <v>9910</v>
       </c>
-      <c r="O9" s="13">
+      <c r="P9" s="13">
         <v>9960</v>
       </c>
-      <c r="P9" s="13">
+      <c r="Q9" s="13">
         <v>9924</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="R9" s="13">
         <v>9999</v>
       </c>
-      <c r="R9" s="13">
+      <c r="S9" s="13">
         <v>9962</v>
       </c>
-      <c r="S9" s="13">
+      <c r="T9" s="13">
         <v>9979</v>
-      </c>
-      <c r="T9" s="13">
-        <v>10130</v>
       </c>
       <c r="U9" s="13">
         <v>10130</v>
       </c>
       <c r="V9" s="13">
+        <v>10130</v>
+      </c>
+      <c r="W9" s="13">
         <v>10400</v>
       </c>
-      <c r="W9" s="13">
+      <c r="X9" s="13">
         <v>10320</v>
       </c>
-      <c r="X9" s="13">
+      <c r="Y9" s="13">
         <v>10300</v>
       </c>
-      <c r="Y9" s="13">
+      <c r="Z9" s="13">
         <v>10310</v>
       </c>
-      <c r="Z9" s="13">
+      <c r="AA9" s="13">
         <v>9672</v>
       </c>
-      <c r="AA9" s="13">
+      <c r="AB9" s="13">
         <v>9953</v>
       </c>
-      <c r="AB9" s="13">
+      <c r="AC9" s="13">
         <v>10090</v>
       </c>
-      <c r="AC9" s="13">
+      <c r="AD9" s="13">
         <v>10070</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AE9" s="13">
         <v>10030</v>
       </c>
-      <c r="AE9" s="13">
+      <c r="AF9" s="13">
         <v>10120</v>
       </c>
-      <c r="AF9" s="13">
+      <c r="AG9" s="13">
         <v>10000</v>
       </c>
-      <c r="AG9" s="13">
+      <c r="AH9" s="13">
         <v>10080</v>
       </c>
-      <c r="AH9" s="13">
+      <c r="AI9" s="13">
         <v>10030</v>
-      </c>
-      <c r="AI9" s="13">
-        <v>9726</v>
       </c>
       <c r="AJ9" s="13">
         <v>9726</v>
       </c>
       <c r="AK9" s="13">
+        <v>9726</v>
+      </c>
+      <c r="AL9" s="13">
         <v>9659</v>
       </c>
-      <c r="AL9" s="13">
+      <c r="AM9" s="13">
         <v>9670</v>
       </c>
-      <c r="AM9" s="13">
+      <c r="AN9" s="13">
         <v>9590</v>
       </c>
-      <c r="AN9" s="13">
+      <c r="AO9" s="13">
         <v>9588</v>
       </c>
-      <c r="AO9" s="13">
+      <c r="AP9" s="13">
         <v>9400</v>
       </c>
-      <c r="AP9" s="13">
+      <c r="AQ9" s="13">
         <v>9320</v>
       </c>
-      <c r="AQ9" s="13">
+      <c r="AR9" s="13">
         <v>9071</v>
       </c>
-      <c r="AR9" s="13">
+      <c r="AS9" s="13">
         <v>9271</v>
       </c>
-      <c r="AS9" s="13"/>
       <c r="AT9" s="13"/>
       <c r="AU9" s="13"/>
       <c r="AV9" s="13"/>
@@ -2544,39 +2582,40 @@
       <c r="BE9" s="13"/>
       <c r="BF9" s="13"/>
       <c r="BG9" s="13"/>
-      <c r="BH9" s="29"/>
-      <c r="BI9" s="13"/>
+      <c r="BH9" s="13"/>
+      <c r="BI9" s="29"/>
       <c r="BJ9" s="13"/>
-      <c r="BK9" s="29"/>
-      <c r="BL9" s="13"/>
+      <c r="BK9" s="13"/>
+      <c r="BL9" s="29"/>
       <c r="BM9" s="13"/>
       <c r="BN9" s="13"/>
       <c r="BO9" s="13"/>
-      <c r="BP9" s="13">
+      <c r="BP9" s="13"/>
+      <c r="BQ9" s="13">
         <f t="shared" si="0"/>
         <v>-38.65</v>
       </c>
-      <c r="BQ9" s="13">
+      <c r="BR9" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BR9" s="13">
+      <c r="BS9" s="13">
         <f t="shared" si="3"/>
         <v>38.65</v>
       </c>
-      <c r="BS9" s="13"/>
-      <c r="BT9">
+      <c r="BT9" s="13"/>
+      <c r="BU9">
         <v>5</v>
       </c>
-      <c r="BU9">
+      <c r="BV9">
         <v>10000</v>
       </c>
-      <c r="BV9" s="15">
-        <f>(BT9*BU9-BT9*H9)/100</f>
+      <c r="BW9" s="15">
+        <f>(BU9*BV9-BU9*H9)/100</f>
         <v>38.65</v>
       </c>
     </row>
-    <row r="10" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1141464</v>
       </c>
@@ -2590,7 +2629,7 @@
       </c>
       <c r="D10" s="6" t="str">
         <f>IF(I10&lt;GEMINI!L10,"למכור בהפסד",IF(I10&gt;GEMINI!M10,"למכור ברווח","לשמור"))</f>
-        <v>למכור בהפסד</v>
+        <v>לשמור</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>39</v>
@@ -2605,196 +2644,199 @@
         <v>4834</v>
       </c>
       <c r="I10" s="13">
-        <v>4809</v>
+        <v>5164</v>
       </c>
       <c r="J10" s="13">
         <v>4809</v>
       </c>
       <c r="K10" s="13">
+        <v>4809</v>
+      </c>
+      <c r="L10" s="13">
         <v>4849</v>
       </c>
-      <c r="L10" s="13">
+      <c r="M10" s="13">
         <v>4821</v>
       </c>
-      <c r="M10" s="13">
+      <c r="N10" s="13">
         <v>4925</v>
       </c>
-      <c r="N10" s="13">
+      <c r="O10" s="13">
         <v>5013</v>
-      </c>
-      <c r="O10" s="13">
-        <v>5050</v>
       </c>
       <c r="P10" s="13">
         <v>5050</v>
       </c>
       <c r="Q10" s="13">
+        <v>5050</v>
+      </c>
+      <c r="R10" s="13">
         <v>4930</v>
       </c>
-      <c r="R10" s="13">
+      <c r="S10" s="13">
         <v>5150</v>
       </c>
-      <c r="S10" s="13">
+      <c r="T10" s="13">
         <v>5283</v>
-      </c>
-      <c r="T10" s="13">
-        <v>5253</v>
       </c>
       <c r="U10" s="13">
         <v>5253</v>
       </c>
       <c r="V10" s="13">
+        <v>5253</v>
+      </c>
+      <c r="W10" s="13">
         <v>5400</v>
       </c>
-      <c r="W10" s="13">
+      <c r="X10" s="13">
         <v>5522</v>
       </c>
-      <c r="X10" s="13">
+      <c r="Y10" s="13">
         <v>5690</v>
       </c>
-      <c r="Y10" s="13">
+      <c r="Z10" s="13">
         <v>5749</v>
       </c>
-      <c r="Z10" s="13">
+      <c r="AA10" s="13">
         <v>5840</v>
-      </c>
-      <c r="AA10" s="13">
-        <v>5650</v>
       </c>
       <c r="AB10" s="13">
         <v>5650</v>
       </c>
       <c r="AC10" s="13">
+        <v>5650</v>
+      </c>
+      <c r="AD10" s="13">
         <v>5841</v>
       </c>
-      <c r="AD10" s="13">
+      <c r="AE10" s="13">
         <v>5758</v>
       </c>
-      <c r="AE10" s="13">
+      <c r="AF10" s="13">
         <v>5673</v>
       </c>
-      <c r="AF10" s="13">
+      <c r="AG10" s="13">
         <v>5609</v>
       </c>
-      <c r="AG10" s="13">
+      <c r="AH10" s="13">
         <v>5750</v>
       </c>
-      <c r="AH10" s="13">
+      <c r="AI10" s="13">
         <v>5841</v>
-      </c>
-      <c r="AI10" s="13">
-        <v>5564</v>
       </c>
       <c r="AJ10" s="13">
         <v>5564</v>
       </c>
       <c r="AK10" s="13">
+        <v>5564</v>
+      </c>
+      <c r="AL10" s="13">
         <v>5557</v>
       </c>
-      <c r="AL10" s="13">
+      <c r="AM10" s="13">
         <v>5501</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AN10" s="13">
         <v>5250</v>
       </c>
-      <c r="AN10" s="13">
+      <c r="AO10" s="13">
         <v>5270</v>
       </c>
-      <c r="AO10" s="13">
+      <c r="AP10" s="13">
         <v>5149</v>
       </c>
-      <c r="AP10" s="13">
+      <c r="AQ10" s="13">
         <v>5092</v>
       </c>
-      <c r="AQ10" s="13">
+      <c r="AR10" s="13">
         <v>5228</v>
       </c>
-      <c r="AR10" s="13">
+      <c r="AS10" s="13">
         <v>5301</v>
       </c>
-      <c r="AS10" s="13">
+      <c r="AT10" s="13">
         <v>5159</v>
       </c>
-      <c r="AT10" s="13">
+      <c r="AU10" s="13">
         <v>5198</v>
       </c>
-      <c r="AU10" s="13">
+      <c r="AV10" s="13">
         <v>5077</v>
       </c>
-      <c r="AV10" s="13">
+      <c r="AW10" s="13">
         <v>4842</v>
       </c>
-      <c r="AW10" s="13">
+      <c r="AX10" s="13">
         <v>5050</v>
       </c>
-      <c r="AX10" s="13">
+      <c r="AY10" s="13">
         <v>4970</v>
       </c>
-      <c r="AY10" s="13">
+      <c r="AZ10" s="13">
         <v>4880</v>
       </c>
-      <c r="AZ10" s="13">
+      <c r="BA10" s="13">
         <v>4704</v>
       </c>
-      <c r="BA10" s="13">
+      <c r="BB10" s="13">
         <v>4770</v>
       </c>
-      <c r="BB10" s="13">
+      <c r="BC10" s="13">
         <v>4609</v>
       </c>
-      <c r="BC10" s="13">
+      <c r="BD10" s="13">
         <v>4674</v>
       </c>
-      <c r="BD10" s="13">
+      <c r="BE10" s="13">
         <v>4710</v>
       </c>
-      <c r="BE10" s="13">
+      <c r="BF10" s="13">
         <v>4688</v>
       </c>
-      <c r="BF10" s="13">
+      <c r="BG10" s="13">
         <v>4900</v>
       </c>
-      <c r="BG10" s="13">
+      <c r="BH10" s="13">
         <v>5000</v>
       </c>
-      <c r="BH10" s="29">
+      <c r="BI10" s="29">
         <v>4932</v>
       </c>
-      <c r="BI10" s="13"/>
       <c r="BJ10" s="13"/>
-      <c r="BK10" s="29"/>
-      <c r="BL10" s="13"/>
+      <c r="BK10" s="13"/>
+      <c r="BL10" s="29"/>
       <c r="BM10" s="13"/>
       <c r="BN10" s="13"/>
       <c r="BO10" s="13"/>
-      <c r="BP10" s="13">
+      <c r="BP10" s="13"/>
+      <c r="BQ10" s="13">
         <f t="shared" si="0"/>
         <v>-87.859799999999964</v>
       </c>
-      <c r="BQ10" s="13">
+      <c r="BR10" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BR10" s="13">
+      <c r="BS10" s="13">
         <f t="shared" si="3"/>
         <v>87.859799999999964</v>
       </c>
-      <c r="BS10" s="13">
-        <f>((BG10-H10)/H10)*100</f>
+      <c r="BT10" s="13">
+        <f>((BH10-H10)/H10)*100</f>
         <v>3.434009102192801</v>
       </c>
-      <c r="BT10">
+      <c r="BU10">
         <v>21</v>
       </c>
-      <c r="BU10">
+      <c r="BV10">
         <v>5252.38</v>
       </c>
-      <c r="BV10" s="15">
-        <f>(BT10*BU10-BT10*H10)/100</f>
+      <c r="BW10" s="15">
+        <f>(BU10*BV10-BU10*H10)/100</f>
         <v>87.859799999999964</v>
       </c>
     </row>
-    <row r="11" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1166974</v>
       </c>
@@ -2808,7 +2850,7 @@
       </c>
       <c r="D11" s="6" t="str">
         <f>IF(I11&lt;GEMINI!L11,"למכור בהפסד",IF(I11&gt;GEMINI!M11,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>72</v>
@@ -2823,78 +2865,80 @@
         <v>901.87</v>
       </c>
       <c r="I11" s="13">
+        <v>1173</v>
+      </c>
+      <c r="J11" s="13">
+        <v>1114</v>
+      </c>
+      <c r="K11" s="13">
         <v>1075</v>
       </c>
-      <c r="J11" s="13">
-        <v>1075</v>
-      </c>
-      <c r="K11" s="13">
+      <c r="L11" s="13">
         <v>1109</v>
       </c>
-      <c r="L11" s="13">
+      <c r="M11" s="13">
         <v>1090</v>
       </c>
-      <c r="M11" s="13">
+      <c r="N11" s="13">
         <v>1144</v>
       </c>
-      <c r="N11" s="13">
+      <c r="O11" s="13">
         <v>1162</v>
       </c>
-      <c r="O11" s="13">
+      <c r="P11" s="13">
         <v>1109</v>
       </c>
-      <c r="P11" s="13">
+      <c r="Q11" s="13">
         <v>1029</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="R11" s="13">
         <v>993</v>
       </c>
-      <c r="R11" s="13">
+      <c r="S11" s="13">
         <v>1017</v>
       </c>
-      <c r="S11" s="13">
+      <c r="T11" s="13">
         <v>960</v>
-      </c>
-      <c r="T11" s="13">
-        <v>965</v>
       </c>
       <c r="U11" s="13">
         <v>965</v>
       </c>
       <c r="V11" s="13">
+        <v>965</v>
+      </c>
+      <c r="W11" s="13">
         <v>951.7</v>
       </c>
-      <c r="W11" s="13">
+      <c r="X11" s="13">
         <v>946</v>
       </c>
-      <c r="X11" s="13">
+      <c r="Y11" s="13">
         <v>869.2</v>
       </c>
-      <c r="Y11" s="13">
+      <c r="Z11" s="13">
         <v>865</v>
       </c>
-      <c r="Z11" s="13">
+      <c r="AA11" s="13">
         <v>851</v>
       </c>
-      <c r="AA11" s="13">
+      <c r="AB11" s="13">
         <v>829.3</v>
       </c>
-      <c r="AB11" s="13">
+      <c r="AC11" s="13">
         <v>830</v>
       </c>
-      <c r="AC11" s="13">
+      <c r="AD11" s="13">
         <v>810</v>
       </c>
-      <c r="AD11" s="13">
+      <c r="AE11" s="13">
         <v>812.8</v>
       </c>
-      <c r="AE11" s="13">
+      <c r="AF11" s="13">
         <v>788</v>
       </c>
-      <c r="AF11" s="13">
+      <c r="AG11" s="13">
         <v>772</v>
       </c>
-      <c r="AG11" s="13"/>
       <c r="AH11" s="13"/>
       <c r="AI11" s="13"/>
       <c r="AJ11" s="13"/>
@@ -2921,33 +2965,34 @@
       <c r="BE11" s="13"/>
       <c r="BF11" s="13"/>
       <c r="BG11" s="13"/>
-      <c r="BH11" s="29"/>
-      <c r="BI11" s="13"/>
+      <c r="BH11" s="13"/>
+      <c r="BI11" s="29"/>
       <c r="BJ11" s="13"/>
-      <c r="BK11" s="29"/>
-      <c r="BL11" s="13"/>
+      <c r="BK11" s="13"/>
+      <c r="BL11" s="29"/>
       <c r="BM11" s="13"/>
       <c r="BN11" s="13"/>
       <c r="BO11" s="13"/>
-      <c r="BP11" s="13">
+      <c r="BP11" s="13"/>
+      <c r="BQ11" s="13">
         <f t="shared" si="0"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BQ11" s="13">
+      <c r="BR11" s="13">
         <f t="shared" si="2"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BR11" s="13">
+      <c r="BS11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BS11" s="13"/>
-      <c r="BV11" s="15">
-        <f>(BT11*BU11-BT11*H11)/100</f>
+      <c r="BT11" s="13"/>
+      <c r="BW11" s="15">
+        <f>(BU11*BV11-BU11*H11)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1176593</v>
       </c>
@@ -2961,7 +3006,7 @@
       </c>
       <c r="D12" s="6" t="str">
         <f>IF(I12&lt;GEMINI!L12,"למכור בהפסד",IF(I12&gt;GEMINI!M12,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>68</v>
@@ -2976,84 +3021,86 @@
         <v>22581.42</v>
       </c>
       <c r="I12" s="13">
-        <v>27890</v>
+        <v>28720</v>
       </c>
       <c r="J12" s="13">
         <v>27890</v>
       </c>
       <c r="K12" s="13">
+        <v>27890</v>
+      </c>
+      <c r="L12" s="13">
         <v>30100</v>
       </c>
-      <c r="L12" s="13">
+      <c r="M12" s="13">
         <v>30500</v>
       </c>
-      <c r="M12" s="13">
+      <c r="N12" s="13">
         <v>28850</v>
       </c>
-      <c r="N12" s="13">
+      <c r="O12" s="13">
         <v>27450</v>
       </c>
-      <c r="O12" s="13">
+      <c r="P12" s="13">
         <v>26940</v>
       </c>
-      <c r="P12" s="13">
+      <c r="Q12" s="13">
         <v>26800</v>
       </c>
-      <c r="Q12" s="13">
+      <c r="R12" s="13">
         <v>25950</v>
       </c>
-      <c r="R12" s="13">
+      <c r="S12" s="13">
         <v>26000</v>
       </c>
-      <c r="S12" s="13">
+      <c r="T12" s="13">
         <v>26600</v>
-      </c>
-      <c r="T12" s="13">
-        <v>24630</v>
       </c>
       <c r="U12" s="13">
         <v>24630</v>
       </c>
       <c r="V12" s="13">
+        <v>24630</v>
+      </c>
+      <c r="W12" s="13">
         <v>25230</v>
       </c>
-      <c r="W12" s="13">
+      <c r="X12" s="13">
         <v>24700</v>
       </c>
-      <c r="X12" s="13">
+      <c r="Y12" s="13">
         <v>23780</v>
       </c>
-      <c r="Y12" s="13">
+      <c r="Z12" s="13">
         <v>23920</v>
       </c>
-      <c r="Z12" s="13">
+      <c r="AA12" s="13">
         <v>22390</v>
       </c>
-      <c r="AA12" s="13">
+      <c r="AB12" s="13">
         <v>23000</v>
       </c>
-      <c r="AB12" s="13">
+      <c r="AC12" s="13">
         <v>20990</v>
       </c>
-      <c r="AC12" s="13">
+      <c r="AD12" s="13">
         <v>20260</v>
       </c>
-      <c r="AD12" s="13">
+      <c r="AE12" s="13">
         <v>19200</v>
       </c>
-      <c r="AE12" s="13">
+      <c r="AF12" s="13">
         <v>19860</v>
       </c>
-      <c r="AF12" s="13">
+      <c r="AG12" s="13">
         <v>19700</v>
       </c>
-      <c r="AG12" s="13">
+      <c r="AH12" s="13">
         <v>19430</v>
       </c>
-      <c r="AH12" s="13">
+      <c r="AI12" s="13">
         <v>19020</v>
       </c>
-      <c r="AI12" s="13"/>
       <c r="AJ12" s="13"/>
       <c r="AK12" s="13"/>
       <c r="AL12" s="13"/>
@@ -3078,36 +3125,37 @@
       <c r="BE12" s="13"/>
       <c r="BF12" s="13"/>
       <c r="BG12" s="13"/>
-      <c r="BH12" s="29"/>
-      <c r="BI12" s="13"/>
+      <c r="BH12" s="13"/>
+      <c r="BI12" s="29"/>
       <c r="BJ12" s="13"/>
-      <c r="BK12" s="29"/>
-      <c r="BL12" s="13"/>
+      <c r="BK12" s="13"/>
+      <c r="BL12" s="29"/>
       <c r="BM12" s="13"/>
       <c r="BN12" s="13"/>
       <c r="BO12" s="13"/>
-      <c r="BP12" s="13">
+      <c r="BP12" s="13"/>
+      <c r="BQ12" s="13">
         <f t="shared" si="0"/>
         <v>-331.70059999999995</v>
       </c>
-      <c r="BQ12" s="13">
+      <c r="BR12" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BR12" s="13"/>
       <c r="BS12" s="13"/>
-      <c r="BT12">
+      <c r="BT12" s="13"/>
+      <c r="BU12">
         <v>7</v>
       </c>
-      <c r="BU12">
+      <c r="BV12">
         <v>27320</v>
       </c>
-      <c r="BV12" s="15">
-        <f t="shared" ref="BV12:BV14" si="4">(BT12*BU12-BT12*H12)/100</f>
+      <c r="BW12" s="15">
+        <f t="shared" ref="BW12:BW14" si="4">(BU12*BV12-BU12*H12)/100</f>
         <v>331.70059999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>397018</v>
       </c>
@@ -3129,39 +3177,43 @@
       <c r="F13" s="4">
         <v>46042</v>
       </c>
-      <c r="G13" s="27"/>
+      <c r="G13" s="27">
+        <v>0</v>
+      </c>
       <c r="H13" s="13">
         <v>723</v>
       </c>
       <c r="I13" s="13">
-        <v>900</v>
+        <v>1074</v>
       </c>
       <c r="J13" s="13">
         <v>900</v>
       </c>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13">
+      <c r="K13" s="13">
+        <v>900</v>
+      </c>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13">
         <v>1490</v>
       </c>
-      <c r="M13" s="13">
+      <c r="N13" s="13">
         <v>1210</v>
       </c>
-      <c r="N13" s="13">
+      <c r="O13" s="13">
         <v>1100</v>
       </c>
-      <c r="O13" s="13">
+      <c r="P13" s="13">
         <v>980</v>
       </c>
-      <c r="P13" s="13">
+      <c r="Q13" s="13">
         <v>932.1</v>
       </c>
-      <c r="Q13" s="13">
+      <c r="R13" s="13">
         <v>822</v>
       </c>
-      <c r="R13" s="13">
+      <c r="S13" s="13">
         <v>790</v>
       </c>
-      <c r="S13" s="13"/>
       <c r="T13" s="13"/>
       <c r="U13" s="13"/>
       <c r="V13" s="13"/>
@@ -3202,30 +3254,31 @@
       <c r="BE13" s="13"/>
       <c r="BF13" s="13"/>
       <c r="BG13" s="13"/>
-      <c r="BH13" s="29"/>
-      <c r="BI13" s="13"/>
+      <c r="BH13" s="13"/>
+      <c r="BI13" s="29"/>
       <c r="BJ13" s="13"/>
-      <c r="BK13" s="29"/>
-      <c r="BL13" s="13"/>
+      <c r="BK13" s="13"/>
+      <c r="BL13" s="29"/>
       <c r="BM13" s="13"/>
       <c r="BN13" s="13"/>
       <c r="BO13" s="13"/>
-      <c r="BP13" s="13">
+      <c r="BP13" s="13"/>
+      <c r="BQ13" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BQ13" s="13">
+      <c r="BR13" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="BR13" s="13"/>
       <c r="BS13" s="13"/>
-      <c r="BV13" s="15">
+      <c r="BT13" s="13"/>
+      <c r="BW13" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>662577</v>
       </c>
@@ -3254,204 +3307,207 @@
         <v>7204.22</v>
       </c>
       <c r="I14" s="13">
+        <v>7911</v>
+      </c>
+      <c r="J14" s="13">
+        <v>7833</v>
+      </c>
+      <c r="K14" s="13">
         <v>7687</v>
       </c>
-      <c r="J14" s="13">
-        <v>7687</v>
-      </c>
-      <c r="K14" s="13">
+      <c r="L14" s="13">
         <v>7672</v>
       </c>
-      <c r="L14" s="13">
+      <c r="M14" s="13">
         <v>7676</v>
       </c>
-      <c r="M14" s="13">
+      <c r="N14" s="13">
         <v>7844</v>
       </c>
-      <c r="N14" s="13">
+      <c r="O14" s="13">
         <v>7810</v>
       </c>
-      <c r="O14" s="13">
+      <c r="P14" s="13">
         <v>7710</v>
       </c>
-      <c r="P14" s="13">
+      <c r="Q14" s="13">
         <v>7735</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="R14" s="13">
         <v>7725</v>
       </c>
-      <c r="R14" s="13">
+      <c r="S14" s="13">
         <v>7787</v>
       </c>
-      <c r="S14" s="13">
+      <c r="T14" s="13">
         <v>7955</v>
-      </c>
-      <c r="T14" s="13">
-        <v>7627</v>
       </c>
       <c r="U14" s="13">
         <v>7627</v>
       </c>
       <c r="V14" s="13">
+        <v>7627</v>
+      </c>
+      <c r="W14" s="13">
         <v>7656</v>
       </c>
-      <c r="W14" s="13">
+      <c r="X14" s="13">
         <v>7507</v>
       </c>
-      <c r="X14" s="13">
+      <c r="Y14" s="13">
         <v>7590</v>
       </c>
-      <c r="Y14" s="13">
+      <c r="Z14" s="13">
         <v>7569</v>
       </c>
-      <c r="Z14" s="13">
+      <c r="AA14" s="13">
         <v>7269</v>
       </c>
-      <c r="AA14" s="13">
+      <c r="AB14" s="13">
         <v>7444</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AC14" s="13">
         <v>7205</v>
       </c>
-      <c r="AC14" s="13">
+      <c r="AD14" s="13">
         <v>7298</v>
       </c>
-      <c r="AD14" s="13">
+      <c r="AE14" s="13">
         <v>7222</v>
       </c>
-      <c r="AE14" s="13">
+      <c r="AF14" s="13">
         <v>7079</v>
       </c>
-      <c r="AF14" s="13">
+      <c r="AG14" s="13">
         <v>7140</v>
       </c>
-      <c r="AG14" s="13">
+      <c r="AH14" s="13">
         <v>7440</v>
       </c>
-      <c r="AH14" s="13">
+      <c r="AI14" s="13">
         <v>7530</v>
-      </c>
-      <c r="AI14" s="13">
-        <v>7535</v>
       </c>
       <c r="AJ14" s="13">
         <v>7535</v>
       </c>
       <c r="AK14" s="13">
+        <v>7535</v>
+      </c>
+      <c r="AL14" s="13">
         <v>7568</v>
       </c>
-      <c r="AL14" s="13">
+      <c r="AM14" s="13">
         <v>7699</v>
       </c>
-      <c r="AM14" s="13">
+      <c r="AN14" s="13">
         <v>7638</v>
       </c>
-      <c r="AN14" s="13">
+      <c r="AO14" s="13">
         <v>7654</v>
       </c>
-      <c r="AO14" s="13">
+      <c r="AP14" s="13">
         <v>7584</v>
       </c>
-      <c r="AP14" s="13">
+      <c r="AQ14" s="13">
         <v>7479</v>
       </c>
-      <c r="AQ14" s="13">
+      <c r="AR14" s="13">
         <v>7490</v>
       </c>
-      <c r="AR14" s="13">
+      <c r="AS14" s="13">
         <v>7480</v>
       </c>
-      <c r="AS14" s="13">
+      <c r="AT14" s="13">
         <v>7270</v>
       </c>
-      <c r="AT14" s="13">
+      <c r="AU14" s="13">
         <v>7163</v>
       </c>
-      <c r="AU14" s="13">
+      <c r="AV14" s="13">
         <v>7231</v>
-      </c>
-      <c r="AV14" s="13">
-        <v>7100</v>
       </c>
       <c r="AW14" s="13">
         <v>7100</v>
       </c>
       <c r="AX14" s="13">
+        <v>7100</v>
+      </c>
+      <c r="AY14" s="13">
         <v>7027</v>
       </c>
-      <c r="AY14" s="13">
+      <c r="AZ14" s="13">
         <v>6984</v>
       </c>
-      <c r="AZ14" s="13">
+      <c r="BA14" s="13">
         <v>6944</v>
       </c>
-      <c r="BA14" s="13">
+      <c r="BB14" s="13">
         <v>6924</v>
       </c>
-      <c r="BB14" s="13">
+      <c r="BC14" s="13">
         <v>6930</v>
       </c>
-      <c r="BC14" s="13">
+      <c r="BD14" s="13">
         <v>6938</v>
       </c>
-      <c r="BD14" s="13">
+      <c r="BE14" s="13">
         <v>6989</v>
       </c>
-      <c r="BE14" s="13">
+      <c r="BF14" s="13">
         <v>6871</v>
       </c>
-      <c r="BF14" s="13">
+      <c r="BG14" s="13">
         <v>6943</v>
       </c>
-      <c r="BG14" s="13">
+      <c r="BH14" s="13">
         <v>7040</v>
       </c>
-      <c r="BH14" s="29">
+      <c r="BI14" s="29">
         <v>6696</v>
       </c>
-      <c r="BI14" s="13">
+      <c r="BJ14" s="13">
         <v>6965</v>
       </c>
-      <c r="BJ14" s="13">
+      <c r="BK14" s="13">
         <v>6788</v>
       </c>
-      <c r="BK14" s="29">
+      <c r="BL14" s="29">
         <v>6696</v>
       </c>
-      <c r="BL14" s="13">
+      <c r="BM14" s="13">
         <v>6625</v>
       </c>
-      <c r="BM14" s="13">
+      <c r="BN14" s="13">
         <v>6660</v>
       </c>
-      <c r="BN14" s="13">
+      <c r="BO14" s="13">
         <v>6791</v>
       </c>
-      <c r="BO14" s="13">
+      <c r="BP14" s="13">
         <v>6610</v>
       </c>
-      <c r="BP14" s="13">
+      <c r="BQ14" s="13">
         <f t="shared" si="0"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BQ14" s="13">
+      <c r="BR14" s="13">
         <f t="shared" si="2"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BR14" s="13">
-        <f t="shared" ref="BR14" si="5">(BQ14-BP14)</f>
+      <c r="BS14" s="13">
+        <f t="shared" ref="BS14" si="5">(BR14-BQ14)</f>
         <v>0</v>
       </c>
-      <c r="BS14" s="13">
-        <f>((BG14-H14)/H14)*100</f>
+      <c r="BT14" s="13">
+        <f>((BH14-H14)/H14)*100</f>
         <v>-2.2794972946411995</v>
       </c>
-      <c r="BV14" s="15">
+      <c r="BW14" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>5137534</v>
       </c>
@@ -3480,72 +3536,74 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
-        <v>11946.75</v>
+        <v>11855.12</v>
       </c>
       <c r="J15" s="13">
         <v>11946.75</v>
       </c>
       <c r="K15" s="13">
-        <v>14679.12</v>
+        <v>11946.75</v>
       </c>
       <c r="L15" s="13">
         <v>14679.12</v>
       </c>
       <c r="M15" s="13">
+        <v>14679.12</v>
+      </c>
+      <c r="N15" s="13">
         <v>13968</v>
       </c>
-      <c r="N15" s="13">
+      <c r="O15" s="13">
         <v>15528.12</v>
       </c>
-      <c r="O15" s="13">
+      <c r="P15" s="13">
         <v>14358.25</v>
       </c>
-      <c r="P15" s="13">
+      <c r="Q15" s="13">
         <v>14385.75</v>
       </c>
-      <c r="Q15" s="13">
+      <c r="R15" s="13">
         <v>13880</v>
       </c>
-      <c r="R15" s="13">
+      <c r="S15" s="13">
         <v>13610.62</v>
       </c>
-      <c r="S15" s="13">
+      <c r="T15" s="13">
         <v>13016</v>
       </c>
-      <c r="T15" s="13">
+      <c r="U15" s="13">
         <v>12487.37</v>
       </c>
-      <c r="U15" s="13">
+      <c r="V15" s="13">
         <v>12638.62</v>
       </c>
-      <c r="V15" s="13">
+      <c r="W15" s="13">
         <v>12533.87</v>
       </c>
-      <c r="W15" s="13">
+      <c r="X15" s="13">
         <v>11299.5</v>
       </c>
-      <c r="X15" s="13">
+      <c r="Y15" s="13">
         <v>11193.12</v>
       </c>
-      <c r="Y15" s="13">
+      <c r="Z15" s="13">
         <v>11548.62</v>
       </c>
-      <c r="Z15" s="13">
+      <c r="AA15" s="13">
         <v>11125.62</v>
       </c>
-      <c r="AA15" s="13">
+      <c r="AB15" s="13">
         <v>10932.12</v>
       </c>
-      <c r="AB15" s="13">
+      <c r="AC15" s="13">
         <v>11095.62</v>
       </c>
-      <c r="AC15" s="13">
+      <c r="AD15" s="13">
         <v>10910.58</v>
       </c>
-      <c r="AD15" s="13">
+      <c r="AE15" s="13">
         <v>11609.37</v>
       </c>
-      <c r="AE15" s="13"/>
       <c r="AF15" s="13"/>
       <c r="AG15" s="13"/>
       <c r="AH15" s="13"/>
@@ -3555,8 +3613,8 @@
       <c r="AL15" s="13"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="13"/>
-      <c r="AO15" s="14"/>
-      <c r="AP15" s="13"/>
+      <c r="AO15" s="13"/>
+      <c r="AP15" s="14"/>
       <c r="AQ15" s="13"/>
       <c r="AR15" s="13"/>
       <c r="AS15" s="13"/>
@@ -3574,36 +3632,37 @@
       <c r="BE15" s="13"/>
       <c r="BF15" s="13"/>
       <c r="BG15" s="13"/>
-      <c r="BH15" s="29"/>
-      <c r="BI15" s="13"/>
+      <c r="BH15" s="13"/>
+      <c r="BI15" s="29"/>
       <c r="BJ15" s="13"/>
-      <c r="BK15" s="29"/>
-      <c r="BL15" s="13"/>
+      <c r="BK15" s="13"/>
+      <c r="BL15" s="29"/>
       <c r="BM15" s="13"/>
       <c r="BN15" s="13"/>
       <c r="BO15" s="13"/>
-      <c r="BP15" s="13">
+      <c r="BP15" s="13"/>
+      <c r="BQ15" s="13">
         <f t="shared" si="0"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BQ15" s="13">
+      <c r="BR15" s="13">
         <f t="shared" si="2"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BR15" s="13">
-        <f t="shared" ref="BR15:BR18" si="6">(BQ15-BP15)</f>
+      <c r="BS15" s="13">
+        <f t="shared" ref="BS15:BS18" si="6">(BR15-BQ15)</f>
         <v>0</v>
       </c>
-      <c r="BS15" s="13">
-        <f>((BG15-H15)/H15)*100</f>
+      <c r="BT15" s="13">
+        <f>((BH15-H15)/H15)*100</f>
         <v>-100</v>
       </c>
-      <c r="BV15" s="15">
-        <f t="shared" ref="BV15:BV18" si="7">(BT15*BU15-BT15*H15)/100</f>
+      <c r="BW15" s="15">
+        <f t="shared" ref="BW15:BW18" si="7">(BU15*BV15-BU15*H15)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>5135470</v>
       </c>
@@ -3632,210 +3691,213 @@
         <v>199.49</v>
       </c>
       <c r="I16" s="13">
+        <v>218.38</v>
+      </c>
+      <c r="J16" s="13">
+        <v>218.36</v>
+      </c>
+      <c r="K16" s="13">
         <v>223.13</v>
       </c>
-      <c r="J16" s="13">
-        <v>223.13</v>
-      </c>
-      <c r="K16" s="13">
+      <c r="L16" s="13">
         <v>227.54</v>
       </c>
-      <c r="L16" s="13">
+      <c r="M16" s="13">
         <v>226.96</v>
       </c>
-      <c r="M16" s="13">
+      <c r="N16" s="13">
         <v>225.24</v>
       </c>
-      <c r="N16" s="13">
+      <c r="O16" s="13">
         <v>223.25</v>
-      </c>
-      <c r="O16" s="13">
-        <v>219.14</v>
       </c>
       <c r="P16" s="13">
         <v>219.14</v>
       </c>
       <c r="Q16" s="13">
+        <v>219.14</v>
+      </c>
+      <c r="R16" s="13">
         <v>219.3</v>
       </c>
-      <c r="R16" s="13">
+      <c r="S16" s="13">
         <v>222.79</v>
       </c>
-      <c r="S16" s="13">
+      <c r="T16" s="13">
         <v>221.16</v>
       </c>
-      <c r="T16" s="13">
+      <c r="U16" s="13">
         <v>220.66</v>
       </c>
-      <c r="U16" s="13">
+      <c r="V16" s="13">
         <v>222.06</v>
       </c>
-      <c r="V16" s="13">
+      <c r="W16" s="13">
         <v>218.71</v>
       </c>
-      <c r="W16" s="13">
+      <c r="X16" s="13">
         <v>216.74</v>
       </c>
-      <c r="X16" s="13">
+      <c r="Y16" s="13">
         <v>216.04</v>
-      </c>
-      <c r="Y16" s="13">
-        <v>210.69</v>
       </c>
       <c r="Z16" s="13">
         <v>210.69</v>
       </c>
       <c r="AA16" s="13">
+        <v>210.69</v>
+      </c>
+      <c r="AB16" s="13">
         <v>198</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AC16" s="13">
         <v>196.74</v>
       </c>
-      <c r="AC16" s="13">
+      <c r="AD16" s="13">
         <v>192.56</v>
       </c>
-      <c r="AD16" s="13">
+      <c r="AE16" s="13">
         <v>192.23</v>
       </c>
-      <c r="AE16" s="13">
+      <c r="AF16" s="13">
         <v>191.19</v>
       </c>
-      <c r="AF16" s="13">
+      <c r="AG16" s="13">
         <v>193.62</v>
       </c>
-      <c r="AG16" s="13">
+      <c r="AH16" s="13">
         <v>190.75</v>
       </c>
-      <c r="AH16" s="13">
+      <c r="AI16" s="13">
         <v>189.06</v>
-      </c>
-      <c r="AI16" s="13">
-        <v>182.73</v>
       </c>
       <c r="AJ16" s="13">
         <v>182.73</v>
       </c>
       <c r="AK16" s="13">
+        <v>182.73</v>
+      </c>
+      <c r="AL16" s="13">
         <v>177.92</v>
       </c>
-      <c r="AL16" s="13">
+      <c r="AM16" s="13">
         <v>179.16</v>
       </c>
-      <c r="AM16" s="13">
+      <c r="AN16" s="13">
         <v>179.34</v>
-      </c>
-      <c r="AN16" s="13">
-        <v>176.5</v>
       </c>
       <c r="AO16" s="13">
         <v>176.5</v>
       </c>
       <c r="AP16" s="13">
+        <v>176.5</v>
+      </c>
+      <c r="AQ16" s="13">
         <v>175.93</v>
       </c>
-      <c r="AQ16" s="13">
+      <c r="AR16" s="13">
         <v>174.51</v>
       </c>
-      <c r="AR16" s="13">
+      <c r="AS16" s="13">
         <v>173.91</v>
       </c>
-      <c r="AS16" s="13">
+      <c r="AT16" s="13">
         <v>177.1</v>
       </c>
-      <c r="AT16" s="13">
+      <c r="AU16" s="13">
         <v>178.24</v>
       </c>
-      <c r="AU16" s="13">
+      <c r="AV16" s="13">
         <v>176.52</v>
       </c>
-      <c r="AV16" s="13">
+      <c r="AW16" s="13">
         <v>178.27</v>
       </c>
-      <c r="AW16" s="13">
+      <c r="AX16" s="13">
         <v>175.29</v>
       </c>
-      <c r="AX16" s="13">
+      <c r="AY16" s="13">
         <v>175.34</v>
       </c>
-      <c r="AY16" s="13">
+      <c r="AZ16" s="13">
         <v>174.41</v>
       </c>
-      <c r="AZ16" s="13">
+      <c r="BA16" s="13">
         <v>176.22</v>
       </c>
-      <c r="BA16" s="13">
+      <c r="BB16" s="13">
         <v>174</v>
       </c>
-      <c r="BB16" s="13">
+      <c r="BC16" s="13">
         <v>176.35</v>
       </c>
-      <c r="BC16" s="13">
+      <c r="BD16" s="13">
         <v>177.71</v>
       </c>
-      <c r="BD16" s="13">
+      <c r="BE16" s="13">
         <v>180.08</v>
       </c>
-      <c r="BE16" s="13">
+      <c r="BF16" s="13">
         <v>181.96</v>
       </c>
-      <c r="BF16" s="13">
+      <c r="BG16" s="13">
         <v>182.9</v>
       </c>
-      <c r="BG16" s="13">
+      <c r="BH16" s="13">
         <v>181.86</v>
       </c>
-      <c r="BH16" s="29">
+      <c r="BI16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BI16" s="13">
+      <c r="BJ16" s="13">
         <v>181.07</v>
       </c>
-      <c r="BJ16" s="13">
+      <c r="BK16" s="13">
         <v>182.56</v>
       </c>
-      <c r="BK16" s="29">
+      <c r="BL16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BL16" s="13">
+      <c r="BM16" s="13">
         <v>178.86</v>
       </c>
-      <c r="BM16" s="13">
+      <c r="BN16" s="13">
         <v>180.16</v>
       </c>
-      <c r="BN16" s="13">
+      <c r="BO16" s="13">
         <v>179.56</v>
       </c>
-      <c r="BO16" s="13">
+      <c r="BP16" s="13">
         <v>176.55</v>
       </c>
-      <c r="BP16" s="13">
+      <c r="BQ16" s="13">
         <f t="shared" si="0"/>
         <v>1413.1220000000008</v>
       </c>
-      <c r="BQ16" s="13">
+      <c r="BR16" s="13">
         <f t="shared" si="2"/>
         <v>997.45</v>
       </c>
-      <c r="BR16" s="13">
+      <c r="BS16" s="13">
         <f t="shared" si="6"/>
         <v>-415.67200000000071</v>
       </c>
-      <c r="BS16" s="13">
-        <f>((BG16-H16)/H16)*100</f>
+      <c r="BT16" s="13">
+        <f>((BH16-H16)/H16)*100</f>
         <v>-8.8375357160759904</v>
       </c>
-      <c r="BT16">
+      <c r="BU16">
         <v>1864</v>
       </c>
-      <c r="BU16">
+      <c r="BV16">
         <v>177.19</v>
       </c>
-      <c r="BV16" s="15">
+      <c r="BW16" s="15">
         <f t="shared" si="7"/>
         <v>-415.67200000000071</v>
       </c>
     </row>
-    <row r="17" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>5134135</v>
       </c>
@@ -3864,16 +3926,16 @@
         <v>159.65</v>
       </c>
       <c r="I17" s="13">
+        <v>184.42</v>
+      </c>
+      <c r="J17" s="13">
+        <v>184.42</v>
+      </c>
+      <c r="K17" s="13">
         <v>199.37</v>
       </c>
-      <c r="J17" s="13">
-        <v>199.37</v>
-      </c>
-      <c r="K17" s="13">
+      <c r="L17" s="13">
         <v>194.88</v>
-      </c>
-      <c r="L17" s="13">
-        <v>189.51</v>
       </c>
       <c r="M17" s="13">
         <v>189.51</v>
@@ -3882,13 +3944,13 @@
         <v>189.51</v>
       </c>
       <c r="O17" s="13">
-        <v>185.52</v>
+        <v>189.51</v>
       </c>
       <c r="P17" s="13">
         <v>185.52</v>
       </c>
       <c r="Q17" s="13">
-        <v>178.98</v>
+        <v>185.52</v>
       </c>
       <c r="R17" s="13">
         <v>178.98</v>
@@ -3897,7 +3959,7 @@
         <v>178.98</v>
       </c>
       <c r="T17" s="13">
-        <v>170.7</v>
+        <v>178.98</v>
       </c>
       <c r="U17" s="13">
         <v>170.7</v>
@@ -3906,10 +3968,10 @@
         <v>170.7</v>
       </c>
       <c r="W17" s="13">
+        <v>170.7</v>
+      </c>
+      <c r="X17" s="13">
         <v>170.45</v>
-      </c>
-      <c r="X17" s="13">
-        <v>160.84</v>
       </c>
       <c r="Y17" s="13">
         <v>160.84</v>
@@ -3918,15 +3980,17 @@
         <v>160.84</v>
       </c>
       <c r="AA17" s="13">
+        <v>160.84</v>
+      </c>
+      <c r="AB17" s="13">
         <v>159.02000000000001</v>
-      </c>
-      <c r="AB17" s="13">
-        <v>159.65</v>
       </c>
       <c r="AC17" s="13">
         <v>159.65</v>
       </c>
-      <c r="AD17" s="13"/>
+      <c r="AD17" s="13">
+        <v>159.65</v>
+      </c>
       <c r="AE17" s="13"/>
       <c r="AF17" s="13"/>
       <c r="AG17" s="13"/>
@@ -3956,36 +4020,37 @@
       <c r="BE17" s="13"/>
       <c r="BF17" s="13"/>
       <c r="BG17" s="13"/>
-      <c r="BH17" s="29"/>
-      <c r="BI17" s="13"/>
+      <c r="BH17" s="13"/>
+      <c r="BI17" s="29"/>
       <c r="BJ17" s="13"/>
-      <c r="BK17" s="29"/>
-      <c r="BL17" s="13"/>
+      <c r="BK17" s="13"/>
+      <c r="BL17" s="29"/>
       <c r="BM17" s="13"/>
       <c r="BN17" s="13"/>
       <c r="BO17" s="13"/>
-      <c r="BP17" s="13">
+      <c r="BP17" s="13"/>
+      <c r="BQ17" s="13">
         <f t="shared" si="0"/>
         <v>957.9</v>
       </c>
-      <c r="BQ17" s="13">
+      <c r="BR17" s="13">
         <f t="shared" si="2"/>
         <v>957.9</v>
       </c>
-      <c r="BR17" s="13">
-        <f t="shared" ref="BR17" si="8">(BQ17-BP17)</f>
+      <c r="BS17" s="13">
+        <f t="shared" ref="BS17" si="8">(BR17-BQ17)</f>
         <v>0</v>
       </c>
-      <c r="BS17" s="13">
-        <f>((BG17-H17)/H17)*100</f>
+      <c r="BT17" s="13">
+        <f>((BH17-H17)/H17)*100</f>
         <v>-100</v>
       </c>
-      <c r="BV17" s="15">
+      <c r="BW17" s="15">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1168723</v>
       </c>
@@ -4014,75 +4079,77 @@
         <v>1434</v>
       </c>
       <c r="I18" s="13">
+        <v>1886</v>
+      </c>
+      <c r="J18" s="13">
+        <v>1818</v>
+      </c>
+      <c r="K18" s="13">
         <v>1785</v>
       </c>
-      <c r="J18" s="13">
-        <v>1785</v>
-      </c>
-      <c r="K18" s="13">
+      <c r="L18" s="13">
         <v>1828</v>
       </c>
-      <c r="L18" s="13">
+      <c r="M18" s="13">
         <v>1811</v>
       </c>
-      <c r="M18" s="13">
+      <c r="N18" s="13">
         <v>1825</v>
       </c>
-      <c r="N18" s="13">
+      <c r="O18" s="13">
         <v>1831</v>
       </c>
-      <c r="O18" s="13">
+      <c r="P18" s="13">
         <v>1799</v>
       </c>
-      <c r="P18" s="13">
+      <c r="Q18" s="13">
         <v>1757</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="R18" s="13">
         <v>1698</v>
       </c>
-      <c r="R18" s="13">
+      <c r="S18" s="13">
         <v>1694</v>
       </c>
-      <c r="S18" s="13">
+      <c r="T18" s="13">
         <v>1671</v>
-      </c>
-      <c r="T18" s="13">
-        <v>1660</v>
       </c>
       <c r="U18" s="13">
         <v>1660</v>
       </c>
       <c r="V18" s="13">
+        <v>1660</v>
+      </c>
+      <c r="W18" s="13">
         <v>1646</v>
       </c>
-      <c r="W18" s="13">
+      <c r="X18" s="13">
         <v>1648</v>
       </c>
-      <c r="X18" s="13">
+      <c r="Y18" s="13">
         <v>1614</v>
       </c>
-      <c r="Y18" s="13">
+      <c r="Z18" s="13">
         <v>1626</v>
       </c>
-      <c r="Z18" s="13">
+      <c r="AA18" s="13">
         <v>1587</v>
       </c>
-      <c r="AA18" s="13">
+      <c r="AB18" s="13">
         <v>1548</v>
       </c>
-      <c r="AB18" s="13">
+      <c r="AC18" s="13">
         <v>1500</v>
       </c>
-      <c r="AC18" s="13">
+      <c r="AD18" s="13">
         <v>1491</v>
       </c>
-      <c r="AD18" s="13">
+      <c r="AE18" s="13">
         <v>1444</v>
       </c>
-      <c r="AE18" s="13">
+      <c r="AF18" s="13">
         <v>1431</v>
       </c>
-      <c r="AF18" s="13"/>
       <c r="AG18" s="13"/>
       <c r="AH18" s="13"/>
       <c r="AI18" s="13"/>
@@ -4108,64 +4175,65 @@
       <c r="BC18" s="13"/>
       <c r="BD18" s="13"/>
       <c r="BE18" s="13"/>
-      <c r="BF18" s="13">
-        <v>1788</v>
-      </c>
+      <c r="BF18" s="13"/>
       <c r="BG18" s="13">
         <v>1788</v>
       </c>
-      <c r="BH18" s="29">
+      <c r="BH18" s="13">
+        <v>1788</v>
+      </c>
+      <c r="BI18" s="29">
         <v>1780</v>
       </c>
-      <c r="BI18" s="13">
+      <c r="BJ18" s="13">
         <v>1814</v>
       </c>
-      <c r="BJ18" s="13">
+      <c r="BK18" s="13">
         <v>1794</v>
       </c>
-      <c r="BK18" s="29">
+      <c r="BL18" s="29">
         <v>1780</v>
       </c>
-      <c r="BL18" s="13">
+      <c r="BM18" s="13">
         <v>1772</v>
       </c>
-      <c r="BM18" s="13">
+      <c r="BN18" s="13">
         <v>1798</v>
       </c>
-      <c r="BN18" s="13">
+      <c r="BO18" s="13">
         <v>1806</v>
       </c>
-      <c r="BO18" s="13">
+      <c r="BP18" s="13">
         <v>1801</v>
       </c>
-      <c r="BP18" s="13">
+      <c r="BQ18" s="13">
         <f t="shared" si="0"/>
         <v>292.79999999999995</v>
       </c>
-      <c r="BQ18" s="13">
+      <c r="BR18" s="13">
         <f t="shared" si="2"/>
         <v>645.29999999999995</v>
       </c>
-      <c r="BR18" s="13">
+      <c r="BS18" s="13">
         <f t="shared" si="6"/>
         <v>352.5</v>
       </c>
-      <c r="BS18" s="13">
-        <f>((BG18-H18)/H18)*100</f>
+      <c r="BT18" s="13">
+        <f>((BH18-H18)/H18)*100</f>
         <v>24.686192468619247</v>
       </c>
-      <c r="BT18">
+      <c r="BU18">
         <v>100</v>
       </c>
-      <c r="BU18">
+      <c r="BV18">
         <v>1786.5</v>
       </c>
-      <c r="BV18" s="15">
+      <c r="BW18" s="15">
         <f t="shared" si="7"/>
         <v>352.5</v>
       </c>
     </row>
-    <row r="19" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1122654</v>
       </c>
@@ -4188,18 +4256,20 @@
         <v>46052</v>
       </c>
       <c r="G19" s="27">
-        <v>470</v>
+        <v>700</v>
       </c>
       <c r="H19" s="13">
-        <v>110</v>
+        <v>102.77</v>
       </c>
       <c r="I19" s="13">
+        <v>91.5</v>
+      </c>
+      <c r="J19" s="13">
+        <v>91.5</v>
+      </c>
+      <c r="K19" s="13">
         <v>132.6</v>
       </c>
-      <c r="J19" s="13">
-        <v>132.6</v>
-      </c>
-      <c r="K19" s="13"/>
       <c r="L19" s="13"/>
       <c r="M19" s="13"/>
       <c r="N19" s="13"/>
@@ -4215,22 +4285,22 @@
       <c r="X19" s="13"/>
       <c r="Y19" s="13"/>
       <c r="Z19" s="13"/>
-      <c r="AA19" s="13">
+      <c r="AA19" s="13"/>
+      <c r="AB19" s="13">
         <v>6461</v>
       </c>
-      <c r="AB19" s="13">
+      <c r="AC19" s="13">
         <v>6503</v>
       </c>
-      <c r="AC19" s="13">
+      <c r="AD19" s="13">
         <v>6535</v>
       </c>
-      <c r="AD19" s="13">
+      <c r="AE19" s="13">
         <v>6532</v>
       </c>
-      <c r="AE19" s="13">
+      <c r="AF19" s="13">
         <v>6515</v>
       </c>
-      <c r="AF19" s="13"/>
       <c r="AG19" s="13"/>
       <c r="AH19" s="13"/>
       <c r="AI19" s="13"/>
@@ -4258,35 +4328,36 @@
       <c r="BE19" s="13"/>
       <c r="BF19" s="13"/>
       <c r="BG19" s="13"/>
-      <c r="BH19" s="29"/>
-      <c r="BI19" s="13"/>
+      <c r="BH19" s="13"/>
+      <c r="BI19" s="29"/>
       <c r="BJ19" s="13"/>
-      <c r="BK19" s="29"/>
-      <c r="BL19" s="13"/>
+      <c r="BK19" s="13"/>
+      <c r="BL19" s="29"/>
       <c r="BM19" s="13"/>
       <c r="BN19" s="13"/>
       <c r="BO19" s="13"/>
-      <c r="BP19" s="13">
+      <c r="BP19" s="13"/>
+      <c r="BQ19" s="13">
         <f t="shared" si="0"/>
-        <v>517</v>
-      </c>
-      <c r="BQ19" s="13">
+        <v>719.39</v>
+      </c>
+      <c r="BR19" s="13">
         <f t="shared" si="2"/>
-        <v>517</v>
-      </c>
-      <c r="BR19" s="13"/>
+        <v>719.39</v>
+      </c>
       <c r="BS19" s="13"/>
-      <c r="BT19">
+      <c r="BT19" s="13"/>
+      <c r="BU19">
         <v>7</v>
       </c>
-      <c r="BU19">
+      <c r="BV19">
         <v>6461</v>
       </c>
-      <c r="BV19" s="15"/>
-    </row>
-    <row r="20" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BW19" s="15"/>
+    </row>
+    <row r="20" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <v>1144807</v>
+        <v>363010</v>
       </c>
       <c r="B20" s="17">
         <f>GEMINI!L12</f>
@@ -4300,11 +4371,21 @@
         <f>IF(I20&lt;GEMINI!L12,"למכור בהפסד",IF(I20&gt;GEMINI!M12,"למכור ברווח","לשמור"))</f>
         <v>למכור בהפסד</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
+      <c r="E20" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" s="28">
+        <v>46056</v>
+      </c>
+      <c r="G20" s="27">
+        <v>300</v>
+      </c>
+      <c r="H20" s="13">
+        <v>65</v>
+      </c>
+      <c r="I20" s="13">
+        <v>87.5</v>
+      </c>
       <c r="J20" s="13"/>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
@@ -4355,28 +4436,29 @@
       <c r="BE20" s="13"/>
       <c r="BF20" s="13"/>
       <c r="BG20" s="13"/>
-      <c r="BH20" s="29"/>
-      <c r="BI20" s="13"/>
+      <c r="BH20" s="13"/>
+      <c r="BI20" s="29"/>
       <c r="BJ20" s="13"/>
-      <c r="BK20" s="29"/>
-      <c r="BL20" s="13"/>
+      <c r="BK20" s="13"/>
+      <c r="BL20" s="29"/>
       <c r="BM20" s="13"/>
       <c r="BN20" s="13"/>
       <c r="BO20" s="13"/>
-      <c r="BP20" s="13">
-        <f>(G20*H20)/100-BV20</f>
-        <v>0</v>
-      </c>
+      <c r="BP20" s="13"/>
       <c r="BQ20" s="13">
+        <f>(G20*H20)/100-BW20</f>
+        <v>195</v>
+      </c>
+      <c r="BR20" s="13">
         <f>(G20*H20)/100</f>
-        <v>0</v>
-      </c>
-      <c r="BR20" s="13"/>
+        <v>195</v>
+      </c>
       <c r="BS20" s="13"/>
-      <c r="BV20" s="15"/>
-    </row>
-    <row r="21" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:74" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT20" s="13"/>
+      <c r="BW20" s="15"/>
+    </row>
+    <row r="21" spans="1:75" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4436,11 +4518,11 @@
       <c r="BE22" s="13"/>
       <c r="BF22" s="13"/>
       <c r="BG22" s="13"/>
-      <c r="BH22" s="29"/>
-      <c r="BI22" s="13"/>
+      <c r="BH22" s="13"/>
+      <c r="BI22" s="29"/>
       <c r="BJ22" s="13"/>
-      <c r="BK22" s="29"/>
-      <c r="BL22" s="13"/>
+      <c r="BK22" s="13"/>
+      <c r="BL22" s="29"/>
       <c r="BM22" s="13"/>
       <c r="BN22" s="13"/>
       <c r="BO22" s="13"/>
@@ -4448,9 +4530,10 @@
       <c r="BQ22" s="13"/>
       <c r="BR22" s="13"/>
       <c r="BS22" s="13"/>
-      <c r="BV22" s="15"/>
-    </row>
-    <row r="23" spans="1:74" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BT22" s="13"/>
+      <c r="BW22" s="15"/>
+    </row>
+    <row r="23" spans="1:75" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4460,80 +4543,80 @@
       <c r="G23" s="27"/>
       <c r="H23" s="13"/>
       <c r="I23" s="23">
-        <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19)/100</f>
-        <v>13728.55</v>
+        <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19+G20*I20)/100</f>
+        <v>14302.159599999999</v>
       </c>
       <c r="J23" s="23">
-        <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19)/100</f>
-        <v>13728.55</v>
+        <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19+G20*J20)/100</f>
+        <v>13804.511999999999</v>
       </c>
       <c r="K23" s="23">
         <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19)/100</f>
-        <v>13844.2896</v>
+        <v>14033.53</v>
       </c>
       <c r="L23" s="23">
         <f>(L2*G2+G3*L3+L4*G4+G5*L5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+L13*G13+G14*L14+L15*G15+G16*L16+G17*L17+L18*G18+G19*L19)/100</f>
-        <v>13659.785600000001</v>
+        <v>13844.2896</v>
       </c>
       <c r="M23" s="23">
         <f>(M2*G2+G3*M3+M4*G4+G5*M5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+M13*G13+G14*M14+M15*G15+G16*M16+G17*M17+M18*G18+G19*M19)/100</f>
-        <v>13683.918</v>
+        <v>13659.785600000001</v>
       </c>
       <c r="N23" s="23">
         <f>(N2*G2+G3*N3+N4*G4+G5*N5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+N13*G13+G14*N14+N15*G15+G16*N16+G17*N17+N18*G18+G19*N19)/100</f>
-        <v>13839.923600000002</v>
+        <v>13683.918</v>
       </c>
       <c r="O23" s="23">
         <f>(O2*G2+G3*O3+O4*G4+G5*O5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+O13*G13+G14*O14+O15*G15+G16*O16+G17*O17+O18*G18+G19*O19)/100</f>
-        <v>13475.503999999999</v>
+        <v>13839.923600000002</v>
       </c>
       <c r="P23" s="23">
         <f>(P2*G2+G3*P3+P4*G4+G5*P5+G6*P6+G7*P7+G8*P8+G9*P9+G10*P10+G11*P11+G12*P12+P13*G13+G14*P14+P15*G15+G16*P16+G17*P17+P18*G18+G19*P19)/100</f>
-        <v>13192.96</v>
+        <v>13475.503999999999</v>
       </c>
       <c r="Q23" s="23">
         <f>(Q2*G2+G3*Q3+Q4*G4+G5*Q5+G6*Q6+G7*Q7+G8*Q8+G9*Q9+G10*Q10+G11*Q11+G12*Q12+Q13*G13+G14*Q14+Q15*G15+G16*Q16+G17*Q17+Q18*G18+G19*Q19)/100</f>
-        <v>12923.761999999999</v>
+        <v>13192.96</v>
       </c>
       <c r="R23" s="23">
         <f>(R2*G2+G3*R3+R4*G4+G5*R5+G6*R6+G7*R7+G8*R8+G9*R9+G10*R10+G11*R11+G12*R12+R13*G13+G14*R14+R15*G15+G16*R16+G17*R17+R18*G18+G19*R19)/100</f>
+        <v>12923.761999999999</v>
+      </c>
+      <c r="S23" s="23">
+        <f>(S2*G2+G3*S3+S4*G4+G5*S5+G6*S6+G7*S7+G8*S8+G9*S9+G10*S10+G11*S11+G12*S12+S13*G13+G14*S14+S15*G15+G16*S16+G17*S17+S18*G18+G19*S19)/100</f>
         <v>13102.8776</v>
-      </c>
-      <c r="S23" s="23">
-        <f>(S3*G3+G4*S4+S5*G5+G6*S6+G7*S7+G8*S8+G9*S9+G10*S10+G11*S11+G12*S12+G14*S14+S15*G15+G16*S16+S17*G17+G18*S18+G19*S19)/100</f>
-        <v>12191.99</v>
       </c>
       <c r="T23" s="23">
         <f>(T3*G3+G4*T4+T5*G5+G6*T6+G7*T7+G8*T8+G9*T9+G10*T10+G11*T11+G12*T12+G14*T14+T15*G15+G16*T16+T17*G17+G18*T18+G19*T19)/100</f>
-        <v>11970.357599999999</v>
+        <v>12191.99</v>
       </c>
       <c r="U23" s="23">
         <f>(U3*G3+G4*U4+U5*G5+G6*U6+G7*U7+G8*U8+G9*U9+G10*U10+G11*U11+G12*U12+G14*U14+U15*G15+G16*U16+U17*G17+G18*U18+G19*U19)/100</f>
-        <v>11989.4576</v>
+        <v>11970.357599999999</v>
       </c>
       <c r="V23" s="23">
         <f>(V3*G3+G4*V4+V5*G5+G6*V6+G7*V7+G8*V8+G9*V9+G10*V10+G11*V11+G12*V12+G14*V14+V15*G15+G16*V16+V17*G17+G18*V18+G19*V19)/100</f>
-        <v>11896.177600000001</v>
+        <v>11989.4576</v>
       </c>
       <c r="W23" s="23">
         <f>(W3*G3+G4*W4+W5*G5+G6*W6+G7*W7+G8*W8+G9*W9+G10*W10+G11*W11+G12*W12+G14*W14+W15*G15+G16*W16+W17*G17+G18*W18+G19*W19)/100</f>
-        <v>11552.98</v>
+        <v>11896.177600000001</v>
       </c>
       <c r="X23" s="23">
         <f>(X3*G3+G4*X4+X5*G5+G6*X6+G7*X7+G8*X8+G9*X9+G10*X10+G11*X11+G12*X12+G14*X14+X15*G15+G16*X16+X17*G17+G18*X18+G19*X19)/100</f>
-        <v>11467.277599999999</v>
+        <v>11552.98</v>
       </c>
       <c r="Y23" s="23">
         <f>(Y3*G3+G4*Y4+Y5*G5+G6*Y6+G7*Y7+G8*Y8+G9*Y9+G10*Y10+G11*Y11+G12*Y12+G14*Y14+Y15*G15+G16*Y16+Y17*G17+G18*Y18+G19*Y19)/100</f>
+        <v>11467.277599999999</v>
+      </c>
+      <c r="Z23" s="23">
+        <f>(Z3*G3+G4*Z4+Z5*G5+G6*Z6+G7*Z7+G8*Z8+G9*Z9+G10*Z10+G11*Z11+G12*Z12+G14*Z14+Z15*G15+G16*Z16+Z17*G17+G18*Z18+G19*Z19)/100</f>
         <v>10332.035599999999</v>
       </c>
-      <c r="Z23" s="23">
-        <f>(Z5*G5+G6*Z6+Z7*G7+G8*Z8+G9*Z9+G10*Z10+G11*Z11+G12*Z12+G14*Z14+G20*Z20+G15*Z15+Z16*G16+G17*Z17+Z18*G18+G19*Z19)/100</f>
+      <c r="AA23" s="23">
+        <f>(AA5*G5+G6*AA6+AA7*G7+G8*AA8+G9*AA9+G10*AA10+G11*AA11+G12*AA12+G14*AA14+G20*AA20+G15*AA15+AA16*G16+G17*AA17+AA18*G18+G19*AA19)/100</f>
         <v>9234.9995999999992</v>
-      </c>
-      <c r="AA23" s="23" t="e">
-        <f>(AA5*G5+G7*AA7+AA8*G8+G9*AA9+#REF!*#REF!+G10*AA10+G11*AA11+G12*AA12+G14*AA14+G19*AA19+G20*AA20+AA6*G6+G15*AA15+#REF!*#REF!+G16*AA16+G17*AA17+AA18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AA3+#REF!*#REF!)/100</f>
-        <v>#REF!</v>
       </c>
       <c r="AB23" s="23" t="e">
         <f>(AB5*G5+G7*AB7+AB8*G8+G9*AB9+#REF!*#REF!+G10*AB10+G11*AB11+G12*AB12+G14*AB14+G19*AB19+G20*AB20+AB6*G6+G15*AB15+#REF!*#REF!+G16*AB16+G17*AB17+AB18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AB3+#REF!*#REF!)/100</f>
@@ -4544,11 +4627,11 @@
         <v>#REF!</v>
       </c>
       <c r="AD23" s="23" t="e">
-        <f>(AD5*G5+G7*AD7+AD8*G8+G9*AD9+#REF!*#REF!+G10*AD10+G11*AD11+G12*AD12+G14*AD14+G19*AD19+G20*AD20+AD6*G6+G15*AD15+#REF!*#REF!+G16*AD16+G18*AD18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AD3+#REF!*#REF!+G4*AD4)/100</f>
+        <f>(AD5*G5+G7*AD7+AD8*G8+G9*AD9+#REF!*#REF!+G10*AD10+G11*AD11+G12*AD12+G14*AD14+G19*AD19+G20*AD20+AD6*G6+G15*AD15+#REF!*#REF!+G16*AD16+G17*AD17+AD18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AD3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AE23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AE3*G3+#REF!*#REF!+G4*AE4+G5*AE5+G7*AE7+G8*AE8+G9*AE9+#REF!*#REF!+G10*AE10+AE11*G11+G12*AE12+AE14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AE20+AE6*G6+#REF!*#REF!+G16*AE16+G18*AE18+G19*AE19)/100</f>
+        <f>(AE5*G5+G7*AE7+AE8*G8+G9*AE9+#REF!*#REF!+G10*AE10+G11*AE11+G12*AE12+G14*AE14+G19*AE19+G20*AE20+AE6*G6+G15*AE15+#REF!*#REF!+G16*AE16+G18*AE18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AE3+#REF!*#REF!+G4*AE4)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AF23" s="23" t="e">
@@ -4556,7 +4639,7 @@
         <v>#REF!</v>
       </c>
       <c r="AG23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AG3*G3+#REF!*#REF!+G4*AG4+G5*AG5+AG7*G7+AG8*G8+AG9*G9+#REF!*#REF!+G10*AG10+AG11*G11+G12*AG12+AG14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AG20+G6*AG6+#REF!*#REF!+G16*AG16+G18*AG18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AG3*G3+#REF!*#REF!+G4*AG4+G5*AG5+G7*AG7+G8*AG8+G9*AG9+#REF!*#REF!+G10*AG10+AG11*G11+G12*AG12+AG14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AG20+AG6*G6+#REF!*#REF!+G16*AG16+G18*AG18+G19*AG19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AH23" s="23" t="e">
@@ -4564,19 +4647,19 @@
         <v>#REF!</v>
       </c>
       <c r="AI23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AI3*G3+#REF!*#REF!+G4*AI4+G8*AI8+AI9*G9+#REF!*#REF!+AI10*G10+G11*AI11+G14*AI14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AI6+#REF!*#REF!+G16*AI16+G18*AI18+G7*AI7+G5*AI5+G12*AI12+G20*AI20)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AI3*G3+#REF!*#REF!+G4*AI4+G5*AI5+AI7*G7+AI8*G8+AI9*G9+#REF!*#REF!+G10*AI10+AI11*G11+G12*AI12+AI14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AI20+G6*AI6+#REF!*#REF!+G16*AI16+G18*AI18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AJ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AJ3*G3+#REF!*#REF!+G4*AJ4+G8*AJ8+AJ9*G9+#REF!*#REF!+AJ10*G10+G11*AJ11+G14*AJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AJ6+#REF!*#REF!+G16*AJ16+G18*AJ18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AJ3*G3+#REF!*#REF!+G4*AJ4+G8*AJ8+AJ9*G9+#REF!*#REF!+AJ10*G10+G11*AJ11+G14*AJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AJ6+#REF!*#REF!+G16*AJ16+G18*AJ18+G7*AJ7+G5*AJ5+G12*AJ12+G20*AJ20)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AK23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AK3*G3+#REF!*#REF!+G4*AK4+G8*AK8+G9*AK9+#REF!*#REF!+G10*AK10+AK11*G11+AK14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AK6*G6+#REF!*#REF!+G16*AK16+G18*AK18+G19*AK19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AK3*G3+#REF!*#REF!+G4*AK4+G8*AK8+AK9*G9+#REF!*#REF!+AK10*G10+G11*AK11+G14*AK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AK6+#REF!*#REF!+G16*AK16+G18*AK18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AL23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AL3*G3+#REF!*#REF!+G4*AL4+G8*AL8+AL9*G9+#REF!*#REF!+AL10*G10+G11*AL11+G14*AL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AL6+#REF!*#REF!+G16*AL16+G18*AL18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AL3*G3+#REF!*#REF!+G4*AL4+G8*AL8+G9*AL9+#REF!*#REF!+G10*AL10+AL11*G11+AL14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AL6*G6+#REF!*#REF!+G16*AL16+G18*AL18+G19*AL19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AM23" s="23" t="e">
@@ -4584,7 +4667,7 @@
         <v>#REF!</v>
       </c>
       <c r="AN23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+AN9*G9+AN10*G10+AN11*G11+G14*AN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AN6+#REF!*#REF!+G16*AN16+G18*AN18+G19*AN19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+AN9*G9+#REF!*#REF!+AN10*G10+G11*AN11+G14*AN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AN6+#REF!*#REF!+G16*AN16+G18*AN18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AO23" s="23" t="e">
@@ -4604,19 +4687,19 @@
         <v>#REF!</v>
       </c>
       <c r="AS23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AS3*G3+#REF!*#REF!+G4*AS4+G8*AS8+AS9*G9+AS10*G10+AS11*G11+G14*AS14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AS6+#REF!*#REF!+G16*AS16+G18*AS18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AS3*G3+#REF!*#REF!+G4*AS4+G8*AS8+AS9*G9+AS10*G10+AS11*G11+G14*AS14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AS6+#REF!*#REF!+G16*AS16+G18*AS18+G19*AS19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AT23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AT3*G3+#REF!*#REF!+G4*AT4+G8*AT8+AT10*G10+AT11*G11+G14*AT14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AT6+#REF!*#REF!+G16*AT16+G18*AT18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AT3*G3+#REF!*#REF!+G4*AT4+G8*AT8+AT9*G9+AT10*G10+AT11*G11+G14*AT14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AT6+#REF!*#REF!+G16*AT16+G18*AT18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AU23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AU3*G3+#REF!*#REF!+G4*AU4+G8*AU8+G10*AU10+AU11*G11+AU14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AU6*G6+#REF!*#REF!+G16*AU16+G18*AU18+G19*AU19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AU3*G3+#REF!*#REF!+G4*AU4+G8*AU8+AU10*G10+AU11*G11+G14*AU14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AU6+#REF!*#REF!+G16*AU16+G18*AU18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AV23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AV3*G3+#REF!*#REF!+G4*AV4+G10*AV10+AV11*G11+AV14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AV6*G6+#REF!*#REF!+G16*AV16+G18*AV18+G19*AV19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AV3*G3+#REF!*#REF!+G4*AV4+G8*AV8+G10*AV10+AV11*G11+AV14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AV6*G6+#REF!*#REF!+G16*AV16+G18*AV18+G19*AV19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AW23" s="23" t="e">
@@ -4628,7 +4711,7 @@
         <v>#REF!</v>
       </c>
       <c r="AY23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AY3*G3+#REF!*#REF!+G4*AY4+G10*AY10+AY11*G11+AY14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AY6*G6+G16*AY16+G18*AY18+G19*AY19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AY3*G3+#REF!*#REF!+G4*AY4+G10*AY10+AY11*G11+AY14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AY6*G6+#REF!*#REF!+G16*AY16+G18*AY18+G19*AY19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AZ23" s="23" t="e">
@@ -4656,15 +4739,15 @@
         <v>#REF!</v>
       </c>
       <c r="BF23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BF3*G3+#REF!*#REF!+G4*BF4+G10*BF10+G11*BF11+G14*BF14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BF6+BF16*G16+G18*BF18+G19*BF19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BF3*G3+#REF!*#REF!+G4*BF4+G10*BF10+BF11*G11+BF14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BF6*G6+G16*BF16+G18*BF18+G19*BF19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BG23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BG3*G3+#REF!*#REF!+G4*BG4+G10*BG10+G14*BG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BG6+BG16*G16+G18*BG18+G19*BG19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BG3*G3+#REF!*#REF!+G4*BG4+G10*BG10+G11*BG11+G14*BG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BG6+BG16*G16+G18*BG18+G19*BG19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BH23" s="23" t="e">
-        <f>(#REF!*#REF!+BH3*G3+G4*BH4+G14*BH14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BH6+BH16*G16+G18*BH18+G19*BH19+G22*BH22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BH3*G3+#REF!*#REF!+G4*BH4+G10*BH10+G14*BH14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BH6+BH16*G16+G18*BH18+G19*BH19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BI23" s="23" t="e">
@@ -4675,16 +4758,16 @@
         <f>(#REF!*#REF!+BJ3*G3+G4*BJ4+G14*BJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BJ6+BJ16*G16+G18*BJ18+G19*BJ19+G22*BJ22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BK23" s="30" t="e">
+      <c r="BK23" s="23" t="e">
         <f>(#REF!*#REF!+BK3*G3+G4*BK4+G14*BK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BK6+BK16*G16+G18*BK18+G19*BK19+G22*BK22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BL23" s="23" t="e">
+      <c r="BL23" s="30" t="e">
         <f>(#REF!*#REF!+BL3*G3+G4*BL4+G14*BL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BL6+BL16*G16+G18*BL18+G19*BL19+G22*BL22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BM23" s="23" t="e">
-        <f>(#REF!*#REF!+BM3*G3+G14*BM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BM6+BM16*G16+G18*BM18+G19*BM19+G22*BM22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+BM3*G3+G4*BM4+G14*BM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BM6+BM16*G16+G18*BM18+G19*BM19+G22*BM22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BN23" s="23" t="e">
@@ -4695,15 +4778,19 @@
         <f>(#REF!*#REF!+BO3*G3+G14*BO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BO6+BO16*G16+G18*BO18+G19*BO19+G22*BO22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BP23" s="13"/>
+      <c r="BP23" s="23" t="e">
+        <f>(#REF!*#REF!+BP3*G3+G14*BP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BP6+BP16*G16+G18*BP18+G19*BP19+G22*BP22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <v>#REF!</v>
+      </c>
       <c r="BQ23" s="13"/>
       <c r="BR23" s="13"/>
       <c r="BS23" s="13"/>
-      <c r="BV23" s="15">
+      <c r="BT23" s="13"/>
+      <c r="BW23" s="15">
         <v>1149.48</v>
       </c>
     </row>
-    <row r="24" spans="1:74" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:75" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4771,29 +4858,30 @@
       <c r="BM24" s="14"/>
       <c r="BN24" s="14"/>
       <c r="BO24" s="14"/>
-      <c r="BP24" s="23">
-        <f>SUM(BP2:BP20)</f>
-        <v>12173.8128</v>
-      </c>
+      <c r="BP24" s="14"/>
       <c r="BQ24" s="23">
         <f>SUM(BQ2:BQ20)</f>
-        <v>12623.132800000001</v>
-      </c>
-      <c r="BR24" s="24">
-        <f>BQ24-BP24</f>
+        <v>12571.202799999999</v>
+      </c>
+      <c r="BR24" s="23">
+        <f>SUM(BR2:BR20)</f>
+        <v>13020.522800000001</v>
+      </c>
+      <c r="BS24" s="24">
+        <f>BR24-BQ24</f>
         <v>449.32000000000153</v>
       </c>
-      <c r="BS24" s="13">
-        <f>((BQ24-BP24)/BP24)*100</f>
-        <v>3.690873248847736</v>
-      </c>
-      <c r="BV24" s="15">
-        <f>SUM(BV5:BV23)</f>
+      <c r="BT24" s="13">
+        <f>((BR24-BQ24)/BQ24)*100</f>
+        <v>3.5742005530290353</v>
+      </c>
+      <c r="BW24" s="15">
+        <f>SUM(BW5:BW23)</f>
         <v>1472.0683999999992</v>
       </c>
     </row>
-    <row r="25" spans="1:74" x14ac:dyDescent="0.25">
-      <c r="BP25" s="15">
+    <row r="25" spans="1:75" x14ac:dyDescent="0.25">
+      <c r="BQ25" s="15">
         <v>12034.32</v>
       </c>
     </row>
@@ -4920,7 +5008,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>9981</v>
+        <v>9787</v>
       </c>
       <c r="J2" s="25"/>
       <c r="L2" s="21">
@@ -4958,7 +5046,7 @@
       <c r="G3" s="17"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1311</v>
+        <v>1245</v>
       </c>
       <c r="J3" s="26"/>
       <c r="L3" s="21">
@@ -4996,7 +5084,7 @@
       <c r="G4" s="17"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6140</v>
+        <v>6295</v>
       </c>
       <c r="J4" s="26"/>
       <c r="L4" s="21">
@@ -5033,7 +5121,7 @@
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>559</v>
+        <v>587.5</v>
       </c>
       <c r="J5" s="26"/>
       <c r="L5" s="21">
@@ -5070,7 +5158,7 @@
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4355</v>
+        <v>4740</v>
       </c>
       <c r="J6" s="26"/>
       <c r="L6" s="21">
@@ -5108,7 +5196,7 @@
       <c r="G7" s="18"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3916</v>
+        <v>4033</v>
       </c>
       <c r="J7" s="26"/>
       <c r="L7" s="21">
@@ -5146,7 +5234,7 @@
       <c r="G8" s="18"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>42140</v>
+        <v>43640</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -5183,7 +5271,7 @@
       <c r="G9" s="17"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10100</v>
+        <v>11020</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -5220,7 +5308,7 @@
       <c r="G10" s="18"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4809</v>
+        <v>5164</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -5257,7 +5345,7 @@
       <c r="G11" s="18"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1075</v>
+        <v>1173</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -5294,7 +5382,7 @@
       <c r="G12" s="18"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>27890</v>
+        <v>28720</v>
       </c>
       <c r="J12" s="26"/>
       <c r="L12" s="21">
@@ -5332,7 +5420,7 @@
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>900</v>
+        <v>1074</v>
       </c>
       <c r="J13" s="26"/>
       <c r="L13" s="21">
@@ -5370,7 +5458,7 @@
       <c r="G14" s="17"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7687</v>
+        <v>7911</v>
       </c>
       <c r="J14" s="26"/>
       <c r="L14" s="21">
@@ -5408,7 +5496,7 @@
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>11946.75</v>
+        <v>11855.12</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
@@ -5446,7 +5534,7 @@
       <c r="G16" s="17"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>223.13</v>
+        <v>218.38</v>
       </c>
       <c r="J16" s="26"/>
       <c r="L16" s="21">
@@ -5484,7 +5572,7 @@
       <c r="G17" s="17"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>199.37</v>
+        <v>184.42</v>
       </c>
       <c r="J17" s="26"/>
       <c r="L17" s="21">
@@ -5522,7 +5610,7 @@
       <c r="G18" s="18"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1785</v>
+        <v>1886</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -5544,18 +5632,18 @@
       </c>
       <c r="C19" s="18">
         <f>'התיק העדכני'!H19</f>
-        <v>110</v>
+        <v>102.77</v>
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
-        <v>470</v>
+        <v>700</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
       <c r="G19" s="18"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>132.6</v>
+        <v>91.5</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -5839,28 +5927,28 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="17">
+      <c r="A28" s="17" t="str">
         <f>'התיק העדכני'!E20</f>
-        <v>0</v>
+        <v>אירודרום קבוצה</v>
       </c>
       <c r="B28" s="17">
         <f>'התיק העדכני'!A20</f>
-        <v>1144807</v>
+        <v>363010</v>
       </c>
       <c r="C28" s="18">
         <f>'התיק העדכני'!H20</f>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D28" s="19">
         <f>'התיק העדכני'!G20</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="19"/>
       <c r="I28" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="J28" s="26"/>
       <c r="L28" s="21">
@@ -5944,7 +6032,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>9981</v>
+        <v>9787</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+GEMINI!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
@@ -5981,7 +6069,7 @@
       <c r="G3" s="7"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1311</v>
+        <v>1245</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
@@ -6018,7 +6106,7 @@
       <c r="G4" s="7"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6140</v>
+        <v>6295</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+GEMINI!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
@@ -6055,7 +6143,7 @@
       <c r="G5" s="7"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>559</v>
+        <v>587.5</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
@@ -6092,7 +6180,7 @@
       <c r="G6" s="7"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4355</v>
+        <v>4740</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
@@ -6129,7 +6217,7 @@
       <c r="G7" s="8"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3916</v>
+        <v>4033</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+GEMINI!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
@@ -6166,7 +6254,7 @@
       <c r="G8" s="8"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>42140</v>
+        <v>43640</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+GEMINI!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -6203,7 +6291,7 @@
       <c r="G9" s="8"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10100</v>
+        <v>11020</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+GEMINI!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -6240,7 +6328,7 @@
       <c r="G10" s="8"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4809</v>
+        <v>5164</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+GEMINI!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -6277,7 +6365,7 @@
       <c r="G11" s="8"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1075</v>
+        <v>1173</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+GEMINI!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -6314,7 +6402,7 @@
       <c r="G12" s="8"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>27890</v>
+        <v>28720</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+GEMINI!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
@@ -6351,7 +6439,7 @@
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>900</v>
+        <v>1074</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+GEMINI!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
@@ -6388,7 +6476,7 @@
       <c r="G14" s="7"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7687</v>
+        <v>7911</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
@@ -6425,7 +6513,7 @@
       <c r="G15" s="7"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>11946.75</v>
+        <v>11855.12</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+GEMINI!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
@@ -6462,7 +6550,7 @@
       <c r="G16" s="7"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>223.13</v>
+        <v>218.38</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
@@ -6499,7 +6587,7 @@
       <c r="G17" s="7"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>199.37</v>
+        <v>184.42</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+GEMINI!E17+PERPLIXITY!E17+DEEPSEEK!E17)/4</f>
@@ -6536,7 +6624,7 @@
       <c r="G18" s="8"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1785</v>
+        <v>1886</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+GEMINI!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -6558,18 +6646,18 @@
       </c>
       <c r="C19" s="18">
         <f>'התיק העדכני'!H19</f>
-        <v>110</v>
+        <v>102.77</v>
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
-        <v>470</v>
+        <v>700</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
       <c r="G19" s="8"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>132.6</v>
+        <v>91.5</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+GEMINI!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -6760,7 +6848,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>9981</v>
+        <v>9787</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+GEMINI!E2+DEEPSEEK!E2)/4</f>
@@ -6797,7 +6885,7 @@
       <c r="G3" s="10"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1311</v>
+        <v>1245</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
@@ -6834,7 +6922,7 @@
       <c r="G4" s="10"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6140</v>
+        <v>6295</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+GEMINI!E4+DEEPSEEK!E4)/4</f>
@@ -6871,7 +6959,7 @@
       <c r="G5" s="10"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>559</v>
+        <v>587.5</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
@@ -6908,7 +6996,7 @@
       <c r="G6" s="10"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4355</v>
+        <v>4740</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
@@ -6945,7 +7033,7 @@
       <c r="G7" s="10"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3916</v>
+        <v>4033</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+GEMINI!E7+DEEPSEEK!E7)/4</f>
@@ -6981,7 +7069,7 @@
       </c>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>42140</v>
+        <v>43640</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+GEMINI!E8+DEEPSEEK!E8)/4</f>
@@ -7017,7 +7105,7 @@
       </c>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10100</v>
+        <v>11020</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+GEMINI!E9+DEEPSEEK!E9)/4</f>
@@ -7053,7 +7141,7 @@
       </c>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4809</v>
+        <v>5164</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+GEMINI!E10+DEEPSEEK!E10)/4</f>
@@ -7089,7 +7177,7 @@
       </c>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1075</v>
+        <v>1173</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+GEMINI!E11+DEEPSEEK!E11)/4</f>
@@ -7126,7 +7214,7 @@
       <c r="G12" s="10"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>27890</v>
+        <v>28720</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+GEMINI!E12+DEEPSEEK!E12)/4</f>
@@ -7163,7 +7251,7 @@
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>900</v>
+        <v>1074</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+CHATGPT!E13+GEMINI!E13+DEEPSEEK!E13)/4</f>
@@ -7200,7 +7288,7 @@
       <c r="G14" s="10"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7687</v>
+        <v>7911</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
@@ -7237,7 +7325,7 @@
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>11946.75</v>
+        <v>11855.12</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
@@ -7274,7 +7362,7 @@
       <c r="G16" s="10"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>223.13</v>
+        <v>218.38</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+GEMINI!E16+DEEPSEEK!E16)/4</f>
@@ -7311,7 +7399,7 @@
       <c r="G17" s="10"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>199.37</v>
+        <v>184.42</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+GEMINI!E17+DEEPSEEK!E17)/4</f>
@@ -7347,7 +7435,7 @@
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1785</v>
+        <v>1886</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
@@ -7369,17 +7457,17 @@
       </c>
       <c r="C19" s="18">
         <f>'התיק העדכני'!H19</f>
-        <v>110</v>
+        <v>102.77</v>
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
-        <v>470</v>
+        <v>700</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>132.6</v>
+        <v>91.5</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+GEMINI!E19+DEEPSEEK!E19)/4</f>
@@ -7570,7 +7658,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>9981</v>
+        <v>9787</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+PERPLIXITY!E2+GEMINI!E2)/4</f>
@@ -7607,7 +7695,7 @@
       <c r="G3" s="31"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1311</v>
+        <v>1245</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
@@ -7643,7 +7731,7 @@
       </c>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6140</v>
+        <v>6295</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+GEMINI!E4)/4</f>
@@ -7680,7 +7768,7 @@
       <c r="G5" s="31"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>559</v>
+        <v>587.5</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
@@ -7717,7 +7805,7 @@
       <c r="G6" s="31"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4355</v>
+        <v>4740</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
@@ -7753,7 +7841,7 @@
       </c>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3916</v>
+        <v>4033</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+GEMINI!E7)/4</f>
@@ -7790,7 +7878,7 @@
       <c r="G8" s="31"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>42140</v>
+        <v>43640</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+GEMINI!E8)/4</f>
@@ -7827,7 +7915,7 @@
       <c r="G9" s="31"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10100</v>
+        <v>11020</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+GEMINI!E9)/4</f>
@@ -7864,7 +7952,7 @@
       <c r="G10" s="31"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>4809</v>
+        <v>5164</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+GEMINI!E10)/4</f>
@@ -7901,7 +7989,7 @@
       <c r="G11" s="31"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1075</v>
+        <v>1173</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+GEMINI!E11)/4</f>
@@ -7938,7 +8026,7 @@
       <c r="G12" s="31"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>27890</v>
+        <v>28720</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+GEMINI!E12)/4</f>
@@ -7975,7 +8063,7 @@
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>900</v>
+        <v>1074</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
@@ -8006,7 +8094,7 @@
       <c r="G14" s="31"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7687</v>
+        <v>7911</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
@@ -8042,7 +8130,7 @@
       </c>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+PERPLIXITY!E15+GEMINI!E15)/4</f>
@@ -8078,7 +8166,7 @@
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>11946.75</v>
+        <v>11855.12</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
@@ -8115,7 +8203,7 @@
       <c r="G17" s="31"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>223.13</v>
+        <v>218.38</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+GEMINI!E17)/4</f>
@@ -8152,7 +8240,7 @@
       <c r="G18" s="31"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>199.37</v>
+        <v>184.42</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+GEMINI!E18)/4</f>
@@ -8174,15 +8262,15 @@
       </c>
       <c r="C19" s="18">
         <f>'התיק העדכני'!H19</f>
-        <v>110</v>
+        <v>102.77</v>
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
-        <v>470</v>
+        <v>700</v>
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1785</v>
+        <v>1886</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+GEMINI!E19)/4</f>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\BURSA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/673b1203f7e82b27/מסמכים/GitHub/BURSA/BURSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB1D6B3-6D51-49E5-82E7-092D73AC6EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{0EB1D6B3-6D51-49E5-82E7-092D73AC6EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FEFCB76-9B35-4691-8C02-F24B1305AC67}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
   <sheets>
     <sheet name="התיק העדכני" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="110">
   <si>
     <t>MTF מחקה אינדקס תעשיה ישראל</t>
   </si>
@@ -353,6 +364,12 @@
   </si>
   <si>
     <t>אירודרום קבוצה</t>
+  </si>
+  <si>
+    <t>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19+G20*J20)/100</t>
+  </si>
+  <si>
+    <t>מחיר 03/02/2026</t>
   </si>
 </sst>
 </file>
@@ -362,11 +379,11 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₪&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -375,7 +392,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -426,13 +443,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -822,14 +839,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא של Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -867,7 +880,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -973,7 +986,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1115,7 +1128,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1123,22 +1136,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86B4639-EF9D-4B16-B2C9-0D5E9C5EEC8B}">
-  <dimension ref="A1:BW25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BY25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="5" width="17.5703125" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="58" width="14.85546875" customWidth="1"/>
-    <col min="59" max="68" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="13" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="11" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="11.5703125" customWidth="1"/>
+    <col min="1" max="5" width="17.59765625" customWidth="1"/>
+    <col min="6" max="6" width="13.296875" customWidth="1"/>
+    <col min="7" max="7" width="11.59765625" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="60" width="14.8984375" customWidth="1"/>
+    <col min="61" max="70" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="13" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="11" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="11.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1167,205 +1180,211 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BK1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BL1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BM1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BN1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BO1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BP1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="BO1" s="6" t="s">
+      <c r="BQ1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BP1" s="6" t="s">
+      <c r="BR1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="BQ1" s="6" t="s">
+      <c r="BS1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="BR1" s="6" t="s">
+      <c r="BT1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="BS1" s="6" t="s">
+      <c r="BU1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BV1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="BU1" s="12" t="s">
+      <c r="BW1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="BV1" s="12" t="s">
+      <c r="BX1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="BW1" s="12" t="s">
+      <c r="BY1" s="12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A2" s="1">
         <v>282012</v>
       </c>
@@ -1394,40 +1413,44 @@
         <v>11000</v>
       </c>
       <c r="I2" s="13">
+        <v>9823</v>
+      </c>
+      <c r="J2" s="13">
+        <v>9823</v>
+      </c>
+      <c r="K2" s="13">
         <v>9787</v>
       </c>
-      <c r="J2" s="13">
+      <c r="L2" s="13">
         <v>9650</v>
       </c>
-      <c r="K2" s="13">
+      <c r="M2" s="13">
         <v>9981</v>
       </c>
-      <c r="L2" s="13">
+      <c r="N2" s="13">
         <v>12130</v>
       </c>
-      <c r="M2" s="13">
+      <c r="O2" s="13">
         <v>11840</v>
       </c>
-      <c r="N2" s="13">
+      <c r="P2" s="13">
         <v>11400</v>
       </c>
-      <c r="O2" s="13">
+      <c r="Q2" s="13">
         <v>11360</v>
       </c>
-      <c r="P2" s="13">
+      <c r="R2" s="13">
         <v>11000</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="S2" s="13">
         <v>10700</v>
       </c>
-      <c r="R2" s="13">
+      <c r="T2" s="13">
         <v>10400</v>
       </c>
-      <c r="S2" s="13">
+      <c r="U2" s="13">
         <v>11230</v>
       </c>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
       <c r="V2" s="6"/>
       <c r="W2" s="6"/>
       <c r="X2" s="6"/>
@@ -1467,29 +1490,31 @@
       <c r="BF2" s="6"/>
       <c r="BG2" s="6"/>
       <c r="BH2" s="6"/>
-      <c r="BI2" s="32"/>
+      <c r="BI2" s="6"/>
       <c r="BJ2" s="6"/>
-      <c r="BK2" s="6"/>
-      <c r="BL2" s="32"/>
+      <c r="BK2" s="32"/>
+      <c r="BL2" s="6"/>
       <c r="BM2" s="6"/>
-      <c r="BN2" s="6"/>
+      <c r="BN2" s="32"/>
       <c r="BO2" s="6"/>
       <c r="BP2" s="6"/>
-      <c r="BQ2" s="13">
-        <f>(G2*H2)/100-BW2</f>
+      <c r="BQ2" s="6"/>
+      <c r="BR2" s="6"/>
+      <c r="BS2" s="13">
+        <f>(G2*H2)/100-BY2</f>
         <v>770</v>
       </c>
-      <c r="BR2" s="13">
+      <c r="BT2" s="13">
         <f>(G2*H2)/100</f>
         <v>770</v>
       </c>
-      <c r="BS2" s="6"/>
-      <c r="BT2" s="6"/>
-      <c r="BU2" s="25"/>
-      <c r="BV2" s="25"/>
+      <c r="BU2" s="6"/>
+      <c r="BV2" s="6"/>
       <c r="BW2" s="25"/>
-    </row>
-    <row r="3" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BX2" s="25"/>
+      <c r="BY2" s="25"/>
+    </row>
+    <row r="3" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A3" s="1">
         <v>1227552</v>
       </c>
@@ -1503,7 +1528,7 @@
       </c>
       <c r="D3" s="6" t="str">
         <f>IF(I3&lt;GEMINI!L3,"למכור בהפסד",IF(I3&gt;GEMINI!M3,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור בהפסד</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>87</v>
@@ -1518,58 +1543,62 @@
         <v>1153.6300000000001</v>
       </c>
       <c r="I3" s="13">
+        <v>1074</v>
+      </c>
+      <c r="J3" s="13">
+        <v>1074</v>
+      </c>
+      <c r="K3" s="13">
         <v>1245</v>
       </c>
-      <c r="J3" s="13">
+      <c r="L3" s="13">
         <v>1311</v>
       </c>
-      <c r="K3" s="13">
+      <c r="M3" s="13">
         <v>1311</v>
       </c>
-      <c r="L3" s="13">
+      <c r="N3" s="13">
         <v>1340</v>
       </c>
-      <c r="M3" s="13">
+      <c r="O3" s="13">
         <v>1500</v>
       </c>
-      <c r="N3" s="13">
+      <c r="P3" s="13">
         <v>1424</v>
       </c>
-      <c r="O3" s="13">
+      <c r="Q3" s="13">
         <v>1348</v>
       </c>
-      <c r="P3" s="13">
+      <c r="R3" s="13">
         <v>1373</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="S3" s="13">
         <v>1331</v>
       </c>
-      <c r="R3" s="13">
+      <c r="T3" s="13">
         <v>1386</v>
       </c>
-      <c r="S3" s="13">
+      <c r="U3" s="13">
         <v>1342</v>
       </c>
-      <c r="T3" s="13">
+      <c r="V3" s="13">
         <v>1250</v>
       </c>
-      <c r="U3" s="13">
+      <c r="W3" s="13">
         <v>1389</v>
       </c>
-      <c r="V3" s="13">
+      <c r="X3" s="13">
         <v>1389</v>
       </c>
-      <c r="W3" s="13">
+      <c r="Y3" s="13">
         <v>1367</v>
       </c>
-      <c r="X3" s="13">
+      <c r="Z3" s="13">
         <v>1026</v>
       </c>
-      <c r="Y3" s="13">
+      <c r="AA3" s="13">
         <v>949.1</v>
       </c>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
       <c r="AB3" s="13"/>
       <c r="AC3" s="13"/>
       <c r="AD3" s="13"/>
@@ -1584,9 +1613,9 @@
       <c r="AM3" s="13"/>
       <c r="AN3" s="13"/>
       <c r="AO3" s="13"/>
-      <c r="AP3" s="14"/>
+      <c r="AP3" s="13"/>
       <c r="AQ3" s="13"/>
-      <c r="AR3" s="13"/>
+      <c r="AR3" s="14"/>
       <c r="AS3" s="13"/>
       <c r="AT3" s="13"/>
       <c r="AU3" s="13"/>
@@ -1603,42 +1632,44 @@
       <c r="BF3" s="13"/>
       <c r="BG3" s="13"/>
       <c r="BH3" s="13"/>
-      <c r="BI3" s="29"/>
+      <c r="BI3" s="13"/>
       <c r="BJ3" s="13"/>
-      <c r="BK3" s="13"/>
-      <c r="BL3" s="29"/>
+      <c r="BK3" s="29"/>
+      <c r="BL3" s="13"/>
       <c r="BM3" s="13"/>
-      <c r="BN3" s="13"/>
+      <c r="BN3" s="29"/>
       <c r="BO3" s="13"/>
       <c r="BP3" s="13"/>
-      <c r="BQ3" s="13">
-        <f>(G3*H3)/100-BW3</f>
+      <c r="BQ3" s="13"/>
+      <c r="BR3" s="13"/>
+      <c r="BS3" s="13">
+        <f>(G3*H3)/100-BY3</f>
         <v>-126.73159999999989</v>
       </c>
-      <c r="BR3" s="13">
+      <c r="BT3" s="13">
         <f>(G3*H3)/100</f>
         <v>0</v>
       </c>
-      <c r="BS3" s="13">
-        <f>(BR3-BQ3)</f>
+      <c r="BU3" s="13">
+        <f>(BT3-BS3)</f>
         <v>126.73159999999989</v>
       </c>
-      <c r="BT3" s="13">
-        <f>((BH3-H3)/H3)*100</f>
+      <c r="BV3" s="13">
+        <f>((BJ3-H3)/H3)*100</f>
         <v>-100</v>
       </c>
-      <c r="BU3">
+      <c r="BW3">
         <v>68</v>
       </c>
-      <c r="BV3">
+      <c r="BX3">
         <v>1340</v>
       </c>
-      <c r="BW3" s="15">
-        <f>(BU3*BV3-BU3*H3)/100</f>
+      <c r="BY3" s="15">
+        <f>(BW3*BX3-BW3*H3)/100</f>
         <v>126.73159999999989</v>
       </c>
     </row>
-    <row r="4" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A4" s="1">
         <v>587014</v>
       </c>
@@ -1667,58 +1698,62 @@
         <v>5925</v>
       </c>
       <c r="I4" s="13">
+        <v>6298</v>
+      </c>
+      <c r="J4" s="13">
+        <v>6298</v>
+      </c>
+      <c r="K4" s="13">
         <v>6295</v>
       </c>
-      <c r="J4" s="13">
+      <c r="L4" s="13">
         <v>6370</v>
       </c>
-      <c r="K4" s="13">
+      <c r="M4" s="13">
         <v>6140</v>
       </c>
-      <c r="L4" s="13">
+      <c r="N4" s="13">
         <v>7252</v>
       </c>
-      <c r="M4" s="13">
+      <c r="O4" s="13">
         <v>7120</v>
       </c>
-      <c r="N4" s="13">
+      <c r="P4" s="13">
         <v>7048</v>
       </c>
-      <c r="O4" s="13">
+      <c r="Q4" s="13">
         <v>6979</v>
       </c>
-      <c r="P4" s="13">
+      <c r="R4" s="13">
         <v>6680</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="S4" s="13">
         <v>6111</v>
       </c>
-      <c r="R4" s="13">
+      <c r="T4" s="13">
         <v>6050</v>
       </c>
-      <c r="S4" s="13">
+      <c r="U4" s="13">
         <v>6169</v>
       </c>
-      <c r="T4" s="13">
+      <c r="V4" s="13">
         <v>6300</v>
       </c>
-      <c r="U4" s="13">
+      <c r="W4" s="13">
         <v>6335</v>
       </c>
-      <c r="V4" s="13">
+      <c r="X4" s="13">
         <v>6335</v>
       </c>
-      <c r="W4" s="13">
+      <c r="Y4" s="13">
         <v>6444</v>
       </c>
-      <c r="X4" s="13">
+      <c r="Z4" s="13">
         <v>5749</v>
       </c>
-      <c r="Y4" s="13">
+      <c r="AA4" s="13">
         <v>5749</v>
       </c>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
       <c r="AB4" s="13"/>
       <c r="AC4" s="13"/>
       <c r="AD4" s="13"/>
@@ -1752,36 +1787,38 @@
       <c r="BF4" s="13"/>
       <c r="BG4" s="13"/>
       <c r="BH4" s="13"/>
-      <c r="BI4" s="29"/>
+      <c r="BI4" s="13"/>
       <c r="BJ4" s="13"/>
-      <c r="BK4" s="13"/>
-      <c r="BL4" s="29"/>
+      <c r="BK4" s="29"/>
+      <c r="BL4" s="13"/>
       <c r="BM4" s="13"/>
-      <c r="BN4" s="13"/>
+      <c r="BN4" s="29"/>
       <c r="BO4" s="13"/>
       <c r="BP4" s="13"/>
-      <c r="BQ4" s="13">
-        <f>(G4*H4)/100-BW4</f>
+      <c r="BQ4" s="13"/>
+      <c r="BR4" s="13"/>
+      <c r="BS4" s="13">
+        <f>(G4*H4)/100-BY4</f>
         <v>1185</v>
       </c>
-      <c r="BR4" s="13">
+      <c r="BT4" s="13">
         <f>(G4*H4)/100</f>
         <v>1185</v>
       </c>
-      <c r="BS4" s="13">
-        <f>(BR4-BQ4)</f>
+      <c r="BU4" s="13">
+        <f>(BT4-BS4)</f>
         <v>0</v>
       </c>
-      <c r="BT4" s="13">
-        <f>((BH4-H4)/H4)*100</f>
+      <c r="BV4" s="13">
+        <f>((BJ4-H4)/H4)*100</f>
         <v>-100</v>
       </c>
-      <c r="BW4" s="15">
-        <f>(BU4*BV4-BU4*H4)/100</f>
+      <c r="BY4" s="15">
+        <f>(BW4*BX4-BW4*H4)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A5" s="1">
         <v>1099787</v>
       </c>
@@ -1795,7 +1832,7 @@
       </c>
       <c r="D5" s="6" t="str">
         <f>IF(I5&lt;GEMINI!L5,"למכור בהפסד",IF(I5&gt;GEMINI!M5,"למכור ברווח","לשמור"))</f>
-        <v>למכור בהפסד</v>
+        <v>לשמור</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>67</v>
@@ -1810,88 +1847,92 @@
         <v>617.53</v>
       </c>
       <c r="I5" s="13">
+        <v>638</v>
+      </c>
+      <c r="J5" s="13">
+        <v>638</v>
+      </c>
+      <c r="K5" s="13">
         <v>587.5</v>
       </c>
-      <c r="J5" s="13">
+      <c r="L5" s="13">
         <v>577.9</v>
       </c>
-      <c r="K5" s="13">
+      <c r="M5" s="13">
         <v>559</v>
       </c>
-      <c r="L5" s="13">
+      <c r="N5" s="13">
         <v>570</v>
       </c>
-      <c r="M5" s="13">
+      <c r="O5" s="13">
         <v>575.70000000000005</v>
       </c>
-      <c r="N5" s="13">
+      <c r="P5" s="13">
         <v>612.6</v>
       </c>
-      <c r="O5" s="13">
+      <c r="Q5" s="13">
         <v>638.29999999999995</v>
       </c>
-      <c r="P5" s="13">
+      <c r="R5" s="13">
         <v>630.29999999999995</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="S5" s="13">
         <v>626</v>
       </c>
-      <c r="R5" s="13">
+      <c r="T5" s="13">
         <v>595.4</v>
       </c>
-      <c r="S5" s="13">
+      <c r="U5" s="13">
         <v>667.1</v>
       </c>
-      <c r="T5" s="13">
+      <c r="V5" s="13">
         <v>651</v>
       </c>
-      <c r="U5" s="13">
+      <c r="W5" s="13">
         <v>641.1</v>
       </c>
-      <c r="V5" s="13">
+      <c r="X5" s="13">
         <v>641.1</v>
       </c>
-      <c r="W5" s="13">
+      <c r="Y5" s="13">
         <v>607.1</v>
       </c>
-      <c r="X5" s="13">
+      <c r="Z5" s="13">
         <v>583</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="AA5" s="13">
         <v>581.6</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="AB5" s="13">
         <v>578.70000000000005</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AC5" s="13">
         <v>590</v>
       </c>
-      <c r="AB5" s="13">
+      <c r="AD5" s="13">
         <v>554.70000000000005</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AE5" s="13">
         <v>511.8</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AF5" s="13">
         <v>487</v>
       </c>
-      <c r="AE5" s="13">
+      <c r="AG5" s="13">
         <v>478.8</v>
       </c>
-      <c r="AF5" s="13">
+      <c r="AH5" s="13">
         <v>485.5</v>
       </c>
-      <c r="AG5" s="13">
+      <c r="AI5" s="13">
         <v>453.4</v>
       </c>
-      <c r="AH5" s="13">
+      <c r="AJ5" s="13">
         <v>426.1</v>
       </c>
-      <c r="AI5" s="13">
+      <c r="AK5" s="13">
         <v>423.2</v>
       </c>
-      <c r="AJ5" s="13"/>
-      <c r="AK5" s="13"/>
       <c r="AL5" s="13"/>
       <c r="AM5" s="13"/>
       <c r="AN5" s="13"/>
@@ -1915,27 +1956,29 @@
       <c r="BF5" s="13"/>
       <c r="BG5" s="13"/>
       <c r="BH5" s="13"/>
-      <c r="BI5" s="29"/>
+      <c r="BI5" s="13"/>
       <c r="BJ5" s="13"/>
-      <c r="BK5" s="13"/>
-      <c r="BL5" s="29"/>
+      <c r="BK5" s="29"/>
+      <c r="BL5" s="13"/>
       <c r="BM5" s="13"/>
-      <c r="BN5" s="13"/>
+      <c r="BN5" s="29"/>
       <c r="BO5" s="13"/>
       <c r="BP5" s="13"/>
-      <c r="BQ5" s="13">
-        <f t="shared" ref="BQ5:BQ19" si="0">(G5*H5)/100-BW5</f>
+      <c r="BQ5" s="13"/>
+      <c r="BR5" s="13"/>
+      <c r="BS5" s="13">
+        <f>(G5*H5)/100-BY5</f>
         <v>975.6973999999999</v>
       </c>
-      <c r="BR5" s="13">
+      <c r="BT5" s="13">
         <f>(G5*H5)/100</f>
         <v>975.6973999999999</v>
       </c>
-      <c r="BS5" s="13"/>
-      <c r="BT5" s="13"/>
-      <c r="BW5" s="15"/>
-    </row>
-    <row r="6" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BU5" s="13"/>
+      <c r="BV5" s="13"/>
+      <c r="BY5" s="15"/>
+    </row>
+    <row r="6" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A6" s="2">
         <v>1166768</v>
       </c>
@@ -1964,61 +2007,65 @@
         <v>4040</v>
       </c>
       <c r="I6" s="13">
+        <v>4799</v>
+      </c>
+      <c r="J6" s="13">
+        <v>4799</v>
+      </c>
+      <c r="K6" s="13">
         <v>4740</v>
       </c>
-      <c r="J6" s="13">
+      <c r="L6" s="13">
         <v>4350</v>
       </c>
-      <c r="K6" s="13">
+      <c r="M6" s="13">
         <v>4355</v>
       </c>
-      <c r="L6" s="13">
+      <c r="N6" s="13">
         <v>4500</v>
       </c>
-      <c r="M6" s="13">
+      <c r="O6" s="13">
         <v>4424</v>
       </c>
-      <c r="N6" s="13">
+      <c r="P6" s="13">
         <v>4412</v>
       </c>
-      <c r="O6" s="13">
+      <c r="Q6" s="13">
         <v>4450</v>
       </c>
-      <c r="P6" s="13">
+      <c r="R6" s="13">
         <v>4238</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="S6" s="13">
         <v>3970</v>
       </c>
-      <c r="R6" s="13">
+      <c r="T6" s="13">
         <v>3870</v>
       </c>
-      <c r="S6" s="13">
+      <c r="U6" s="13">
         <v>3805</v>
       </c>
-      <c r="T6" s="13">
+      <c r="V6" s="13">
         <v>3667</v>
       </c>
-      <c r="U6" s="13">
+      <c r="W6" s="13">
         <v>3582</v>
       </c>
-      <c r="V6" s="13">
+      <c r="X6" s="13">
         <v>3582</v>
       </c>
-      <c r="W6" s="13">
+      <c r="Y6" s="13">
         <v>3570</v>
       </c>
-      <c r="X6" s="13">
+      <c r="Z6" s="13">
         <v>3619</v>
       </c>
-      <c r="Y6" s="13">
+      <c r="AA6" s="13">
         <v>3650</v>
       </c>
-      <c r="Z6" s="13">
+      <c r="AB6" s="13">
         <v>3720</v>
       </c>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13"/>
       <c r="AC6" s="13"/>
       <c r="AD6" s="13"/>
       <c r="AE6" s="13"/>
@@ -2051,41 +2098,43 @@
       <c r="BF6" s="13"/>
       <c r="BG6" s="13"/>
       <c r="BH6" s="13"/>
-      <c r="BI6" s="29"/>
+      <c r="BI6" s="13"/>
       <c r="BJ6" s="13"/>
-      <c r="BK6" s="13"/>
-      <c r="BL6" s="29"/>
+      <c r="BK6" s="29"/>
+      <c r="BL6" s="13"/>
       <c r="BM6" s="13"/>
-      <c r="BN6" s="13"/>
+      <c r="BN6" s="29"/>
       <c r="BO6" s="13"/>
-      <c r="BQ6" s="13">
-        <f>(G6*H6)/100-BW6</f>
+      <c r="BP6" s="13"/>
+      <c r="BQ6" s="13"/>
+      <c r="BS6" s="13">
+        <f>(G6*H6)/100-BY6</f>
         <v>1033.7</v>
       </c>
-      <c r="BR6" s="13">
+      <c r="BT6" s="13">
         <f>(G6*H6)/100</f>
         <v>1010</v>
       </c>
-      <c r="BS6" s="13">
-        <f t="shared" ref="BS6" si="1">(BR6-BQ6)</f>
+      <c r="BU6" s="13">
+        <f t="shared" ref="BU6" si="0">(BT6-BS6)</f>
         <v>-23.700000000000045</v>
       </c>
-      <c r="BT6" s="13">
-        <f>((BH6-H6)/H6)*100</f>
+      <c r="BV6" s="13">
+        <f>((BJ6-H6)/H6)*100</f>
         <v>-100</v>
       </c>
-      <c r="BU6">
+      <c r="BW6">
         <v>5</v>
       </c>
-      <c r="BV6">
+      <c r="BX6">
         <v>3566</v>
       </c>
-      <c r="BW6" s="15">
-        <f>(BU6*BV6-BU6*H6)/100</f>
+      <c r="BY6" s="15">
+        <f>(BW6*BX6-BW6*H6)/100</f>
         <v>-23.7</v>
       </c>
     </row>
-    <row r="7" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A7" s="1">
         <v>1148899</v>
       </c>
@@ -2114,88 +2163,92 @@
         <v>3585</v>
       </c>
       <c r="I7" s="13">
+        <v>4022</v>
+      </c>
+      <c r="J7" s="13">
+        <v>4022</v>
+      </c>
+      <c r="K7" s="13">
         <v>4033</v>
       </c>
-      <c r="J7" s="13">
+      <c r="L7" s="13">
         <v>3988</v>
       </c>
-      <c r="K7" s="13">
+      <c r="M7" s="13">
         <v>3916</v>
       </c>
-      <c r="L7" s="13">
+      <c r="N7" s="13">
         <v>3954</v>
       </c>
-      <c r="M7" s="13">
+      <c r="O7" s="13">
         <v>3932</v>
       </c>
-      <c r="N7" s="13">
+      <c r="P7" s="13">
         <v>3949</v>
       </c>
-      <c r="O7" s="13">
+      <c r="Q7" s="13">
         <v>3943</v>
       </c>
-      <c r="P7" s="13">
+      <c r="R7" s="13">
         <v>3928</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="S7" s="13">
         <v>3913</v>
       </c>
-      <c r="R7" s="13">
+      <c r="T7" s="13">
         <v>3860</v>
       </c>
-      <c r="S7" s="13">
+      <c r="U7" s="13">
         <v>3893</v>
       </c>
-      <c r="T7" s="13">
+      <c r="V7" s="13">
         <v>3900</v>
       </c>
-      <c r="U7" s="13">
+      <c r="W7" s="13">
         <v>3842</v>
       </c>
-      <c r="V7" s="13">
+      <c r="X7" s="13">
         <v>3842</v>
       </c>
-      <c r="W7" s="13">
+      <c r="Y7" s="13">
         <v>3841</v>
       </c>
-      <c r="X7" s="13">
+      <c r="Z7" s="13">
         <v>3809</v>
       </c>
-      <c r="Y7" s="13">
+      <c r="AA7" s="13">
         <v>3810</v>
       </c>
-      <c r="Z7" s="13">
+      <c r="AB7" s="13">
         <v>3798</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="AC7" s="13">
         <v>3713</v>
       </c>
-      <c r="AB7" s="13">
+      <c r="AD7" s="13">
         <v>3657</v>
       </c>
-      <c r="AC7" s="13">
+      <c r="AE7" s="13">
         <v>3592</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AF7" s="13">
         <v>3621</v>
       </c>
-      <c r="AE7" s="13">
+      <c r="AG7" s="13">
         <v>3572</v>
       </c>
-      <c r="AF7" s="13">
+      <c r="AH7" s="13">
         <v>3580</v>
       </c>
-      <c r="AG7" s="13">
+      <c r="AI7" s="13">
         <v>3569</v>
       </c>
-      <c r="AH7" s="13">
+      <c r="AJ7" s="13">
         <v>3659</v>
       </c>
-      <c r="AI7" s="13">
+      <c r="AK7" s="13">
         <v>3656</v>
       </c>
-      <c r="AJ7" s="13"/>
-      <c r="AK7" s="13"/>
       <c r="AL7" s="13"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="13"/>
@@ -2219,27 +2272,29 @@
       <c r="BF7" s="13"/>
       <c r="BG7" s="13"/>
       <c r="BH7" s="13"/>
-      <c r="BI7" s="29"/>
+      <c r="BI7" s="13"/>
       <c r="BJ7" s="13"/>
-      <c r="BK7" s="13"/>
-      <c r="BL7" s="29"/>
+      <c r="BK7" s="29"/>
+      <c r="BL7" s="13"/>
       <c r="BM7" s="13"/>
-      <c r="BN7" s="13"/>
+      <c r="BN7" s="29"/>
       <c r="BO7" s="13"/>
       <c r="BP7" s="13"/>
-      <c r="BQ7" s="13">
-        <f t="shared" si="0"/>
+      <c r="BQ7" s="13"/>
+      <c r="BR7" s="13"/>
+      <c r="BS7" s="13">
+        <f>(G7*H7)/100-BY7</f>
         <v>2509.5</v>
       </c>
-      <c r="BR7" s="13">
-        <f t="shared" ref="BR7:BR19" si="2">(G7*H7)/100</f>
+      <c r="BT7" s="13">
+        <f>(G7*H7)/100</f>
         <v>2509.5</v>
       </c>
-      <c r="BS7" s="13"/>
-      <c r="BT7" s="13"/>
-      <c r="BW7" s="15"/>
-    </row>
-    <row r="8" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BU7" s="13"/>
+      <c r="BV7" s="13"/>
+      <c r="BY7" s="15"/>
+    </row>
+    <row r="8" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A8" s="1">
         <v>1082379</v>
       </c>
@@ -2253,7 +2308,7 @@
       </c>
       <c r="D8" s="6" t="str">
         <f>IF(I8&lt;GEMINI!L8,"למכור בהפסד",IF(I8&gt;GEMINI!M8,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>52</v>
@@ -2268,124 +2323,128 @@
         <v>37875</v>
       </c>
       <c r="I8" s="13">
+        <v>39600</v>
+      </c>
+      <c r="J8" s="13">
+        <v>39600</v>
+      </c>
+      <c r="K8" s="13">
         <v>43640</v>
       </c>
-      <c r="J8" s="13">
+      <c r="L8" s="13">
         <v>42700</v>
       </c>
-      <c r="K8" s="13">
+      <c r="M8" s="13">
         <v>42140</v>
       </c>
-      <c r="L8" s="13">
+      <c r="N8" s="13">
         <v>43490</v>
       </c>
-      <c r="M8" s="13">
+      <c r="O8" s="13">
         <v>40750</v>
       </c>
-      <c r="N8" s="13">
+      <c r="P8" s="13">
         <v>40900</v>
       </c>
-      <c r="O8" s="13">
+      <c r="Q8" s="13">
         <v>40790</v>
       </c>
-      <c r="P8" s="13">
+      <c r="R8" s="13">
         <v>40820</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="S8" s="13">
         <v>41570</v>
       </c>
-      <c r="R8" s="13">
+      <c r="T8" s="13">
         <v>42050</v>
       </c>
-      <c r="S8" s="13">
+      <c r="U8" s="13">
         <v>39960</v>
       </c>
-      <c r="T8" s="13">
+      <c r="V8" s="13">
         <v>39990</v>
       </c>
-      <c r="U8" s="13">
+      <c r="W8" s="13">
         <v>38680</v>
       </c>
-      <c r="V8" s="13">
+      <c r="X8" s="13">
         <v>38680</v>
       </c>
-      <c r="W8" s="13">
+      <c r="Y8" s="13">
         <v>37770</v>
       </c>
-      <c r="X8" s="13">
+      <c r="Z8" s="13">
         <v>36330</v>
       </c>
-      <c r="Y8" s="13">
+      <c r="AA8" s="13">
         <v>38680</v>
       </c>
-      <c r="Z8" s="13">
+      <c r="AB8" s="13">
         <v>39090</v>
-      </c>
-      <c r="AA8" s="13">
-        <v>37300</v>
-      </c>
-      <c r="AB8" s="13">
-        <v>37650</v>
       </c>
       <c r="AC8" s="13">
         <v>37300</v>
       </c>
       <c r="AD8" s="13">
+        <v>37650</v>
+      </c>
+      <c r="AE8" s="13">
+        <v>37300</v>
+      </c>
+      <c r="AF8" s="13">
         <v>39450</v>
       </c>
-      <c r="AE8" s="13">
+      <c r="AG8" s="13">
         <v>38390</v>
       </c>
-      <c r="AF8" s="13">
+      <c r="AH8" s="13">
         <v>38800</v>
       </c>
-      <c r="AG8" s="13">
+      <c r="AI8" s="13">
         <v>38510</v>
       </c>
-      <c r="AH8" s="13">
+      <c r="AJ8" s="13">
         <v>38970</v>
       </c>
-      <c r="AI8" s="13">
+      <c r="AK8" s="13">
         <v>38970</v>
       </c>
-      <c r="AJ8" s="13">
+      <c r="AL8" s="13">
         <v>37700</v>
       </c>
-      <c r="AK8" s="13">
+      <c r="AM8" s="13">
         <v>37700</v>
       </c>
-      <c r="AL8" s="13">
+      <c r="AN8" s="13">
         <v>37750</v>
       </c>
-      <c r="AM8" s="13">
+      <c r="AO8" s="13">
         <v>38430</v>
       </c>
-      <c r="AN8" s="13">
+      <c r="AP8" s="13">
         <v>38250</v>
       </c>
-      <c r="AO8" s="13">
+      <c r="AQ8" s="13">
         <v>40110</v>
       </c>
-      <c r="AP8" s="13">
+      <c r="AR8" s="13">
         <v>40820</v>
       </c>
-      <c r="AQ8" s="13">
+      <c r="AS8" s="13">
         <v>39320</v>
       </c>
-      <c r="AR8" s="13">
+      <c r="AT8" s="13">
         <v>37800</v>
       </c>
-      <c r="AS8" s="13">
+      <c r="AU8" s="13">
         <v>36620</v>
       </c>
-      <c r="AT8" s="13">
+      <c r="AV8" s="13">
         <v>37130</v>
       </c>
-      <c r="AU8" s="13">
+      <c r="AW8" s="13">
         <v>35850</v>
       </c>
-      <c r="AV8" s="13"/>
-      <c r="AW8" s="13"/>
       <c r="AX8" s="13"/>
       <c r="AY8" s="13"/>
       <c r="AZ8" s="13"/>
@@ -2397,39 +2456,41 @@
       <c r="BF8" s="13"/>
       <c r="BG8" s="13"/>
       <c r="BH8" s="13"/>
-      <c r="BI8" s="29"/>
+      <c r="BI8" s="13"/>
       <c r="BJ8" s="13"/>
-      <c r="BK8" s="13"/>
-      <c r="BL8" s="29"/>
+      <c r="BK8" s="29"/>
+      <c r="BL8" s="13"/>
       <c r="BM8" s="13"/>
-      <c r="BN8" s="13"/>
+      <c r="BN8" s="29"/>
       <c r="BO8" s="13"/>
       <c r="BP8" s="13"/>
-      <c r="BQ8" s="13">
-        <f t="shared" si="0"/>
+      <c r="BQ8" s="13"/>
+      <c r="BR8" s="13"/>
+      <c r="BS8" s="13">
+        <f>(G8*H8)/100-BY8</f>
         <v>806.25</v>
       </c>
-      <c r="BR8" s="13">
-        <f t="shared" si="2"/>
+      <c r="BT8" s="13">
+        <f>(G8*H8)/100</f>
         <v>757.5</v>
       </c>
-      <c r="BS8" s="13">
-        <f t="shared" ref="BS8:BS11" si="3">(BR8-BQ8)</f>
+      <c r="BU8" s="13">
+        <f t="shared" ref="BU8:BU11" si="1">(BT8-BS8)</f>
         <v>-48.75</v>
       </c>
-      <c r="BT8" s="13"/>
-      <c r="BU8">
+      <c r="BV8" s="13"/>
+      <c r="BW8">
         <v>3</v>
       </c>
-      <c r="BV8">
+      <c r="BX8">
         <v>36250</v>
       </c>
-      <c r="BW8" s="15">
-        <f>(BU8*BV8-BU8*H8)/100</f>
+      <c r="BY8" s="15">
+        <f>(BW8*BX8-BW8*H8)/100</f>
         <v>-48.75</v>
       </c>
     </row>
-    <row r="9" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A9" s="1">
         <v>629014</v>
       </c>
@@ -2443,7 +2504,7 @@
       </c>
       <c r="D9" s="6" t="str">
         <f>IF(I9&lt;GEMINI!L9,"למכור בהפסד",IF(I9&gt;GEMINI!M9,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>56</v>
@@ -2458,118 +2519,122 @@
         <v>9227</v>
       </c>
       <c r="I9" s="13">
+        <v>11290</v>
+      </c>
+      <c r="J9" s="13">
+        <v>11290</v>
+      </c>
+      <c r="K9" s="13">
         <v>11020</v>
       </c>
-      <c r="J9" s="13">
+      <c r="L9" s="13">
         <v>10100</v>
       </c>
-      <c r="K9" s="13">
+      <c r="M9" s="13">
         <v>10100</v>
       </c>
-      <c r="L9" s="13">
+      <c r="N9" s="13">
         <v>10240</v>
       </c>
-      <c r="M9" s="13">
+      <c r="O9" s="13">
         <v>9891</v>
       </c>
-      <c r="N9" s="13">
+      <c r="P9" s="13">
         <v>9956</v>
       </c>
-      <c r="O9" s="13">
+      <c r="Q9" s="13">
         <v>9910</v>
       </c>
-      <c r="P9" s="13">
+      <c r="R9" s="13">
         <v>9960</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="S9" s="13">
         <v>9924</v>
       </c>
-      <c r="R9" s="13">
+      <c r="T9" s="13">
         <v>9999</v>
       </c>
-      <c r="S9" s="13">
+      <c r="U9" s="13">
         <v>9962</v>
       </c>
-      <c r="T9" s="13">
+      <c r="V9" s="13">
         <v>9979</v>
       </c>
-      <c r="U9" s="13">
+      <c r="W9" s="13">
         <v>10130</v>
       </c>
-      <c r="V9" s="13">
+      <c r="X9" s="13">
         <v>10130</v>
       </c>
-      <c r="W9" s="13">
+      <c r="Y9" s="13">
         <v>10400</v>
       </c>
-      <c r="X9" s="13">
+      <c r="Z9" s="13">
         <v>10320</v>
       </c>
-      <c r="Y9" s="13">
+      <c r="AA9" s="13">
         <v>10300</v>
       </c>
-      <c r="Z9" s="13">
+      <c r="AB9" s="13">
         <v>10310</v>
       </c>
-      <c r="AA9" s="13">
+      <c r="AC9" s="13">
         <v>9672</v>
       </c>
-      <c r="AB9" s="13">
+      <c r="AD9" s="13">
         <v>9953</v>
       </c>
-      <c r="AC9" s="13">
+      <c r="AE9" s="13">
         <v>10090</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AF9" s="13">
         <v>10070</v>
       </c>
-      <c r="AE9" s="13">
+      <c r="AG9" s="13">
         <v>10030</v>
       </c>
-      <c r="AF9" s="13">
+      <c r="AH9" s="13">
         <v>10120</v>
       </c>
-      <c r="AG9" s="13">
+      <c r="AI9" s="13">
         <v>10000</v>
       </c>
-      <c r="AH9" s="13">
+      <c r="AJ9" s="13">
         <v>10080</v>
       </c>
-      <c r="AI9" s="13">
+      <c r="AK9" s="13">
         <v>10030</v>
       </c>
-      <c r="AJ9" s="13">
+      <c r="AL9" s="13">
         <v>9726</v>
       </c>
-      <c r="AK9" s="13">
+      <c r="AM9" s="13">
         <v>9726</v>
       </c>
-      <c r="AL9" s="13">
+      <c r="AN9" s="13">
         <v>9659</v>
       </c>
-      <c r="AM9" s="13">
+      <c r="AO9" s="13">
         <v>9670</v>
       </c>
-      <c r="AN9" s="13">
+      <c r="AP9" s="13">
         <v>9590</v>
       </c>
-      <c r="AO9" s="13">
+      <c r="AQ9" s="13">
         <v>9588</v>
       </c>
-      <c r="AP9" s="13">
+      <c r="AR9" s="13">
         <v>9400</v>
       </c>
-      <c r="AQ9" s="13">
+      <c r="AS9" s="13">
         <v>9320</v>
       </c>
-      <c r="AR9" s="13">
+      <c r="AT9" s="13">
         <v>9071</v>
       </c>
-      <c r="AS9" s="13">
+      <c r="AU9" s="13">
         <v>9271</v>
       </c>
-      <c r="AT9" s="13"/>
-      <c r="AU9" s="13"/>
       <c r="AV9" s="13"/>
       <c r="AW9" s="13"/>
       <c r="AX9" s="13"/>
@@ -2583,39 +2648,41 @@
       <c r="BF9" s="13"/>
       <c r="BG9" s="13"/>
       <c r="BH9" s="13"/>
-      <c r="BI9" s="29"/>
+      <c r="BI9" s="13"/>
       <c r="BJ9" s="13"/>
-      <c r="BK9" s="13"/>
-      <c r="BL9" s="29"/>
+      <c r="BK9" s="29"/>
+      <c r="BL9" s="13"/>
       <c r="BM9" s="13"/>
-      <c r="BN9" s="13"/>
+      <c r="BN9" s="29"/>
       <c r="BO9" s="13"/>
       <c r="BP9" s="13"/>
-      <c r="BQ9" s="13">
-        <f t="shared" si="0"/>
+      <c r="BQ9" s="13"/>
+      <c r="BR9" s="13"/>
+      <c r="BS9" s="13">
+        <f>(G9*H9)/100-BY9</f>
         <v>-38.65</v>
       </c>
-      <c r="BR9" s="13">
-        <f t="shared" si="2"/>
+      <c r="BT9" s="13">
+        <f>(G9*H9)/100</f>
         <v>0</v>
       </c>
-      <c r="BS9" s="13">
-        <f t="shared" si="3"/>
+      <c r="BU9" s="13">
+        <f t="shared" si="1"/>
         <v>38.65</v>
       </c>
-      <c r="BT9" s="13"/>
-      <c r="BU9">
+      <c r="BV9" s="13"/>
+      <c r="BW9">
         <v>5</v>
       </c>
-      <c r="BV9">
+      <c r="BX9">
         <v>10000</v>
       </c>
-      <c r="BW9" s="15">
-        <f>(BU9*BV9-BU9*H9)/100</f>
+      <c r="BY9" s="15">
+        <f>(BW9*BX9-BW9*H9)/100</f>
         <v>38.65</v>
       </c>
     </row>
-    <row r="10" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A10" s="1">
         <v>1141464</v>
       </c>
@@ -2644,199 +2711,205 @@
         <v>4834</v>
       </c>
       <c r="I10" s="13">
+        <v>5126</v>
+      </c>
+      <c r="J10" s="13">
+        <v>5126</v>
+      </c>
+      <c r="K10" s="13">
         <v>5164</v>
       </c>
-      <c r="J10" s="13">
+      <c r="L10" s="13">
         <v>4809</v>
       </c>
-      <c r="K10" s="13">
+      <c r="M10" s="13">
         <v>4809</v>
       </c>
-      <c r="L10" s="13">
+      <c r="N10" s="13">
         <v>4849</v>
       </c>
-      <c r="M10" s="13">
+      <c r="O10" s="13">
         <v>4821</v>
       </c>
-      <c r="N10" s="13">
+      <c r="P10" s="13">
         <v>4925</v>
       </c>
-      <c r="O10" s="13">
+      <c r="Q10" s="13">
         <v>5013</v>
       </c>
-      <c r="P10" s="13">
+      <c r="R10" s="13">
         <v>5050</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="S10" s="13">
         <v>5050</v>
       </c>
-      <c r="R10" s="13">
+      <c r="T10" s="13">
         <v>4930</v>
       </c>
-      <c r="S10" s="13">
+      <c r="U10" s="13">
         <v>5150</v>
       </c>
-      <c r="T10" s="13">
+      <c r="V10" s="13">
         <v>5283</v>
       </c>
-      <c r="U10" s="13">
+      <c r="W10" s="13">
         <v>5253</v>
       </c>
-      <c r="V10" s="13">
+      <c r="X10" s="13">
         <v>5253</v>
       </c>
-      <c r="W10" s="13">
+      <c r="Y10" s="13">
         <v>5400</v>
       </c>
-      <c r="X10" s="13">
+      <c r="Z10" s="13">
         <v>5522</v>
       </c>
-      <c r="Y10" s="13">
+      <c r="AA10" s="13">
         <v>5690</v>
       </c>
-      <c r="Z10" s="13">
+      <c r="AB10" s="13">
         <v>5749</v>
       </c>
-      <c r="AA10" s="13">
+      <c r="AC10" s="13">
         <v>5840</v>
       </c>
-      <c r="AB10" s="13">
+      <c r="AD10" s="13">
         <v>5650</v>
       </c>
-      <c r="AC10" s="13">
+      <c r="AE10" s="13">
         <v>5650</v>
       </c>
-      <c r="AD10" s="13">
+      <c r="AF10" s="13">
         <v>5841</v>
       </c>
-      <c r="AE10" s="13">
+      <c r="AG10" s="13">
         <v>5758</v>
       </c>
-      <c r="AF10" s="13">
+      <c r="AH10" s="13">
         <v>5673</v>
       </c>
-      <c r="AG10" s="13">
+      <c r="AI10" s="13">
         <v>5609</v>
       </c>
-      <c r="AH10" s="13">
+      <c r="AJ10" s="13">
         <v>5750</v>
       </c>
-      <c r="AI10" s="13">
+      <c r="AK10" s="13">
         <v>5841</v>
       </c>
-      <c r="AJ10" s="13">
+      <c r="AL10" s="13">
         <v>5564</v>
       </c>
-      <c r="AK10" s="13">
+      <c r="AM10" s="13">
         <v>5564</v>
       </c>
-      <c r="AL10" s="13">
+      <c r="AN10" s="13">
         <v>5557</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AO10" s="13">
         <v>5501</v>
       </c>
-      <c r="AN10" s="13">
+      <c r="AP10" s="13">
         <v>5250</v>
       </c>
-      <c r="AO10" s="13">
+      <c r="AQ10" s="13">
         <v>5270</v>
       </c>
-      <c r="AP10" s="13">
+      <c r="AR10" s="13">
         <v>5149</v>
       </c>
-      <c r="AQ10" s="13">
+      <c r="AS10" s="13">
         <v>5092</v>
       </c>
-      <c r="AR10" s="13">
+      <c r="AT10" s="13">
         <v>5228</v>
       </c>
-      <c r="AS10" s="13">
+      <c r="AU10" s="13">
         <v>5301</v>
       </c>
-      <c r="AT10" s="13">
+      <c r="AV10" s="13">
         <v>5159</v>
       </c>
-      <c r="AU10" s="13">
+      <c r="AW10" s="13">
         <v>5198</v>
       </c>
-      <c r="AV10" s="13">
+      <c r="AX10" s="13">
         <v>5077</v>
       </c>
-      <c r="AW10" s="13">
+      <c r="AY10" s="13">
         <v>4842</v>
       </c>
-      <c r="AX10" s="13">
+      <c r="AZ10" s="13">
         <v>5050</v>
       </c>
-      <c r="AY10" s="13">
+      <c r="BA10" s="13">
         <v>4970</v>
       </c>
-      <c r="AZ10" s="13">
+      <c r="BB10" s="13">
         <v>4880</v>
       </c>
-      <c r="BA10" s="13">
+      <c r="BC10" s="13">
         <v>4704</v>
       </c>
-      <c r="BB10" s="13">
+      <c r="BD10" s="13">
         <v>4770</v>
       </c>
-      <c r="BC10" s="13">
+      <c r="BE10" s="13">
         <v>4609</v>
       </c>
-      <c r="BD10" s="13">
+      <c r="BF10" s="13">
         <v>4674</v>
       </c>
-      <c r="BE10" s="13">
+      <c r="BG10" s="13">
         <v>4710</v>
       </c>
-      <c r="BF10" s="13">
+      <c r="BH10" s="13">
         <v>4688</v>
       </c>
-      <c r="BG10" s="13">
+      <c r="BI10" s="13">
         <v>4900</v>
       </c>
-      <c r="BH10" s="13">
+      <c r="BJ10" s="13">
         <v>5000</v>
       </c>
-      <c r="BI10" s="29">
+      <c r="BK10" s="29">
         <v>4932</v>
       </c>
-      <c r="BJ10" s="13"/>
-      <c r="BK10" s="13"/>
-      <c r="BL10" s="29"/>
+      <c r="BL10" s="13"/>
       <c r="BM10" s="13"/>
-      <c r="BN10" s="13"/>
+      <c r="BN10" s="29"/>
       <c r="BO10" s="13"/>
       <c r="BP10" s="13"/>
-      <c r="BQ10" s="13">
-        <f t="shared" si="0"/>
+      <c r="BQ10" s="13"/>
+      <c r="BR10" s="13"/>
+      <c r="BS10" s="13">
+        <f>(G10*H10)/100-BY10</f>
         <v>-87.859799999999964</v>
       </c>
-      <c r="BR10" s="13">
-        <f t="shared" si="2"/>
+      <c r="BT10" s="13">
+        <f>(G10*H10)/100</f>
         <v>0</v>
       </c>
-      <c r="BS10" s="13">
-        <f t="shared" si="3"/>
+      <c r="BU10" s="13">
+        <f t="shared" si="1"/>
         <v>87.859799999999964</v>
       </c>
-      <c r="BT10" s="13">
-        <f>((BH10-H10)/H10)*100</f>
+      <c r="BV10" s="13">
+        <f>((BJ10-H10)/H10)*100</f>
         <v>3.434009102192801</v>
       </c>
-      <c r="BU10">
+      <c r="BW10">
         <v>21</v>
       </c>
-      <c r="BV10">
+      <c r="BX10">
         <v>5252.38</v>
       </c>
-      <c r="BW10" s="15">
-        <f>(BU10*BV10-BU10*H10)/100</f>
+      <c r="BY10" s="15">
+        <f>(BW10*BX10-BW10*H10)/100</f>
         <v>87.859799999999964</v>
       </c>
     </row>
-    <row r="11" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A11" s="1">
         <v>1166974</v>
       </c>
@@ -2850,7 +2923,7 @@
       </c>
       <c r="D11" s="6" t="str">
         <f>IF(I11&lt;GEMINI!L11,"למכור בהפסד",IF(I11&gt;GEMINI!M11,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>72</v>
@@ -2865,82 +2938,86 @@
         <v>901.87</v>
       </c>
       <c r="I11" s="13">
+        <v>1099</v>
+      </c>
+      <c r="J11" s="13">
+        <v>1099</v>
+      </c>
+      <c r="K11" s="13">
         <v>1173</v>
       </c>
-      <c r="J11" s="13">
+      <c r="L11" s="13">
         <v>1114</v>
       </c>
-      <c r="K11" s="13">
+      <c r="M11" s="13">
         <v>1075</v>
       </c>
-      <c r="L11" s="13">
+      <c r="N11" s="13">
         <v>1109</v>
       </c>
-      <c r="M11" s="13">
+      <c r="O11" s="13">
         <v>1090</v>
       </c>
-      <c r="N11" s="13">
+      <c r="P11" s="13">
         <v>1144</v>
       </c>
-      <c r="O11" s="13">
+      <c r="Q11" s="13">
         <v>1162</v>
       </c>
-      <c r="P11" s="13">
+      <c r="R11" s="13">
         <v>1109</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="S11" s="13">
         <v>1029</v>
       </c>
-      <c r="R11" s="13">
+      <c r="T11" s="13">
         <v>993</v>
       </c>
-      <c r="S11" s="13">
+      <c r="U11" s="13">
         <v>1017</v>
       </c>
-      <c r="T11" s="13">
+      <c r="V11" s="13">
         <v>960</v>
       </c>
-      <c r="U11" s="13">
+      <c r="W11" s="13">
         <v>965</v>
       </c>
-      <c r="V11" s="13">
+      <c r="X11" s="13">
         <v>965</v>
       </c>
-      <c r="W11" s="13">
+      <c r="Y11" s="13">
         <v>951.7</v>
       </c>
-      <c r="X11" s="13">
+      <c r="Z11" s="13">
         <v>946</v>
       </c>
-      <c r="Y11" s="13">
+      <c r="AA11" s="13">
         <v>869.2</v>
       </c>
-      <c r="Z11" s="13">
+      <c r="AB11" s="13">
         <v>865</v>
       </c>
-      <c r="AA11" s="13">
+      <c r="AC11" s="13">
         <v>851</v>
       </c>
-      <c r="AB11" s="13">
+      <c r="AD11" s="13">
         <v>829.3</v>
       </c>
-      <c r="AC11" s="13">
+      <c r="AE11" s="13">
         <v>830</v>
       </c>
-      <c r="AD11" s="13">
+      <c r="AF11" s="13">
         <v>810</v>
       </c>
-      <c r="AE11" s="13">
+      <c r="AG11" s="13">
         <v>812.8</v>
       </c>
-      <c r="AF11" s="13">
+      <c r="AH11" s="13">
         <v>788</v>
       </c>
-      <c r="AG11" s="13">
+      <c r="AI11" s="13">
         <v>772</v>
       </c>
-      <c r="AH11" s="13"/>
-      <c r="AI11" s="13"/>
       <c r="AJ11" s="13"/>
       <c r="AK11" s="13"/>
       <c r="AL11" s="13"/>
@@ -2966,33 +3043,35 @@
       <c r="BF11" s="13"/>
       <c r="BG11" s="13"/>
       <c r="BH11" s="13"/>
-      <c r="BI11" s="29"/>
+      <c r="BI11" s="13"/>
       <c r="BJ11" s="13"/>
-      <c r="BK11" s="13"/>
-      <c r="BL11" s="29"/>
+      <c r="BK11" s="29"/>
+      <c r="BL11" s="13"/>
       <c r="BM11" s="13"/>
-      <c r="BN11" s="13"/>
+      <c r="BN11" s="29"/>
       <c r="BO11" s="13"/>
       <c r="BP11" s="13"/>
-      <c r="BQ11" s="13">
-        <f t="shared" si="0"/>
+      <c r="BQ11" s="13"/>
+      <c r="BR11" s="13"/>
+      <c r="BS11" s="13">
+        <f>(G11*H11)/100-BY11</f>
         <v>721.49600000000009</v>
       </c>
-      <c r="BR11" s="13">
-        <f t="shared" si="2"/>
+      <c r="BT11" s="13">
+        <f>(G11*H11)/100</f>
         <v>721.49600000000009</v>
       </c>
-      <c r="BS11" s="13">
-        <f t="shared" si="3"/>
+      <c r="BU11" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BT11" s="13"/>
-      <c r="BW11" s="15">
-        <f>(BU11*BV11-BU11*H11)/100</f>
+      <c r="BV11" s="13"/>
+      <c r="BY11" s="15">
+        <f>(BW11*BX11-BW11*H11)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A12" s="1">
         <v>1176593</v>
       </c>
@@ -3021,88 +3100,92 @@
         <v>22581.42</v>
       </c>
       <c r="I12" s="13">
+        <v>29460</v>
+      </c>
+      <c r="J12" s="13">
+        <v>29460</v>
+      </c>
+      <c r="K12" s="13">
         <v>28720</v>
       </c>
-      <c r="J12" s="13">
+      <c r="L12" s="13">
         <v>27890</v>
       </c>
-      <c r="K12" s="13">
+      <c r="M12" s="13">
         <v>27890</v>
       </c>
-      <c r="L12" s="13">
+      <c r="N12" s="13">
         <v>30100</v>
       </c>
-      <c r="M12" s="13">
+      <c r="O12" s="13">
         <v>30500</v>
       </c>
-      <c r="N12" s="13">
+      <c r="P12" s="13">
         <v>28850</v>
       </c>
-      <c r="O12" s="13">
+      <c r="Q12" s="13">
         <v>27450</v>
       </c>
-      <c r="P12" s="13">
+      <c r="R12" s="13">
         <v>26940</v>
       </c>
-      <c r="Q12" s="13">
+      <c r="S12" s="13">
         <v>26800</v>
       </c>
-      <c r="R12" s="13">
+      <c r="T12" s="13">
         <v>25950</v>
       </c>
-      <c r="S12" s="13">
+      <c r="U12" s="13">
         <v>26000</v>
       </c>
-      <c r="T12" s="13">
+      <c r="V12" s="13">
         <v>26600</v>
       </c>
-      <c r="U12" s="13">
+      <c r="W12" s="13">
         <v>24630</v>
       </c>
-      <c r="V12" s="13">
+      <c r="X12" s="13">
         <v>24630</v>
       </c>
-      <c r="W12" s="13">
+      <c r="Y12" s="13">
         <v>25230</v>
       </c>
-      <c r="X12" s="13">
+      <c r="Z12" s="13">
         <v>24700</v>
       </c>
-      <c r="Y12" s="13">
+      <c r="AA12" s="13">
         <v>23780</v>
       </c>
-      <c r="Z12" s="13">
+      <c r="AB12" s="13">
         <v>23920</v>
       </c>
-      <c r="AA12" s="13">
+      <c r="AC12" s="13">
         <v>22390</v>
       </c>
-      <c r="AB12" s="13">
+      <c r="AD12" s="13">
         <v>23000</v>
       </c>
-      <c r="AC12" s="13">
+      <c r="AE12" s="13">
         <v>20990</v>
       </c>
-      <c r="AD12" s="13">
+      <c r="AF12" s="13">
         <v>20260</v>
       </c>
-      <c r="AE12" s="13">
+      <c r="AG12" s="13">
         <v>19200</v>
       </c>
-      <c r="AF12" s="13">
+      <c r="AH12" s="13">
         <v>19860</v>
       </c>
-      <c r="AG12" s="13">
+      <c r="AI12" s="13">
         <v>19700</v>
       </c>
-      <c r="AH12" s="13">
+      <c r="AJ12" s="13">
         <v>19430</v>
       </c>
-      <c r="AI12" s="13">
+      <c r="AK12" s="13">
         <v>19020</v>
       </c>
-      <c r="AJ12" s="13"/>
-      <c r="AK12" s="13"/>
       <c r="AL12" s="13"/>
       <c r="AM12" s="13"/>
       <c r="AN12" s="13"/>
@@ -3126,36 +3209,38 @@
       <c r="BF12" s="13"/>
       <c r="BG12" s="13"/>
       <c r="BH12" s="13"/>
-      <c r="BI12" s="29"/>
+      <c r="BI12" s="13"/>
       <c r="BJ12" s="13"/>
-      <c r="BK12" s="13"/>
-      <c r="BL12" s="29"/>
+      <c r="BK12" s="29"/>
+      <c r="BL12" s="13"/>
       <c r="BM12" s="13"/>
-      <c r="BN12" s="13"/>
+      <c r="BN12" s="29"/>
       <c r="BO12" s="13"/>
       <c r="BP12" s="13"/>
-      <c r="BQ12" s="13">
-        <f t="shared" si="0"/>
+      <c r="BQ12" s="13"/>
+      <c r="BR12" s="13"/>
+      <c r="BS12" s="13">
+        <f>(G12*H12)/100-BY12</f>
         <v>-331.70059999999995</v>
       </c>
-      <c r="BR12" s="13">
-        <f t="shared" si="2"/>
+      <c r="BT12" s="13">
+        <f>(G12*H12)/100</f>
         <v>0</v>
       </c>
-      <c r="BS12" s="13"/>
-      <c r="BT12" s="13"/>
-      <c r="BU12">
+      <c r="BU12" s="13"/>
+      <c r="BV12" s="13"/>
+      <c r="BW12">
         <v>7</v>
       </c>
-      <c r="BV12">
+      <c r="BX12">
         <v>27320</v>
       </c>
-      <c r="BW12" s="15">
-        <f t="shared" ref="BW12:BW14" si="4">(BU12*BV12-BU12*H12)/100</f>
+      <c r="BY12" s="15">
+        <f>(BW12*BX12-BW12*H12)/100</f>
         <v>331.70059999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A13" s="1">
         <v>397018</v>
       </c>
@@ -3184,38 +3269,42 @@
         <v>723</v>
       </c>
       <c r="I13" s="13">
+        <v>1009</v>
+      </c>
+      <c r="J13" s="13">
+        <v>1009</v>
+      </c>
+      <c r="K13" s="13">
         <v>1074</v>
       </c>
-      <c r="J13" s="13">
+      <c r="L13" s="13">
         <v>900</v>
       </c>
-      <c r="K13" s="13">
+      <c r="M13" s="13">
         <v>900</v>
       </c>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13">
+      <c r="N13" s="13"/>
+      <c r="O13" s="13">
         <v>1490</v>
       </c>
-      <c r="N13" s="13">
+      <c r="P13" s="13">
         <v>1210</v>
       </c>
-      <c r="O13" s="13">
+      <c r="Q13" s="13">
         <v>1100</v>
       </c>
-      <c r="P13" s="13">
+      <c r="R13" s="13">
         <v>980</v>
       </c>
-      <c r="Q13" s="13">
+      <c r="S13" s="13">
         <v>932.1</v>
       </c>
-      <c r="R13" s="13">
+      <c r="T13" s="13">
         <v>822</v>
       </c>
-      <c r="S13" s="13">
+      <c r="U13" s="13">
         <v>790</v>
       </c>
-      <c r="T13" s="13"/>
-      <c r="U13" s="13"/>
       <c r="V13" s="13"/>
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
@@ -3255,30 +3344,32 @@
       <c r="BF13" s="13"/>
       <c r="BG13" s="13"/>
       <c r="BH13" s="13"/>
-      <c r="BI13" s="29"/>
+      <c r="BI13" s="13"/>
       <c r="BJ13" s="13"/>
-      <c r="BK13" s="13"/>
-      <c r="BL13" s="29"/>
+      <c r="BK13" s="29"/>
+      <c r="BL13" s="13"/>
       <c r="BM13" s="13"/>
-      <c r="BN13" s="13"/>
+      <c r="BN13" s="29"/>
       <c r="BO13" s="13"/>
       <c r="BP13" s="13"/>
-      <c r="BQ13" s="13">
-        <f t="shared" si="0"/>
+      <c r="BQ13" s="13"/>
+      <c r="BR13" s="13"/>
+      <c r="BS13" s="13">
+        <f>(G13*H13)/100-BY13</f>
         <v>0</v>
       </c>
-      <c r="BR13" s="13">
-        <f t="shared" si="2"/>
+      <c r="BT13" s="13">
+        <f>(G13*H13)/100</f>
         <v>0</v>
       </c>
-      <c r="BS13" s="13"/>
-      <c r="BT13" s="13"/>
-      <c r="BW13" s="15">
-        <f t="shared" si="4"/>
+      <c r="BU13" s="13"/>
+      <c r="BV13" s="13"/>
+      <c r="BY13" s="15">
+        <f>(BW13*BX13-BW13*H13)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A14" s="1">
         <v>662577</v>
       </c>
@@ -3307,207 +3398,213 @@
         <v>7204.22</v>
       </c>
       <c r="I14" s="13">
+        <v>8051</v>
+      </c>
+      <c r="J14" s="13">
+        <v>8051</v>
+      </c>
+      <c r="K14" s="13">
         <v>7911</v>
       </c>
-      <c r="J14" s="13">
+      <c r="L14" s="13">
         <v>7833</v>
       </c>
-      <c r="K14" s="13">
+      <c r="M14" s="13">
         <v>7687</v>
       </c>
-      <c r="L14" s="13">
+      <c r="N14" s="13">
         <v>7672</v>
       </c>
-      <c r="M14" s="13">
+      <c r="O14" s="13">
         <v>7676</v>
       </c>
-      <c r="N14" s="13">
+      <c r="P14" s="13">
         <v>7844</v>
       </c>
-      <c r="O14" s="13">
+      <c r="Q14" s="13">
         <v>7810</v>
       </c>
-      <c r="P14" s="13">
+      <c r="R14" s="13">
         <v>7710</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="S14" s="13">
         <v>7735</v>
       </c>
-      <c r="R14" s="13">
+      <c r="T14" s="13">
         <v>7725</v>
       </c>
-      <c r="S14" s="13">
+      <c r="U14" s="13">
         <v>7787</v>
       </c>
-      <c r="T14" s="13">
+      <c r="V14" s="13">
         <v>7955</v>
       </c>
-      <c r="U14" s="13">
+      <c r="W14" s="13">
         <v>7627</v>
       </c>
-      <c r="V14" s="13">
+      <c r="X14" s="13">
         <v>7627</v>
       </c>
-      <c r="W14" s="13">
+      <c r="Y14" s="13">
         <v>7656</v>
       </c>
-      <c r="X14" s="13">
+      <c r="Z14" s="13">
         <v>7507</v>
       </c>
-      <c r="Y14" s="13">
+      <c r="AA14" s="13">
         <v>7590</v>
       </c>
-      <c r="Z14" s="13">
+      <c r="AB14" s="13">
         <v>7569</v>
       </c>
-      <c r="AA14" s="13">
+      <c r="AC14" s="13">
         <v>7269</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AD14" s="13">
         <v>7444</v>
       </c>
-      <c r="AC14" s="13">
+      <c r="AE14" s="13">
         <v>7205</v>
       </c>
-      <c r="AD14" s="13">
+      <c r="AF14" s="13">
         <v>7298</v>
       </c>
-      <c r="AE14" s="13">
+      <c r="AG14" s="13">
         <v>7222</v>
       </c>
-      <c r="AF14" s="13">
+      <c r="AH14" s="13">
         <v>7079</v>
       </c>
-      <c r="AG14" s="13">
+      <c r="AI14" s="13">
         <v>7140</v>
       </c>
-      <c r="AH14" s="13">
+      <c r="AJ14" s="13">
         <v>7440</v>
       </c>
-      <c r="AI14" s="13">
+      <c r="AK14" s="13">
         <v>7530</v>
       </c>
-      <c r="AJ14" s="13">
+      <c r="AL14" s="13">
         <v>7535</v>
       </c>
-      <c r="AK14" s="13">
+      <c r="AM14" s="13">
         <v>7535</v>
       </c>
-      <c r="AL14" s="13">
+      <c r="AN14" s="13">
         <v>7568</v>
       </c>
-      <c r="AM14" s="13">
+      <c r="AO14" s="13">
         <v>7699</v>
       </c>
-      <c r="AN14" s="13">
+      <c r="AP14" s="13">
         <v>7638</v>
       </c>
-      <c r="AO14" s="13">
+      <c r="AQ14" s="13">
         <v>7654</v>
       </c>
-      <c r="AP14" s="13">
+      <c r="AR14" s="13">
         <v>7584</v>
       </c>
-      <c r="AQ14" s="13">
+      <c r="AS14" s="13">
         <v>7479</v>
       </c>
-      <c r="AR14" s="13">
+      <c r="AT14" s="13">
         <v>7490</v>
       </c>
-      <c r="AS14" s="13">
+      <c r="AU14" s="13">
         <v>7480</v>
       </c>
-      <c r="AT14" s="13">
+      <c r="AV14" s="13">
         <v>7270</v>
       </c>
-      <c r="AU14" s="13">
+      <c r="AW14" s="13">
         <v>7163</v>
       </c>
-      <c r="AV14" s="13">
+      <c r="AX14" s="13">
         <v>7231</v>
       </c>
-      <c r="AW14" s="13">
+      <c r="AY14" s="13">
         <v>7100</v>
       </c>
-      <c r="AX14" s="13">
+      <c r="AZ14" s="13">
         <v>7100</v>
       </c>
-      <c r="AY14" s="13">
+      <c r="BA14" s="13">
         <v>7027</v>
       </c>
-      <c r="AZ14" s="13">
+      <c r="BB14" s="13">
         <v>6984</v>
       </c>
-      <c r="BA14" s="13">
+      <c r="BC14" s="13">
         <v>6944</v>
       </c>
-      <c r="BB14" s="13">
+      <c r="BD14" s="13">
         <v>6924</v>
       </c>
-      <c r="BC14" s="13">
+      <c r="BE14" s="13">
         <v>6930</v>
       </c>
-      <c r="BD14" s="13">
+      <c r="BF14" s="13">
         <v>6938</v>
       </c>
-      <c r="BE14" s="13">
+      <c r="BG14" s="13">
         <v>6989</v>
       </c>
-      <c r="BF14" s="13">
+      <c r="BH14" s="13">
         <v>6871</v>
       </c>
-      <c r="BG14" s="13">
+      <c r="BI14" s="13">
         <v>6943</v>
       </c>
-      <c r="BH14" s="13">
+      <c r="BJ14" s="13">
         <v>7040</v>
       </c>
-      <c r="BI14" s="29">
+      <c r="BK14" s="29">
         <v>6696</v>
       </c>
-      <c r="BJ14" s="13">
+      <c r="BL14" s="13">
         <v>6965</v>
       </c>
-      <c r="BK14" s="13">
+      <c r="BM14" s="13">
         <v>6788</v>
       </c>
-      <c r="BL14" s="29">
+      <c r="BN14" s="29">
         <v>6696</v>
       </c>
-      <c r="BM14" s="13">
+      <c r="BO14" s="13">
         <v>6625</v>
       </c>
-      <c r="BN14" s="13">
+      <c r="BP14" s="13">
         <v>6660</v>
       </c>
-      <c r="BO14" s="13">
+      <c r="BQ14" s="13">
         <v>6791</v>
       </c>
-      <c r="BP14" s="13">
+      <c r="BR14" s="13">
         <v>6610</v>
       </c>
-      <c r="BQ14" s="13">
-        <f t="shared" si="0"/>
+      <c r="BS14" s="13">
+        <f>(G14*H14)/100-BY14</f>
         <v>648.37980000000005</v>
       </c>
-      <c r="BR14" s="13">
-        <f t="shared" si="2"/>
+      <c r="BT14" s="13">
+        <f>(G14*H14)/100</f>
         <v>648.37980000000005</v>
       </c>
-      <c r="BS14" s="13">
-        <f t="shared" ref="BS14" si="5">(BR14-BQ14)</f>
+      <c r="BU14" s="13">
+        <f t="shared" ref="BU14" si="2">(BT14-BS14)</f>
         <v>0</v>
       </c>
-      <c r="BT14" s="13">
-        <f>((BH14-H14)/H14)*100</f>
+      <c r="BV14" s="13">
+        <f>((BJ14-H14)/H14)*100</f>
         <v>-2.2794972946411995</v>
       </c>
-      <c r="BW14" s="15">
-        <f t="shared" si="4"/>
+      <c r="BY14" s="15">
+        <f>(BW14*BX14-BW14*H14)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A15" s="1">
         <v>5137534</v>
       </c>
@@ -3536,76 +3633,80 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
+        <v>12145</v>
+      </c>
+      <c r="J15" s="13">
+        <v>12145</v>
+      </c>
+      <c r="K15" s="13">
         <v>11855.12</v>
       </c>
-      <c r="J15" s="13">
+      <c r="L15" s="13">
         <v>11946.75</v>
       </c>
-      <c r="K15" s="13">
+      <c r="M15" s="13">
         <v>11946.75</v>
       </c>
-      <c r="L15" s="13">
+      <c r="N15" s="13">
         <v>14679.12</v>
       </c>
-      <c r="M15" s="13">
+      <c r="O15" s="13">
         <v>14679.12</v>
       </c>
-      <c r="N15" s="13">
+      <c r="P15" s="13">
         <v>13968</v>
       </c>
-      <c r="O15" s="13">
+      <c r="Q15" s="13">
         <v>15528.12</v>
       </c>
-      <c r="P15" s="13">
+      <c r="R15" s="13">
         <v>14358.25</v>
       </c>
-      <c r="Q15" s="13">
+      <c r="S15" s="13">
         <v>14385.75</v>
       </c>
-      <c r="R15" s="13">
+      <c r="T15" s="13">
         <v>13880</v>
       </c>
-      <c r="S15" s="13">
+      <c r="U15" s="13">
         <v>13610.62</v>
       </c>
-      <c r="T15" s="13">
+      <c r="V15" s="13">
         <v>13016</v>
       </c>
-      <c r="U15" s="13">
+      <c r="W15" s="13">
         <v>12487.37</v>
       </c>
-      <c r="V15" s="13">
+      <c r="X15" s="13">
         <v>12638.62</v>
       </c>
-      <c r="W15" s="13">
+      <c r="Y15" s="13">
         <v>12533.87</v>
       </c>
-      <c r="X15" s="13">
+      <c r="Z15" s="13">
         <v>11299.5</v>
       </c>
-      <c r="Y15" s="13">
+      <c r="AA15" s="13">
         <v>11193.12</v>
       </c>
-      <c r="Z15" s="13">
+      <c r="AB15" s="13">
         <v>11548.62</v>
       </c>
-      <c r="AA15" s="13">
+      <c r="AC15" s="13">
         <v>11125.62</v>
       </c>
-      <c r="AB15" s="13">
+      <c r="AD15" s="13">
         <v>10932.12</v>
       </c>
-      <c r="AC15" s="13">
+      <c r="AE15" s="13">
         <v>11095.62</v>
       </c>
-      <c r="AD15" s="13">
+      <c r="AF15" s="13">
         <v>10910.58</v>
       </c>
-      <c r="AE15" s="13">
+      <c r="AG15" s="13">
         <v>11609.37</v>
       </c>
-      <c r="AF15" s="13"/>
-      <c r="AG15" s="13"/>
       <c r="AH15" s="13"/>
       <c r="AI15" s="13"/>
       <c r="AJ15" s="13"/>
@@ -3614,9 +3715,9 @@
       <c r="AM15" s="13"/>
       <c r="AN15" s="13"/>
       <c r="AO15" s="13"/>
-      <c r="AP15" s="14"/>
+      <c r="AP15" s="13"/>
       <c r="AQ15" s="13"/>
-      <c r="AR15" s="13"/>
+      <c r="AR15" s="14"/>
       <c r="AS15" s="13"/>
       <c r="AT15" s="13"/>
       <c r="AU15" s="13"/>
@@ -3633,36 +3734,38 @@
       <c r="BF15" s="13"/>
       <c r="BG15" s="13"/>
       <c r="BH15" s="13"/>
-      <c r="BI15" s="29"/>
+      <c r="BI15" s="13"/>
       <c r="BJ15" s="13"/>
-      <c r="BK15" s="13"/>
-      <c r="BL15" s="29"/>
+      <c r="BK15" s="29"/>
+      <c r="BL15" s="13"/>
       <c r="BM15" s="13"/>
-      <c r="BN15" s="13"/>
+      <c r="BN15" s="29"/>
       <c r="BO15" s="13"/>
       <c r="BP15" s="13"/>
-      <c r="BQ15" s="13">
-        <f t="shared" si="0"/>
+      <c r="BQ15" s="13"/>
+      <c r="BR15" s="13"/>
+      <c r="BS15" s="13">
+        <f>(G15*H15)/100-BY15</f>
         <v>927.90960000000007</v>
       </c>
-      <c r="BR15" s="13">
-        <f t="shared" si="2"/>
+      <c r="BT15" s="13">
+        <f>(G15*H15)/100</f>
         <v>927.90960000000007</v>
       </c>
-      <c r="BS15" s="13">
-        <f t="shared" ref="BS15:BS18" si="6">(BR15-BQ15)</f>
+      <c r="BU15" s="13">
+        <f t="shared" ref="BU15:BU18" si="3">(BT15-BS15)</f>
         <v>0</v>
       </c>
-      <c r="BT15" s="13">
-        <f>((BH15-H15)/H15)*100</f>
+      <c r="BV15" s="13">
+        <f>((BJ15-H15)/H15)*100</f>
         <v>-100</v>
       </c>
-      <c r="BW15" s="15">
-        <f t="shared" ref="BW15:BW18" si="7">(BU15*BV15-BU15*H15)/100</f>
+      <c r="BY15" s="15">
+        <f>(BW15*BX15-BW15*H15)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A16" s="1">
         <v>5135470</v>
       </c>
@@ -3691,213 +3794,219 @@
         <v>199.49</v>
       </c>
       <c r="I16" s="13">
+        <v>221.02</v>
+      </c>
+      <c r="J16" s="13">
+        <v>221.02</v>
+      </c>
+      <c r="K16" s="13">
         <v>218.38</v>
       </c>
-      <c r="J16" s="13">
+      <c r="L16" s="13">
         <v>218.36</v>
       </c>
-      <c r="K16" s="13">
+      <c r="M16" s="13">
         <v>223.13</v>
       </c>
-      <c r="L16" s="13">
+      <c r="N16" s="13">
         <v>227.54</v>
       </c>
-      <c r="M16" s="13">
+      <c r="O16" s="13">
         <v>226.96</v>
       </c>
-      <c r="N16" s="13">
+      <c r="P16" s="13">
         <v>225.24</v>
       </c>
-      <c r="O16" s="13">
+      <c r="Q16" s="13">
         <v>223.25</v>
       </c>
-      <c r="P16" s="13">
+      <c r="R16" s="13">
         <v>219.14</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="S16" s="13">
         <v>219.14</v>
       </c>
-      <c r="R16" s="13">
+      <c r="T16" s="13">
         <v>219.3</v>
       </c>
-      <c r="S16" s="13">
+      <c r="U16" s="13">
         <v>222.79</v>
       </c>
-      <c r="T16" s="13">
+      <c r="V16" s="13">
         <v>221.16</v>
       </c>
-      <c r="U16" s="13">
+      <c r="W16" s="13">
         <v>220.66</v>
       </c>
-      <c r="V16" s="13">
+      <c r="X16" s="13">
         <v>222.06</v>
       </c>
-      <c r="W16" s="13">
+      <c r="Y16" s="13">
         <v>218.71</v>
       </c>
-      <c r="X16" s="13">
+      <c r="Z16" s="13">
         <v>216.74</v>
       </c>
-      <c r="Y16" s="13">
+      <c r="AA16" s="13">
         <v>216.04</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="AB16" s="13">
         <v>210.69</v>
       </c>
-      <c r="AA16" s="13">
+      <c r="AC16" s="13">
         <v>210.69</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AD16" s="13">
         <v>198</v>
       </c>
-      <c r="AC16" s="13">
+      <c r="AE16" s="13">
         <v>196.74</v>
       </c>
-      <c r="AD16" s="13">
+      <c r="AF16" s="13">
         <v>192.56</v>
       </c>
-      <c r="AE16" s="13">
+      <c r="AG16" s="13">
         <v>192.23</v>
       </c>
-      <c r="AF16" s="13">
+      <c r="AH16" s="13">
         <v>191.19</v>
       </c>
-      <c r="AG16" s="13">
+      <c r="AI16" s="13">
         <v>193.62</v>
       </c>
-      <c r="AH16" s="13">
+      <c r="AJ16" s="13">
         <v>190.75</v>
       </c>
-      <c r="AI16" s="13">
+      <c r="AK16" s="13">
         <v>189.06</v>
       </c>
-      <c r="AJ16" s="13">
+      <c r="AL16" s="13">
         <v>182.73</v>
       </c>
-      <c r="AK16" s="13">
+      <c r="AM16" s="13">
         <v>182.73</v>
       </c>
-      <c r="AL16" s="13">
+      <c r="AN16" s="13">
         <v>177.92</v>
       </c>
-      <c r="AM16" s="13">
+      <c r="AO16" s="13">
         <v>179.16</v>
       </c>
-      <c r="AN16" s="13">
+      <c r="AP16" s="13">
         <v>179.34</v>
       </c>
-      <c r="AO16" s="13">
+      <c r="AQ16" s="13">
         <v>176.5</v>
       </c>
-      <c r="AP16" s="13">
+      <c r="AR16" s="13">
         <v>176.5</v>
       </c>
-      <c r="AQ16" s="13">
+      <c r="AS16" s="13">
         <v>175.93</v>
       </c>
-      <c r="AR16" s="13">
+      <c r="AT16" s="13">
         <v>174.51</v>
       </c>
-      <c r="AS16" s="13">
+      <c r="AU16" s="13">
         <v>173.91</v>
       </c>
-      <c r="AT16" s="13">
+      <c r="AV16" s="13">
         <v>177.1</v>
       </c>
-      <c r="AU16" s="13">
+      <c r="AW16" s="13">
         <v>178.24</v>
       </c>
-      <c r="AV16" s="13">
+      <c r="AX16" s="13">
         <v>176.52</v>
       </c>
-      <c r="AW16" s="13">
+      <c r="AY16" s="13">
         <v>178.27</v>
       </c>
-      <c r="AX16" s="13">
+      <c r="AZ16" s="13">
         <v>175.29</v>
       </c>
-      <c r="AY16" s="13">
+      <c r="BA16" s="13">
         <v>175.34</v>
       </c>
-      <c r="AZ16" s="13">
+      <c r="BB16" s="13">
         <v>174.41</v>
       </c>
-      <c r="BA16" s="13">
+      <c r="BC16" s="13">
         <v>176.22</v>
       </c>
-      <c r="BB16" s="13">
+      <c r="BD16" s="13">
         <v>174</v>
       </c>
-      <c r="BC16" s="13">
+      <c r="BE16" s="13">
         <v>176.35</v>
       </c>
-      <c r="BD16" s="13">
+      <c r="BF16" s="13">
         <v>177.71</v>
       </c>
-      <c r="BE16" s="13">
+      <c r="BG16" s="13">
         <v>180.08</v>
       </c>
-      <c r="BF16" s="13">
+      <c r="BH16" s="13">
         <v>181.96</v>
       </c>
-      <c r="BG16" s="13">
+      <c r="BI16" s="13">
         <v>182.9</v>
       </c>
-      <c r="BH16" s="13">
+      <c r="BJ16" s="13">
         <v>181.86</v>
       </c>
-      <c r="BI16" s="29">
+      <c r="BK16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BJ16" s="13">
+      <c r="BL16" s="13">
         <v>181.07</v>
       </c>
-      <c r="BK16" s="13">
+      <c r="BM16" s="13">
         <v>182.56</v>
       </c>
-      <c r="BL16" s="29">
+      <c r="BN16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BM16" s="13">
+      <c r="BO16" s="13">
         <v>178.86</v>
       </c>
-      <c r="BN16" s="13">
+      <c r="BP16" s="13">
         <v>180.16</v>
       </c>
-      <c r="BO16" s="13">
+      <c r="BQ16" s="13">
         <v>179.56</v>
       </c>
-      <c r="BP16" s="13">
+      <c r="BR16" s="13">
         <v>176.55</v>
       </c>
-      <c r="BQ16" s="13">
-        <f t="shared" si="0"/>
+      <c r="BS16" s="13">
+        <f>(G16*H16)/100-BY16</f>
         <v>1413.1220000000008</v>
       </c>
-      <c r="BR16" s="13">
-        <f t="shared" si="2"/>
+      <c r="BT16" s="13">
+        <f>(G16*H16)/100</f>
         <v>997.45</v>
       </c>
-      <c r="BS16" s="13">
-        <f t="shared" si="6"/>
+      <c r="BU16" s="13">
+        <f t="shared" si="3"/>
         <v>-415.67200000000071</v>
       </c>
-      <c r="BT16" s="13">
-        <f>((BH16-H16)/H16)*100</f>
+      <c r="BV16" s="13">
+        <f>((BJ16-H16)/H16)*100</f>
         <v>-8.8375357160759904</v>
       </c>
-      <c r="BU16">
+      <c r="BW16">
         <v>1864</v>
       </c>
-      <c r="BV16">
+      <c r="BX16">
         <v>177.19</v>
       </c>
-      <c r="BW16" s="15">
-        <f t="shared" si="7"/>
+      <c r="BY16" s="15">
+        <f>(BW16*BX16-BW16*H16)/100</f>
         <v>-415.67200000000071</v>
       </c>
     </row>
-    <row r="17" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A17" s="1">
         <v>5134135</v>
       </c>
@@ -3932,67 +4041,71 @@
         <v>184.42</v>
       </c>
       <c r="K17" s="13">
+        <v>184.42</v>
+      </c>
+      <c r="L17" s="13">
+        <v>184.42</v>
+      </c>
+      <c r="M17" s="13">
         <v>199.37</v>
       </c>
-      <c r="L17" s="13">
+      <c r="N17" s="13">
         <v>194.88</v>
-      </c>
-      <c r="M17" s="13">
-        <v>189.51</v>
-      </c>
-      <c r="N17" s="13">
-        <v>189.51</v>
       </c>
       <c r="O17" s="13">
         <v>189.51</v>
       </c>
       <c r="P17" s="13">
+        <v>189.51</v>
+      </c>
+      <c r="Q17" s="13">
+        <v>189.51</v>
+      </c>
+      <c r="R17" s="13">
         <v>185.52</v>
       </c>
-      <c r="Q17" s="13">
+      <c r="S17" s="13">
         <v>185.52</v>
-      </c>
-      <c r="R17" s="13">
-        <v>178.98</v>
-      </c>
-      <c r="S17" s="13">
-        <v>178.98</v>
       </c>
       <c r="T17" s="13">
         <v>178.98</v>
       </c>
       <c r="U17" s="13">
-        <v>170.7</v>
+        <v>178.98</v>
       </c>
       <c r="V17" s="13">
-        <v>170.7</v>
+        <v>178.98</v>
       </c>
       <c r="W17" s="13">
         <v>170.7</v>
       </c>
       <c r="X17" s="13">
+        <v>170.7</v>
+      </c>
+      <c r="Y17" s="13">
+        <v>170.7</v>
+      </c>
+      <c r="Z17" s="13">
         <v>170.45</v>
-      </c>
-      <c r="Y17" s="13">
-        <v>160.84</v>
-      </c>
-      <c r="Z17" s="13">
-        <v>160.84</v>
       </c>
       <c r="AA17" s="13">
         <v>160.84</v>
       </c>
       <c r="AB17" s="13">
+        <v>160.84</v>
+      </c>
+      <c r="AC17" s="13">
+        <v>160.84</v>
+      </c>
+      <c r="AD17" s="13">
         <v>159.02000000000001</v>
       </c>
-      <c r="AC17" s="13">
+      <c r="AE17" s="13">
         <v>159.65</v>
       </c>
-      <c r="AD17" s="13">
+      <c r="AF17" s="13">
         <v>159.65</v>
       </c>
-      <c r="AE17" s="13"/>
-      <c r="AF17" s="13"/>
       <c r="AG17" s="13"/>
       <c r="AH17" s="13"/>
       <c r="AI17" s="13"/>
@@ -4021,36 +4134,38 @@
       <c r="BF17" s="13"/>
       <c r="BG17" s="13"/>
       <c r="BH17" s="13"/>
-      <c r="BI17" s="29"/>
+      <c r="BI17" s="13"/>
       <c r="BJ17" s="13"/>
-      <c r="BK17" s="13"/>
-      <c r="BL17" s="29"/>
+      <c r="BK17" s="29"/>
+      <c r="BL17" s="13"/>
       <c r="BM17" s="13"/>
-      <c r="BN17" s="13"/>
+      <c r="BN17" s="29"/>
       <c r="BO17" s="13"/>
       <c r="BP17" s="13"/>
-      <c r="BQ17" s="13">
-        <f t="shared" si="0"/>
+      <c r="BQ17" s="13"/>
+      <c r="BR17" s="13"/>
+      <c r="BS17" s="13">
+        <f>(G17*H17)/100-BY17</f>
         <v>957.9</v>
       </c>
-      <c r="BR17" s="13">
-        <f t="shared" si="2"/>
+      <c r="BT17" s="13">
+        <f>(G17*H17)/100</f>
         <v>957.9</v>
       </c>
-      <c r="BS17" s="13">
-        <f t="shared" ref="BS17" si="8">(BR17-BQ17)</f>
+      <c r="BU17" s="13">
+        <f t="shared" ref="BU17" si="4">(BT17-BS17)</f>
         <v>0</v>
       </c>
-      <c r="BT17" s="13">
-        <f>((BH17-H17)/H17)*100</f>
+      <c r="BV17" s="13">
+        <f>((BJ17-H17)/H17)*100</f>
         <v>-100</v>
       </c>
-      <c r="BW17" s="15">
-        <f t="shared" si="7"/>
+      <c r="BY17" s="15">
+        <f>(BW17*BX17-BW17*H17)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A18" s="1">
         <v>1168723</v>
       </c>
@@ -4079,79 +4194,83 @@
         <v>1434</v>
       </c>
       <c r="I18" s="13">
+        <v>1866</v>
+      </c>
+      <c r="J18" s="13">
+        <v>1866</v>
+      </c>
+      <c r="K18" s="13">
         <v>1886</v>
       </c>
-      <c r="J18" s="13">
+      <c r="L18" s="13">
         <v>1818</v>
       </c>
-      <c r="K18" s="13">
+      <c r="M18" s="13">
         <v>1785</v>
       </c>
-      <c r="L18" s="13">
+      <c r="N18" s="13">
         <v>1828</v>
       </c>
-      <c r="M18" s="13">
+      <c r="O18" s="13">
         <v>1811</v>
       </c>
-      <c r="N18" s="13">
+      <c r="P18" s="13">
         <v>1825</v>
       </c>
-      <c r="O18" s="13">
+      <c r="Q18" s="13">
         <v>1831</v>
       </c>
-      <c r="P18" s="13">
+      <c r="R18" s="13">
         <v>1799</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="S18" s="13">
         <v>1757</v>
       </c>
-      <c r="R18" s="13">
+      <c r="T18" s="13">
         <v>1698</v>
       </c>
-      <c r="S18" s="13">
+      <c r="U18" s="13">
         <v>1694</v>
       </c>
-      <c r="T18" s="13">
+      <c r="V18" s="13">
         <v>1671</v>
       </c>
-      <c r="U18" s="13">
+      <c r="W18" s="13">
         <v>1660</v>
       </c>
-      <c r="V18" s="13">
+      <c r="X18" s="13">
         <v>1660</v>
       </c>
-      <c r="W18" s="13">
+      <c r="Y18" s="13">
         <v>1646</v>
       </c>
-      <c r="X18" s="13">
+      <c r="Z18" s="13">
         <v>1648</v>
       </c>
-      <c r="Y18" s="13">
+      <c r="AA18" s="13">
         <v>1614</v>
       </c>
-      <c r="Z18" s="13">
+      <c r="AB18" s="13">
         <v>1626</v>
       </c>
-      <c r="AA18" s="13">
+      <c r="AC18" s="13">
         <v>1587</v>
       </c>
-      <c r="AB18" s="13">
+      <c r="AD18" s="13">
         <v>1548</v>
       </c>
-      <c r="AC18" s="13">
+      <c r="AE18" s="13">
         <v>1500</v>
       </c>
-      <c r="AD18" s="13">
+      <c r="AF18" s="13">
         <v>1491</v>
       </c>
-      <c r="AE18" s="13">
+      <c r="AG18" s="13">
         <v>1444</v>
       </c>
-      <c r="AF18" s="13">
+      <c r="AH18" s="13">
         <v>1431</v>
       </c>
-      <c r="AG18" s="13"/>
-      <c r="AH18" s="13"/>
       <c r="AI18" s="13"/>
       <c r="AJ18" s="13"/>
       <c r="AK18" s="13"/>
@@ -4176,64 +4295,66 @@
       <c r="BD18" s="13"/>
       <c r="BE18" s="13"/>
       <c r="BF18" s="13"/>
-      <c r="BG18" s="13">
+      <c r="BG18" s="13"/>
+      <c r="BH18" s="13"/>
+      <c r="BI18" s="13">
         <v>1788</v>
       </c>
-      <c r="BH18" s="13">
+      <c r="BJ18" s="13">
         <v>1788</v>
       </c>
-      <c r="BI18" s="29">
+      <c r="BK18" s="29">
         <v>1780</v>
       </c>
-      <c r="BJ18" s="13">
+      <c r="BL18" s="13">
         <v>1814</v>
       </c>
-      <c r="BK18" s="13">
+      <c r="BM18" s="13">
         <v>1794</v>
       </c>
-      <c r="BL18" s="29">
+      <c r="BN18" s="29">
         <v>1780</v>
       </c>
-      <c r="BM18" s="13">
+      <c r="BO18" s="13">
         <v>1772</v>
       </c>
-      <c r="BN18" s="13">
+      <c r="BP18" s="13">
         <v>1798</v>
       </c>
-      <c r="BO18" s="13">
+      <c r="BQ18" s="13">
         <v>1806</v>
       </c>
-      <c r="BP18" s="13">
+      <c r="BR18" s="13">
         <v>1801</v>
       </c>
-      <c r="BQ18" s="13">
-        <f t="shared" si="0"/>
+      <c r="BS18" s="13">
+        <f>(G18*H18)/100-BY18</f>
         <v>292.79999999999995</v>
       </c>
-      <c r="BR18" s="13">
-        <f t="shared" si="2"/>
+      <c r="BT18" s="13">
+        <f>(G18*H18)/100</f>
         <v>645.29999999999995</v>
       </c>
-      <c r="BS18" s="13">
-        <f t="shared" si="6"/>
+      <c r="BU18" s="13">
+        <f t="shared" si="3"/>
         <v>352.5</v>
       </c>
-      <c r="BT18" s="13">
-        <f>((BH18-H18)/H18)*100</f>
+      <c r="BV18" s="13">
+        <f>((BJ18-H18)/H18)*100</f>
         <v>24.686192468619247</v>
       </c>
-      <c r="BU18">
+      <c r="BW18">
         <v>100</v>
       </c>
-      <c r="BV18">
+      <c r="BX18">
         <v>1786.5</v>
       </c>
-      <c r="BW18" s="15">
-        <f t="shared" si="7"/>
+      <c r="BY18" s="15">
+        <f>(BW18*BX18-BW18*H18)/100</f>
         <v>352.5</v>
       </c>
     </row>
-    <row r="19" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A19" s="1">
         <v>1122654</v>
       </c>
@@ -4262,16 +4383,20 @@
         <v>102.77</v>
       </c>
       <c r="I19" s="13">
+        <v>86.7</v>
+      </c>
+      <c r="J19" s="13">
+        <v>86.7</v>
+      </c>
+      <c r="K19" s="13">
         <v>91.5</v>
       </c>
-      <c r="J19" s="13">
+      <c r="L19" s="13">
         <v>91.5</v>
       </c>
-      <c r="K19" s="13">
+      <c r="M19" s="13">
         <v>132.6</v>
       </c>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
       <c r="P19" s="13"/>
@@ -4286,23 +4411,23 @@
       <c r="Y19" s="13"/>
       <c r="Z19" s="13"/>
       <c r="AA19" s="13"/>
-      <c r="AB19" s="13">
+      <c r="AB19" s="13"/>
+      <c r="AC19" s="13"/>
+      <c r="AD19" s="13">
         <v>6461</v>
       </c>
-      <c r="AC19" s="13">
+      <c r="AE19" s="13">
         <v>6503</v>
       </c>
-      <c r="AD19" s="13">
+      <c r="AF19" s="13">
         <v>6535</v>
       </c>
-      <c r="AE19" s="13">
+      <c r="AG19" s="13">
         <v>6532</v>
       </c>
-      <c r="AF19" s="13">
+      <c r="AH19" s="13">
         <v>6515</v>
       </c>
-      <c r="AG19" s="13"/>
-      <c r="AH19" s="13"/>
       <c r="AI19" s="13"/>
       <c r="AJ19" s="13"/>
       <c r="AK19" s="13"/>
@@ -4329,33 +4454,35 @@
       <c r="BF19" s="13"/>
       <c r="BG19" s="13"/>
       <c r="BH19" s="13"/>
-      <c r="BI19" s="29"/>
+      <c r="BI19" s="13"/>
       <c r="BJ19" s="13"/>
-      <c r="BK19" s="13"/>
-      <c r="BL19" s="29"/>
+      <c r="BK19" s="29"/>
+      <c r="BL19" s="13"/>
       <c r="BM19" s="13"/>
-      <c r="BN19" s="13"/>
+      <c r="BN19" s="29"/>
       <c r="BO19" s="13"/>
       <c r="BP19" s="13"/>
-      <c r="BQ19" s="13">
-        <f t="shared" si="0"/>
+      <c r="BQ19" s="13"/>
+      <c r="BR19" s="13"/>
+      <c r="BS19" s="13">
+        <f>(G19*H19)/100-BY19</f>
         <v>719.39</v>
       </c>
-      <c r="BR19" s="13">
-        <f t="shared" si="2"/>
+      <c r="BT19" s="13">
+        <f>(G19*H19)/100</f>
         <v>719.39</v>
       </c>
-      <c r="BS19" s="13"/>
-      <c r="BT19" s="13"/>
-      <c r="BU19">
+      <c r="BU19" s="13"/>
+      <c r="BV19" s="13"/>
+      <c r="BW19">
         <v>7</v>
       </c>
-      <c r="BV19">
+      <c r="BX19">
         <v>6461</v>
       </c>
-      <c r="BW19" s="15"/>
-    </row>
-    <row r="20" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BY19" s="15"/>
+    </row>
+    <row r="20" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A20" s="1">
         <v>363010</v>
       </c>
@@ -4384,10 +4511,14 @@
         <v>65</v>
       </c>
       <c r="I20" s="13">
+        <v>89</v>
+      </c>
+      <c r="J20" s="13">
+        <v>89</v>
+      </c>
+      <c r="K20" s="13">
         <v>87.5</v>
       </c>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
@@ -4437,28 +4568,30 @@
       <c r="BF20" s="13"/>
       <c r="BG20" s="13"/>
       <c r="BH20" s="13"/>
-      <c r="BI20" s="29"/>
+      <c r="BI20" s="13"/>
       <c r="BJ20" s="13"/>
-      <c r="BK20" s="13"/>
-      <c r="BL20" s="29"/>
+      <c r="BK20" s="29"/>
+      <c r="BL20" s="13"/>
       <c r="BM20" s="13"/>
-      <c r="BN20" s="13"/>
+      <c r="BN20" s="29"/>
       <c r="BO20" s="13"/>
       <c r="BP20" s="13"/>
-      <c r="BQ20" s="13">
-        <f>(G20*H20)/100-BW20</f>
+      <c r="BQ20" s="13"/>
+      <c r="BR20" s="13"/>
+      <c r="BS20" s="13">
+        <f>(G20*H20)/100-BY20</f>
         <v>195</v>
       </c>
-      <c r="BR20" s="13">
+      <c r="BT20" s="13">
         <f>(G20*H20)/100</f>
         <v>195</v>
       </c>
-      <c r="BS20" s="13"/>
-      <c r="BT20" s="13"/>
-      <c r="BW20" s="15"/>
-    </row>
-    <row r="21" spans="1:75" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:75" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BU20" s="13"/>
+      <c r="BV20" s="13"/>
+      <c r="BY20" s="15"/>
+    </row>
+    <row r="21" spans="1:77" ht="14.4" thickBot="1"/>
+    <row r="22" spans="1:77" ht="45" customHeight="1" thickBot="1">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4519,147 +4652,151 @@
       <c r="BF22" s="13"/>
       <c r="BG22" s="13"/>
       <c r="BH22" s="13"/>
-      <c r="BI22" s="29"/>
+      <c r="BI22" s="13"/>
       <c r="BJ22" s="13"/>
-      <c r="BK22" s="13"/>
-      <c r="BL22" s="29"/>
+      <c r="BK22" s="29"/>
+      <c r="BL22" s="13"/>
       <c r="BM22" s="13"/>
-      <c r="BN22" s="13"/>
+      <c r="BN22" s="29"/>
       <c r="BO22" s="13"/>
       <c r="BP22" s="13"/>
       <c r="BQ22" s="13"/>
       <c r="BR22" s="13"/>
       <c r="BS22" s="13"/>
       <c r="BT22" s="13"/>
-      <c r="BW22" s="15"/>
-    </row>
-    <row r="23" spans="1:75" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BU22" s="13"/>
+      <c r="BV22" s="13"/>
+      <c r="BY22" s="15"/>
+    </row>
+    <row r="23" spans="1:77" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="3"/>
+      <c r="E23" s="3" t="s">
+        <v>108</v>
+      </c>
       <c r="F23" s="4"/>
       <c r="G23" s="27"/>
       <c r="H23" s="13"/>
       <c r="I23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19+G20*I20)/100</f>
-        <v>14302.159599999999</v>
+        <v>14263.01</v>
       </c>
       <c r="J23" s="23">
         <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19+G20*J20)/100</f>
+        <v>14263.01</v>
+      </c>
+      <c r="K23" s="23">
+        <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19+G20*K20)/100</f>
+        <v>14302.159599999999</v>
+      </c>
+      <c r="L23" s="23">
+        <f>(L2*G2+G3*L3+L4*G4+G5*L5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+L13*G13+G14*L14+L15*G15+G16*L16+G17*L17+L18*G18+G19*L19+G20*L20)/100</f>
         <v>13804.511999999999</v>
-      </c>
-      <c r="K23" s="23">
-        <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19)/100</f>
-        <v>14033.53</v>
-      </c>
-      <c r="L23" s="23">
-        <f>(L2*G2+G3*L3+L4*G4+G5*L5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+L13*G13+G14*L14+L15*G15+G16*L16+G17*L17+L18*G18+G19*L19)/100</f>
-        <v>13844.2896</v>
       </c>
       <c r="M23" s="23">
         <f>(M2*G2+G3*M3+M4*G4+G5*M5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+M13*G13+G14*M14+M15*G15+G16*M16+G17*M17+M18*G18+G19*M19)/100</f>
-        <v>13659.785600000001</v>
+        <v>14033.53</v>
       </c>
       <c r="N23" s="23">
         <f>(N2*G2+G3*N3+N4*G4+G5*N5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+N13*G13+G14*N14+N15*G15+G16*N16+G17*N17+N18*G18+G19*N19)/100</f>
-        <v>13683.918</v>
+        <v>13844.2896</v>
       </c>
       <c r="O23" s="23">
         <f>(O2*G2+G3*O3+O4*G4+G5*O5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+O13*G13+G14*O14+O15*G15+G16*O16+G17*O17+O18*G18+G19*O19)/100</f>
-        <v>13839.923600000002</v>
+        <v>13659.785600000001</v>
       </c>
       <c r="P23" s="23">
         <f>(P2*G2+G3*P3+P4*G4+G5*P5+G6*P6+G7*P7+G8*P8+G9*P9+G10*P10+G11*P11+G12*P12+P13*G13+G14*P14+P15*G15+G16*P16+G17*P17+P18*G18+G19*P19)/100</f>
-        <v>13475.503999999999</v>
+        <v>13683.918</v>
       </c>
       <c r="Q23" s="23">
         <f>(Q2*G2+G3*Q3+Q4*G4+G5*Q5+G6*Q6+G7*Q7+G8*Q8+G9*Q9+G10*Q10+G11*Q11+G12*Q12+Q13*G13+G14*Q14+Q15*G15+G16*Q16+G17*Q17+Q18*G18+G19*Q19)/100</f>
-        <v>13192.96</v>
+        <v>13839.923600000002</v>
       </c>
       <c r="R23" s="23">
         <f>(R2*G2+G3*R3+R4*G4+G5*R5+G6*R6+G7*R7+G8*R8+G9*R9+G10*R10+G11*R11+G12*R12+R13*G13+G14*R14+R15*G15+G16*R16+G17*R17+R18*G18+G19*R19)/100</f>
-        <v>12923.761999999999</v>
+        <v>13475.503999999999</v>
       </c>
       <c r="S23" s="23">
         <f>(S2*G2+G3*S3+S4*G4+G5*S5+G6*S6+G7*S7+G8*S8+G9*S9+G10*S10+G11*S11+G12*S12+S13*G13+G14*S14+S15*G15+G16*S16+G17*S17+S18*G18+G19*S19)/100</f>
+        <v>13192.96</v>
+      </c>
+      <c r="T23" s="23">
+        <f>(T2*G2+G3*T3+T4*G4+G5*T5+G6*T6+G7*T7+G8*T8+G9*T9+G10*T10+G11*T11+G12*T12+T13*G13+G14*T14+T15*G15+G16*T16+G17*T17+T18*G18+G19*T19)/100</f>
+        <v>12923.761999999999</v>
+      </c>
+      <c r="U23" s="23">
+        <f>(U2*G2+G3*U3+U4*G4+G5*U5+G6*U6+G7*U7+G8*U8+G9*U9+G10*U10+G11*U11+G12*U12+U13*G13+G14*U14+U15*G15+G16*U16+G17*U17+U18*G18+G19*U19)/100</f>
         <v>13102.8776</v>
-      </c>
-      <c r="T23" s="23">
-        <f>(T3*G3+G4*T4+T5*G5+G6*T6+G7*T7+G8*T8+G9*T9+G10*T10+G11*T11+G12*T12+G14*T14+T15*G15+G16*T16+T17*G17+G18*T18+G19*T19)/100</f>
-        <v>12191.99</v>
-      </c>
-      <c r="U23" s="23">
-        <f>(U3*G3+G4*U4+U5*G5+G6*U6+G7*U7+G8*U8+G9*U9+G10*U10+G11*U11+G12*U12+G14*U14+U15*G15+G16*U16+U17*G17+G18*U18+G19*U19)/100</f>
-        <v>11970.357599999999</v>
       </c>
       <c r="V23" s="23">
         <f>(V3*G3+G4*V4+V5*G5+G6*V6+G7*V7+G8*V8+G9*V9+G10*V10+G11*V11+G12*V12+G14*V14+V15*G15+G16*V16+V17*G17+G18*V18+G19*V19)/100</f>
-        <v>11989.4576</v>
+        <v>12191.99</v>
       </c>
       <c r="W23" s="23">
         <f>(W3*G3+G4*W4+W5*G5+G6*W6+G7*W7+G8*W8+G9*W9+G10*W10+G11*W11+G12*W12+G14*W14+W15*G15+G16*W16+W17*G17+G18*W18+G19*W19)/100</f>
-        <v>11896.177600000001</v>
+        <v>11970.357599999999</v>
       </c>
       <c r="X23" s="23">
         <f>(X3*G3+G4*X4+X5*G5+G6*X6+G7*X7+G8*X8+G9*X9+G10*X10+G11*X11+G12*X12+G14*X14+X15*G15+G16*X16+X17*G17+G18*X18+G19*X19)/100</f>
-        <v>11552.98</v>
+        <v>11989.4576</v>
       </c>
       <c r="Y23" s="23">
         <f>(Y3*G3+G4*Y4+Y5*G5+G6*Y6+G7*Y7+G8*Y8+G9*Y9+G10*Y10+G11*Y11+G12*Y12+G14*Y14+Y15*G15+G16*Y16+Y17*G17+G18*Y18+G19*Y19)/100</f>
-        <v>11467.277599999999</v>
+        <v>11896.177600000001</v>
       </c>
       <c r="Z23" s="23">
         <f>(Z3*G3+G4*Z4+Z5*G5+G6*Z6+G7*Z7+G8*Z8+G9*Z9+G10*Z10+G11*Z11+G12*Z12+G14*Z14+Z15*G15+G16*Z16+Z17*G17+G18*Z18+G19*Z19)/100</f>
+        <v>11552.98</v>
+      </c>
+      <c r="AA23" s="23">
+        <f>(AA3*G3+G4*AA4+AA5*G5+G6*AA6+G7*AA7+G8*AA8+G9*AA9+G10*AA10+G11*AA11+G12*AA12+G14*AA14+AA15*G15+G16*AA16+AA17*G17+G18*AA18+G19*AA19)/100</f>
+        <v>11467.277599999999</v>
+      </c>
+      <c r="AB23" s="23">
+        <f>(AB3*G3+G4*AB4+AB5*G5+G6*AB6+G7*AB7+G8*AB8+G9*AB9+G10*AB10+G11*AB11+G12*AB12+G14*AB14+AB15*G15+G16*AB16+AB17*G17+G18*AB18+G19*AB19)/100</f>
         <v>10332.035599999999</v>
       </c>
-      <c r="AA23" s="23">
-        <f>(AA5*G5+G6*AA6+AA7*G7+G8*AA8+G9*AA9+G10*AA10+G11*AA11+G12*AA12+G14*AA14+G20*AA20+G15*AA15+AA16*G16+G17*AA17+AA18*G18+G19*AA19)/100</f>
+      <c r="AC23" s="23">
+        <f>(AC5*G5+G6*AC6+AC7*G7+G8*AC8+G9*AC9+G10*AC10+G11*AC11+G12*AC12+G14*AC14+G20*AC20+G15*AC15+AC16*G16+G17*AC17+AC18*G18+G19*AC19)/100</f>
         <v>9234.9995999999992</v>
-      </c>
-      <c r="AB23" s="23" t="e">
-        <f>(AB5*G5+G7*AB7+AB8*G8+G9*AB9+#REF!*#REF!+G10*AB10+G11*AB11+G12*AB12+G14*AB14+G19*AB19+G20*AB20+AB6*G6+G15*AB15+#REF!*#REF!+G16*AB16+G17*AB17+AB18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AB3+#REF!*#REF!)/100</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AC23" s="23" t="e">
-        <f>(AC5*G5+G7*AC7+AC8*G8+G9*AC9+#REF!*#REF!+G10*AC10+G11*AC11+G12*AC12+G14*AC14+G19*AC19+G20*AC20+AC6*G6+G15*AC15+#REF!*#REF!+G16*AC16+G17*AC17+AC18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AC3+#REF!*#REF!)/100</f>
-        <v>#REF!</v>
       </c>
       <c r="AD23" s="23" t="e">
         <f>(AD5*G5+G7*AD7+AD8*G8+G9*AD9+#REF!*#REF!+G10*AD10+G11*AD11+G12*AD12+G14*AD14+G19*AD19+G20*AD20+AD6*G6+G15*AD15+#REF!*#REF!+G16*AD16+G17*AD17+AD18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AD3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AE23" s="23" t="e">
-        <f>(AE5*G5+G7*AE7+AE8*G8+G9*AE9+#REF!*#REF!+G10*AE10+G11*AE11+G12*AE12+G14*AE14+G19*AE19+G20*AE20+AE6*G6+G15*AE15+#REF!*#REF!+G16*AE16+G18*AE18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AE3+#REF!*#REF!+G4*AE4)/100</f>
+        <f>(AE5*G5+G7*AE7+AE8*G8+G9*AE9+#REF!*#REF!+G10*AE10+G11*AE11+G12*AE12+G14*AE14+G19*AE19+G20*AE20+AE6*G6+G15*AE15+#REF!*#REF!+G16*AE16+G17*AE17+AE18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AE3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AF23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AF3*G3+#REF!*#REF!+G4*AF4+G5*AF5+G7*AF7+G8*AF8+G9*AF9+#REF!*#REF!+G10*AF10+AF11*G11+G12*AF12+AF14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AF20+AF6*G6+#REF!*#REF!+G16*AF16+G18*AF18+G19*AF19)/100</f>
+        <f>(AF5*G5+G7*AF7+AF8*G8+G9*AF9+#REF!*#REF!+G10*AF10+G11*AF11+G12*AF12+G14*AF14+G19*AF19+G20*AF20+AF6*G6+G15*AF15+#REF!*#REF!+G16*AF16+G17*AF17+AF18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AF3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AG23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AG3*G3+#REF!*#REF!+G4*AG4+G5*AG5+G7*AG7+G8*AG8+G9*AG9+#REF!*#REF!+G10*AG10+AG11*G11+G12*AG12+AG14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AG20+AG6*G6+#REF!*#REF!+G16*AG16+G18*AG18+G19*AG19)/100</f>
+        <f>(AG5*G5+G7*AG7+AG8*G8+G9*AG9+#REF!*#REF!+G10*AG10+G11*AG11+G12*AG12+G14*AG14+G19*AG19+G20*AG20+AG6*G6+G15*AG15+#REF!*#REF!+G16*AG16+G18*AG18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AG3+#REF!*#REF!+G4*AG4)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AH23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AH3*G3+#REF!*#REF!+G4*AH4+G5*AH5+AH7*G7+AH8*G8+AH9*G9+#REF!*#REF!+G10*AH10+AH11*G11+G12*AH12+AH14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AH20+G6*AH6+#REF!*#REF!+G16*AH16+G18*AH18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AH3*G3+#REF!*#REF!+G4*AH4+G5*AH5+G7*AH7+G8*AH8+G9*AH9+#REF!*#REF!+G10*AH10+AH11*G11+G12*AH12+AH14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AH20+AH6*G6+#REF!*#REF!+G16*AH16+G18*AH18+G19*AH19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AI23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AI3*G3+#REF!*#REF!+G4*AI4+G5*AI5+AI7*G7+AI8*G8+AI9*G9+#REF!*#REF!+G10*AI10+AI11*G11+G12*AI12+AI14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AI20+G6*AI6+#REF!*#REF!+G16*AI16+G18*AI18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AI3*G3+#REF!*#REF!+G4*AI4+G5*AI5+G7*AI7+G8*AI8+G9*AI9+#REF!*#REF!+G10*AI10+AI11*G11+G12*AI12+AI14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AI20+AI6*G6+#REF!*#REF!+G16*AI16+G18*AI18+G19*AI19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AJ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AJ3*G3+#REF!*#REF!+G4*AJ4+G8*AJ8+AJ9*G9+#REF!*#REF!+AJ10*G10+G11*AJ11+G14*AJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AJ6+#REF!*#REF!+G16*AJ16+G18*AJ18+G7*AJ7+G5*AJ5+G12*AJ12+G20*AJ20)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AJ3*G3+#REF!*#REF!+G4*AJ4+G5*AJ5+AJ7*G7+AJ8*G8+AJ9*G9+#REF!*#REF!+G10*AJ10+AJ11*G11+G12*AJ12+AJ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AJ20+G6*AJ6+#REF!*#REF!+G16*AJ16+G18*AJ18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AK23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AK3*G3+#REF!*#REF!+G4*AK4+G8*AK8+AK9*G9+#REF!*#REF!+AK10*G10+G11*AK11+G14*AK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AK6+#REF!*#REF!+G16*AK16+G18*AK18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AK3*G3+#REF!*#REF!+G4*AK4+G5*AK5+AK7*G7+AK8*G8+AK9*G9+#REF!*#REF!+G10*AK10+AK11*G11+G12*AK12+AK14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AK20+G6*AK6+#REF!*#REF!+G16*AK16+G18*AK18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AL23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AL3*G3+#REF!*#REF!+G4*AL4+G8*AL8+G9*AL9+#REF!*#REF!+G10*AL10+AL11*G11+AL14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AL6*G6+#REF!*#REF!+G16*AL16+G18*AL18+G19*AL19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AL3*G3+#REF!*#REF!+G4*AL4+G8*AL8+AL9*G9+#REF!*#REF!+AL10*G10+G11*AL11+G14*AL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AL6+#REF!*#REF!+G16*AL16+G18*AL18+G7*AL7+G5*AL5+G12*AL12+G20*AL20)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AM23" s="23" t="e">
@@ -4667,15 +4804,15 @@
         <v>#REF!</v>
       </c>
       <c r="AN23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+AN9*G9+#REF!*#REF!+AN10*G10+G11*AN11+G14*AN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AN6+#REF!*#REF!+G16*AN16+G18*AN18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+G9*AN9+#REF!*#REF!+G10*AN10+AN11*G11+AN14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AN6*G6+#REF!*#REF!+G16*AN16+G18*AN18+G19*AN19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AO23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+AO9*G9+AO10*G10+AO11*G11+G14*AO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AO6+#REF!*#REF!+G16*AO16+G18*AO18+G19*AO19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+AO9*G9+#REF!*#REF!+AO10*G10+G11*AO11+G14*AO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AO6+#REF!*#REF!+G16*AO16+G18*AO18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AP23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+AP9*G9+AP10*G10+AP11*G11+G14*AP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AP6+#REF!*#REF!+G16*AP16+G18*AP18+G19*AP19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+AP9*G9+#REF!*#REF!+AP10*G10+G11*AP11+G14*AP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AP6+#REF!*#REF!+G16*AP16+G18*AP18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AQ23" s="23" t="e">
@@ -4691,23 +4828,23 @@
         <v>#REF!</v>
       </c>
       <c r="AT23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AT3*G3+#REF!*#REF!+G4*AT4+G8*AT8+AT9*G9+AT10*G10+AT11*G11+G14*AT14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AT6+#REF!*#REF!+G16*AT16+G18*AT18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AT3*G3+#REF!*#REF!+G4*AT4+G8*AT8+AT9*G9+AT10*G10+AT11*G11+G14*AT14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AT6+#REF!*#REF!+G16*AT16+G18*AT18+G19*AT19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AU23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AU3*G3+#REF!*#REF!+G4*AU4+G8*AU8+AU10*G10+AU11*G11+G14*AU14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AU6+#REF!*#REF!+G16*AU16+G18*AU18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AU3*G3+#REF!*#REF!+G4*AU4+G8*AU8+AU9*G9+AU10*G10+AU11*G11+G14*AU14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AU6+#REF!*#REF!+G16*AU16+G18*AU18+G19*AU19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AV23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AV3*G3+#REF!*#REF!+G4*AV4+G8*AV8+G10*AV10+AV11*G11+AV14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AV6*G6+#REF!*#REF!+G16*AV16+G18*AV18+G19*AV19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AV3*G3+#REF!*#REF!+G4*AV4+G8*AV8+AV9*G9+AV10*G10+AV11*G11+G14*AV14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AV6+#REF!*#REF!+G16*AV16+G18*AV18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AW23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AW3*G3+#REF!*#REF!+G4*AW4+G10*AW10+AW11*G11+AW14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AW6*G6+#REF!*#REF!+G16*AW16+G18*AW18+G19*AW19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AW3*G3+#REF!*#REF!+G4*AW4+G8*AW8+AW10*G10+AW11*G11+G14*AW14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AW6+#REF!*#REF!+G16*AW16+G18*AW18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AX23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AX3*G3+#REF!*#REF!+G4*AX4+G10*AX10+AX11*G11+AX14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AX6*G6+#REF!*#REF!+G16*AX16+G18*AX18+G19*AX19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AX3*G3+#REF!*#REF!+G4*AX4+G8*AX8+G10*AX10+AX11*G11+AX14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AX6*G6+#REF!*#REF!+G16*AX16+G18*AX18+G19*AX19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AY23" s="23" t="e">
@@ -4715,11 +4852,11 @@
         <v>#REF!</v>
       </c>
       <c r="AZ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AZ3*G3+#REF!*#REF!+G4*AZ4+G10*AZ10+AZ11*G11+AZ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AZ6*G6+G16*AZ16+G18*AZ18+G19*AZ19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AZ3*G3+#REF!*#REF!+G4*AZ4+G10*AZ10+AZ11*G11+AZ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AZ6*G6+#REF!*#REF!+G16*AZ16+G18*AZ18+G19*AZ19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BA23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BA3*G3+#REF!*#REF!+G4*BA4+G10*BA10+BA11*G11+BA14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BA6*G6+G16*BA16+G18*BA18+G19*BA19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BA3*G3+#REF!*#REF!+G4*BA4+G10*BA10+BA11*G11+BA14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BA6*G6+#REF!*#REF!+G16*BA16+G18*BA18+G19*BA19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BB23" s="23" t="e">
@@ -4743,26 +4880,26 @@
         <v>#REF!</v>
       </c>
       <c r="BG23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BG3*G3+#REF!*#REF!+G4*BG4+G10*BG10+G11*BG11+G14*BG14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BG6+BG16*G16+G18*BG18+G19*BG19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BG3*G3+#REF!*#REF!+G4*BG4+G10*BG10+BG11*G11+BG14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BG6*G6+G16*BG16+G18*BG18+G19*BG19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BH23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BH3*G3+#REF!*#REF!+G4*BH4+G10*BH10+G14*BH14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BH6+BH16*G16+G18*BH18+G19*BH19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BH3*G3+#REF!*#REF!+G4*BH4+G10*BH10+BH11*G11+BH14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BH6*G6+G16*BH16+G18*BH18+G19*BH19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BI23" s="23" t="e">
-        <f>(#REF!*#REF!+BI3*G3+G4*BI4+G14*BI14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BI6+BI16*G16+G18*BI18+G19*BI19+G22*BI22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BI3*G3+#REF!*#REF!+G4*BI4+G10*BI10+G11*BI11+G14*BI14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BI6+BI16*G16+G18*BI18+G19*BI19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BJ23" s="23" t="e">
-        <f>(#REF!*#REF!+BJ3*G3+G4*BJ4+G14*BJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BJ6+BJ16*G16+G18*BJ18+G19*BJ19+G22*BJ22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BJ3*G3+#REF!*#REF!+G4*BJ4+G10*BJ10+G14*BJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BJ6+BJ16*G16+G18*BJ18+G19*BJ19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BK23" s="23" t="e">
         <f>(#REF!*#REF!+BK3*G3+G4*BK4+G14*BK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BK6+BK16*G16+G18*BK18+G19*BK19+G22*BK22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BL23" s="30" t="e">
+      <c r="BL23" s="23" t="e">
         <f>(#REF!*#REF!+BL3*G3+G4*BL4+G14*BL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BL6+BL16*G16+G18*BL18+G19*BL19+G22*BL22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
@@ -4770,27 +4907,35 @@
         <f>(#REF!*#REF!+BM3*G3+G4*BM4+G14*BM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BM6+BM16*G16+G18*BM18+G19*BM19+G22*BM22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BN23" s="23" t="e">
-        <f>(#REF!*#REF!+BN3*G3+G14*BN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BN6+BN16*G16+G18*BN18+G19*BN19+G22*BN22+#REF!*#REF!+#REF!*#REF!)/100</f>
+      <c r="BN23" s="30" t="e">
+        <f>(#REF!*#REF!+BN3*G3+G4*BN4+G14*BN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BN6+BN16*G16+G18*BN18+G19*BN19+G22*BN22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BO23" s="23" t="e">
-        <f>(#REF!*#REF!+BO3*G3+G14*BO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BO6+BO16*G16+G18*BO18+G19*BO19+G22*BO22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+BO3*G3+G4*BO4+G14*BO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BO6+BO16*G16+G18*BO18+G19*BO19+G22*BO22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BP23" s="23" t="e">
         <f>(#REF!*#REF!+BP3*G3+G14*BP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BP6+BP16*G16+G18*BP18+G19*BP19+G22*BP22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BQ23" s="13"/>
-      <c r="BR23" s="13"/>
+      <c r="BQ23" s="23" t="e">
+        <f>(#REF!*#REF!+BQ3*G3+G14*BQ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BQ6+BQ16*G16+G18*BQ18+G19*BQ19+G22*BQ22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <v>#REF!</v>
+      </c>
+      <c r="BR23" s="23" t="e">
+        <f>(#REF!*#REF!+BR3*G3+G14*BR14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BR6+BR16*G16+G18*BR18+G19*BR19+G22*BR22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <v>#REF!</v>
+      </c>
       <c r="BS23" s="13"/>
       <c r="BT23" s="13"/>
-      <c r="BW23" s="15">
+      <c r="BU23" s="13"/>
+      <c r="BV23" s="13"/>
+      <c r="BY23" s="15">
         <v>1149.48</v>
       </c>
     </row>
-    <row r="24" spans="1:75" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:77" ht="44.25" customHeight="1" thickBot="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -4859,29 +5004,31 @@
       <c r="BN24" s="14"/>
       <c r="BO24" s="14"/>
       <c r="BP24" s="14"/>
-      <c r="BQ24" s="23">
-        <f>SUM(BQ2:BQ20)</f>
+      <c r="BQ24" s="14"/>
+      <c r="BR24" s="14"/>
+      <c r="BS24" s="23">
+        <f>SUM(BS2:BS20)</f>
         <v>12571.202799999999</v>
       </c>
-      <c r="BR24" s="23">
-        <f>SUM(BR2:BR20)</f>
+      <c r="BT24" s="23">
+        <f>SUM(BT2:BT20)</f>
         <v>13020.522800000001</v>
       </c>
-      <c r="BS24" s="24">
-        <f>BR24-BQ24</f>
+      <c r="BU24" s="24">
+        <f>BT24-BS24</f>
         <v>449.32000000000153</v>
       </c>
-      <c r="BT24" s="13">
-        <f>((BR24-BQ24)/BQ24)*100</f>
+      <c r="BV24" s="13">
+        <f>((BT24-BS24)/BS24)*100</f>
         <v>3.5742005530290353</v>
       </c>
-      <c r="BW24" s="15">
-        <f>SUM(BW5:BW23)</f>
+      <c r="BY24" s="15">
+        <f>SUM(BY5:BY23)</f>
         <v>1472.0683999999992</v>
       </c>
     </row>
-    <row r="25" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="BQ25" s="15">
+    <row r="25" spans="1:77">
+      <c r="BS25" s="15">
         <v>12034.32</v>
       </c>
     </row>
@@ -4939,17 +5086,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DECD697-7590-4F64-9E15-0FA62A69A078}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="7" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="1" width="17.59765625" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="7" width="17.59765625" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="10" max="10" width="9.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>11</v>
       </c>
@@ -4982,7 +5129,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -5008,7 +5155,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>9787</v>
+        <v>9823</v>
       </c>
       <c r="J2" s="25"/>
       <c r="L2" s="21">
@@ -5020,7 +5167,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -5046,7 +5193,7 @@
       <c r="G3" s="17"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1245</v>
+        <v>1074</v>
       </c>
       <c r="J3" s="26"/>
       <c r="L3" s="21">
@@ -5058,7 +5205,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -5084,7 +5231,7 @@
       <c r="G4" s="17"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6295</v>
+        <v>6298</v>
       </c>
       <c r="J4" s="26"/>
       <c r="L4" s="21">
@@ -5096,7 +5243,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -5121,7 +5268,7 @@
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>587.5</v>
+        <v>638</v>
       </c>
       <c r="J5" s="26"/>
       <c r="L5" s="21">
@@ -5133,7 +5280,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -5158,7 +5305,7 @@
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4740</v>
+        <v>4799</v>
       </c>
       <c r="J6" s="26"/>
       <c r="L6" s="21">
@@ -5170,7 +5317,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -5196,7 +5343,7 @@
       <c r="G7" s="18"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>4033</v>
+        <v>4022</v>
       </c>
       <c r="J7" s="26"/>
       <c r="L7" s="21">
@@ -5208,7 +5355,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -5234,7 +5381,7 @@
       <c r="G8" s="18"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>43640</v>
+        <v>39600</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -5245,7 +5392,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -5271,7 +5418,7 @@
       <c r="G9" s="17"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>11020</v>
+        <v>11290</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -5282,7 +5429,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -5308,7 +5455,7 @@
       <c r="G10" s="18"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5164</v>
+        <v>5126</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -5319,7 +5466,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -5345,7 +5492,7 @@
       <c r="G11" s="18"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1173</v>
+        <v>1099</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -5356,7 +5503,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -5382,7 +5529,7 @@
       <c r="G12" s="18"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>28720</v>
+        <v>29460</v>
       </c>
       <c r="J12" s="26"/>
       <c r="L12" s="21">
@@ -5394,7 +5541,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -5420,7 +5567,7 @@
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1074</v>
+        <v>1009</v>
       </c>
       <c r="J13" s="26"/>
       <c r="L13" s="21">
@@ -5432,7 +5579,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -5458,7 +5605,7 @@
       <c r="G14" s="17"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7911</v>
+        <v>8051</v>
       </c>
       <c r="J14" s="26"/>
       <c r="L14" s="21">
@@ -5470,7 +5617,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -5496,7 +5643,7 @@
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>11855.12</v>
+        <v>12145</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
@@ -5508,7 +5655,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -5534,7 +5681,7 @@
       <c r="G16" s="17"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>218.38</v>
+        <v>221.02</v>
       </c>
       <c r="J16" s="26"/>
       <c r="L16" s="21">
@@ -5546,7 +5693,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -5584,7 +5731,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -5610,7 +5757,7 @@
       <c r="G18" s="18"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1886</v>
+        <v>1866</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -5621,7 +5768,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -5643,7 +5790,7 @@
       <c r="G19" s="18"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>91.5</v>
+        <v>86.7</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -5654,7 +5801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5688,7 +5835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5722,7 +5869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5756,7 +5903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5790,7 +5937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5824,7 +5971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5858,7 +6005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5892,7 +6039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5926,7 +6073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17" t="str">
         <f>'התיק העדכני'!E20</f>
         <v>אירודרום קבוצה</v>
@@ -5948,7 +6095,7 @@
       <c r="G28" s="19"/>
       <c r="I28" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>87.5</v>
+        <v>89</v>
       </c>
       <c r="J28" s="26"/>
       <c r="L28" s="21">
@@ -5968,15 +6115,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7390F3B9-AE45-44AE-B4DF-D92B58EB94BD}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="7" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="7" width="17.59765625" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -6006,7 +6153,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -6032,7 +6179,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>9787</v>
+        <v>9823</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+GEMINI!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
@@ -6043,7 +6190,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -6069,7 +6216,7 @@
       <c r="G3" s="7"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1245</v>
+        <v>1074</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
@@ -6080,7 +6227,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -6106,7 +6253,7 @@
       <c r="G4" s="7"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6295</v>
+        <v>6298</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+GEMINI!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
@@ -6117,7 +6264,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -6143,7 +6290,7 @@
       <c r="G5" s="7"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>587.5</v>
+        <v>638</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
@@ -6154,7 +6301,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -6180,7 +6327,7 @@
       <c r="G6" s="7"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4740</v>
+        <v>4799</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
@@ -6191,7 +6338,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -6217,7 +6364,7 @@
       <c r="G7" s="8"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>4033</v>
+        <v>4022</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+GEMINI!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
@@ -6228,7 +6375,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -6254,7 +6401,7 @@
       <c r="G8" s="8"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>43640</v>
+        <v>39600</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+GEMINI!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -6265,7 +6412,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -6291,7 +6438,7 @@
       <c r="G9" s="8"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>11020</v>
+        <v>11290</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+GEMINI!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -6302,7 +6449,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -6328,7 +6475,7 @@
       <c r="G10" s="8"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5164</v>
+        <v>5126</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+GEMINI!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -6339,7 +6486,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -6365,7 +6512,7 @@
       <c r="G11" s="8"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1173</v>
+        <v>1099</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+GEMINI!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -6376,7 +6523,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -6402,7 +6549,7 @@
       <c r="G12" s="8"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>28720</v>
+        <v>29460</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+GEMINI!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
@@ -6413,7 +6560,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -6439,7 +6586,7 @@
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1074</v>
+        <v>1009</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+GEMINI!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
@@ -6450,7 +6597,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -6476,7 +6623,7 @@
       <c r="G14" s="7"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7911</v>
+        <v>8051</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
@@ -6487,7 +6634,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -6513,7 +6660,7 @@
       <c r="G15" s="7"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>11855.12</v>
+        <v>12145</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+GEMINI!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
@@ -6524,7 +6671,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -6550,7 +6697,7 @@
       <c r="G16" s="7"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>218.38</v>
+        <v>221.02</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
@@ -6561,7 +6708,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -6598,7 +6745,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -6624,7 +6771,7 @@
       <c r="G18" s="8"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1886</v>
+        <v>1866</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+GEMINI!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -6635,7 +6782,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -6657,7 +6804,7 @@
       <c r="G19" s="8"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>91.5</v>
+        <v>86.7</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+GEMINI!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -6668,7 +6815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -6680,7 +6827,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -6692,7 +6839,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -6704,7 +6851,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -6716,7 +6863,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -6728,7 +6875,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -6740,7 +6887,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -6752,7 +6899,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -6764,7 +6911,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -6784,15 +6931,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88497C0-21A8-47C7-B959-3D6DF74EF6E2}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="6" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="6" width="17.59765625" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -6822,7 +6969,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -6848,7 +6995,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>9787</v>
+        <v>9823</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+GEMINI!E2+DEEPSEEK!E2)/4</f>
@@ -6859,7 +7006,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -6885,7 +7032,7 @@
       <c r="G3" s="10"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1245</v>
+        <v>1074</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
@@ -6896,7 +7043,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -6922,7 +7069,7 @@
       <c r="G4" s="10"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6295</v>
+        <v>6298</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+GEMINI!E4+DEEPSEEK!E4)/4</f>
@@ -6933,7 +7080,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -6959,7 +7106,7 @@
       <c r="G5" s="10"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>587.5</v>
+        <v>638</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
@@ -6970,7 +7117,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -6996,7 +7143,7 @@
       <c r="G6" s="10"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4740</v>
+        <v>4799</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
@@ -7007,7 +7154,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -7033,7 +7180,7 @@
       <c r="G7" s="10"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>4033</v>
+        <v>4022</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+GEMINI!E7+DEEPSEEK!E7)/4</f>
@@ -7044,7 +7191,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -7069,7 +7216,7 @@
       </c>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>43640</v>
+        <v>39600</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+GEMINI!E8+DEEPSEEK!E8)/4</f>
@@ -7080,7 +7227,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -7105,7 +7252,7 @@
       </c>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>11020</v>
+        <v>11290</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+GEMINI!E9+DEEPSEEK!E9)/4</f>
@@ -7116,7 +7263,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -7141,7 +7288,7 @@
       </c>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5164</v>
+        <v>5126</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+GEMINI!E10+DEEPSEEK!E10)/4</f>
@@ -7152,7 +7299,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -7177,7 +7324,7 @@
       </c>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1173</v>
+        <v>1099</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+GEMINI!E11+DEEPSEEK!E11)/4</f>
@@ -7188,7 +7335,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -7214,7 +7361,7 @@
       <c r="G12" s="10"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>28720</v>
+        <v>29460</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+GEMINI!E12+DEEPSEEK!E12)/4</f>
@@ -7225,7 +7372,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -7251,7 +7398,7 @@
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1074</v>
+        <v>1009</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+CHATGPT!E13+GEMINI!E13+DEEPSEEK!E13)/4</f>
@@ -7262,7 +7409,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -7288,7 +7435,7 @@
       <c r="G14" s="10"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7911</v>
+        <v>8051</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
@@ -7299,7 +7446,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -7325,7 +7472,7 @@
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>11855.12</v>
+        <v>12145</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
@@ -7336,7 +7483,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -7362,7 +7509,7 @@
       <c r="G16" s="10"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>218.38</v>
+        <v>221.02</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+GEMINI!E16+DEEPSEEK!E16)/4</f>
@@ -7373,7 +7520,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -7410,7 +7557,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -7435,7 +7582,7 @@
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1886</v>
+        <v>1866</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
@@ -7446,7 +7593,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -7467,7 +7614,7 @@
       <c r="F19" s="16"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>91.5</v>
+        <v>86.7</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+GEMINI!E19+DEEPSEEK!E19)/4</f>
@@ -7478,7 +7625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -7490,7 +7637,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -7502,7 +7649,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -7514,7 +7661,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -7526,7 +7673,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -7538,7 +7685,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -7550,7 +7697,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -7562,7 +7709,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -7574,7 +7721,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -7594,16 +7741,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D354D65C-237D-4544-BBD1-8A37190947C4}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="5" width="17.5703125" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="5" width="17.59765625" customWidth="1"/>
+    <col min="6" max="6" width="20.3984375" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -7632,7 +7779,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -7658,7 +7805,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>9787</v>
+        <v>9823</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+PERPLIXITY!E2+GEMINI!E2)/4</f>
@@ -7669,7 +7816,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -7695,7 +7842,7 @@
       <c r="G3" s="31"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1245</v>
+        <v>1074</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
@@ -7706,7 +7853,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -7731,7 +7878,7 @@
       </c>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6295</v>
+        <v>6298</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+GEMINI!E4)/4</f>
@@ -7742,7 +7889,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -7768,7 +7915,7 @@
       <c r="G5" s="31"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>587.5</v>
+        <v>638</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
@@ -7779,7 +7926,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -7805,7 +7952,7 @@
       <c r="G6" s="31"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4740</v>
+        <v>4799</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
@@ -7816,7 +7963,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -7841,7 +7988,7 @@
       </c>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>4033</v>
+        <v>4022</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+GEMINI!E7)/4</f>
@@ -7852,7 +7999,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -7878,7 +8025,7 @@
       <c r="G8" s="31"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>43640</v>
+        <v>39600</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+GEMINI!E8)/4</f>
@@ -7889,7 +8036,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -7915,7 +8062,7 @@
       <c r="G9" s="31"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>11020</v>
+        <v>11290</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+GEMINI!E9)/4</f>
@@ -7926,7 +8073,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -7952,7 +8099,7 @@
       <c r="G10" s="31"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5164</v>
+        <v>5126</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+GEMINI!E10)/4</f>
@@ -7963,7 +8110,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -7989,7 +8136,7 @@
       <c r="G11" s="31"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1173</v>
+        <v>1099</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+GEMINI!E11)/4</f>
@@ -8000,7 +8147,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -8026,7 +8173,7 @@
       <c r="G12" s="31"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>28720</v>
+        <v>29460</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+GEMINI!E12)/4</f>
@@ -8037,7 +8184,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -8063,12 +8210,12 @@
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1074</v>
+        <v>1009</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -8094,7 +8241,7 @@
       <c r="G14" s="31"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7911</v>
+        <v>8051</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
@@ -8105,7 +8252,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -8130,7 +8277,7 @@
       </c>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>87.5</v>
+        <v>89</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+PERPLIXITY!E15+GEMINI!E15)/4</f>
@@ -8141,7 +8288,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -8166,7 +8313,7 @@
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>11855.12</v>
+        <v>12145</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
@@ -8177,7 +8324,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -8203,7 +8350,7 @@
       <c r="G17" s="31"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>218.38</v>
+        <v>221.02</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+GEMINI!E17)/4</f>
@@ -8214,7 +8361,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -8251,7 +8398,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -8270,7 +8417,7 @@
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1886</v>
+        <v>1866</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+GEMINI!E19)/4</f>
@@ -8281,7 +8428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -8292,7 +8439,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -8304,7 +8451,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -8316,7 +8463,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -8328,7 +8475,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -8340,7 +8487,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -8352,7 +8499,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -8364,7 +8511,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -8376,7 +8523,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/673b1203f7e82b27/מסמכים/GitHub/BURSA/BURSA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\BURSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{0EB1D6B3-6D51-49E5-82E7-092D73AC6EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FEFCB76-9B35-4691-8C02-F24B1305AC67}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4C4BA0-E721-42FA-9823-8447E4B0DE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
   <sheets>
     <sheet name="התיק העדכני" sheetId="1" r:id="rId1"/>
@@ -24,23 +24,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="112">
   <si>
     <t>MTF מחקה אינדקס תעשיה ישראל</t>
   </si>
@@ -370,6 +359,12 @@
   </si>
   <si>
     <t>מחיר 03/02/2026</t>
+  </si>
+  <si>
+    <t>מחיר 04/02/2026</t>
+  </si>
+  <si>
+    <t>מחיר 05/02/2026</t>
   </si>
 </sst>
 </file>
@@ -379,11 +374,11 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₪&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -392,7 +387,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -443,13 +438,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -840,9 +835,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא של Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -880,7 +875,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -986,7 +981,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1128,7 +1123,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1136,22 +1131,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86B4639-EF9D-4B16-B2C9-0D5E9C5EEC8B}">
-  <dimension ref="A1:BY25"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:BZ25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="17.59765625" customWidth="1"/>
-    <col min="6" max="6" width="13.296875" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="60" width="14.8984375" customWidth="1"/>
-    <col min="61" max="70" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="13" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="13.09765625" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="11" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="7.09765625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="11.59765625" customWidth="1"/>
+    <col min="1" max="5" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="61" width="14.85546875" customWidth="1"/>
+    <col min="62" max="71" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="13" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="11" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="1" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1180,211 +1175,214 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="K1" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BK1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BL1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BM1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BN1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BO1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="BO1" s="6" t="s">
+      <c r="BP1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="BP1" s="6" t="s">
+      <c r="BQ1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="BQ1" s="6" t="s">
+      <c r="BR1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BR1" s="6" t="s">
+      <c r="BS1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="BS1" s="6" t="s">
+      <c r="BT1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BU1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="BU1" s="6" t="s">
+      <c r="BV1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BW1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="BW1" s="12" t="s">
+      <c r="BX1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="BX1" s="12" t="s">
+      <c r="BY1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="BY1" s="12" t="s">
+      <c r="BZ1" s="12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="2" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>282012</v>
       </c>
@@ -1413,45 +1411,47 @@
         <v>11000</v>
       </c>
       <c r="I2" s="13">
+        <v>7260</v>
+      </c>
+      <c r="J2" s="13">
+        <v>7260</v>
+      </c>
+      <c r="K2" s="13">
         <v>9823</v>
       </c>
-      <c r="J2" s="13">
-        <v>9823</v>
-      </c>
-      <c r="K2" s="13">
+      <c r="L2" s="13">
         <v>9787</v>
       </c>
-      <c r="L2" s="13">
+      <c r="M2" s="13">
         <v>9650</v>
       </c>
-      <c r="M2" s="13">
+      <c r="N2" s="13">
         <v>9981</v>
       </c>
-      <c r="N2" s="13">
+      <c r="O2" s="13">
         <v>12130</v>
       </c>
-      <c r="O2" s="13">
+      <c r="P2" s="13">
         <v>11840</v>
       </c>
-      <c r="P2" s="13">
+      <c r="Q2" s="13">
         <v>11400</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="R2" s="13">
         <v>11360</v>
       </c>
-      <c r="R2" s="13">
+      <c r="S2" s="13">
         <v>11000</v>
       </c>
-      <c r="S2" s="13">
+      <c r="T2" s="13">
         <v>10700</v>
       </c>
-      <c r="T2" s="13">
+      <c r="U2" s="13">
         <v>10400</v>
       </c>
-      <c r="U2" s="13">
+      <c r="V2" s="13">
         <v>11230</v>
       </c>
-      <c r="V2" s="6"/>
       <c r="W2" s="6"/>
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
@@ -1492,29 +1492,30 @@
       <c r="BH2" s="6"/>
       <c r="BI2" s="6"/>
       <c r="BJ2" s="6"/>
-      <c r="BK2" s="32"/>
-      <c r="BL2" s="6"/>
+      <c r="BK2" s="6"/>
+      <c r="BL2" s="32"/>
       <c r="BM2" s="6"/>
-      <c r="BN2" s="32"/>
-      <c r="BO2" s="6"/>
+      <c r="BN2" s="6"/>
+      <c r="BO2" s="32"/>
       <c r="BP2" s="6"/>
       <c r="BQ2" s="6"/>
       <c r="BR2" s="6"/>
-      <c r="BS2" s="13">
-        <f>(G2*H2)/100-BY2</f>
+      <c r="BS2" s="6"/>
+      <c r="BT2" s="13">
+        <f t="shared" ref="BT2:BT20" si="0">(G2*H2)/100-BZ2</f>
         <v>770</v>
       </c>
-      <c r="BT2" s="13">
-        <f>(G2*H2)/100</f>
+      <c r="BU2" s="13">
+        <f t="shared" ref="BU2:BU20" si="1">(G2*H2)/100</f>
         <v>770</v>
       </c>
-      <c r="BU2" s="6"/>
       <c r="BV2" s="6"/>
-      <c r="BW2" s="25"/>
+      <c r="BW2" s="6"/>
       <c r="BX2" s="25"/>
       <c r="BY2" s="25"/>
-    </row>
-    <row r="3" spans="1:77" ht="45" customHeight="1" thickBot="1">
+      <c r="BZ2" s="25"/>
+    </row>
+    <row r="3" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1227552</v>
       </c>
@@ -1543,63 +1544,65 @@
         <v>1153.6300000000001</v>
       </c>
       <c r="I3" s="13">
+        <v>925</v>
+      </c>
+      <c r="J3" s="13">
+        <v>925</v>
+      </c>
+      <c r="K3" s="13">
         <v>1074</v>
       </c>
-      <c r="J3" s="13">
-        <v>1074</v>
-      </c>
-      <c r="K3" s="13">
+      <c r="L3" s="13">
         <v>1245</v>
-      </c>
-      <c r="L3" s="13">
-        <v>1311</v>
       </c>
       <c r="M3" s="13">
         <v>1311</v>
       </c>
       <c r="N3" s="13">
+        <v>1311</v>
+      </c>
+      <c r="O3" s="13">
         <v>1340</v>
       </c>
-      <c r="O3" s="13">
+      <c r="P3" s="13">
         <v>1500</v>
       </c>
-      <c r="P3" s="13">
+      <c r="Q3" s="13">
         <v>1424</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="R3" s="13">
         <v>1348</v>
       </c>
-      <c r="R3" s="13">
+      <c r="S3" s="13">
         <v>1373</v>
       </c>
-      <c r="S3" s="13">
+      <c r="T3" s="13">
         <v>1331</v>
       </c>
-      <c r="T3" s="13">
+      <c r="U3" s="13">
         <v>1386</v>
       </c>
-      <c r="U3" s="13">
+      <c r="V3" s="13">
         <v>1342</v>
       </c>
-      <c r="V3" s="13">
+      <c r="W3" s="13">
         <v>1250</v>
-      </c>
-      <c r="W3" s="13">
-        <v>1389</v>
       </c>
       <c r="X3" s="13">
         <v>1389</v>
       </c>
       <c r="Y3" s="13">
+        <v>1389</v>
+      </c>
+      <c r="Z3" s="13">
         <v>1367</v>
       </c>
-      <c r="Z3" s="13">
+      <c r="AA3" s="13">
         <v>1026</v>
       </c>
-      <c r="AA3" s="13">
+      <c r="AB3" s="13">
         <v>949.1</v>
       </c>
-      <c r="AB3" s="13"/>
       <c r="AC3" s="13"/>
       <c r="AD3" s="13"/>
       <c r="AE3" s="13"/>
@@ -1615,8 +1618,8 @@
       <c r="AO3" s="13"/>
       <c r="AP3" s="13"/>
       <c r="AQ3" s="13"/>
-      <c r="AR3" s="14"/>
-      <c r="AS3" s="13"/>
+      <c r="AR3" s="13"/>
+      <c r="AS3" s="14"/>
       <c r="AT3" s="13"/>
       <c r="AU3" s="13"/>
       <c r="AV3" s="13"/>
@@ -1634,42 +1637,43 @@
       <c r="BH3" s="13"/>
       <c r="BI3" s="13"/>
       <c r="BJ3" s="13"/>
-      <c r="BK3" s="29"/>
-      <c r="BL3" s="13"/>
+      <c r="BK3" s="13"/>
+      <c r="BL3" s="29"/>
       <c r="BM3" s="13"/>
-      <c r="BN3" s="29"/>
-      <c r="BO3" s="13"/>
+      <c r="BN3" s="13"/>
+      <c r="BO3" s="29"/>
       <c r="BP3" s="13"/>
       <c r="BQ3" s="13"/>
       <c r="BR3" s="13"/>
-      <c r="BS3" s="13">
-        <f>(G3*H3)/100-BY3</f>
+      <c r="BS3" s="13"/>
+      <c r="BT3" s="13">
+        <f t="shared" si="0"/>
         <v>-126.73159999999989</v>
       </c>
-      <c r="BT3" s="13">
-        <f>(G3*H3)/100</f>
+      <c r="BU3" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BU3" s="13">
-        <f>(BT3-BS3)</f>
+      <c r="BV3" s="13">
+        <f>(BU3-BT3)</f>
         <v>126.73159999999989</v>
       </c>
-      <c r="BV3" s="13">
-        <f>((BJ3-H3)/H3)*100</f>
+      <c r="BW3" s="13">
+        <f>((BK3-H3)/H3)*100</f>
         <v>-100</v>
       </c>
-      <c r="BW3">
+      <c r="BX3">
         <v>68</v>
       </c>
-      <c r="BX3">
+      <c r="BY3">
         <v>1340</v>
       </c>
-      <c r="BY3" s="15">
-        <f>(BW3*BX3-BW3*H3)/100</f>
+      <c r="BZ3" s="15">
+        <f>(BX3*BY3-BX3*H3)/100</f>
         <v>126.73159999999989</v>
       </c>
     </row>
-    <row r="4" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="4" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>587014</v>
       </c>
@@ -1698,63 +1702,65 @@
         <v>5925</v>
       </c>
       <c r="I4" s="13">
+        <v>6098</v>
+      </c>
+      <c r="J4" s="13">
+        <v>6098</v>
+      </c>
+      <c r="K4" s="13">
         <v>6298</v>
       </c>
-      <c r="J4" s="13">
-        <v>6298</v>
-      </c>
-      <c r="K4" s="13">
+      <c r="L4" s="13">
         <v>6295</v>
       </c>
-      <c r="L4" s="13">
+      <c r="M4" s="13">
         <v>6370</v>
       </c>
-      <c r="M4" s="13">
+      <c r="N4" s="13">
         <v>6140</v>
       </c>
-      <c r="N4" s="13">
+      <c r="O4" s="13">
         <v>7252</v>
       </c>
-      <c r="O4" s="13">
+      <c r="P4" s="13">
         <v>7120</v>
       </c>
-      <c r="P4" s="13">
+      <c r="Q4" s="13">
         <v>7048</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="R4" s="13">
         <v>6979</v>
       </c>
-      <c r="R4" s="13">
+      <c r="S4" s="13">
         <v>6680</v>
       </c>
-      <c r="S4" s="13">
+      <c r="T4" s="13">
         <v>6111</v>
       </c>
-      <c r="T4" s="13">
+      <c r="U4" s="13">
         <v>6050</v>
       </c>
-      <c r="U4" s="13">
+      <c r="V4" s="13">
         <v>6169</v>
       </c>
-      <c r="V4" s="13">
+      <c r="W4" s="13">
         <v>6300</v>
-      </c>
-      <c r="W4" s="13">
-        <v>6335</v>
       </c>
       <c r="X4" s="13">
         <v>6335</v>
       </c>
       <c r="Y4" s="13">
+        <v>6335</v>
+      </c>
+      <c r="Z4" s="13">
         <v>6444</v>
-      </c>
-      <c r="Z4" s="13">
-        <v>5749</v>
       </c>
       <c r="AA4" s="13">
         <v>5749</v>
       </c>
-      <c r="AB4" s="13"/>
+      <c r="AB4" s="13">
+        <v>5749</v>
+      </c>
       <c r="AC4" s="13"/>
       <c r="AD4" s="13"/>
       <c r="AE4" s="13"/>
@@ -1789,36 +1795,37 @@
       <c r="BH4" s="13"/>
       <c r="BI4" s="13"/>
       <c r="BJ4" s="13"/>
-      <c r="BK4" s="29"/>
-      <c r="BL4" s="13"/>
+      <c r="BK4" s="13"/>
+      <c r="BL4" s="29"/>
       <c r="BM4" s="13"/>
-      <c r="BN4" s="29"/>
-      <c r="BO4" s="13"/>
+      <c r="BN4" s="13"/>
+      <c r="BO4" s="29"/>
       <c r="BP4" s="13"/>
       <c r="BQ4" s="13"/>
       <c r="BR4" s="13"/>
-      <c r="BS4" s="13">
-        <f>(G4*H4)/100-BY4</f>
+      <c r="BS4" s="13"/>
+      <c r="BT4" s="13">
+        <f t="shared" si="0"/>
         <v>1185</v>
       </c>
-      <c r="BT4" s="13">
-        <f>(G4*H4)/100</f>
+      <c r="BU4" s="13">
+        <f t="shared" si="1"/>
         <v>1185</v>
       </c>
-      <c r="BU4" s="13">
-        <f>(BT4-BS4)</f>
+      <c r="BV4" s="13">
+        <f>(BU4-BT4)</f>
         <v>0</v>
       </c>
-      <c r="BV4" s="13">
-        <f>((BJ4-H4)/H4)*100</f>
+      <c r="BW4" s="13">
+        <f>((BK4-H4)/H4)*100</f>
         <v>-100</v>
       </c>
-      <c r="BY4" s="15">
-        <f>(BW4*BX4-BW4*H4)/100</f>
+      <c r="BZ4" s="15">
+        <f>(BX4*BY4-BX4*H4)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="5" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1099787</v>
       </c>
@@ -1847,93 +1854,95 @@
         <v>617.53</v>
       </c>
       <c r="I5" s="13">
+        <v>607.9</v>
+      </c>
+      <c r="J5" s="13">
+        <v>607.9</v>
+      </c>
+      <c r="K5" s="13">
         <v>638</v>
       </c>
-      <c r="J5" s="13">
-        <v>638</v>
-      </c>
-      <c r="K5" s="13">
+      <c r="L5" s="13">
         <v>587.5</v>
       </c>
-      <c r="L5" s="13">
+      <c r="M5" s="13">
         <v>577.9</v>
       </c>
-      <c r="M5" s="13">
+      <c r="N5" s="13">
         <v>559</v>
       </c>
-      <c r="N5" s="13">
+      <c r="O5" s="13">
         <v>570</v>
       </c>
-      <c r="O5" s="13">
+      <c r="P5" s="13">
         <v>575.70000000000005</v>
       </c>
-      <c r="P5" s="13">
+      <c r="Q5" s="13">
         <v>612.6</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="R5" s="13">
         <v>638.29999999999995</v>
       </c>
-      <c r="R5" s="13">
+      <c r="S5" s="13">
         <v>630.29999999999995</v>
       </c>
-      <c r="S5" s="13">
+      <c r="T5" s="13">
         <v>626</v>
       </c>
-      <c r="T5" s="13">
+      <c r="U5" s="13">
         <v>595.4</v>
       </c>
-      <c r="U5" s="13">
+      <c r="V5" s="13">
         <v>667.1</v>
       </c>
-      <c r="V5" s="13">
+      <c r="W5" s="13">
         <v>651</v>
-      </c>
-      <c r="W5" s="13">
-        <v>641.1</v>
       </c>
       <c r="X5" s="13">
         <v>641.1</v>
       </c>
       <c r="Y5" s="13">
+        <v>641.1</v>
+      </c>
+      <c r="Z5" s="13">
         <v>607.1</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="AA5" s="13">
         <v>583</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AB5" s="13">
         <v>581.6</v>
       </c>
-      <c r="AB5" s="13">
+      <c r="AC5" s="13">
         <v>578.70000000000005</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AD5" s="13">
         <v>590</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AE5" s="13">
         <v>554.70000000000005</v>
       </c>
-      <c r="AE5" s="13">
+      <c r="AF5" s="13">
         <v>511.8</v>
       </c>
-      <c r="AF5" s="13">
+      <c r="AG5" s="13">
         <v>487</v>
       </c>
-      <c r="AG5" s="13">
+      <c r="AH5" s="13">
         <v>478.8</v>
       </c>
-      <c r="AH5" s="13">
+      <c r="AI5" s="13">
         <v>485.5</v>
       </c>
-      <c r="AI5" s="13">
+      <c r="AJ5" s="13">
         <v>453.4</v>
       </c>
-      <c r="AJ5" s="13">
+      <c r="AK5" s="13">
         <v>426.1</v>
       </c>
-      <c r="AK5" s="13">
+      <c r="AL5" s="13">
         <v>423.2</v>
       </c>
-      <c r="AL5" s="13"/>
       <c r="AM5" s="13"/>
       <c r="AN5" s="13"/>
       <c r="AO5" s="13"/>
@@ -1958,27 +1967,28 @@
       <c r="BH5" s="13"/>
       <c r="BI5" s="13"/>
       <c r="BJ5" s="13"/>
-      <c r="BK5" s="29"/>
-      <c r="BL5" s="13"/>
+      <c r="BK5" s="13"/>
+      <c r="BL5" s="29"/>
       <c r="BM5" s="13"/>
-      <c r="BN5" s="29"/>
-      <c r="BO5" s="13"/>
+      <c r="BN5" s="13"/>
+      <c r="BO5" s="29"/>
       <c r="BP5" s="13"/>
       <c r="BQ5" s="13"/>
       <c r="BR5" s="13"/>
-      <c r="BS5" s="13">
-        <f>(G5*H5)/100-BY5</f>
+      <c r="BS5" s="13"/>
+      <c r="BT5" s="13">
+        <f t="shared" si="0"/>
         <v>975.6973999999999</v>
       </c>
-      <c r="BT5" s="13">
-        <f>(G5*H5)/100</f>
+      <c r="BU5" s="13">
+        <f t="shared" si="1"/>
         <v>975.6973999999999</v>
       </c>
-      <c r="BU5" s="13"/>
       <c r="BV5" s="13"/>
-      <c r="BY5" s="15"/>
-    </row>
-    <row r="6" spans="1:77" ht="45" customHeight="1" thickBot="1">
+      <c r="BW5" s="13"/>
+      <c r="BZ5" s="15"/>
+    </row>
+    <row r="6" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1166768</v>
       </c>
@@ -2007,66 +2017,68 @@
         <v>4040</v>
       </c>
       <c r="I6" s="13">
+        <v>4950</v>
+      </c>
+      <c r="J6" s="13">
+        <v>4950</v>
+      </c>
+      <c r="K6" s="13">
         <v>4799</v>
       </c>
-      <c r="J6" s="13">
-        <v>4799</v>
-      </c>
-      <c r="K6" s="13">
+      <c r="L6" s="13">
         <v>4740</v>
       </c>
-      <c r="L6" s="13">
+      <c r="M6" s="13">
         <v>4350</v>
       </c>
-      <c r="M6" s="13">
+      <c r="N6" s="13">
         <v>4355</v>
       </c>
-      <c r="N6" s="13">
+      <c r="O6" s="13">
         <v>4500</v>
       </c>
-      <c r="O6" s="13">
+      <c r="P6" s="13">
         <v>4424</v>
       </c>
-      <c r="P6" s="13">
+      <c r="Q6" s="13">
         <v>4412</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="R6" s="13">
         <v>4450</v>
       </c>
-      <c r="R6" s="13">
+      <c r="S6" s="13">
         <v>4238</v>
       </c>
-      <c r="S6" s="13">
+      <c r="T6" s="13">
         <v>3970</v>
       </c>
-      <c r="T6" s="13">
+      <c r="U6" s="13">
         <v>3870</v>
       </c>
-      <c r="U6" s="13">
+      <c r="V6" s="13">
         <v>3805</v>
       </c>
-      <c r="V6" s="13">
+      <c r="W6" s="13">
         <v>3667</v>
-      </c>
-      <c r="W6" s="13">
-        <v>3582</v>
       </c>
       <c r="X6" s="13">
         <v>3582</v>
       </c>
       <c r="Y6" s="13">
+        <v>3582</v>
+      </c>
+      <c r="Z6" s="13">
         <v>3570</v>
       </c>
-      <c r="Z6" s="13">
+      <c r="AA6" s="13">
         <v>3619</v>
       </c>
-      <c r="AA6" s="13">
+      <c r="AB6" s="13">
         <v>3650</v>
       </c>
-      <c r="AB6" s="13">
+      <c r="AC6" s="13">
         <v>3720</v>
       </c>
-      <c r="AC6" s="13"/>
       <c r="AD6" s="13"/>
       <c r="AE6" s="13"/>
       <c r="AF6" s="13"/>
@@ -2100,41 +2112,42 @@
       <c r="BH6" s="13"/>
       <c r="BI6" s="13"/>
       <c r="BJ6" s="13"/>
-      <c r="BK6" s="29"/>
-      <c r="BL6" s="13"/>
+      <c r="BK6" s="13"/>
+      <c r="BL6" s="29"/>
       <c r="BM6" s="13"/>
-      <c r="BN6" s="29"/>
-      <c r="BO6" s="13"/>
+      <c r="BN6" s="13"/>
+      <c r="BO6" s="29"/>
       <c r="BP6" s="13"/>
       <c r="BQ6" s="13"/>
-      <c r="BS6" s="13">
-        <f>(G6*H6)/100-BY6</f>
+      <c r="BR6" s="13"/>
+      <c r="BT6" s="13">
+        <f t="shared" si="0"/>
         <v>1033.7</v>
       </c>
-      <c r="BT6" s="13">
-        <f>(G6*H6)/100</f>
+      <c r="BU6" s="13">
+        <f t="shared" si="1"/>
         <v>1010</v>
       </c>
-      <c r="BU6" s="13">
-        <f t="shared" ref="BU6" si="0">(BT6-BS6)</f>
+      <c r="BV6" s="13">
+        <f t="shared" ref="BV6" si="2">(BU6-BT6)</f>
         <v>-23.700000000000045</v>
       </c>
-      <c r="BV6" s="13">
-        <f>((BJ6-H6)/H6)*100</f>
+      <c r="BW6" s="13">
+        <f>((BK6-H6)/H6)*100</f>
         <v>-100</v>
       </c>
-      <c r="BW6">
+      <c r="BX6">
         <v>5</v>
       </c>
-      <c r="BX6">
+      <c r="BY6">
         <v>3566</v>
       </c>
-      <c r="BY6" s="15">
-        <f>(BW6*BX6-BW6*H6)/100</f>
+      <c r="BZ6" s="15">
+        <f>(BX6*BY6-BX6*H6)/100</f>
         <v>-23.7</v>
       </c>
     </row>
-    <row r="7" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="7" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1148899</v>
       </c>
@@ -2163,93 +2176,95 @@
         <v>3585</v>
       </c>
       <c r="I7" s="13">
+        <v>3959</v>
+      </c>
+      <c r="J7" s="13">
+        <v>3959</v>
+      </c>
+      <c r="K7" s="13">
         <v>4022</v>
       </c>
-      <c r="J7" s="13">
-        <v>4022</v>
-      </c>
-      <c r="K7" s="13">
+      <c r="L7" s="13">
         <v>4033</v>
       </c>
-      <c r="L7" s="13">
+      <c r="M7" s="13">
         <v>3988</v>
       </c>
-      <c r="M7" s="13">
+      <c r="N7" s="13">
         <v>3916</v>
       </c>
-      <c r="N7" s="13">
+      <c r="O7" s="13">
         <v>3954</v>
       </c>
-      <c r="O7" s="13">
+      <c r="P7" s="13">
         <v>3932</v>
       </c>
-      <c r="P7" s="13">
+      <c r="Q7" s="13">
         <v>3949</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="R7" s="13">
         <v>3943</v>
       </c>
-      <c r="R7" s="13">
+      <c r="S7" s="13">
         <v>3928</v>
       </c>
-      <c r="S7" s="13">
+      <c r="T7" s="13">
         <v>3913</v>
       </c>
-      <c r="T7" s="13">
+      <c r="U7" s="13">
         <v>3860</v>
       </c>
-      <c r="U7" s="13">
+      <c r="V7" s="13">
         <v>3893</v>
       </c>
-      <c r="V7" s="13">
+      <c r="W7" s="13">
         <v>3900</v>
-      </c>
-      <c r="W7" s="13">
-        <v>3842</v>
       </c>
       <c r="X7" s="13">
         <v>3842</v>
       </c>
       <c r="Y7" s="13">
+        <v>3842</v>
+      </c>
+      <c r="Z7" s="13">
         <v>3841</v>
       </c>
-      <c r="Z7" s="13">
+      <c r="AA7" s="13">
         <v>3809</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="AB7" s="13">
         <v>3810</v>
       </c>
-      <c r="AB7" s="13">
+      <c r="AC7" s="13">
         <v>3798</v>
       </c>
-      <c r="AC7" s="13">
+      <c r="AD7" s="13">
         <v>3713</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AE7" s="13">
         <v>3657</v>
       </c>
-      <c r="AE7" s="13">
+      <c r="AF7" s="13">
         <v>3592</v>
       </c>
-      <c r="AF7" s="13">
+      <c r="AG7" s="13">
         <v>3621</v>
       </c>
-      <c r="AG7" s="13">
+      <c r="AH7" s="13">
         <v>3572</v>
       </c>
-      <c r="AH7" s="13">
+      <c r="AI7" s="13">
         <v>3580</v>
       </c>
-      <c r="AI7" s="13">
+      <c r="AJ7" s="13">
         <v>3569</v>
       </c>
-      <c r="AJ7" s="13">
+      <c r="AK7" s="13">
         <v>3659</v>
       </c>
-      <c r="AK7" s="13">
+      <c r="AL7" s="13">
         <v>3656</v>
       </c>
-      <c r="AL7" s="13"/>
       <c r="AM7" s="13"/>
       <c r="AN7" s="13"/>
       <c r="AO7" s="13"/>
@@ -2274,27 +2289,28 @@
       <c r="BH7" s="13"/>
       <c r="BI7" s="13"/>
       <c r="BJ7" s="13"/>
-      <c r="BK7" s="29"/>
-      <c r="BL7" s="13"/>
+      <c r="BK7" s="13"/>
+      <c r="BL7" s="29"/>
       <c r="BM7" s="13"/>
-      <c r="BN7" s="29"/>
-      <c r="BO7" s="13"/>
+      <c r="BN7" s="13"/>
+      <c r="BO7" s="29"/>
       <c r="BP7" s="13"/>
       <c r="BQ7" s="13"/>
       <c r="BR7" s="13"/>
-      <c r="BS7" s="13">
-        <f>(G7*H7)/100-BY7</f>
+      <c r="BS7" s="13"/>
+      <c r="BT7" s="13">
+        <f t="shared" si="0"/>
         <v>2509.5</v>
       </c>
-      <c r="BT7" s="13">
-        <f>(G7*H7)/100</f>
+      <c r="BU7" s="13">
+        <f t="shared" si="1"/>
         <v>2509.5</v>
       </c>
-      <c r="BU7" s="13"/>
       <c r="BV7" s="13"/>
-      <c r="BY7" s="15"/>
-    </row>
-    <row r="8" spans="1:77" ht="45" customHeight="1" thickBot="1">
+      <c r="BW7" s="13"/>
+      <c r="BZ7" s="15"/>
+    </row>
+    <row r="8" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1082379</v>
       </c>
@@ -2323,129 +2339,131 @@
         <v>37875</v>
       </c>
       <c r="I8" s="13">
+        <v>38000</v>
+      </c>
+      <c r="J8" s="13">
+        <v>38000</v>
+      </c>
+      <c r="K8" s="13">
         <v>39600</v>
       </c>
-      <c r="J8" s="13">
-        <v>39600</v>
-      </c>
-      <c r="K8" s="13">
+      <c r="L8" s="13">
         <v>43640</v>
       </c>
-      <c r="L8" s="13">
+      <c r="M8" s="13">
         <v>42700</v>
       </c>
-      <c r="M8" s="13">
+      <c r="N8" s="13">
         <v>42140</v>
       </c>
-      <c r="N8" s="13">
+      <c r="O8" s="13">
         <v>43490</v>
       </c>
-      <c r="O8" s="13">
+      <c r="P8" s="13">
         <v>40750</v>
       </c>
-      <c r="P8" s="13">
+      <c r="Q8" s="13">
         <v>40900</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="R8" s="13">
         <v>40790</v>
       </c>
-      <c r="R8" s="13">
+      <c r="S8" s="13">
         <v>40820</v>
       </c>
-      <c r="S8" s="13">
+      <c r="T8" s="13">
         <v>41570</v>
       </c>
-      <c r="T8" s="13">
+      <c r="U8" s="13">
         <v>42050</v>
       </c>
-      <c r="U8" s="13">
+      <c r="V8" s="13">
         <v>39960</v>
       </c>
-      <c r="V8" s="13">
+      <c r="W8" s="13">
         <v>39990</v>
-      </c>
-      <c r="W8" s="13">
-        <v>38680</v>
       </c>
       <c r="X8" s="13">
         <v>38680</v>
       </c>
       <c r="Y8" s="13">
+        <v>38680</v>
+      </c>
+      <c r="Z8" s="13">
         <v>37770</v>
       </c>
-      <c r="Z8" s="13">
+      <c r="AA8" s="13">
         <v>36330</v>
       </c>
-      <c r="AA8" s="13">
+      <c r="AB8" s="13">
         <v>38680</v>
       </c>
-      <c r="AB8" s="13">
+      <c r="AC8" s="13">
         <v>39090</v>
       </c>
-      <c r="AC8" s="13">
+      <c r="AD8" s="13">
         <v>37300</v>
       </c>
-      <c r="AD8" s="13">
+      <c r="AE8" s="13">
         <v>37650</v>
       </c>
-      <c r="AE8" s="13">
+      <c r="AF8" s="13">
         <v>37300</v>
       </c>
-      <c r="AF8" s="13">
+      <c r="AG8" s="13">
         <v>39450</v>
       </c>
-      <c r="AG8" s="13">
+      <c r="AH8" s="13">
         <v>38390</v>
       </c>
-      <c r="AH8" s="13">
+      <c r="AI8" s="13">
         <v>38800</v>
       </c>
-      <c r="AI8" s="13">
+      <c r="AJ8" s="13">
         <v>38510</v>
-      </c>
-      <c r="AJ8" s="13">
-        <v>38970</v>
       </c>
       <c r="AK8" s="13">
         <v>38970</v>
       </c>
       <c r="AL8" s="13">
-        <v>37700</v>
+        <v>38970</v>
       </c>
       <c r="AM8" s="13">
         <v>37700</v>
       </c>
       <c r="AN8" s="13">
+        <v>37700</v>
+      </c>
+      <c r="AO8" s="13">
         <v>37750</v>
       </c>
-      <c r="AO8" s="13">
+      <c r="AP8" s="13">
         <v>38430</v>
       </c>
-      <c r="AP8" s="13">
+      <c r="AQ8" s="13">
         <v>38250</v>
       </c>
-      <c r="AQ8" s="13">
+      <c r="AR8" s="13">
         <v>40110</v>
       </c>
-      <c r="AR8" s="13">
+      <c r="AS8" s="13">
         <v>40820</v>
       </c>
-      <c r="AS8" s="13">
+      <c r="AT8" s="13">
         <v>39320</v>
       </c>
-      <c r="AT8" s="13">
+      <c r="AU8" s="13">
         <v>37800</v>
       </c>
-      <c r="AU8" s="13">
+      <c r="AV8" s="13">
         <v>36620</v>
       </c>
-      <c r="AV8" s="13">
+      <c r="AW8" s="13">
         <v>37130</v>
       </c>
-      <c r="AW8" s="13">
+      <c r="AX8" s="13">
         <v>35850</v>
       </c>
-      <c r="AX8" s="13"/>
       <c r="AY8" s="13"/>
       <c r="AZ8" s="13"/>
       <c r="BA8" s="13"/>
@@ -2458,39 +2476,40 @@
       <c r="BH8" s="13"/>
       <c r="BI8" s="13"/>
       <c r="BJ8" s="13"/>
-      <c r="BK8" s="29"/>
-      <c r="BL8" s="13"/>
+      <c r="BK8" s="13"/>
+      <c r="BL8" s="29"/>
       <c r="BM8" s="13"/>
-      <c r="BN8" s="29"/>
-      <c r="BO8" s="13"/>
+      <c r="BN8" s="13"/>
+      <c r="BO8" s="29"/>
       <c r="BP8" s="13"/>
       <c r="BQ8" s="13"/>
       <c r="BR8" s="13"/>
-      <c r="BS8" s="13">
-        <f>(G8*H8)/100-BY8</f>
+      <c r="BS8" s="13"/>
+      <c r="BT8" s="13">
+        <f t="shared" si="0"/>
         <v>806.25</v>
       </c>
-      <c r="BT8" s="13">
-        <f>(G8*H8)/100</f>
+      <c r="BU8" s="13">
+        <f t="shared" si="1"/>
         <v>757.5</v>
       </c>
-      <c r="BU8" s="13">
-        <f t="shared" ref="BU8:BU11" si="1">(BT8-BS8)</f>
+      <c r="BV8" s="13">
+        <f t="shared" ref="BV8:BV11" si="3">(BU8-BT8)</f>
         <v>-48.75</v>
       </c>
-      <c r="BV8" s="13"/>
-      <c r="BW8">
+      <c r="BW8" s="13"/>
+      <c r="BX8">
         <v>3</v>
       </c>
-      <c r="BX8">
+      <c r="BY8">
         <v>36250</v>
       </c>
-      <c r="BY8" s="15">
-        <f>(BW8*BX8-BW8*H8)/100</f>
+      <c r="BZ8" s="15">
+        <f t="shared" ref="BZ8:BZ18" si="4">(BX8*BY8-BX8*H8)/100</f>
         <v>-48.75</v>
       </c>
     </row>
-    <row r="9" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="9" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>629014</v>
       </c>
@@ -2504,7 +2523,7 @@
       </c>
       <c r="D9" s="6" t="str">
         <f>IF(I9&lt;GEMINI!L9,"למכור בהפסד",IF(I9&gt;GEMINI!M9,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>56</v>
@@ -2519,123 +2538,125 @@
         <v>9227</v>
       </c>
       <c r="I9" s="13">
+        <v>10800</v>
+      </c>
+      <c r="J9" s="13">
+        <v>10800</v>
+      </c>
+      <c r="K9" s="13">
         <v>11290</v>
       </c>
-      <c r="J9" s="13">
-        <v>11290</v>
-      </c>
-      <c r="K9" s="13">
+      <c r="L9" s="13">
         <v>11020</v>
-      </c>
-      <c r="L9" s="13">
-        <v>10100</v>
       </c>
       <c r="M9" s="13">
         <v>10100</v>
       </c>
       <c r="N9" s="13">
+        <v>10100</v>
+      </c>
+      <c r="O9" s="13">
         <v>10240</v>
       </c>
-      <c r="O9" s="13">
+      <c r="P9" s="13">
         <v>9891</v>
       </c>
-      <c r="P9" s="13">
+      <c r="Q9" s="13">
         <v>9956</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="R9" s="13">
         <v>9910</v>
       </c>
-      <c r="R9" s="13">
+      <c r="S9" s="13">
         <v>9960</v>
       </c>
-      <c r="S9" s="13">
+      <c r="T9" s="13">
         <v>9924</v>
       </c>
-      <c r="T9" s="13">
+      <c r="U9" s="13">
         <v>9999</v>
       </c>
-      <c r="U9" s="13">
+      <c r="V9" s="13">
         <v>9962</v>
       </c>
-      <c r="V9" s="13">
+      <c r="W9" s="13">
         <v>9979</v>
-      </c>
-      <c r="W9" s="13">
-        <v>10130</v>
       </c>
       <c r="X9" s="13">
         <v>10130</v>
       </c>
       <c r="Y9" s="13">
+        <v>10130</v>
+      </c>
+      <c r="Z9" s="13">
         <v>10400</v>
       </c>
-      <c r="Z9" s="13">
+      <c r="AA9" s="13">
         <v>10320</v>
       </c>
-      <c r="AA9" s="13">
+      <c r="AB9" s="13">
         <v>10300</v>
       </c>
-      <c r="AB9" s="13">
+      <c r="AC9" s="13">
         <v>10310</v>
       </c>
-      <c r="AC9" s="13">
+      <c r="AD9" s="13">
         <v>9672</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AE9" s="13">
         <v>9953</v>
       </c>
-      <c r="AE9" s="13">
+      <c r="AF9" s="13">
         <v>10090</v>
       </c>
-      <c r="AF9" s="13">
+      <c r="AG9" s="13">
         <v>10070</v>
       </c>
-      <c r="AG9" s="13">
+      <c r="AH9" s="13">
         <v>10030</v>
       </c>
-      <c r="AH9" s="13">
+      <c r="AI9" s="13">
         <v>10120</v>
       </c>
-      <c r="AI9" s="13">
+      <c r="AJ9" s="13">
         <v>10000</v>
       </c>
-      <c r="AJ9" s="13">
+      <c r="AK9" s="13">
         <v>10080</v>
       </c>
-      <c r="AK9" s="13">
+      <c r="AL9" s="13">
         <v>10030</v>
-      </c>
-      <c r="AL9" s="13">
-        <v>9726</v>
       </c>
       <c r="AM9" s="13">
         <v>9726</v>
       </c>
       <c r="AN9" s="13">
+        <v>9726</v>
+      </c>
+      <c r="AO9" s="13">
         <v>9659</v>
       </c>
-      <c r="AO9" s="13">
+      <c r="AP9" s="13">
         <v>9670</v>
       </c>
-      <c r="AP9" s="13">
+      <c r="AQ9" s="13">
         <v>9590</v>
       </c>
-      <c r="AQ9" s="13">
+      <c r="AR9" s="13">
         <v>9588</v>
       </c>
-      <c r="AR9" s="13">
+      <c r="AS9" s="13">
         <v>9400</v>
       </c>
-      <c r="AS9" s="13">
+      <c r="AT9" s="13">
         <v>9320</v>
       </c>
-      <c r="AT9" s="13">
+      <c r="AU9" s="13">
         <v>9071</v>
       </c>
-      <c r="AU9" s="13">
+      <c r="AV9" s="13">
         <v>9271</v>
       </c>
-      <c r="AV9" s="13"/>
       <c r="AW9" s="13"/>
       <c r="AX9" s="13"/>
       <c r="AY9" s="13"/>
@@ -2650,39 +2671,40 @@
       <c r="BH9" s="13"/>
       <c r="BI9" s="13"/>
       <c r="BJ9" s="13"/>
-      <c r="BK9" s="29"/>
-      <c r="BL9" s="13"/>
+      <c r="BK9" s="13"/>
+      <c r="BL9" s="29"/>
       <c r="BM9" s="13"/>
-      <c r="BN9" s="29"/>
-      <c r="BO9" s="13"/>
+      <c r="BN9" s="13"/>
+      <c r="BO9" s="29"/>
       <c r="BP9" s="13"/>
       <c r="BQ9" s="13"/>
       <c r="BR9" s="13"/>
-      <c r="BS9" s="13">
-        <f>(G9*H9)/100-BY9</f>
+      <c r="BS9" s="13"/>
+      <c r="BT9" s="13">
+        <f t="shared" si="0"/>
         <v>-38.65</v>
-      </c>
-      <c r="BT9" s="13">
-        <f>(G9*H9)/100</f>
-        <v>0</v>
       </c>
       <c r="BU9" s="13">
         <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BV9" s="13">
+        <f t="shared" si="3"/>
         <v>38.65</v>
       </c>
-      <c r="BV9" s="13"/>
-      <c r="BW9">
+      <c r="BW9" s="13"/>
+      <c r="BX9">
         <v>5</v>
       </c>
-      <c r="BX9">
+      <c r="BY9">
         <v>10000</v>
       </c>
-      <c r="BY9" s="15">
-        <f>(BW9*BX9-BW9*H9)/100</f>
+      <c r="BZ9" s="15">
+        <f t="shared" si="4"/>
         <v>38.65</v>
       </c>
     </row>
-    <row r="10" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="10" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1141464</v>
       </c>
@@ -2711,205 +2733,208 @@
         <v>4834</v>
       </c>
       <c r="I10" s="13">
+        <v>5800</v>
+      </c>
+      <c r="J10" s="13">
+        <v>5800</v>
+      </c>
+      <c r="K10" s="13">
         <v>5126</v>
       </c>
-      <c r="J10" s="13">
-        <v>5126</v>
-      </c>
-      <c r="K10" s="13">
+      <c r="L10" s="13">
         <v>5164</v>
-      </c>
-      <c r="L10" s="13">
-        <v>4809</v>
       </c>
       <c r="M10" s="13">
         <v>4809</v>
       </c>
       <c r="N10" s="13">
+        <v>4809</v>
+      </c>
+      <c r="O10" s="13">
         <v>4849</v>
       </c>
-      <c r="O10" s="13">
+      <c r="P10" s="13">
         <v>4821</v>
       </c>
-      <c r="P10" s="13">
+      <c r="Q10" s="13">
         <v>4925</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="R10" s="13">
         <v>5013</v>
-      </c>
-      <c r="R10" s="13">
-        <v>5050</v>
       </c>
       <c r="S10" s="13">
         <v>5050</v>
       </c>
       <c r="T10" s="13">
+        <v>5050</v>
+      </c>
+      <c r="U10" s="13">
         <v>4930</v>
       </c>
-      <c r="U10" s="13">
+      <c r="V10" s="13">
         <v>5150</v>
       </c>
-      <c r="V10" s="13">
+      <c r="W10" s="13">
         <v>5283</v>
-      </c>
-      <c r="W10" s="13">
-        <v>5253</v>
       </c>
       <c r="X10" s="13">
         <v>5253</v>
       </c>
       <c r="Y10" s="13">
+        <v>5253</v>
+      </c>
+      <c r="Z10" s="13">
         <v>5400</v>
       </c>
-      <c r="Z10" s="13">
+      <c r="AA10" s="13">
         <v>5522</v>
       </c>
-      <c r="AA10" s="13">
+      <c r="AB10" s="13">
         <v>5690</v>
       </c>
-      <c r="AB10" s="13">
+      <c r="AC10" s="13">
         <v>5749</v>
       </c>
-      <c r="AC10" s="13">
+      <c r="AD10" s="13">
         <v>5840</v>
-      </c>
-      <c r="AD10" s="13">
-        <v>5650</v>
       </c>
       <c r="AE10" s="13">
         <v>5650</v>
       </c>
       <c r="AF10" s="13">
+        <v>5650</v>
+      </c>
+      <c r="AG10" s="13">
         <v>5841</v>
       </c>
-      <c r="AG10" s="13">
+      <c r="AH10" s="13">
         <v>5758</v>
       </c>
-      <c r="AH10" s="13">
+      <c r="AI10" s="13">
         <v>5673</v>
       </c>
-      <c r="AI10" s="13">
+      <c r="AJ10" s="13">
         <v>5609</v>
       </c>
-      <c r="AJ10" s="13">
+      <c r="AK10" s="13">
         <v>5750</v>
       </c>
-      <c r="AK10" s="13">
+      <c r="AL10" s="13">
         <v>5841</v>
-      </c>
-      <c r="AL10" s="13">
-        <v>5564</v>
       </c>
       <c r="AM10" s="13">
         <v>5564</v>
       </c>
       <c r="AN10" s="13">
+        <v>5564</v>
+      </c>
+      <c r="AO10" s="13">
         <v>5557</v>
       </c>
-      <c r="AO10" s="13">
+      <c r="AP10" s="13">
         <v>5501</v>
       </c>
-      <c r="AP10" s="13">
+      <c r="AQ10" s="13">
         <v>5250</v>
       </c>
-      <c r="AQ10" s="13">
+      <c r="AR10" s="13">
         <v>5270</v>
       </c>
-      <c r="AR10" s="13">
+      <c r="AS10" s="13">
         <v>5149</v>
       </c>
-      <c r="AS10" s="13">
+      <c r="AT10" s="13">
         <v>5092</v>
       </c>
-      <c r="AT10" s="13">
+      <c r="AU10" s="13">
         <v>5228</v>
       </c>
-      <c r="AU10" s="13">
+      <c r="AV10" s="13">
         <v>5301</v>
       </c>
-      <c r="AV10" s="13">
+      <c r="AW10" s="13">
         <v>5159</v>
       </c>
-      <c r="AW10" s="13">
+      <c r="AX10" s="13">
         <v>5198</v>
       </c>
-      <c r="AX10" s="13">
+      <c r="AY10" s="13">
         <v>5077</v>
       </c>
-      <c r="AY10" s="13">
+      <c r="AZ10" s="13">
         <v>4842</v>
       </c>
-      <c r="AZ10" s="13">
+      <c r="BA10" s="13">
         <v>5050</v>
       </c>
-      <c r="BA10" s="13">
+      <c r="BB10" s="13">
         <v>4970</v>
       </c>
-      <c r="BB10" s="13">
+      <c r="BC10" s="13">
         <v>4880</v>
       </c>
-      <c r="BC10" s="13">
+      <c r="BD10" s="13">
         <v>4704</v>
       </c>
-      <c r="BD10" s="13">
+      <c r="BE10" s="13">
         <v>4770</v>
       </c>
-      <c r="BE10" s="13">
+      <c r="BF10" s="13">
         <v>4609</v>
       </c>
-      <c r="BF10" s="13">
+      <c r="BG10" s="13">
         <v>4674</v>
       </c>
-      <c r="BG10" s="13">
+      <c r="BH10" s="13">
         <v>4710</v>
       </c>
-      <c r="BH10" s="13">
+      <c r="BI10" s="13">
         <v>4688</v>
       </c>
-      <c r="BI10" s="13">
+      <c r="BJ10" s="13">
         <v>4900</v>
       </c>
-      <c r="BJ10" s="13">
+      <c r="BK10" s="13">
         <v>5000</v>
       </c>
-      <c r="BK10" s="29">
+      <c r="BL10" s="29">
         <v>4932</v>
       </c>
-      <c r="BL10" s="13"/>
       <c r="BM10" s="13"/>
-      <c r="BN10" s="29"/>
-      <c r="BO10" s="13"/>
+      <c r="BN10" s="13"/>
+      <c r="BO10" s="29"/>
       <c r="BP10" s="13"/>
       <c r="BQ10" s="13"/>
       <c r="BR10" s="13"/>
-      <c r="BS10" s="13">
-        <f>(G10*H10)/100-BY10</f>
+      <c r="BS10" s="13"/>
+      <c r="BT10" s="13">
+        <f t="shared" si="0"/>
         <v>-87.859799999999964</v>
-      </c>
-      <c r="BT10" s="13">
-        <f>(G10*H10)/100</f>
-        <v>0</v>
       </c>
       <c r="BU10" s="13">
         <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BV10" s="13">
+        <f t="shared" si="3"/>
         <v>87.859799999999964</v>
       </c>
-      <c r="BV10" s="13">
-        <f>((BJ10-H10)/H10)*100</f>
+      <c r="BW10" s="13">
+        <f>((BK10-H10)/H10)*100</f>
         <v>3.434009102192801</v>
       </c>
-      <c r="BW10">
+      <c r="BX10">
         <v>21</v>
       </c>
-      <c r="BX10">
+      <c r="BY10">
         <v>5252.38</v>
       </c>
-      <c r="BY10" s="15">
-        <f>(BW10*BX10-BW10*H10)/100</f>
+      <c r="BZ10" s="15">
+        <f t="shared" si="4"/>
         <v>87.859799999999964</v>
       </c>
     </row>
-    <row r="11" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="11" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1166974</v>
       </c>
@@ -2944,81 +2969,83 @@
         <v>1099</v>
       </c>
       <c r="K11" s="13">
+        <v>1099</v>
+      </c>
+      <c r="L11" s="13">
         <v>1173</v>
       </c>
-      <c r="L11" s="13">
+      <c r="M11" s="13">
         <v>1114</v>
       </c>
-      <c r="M11" s="13">
+      <c r="N11" s="13">
         <v>1075</v>
       </c>
-      <c r="N11" s="13">
+      <c r="O11" s="13">
         <v>1109</v>
       </c>
-      <c r="O11" s="13">
+      <c r="P11" s="13">
         <v>1090</v>
       </c>
-      <c r="P11" s="13">
+      <c r="Q11" s="13">
         <v>1144</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="R11" s="13">
         <v>1162</v>
       </c>
-      <c r="R11" s="13">
+      <c r="S11" s="13">
         <v>1109</v>
       </c>
-      <c r="S11" s="13">
+      <c r="T11" s="13">
         <v>1029</v>
       </c>
-      <c r="T11" s="13">
+      <c r="U11" s="13">
         <v>993</v>
       </c>
-      <c r="U11" s="13">
+      <c r="V11" s="13">
         <v>1017</v>
       </c>
-      <c r="V11" s="13">
+      <c r="W11" s="13">
         <v>960</v>
-      </c>
-      <c r="W11" s="13">
-        <v>965</v>
       </c>
       <c r="X11" s="13">
         <v>965</v>
       </c>
       <c r="Y11" s="13">
+        <v>965</v>
+      </c>
+      <c r="Z11" s="13">
         <v>951.7</v>
       </c>
-      <c r="Z11" s="13">
+      <c r="AA11" s="13">
         <v>946</v>
       </c>
-      <c r="AA11" s="13">
+      <c r="AB11" s="13">
         <v>869.2</v>
       </c>
-      <c r="AB11" s="13">
+      <c r="AC11" s="13">
         <v>865</v>
       </c>
-      <c r="AC11" s="13">
+      <c r="AD11" s="13">
         <v>851</v>
       </c>
-      <c r="AD11" s="13">
+      <c r="AE11" s="13">
         <v>829.3</v>
       </c>
-      <c r="AE11" s="13">
+      <c r="AF11" s="13">
         <v>830</v>
       </c>
-      <c r="AF11" s="13">
+      <c r="AG11" s="13">
         <v>810</v>
       </c>
-      <c r="AG11" s="13">
+      <c r="AH11" s="13">
         <v>812.8</v>
       </c>
-      <c r="AH11" s="13">
+      <c r="AI11" s="13">
         <v>788</v>
       </c>
-      <c r="AI11" s="13">
+      <c r="AJ11" s="13">
         <v>772</v>
       </c>
-      <c r="AJ11" s="13"/>
       <c r="AK11" s="13"/>
       <c r="AL11" s="13"/>
       <c r="AM11" s="13"/>
@@ -3045,33 +3072,34 @@
       <c r="BH11" s="13"/>
       <c r="BI11" s="13"/>
       <c r="BJ11" s="13"/>
-      <c r="BK11" s="29"/>
-      <c r="BL11" s="13"/>
+      <c r="BK11" s="13"/>
+      <c r="BL11" s="29"/>
       <c r="BM11" s="13"/>
-      <c r="BN11" s="29"/>
-      <c r="BO11" s="13"/>
+      <c r="BN11" s="13"/>
+      <c r="BO11" s="29"/>
       <c r="BP11" s="13"/>
       <c r="BQ11" s="13"/>
       <c r="BR11" s="13"/>
-      <c r="BS11" s="13">
-        <f>(G11*H11)/100-BY11</f>
-        <v>721.49600000000009</v>
-      </c>
+      <c r="BS11" s="13"/>
       <c r="BT11" s="13">
-        <f>(G11*H11)/100</f>
+        <f t="shared" si="0"/>
         <v>721.49600000000009</v>
       </c>
       <c r="BU11" s="13">
         <f t="shared" si="1"/>
+        <v>721.49600000000009</v>
+      </c>
+      <c r="BV11" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BV11" s="13"/>
-      <c r="BY11" s="15">
-        <f>(BW11*BX11-BW11*H11)/100</f>
+      <c r="BW11" s="13"/>
+      <c r="BZ11" s="15">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="12" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1176593</v>
       </c>
@@ -3085,7 +3113,7 @@
       </c>
       <c r="D12" s="6" t="str">
         <f>IF(I12&lt;GEMINI!L12,"למכור בהפסד",IF(I12&gt;GEMINI!M12,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>68</v>
@@ -3100,93 +3128,95 @@
         <v>22581.42</v>
       </c>
       <c r="I12" s="13">
+        <v>28240</v>
+      </c>
+      <c r="J12" s="13">
+        <v>28240</v>
+      </c>
+      <c r="K12" s="13">
         <v>29460</v>
       </c>
-      <c r="J12" s="13">
-        <v>29460</v>
-      </c>
-      <c r="K12" s="13">
+      <c r="L12" s="13">
         <v>28720</v>
-      </c>
-      <c r="L12" s="13">
-        <v>27890</v>
       </c>
       <c r="M12" s="13">
         <v>27890</v>
       </c>
       <c r="N12" s="13">
+        <v>27890</v>
+      </c>
+      <c r="O12" s="13">
         <v>30100</v>
       </c>
-      <c r="O12" s="13">
+      <c r="P12" s="13">
         <v>30500</v>
       </c>
-      <c r="P12" s="13">
+      <c r="Q12" s="13">
         <v>28850</v>
       </c>
-      <c r="Q12" s="13">
+      <c r="R12" s="13">
         <v>27450</v>
       </c>
-      <c r="R12" s="13">
+      <c r="S12" s="13">
         <v>26940</v>
       </c>
-      <c r="S12" s="13">
+      <c r="T12" s="13">
         <v>26800</v>
       </c>
-      <c r="T12" s="13">
+      <c r="U12" s="13">
         <v>25950</v>
       </c>
-      <c r="U12" s="13">
+      <c r="V12" s="13">
         <v>26000</v>
       </c>
-      <c r="V12" s="13">
+      <c r="W12" s="13">
         <v>26600</v>
-      </c>
-      <c r="W12" s="13">
-        <v>24630</v>
       </c>
       <c r="X12" s="13">
         <v>24630</v>
       </c>
       <c r="Y12" s="13">
+        <v>24630</v>
+      </c>
+      <c r="Z12" s="13">
         <v>25230</v>
       </c>
-      <c r="Z12" s="13">
+      <c r="AA12" s="13">
         <v>24700</v>
       </c>
-      <c r="AA12" s="13">
+      <c r="AB12" s="13">
         <v>23780</v>
       </c>
-      <c r="AB12" s="13">
+      <c r="AC12" s="13">
         <v>23920</v>
       </c>
-      <c r="AC12" s="13">
+      <c r="AD12" s="13">
         <v>22390</v>
       </c>
-      <c r="AD12" s="13">
+      <c r="AE12" s="13">
         <v>23000</v>
       </c>
-      <c r="AE12" s="13">
+      <c r="AF12" s="13">
         <v>20990</v>
       </c>
-      <c r="AF12" s="13">
+      <c r="AG12" s="13">
         <v>20260</v>
       </c>
-      <c r="AG12" s="13">
+      <c r="AH12" s="13">
         <v>19200</v>
       </c>
-      <c r="AH12" s="13">
+      <c r="AI12" s="13">
         <v>19860</v>
       </c>
-      <c r="AI12" s="13">
+      <c r="AJ12" s="13">
         <v>19700</v>
       </c>
-      <c r="AJ12" s="13">
+      <c r="AK12" s="13">
         <v>19430</v>
       </c>
-      <c r="AK12" s="13">
+      <c r="AL12" s="13">
         <v>19020</v>
       </c>
-      <c r="AL12" s="13"/>
       <c r="AM12" s="13"/>
       <c r="AN12" s="13"/>
       <c r="AO12" s="13"/>
@@ -3211,36 +3241,37 @@
       <c r="BH12" s="13"/>
       <c r="BI12" s="13"/>
       <c r="BJ12" s="13"/>
-      <c r="BK12" s="29"/>
-      <c r="BL12" s="13"/>
+      <c r="BK12" s="13"/>
+      <c r="BL12" s="29"/>
       <c r="BM12" s="13"/>
-      <c r="BN12" s="29"/>
-      <c r="BO12" s="13"/>
+      <c r="BN12" s="13"/>
+      <c r="BO12" s="29"/>
       <c r="BP12" s="13"/>
       <c r="BQ12" s="13"/>
       <c r="BR12" s="13"/>
-      <c r="BS12" s="13">
-        <f>(G12*H12)/100-BY12</f>
+      <c r="BS12" s="13"/>
+      <c r="BT12" s="13">
+        <f t="shared" si="0"/>
         <v>-331.70059999999995</v>
       </c>
-      <c r="BT12" s="13">
-        <f>(G12*H12)/100</f>
+      <c r="BU12" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BU12" s="13"/>
       <c r="BV12" s="13"/>
-      <c r="BW12">
+      <c r="BW12" s="13"/>
+      <c r="BX12">
         <v>7</v>
       </c>
-      <c r="BX12">
+      <c r="BY12">
         <v>27320</v>
       </c>
-      <c r="BY12" s="15">
-        <f>(BW12*BX12-BW12*H12)/100</f>
+      <c r="BZ12" s="15">
+        <f t="shared" si="4"/>
         <v>331.70059999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="13" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>397018</v>
       </c>
@@ -3254,7 +3285,7 @@
       </c>
       <c r="D13" s="6" t="str">
         <f>IF(I13&lt;GEMINI!L13,"למכור בהפסד",IF(I13&gt;GEMINI!M13,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור בהפסד</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>95</v>
@@ -3269,43 +3300,45 @@
         <v>723</v>
       </c>
       <c r="I13" s="13">
+        <v>680.1</v>
+      </c>
+      <c r="J13" s="13">
+        <v>680.1</v>
+      </c>
+      <c r="K13" s="13">
         <v>1009</v>
       </c>
-      <c r="J13" s="13">
-        <v>1009</v>
-      </c>
-      <c r="K13" s="13">
+      <c r="L13" s="13">
         <v>1074</v>
-      </c>
-      <c r="L13" s="13">
-        <v>900</v>
       </c>
       <c r="M13" s="13">
         <v>900</v>
       </c>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13">
+      <c r="N13" s="13">
+        <v>900</v>
+      </c>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13">
         <v>1490</v>
       </c>
-      <c r="P13" s="13">
+      <c r="Q13" s="13">
         <v>1210</v>
       </c>
-      <c r="Q13" s="13">
+      <c r="R13" s="13">
         <v>1100</v>
       </c>
-      <c r="R13" s="13">
+      <c r="S13" s="13">
         <v>980</v>
       </c>
-      <c r="S13" s="13">
+      <c r="T13" s="13">
         <v>932.1</v>
       </c>
-      <c r="T13" s="13">
+      <c r="U13" s="13">
         <v>822</v>
       </c>
-      <c r="U13" s="13">
+      <c r="V13" s="13">
         <v>790</v>
       </c>
-      <c r="V13" s="13"/>
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
@@ -3346,30 +3379,34 @@
       <c r="BH13" s="13"/>
       <c r="BI13" s="13"/>
       <c r="BJ13" s="13"/>
-      <c r="BK13" s="29"/>
-      <c r="BL13" s="13"/>
+      <c r="BK13" s="13"/>
+      <c r="BL13" s="29"/>
       <c r="BM13" s="13"/>
-      <c r="BN13" s="29"/>
-      <c r="BO13" s="13"/>
+      <c r="BN13" s="13"/>
+      <c r="BO13" s="29"/>
       <c r="BP13" s="13"/>
       <c r="BQ13" s="13"/>
       <c r="BR13" s="13"/>
-      <c r="BS13" s="13">
-        <f>(G13*H13)/100-BY13</f>
+      <c r="BS13" s="13"/>
+      <c r="BT13" s="13">
+        <f t="shared" si="0"/>
+        <v>816.99</v>
+      </c>
+      <c r="BU13" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BT13" s="13">
-        <f>(G13*H13)/100</f>
-        <v>0</v>
-      </c>
-      <c r="BU13" s="13"/>
       <c r="BV13" s="13"/>
-      <c r="BY13" s="15">
-        <f>(BW13*BX13-BW13*H13)/100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:77" ht="45" customHeight="1" thickBot="1">
+      <c r="BW13" s="13"/>
+      <c r="BX13">
+        <v>113</v>
+      </c>
+      <c r="BZ13" s="15">
+        <f t="shared" si="4"/>
+        <v>-816.99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>662577</v>
       </c>
@@ -3398,213 +3435,216 @@
         <v>7204.22</v>
       </c>
       <c r="I14" s="13">
+        <v>7678</v>
+      </c>
+      <c r="J14" s="13">
+        <v>7678</v>
+      </c>
+      <c r="K14" s="13">
         <v>8051</v>
       </c>
-      <c r="J14" s="13">
-        <v>8051</v>
-      </c>
-      <c r="K14" s="13">
+      <c r="L14" s="13">
         <v>7911</v>
       </c>
-      <c r="L14" s="13">
+      <c r="M14" s="13">
         <v>7833</v>
       </c>
-      <c r="M14" s="13">
+      <c r="N14" s="13">
         <v>7687</v>
       </c>
-      <c r="N14" s="13">
+      <c r="O14" s="13">
         <v>7672</v>
       </c>
-      <c r="O14" s="13">
+      <c r="P14" s="13">
         <v>7676</v>
       </c>
-      <c r="P14" s="13">
+      <c r="Q14" s="13">
         <v>7844</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="R14" s="13">
         <v>7810</v>
       </c>
-      <c r="R14" s="13">
+      <c r="S14" s="13">
         <v>7710</v>
       </c>
-      <c r="S14" s="13">
+      <c r="T14" s="13">
         <v>7735</v>
       </c>
-      <c r="T14" s="13">
+      <c r="U14" s="13">
         <v>7725</v>
       </c>
-      <c r="U14" s="13">
+      <c r="V14" s="13">
         <v>7787</v>
       </c>
-      <c r="V14" s="13">
+      <c r="W14" s="13">
         <v>7955</v>
-      </c>
-      <c r="W14" s="13">
-        <v>7627</v>
       </c>
       <c r="X14" s="13">
         <v>7627</v>
       </c>
       <c r="Y14" s="13">
+        <v>7627</v>
+      </c>
+      <c r="Z14" s="13">
         <v>7656</v>
       </c>
-      <c r="Z14" s="13">
+      <c r="AA14" s="13">
         <v>7507</v>
       </c>
-      <c r="AA14" s="13">
+      <c r="AB14" s="13">
         <v>7590</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AC14" s="13">
         <v>7569</v>
       </c>
-      <c r="AC14" s="13">
+      <c r="AD14" s="13">
         <v>7269</v>
       </c>
-      <c r="AD14" s="13">
+      <c r="AE14" s="13">
         <v>7444</v>
       </c>
-      <c r="AE14" s="13">
+      <c r="AF14" s="13">
         <v>7205</v>
       </c>
-      <c r="AF14" s="13">
+      <c r="AG14" s="13">
         <v>7298</v>
       </c>
-      <c r="AG14" s="13">
+      <c r="AH14" s="13">
         <v>7222</v>
       </c>
-      <c r="AH14" s="13">
+      <c r="AI14" s="13">
         <v>7079</v>
       </c>
-      <c r="AI14" s="13">
+      <c r="AJ14" s="13">
         <v>7140</v>
       </c>
-      <c r="AJ14" s="13">
+      <c r="AK14" s="13">
         <v>7440</v>
       </c>
-      <c r="AK14" s="13">
+      <c r="AL14" s="13">
         <v>7530</v>
-      </c>
-      <c r="AL14" s="13">
-        <v>7535</v>
       </c>
       <c r="AM14" s="13">
         <v>7535</v>
       </c>
       <c r="AN14" s="13">
+        <v>7535</v>
+      </c>
+      <c r="AO14" s="13">
         <v>7568</v>
       </c>
-      <c r="AO14" s="13">
+      <c r="AP14" s="13">
         <v>7699</v>
       </c>
-      <c r="AP14" s="13">
+      <c r="AQ14" s="13">
         <v>7638</v>
       </c>
-      <c r="AQ14" s="13">
+      <c r="AR14" s="13">
         <v>7654</v>
       </c>
-      <c r="AR14" s="13">
+      <c r="AS14" s="13">
         <v>7584</v>
       </c>
-      <c r="AS14" s="13">
+      <c r="AT14" s="13">
         <v>7479</v>
       </c>
-      <c r="AT14" s="13">
+      <c r="AU14" s="13">
         <v>7490</v>
       </c>
-      <c r="AU14" s="13">
+      <c r="AV14" s="13">
         <v>7480</v>
       </c>
-      <c r="AV14" s="13">
+      <c r="AW14" s="13">
         <v>7270</v>
       </c>
-      <c r="AW14" s="13">
+      <c r="AX14" s="13">
         <v>7163</v>
       </c>
-      <c r="AX14" s="13">
+      <c r="AY14" s="13">
         <v>7231</v>
-      </c>
-      <c r="AY14" s="13">
-        <v>7100</v>
       </c>
       <c r="AZ14" s="13">
         <v>7100</v>
       </c>
       <c r="BA14" s="13">
+        <v>7100</v>
+      </c>
+      <c r="BB14" s="13">
         <v>7027</v>
       </c>
-      <c r="BB14" s="13">
+      <c r="BC14" s="13">
         <v>6984</v>
       </c>
-      <c r="BC14" s="13">
+      <c r="BD14" s="13">
         <v>6944</v>
       </c>
-      <c r="BD14" s="13">
+      <c r="BE14" s="13">
         <v>6924</v>
       </c>
-      <c r="BE14" s="13">
+      <c r="BF14" s="13">
         <v>6930</v>
       </c>
-      <c r="BF14" s="13">
+      <c r="BG14" s="13">
         <v>6938</v>
       </c>
-      <c r="BG14" s="13">
+      <c r="BH14" s="13">
         <v>6989</v>
       </c>
-      <c r="BH14" s="13">
+      <c r="BI14" s="13">
         <v>6871</v>
       </c>
-      <c r="BI14" s="13">
+      <c r="BJ14" s="13">
         <v>6943</v>
       </c>
-      <c r="BJ14" s="13">
+      <c r="BK14" s="13">
         <v>7040</v>
       </c>
-      <c r="BK14" s="29">
+      <c r="BL14" s="29">
         <v>6696</v>
       </c>
-      <c r="BL14" s="13">
+      <c r="BM14" s="13">
         <v>6965</v>
       </c>
-      <c r="BM14" s="13">
+      <c r="BN14" s="13">
         <v>6788</v>
       </c>
-      <c r="BN14" s="29">
+      <c r="BO14" s="29">
         <v>6696</v>
       </c>
-      <c r="BO14" s="13">
+      <c r="BP14" s="13">
         <v>6625</v>
       </c>
-      <c r="BP14" s="13">
+      <c r="BQ14" s="13">
         <v>6660</v>
       </c>
-      <c r="BQ14" s="13">
+      <c r="BR14" s="13">
         <v>6791</v>
       </c>
-      <c r="BR14" s="13">
+      <c r="BS14" s="13">
         <v>6610</v>
       </c>
-      <c r="BS14" s="13">
-        <f>(G14*H14)/100-BY14</f>
+      <c r="BT14" s="13">
+        <f t="shared" si="0"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BT14" s="13">
-        <f>(G14*H14)/100</f>
+      <c r="BU14" s="13">
+        <f t="shared" si="1"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BU14" s="13">
-        <f t="shared" ref="BU14" si="2">(BT14-BS14)</f>
+      <c r="BV14" s="13">
+        <f t="shared" ref="BV14" si="5">(BU14-BT14)</f>
         <v>0</v>
       </c>
-      <c r="BV14" s="13">
-        <f>((BJ14-H14)/H14)*100</f>
+      <c r="BW14" s="13">
+        <f>((BK14-H14)/H14)*100</f>
         <v>-2.2794972946411995</v>
       </c>
-      <c r="BY14" s="15">
-        <f>(BW14*BX14-BW14*H14)/100</f>
+      <c r="BZ14" s="15">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="15" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>5137534</v>
       </c>
@@ -3633,81 +3673,83 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
+        <v>12256</v>
+      </c>
+      <c r="J15" s="13">
+        <v>12256</v>
+      </c>
+      <c r="K15" s="13">
         <v>12145</v>
       </c>
-      <c r="J15" s="13">
-        <v>12145</v>
-      </c>
-      <c r="K15" s="13">
+      <c r="L15" s="13">
         <v>11855.12</v>
-      </c>
-      <c r="L15" s="13">
-        <v>11946.75</v>
       </c>
       <c r="M15" s="13">
         <v>11946.75</v>
       </c>
       <c r="N15" s="13">
-        <v>14679.12</v>
+        <v>11946.75</v>
       </c>
       <c r="O15" s="13">
         <v>14679.12</v>
       </c>
       <c r="P15" s="13">
+        <v>14679.12</v>
+      </c>
+      <c r="Q15" s="13">
         <v>13968</v>
       </c>
-      <c r="Q15" s="13">
+      <c r="R15" s="13">
         <v>15528.12</v>
       </c>
-      <c r="R15" s="13">
+      <c r="S15" s="13">
         <v>14358.25</v>
       </c>
-      <c r="S15" s="13">
+      <c r="T15" s="13">
         <v>14385.75</v>
       </c>
-      <c r="T15" s="13">
+      <c r="U15" s="13">
         <v>13880</v>
       </c>
-      <c r="U15" s="13">
+      <c r="V15" s="13">
         <v>13610.62</v>
       </c>
-      <c r="V15" s="13">
+      <c r="W15" s="13">
         <v>13016</v>
       </c>
-      <c r="W15" s="13">
+      <c r="X15" s="13">
         <v>12487.37</v>
       </c>
-      <c r="X15" s="13">
+      <c r="Y15" s="13">
         <v>12638.62</v>
       </c>
-      <c r="Y15" s="13">
+      <c r="Z15" s="13">
         <v>12533.87</v>
       </c>
-      <c r="Z15" s="13">
+      <c r="AA15" s="13">
         <v>11299.5</v>
       </c>
-      <c r="AA15" s="13">
+      <c r="AB15" s="13">
         <v>11193.12</v>
       </c>
-      <c r="AB15" s="13">
+      <c r="AC15" s="13">
         <v>11548.62</v>
       </c>
-      <c r="AC15" s="13">
+      <c r="AD15" s="13">
         <v>11125.62</v>
       </c>
-      <c r="AD15" s="13">
+      <c r="AE15" s="13">
         <v>10932.12</v>
       </c>
-      <c r="AE15" s="13">
+      <c r="AF15" s="13">
         <v>11095.62</v>
       </c>
-      <c r="AF15" s="13">
+      <c r="AG15" s="13">
         <v>10910.58</v>
       </c>
-      <c r="AG15" s="13">
+      <c r="AH15" s="13">
         <v>11609.37</v>
       </c>
-      <c r="AH15" s="13"/>
       <c r="AI15" s="13"/>
       <c r="AJ15" s="13"/>
       <c r="AK15" s="13"/>
@@ -3717,8 +3759,8 @@
       <c r="AO15" s="13"/>
       <c r="AP15" s="13"/>
       <c r="AQ15" s="13"/>
-      <c r="AR15" s="14"/>
-      <c r="AS15" s="13"/>
+      <c r="AR15" s="13"/>
+      <c r="AS15" s="14"/>
       <c r="AT15" s="13"/>
       <c r="AU15" s="13"/>
       <c r="AV15" s="13"/>
@@ -3736,36 +3778,37 @@
       <c r="BH15" s="13"/>
       <c r="BI15" s="13"/>
       <c r="BJ15" s="13"/>
-      <c r="BK15" s="29"/>
-      <c r="BL15" s="13"/>
+      <c r="BK15" s="13"/>
+      <c r="BL15" s="29"/>
       <c r="BM15" s="13"/>
-      <c r="BN15" s="29"/>
-      <c r="BO15" s="13"/>
+      <c r="BN15" s="13"/>
+      <c r="BO15" s="29"/>
       <c r="BP15" s="13"/>
       <c r="BQ15" s="13"/>
       <c r="BR15" s="13"/>
-      <c r="BS15" s="13">
-        <f>(G15*H15)/100-BY15</f>
+      <c r="BS15" s="13"/>
+      <c r="BT15" s="13">
+        <f t="shared" si="0"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BT15" s="13">
-        <f>(G15*H15)/100</f>
+      <c r="BU15" s="13">
+        <f t="shared" si="1"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BU15" s="13">
-        <f t="shared" ref="BU15:BU18" si="3">(BT15-BS15)</f>
+      <c r="BV15" s="13">
+        <f t="shared" ref="BV15:BV18" si="6">(BU15-BT15)</f>
         <v>0</v>
       </c>
-      <c r="BV15" s="13">
-        <f>((BJ15-H15)/H15)*100</f>
+      <c r="BW15" s="13">
+        <f>((BK15-H15)/H15)*100</f>
         <v>-100</v>
       </c>
-      <c r="BY15" s="15">
-        <f>(BW15*BX15-BW15*H15)/100</f>
+      <c r="BZ15" s="15">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="16" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>5135470</v>
       </c>
@@ -3794,219 +3837,222 @@
         <v>199.49</v>
       </c>
       <c r="I16" s="13">
+        <v>220.86</v>
+      </c>
+      <c r="J16" s="13">
+        <v>220.86</v>
+      </c>
+      <c r="K16" s="13">
         <v>221.02</v>
       </c>
-      <c r="J16" s="13">
-        <v>221.02</v>
-      </c>
-      <c r="K16" s="13">
+      <c r="L16" s="13">
         <v>218.38</v>
       </c>
-      <c r="L16" s="13">
+      <c r="M16" s="13">
         <v>218.36</v>
       </c>
-      <c r="M16" s="13">
+      <c r="N16" s="13">
         <v>223.13</v>
       </c>
-      <c r="N16" s="13">
+      <c r="O16" s="13">
         <v>227.54</v>
       </c>
-      <c r="O16" s="13">
+      <c r="P16" s="13">
         <v>226.96</v>
       </c>
-      <c r="P16" s="13">
+      <c r="Q16" s="13">
         <v>225.24</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="R16" s="13">
         <v>223.25</v>
-      </c>
-      <c r="R16" s="13">
-        <v>219.14</v>
       </c>
       <c r="S16" s="13">
         <v>219.14</v>
       </c>
       <c r="T16" s="13">
+        <v>219.14</v>
+      </c>
+      <c r="U16" s="13">
         <v>219.3</v>
       </c>
-      <c r="U16" s="13">
+      <c r="V16" s="13">
         <v>222.79</v>
       </c>
-      <c r="V16" s="13">
+      <c r="W16" s="13">
         <v>221.16</v>
       </c>
-      <c r="W16" s="13">
+      <c r="X16" s="13">
         <v>220.66</v>
       </c>
-      <c r="X16" s="13">
+      <c r="Y16" s="13">
         <v>222.06</v>
       </c>
-      <c r="Y16" s="13">
+      <c r="Z16" s="13">
         <v>218.71</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="AA16" s="13">
         <v>216.74</v>
       </c>
-      <c r="AA16" s="13">
+      <c r="AB16" s="13">
         <v>216.04</v>
-      </c>
-      <c r="AB16" s="13">
-        <v>210.69</v>
       </c>
       <c r="AC16" s="13">
         <v>210.69</v>
       </c>
       <c r="AD16" s="13">
+        <v>210.69</v>
+      </c>
+      <c r="AE16" s="13">
         <v>198</v>
       </c>
-      <c r="AE16" s="13">
+      <c r="AF16" s="13">
         <v>196.74</v>
       </c>
-      <c r="AF16" s="13">
+      <c r="AG16" s="13">
         <v>192.56</v>
       </c>
-      <c r="AG16" s="13">
+      <c r="AH16" s="13">
         <v>192.23</v>
       </c>
-      <c r="AH16" s="13">
+      <c r="AI16" s="13">
         <v>191.19</v>
       </c>
-      <c r="AI16" s="13">
+      <c r="AJ16" s="13">
         <v>193.62</v>
       </c>
-      <c r="AJ16" s="13">
+      <c r="AK16" s="13">
         <v>190.75</v>
       </c>
-      <c r="AK16" s="13">
+      <c r="AL16" s="13">
         <v>189.06</v>
-      </c>
-      <c r="AL16" s="13">
-        <v>182.73</v>
       </c>
       <c r="AM16" s="13">
         <v>182.73</v>
       </c>
       <c r="AN16" s="13">
+        <v>182.73</v>
+      </c>
+      <c r="AO16" s="13">
         <v>177.92</v>
       </c>
-      <c r="AO16" s="13">
+      <c r="AP16" s="13">
         <v>179.16</v>
       </c>
-      <c r="AP16" s="13">
+      <c r="AQ16" s="13">
         <v>179.34</v>
-      </c>
-      <c r="AQ16" s="13">
-        <v>176.5</v>
       </c>
       <c r="AR16" s="13">
         <v>176.5</v>
       </c>
       <c r="AS16" s="13">
+        <v>176.5</v>
+      </c>
+      <c r="AT16" s="13">
         <v>175.93</v>
       </c>
-      <c r="AT16" s="13">
+      <c r="AU16" s="13">
         <v>174.51</v>
       </c>
-      <c r="AU16" s="13">
+      <c r="AV16" s="13">
         <v>173.91</v>
       </c>
-      <c r="AV16" s="13">
+      <c r="AW16" s="13">
         <v>177.1</v>
       </c>
-      <c r="AW16" s="13">
+      <c r="AX16" s="13">
         <v>178.24</v>
       </c>
-      <c r="AX16" s="13">
+      <c r="AY16" s="13">
         <v>176.52</v>
       </c>
-      <c r="AY16" s="13">
+      <c r="AZ16" s="13">
         <v>178.27</v>
       </c>
-      <c r="AZ16" s="13">
+      <c r="BA16" s="13">
         <v>175.29</v>
       </c>
-      <c r="BA16" s="13">
+      <c r="BB16" s="13">
         <v>175.34</v>
       </c>
-      <c r="BB16" s="13">
+      <c r="BC16" s="13">
         <v>174.41</v>
       </c>
-      <c r="BC16" s="13">
+      <c r="BD16" s="13">
         <v>176.22</v>
       </c>
-      <c r="BD16" s="13">
+      <c r="BE16" s="13">
         <v>174</v>
       </c>
-      <c r="BE16" s="13">
+      <c r="BF16" s="13">
         <v>176.35</v>
       </c>
-      <c r="BF16" s="13">
+      <c r="BG16" s="13">
         <v>177.71</v>
       </c>
-      <c r="BG16" s="13">
+      <c r="BH16" s="13">
         <v>180.08</v>
       </c>
-      <c r="BH16" s="13">
+      <c r="BI16" s="13">
         <v>181.96</v>
       </c>
-      <c r="BI16" s="13">
+      <c r="BJ16" s="13">
         <v>182.9</v>
       </c>
-      <c r="BJ16" s="13">
+      <c r="BK16" s="13">
         <v>181.86</v>
       </c>
-      <c r="BK16" s="29">
+      <c r="BL16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BL16" s="13">
+      <c r="BM16" s="13">
         <v>181.07</v>
       </c>
-      <c r="BM16" s="13">
+      <c r="BN16" s="13">
         <v>182.56</v>
       </c>
-      <c r="BN16" s="29">
+      <c r="BO16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BO16" s="13">
+      <c r="BP16" s="13">
         <v>178.86</v>
       </c>
-      <c r="BP16" s="13">
+      <c r="BQ16" s="13">
         <v>180.16</v>
       </c>
-      <c r="BQ16" s="13">
+      <c r="BR16" s="13">
         <v>179.56</v>
       </c>
-      <c r="BR16" s="13">
+      <c r="BS16" s="13">
         <v>176.55</v>
       </c>
-      <c r="BS16" s="13">
-        <f>(G16*H16)/100-BY16</f>
+      <c r="BT16" s="13">
+        <f t="shared" si="0"/>
         <v>1413.1220000000008</v>
       </c>
-      <c r="BT16" s="13">
-        <f>(G16*H16)/100</f>
+      <c r="BU16" s="13">
+        <f t="shared" si="1"/>
         <v>997.45</v>
       </c>
-      <c r="BU16" s="13">
-        <f t="shared" si="3"/>
+      <c r="BV16" s="13">
+        <f t="shared" si="6"/>
         <v>-415.67200000000071</v>
       </c>
-      <c r="BV16" s="13">
-        <f>((BJ16-H16)/H16)*100</f>
+      <c r="BW16" s="13">
+        <f>((BK16-H16)/H16)*100</f>
         <v>-8.8375357160759904</v>
       </c>
-      <c r="BW16">
+      <c r="BX16">
         <v>1864</v>
       </c>
-      <c r="BX16">
+      <c r="BY16">
         <v>177.19</v>
       </c>
-      <c r="BY16" s="15">
-        <f>(BW16*BX16-BW16*H16)/100</f>
+      <c r="BZ16" s="15">
+        <f t="shared" si="4"/>
         <v>-415.67200000000071</v>
       </c>
     </row>
-    <row r="17" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="17" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>5134135</v>
       </c>
@@ -4035,10 +4081,10 @@
         <v>159.65</v>
       </c>
       <c r="I17" s="13">
-        <v>184.42</v>
+        <v>190.72</v>
       </c>
       <c r="J17" s="13">
-        <v>184.42</v>
+        <v>190.72</v>
       </c>
       <c r="K17" s="13">
         <v>184.42</v>
@@ -4047,13 +4093,13 @@
         <v>184.42</v>
       </c>
       <c r="M17" s="13">
+        <v>184.42</v>
+      </c>
+      <c r="N17" s="13">
         <v>199.37</v>
       </c>
-      <c r="N17" s="13">
+      <c r="O17" s="13">
         <v>194.88</v>
-      </c>
-      <c r="O17" s="13">
-        <v>189.51</v>
       </c>
       <c r="P17" s="13">
         <v>189.51</v>
@@ -4062,13 +4108,13 @@
         <v>189.51</v>
       </c>
       <c r="R17" s="13">
-        <v>185.52</v>
+        <v>189.51</v>
       </c>
       <c r="S17" s="13">
         <v>185.52</v>
       </c>
       <c r="T17" s="13">
-        <v>178.98</v>
+        <v>185.52</v>
       </c>
       <c r="U17" s="13">
         <v>178.98</v>
@@ -4077,7 +4123,7 @@
         <v>178.98</v>
       </c>
       <c r="W17" s="13">
-        <v>170.7</v>
+        <v>178.98</v>
       </c>
       <c r="X17" s="13">
         <v>170.7</v>
@@ -4086,10 +4132,10 @@
         <v>170.7</v>
       </c>
       <c r="Z17" s="13">
+        <v>170.7</v>
+      </c>
+      <c r="AA17" s="13">
         <v>170.45</v>
-      </c>
-      <c r="AA17" s="13">
-        <v>160.84</v>
       </c>
       <c r="AB17" s="13">
         <v>160.84</v>
@@ -4098,15 +4144,17 @@
         <v>160.84</v>
       </c>
       <c r="AD17" s="13">
+        <v>160.84</v>
+      </c>
+      <c r="AE17" s="13">
         <v>159.02000000000001</v>
-      </c>
-      <c r="AE17" s="13">
-        <v>159.65</v>
       </c>
       <c r="AF17" s="13">
         <v>159.65</v>
       </c>
-      <c r="AG17" s="13"/>
+      <c r="AG17" s="13">
+        <v>159.65</v>
+      </c>
       <c r="AH17" s="13"/>
       <c r="AI17" s="13"/>
       <c r="AJ17" s="13"/>
@@ -4136,36 +4184,37 @@
       <c r="BH17" s="13"/>
       <c r="BI17" s="13"/>
       <c r="BJ17" s="13"/>
-      <c r="BK17" s="29"/>
-      <c r="BL17" s="13"/>
+      <c r="BK17" s="13"/>
+      <c r="BL17" s="29"/>
       <c r="BM17" s="13"/>
-      <c r="BN17" s="29"/>
-      <c r="BO17" s="13"/>
+      <c r="BN17" s="13"/>
+      <c r="BO17" s="29"/>
       <c r="BP17" s="13"/>
       <c r="BQ17" s="13"/>
       <c r="BR17" s="13"/>
-      <c r="BS17" s="13">
-        <f>(G17*H17)/100-BY17</f>
+      <c r="BS17" s="13"/>
+      <c r="BT17" s="13">
+        <f t="shared" si="0"/>
         <v>957.9</v>
       </c>
-      <c r="BT17" s="13">
-        <f>(G17*H17)/100</f>
+      <c r="BU17" s="13">
+        <f t="shared" si="1"/>
         <v>957.9</v>
       </c>
-      <c r="BU17" s="13">
-        <f t="shared" ref="BU17" si="4">(BT17-BS17)</f>
+      <c r="BV17" s="13">
+        <f t="shared" ref="BV17" si="7">(BU17-BT17)</f>
         <v>0</v>
       </c>
-      <c r="BV17" s="13">
-        <f>((BJ17-H17)/H17)*100</f>
+      <c r="BW17" s="13">
+        <f>((BK17-H17)/H17)*100</f>
         <v>-100</v>
       </c>
-      <c r="BY17" s="15">
-        <f>(BW17*BX17-BW17*H17)/100</f>
+      <c r="BZ17" s="15">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="18" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1168723</v>
       </c>
@@ -4194,84 +4243,86 @@
         <v>1434</v>
       </c>
       <c r="I18" s="13">
+        <v>1818</v>
+      </c>
+      <c r="J18" s="13">
+        <v>1818</v>
+      </c>
+      <c r="K18" s="13">
         <v>1866</v>
       </c>
-      <c r="J18" s="13">
-        <v>1866</v>
-      </c>
-      <c r="K18" s="13">
+      <c r="L18" s="13">
         <v>1886</v>
       </c>
-      <c r="L18" s="13">
+      <c r="M18" s="13">
         <v>1818</v>
       </c>
-      <c r="M18" s="13">
+      <c r="N18" s="13">
         <v>1785</v>
       </c>
-      <c r="N18" s="13">
+      <c r="O18" s="13">
         <v>1828</v>
       </c>
-      <c r="O18" s="13">
+      <c r="P18" s="13">
         <v>1811</v>
       </c>
-      <c r="P18" s="13">
+      <c r="Q18" s="13">
         <v>1825</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="R18" s="13">
         <v>1831</v>
       </c>
-      <c r="R18" s="13">
+      <c r="S18" s="13">
         <v>1799</v>
       </c>
-      <c r="S18" s="13">
+      <c r="T18" s="13">
         <v>1757</v>
       </c>
-      <c r="T18" s="13">
+      <c r="U18" s="13">
         <v>1698</v>
       </c>
-      <c r="U18" s="13">
+      <c r="V18" s="13">
         <v>1694</v>
       </c>
-      <c r="V18" s="13">
+      <c r="W18" s="13">
         <v>1671</v>
-      </c>
-      <c r="W18" s="13">
-        <v>1660</v>
       </c>
       <c r="X18" s="13">
         <v>1660</v>
       </c>
       <c r="Y18" s="13">
+        <v>1660</v>
+      </c>
+      <c r="Z18" s="13">
         <v>1646</v>
       </c>
-      <c r="Z18" s="13">
+      <c r="AA18" s="13">
         <v>1648</v>
       </c>
-      <c r="AA18" s="13">
+      <c r="AB18" s="13">
         <v>1614</v>
       </c>
-      <c r="AB18" s="13">
+      <c r="AC18" s="13">
         <v>1626</v>
       </c>
-      <c r="AC18" s="13">
+      <c r="AD18" s="13">
         <v>1587</v>
       </c>
-      <c r="AD18" s="13">
+      <c r="AE18" s="13">
         <v>1548</v>
       </c>
-      <c r="AE18" s="13">
+      <c r="AF18" s="13">
         <v>1500</v>
       </c>
-      <c r="AF18" s="13">
+      <c r="AG18" s="13">
         <v>1491</v>
       </c>
-      <c r="AG18" s="13">
+      <c r="AH18" s="13">
         <v>1444</v>
       </c>
-      <c r="AH18" s="13">
+      <c r="AI18" s="13">
         <v>1431</v>
       </c>
-      <c r="AI18" s="13"/>
       <c r="AJ18" s="13"/>
       <c r="AK18" s="13"/>
       <c r="AL18" s="13"/>
@@ -4297,64 +4348,65 @@
       <c r="BF18" s="13"/>
       <c r="BG18" s="13"/>
       <c r="BH18" s="13"/>
-      <c r="BI18" s="13">
-        <v>1788</v>
-      </c>
+      <c r="BI18" s="13"/>
       <c r="BJ18" s="13">
         <v>1788</v>
       </c>
-      <c r="BK18" s="29">
+      <c r="BK18" s="13">
+        <v>1788</v>
+      </c>
+      <c r="BL18" s="29">
         <v>1780</v>
       </c>
-      <c r="BL18" s="13">
+      <c r="BM18" s="13">
         <v>1814</v>
       </c>
-      <c r="BM18" s="13">
+      <c r="BN18" s="13">
         <v>1794</v>
       </c>
-      <c r="BN18" s="29">
+      <c r="BO18" s="29">
         <v>1780</v>
       </c>
-      <c r="BO18" s="13">
+      <c r="BP18" s="13">
         <v>1772</v>
       </c>
-      <c r="BP18" s="13">
+      <c r="BQ18" s="13">
         <v>1798</v>
       </c>
-      <c r="BQ18" s="13">
+      <c r="BR18" s="13">
         <v>1806</v>
       </c>
-      <c r="BR18" s="13">
+      <c r="BS18" s="13">
         <v>1801</v>
       </c>
-      <c r="BS18" s="13">
-        <f>(G18*H18)/100-BY18</f>
+      <c r="BT18" s="13">
+        <f t="shared" si="0"/>
         <v>292.79999999999995</v>
       </c>
-      <c r="BT18" s="13">
-        <f>(G18*H18)/100</f>
+      <c r="BU18" s="13">
+        <f t="shared" si="1"/>
         <v>645.29999999999995</v>
       </c>
-      <c r="BU18" s="13">
-        <f t="shared" si="3"/>
+      <c r="BV18" s="13">
+        <f t="shared" si="6"/>
         <v>352.5</v>
       </c>
-      <c r="BV18" s="13">
-        <f>((BJ18-H18)/H18)*100</f>
+      <c r="BW18" s="13">
+        <f>((BK18-H18)/H18)*100</f>
         <v>24.686192468619247</v>
       </c>
-      <c r="BW18">
+      <c r="BX18">
         <v>100</v>
       </c>
-      <c r="BX18">
+      <c r="BY18">
         <v>1786.5</v>
       </c>
-      <c r="BY18" s="15">
-        <f>(BW18*BX18-BW18*H18)/100</f>
+      <c r="BZ18" s="15">
+        <f t="shared" si="4"/>
         <v>352.5</v>
       </c>
     </row>
-    <row r="19" spans="1:77" ht="45" customHeight="1" thickBot="1">
+    <row r="19" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1122654</v>
       </c>
@@ -4377,27 +4429,29 @@
         <v>46052</v>
       </c>
       <c r="G19" s="27">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="H19" s="13">
         <v>102.77</v>
       </c>
       <c r="I19" s="13">
+        <v>72</v>
+      </c>
+      <c r="J19" s="13">
+        <v>72</v>
+      </c>
+      <c r="K19" s="13">
         <v>86.7</v>
-      </c>
-      <c r="J19" s="13">
-        <v>86.7</v>
-      </c>
-      <c r="K19" s="13">
-        <v>91.5</v>
       </c>
       <c r="L19" s="13">
         <v>91.5</v>
       </c>
       <c r="M19" s="13">
+        <v>91.5</v>
+      </c>
+      <c r="N19" s="13">
         <v>132.6</v>
       </c>
-      <c r="N19" s="13"/>
       <c r="O19" s="13"/>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
@@ -4413,22 +4467,22 @@
       <c r="AA19" s="13"/>
       <c r="AB19" s="13"/>
       <c r="AC19" s="13"/>
-      <c r="AD19" s="13">
+      <c r="AD19" s="13"/>
+      <c r="AE19" s="13">
         <v>6461</v>
       </c>
-      <c r="AE19" s="13">
+      <c r="AF19" s="13">
         <v>6503</v>
       </c>
-      <c r="AF19" s="13">
+      <c r="AG19" s="13">
         <v>6535</v>
       </c>
-      <c r="AG19" s="13">
+      <c r="AH19" s="13">
         <v>6532</v>
       </c>
-      <c r="AH19" s="13">
+      <c r="AI19" s="13">
         <v>6515</v>
       </c>
-      <c r="AI19" s="13"/>
       <c r="AJ19" s="13"/>
       <c r="AK19" s="13"/>
       <c r="AL19" s="13"/>
@@ -4456,33 +4510,34 @@
       <c r="BH19" s="13"/>
       <c r="BI19" s="13"/>
       <c r="BJ19" s="13"/>
-      <c r="BK19" s="29"/>
-      <c r="BL19" s="13"/>
+      <c r="BK19" s="13"/>
+      <c r="BL19" s="29"/>
       <c r="BM19" s="13"/>
-      <c r="BN19" s="29"/>
-      <c r="BO19" s="13"/>
+      <c r="BN19" s="13"/>
+      <c r="BO19" s="29"/>
       <c r="BP19" s="13"/>
       <c r="BQ19" s="13"/>
       <c r="BR19" s="13"/>
-      <c r="BS19" s="13">
-        <f>(G19*H19)/100-BY19</f>
-        <v>719.39</v>
-      </c>
+      <c r="BS19" s="13"/>
       <c r="BT19" s="13">
-        <f>(G19*H19)/100</f>
-        <v>719.39</v>
-      </c>
-      <c r="BU19" s="13"/>
+        <f t="shared" si="0"/>
+        <v>308.31</v>
+      </c>
+      <c r="BU19" s="13">
+        <f t="shared" si="1"/>
+        <v>308.31</v>
+      </c>
       <c r="BV19" s="13"/>
-      <c r="BW19">
+      <c r="BW19" s="13"/>
+      <c r="BX19">
         <v>7</v>
       </c>
-      <c r="BX19">
+      <c r="BY19">
         <v>6461</v>
       </c>
-      <c r="BY19" s="15"/>
-    </row>
-    <row r="20" spans="1:77" ht="45" customHeight="1" thickBot="1">
+      <c r="BZ19" s="15"/>
+    </row>
+    <row r="20" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>363010</v>
       </c>
@@ -4511,15 +4566,17 @@
         <v>65</v>
       </c>
       <c r="I20" s="13">
+        <v>70</v>
+      </c>
+      <c r="J20" s="13">
+        <v>70</v>
+      </c>
+      <c r="K20" s="13">
         <v>89</v>
       </c>
-      <c r="J20" s="13">
-        <v>89</v>
-      </c>
-      <c r="K20" s="13">
+      <c r="L20" s="13">
         <v>87.5</v>
       </c>
-      <c r="L20" s="13"/>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
       <c r="O20" s="13"/>
@@ -4570,28 +4627,29 @@
       <c r="BH20" s="13"/>
       <c r="BI20" s="13"/>
       <c r="BJ20" s="13"/>
-      <c r="BK20" s="29"/>
-      <c r="BL20" s="13"/>
+      <c r="BK20" s="13"/>
+      <c r="BL20" s="29"/>
       <c r="BM20" s="13"/>
-      <c r="BN20" s="29"/>
-      <c r="BO20" s="13"/>
+      <c r="BN20" s="13"/>
+      <c r="BO20" s="29"/>
       <c r="BP20" s="13"/>
       <c r="BQ20" s="13"/>
       <c r="BR20" s="13"/>
-      <c r="BS20" s="13">
-        <f>(G20*H20)/100-BY20</f>
+      <c r="BS20" s="13"/>
+      <c r="BT20" s="13">
+        <f t="shared" si="0"/>
         <v>195</v>
       </c>
-      <c r="BT20" s="13">
-        <f>(G20*H20)/100</f>
+      <c r="BU20" s="13">
+        <f t="shared" si="1"/>
         <v>195</v>
       </c>
-      <c r="BU20" s="13"/>
       <c r="BV20" s="13"/>
-      <c r="BY20" s="15"/>
-    </row>
-    <row r="21" spans="1:77" ht="14.4" thickBot="1"/>
-    <row r="22" spans="1:77" ht="45" customHeight="1" thickBot="1">
+      <c r="BW20" s="13"/>
+      <c r="BZ20" s="15"/>
+    </row>
+    <row r="21" spans="1:78" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4654,11 +4712,11 @@
       <c r="BH22" s="13"/>
       <c r="BI22" s="13"/>
       <c r="BJ22" s="13"/>
-      <c r="BK22" s="29"/>
-      <c r="BL22" s="13"/>
+      <c r="BK22" s="13"/>
+      <c r="BL22" s="29"/>
       <c r="BM22" s="13"/>
-      <c r="BN22" s="29"/>
-      <c r="BO22" s="13"/>
+      <c r="BN22" s="13"/>
+      <c r="BO22" s="29"/>
       <c r="BP22" s="13"/>
       <c r="BQ22" s="13"/>
       <c r="BR22" s="13"/>
@@ -4666,9 +4724,10 @@
       <c r="BT22" s="13"/>
       <c r="BU22" s="13"/>
       <c r="BV22" s="13"/>
-      <c r="BY22" s="15"/>
-    </row>
-    <row r="23" spans="1:77" ht="54.9" customHeight="1" thickBot="1">
+      <c r="BW22" s="13"/>
+      <c r="BZ22" s="15"/>
+    </row>
+    <row r="23" spans="1:78" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4681,91 +4740,91 @@
       <c r="H23" s="13"/>
       <c r="I23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19+G20*I20)/100</f>
-        <v>14263.01</v>
+        <v>13500.502</v>
       </c>
       <c r="J23" s="23">
         <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19+G20*J20)/100</f>
-        <v>14263.01</v>
+        <v>13500.502</v>
       </c>
       <c r="K23" s="23">
         <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19+G20*K20)/100</f>
-        <v>14302.159599999999</v>
+        <v>13916.21</v>
       </c>
       <c r="L23" s="23">
         <f>(L2*G2+G3*L3+L4*G4+G5*L5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+L13*G13+G14*L14+L15*G15+G16*L16+G17*L17+L18*G18+G19*L19+G20*L20)/100</f>
-        <v>13804.511999999999</v>
+        <v>13936.159599999999</v>
       </c>
       <c r="M23" s="23">
-        <f>(M2*G2+G3*M3+M4*G4+G5*M5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+M13*G13+G14*M14+M15*G15+G16*M16+G17*M17+M18*G18+G19*M19)/100</f>
-        <v>14033.53</v>
+        <f>(M2*G2+G3*M3+M4*G4+G5*M5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+M13*G13+G14*M14+M15*G15+G16*M16+G17*M17+M18*G18+G19*M19+G20*M20)/100</f>
+        <v>13438.511999999999</v>
       </c>
       <c r="N23" s="23">
         <f>(N2*G2+G3*N3+N4*G4+G5*N5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+N13*G13+G14*N14+N15*G15+G16*N16+G17*N17+N18*G18+G19*N19)/100</f>
-        <v>13844.2896</v>
+        <v>13503.13</v>
       </c>
       <c r="O23" s="23">
         <f>(O2*G2+G3*O3+O4*G4+G5*O5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+O13*G13+G14*O14+O15*G15+G16*O16+G17*O17+O18*G18+G19*O19)/100</f>
-        <v>13659.785600000001</v>
+        <v>13844.2896</v>
       </c>
       <c r="P23" s="23">
         <f>(P2*G2+G3*P3+P4*G4+G5*P5+G6*P6+G7*P7+G8*P8+G9*P9+G10*P10+G11*P11+G12*P12+P13*G13+G14*P14+P15*G15+G16*P16+G17*P17+P18*G18+G19*P19)/100</f>
-        <v>13683.918</v>
+        <v>13659.785600000001</v>
       </c>
       <c r="Q23" s="23">
         <f>(Q2*G2+G3*Q3+Q4*G4+G5*Q5+G6*Q6+G7*Q7+G8*Q8+G9*Q9+G10*Q10+G11*Q11+G12*Q12+Q13*G13+G14*Q14+Q15*G15+G16*Q16+G17*Q17+Q18*G18+G19*Q19)/100</f>
-        <v>13839.923600000002</v>
+        <v>13683.918</v>
       </c>
       <c r="R23" s="23">
         <f>(R2*G2+G3*R3+R4*G4+G5*R5+G6*R6+G7*R7+G8*R8+G9*R9+G10*R10+G11*R11+G12*R12+R13*G13+G14*R14+R15*G15+G16*R16+G17*R17+R18*G18+G19*R19)/100</f>
-        <v>13475.503999999999</v>
+        <v>13839.923600000002</v>
       </c>
       <c r="S23" s="23">
         <f>(S2*G2+G3*S3+S4*G4+G5*S5+G6*S6+G7*S7+G8*S8+G9*S9+G10*S10+G11*S11+G12*S12+S13*G13+G14*S14+S15*G15+G16*S16+G17*S17+S18*G18+G19*S19)/100</f>
-        <v>13192.96</v>
+        <v>13475.503999999999</v>
       </c>
       <c r="T23" s="23">
         <f>(T2*G2+G3*T3+T4*G4+G5*T5+G6*T6+G7*T7+G8*T8+G9*T9+G10*T10+G11*T11+G12*T12+T13*G13+G14*T14+T15*G15+G16*T16+G17*T17+T18*G18+G19*T19)/100</f>
-        <v>12923.761999999999</v>
+        <v>13192.96</v>
       </c>
       <c r="U23" s="23">
         <f>(U2*G2+G3*U3+U4*G4+G5*U5+G6*U6+G7*U7+G8*U8+G9*U9+G10*U10+G11*U11+G12*U12+U13*G13+G14*U14+U15*G15+G16*U16+G17*U17+U18*G18+G19*U19)/100</f>
+        <v>12923.761999999999</v>
+      </c>
+      <c r="V23" s="23">
+        <f>(V2*G2+G3*V3+V4*G4+G5*V5+G6*V6+G7*V7+G8*V8+G9*V9+G10*V10+G11*V11+G12*V12+V13*G13+G14*V14+V15*G15+G16*V16+G17*V17+V18*G18+G19*V19)/100</f>
         <v>13102.8776</v>
-      </c>
-      <c r="V23" s="23">
-        <f>(V3*G3+G4*V4+V5*G5+G6*V6+G7*V7+G8*V8+G9*V9+G10*V10+G11*V11+G12*V12+G14*V14+V15*G15+G16*V16+V17*G17+G18*V18+G19*V19)/100</f>
-        <v>12191.99</v>
       </c>
       <c r="W23" s="23">
         <f>(W3*G3+G4*W4+W5*G5+G6*W6+G7*W7+G8*W8+G9*W9+G10*W10+G11*W11+G12*W12+G14*W14+W15*G15+G16*W16+W17*G17+G18*W18+G19*W19)/100</f>
-        <v>11970.357599999999</v>
+        <v>12191.99</v>
       </c>
       <c r="X23" s="23">
         <f>(X3*G3+G4*X4+X5*G5+G6*X6+G7*X7+G8*X8+G9*X9+G10*X10+G11*X11+G12*X12+G14*X14+X15*G15+G16*X16+X17*G17+G18*X18+G19*X19)/100</f>
-        <v>11989.4576</v>
+        <v>11970.357599999999</v>
       </c>
       <c r="Y23" s="23">
         <f>(Y3*G3+G4*Y4+Y5*G5+G6*Y6+G7*Y7+G8*Y8+G9*Y9+G10*Y10+G11*Y11+G12*Y12+G14*Y14+Y15*G15+G16*Y16+Y17*G17+G18*Y18+G19*Y19)/100</f>
-        <v>11896.177600000001</v>
+        <v>11989.4576</v>
       </c>
       <c r="Z23" s="23">
         <f>(Z3*G3+G4*Z4+Z5*G5+G6*Z6+G7*Z7+G8*Z8+G9*Z9+G10*Z10+G11*Z11+G12*Z12+G14*Z14+Z15*G15+G16*Z16+Z17*G17+G18*Z18+G19*Z19)/100</f>
-        <v>11552.98</v>
+        <v>11896.177600000001</v>
       </c>
       <c r="AA23" s="23">
         <f>(AA3*G3+G4*AA4+AA5*G5+G6*AA6+G7*AA7+G8*AA8+G9*AA9+G10*AA10+G11*AA11+G12*AA12+G14*AA14+AA15*G15+G16*AA16+AA17*G17+G18*AA18+G19*AA19)/100</f>
-        <v>11467.277599999999</v>
+        <v>11552.98</v>
       </c>
       <c r="AB23" s="23">
         <f>(AB3*G3+G4*AB4+AB5*G5+G6*AB6+G7*AB7+G8*AB8+G9*AB9+G10*AB10+G11*AB11+G12*AB12+G14*AB14+AB15*G15+G16*AB16+AB17*G17+G18*AB18+G19*AB19)/100</f>
+        <v>11467.277599999999</v>
+      </c>
+      <c r="AC23" s="23">
+        <f>(AC3*G3+G4*AC4+AC5*G5+G6*AC6+G7*AC7+G8*AC8+G9*AC9+G10*AC10+G11*AC11+G12*AC12+G14*AC14+AC15*G15+G16*AC16+AC17*G17+G18*AC18+G19*AC19)/100</f>
         <v>10332.035599999999</v>
       </c>
-      <c r="AC23" s="23">
-        <f>(AC5*G5+G6*AC6+AC7*G7+G8*AC8+G9*AC9+G10*AC10+G11*AC11+G12*AC12+G14*AC14+G20*AC20+G15*AC15+AC16*G16+G17*AC17+AC18*G18+G19*AC19)/100</f>
+      <c r="AD23" s="23">
+        <f>(AD5*G5+G6*AD6+AD7*G7+G8*AD8+G9*AD9+G10*AD10+G11*AD11+G12*AD12+G14*AD14+G20*AD20+G15*AD15+AD16*G16+G17*AD17+AD18*G18+G19*AD19)/100</f>
         <v>9234.9995999999992</v>
-      </c>
-      <c r="AD23" s="23" t="e">
-        <f>(AD5*G5+G7*AD7+AD8*G8+G9*AD9+#REF!*#REF!+G10*AD10+G11*AD11+G12*AD12+G14*AD14+G19*AD19+G20*AD20+AD6*G6+G15*AD15+#REF!*#REF!+G16*AD16+G17*AD17+AD18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AD3+#REF!*#REF!)/100</f>
-        <v>#REF!</v>
       </c>
       <c r="AE23" s="23" t="e">
         <f>(AE5*G5+G7*AE7+AE8*G8+G9*AE9+#REF!*#REF!+G10*AE10+G11*AE11+G12*AE12+G14*AE14+G19*AE19+G20*AE20+AE6*G6+G15*AE15+#REF!*#REF!+G16*AE16+G17*AE17+AE18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AE3+#REF!*#REF!)/100</f>
@@ -4776,11 +4835,11 @@
         <v>#REF!</v>
       </c>
       <c r="AG23" s="23" t="e">
-        <f>(AG5*G5+G7*AG7+AG8*G8+G9*AG9+#REF!*#REF!+G10*AG10+G11*AG11+G12*AG12+G14*AG14+G19*AG19+G20*AG20+AG6*G6+G15*AG15+#REF!*#REF!+G16*AG16+G18*AG18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AG3+#REF!*#REF!+G4*AG4)/100</f>
+        <f>(AG5*G5+G7*AG7+AG8*G8+G9*AG9+#REF!*#REF!+G10*AG10+G11*AG11+G12*AG12+G14*AG14+G19*AG19+G20*AG20+AG6*G6+G15*AG15+#REF!*#REF!+G16*AG16+G17*AG17+AG18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AG3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AH23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AH3*G3+#REF!*#REF!+G4*AH4+G5*AH5+G7*AH7+G8*AH8+G9*AH9+#REF!*#REF!+G10*AH10+AH11*G11+G12*AH12+AH14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AH20+AH6*G6+#REF!*#REF!+G16*AH16+G18*AH18+G19*AH19)/100</f>
+        <f>(AH5*G5+G7*AH7+AH8*G8+G9*AH9+#REF!*#REF!+G10*AH10+G11*AH11+G12*AH12+G14*AH14+G19*AH19+G20*AH20+AH6*G6+G15*AH15+#REF!*#REF!+G16*AH16+G18*AH18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AH3+#REF!*#REF!+G4*AH4)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AI23" s="23" t="e">
@@ -4788,7 +4847,7 @@
         <v>#REF!</v>
       </c>
       <c r="AJ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AJ3*G3+#REF!*#REF!+G4*AJ4+G5*AJ5+AJ7*G7+AJ8*G8+AJ9*G9+#REF!*#REF!+G10*AJ10+AJ11*G11+G12*AJ12+AJ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AJ20+G6*AJ6+#REF!*#REF!+G16*AJ16+G18*AJ18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AJ3*G3+#REF!*#REF!+G4*AJ4+G5*AJ5+G7*AJ7+G8*AJ8+G9*AJ9+#REF!*#REF!+G10*AJ10+AJ11*G11+G12*AJ12+AJ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AJ20+AJ6*G6+#REF!*#REF!+G16*AJ16+G18*AJ18+G19*AJ19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AK23" s="23" t="e">
@@ -4796,19 +4855,19 @@
         <v>#REF!</v>
       </c>
       <c r="AL23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AL3*G3+#REF!*#REF!+G4*AL4+G8*AL8+AL9*G9+#REF!*#REF!+AL10*G10+G11*AL11+G14*AL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AL6+#REF!*#REF!+G16*AL16+G18*AL18+G7*AL7+G5*AL5+G12*AL12+G20*AL20)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AL3*G3+#REF!*#REF!+G4*AL4+G5*AL5+AL7*G7+AL8*G8+AL9*G9+#REF!*#REF!+G10*AL10+AL11*G11+G12*AL12+AL14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AL20+G6*AL6+#REF!*#REF!+G16*AL16+G18*AL18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AM23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AM3*G3+#REF!*#REF!+G4*AM4+G8*AM8+AM9*G9+#REF!*#REF!+AM10*G10+G11*AM11+G14*AM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AM6+#REF!*#REF!+G16*AM16+G18*AM18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AM3*G3+#REF!*#REF!+G4*AM4+G8*AM8+AM9*G9+#REF!*#REF!+AM10*G10+G11*AM11+G14*AM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AM6+#REF!*#REF!+G16*AM16+G18*AM18+G7*AM7+G5*AM5+G12*AM12+G20*AM20)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AN23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+G9*AN9+#REF!*#REF!+G10*AN10+AN11*G11+AN14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AN6*G6+#REF!*#REF!+G16*AN16+G18*AN18+G19*AN19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+AN9*G9+#REF!*#REF!+AN10*G10+G11*AN11+G14*AN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AN6+#REF!*#REF!+G16*AN16+G18*AN18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AO23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+AO9*G9+#REF!*#REF!+AO10*G10+G11*AO11+G14*AO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AO6+#REF!*#REF!+G16*AO16+G18*AO18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+G9*AO9+#REF!*#REF!+G10*AO10+AO11*G11+AO14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AO6*G6+#REF!*#REF!+G16*AO16+G18*AO18+G19*AO19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AP23" s="23" t="e">
@@ -4816,7 +4875,7 @@
         <v>#REF!</v>
       </c>
       <c r="AQ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AQ3*G3+#REF!*#REF!+G4*AQ4+G8*AQ8+AQ9*G9+AQ10*G10+AQ11*G11+G14*AQ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AQ6+#REF!*#REF!+G16*AQ16+G18*AQ18+G19*AQ19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AQ3*G3+#REF!*#REF!+G4*AQ4+G8*AQ8+AQ9*G9+#REF!*#REF!+AQ10*G10+G11*AQ11+G14*AQ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AQ6+#REF!*#REF!+G16*AQ16+G18*AQ18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AR23" s="23" t="e">
@@ -4836,19 +4895,19 @@
         <v>#REF!</v>
       </c>
       <c r="AV23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AV3*G3+#REF!*#REF!+G4*AV4+G8*AV8+AV9*G9+AV10*G10+AV11*G11+G14*AV14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AV6+#REF!*#REF!+G16*AV16+G18*AV18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AV3*G3+#REF!*#REF!+G4*AV4+G8*AV8+AV9*G9+AV10*G10+AV11*G11+G14*AV14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AV6+#REF!*#REF!+G16*AV16+G18*AV18+G19*AV19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AW23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AW3*G3+#REF!*#REF!+G4*AW4+G8*AW8+AW10*G10+AW11*G11+G14*AW14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AW6+#REF!*#REF!+G16*AW16+G18*AW18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AW3*G3+#REF!*#REF!+G4*AW4+G8*AW8+AW9*G9+AW10*G10+AW11*G11+G14*AW14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AW6+#REF!*#REF!+G16*AW16+G18*AW18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AX23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AX3*G3+#REF!*#REF!+G4*AX4+G8*AX8+G10*AX10+AX11*G11+AX14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AX6*G6+#REF!*#REF!+G16*AX16+G18*AX18+G19*AX19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AX3*G3+#REF!*#REF!+G4*AX4+G8*AX8+AX10*G10+AX11*G11+G14*AX14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AX6+#REF!*#REF!+G16*AX16+G18*AX18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AY23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AY3*G3+#REF!*#REF!+G4*AY4+G10*AY10+AY11*G11+AY14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AY6*G6+#REF!*#REF!+G16*AY16+G18*AY18+G19*AY19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AY3*G3+#REF!*#REF!+G4*AY4+G8*AY8+G10*AY10+AY11*G11+AY14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AY6*G6+#REF!*#REF!+G16*AY16+G18*AY18+G19*AY19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AZ23" s="23" t="e">
@@ -4860,7 +4919,7 @@
         <v>#REF!</v>
       </c>
       <c r="BB23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BB3*G3+#REF!*#REF!+G4*BB4+G10*BB10+BB11*G11+BB14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BB6*G6+G16*BB16+G18*BB18+G19*BB19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BB3*G3+#REF!*#REF!+G4*BB4+G10*BB10+BB11*G11+BB14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BB6*G6+#REF!*#REF!+G16*BB16+G18*BB18+G19*BB19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BC23" s="23" t="e">
@@ -4888,15 +4947,15 @@
         <v>#REF!</v>
       </c>
       <c r="BI23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BI3*G3+#REF!*#REF!+G4*BI4+G10*BI10+G11*BI11+G14*BI14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BI6+BI16*G16+G18*BI18+G19*BI19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BI3*G3+#REF!*#REF!+G4*BI4+G10*BI10+BI11*G11+BI14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BI6*G6+G16*BI16+G18*BI18+G19*BI19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BJ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BJ3*G3+#REF!*#REF!+G4*BJ4+G10*BJ10+G14*BJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BJ6+BJ16*G16+G18*BJ18+G19*BJ19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BJ3*G3+#REF!*#REF!+G4*BJ4+G10*BJ10+G11*BJ11+G14*BJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BJ6+BJ16*G16+G18*BJ18+G19*BJ19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BK23" s="23" t="e">
-        <f>(#REF!*#REF!+BK3*G3+G4*BK4+G14*BK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BK6+BK16*G16+G18*BK18+G19*BK19+G22*BK22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BK3*G3+#REF!*#REF!+G4*BK4+G10*BK10+G14*BK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BK6+BK16*G16+G18*BK18+G19*BK19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BL23" s="23" t="e">
@@ -4907,16 +4966,16 @@
         <f>(#REF!*#REF!+BM3*G3+G4*BM4+G14*BM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BM6+BM16*G16+G18*BM18+G19*BM19+G22*BM22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BN23" s="30" t="e">
+      <c r="BN23" s="23" t="e">
         <f>(#REF!*#REF!+BN3*G3+G4*BN4+G14*BN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BN6+BN16*G16+G18*BN18+G19*BN19+G22*BN22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BO23" s="23" t="e">
+      <c r="BO23" s="30" t="e">
         <f>(#REF!*#REF!+BO3*G3+G4*BO4+G14*BO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BO6+BO16*G16+G18*BO18+G19*BO19+G22*BO22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BP23" s="23" t="e">
-        <f>(#REF!*#REF!+BP3*G3+G14*BP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BP6+BP16*G16+G18*BP18+G19*BP19+G22*BP22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+BP3*G3+G4*BP4+G14*BP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BP6+BP16*G16+G18*BP18+G19*BP19+G22*BP22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BQ23" s="23" t="e">
@@ -4927,15 +4986,19 @@
         <f>(#REF!*#REF!+BR3*G3+G14*BR14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BR6+BR16*G16+G18*BR18+G19*BR19+G22*BR22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BS23" s="13"/>
+      <c r="BS23" s="23" t="e">
+        <f>(#REF!*#REF!+BS3*G3+G14*BS14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BS6+BS16*G16+G18*BS18+G19*BS19+G22*BS22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <v>#REF!</v>
+      </c>
       <c r="BT23" s="13"/>
       <c r="BU23" s="13"/>
       <c r="BV23" s="13"/>
-      <c r="BY23" s="15">
+      <c r="BW23" s="13"/>
+      <c r="BZ23" s="15">
         <v>1149.48</v>
       </c>
     </row>
-    <row r="24" spans="1:77" ht="44.25" customHeight="1" thickBot="1">
+    <row r="24" spans="1:78" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -5006,29 +5069,30 @@
       <c r="BP24" s="14"/>
       <c r="BQ24" s="14"/>
       <c r="BR24" s="14"/>
-      <c r="BS24" s="23">
-        <f>SUM(BS2:BS20)</f>
-        <v>12571.202799999999</v>
-      </c>
+      <c r="BS24" s="14"/>
       <c r="BT24" s="23">
         <f>SUM(BT2:BT20)</f>
-        <v>13020.522800000001</v>
-      </c>
-      <c r="BU24" s="24">
-        <f>BT24-BS24</f>
-        <v>449.32000000000153</v>
-      </c>
-      <c r="BV24" s="13">
-        <f>((BT24-BS24)/BS24)*100</f>
-        <v>3.5742005530290353</v>
-      </c>
-      <c r="BY24" s="15">
-        <f>SUM(BY5:BY23)</f>
-        <v>1472.0683999999992</v>
-      </c>
-    </row>
-    <row r="25" spans="1:77">
-      <c r="BS25" s="15">
+        <v>12977.112800000001</v>
+      </c>
+      <c r="BU24" s="23">
+        <f>SUM(BU2:BU20)</f>
+        <v>12609.442800000001</v>
+      </c>
+      <c r="BV24" s="24">
+        <f>BU24-BT24</f>
+        <v>-367.67000000000007</v>
+      </c>
+      <c r="BW24" s="13">
+        <f>((BU24-BT24)/BT24)*100</f>
+        <v>-2.8332188034922532</v>
+      </c>
+      <c r="BZ24" s="15">
+        <f>SUM(BZ5:BZ23)</f>
+        <v>655.07839999999919</v>
+      </c>
+    </row>
+    <row r="25" spans="1:78" x14ac:dyDescent="0.25">
+      <c r="BT25" s="15">
         <v>12034.32</v>
       </c>
     </row>
@@ -5086,17 +5150,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DECD697-7590-4F64-9E15-0FA62A69A078}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.59765625" customWidth="1"/>
-    <col min="2" max="2" width="17.59765625" style="20" customWidth="1"/>
-    <col min="3" max="7" width="17.59765625" customWidth="1"/>
-    <col min="9" max="9" width="17.59765625" customWidth="1"/>
-    <col min="10" max="10" width="9.59765625" customWidth="1"/>
-    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="20" customWidth="1"/>
+    <col min="3" max="7" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>11</v>
       </c>
@@ -5129,7 +5193,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -5155,7 +5219,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>9823</v>
+        <v>7260</v>
       </c>
       <c r="J2" s="25"/>
       <c r="L2" s="21">
@@ -5167,7 +5231,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -5193,7 +5257,7 @@
       <c r="G3" s="17"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1074</v>
+        <v>925</v>
       </c>
       <c r="J3" s="26"/>
       <c r="L3" s="21">
@@ -5205,7 +5269,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -5231,7 +5295,7 @@
       <c r="G4" s="17"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6298</v>
+        <v>6098</v>
       </c>
       <c r="J4" s="26"/>
       <c r="L4" s="21">
@@ -5243,7 +5307,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -5268,7 +5332,7 @@
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>638</v>
+        <v>607.9</v>
       </c>
       <c r="J5" s="26"/>
       <c r="L5" s="21">
@@ -5280,7 +5344,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -5305,7 +5369,7 @@
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4799</v>
+        <v>4950</v>
       </c>
       <c r="J6" s="26"/>
       <c r="L6" s="21">
@@ -5317,7 +5381,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -5343,7 +5407,7 @@
       <c r="G7" s="18"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>4022</v>
+        <v>3959</v>
       </c>
       <c r="J7" s="26"/>
       <c r="L7" s="21">
@@ -5355,7 +5419,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -5381,7 +5445,7 @@
       <c r="G8" s="18"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>39600</v>
+        <v>38000</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -5392,7 +5456,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -5418,7 +5482,7 @@
       <c r="G9" s="17"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>11290</v>
+        <v>10800</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -5429,7 +5493,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -5455,7 +5519,7 @@
       <c r="G10" s="18"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5126</v>
+        <v>5800</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -5466,7 +5530,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -5503,7 +5567,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -5529,7 +5593,7 @@
       <c r="G12" s="18"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>29460</v>
+        <v>28240</v>
       </c>
       <c r="J12" s="26"/>
       <c r="L12" s="21">
@@ -5541,7 +5605,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -5567,7 +5631,7 @@
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1009</v>
+        <v>680.1</v>
       </c>
       <c r="J13" s="26"/>
       <c r="L13" s="21">
@@ -5579,7 +5643,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -5605,7 +5669,7 @@
       <c r="G14" s="17"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8051</v>
+        <v>7678</v>
       </c>
       <c r="J14" s="26"/>
       <c r="L14" s="21">
@@ -5617,7 +5681,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -5643,7 +5707,7 @@
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12145</v>
+        <v>12256</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
@@ -5655,7 +5719,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -5681,7 +5745,7 @@
       <c r="G16" s="17"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>221.02</v>
+        <v>220.86</v>
       </c>
       <c r="J16" s="26"/>
       <c r="L16" s="21">
@@ -5693,7 +5757,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -5719,7 +5783,7 @@
       <c r="G17" s="17"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>184.42</v>
+        <v>190.72</v>
       </c>
       <c r="J17" s="26"/>
       <c r="L17" s="21">
@@ -5731,7 +5795,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -5757,7 +5821,7 @@
       <c r="G18" s="18"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1866</v>
+        <v>1818</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -5768,7 +5832,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -5783,14 +5847,14 @@
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
       <c r="G19" s="18"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>86.7</v>
+        <v>72</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -5801,7 +5865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5835,7 +5899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5869,7 +5933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5903,7 +5967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5937,7 +6001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5971,7 +6035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6005,7 +6069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6039,7 +6103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6073,7 +6137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="str">
         <f>'התיק העדכני'!E20</f>
         <v>אירודרום קבוצה</v>
@@ -6095,7 +6159,7 @@
       <c r="G28" s="19"/>
       <c r="I28" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="J28" s="26"/>
       <c r="L28" s="21">
@@ -6115,15 +6179,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7390F3B9-AE45-44AE-B4DF-D92B58EB94BD}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
-    <col min="3" max="7" width="17.59765625" customWidth="1"/>
-    <col min="9" max="9" width="17.59765625" customWidth="1"/>
-    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
+    <col min="3" max="7" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -6153,7 +6217,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -6179,7 +6243,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>9823</v>
+        <v>7260</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+GEMINI!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
@@ -6190,7 +6254,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -6216,7 +6280,7 @@
       <c r="G3" s="7"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1074</v>
+        <v>925</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
@@ -6227,7 +6291,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -6253,7 +6317,7 @@
       <c r="G4" s="7"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6298</v>
+        <v>6098</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+GEMINI!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
@@ -6264,7 +6328,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -6290,7 +6354,7 @@
       <c r="G5" s="7"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>638</v>
+        <v>607.9</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
@@ -6301,7 +6365,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -6327,7 +6391,7 @@
       <c r="G6" s="7"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4799</v>
+        <v>4950</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
@@ -6338,7 +6402,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -6364,7 +6428,7 @@
       <c r="G7" s="8"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>4022</v>
+        <v>3959</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+GEMINI!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
@@ -6375,7 +6439,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -6401,7 +6465,7 @@
       <c r="G8" s="8"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>39600</v>
+        <v>38000</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+GEMINI!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -6412,7 +6476,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -6438,7 +6502,7 @@
       <c r="G9" s="8"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>11290</v>
+        <v>10800</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+GEMINI!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -6449,7 +6513,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -6475,7 +6539,7 @@
       <c r="G10" s="8"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5126</v>
+        <v>5800</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+GEMINI!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -6486,7 +6550,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -6523,7 +6587,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -6549,7 +6613,7 @@
       <c r="G12" s="8"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>29460</v>
+        <v>28240</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+GEMINI!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
@@ -6560,7 +6624,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -6586,7 +6650,7 @@
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1009</v>
+        <v>680.1</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+GEMINI!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
@@ -6597,7 +6661,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -6623,7 +6687,7 @@
       <c r="G14" s="7"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8051</v>
+        <v>7678</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
@@ -6634,7 +6698,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -6660,7 +6724,7 @@
       <c r="G15" s="7"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12145</v>
+        <v>12256</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+GEMINI!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
@@ -6671,7 +6735,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -6697,7 +6761,7 @@
       <c r="G16" s="7"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>221.02</v>
+        <v>220.86</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
@@ -6708,7 +6772,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -6734,7 +6798,7 @@
       <c r="G17" s="7"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>184.42</v>
+        <v>190.72</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+GEMINI!E17+PERPLIXITY!E17+DEEPSEEK!E17)/4</f>
@@ -6745,7 +6809,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -6771,7 +6835,7 @@
       <c r="G18" s="8"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1866</v>
+        <v>1818</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+GEMINI!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -6782,7 +6846,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -6797,14 +6861,14 @@
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
       <c r="G19" s="8"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>86.7</v>
+        <v>72</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+GEMINI!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -6815,7 +6879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -6827,7 +6891,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -6839,7 +6903,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -6851,7 +6915,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -6863,7 +6927,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -6875,7 +6939,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -6887,7 +6951,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -6899,7 +6963,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -6911,7 +6975,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -6931,15 +6995,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88497C0-21A8-47C7-B959-3D6DF74EF6E2}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
-    <col min="3" max="6" width="17.59765625" customWidth="1"/>
-    <col min="9" max="9" width="17.59765625" customWidth="1"/>
-    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
+    <col min="3" max="6" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -6969,7 +7033,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -6995,7 +7059,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>9823</v>
+        <v>7260</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+GEMINI!E2+DEEPSEEK!E2)/4</f>
@@ -7006,7 +7070,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -7032,7 +7096,7 @@
       <c r="G3" s="10"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1074</v>
+        <v>925</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
@@ -7043,7 +7107,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -7069,7 +7133,7 @@
       <c r="G4" s="10"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6298</v>
+        <v>6098</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+GEMINI!E4+DEEPSEEK!E4)/4</f>
@@ -7080,7 +7144,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -7106,7 +7170,7 @@
       <c r="G5" s="10"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>638</v>
+        <v>607.9</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
@@ -7117,7 +7181,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -7143,7 +7207,7 @@
       <c r="G6" s="10"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4799</v>
+        <v>4950</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
@@ -7154,7 +7218,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -7180,7 +7244,7 @@
       <c r="G7" s="10"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>4022</v>
+        <v>3959</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+GEMINI!E7+DEEPSEEK!E7)/4</f>
@@ -7191,7 +7255,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -7216,7 +7280,7 @@
       </c>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>39600</v>
+        <v>38000</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+GEMINI!E8+DEEPSEEK!E8)/4</f>
@@ -7227,7 +7291,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -7252,7 +7316,7 @@
       </c>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>11290</v>
+        <v>10800</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+GEMINI!E9+DEEPSEEK!E9)/4</f>
@@ -7263,7 +7327,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -7288,7 +7352,7 @@
       </c>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5126</v>
+        <v>5800</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+GEMINI!E10+DEEPSEEK!E10)/4</f>
@@ -7299,7 +7363,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -7335,7 +7399,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -7361,7 +7425,7 @@
       <c r="G12" s="10"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>29460</v>
+        <v>28240</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+GEMINI!E12+DEEPSEEK!E12)/4</f>
@@ -7372,7 +7436,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -7398,7 +7462,7 @@
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1009</v>
+        <v>680.1</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+CHATGPT!E13+GEMINI!E13+DEEPSEEK!E13)/4</f>
@@ -7409,7 +7473,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -7435,7 +7499,7 @@
       <c r="G14" s="10"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8051</v>
+        <v>7678</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
@@ -7446,7 +7510,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -7472,7 +7536,7 @@
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12145</v>
+        <v>12256</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
@@ -7483,7 +7547,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -7509,7 +7573,7 @@
       <c r="G16" s="10"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>221.02</v>
+        <v>220.86</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+GEMINI!E16+DEEPSEEK!E16)/4</f>
@@ -7520,7 +7584,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -7546,7 +7610,7 @@
       <c r="G17" s="10"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>184.42</v>
+        <v>190.72</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+GEMINI!E17+DEEPSEEK!E17)/4</f>
@@ -7557,7 +7621,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -7582,7 +7646,7 @@
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1866</v>
+        <v>1818</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
@@ -7593,7 +7657,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -7608,13 +7672,13 @@
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>86.7</v>
+        <v>72</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+GEMINI!E19+DEEPSEEK!E19)/4</f>
@@ -7625,7 +7689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -7637,7 +7701,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -7649,7 +7713,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -7661,7 +7725,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -7673,7 +7737,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -7685,7 +7749,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -7697,7 +7761,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -7709,7 +7773,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -7721,7 +7785,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -7741,16 +7805,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D354D65C-237D-4544-BBD1-8A37190947C4}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
-    <col min="3" max="5" width="17.59765625" customWidth="1"/>
-    <col min="6" max="6" width="20.3984375" customWidth="1"/>
-    <col min="9" max="9" width="17.59765625" customWidth="1"/>
-    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
+    <col min="3" max="5" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -7779,7 +7843,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -7805,7 +7869,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>9823</v>
+        <v>7260</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+PERPLIXITY!E2+GEMINI!E2)/4</f>
@@ -7816,7 +7880,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -7842,7 +7906,7 @@
       <c r="G3" s="31"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>1074</v>
+        <v>925</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
@@ -7853,7 +7917,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -7878,7 +7942,7 @@
       </c>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6298</v>
+        <v>6098</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+GEMINI!E4)/4</f>
@@ -7889,7 +7953,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -7915,7 +7979,7 @@
       <c r="G5" s="31"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>638</v>
+        <v>607.9</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
@@ -7926,7 +7990,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -7952,7 +8016,7 @@
       <c r="G6" s="31"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4799</v>
+        <v>4950</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
@@ -7963,7 +8027,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -7988,7 +8052,7 @@
       </c>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>4022</v>
+        <v>3959</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+GEMINI!E7)/4</f>
@@ -7999,7 +8063,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -8025,7 +8089,7 @@
       <c r="G8" s="31"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>39600</v>
+        <v>38000</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+GEMINI!E8)/4</f>
@@ -8036,7 +8100,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -8062,7 +8126,7 @@
       <c r="G9" s="31"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>11290</v>
+        <v>10800</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+GEMINI!E9)/4</f>
@@ -8073,7 +8137,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -8099,7 +8163,7 @@
       <c r="G10" s="31"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5126</v>
+        <v>5800</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+GEMINI!E10)/4</f>
@@ -8110,7 +8174,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -8147,7 +8211,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -8173,7 +8237,7 @@
       <c r="G12" s="31"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>29460</v>
+        <v>28240</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+GEMINI!E12)/4</f>
@@ -8184,7 +8248,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -8210,12 +8274,12 @@
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>1009</v>
+        <v>680.1</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
     </row>
-    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -8241,7 +8305,7 @@
       <c r="G14" s="31"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8051</v>
+        <v>7678</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
@@ -8252,7 +8316,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -8277,7 +8341,7 @@
       </c>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+PERPLIXITY!E15+GEMINI!E15)/4</f>
@@ -8288,7 +8352,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -8313,7 +8377,7 @@
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12145</v>
+        <v>12256</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
@@ -8324,7 +8388,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -8350,7 +8414,7 @@
       <c r="G17" s="31"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>221.02</v>
+        <v>220.86</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+GEMINI!E17)/4</f>
@@ -8361,7 +8425,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -8387,7 +8451,7 @@
       <c r="G18" s="31"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>184.42</v>
+        <v>190.72</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+GEMINI!E18)/4</f>
@@ -8398,7 +8462,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -8413,11 +8477,11 @@
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1866</v>
+        <v>1818</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+GEMINI!E19)/4</f>
@@ -8428,7 +8492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -8439,7 +8503,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -8451,7 +8515,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -8463,7 +8527,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -8475,7 +8539,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -8487,7 +8551,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -8499,7 +8563,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -8511,7 +8575,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -8523,7 +8587,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\BURSA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/673b1203f7e82b27/מסמכים/GitHub/BURSA/BURSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4C4BA0-E721-42FA-9823-8447E4B0DE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{7B4C4BA0-E721-42FA-9823-8447E4B0DE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{681CB859-165D-4DEC-8AF5-36B27A466259}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
   <sheets>
     <sheet name="התיק העדכני" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="113">
   <si>
     <t>MTF מחקה אינדקס תעשיה ישראל</t>
   </si>
@@ -365,6 +376,9 @@
   </si>
   <si>
     <t>מחיר 05/02/2026</t>
+  </si>
+  <si>
+    <t>מחיר 06/02/2026</t>
   </si>
 </sst>
 </file>
@@ -374,11 +388,11 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₪&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -387,7 +401,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -438,13 +452,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -835,9 +849,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא של Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -875,7 +889,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -981,7 +995,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1123,7 +1137,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1131,22 +1145,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86B4639-EF9D-4B16-B2C9-0D5E9C5EEC8B}">
-  <dimension ref="A1:BZ25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:CA25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="5" width="17.5703125" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="61" width="14.85546875" customWidth="1"/>
-    <col min="62" max="71" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="13" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="11" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="11.5703125" customWidth="1"/>
+    <col min="1" max="5" width="17.59765625" customWidth="1"/>
+    <col min="6" max="6" width="13.296875" customWidth="1"/>
+    <col min="7" max="7" width="11.59765625" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="62" width="14.8984375" customWidth="1"/>
+    <col min="63" max="72" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="13" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="11" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="11.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1175,214 +1189,217 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BK1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BL1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BM1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BN1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BO1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="BO1" s="6" t="s">
+      <c r="BP1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="BP1" s="6" t="s">
+      <c r="BQ1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="BQ1" s="6" t="s">
+      <c r="BR1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="BR1" s="6" t="s">
+      <c r="BS1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BS1" s="6" t="s">
+      <c r="BT1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BU1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="BU1" s="6" t="s">
+      <c r="BV1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BW1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="BX1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="BX1" s="12" t="s">
+      <c r="BY1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="BY1" s="12" t="s">
+      <c r="BZ1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="BZ1" s="12" t="s">
+      <c r="CA1" s="12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A2" s="1">
         <v>282012</v>
       </c>
@@ -1411,48 +1428,50 @@
         <v>11000</v>
       </c>
       <c r="I2" s="13">
-        <v>7260</v>
+        <v>8800</v>
       </c>
       <c r="J2" s="13">
-        <v>7260</v>
+        <v>8800</v>
       </c>
       <c r="K2" s="13">
+        <v>9030</v>
+      </c>
+      <c r="L2" s="13">
         <v>9823</v>
       </c>
-      <c r="L2" s="13">
+      <c r="M2" s="13">
         <v>9787</v>
       </c>
-      <c r="M2" s="13">
+      <c r="N2" s="13">
         <v>9650</v>
       </c>
-      <c r="N2" s="13">
+      <c r="O2" s="13">
         <v>9981</v>
       </c>
-      <c r="O2" s="13">
+      <c r="P2" s="13">
         <v>12130</v>
       </c>
-      <c r="P2" s="13">
+      <c r="Q2" s="13">
         <v>11840</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="R2" s="13">
         <v>11400</v>
       </c>
-      <c r="R2" s="13">
+      <c r="S2" s="13">
         <v>11360</v>
       </c>
-      <c r="S2" s="13">
+      <c r="T2" s="13">
         <v>11000</v>
       </c>
-      <c r="T2" s="13">
+      <c r="U2" s="13">
         <v>10700</v>
       </c>
-      <c r="U2" s="13">
+      <c r="V2" s="13">
         <v>10400</v>
       </c>
-      <c r="V2" s="13">
+      <c r="W2" s="13">
         <v>11230</v>
       </c>
-      <c r="W2" s="6"/>
       <c r="X2" s="6"/>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
@@ -1493,29 +1512,30 @@
       <c r="BI2" s="6"/>
       <c r="BJ2" s="6"/>
       <c r="BK2" s="6"/>
-      <c r="BL2" s="32"/>
-      <c r="BM2" s="6"/>
+      <c r="BL2" s="6"/>
+      <c r="BM2" s="32"/>
       <c r="BN2" s="6"/>
-      <c r="BO2" s="32"/>
-      <c r="BP2" s="6"/>
+      <c r="BO2" s="6"/>
+      <c r="BP2" s="32"/>
       <c r="BQ2" s="6"/>
       <c r="BR2" s="6"/>
       <c r="BS2" s="6"/>
-      <c r="BT2" s="13">
-        <f t="shared" ref="BT2:BT20" si="0">(G2*H2)/100-BZ2</f>
+      <c r="BT2" s="6"/>
+      <c r="BU2" s="13">
+        <f t="shared" ref="BU2:BU20" si="0">(G2*H2)/100-CA2</f>
         <v>770</v>
       </c>
-      <c r="BU2" s="13">
-        <f t="shared" ref="BU2:BU20" si="1">(G2*H2)/100</f>
+      <c r="BV2" s="13">
+        <f t="shared" ref="BV2:BV20" si="1">(G2*H2)/100</f>
         <v>770</v>
       </c>
-      <c r="BV2" s="6"/>
       <c r="BW2" s="6"/>
-      <c r="BX2" s="25"/>
+      <c r="BX2" s="6"/>
       <c r="BY2" s="25"/>
       <c r="BZ2" s="25"/>
-    </row>
-    <row r="3" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CA2" s="25"/>
+    </row>
+    <row r="3" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A3" s="1">
         <v>1227552</v>
       </c>
@@ -1544,66 +1564,68 @@
         <v>1153.6300000000001</v>
       </c>
       <c r="I3" s="13">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="J3" s="13">
-        <v>925</v>
+        <v>969.7</v>
       </c>
       <c r="K3" s="13">
+        <v>921</v>
+      </c>
+      <c r="L3" s="13">
         <v>1074</v>
       </c>
-      <c r="L3" s="13">
+      <c r="M3" s="13">
         <v>1245</v>
-      </c>
-      <c r="M3" s="13">
-        <v>1311</v>
       </c>
       <c r="N3" s="13">
         <v>1311</v>
       </c>
       <c r="O3" s="13">
+        <v>1311</v>
+      </c>
+      <c r="P3" s="13">
         <v>1340</v>
       </c>
-      <c r="P3" s="13">
+      <c r="Q3" s="13">
         <v>1500</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="R3" s="13">
         <v>1424</v>
       </c>
-      <c r="R3" s="13">
+      <c r="S3" s="13">
         <v>1348</v>
       </c>
-      <c r="S3" s="13">
+      <c r="T3" s="13">
         <v>1373</v>
       </c>
-      <c r="T3" s="13">
+      <c r="U3" s="13">
         <v>1331</v>
       </c>
-      <c r="U3" s="13">
+      <c r="V3" s="13">
         <v>1386</v>
       </c>
-      <c r="V3" s="13">
+      <c r="W3" s="13">
         <v>1342</v>
       </c>
-      <c r="W3" s="13">
+      <c r="X3" s="13">
         <v>1250</v>
-      </c>
-      <c r="X3" s="13">
-        <v>1389</v>
       </c>
       <c r="Y3" s="13">
         <v>1389</v>
       </c>
       <c r="Z3" s="13">
+        <v>1389</v>
+      </c>
+      <c r="AA3" s="13">
         <v>1367</v>
       </c>
-      <c r="AA3" s="13">
+      <c r="AB3" s="13">
         <v>1026</v>
       </c>
-      <c r="AB3" s="13">
+      <c r="AC3" s="13">
         <v>949.1</v>
       </c>
-      <c r="AC3" s="13"/>
       <c r="AD3" s="13"/>
       <c r="AE3" s="13"/>
       <c r="AF3" s="13"/>
@@ -1619,8 +1641,8 @@
       <c r="AP3" s="13"/>
       <c r="AQ3" s="13"/>
       <c r="AR3" s="13"/>
-      <c r="AS3" s="14"/>
-      <c r="AT3" s="13"/>
+      <c r="AS3" s="13"/>
+      <c r="AT3" s="14"/>
       <c r="AU3" s="13"/>
       <c r="AV3" s="13"/>
       <c r="AW3" s="13"/>
@@ -1638,42 +1660,43 @@
       <c r="BI3" s="13"/>
       <c r="BJ3" s="13"/>
       <c r="BK3" s="13"/>
-      <c r="BL3" s="29"/>
-      <c r="BM3" s="13"/>
+      <c r="BL3" s="13"/>
+      <c r="BM3" s="29"/>
       <c r="BN3" s="13"/>
-      <c r="BO3" s="29"/>
-      <c r="BP3" s="13"/>
+      <c r="BO3" s="13"/>
+      <c r="BP3" s="29"/>
       <c r="BQ3" s="13"/>
       <c r="BR3" s="13"/>
       <c r="BS3" s="13"/>
-      <c r="BT3" s="13">
+      <c r="BT3" s="13"/>
+      <c r="BU3" s="13">
         <f t="shared" si="0"/>
         <v>-126.73159999999989</v>
       </c>
-      <c r="BU3" s="13">
+      <c r="BV3" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BV3" s="13">
-        <f>(BU3-BT3)</f>
+      <c r="BW3" s="13">
+        <f>(BV3-BU3)</f>
         <v>126.73159999999989</v>
       </c>
-      <c r="BW3" s="13">
-        <f>((BK3-H3)/H3)*100</f>
+      <c r="BX3" s="13">
+        <f>((BL3-H3)/H3)*100</f>
         <v>-100</v>
       </c>
-      <c r="BX3">
+      <c r="BY3">
         <v>68</v>
       </c>
-      <c r="BY3">
+      <c r="BZ3">
         <v>1340</v>
       </c>
-      <c r="BZ3" s="15">
-        <f>(BX3*BY3-BX3*H3)/100</f>
+      <c r="CA3" s="15">
+        <f>(BY3*BZ3-BY3*H3)/100</f>
         <v>126.73159999999989</v>
       </c>
     </row>
-    <row r="4" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A4" s="1">
         <v>587014</v>
       </c>
@@ -1687,7 +1710,7 @@
       </c>
       <c r="D4" s="6" t="str">
         <f>IF(I4&lt;GEMINI!L4,"למכור בהפסד",IF(I4&gt;GEMINI!M4,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור בהפסד</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>33</v>
@@ -1702,66 +1725,68 @@
         <v>5925</v>
       </c>
       <c r="I4" s="13">
-        <v>6098</v>
+        <v>5990</v>
       </c>
       <c r="J4" s="13">
-        <v>6098</v>
+        <v>5990</v>
       </c>
       <c r="K4" s="13">
+        <v>5956</v>
+      </c>
+      <c r="L4" s="13">
         <v>6298</v>
       </c>
-      <c r="L4" s="13">
+      <c r="M4" s="13">
         <v>6295</v>
       </c>
-      <c r="M4" s="13">
+      <c r="N4" s="13">
         <v>6370</v>
       </c>
-      <c r="N4" s="13">
+      <c r="O4" s="13">
         <v>6140</v>
       </c>
-      <c r="O4" s="13">
+      <c r="P4" s="13">
         <v>7252</v>
       </c>
-      <c r="P4" s="13">
+      <c r="Q4" s="13">
         <v>7120</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="R4" s="13">
         <v>7048</v>
       </c>
-      <c r="R4" s="13">
+      <c r="S4" s="13">
         <v>6979</v>
       </c>
-      <c r="S4" s="13">
+      <c r="T4" s="13">
         <v>6680</v>
       </c>
-      <c r="T4" s="13">
+      <c r="U4" s="13">
         <v>6111</v>
       </c>
-      <c r="U4" s="13">
+      <c r="V4" s="13">
         <v>6050</v>
       </c>
-      <c r="V4" s="13">
+      <c r="W4" s="13">
         <v>6169</v>
       </c>
-      <c r="W4" s="13">
+      <c r="X4" s="13">
         <v>6300</v>
-      </c>
-      <c r="X4" s="13">
-        <v>6335</v>
       </c>
       <c r="Y4" s="13">
         <v>6335</v>
       </c>
       <c r="Z4" s="13">
+        <v>6335</v>
+      </c>
+      <c r="AA4" s="13">
         <v>6444</v>
-      </c>
-      <c r="AA4" s="13">
-        <v>5749</v>
       </c>
       <c r="AB4" s="13">
         <v>5749</v>
       </c>
-      <c r="AC4" s="13"/>
+      <c r="AC4" s="13">
+        <v>5749</v>
+      </c>
       <c r="AD4" s="13"/>
       <c r="AE4" s="13"/>
       <c r="AF4" s="13"/>
@@ -1796,36 +1821,37 @@
       <c r="BI4" s="13"/>
       <c r="BJ4" s="13"/>
       <c r="BK4" s="13"/>
-      <c r="BL4" s="29"/>
-      <c r="BM4" s="13"/>
+      <c r="BL4" s="13"/>
+      <c r="BM4" s="29"/>
       <c r="BN4" s="13"/>
-      <c r="BO4" s="29"/>
-      <c r="BP4" s="13"/>
+      <c r="BO4" s="13"/>
+      <c r="BP4" s="29"/>
       <c r="BQ4" s="13"/>
       <c r="BR4" s="13"/>
       <c r="BS4" s="13"/>
-      <c r="BT4" s="13">
+      <c r="BT4" s="13"/>
+      <c r="BU4" s="13">
         <f t="shared" si="0"/>
         <v>1185</v>
       </c>
-      <c r="BU4" s="13">
+      <c r="BV4" s="13">
         <f t="shared" si="1"/>
         <v>1185</v>
       </c>
-      <c r="BV4" s="13">
-        <f>(BU4-BT4)</f>
+      <c r="BW4" s="13">
+        <f>(BV4-BU4)</f>
         <v>0</v>
       </c>
-      <c r="BW4" s="13">
-        <f>((BK4-H4)/H4)*100</f>
+      <c r="BX4" s="13">
+        <f>((BL4-H4)/H4)*100</f>
         <v>-100</v>
       </c>
-      <c r="BZ4" s="15">
-        <f>(BX4*BY4-BX4*H4)/100</f>
+      <c r="CA4" s="15">
+        <f>(BY4*BZ4-BY4*H4)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A5" s="1">
         <v>1099787</v>
       </c>
@@ -1854,96 +1880,98 @@
         <v>617.53</v>
       </c>
       <c r="I5" s="13">
-        <v>607.9</v>
+        <v>622.4</v>
       </c>
       <c r="J5" s="13">
-        <v>607.9</v>
+        <v>622.4</v>
       </c>
       <c r="K5" s="13">
+        <v>594.9</v>
+      </c>
+      <c r="L5" s="13">
         <v>638</v>
       </c>
-      <c r="L5" s="13">
+      <c r="M5" s="13">
         <v>587.5</v>
       </c>
-      <c r="M5" s="13">
+      <c r="N5" s="13">
         <v>577.9</v>
       </c>
-      <c r="N5" s="13">
+      <c r="O5" s="13">
         <v>559</v>
       </c>
-      <c r="O5" s="13">
+      <c r="P5" s="13">
         <v>570</v>
       </c>
-      <c r="P5" s="13">
+      <c r="Q5" s="13">
         <v>575.70000000000005</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="R5" s="13">
         <v>612.6</v>
       </c>
-      <c r="R5" s="13">
+      <c r="S5" s="13">
         <v>638.29999999999995</v>
       </c>
-      <c r="S5" s="13">
+      <c r="T5" s="13">
         <v>630.29999999999995</v>
       </c>
-      <c r="T5" s="13">
+      <c r="U5" s="13">
         <v>626</v>
       </c>
-      <c r="U5" s="13">
+      <c r="V5" s="13">
         <v>595.4</v>
       </c>
-      <c r="V5" s="13">
+      <c r="W5" s="13">
         <v>667.1</v>
       </c>
-      <c r="W5" s="13">
+      <c r="X5" s="13">
         <v>651</v>
-      </c>
-      <c r="X5" s="13">
-        <v>641.1</v>
       </c>
       <c r="Y5" s="13">
         <v>641.1</v>
       </c>
       <c r="Z5" s="13">
+        <v>641.1</v>
+      </c>
+      <c r="AA5" s="13">
         <v>607.1</v>
       </c>
-      <c r="AA5" s="13">
+      <c r="AB5" s="13">
         <v>583</v>
       </c>
-      <c r="AB5" s="13">
+      <c r="AC5" s="13">
         <v>581.6</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AD5" s="13">
         <v>578.70000000000005</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AE5" s="13">
         <v>590</v>
       </c>
-      <c r="AE5" s="13">
+      <c r="AF5" s="13">
         <v>554.70000000000005</v>
       </c>
-      <c r="AF5" s="13">
+      <c r="AG5" s="13">
         <v>511.8</v>
       </c>
-      <c r="AG5" s="13">
+      <c r="AH5" s="13">
         <v>487</v>
       </c>
-      <c r="AH5" s="13">
+      <c r="AI5" s="13">
         <v>478.8</v>
       </c>
-      <c r="AI5" s="13">
+      <c r="AJ5" s="13">
         <v>485.5</v>
       </c>
-      <c r="AJ5" s="13">
+      <c r="AK5" s="13">
         <v>453.4</v>
       </c>
-      <c r="AK5" s="13">
+      <c r="AL5" s="13">
         <v>426.1</v>
       </c>
-      <c r="AL5" s="13">
+      <c r="AM5" s="13">
         <v>423.2</v>
       </c>
-      <c r="AM5" s="13"/>
       <c r="AN5" s="13"/>
       <c r="AO5" s="13"/>
       <c r="AP5" s="13"/>
@@ -1968,27 +1996,28 @@
       <c r="BI5" s="13"/>
       <c r="BJ5" s="13"/>
       <c r="BK5" s="13"/>
-      <c r="BL5" s="29"/>
-      <c r="BM5" s="13"/>
+      <c r="BL5" s="13"/>
+      <c r="BM5" s="29"/>
       <c r="BN5" s="13"/>
-      <c r="BO5" s="29"/>
-      <c r="BP5" s="13"/>
+      <c r="BO5" s="13"/>
+      <c r="BP5" s="29"/>
       <c r="BQ5" s="13"/>
       <c r="BR5" s="13"/>
       <c r="BS5" s="13"/>
-      <c r="BT5" s="13">
+      <c r="BT5" s="13"/>
+      <c r="BU5" s="13">
         <f t="shared" si="0"/>
         <v>975.6973999999999</v>
       </c>
-      <c r="BU5" s="13">
+      <c r="BV5" s="13">
         <f t="shared" si="1"/>
         <v>975.6973999999999</v>
       </c>
-      <c r="BV5" s="13"/>
       <c r="BW5" s="13"/>
-      <c r="BZ5" s="15"/>
-    </row>
-    <row r="6" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BX5" s="13"/>
+      <c r="CA5" s="15"/>
+    </row>
+    <row r="6" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A6" s="2">
         <v>1166768</v>
       </c>
@@ -2017,69 +2046,71 @@
         <v>4040</v>
       </c>
       <c r="I6" s="13">
-        <v>4950</v>
+        <v>4647</v>
       </c>
       <c r="J6" s="13">
-        <v>4950</v>
+        <v>4647</v>
       </c>
       <c r="K6" s="13">
+        <v>4650</v>
+      </c>
+      <c r="L6" s="13">
         <v>4799</v>
       </c>
-      <c r="L6" s="13">
+      <c r="M6" s="13">
         <v>4740</v>
       </c>
-      <c r="M6" s="13">
+      <c r="N6" s="13">
         <v>4350</v>
       </c>
-      <c r="N6" s="13">
+      <c r="O6" s="13">
         <v>4355</v>
       </c>
-      <c r="O6" s="13">
+      <c r="P6" s="13">
         <v>4500</v>
       </c>
-      <c r="P6" s="13">
+      <c r="Q6" s="13">
         <v>4424</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="R6" s="13">
         <v>4412</v>
       </c>
-      <c r="R6" s="13">
+      <c r="S6" s="13">
         <v>4450</v>
       </c>
-      <c r="S6" s="13">
+      <c r="T6" s="13">
         <v>4238</v>
       </c>
-      <c r="T6" s="13">
+      <c r="U6" s="13">
         <v>3970</v>
       </c>
-      <c r="U6" s="13">
+      <c r="V6" s="13">
         <v>3870</v>
       </c>
-      <c r="V6" s="13">
+      <c r="W6" s="13">
         <v>3805</v>
       </c>
-      <c r="W6" s="13">
+      <c r="X6" s="13">
         <v>3667</v>
-      </c>
-      <c r="X6" s="13">
-        <v>3582</v>
       </c>
       <c r="Y6" s="13">
         <v>3582</v>
       </c>
       <c r="Z6" s="13">
+        <v>3582</v>
+      </c>
+      <c r="AA6" s="13">
         <v>3570</v>
       </c>
-      <c r="AA6" s="13">
+      <c r="AB6" s="13">
         <v>3619</v>
       </c>
-      <c r="AB6" s="13">
+      <c r="AC6" s="13">
         <v>3650</v>
       </c>
-      <c r="AC6" s="13">
+      <c r="AD6" s="13">
         <v>3720</v>
       </c>
-      <c r="AD6" s="13"/>
       <c r="AE6" s="13"/>
       <c r="AF6" s="13"/>
       <c r="AG6" s="13"/>
@@ -2113,41 +2144,42 @@
       <c r="BI6" s="13"/>
       <c r="BJ6" s="13"/>
       <c r="BK6" s="13"/>
-      <c r="BL6" s="29"/>
-      <c r="BM6" s="13"/>
+      <c r="BL6" s="13"/>
+      <c r="BM6" s="29"/>
       <c r="BN6" s="13"/>
-      <c r="BO6" s="29"/>
-      <c r="BP6" s="13"/>
+      <c r="BO6" s="13"/>
+      <c r="BP6" s="29"/>
       <c r="BQ6" s="13"/>
       <c r="BR6" s="13"/>
-      <c r="BT6" s="13">
+      <c r="BS6" s="13"/>
+      <c r="BU6" s="13">
         <f t="shared" si="0"/>
         <v>1033.7</v>
       </c>
-      <c r="BU6" s="13">
+      <c r="BV6" s="13">
         <f t="shared" si="1"/>
         <v>1010</v>
       </c>
-      <c r="BV6" s="13">
-        <f t="shared" ref="BV6" si="2">(BU6-BT6)</f>
+      <c r="BW6" s="13">
+        <f t="shared" ref="BW6" si="2">(BV6-BU6)</f>
         <v>-23.700000000000045</v>
       </c>
-      <c r="BW6" s="13">
-        <f>((BK6-H6)/H6)*100</f>
+      <c r="BX6" s="13">
+        <f>((BL6-H6)/H6)*100</f>
         <v>-100</v>
       </c>
-      <c r="BX6">
+      <c r="BY6">
         <v>5</v>
       </c>
-      <c r="BY6">
+      <c r="BZ6">
         <v>3566</v>
       </c>
-      <c r="BZ6" s="15">
-        <f>(BX6*BY6-BX6*H6)/100</f>
+      <c r="CA6" s="15">
+        <f>(BY6*BZ6-BY6*H6)/100</f>
         <v>-23.7</v>
       </c>
     </row>
-    <row r="7" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A7" s="1">
         <v>1148899</v>
       </c>
@@ -2176,96 +2208,98 @@
         <v>3585</v>
       </c>
       <c r="I7" s="13">
-        <v>3959</v>
+        <v>3954</v>
       </c>
       <c r="J7" s="13">
-        <v>3959</v>
+        <v>3954</v>
       </c>
       <c r="K7" s="13">
+        <v>3955</v>
+      </c>
+      <c r="L7" s="13">
         <v>4022</v>
       </c>
-      <c r="L7" s="13">
+      <c r="M7" s="13">
         <v>4033</v>
       </c>
-      <c r="M7" s="13">
+      <c r="N7" s="13">
         <v>3988</v>
       </c>
-      <c r="N7" s="13">
+      <c r="O7" s="13">
         <v>3916</v>
       </c>
-      <c r="O7" s="13">
+      <c r="P7" s="13">
         <v>3954</v>
       </c>
-      <c r="P7" s="13">
+      <c r="Q7" s="13">
         <v>3932</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="R7" s="13">
         <v>3949</v>
       </c>
-      <c r="R7" s="13">
+      <c r="S7" s="13">
         <v>3943</v>
       </c>
-      <c r="S7" s="13">
+      <c r="T7" s="13">
         <v>3928</v>
       </c>
-      <c r="T7" s="13">
+      <c r="U7" s="13">
         <v>3913</v>
       </c>
-      <c r="U7" s="13">
+      <c r="V7" s="13">
         <v>3860</v>
       </c>
-      <c r="V7" s="13">
+      <c r="W7" s="13">
         <v>3893</v>
       </c>
-      <c r="W7" s="13">
+      <c r="X7" s="13">
         <v>3900</v>
-      </c>
-      <c r="X7" s="13">
-        <v>3842</v>
       </c>
       <c r="Y7" s="13">
         <v>3842</v>
       </c>
       <c r="Z7" s="13">
+        <v>3842</v>
+      </c>
+      <c r="AA7" s="13">
         <v>3841</v>
       </c>
-      <c r="AA7" s="13">
+      <c r="AB7" s="13">
         <v>3809</v>
       </c>
-      <c r="AB7" s="13">
+      <c r="AC7" s="13">
         <v>3810</v>
       </c>
-      <c r="AC7" s="13">
+      <c r="AD7" s="13">
         <v>3798</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AE7" s="13">
         <v>3713</v>
       </c>
-      <c r="AE7" s="13">
+      <c r="AF7" s="13">
         <v>3657</v>
       </c>
-      <c r="AF7" s="13">
+      <c r="AG7" s="13">
         <v>3592</v>
       </c>
-      <c r="AG7" s="13">
+      <c r="AH7" s="13">
         <v>3621</v>
       </c>
-      <c r="AH7" s="13">
+      <c r="AI7" s="13">
         <v>3572</v>
       </c>
-      <c r="AI7" s="13">
+      <c r="AJ7" s="13">
         <v>3580</v>
       </c>
-      <c r="AJ7" s="13">
+      <c r="AK7" s="13">
         <v>3569</v>
       </c>
-      <c r="AK7" s="13">
+      <c r="AL7" s="13">
         <v>3659</v>
       </c>
-      <c r="AL7" s="13">
+      <c r="AM7" s="13">
         <v>3656</v>
       </c>
-      <c r="AM7" s="13"/>
       <c r="AN7" s="13"/>
       <c r="AO7" s="13"/>
       <c r="AP7" s="13"/>
@@ -2290,27 +2324,28 @@
       <c r="BI7" s="13"/>
       <c r="BJ7" s="13"/>
       <c r="BK7" s="13"/>
-      <c r="BL7" s="29"/>
-      <c r="BM7" s="13"/>
+      <c r="BL7" s="13"/>
+      <c r="BM7" s="29"/>
       <c r="BN7" s="13"/>
-      <c r="BO7" s="29"/>
-      <c r="BP7" s="13"/>
+      <c r="BO7" s="13"/>
+      <c r="BP7" s="29"/>
       <c r="BQ7" s="13"/>
       <c r="BR7" s="13"/>
       <c r="BS7" s="13"/>
-      <c r="BT7" s="13">
+      <c r="BT7" s="13"/>
+      <c r="BU7" s="13">
         <f t="shared" si="0"/>
         <v>2509.5</v>
       </c>
-      <c r="BU7" s="13">
+      <c r="BV7" s="13">
         <f t="shared" si="1"/>
         <v>2509.5</v>
       </c>
-      <c r="BV7" s="13"/>
       <c r="BW7" s="13"/>
-      <c r="BZ7" s="15"/>
-    </row>
-    <row r="8" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BX7" s="13"/>
+      <c r="CA7" s="15"/>
+    </row>
+    <row r="8" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A8" s="1">
         <v>1082379</v>
       </c>
@@ -2339,132 +2374,134 @@
         <v>37875</v>
       </c>
       <c r="I8" s="13">
-        <v>38000</v>
+        <v>40740</v>
       </c>
       <c r="J8" s="13">
-        <v>38000</v>
+        <v>40740</v>
       </c>
       <c r="K8" s="13">
+        <v>39070</v>
+      </c>
+      <c r="L8" s="13">
         <v>39600</v>
       </c>
-      <c r="L8" s="13">
+      <c r="M8" s="13">
         <v>43640</v>
       </c>
-      <c r="M8" s="13">
+      <c r="N8" s="13">
         <v>42700</v>
       </c>
-      <c r="N8" s="13">
+      <c r="O8" s="13">
         <v>42140</v>
       </c>
-      <c r="O8" s="13">
+      <c r="P8" s="13">
         <v>43490</v>
       </c>
-      <c r="P8" s="13">
+      <c r="Q8" s="13">
         <v>40750</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="R8" s="13">
         <v>40900</v>
       </c>
-      <c r="R8" s="13">
+      <c r="S8" s="13">
         <v>40790</v>
       </c>
-      <c r="S8" s="13">
+      <c r="T8" s="13">
         <v>40820</v>
       </c>
-      <c r="T8" s="13">
+      <c r="U8" s="13">
         <v>41570</v>
       </c>
-      <c r="U8" s="13">
+      <c r="V8" s="13">
         <v>42050</v>
       </c>
-      <c r="V8" s="13">
+      <c r="W8" s="13">
         <v>39960</v>
       </c>
-      <c r="W8" s="13">
+      <c r="X8" s="13">
         <v>39990</v>
-      </c>
-      <c r="X8" s="13">
-        <v>38680</v>
       </c>
       <c r="Y8" s="13">
         <v>38680</v>
       </c>
       <c r="Z8" s="13">
+        <v>38680</v>
+      </c>
+      <c r="AA8" s="13">
         <v>37770</v>
       </c>
-      <c r="AA8" s="13">
+      <c r="AB8" s="13">
         <v>36330</v>
       </c>
-      <c r="AB8" s="13">
+      <c r="AC8" s="13">
         <v>38680</v>
       </c>
-      <c r="AC8" s="13">
+      <c r="AD8" s="13">
         <v>39090</v>
       </c>
-      <c r="AD8" s="13">
+      <c r="AE8" s="13">
         <v>37300</v>
       </c>
-      <c r="AE8" s="13">
+      <c r="AF8" s="13">
         <v>37650</v>
       </c>
-      <c r="AF8" s="13">
+      <c r="AG8" s="13">
         <v>37300</v>
       </c>
-      <c r="AG8" s="13">
+      <c r="AH8" s="13">
         <v>39450</v>
       </c>
-      <c r="AH8" s="13">
+      <c r="AI8" s="13">
         <v>38390</v>
       </c>
-      <c r="AI8" s="13">
+      <c r="AJ8" s="13">
         <v>38800</v>
       </c>
-      <c r="AJ8" s="13">
+      <c r="AK8" s="13">
         <v>38510</v>
-      </c>
-      <c r="AK8" s="13">
-        <v>38970</v>
       </c>
       <c r="AL8" s="13">
         <v>38970</v>
       </c>
       <c r="AM8" s="13">
-        <v>37700</v>
+        <v>38970</v>
       </c>
       <c r="AN8" s="13">
         <v>37700</v>
       </c>
       <c r="AO8" s="13">
+        <v>37700</v>
+      </c>
+      <c r="AP8" s="13">
         <v>37750</v>
       </c>
-      <c r="AP8" s="13">
+      <c r="AQ8" s="13">
         <v>38430</v>
       </c>
-      <c r="AQ8" s="13">
+      <c r="AR8" s="13">
         <v>38250</v>
       </c>
-      <c r="AR8" s="13">
+      <c r="AS8" s="13">
         <v>40110</v>
       </c>
-      <c r="AS8" s="13">
+      <c r="AT8" s="13">
         <v>40820</v>
       </c>
-      <c r="AT8" s="13">
+      <c r="AU8" s="13">
         <v>39320</v>
       </c>
-      <c r="AU8" s="13">
+      <c r="AV8" s="13">
         <v>37800</v>
       </c>
-      <c r="AV8" s="13">
+      <c r="AW8" s="13">
         <v>36620</v>
       </c>
-      <c r="AW8" s="13">
+      <c r="AX8" s="13">
         <v>37130</v>
       </c>
-      <c r="AX8" s="13">
+      <c r="AY8" s="13">
         <v>35850</v>
       </c>
-      <c r="AY8" s="13"/>
       <c r="AZ8" s="13"/>
       <c r="BA8" s="13"/>
       <c r="BB8" s="13"/>
@@ -2477,39 +2514,40 @@
       <c r="BI8" s="13"/>
       <c r="BJ8" s="13"/>
       <c r="BK8" s="13"/>
-      <c r="BL8" s="29"/>
-      <c r="BM8" s="13"/>
+      <c r="BL8" s="13"/>
+      <c r="BM8" s="29"/>
       <c r="BN8" s="13"/>
-      <c r="BO8" s="29"/>
-      <c r="BP8" s="13"/>
+      <c r="BO8" s="13"/>
+      <c r="BP8" s="29"/>
       <c r="BQ8" s="13"/>
       <c r="BR8" s="13"/>
       <c r="BS8" s="13"/>
-      <c r="BT8" s="13">
+      <c r="BT8" s="13"/>
+      <c r="BU8" s="13">
         <f t="shared" si="0"/>
         <v>806.25</v>
       </c>
-      <c r="BU8" s="13">
+      <c r="BV8" s="13">
         <f t="shared" si="1"/>
         <v>757.5</v>
       </c>
-      <c r="BV8" s="13">
-        <f t="shared" ref="BV8:BV11" si="3">(BU8-BT8)</f>
+      <c r="BW8" s="13">
+        <f t="shared" ref="BW8:BW11" si="3">(BV8-BU8)</f>
         <v>-48.75</v>
       </c>
-      <c r="BW8" s="13"/>
-      <c r="BX8">
+      <c r="BX8" s="13"/>
+      <c r="BY8">
         <v>3</v>
       </c>
-      <c r="BY8">
+      <c r="BZ8">
         <v>36250</v>
       </c>
-      <c r="BZ8" s="15">
-        <f t="shared" ref="BZ8:BZ18" si="4">(BX8*BY8-BX8*H8)/100</f>
+      <c r="CA8" s="15">
+        <f t="shared" ref="CA8:CA18" si="4">(BY8*BZ8-BY8*H8)/100</f>
         <v>-48.75</v>
       </c>
     </row>
-    <row r="9" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A9" s="1">
         <v>629014</v>
       </c>
@@ -2538,126 +2576,128 @@
         <v>9227</v>
       </c>
       <c r="I9" s="13">
-        <v>10800</v>
+        <v>10820</v>
       </c>
       <c r="J9" s="13">
-        <v>10800</v>
+        <v>10820</v>
       </c>
       <c r="K9" s="13">
+        <v>10680</v>
+      </c>
+      <c r="L9" s="13">
         <v>11290</v>
       </c>
-      <c r="L9" s="13">
+      <c r="M9" s="13">
         <v>11020</v>
-      </c>
-      <c r="M9" s="13">
-        <v>10100</v>
       </c>
       <c r="N9" s="13">
         <v>10100</v>
       </c>
       <c r="O9" s="13">
+        <v>10100</v>
+      </c>
+      <c r="P9" s="13">
         <v>10240</v>
       </c>
-      <c r="P9" s="13">
+      <c r="Q9" s="13">
         <v>9891</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="R9" s="13">
         <v>9956</v>
       </c>
-      <c r="R9" s="13">
+      <c r="S9" s="13">
         <v>9910</v>
       </c>
-      <c r="S9" s="13">
+      <c r="T9" s="13">
         <v>9960</v>
       </c>
-      <c r="T9" s="13">
+      <c r="U9" s="13">
         <v>9924</v>
       </c>
-      <c r="U9" s="13">
+      <c r="V9" s="13">
         <v>9999</v>
       </c>
-      <c r="V9" s="13">
+      <c r="W9" s="13">
         <v>9962</v>
       </c>
-      <c r="W9" s="13">
+      <c r="X9" s="13">
         <v>9979</v>
-      </c>
-      <c r="X9" s="13">
-        <v>10130</v>
       </c>
       <c r="Y9" s="13">
         <v>10130</v>
       </c>
       <c r="Z9" s="13">
+        <v>10130</v>
+      </c>
+      <c r="AA9" s="13">
         <v>10400</v>
       </c>
-      <c r="AA9" s="13">
+      <c r="AB9" s="13">
         <v>10320</v>
       </c>
-      <c r="AB9" s="13">
+      <c r="AC9" s="13">
         <v>10300</v>
       </c>
-      <c r="AC9" s="13">
+      <c r="AD9" s="13">
         <v>10310</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AE9" s="13">
         <v>9672</v>
       </c>
-      <c r="AE9" s="13">
+      <c r="AF9" s="13">
         <v>9953</v>
       </c>
-      <c r="AF9" s="13">
+      <c r="AG9" s="13">
         <v>10090</v>
       </c>
-      <c r="AG9" s="13">
+      <c r="AH9" s="13">
         <v>10070</v>
       </c>
-      <c r="AH9" s="13">
+      <c r="AI9" s="13">
         <v>10030</v>
       </c>
-      <c r="AI9" s="13">
+      <c r="AJ9" s="13">
         <v>10120</v>
       </c>
-      <c r="AJ9" s="13">
+      <c r="AK9" s="13">
         <v>10000</v>
       </c>
-      <c r="AK9" s="13">
+      <c r="AL9" s="13">
         <v>10080</v>
       </c>
-      <c r="AL9" s="13">
+      <c r="AM9" s="13">
         <v>10030</v>
-      </c>
-      <c r="AM9" s="13">
-        <v>9726</v>
       </c>
       <c r="AN9" s="13">
         <v>9726</v>
       </c>
       <c r="AO9" s="13">
+        <v>9726</v>
+      </c>
+      <c r="AP9" s="13">
         <v>9659</v>
       </c>
-      <c r="AP9" s="13">
+      <c r="AQ9" s="13">
         <v>9670</v>
       </c>
-      <c r="AQ9" s="13">
+      <c r="AR9" s="13">
         <v>9590</v>
       </c>
-      <c r="AR9" s="13">
+      <c r="AS9" s="13">
         <v>9588</v>
       </c>
-      <c r="AS9" s="13">
+      <c r="AT9" s="13">
         <v>9400</v>
       </c>
-      <c r="AT9" s="13">
+      <c r="AU9" s="13">
         <v>9320</v>
       </c>
-      <c r="AU9" s="13">
+      <c r="AV9" s="13">
         <v>9071</v>
       </c>
-      <c r="AV9" s="13">
+      <c r="AW9" s="13">
         <v>9271</v>
       </c>
-      <c r="AW9" s="13"/>
       <c r="AX9" s="13"/>
       <c r="AY9" s="13"/>
       <c r="AZ9" s="13"/>
@@ -2672,39 +2712,40 @@
       <c r="BI9" s="13"/>
       <c r="BJ9" s="13"/>
       <c r="BK9" s="13"/>
-      <c r="BL9" s="29"/>
-      <c r="BM9" s="13"/>
+      <c r="BL9" s="13"/>
+      <c r="BM9" s="29"/>
       <c r="BN9" s="13"/>
-      <c r="BO9" s="29"/>
-      <c r="BP9" s="13"/>
+      <c r="BO9" s="13"/>
+      <c r="BP9" s="29"/>
       <c r="BQ9" s="13"/>
       <c r="BR9" s="13"/>
       <c r="BS9" s="13"/>
-      <c r="BT9" s="13">
+      <c r="BT9" s="13"/>
+      <c r="BU9" s="13">
         <f t="shared" si="0"/>
         <v>-38.65</v>
       </c>
-      <c r="BU9" s="13">
+      <c r="BV9" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BV9" s="13">
+      <c r="BW9" s="13">
         <f t="shared" si="3"/>
         <v>38.65</v>
       </c>
-      <c r="BW9" s="13"/>
-      <c r="BX9">
+      <c r="BX9" s="13"/>
+      <c r="BY9">
         <v>5</v>
       </c>
-      <c r="BY9">
+      <c r="BZ9">
         <v>10000</v>
       </c>
-      <c r="BZ9" s="15">
+      <c r="CA9" s="15">
         <f t="shared" si="4"/>
         <v>38.65</v>
       </c>
     </row>
-    <row r="10" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A10" s="1">
         <v>1141464</v>
       </c>
@@ -2733,208 +2774,211 @@
         <v>4834</v>
       </c>
       <c r="I10" s="13">
-        <v>5800</v>
+        <v>5067</v>
       </c>
       <c r="J10" s="13">
-        <v>5800</v>
+        <v>5067</v>
       </c>
       <c r="K10" s="13">
+        <v>5067</v>
+      </c>
+      <c r="L10" s="13">
         <v>5126</v>
       </c>
-      <c r="L10" s="13">
+      <c r="M10" s="13">
         <v>5164</v>
-      </c>
-      <c r="M10" s="13">
-        <v>4809</v>
       </c>
       <c r="N10" s="13">
         <v>4809</v>
       </c>
       <c r="O10" s="13">
+        <v>4809</v>
+      </c>
+      <c r="P10" s="13">
         <v>4849</v>
       </c>
-      <c r="P10" s="13">
+      <c r="Q10" s="13">
         <v>4821</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="R10" s="13">
         <v>4925</v>
       </c>
-      <c r="R10" s="13">
+      <c r="S10" s="13">
         <v>5013</v>
-      </c>
-      <c r="S10" s="13">
-        <v>5050</v>
       </c>
       <c r="T10" s="13">
         <v>5050</v>
       </c>
       <c r="U10" s="13">
+        <v>5050</v>
+      </c>
+      <c r="V10" s="13">
         <v>4930</v>
       </c>
-      <c r="V10" s="13">
+      <c r="W10" s="13">
         <v>5150</v>
       </c>
-      <c r="W10" s="13">
+      <c r="X10" s="13">
         <v>5283</v>
-      </c>
-      <c r="X10" s="13">
-        <v>5253</v>
       </c>
       <c r="Y10" s="13">
         <v>5253</v>
       </c>
       <c r="Z10" s="13">
+        <v>5253</v>
+      </c>
+      <c r="AA10" s="13">
         <v>5400</v>
       </c>
-      <c r="AA10" s="13">
+      <c r="AB10" s="13">
         <v>5522</v>
       </c>
-      <c r="AB10" s="13">
+      <c r="AC10" s="13">
         <v>5690</v>
       </c>
-      <c r="AC10" s="13">
+      <c r="AD10" s="13">
         <v>5749</v>
       </c>
-      <c r="AD10" s="13">
+      <c r="AE10" s="13">
         <v>5840</v>
-      </c>
-      <c r="AE10" s="13">
-        <v>5650</v>
       </c>
       <c r="AF10" s="13">
         <v>5650</v>
       </c>
       <c r="AG10" s="13">
+        <v>5650</v>
+      </c>
+      <c r="AH10" s="13">
         <v>5841</v>
       </c>
-      <c r="AH10" s="13">
+      <c r="AI10" s="13">
         <v>5758</v>
       </c>
-      <c r="AI10" s="13">
+      <c r="AJ10" s="13">
         <v>5673</v>
       </c>
-      <c r="AJ10" s="13">
+      <c r="AK10" s="13">
         <v>5609</v>
       </c>
-      <c r="AK10" s="13">
+      <c r="AL10" s="13">
         <v>5750</v>
       </c>
-      <c r="AL10" s="13">
+      <c r="AM10" s="13">
         <v>5841</v>
-      </c>
-      <c r="AM10" s="13">
-        <v>5564</v>
       </c>
       <c r="AN10" s="13">
         <v>5564</v>
       </c>
       <c r="AO10" s="13">
+        <v>5564</v>
+      </c>
+      <c r="AP10" s="13">
         <v>5557</v>
       </c>
-      <c r="AP10" s="13">
+      <c r="AQ10" s="13">
         <v>5501</v>
       </c>
-      <c r="AQ10" s="13">
+      <c r="AR10" s="13">
         <v>5250</v>
       </c>
-      <c r="AR10" s="13">
+      <c r="AS10" s="13">
         <v>5270</v>
       </c>
-      <c r="AS10" s="13">
+      <c r="AT10" s="13">
         <v>5149</v>
       </c>
-      <c r="AT10" s="13">
+      <c r="AU10" s="13">
         <v>5092</v>
       </c>
-      <c r="AU10" s="13">
+      <c r="AV10" s="13">
         <v>5228</v>
       </c>
-      <c r="AV10" s="13">
+      <c r="AW10" s="13">
         <v>5301</v>
       </c>
-      <c r="AW10" s="13">
+      <c r="AX10" s="13">
         <v>5159</v>
       </c>
-      <c r="AX10" s="13">
+      <c r="AY10" s="13">
         <v>5198</v>
       </c>
-      <c r="AY10" s="13">
+      <c r="AZ10" s="13">
         <v>5077</v>
       </c>
-      <c r="AZ10" s="13">
+      <c r="BA10" s="13">
         <v>4842</v>
       </c>
-      <c r="BA10" s="13">
+      <c r="BB10" s="13">
         <v>5050</v>
       </c>
-      <c r="BB10" s="13">
+      <c r="BC10" s="13">
         <v>4970</v>
       </c>
-      <c r="BC10" s="13">
+      <c r="BD10" s="13">
         <v>4880</v>
       </c>
-      <c r="BD10" s="13">
+      <c r="BE10" s="13">
         <v>4704</v>
       </c>
-      <c r="BE10" s="13">
+      <c r="BF10" s="13">
         <v>4770</v>
       </c>
-      <c r="BF10" s="13">
+      <c r="BG10" s="13">
         <v>4609</v>
       </c>
-      <c r="BG10" s="13">
+      <c r="BH10" s="13">
         <v>4674</v>
       </c>
-      <c r="BH10" s="13">
+      <c r="BI10" s="13">
         <v>4710</v>
       </c>
-      <c r="BI10" s="13">
+      <c r="BJ10" s="13">
         <v>4688</v>
       </c>
-      <c r="BJ10" s="13">
+      <c r="BK10" s="13">
         <v>4900</v>
       </c>
-      <c r="BK10" s="13">
+      <c r="BL10" s="13">
         <v>5000</v>
       </c>
-      <c r="BL10" s="29">
+      <c r="BM10" s="29">
         <v>4932</v>
       </c>
-      <c r="BM10" s="13"/>
       <c r="BN10" s="13"/>
-      <c r="BO10" s="29"/>
-      <c r="BP10" s="13"/>
+      <c r="BO10" s="13"/>
+      <c r="BP10" s="29"/>
       <c r="BQ10" s="13"/>
       <c r="BR10" s="13"/>
       <c r="BS10" s="13"/>
-      <c r="BT10" s="13">
+      <c r="BT10" s="13"/>
+      <c r="BU10" s="13">
         <f t="shared" si="0"/>
         <v>-87.859799999999964</v>
       </c>
-      <c r="BU10" s="13">
+      <c r="BV10" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BV10" s="13">
+      <c r="BW10" s="13">
         <f t="shared" si="3"/>
         <v>87.859799999999964</v>
       </c>
-      <c r="BW10" s="13">
-        <f>((BK10-H10)/H10)*100</f>
+      <c r="BX10" s="13">
+        <f>((BL10-H10)/H10)*100</f>
         <v>3.434009102192801</v>
       </c>
-      <c r="BX10">
+      <c r="BY10">
         <v>21</v>
       </c>
-      <c r="BY10">
+      <c r="BZ10">
         <v>5252.38</v>
       </c>
-      <c r="BZ10" s="15">
+      <c r="CA10" s="15">
         <f t="shared" si="4"/>
         <v>87.859799999999964</v>
       </c>
     </row>
-    <row r="11" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A11" s="1">
         <v>1166974</v>
       </c>
@@ -2963,90 +3007,92 @@
         <v>901.87</v>
       </c>
       <c r="I11" s="13">
+        <v>1054</v>
+      </c>
+      <c r="J11" s="13">
+        <v>1054</v>
+      </c>
+      <c r="K11" s="13">
+        <v>1063</v>
+      </c>
+      <c r="L11" s="13">
         <v>1099</v>
       </c>
-      <c r="J11" s="13">
-        <v>1099</v>
-      </c>
-      <c r="K11" s="13">
-        <v>1099</v>
-      </c>
-      <c r="L11" s="13">
+      <c r="M11" s="13">
         <v>1173</v>
       </c>
-      <c r="M11" s="13">
+      <c r="N11" s="13">
         <v>1114</v>
       </c>
-      <c r="N11" s="13">
+      <c r="O11" s="13">
         <v>1075</v>
       </c>
-      <c r="O11" s="13">
+      <c r="P11" s="13">
         <v>1109</v>
       </c>
-      <c r="P11" s="13">
+      <c r="Q11" s="13">
         <v>1090</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="R11" s="13">
         <v>1144</v>
       </c>
-      <c r="R11" s="13">
+      <c r="S11" s="13">
         <v>1162</v>
       </c>
-      <c r="S11" s="13">
+      <c r="T11" s="13">
         <v>1109</v>
       </c>
-      <c r="T11" s="13">
+      <c r="U11" s="13">
         <v>1029</v>
       </c>
-      <c r="U11" s="13">
+      <c r="V11" s="13">
         <v>993</v>
       </c>
-      <c r="V11" s="13">
+      <c r="W11" s="13">
         <v>1017</v>
       </c>
-      <c r="W11" s="13">
+      <c r="X11" s="13">
         <v>960</v>
-      </c>
-      <c r="X11" s="13">
-        <v>965</v>
       </c>
       <c r="Y11" s="13">
         <v>965</v>
       </c>
       <c r="Z11" s="13">
+        <v>965</v>
+      </c>
+      <c r="AA11" s="13">
         <v>951.7</v>
       </c>
-      <c r="AA11" s="13">
+      <c r="AB11" s="13">
         <v>946</v>
       </c>
-      <c r="AB11" s="13">
+      <c r="AC11" s="13">
         <v>869.2</v>
       </c>
-      <c r="AC11" s="13">
+      <c r="AD11" s="13">
         <v>865</v>
       </c>
-      <c r="AD11" s="13">
+      <c r="AE11" s="13">
         <v>851</v>
       </c>
-      <c r="AE11" s="13">
+      <c r="AF11" s="13">
         <v>829.3</v>
       </c>
-      <c r="AF11" s="13">
+      <c r="AG11" s="13">
         <v>830</v>
       </c>
-      <c r="AG11" s="13">
+      <c r="AH11" s="13">
         <v>810</v>
       </c>
-      <c r="AH11" s="13">
+      <c r="AI11" s="13">
         <v>812.8</v>
       </c>
-      <c r="AI11" s="13">
+      <c r="AJ11" s="13">
         <v>788</v>
       </c>
-      <c r="AJ11" s="13">
+      <c r="AK11" s="13">
         <v>772</v>
       </c>
-      <c r="AK11" s="13"/>
       <c r="AL11" s="13"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="13"/>
@@ -3073,33 +3119,34 @@
       <c r="BI11" s="13"/>
       <c r="BJ11" s="13"/>
       <c r="BK11" s="13"/>
-      <c r="BL11" s="29"/>
-      <c r="BM11" s="13"/>
+      <c r="BL11" s="13"/>
+      <c r="BM11" s="29"/>
       <c r="BN11" s="13"/>
-      <c r="BO11" s="29"/>
-      <c r="BP11" s="13"/>
+      <c r="BO11" s="13"/>
+      <c r="BP11" s="29"/>
       <c r="BQ11" s="13"/>
       <c r="BR11" s="13"/>
       <c r="BS11" s="13"/>
-      <c r="BT11" s="13">
+      <c r="BT11" s="13"/>
+      <c r="BU11" s="13">
         <f t="shared" si="0"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BU11" s="13">
+      <c r="BV11" s="13">
         <f t="shared" si="1"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BV11" s="13">
+      <c r="BW11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BW11" s="13"/>
-      <c r="BZ11" s="15">
+      <c r="BX11" s="13"/>
+      <c r="CA11" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A12" s="1">
         <v>1176593</v>
       </c>
@@ -3113,7 +3160,7 @@
       </c>
       <c r="D12" s="6" t="str">
         <f>IF(I12&lt;GEMINI!L12,"למכור בהפסד",IF(I12&gt;GEMINI!M12,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>68</v>
@@ -3128,96 +3175,98 @@
         <v>22581.42</v>
       </c>
       <c r="I12" s="13">
+        <v>28730</v>
+      </c>
+      <c r="J12" s="13">
+        <v>28730</v>
+      </c>
+      <c r="K12" s="13">
         <v>28240</v>
       </c>
-      <c r="J12" s="13">
-        <v>28240</v>
-      </c>
-      <c r="K12" s="13">
+      <c r="L12" s="13">
         <v>29460</v>
       </c>
-      <c r="L12" s="13">
+      <c r="M12" s="13">
         <v>28720</v>
-      </c>
-      <c r="M12" s="13">
-        <v>27890</v>
       </c>
       <c r="N12" s="13">
         <v>27890</v>
       </c>
       <c r="O12" s="13">
+        <v>27890</v>
+      </c>
+      <c r="P12" s="13">
         <v>30100</v>
       </c>
-      <c r="P12" s="13">
+      <c r="Q12" s="13">
         <v>30500</v>
       </c>
-      <c r="Q12" s="13">
+      <c r="R12" s="13">
         <v>28850</v>
       </c>
-      <c r="R12" s="13">
+      <c r="S12" s="13">
         <v>27450</v>
       </c>
-      <c r="S12" s="13">
+      <c r="T12" s="13">
         <v>26940</v>
       </c>
-      <c r="T12" s="13">
+      <c r="U12" s="13">
         <v>26800</v>
       </c>
-      <c r="U12" s="13">
+      <c r="V12" s="13">
         <v>25950</v>
       </c>
-      <c r="V12" s="13">
+      <c r="W12" s="13">
         <v>26000</v>
       </c>
-      <c r="W12" s="13">
+      <c r="X12" s="13">
         <v>26600</v>
-      </c>
-      <c r="X12" s="13">
-        <v>24630</v>
       </c>
       <c r="Y12" s="13">
         <v>24630</v>
       </c>
       <c r="Z12" s="13">
+        <v>24630</v>
+      </c>
+      <c r="AA12" s="13">
         <v>25230</v>
       </c>
-      <c r="AA12" s="13">
+      <c r="AB12" s="13">
         <v>24700</v>
       </c>
-      <c r="AB12" s="13">
+      <c r="AC12" s="13">
         <v>23780</v>
       </c>
-      <c r="AC12" s="13">
+      <c r="AD12" s="13">
         <v>23920</v>
       </c>
-      <c r="AD12" s="13">
+      <c r="AE12" s="13">
         <v>22390</v>
       </c>
-      <c r="AE12" s="13">
+      <c r="AF12" s="13">
         <v>23000</v>
       </c>
-      <c r="AF12" s="13">
+      <c r="AG12" s="13">
         <v>20990</v>
       </c>
-      <c r="AG12" s="13">
+      <c r="AH12" s="13">
         <v>20260</v>
       </c>
-      <c r="AH12" s="13">
+      <c r="AI12" s="13">
         <v>19200</v>
       </c>
-      <c r="AI12" s="13">
+      <c r="AJ12" s="13">
         <v>19860</v>
       </c>
-      <c r="AJ12" s="13">
+      <c r="AK12" s="13">
         <v>19700</v>
       </c>
-      <c r="AK12" s="13">
+      <c r="AL12" s="13">
         <v>19430</v>
       </c>
-      <c r="AL12" s="13">
+      <c r="AM12" s="13">
         <v>19020</v>
       </c>
-      <c r="AM12" s="13"/>
       <c r="AN12" s="13"/>
       <c r="AO12" s="13"/>
       <c r="AP12" s="13"/>
@@ -3242,36 +3291,37 @@
       <c r="BI12" s="13"/>
       <c r="BJ12" s="13"/>
       <c r="BK12" s="13"/>
-      <c r="BL12" s="29"/>
-      <c r="BM12" s="13"/>
+      <c r="BL12" s="13"/>
+      <c r="BM12" s="29"/>
       <c r="BN12" s="13"/>
-      <c r="BO12" s="29"/>
-      <c r="BP12" s="13"/>
+      <c r="BO12" s="13"/>
+      <c r="BP12" s="29"/>
       <c r="BQ12" s="13"/>
       <c r="BR12" s="13"/>
       <c r="BS12" s="13"/>
-      <c r="BT12" s="13">
+      <c r="BT12" s="13"/>
+      <c r="BU12" s="13">
         <f t="shared" si="0"/>
         <v>-331.70059999999995</v>
       </c>
-      <c r="BU12" s="13">
+      <c r="BV12" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BV12" s="13"/>
       <c r="BW12" s="13"/>
-      <c r="BX12">
+      <c r="BX12" s="13"/>
+      <c r="BY12">
         <v>7</v>
       </c>
-      <c r="BY12">
+      <c r="BZ12">
         <v>27320</v>
       </c>
-      <c r="BZ12" s="15">
+      <c r="CA12" s="15">
         <f t="shared" si="4"/>
         <v>331.70059999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A13" s="1">
         <v>397018</v>
       </c>
@@ -3300,46 +3350,48 @@
         <v>723</v>
       </c>
       <c r="I13" s="13">
-        <v>680.1</v>
+        <v>837.7</v>
       </c>
       <c r="J13" s="13">
-        <v>680.1</v>
+        <v>837.7</v>
       </c>
       <c r="K13" s="13">
+        <v>802</v>
+      </c>
+      <c r="L13" s="13">
         <v>1009</v>
       </c>
-      <c r="L13" s="13">
+      <c r="M13" s="13">
         <v>1074</v>
-      </c>
-      <c r="M13" s="13">
-        <v>900</v>
       </c>
       <c r="N13" s="13">
         <v>900</v>
       </c>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13">
+      <c r="O13" s="13">
+        <v>900</v>
+      </c>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13">
         <v>1490</v>
       </c>
-      <c r="Q13" s="13">
+      <c r="R13" s="13">
         <v>1210</v>
       </c>
-      <c r="R13" s="13">
+      <c r="S13" s="13">
         <v>1100</v>
       </c>
-      <c r="S13" s="13">
+      <c r="T13" s="13">
         <v>980</v>
       </c>
-      <c r="T13" s="13">
+      <c r="U13" s="13">
         <v>932.1</v>
       </c>
-      <c r="U13" s="13">
+      <c r="V13" s="13">
         <v>822</v>
       </c>
-      <c r="V13" s="13">
+      <c r="W13" s="13">
         <v>790</v>
       </c>
-      <c r="W13" s="13"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
       <c r="Z13" s="13"/>
@@ -3380,33 +3432,34 @@
       <c r="BI13" s="13"/>
       <c r="BJ13" s="13"/>
       <c r="BK13" s="13"/>
-      <c r="BL13" s="29"/>
-      <c r="BM13" s="13"/>
+      <c r="BL13" s="13"/>
+      <c r="BM13" s="29"/>
       <c r="BN13" s="13"/>
-      <c r="BO13" s="29"/>
-      <c r="BP13" s="13"/>
+      <c r="BO13" s="13"/>
+      <c r="BP13" s="29"/>
       <c r="BQ13" s="13"/>
       <c r="BR13" s="13"/>
       <c r="BS13" s="13"/>
-      <c r="BT13" s="13">
+      <c r="BT13" s="13"/>
+      <c r="BU13" s="13">
         <f t="shared" si="0"/>
         <v>816.99</v>
       </c>
-      <c r="BU13" s="13">
+      <c r="BV13" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BV13" s="13"/>
       <c r="BW13" s="13"/>
-      <c r="BX13">
+      <c r="BX13" s="13"/>
+      <c r="BY13">
         <v>113</v>
       </c>
-      <c r="BZ13" s="15">
+      <c r="CA13" s="15">
         <f t="shared" si="4"/>
         <v>-816.99</v>
       </c>
     </row>
-    <row r="14" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A14" s="1">
         <v>662577</v>
       </c>
@@ -3435,216 +3488,219 @@
         <v>7204.22</v>
       </c>
       <c r="I14" s="13">
-        <v>7678</v>
+        <v>7922</v>
       </c>
       <c r="J14" s="13">
-        <v>7678</v>
+        <v>7922</v>
       </c>
       <c r="K14" s="13">
+        <v>7884</v>
+      </c>
+      <c r="L14" s="13">
         <v>8051</v>
       </c>
-      <c r="L14" s="13">
+      <c r="M14" s="13">
         <v>7911</v>
       </c>
-      <c r="M14" s="13">
+      <c r="N14" s="13">
         <v>7833</v>
       </c>
-      <c r="N14" s="13">
+      <c r="O14" s="13">
         <v>7687</v>
       </c>
-      <c r="O14" s="13">
+      <c r="P14" s="13">
         <v>7672</v>
       </c>
-      <c r="P14" s="13">
+      <c r="Q14" s="13">
         <v>7676</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="R14" s="13">
         <v>7844</v>
       </c>
-      <c r="R14" s="13">
+      <c r="S14" s="13">
         <v>7810</v>
       </c>
-      <c r="S14" s="13">
+      <c r="T14" s="13">
         <v>7710</v>
       </c>
-      <c r="T14" s="13">
+      <c r="U14" s="13">
         <v>7735</v>
       </c>
-      <c r="U14" s="13">
+      <c r="V14" s="13">
         <v>7725</v>
       </c>
-      <c r="V14" s="13">
+      <c r="W14" s="13">
         <v>7787</v>
       </c>
-      <c r="W14" s="13">
+      <c r="X14" s="13">
         <v>7955</v>
-      </c>
-      <c r="X14" s="13">
-        <v>7627</v>
       </c>
       <c r="Y14" s="13">
         <v>7627</v>
       </c>
       <c r="Z14" s="13">
+        <v>7627</v>
+      </c>
+      <c r="AA14" s="13">
         <v>7656</v>
       </c>
-      <c r="AA14" s="13">
+      <c r="AB14" s="13">
         <v>7507</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AC14" s="13">
         <v>7590</v>
       </c>
-      <c r="AC14" s="13">
+      <c r="AD14" s="13">
         <v>7569</v>
       </c>
-      <c r="AD14" s="13">
+      <c r="AE14" s="13">
         <v>7269</v>
       </c>
-      <c r="AE14" s="13">
+      <c r="AF14" s="13">
         <v>7444</v>
       </c>
-      <c r="AF14" s="13">
+      <c r="AG14" s="13">
         <v>7205</v>
       </c>
-      <c r="AG14" s="13">
+      <c r="AH14" s="13">
         <v>7298</v>
       </c>
-      <c r="AH14" s="13">
+      <c r="AI14" s="13">
         <v>7222</v>
       </c>
-      <c r="AI14" s="13">
+      <c r="AJ14" s="13">
         <v>7079</v>
       </c>
-      <c r="AJ14" s="13">
+      <c r="AK14" s="13">
         <v>7140</v>
       </c>
-      <c r="AK14" s="13">
+      <c r="AL14" s="13">
         <v>7440</v>
       </c>
-      <c r="AL14" s="13">
+      <c r="AM14" s="13">
         <v>7530</v>
-      </c>
-      <c r="AM14" s="13">
-        <v>7535</v>
       </c>
       <c r="AN14" s="13">
         <v>7535</v>
       </c>
       <c r="AO14" s="13">
+        <v>7535</v>
+      </c>
+      <c r="AP14" s="13">
         <v>7568</v>
       </c>
-      <c r="AP14" s="13">
+      <c r="AQ14" s="13">
         <v>7699</v>
       </c>
-      <c r="AQ14" s="13">
+      <c r="AR14" s="13">
         <v>7638</v>
       </c>
-      <c r="AR14" s="13">
+      <c r="AS14" s="13">
         <v>7654</v>
       </c>
-      <c r="AS14" s="13">
+      <c r="AT14" s="13">
         <v>7584</v>
       </c>
-      <c r="AT14" s="13">
+      <c r="AU14" s="13">
         <v>7479</v>
       </c>
-      <c r="AU14" s="13">
+      <c r="AV14" s="13">
         <v>7490</v>
       </c>
-      <c r="AV14" s="13">
+      <c r="AW14" s="13">
         <v>7480</v>
       </c>
-      <c r="AW14" s="13">
+      <c r="AX14" s="13">
         <v>7270</v>
       </c>
-      <c r="AX14" s="13">
+      <c r="AY14" s="13">
         <v>7163</v>
       </c>
-      <c r="AY14" s="13">
+      <c r="AZ14" s="13">
         <v>7231</v>
-      </c>
-      <c r="AZ14" s="13">
-        <v>7100</v>
       </c>
       <c r="BA14" s="13">
         <v>7100</v>
       </c>
       <c r="BB14" s="13">
+        <v>7100</v>
+      </c>
+      <c r="BC14" s="13">
         <v>7027</v>
       </c>
-      <c r="BC14" s="13">
+      <c r="BD14" s="13">
         <v>6984</v>
       </c>
-      <c r="BD14" s="13">
+      <c r="BE14" s="13">
         <v>6944</v>
       </c>
-      <c r="BE14" s="13">
+      <c r="BF14" s="13">
         <v>6924</v>
       </c>
-      <c r="BF14" s="13">
+      <c r="BG14" s="13">
         <v>6930</v>
       </c>
-      <c r="BG14" s="13">
+      <c r="BH14" s="13">
         <v>6938</v>
       </c>
-      <c r="BH14" s="13">
+      <c r="BI14" s="13">
         <v>6989</v>
       </c>
-      <c r="BI14" s="13">
+      <c r="BJ14" s="13">
         <v>6871</v>
       </c>
-      <c r="BJ14" s="13">
+      <c r="BK14" s="13">
         <v>6943</v>
       </c>
-      <c r="BK14" s="13">
+      <c r="BL14" s="13">
         <v>7040</v>
       </c>
-      <c r="BL14" s="29">
+      <c r="BM14" s="29">
         <v>6696</v>
       </c>
-      <c r="BM14" s="13">
+      <c r="BN14" s="13">
         <v>6965</v>
       </c>
-      <c r="BN14" s="13">
+      <c r="BO14" s="13">
         <v>6788</v>
       </c>
-      <c r="BO14" s="29">
+      <c r="BP14" s="29">
         <v>6696</v>
       </c>
-      <c r="BP14" s="13">
+      <c r="BQ14" s="13">
         <v>6625</v>
       </c>
-      <c r="BQ14" s="13">
+      <c r="BR14" s="13">
         <v>6660</v>
       </c>
-      <c r="BR14" s="13">
+      <c r="BS14" s="13">
         <v>6791</v>
       </c>
-      <c r="BS14" s="13">
+      <c r="BT14" s="13">
         <v>6610</v>
       </c>
-      <c r="BT14" s="13">
+      <c r="BU14" s="13">
         <f t="shared" si="0"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BU14" s="13">
+      <c r="BV14" s="13">
         <f t="shared" si="1"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BV14" s="13">
-        <f t="shared" ref="BV14" si="5">(BU14-BT14)</f>
+      <c r="BW14" s="13">
+        <f t="shared" ref="BW14" si="5">(BV14-BU14)</f>
         <v>0</v>
       </c>
-      <c r="BW14" s="13">
-        <f>((BK14-H14)/H14)*100</f>
+      <c r="BX14" s="13">
+        <f>((BL14-H14)/H14)*100</f>
         <v>-2.2794972946411995</v>
       </c>
-      <c r="BZ14" s="15">
+      <c r="CA14" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A15" s="1">
         <v>5137534</v>
       </c>
@@ -3658,7 +3714,7 @@
       </c>
       <c r="D15" s="6" t="str">
         <f>IF(I15&lt;GEMINI!L15,"למכור בהפסד",IF(I15&gt;GEMINI!M15,"למכור ברווח","לשמור"))</f>
-        <v>למכור בהפסד</v>
+        <v>לשמור</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>77</v>
@@ -3673,84 +3729,86 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
-        <v>12256</v>
+        <v>12628.12</v>
       </c>
       <c r="J15" s="13">
-        <v>12256</v>
+        <v>12628.12</v>
       </c>
       <c r="K15" s="13">
+        <v>11710.62</v>
+      </c>
+      <c r="L15" s="13">
         <v>12145</v>
       </c>
-      <c r="L15" s="13">
+      <c r="M15" s="13">
         <v>11855.12</v>
-      </c>
-      <c r="M15" s="13">
-        <v>11946.75</v>
       </c>
       <c r="N15" s="13">
         <v>11946.75</v>
       </c>
       <c r="O15" s="13">
-        <v>14679.12</v>
+        <v>11946.75</v>
       </c>
       <c r="P15" s="13">
         <v>14679.12</v>
       </c>
       <c r="Q15" s="13">
+        <v>14679.12</v>
+      </c>
+      <c r="R15" s="13">
         <v>13968</v>
       </c>
-      <c r="R15" s="13">
+      <c r="S15" s="13">
         <v>15528.12</v>
       </c>
-      <c r="S15" s="13">
+      <c r="T15" s="13">
         <v>14358.25</v>
       </c>
-      <c r="T15" s="13">
+      <c r="U15" s="13">
         <v>14385.75</v>
       </c>
-      <c r="U15" s="13">
+      <c r="V15" s="13">
         <v>13880</v>
       </c>
-      <c r="V15" s="13">
+      <c r="W15" s="13">
         <v>13610.62</v>
       </c>
-      <c r="W15" s="13">
+      <c r="X15" s="13">
         <v>13016</v>
       </c>
-      <c r="X15" s="13">
+      <c r="Y15" s="13">
         <v>12487.37</v>
       </c>
-      <c r="Y15" s="13">
+      <c r="Z15" s="13">
         <v>12638.62</v>
       </c>
-      <c r="Z15" s="13">
+      <c r="AA15" s="13">
         <v>12533.87</v>
       </c>
-      <c r="AA15" s="13">
+      <c r="AB15" s="13">
         <v>11299.5</v>
       </c>
-      <c r="AB15" s="13">
+      <c r="AC15" s="13">
         <v>11193.12</v>
       </c>
-      <c r="AC15" s="13">
+      <c r="AD15" s="13">
         <v>11548.62</v>
       </c>
-      <c r="AD15" s="13">
+      <c r="AE15" s="13">
         <v>11125.62</v>
       </c>
-      <c r="AE15" s="13">
+      <c r="AF15" s="13">
         <v>10932.12</v>
       </c>
-      <c r="AF15" s="13">
+      <c r="AG15" s="13">
         <v>11095.62</v>
       </c>
-      <c r="AG15" s="13">
+      <c r="AH15" s="13">
         <v>10910.58</v>
       </c>
-      <c r="AH15" s="13">
+      <c r="AI15" s="13">
         <v>11609.37</v>
       </c>
-      <c r="AI15" s="13"/>
       <c r="AJ15" s="13"/>
       <c r="AK15" s="13"/>
       <c r="AL15" s="13"/>
@@ -3760,8 +3818,8 @@
       <c r="AP15" s="13"/>
       <c r="AQ15" s="13"/>
       <c r="AR15" s="13"/>
-      <c r="AS15" s="14"/>
-      <c r="AT15" s="13"/>
+      <c r="AS15" s="13"/>
+      <c r="AT15" s="14"/>
       <c r="AU15" s="13"/>
       <c r="AV15" s="13"/>
       <c r="AW15" s="13"/>
@@ -3779,36 +3837,37 @@
       <c r="BI15" s="13"/>
       <c r="BJ15" s="13"/>
       <c r="BK15" s="13"/>
-      <c r="BL15" s="29"/>
-      <c r="BM15" s="13"/>
+      <c r="BL15" s="13"/>
+      <c r="BM15" s="29"/>
       <c r="BN15" s="13"/>
-      <c r="BO15" s="29"/>
-      <c r="BP15" s="13"/>
+      <c r="BO15" s="13"/>
+      <c r="BP15" s="29"/>
       <c r="BQ15" s="13"/>
       <c r="BR15" s="13"/>
       <c r="BS15" s="13"/>
-      <c r="BT15" s="13">
+      <c r="BT15" s="13"/>
+      <c r="BU15" s="13">
         <f t="shared" si="0"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BU15" s="13">
+      <c r="BV15" s="13">
         <f t="shared" si="1"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BV15" s="13">
-        <f t="shared" ref="BV15:BV18" si="6">(BU15-BT15)</f>
+      <c r="BW15" s="13">
+        <f t="shared" ref="BW15:BW18" si="6">(BV15-BU15)</f>
         <v>0</v>
       </c>
-      <c r="BW15" s="13">
-        <f>((BK15-H15)/H15)*100</f>
+      <c r="BX15" s="13">
+        <f>((BL15-H15)/H15)*100</f>
         <v>-100</v>
       </c>
-      <c r="BZ15" s="15">
+      <c r="CA15" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A16" s="1">
         <v>5135470</v>
       </c>
@@ -3837,222 +3896,225 @@
         <v>199.49</v>
       </c>
       <c r="I16" s="13">
-        <v>220.86</v>
+        <v>216.57</v>
       </c>
       <c r="J16" s="13">
-        <v>220.86</v>
+        <v>216.57</v>
       </c>
       <c r="K16" s="13">
+        <v>216.57</v>
+      </c>
+      <c r="L16" s="13">
         <v>221.02</v>
       </c>
-      <c r="L16" s="13">
+      <c r="M16" s="13">
         <v>218.38</v>
       </c>
-      <c r="M16" s="13">
+      <c r="N16" s="13">
         <v>218.36</v>
       </c>
-      <c r="N16" s="13">
+      <c r="O16" s="13">
         <v>223.13</v>
       </c>
-      <c r="O16" s="13">
+      <c r="P16" s="13">
         <v>227.54</v>
       </c>
-      <c r="P16" s="13">
+      <c r="Q16" s="13">
         <v>226.96</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="R16" s="13">
         <v>225.24</v>
       </c>
-      <c r="R16" s="13">
+      <c r="S16" s="13">
         <v>223.25</v>
-      </c>
-      <c r="S16" s="13">
-        <v>219.14</v>
       </c>
       <c r="T16" s="13">
         <v>219.14</v>
       </c>
       <c r="U16" s="13">
+        <v>219.14</v>
+      </c>
+      <c r="V16" s="13">
         <v>219.3</v>
       </c>
-      <c r="V16" s="13">
+      <c r="W16" s="13">
         <v>222.79</v>
       </c>
-      <c r="W16" s="13">
+      <c r="X16" s="13">
         <v>221.16</v>
       </c>
-      <c r="X16" s="13">
+      <c r="Y16" s="13">
         <v>220.66</v>
       </c>
-      <c r="Y16" s="13">
+      <c r="Z16" s="13">
         <v>222.06</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="AA16" s="13">
         <v>218.71</v>
       </c>
-      <c r="AA16" s="13">
+      <c r="AB16" s="13">
         <v>216.74</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AC16" s="13">
         <v>216.04</v>
-      </c>
-      <c r="AC16" s="13">
-        <v>210.69</v>
       </c>
       <c r="AD16" s="13">
         <v>210.69</v>
       </c>
       <c r="AE16" s="13">
+        <v>210.69</v>
+      </c>
+      <c r="AF16" s="13">
         <v>198</v>
       </c>
-      <c r="AF16" s="13">
+      <c r="AG16" s="13">
         <v>196.74</v>
       </c>
-      <c r="AG16" s="13">
+      <c r="AH16" s="13">
         <v>192.56</v>
       </c>
-      <c r="AH16" s="13">
+      <c r="AI16" s="13">
         <v>192.23</v>
       </c>
-      <c r="AI16" s="13">
+      <c r="AJ16" s="13">
         <v>191.19</v>
       </c>
-      <c r="AJ16" s="13">
+      <c r="AK16" s="13">
         <v>193.62</v>
       </c>
-      <c r="AK16" s="13">
+      <c r="AL16" s="13">
         <v>190.75</v>
       </c>
-      <c r="AL16" s="13">
+      <c r="AM16" s="13">
         <v>189.06</v>
-      </c>
-      <c r="AM16" s="13">
-        <v>182.73</v>
       </c>
       <c r="AN16" s="13">
         <v>182.73</v>
       </c>
       <c r="AO16" s="13">
+        <v>182.73</v>
+      </c>
+      <c r="AP16" s="13">
         <v>177.92</v>
       </c>
-      <c r="AP16" s="13">
+      <c r="AQ16" s="13">
         <v>179.16</v>
       </c>
-      <c r="AQ16" s="13">
+      <c r="AR16" s="13">
         <v>179.34</v>
-      </c>
-      <c r="AR16" s="13">
-        <v>176.5</v>
       </c>
       <c r="AS16" s="13">
         <v>176.5</v>
       </c>
       <c r="AT16" s="13">
+        <v>176.5</v>
+      </c>
+      <c r="AU16" s="13">
         <v>175.93</v>
       </c>
-      <c r="AU16" s="13">
+      <c r="AV16" s="13">
         <v>174.51</v>
       </c>
-      <c r="AV16" s="13">
+      <c r="AW16" s="13">
         <v>173.91</v>
       </c>
-      <c r="AW16" s="13">
+      <c r="AX16" s="13">
         <v>177.1</v>
       </c>
-      <c r="AX16" s="13">
+      <c r="AY16" s="13">
         <v>178.24</v>
       </c>
-      <c r="AY16" s="13">
+      <c r="AZ16" s="13">
         <v>176.52</v>
       </c>
-      <c r="AZ16" s="13">
+      <c r="BA16" s="13">
         <v>178.27</v>
       </c>
-      <c r="BA16" s="13">
+      <c r="BB16" s="13">
         <v>175.29</v>
       </c>
-      <c r="BB16" s="13">
+      <c r="BC16" s="13">
         <v>175.34</v>
       </c>
-      <c r="BC16" s="13">
+      <c r="BD16" s="13">
         <v>174.41</v>
       </c>
-      <c r="BD16" s="13">
+      <c r="BE16" s="13">
         <v>176.22</v>
       </c>
-      <c r="BE16" s="13">
+      <c r="BF16" s="13">
         <v>174</v>
       </c>
-      <c r="BF16" s="13">
+      <c r="BG16" s="13">
         <v>176.35</v>
       </c>
-      <c r="BG16" s="13">
+      <c r="BH16" s="13">
         <v>177.71</v>
       </c>
-      <c r="BH16" s="13">
+      <c r="BI16" s="13">
         <v>180.08</v>
       </c>
-      <c r="BI16" s="13">
+      <c r="BJ16" s="13">
         <v>181.96</v>
       </c>
-      <c r="BJ16" s="13">
+      <c r="BK16" s="13">
         <v>182.9</v>
       </c>
-      <c r="BK16" s="13">
+      <c r="BL16" s="13">
         <v>181.86</v>
       </c>
-      <c r="BL16" s="29">
+      <c r="BM16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BM16" s="13">
+      <c r="BN16" s="13">
         <v>181.07</v>
       </c>
-      <c r="BN16" s="13">
+      <c r="BO16" s="13">
         <v>182.56</v>
       </c>
-      <c r="BO16" s="29">
+      <c r="BP16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BP16" s="13">
+      <c r="BQ16" s="13">
         <v>178.86</v>
       </c>
-      <c r="BQ16" s="13">
+      <c r="BR16" s="13">
         <v>180.16</v>
       </c>
-      <c r="BR16" s="13">
+      <c r="BS16" s="13">
         <v>179.56</v>
       </c>
-      <c r="BS16" s="13">
+      <c r="BT16" s="13">
         <v>176.55</v>
       </c>
-      <c r="BT16" s="13">
+      <c r="BU16" s="13">
         <f t="shared" si="0"/>
         <v>1413.1220000000008</v>
       </c>
-      <c r="BU16" s="13">
+      <c r="BV16" s="13">
         <f t="shared" si="1"/>
         <v>997.45</v>
       </c>
-      <c r="BV16" s="13">
+      <c r="BW16" s="13">
         <f t="shared" si="6"/>
         <v>-415.67200000000071</v>
       </c>
-      <c r="BW16" s="13">
-        <f>((BK16-H16)/H16)*100</f>
+      <c r="BX16" s="13">
+        <f>((BL16-H16)/H16)*100</f>
         <v>-8.8375357160759904</v>
       </c>
-      <c r="BX16">
+      <c r="BY16">
         <v>1864</v>
       </c>
-      <c r="BY16">
+      <c r="BZ16">
         <v>177.19</v>
       </c>
-      <c r="BZ16" s="15">
+      <c r="CA16" s="15">
         <f t="shared" si="4"/>
         <v>-415.67200000000071</v>
       </c>
     </row>
-    <row r="17" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A17" s="1">
         <v>5134135</v>
       </c>
@@ -4081,13 +4143,13 @@
         <v>159.65</v>
       </c>
       <c r="I17" s="13">
-        <v>190.72</v>
+        <v>177.17</v>
       </c>
       <c r="J17" s="13">
-        <v>190.72</v>
+        <v>177.17</v>
       </c>
       <c r="K17" s="13">
-        <v>184.42</v>
+        <v>186.88</v>
       </c>
       <c r="L17" s="13">
         <v>184.42</v>
@@ -4096,13 +4158,13 @@
         <v>184.42</v>
       </c>
       <c r="N17" s="13">
+        <v>184.42</v>
+      </c>
+      <c r="O17" s="13">
         <v>199.37</v>
       </c>
-      <c r="O17" s="13">
+      <c r="P17" s="13">
         <v>194.88</v>
-      </c>
-      <c r="P17" s="13">
-        <v>189.51</v>
       </c>
       <c r="Q17" s="13">
         <v>189.51</v>
@@ -4111,13 +4173,13 @@
         <v>189.51</v>
       </c>
       <c r="S17" s="13">
-        <v>185.52</v>
+        <v>189.51</v>
       </c>
       <c r="T17" s="13">
         <v>185.52</v>
       </c>
       <c r="U17" s="13">
-        <v>178.98</v>
+        <v>185.52</v>
       </c>
       <c r="V17" s="13">
         <v>178.98</v>
@@ -4126,7 +4188,7 @@
         <v>178.98</v>
       </c>
       <c r="X17" s="13">
-        <v>170.7</v>
+        <v>178.98</v>
       </c>
       <c r="Y17" s="13">
         <v>170.7</v>
@@ -4135,10 +4197,10 @@
         <v>170.7</v>
       </c>
       <c r="AA17" s="13">
+        <v>170.7</v>
+      </c>
+      <c r="AB17" s="13">
         <v>170.45</v>
-      </c>
-      <c r="AB17" s="13">
-        <v>160.84</v>
       </c>
       <c r="AC17" s="13">
         <v>160.84</v>
@@ -4147,15 +4209,17 @@
         <v>160.84</v>
       </c>
       <c r="AE17" s="13">
+        <v>160.84</v>
+      </c>
+      <c r="AF17" s="13">
         <v>159.02000000000001</v>
-      </c>
-      <c r="AF17" s="13">
-        <v>159.65</v>
       </c>
       <c r="AG17" s="13">
         <v>159.65</v>
       </c>
-      <c r="AH17" s="13"/>
+      <c r="AH17" s="13">
+        <v>159.65</v>
+      </c>
       <c r="AI17" s="13"/>
       <c r="AJ17" s="13"/>
       <c r="AK17" s="13"/>
@@ -4185,36 +4249,37 @@
       <c r="BI17" s="13"/>
       <c r="BJ17" s="13"/>
       <c r="BK17" s="13"/>
-      <c r="BL17" s="29"/>
-      <c r="BM17" s="13"/>
+      <c r="BL17" s="13"/>
+      <c r="BM17" s="29"/>
       <c r="BN17" s="13"/>
-      <c r="BO17" s="29"/>
-      <c r="BP17" s="13"/>
+      <c r="BO17" s="13"/>
+      <c r="BP17" s="29"/>
       <c r="BQ17" s="13"/>
       <c r="BR17" s="13"/>
       <c r="BS17" s="13"/>
-      <c r="BT17" s="13">
+      <c r="BT17" s="13"/>
+      <c r="BU17" s="13">
         <f t="shared" si="0"/>
         <v>957.9</v>
       </c>
-      <c r="BU17" s="13">
+      <c r="BV17" s="13">
         <f t="shared" si="1"/>
         <v>957.9</v>
       </c>
-      <c r="BV17" s="13">
-        <f t="shared" ref="BV17" si="7">(BU17-BT17)</f>
+      <c r="BW17" s="13">
+        <f t="shared" ref="BW17" si="7">(BV17-BU17)</f>
         <v>0</v>
       </c>
-      <c r="BW17" s="13">
-        <f>((BK17-H17)/H17)*100</f>
+      <c r="BX17" s="13">
+        <f>((BL17-H17)/H17)*100</f>
         <v>-100</v>
       </c>
-      <c r="BZ17" s="15">
+      <c r="CA17" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A18" s="1">
         <v>1168723</v>
       </c>
@@ -4243,87 +4308,89 @@
         <v>1434</v>
       </c>
       <c r="I18" s="13">
+        <v>1823</v>
+      </c>
+      <c r="J18" s="13">
+        <v>1823</v>
+      </c>
+      <c r="K18" s="13">
+        <v>1819</v>
+      </c>
+      <c r="L18" s="13">
+        <v>1866</v>
+      </c>
+      <c r="M18" s="13">
+        <v>1886</v>
+      </c>
+      <c r="N18" s="13">
         <v>1818</v>
       </c>
-      <c r="J18" s="13">
-        <v>1818</v>
-      </c>
-      <c r="K18" s="13">
-        <v>1866</v>
-      </c>
-      <c r="L18" s="13">
-        <v>1886</v>
-      </c>
-      <c r="M18" s="13">
-        <v>1818</v>
-      </c>
-      <c r="N18" s="13">
+      <c r="O18" s="13">
         <v>1785</v>
       </c>
-      <c r="O18" s="13">
+      <c r="P18" s="13">
         <v>1828</v>
       </c>
-      <c r="P18" s="13">
+      <c r="Q18" s="13">
         <v>1811</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="R18" s="13">
         <v>1825</v>
       </c>
-      <c r="R18" s="13">
+      <c r="S18" s="13">
         <v>1831</v>
       </c>
-      <c r="S18" s="13">
+      <c r="T18" s="13">
         <v>1799</v>
       </c>
-      <c r="T18" s="13">
+      <c r="U18" s="13">
         <v>1757</v>
       </c>
-      <c r="U18" s="13">
+      <c r="V18" s="13">
         <v>1698</v>
       </c>
-      <c r="V18" s="13">
+      <c r="W18" s="13">
         <v>1694</v>
       </c>
-      <c r="W18" s="13">
+      <c r="X18" s="13">
         <v>1671</v>
-      </c>
-      <c r="X18" s="13">
-        <v>1660</v>
       </c>
       <c r="Y18" s="13">
         <v>1660</v>
       </c>
       <c r="Z18" s="13">
+        <v>1660</v>
+      </c>
+      <c r="AA18" s="13">
         <v>1646</v>
       </c>
-      <c r="AA18" s="13">
+      <c r="AB18" s="13">
         <v>1648</v>
       </c>
-      <c r="AB18" s="13">
+      <c r="AC18" s="13">
         <v>1614</v>
       </c>
-      <c r="AC18" s="13">
+      <c r="AD18" s="13">
         <v>1626</v>
       </c>
-      <c r="AD18" s="13">
+      <c r="AE18" s="13">
         <v>1587</v>
       </c>
-      <c r="AE18" s="13">
+      <c r="AF18" s="13">
         <v>1548</v>
       </c>
-      <c r="AF18" s="13">
+      <c r="AG18" s="13">
         <v>1500</v>
       </c>
-      <c r="AG18" s="13">
+      <c r="AH18" s="13">
         <v>1491</v>
       </c>
-      <c r="AH18" s="13">
+      <c r="AI18" s="13">
         <v>1444</v>
       </c>
-      <c r="AI18" s="13">
+      <c r="AJ18" s="13">
         <v>1431</v>
       </c>
-      <c r="AJ18" s="13"/>
       <c r="AK18" s="13"/>
       <c r="AL18" s="13"/>
       <c r="AM18" s="13"/>
@@ -4349,64 +4416,65 @@
       <c r="BG18" s="13"/>
       <c r="BH18" s="13"/>
       <c r="BI18" s="13"/>
-      <c r="BJ18" s="13">
-        <v>1788</v>
-      </c>
+      <c r="BJ18" s="13"/>
       <c r="BK18" s="13">
         <v>1788</v>
       </c>
-      <c r="BL18" s="29">
+      <c r="BL18" s="13">
+        <v>1788</v>
+      </c>
+      <c r="BM18" s="29">
         <v>1780</v>
       </c>
-      <c r="BM18" s="13">
+      <c r="BN18" s="13">
         <v>1814</v>
       </c>
-      <c r="BN18" s="13">
+      <c r="BO18" s="13">
         <v>1794</v>
       </c>
-      <c r="BO18" s="29">
+      <c r="BP18" s="29">
         <v>1780</v>
       </c>
-      <c r="BP18" s="13">
+      <c r="BQ18" s="13">
         <v>1772</v>
       </c>
-      <c r="BQ18" s="13">
+      <c r="BR18" s="13">
         <v>1798</v>
       </c>
-      <c r="BR18" s="13">
+      <c r="BS18" s="13">
         <v>1806</v>
       </c>
-      <c r="BS18" s="13">
+      <c r="BT18" s="13">
         <v>1801</v>
       </c>
-      <c r="BT18" s="13">
+      <c r="BU18" s="13">
         <f t="shared" si="0"/>
         <v>292.79999999999995</v>
       </c>
-      <c r="BU18" s="13">
+      <c r="BV18" s="13">
         <f t="shared" si="1"/>
         <v>645.29999999999995</v>
       </c>
-      <c r="BV18" s="13">
+      <c r="BW18" s="13">
         <f t="shared" si="6"/>
         <v>352.5</v>
       </c>
-      <c r="BW18" s="13">
-        <f>((BK18-H18)/H18)*100</f>
+      <c r="BX18" s="13">
+        <f>((BL18-H18)/H18)*100</f>
         <v>24.686192468619247</v>
       </c>
-      <c r="BX18">
+      <c r="BY18">
         <v>100</v>
       </c>
-      <c r="BY18">
+      <c r="BZ18">
         <v>1786.5</v>
       </c>
-      <c r="BZ18" s="15">
+      <c r="CA18" s="15">
         <f t="shared" si="4"/>
         <v>352.5</v>
       </c>
     </row>
-    <row r="19" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A19" s="1">
         <v>1122654</v>
       </c>
@@ -4435,24 +4503,26 @@
         <v>102.77</v>
       </c>
       <c r="I19" s="13">
-        <v>72</v>
+        <v>71.3</v>
       </c>
       <c r="J19" s="13">
-        <v>72</v>
+        <v>71.3</v>
       </c>
       <c r="K19" s="13">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="L19" s="13">
         <v>86.7</v>
-      </c>
-      <c r="L19" s="13">
-        <v>91.5</v>
       </c>
       <c r="M19" s="13">
         <v>91.5</v>
       </c>
       <c r="N19" s="13">
+        <v>91.5</v>
+      </c>
+      <c r="O19" s="13">
         <v>132.6</v>
       </c>
-      <c r="O19" s="13"/>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
       <c r="R19" s="13"/>
@@ -4468,22 +4538,22 @@
       <c r="AB19" s="13"/>
       <c r="AC19" s="13"/>
       <c r="AD19" s="13"/>
-      <c r="AE19" s="13">
+      <c r="AE19" s="13"/>
+      <c r="AF19" s="13">
         <v>6461</v>
       </c>
-      <c r="AF19" s="13">
+      <c r="AG19" s="13">
         <v>6503</v>
       </c>
-      <c r="AG19" s="13">
+      <c r="AH19" s="13">
         <v>6535</v>
       </c>
-      <c r="AH19" s="13">
+      <c r="AI19" s="13">
         <v>6532</v>
       </c>
-      <c r="AI19" s="13">
+      <c r="AJ19" s="13">
         <v>6515</v>
       </c>
-      <c r="AJ19" s="13"/>
       <c r="AK19" s="13"/>
       <c r="AL19" s="13"/>
       <c r="AM19" s="13"/>
@@ -4511,33 +4581,34 @@
       <c r="BI19" s="13"/>
       <c r="BJ19" s="13"/>
       <c r="BK19" s="13"/>
-      <c r="BL19" s="29"/>
-      <c r="BM19" s="13"/>
+      <c r="BL19" s="13"/>
+      <c r="BM19" s="29"/>
       <c r="BN19" s="13"/>
-      <c r="BO19" s="29"/>
-      <c r="BP19" s="13"/>
+      <c r="BO19" s="13"/>
+      <c r="BP19" s="29"/>
       <c r="BQ19" s="13"/>
       <c r="BR19" s="13"/>
       <c r="BS19" s="13"/>
-      <c r="BT19" s="13">
+      <c r="BT19" s="13"/>
+      <c r="BU19" s="13">
         <f t="shared" si="0"/>
         <v>308.31</v>
       </c>
-      <c r="BU19" s="13">
+      <c r="BV19" s="13">
         <f t="shared" si="1"/>
         <v>308.31</v>
       </c>
-      <c r="BV19" s="13"/>
       <c r="BW19" s="13"/>
-      <c r="BX19">
+      <c r="BX19" s="13"/>
+      <c r="BY19">
         <v>7</v>
       </c>
-      <c r="BY19">
+      <c r="BZ19">
         <v>6461</v>
       </c>
-      <c r="BZ19" s="15"/>
-    </row>
-    <row r="20" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CA19" s="15"/>
+    </row>
+    <row r="20" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A20" s="1">
         <v>363010</v>
       </c>
@@ -4566,18 +4637,20 @@
         <v>65</v>
       </c>
       <c r="I20" s="13">
-        <v>70</v>
+        <v>75.2</v>
       </c>
       <c r="J20" s="13">
-        <v>70</v>
+        <v>75.2</v>
       </c>
       <c r="K20" s="13">
+        <v>68.8</v>
+      </c>
+      <c r="L20" s="13">
         <v>89</v>
       </c>
-      <c r="L20" s="13">
+      <c r="M20" s="13">
         <v>87.5</v>
       </c>
-      <c r="M20" s="13"/>
       <c r="N20" s="13"/>
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
@@ -4628,28 +4701,29 @@
       <c r="BI20" s="13"/>
       <c r="BJ20" s="13"/>
       <c r="BK20" s="13"/>
-      <c r="BL20" s="29"/>
-      <c r="BM20" s="13"/>
+      <c r="BL20" s="13"/>
+      <c r="BM20" s="29"/>
       <c r="BN20" s="13"/>
-      <c r="BO20" s="29"/>
-      <c r="BP20" s="13"/>
+      <c r="BO20" s="13"/>
+      <c r="BP20" s="29"/>
       <c r="BQ20" s="13"/>
       <c r="BR20" s="13"/>
       <c r="BS20" s="13"/>
-      <c r="BT20" s="13">
+      <c r="BT20" s="13"/>
+      <c r="BU20" s="13">
         <f t="shared" si="0"/>
         <v>195</v>
       </c>
-      <c r="BU20" s="13">
+      <c r="BV20" s="13">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-      <c r="BV20" s="13"/>
       <c r="BW20" s="13"/>
-      <c r="BZ20" s="15"/>
-    </row>
-    <row r="21" spans="1:78" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:78" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BX20" s="13"/>
+      <c r="CA20" s="15"/>
+    </row>
+    <row r="21" spans="1:79" ht="14.4" thickBot="1"/>
+    <row r="22" spans="1:79" ht="45" customHeight="1" thickBot="1">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4713,11 +4787,11 @@
       <c r="BI22" s="13"/>
       <c r="BJ22" s="13"/>
       <c r="BK22" s="13"/>
-      <c r="BL22" s="29"/>
-      <c r="BM22" s="13"/>
+      <c r="BL22" s="13"/>
+      <c r="BM22" s="29"/>
       <c r="BN22" s="13"/>
-      <c r="BO22" s="29"/>
-      <c r="BP22" s="13"/>
+      <c r="BO22" s="13"/>
+      <c r="BP22" s="29"/>
       <c r="BQ22" s="13"/>
       <c r="BR22" s="13"/>
       <c r="BS22" s="13"/>
@@ -4725,9 +4799,10 @@
       <c r="BU22" s="13"/>
       <c r="BV22" s="13"/>
       <c r="BW22" s="13"/>
-      <c r="BZ22" s="15"/>
-    </row>
-    <row r="23" spans="1:78" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BX22" s="13"/>
+      <c r="CA22" s="15"/>
+    </row>
+    <row r="23" spans="1:79" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4740,95 +4815,95 @@
       <c r="H23" s="13"/>
       <c r="I23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19+G20*I20)/100</f>
-        <v>13500.502</v>
+        <v>13513.891599999999</v>
       </c>
       <c r="J23" s="23">
         <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19+G20*J20)/100</f>
-        <v>13500.502</v>
+        <v>13513.891599999999</v>
       </c>
       <c r="K23" s="23">
         <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19+G20*K20)/100</f>
-        <v>13916.21</v>
+        <v>13417.8316</v>
       </c>
       <c r="L23" s="23">
         <f>(L2*G2+G3*L3+L4*G4+G5*L5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+L13*G13+G14*L14+L15*G15+G16*L16+G17*L17+L18*G18+G19*L19+G20*L20)/100</f>
-        <v>13936.159599999999</v>
+        <v>13916.21</v>
       </c>
       <c r="M23" s="23">
         <f>(M2*G2+G3*M3+M4*G4+G5*M5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+M13*G13+G14*M14+M15*G15+G16*M16+G17*M17+M18*G18+G19*M19+G20*M20)/100</f>
+        <v>13936.159599999999</v>
+      </c>
+      <c r="N23" s="23">
+        <f>(N2*G2+G3*N3+N4*G4+G5*N5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+N13*G13+G14*N14+N15*G15+G16*N16+G17*N17+N18*G18+G19*N19+G20*N20)/100</f>
         <v>13438.511999999999</v>
-      </c>
-      <c r="N23" s="23">
-        <f>(N2*G2+G3*N3+N4*G4+G5*N5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+N13*G13+G14*N14+N15*G15+G16*N16+G17*N17+N18*G18+G19*N19)/100</f>
-        <v>13503.13</v>
       </c>
       <c r="O23" s="23">
         <f>(O2*G2+G3*O3+O4*G4+G5*O5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+O13*G13+G14*O14+O15*G15+G16*O16+G17*O17+O18*G18+G19*O19)/100</f>
-        <v>13844.2896</v>
+        <v>13503.13</v>
       </c>
       <c r="P23" s="23">
         <f>(P2*G2+G3*P3+P4*G4+G5*P5+G6*P6+G7*P7+G8*P8+G9*P9+G10*P10+G11*P11+G12*P12+P13*G13+G14*P14+P15*G15+G16*P16+G17*P17+P18*G18+G19*P19)/100</f>
-        <v>13659.785600000001</v>
+        <v>13844.2896</v>
       </c>
       <c r="Q23" s="23">
         <f>(Q2*G2+G3*Q3+Q4*G4+G5*Q5+G6*Q6+G7*Q7+G8*Q8+G9*Q9+G10*Q10+G11*Q11+G12*Q12+Q13*G13+G14*Q14+Q15*G15+G16*Q16+G17*Q17+Q18*G18+G19*Q19)/100</f>
-        <v>13683.918</v>
+        <v>13659.785600000001</v>
       </c>
       <c r="R23" s="23">
         <f>(R2*G2+G3*R3+R4*G4+G5*R5+G6*R6+G7*R7+G8*R8+G9*R9+G10*R10+G11*R11+G12*R12+R13*G13+G14*R14+R15*G15+G16*R16+G17*R17+R18*G18+G19*R19)/100</f>
-        <v>13839.923600000002</v>
+        <v>13683.918</v>
       </c>
       <c r="S23" s="23">
         <f>(S2*G2+G3*S3+S4*G4+G5*S5+G6*S6+G7*S7+G8*S8+G9*S9+G10*S10+G11*S11+G12*S12+S13*G13+G14*S14+S15*G15+G16*S16+G17*S17+S18*G18+G19*S19)/100</f>
-        <v>13475.503999999999</v>
+        <v>13839.923600000002</v>
       </c>
       <c r="T23" s="23">
         <f>(T2*G2+G3*T3+T4*G4+G5*T5+G6*T6+G7*T7+G8*T8+G9*T9+G10*T10+G11*T11+G12*T12+T13*G13+G14*T14+T15*G15+G16*T16+G17*T17+T18*G18+G19*T19)/100</f>
-        <v>13192.96</v>
+        <v>13475.503999999999</v>
       </c>
       <c r="U23" s="23">
         <f>(U2*G2+G3*U3+U4*G4+G5*U5+G6*U6+G7*U7+G8*U8+G9*U9+G10*U10+G11*U11+G12*U12+U13*G13+G14*U14+U15*G15+G16*U16+G17*U17+U18*G18+G19*U19)/100</f>
-        <v>12923.761999999999</v>
+        <v>13192.96</v>
       </c>
       <c r="V23" s="23">
         <f>(V2*G2+G3*V3+V4*G4+G5*V5+G6*V6+G7*V7+G8*V8+G9*V9+G10*V10+G11*V11+G12*V12+V13*G13+G14*V14+V15*G15+G16*V16+G17*V17+V18*G18+G19*V19)/100</f>
+        <v>12923.761999999999</v>
+      </c>
+      <c r="W23" s="23">
+        <f>(W2*G2+G3*W3+W4*G4+G5*W5+G6*W6+G7*W7+G8*W8+G9*W9+G10*W10+G11*W11+G12*W12+W13*G13+G14*W14+W15*G15+G16*W16+G17*W17+W18*G18+G19*W19)/100</f>
         <v>13102.8776</v>
-      </c>
-      <c r="W23" s="23">
-        <f>(W3*G3+G4*W4+W5*G5+G6*W6+G7*W7+G8*W8+G9*W9+G10*W10+G11*W11+G12*W12+G14*W14+W15*G15+G16*W16+W17*G17+G18*W18+G19*W19)/100</f>
-        <v>12191.99</v>
       </c>
       <c r="X23" s="23">
         <f>(X3*G3+G4*X4+X5*G5+G6*X6+G7*X7+G8*X8+G9*X9+G10*X10+G11*X11+G12*X12+G14*X14+X15*G15+G16*X16+X17*G17+G18*X18+G19*X19)/100</f>
-        <v>11970.357599999999</v>
+        <v>12191.99</v>
       </c>
       <c r="Y23" s="23">
         <f>(Y3*G3+G4*Y4+Y5*G5+G6*Y6+G7*Y7+G8*Y8+G9*Y9+G10*Y10+G11*Y11+G12*Y12+G14*Y14+Y15*G15+G16*Y16+Y17*G17+G18*Y18+G19*Y19)/100</f>
-        <v>11989.4576</v>
+        <v>11970.357599999999</v>
       </c>
       <c r="Z23" s="23">
         <f>(Z3*G3+G4*Z4+Z5*G5+G6*Z6+G7*Z7+G8*Z8+G9*Z9+G10*Z10+G11*Z11+G12*Z12+G14*Z14+Z15*G15+G16*Z16+Z17*G17+G18*Z18+G19*Z19)/100</f>
-        <v>11896.177600000001</v>
+        <v>11989.4576</v>
       </c>
       <c r="AA23" s="23">
         <f>(AA3*G3+G4*AA4+AA5*G5+G6*AA6+G7*AA7+G8*AA8+G9*AA9+G10*AA10+G11*AA11+G12*AA12+G14*AA14+AA15*G15+G16*AA16+AA17*G17+G18*AA18+G19*AA19)/100</f>
-        <v>11552.98</v>
+        <v>11896.177600000001</v>
       </c>
       <c r="AB23" s="23">
         <f>(AB3*G3+G4*AB4+AB5*G5+G6*AB6+G7*AB7+G8*AB8+G9*AB9+G10*AB10+G11*AB11+G12*AB12+G14*AB14+AB15*G15+G16*AB16+AB17*G17+G18*AB18+G19*AB19)/100</f>
-        <v>11467.277599999999</v>
+        <v>11552.98</v>
       </c>
       <c r="AC23" s="23">
         <f>(AC3*G3+G4*AC4+AC5*G5+G6*AC6+G7*AC7+G8*AC8+G9*AC9+G10*AC10+G11*AC11+G12*AC12+G14*AC14+AC15*G15+G16*AC16+AC17*G17+G18*AC18+G19*AC19)/100</f>
+        <v>11467.277599999999</v>
+      </c>
+      <c r="AD23" s="23">
+        <f>(AD3*G3+G4*AD4+AD5*G5+G6*AD6+G7*AD7+G8*AD8+G9*AD9+G10*AD10+G11*AD11+G12*AD12+G14*AD14+AD15*G15+G16*AD16+AD17*G17+G18*AD18+G19*AD19)/100</f>
         <v>10332.035599999999</v>
       </c>
-      <c r="AD23" s="23">
-        <f>(AD5*G5+G6*AD6+AD7*G7+G8*AD8+G9*AD9+G10*AD10+G11*AD11+G12*AD12+G14*AD14+G20*AD20+G15*AD15+AD16*G16+G17*AD17+AD18*G18+G19*AD19)/100</f>
+      <c r="AE23" s="23">
+        <f>(AE5*G5+G6*AE6+AE7*G7+G8*AE8+G9*AE9+G10*AE10+G11*AE11+G12*AE12+G14*AE14+G20*AE20+G15*AE15+AE16*G16+G17*AE17+AE18*G18+G19*AE19)/100</f>
         <v>9234.9995999999992</v>
-      </c>
-      <c r="AE23" s="23" t="e">
-        <f>(AE5*G5+G7*AE7+AE8*G8+G9*AE9+#REF!*#REF!+G10*AE10+G11*AE11+G12*AE12+G14*AE14+G19*AE19+G20*AE20+AE6*G6+G15*AE15+#REF!*#REF!+G16*AE16+G17*AE17+AE18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AE3+#REF!*#REF!)/100</f>
-        <v>#REF!</v>
       </c>
       <c r="AF23" s="23" t="e">
         <f>(AF5*G5+G7*AF7+AF8*G8+G9*AF9+#REF!*#REF!+G10*AF10+G11*AF11+G12*AF12+G14*AF14+G19*AF19+G20*AF20+AF6*G6+G15*AF15+#REF!*#REF!+G16*AF16+G17*AF17+AF18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AF3+#REF!*#REF!)/100</f>
@@ -4839,11 +4914,11 @@
         <v>#REF!</v>
       </c>
       <c r="AH23" s="23" t="e">
-        <f>(AH5*G5+G7*AH7+AH8*G8+G9*AH9+#REF!*#REF!+G10*AH10+G11*AH11+G12*AH12+G14*AH14+G19*AH19+G20*AH20+AH6*G6+G15*AH15+#REF!*#REF!+G16*AH16+G18*AH18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AH3+#REF!*#REF!+G4*AH4)/100</f>
+        <f>(AH5*G5+G7*AH7+AH8*G8+G9*AH9+#REF!*#REF!+G10*AH10+G11*AH11+G12*AH12+G14*AH14+G19*AH19+G20*AH20+AH6*G6+G15*AH15+#REF!*#REF!+G16*AH16+G17*AH17+AH18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AH3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AI23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AI3*G3+#REF!*#REF!+G4*AI4+G5*AI5+G7*AI7+G8*AI8+G9*AI9+#REF!*#REF!+G10*AI10+AI11*G11+G12*AI12+AI14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AI20+AI6*G6+#REF!*#REF!+G16*AI16+G18*AI18+G19*AI19)/100</f>
+        <f>(AI5*G5+G7*AI7+AI8*G8+G9*AI9+#REF!*#REF!+G10*AI10+G11*AI11+G12*AI12+G14*AI14+G19*AI19+G20*AI20+AI6*G6+G15*AI15+#REF!*#REF!+G16*AI16+G18*AI18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AI3+#REF!*#REF!+G4*AI4)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AJ23" s="23" t="e">
@@ -4851,7 +4926,7 @@
         <v>#REF!</v>
       </c>
       <c r="AK23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AK3*G3+#REF!*#REF!+G4*AK4+G5*AK5+AK7*G7+AK8*G8+AK9*G9+#REF!*#REF!+G10*AK10+AK11*G11+G12*AK12+AK14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AK20+G6*AK6+#REF!*#REF!+G16*AK16+G18*AK18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AK3*G3+#REF!*#REF!+G4*AK4+G5*AK5+G7*AK7+G8*AK8+G9*AK9+#REF!*#REF!+G10*AK10+AK11*G11+G12*AK12+AK14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AK20+AK6*G6+#REF!*#REF!+G16*AK16+G18*AK18+G19*AK19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AL23" s="23" t="e">
@@ -4859,19 +4934,19 @@
         <v>#REF!</v>
       </c>
       <c r="AM23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AM3*G3+#REF!*#REF!+G4*AM4+G8*AM8+AM9*G9+#REF!*#REF!+AM10*G10+G11*AM11+G14*AM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AM6+#REF!*#REF!+G16*AM16+G18*AM18+G7*AM7+G5*AM5+G12*AM12+G20*AM20)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AM3*G3+#REF!*#REF!+G4*AM4+G5*AM5+AM7*G7+AM8*G8+AM9*G9+#REF!*#REF!+G10*AM10+AM11*G11+G12*AM12+AM14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AM20+G6*AM6+#REF!*#REF!+G16*AM16+G18*AM18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AN23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+AN9*G9+#REF!*#REF!+AN10*G10+G11*AN11+G14*AN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AN6+#REF!*#REF!+G16*AN16+G18*AN18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+AN9*G9+#REF!*#REF!+AN10*G10+G11*AN11+G14*AN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AN6+#REF!*#REF!+G16*AN16+G18*AN18+G7*AN7+G5*AN5+G12*AN12+G20*AN20)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AO23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+G9*AO9+#REF!*#REF!+G10*AO10+AO11*G11+AO14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AO6*G6+#REF!*#REF!+G16*AO16+G18*AO18+G19*AO19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+AO9*G9+#REF!*#REF!+AO10*G10+G11*AO11+G14*AO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AO6+#REF!*#REF!+G16*AO16+G18*AO18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AP23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+AP9*G9+#REF!*#REF!+AP10*G10+G11*AP11+G14*AP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AP6+#REF!*#REF!+G16*AP16+G18*AP18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+G9*AP9+#REF!*#REF!+G10*AP10+AP11*G11+AP14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AP6*G6+#REF!*#REF!+G16*AP16+G18*AP18+G19*AP19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AQ23" s="23" t="e">
@@ -4879,7 +4954,7 @@
         <v>#REF!</v>
       </c>
       <c r="AR23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AR3*G3+#REF!*#REF!+G4*AR4+G8*AR8+AR9*G9+AR10*G10+AR11*G11+G14*AR14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AR6+#REF!*#REF!+G16*AR16+G18*AR18+G19*AR19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AR3*G3+#REF!*#REF!+G4*AR4+G8*AR8+AR9*G9+#REF!*#REF!+AR10*G10+G11*AR11+G14*AR14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AR6+#REF!*#REF!+G16*AR16+G18*AR18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AS23" s="23" t="e">
@@ -4899,19 +4974,19 @@
         <v>#REF!</v>
       </c>
       <c r="AW23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AW3*G3+#REF!*#REF!+G4*AW4+G8*AW8+AW9*G9+AW10*G10+AW11*G11+G14*AW14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AW6+#REF!*#REF!+G16*AW16+G18*AW18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AW3*G3+#REF!*#REF!+G4*AW4+G8*AW8+AW9*G9+AW10*G10+AW11*G11+G14*AW14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AW6+#REF!*#REF!+G16*AW16+G18*AW18+G19*AW19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AX23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AX3*G3+#REF!*#REF!+G4*AX4+G8*AX8+AX10*G10+AX11*G11+G14*AX14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AX6+#REF!*#REF!+G16*AX16+G18*AX18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AX3*G3+#REF!*#REF!+G4*AX4+G8*AX8+AX9*G9+AX10*G10+AX11*G11+G14*AX14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AX6+#REF!*#REF!+G16*AX16+G18*AX18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AY23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AY3*G3+#REF!*#REF!+G4*AY4+G8*AY8+G10*AY10+AY11*G11+AY14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AY6*G6+#REF!*#REF!+G16*AY16+G18*AY18+G19*AY19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AY3*G3+#REF!*#REF!+G4*AY4+G8*AY8+AY10*G10+AY11*G11+G14*AY14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AY6+#REF!*#REF!+G16*AY16+G18*AY18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AZ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AZ3*G3+#REF!*#REF!+G4*AZ4+G10*AZ10+AZ11*G11+AZ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AZ6*G6+#REF!*#REF!+G16*AZ16+G18*AZ18+G19*AZ19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AZ3*G3+#REF!*#REF!+G4*AZ4+G8*AZ8+G10*AZ10+AZ11*G11+AZ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AZ6*G6+#REF!*#REF!+G16*AZ16+G18*AZ18+G19*AZ19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BA23" s="23" t="e">
@@ -4923,7 +4998,7 @@
         <v>#REF!</v>
       </c>
       <c r="BC23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BC3*G3+#REF!*#REF!+G4*BC4+G10*BC10+BC11*G11+BC14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BC6*G6+G16*BC16+G18*BC18+G19*BC19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BC3*G3+#REF!*#REF!+G4*BC4+G10*BC10+BC11*G11+BC14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BC6*G6+#REF!*#REF!+G16*BC16+G18*BC18+G19*BC19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BD23" s="23" t="e">
@@ -4951,15 +5026,15 @@
         <v>#REF!</v>
       </c>
       <c r="BJ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BJ3*G3+#REF!*#REF!+G4*BJ4+G10*BJ10+G11*BJ11+G14*BJ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BJ6+BJ16*G16+G18*BJ18+G19*BJ19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BJ3*G3+#REF!*#REF!+G4*BJ4+G10*BJ10+BJ11*G11+BJ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BJ6*G6+G16*BJ16+G18*BJ18+G19*BJ19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BK23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BK3*G3+#REF!*#REF!+G4*BK4+G10*BK10+G14*BK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BK6+BK16*G16+G18*BK18+G19*BK19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BK3*G3+#REF!*#REF!+G4*BK4+G10*BK10+G11*BK11+G14*BK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BK6+BK16*G16+G18*BK18+G19*BK19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BL23" s="23" t="e">
-        <f>(#REF!*#REF!+BL3*G3+G4*BL4+G14*BL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BL6+BL16*G16+G18*BL18+G19*BL19+G22*BL22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BL3*G3+#REF!*#REF!+G4*BL4+G10*BL10+G14*BL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BL6+BL16*G16+G18*BL18+G19*BL19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BM23" s="23" t="e">
@@ -4970,16 +5045,16 @@
         <f>(#REF!*#REF!+BN3*G3+G4*BN4+G14*BN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BN6+BN16*G16+G18*BN18+G19*BN19+G22*BN22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BO23" s="30" t="e">
+      <c r="BO23" s="23" t="e">
         <f>(#REF!*#REF!+BO3*G3+G4*BO4+G14*BO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BO6+BO16*G16+G18*BO18+G19*BO19+G22*BO22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BP23" s="23" t="e">
+      <c r="BP23" s="30" t="e">
         <f>(#REF!*#REF!+BP3*G3+G4*BP4+G14*BP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BP6+BP16*G16+G18*BP18+G19*BP19+G22*BP22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BQ23" s="23" t="e">
-        <f>(#REF!*#REF!+BQ3*G3+G14*BQ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BQ6+BQ16*G16+G18*BQ18+G19*BQ19+G22*BQ22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+BQ3*G3+G4*BQ4+G14*BQ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BQ6+BQ16*G16+G18*BQ18+G19*BQ19+G22*BQ22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BR23" s="23" t="e">
@@ -4990,15 +5065,19 @@
         <f>(#REF!*#REF!+BS3*G3+G14*BS14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BS6+BS16*G16+G18*BS18+G19*BS19+G22*BS22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BT23" s="13"/>
+      <c r="BT23" s="23" t="e">
+        <f>(#REF!*#REF!+BT3*G3+G14*BT14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BT6+BT16*G16+G18*BT18+G19*BT19+G22*BT22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <v>#REF!</v>
+      </c>
       <c r="BU23" s="13"/>
       <c r="BV23" s="13"/>
       <c r="BW23" s="13"/>
-      <c r="BZ23" s="15">
+      <c r="BX23" s="13"/>
+      <c r="CA23" s="15">
         <v>1149.48</v>
       </c>
     </row>
-    <row r="24" spans="1:78" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:79" ht="44.25" customHeight="1" thickBot="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -5070,29 +5149,30 @@
       <c r="BQ24" s="14"/>
       <c r="BR24" s="14"/>
       <c r="BS24" s="14"/>
-      <c r="BT24" s="23">
-        <f>SUM(BT2:BT20)</f>
-        <v>12977.112800000001</v>
-      </c>
+      <c r="BT24" s="14"/>
       <c r="BU24" s="23">
         <f>SUM(BU2:BU20)</f>
+        <v>12977.112800000001</v>
+      </c>
+      <c r="BV24" s="23">
+        <f>SUM(BV2:BV20)</f>
         <v>12609.442800000001</v>
       </c>
-      <c r="BV24" s="24">
-        <f>BU24-BT24</f>
+      <c r="BW24" s="24">
+        <f>BV24-BU24</f>
         <v>-367.67000000000007</v>
       </c>
-      <c r="BW24" s="13">
-        <f>((BU24-BT24)/BT24)*100</f>
+      <c r="BX24" s="13">
+        <f>((BV24-BU24)/BU24)*100</f>
         <v>-2.8332188034922532</v>
       </c>
-      <c r="BZ24" s="15">
-        <f>SUM(BZ5:BZ23)</f>
+      <c r="CA24" s="15">
+        <f>SUM(CA5:CA23)</f>
         <v>655.07839999999919</v>
       </c>
     </row>
-    <row r="25" spans="1:78" x14ac:dyDescent="0.25">
-      <c r="BT25" s="15">
+    <row r="25" spans="1:79">
+      <c r="BU25" s="15">
         <v>12034.32</v>
       </c>
     </row>
@@ -5150,17 +5230,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DECD697-7590-4F64-9E15-0FA62A69A078}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="7" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="1" width="17.59765625" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="7" width="17.59765625" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="10" max="10" width="9.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>11</v>
       </c>
@@ -5193,7 +5273,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -5219,7 +5299,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>7260</v>
+        <v>8800</v>
       </c>
       <c r="J2" s="25"/>
       <c r="L2" s="21">
@@ -5231,7 +5311,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -5257,7 +5337,7 @@
       <c r="G3" s="17"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="J3" s="26"/>
       <c r="L3" s="21">
@@ -5269,7 +5349,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -5295,7 +5375,7 @@
       <c r="G4" s="17"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6098</v>
+        <v>5990</v>
       </c>
       <c r="J4" s="26"/>
       <c r="L4" s="21">
@@ -5307,7 +5387,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -5332,7 +5412,7 @@
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>607.9</v>
+        <v>622.4</v>
       </c>
       <c r="J5" s="26"/>
       <c r="L5" s="21">
@@ -5344,7 +5424,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -5369,7 +5449,7 @@
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4950</v>
+        <v>4647</v>
       </c>
       <c r="J6" s="26"/>
       <c r="L6" s="21">
@@ -5381,7 +5461,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -5407,7 +5487,7 @@
       <c r="G7" s="18"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3959</v>
+        <v>3954</v>
       </c>
       <c r="J7" s="26"/>
       <c r="L7" s="21">
@@ -5419,7 +5499,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -5445,7 +5525,7 @@
       <c r="G8" s="18"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>38000</v>
+        <v>40740</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -5456,7 +5536,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -5482,7 +5562,7 @@
       <c r="G9" s="17"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10800</v>
+        <v>10820</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -5493,7 +5573,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -5519,7 +5599,7 @@
       <c r="G10" s="18"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5800</v>
+        <v>5067</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -5530,7 +5610,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -5556,7 +5636,7 @@
       <c r="G11" s="18"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1099</v>
+        <v>1054</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -5567,7 +5647,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -5593,7 +5673,7 @@
       <c r="G12" s="18"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>28240</v>
+        <v>28730</v>
       </c>
       <c r="J12" s="26"/>
       <c r="L12" s="21">
@@ -5605,7 +5685,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -5631,7 +5711,7 @@
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>680.1</v>
+        <v>837.7</v>
       </c>
       <c r="J13" s="26"/>
       <c r="L13" s="21">
@@ -5643,7 +5723,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -5669,7 +5749,7 @@
       <c r="G14" s="17"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7678</v>
+        <v>7922</v>
       </c>
       <c r="J14" s="26"/>
       <c r="L14" s="21">
@@ -5681,7 +5761,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -5707,7 +5787,7 @@
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12256</v>
+        <v>12628.12</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
@@ -5719,7 +5799,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -5745,7 +5825,7 @@
       <c r="G16" s="17"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>220.86</v>
+        <v>216.57</v>
       </c>
       <c r="J16" s="26"/>
       <c r="L16" s="21">
@@ -5757,7 +5837,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -5783,7 +5863,7 @@
       <c r="G17" s="17"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>190.72</v>
+        <v>177.17</v>
       </c>
       <c r="J17" s="26"/>
       <c r="L17" s="21">
@@ -5795,7 +5875,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -5821,7 +5901,7 @@
       <c r="G18" s="18"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -5832,7 +5912,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -5854,7 +5934,7 @@
       <c r="G19" s="18"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>72</v>
+        <v>71.3</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -5865,7 +5945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5899,7 +5979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5933,7 +6013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5967,7 +6047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6001,7 +6081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6035,7 +6115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6069,7 +6149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6103,7 +6183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6137,7 +6217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17" t="str">
         <f>'התיק העדכני'!E20</f>
         <v>אירודרום קבוצה</v>
@@ -6159,7 +6239,7 @@
       <c r="G28" s="19"/>
       <c r="I28" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>70</v>
+        <v>75.2</v>
       </c>
       <c r="J28" s="26"/>
       <c r="L28" s="21">
@@ -6179,15 +6259,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7390F3B9-AE45-44AE-B4DF-D92B58EB94BD}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="7" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="7" width="17.59765625" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -6217,7 +6297,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -6243,7 +6323,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>7260</v>
+        <v>8800</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+GEMINI!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
@@ -6254,7 +6334,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -6280,7 +6360,7 @@
       <c r="G3" s="7"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
@@ -6291,7 +6371,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -6317,7 +6397,7 @@
       <c r="G4" s="7"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6098</v>
+        <v>5990</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+GEMINI!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
@@ -6328,7 +6408,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -6354,7 +6434,7 @@
       <c r="G5" s="7"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>607.9</v>
+        <v>622.4</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
@@ -6365,7 +6445,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -6391,7 +6471,7 @@
       <c r="G6" s="7"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4950</v>
+        <v>4647</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
@@ -6402,7 +6482,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -6428,7 +6508,7 @@
       <c r="G7" s="8"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3959</v>
+        <v>3954</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+GEMINI!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
@@ -6439,7 +6519,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -6465,7 +6545,7 @@
       <c r="G8" s="8"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>38000</v>
+        <v>40740</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+GEMINI!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -6476,7 +6556,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -6502,7 +6582,7 @@
       <c r="G9" s="8"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10800</v>
+        <v>10820</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+GEMINI!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -6513,7 +6593,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -6539,7 +6619,7 @@
       <c r="G10" s="8"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5800</v>
+        <v>5067</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+GEMINI!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -6550,7 +6630,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -6576,7 +6656,7 @@
       <c r="G11" s="8"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1099</v>
+        <v>1054</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+GEMINI!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -6587,7 +6667,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -6613,7 +6693,7 @@
       <c r="G12" s="8"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>28240</v>
+        <v>28730</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+GEMINI!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
@@ -6624,7 +6704,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -6650,7 +6730,7 @@
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>680.1</v>
+        <v>837.7</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+GEMINI!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
@@ -6661,7 +6741,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -6687,7 +6767,7 @@
       <c r="G14" s="7"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7678</v>
+        <v>7922</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
@@ -6698,7 +6778,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -6724,7 +6804,7 @@
       <c r="G15" s="7"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12256</v>
+        <v>12628.12</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+GEMINI!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
@@ -6735,7 +6815,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -6761,7 +6841,7 @@
       <c r="G16" s="7"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>220.86</v>
+        <v>216.57</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
@@ -6772,7 +6852,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -6798,7 +6878,7 @@
       <c r="G17" s="7"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>190.72</v>
+        <v>177.17</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+GEMINI!E17+PERPLIXITY!E17+DEEPSEEK!E17)/4</f>
@@ -6809,7 +6889,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -6835,7 +6915,7 @@
       <c r="G18" s="8"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+GEMINI!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -6846,7 +6926,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -6868,7 +6948,7 @@
       <c r="G19" s="8"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>72</v>
+        <v>71.3</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+GEMINI!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -6879,7 +6959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -6891,7 +6971,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -6903,7 +6983,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -6915,7 +6995,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -6927,7 +7007,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -6939,7 +7019,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -6951,7 +7031,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -6963,7 +7043,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -6975,7 +7055,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -6995,15 +7075,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88497C0-21A8-47C7-B959-3D6DF74EF6E2}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="6" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="6" width="17.59765625" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -7033,7 +7113,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -7059,7 +7139,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>7260</v>
+        <v>8800</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+GEMINI!E2+DEEPSEEK!E2)/4</f>
@@ -7070,7 +7150,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -7096,7 +7176,7 @@
       <c r="G3" s="10"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
@@ -7107,7 +7187,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -7133,7 +7213,7 @@
       <c r="G4" s="10"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6098</v>
+        <v>5990</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+GEMINI!E4+DEEPSEEK!E4)/4</f>
@@ -7144,7 +7224,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -7170,7 +7250,7 @@
       <c r="G5" s="10"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>607.9</v>
+        <v>622.4</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
@@ -7181,7 +7261,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -7207,7 +7287,7 @@
       <c r="G6" s="10"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4950</v>
+        <v>4647</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
@@ -7218,7 +7298,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -7244,7 +7324,7 @@
       <c r="G7" s="10"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3959</v>
+        <v>3954</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+GEMINI!E7+DEEPSEEK!E7)/4</f>
@@ -7255,7 +7335,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -7280,7 +7360,7 @@
       </c>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>38000</v>
+        <v>40740</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+GEMINI!E8+DEEPSEEK!E8)/4</f>
@@ -7291,7 +7371,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -7316,7 +7396,7 @@
       </c>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10800</v>
+        <v>10820</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+GEMINI!E9+DEEPSEEK!E9)/4</f>
@@ -7327,7 +7407,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -7352,7 +7432,7 @@
       </c>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5800</v>
+        <v>5067</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+GEMINI!E10+DEEPSEEK!E10)/4</f>
@@ -7363,7 +7443,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -7388,7 +7468,7 @@
       </c>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1099</v>
+        <v>1054</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+GEMINI!E11+DEEPSEEK!E11)/4</f>
@@ -7399,7 +7479,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -7425,7 +7505,7 @@
       <c r="G12" s="10"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>28240</v>
+        <v>28730</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+GEMINI!E12+DEEPSEEK!E12)/4</f>
@@ -7436,7 +7516,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -7462,7 +7542,7 @@
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>680.1</v>
+        <v>837.7</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+CHATGPT!E13+GEMINI!E13+DEEPSEEK!E13)/4</f>
@@ -7473,7 +7553,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -7499,7 +7579,7 @@
       <c r="G14" s="10"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7678</v>
+        <v>7922</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
@@ -7510,7 +7590,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -7536,7 +7616,7 @@
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12256</v>
+        <v>12628.12</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
@@ -7547,7 +7627,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -7573,7 +7653,7 @@
       <c r="G16" s="10"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>220.86</v>
+        <v>216.57</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+GEMINI!E16+DEEPSEEK!E16)/4</f>
@@ -7584,7 +7664,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -7610,7 +7690,7 @@
       <c r="G17" s="10"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>190.72</v>
+        <v>177.17</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+GEMINI!E17+DEEPSEEK!E17)/4</f>
@@ -7621,7 +7701,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -7646,7 +7726,7 @@
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
@@ -7657,7 +7737,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -7678,7 +7758,7 @@
       <c r="F19" s="16"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>72</v>
+        <v>71.3</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+GEMINI!E19+DEEPSEEK!E19)/4</f>
@@ -7689,7 +7769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -7701,7 +7781,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -7713,7 +7793,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -7725,7 +7805,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -7737,7 +7817,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -7749,7 +7829,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -7761,7 +7841,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -7773,7 +7853,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -7785,7 +7865,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -7805,16 +7885,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D354D65C-237D-4544-BBD1-8A37190947C4}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="5" width="17.5703125" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="5" width="17.59765625" customWidth="1"/>
+    <col min="6" max="6" width="20.3984375" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -7843,7 +7923,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אימקו</v>
@@ -7869,7 +7949,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>7260</v>
+        <v>8800</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+PERPLIXITY!E2+GEMINI!E2)/4</f>
@@ -7880,7 +7960,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -7906,7 +7986,7 @@
       <c r="G3" s="31"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
@@ -7917,7 +7997,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -7942,7 +8022,7 @@
       </c>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6098</v>
+        <v>5990</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+GEMINI!E4)/4</f>
@@ -7953,7 +8033,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -7979,7 +8059,7 @@
       <c r="G5" s="31"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>607.9</v>
+        <v>622.4</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
@@ -7990,7 +8070,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -8016,7 +8096,7 @@
       <c r="G6" s="31"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4950</v>
+        <v>4647</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
@@ -8027,7 +8107,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -8052,7 +8132,7 @@
       </c>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3959</v>
+        <v>3954</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+GEMINI!E7)/4</f>
@@ -8063,7 +8143,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -8089,7 +8169,7 @@
       <c r="G8" s="31"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>38000</v>
+        <v>40740</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+GEMINI!E8)/4</f>
@@ -8100,7 +8180,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -8126,7 +8206,7 @@
       <c r="G9" s="31"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10800</v>
+        <v>10820</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+GEMINI!E9)/4</f>
@@ -8137,7 +8217,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -8163,7 +8243,7 @@
       <c r="G10" s="31"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5800</v>
+        <v>5067</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+GEMINI!E10)/4</f>
@@ -8174,7 +8254,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -8200,7 +8280,7 @@
       <c r="G11" s="31"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1099</v>
+        <v>1054</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+GEMINI!E11)/4</f>
@@ -8211,7 +8291,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -8237,7 +8317,7 @@
       <c r="G12" s="31"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>28240</v>
+        <v>28730</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+GEMINI!E12)/4</f>
@@ -8248,7 +8328,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -8274,12 +8354,12 @@
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>680.1</v>
+        <v>837.7</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -8305,7 +8385,7 @@
       <c r="G14" s="31"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7678</v>
+        <v>7922</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
@@ -8316,7 +8396,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -8341,7 +8421,7 @@
       </c>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>70</v>
+        <v>75.2</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+PERPLIXITY!E15+GEMINI!E15)/4</f>
@@ -8352,7 +8432,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -8377,7 +8457,7 @@
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12256</v>
+        <v>12628.12</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
@@ -8388,7 +8468,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -8414,7 +8494,7 @@
       <c r="G17" s="31"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>220.86</v>
+        <v>216.57</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+GEMINI!E17)/4</f>
@@ -8425,7 +8505,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -8451,7 +8531,7 @@
       <c r="G18" s="31"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>190.72</v>
+        <v>177.17</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+GEMINI!E18)/4</f>
@@ -8462,7 +8542,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -8481,7 +8561,7 @@
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+GEMINI!E19)/4</f>
@@ -8492,7 +8572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -8503,7 +8583,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -8515,7 +8595,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -8527,7 +8607,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -8539,7 +8619,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -8551,7 +8631,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -8563,7 +8643,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -8575,7 +8655,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -8587,7 +8667,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/673b1203f7e82b27/מסמכים/GitHub/BURSA/BURSA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\BURSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{7B4C4BA0-E721-42FA-9823-8447E4B0DE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{681CB859-165D-4DEC-8AF5-36B27A466259}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4134F334-8E19-4E08-958B-01E4DA8AE313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
   <sheets>
     <sheet name="התיק העדכני" sheetId="1" r:id="rId1"/>
@@ -24,23 +24,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="113">
   <si>
     <t>MTF מחקה אינדקס תעשיה ישראל</t>
   </si>
@@ -324,9 +313,6 @@
     <t>מחיר 19/01/2026</t>
   </si>
   <si>
-    <t>אימקו</t>
-  </si>
-  <si>
     <t>עין השלישית</t>
   </si>
   <si>
@@ -379,6 +365,9 @@
   </si>
   <si>
     <t>מחיר 06/02/2026</t>
+  </si>
+  <si>
+    <t>אייראנג'י טק</t>
   </si>
 </sst>
 </file>
@@ -388,11 +377,11 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₪&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -401,7 +390,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -452,13 +441,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -849,9 +838,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא של Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -889,7 +878,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -995,7 +984,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1137,7 +1126,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1145,22 +1134,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86B4639-EF9D-4B16-B2C9-0D5E9C5EEC8B}">
-  <dimension ref="A1:CA25"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:CB25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="17.59765625" customWidth="1"/>
-    <col min="6" max="6" width="13.296875" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="62" width="14.8984375" customWidth="1"/>
-    <col min="63" max="72" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="13" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="13.09765625" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="11" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="7.09765625" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="11.59765625" customWidth="1"/>
+    <col min="1" max="5" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="63" width="14.85546875" customWidth="1"/>
+    <col min="64" max="73" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="13" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="11" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="1" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1189,7 +1178,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>111</v>
@@ -1201,16 +1190,16 @@
         <v>109</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O1" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q1" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="R1" s="6" t="s">
         <v>101</v>
@@ -1231,177 +1220,180 @@
         <v>96</v>
       </c>
       <c r="X1" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BK1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BL1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BM1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BN1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BO1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="BO1" s="6" t="s">
+      <c r="BP1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="BP1" s="6" t="s">
+      <c r="BQ1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="BQ1" s="6" t="s">
+      <c r="BR1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="BR1" s="6" t="s">
+      <c r="BS1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="BS1" s="6" t="s">
+      <c r="BT1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BU1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="BU1" s="6" t="s">
+      <c r="BV1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BW1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="BX1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="BY1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="BY1" s="12" t="s">
+      <c r="BZ1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="BZ1" s="12" t="s">
+      <c r="CA1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="CA1" s="12" t="s">
+      <c r="CB1" s="12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="2" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>282012</v>
+        <v>1105907</v>
       </c>
       <c r="B2" s="17">
         <f>GEMINI!L2</f>
@@ -1416,63 +1408,37 @@
         <v>למכור בהפסד</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="F2" s="4">
         <v>46042</v>
       </c>
       <c r="G2" s="27">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="H2" s="13">
-        <v>11000</v>
+        <v>744</v>
       </c>
       <c r="I2" s="13">
-        <v>8800</v>
+        <v>799.8</v>
       </c>
       <c r="J2" s="13">
-        <v>8800</v>
-      </c>
-      <c r="K2" s="13">
-        <v>9030</v>
-      </c>
-      <c r="L2" s="13">
-        <v>9823</v>
-      </c>
-      <c r="M2" s="13">
-        <v>9787</v>
-      </c>
-      <c r="N2" s="13">
-        <v>9650</v>
-      </c>
-      <c r="O2" s="13">
-        <v>9981</v>
-      </c>
-      <c r="P2" s="13">
-        <v>12130</v>
-      </c>
-      <c r="Q2" s="13">
-        <v>11840</v>
-      </c>
-      <c r="R2" s="13">
-        <v>11400</v>
-      </c>
-      <c r="S2" s="13">
-        <v>11360</v>
-      </c>
-      <c r="T2" s="13">
-        <v>11000</v>
-      </c>
-      <c r="U2" s="13">
-        <v>10700</v>
-      </c>
-      <c r="V2" s="13">
-        <v>10400</v>
-      </c>
-      <c r="W2" s="13">
-        <v>11230</v>
-      </c>
-      <c r="X2" s="6"/>
+        <v>799.8</v>
+      </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
       <c r="AA2" s="6"/>
@@ -1513,29 +1479,31 @@
       <c r="BJ2" s="6"/>
       <c r="BK2" s="6"/>
       <c r="BL2" s="6"/>
-      <c r="BM2" s="32"/>
-      <c r="BN2" s="6"/>
+      <c r="BM2" s="6"/>
+      <c r="BN2" s="32"/>
       <c r="BO2" s="6"/>
-      <c r="BP2" s="32"/>
-      <c r="BQ2" s="6"/>
+      <c r="BP2" s="6"/>
+      <c r="BQ2" s="32"/>
       <c r="BR2" s="6"/>
       <c r="BS2" s="6"/>
       <c r="BT2" s="6"/>
-      <c r="BU2" s="13">
-        <f t="shared" ref="BU2:BU20" si="0">(G2*H2)/100-CA2</f>
-        <v>770</v>
-      </c>
+      <c r="BU2" s="6"/>
       <c r="BV2" s="13">
-        <f t="shared" ref="BV2:BV20" si="1">(G2*H2)/100</f>
-        <v>770</v>
-      </c>
-      <c r="BW2" s="6"/>
+        <f t="shared" ref="BV2:BV20" si="0">(G2*H2)/100-CB2</f>
+        <v>372</v>
+      </c>
+      <c r="BW2" s="13">
+        <f t="shared" ref="BW2:BW20" si="1">(G2*H2)/100</f>
+        <v>372</v>
+      </c>
       <c r="BX2" s="6"/>
-      <c r="BY2" s="25"/>
-      <c r="BZ2" s="25"/>
-      <c r="CA2" s="25"/>
-    </row>
-    <row r="3" spans="1:79" ht="45" customHeight="1" thickBot="1">
+      <c r="BY2" s="6"/>
+      <c r="CB2" s="15">
+        <f>(BZ2*CA2-BZ2*H2)/100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1227552</v>
       </c>
@@ -1564,69 +1532,71 @@
         <v>1153.6300000000001</v>
       </c>
       <c r="I3" s="13">
+        <v>941.8</v>
+      </c>
+      <c r="J3" s="13">
+        <v>941.8</v>
+      </c>
+      <c r="K3" s="13">
+        <v>969.7</v>
+      </c>
+      <c r="L3" s="13">
         <v>921</v>
       </c>
-      <c r="J3" s="13">
-        <v>969.7</v>
-      </c>
-      <c r="K3" s="13">
-        <v>921</v>
-      </c>
-      <c r="L3" s="13">
+      <c r="M3" s="13">
         <v>1074</v>
       </c>
-      <c r="M3" s="13">
+      <c r="N3" s="13">
         <v>1245</v>
-      </c>
-      <c r="N3" s="13">
-        <v>1311</v>
       </c>
       <c r="O3" s="13">
         <v>1311</v>
       </c>
       <c r="P3" s="13">
+        <v>1311</v>
+      </c>
+      <c r="Q3" s="13">
         <v>1340</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="R3" s="13">
         <v>1500</v>
       </c>
-      <c r="R3" s="13">
+      <c r="S3" s="13">
         <v>1424</v>
       </c>
-      <c r="S3" s="13">
+      <c r="T3" s="13">
         <v>1348</v>
       </c>
-      <c r="T3" s="13">
+      <c r="U3" s="13">
         <v>1373</v>
       </c>
-      <c r="U3" s="13">
+      <c r="V3" s="13">
         <v>1331</v>
       </c>
-      <c r="V3" s="13">
+      <c r="W3" s="13">
         <v>1386</v>
       </c>
-      <c r="W3" s="13">
+      <c r="X3" s="13">
         <v>1342</v>
       </c>
-      <c r="X3" s="13">
+      <c r="Y3" s="13">
         <v>1250</v>
-      </c>
-      <c r="Y3" s="13">
-        <v>1389</v>
       </c>
       <c r="Z3" s="13">
         <v>1389</v>
       </c>
       <c r="AA3" s="13">
+        <v>1389</v>
+      </c>
+      <c r="AB3" s="13">
         <v>1367</v>
       </c>
-      <c r="AB3" s="13">
+      <c r="AC3" s="13">
         <v>1026</v>
       </c>
-      <c r="AC3" s="13">
+      <c r="AD3" s="13">
         <v>949.1</v>
       </c>
-      <c r="AD3" s="13"/>
       <c r="AE3" s="13"/>
       <c r="AF3" s="13"/>
       <c r="AG3" s="13"/>
@@ -1642,8 +1612,8 @@
       <c r="AQ3" s="13"/>
       <c r="AR3" s="13"/>
       <c r="AS3" s="13"/>
-      <c r="AT3" s="14"/>
-      <c r="AU3" s="13"/>
+      <c r="AT3" s="13"/>
+      <c r="AU3" s="14"/>
       <c r="AV3" s="13"/>
       <c r="AW3" s="13"/>
       <c r="AX3" s="13"/>
@@ -1661,42 +1631,43 @@
       <c r="BJ3" s="13"/>
       <c r="BK3" s="13"/>
       <c r="BL3" s="13"/>
-      <c r="BM3" s="29"/>
-      <c r="BN3" s="13"/>
+      <c r="BM3" s="13"/>
+      <c r="BN3" s="29"/>
       <c r="BO3" s="13"/>
-      <c r="BP3" s="29"/>
-      <c r="BQ3" s="13"/>
+      <c r="BP3" s="13"/>
+      <c r="BQ3" s="29"/>
       <c r="BR3" s="13"/>
       <c r="BS3" s="13"/>
       <c r="BT3" s="13"/>
-      <c r="BU3" s="13">
+      <c r="BU3" s="13"/>
+      <c r="BV3" s="13">
         <f t="shared" si="0"/>
         <v>-126.73159999999989</v>
       </c>
-      <c r="BV3" s="13">
+      <c r="BW3" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BW3" s="13">
-        <f>(BV3-BU3)</f>
+      <c r="BX3" s="13">
+        <f>(BW3-BV3)</f>
         <v>126.73159999999989</v>
       </c>
-      <c r="BX3" s="13">
-        <f>((BL3-H3)/H3)*100</f>
+      <c r="BY3" s="13">
+        <f>((BM3-H3)/H3)*100</f>
         <v>-100</v>
       </c>
-      <c r="BY3">
+      <c r="BZ3">
         <v>68</v>
       </c>
-      <c r="BZ3">
+      <c r="CA3">
         <v>1340</v>
       </c>
-      <c r="CA3" s="15">
-        <f>(BY3*BZ3-BY3*H3)/100</f>
+      <c r="CB3" s="15">
+        <f>(BZ3*CA3-BZ3*H3)/100</f>
         <v>126.73159999999989</v>
       </c>
     </row>
-    <row r="4" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="4" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>587014</v>
       </c>
@@ -1731,63 +1702,65 @@
         <v>5990</v>
       </c>
       <c r="K4" s="13">
+        <v>5990</v>
+      </c>
+      <c r="L4" s="13">
         <v>5956</v>
       </c>
-      <c r="L4" s="13">
+      <c r="M4" s="13">
         <v>6298</v>
       </c>
-      <c r="M4" s="13">
+      <c r="N4" s="13">
         <v>6295</v>
       </c>
-      <c r="N4" s="13">
+      <c r="O4" s="13">
         <v>6370</v>
       </c>
-      <c r="O4" s="13">
+      <c r="P4" s="13">
         <v>6140</v>
       </c>
-      <c r="P4" s="13">
+      <c r="Q4" s="13">
         <v>7252</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="R4" s="13">
         <v>7120</v>
       </c>
-      <c r="R4" s="13">
+      <c r="S4" s="13">
         <v>7048</v>
       </c>
-      <c r="S4" s="13">
+      <c r="T4" s="13">
         <v>6979</v>
       </c>
-      <c r="T4" s="13">
+      <c r="U4" s="13">
         <v>6680</v>
       </c>
-      <c r="U4" s="13">
+      <c r="V4" s="13">
         <v>6111</v>
       </c>
-      <c r="V4" s="13">
+      <c r="W4" s="13">
         <v>6050</v>
       </c>
-      <c r="W4" s="13">
+      <c r="X4" s="13">
         <v>6169</v>
       </c>
-      <c r="X4" s="13">
+      <c r="Y4" s="13">
         <v>6300</v>
-      </c>
-      <c r="Y4" s="13">
-        <v>6335</v>
       </c>
       <c r="Z4" s="13">
         <v>6335</v>
       </c>
       <c r="AA4" s="13">
+        <v>6335</v>
+      </c>
+      <c r="AB4" s="13">
         <v>6444</v>
-      </c>
-      <c r="AB4" s="13">
-        <v>5749</v>
       </c>
       <c r="AC4" s="13">
         <v>5749</v>
       </c>
-      <c r="AD4" s="13"/>
+      <c r="AD4" s="13">
+        <v>5749</v>
+      </c>
       <c r="AE4" s="13"/>
       <c r="AF4" s="13"/>
       <c r="AG4" s="13"/>
@@ -1822,36 +1795,37 @@
       <c r="BJ4" s="13"/>
       <c r="BK4" s="13"/>
       <c r="BL4" s="13"/>
-      <c r="BM4" s="29"/>
-      <c r="BN4" s="13"/>
+      <c r="BM4" s="13"/>
+      <c r="BN4" s="29"/>
       <c r="BO4" s="13"/>
-      <c r="BP4" s="29"/>
-      <c r="BQ4" s="13"/>
+      <c r="BP4" s="13"/>
+      <c r="BQ4" s="29"/>
       <c r="BR4" s="13"/>
       <c r="BS4" s="13"/>
       <c r="BT4" s="13"/>
-      <c r="BU4" s="13">
+      <c r="BU4" s="13"/>
+      <c r="BV4" s="13">
         <f t="shared" si="0"/>
         <v>1185</v>
       </c>
-      <c r="BV4" s="13">
+      <c r="BW4" s="13">
         <f t="shared" si="1"/>
         <v>1185</v>
       </c>
-      <c r="BW4" s="13">
-        <f>(BV4-BU4)</f>
+      <c r="BX4" s="13">
+        <f>(BW4-BV4)</f>
         <v>0</v>
       </c>
-      <c r="BX4" s="13">
-        <f>((BL4-H4)/H4)*100</f>
+      <c r="BY4" s="13">
+        <f>((BM4-H4)/H4)*100</f>
         <v>-100</v>
       </c>
-      <c r="CA4" s="15">
-        <f>(BY4*BZ4-BY4*H4)/100</f>
+      <c r="CB4" s="15">
+        <f>(BZ4*CA4-BZ4*H4)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="5" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1099787</v>
       </c>
@@ -1880,99 +1854,101 @@
         <v>617.53</v>
       </c>
       <c r="I5" s="13">
+        <v>656.2</v>
+      </c>
+      <c r="J5" s="13">
+        <v>656.2</v>
+      </c>
+      <c r="K5" s="13">
         <v>622.4</v>
       </c>
-      <c r="J5" s="13">
-        <v>622.4</v>
-      </c>
-      <c r="K5" s="13">
+      <c r="L5" s="13">
         <v>594.9</v>
       </c>
-      <c r="L5" s="13">
+      <c r="M5" s="13">
         <v>638</v>
       </c>
-      <c r="M5" s="13">
+      <c r="N5" s="13">
         <v>587.5</v>
       </c>
-      <c r="N5" s="13">
+      <c r="O5" s="13">
         <v>577.9</v>
       </c>
-      <c r="O5" s="13">
+      <c r="P5" s="13">
         <v>559</v>
       </c>
-      <c r="P5" s="13">
+      <c r="Q5" s="13">
         <v>570</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="R5" s="13">
         <v>575.70000000000005</v>
       </c>
-      <c r="R5" s="13">
+      <c r="S5" s="13">
         <v>612.6</v>
       </c>
-      <c r="S5" s="13">
+      <c r="T5" s="13">
         <v>638.29999999999995</v>
       </c>
-      <c r="T5" s="13">
+      <c r="U5" s="13">
         <v>630.29999999999995</v>
       </c>
-      <c r="U5" s="13">
+      <c r="V5" s="13">
         <v>626</v>
       </c>
-      <c r="V5" s="13">
+      <c r="W5" s="13">
         <v>595.4</v>
       </c>
-      <c r="W5" s="13">
+      <c r="X5" s="13">
         <v>667.1</v>
       </c>
-      <c r="X5" s="13">
+      <c r="Y5" s="13">
         <v>651</v>
-      </c>
-      <c r="Y5" s="13">
-        <v>641.1</v>
       </c>
       <c r="Z5" s="13">
         <v>641.1</v>
       </c>
       <c r="AA5" s="13">
+        <v>641.1</v>
+      </c>
+      <c r="AB5" s="13">
         <v>607.1</v>
       </c>
-      <c r="AB5" s="13">
+      <c r="AC5" s="13">
         <v>583</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AD5" s="13">
         <v>581.6</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AE5" s="13">
         <v>578.70000000000005</v>
       </c>
-      <c r="AE5" s="13">
+      <c r="AF5" s="13">
         <v>590</v>
       </c>
-      <c r="AF5" s="13">
+      <c r="AG5" s="13">
         <v>554.70000000000005</v>
       </c>
-      <c r="AG5" s="13">
+      <c r="AH5" s="13">
         <v>511.8</v>
       </c>
-      <c r="AH5" s="13">
+      <c r="AI5" s="13">
         <v>487</v>
       </c>
-      <c r="AI5" s="13">
+      <c r="AJ5" s="13">
         <v>478.8</v>
       </c>
-      <c r="AJ5" s="13">
+      <c r="AK5" s="13">
         <v>485.5</v>
       </c>
-      <c r="AK5" s="13">
+      <c r="AL5" s="13">
         <v>453.4</v>
       </c>
-      <c r="AL5" s="13">
+      <c r="AM5" s="13">
         <v>426.1</v>
       </c>
-      <c r="AM5" s="13">
+      <c r="AN5" s="13">
         <v>423.2</v>
       </c>
-      <c r="AN5" s="13"/>
       <c r="AO5" s="13"/>
       <c r="AP5" s="13"/>
       <c r="AQ5" s="13"/>
@@ -1997,27 +1973,28 @@
       <c r="BJ5" s="13"/>
       <c r="BK5" s="13"/>
       <c r="BL5" s="13"/>
-      <c r="BM5" s="29"/>
-      <c r="BN5" s="13"/>
+      <c r="BM5" s="13"/>
+      <c r="BN5" s="29"/>
       <c r="BO5" s="13"/>
-      <c r="BP5" s="29"/>
-      <c r="BQ5" s="13"/>
+      <c r="BP5" s="13"/>
+      <c r="BQ5" s="29"/>
       <c r="BR5" s="13"/>
       <c r="BS5" s="13"/>
       <c r="BT5" s="13"/>
-      <c r="BU5" s="13">
+      <c r="BU5" s="13"/>
+      <c r="BV5" s="13">
         <f t="shared" si="0"/>
         <v>975.6973999999999</v>
       </c>
-      <c r="BV5" s="13">
+      <c r="BW5" s="13">
         <f t="shared" si="1"/>
         <v>975.6973999999999</v>
       </c>
-      <c r="BW5" s="13"/>
       <c r="BX5" s="13"/>
-      <c r="CA5" s="15"/>
-    </row>
-    <row r="6" spans="1:79" ht="45" customHeight="1" thickBot="1">
+      <c r="BY5" s="13"/>
+      <c r="CB5" s="15"/>
+    </row>
+    <row r="6" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1166768</v>
       </c>
@@ -2046,72 +2023,74 @@
         <v>4040</v>
       </c>
       <c r="I6" s="13">
+        <v>4880</v>
+      </c>
+      <c r="J6" s="13">
+        <v>4880</v>
+      </c>
+      <c r="K6" s="13">
         <v>4647</v>
       </c>
-      <c r="J6" s="13">
-        <v>4647</v>
-      </c>
-      <c r="K6" s="13">
+      <c r="L6" s="13">
         <v>4650</v>
       </c>
-      <c r="L6" s="13">
+      <c r="M6" s="13">
         <v>4799</v>
       </c>
-      <c r="M6" s="13">
+      <c r="N6" s="13">
         <v>4740</v>
       </c>
-      <c r="N6" s="13">
+      <c r="O6" s="13">
         <v>4350</v>
       </c>
-      <c r="O6" s="13">
+      <c r="P6" s="13">
         <v>4355</v>
       </c>
-      <c r="P6" s="13">
+      <c r="Q6" s="13">
         <v>4500</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="R6" s="13">
         <v>4424</v>
       </c>
-      <c r="R6" s="13">
+      <c r="S6" s="13">
         <v>4412</v>
       </c>
-      <c r="S6" s="13">
+      <c r="T6" s="13">
         <v>4450</v>
       </c>
-      <c r="T6" s="13">
+      <c r="U6" s="13">
         <v>4238</v>
       </c>
-      <c r="U6" s="13">
+      <c r="V6" s="13">
         <v>3970</v>
       </c>
-      <c r="V6" s="13">
+      <c r="W6" s="13">
         <v>3870</v>
       </c>
-      <c r="W6" s="13">
+      <c r="X6" s="13">
         <v>3805</v>
       </c>
-      <c r="X6" s="13">
+      <c r="Y6" s="13">
         <v>3667</v>
-      </c>
-      <c r="Y6" s="13">
-        <v>3582</v>
       </c>
       <c r="Z6" s="13">
         <v>3582</v>
       </c>
       <c r="AA6" s="13">
+        <v>3582</v>
+      </c>
+      <c r="AB6" s="13">
         <v>3570</v>
       </c>
-      <c r="AB6" s="13">
+      <c r="AC6" s="13">
         <v>3619</v>
       </c>
-      <c r="AC6" s="13">
+      <c r="AD6" s="13">
         <v>3650</v>
       </c>
-      <c r="AD6" s="13">
+      <c r="AE6" s="13">
         <v>3720</v>
       </c>
-      <c r="AE6" s="13"/>
       <c r="AF6" s="13"/>
       <c r="AG6" s="13"/>
       <c r="AH6" s="13"/>
@@ -2145,41 +2124,42 @@
       <c r="BJ6" s="13"/>
       <c r="BK6" s="13"/>
       <c r="BL6" s="13"/>
-      <c r="BM6" s="29"/>
-      <c r="BN6" s="13"/>
+      <c r="BM6" s="13"/>
+      <c r="BN6" s="29"/>
       <c r="BO6" s="13"/>
-      <c r="BP6" s="29"/>
-      <c r="BQ6" s="13"/>
+      <c r="BP6" s="13"/>
+      <c r="BQ6" s="29"/>
       <c r="BR6" s="13"/>
       <c r="BS6" s="13"/>
-      <c r="BU6" s="13">
+      <c r="BT6" s="13"/>
+      <c r="BV6" s="13">
         <f t="shared" si="0"/>
         <v>1033.7</v>
       </c>
-      <c r="BV6" s="13">
+      <c r="BW6" s="13">
         <f t="shared" si="1"/>
         <v>1010</v>
       </c>
-      <c r="BW6" s="13">
-        <f t="shared" ref="BW6" si="2">(BV6-BU6)</f>
+      <c r="BX6" s="13">
+        <f t="shared" ref="BX6" si="2">(BW6-BV6)</f>
         <v>-23.700000000000045</v>
       </c>
-      <c r="BX6" s="13">
-        <f>((BL6-H6)/H6)*100</f>
+      <c r="BY6" s="13">
+        <f>((BM6-H6)/H6)*100</f>
         <v>-100</v>
       </c>
-      <c r="BY6">
+      <c r="BZ6">
         <v>5</v>
       </c>
-      <c r="BZ6">
+      <c r="CA6">
         <v>3566</v>
       </c>
-      <c r="CA6" s="15">
-        <f>(BY6*BZ6-BY6*H6)/100</f>
+      <c r="CB6" s="15">
+        <f>(BZ6*CA6-BZ6*H6)/100</f>
         <v>-23.7</v>
       </c>
     </row>
-    <row r="7" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="7" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1148899</v>
       </c>
@@ -2208,99 +2188,101 @@
         <v>3585</v>
       </c>
       <c r="I7" s="13">
+        <v>3996</v>
+      </c>
+      <c r="J7" s="13">
+        <v>3996</v>
+      </c>
+      <c r="K7" s="13">
         <v>3954</v>
       </c>
-      <c r="J7" s="13">
+      <c r="L7" s="13">
+        <v>3955</v>
+      </c>
+      <c r="M7" s="13">
+        <v>4022</v>
+      </c>
+      <c r="N7" s="13">
+        <v>4033</v>
+      </c>
+      <c r="O7" s="13">
+        <v>3988</v>
+      </c>
+      <c r="P7" s="13">
+        <v>3916</v>
+      </c>
+      <c r="Q7" s="13">
         <v>3954</v>
       </c>
-      <c r="K7" s="13">
-        <v>3955</v>
-      </c>
-      <c r="L7" s="13">
-        <v>4022</v>
-      </c>
-      <c r="M7" s="13">
-        <v>4033</v>
-      </c>
-      <c r="N7" s="13">
-        <v>3988</v>
-      </c>
-      <c r="O7" s="13">
-        <v>3916</v>
-      </c>
-      <c r="P7" s="13">
-        <v>3954</v>
-      </c>
-      <c r="Q7" s="13">
+      <c r="R7" s="13">
         <v>3932</v>
       </c>
-      <c r="R7" s="13">
+      <c r="S7" s="13">
         <v>3949</v>
       </c>
-      <c r="S7" s="13">
+      <c r="T7" s="13">
         <v>3943</v>
       </c>
-      <c r="T7" s="13">
+      <c r="U7" s="13">
         <v>3928</v>
       </c>
-      <c r="U7" s="13">
+      <c r="V7" s="13">
         <v>3913</v>
       </c>
-      <c r="V7" s="13">
+      <c r="W7" s="13">
         <v>3860</v>
       </c>
-      <c r="W7" s="13">
+      <c r="X7" s="13">
         <v>3893</v>
       </c>
-      <c r="X7" s="13">
+      <c r="Y7" s="13">
         <v>3900</v>
-      </c>
-      <c r="Y7" s="13">
-        <v>3842</v>
       </c>
       <c r="Z7" s="13">
         <v>3842</v>
       </c>
       <c r="AA7" s="13">
+        <v>3842</v>
+      </c>
+      <c r="AB7" s="13">
         <v>3841</v>
       </c>
-      <c r="AB7" s="13">
+      <c r="AC7" s="13">
         <v>3809</v>
       </c>
-      <c r="AC7" s="13">
+      <c r="AD7" s="13">
         <v>3810</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AE7" s="13">
         <v>3798</v>
       </c>
-      <c r="AE7" s="13">
+      <c r="AF7" s="13">
         <v>3713</v>
       </c>
-      <c r="AF7" s="13">
+      <c r="AG7" s="13">
         <v>3657</v>
       </c>
-      <c r="AG7" s="13">
+      <c r="AH7" s="13">
         <v>3592</v>
       </c>
-      <c r="AH7" s="13">
+      <c r="AI7" s="13">
         <v>3621</v>
       </c>
-      <c r="AI7" s="13">
+      <c r="AJ7" s="13">
         <v>3572</v>
       </c>
-      <c r="AJ7" s="13">
+      <c r="AK7" s="13">
         <v>3580</v>
       </c>
-      <c r="AK7" s="13">
+      <c r="AL7" s="13">
         <v>3569</v>
       </c>
-      <c r="AL7" s="13">
+      <c r="AM7" s="13">
         <v>3659</v>
       </c>
-      <c r="AM7" s="13">
+      <c r="AN7" s="13">
         <v>3656</v>
       </c>
-      <c r="AN7" s="13"/>
       <c r="AO7" s="13"/>
       <c r="AP7" s="13"/>
       <c r="AQ7" s="13"/>
@@ -2325,27 +2307,28 @@
       <c r="BJ7" s="13"/>
       <c r="BK7" s="13"/>
       <c r="BL7" s="13"/>
-      <c r="BM7" s="29"/>
-      <c r="BN7" s="13"/>
+      <c r="BM7" s="13"/>
+      <c r="BN7" s="29"/>
       <c r="BO7" s="13"/>
-      <c r="BP7" s="29"/>
-      <c r="BQ7" s="13"/>
+      <c r="BP7" s="13"/>
+      <c r="BQ7" s="29"/>
       <c r="BR7" s="13"/>
       <c r="BS7" s="13"/>
       <c r="BT7" s="13"/>
-      <c r="BU7" s="13">
+      <c r="BU7" s="13"/>
+      <c r="BV7" s="13">
         <f t="shared" si="0"/>
         <v>2509.5</v>
       </c>
-      <c r="BV7" s="13">
+      <c r="BW7" s="13">
         <f t="shared" si="1"/>
         <v>2509.5</v>
       </c>
-      <c r="BW7" s="13"/>
       <c r="BX7" s="13"/>
-      <c r="CA7" s="15"/>
-    </row>
-    <row r="8" spans="1:79" ht="45" customHeight="1" thickBot="1">
+      <c r="BY7" s="13"/>
+      <c r="CB7" s="15"/>
+    </row>
+    <row r="8" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1082379</v>
       </c>
@@ -2359,7 +2342,7 @@
       </c>
       <c r="D8" s="6" t="str">
         <f>IF(I8&lt;GEMINI!L8,"למכור בהפסד",IF(I8&gt;GEMINI!M8,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור ברווח</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>52</v>
@@ -2374,135 +2357,137 @@
         <v>37875</v>
       </c>
       <c r="I8" s="13">
+        <v>45300</v>
+      </c>
+      <c r="J8" s="13">
+        <v>45300</v>
+      </c>
+      <c r="K8" s="13">
         <v>40740</v>
       </c>
-      <c r="J8" s="13">
-        <v>40740</v>
-      </c>
-      <c r="K8" s="13">
+      <c r="L8" s="13">
         <v>39070</v>
       </c>
-      <c r="L8" s="13">
+      <c r="M8" s="13">
         <v>39600</v>
       </c>
-      <c r="M8" s="13">
+      <c r="N8" s="13">
         <v>43640</v>
       </c>
-      <c r="N8" s="13">
+      <c r="O8" s="13">
         <v>42700</v>
       </c>
-      <c r="O8" s="13">
+      <c r="P8" s="13">
         <v>42140</v>
       </c>
-      <c r="P8" s="13">
+      <c r="Q8" s="13">
         <v>43490</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="R8" s="13">
         <v>40750</v>
       </c>
-      <c r="R8" s="13">
+      <c r="S8" s="13">
         <v>40900</v>
       </c>
-      <c r="S8" s="13">
+      <c r="T8" s="13">
         <v>40790</v>
       </c>
-      <c r="T8" s="13">
+      <c r="U8" s="13">
         <v>40820</v>
       </c>
-      <c r="U8" s="13">
+      <c r="V8" s="13">
         <v>41570</v>
       </c>
-      <c r="V8" s="13">
+      <c r="W8" s="13">
         <v>42050</v>
       </c>
-      <c r="W8" s="13">
+      <c r="X8" s="13">
         <v>39960</v>
       </c>
-      <c r="X8" s="13">
+      <c r="Y8" s="13">
         <v>39990</v>
-      </c>
-      <c r="Y8" s="13">
-        <v>38680</v>
       </c>
       <c r="Z8" s="13">
         <v>38680</v>
       </c>
       <c r="AA8" s="13">
+        <v>38680</v>
+      </c>
+      <c r="AB8" s="13">
         <v>37770</v>
       </c>
-      <c r="AB8" s="13">
+      <c r="AC8" s="13">
         <v>36330</v>
       </c>
-      <c r="AC8" s="13">
+      <c r="AD8" s="13">
         <v>38680</v>
       </c>
-      <c r="AD8" s="13">
+      <c r="AE8" s="13">
         <v>39090</v>
       </c>
-      <c r="AE8" s="13">
+      <c r="AF8" s="13">
         <v>37300</v>
       </c>
-      <c r="AF8" s="13">
+      <c r="AG8" s="13">
         <v>37650</v>
       </c>
-      <c r="AG8" s="13">
+      <c r="AH8" s="13">
         <v>37300</v>
       </c>
-      <c r="AH8" s="13">
+      <c r="AI8" s="13">
         <v>39450</v>
       </c>
-      <c r="AI8" s="13">
+      <c r="AJ8" s="13">
         <v>38390</v>
       </c>
-      <c r="AJ8" s="13">
+      <c r="AK8" s="13">
         <v>38800</v>
       </c>
-      <c r="AK8" s="13">
+      <c r="AL8" s="13">
         <v>38510</v>
-      </c>
-      <c r="AL8" s="13">
-        <v>38970</v>
       </c>
       <c r="AM8" s="13">
         <v>38970</v>
       </c>
       <c r="AN8" s="13">
-        <v>37700</v>
+        <v>38970</v>
       </c>
       <c r="AO8" s="13">
         <v>37700</v>
       </c>
       <c r="AP8" s="13">
+        <v>37700</v>
+      </c>
+      <c r="AQ8" s="13">
         <v>37750</v>
       </c>
-      <c r="AQ8" s="13">
+      <c r="AR8" s="13">
         <v>38430</v>
       </c>
-      <c r="AR8" s="13">
+      <c r="AS8" s="13">
         <v>38250</v>
       </c>
-      <c r="AS8" s="13">
+      <c r="AT8" s="13">
         <v>40110</v>
       </c>
-      <c r="AT8" s="13">
+      <c r="AU8" s="13">
         <v>40820</v>
       </c>
-      <c r="AU8" s="13">
+      <c r="AV8" s="13">
         <v>39320</v>
       </c>
-      <c r="AV8" s="13">
+      <c r="AW8" s="13">
         <v>37800</v>
       </c>
-      <c r="AW8" s="13">
+      <c r="AX8" s="13">
         <v>36620</v>
       </c>
-      <c r="AX8" s="13">
+      <c r="AY8" s="13">
         <v>37130</v>
       </c>
-      <c r="AY8" s="13">
+      <c r="AZ8" s="13">
         <v>35850</v>
       </c>
-      <c r="AZ8" s="13"/>
       <c r="BA8" s="13"/>
       <c r="BB8" s="13"/>
       <c r="BC8" s="13"/>
@@ -2515,39 +2500,40 @@
       <c r="BJ8" s="13"/>
       <c r="BK8" s="13"/>
       <c r="BL8" s="13"/>
-      <c r="BM8" s="29"/>
-      <c r="BN8" s="13"/>
+      <c r="BM8" s="13"/>
+      <c r="BN8" s="29"/>
       <c r="BO8" s="13"/>
-      <c r="BP8" s="29"/>
-      <c r="BQ8" s="13"/>
+      <c r="BP8" s="13"/>
+      <c r="BQ8" s="29"/>
       <c r="BR8" s="13"/>
       <c r="BS8" s="13"/>
       <c r="BT8" s="13"/>
-      <c r="BU8" s="13">
+      <c r="BU8" s="13"/>
+      <c r="BV8" s="13">
         <f t="shared" si="0"/>
         <v>806.25</v>
       </c>
-      <c r="BV8" s="13">
+      <c r="BW8" s="13">
         <f t="shared" si="1"/>
         <v>757.5</v>
       </c>
-      <c r="BW8" s="13">
-        <f t="shared" ref="BW8:BW11" si="3">(BV8-BU8)</f>
+      <c r="BX8" s="13">
+        <f t="shared" ref="BX8:BX11" si="3">(BW8-BV8)</f>
         <v>-48.75</v>
       </c>
-      <c r="BX8" s="13"/>
-      <c r="BY8">
+      <c r="BY8" s="13"/>
+      <c r="BZ8">
         <v>3</v>
       </c>
-      <c r="BZ8">
+      <c r="CA8">
         <v>36250</v>
       </c>
-      <c r="CA8" s="15">
-        <f t="shared" ref="CA8:CA18" si="4">(BY8*BZ8-BY8*H8)/100</f>
+      <c r="CB8" s="15">
+        <f t="shared" ref="CB8:CB18" si="4">(BZ8*CA8-BZ8*H8)/100</f>
         <v>-48.75</v>
       </c>
     </row>
-    <row r="9" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="9" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>629014</v>
       </c>
@@ -2576,129 +2562,131 @@
         <v>9227</v>
       </c>
       <c r="I9" s="13">
+        <v>10660</v>
+      </c>
+      <c r="J9" s="13">
+        <v>10660</v>
+      </c>
+      <c r="K9" s="13">
         <v>10820</v>
       </c>
-      <c r="J9" s="13">
-        <v>10820</v>
-      </c>
-      <c r="K9" s="13">
+      <c r="L9" s="13">
         <v>10680</v>
       </c>
-      <c r="L9" s="13">
+      <c r="M9" s="13">
         <v>11290</v>
       </c>
-      <c r="M9" s="13">
+      <c r="N9" s="13">
         <v>11020</v>
-      </c>
-      <c r="N9" s="13">
-        <v>10100</v>
       </c>
       <c r="O9" s="13">
         <v>10100</v>
       </c>
       <c r="P9" s="13">
+        <v>10100</v>
+      </c>
+      <c r="Q9" s="13">
         <v>10240</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="R9" s="13">
         <v>9891</v>
       </c>
-      <c r="R9" s="13">
+      <c r="S9" s="13">
         <v>9956</v>
       </c>
-      <c r="S9" s="13">
+      <c r="T9" s="13">
         <v>9910</v>
       </c>
-      <c r="T9" s="13">
+      <c r="U9" s="13">
         <v>9960</v>
       </c>
-      <c r="U9" s="13">
+      <c r="V9" s="13">
         <v>9924</v>
       </c>
-      <c r="V9" s="13">
+      <c r="W9" s="13">
         <v>9999</v>
       </c>
-      <c r="W9" s="13">
+      <c r="X9" s="13">
         <v>9962</v>
       </c>
-      <c r="X9" s="13">
+      <c r="Y9" s="13">
         <v>9979</v>
-      </c>
-      <c r="Y9" s="13">
-        <v>10130</v>
       </c>
       <c r="Z9" s="13">
         <v>10130</v>
       </c>
       <c r="AA9" s="13">
+        <v>10130</v>
+      </c>
+      <c r="AB9" s="13">
         <v>10400</v>
       </c>
-      <c r="AB9" s="13">
+      <c r="AC9" s="13">
         <v>10320</v>
       </c>
-      <c r="AC9" s="13">
+      <c r="AD9" s="13">
         <v>10300</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AE9" s="13">
         <v>10310</v>
       </c>
-      <c r="AE9" s="13">
+      <c r="AF9" s="13">
         <v>9672</v>
       </c>
-      <c r="AF9" s="13">
+      <c r="AG9" s="13">
         <v>9953</v>
       </c>
-      <c r="AG9" s="13">
+      <c r="AH9" s="13">
         <v>10090</v>
       </c>
-      <c r="AH9" s="13">
+      <c r="AI9" s="13">
         <v>10070</v>
       </c>
-      <c r="AI9" s="13">
+      <c r="AJ9" s="13">
         <v>10030</v>
       </c>
-      <c r="AJ9" s="13">
+      <c r="AK9" s="13">
         <v>10120</v>
       </c>
-      <c r="AK9" s="13">
+      <c r="AL9" s="13">
         <v>10000</v>
       </c>
-      <c r="AL9" s="13">
+      <c r="AM9" s="13">
         <v>10080</v>
       </c>
-      <c r="AM9" s="13">
+      <c r="AN9" s="13">
         <v>10030</v>
-      </c>
-      <c r="AN9" s="13">
-        <v>9726</v>
       </c>
       <c r="AO9" s="13">
         <v>9726</v>
       </c>
       <c r="AP9" s="13">
+        <v>9726</v>
+      </c>
+      <c r="AQ9" s="13">
         <v>9659</v>
       </c>
-      <c r="AQ9" s="13">
+      <c r="AR9" s="13">
         <v>9670</v>
       </c>
-      <c r="AR9" s="13">
+      <c r="AS9" s="13">
         <v>9590</v>
       </c>
-      <c r="AS9" s="13">
+      <c r="AT9" s="13">
         <v>9588</v>
       </c>
-      <c r="AT9" s="13">
+      <c r="AU9" s="13">
         <v>9400</v>
       </c>
-      <c r="AU9" s="13">
+      <c r="AV9" s="13">
         <v>9320</v>
       </c>
-      <c r="AV9" s="13">
+      <c r="AW9" s="13">
         <v>9071</v>
       </c>
-      <c r="AW9" s="13">
+      <c r="AX9" s="13">
         <v>9271</v>
       </c>
-      <c r="AX9" s="13"/>
       <c r="AY9" s="13"/>
       <c r="AZ9" s="13"/>
       <c r="BA9" s="13"/>
@@ -2713,39 +2701,40 @@
       <c r="BJ9" s="13"/>
       <c r="BK9" s="13"/>
       <c r="BL9" s="13"/>
-      <c r="BM9" s="29"/>
-      <c r="BN9" s="13"/>
+      <c r="BM9" s="13"/>
+      <c r="BN9" s="29"/>
       <c r="BO9" s="13"/>
-      <c r="BP9" s="29"/>
-      <c r="BQ9" s="13"/>
+      <c r="BP9" s="13"/>
+      <c r="BQ9" s="29"/>
       <c r="BR9" s="13"/>
       <c r="BS9" s="13"/>
       <c r="BT9" s="13"/>
-      <c r="BU9" s="13">
+      <c r="BU9" s="13"/>
+      <c r="BV9" s="13">
         <f t="shared" si="0"/>
         <v>-38.65</v>
       </c>
-      <c r="BV9" s="13">
+      <c r="BW9" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BW9" s="13">
+      <c r="BX9" s="13">
         <f t="shared" si="3"/>
         <v>38.65</v>
       </c>
-      <c r="BX9" s="13"/>
-      <c r="BY9">
+      <c r="BY9" s="13"/>
+      <c r="BZ9">
         <v>5</v>
       </c>
-      <c r="BZ9">
+      <c r="CA9">
         <v>10000</v>
       </c>
-      <c r="CA9" s="15">
+      <c r="CB9" s="15">
         <f t="shared" si="4"/>
         <v>38.65</v>
       </c>
     </row>
-    <row r="10" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="10" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1141464</v>
       </c>
@@ -2774,211 +2763,214 @@
         <v>4834</v>
       </c>
       <c r="I10" s="13">
-        <v>5067</v>
+        <v>5027</v>
       </c>
       <c r="J10" s="13">
-        <v>5067</v>
+        <v>5027</v>
       </c>
       <c r="K10" s="13">
         <v>5067</v>
       </c>
       <c r="L10" s="13">
+        <v>5067</v>
+      </c>
+      <c r="M10" s="13">
         <v>5126</v>
       </c>
-      <c r="M10" s="13">
+      <c r="N10" s="13">
         <v>5164</v>
-      </c>
-      <c r="N10" s="13">
-        <v>4809</v>
       </c>
       <c r="O10" s="13">
         <v>4809</v>
       </c>
       <c r="P10" s="13">
+        <v>4809</v>
+      </c>
+      <c r="Q10" s="13">
         <v>4849</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="R10" s="13">
         <v>4821</v>
       </c>
-      <c r="R10" s="13">
+      <c r="S10" s="13">
         <v>4925</v>
       </c>
-      <c r="S10" s="13">
+      <c r="T10" s="13">
         <v>5013</v>
-      </c>
-      <c r="T10" s="13">
-        <v>5050</v>
       </c>
       <c r="U10" s="13">
         <v>5050</v>
       </c>
       <c r="V10" s="13">
+        <v>5050</v>
+      </c>
+      <c r="W10" s="13">
         <v>4930</v>
       </c>
-      <c r="W10" s="13">
+      <c r="X10" s="13">
         <v>5150</v>
       </c>
-      <c r="X10" s="13">
+      <c r="Y10" s="13">
         <v>5283</v>
-      </c>
-      <c r="Y10" s="13">
-        <v>5253</v>
       </c>
       <c r="Z10" s="13">
         <v>5253</v>
       </c>
       <c r="AA10" s="13">
+        <v>5253</v>
+      </c>
+      <c r="AB10" s="13">
         <v>5400</v>
       </c>
-      <c r="AB10" s="13">
+      <c r="AC10" s="13">
         <v>5522</v>
       </c>
-      <c r="AC10" s="13">
+      <c r="AD10" s="13">
         <v>5690</v>
       </c>
-      <c r="AD10" s="13">
+      <c r="AE10" s="13">
         <v>5749</v>
       </c>
-      <c r="AE10" s="13">
+      <c r="AF10" s="13">
         <v>5840</v>
-      </c>
-      <c r="AF10" s="13">
-        <v>5650</v>
       </c>
       <c r="AG10" s="13">
         <v>5650</v>
       </c>
       <c r="AH10" s="13">
+        <v>5650</v>
+      </c>
+      <c r="AI10" s="13">
         <v>5841</v>
       </c>
-      <c r="AI10" s="13">
+      <c r="AJ10" s="13">
         <v>5758</v>
       </c>
-      <c r="AJ10" s="13">
+      <c r="AK10" s="13">
         <v>5673</v>
       </c>
-      <c r="AK10" s="13">
+      <c r="AL10" s="13">
         <v>5609</v>
       </c>
-      <c r="AL10" s="13">
+      <c r="AM10" s="13">
         <v>5750</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AN10" s="13">
         <v>5841</v>
-      </c>
-      <c r="AN10" s="13">
-        <v>5564</v>
       </c>
       <c r="AO10" s="13">
         <v>5564</v>
       </c>
       <c r="AP10" s="13">
+        <v>5564</v>
+      </c>
+      <c r="AQ10" s="13">
         <v>5557</v>
       </c>
-      <c r="AQ10" s="13">
+      <c r="AR10" s="13">
         <v>5501</v>
       </c>
-      <c r="AR10" s="13">
+      <c r="AS10" s="13">
         <v>5250</v>
       </c>
-      <c r="AS10" s="13">
+      <c r="AT10" s="13">
         <v>5270</v>
       </c>
-      <c r="AT10" s="13">
+      <c r="AU10" s="13">
         <v>5149</v>
       </c>
-      <c r="AU10" s="13">
+      <c r="AV10" s="13">
         <v>5092</v>
       </c>
-      <c r="AV10" s="13">
+      <c r="AW10" s="13">
         <v>5228</v>
       </c>
-      <c r="AW10" s="13">
+      <c r="AX10" s="13">
         <v>5301</v>
       </c>
-      <c r="AX10" s="13">
+      <c r="AY10" s="13">
         <v>5159</v>
       </c>
-      <c r="AY10" s="13">
+      <c r="AZ10" s="13">
         <v>5198</v>
       </c>
-      <c r="AZ10" s="13">
+      <c r="BA10" s="13">
         <v>5077</v>
       </c>
-      <c r="BA10" s="13">
+      <c r="BB10" s="13">
         <v>4842</v>
       </c>
-      <c r="BB10" s="13">
+      <c r="BC10" s="13">
         <v>5050</v>
       </c>
-      <c r="BC10" s="13">
+      <c r="BD10" s="13">
         <v>4970</v>
       </c>
-      <c r="BD10" s="13">
+      <c r="BE10" s="13">
         <v>4880</v>
       </c>
-      <c r="BE10" s="13">
+      <c r="BF10" s="13">
         <v>4704</v>
       </c>
-      <c r="BF10" s="13">
+      <c r="BG10" s="13">
         <v>4770</v>
       </c>
-      <c r="BG10" s="13">
+      <c r="BH10" s="13">
         <v>4609</v>
       </c>
-      <c r="BH10" s="13">
+      <c r="BI10" s="13">
         <v>4674</v>
       </c>
-      <c r="BI10" s="13">
+      <c r="BJ10" s="13">
         <v>4710</v>
       </c>
-      <c r="BJ10" s="13">
+      <c r="BK10" s="13">
         <v>4688</v>
       </c>
-      <c r="BK10" s="13">
+      <c r="BL10" s="13">
         <v>4900</v>
       </c>
-      <c r="BL10" s="13">
+      <c r="BM10" s="13">
         <v>5000</v>
       </c>
-      <c r="BM10" s="29">
+      <c r="BN10" s="29">
         <v>4932</v>
       </c>
-      <c r="BN10" s="13"/>
       <c r="BO10" s="13"/>
-      <c r="BP10" s="29"/>
-      <c r="BQ10" s="13"/>
+      <c r="BP10" s="13"/>
+      <c r="BQ10" s="29"/>
       <c r="BR10" s="13"/>
       <c r="BS10" s="13"/>
       <c r="BT10" s="13"/>
-      <c r="BU10" s="13">
+      <c r="BU10" s="13"/>
+      <c r="BV10" s="13">
         <f t="shared" si="0"/>
         <v>-87.859799999999964</v>
       </c>
-      <c r="BV10" s="13">
+      <c r="BW10" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BW10" s="13">
+      <c r="BX10" s="13">
         <f t="shared" si="3"/>
         <v>87.859799999999964</v>
       </c>
-      <c r="BX10" s="13">
-        <f>((BL10-H10)/H10)*100</f>
+      <c r="BY10" s="13">
+        <f>((BM10-H10)/H10)*100</f>
         <v>3.434009102192801</v>
       </c>
-      <c r="BY10">
+      <c r="BZ10">
         <v>21</v>
       </c>
-      <c r="BZ10">
+      <c r="CA10">
         <v>5252.38</v>
       </c>
-      <c r="CA10" s="15">
+      <c r="CB10" s="15">
         <f t="shared" si="4"/>
         <v>87.859799999999964</v>
       </c>
     </row>
-    <row r="11" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="11" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1166974</v>
       </c>
@@ -3007,93 +2999,95 @@
         <v>901.87</v>
       </c>
       <c r="I11" s="13">
+        <v>1086</v>
+      </c>
+      <c r="J11" s="13">
+        <v>1086</v>
+      </c>
+      <c r="K11" s="13">
         <v>1054</v>
       </c>
-      <c r="J11" s="13">
-        <v>1054</v>
-      </c>
-      <c r="K11" s="13">
+      <c r="L11" s="13">
         <v>1063</v>
       </c>
-      <c r="L11" s="13">
+      <c r="M11" s="13">
         <v>1099</v>
       </c>
-      <c r="M11" s="13">
+      <c r="N11" s="13">
         <v>1173</v>
       </c>
-      <c r="N11" s="13">
+      <c r="O11" s="13">
         <v>1114</v>
       </c>
-      <c r="O11" s="13">
+      <c r="P11" s="13">
         <v>1075</v>
       </c>
-      <c r="P11" s="13">
+      <c r="Q11" s="13">
         <v>1109</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="R11" s="13">
         <v>1090</v>
       </c>
-      <c r="R11" s="13">
+      <c r="S11" s="13">
         <v>1144</v>
       </c>
-      <c r="S11" s="13">
+      <c r="T11" s="13">
         <v>1162</v>
       </c>
-      <c r="T11" s="13">
+      <c r="U11" s="13">
         <v>1109</v>
       </c>
-      <c r="U11" s="13">
+      <c r="V11" s="13">
         <v>1029</v>
       </c>
-      <c r="V11" s="13">
+      <c r="W11" s="13">
         <v>993</v>
       </c>
-      <c r="W11" s="13">
+      <c r="X11" s="13">
         <v>1017</v>
       </c>
-      <c r="X11" s="13">
+      <c r="Y11" s="13">
         <v>960</v>
-      </c>
-      <c r="Y11" s="13">
-        <v>965</v>
       </c>
       <c r="Z11" s="13">
         <v>965</v>
       </c>
       <c r="AA11" s="13">
+        <v>965</v>
+      </c>
+      <c r="AB11" s="13">
         <v>951.7</v>
       </c>
-      <c r="AB11" s="13">
+      <c r="AC11" s="13">
         <v>946</v>
       </c>
-      <c r="AC11" s="13">
+      <c r="AD11" s="13">
         <v>869.2</v>
       </c>
-      <c r="AD11" s="13">
+      <c r="AE11" s="13">
         <v>865</v>
       </c>
-      <c r="AE11" s="13">
+      <c r="AF11" s="13">
         <v>851</v>
       </c>
-      <c r="AF11" s="13">
+      <c r="AG11" s="13">
         <v>829.3</v>
       </c>
-      <c r="AG11" s="13">
+      <c r="AH11" s="13">
         <v>830</v>
       </c>
-      <c r="AH11" s="13">
+      <c r="AI11" s="13">
         <v>810</v>
       </c>
-      <c r="AI11" s="13">
+      <c r="AJ11" s="13">
         <v>812.8</v>
       </c>
-      <c r="AJ11" s="13">
+      <c r="AK11" s="13">
         <v>788</v>
       </c>
-      <c r="AK11" s="13">
+      <c r="AL11" s="13">
         <v>772</v>
       </c>
-      <c r="AL11" s="13"/>
       <c r="AM11" s="13"/>
       <c r="AN11" s="13"/>
       <c r="AO11" s="13"/>
@@ -3120,33 +3114,34 @@
       <c r="BJ11" s="13"/>
       <c r="BK11" s="13"/>
       <c r="BL11" s="13"/>
-      <c r="BM11" s="29"/>
-      <c r="BN11" s="13"/>
+      <c r="BM11" s="13"/>
+      <c r="BN11" s="29"/>
       <c r="BO11" s="13"/>
-      <c r="BP11" s="29"/>
-      <c r="BQ11" s="13"/>
+      <c r="BP11" s="13"/>
+      <c r="BQ11" s="29"/>
       <c r="BR11" s="13"/>
       <c r="BS11" s="13"/>
       <c r="BT11" s="13"/>
-      <c r="BU11" s="13">
+      <c r="BU11" s="13"/>
+      <c r="BV11" s="13">
         <f t="shared" si="0"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BV11" s="13">
+      <c r="BW11" s="13">
         <f t="shared" si="1"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BW11" s="13">
+      <c r="BX11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BX11" s="13"/>
-      <c r="CA11" s="15">
+      <c r="BY11" s="13"/>
+      <c r="CB11" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="12" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1176593</v>
       </c>
@@ -3175,99 +3170,101 @@
         <v>22581.42</v>
       </c>
       <c r="I12" s="13">
+        <v>29650</v>
+      </c>
+      <c r="J12" s="13">
+        <v>29650</v>
+      </c>
+      <c r="K12" s="13">
         <v>28730</v>
       </c>
-      <c r="J12" s="13">
-        <v>28730</v>
-      </c>
-      <c r="K12" s="13">
+      <c r="L12" s="13">
         <v>28240</v>
       </c>
-      <c r="L12" s="13">
+      <c r="M12" s="13">
         <v>29460</v>
       </c>
-      <c r="M12" s="13">
+      <c r="N12" s="13">
         <v>28720</v>
-      </c>
-      <c r="N12" s="13">
-        <v>27890</v>
       </c>
       <c r="O12" s="13">
         <v>27890</v>
       </c>
       <c r="P12" s="13">
+        <v>27890</v>
+      </c>
+      <c r="Q12" s="13">
         <v>30100</v>
       </c>
-      <c r="Q12" s="13">
+      <c r="R12" s="13">
         <v>30500</v>
       </c>
-      <c r="R12" s="13">
+      <c r="S12" s="13">
         <v>28850</v>
       </c>
-      <c r="S12" s="13">
+      <c r="T12" s="13">
         <v>27450</v>
       </c>
-      <c r="T12" s="13">
+      <c r="U12" s="13">
         <v>26940</v>
       </c>
-      <c r="U12" s="13">
+      <c r="V12" s="13">
         <v>26800</v>
       </c>
-      <c r="V12" s="13">
+      <c r="W12" s="13">
         <v>25950</v>
       </c>
-      <c r="W12" s="13">
+      <c r="X12" s="13">
         <v>26000</v>
       </c>
-      <c r="X12" s="13">
+      <c r="Y12" s="13">
         <v>26600</v>
-      </c>
-      <c r="Y12" s="13">
-        <v>24630</v>
       </c>
       <c r="Z12" s="13">
         <v>24630</v>
       </c>
       <c r="AA12" s="13">
+        <v>24630</v>
+      </c>
+      <c r="AB12" s="13">
         <v>25230</v>
       </c>
-      <c r="AB12" s="13">
+      <c r="AC12" s="13">
         <v>24700</v>
       </c>
-      <c r="AC12" s="13">
+      <c r="AD12" s="13">
         <v>23780</v>
       </c>
-      <c r="AD12" s="13">
+      <c r="AE12" s="13">
         <v>23920</v>
       </c>
-      <c r="AE12" s="13">
+      <c r="AF12" s="13">
         <v>22390</v>
       </c>
-      <c r="AF12" s="13">
+      <c r="AG12" s="13">
         <v>23000</v>
       </c>
-      <c r="AG12" s="13">
+      <c r="AH12" s="13">
         <v>20990</v>
       </c>
-      <c r="AH12" s="13">
+      <c r="AI12" s="13">
         <v>20260</v>
       </c>
-      <c r="AI12" s="13">
+      <c r="AJ12" s="13">
         <v>19200</v>
       </c>
-      <c r="AJ12" s="13">
+      <c r="AK12" s="13">
         <v>19860</v>
       </c>
-      <c r="AK12" s="13">
+      <c r="AL12" s="13">
         <v>19700</v>
       </c>
-      <c r="AL12" s="13">
+      <c r="AM12" s="13">
         <v>19430</v>
       </c>
-      <c r="AM12" s="13">
+      <c r="AN12" s="13">
         <v>19020</v>
       </c>
-      <c r="AN12" s="13"/>
       <c r="AO12" s="13"/>
       <c r="AP12" s="13"/>
       <c r="AQ12" s="13"/>
@@ -3292,36 +3289,37 @@
       <c r="BJ12" s="13"/>
       <c r="BK12" s="13"/>
       <c r="BL12" s="13"/>
-      <c r="BM12" s="29"/>
-      <c r="BN12" s="13"/>
+      <c r="BM12" s="13"/>
+      <c r="BN12" s="29"/>
       <c r="BO12" s="13"/>
-      <c r="BP12" s="29"/>
-      <c r="BQ12" s="13"/>
+      <c r="BP12" s="13"/>
+      <c r="BQ12" s="29"/>
       <c r="BR12" s="13"/>
       <c r="BS12" s="13"/>
       <c r="BT12" s="13"/>
-      <c r="BU12" s="13">
+      <c r="BU12" s="13"/>
+      <c r="BV12" s="13">
         <f t="shared" si="0"/>
         <v>-331.70059999999995</v>
       </c>
-      <c r="BV12" s="13">
+      <c r="BW12" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BW12" s="13"/>
       <c r="BX12" s="13"/>
-      <c r="BY12">
+      <c r="BY12" s="13"/>
+      <c r="BZ12">
         <v>7</v>
       </c>
-      <c r="BZ12">
+      <c r="CA12">
         <v>27320</v>
       </c>
-      <c r="CA12" s="15">
+      <c r="CB12" s="15">
         <f t="shared" si="4"/>
         <v>331.70059999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="13" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>397018</v>
       </c>
@@ -3338,61 +3336,63 @@
         <v>למכור בהפסד</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F13" s="4">
-        <v>46042</v>
+        <v>46062</v>
       </c>
       <c r="G13" s="27">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H13" s="13">
-        <v>723</v>
+        <v>840</v>
       </c>
       <c r="I13" s="13">
+        <v>840</v>
+      </c>
+      <c r="J13" s="13">
+        <v>840</v>
+      </c>
+      <c r="K13" s="13">
         <v>837.7</v>
       </c>
-      <c r="J13" s="13">
-        <v>837.7</v>
-      </c>
-      <c r="K13" s="13">
+      <c r="L13" s="13">
         <v>802</v>
       </c>
-      <c r="L13" s="13">
+      <c r="M13" s="13">
         <v>1009</v>
       </c>
-      <c r="M13" s="13">
+      <c r="N13" s="13">
         <v>1074</v>
-      </c>
-      <c r="N13" s="13">
-        <v>900</v>
       </c>
       <c r="O13" s="13">
         <v>900</v>
       </c>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13">
+      <c r="P13" s="13">
+        <v>900</v>
+      </c>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13">
         <v>1490</v>
       </c>
-      <c r="R13" s="13">
+      <c r="S13" s="13">
         <v>1210</v>
       </c>
-      <c r="S13" s="13">
+      <c r="T13" s="13">
         <v>1100</v>
       </c>
-      <c r="T13" s="13">
+      <c r="U13" s="13">
         <v>980</v>
       </c>
-      <c r="U13" s="13">
+      <c r="V13" s="13">
         <v>932.1</v>
       </c>
-      <c r="V13" s="13">
+      <c r="W13" s="13">
         <v>822</v>
       </c>
-      <c r="W13" s="13">
+      <c r="X13" s="13">
         <v>790</v>
       </c>
-      <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
@@ -3433,33 +3433,34 @@
       <c r="BJ13" s="13"/>
       <c r="BK13" s="13"/>
       <c r="BL13" s="13"/>
-      <c r="BM13" s="29"/>
-      <c r="BN13" s="13"/>
+      <c r="BM13" s="13"/>
+      <c r="BN13" s="29"/>
       <c r="BO13" s="13"/>
-      <c r="BP13" s="29"/>
-      <c r="BQ13" s="13"/>
+      <c r="BP13" s="13"/>
+      <c r="BQ13" s="29"/>
       <c r="BR13" s="13"/>
       <c r="BS13" s="13"/>
       <c r="BT13" s="13"/>
-      <c r="BU13" s="13">
+      <c r="BU13" s="13"/>
+      <c r="BV13" s="13">
         <f t="shared" si="0"/>
-        <v>816.99</v>
-      </c>
-      <c r="BV13" s="13">
+        <v>1369.2</v>
+      </c>
+      <c r="BW13" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BW13" s="13"/>
+        <v>420</v>
+      </c>
       <c r="BX13" s="13"/>
-      <c r="BY13">
+      <c r="BY13" s="13"/>
+      <c r="BZ13">
         <v>113</v>
       </c>
-      <c r="CA13" s="15">
+      <c r="CB13" s="15">
         <f t="shared" si="4"/>
-        <v>-816.99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:79" ht="45" customHeight="1" thickBot="1">
+        <v>-949.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>662577</v>
       </c>
@@ -3488,219 +3489,222 @@
         <v>7204.22</v>
       </c>
       <c r="I14" s="13">
+        <v>8100</v>
+      </c>
+      <c r="J14" s="13">
+        <v>8100</v>
+      </c>
+      <c r="K14" s="13">
         <v>7922</v>
       </c>
-      <c r="J14" s="13">
-        <v>7922</v>
-      </c>
-      <c r="K14" s="13">
+      <c r="L14" s="13">
         <v>7884</v>
       </c>
-      <c r="L14" s="13">
+      <c r="M14" s="13">
         <v>8051</v>
       </c>
-      <c r="M14" s="13">
+      <c r="N14" s="13">
         <v>7911</v>
       </c>
-      <c r="N14" s="13">
+      <c r="O14" s="13">
         <v>7833</v>
       </c>
-      <c r="O14" s="13">
+      <c r="P14" s="13">
         <v>7687</v>
       </c>
-      <c r="P14" s="13">
+      <c r="Q14" s="13">
         <v>7672</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="R14" s="13">
         <v>7676</v>
       </c>
-      <c r="R14" s="13">
+      <c r="S14" s="13">
         <v>7844</v>
       </c>
-      <c r="S14" s="13">
+      <c r="T14" s="13">
         <v>7810</v>
       </c>
-      <c r="T14" s="13">
+      <c r="U14" s="13">
         <v>7710</v>
       </c>
-      <c r="U14" s="13">
+      <c r="V14" s="13">
         <v>7735</v>
       </c>
-      <c r="V14" s="13">
+      <c r="W14" s="13">
         <v>7725</v>
       </c>
-      <c r="W14" s="13">
+      <c r="X14" s="13">
         <v>7787</v>
       </c>
-      <c r="X14" s="13">
+      <c r="Y14" s="13">
         <v>7955</v>
-      </c>
-      <c r="Y14" s="13">
-        <v>7627</v>
       </c>
       <c r="Z14" s="13">
         <v>7627</v>
       </c>
       <c r="AA14" s="13">
+        <v>7627</v>
+      </c>
+      <c r="AB14" s="13">
         <v>7656</v>
       </c>
-      <c r="AB14" s="13">
+      <c r="AC14" s="13">
         <v>7507</v>
       </c>
-      <c r="AC14" s="13">
+      <c r="AD14" s="13">
         <v>7590</v>
       </c>
-      <c r="AD14" s="13">
+      <c r="AE14" s="13">
         <v>7569</v>
       </c>
-      <c r="AE14" s="13">
+      <c r="AF14" s="13">
         <v>7269</v>
       </c>
-      <c r="AF14" s="13">
+      <c r="AG14" s="13">
         <v>7444</v>
       </c>
-      <c r="AG14" s="13">
+      <c r="AH14" s="13">
         <v>7205</v>
       </c>
-      <c r="AH14" s="13">
+      <c r="AI14" s="13">
         <v>7298</v>
       </c>
-      <c r="AI14" s="13">
+      <c r="AJ14" s="13">
         <v>7222</v>
       </c>
-      <c r="AJ14" s="13">
+      <c r="AK14" s="13">
         <v>7079</v>
       </c>
-      <c r="AK14" s="13">
+      <c r="AL14" s="13">
         <v>7140</v>
       </c>
-      <c r="AL14" s="13">
+      <c r="AM14" s="13">
         <v>7440</v>
       </c>
-      <c r="AM14" s="13">
+      <c r="AN14" s="13">
         <v>7530</v>
-      </c>
-      <c r="AN14" s="13">
-        <v>7535</v>
       </c>
       <c r="AO14" s="13">
         <v>7535</v>
       </c>
       <c r="AP14" s="13">
+        <v>7535</v>
+      </c>
+      <c r="AQ14" s="13">
         <v>7568</v>
       </c>
-      <c r="AQ14" s="13">
+      <c r="AR14" s="13">
         <v>7699</v>
       </c>
-      <c r="AR14" s="13">
+      <c r="AS14" s="13">
         <v>7638</v>
       </c>
-      <c r="AS14" s="13">
+      <c r="AT14" s="13">
         <v>7654</v>
       </c>
-      <c r="AT14" s="13">
+      <c r="AU14" s="13">
         <v>7584</v>
       </c>
-      <c r="AU14" s="13">
+      <c r="AV14" s="13">
         <v>7479</v>
       </c>
-      <c r="AV14" s="13">
+      <c r="AW14" s="13">
         <v>7490</v>
       </c>
-      <c r="AW14" s="13">
+      <c r="AX14" s="13">
         <v>7480</v>
       </c>
-      <c r="AX14" s="13">
+      <c r="AY14" s="13">
         <v>7270</v>
       </c>
-      <c r="AY14" s="13">
+      <c r="AZ14" s="13">
         <v>7163</v>
       </c>
-      <c r="AZ14" s="13">
+      <c r="BA14" s="13">
         <v>7231</v>
-      </c>
-      <c r="BA14" s="13">
-        <v>7100</v>
       </c>
       <c r="BB14" s="13">
         <v>7100</v>
       </c>
       <c r="BC14" s="13">
+        <v>7100</v>
+      </c>
+      <c r="BD14" s="13">
         <v>7027</v>
       </c>
-      <c r="BD14" s="13">
+      <c r="BE14" s="13">
         <v>6984</v>
       </c>
-      <c r="BE14" s="13">
+      <c r="BF14" s="13">
         <v>6944</v>
       </c>
-      <c r="BF14" s="13">
+      <c r="BG14" s="13">
         <v>6924</v>
       </c>
-      <c r="BG14" s="13">
+      <c r="BH14" s="13">
         <v>6930</v>
       </c>
-      <c r="BH14" s="13">
+      <c r="BI14" s="13">
         <v>6938</v>
       </c>
-      <c r="BI14" s="13">
+      <c r="BJ14" s="13">
         <v>6989</v>
       </c>
-      <c r="BJ14" s="13">
+      <c r="BK14" s="13">
         <v>6871</v>
       </c>
-      <c r="BK14" s="13">
+      <c r="BL14" s="13">
         <v>6943</v>
       </c>
-      <c r="BL14" s="13">
+      <c r="BM14" s="13">
         <v>7040</v>
       </c>
-      <c r="BM14" s="29">
+      <c r="BN14" s="29">
         <v>6696</v>
       </c>
-      <c r="BN14" s="13">
+      <c r="BO14" s="13">
         <v>6965</v>
       </c>
-      <c r="BO14" s="13">
+      <c r="BP14" s="13">
         <v>6788</v>
       </c>
-      <c r="BP14" s="29">
+      <c r="BQ14" s="29">
         <v>6696</v>
       </c>
-      <c r="BQ14" s="13">
+      <c r="BR14" s="13">
         <v>6625</v>
       </c>
-      <c r="BR14" s="13">
+      <c r="BS14" s="13">
         <v>6660</v>
       </c>
-      <c r="BS14" s="13">
+      <c r="BT14" s="13">
         <v>6791</v>
       </c>
-      <c r="BT14" s="13">
+      <c r="BU14" s="13">
         <v>6610</v>
       </c>
-      <c r="BU14" s="13">
+      <c r="BV14" s="13">
         <f t="shared" si="0"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BV14" s="13">
+      <c r="BW14" s="13">
         <f t="shared" si="1"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BW14" s="13">
-        <f t="shared" ref="BW14" si="5">(BV14-BU14)</f>
+      <c r="BX14" s="13">
+        <f t="shared" ref="BX14" si="5">(BW14-BV14)</f>
         <v>0</v>
       </c>
-      <c r="BX14" s="13">
-        <f>((BL14-H14)/H14)*100</f>
+      <c r="BY14" s="13">
+        <f>((BM14-H14)/H14)*100</f>
         <v>-2.2794972946411995</v>
       </c>
-      <c r="CA14" s="15">
+      <c r="CB14" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="15" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>5137534</v>
       </c>
@@ -3729,87 +3733,89 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
+        <v>12994</v>
+      </c>
+      <c r="J15" s="13">
+        <v>12994</v>
+      </c>
+      <c r="K15" s="13">
         <v>12628.12</v>
       </c>
-      <c r="J15" s="13">
-        <v>12628.12</v>
-      </c>
-      <c r="K15" s="13">
+      <c r="L15" s="13">
         <v>11710.62</v>
       </c>
-      <c r="L15" s="13">
+      <c r="M15" s="13">
         <v>12145</v>
       </c>
-      <c r="M15" s="13">
+      <c r="N15" s="13">
         <v>11855.12</v>
-      </c>
-      <c r="N15" s="13">
-        <v>11946.75</v>
       </c>
       <c r="O15" s="13">
         <v>11946.75</v>
       </c>
       <c r="P15" s="13">
-        <v>14679.12</v>
+        <v>11946.75</v>
       </c>
       <c r="Q15" s="13">
         <v>14679.12</v>
       </c>
       <c r="R15" s="13">
+        <v>14679.12</v>
+      </c>
+      <c r="S15" s="13">
         <v>13968</v>
       </c>
-      <c r="S15" s="13">
+      <c r="T15" s="13">
         <v>15528.12</v>
       </c>
-      <c r="T15" s="13">
+      <c r="U15" s="13">
         <v>14358.25</v>
       </c>
-      <c r="U15" s="13">
+      <c r="V15" s="13">
         <v>14385.75</v>
       </c>
-      <c r="V15" s="13">
+      <c r="W15" s="13">
         <v>13880</v>
       </c>
-      <c r="W15" s="13">
+      <c r="X15" s="13">
         <v>13610.62</v>
       </c>
-      <c r="X15" s="13">
+      <c r="Y15" s="13">
         <v>13016</v>
       </c>
-      <c r="Y15" s="13">
+      <c r="Z15" s="13">
         <v>12487.37</v>
       </c>
-      <c r="Z15" s="13">
+      <c r="AA15" s="13">
         <v>12638.62</v>
       </c>
-      <c r="AA15" s="13">
+      <c r="AB15" s="13">
         <v>12533.87</v>
       </c>
-      <c r="AB15" s="13">
+      <c r="AC15" s="13">
         <v>11299.5</v>
       </c>
-      <c r="AC15" s="13">
+      <c r="AD15" s="13">
         <v>11193.12</v>
       </c>
-      <c r="AD15" s="13">
+      <c r="AE15" s="13">
         <v>11548.62</v>
       </c>
-      <c r="AE15" s="13">
+      <c r="AF15" s="13">
         <v>11125.62</v>
       </c>
-      <c r="AF15" s="13">
+      <c r="AG15" s="13">
         <v>10932.12</v>
       </c>
-      <c r="AG15" s="13">
+      <c r="AH15" s="13">
         <v>11095.62</v>
       </c>
-      <c r="AH15" s="13">
+      <c r="AI15" s="13">
         <v>10910.58</v>
       </c>
-      <c r="AI15" s="13">
+      <c r="AJ15" s="13">
         <v>11609.37</v>
       </c>
-      <c r="AJ15" s="13"/>
       <c r="AK15" s="13"/>
       <c r="AL15" s="13"/>
       <c r="AM15" s="13"/>
@@ -3819,8 +3825,8 @@
       <c r="AQ15" s="13"/>
       <c r="AR15" s="13"/>
       <c r="AS15" s="13"/>
-      <c r="AT15" s="14"/>
-      <c r="AU15" s="13"/>
+      <c r="AT15" s="13"/>
+      <c r="AU15" s="14"/>
       <c r="AV15" s="13"/>
       <c r="AW15" s="13"/>
       <c r="AX15" s="13"/>
@@ -3838,36 +3844,37 @@
       <c r="BJ15" s="13"/>
       <c r="BK15" s="13"/>
       <c r="BL15" s="13"/>
-      <c r="BM15" s="29"/>
-      <c r="BN15" s="13"/>
+      <c r="BM15" s="13"/>
+      <c r="BN15" s="29"/>
       <c r="BO15" s="13"/>
-      <c r="BP15" s="29"/>
-      <c r="BQ15" s="13"/>
+      <c r="BP15" s="13"/>
+      <c r="BQ15" s="29"/>
       <c r="BR15" s="13"/>
       <c r="BS15" s="13"/>
       <c r="BT15" s="13"/>
-      <c r="BU15" s="13">
+      <c r="BU15" s="13"/>
+      <c r="BV15" s="13">
         <f t="shared" si="0"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BV15" s="13">
+      <c r="BW15" s="13">
         <f t="shared" si="1"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BW15" s="13">
-        <f t="shared" ref="BW15:BW18" si="6">(BV15-BU15)</f>
+      <c r="BX15" s="13">
+        <f t="shared" ref="BX15:BX18" si="6">(BW15-BV15)</f>
         <v>0</v>
       </c>
-      <c r="BX15" s="13">
-        <f>((BL15-H15)/H15)*100</f>
+      <c r="BY15" s="13">
+        <f>((BM15-H15)/H15)*100</f>
         <v>-100</v>
       </c>
-      <c r="CA15" s="15">
+      <c r="CB15" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="16" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>5135470</v>
       </c>
@@ -3896,225 +3903,228 @@
         <v>199.49</v>
       </c>
       <c r="I16" s="13">
-        <v>216.57</v>
+        <v>216</v>
       </c>
       <c r="J16" s="13">
-        <v>216.57</v>
+        <v>216</v>
       </c>
       <c r="K16" s="13">
         <v>216.57</v>
       </c>
       <c r="L16" s="13">
+        <v>216.57</v>
+      </c>
+      <c r="M16" s="13">
         <v>221.02</v>
       </c>
-      <c r="M16" s="13">
+      <c r="N16" s="13">
         <v>218.38</v>
       </c>
-      <c r="N16" s="13">
+      <c r="O16" s="13">
         <v>218.36</v>
       </c>
-      <c r="O16" s="13">
+      <c r="P16" s="13">
         <v>223.13</v>
       </c>
-      <c r="P16" s="13">
+      <c r="Q16" s="13">
         <v>227.54</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="R16" s="13">
         <v>226.96</v>
       </c>
-      <c r="R16" s="13">
+      <c r="S16" s="13">
         <v>225.24</v>
       </c>
-      <c r="S16" s="13">
+      <c r="T16" s="13">
         <v>223.25</v>
-      </c>
-      <c r="T16" s="13">
-        <v>219.14</v>
       </c>
       <c r="U16" s="13">
         <v>219.14</v>
       </c>
       <c r="V16" s="13">
+        <v>219.14</v>
+      </c>
+      <c r="W16" s="13">
         <v>219.3</v>
       </c>
-      <c r="W16" s="13">
+      <c r="X16" s="13">
         <v>222.79</v>
       </c>
-      <c r="X16" s="13">
+      <c r="Y16" s="13">
         <v>221.16</v>
       </c>
-      <c r="Y16" s="13">
+      <c r="Z16" s="13">
         <v>220.66</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="AA16" s="13">
         <v>222.06</v>
       </c>
-      <c r="AA16" s="13">
+      <c r="AB16" s="13">
         <v>218.71</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AC16" s="13">
         <v>216.74</v>
       </c>
-      <c r="AC16" s="13">
+      <c r="AD16" s="13">
         <v>216.04</v>
-      </c>
-      <c r="AD16" s="13">
-        <v>210.69</v>
       </c>
       <c r="AE16" s="13">
         <v>210.69</v>
       </c>
       <c r="AF16" s="13">
+        <v>210.69</v>
+      </c>
+      <c r="AG16" s="13">
         <v>198</v>
       </c>
-      <c r="AG16" s="13">
+      <c r="AH16" s="13">
         <v>196.74</v>
       </c>
-      <c r="AH16" s="13">
+      <c r="AI16" s="13">
         <v>192.56</v>
       </c>
-      <c r="AI16" s="13">
+      <c r="AJ16" s="13">
         <v>192.23</v>
       </c>
-      <c r="AJ16" s="13">
+      <c r="AK16" s="13">
         <v>191.19</v>
       </c>
-      <c r="AK16" s="13">
+      <c r="AL16" s="13">
         <v>193.62</v>
       </c>
-      <c r="AL16" s="13">
+      <c r="AM16" s="13">
         <v>190.75</v>
       </c>
-      <c r="AM16" s="13">
+      <c r="AN16" s="13">
         <v>189.06</v>
-      </c>
-      <c r="AN16" s="13">
-        <v>182.73</v>
       </c>
       <c r="AO16" s="13">
         <v>182.73</v>
       </c>
       <c r="AP16" s="13">
+        <v>182.73</v>
+      </c>
+      <c r="AQ16" s="13">
         <v>177.92</v>
       </c>
-      <c r="AQ16" s="13">
+      <c r="AR16" s="13">
         <v>179.16</v>
       </c>
-      <c r="AR16" s="13">
+      <c r="AS16" s="13">
         <v>179.34</v>
-      </c>
-      <c r="AS16" s="13">
-        <v>176.5</v>
       </c>
       <c r="AT16" s="13">
         <v>176.5</v>
       </c>
       <c r="AU16" s="13">
+        <v>176.5</v>
+      </c>
+      <c r="AV16" s="13">
         <v>175.93</v>
       </c>
-      <c r="AV16" s="13">
+      <c r="AW16" s="13">
         <v>174.51</v>
       </c>
-      <c r="AW16" s="13">
+      <c r="AX16" s="13">
         <v>173.91</v>
       </c>
-      <c r="AX16" s="13">
+      <c r="AY16" s="13">
         <v>177.1</v>
       </c>
-      <c r="AY16" s="13">
+      <c r="AZ16" s="13">
         <v>178.24</v>
       </c>
-      <c r="AZ16" s="13">
+      <c r="BA16" s="13">
         <v>176.52</v>
       </c>
-      <c r="BA16" s="13">
+      <c r="BB16" s="13">
         <v>178.27</v>
       </c>
-      <c r="BB16" s="13">
+      <c r="BC16" s="13">
         <v>175.29</v>
       </c>
-      <c r="BC16" s="13">
+      <c r="BD16" s="13">
         <v>175.34</v>
       </c>
-      <c r="BD16" s="13">
+      <c r="BE16" s="13">
         <v>174.41</v>
       </c>
-      <c r="BE16" s="13">
+      <c r="BF16" s="13">
         <v>176.22</v>
       </c>
-      <c r="BF16" s="13">
+      <c r="BG16" s="13">
         <v>174</v>
       </c>
-      <c r="BG16" s="13">
+      <c r="BH16" s="13">
         <v>176.35</v>
       </c>
-      <c r="BH16" s="13">
+      <c r="BI16" s="13">
         <v>177.71</v>
       </c>
-      <c r="BI16" s="13">
+      <c r="BJ16" s="13">
         <v>180.08</v>
       </c>
-      <c r="BJ16" s="13">
+      <c r="BK16" s="13">
         <v>181.96</v>
       </c>
-      <c r="BK16" s="13">
+      <c r="BL16" s="13">
         <v>182.9</v>
       </c>
-      <c r="BL16" s="13">
+      <c r="BM16" s="13">
         <v>181.86</v>
       </c>
-      <c r="BM16" s="29">
+      <c r="BN16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BN16" s="13">
+      <c r="BO16" s="13">
         <v>181.07</v>
       </c>
-      <c r="BO16" s="13">
+      <c r="BP16" s="13">
         <v>182.56</v>
       </c>
-      <c r="BP16" s="29">
+      <c r="BQ16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BQ16" s="13">
+      <c r="BR16" s="13">
         <v>178.86</v>
       </c>
-      <c r="BR16" s="13">
+      <c r="BS16" s="13">
         <v>180.16</v>
       </c>
-      <c r="BS16" s="13">
+      <c r="BT16" s="13">
         <v>179.56</v>
       </c>
-      <c r="BT16" s="13">
+      <c r="BU16" s="13">
         <v>176.55</v>
       </c>
-      <c r="BU16" s="13">
+      <c r="BV16" s="13">
         <f t="shared" si="0"/>
         <v>1413.1220000000008</v>
       </c>
-      <c r="BV16" s="13">
+      <c r="BW16" s="13">
         <f t="shared" si="1"/>
         <v>997.45</v>
       </c>
-      <c r="BW16" s="13">
+      <c r="BX16" s="13">
         <f t="shared" si="6"/>
         <v>-415.67200000000071</v>
       </c>
-      <c r="BX16" s="13">
-        <f>((BL16-H16)/H16)*100</f>
+      <c r="BY16" s="13">
+        <f>((BM16-H16)/H16)*100</f>
         <v>-8.8375357160759904</v>
       </c>
-      <c r="BY16">
+      <c r="BZ16">
         <v>1864</v>
       </c>
-      <c r="BZ16">
+      <c r="CA16">
         <v>177.19</v>
       </c>
-      <c r="CA16" s="15">
+      <c r="CB16" s="15">
         <f t="shared" si="4"/>
         <v>-415.67200000000071</v>
       </c>
     </row>
-    <row r="17" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="17" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>5134135</v>
       </c>
@@ -4143,16 +4153,16 @@
         <v>159.65</v>
       </c>
       <c r="I17" s="13">
+        <v>181.5</v>
+      </c>
+      <c r="J17" s="13">
+        <v>181.5</v>
+      </c>
+      <c r="K17" s="13">
         <v>177.17</v>
       </c>
-      <c r="J17" s="13">
-        <v>177.17</v>
-      </c>
-      <c r="K17" s="13">
+      <c r="L17" s="13">
         <v>186.88</v>
-      </c>
-      <c r="L17" s="13">
-        <v>184.42</v>
       </c>
       <c r="M17" s="13">
         <v>184.42</v>
@@ -4161,13 +4171,13 @@
         <v>184.42</v>
       </c>
       <c r="O17" s="13">
+        <v>184.42</v>
+      </c>
+      <c r="P17" s="13">
         <v>199.37</v>
       </c>
-      <c r="P17" s="13">
+      <c r="Q17" s="13">
         <v>194.88</v>
-      </c>
-      <c r="Q17" s="13">
-        <v>189.51</v>
       </c>
       <c r="R17" s="13">
         <v>189.51</v>
@@ -4176,13 +4186,13 @@
         <v>189.51</v>
       </c>
       <c r="T17" s="13">
-        <v>185.52</v>
+        <v>189.51</v>
       </c>
       <c r="U17" s="13">
         <v>185.52</v>
       </c>
       <c r="V17" s="13">
-        <v>178.98</v>
+        <v>185.52</v>
       </c>
       <c r="W17" s="13">
         <v>178.98</v>
@@ -4191,7 +4201,7 @@
         <v>178.98</v>
       </c>
       <c r="Y17" s="13">
-        <v>170.7</v>
+        <v>178.98</v>
       </c>
       <c r="Z17" s="13">
         <v>170.7</v>
@@ -4200,10 +4210,10 @@
         <v>170.7</v>
       </c>
       <c r="AB17" s="13">
+        <v>170.7</v>
+      </c>
+      <c r="AC17" s="13">
         <v>170.45</v>
-      </c>
-      <c r="AC17" s="13">
-        <v>160.84</v>
       </c>
       <c r="AD17" s="13">
         <v>160.84</v>
@@ -4212,15 +4222,17 @@
         <v>160.84</v>
       </c>
       <c r="AF17" s="13">
+        <v>160.84</v>
+      </c>
+      <c r="AG17" s="13">
         <v>159.02000000000001</v>
-      </c>
-      <c r="AG17" s="13">
-        <v>159.65</v>
       </c>
       <c r="AH17" s="13">
         <v>159.65</v>
       </c>
-      <c r="AI17" s="13"/>
+      <c r="AI17" s="13">
+        <v>159.65</v>
+      </c>
       <c r="AJ17" s="13"/>
       <c r="AK17" s="13"/>
       <c r="AL17" s="13"/>
@@ -4250,36 +4262,37 @@
       <c r="BJ17" s="13"/>
       <c r="BK17" s="13"/>
       <c r="BL17" s="13"/>
-      <c r="BM17" s="29"/>
-      <c r="BN17" s="13"/>
+      <c r="BM17" s="13"/>
+      <c r="BN17" s="29"/>
       <c r="BO17" s="13"/>
-      <c r="BP17" s="29"/>
-      <c r="BQ17" s="13"/>
+      <c r="BP17" s="13"/>
+      <c r="BQ17" s="29"/>
       <c r="BR17" s="13"/>
       <c r="BS17" s="13"/>
       <c r="BT17" s="13"/>
-      <c r="BU17" s="13">
+      <c r="BU17" s="13"/>
+      <c r="BV17" s="13">
         <f t="shared" si="0"/>
         <v>957.9</v>
       </c>
-      <c r="BV17" s="13">
+      <c r="BW17" s="13">
         <f t="shared" si="1"/>
         <v>957.9</v>
       </c>
-      <c r="BW17" s="13">
-        <f t="shared" ref="BW17" si="7">(BV17-BU17)</f>
+      <c r="BX17" s="13">
+        <f t="shared" ref="BX17" si="7">(BW17-BV17)</f>
         <v>0</v>
       </c>
-      <c r="BX17" s="13">
-        <f>((BL17-H17)/H17)*100</f>
+      <c r="BY17" s="13">
+        <f>((BM17-H17)/H17)*100</f>
         <v>-100</v>
       </c>
-      <c r="CA17" s="15">
+      <c r="CB17" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="18" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1168723</v>
       </c>
@@ -4308,90 +4321,92 @@
         <v>1434</v>
       </c>
       <c r="I18" s="13">
+        <v>1864</v>
+      </c>
+      <c r="J18" s="13">
+        <v>1864</v>
+      </c>
+      <c r="K18" s="13">
         <v>1823</v>
       </c>
-      <c r="J18" s="13">
-        <v>1823</v>
-      </c>
-      <c r="K18" s="13">
+      <c r="L18" s="13">
         <v>1819</v>
       </c>
-      <c r="L18" s="13">
+      <c r="M18" s="13">
         <v>1866</v>
       </c>
-      <c r="M18" s="13">
+      <c r="N18" s="13">
         <v>1886</v>
       </c>
-      <c r="N18" s="13">
+      <c r="O18" s="13">
         <v>1818</v>
       </c>
-      <c r="O18" s="13">
+      <c r="P18" s="13">
         <v>1785</v>
       </c>
-      <c r="P18" s="13">
+      <c r="Q18" s="13">
         <v>1828</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="R18" s="13">
         <v>1811</v>
       </c>
-      <c r="R18" s="13">
+      <c r="S18" s="13">
         <v>1825</v>
       </c>
-      <c r="S18" s="13">
+      <c r="T18" s="13">
         <v>1831</v>
       </c>
-      <c r="T18" s="13">
+      <c r="U18" s="13">
         <v>1799</v>
       </c>
-      <c r="U18" s="13">
+      <c r="V18" s="13">
         <v>1757</v>
       </c>
-      <c r="V18" s="13">
+      <c r="W18" s="13">
         <v>1698</v>
       </c>
-      <c r="W18" s="13">
+      <c r="X18" s="13">
         <v>1694</v>
       </c>
-      <c r="X18" s="13">
+      <c r="Y18" s="13">
         <v>1671</v>
-      </c>
-      <c r="Y18" s="13">
-        <v>1660</v>
       </c>
       <c r="Z18" s="13">
         <v>1660</v>
       </c>
       <c r="AA18" s="13">
+        <v>1660</v>
+      </c>
+      <c r="AB18" s="13">
         <v>1646</v>
       </c>
-      <c r="AB18" s="13">
+      <c r="AC18" s="13">
         <v>1648</v>
       </c>
-      <c r="AC18" s="13">
+      <c r="AD18" s="13">
         <v>1614</v>
       </c>
-      <c r="AD18" s="13">
+      <c r="AE18" s="13">
         <v>1626</v>
       </c>
-      <c r="AE18" s="13">
+      <c r="AF18" s="13">
         <v>1587</v>
       </c>
-      <c r="AF18" s="13">
+      <c r="AG18" s="13">
         <v>1548</v>
       </c>
-      <c r="AG18" s="13">
+      <c r="AH18" s="13">
         <v>1500</v>
       </c>
-      <c r="AH18" s="13">
+      <c r="AI18" s="13">
         <v>1491</v>
       </c>
-      <c r="AI18" s="13">
+      <c r="AJ18" s="13">
         <v>1444</v>
       </c>
-      <c r="AJ18" s="13">
+      <c r="AK18" s="13">
         <v>1431</v>
       </c>
-      <c r="AK18" s="13"/>
       <c r="AL18" s="13"/>
       <c r="AM18" s="13"/>
       <c r="AN18" s="13"/>
@@ -4417,64 +4432,65 @@
       <c r="BH18" s="13"/>
       <c r="BI18" s="13"/>
       <c r="BJ18" s="13"/>
-      <c r="BK18" s="13">
-        <v>1788</v>
-      </c>
+      <c r="BK18" s="13"/>
       <c r="BL18" s="13">
         <v>1788</v>
       </c>
-      <c r="BM18" s="29">
+      <c r="BM18" s="13">
+        <v>1788</v>
+      </c>
+      <c r="BN18" s="29">
         <v>1780</v>
       </c>
-      <c r="BN18" s="13">
+      <c r="BO18" s="13">
         <v>1814</v>
       </c>
-      <c r="BO18" s="13">
+      <c r="BP18" s="13">
         <v>1794</v>
       </c>
-      <c r="BP18" s="29">
+      <c r="BQ18" s="29">
         <v>1780</v>
       </c>
-      <c r="BQ18" s="13">
+      <c r="BR18" s="13">
         <v>1772</v>
       </c>
-      <c r="BR18" s="13">
+      <c r="BS18" s="13">
         <v>1798</v>
       </c>
-      <c r="BS18" s="13">
+      <c r="BT18" s="13">
         <v>1806</v>
       </c>
-      <c r="BT18" s="13">
+      <c r="BU18" s="13">
         <v>1801</v>
       </c>
-      <c r="BU18" s="13">
+      <c r="BV18" s="13">
         <f t="shared" si="0"/>
         <v>292.79999999999995</v>
       </c>
-      <c r="BV18" s="13">
+      <c r="BW18" s="13">
         <f t="shared" si="1"/>
         <v>645.29999999999995</v>
       </c>
-      <c r="BW18" s="13">
+      <c r="BX18" s="13">
         <f t="shared" si="6"/>
         <v>352.5</v>
       </c>
-      <c r="BX18" s="13">
-        <f>((BL18-H18)/H18)*100</f>
+      <c r="BY18" s="13">
+        <f>((BM18-H18)/H18)*100</f>
         <v>24.686192468619247</v>
       </c>
-      <c r="BY18">
+      <c r="BZ18">
         <v>100</v>
       </c>
-      <c r="BZ18">
+      <c r="CA18">
         <v>1786.5</v>
       </c>
-      <c r="CA18" s="15">
+      <c r="CB18" s="15">
         <f t="shared" si="4"/>
         <v>352.5</v>
       </c>
     </row>
-    <row r="19" spans="1:79" ht="45" customHeight="1" thickBot="1">
+    <row r="19" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1122654</v>
       </c>
@@ -4491,7 +4507,7 @@
         <v>למכור ברווח</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F19" s="4">
         <v>46052</v>
@@ -4500,30 +4516,32 @@
         <v>300</v>
       </c>
       <c r="H19" s="13">
-        <v>102.77</v>
+        <v>93.13</v>
       </c>
       <c r="I19" s="13">
+        <v>67.900000000000006</v>
+      </c>
+      <c r="J19" s="13">
+        <v>67.900000000000006</v>
+      </c>
+      <c r="K19" s="13">
         <v>71.3</v>
       </c>
-      <c r="J19" s="13">
-        <v>71.3</v>
-      </c>
-      <c r="K19" s="13">
+      <c r="L19" s="13">
         <v>72.099999999999994</v>
       </c>
-      <c r="L19" s="13">
+      <c r="M19" s="13">
         <v>86.7</v>
-      </c>
-      <c r="M19" s="13">
-        <v>91.5</v>
       </c>
       <c r="N19" s="13">
         <v>91.5</v>
       </c>
       <c r="O19" s="13">
+        <v>91.5</v>
+      </c>
+      <c r="P19" s="13">
         <v>132.6</v>
       </c>
-      <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
       <c r="R19" s="13"/>
       <c r="S19" s="13"/>
@@ -4539,22 +4557,22 @@
       <c r="AC19" s="13"/>
       <c r="AD19" s="13"/>
       <c r="AE19" s="13"/>
-      <c r="AF19" s="13">
+      <c r="AF19" s="13"/>
+      <c r="AG19" s="13">
         <v>6461</v>
       </c>
-      <c r="AG19" s="13">
+      <c r="AH19" s="13">
         <v>6503</v>
       </c>
-      <c r="AH19" s="13">
+      <c r="AI19" s="13">
         <v>6535</v>
       </c>
-      <c r="AI19" s="13">
+      <c r="AJ19" s="13">
         <v>6532</v>
       </c>
-      <c r="AJ19" s="13">
+      <c r="AK19" s="13">
         <v>6515</v>
       </c>
-      <c r="AK19" s="13"/>
       <c r="AL19" s="13"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="13"/>
@@ -4582,33 +4600,34 @@
       <c r="BJ19" s="13"/>
       <c r="BK19" s="13"/>
       <c r="BL19" s="13"/>
-      <c r="BM19" s="29"/>
-      <c r="BN19" s="13"/>
+      <c r="BM19" s="13"/>
+      <c r="BN19" s="29"/>
       <c r="BO19" s="13"/>
-      <c r="BP19" s="29"/>
-      <c r="BQ19" s="13"/>
+      <c r="BP19" s="13"/>
+      <c r="BQ19" s="29"/>
       <c r="BR19" s="13"/>
       <c r="BS19" s="13"/>
       <c r="BT19" s="13"/>
-      <c r="BU19" s="13">
+      <c r="BU19" s="13"/>
+      <c r="BV19" s="13">
         <f t="shared" si="0"/>
-        <v>308.31</v>
-      </c>
-      <c r="BV19" s="13">
+        <v>279.39</v>
+      </c>
+      <c r="BW19" s="13">
         <f t="shared" si="1"/>
-        <v>308.31</v>
-      </c>
-      <c r="BW19" s="13"/>
+        <v>279.39</v>
+      </c>
       <c r="BX19" s="13"/>
-      <c r="BY19">
+      <c r="BY19" s="13"/>
+      <c r="BZ19">
         <v>7</v>
       </c>
-      <c r="BZ19">
+      <c r="CA19">
         <v>6461</v>
       </c>
-      <c r="CA19" s="15"/>
-    </row>
-    <row r="20" spans="1:79" ht="45" customHeight="1" thickBot="1">
+      <c r="CB19" s="15"/>
+    </row>
+    <row r="20" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>363010</v>
       </c>
@@ -4625,7 +4644,7 @@
         <v>למכור בהפסד</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F20" s="28">
         <v>46056</v>
@@ -4637,21 +4656,23 @@
         <v>65</v>
       </c>
       <c r="I20" s="13">
+        <v>82.3</v>
+      </c>
+      <c r="J20" s="13">
+        <v>82.3</v>
+      </c>
+      <c r="K20" s="13">
         <v>75.2</v>
       </c>
-      <c r="J20" s="13">
-        <v>75.2</v>
-      </c>
-      <c r="K20" s="13">
+      <c r="L20" s="13">
         <v>68.8</v>
       </c>
-      <c r="L20" s="13">
+      <c r="M20" s="13">
         <v>89</v>
       </c>
-      <c r="M20" s="13">
+      <c r="N20" s="13">
         <v>87.5</v>
       </c>
-      <c r="N20" s="13"/>
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
@@ -4702,28 +4723,29 @@
       <c r="BJ20" s="13"/>
       <c r="BK20" s="13"/>
       <c r="BL20" s="13"/>
-      <c r="BM20" s="29"/>
-      <c r="BN20" s="13"/>
+      <c r="BM20" s="13"/>
+      <c r="BN20" s="29"/>
       <c r="BO20" s="13"/>
-      <c r="BP20" s="29"/>
-      <c r="BQ20" s="13"/>
+      <c r="BP20" s="13"/>
+      <c r="BQ20" s="29"/>
       <c r="BR20" s="13"/>
       <c r="BS20" s="13"/>
       <c r="BT20" s="13"/>
-      <c r="BU20" s="13">
+      <c r="BU20" s="13"/>
+      <c r="BV20" s="13">
         <f t="shared" si="0"/>
         <v>195</v>
       </c>
-      <c r="BV20" s="13">
+      <c r="BW20" s="13">
         <f t="shared" si="1"/>
         <v>195</v>
       </c>
-      <c r="BW20" s="13"/>
       <c r="BX20" s="13"/>
-      <c r="CA20" s="15"/>
-    </row>
-    <row r="21" spans="1:79" ht="14.4" thickBot="1"/>
-    <row r="22" spans="1:79" ht="45" customHeight="1" thickBot="1">
+      <c r="BY20" s="13"/>
+      <c r="CB20" s="15"/>
+    </row>
+    <row r="21" spans="1:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4788,11 +4810,11 @@
       <c r="BJ22" s="13"/>
       <c r="BK22" s="13"/>
       <c r="BL22" s="13"/>
-      <c r="BM22" s="29"/>
-      <c r="BN22" s="13"/>
+      <c r="BM22" s="13"/>
+      <c r="BN22" s="29"/>
       <c r="BO22" s="13"/>
-      <c r="BP22" s="29"/>
-      <c r="BQ22" s="13"/>
+      <c r="BP22" s="13"/>
+      <c r="BQ22" s="29"/>
       <c r="BR22" s="13"/>
       <c r="BS22" s="13"/>
       <c r="BT22" s="13"/>
@@ -4800,114 +4822,115 @@
       <c r="BV22" s="13"/>
       <c r="BW22" s="13"/>
       <c r="BX22" s="13"/>
-      <c r="CA22" s="15"/>
-    </row>
-    <row r="23" spans="1:79" ht="54.9" customHeight="1" thickBot="1">
+      <c r="BY22" s="13"/>
+      <c r="CB22" s="15"/>
+    </row>
+    <row r="23" spans="1:80" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="27"/>
       <c r="H23" s="13"/>
       <c r="I23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19+G20*I20)/100</f>
-        <v>13513.891599999999</v>
+        <v>14073.616000000002</v>
       </c>
       <c r="J23" s="23">
         <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19+G20*J20)/100</f>
-        <v>13513.891599999999</v>
+        <v>14073.616000000002</v>
       </c>
       <c r="K23" s="23">
         <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19+G20*K20)/100</f>
-        <v>13417.8316</v>
+        <v>13316.741599999999</v>
       </c>
       <c r="L23" s="23">
         <f>(L2*G2+G3*L3+L4*G4+G5*L5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+L13*G13+G14*L14+L15*G15+G16*L16+G17*L17+L18*G18+G19*L19+G20*L20)/100</f>
-        <v>13916.21</v>
+        <v>13186.731599999999</v>
       </c>
       <c r="M23" s="23">
         <f>(M2*G2+G3*M3+M4*G4+G5*M5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+M13*G13+G14*M14+M15*G15+G16*M16+G17*M17+M18*G18+G19*M19+G20*M20)/100</f>
-        <v>13936.159599999999</v>
+        <v>13733.1</v>
       </c>
       <c r="N23" s="23">
         <f>(N2*G2+G3*N3+N4*G4+G5*N5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+N13*G13+G14*N14+N15*G15+G16*N16+G17*N17+N18*G18+G19*N19+G20*N20)/100</f>
-        <v>13438.511999999999</v>
+        <v>13788.069599999999</v>
       </c>
       <c r="O23" s="23">
-        <f>(O2*G2+G3*O3+O4*G4+G5*O5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+O13*G13+G14*O14+O15*G15+G16*O16+G17*O17+O18*G18+G19*O19)/100</f>
-        <v>13503.13</v>
+        <f>(O2*G2+G3*O3+O4*G4+G5*O5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+O13*G13+G14*O14+O15*G15+G16*O16+G17*O17+O18*G18+G19*O19+G20*O20)/100</f>
+        <v>13213.011999999999</v>
       </c>
       <c r="P23" s="23">
         <f>(P2*G2+G3*P3+P4*G4+G5*P5+G6*P6+G7*P7+G8*P8+G9*P9+G10*P10+G11*P11+G12*P12+P13*G13+G14*P14+P15*G15+G16*P16+G17*P17+P18*G18+G19*P19)/100</f>
-        <v>13844.2896</v>
+        <v>13254.46</v>
       </c>
       <c r="Q23" s="23">
         <f>(Q2*G2+G3*Q3+Q4*G4+G5*Q5+G6*Q6+G7*Q7+G8*Q8+G9*Q9+G10*Q10+G11*Q11+G12*Q12+Q13*G13+G14*Q14+Q15*G15+G16*Q16+G17*Q17+Q18*G18+G19*Q19)/100</f>
-        <v>13659.785600000001</v>
+        <v>12995.1896</v>
       </c>
       <c r="R23" s="23">
         <f>(R2*G2+G3*R3+R4*G4+G5*R5+G6*R6+G7*R7+G8*R8+G9*R9+G10*R10+G11*R11+G12*R12+R13*G13+G14*R14+R15*G15+G16*R16+G17*R17+R18*G18+G19*R19)/100</f>
-        <v>13683.918</v>
+        <v>13575.9856</v>
       </c>
       <c r="S23" s="23">
         <f>(S2*G2+G3*S3+S4*G4+G5*S5+G6*S6+G7*S7+G8*S8+G9*S9+G10*S10+G11*S11+G12*S12+S13*G13+G14*S14+S15*G15+G16*S16+G17*S17+S18*G18+G19*S19)/100</f>
-        <v>13839.923600000002</v>
+        <v>13490.918</v>
       </c>
       <c r="T23" s="23">
         <f>(T2*G2+G3*T3+T4*G4+G5*T5+G6*T6+G7*T7+G8*T8+G9*T9+G10*T10+G11*T11+G12*T12+T13*G13+G14*T14+T15*G15+G16*T16+G17*T17+T18*G18+G19*T19)/100</f>
-        <v>13475.503999999999</v>
+        <v>13594.723600000001</v>
       </c>
       <c r="U23" s="23">
         <f>(U2*G2+G3*U3+U4*G4+G5*U5+G6*U6+G7*U7+G8*U8+G9*U9+G10*U10+G11*U11+G12*U12+U13*G13+G14*U14+U15*G15+G16*U16+G17*U17+U18*G18+G19*U19)/100</f>
-        <v>13192.96</v>
+        <v>13195.503999999999</v>
       </c>
       <c r="V23" s="23">
         <f>(V2*G2+G3*V3+V4*G4+G5*V5+G6*V6+G7*V7+G8*V8+G9*V9+G10*V10+G11*V11+G12*V12+V13*G13+G14*V14+V15*G15+G16*V16+G17*V17+V18*G18+G19*V19)/100</f>
-        <v>12923.761999999999</v>
+        <v>12910.01</v>
       </c>
       <c r="W23" s="23">
         <f>(W2*G2+G3*W3+W4*G4+G5*W5+G6*W6+G7*W7+G8*W8+G9*W9+G10*W10+G11*W11+G12*W12+W13*G13+G14*W14+W15*G15+G16*W16+G17*W17+W18*G18+G19*W19)/100</f>
-        <v>13102.8776</v>
+        <v>12606.761999999999</v>
       </c>
       <c r="X23" s="23">
-        <f>(X3*G3+G4*X4+X5*G5+G6*X6+G7*X7+G8*X8+G9*X9+G10*X10+G11*X11+G12*X12+G14*X14+X15*G15+G16*X16+X17*G17+G18*X18+G19*X19)/100</f>
-        <v>12191.99</v>
+        <f>(X2*G2+G3*X3+X4*G4+G5*X5+G6*X6+G7*X7+G8*X8+G9*X9+G10*X10+G11*X11+G12*X12+X13*G13+G14*X14+X15*G15+G16*X16+G17*X17+X18*G18+G19*X19)/100</f>
+        <v>12711.777599999999</v>
       </c>
       <c r="Y23" s="23">
         <f>(Y3*G3+G4*Y4+Y5*G5+G6*Y6+G7*Y7+G8*Y8+G9*Y9+G10*Y10+G11*Y11+G12*Y12+G14*Y14+Y15*G15+G16*Y16+Y17*G17+G18*Y18+G19*Y19)/100</f>
-        <v>11970.357599999999</v>
+        <v>12191.99</v>
       </c>
       <c r="Z23" s="23">
         <f>(Z3*G3+G4*Z4+Z5*G5+G6*Z6+G7*Z7+G8*Z8+G9*Z9+G10*Z10+G11*Z11+G12*Z12+G14*Z14+Z15*G15+G16*Z16+Z17*G17+G18*Z18+G19*Z19)/100</f>
-        <v>11989.4576</v>
+        <v>11970.357599999999</v>
       </c>
       <c r="AA23" s="23">
         <f>(AA3*G3+G4*AA4+AA5*G5+G6*AA6+G7*AA7+G8*AA8+G9*AA9+G10*AA10+G11*AA11+G12*AA12+G14*AA14+AA15*G15+G16*AA16+AA17*G17+G18*AA18+G19*AA19)/100</f>
-        <v>11896.177600000001</v>
+        <v>11989.4576</v>
       </c>
       <c r="AB23" s="23">
         <f>(AB3*G3+G4*AB4+AB5*G5+G6*AB6+G7*AB7+G8*AB8+G9*AB9+G10*AB10+G11*AB11+G12*AB12+G14*AB14+AB15*G15+G16*AB16+AB17*G17+G18*AB18+G19*AB19)/100</f>
-        <v>11552.98</v>
+        <v>11896.177600000001</v>
       </c>
       <c r="AC23" s="23">
         <f>(AC3*G3+G4*AC4+AC5*G5+G6*AC6+G7*AC7+G8*AC8+G9*AC9+G10*AC10+G11*AC11+G12*AC12+G14*AC14+AC15*G15+G16*AC16+AC17*G17+G18*AC18+G19*AC19)/100</f>
-        <v>11467.277599999999</v>
+        <v>11552.98</v>
       </c>
       <c r="AD23" s="23">
         <f>(AD3*G3+G4*AD4+AD5*G5+G6*AD6+G7*AD7+G8*AD8+G9*AD9+G10*AD10+G11*AD11+G12*AD12+G14*AD14+AD15*G15+G16*AD16+AD17*G17+G18*AD18+G19*AD19)/100</f>
+        <v>11467.277599999999</v>
+      </c>
+      <c r="AE23" s="23">
+        <f>(AE3*G3+G4*AE4+AE5*G5+G6*AE6+G7*AE7+G8*AE8+G9*AE9+G10*AE10+G11*AE11+G12*AE12+G14*AE14+AE15*G15+G16*AE16+AE17*G17+G18*AE18+G19*AE19)/100</f>
         <v>10332.035599999999</v>
       </c>
-      <c r="AE23" s="23">
-        <f>(AE5*G5+G6*AE6+AE7*G7+G8*AE8+G9*AE9+G10*AE10+G11*AE11+G12*AE12+G14*AE14+G20*AE20+G15*AE15+AE16*G16+G17*AE17+AE18*G18+G19*AE19)/100</f>
+      <c r="AF23" s="23">
+        <f>(AF5*G5+G6*AF6+AF7*G7+G8*AF8+G9*AF9+G10*AF10+G11*AF11+G12*AF12+G14*AF14+G20*AF20+G15*AF15+AF16*G16+G17*AF17+AF18*G18+G19*AF19)/100</f>
         <v>9234.9995999999992</v>
-      </c>
-      <c r="AF23" s="23" t="e">
-        <f>(AF5*G5+G7*AF7+AF8*G8+G9*AF9+#REF!*#REF!+G10*AF10+G11*AF11+G12*AF12+G14*AF14+G19*AF19+G20*AF20+AF6*G6+G15*AF15+#REF!*#REF!+G16*AF16+G17*AF17+AF18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AF3+#REF!*#REF!)/100</f>
-        <v>#REF!</v>
       </c>
       <c r="AG23" s="23" t="e">
         <f>(AG5*G5+G7*AG7+AG8*G8+G9*AG9+#REF!*#REF!+G10*AG10+G11*AG11+G12*AG12+G14*AG14+G19*AG19+G20*AG20+AG6*G6+G15*AG15+#REF!*#REF!+G16*AG16+G17*AG17+AG18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AG3+#REF!*#REF!)/100</f>
@@ -4918,11 +4941,11 @@
         <v>#REF!</v>
       </c>
       <c r="AI23" s="23" t="e">
-        <f>(AI5*G5+G7*AI7+AI8*G8+G9*AI9+#REF!*#REF!+G10*AI10+G11*AI11+G12*AI12+G14*AI14+G19*AI19+G20*AI20+AI6*G6+G15*AI15+#REF!*#REF!+G16*AI16+G18*AI18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AI3+#REF!*#REF!+G4*AI4)/100</f>
+        <f>(AI5*G5+G7*AI7+AI8*G8+G9*AI9+#REF!*#REF!+G10*AI10+G11*AI11+G12*AI12+G14*AI14+G19*AI19+G20*AI20+AI6*G6+G15*AI15+#REF!*#REF!+G16*AI16+G17*AI17+AI18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AI3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AJ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AJ3*G3+#REF!*#REF!+G4*AJ4+G5*AJ5+G7*AJ7+G8*AJ8+G9*AJ9+#REF!*#REF!+G10*AJ10+AJ11*G11+G12*AJ12+AJ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AJ20+AJ6*G6+#REF!*#REF!+G16*AJ16+G18*AJ18+G19*AJ19)/100</f>
+        <f>(AJ5*G5+G7*AJ7+AJ8*G8+G9*AJ9+#REF!*#REF!+G10*AJ10+G11*AJ11+G12*AJ12+G14*AJ14+G19*AJ19+G20*AJ20+AJ6*G6+G15*AJ15+#REF!*#REF!+G16*AJ16+G18*AJ18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AJ3+#REF!*#REF!+G4*AJ4)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AK23" s="23" t="e">
@@ -4930,7 +4953,7 @@
         <v>#REF!</v>
       </c>
       <c r="AL23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AL3*G3+#REF!*#REF!+G4*AL4+G5*AL5+AL7*G7+AL8*G8+AL9*G9+#REF!*#REF!+G10*AL10+AL11*G11+G12*AL12+AL14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AL20+G6*AL6+#REF!*#REF!+G16*AL16+G18*AL18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AL3*G3+#REF!*#REF!+G4*AL4+G5*AL5+G7*AL7+G8*AL8+G9*AL9+#REF!*#REF!+G10*AL10+AL11*G11+G12*AL12+AL14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AL20+AL6*G6+#REF!*#REF!+G16*AL16+G18*AL18+G19*AL19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AM23" s="23" t="e">
@@ -4938,19 +4961,19 @@
         <v>#REF!</v>
       </c>
       <c r="AN23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G8*AN8+AN9*G9+#REF!*#REF!+AN10*G10+G11*AN11+G14*AN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AN6+#REF!*#REF!+G16*AN16+G18*AN18+G7*AN7+G5*AN5+G12*AN12+G20*AN20)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AN3*G3+#REF!*#REF!+G4*AN4+G5*AN5+AN7*G7+AN8*G8+AN9*G9+#REF!*#REF!+G10*AN10+AN11*G11+G12*AN12+AN14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AN20+G6*AN6+#REF!*#REF!+G16*AN16+G18*AN18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AO23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+AO9*G9+#REF!*#REF!+AO10*G10+G11*AO11+G14*AO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AO6+#REF!*#REF!+G16*AO16+G18*AO18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+AO9*G9+#REF!*#REF!+AO10*G10+G11*AO11+G14*AO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AO6+#REF!*#REF!+G16*AO16+G18*AO18+G7*AO7+G5*AO5+G12*AO12+G20*AO20)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AP23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+G9*AP9+#REF!*#REF!+G10*AP10+AP11*G11+AP14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AP6*G6+#REF!*#REF!+G16*AP16+G18*AP18+G19*AP19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+AP9*G9+#REF!*#REF!+AP10*G10+G11*AP11+G14*AP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AP6+#REF!*#REF!+G16*AP16+G18*AP18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AQ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AQ3*G3+#REF!*#REF!+G4*AQ4+G8*AQ8+AQ9*G9+#REF!*#REF!+AQ10*G10+G11*AQ11+G14*AQ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AQ6+#REF!*#REF!+G16*AQ16+G18*AQ18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AQ3*G3+#REF!*#REF!+G4*AQ4+G8*AQ8+G9*AQ9+#REF!*#REF!+G10*AQ10+AQ11*G11+AQ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AQ6*G6+#REF!*#REF!+G16*AQ16+G18*AQ18+G19*AQ19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AR23" s="23" t="e">
@@ -4958,7 +4981,7 @@
         <v>#REF!</v>
       </c>
       <c r="AS23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AS3*G3+#REF!*#REF!+G4*AS4+G8*AS8+AS9*G9+AS10*G10+AS11*G11+G14*AS14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AS6+#REF!*#REF!+G16*AS16+G18*AS18+G19*AS19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AS3*G3+#REF!*#REF!+G4*AS4+G8*AS8+AS9*G9+#REF!*#REF!+AS10*G10+G11*AS11+G14*AS14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AS6+#REF!*#REF!+G16*AS16+G18*AS18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AT23" s="23" t="e">
@@ -4978,19 +5001,19 @@
         <v>#REF!</v>
       </c>
       <c r="AX23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AX3*G3+#REF!*#REF!+G4*AX4+G8*AX8+AX9*G9+AX10*G10+AX11*G11+G14*AX14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AX6+#REF!*#REF!+G16*AX16+G18*AX18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AX3*G3+#REF!*#REF!+G4*AX4+G8*AX8+AX9*G9+AX10*G10+AX11*G11+G14*AX14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AX6+#REF!*#REF!+G16*AX16+G18*AX18+G19*AX19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AY23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AY3*G3+#REF!*#REF!+G4*AY4+G8*AY8+AY10*G10+AY11*G11+G14*AY14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AY6+#REF!*#REF!+G16*AY16+G18*AY18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AY3*G3+#REF!*#REF!+G4*AY4+G8*AY8+AY9*G9+AY10*G10+AY11*G11+G14*AY14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AY6+#REF!*#REF!+G16*AY16+G18*AY18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AZ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AZ3*G3+#REF!*#REF!+G4*AZ4+G8*AZ8+G10*AZ10+AZ11*G11+AZ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AZ6*G6+#REF!*#REF!+G16*AZ16+G18*AZ18+G19*AZ19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AZ3*G3+#REF!*#REF!+G4*AZ4+G8*AZ8+AZ10*G10+AZ11*G11+G14*AZ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AZ6+#REF!*#REF!+G16*AZ16+G18*AZ18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BA23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BA3*G3+#REF!*#REF!+G4*BA4+G10*BA10+BA11*G11+BA14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BA6*G6+#REF!*#REF!+G16*BA16+G18*BA18+G19*BA19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BA3*G3+#REF!*#REF!+G4*BA4+G8*BA8+G10*BA10+BA11*G11+BA14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BA6*G6+#REF!*#REF!+G16*BA16+G18*BA18+G19*BA19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BB23" s="23" t="e">
@@ -5002,7 +5025,7 @@
         <v>#REF!</v>
       </c>
       <c r="BD23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BD3*G3+#REF!*#REF!+G4*BD4+G10*BD10+BD11*G11+BD14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BD6*G6+G16*BD16+G18*BD18+G19*BD19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BD3*G3+#REF!*#REF!+G4*BD4+G10*BD10+BD11*G11+BD14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BD6*G6+#REF!*#REF!+G16*BD16+G18*BD18+G19*BD19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BE23" s="23" t="e">
@@ -5030,15 +5053,15 @@
         <v>#REF!</v>
       </c>
       <c r="BK23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BK3*G3+#REF!*#REF!+G4*BK4+G10*BK10+G11*BK11+G14*BK14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BK6+BK16*G16+G18*BK18+G19*BK19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BK3*G3+#REF!*#REF!+G4*BK4+G10*BK10+BK11*G11+BK14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BK6*G6+G16*BK16+G18*BK18+G19*BK19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BL23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BL3*G3+#REF!*#REF!+G4*BL4+G10*BL10+G14*BL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BL6+BL16*G16+G18*BL18+G19*BL19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BL3*G3+#REF!*#REF!+G4*BL4+G10*BL10+G11*BL11+G14*BL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BL6+BL16*G16+G18*BL18+G19*BL19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BM23" s="23" t="e">
-        <f>(#REF!*#REF!+BM3*G3+G4*BM4+G14*BM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BM6+BM16*G16+G18*BM18+G19*BM19+G22*BM22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BM3*G3+#REF!*#REF!+G4*BM4+G10*BM10+G14*BM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BM6+BM16*G16+G18*BM18+G19*BM19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BN23" s="23" t="e">
@@ -5049,16 +5072,16 @@
         <f>(#REF!*#REF!+BO3*G3+G4*BO4+G14*BO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BO6+BO16*G16+G18*BO18+G19*BO19+G22*BO22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BP23" s="30" t="e">
+      <c r="BP23" s="23" t="e">
         <f>(#REF!*#REF!+BP3*G3+G4*BP4+G14*BP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BP6+BP16*G16+G18*BP18+G19*BP19+G22*BP22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BQ23" s="23" t="e">
+      <c r="BQ23" s="30" t="e">
         <f>(#REF!*#REF!+BQ3*G3+G4*BQ4+G14*BQ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BQ6+BQ16*G16+G18*BQ18+G19*BQ19+G22*BQ22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BR23" s="23" t="e">
-        <f>(#REF!*#REF!+BR3*G3+G14*BR14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BR6+BR16*G16+G18*BR18+G19*BR19+G22*BR22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+BR3*G3+G4*BR4+G14*BR14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BR6+BR16*G16+G18*BR18+G19*BR19+G22*BR22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BS23" s="23" t="e">
@@ -5069,15 +5092,19 @@
         <f>(#REF!*#REF!+BT3*G3+G14*BT14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BT6+BT16*G16+G18*BT18+G19*BT19+G22*BT22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BU23" s="13"/>
+      <c r="BU23" s="23" t="e">
+        <f>(#REF!*#REF!+BU3*G3+G14*BU14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BU6+BU16*G16+G18*BU18+G19*BU19+G22*BU22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <v>#REF!</v>
+      </c>
       <c r="BV23" s="13"/>
       <c r="BW23" s="13"/>
       <c r="BX23" s="13"/>
-      <c r="CA23" s="15">
+      <c r="BY23" s="13"/>
+      <c r="CB23" s="15">
         <v>1149.48</v>
       </c>
     </row>
-    <row r="24" spans="1:79" ht="44.25" customHeight="1" thickBot="1">
+    <row r="24" spans="1:80" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -5150,29 +5177,30 @@
       <c r="BR24" s="14"/>
       <c r="BS24" s="14"/>
       <c r="BT24" s="14"/>
-      <c r="BU24" s="23">
-        <f>SUM(BU2:BU20)</f>
-        <v>12977.112800000001</v>
-      </c>
+      <c r="BU24" s="14"/>
       <c r="BV24" s="23">
         <f>SUM(BV2:BV20)</f>
-        <v>12609.442800000001</v>
-      </c>
-      <c r="BW24" s="24">
-        <f>BV24-BU24</f>
-        <v>-367.67000000000007</v>
-      </c>
-      <c r="BX24" s="13">
-        <f>((BV24-BU24)/BU24)*100</f>
-        <v>-2.8332188034922532</v>
-      </c>
-      <c r="CA24" s="15">
-        <f>SUM(CA5:CA23)</f>
-        <v>655.07839999999919</v>
-      </c>
-    </row>
-    <row r="25" spans="1:79">
-      <c r="BU25" s="15">
+        <v>13102.402800000002</v>
+      </c>
+      <c r="BW24" s="23">
+        <f>SUM(BW2:BW20)</f>
+        <v>12602.522800000001</v>
+      </c>
+      <c r="BX24" s="24">
+        <f>BW24-BV24</f>
+        <v>-499.88000000000102</v>
+      </c>
+      <c r="BY24" s="13">
+        <f>((BW24-BV24)/BV24)*100</f>
+        <v>-3.8151780832138744</v>
+      </c>
+      <c r="CB24" s="15">
+        <f>SUM(CB5:CB23)</f>
+        <v>522.86839999999916</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="BV25" s="15">
         <v>12034.32</v>
       </c>
     </row>
@@ -5230,17 +5258,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DECD697-7590-4F64-9E15-0FA62A69A078}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.59765625" customWidth="1"/>
-    <col min="2" max="2" width="17.59765625" style="20" customWidth="1"/>
-    <col min="3" max="7" width="17.59765625" customWidth="1"/>
-    <col min="9" max="9" width="17.59765625" customWidth="1"/>
-    <col min="10" max="10" width="9.59765625" customWidth="1"/>
-    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="20" customWidth="1"/>
+    <col min="3" max="7" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>11</v>
       </c>
@@ -5273,22 +5301,22 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
-        <v>אימקו</v>
+        <v>אייראנג'י טק</v>
       </c>
       <c r="B2" s="17">
         <f>'התיק העדכני'!A2</f>
-        <v>282012</v>
+        <v>1105907</v>
       </c>
       <c r="C2" s="18">
         <f>'התיק העדכני'!H2</f>
-        <v>11000</v>
+        <v>744</v>
       </c>
       <c r="D2" s="19">
         <f>'התיק העדכני'!G2</f>
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="E2" s="17">
         <v>10800</v>
@@ -5299,7 +5327,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>8800</v>
+        <v>799.8</v>
       </c>
       <c r="J2" s="25"/>
       <c r="L2" s="21">
@@ -5311,7 +5339,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -5337,7 +5365,7 @@
       <c r="G3" s="17"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>921</v>
+        <v>941.8</v>
       </c>
       <c r="J3" s="26"/>
       <c r="L3" s="21">
@@ -5349,7 +5377,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -5387,7 +5415,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -5412,7 +5440,7 @@
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>622.4</v>
+        <v>656.2</v>
       </c>
       <c r="J5" s="26"/>
       <c r="L5" s="21">
@@ -5424,7 +5452,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -5449,7 +5477,7 @@
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4647</v>
+        <v>4880</v>
       </c>
       <c r="J6" s="26"/>
       <c r="L6" s="21">
@@ -5461,7 +5489,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -5487,7 +5515,7 @@
       <c r="G7" s="18"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3954</v>
+        <v>3996</v>
       </c>
       <c r="J7" s="26"/>
       <c r="L7" s="21">
@@ -5499,7 +5527,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -5525,7 +5553,7 @@
       <c r="G8" s="18"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40740</v>
+        <v>45300</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -5536,7 +5564,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -5562,7 +5590,7 @@
       <c r="G9" s="17"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10820</v>
+        <v>10660</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -5573,7 +5601,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -5599,7 +5627,7 @@
       <c r="G10" s="18"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5067</v>
+        <v>5027</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -5610,7 +5638,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -5636,7 +5664,7 @@
       <c r="G11" s="18"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1054</v>
+        <v>1086</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -5647,7 +5675,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -5673,7 +5701,7 @@
       <c r="G12" s="18"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>28730</v>
+        <v>29650</v>
       </c>
       <c r="J12" s="26"/>
       <c r="L12" s="21">
@@ -5685,7 +5713,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -5696,11 +5724,11 @@
       </c>
       <c r="C13" s="18">
         <f>'התיק העדכני'!H13</f>
-        <v>723</v>
+        <v>840</v>
       </c>
       <c r="D13" s="19">
         <f>'התיק העדכני'!G13</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E13" s="16">
         <v>890</v>
@@ -5711,7 +5739,7 @@
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>837.7</v>
+        <v>840</v>
       </c>
       <c r="J13" s="26"/>
       <c r="L13" s="21">
@@ -5723,7 +5751,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -5749,7 +5777,7 @@
       <c r="G14" s="17"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7922</v>
+        <v>8100</v>
       </c>
       <c r="J14" s="26"/>
       <c r="L14" s="21">
@@ -5761,7 +5789,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -5787,7 +5815,7 @@
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12628.12</v>
+        <v>12994</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
@@ -5799,7 +5827,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -5825,7 +5853,7 @@
       <c r="G16" s="17"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216.57</v>
+        <v>216</v>
       </c>
       <c r="J16" s="26"/>
       <c r="L16" s="21">
@@ -5837,7 +5865,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -5863,7 +5891,7 @@
       <c r="G17" s="17"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>177.17</v>
+        <v>181.5</v>
       </c>
       <c r="J17" s="26"/>
       <c r="L17" s="21">
@@ -5875,7 +5903,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -5901,7 +5929,7 @@
       <c r="G18" s="18"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1823</v>
+        <v>1864</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -5912,7 +5940,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -5923,7 +5951,7 @@
       </c>
       <c r="C19" s="18">
         <f>'התיק העדכני'!H19</f>
-        <v>102.77</v>
+        <v>93.13</v>
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
@@ -5934,7 +5962,7 @@
       <c r="G19" s="18"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>71.3</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -5945,7 +5973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -5979,7 +6007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6013,7 +6041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6047,7 +6075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6081,7 +6109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6115,7 +6143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6149,7 +6177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6183,7 +6211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6217,7 +6245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="str">
         <f>'התיק העדכני'!E20</f>
         <v>אירודרום קבוצה</v>
@@ -6239,7 +6267,7 @@
       <c r="G28" s="19"/>
       <c r="I28" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>75.2</v>
+        <v>82.3</v>
       </c>
       <c r="J28" s="26"/>
       <c r="L28" s="21">
@@ -6259,15 +6287,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7390F3B9-AE45-44AE-B4DF-D92B58EB94BD}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
-    <col min="3" max="7" width="17.59765625" customWidth="1"/>
-    <col min="9" max="9" width="17.59765625" customWidth="1"/>
-    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
+    <col min="3" max="7" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -6297,22 +6325,22 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
-        <v>אימקו</v>
+        <v>אייראנג'י טק</v>
       </c>
       <c r="B2" s="17">
         <f>'התיק העדכני'!A2</f>
-        <v>282012</v>
+        <v>1105907</v>
       </c>
       <c r="C2" s="18">
         <f>'התיק העדכני'!H2</f>
-        <v>11000</v>
+        <v>744</v>
       </c>
       <c r="D2" s="19">
         <f>'התיק העדכני'!G2</f>
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="E2" s="17">
         <v>10500</v>
@@ -6323,7 +6351,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>8800</v>
+        <v>799.8</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+GEMINI!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
@@ -6334,7 +6362,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -6360,7 +6388,7 @@
       <c r="G3" s="7"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>921</v>
+        <v>941.8</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
@@ -6371,7 +6399,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -6408,7 +6436,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -6434,7 +6462,7 @@
       <c r="G5" s="7"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>622.4</v>
+        <v>656.2</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
@@ -6445,7 +6473,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -6471,7 +6499,7 @@
       <c r="G6" s="7"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4647</v>
+        <v>4880</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
@@ -6482,7 +6510,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -6508,7 +6536,7 @@
       <c r="G7" s="8"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3954</v>
+        <v>3996</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+GEMINI!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
@@ -6519,7 +6547,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -6545,7 +6573,7 @@
       <c r="G8" s="8"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40740</v>
+        <v>45300</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+GEMINI!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
@@ -6556,7 +6584,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -6582,7 +6610,7 @@
       <c r="G9" s="8"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10820</v>
+        <v>10660</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+GEMINI!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -6593,7 +6621,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -6619,7 +6647,7 @@
       <c r="G10" s="8"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5067</v>
+        <v>5027</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+GEMINI!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -6630,7 +6658,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -6656,7 +6684,7 @@
       <c r="G11" s="8"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1054</v>
+        <v>1086</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+GEMINI!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -6667,7 +6695,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -6693,7 +6721,7 @@
       <c r="G12" s="8"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>28730</v>
+        <v>29650</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+GEMINI!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
@@ -6704,7 +6732,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -6715,11 +6743,11 @@
       </c>
       <c r="C13" s="18">
         <f>'התיק העדכני'!H13</f>
-        <v>723</v>
+        <v>840</v>
       </c>
       <c r="D13" s="19">
         <f>'התיק העדכני'!G13</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E13" s="16">
         <v>890</v>
@@ -6730,7 +6758,7 @@
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>837.7</v>
+        <v>840</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+GEMINI!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
@@ -6741,7 +6769,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -6767,7 +6795,7 @@
       <c r="G14" s="7"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7922</v>
+        <v>8100</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
@@ -6778,7 +6806,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -6804,7 +6832,7 @@
       <c r="G15" s="7"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12628.12</v>
+        <v>12994</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+GEMINI!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
@@ -6815,7 +6843,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -6841,7 +6869,7 @@
       <c r="G16" s="7"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216.57</v>
+        <v>216</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
@@ -6852,7 +6880,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -6878,7 +6906,7 @@
       <c r="G17" s="7"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>177.17</v>
+        <v>181.5</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+GEMINI!E17+PERPLIXITY!E17+DEEPSEEK!E17)/4</f>
@@ -6889,7 +6917,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -6915,7 +6943,7 @@
       <c r="G18" s="8"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1823</v>
+        <v>1864</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+GEMINI!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -6926,7 +6954,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -6937,7 +6965,7 @@
       </c>
       <c r="C19" s="18">
         <f>'התיק העדכני'!H19</f>
-        <v>102.77</v>
+        <v>93.13</v>
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
@@ -6948,7 +6976,7 @@
       <c r="G19" s="8"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>71.3</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+GEMINI!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -6959,7 +6987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -6971,7 +6999,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -6983,7 +7011,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -6995,7 +7023,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -7007,7 +7035,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -7019,7 +7047,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -7031,7 +7059,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -7043,7 +7071,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -7055,7 +7083,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -7075,15 +7103,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88497C0-21A8-47C7-B959-3D6DF74EF6E2}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
-    <col min="3" max="6" width="17.59765625" customWidth="1"/>
-    <col min="9" max="9" width="17.59765625" customWidth="1"/>
-    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
+    <col min="3" max="6" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -7113,22 +7141,22 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
-        <v>אימקו</v>
+        <v>אייראנג'י טק</v>
       </c>
       <c r="B2" s="17">
         <f>'התיק העדכני'!A2</f>
-        <v>282012</v>
+        <v>1105907</v>
       </c>
       <c r="C2" s="18">
         <f>'התיק העדכני'!H2</f>
-        <v>11000</v>
+        <v>744</v>
       </c>
       <c r="D2" s="19">
         <f>'התיק העדכני'!G2</f>
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="E2" s="17">
         <v>10500</v>
@@ -7139,7 +7167,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>8800</v>
+        <v>799.8</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+GEMINI!E2+DEEPSEEK!E2)/4</f>
@@ -7150,7 +7178,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -7176,7 +7204,7 @@
       <c r="G3" s="10"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>921</v>
+        <v>941.8</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
@@ -7187,7 +7215,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -7224,7 +7252,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -7250,7 +7278,7 @@
       <c r="G5" s="10"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>622.4</v>
+        <v>656.2</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
@@ -7261,7 +7289,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -7287,7 +7315,7 @@
       <c r="G6" s="10"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4647</v>
+        <v>4880</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
@@ -7298,7 +7326,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -7324,7 +7352,7 @@
       <c r="G7" s="10"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3954</v>
+        <v>3996</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+GEMINI!E7+DEEPSEEK!E7)/4</f>
@@ -7335,7 +7363,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -7360,7 +7388,7 @@
       </c>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40740</v>
+        <v>45300</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+GEMINI!E8+DEEPSEEK!E8)/4</f>
@@ -7371,7 +7399,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -7396,7 +7424,7 @@
       </c>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10820</v>
+        <v>10660</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+GEMINI!E9+DEEPSEEK!E9)/4</f>
@@ -7407,7 +7435,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -7432,7 +7460,7 @@
       </c>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5067</v>
+        <v>5027</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+GEMINI!E10+DEEPSEEK!E10)/4</f>
@@ -7443,7 +7471,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -7468,7 +7496,7 @@
       </c>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1054</v>
+        <v>1086</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+GEMINI!E11+DEEPSEEK!E11)/4</f>
@@ -7479,7 +7507,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -7505,7 +7533,7 @@
       <c r="G12" s="10"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>28730</v>
+        <v>29650</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+GEMINI!E12+DEEPSEEK!E12)/4</f>
@@ -7516,7 +7544,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -7527,11 +7555,11 @@
       </c>
       <c r="C13" s="18">
         <f>'התיק העדכני'!H13</f>
-        <v>723</v>
+        <v>840</v>
       </c>
       <c r="D13" s="19">
         <f>'התיק העדכני'!G13</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E13" s="16">
         <v>880</v>
@@ -7542,7 +7570,7 @@
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>837.7</v>
+        <v>840</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+CHATGPT!E13+GEMINI!E13+DEEPSEEK!E13)/4</f>
@@ -7553,7 +7581,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -7579,7 +7607,7 @@
       <c r="G14" s="10"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7922</v>
+        <v>8100</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
@@ -7590,7 +7618,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -7616,7 +7644,7 @@
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12628.12</v>
+        <v>12994</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
@@ -7627,7 +7655,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -7653,7 +7681,7 @@
       <c r="G16" s="10"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216.57</v>
+        <v>216</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+GEMINI!E16+DEEPSEEK!E16)/4</f>
@@ -7664,7 +7692,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -7690,7 +7718,7 @@
       <c r="G17" s="10"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>177.17</v>
+        <v>181.5</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+GEMINI!E17+DEEPSEEK!E17)/4</f>
@@ -7701,7 +7729,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -7726,7 +7754,7 @@
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1823</v>
+        <v>1864</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
@@ -7737,7 +7765,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -7748,7 +7776,7 @@
       </c>
       <c r="C19" s="18">
         <f>'התיק העדכני'!H19</f>
-        <v>102.77</v>
+        <v>93.13</v>
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
@@ -7758,7 +7786,7 @@
       <c r="F19" s="16"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>71.3</v>
+        <v>67.900000000000006</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+GEMINI!E19+DEEPSEEK!E19)/4</f>
@@ -7769,7 +7797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -7781,7 +7809,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -7793,7 +7821,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -7805,7 +7833,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -7817,7 +7845,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -7829,7 +7857,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -7841,7 +7869,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -7853,7 +7881,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -7865,7 +7893,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -7885,16 +7913,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D354D65C-237D-4544-BBD1-8A37190947C4}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
-    <col min="3" max="5" width="17.59765625" customWidth="1"/>
-    <col min="6" max="6" width="20.3984375" customWidth="1"/>
-    <col min="9" max="9" width="17.59765625" customWidth="1"/>
-    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
+    <col min="3" max="5" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="9" max="9" width="17.5703125" customWidth="1"/>
+    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -7923,22 +7951,22 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
-        <v>אימקו</v>
+        <v>אייראנג'י טק</v>
       </c>
       <c r="B2" s="17">
         <f>'התיק העדכני'!A2</f>
-        <v>282012</v>
+        <v>1105907</v>
       </c>
       <c r="C2" s="18">
         <f>'התיק העדכני'!H2</f>
-        <v>11000</v>
+        <v>744</v>
       </c>
       <c r="D2" s="19">
         <f>'התיק העדכני'!G2</f>
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="E2" s="17">
         <v>10400</v>
@@ -7949,7 +7977,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>8800</v>
+        <v>799.8</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+PERPLIXITY!E2+GEMINI!E2)/4</f>
@@ -7960,7 +7988,7 @@
         <v>12350</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -7986,7 +8014,7 @@
       <c r="G3" s="31"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>921</v>
+        <v>941.8</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
@@ -7997,7 +8025,7 @@
         <v>1368.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -8033,7 +8061,7 @@
         <v>6975.25</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -8059,7 +8087,7 @@
       <c r="G5" s="31"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>622.4</v>
+        <v>656.2</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
@@ -8070,7 +8098,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -8096,7 +8124,7 @@
       <c r="G6" s="31"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4647</v>
+        <v>4880</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
@@ -8107,7 +8135,7 @@
         <v>4332.75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -8132,7 +8160,7 @@
       </c>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3954</v>
+        <v>3996</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+GEMINI!E7)/4</f>
@@ -8143,7 +8171,7 @@
         <v>4213.25</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -8169,7 +8197,7 @@
       <c r="G8" s="31"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>40740</v>
+        <v>45300</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+GEMINI!E8)/4</f>
@@ -8180,7 +8208,7 @@
         <v>43218.75</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -8206,7 +8234,7 @@
       <c r="G9" s="31"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10820</v>
+        <v>10660</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+GEMINI!E9)/4</f>
@@ -8217,7 +8245,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -8243,7 +8271,7 @@
       <c r="G10" s="31"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5067</v>
+        <v>5027</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+GEMINI!E10)/4</f>
@@ -8254,7 +8282,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -8280,7 +8308,7 @@
       <c r="G11" s="31"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1054</v>
+        <v>1086</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+GEMINI!E11)/4</f>
@@ -8291,7 +8319,7 @@
         <v>1146.25</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -8317,7 +8345,7 @@
       <c r="G12" s="31"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>28730</v>
+        <v>29650</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+GEMINI!E12)/4</f>
@@ -8328,7 +8356,7 @@
         <v>28496.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -8339,11 +8367,11 @@
       </c>
       <c r="C13" s="18">
         <f>'התיק העדכני'!H13</f>
-        <v>723</v>
+        <v>840</v>
       </c>
       <c r="D13" s="19">
         <f>'התיק העדכני'!G13</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E13" s="16">
         <v>900</v>
@@ -8354,12 +8382,12 @@
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>837.7</v>
+        <v>840</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
     </row>
-    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -8385,7 +8413,7 @@
       <c r="G14" s="31"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>7922</v>
+        <v>8100</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
@@ -8396,7 +8424,7 @@
         <v>8391</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -8421,7 +8449,7 @@
       </c>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>75.2</v>
+        <v>82.3</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+PERPLIXITY!E15+GEMINI!E15)/4</f>
@@ -8432,7 +8460,7 @@
         <v>15132.75</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -8457,7 +8485,7 @@
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12628.12</v>
+        <v>12994</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
@@ -8468,7 +8496,7 @@
         <v>239.75</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -8494,7 +8522,7 @@
       <c r="G17" s="31"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216.57</v>
+        <v>216</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+GEMINI!E17)/4</f>
@@ -8505,7 +8533,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -8531,7 +8559,7 @@
       <c r="G18" s="31"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I17</f>
-        <v>177.17</v>
+        <v>181.5</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+GEMINI!E18)/4</f>
@@ -8542,7 +8570,7 @@
         <v>1928.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -8553,7 +8581,7 @@
       </c>
       <c r="C19" s="18">
         <f>'התיק העדכני'!H19</f>
-        <v>102.77</v>
+        <v>93.13</v>
       </c>
       <c r="D19" s="19">
         <f>'התיק העדכני'!G19</f>
@@ -8561,7 +8589,7 @@
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1823</v>
+        <v>1864</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+GEMINI!E19)/4</f>
@@ -8572,7 +8600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -8583,7 +8611,7 @@
       <c r="L20" s="21"/>
       <c r="M20" s="21"/>
     </row>
-    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="17"/>
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
@@ -8595,7 +8623,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -8607,7 +8635,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -8619,7 +8647,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -8631,7 +8659,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -8643,7 +8671,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -8655,7 +8683,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -8667,7 +8695,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
+    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\BURSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4134F334-8E19-4E08-958B-01E4DA8AE313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBB11F7-40EA-423C-BB3D-0E2A60544D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="114">
   <si>
     <t>MTF מחקה אינדקס תעשיה ישראל</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>אייראנג'י טק</t>
+  </si>
+  <si>
+    <t>מחיר 09/02/2026</t>
   </si>
 </sst>
 </file>
@@ -1178,7 +1181,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>111</v>
@@ -1397,15 +1400,15 @@
       </c>
       <c r="B2" s="17">
         <f>GEMINI!L2</f>
-        <v>10550</v>
+        <v>742.75</v>
       </c>
       <c r="C2" s="17">
         <f>GEMINI!M2</f>
-        <v>12350</v>
+        <v>916</v>
       </c>
       <c r="D2" s="6" t="str">
         <f>IF(I2&lt;GEMINI!L2,"למכור בהפסד",IF(I2&gt;GEMINI!M2,"למכור ברווח","לשמור"))</f>
-        <v>למכור בהפסד</v>
+        <v>לשמור</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>112</v>
@@ -1414,13 +1417,13 @@
         <v>46042</v>
       </c>
       <c r="G2" s="27">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H2" s="13">
-        <v>744</v>
+        <v>774.5</v>
       </c>
       <c r="I2" s="13">
-        <v>799.8</v>
+        <v>844</v>
       </c>
       <c r="J2" s="13">
         <v>799.8</v>
@@ -1490,11 +1493,11 @@
       <c r="BU2" s="6"/>
       <c r="BV2" s="13">
         <f t="shared" ref="BV2:BV20" si="0">(G2*H2)/100-CB2</f>
-        <v>372</v>
+        <v>774.5</v>
       </c>
       <c r="BW2" s="13">
         <f t="shared" ref="BW2:BW20" si="1">(G2*H2)/100</f>
-        <v>372</v>
+        <v>774.5</v>
       </c>
       <c r="BX2" s="6"/>
       <c r="BY2" s="6"/>
@@ -1509,11 +1512,11 @@
       </c>
       <c r="B3" s="17">
         <f>GEMINI!L3</f>
-        <v>1098</v>
+        <v>1004.25</v>
       </c>
       <c r="C3" s="17">
         <f>GEMINI!M3</f>
-        <v>1368.25</v>
+        <v>1193.25</v>
       </c>
       <c r="D3" s="6" t="str">
         <f>IF(I3&lt;GEMINI!L3,"למכור בהפסד",IF(I3&gt;GEMINI!M3,"למכור ברווח","לשמור"))</f>
@@ -1523,80 +1526,38 @@
         <v>87</v>
       </c>
       <c r="F3" s="4">
-        <v>46029</v>
+        <v>46063</v>
       </c>
       <c r="G3" s="27">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H3" s="13">
-        <v>1153.6300000000001</v>
+        <v>950</v>
       </c>
       <c r="I3" s="13">
-        <v>941.8</v>
-      </c>
-      <c r="J3" s="13">
-        <v>941.8</v>
-      </c>
-      <c r="K3" s="13">
-        <v>969.7</v>
-      </c>
-      <c r="L3" s="13">
-        <v>921</v>
-      </c>
-      <c r="M3" s="13">
-        <v>1074</v>
-      </c>
-      <c r="N3" s="13">
-        <v>1245</v>
-      </c>
-      <c r="O3" s="13">
-        <v>1311</v>
-      </c>
-      <c r="P3" s="13">
-        <v>1311</v>
-      </c>
-      <c r="Q3" s="13">
-        <v>1340</v>
-      </c>
-      <c r="R3" s="13">
-        <v>1500</v>
-      </c>
-      <c r="S3" s="13">
-        <v>1424</v>
-      </c>
-      <c r="T3" s="13">
-        <v>1348</v>
-      </c>
-      <c r="U3" s="13">
-        <v>1373</v>
-      </c>
-      <c r="V3" s="13">
-        <v>1331</v>
-      </c>
-      <c r="W3" s="13">
-        <v>1386</v>
-      </c>
-      <c r="X3" s="13">
-        <v>1342</v>
-      </c>
-      <c r="Y3" s="13">
-        <v>1250</v>
-      </c>
-      <c r="Z3" s="13">
-        <v>1389</v>
-      </c>
-      <c r="AA3" s="13">
-        <v>1389</v>
-      </c>
-      <c r="AB3" s="13">
-        <v>1367</v>
-      </c>
-      <c r="AC3" s="13">
-        <v>1026</v>
-      </c>
-      <c r="AD3" s="13">
-        <v>949.1</v>
-      </c>
+        <v>888</v>
+      </c>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="13"/>
+      <c r="AB3" s="13"/>
+      <c r="AC3" s="13"/>
+      <c r="AD3" s="13"/>
       <c r="AE3" s="13"/>
       <c r="AF3" s="13"/>
       <c r="AG3" s="13"/>
@@ -1642,29 +1603,23 @@
       <c r="BU3" s="13"/>
       <c r="BV3" s="13">
         <f t="shared" si="0"/>
-        <v>-126.73159999999989</v>
+        <v>285</v>
       </c>
       <c r="BW3" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="BX3" s="13">
         <f>(BW3-BV3)</f>
-        <v>126.73159999999989</v>
+        <v>0</v>
       </c>
       <c r="BY3" s="13">
         <f>((BM3-H3)/H3)*100</f>
         <v>-100</v>
       </c>
-      <c r="BZ3">
-        <v>68</v>
-      </c>
-      <c r="CA3">
-        <v>1340</v>
-      </c>
       <c r="CB3" s="15">
         <f>(BZ3*CA3-BZ3*H3)/100</f>
-        <v>126.73159999999989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1673,15 +1628,15 @@
       </c>
       <c r="B4" s="17">
         <f>GEMINI!L4</f>
-        <v>6030.25</v>
+        <v>5855</v>
       </c>
       <c r="C4" s="17">
         <f>GEMINI!M4</f>
-        <v>6975.25</v>
+        <v>7051.25</v>
       </c>
       <c r="D4" s="6" t="str">
         <f>IF(I4&lt;GEMINI!L4,"למכור בהפסד",IF(I4&gt;GEMINI!M4,"למכור ברווח","לשמור"))</f>
-        <v>למכור בהפסד</v>
+        <v>לשמור</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>33</v>
@@ -1696,7 +1651,7 @@
         <v>5925</v>
       </c>
       <c r="I4" s="13">
-        <v>5990</v>
+        <v>6030</v>
       </c>
       <c r="J4" s="13">
         <v>5990</v>
@@ -1831,11 +1786,11 @@
       </c>
       <c r="B5" s="17">
         <f>GEMINI!L5</f>
-        <v>607.75</v>
+        <v>593.75</v>
       </c>
       <c r="C5" s="17">
         <f>GEMINI!M5</f>
-        <v>768</v>
+        <v>741.25</v>
       </c>
       <c r="D5" s="6" t="str">
         <f>IF(I5&lt;GEMINI!L5,"למכור בהפסד",IF(I5&gt;GEMINI!M5,"למכור ברווח","לשמור"))</f>
@@ -1854,7 +1809,7 @@
         <v>617.53</v>
       </c>
       <c r="I5" s="13">
-        <v>656.2</v>
+        <v>647</v>
       </c>
       <c r="J5" s="13">
         <v>656.2</v>
@@ -2000,15 +1955,15 @@
       </c>
       <c r="B6" s="17">
         <f>GEMINI!L6</f>
-        <v>3560</v>
+        <v>4409</v>
       </c>
       <c r="C6" s="17">
         <f>GEMINI!M6</f>
-        <v>4332.75</v>
+        <v>5478.5</v>
       </c>
       <c r="D6" s="6" t="str">
         <f>IF(I6&lt;GEMINI!L6,"למכור בהפסד",IF(I6&gt;GEMINI!M6,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>84</v>
@@ -2023,7 +1978,7 @@
         <v>4040</v>
       </c>
       <c r="I6" s="13">
-        <v>4880</v>
+        <v>5001</v>
       </c>
       <c r="J6" s="13">
         <v>4880</v>
@@ -2165,11 +2120,11 @@
       </c>
       <c r="B7" s="17">
         <f>GEMINI!L7</f>
-        <v>3663.25</v>
+        <v>3713.25</v>
       </c>
       <c r="C7" s="17">
         <f>GEMINI!M7</f>
-        <v>4213.25</v>
+        <v>4350.75</v>
       </c>
       <c r="D7" s="6" t="str">
         <f>IF(I7&lt;GEMINI!L7,"למכור בהפסד",IF(I7&gt;GEMINI!M7,"למכור ברווח","לשמור"))</f>
@@ -2188,7 +2143,7 @@
         <v>3585</v>
       </c>
       <c r="I7" s="13">
-        <v>3996</v>
+        <v>4084</v>
       </c>
       <c r="J7" s="13">
         <v>3996</v>
@@ -2334,15 +2289,15 @@
       </c>
       <c r="B8" s="17">
         <f>GEMINI!L8</f>
-        <v>37884</v>
+        <v>40488.25</v>
       </c>
       <c r="C8" s="17">
         <f>GEMINI!M8</f>
-        <v>43218.75</v>
+        <v>47899</v>
       </c>
       <c r="D8" s="6" t="str">
         <f>IF(I8&lt;GEMINI!L8,"למכור בהפסד",IF(I8&gt;GEMINI!M8,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>52</v>
@@ -2357,7 +2312,7 @@
         <v>37875</v>
       </c>
       <c r="I8" s="13">
-        <v>45300</v>
+        <v>45190</v>
       </c>
       <c r="J8" s="13">
         <v>45300</v>
@@ -2562,7 +2517,7 @@
         <v>9227</v>
       </c>
       <c r="I9" s="13">
-        <v>10660</v>
+        <v>10640</v>
       </c>
       <c r="J9" s="13">
         <v>10660</v>
@@ -2763,7 +2718,7 @@
         <v>4834</v>
       </c>
       <c r="I10" s="13">
-        <v>5027</v>
+        <v>4987</v>
       </c>
       <c r="J10" s="13">
         <v>5027</v>
@@ -2976,11 +2931,11 @@
       </c>
       <c r="B11" s="17">
         <f>GEMINI!L11</f>
-        <v>940.75</v>
+        <v>980.75</v>
       </c>
       <c r="C11" s="17">
         <f>GEMINI!M11</f>
-        <v>1146.25</v>
+        <v>1246.25</v>
       </c>
       <c r="D11" s="6" t="str">
         <f>IF(I11&lt;GEMINI!L11,"למכור בהפסד",IF(I11&gt;GEMINI!M11,"למכור ברווח","לשמור"))</f>
@@ -2999,7 +2954,7 @@
         <v>901.87</v>
       </c>
       <c r="I11" s="13">
-        <v>1086</v>
+        <v>1066</v>
       </c>
       <c r="J11" s="13">
         <v>1086</v>
@@ -3147,11 +3102,11 @@
       </c>
       <c r="B12" s="17">
         <f>GEMINI!L12</f>
-        <v>23843.25</v>
+        <v>23993.25</v>
       </c>
       <c r="C12" s="17">
         <f>GEMINI!M12</f>
-        <v>28496.25</v>
+        <v>28871.25</v>
       </c>
       <c r="D12" s="6" t="str">
         <f>IF(I12&lt;GEMINI!L12,"למכור בהפסד",IF(I12&gt;GEMINI!M12,"למכור ברווח","לשמור"))</f>
@@ -3170,7 +3125,7 @@
         <v>22581.42</v>
       </c>
       <c r="I12" s="13">
-        <v>29650</v>
+        <v>29670</v>
       </c>
       <c r="J12" s="13">
         <v>29650</v>
@@ -3325,11 +3280,11 @@
       </c>
       <c r="B13" s="17">
         <f>GEMINI!L13</f>
-        <v>890</v>
+        <v>871.25</v>
       </c>
       <c r="C13" s="17">
         <f>GEMINI!M13</f>
-        <v>1125</v>
+        <v>1037.5</v>
       </c>
       <c r="D13" s="6" t="str">
         <f>IF(I13&lt;GEMINI!L13,"למכור בהפסד",IF(I13&gt;GEMINI!M13,"למכור ברווח","לשמור"))</f>
@@ -3348,7 +3303,7 @@
         <v>840</v>
       </c>
       <c r="I13" s="13">
-        <v>840</v>
+        <v>788.6</v>
       </c>
       <c r="J13" s="13">
         <v>840</v>
@@ -3466,11 +3421,11 @@
       </c>
       <c r="B14" s="17">
         <f>GEMINI!L14</f>
-        <v>7315</v>
+        <v>7564.5</v>
       </c>
       <c r="C14" s="17">
         <f>GEMINI!M14</f>
-        <v>8391</v>
+        <v>8702.5</v>
       </c>
       <c r="D14" s="6" t="str">
         <f>IF(I14&lt;GEMINI!L14,"למכור בהפסד",IF(I14&gt;GEMINI!M14,"למכור ברווח","לשמור"))</f>
@@ -3489,7 +3444,7 @@
         <v>7204.22</v>
       </c>
       <c r="I14" s="13">
-        <v>8100</v>
+        <v>8253</v>
       </c>
       <c r="J14" s="13">
         <v>8100</v>
@@ -3714,7 +3669,7 @@
       </c>
       <c r="C15" s="17">
         <f>GEMINI!M15</f>
-        <v>15132.75</v>
+        <v>15005.5</v>
       </c>
       <c r="D15" s="6" t="str">
         <f>IF(I15&lt;GEMINI!L15,"למכור בהפסד",IF(I15&gt;GEMINI!M15,"למכור ברווח","לשמור"))</f>
@@ -3733,10 +3688,10 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
-        <v>12994</v>
+        <v>13244</v>
       </c>
       <c r="J15" s="13">
-        <v>12994</v>
+        <v>13244</v>
       </c>
       <c r="K15" s="13">
         <v>12628.12</v>
@@ -3880,11 +3835,11 @@
       </c>
       <c r="B16" s="17">
         <f>GEMINI!L16</f>
-        <v>198.5</v>
+        <v>203.5</v>
       </c>
       <c r="C16" s="17">
         <f>GEMINI!M16</f>
-        <v>239.75</v>
+        <v>243.25</v>
       </c>
       <c r="D16" s="6" t="str">
         <f>IF(I16&lt;GEMINI!L16,"למכור בהפסד",IF(I16&gt;GEMINI!M16,"למכור ברווח","לשמור"))</f>
@@ -3903,7 +3858,7 @@
         <v>199.49</v>
       </c>
       <c r="I16" s="13">
-        <v>216</v>
+        <v>216.71</v>
       </c>
       <c r="J16" s="13">
         <v>216</v>
@@ -4130,11 +4085,11 @@
       </c>
       <c r="B17" s="17">
         <f>GEMINI!L17</f>
-        <v>170</v>
+        <v>170.5</v>
       </c>
       <c r="C17" s="17">
         <f>GEMINI!M17</f>
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D17" s="6" t="str">
         <f>IF(I17&lt;GEMINI!L17,"למכור בהפסד",IF(I17&gt;GEMINI!M17,"למכור ברווח","לשמור"))</f>
@@ -4298,11 +4253,11 @@
       </c>
       <c r="B18" s="17">
         <f>GEMINI!L18</f>
-        <v>1608.75</v>
+        <v>1680.75</v>
       </c>
       <c r="C18" s="17">
         <f>GEMINI!M18</f>
-        <v>1928.25</v>
+        <v>2053.25</v>
       </c>
       <c r="D18" s="6" t="str">
         <f>IF(I18&lt;GEMINI!L18,"למכור בהפסד",IF(I18&gt;GEMINI!M18,"למכור ברווח","לשמור"))</f>
@@ -4321,7 +4276,7 @@
         <v>1434</v>
       </c>
       <c r="I18" s="13">
-        <v>1864</v>
+        <v>1895</v>
       </c>
       <c r="J18" s="13">
         <v>1864</v>
@@ -4496,15 +4451,15 @@
       </c>
       <c r="B19" s="17">
         <f>GEMINI!L19</f>
-        <v>0</v>
+        <v>64.3</v>
       </c>
       <c r="C19" s="17">
         <f>GEMINI!M19</f>
-        <v>0</v>
+        <v>94.25</v>
       </c>
       <c r="D19" s="6" t="str">
         <f>IF(I19&lt;GEMINI!L19,"למכור בהפסד",IF(I19&gt;GEMINI!M19,"למכור ברווח","לשמור"))</f>
-        <v>למכור ברווח</v>
+        <v>לשמור</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>102</v>
@@ -4519,7 +4474,7 @@
         <v>93.13</v>
       </c>
       <c r="I19" s="13">
-        <v>67.900000000000006</v>
+        <v>71</v>
       </c>
       <c r="J19" s="13">
         <v>67.900000000000006</v>
@@ -4633,11 +4588,11 @@
       </c>
       <c r="B20" s="17">
         <f>GEMINI!L12</f>
-        <v>23843.25</v>
+        <v>23993.25</v>
       </c>
       <c r="C20" s="17">
         <f>GEMINI!M12</f>
-        <v>28496.25</v>
+        <v>28871.25</v>
       </c>
       <c r="D20" s="6" t="str">
         <f>IF(I20&lt;GEMINI!L12,"למכור בהפסד",IF(I20&gt;GEMINI!M12,"למכור ברווח","לשמור"))</f>
@@ -4650,13 +4605,13 @@
         <v>46056</v>
       </c>
       <c r="G20" s="27">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="H20" s="13">
-        <v>65</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="I20" s="13">
-        <v>82.3</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="J20" s="13">
         <v>82.3</v>
@@ -4734,11 +4689,11 @@
       <c r="BU20" s="13"/>
       <c r="BV20" s="13">
         <f t="shared" si="0"/>
-        <v>195</v>
+        <v>449.4</v>
       </c>
       <c r="BW20" s="13">
         <f t="shared" si="1"/>
-        <v>195</v>
+        <v>449.4</v>
       </c>
       <c r="BX20" s="13"/>
       <c r="BY20" s="13"/>
@@ -4838,27 +4793,27 @@
       <c r="H23" s="13"/>
       <c r="I23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19+G20*I20)/100</f>
-        <v>14073.616000000002</v>
+        <v>15109.6</v>
       </c>
       <c r="J23" s="23">
         <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19+G20*J20)/100</f>
-        <v>14073.616000000002</v>
+        <v>14740.416000000001</v>
       </c>
       <c r="K23" s="23">
         <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19+G20*K20)/100</f>
-        <v>13316.741599999999</v>
+        <v>13542.3416</v>
       </c>
       <c r="L23" s="23">
         <f>(L2*G2+G3*L3+L4*G4+G5*L5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+L13*G13+G14*L14+L15*G15+G16*L16+G17*L17+L18*G18+G19*L19+G20*L20)/100</f>
-        <v>13186.731599999999</v>
+        <v>13393.131599999999</v>
       </c>
       <c r="M23" s="23">
         <f>(M2*G2+G3*M3+M4*G4+G5*M5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+M13*G13+G14*M14+M15*G15+G16*M16+G17*M17+M18*G18+G19*M19+G20*M20)/100</f>
-        <v>13733.1</v>
+        <v>14000.1</v>
       </c>
       <c r="N23" s="23">
         <f>(N2*G2+G3*N3+N4*G4+G5*N5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+N13*G13+G14*N14+N15*G15+G16*N16+G17*N17+N18*G18+G19*N19+G20*N20)/100</f>
-        <v>13788.069599999999</v>
+        <v>14050.569599999999</v>
       </c>
       <c r="O23" s="23">
         <f>(O2*G2+G3*O3+O4*G4+G5*O5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+O13*G13+G14*O14+O15*G15+G16*O16+G17*O17+O18*G18+G19*O19+G20*O20)/100</f>
@@ -5101,7 +5056,7 @@
       <c r="BX23" s="13"/>
       <c r="BY23" s="13"/>
       <c r="CB23" s="15">
-        <v>1149.48</v>
+        <v>1414.68</v>
       </c>
     </row>
     <row r="24" spans="1:80" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5180,23 +5135,23 @@
       <c r="BU24" s="14"/>
       <c r="BV24" s="23">
         <f>SUM(BV2:BV20)</f>
-        <v>13102.402800000002</v>
+        <v>14171.0344</v>
       </c>
       <c r="BW24" s="23">
         <f>SUM(BW2:BW20)</f>
-        <v>12602.522800000001</v>
+        <v>13544.4228</v>
       </c>
       <c r="BX24" s="24">
         <f>BW24-BV24</f>
-        <v>-499.88000000000102</v>
+        <v>-626.61160000000018</v>
       </c>
       <c r="BY24" s="13">
         <f>((BW24-BV24)/BV24)*100</f>
-        <v>-3.8151780832138744</v>
+        <v>-4.4217774250833815</v>
       </c>
       <c r="CB24" s="15">
         <f>SUM(CB5:CB23)</f>
-        <v>522.86839999999916</v>
+        <v>788.0683999999992</v>
       </c>
     </row>
     <row r="25" spans="1:80" x14ac:dyDescent="0.25">
@@ -5312,31 +5267,31 @@
       </c>
       <c r="C2" s="18">
         <f>'התיק העדכני'!H2</f>
-        <v>744</v>
+        <v>774.5</v>
       </c>
       <c r="D2" s="19">
         <f>'התיק העדכני'!G2</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E2" s="17">
-        <v>10800</v>
+        <v>770</v>
       </c>
       <c r="F2" s="17">
-        <v>13000</v>
+        <v>980</v>
       </c>
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>799.8</v>
+        <v>844</v>
       </c>
       <c r="J2" s="25"/>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
-        <v>10550</v>
+        <v>742.75</v>
       </c>
       <c r="M2" s="21">
         <f>(F2+CHATGPT!F2+PERPLIXITY!F2+DEEPSEEK!F2)/4</f>
-        <v>12350</v>
+        <v>916</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5350,31 +5305,31 @@
       </c>
       <c r="C3" s="18">
         <f>'התיק העדכני'!H3</f>
-        <v>1153.6300000000001</v>
+        <v>950</v>
       </c>
       <c r="D3" s="19">
         <f>'התיק העדכני'!G3</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E3" s="16">
+        <v>895</v>
+      </c>
+      <c r="F3" s="16">
         <v>950</v>
-      </c>
-      <c r="F3" s="16">
-        <v>1250</v>
       </c>
       <c r="G3" s="17"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>941.8</v>
+        <v>888</v>
       </c>
       <c r="J3" s="26"/>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
-        <v>1098</v>
+        <v>1004.25</v>
       </c>
       <c r="M3" s="21">
         <f>(F3+CHATGPT!F3+PERPLIXITY!F3+DEEPSEEK!F3)/4</f>
-        <v>1368.25</v>
+        <v>1193.25</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5403,16 +5358,16 @@
       <c r="G4" s="17"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>5990</v>
+        <v>6030</v>
       </c>
       <c r="J4" s="26"/>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
-        <v>6030.25</v>
+        <v>5855</v>
       </c>
       <c r="M4" s="21">
         <f>(F4+CHATGPT!F4+PERPLIXITY!F4+DEEPSEEK!F4)/4</f>
-        <v>6975.25</v>
+        <v>7051.25</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5433,23 +5388,23 @@
         <v>158</v>
       </c>
       <c r="E5" s="16">
-        <v>650</v>
+        <v>618</v>
       </c>
       <c r="F5" s="16">
-        <v>850</v>
+        <v>780</v>
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>656.2</v>
+        <v>647</v>
       </c>
       <c r="J5" s="26"/>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
-        <v>607.75</v>
+        <v>593.75</v>
       </c>
       <c r="M5" s="21">
         <f>(F5+CHATGPT!F5+PERPLIXITY!F5+DEEPSEEK!F5)/4</f>
-        <v>768</v>
+        <v>741.25</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5470,23 +5425,23 @@
         <v>25</v>
       </c>
       <c r="E6" s="16">
-        <v>3300</v>
+        <v>4620</v>
       </c>
       <c r="F6" s="16">
-        <v>4200</v>
+        <v>5400</v>
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4880</v>
+        <v>5001</v>
       </c>
       <c r="J6" s="26"/>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
-        <v>3560</v>
+        <v>4409</v>
       </c>
       <c r="M6" s="21">
         <f>(F6+CHATGPT!F6+PERPLIXITY!F6+DEEPSEEK!F6)/4</f>
-        <v>4332.75</v>
+        <v>5478.5</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5515,16 +5470,16 @@
       <c r="G7" s="18"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3996</v>
+        <v>4084</v>
       </c>
       <c r="J7" s="26"/>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
-        <v>3663.25</v>
+        <v>3713.25</v>
       </c>
       <c r="M7" s="21">
         <f>(F7+CHATGPT!F7+PERPLIXITY!F7+DEEPSEEK!F7)/4</f>
-        <v>4213.25</v>
+        <v>4350.75</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5545,23 +5500,23 @@
         <v>2</v>
       </c>
       <c r="E8" s="16">
-        <v>38000</v>
+        <v>43000</v>
       </c>
       <c r="F8" s="16">
-        <v>44000</v>
+        <v>52000</v>
       </c>
       <c r="G8" s="18"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>45300</v>
+        <v>45190</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
-        <v>37884</v>
+        <v>40488.25</v>
       </c>
       <c r="M8" s="21">
         <f>(F8+CHATGPT!F8+PERPLIXITY!F8+DEEPSEEK!F8)/4</f>
-        <v>43218.75</v>
+        <v>47899</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5590,7 +5545,7 @@
       <c r="G9" s="17"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10660</v>
+        <v>10640</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -5627,7 +5582,7 @@
       <c r="G10" s="18"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5027</v>
+        <v>4987</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -5664,15 +5619,15 @@
       <c r="G11" s="18"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1086</v>
+        <v>1066</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
-        <v>940.75</v>
+        <v>980.75</v>
       </c>
       <c r="M11" s="21">
         <f>(F11+CHATGPT!F11+PERPLIXITY!F11+DEEPSEEK!F11)/4</f>
-        <v>1146.25</v>
+        <v>1246.25</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5693,24 +5648,24 @@
         <v>0</v>
       </c>
       <c r="E12" s="16">
-        <v>23800</v>
+        <v>24400</v>
       </c>
       <c r="F12" s="16">
-        <v>28000</v>
+        <v>29500</v>
       </c>
       <c r="G12" s="18"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>29650</v>
+        <v>29670</v>
       </c>
       <c r="J12" s="26"/>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
-        <v>23843.25</v>
+        <v>23993.25</v>
       </c>
       <c r="M12" s="21">
         <f>(F12+CHATGPT!F12+PERPLIXITY!F12+DEEPSEEK!F12)/4</f>
-        <v>28496.25</v>
+        <v>28871.25</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5731,24 +5686,24 @@
         <v>50</v>
       </c>
       <c r="E13" s="16">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="F13" s="16">
-        <v>1200</v>
+        <v>950</v>
       </c>
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>840</v>
+        <v>788.6</v>
       </c>
       <c r="J13" s="26"/>
       <c r="L13" s="21">
         <f>(E13+CHATGPT!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
-        <v>890</v>
+        <v>871.25</v>
       </c>
       <c r="M13" s="21">
         <f>(F13+CHATGPT!F13+PERPLIXITY!F13+DEEPSEEK!F13)/4</f>
-        <v>1125</v>
+        <v>1037.5</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5769,24 +5724,24 @@
         <v>9</v>
       </c>
       <c r="E14" s="16">
-        <v>7600</v>
+        <v>7950</v>
       </c>
       <c r="F14" s="16">
-        <v>8500</v>
+        <v>8800</v>
       </c>
       <c r="G14" s="17"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8100</v>
+        <v>8253</v>
       </c>
       <c r="J14" s="26"/>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
-        <v>7315</v>
+        <v>7564.5</v>
       </c>
       <c r="M14" s="21">
         <f>(F14+CHATGPT!F14+PERPLIXITY!F14+DEEPSEEK!F14)/4</f>
-        <v>8391</v>
+        <v>8702.5</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5815,7 +5770,7 @@
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12994</v>
+        <v>13244</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
@@ -5824,7 +5779,7 @@
       </c>
       <c r="M15" s="21">
         <f>(F15+CHATGPT!F15+PERPLIXITY!F15+DEEPSEEK!F15)/4</f>
-        <v>15132.75</v>
+        <v>15005.5</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5845,7 +5800,7 @@
         <v>500</v>
       </c>
       <c r="E16" s="16">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="F16" s="16">
         <v>250</v>
@@ -5853,16 +5808,16 @@
       <c r="G16" s="17"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216</v>
+        <v>216.71</v>
       </c>
       <c r="J16" s="26"/>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
-        <v>198.5</v>
+        <v>203.5</v>
       </c>
       <c r="M16" s="21">
         <f>(F16+CHATGPT!F16+PERPLIXITY!F16+DEEPSEEK!F16)/4</f>
-        <v>239.75</v>
+        <v>243.25</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5896,11 +5851,11 @@
       <c r="J17" s="26"/>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+DEEPSEEK!E17)/4</f>
-        <v>170</v>
+        <v>170.5</v>
       </c>
       <c r="M17" s="21">
         <f>(F17+CHATGPT!F17+PERPLIXITY!F17+DEEPSEEK!F17)/4</f>
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5929,15 +5884,15 @@
       <c r="G18" s="18"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1864</v>
+        <v>1895</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
-        <v>1608.75</v>
+        <v>1680.75</v>
       </c>
       <c r="M18" s="21">
         <f>(F18+CHATGPT!F18+PERPLIXITY!F18+DEEPSEEK!F18)/4</f>
-        <v>1928.25</v>
+        <v>2053.25</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5957,72 +5912,79 @@
         <f>'התיק העדכני'!G19</f>
         <v>300</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
+      <c r="E19" s="16">
+        <v>65</v>
+      </c>
+      <c r="F19" s="16">
+        <v>110</v>
+      </c>
       <c r="G19" s="18"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>67.900000000000006</v>
+        <v>71</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
-        <v>0</v>
+        <v>64.3</v>
       </c>
       <c r="M19" s="21">
         <f>(F19+CHATGPT!F19+PERPLIXITY!F19+DEEPSEEK!F19)/4</f>
-        <v>0</v>
+        <v>94.25</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B20" s="17" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C20" s="18" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D20" s="19" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
+      <c r="A20" s="17" t="str">
+        <f>'התיק העדכני'!E20</f>
+        <v>אירודרום קבוצה</v>
+      </c>
+      <c r="B20" s="17">
+        <f>'התיק העדכני'!A20</f>
+        <v>363010</v>
+      </c>
+      <c r="C20" s="18">
+        <f>'התיק העדכני'!H20</f>
+        <v>74.900000000000006</v>
+      </c>
+      <c r="D20" s="19">
+        <f>'התיק העדכני'!G20</f>
+        <v>600</v>
+      </c>
+      <c r="E20" s="16">
+        <v>78</v>
+      </c>
+      <c r="F20" s="16">
+        <v>110</v>
+      </c>
       <c r="G20" s="19"/>
-      <c r="I20" s="13" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J20" s="26"/>
+      <c r="I20" s="13">
+        <f>'התיק העדכני'!I20</f>
+        <v>78.400000000000006</v>
+      </c>
       <c r="L20" s="21">
         <f>(E20+CHATGPT!E20+PERPLIXITY!E20+DEEPSEEK!E20)/4</f>
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="M20" s="21">
         <f>(F20+CHATGPT!F20+PERPLIXITY!F20+DEEPSEEK!F20)/4</f>
+        <v>96.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="17">
+        <f>'התיק העדכני'!E21</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B21" s="17" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C21" s="18" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D21" s="19" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
+      <c r="B21" s="17">
+        <f>'התיק העדכני'!A21</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="18">
+        <f>'התיק העדכני'!H21</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="19">
+        <f>'התיק העדכני'!G21</f>
+        <v>0</v>
       </c>
       <c r="E21" s="16"/>
       <c r="F21" s="16"/>
@@ -6042,21 +6004,21 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B22" s="17" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C22" s="18" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D22" s="19" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
+      <c r="A22" s="17">
+        <f>'התיק העדכני'!E22</f>
+        <v>0</v>
+      </c>
+      <c r="B22" s="17">
+        <f>'התיק העדכני'!A22</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="18">
+        <f>'התיק העדכני'!H22</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="19">
+        <f>'התיק העדכני'!G22</f>
+        <v>0</v>
       </c>
       <c r="E22" s="16"/>
       <c r="F22" s="16"/>
@@ -6076,21 +6038,18 @@
       </c>
     </row>
     <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="17" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B23" s="17" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C23" s="18" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D23" s="19" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
+      <c r="A23" s="17"/>
+      <c r="B23" s="17">
+        <f>'התיק העדכני'!A23</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="18">
+        <f>'התיק העדכני'!H23</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="19">
+        <f>'התיק העדכני'!G23</f>
+        <v>0</v>
       </c>
       <c r="E23" s="18"/>
       <c r="F23" s="18"/>
@@ -6110,21 +6069,21 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="17" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B24" s="17" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C24" s="18" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D24" s="19" t="e">
-        <f>'התיק העדכני'!#REF!</f>
-        <v>#REF!</v>
+      <c r="A24" s="17">
+        <f>'התיק העדכני'!E24</f>
+        <v>0</v>
+      </c>
+      <c r="B24" s="17">
+        <f>'התיק העדכני'!A24</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="18">
+        <f>'התיק העדכני'!H24</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="19">
+        <f>'התיק העדכני'!G24</f>
+        <v>0</v>
       </c>
       <c r="E24" s="18"/>
       <c r="F24" s="18"/>
@@ -6256,18 +6215,18 @@
       </c>
       <c r="C28" s="18">
         <f>'התיק העדכני'!H20</f>
-        <v>65</v>
+        <v>74.900000000000006</v>
       </c>
       <c r="D28" s="19">
         <f>'התיק העדכני'!G20</f>
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="19"/>
       <c r="I28" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>82.3</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="J28" s="26"/>
       <c r="L28" s="21">
@@ -6336,30 +6295,30 @@
       </c>
       <c r="C2" s="18">
         <f>'התיק העדכני'!H2</f>
-        <v>744</v>
+        <v>774.5</v>
       </c>
       <c r="D2" s="19">
         <f>'התיק העדכני'!G2</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E2" s="17">
-        <v>10500</v>
+        <v>731</v>
       </c>
       <c r="F2" s="17">
-        <v>12500</v>
+        <v>934</v>
       </c>
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>799.8</v>
+        <v>844</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+GEMINI!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
-        <v>10550</v>
+        <v>742.75</v>
       </c>
       <c r="M2" s="21">
         <f>(F2+GEMINI!F2+PERPLIXITY!F2+DEEPSEEK!F2)/4</f>
-        <v>12350</v>
+        <v>916</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6373,11 +6332,11 @@
       </c>
       <c r="C3" s="18">
         <f>'התיק העדכני'!H3</f>
-        <v>1153.6300000000001</v>
+        <v>950</v>
       </c>
       <c r="D3" s="19">
         <f>'התיק העדכני'!G3</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E3" s="16">
         <v>962</v>
@@ -6388,15 +6347,15 @@
       <c r="G3" s="7"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>941.8</v>
+        <v>888</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
-        <v>1098</v>
+        <v>1004.25</v>
       </c>
       <c r="M3" s="21">
         <f>(F3+GEMINI!F3+PERPLIXITY!F3+DEEPSEEK!F3)/4</f>
-        <v>1368.25</v>
+        <v>1193.25</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6417,23 +6376,23 @@
         <v>20</v>
       </c>
       <c r="E4" s="16">
-        <v>5621</v>
+        <v>5560</v>
       </c>
       <c r="F4" s="16">
-        <v>6701</v>
+        <v>7105</v>
       </c>
       <c r="G4" s="7"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>5990</v>
+        <v>6030</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+GEMINI!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
-        <v>6030.25</v>
+        <v>5855</v>
       </c>
       <c r="M4" s="21">
         <f>(F4+GEMINI!F4+PERPLIXITY!F4+DEEPSEEK!F4)/4</f>
-        <v>6975.25</v>
+        <v>7051.25</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6454,23 +6413,23 @@
         <v>158</v>
       </c>
       <c r="E5" s="16">
-        <v>601</v>
+        <v>572</v>
       </c>
       <c r="F5" s="16">
-        <v>772</v>
+        <v>730</v>
       </c>
       <c r="G5" s="7"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>656.2</v>
+        <v>647</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
-        <v>607.75</v>
+        <v>593.75</v>
       </c>
       <c r="M5" s="21">
         <f>(F5+GEMINI!F5+PERPLIXITY!F5+DEEPSEEK!F5)/4</f>
-        <v>768</v>
+        <v>741.25</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6491,23 +6450,23 @@
         <v>25</v>
       </c>
       <c r="E6" s="16">
-        <v>3340</v>
+        <v>4316</v>
       </c>
       <c r="F6" s="16">
-        <v>4231</v>
+        <v>5514</v>
       </c>
       <c r="G6" s="7"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4880</v>
+        <v>5001</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
-        <v>3560</v>
+        <v>4409</v>
       </c>
       <c r="M6" s="21">
         <f>(F6+GEMINI!F6+PERPLIXITY!F6+DEEPSEEK!F6)/4</f>
-        <v>4332.75</v>
+        <v>5478.5</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6531,20 +6490,20 @@
         <v>3603</v>
       </c>
       <c r="F7" s="16">
-        <v>4253</v>
+        <v>4603</v>
       </c>
       <c r="G7" s="8"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3996</v>
+        <v>4084</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+GEMINI!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
-        <v>3663.25</v>
+        <v>3713.25</v>
       </c>
       <c r="M7" s="21">
         <f>(F7+GEMINI!F7+PERPLIXITY!F7+DEEPSEEK!F7)/4</f>
-        <v>4213.25</v>
+        <v>4350.75</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6565,23 +6524,23 @@
         <v>2</v>
       </c>
       <c r="E8" s="16">
-        <v>36536</v>
+        <v>37953</v>
       </c>
       <c r="F8" s="16">
-        <v>42875</v>
+        <v>48596</v>
       </c>
       <c r="G8" s="8"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>45300</v>
+        <v>45190</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+GEMINI!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
-        <v>37884</v>
+        <v>40488.25</v>
       </c>
       <c r="M8" s="21">
         <f>(F8+GEMINI!F8+PERPLIXITY!F8+DEEPSEEK!F8)/4</f>
-        <v>43218.75</v>
+        <v>47899</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6610,7 +6569,7 @@
       <c r="G9" s="8"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10660</v>
+        <v>10640</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+GEMINI!E9+PERPLIXITY!E9+DEEPSEEK!E9)/4</f>
@@ -6647,7 +6606,7 @@
       <c r="G10" s="8"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5027</v>
+        <v>4987</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+GEMINI!E10+PERPLIXITY!E10+DEEPSEEK!E10)/4</f>
@@ -6676,23 +6635,23 @@
         <v>80</v>
       </c>
       <c r="E11" s="16">
-        <v>863</v>
+        <v>1013</v>
       </c>
       <c r="F11" s="16">
-        <v>1085</v>
+        <v>1295</v>
       </c>
       <c r="G11" s="8"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1086</v>
+        <v>1066</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+GEMINI!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
-        <v>940.75</v>
+        <v>980.75</v>
       </c>
       <c r="M11" s="21">
         <f>(F11+GEMINI!F11+PERPLIXITY!F11+DEEPSEEK!F11)/4</f>
-        <v>1146.25</v>
+        <v>1246.25</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6721,15 +6680,15 @@
       <c r="G12" s="8"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>29650</v>
+        <v>29670</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+GEMINI!E12+PERPLIXITY!E12+DEEPSEEK!E12)/4</f>
-        <v>23843.25</v>
+        <v>23993.25</v>
       </c>
       <c r="M12" s="21">
         <f>(F12+GEMINI!F12+PERPLIXITY!F12+DEEPSEEK!F12)/4</f>
-        <v>28496.25</v>
+        <v>28871.25</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6758,15 +6717,15 @@
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>840</v>
+        <v>788.6</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+GEMINI!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
-        <v>890</v>
+        <v>871.25</v>
       </c>
       <c r="M13" s="21">
         <f>(F13+GEMINI!F13+PERPLIXITY!F13+DEEPSEEK!F13)/4</f>
-        <v>1125</v>
+        <v>1037.5</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6787,23 +6746,23 @@
         <v>9</v>
       </c>
       <c r="E14" s="16">
-        <v>7260</v>
+        <v>7208</v>
       </c>
       <c r="F14" s="16">
-        <v>8564</v>
+        <v>9210</v>
       </c>
       <c r="G14" s="7"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8100</v>
+        <v>8253</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
-        <v>7315</v>
+        <v>7564.5</v>
       </c>
       <c r="M14" s="21">
         <f>(F14+GEMINI!F14+PERPLIXITY!F14+DEEPSEEK!F14)/4</f>
-        <v>8391</v>
+        <v>8702.5</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6827,12 +6786,12 @@
         <v>11369</v>
       </c>
       <c r="F15" s="16">
-        <v>14031</v>
+        <v>14522</v>
       </c>
       <c r="G15" s="7"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12994</v>
+        <v>13244</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+GEMINI!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
@@ -6840,7 +6799,7 @@
       </c>
       <c r="M15" s="21">
         <f>(F15+GEMINI!F15+PERPLIXITY!F15+DEEPSEEK!F15)/4</f>
-        <v>15132.75</v>
+        <v>15005.5</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6861,23 +6820,23 @@
         <v>500</v>
       </c>
       <c r="E16" s="16">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="F16" s="16">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="G16" s="7"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216</v>
+        <v>216.71</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
-        <v>198.5</v>
+        <v>203.5</v>
       </c>
       <c r="M16" s="21">
         <f>(F16+GEMINI!F16+PERPLIXITY!F16+DEEPSEEK!F16)/4</f>
-        <v>239.75</v>
+        <v>243.25</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6898,10 +6857,10 @@
         <v>600</v>
       </c>
       <c r="E17" s="16">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F17" s="16">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G17" s="7"/>
       <c r="I17" s="13">
@@ -6910,11 +6869,11 @@
       </c>
       <c r="L17" s="21">
         <f>(E17+GEMINI!E17+PERPLIXITY!E17+DEEPSEEK!E17)/4</f>
-        <v>170</v>
+        <v>170.5</v>
       </c>
       <c r="M17" s="21">
         <f>(F17+GEMINI!F17+PERPLIXITY!F17+DEEPSEEK!F17)/4</f>
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6935,23 +6894,23 @@
         <v>45</v>
       </c>
       <c r="E18" s="16">
-        <v>1455</v>
+        <v>1693</v>
       </c>
       <c r="F18" s="16">
-        <v>1863</v>
+        <v>2163</v>
       </c>
       <c r="G18" s="8"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1864</v>
+        <v>1895</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+GEMINI!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
-        <v>1608.75</v>
+        <v>1680.75</v>
       </c>
       <c r="M18" s="21">
         <f>(F18+GEMINI!F18+PERPLIXITY!F18+DEEPSEEK!F18)/4</f>
-        <v>1928.25</v>
+        <v>2053.25</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6971,39 +6930,80 @@
         <f>'התיק העדכני'!G19</f>
         <v>300</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
+      <c r="E19" s="16">
+        <v>64.2</v>
+      </c>
+      <c r="F19" s="16">
+        <v>82</v>
+      </c>
       <c r="G19" s="8"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>67.900000000000006</v>
+        <v>71</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+GEMINI!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
-        <v>0</v>
+        <v>64.3</v>
       </c>
       <c r="M19" s="21">
         <f>(F19+GEMINI!F19+PERPLIXITY!F19+DEEPSEEK!F19)/4</f>
+        <v>94.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="17" t="str">
+        <f>'התיק העדכני'!E20</f>
+        <v>אירודרום קבוצה</v>
+      </c>
+      <c r="B20" s="17">
+        <f>'התיק העדכני'!A20</f>
+        <v>363010</v>
+      </c>
+      <c r="C20" s="18">
+        <f>'התיק העדכני'!H20</f>
+        <v>74.900000000000006</v>
+      </c>
+      <c r="D20" s="19">
+        <f>'התיק העדכני'!G20</f>
+        <v>600</v>
+      </c>
+      <c r="E20" s="16">
+        <v>72</v>
+      </c>
+      <c r="F20" s="16">
+        <v>92</v>
+      </c>
+      <c r="G20" s="8"/>
+      <c r="I20" s="13">
+        <f>'התיק העדכני'!I20</f>
+        <v>78.400000000000006</v>
+      </c>
+      <c r="L20" s="21">
+        <f>(E20+GEMINI!E20+PERPLIXITY!E20+DEEPSEEK!E20)/4</f>
+        <v>72.5</v>
+      </c>
+      <c r="M20" s="21">
+        <f>(F20+GEMINI!F20+PERPLIXITY!F20+DEEPSEEK!F20)/4</f>
+        <v>96.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="17">
+        <f>'התיק העדכני'!E21</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="8"/>
-      <c r="I20" s="13"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-    </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
+      <c r="B21" s="17">
+        <f>'התיק העדכני'!A21</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="18">
+        <f>'התיק העדכני'!H21</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="19">
+        <f>'התיק העדכני'!G21</f>
+        <v>0</v>
+      </c>
       <c r="E21" s="16"/>
       <c r="F21" s="16"/>
       <c r="G21" s="8"/>
@@ -7152,30 +7152,30 @@
       </c>
       <c r="C2" s="18">
         <f>'התיק העדכני'!H2</f>
-        <v>744</v>
+        <v>774.5</v>
       </c>
       <c r="D2" s="19">
         <f>'התיק העדכני'!G2</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E2" s="17">
-        <v>10500</v>
+        <v>730</v>
       </c>
       <c r="F2" s="17">
-        <v>12100</v>
-      </c>
-      <c r="G2" s="17"/>
+        <v>930</v>
+      </c>
+      <c r="G2" s="10"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>799.8</v>
+        <v>844</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+GEMINI!E2+DEEPSEEK!E2)/4</f>
-        <v>10550</v>
+        <v>742.75</v>
       </c>
       <c r="M2" s="21">
         <f>(F2+CHATGPT!F2+GEMINI!F2+DEEPSEEK!F2)/4</f>
-        <v>12350</v>
+        <v>916</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7189,30 +7189,30 @@
       </c>
       <c r="C3" s="18">
         <f>'התיק העדכני'!H3</f>
-        <v>1153.6300000000001</v>
+        <v>950</v>
       </c>
       <c r="D3" s="19">
         <f>'התיק העדכני'!G3</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E3" s="16">
-        <v>1200</v>
+        <v>880</v>
       </c>
       <c r="F3" s="16">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="G3" s="10"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>941.8</v>
+        <v>888</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
-        <v>1098</v>
+        <v>1004.25</v>
       </c>
       <c r="M3" s="21">
         <f>(F3+CHATGPT!F3+GEMINI!F3+DEEPSEEK!F3)/4</f>
-        <v>1368.25</v>
+        <v>1193.25</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7233,23 +7233,23 @@
         <v>20</v>
       </c>
       <c r="E4" s="16">
-        <v>6200</v>
+        <v>5560</v>
       </c>
       <c r="F4" s="16">
-        <v>7200</v>
+        <v>7100</v>
       </c>
       <c r="G4" s="10"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>5990</v>
+        <v>6030</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+GEMINI!E4+DEEPSEEK!E4)/4</f>
-        <v>6030.25</v>
+        <v>5855</v>
       </c>
       <c r="M4" s="21">
         <f>(F4+CHATGPT!F4+GEMINI!F4+DEEPSEEK!F4)/4</f>
-        <v>6975.25</v>
+        <v>7051.25</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7270,23 +7270,23 @@
         <v>158</v>
       </c>
       <c r="E5" s="16">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F5" s="16">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="G5" s="10"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>656.2</v>
+        <v>647</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
-        <v>607.75</v>
+        <v>593.75</v>
       </c>
       <c r="M5" s="21">
         <f>(F5+CHATGPT!F5+GEMINI!F5+DEEPSEEK!F5)/4</f>
-        <v>768</v>
+        <v>741.25</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7307,23 +7307,23 @@
         <v>25</v>
       </c>
       <c r="E6" s="16">
-        <v>3600</v>
+        <v>4400</v>
       </c>
       <c r="F6" s="16">
-        <v>4400</v>
+        <v>5500</v>
       </c>
       <c r="G6" s="10"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4880</v>
+        <v>5001</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
-        <v>3560</v>
+        <v>4409</v>
       </c>
       <c r="M6" s="21">
         <f>(F6+CHATGPT!F6+GEMINI!F6+DEEPSEEK!F6)/4</f>
-        <v>4332.75</v>
+        <v>5478.5</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7344,23 +7344,23 @@
         <v>70</v>
       </c>
       <c r="E7" s="16">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="F7" s="16">
-        <v>4200</v>
+        <v>4400</v>
       </c>
       <c r="G7" s="10"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3996</v>
+        <v>4084</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+GEMINI!E7+DEEPSEEK!E7)/4</f>
-        <v>3663.25</v>
+        <v>3713.25</v>
       </c>
       <c r="M7" s="21">
         <f>(F7+CHATGPT!F7+GEMINI!F7+DEEPSEEK!F7)/4</f>
-        <v>4213.25</v>
+        <v>4350.75</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7381,22 +7381,22 @@
         <v>2</v>
       </c>
       <c r="E8" s="16">
-        <v>38000</v>
+        <v>42000</v>
       </c>
       <c r="F8" s="16">
-        <v>43000</v>
+        <v>48000</v>
       </c>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>45300</v>
+        <v>45190</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+GEMINI!E8+DEEPSEEK!E8)/4</f>
-        <v>37884</v>
+        <v>40488.25</v>
       </c>
       <c r="M8" s="21">
         <f>(F8+CHATGPT!F8+GEMINI!F8+DEEPSEEK!F8)/4</f>
-        <v>43218.75</v>
+        <v>47899</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10660</v>
+        <v>10640</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+GEMINI!E9+DEEPSEEK!E9)/4</f>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5027</v>
+        <v>4987</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+GEMINI!E10+DEEPSEEK!E10)/4</f>
@@ -7489,22 +7489,22 @@
         <v>80</v>
       </c>
       <c r="E11" s="16">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="F11" s="16">
-        <v>1200</v>
+        <v>1290</v>
       </c>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1086</v>
+        <v>1066</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+GEMINI!E11+DEEPSEEK!E11)/4</f>
-        <v>940.75</v>
+        <v>980.75</v>
       </c>
       <c r="M11" s="21">
         <f>(F11+CHATGPT!F11+GEMINI!F11+DEEPSEEK!F11)/4</f>
-        <v>1146.25</v>
+        <v>1246.25</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7533,15 +7533,15 @@
       <c r="G12" s="10"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>29650</v>
+        <v>29670</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+GEMINI!E12+DEEPSEEK!E12)/4</f>
-        <v>23843.25</v>
+        <v>23993.25</v>
       </c>
       <c r="M12" s="21">
         <f>(F12+CHATGPT!F12+GEMINI!F12+DEEPSEEK!F12)/4</f>
-        <v>28496.25</v>
+        <v>28871.25</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7562,23 +7562,23 @@
         <v>50</v>
       </c>
       <c r="E13" s="16">
-        <v>880</v>
+        <v>800</v>
       </c>
       <c r="F13" s="16">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>840</v>
+        <v>788.6</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+CHATGPT!E13+GEMINI!E13+DEEPSEEK!E13)/4</f>
-        <v>890</v>
+        <v>871.25</v>
       </c>
       <c r="M13" s="21">
         <f>(F13+CHATGPT!F13+GEMINI!F13+DEEPSEEK!F13)/4</f>
-        <v>1125</v>
+        <v>1037.5</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7599,23 +7599,23 @@
         <v>9</v>
       </c>
       <c r="E14" s="16">
-        <v>7000</v>
+        <v>7700</v>
       </c>
       <c r="F14" s="16">
-        <v>8300</v>
+        <v>8600</v>
       </c>
       <c r="G14" s="10"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8100</v>
+        <v>8253</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
-        <v>7315</v>
+        <v>7564.5</v>
       </c>
       <c r="M14" s="21">
         <f>(F14+CHATGPT!F14+GEMINI!F14+DEEPSEEK!F14)/4</f>
-        <v>8391</v>
+        <v>8702.5</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7639,12 +7639,12 @@
         <v>12500</v>
       </c>
       <c r="F15" s="16">
-        <v>16000</v>
+        <v>15000</v>
       </c>
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12994</v>
+        <v>13244</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
@@ -7652,7 +7652,7 @@
       </c>
       <c r="M15" s="21">
         <f>(F15+CHATGPT!F15+GEMINI!F15+DEEPSEEK!F15)/4</f>
-        <v>15132.75</v>
+        <v>15005.5</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7673,7 +7673,7 @@
         <v>500</v>
       </c>
       <c r="E16" s="16">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F16" s="16">
         <v>240</v>
@@ -7681,15 +7681,15 @@
       <c r="G16" s="10"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216</v>
+        <v>216.71</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+GEMINI!E16+DEEPSEEK!E16)/4</f>
-        <v>198.5</v>
+        <v>203.5</v>
       </c>
       <c r="M16" s="21">
         <f>(F16+CHATGPT!F16+GEMINI!F16+DEEPSEEK!F16)/4</f>
-        <v>239.75</v>
+        <v>243.25</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7722,11 +7722,11 @@
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+GEMINI!E17+DEEPSEEK!E17)/4</f>
-        <v>170</v>
+        <v>170.5</v>
       </c>
       <c r="M17" s="21">
         <f>(F17+CHATGPT!F17+GEMINI!F17+DEEPSEEK!F17)/4</f>
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7747,22 +7747,22 @@
         <v>45</v>
       </c>
       <c r="E18" s="16">
-        <v>1650</v>
+        <v>1700</v>
       </c>
       <c r="F18" s="16">
-        <v>1900</v>
+        <v>2100</v>
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1864</v>
+        <v>1895</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
-        <v>1608.75</v>
+        <v>1680.75</v>
       </c>
       <c r="M18" s="21">
         <f>(F18+CHATGPT!F18+GEMINI!F18+DEEPSEEK!F18)/4</f>
-        <v>1928.25</v>
+        <v>2053.25</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7782,38 +7782,79 @@
         <f>'התיק העדכני'!G19</f>
         <v>300</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
+      <c r="E19" s="16">
+        <v>63</v>
+      </c>
+      <c r="F19" s="16">
+        <v>95</v>
+      </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>67.900000000000006</v>
+        <v>71</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+GEMINI!E19+DEEPSEEK!E19)/4</f>
-        <v>0</v>
+        <v>64.3</v>
       </c>
       <c r="M19" s="21">
         <f>(F19+CHATGPT!F19+GEMINI!F19+DEEPSEEK!F19)/4</f>
+        <v>94.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="17" t="str">
+        <f>'התיק העדכני'!E20</f>
+        <v>אירודרום קבוצה</v>
+      </c>
+      <c r="B20" s="17">
+        <f>'התיק העדכני'!A20</f>
+        <v>363010</v>
+      </c>
+      <c r="C20" s="18">
+        <f>'התיק העדכני'!H20</f>
+        <v>74.900000000000006</v>
+      </c>
+      <c r="D20" s="19">
+        <f>'התיק העדכני'!G20</f>
+        <v>600</v>
+      </c>
+      <c r="E20" s="16">
+        <v>72</v>
+      </c>
+      <c r="F20" s="16">
+        <v>95</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="I20" s="13">
+        <f>'התיק העדכני'!I20</f>
+        <v>78.400000000000006</v>
+      </c>
+      <c r="L20" s="21">
+        <f>(E20+CHATGPT!E20+GEMINI!E20+DEEPSEEK!E20)/4</f>
+        <v>72.5</v>
+      </c>
+      <c r="M20" s="21">
+        <f>(F20+CHATGPT!F20+GEMINI!F20+DEEPSEEK!F20)/4</f>
+        <v>96.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="17">
+        <f>'התיק העדכני'!E21</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="10"/>
-      <c r="I20" s="13"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-    </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
+      <c r="B21" s="17">
+        <f>'התיק העדכני'!A21</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="18">
+        <f>'התיק העדכני'!H21</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="19">
+        <f>'התיק העדכני'!G21</f>
+        <v>0</v>
+      </c>
       <c r="E21" s="16"/>
       <c r="F21" s="16"/>
       <c r="G21" s="10"/>
@@ -7951,7 +7992,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אייראנג'י טק</v>
@@ -7962,30 +8003,30 @@
       </c>
       <c r="C2" s="18">
         <f>'התיק העדכני'!H2</f>
-        <v>744</v>
+        <v>774.5</v>
       </c>
       <c r="D2" s="19">
         <f>'התיק העדכני'!G2</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E2" s="17">
-        <v>10400</v>
+        <v>740</v>
       </c>
       <c r="F2" s="17">
-        <v>11800</v>
-      </c>
-      <c r="G2" s="17"/>
+        <v>820</v>
+      </c>
+      <c r="G2" s="31"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>799.8</v>
+        <v>844</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+PERPLIXITY!E2+GEMINI!E2)/4</f>
-        <v>10550</v>
+        <v>742.75</v>
       </c>
       <c r="M2" s="21">
         <f>(F2+CHATGPT!F2+PERPLIXITY!F2+GEMINI!F2)/4</f>
-        <v>12350</v>
+        <v>916</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -7999,11 +8040,11 @@
       </c>
       <c r="C3" s="18">
         <f>'התיק העדכני'!H3</f>
-        <v>1153.6300000000001</v>
+        <v>950</v>
       </c>
       <c r="D3" s="19">
         <f>'התיק העדכני'!G3</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E3" s="16">
         <v>1280</v>
@@ -8014,15 +8055,15 @@
       <c r="G3" s="31"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>941.8</v>
+        <v>888</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
-        <v>1098</v>
+        <v>1004.25</v>
       </c>
       <c r="M3" s="21">
         <f>(F3+CHATGPT!F3+PERPLIXITY!F3+GEMINI!F3)/4</f>
-        <v>1368.25</v>
+        <v>1193.25</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8050,15 +8091,15 @@
       </c>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>5990</v>
+        <v>6030</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+GEMINI!E4)/4</f>
-        <v>6030.25</v>
+        <v>5855</v>
       </c>
       <c r="M4" s="21">
         <f>(F4+CHATGPT!F4+PERPLIXITY!F4+GEMINI!F4)/4</f>
-        <v>6975.25</v>
+        <v>7051.25</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8087,15 +8128,15 @@
       <c r="G5" s="31"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>656.2</v>
+        <v>647</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
-        <v>607.75</v>
+        <v>593.75</v>
       </c>
       <c r="M5" s="21">
         <f>(F5+CHATGPT!F5+PERPLIXITY!F5+GEMINI!F5)/4</f>
-        <v>768</v>
+        <v>741.25</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8116,23 +8157,23 @@
         <v>25</v>
       </c>
       <c r="E6" s="16">
-        <v>4000</v>
+        <v>4300</v>
       </c>
       <c r="F6" s="16">
-        <v>4500</v>
+        <v>5500</v>
       </c>
       <c r="G6" s="31"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>4880</v>
+        <v>5001</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
-        <v>3560</v>
+        <v>4409</v>
       </c>
       <c r="M6" s="21">
         <f>(F6+CHATGPT!F6+PERPLIXITY!F6+GEMINI!F6)/4</f>
-        <v>4332.75</v>
+        <v>5478.5</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8160,15 +8201,15 @@
       </c>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>3996</v>
+        <v>4084</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+GEMINI!E7)/4</f>
-        <v>3663.25</v>
+        <v>3713.25</v>
       </c>
       <c r="M7" s="21">
         <f>(F7+CHATGPT!F7+PERPLIXITY!F7+GEMINI!F7)/4</f>
-        <v>4213.25</v>
+        <v>4350.75</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8197,15 +8238,15 @@
       <c r="G8" s="31"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>45300</v>
+        <v>45190</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+GEMINI!E8)/4</f>
-        <v>37884</v>
+        <v>40488.25</v>
       </c>
       <c r="M8" s="21">
         <f>(F8+CHATGPT!F8+PERPLIXITY!F8+GEMINI!F8)/4</f>
-        <v>43218.75</v>
+        <v>47899</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8234,7 +8275,7 @@
       <c r="G9" s="31"/>
       <c r="I9" s="13">
         <f>'התיק העדכני'!I9</f>
-        <v>10660</v>
+        <v>10640</v>
       </c>
       <c r="L9" s="21">
         <f>(E9+CHATGPT!E9+PERPLIXITY!E9+GEMINI!E9)/4</f>
@@ -8271,7 +8312,7 @@
       <c r="G10" s="31"/>
       <c r="I10" s="13">
         <f>'התיק העדכני'!I10</f>
-        <v>5027</v>
+        <v>4987</v>
       </c>
       <c r="L10" s="21">
         <f>(E10+CHATGPT!E10+PERPLIXITY!E10+GEMINI!E10)/4</f>
@@ -8300,23 +8341,23 @@
         <v>80</v>
       </c>
       <c r="E11" s="16">
-        <v>1040</v>
+        <v>1000</v>
       </c>
       <c r="F11" s="16">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="G11" s="31"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1086</v>
+        <v>1066</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+GEMINI!E11)/4</f>
-        <v>940.75</v>
+        <v>980.75</v>
       </c>
       <c r="M11" s="21">
         <f>(F11+CHATGPT!F11+PERPLIXITY!F11+GEMINI!F11)/4</f>
-        <v>1146.25</v>
+        <v>1246.25</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8345,15 +8386,15 @@
       <c r="G12" s="31"/>
       <c r="I12" s="13">
         <f>'התיק העדכני'!I12</f>
-        <v>29650</v>
+        <v>29670</v>
       </c>
       <c r="L12" s="21">
         <f>(E12+CHATGPT!E12+PERPLIXITY!E12+GEMINI!E12)/4</f>
-        <v>23843.25</v>
+        <v>23993.25</v>
       </c>
       <c r="M12" s="21">
         <f>(F12+CHATGPT!F12+PERPLIXITY!F12+GEMINI!F12)/4</f>
-        <v>28496.25</v>
+        <v>28871.25</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8382,7 +8423,7 @@
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>840</v>
+        <v>788.6</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
@@ -8413,15 +8454,15 @@
       <c r="G14" s="31"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8100</v>
+        <v>8253</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
-        <v>7315</v>
+        <v>7564.5</v>
       </c>
       <c r="M14" s="21">
         <f>(F14+CHATGPT!F14+PERPLIXITY!F14+GEMINI!F14)/4</f>
-        <v>8391</v>
+        <v>8702.5</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8449,7 +8490,7 @@
       </c>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>82.3</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+PERPLIXITY!E15+GEMINI!E15)/4</f>
@@ -8457,7 +8498,7 @@
       </c>
       <c r="M15" s="21">
         <f>(F15+CHATGPT!F15+PERPLIXITY!F15+GEMINI!F15)/4</f>
-        <v>15132.75</v>
+        <v>15005.5</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8485,15 +8526,15 @@
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>12994</v>
+        <v>13244</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
-        <v>198.5</v>
+        <v>203.5</v>
       </c>
       <c r="M16" s="21">
         <f>(F16+CHATGPT!F16+PERPLIXITY!F16+GEMINI!F16)/4</f>
-        <v>239.75</v>
+        <v>243.25</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8522,15 +8563,15 @@
       <c r="G17" s="31"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216</v>
+        <v>216.71</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+GEMINI!E17)/4</f>
-        <v>170</v>
+        <v>170.5</v>
       </c>
       <c r="M17" s="21">
         <f>(F17+CHATGPT!F17+PERPLIXITY!F17+GEMINI!F17)/4</f>
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8563,11 +8604,11 @@
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+GEMINI!E18)/4</f>
-        <v>1608.75</v>
+        <v>1680.75</v>
       </c>
       <c r="M18" s="21">
         <f>(F18+CHATGPT!F18+PERPLIXITY!F18+GEMINI!F18)/4</f>
-        <v>1928.25</v>
+        <v>2053.25</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8587,41 +8628,93 @@
         <f>'התיק העדכני'!G19</f>
         <v>300</v>
       </c>
+      <c r="E19" s="16">
+        <v>65</v>
+      </c>
+      <c r="F19" s="16">
+        <v>90</v>
+      </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1864</v>
+        <v>1895</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+GEMINI!E19)/4</f>
-        <v>0</v>
+        <v>64.3</v>
       </c>
       <c r="M19" s="21">
         <f>(F19+CHATGPT!F19+PERPLIXITY!F19+GEMINI!F19)/4</f>
+        <v>94.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="17" t="str">
+        <f>'התיק העדכני'!E20</f>
+        <v>אירודרום קבוצה</v>
+      </c>
+      <c r="B20" s="17">
+        <f>'התיק העדכני'!A20</f>
+        <v>363010</v>
+      </c>
+      <c r="C20" s="18">
+        <f>'התיק העדכני'!H20</f>
+        <v>74.900000000000006</v>
+      </c>
+      <c r="D20" s="19">
+        <f>'התיק העדכני'!G20</f>
+        <v>600</v>
+      </c>
+      <c r="E20" s="16">
+        <v>68</v>
+      </c>
+      <c r="F20" s="16">
+        <v>90</v>
+      </c>
+      <c r="I20" s="13">
+        <f>'התיק העדכני'!I19</f>
+        <v>71</v>
+      </c>
+      <c r="L20" s="21">
+        <f>(E20+CHATGPT!E20+PERPLIXITY!E20+GEMINI!E20)/4</f>
+        <v>72.5</v>
+      </c>
+      <c r="M20" s="21">
+        <f>(F20+CHATGPT!F20+PERPLIXITY!F20+GEMINI!F20)/4</f>
+        <v>96.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="17">
+        <f>'התיק העדכני'!E21</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="I20" s="13"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-    </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
+      <c r="B21" s="17">
+        <f>'התיק העדכני'!A21</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="18">
+        <f>'התיק העדכני'!H21</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="19">
+        <f>'התיק העדכני'!G21</f>
+        <v>0</v>
+      </c>
       <c r="E21" s="16"/>
       <c r="F21" s="16"/>
       <c r="G21" s="31"/>
-      <c r="I21" s="13"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
+      <c r="I21" s="13">
+        <f>'התיק העדכני'!I20</f>
+        <v>78.400000000000006</v>
+      </c>
+      <c r="L21" s="21">
+        <f>(E21+CHATGPT!E21+PERPLIXITY!E21+GEMINI!E21)/4</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="21">
+        <f>(F21+CHATGPT!F21+PERPLIXITY!F21+GEMINI!F21)/4</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="17"/>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\BURSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBB11F7-40EA-423C-BB3D-0E2A60544D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4181241-0E48-4B5D-963A-71CF514C7A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
   <sheets>
     <sheet name="התיק העדכני" sheetId="1" r:id="rId1"/>
@@ -1423,7 +1423,7 @@
         <v>774.5</v>
       </c>
       <c r="I2" s="13">
-        <v>844</v>
+        <v>857.5</v>
       </c>
       <c r="J2" s="13">
         <v>799.8</v>
@@ -1512,11 +1512,11 @@
       </c>
       <c r="B3" s="17">
         <f>GEMINI!L3</f>
-        <v>1004.25</v>
+        <v>983.75</v>
       </c>
       <c r="C3" s="17">
         <f>GEMINI!M3</f>
-        <v>1193.25</v>
+        <v>1151.25</v>
       </c>
       <c r="D3" s="6" t="str">
         <f>IF(I3&lt;GEMINI!L3,"למכור בהפסד",IF(I3&gt;GEMINI!M3,"למכור ברווח","לשמור"))</f>
@@ -1535,7 +1535,7 @@
         <v>950</v>
       </c>
       <c r="I3" s="13">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="J3" s="13"/>
       <c r="K3" s="13"/>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="C4" s="17">
         <f>GEMINI!M4</f>
-        <v>7051.25</v>
+        <v>7050</v>
       </c>
       <c r="D4" s="6" t="str">
         <f>IF(I4&lt;GEMINI!L4,"למכור בהפסד",IF(I4&gt;GEMINI!M4,"למכור ברווח","לשמור"))</f>
@@ -1651,7 +1651,7 @@
         <v>5925</v>
       </c>
       <c r="I4" s="13">
-        <v>6030</v>
+        <v>6032</v>
       </c>
       <c r="J4" s="13">
         <v>5990</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B5" s="17">
         <f>GEMINI!L5</f>
-        <v>593.75</v>
+        <v>598.25</v>
       </c>
       <c r="C5" s="17">
         <f>GEMINI!M5</f>
@@ -1809,7 +1809,7 @@
         <v>617.53</v>
       </c>
       <c r="I5" s="13">
-        <v>647</v>
+        <v>649.6</v>
       </c>
       <c r="J5" s="13">
         <v>656.2</v>
@@ -1955,11 +1955,11 @@
       </c>
       <c r="B6" s="17">
         <f>GEMINI!L6</f>
-        <v>4409</v>
+        <v>4425</v>
       </c>
       <c r="C6" s="17">
         <f>GEMINI!M6</f>
-        <v>5478.5</v>
+        <v>5480</v>
       </c>
       <c r="D6" s="6" t="str">
         <f>IF(I6&lt;GEMINI!L6,"למכור בהפסד",IF(I6&gt;GEMINI!M6,"למכור ברווח","לשמור"))</f>
@@ -1978,7 +1978,7 @@
         <v>4040</v>
       </c>
       <c r="I6" s="13">
-        <v>5001</v>
+        <v>5041</v>
       </c>
       <c r="J6" s="13">
         <v>4880</v>
@@ -2120,11 +2120,11 @@
       </c>
       <c r="B7" s="17">
         <f>GEMINI!L7</f>
-        <v>3713.25</v>
+        <v>3737.5</v>
       </c>
       <c r="C7" s="17">
         <f>GEMINI!M7</f>
-        <v>4350.75</v>
+        <v>4350</v>
       </c>
       <c r="D7" s="6" t="str">
         <f>IF(I7&lt;GEMINI!L7,"למכור בהפסד",IF(I7&gt;GEMINI!M7,"למכור ברווח","לשמור"))</f>
@@ -2143,7 +2143,7 @@
         <v>3585</v>
       </c>
       <c r="I7" s="13">
-        <v>4084</v>
+        <v>4085</v>
       </c>
       <c r="J7" s="13">
         <v>3996</v>
@@ -2289,11 +2289,11 @@
       </c>
       <c r="B8" s="17">
         <f>GEMINI!L8</f>
-        <v>40488.25</v>
+        <v>41525</v>
       </c>
       <c r="C8" s="17">
         <f>GEMINI!M8</f>
-        <v>47899</v>
+        <v>48125</v>
       </c>
       <c r="D8" s="6" t="str">
         <f>IF(I8&lt;GEMINI!L8,"למכור בהפסד",IF(I8&gt;GEMINI!M8,"למכור ברווח","לשמור"))</f>
@@ -2312,7 +2312,7 @@
         <v>37875</v>
       </c>
       <c r="I8" s="13">
-        <v>45190</v>
+        <v>43310</v>
       </c>
       <c r="J8" s="13">
         <v>45300</v>
@@ -2931,11 +2931,11 @@
       </c>
       <c r="B11" s="17">
         <f>GEMINI!L11</f>
-        <v>980.75</v>
+        <v>981.25</v>
       </c>
       <c r="C11" s="17">
         <f>GEMINI!M11</f>
-        <v>1246.25</v>
+        <v>1245</v>
       </c>
       <c r="D11" s="6" t="str">
         <f>IF(I11&lt;GEMINI!L11,"למכור בהפסד",IF(I11&gt;GEMINI!M11,"למכור ברווח","לשמור"))</f>
@@ -2954,7 +2954,7 @@
         <v>901.87</v>
       </c>
       <c r="I11" s="13">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="J11" s="13">
         <v>1086</v>
@@ -3280,11 +3280,11 @@
       </c>
       <c r="B13" s="17">
         <f>GEMINI!L13</f>
-        <v>871.25</v>
+        <v>842.5</v>
       </c>
       <c r="C13" s="17">
         <f>GEMINI!M13</f>
-        <v>1037.5</v>
+        <v>1002.5</v>
       </c>
       <c r="D13" s="6" t="str">
         <f>IF(I13&lt;GEMINI!L13,"למכור בהפסד",IF(I13&gt;GEMINI!M13,"למכור ברווח","לשמור"))</f>
@@ -3303,7 +3303,7 @@
         <v>840</v>
       </c>
       <c r="I13" s="13">
-        <v>788.6</v>
+        <v>788.2</v>
       </c>
       <c r="J13" s="13">
         <v>840</v>
@@ -3421,11 +3421,11 @@
       </c>
       <c r="B14" s="17">
         <f>GEMINI!L14</f>
-        <v>7564.5</v>
+        <v>7632.5</v>
       </c>
       <c r="C14" s="17">
         <f>GEMINI!M14</f>
-        <v>8702.5</v>
+        <v>8700</v>
       </c>
       <c r="D14" s="6" t="str">
         <f>IF(I14&lt;GEMINI!L14,"למכור בהפסד",IF(I14&gt;GEMINI!M14,"למכור ברווח","לשמור"))</f>
@@ -3444,7 +3444,7 @@
         <v>7204.22</v>
       </c>
       <c r="I14" s="13">
-        <v>8253</v>
+        <v>8274</v>
       </c>
       <c r="J14" s="13">
         <v>8100</v>
@@ -3665,11 +3665,11 @@
       </c>
       <c r="B15" s="17">
         <f>GEMINI!L15</f>
-        <v>12492.25</v>
+        <v>12742.5</v>
       </c>
       <c r="C15" s="17">
         <f>GEMINI!M15</f>
-        <v>15005.5</v>
+        <v>15095</v>
       </c>
       <c r="D15" s="6" t="str">
         <f>IF(I15&lt;GEMINI!L15,"למכור בהפסד",IF(I15&gt;GEMINI!M15,"למכור ברווח","לשמור"))</f>
@@ -3688,7 +3688,7 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
-        <v>13244</v>
+        <v>13033</v>
       </c>
       <c r="J15" s="13">
         <v>13244</v>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="B16" s="17">
         <f>GEMINI!L16</f>
-        <v>203.5</v>
+        <v>203.75</v>
       </c>
       <c r="C16" s="17">
         <f>GEMINI!M16</f>
@@ -4276,7 +4276,7 @@
         <v>1434</v>
       </c>
       <c r="I18" s="13">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="J18" s="13">
         <v>1864</v>
@@ -4451,11 +4451,11 @@
       </c>
       <c r="B19" s="17">
         <f>GEMINI!L19</f>
-        <v>64.3</v>
+        <v>63.5</v>
       </c>
       <c r="C19" s="17">
         <f>GEMINI!M19</f>
-        <v>94.25</v>
+        <v>93.25</v>
       </c>
       <c r="D19" s="6" t="str">
         <f>IF(I19&lt;GEMINI!L19,"למכור בהפסד",IF(I19&gt;GEMINI!M19,"למכור ברווח","לשמור"))</f>
@@ -4474,7 +4474,7 @@
         <v>93.13</v>
       </c>
       <c r="I19" s="13">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J19" s="13">
         <v>67.900000000000006</v>
@@ -4611,7 +4611,7 @@
         <v>74.900000000000006</v>
       </c>
       <c r="I20" s="13">
-        <v>78.400000000000006</v>
+        <v>77.2</v>
       </c>
       <c r="J20" s="13">
         <v>82.3</v>
@@ -4793,7 +4793,7 @@
       <c r="H23" s="13"/>
       <c r="I23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19+G20*I20)/100</f>
-        <v>15109.6</v>
+        <v>15091.768</v>
       </c>
       <c r="J23" s="23">
         <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19+G20*J20)/100</f>
@@ -5282,7 +5282,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>844</v>
+        <v>857.5</v>
       </c>
       <c r="J2" s="25"/>
       <c r="L2" s="21">
@@ -5320,16 +5320,16 @@
       <c r="G3" s="17"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="J3" s="26"/>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
-        <v>1004.25</v>
+        <v>983.75</v>
       </c>
       <c r="M3" s="21">
         <f>(F3+CHATGPT!F3+PERPLIXITY!F3+DEEPSEEK!F3)/4</f>
-        <v>1193.25</v>
+        <v>1151.25</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5358,7 +5358,7 @@
       <c r="G4" s="17"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6030</v>
+        <v>6032</v>
       </c>
       <c r="J4" s="26"/>
       <c r="L4" s="21">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="M4" s="21">
         <f>(F4+CHATGPT!F4+PERPLIXITY!F4+DEEPSEEK!F4)/4</f>
-        <v>7051.25</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>647</v>
+        <v>649.6</v>
       </c>
       <c r="J5" s="26"/>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
-        <v>593.75</v>
+        <v>598.25</v>
       </c>
       <c r="M5" s="21">
         <f>(F5+CHATGPT!F5+PERPLIXITY!F5+DEEPSEEK!F5)/4</f>
@@ -5432,16 +5432,16 @@
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>5001</v>
+        <v>5041</v>
       </c>
       <c r="J6" s="26"/>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
-        <v>4409</v>
+        <v>4425</v>
       </c>
       <c r="M6" s="21">
         <f>(F6+CHATGPT!F6+PERPLIXITY!F6+DEEPSEEK!F6)/4</f>
-        <v>5478.5</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5470,16 +5470,16 @@
       <c r="G7" s="18"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>4084</v>
+        <v>4085</v>
       </c>
       <c r="J7" s="26"/>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
-        <v>3713.25</v>
+        <v>3737.5</v>
       </c>
       <c r="M7" s="21">
         <f>(F7+CHATGPT!F7+PERPLIXITY!F7+DEEPSEEK!F7)/4</f>
-        <v>4350.75</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5508,15 +5508,15 @@
       <c r="G8" s="18"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>45190</v>
+        <v>43310</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
-        <v>40488.25</v>
+        <v>41525</v>
       </c>
       <c r="M8" s="21">
         <f>(F8+CHATGPT!F8+PERPLIXITY!F8+DEEPSEEK!F8)/4</f>
-        <v>47899</v>
+        <v>48125</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5619,15 +5619,15 @@
       <c r="G11" s="18"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
-        <v>980.75</v>
+        <v>981.25</v>
       </c>
       <c r="M11" s="21">
         <f>(F11+CHATGPT!F11+PERPLIXITY!F11+DEEPSEEK!F11)/4</f>
-        <v>1246.25</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5694,16 +5694,16 @@
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>788.6</v>
+        <v>788.2</v>
       </c>
       <c r="J13" s="26"/>
       <c r="L13" s="21">
         <f>(E13+CHATGPT!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
-        <v>871.25</v>
+        <v>842.5</v>
       </c>
       <c r="M13" s="21">
         <f>(F13+CHATGPT!F13+PERPLIXITY!F13+DEEPSEEK!F13)/4</f>
-        <v>1037.5</v>
+        <v>1002.5</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5732,16 +5732,16 @@
       <c r="G14" s="17"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8253</v>
+        <v>8274</v>
       </c>
       <c r="J14" s="26"/>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
-        <v>7564.5</v>
+        <v>7632.5</v>
       </c>
       <c r="M14" s="21">
         <f>(F14+CHATGPT!F14+PERPLIXITY!F14+DEEPSEEK!F14)/4</f>
-        <v>8702.5</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5770,16 +5770,16 @@
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>13244</v>
+        <v>13033</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
-        <v>12492.25</v>
+        <v>12742.5</v>
       </c>
       <c r="M15" s="21">
         <f>(F15+CHATGPT!F15+PERPLIXITY!F15+DEEPSEEK!F15)/4</f>
-        <v>15005.5</v>
+        <v>15095</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5813,7 +5813,7 @@
       <c r="J16" s="26"/>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
-        <v>203.5</v>
+        <v>203.75</v>
       </c>
       <c r="M16" s="21">
         <f>(F16+CHATGPT!F16+PERPLIXITY!F16+DEEPSEEK!F16)/4</f>
@@ -5884,7 +5884,7 @@
       <c r="G18" s="18"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -5921,15 +5921,15 @@
       <c r="G19" s="18"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
-        <v>64.3</v>
+        <v>63.5</v>
       </c>
       <c r="M19" s="21">
         <f>(F19+CHATGPT!F19+PERPLIXITY!F19+DEEPSEEK!F19)/4</f>
-        <v>94.25</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5958,7 +5958,7 @@
       <c r="G20" s="19"/>
       <c r="I20" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>78.400000000000006</v>
+        <v>77.2</v>
       </c>
       <c r="L20" s="21">
         <f>(E20+CHATGPT!E20+PERPLIXITY!E20+DEEPSEEK!E20)/4</f>
@@ -6226,7 +6226,7 @@
       <c r="G28" s="19"/>
       <c r="I28" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>78.400000000000006</v>
+        <v>77.2</v>
       </c>
       <c r="J28" s="26"/>
       <c r="L28" s="21">
@@ -6310,7 +6310,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>844</v>
+        <v>857.5</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+GEMINI!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
@@ -6339,23 +6339,23 @@
         <v>30</v>
       </c>
       <c r="E3" s="16">
-        <v>962</v>
+        <v>880</v>
       </c>
       <c r="F3" s="16">
-        <v>1273</v>
+        <v>1105</v>
       </c>
       <c r="G3" s="7"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
-        <v>1004.25</v>
+        <v>983.75</v>
       </c>
       <c r="M3" s="21">
         <f>(F3+GEMINI!F3+PERPLIXITY!F3+DEEPSEEK!F3)/4</f>
-        <v>1193.25</v>
+        <v>1151.25</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6379,12 +6379,12 @@
         <v>5560</v>
       </c>
       <c r="F4" s="16">
-        <v>7105</v>
+        <v>7100</v>
       </c>
       <c r="G4" s="7"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6030</v>
+        <v>6032</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+GEMINI!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
@@ -6392,7 +6392,7 @@
       </c>
       <c r="M4" s="21">
         <f>(F4+GEMINI!F4+PERPLIXITY!F4+DEEPSEEK!F4)/4</f>
-        <v>7051.25</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6413,7 +6413,7 @@
         <v>158</v>
       </c>
       <c r="E5" s="16">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="F5" s="16">
         <v>730</v>
@@ -6421,11 +6421,11 @@
       <c r="G5" s="7"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>647</v>
+        <v>649.6</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
-        <v>593.75</v>
+        <v>598.25</v>
       </c>
       <c r="M5" s="21">
         <f>(F5+GEMINI!F5+PERPLIXITY!F5+DEEPSEEK!F5)/4</f>
@@ -6450,23 +6450,23 @@
         <v>25</v>
       </c>
       <c r="E6" s="16">
-        <v>4316</v>
+        <v>4380</v>
       </c>
       <c r="F6" s="16">
-        <v>5514</v>
+        <v>5520</v>
       </c>
       <c r="G6" s="7"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>5001</v>
+        <v>5041</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
-        <v>4409</v>
+        <v>4425</v>
       </c>
       <c r="M6" s="21">
         <f>(F6+GEMINI!F6+PERPLIXITY!F6+DEEPSEEK!F6)/4</f>
-        <v>5478.5</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6487,23 +6487,23 @@
         <v>70</v>
       </c>
       <c r="E7" s="16">
-        <v>3603</v>
+        <v>3700</v>
       </c>
       <c r="F7" s="16">
-        <v>4603</v>
+        <v>4600</v>
       </c>
       <c r="G7" s="8"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>4084</v>
+        <v>4085</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+GEMINI!E7+PERPLIXITY!E7+DEEPSEEK!E7)/4</f>
-        <v>3713.25</v>
+        <v>3737.5</v>
       </c>
       <c r="M7" s="21">
         <f>(F7+GEMINI!F7+PERPLIXITY!F7+DEEPSEEK!F7)/4</f>
-        <v>4350.75</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6524,23 +6524,23 @@
         <v>2</v>
       </c>
       <c r="E8" s="16">
-        <v>37953</v>
+        <v>42100</v>
       </c>
       <c r="F8" s="16">
-        <v>48596</v>
+        <v>49500</v>
       </c>
       <c r="G8" s="8"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>45190</v>
+        <v>43310</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+GEMINI!E8+PERPLIXITY!E8+DEEPSEEK!E8)/4</f>
-        <v>40488.25</v>
+        <v>41525</v>
       </c>
       <c r="M8" s="21">
         <f>(F8+GEMINI!F8+PERPLIXITY!F8+DEEPSEEK!F8)/4</f>
-        <v>47899</v>
+        <v>48125</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6635,23 +6635,23 @@
         <v>80</v>
       </c>
       <c r="E11" s="16">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="F11" s="16">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="G11" s="8"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+GEMINI!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
-        <v>980.75</v>
+        <v>981.25</v>
       </c>
       <c r="M11" s="21">
         <f>(F11+GEMINI!F11+PERPLIXITY!F11+DEEPSEEK!F11)/4</f>
-        <v>1246.25</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6709,23 +6709,23 @@
         <v>50</v>
       </c>
       <c r="E13" s="16">
-        <v>890</v>
+        <v>775</v>
       </c>
       <c r="F13" s="16">
-        <v>1120</v>
+        <v>980</v>
       </c>
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>788.6</v>
+        <v>788.2</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+GEMINI!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
-        <v>871.25</v>
+        <v>842.5</v>
       </c>
       <c r="M13" s="21">
         <f>(F13+GEMINI!F13+PERPLIXITY!F13+DEEPSEEK!F13)/4</f>
-        <v>1037.5</v>
+        <v>1002.5</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6746,23 +6746,23 @@
         <v>9</v>
       </c>
       <c r="E14" s="16">
-        <v>7208</v>
+        <v>7480</v>
       </c>
       <c r="F14" s="16">
-        <v>9210</v>
+        <v>9200</v>
       </c>
       <c r="G14" s="7"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8253</v>
+        <v>8274</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
-        <v>7564.5</v>
+        <v>7632.5</v>
       </c>
       <c r="M14" s="21">
         <f>(F14+GEMINI!F14+PERPLIXITY!F14+DEEPSEEK!F14)/4</f>
-        <v>8702.5</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6783,23 +6783,23 @@
         <v>8</v>
       </c>
       <c r="E15" s="16">
-        <v>11369</v>
+        <v>12370</v>
       </c>
       <c r="F15" s="16">
-        <v>14522</v>
+        <v>14880</v>
       </c>
       <c r="G15" s="7"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>13244</v>
+        <v>13033</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+GEMINI!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
-        <v>12492.25</v>
+        <v>12742.5</v>
       </c>
       <c r="M15" s="21">
         <f>(F15+GEMINI!F15+PERPLIXITY!F15+DEEPSEEK!F15)/4</f>
-        <v>15005.5</v>
+        <v>15095</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6820,7 +6820,7 @@
         <v>500</v>
       </c>
       <c r="E16" s="16">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F16" s="16">
         <v>248</v>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
-        <v>203.5</v>
+        <v>203.75</v>
       </c>
       <c r="M16" s="21">
         <f>(F16+GEMINI!F16+PERPLIXITY!F16+DEEPSEEK!F16)/4</f>
@@ -6902,7 +6902,7 @@
       <c r="G18" s="8"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+GEMINI!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -6931,23 +6931,23 @@
         <v>300</v>
       </c>
       <c r="E19" s="16">
-        <v>64.2</v>
+        <v>61</v>
       </c>
       <c r="F19" s="16">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G19" s="8"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+GEMINI!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
-        <v>64.3</v>
+        <v>63.5</v>
       </c>
       <c r="M19" s="21">
         <f>(F19+GEMINI!F19+PERPLIXITY!F19+DEEPSEEK!F19)/4</f>
-        <v>94.25</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6976,7 +6976,7 @@
       <c r="G20" s="8"/>
       <c r="I20" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>78.400000000000006</v>
+        <v>77.2</v>
       </c>
       <c r="L20" s="21">
         <f>(E20+GEMINI!E20+PERPLIXITY!E20+DEEPSEEK!E20)/4</f>
@@ -7167,7 +7167,7 @@
       <c r="G2" s="10"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>844</v>
+        <v>857.5</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+GEMINI!E2+DEEPSEEK!E2)/4</f>
@@ -7204,15 +7204,15 @@
       <c r="G3" s="10"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
-        <v>1004.25</v>
+        <v>983.75</v>
       </c>
       <c r="M3" s="21">
         <f>(F3+CHATGPT!F3+GEMINI!F3+DEEPSEEK!F3)/4</f>
-        <v>1193.25</v>
+        <v>1151.25</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7241,7 +7241,7 @@
       <c r="G4" s="10"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6030</v>
+        <v>6032</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+GEMINI!E4+DEEPSEEK!E4)/4</f>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="M4" s="21">
         <f>(F4+CHATGPT!F4+GEMINI!F4+DEEPSEEK!F4)/4</f>
-        <v>7051.25</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7278,11 +7278,11 @@
       <c r="G5" s="10"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>647</v>
+        <v>649.6</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
-        <v>593.75</v>
+        <v>598.25</v>
       </c>
       <c r="M5" s="21">
         <f>(F5+CHATGPT!F5+GEMINI!F5+DEEPSEEK!F5)/4</f>
@@ -7315,15 +7315,15 @@
       <c r="G6" s="10"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>5001</v>
+        <v>5041</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
-        <v>4409</v>
+        <v>4425</v>
       </c>
       <c r="M6" s="21">
         <f>(F6+CHATGPT!F6+GEMINI!F6+DEEPSEEK!F6)/4</f>
-        <v>5478.5</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7352,15 +7352,15 @@
       <c r="G7" s="10"/>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>4084</v>
+        <v>4085</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+GEMINI!E7+DEEPSEEK!E7)/4</f>
-        <v>3713.25</v>
+        <v>3737.5</v>
       </c>
       <c r="M7" s="21">
         <f>(F7+CHATGPT!F7+GEMINI!F7+DEEPSEEK!F7)/4</f>
-        <v>4350.75</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7388,15 +7388,15 @@
       </c>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>45190</v>
+        <v>43310</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+GEMINI!E8+DEEPSEEK!E8)/4</f>
-        <v>40488.25</v>
+        <v>41525</v>
       </c>
       <c r="M8" s="21">
         <f>(F8+CHATGPT!F8+GEMINI!F8+DEEPSEEK!F8)/4</f>
-        <v>47899</v>
+        <v>48125</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7496,15 +7496,15 @@
       </c>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+GEMINI!E11+DEEPSEEK!E11)/4</f>
-        <v>980.75</v>
+        <v>981.25</v>
       </c>
       <c r="M11" s="21">
         <f>(F11+CHATGPT!F11+GEMINI!F11+DEEPSEEK!F11)/4</f>
-        <v>1246.25</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7570,15 +7570,15 @@
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>788.6</v>
+        <v>788.2</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+CHATGPT!E13+GEMINI!E13+DEEPSEEK!E13)/4</f>
-        <v>871.25</v>
+        <v>842.5</v>
       </c>
       <c r="M13" s="21">
         <f>(F13+CHATGPT!F13+GEMINI!F13+DEEPSEEK!F13)/4</f>
-        <v>1037.5</v>
+        <v>1002.5</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7607,15 +7607,15 @@
       <c r="G14" s="10"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8253</v>
+        <v>8274</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
-        <v>7564.5</v>
+        <v>7632.5</v>
       </c>
       <c r="M14" s="21">
         <f>(F14+CHATGPT!F14+GEMINI!F14+DEEPSEEK!F14)/4</f>
-        <v>8702.5</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7644,15 +7644,15 @@
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>13244</v>
+        <v>13033</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
-        <v>12492.25</v>
+        <v>12742.5</v>
       </c>
       <c r="M15" s="21">
         <f>(F15+CHATGPT!F15+GEMINI!F15+DEEPSEEK!F15)/4</f>
-        <v>15005.5</v>
+        <v>15095</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+GEMINI!E16+DEEPSEEK!E16)/4</f>
-        <v>203.5</v>
+        <v>203.75</v>
       </c>
       <c r="M16" s="21">
         <f>(F16+CHATGPT!F16+GEMINI!F16+DEEPSEEK!F16)/4</f>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
@@ -7790,15 +7790,15 @@
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+GEMINI!E19+DEEPSEEK!E19)/4</f>
-        <v>64.3</v>
+        <v>63.5</v>
       </c>
       <c r="M19" s="21">
         <f>(F19+CHATGPT!F19+GEMINI!F19+DEEPSEEK!F19)/4</f>
-        <v>94.25</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7827,7 +7827,7 @@
       <c r="G20" s="10"/>
       <c r="I20" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>78.400000000000006</v>
+        <v>77.2</v>
       </c>
       <c r="L20" s="21">
         <f>(E20+CHATGPT!E20+GEMINI!E20+DEEPSEEK!E20)/4</f>
@@ -8018,7 +8018,7 @@
       <c r="G2" s="31"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>844</v>
+        <v>857.5</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+PERPLIXITY!E2+GEMINI!E2)/4</f>
@@ -8055,15 +8055,15 @@
       <c r="G3" s="31"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
-        <v>1004.25</v>
+        <v>983.75</v>
       </c>
       <c r="M3" s="21">
         <f>(F3+CHATGPT!F3+PERPLIXITY!F3+GEMINI!F3)/4</f>
-        <v>1193.25</v>
+        <v>1151.25</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6030</v>
+        <v>6032</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+GEMINI!E4)/4</f>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M4" s="21">
         <f>(F4+CHATGPT!F4+PERPLIXITY!F4+GEMINI!F4)/4</f>
-        <v>7051.25</v>
+        <v>7050</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8128,11 +8128,11 @@
       <c r="G5" s="31"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>647</v>
+        <v>649.6</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
-        <v>593.75</v>
+        <v>598.25</v>
       </c>
       <c r="M5" s="21">
         <f>(F5+CHATGPT!F5+PERPLIXITY!F5+GEMINI!F5)/4</f>
@@ -8165,15 +8165,15 @@
       <c r="G6" s="31"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>5001</v>
+        <v>5041</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
-        <v>4409</v>
+        <v>4425</v>
       </c>
       <c r="M6" s="21">
         <f>(F6+CHATGPT!F6+PERPLIXITY!F6+GEMINI!F6)/4</f>
-        <v>5478.5</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8201,15 +8201,15 @@
       </c>
       <c r="I7" s="13">
         <f>'התיק העדכני'!I7</f>
-        <v>4084</v>
+        <v>4085</v>
       </c>
       <c r="L7" s="21">
         <f>(E7+CHATGPT!E7+PERPLIXITY!E7+GEMINI!E7)/4</f>
-        <v>3713.25</v>
+        <v>3737.5</v>
       </c>
       <c r="M7" s="21">
         <f>(F7+CHATGPT!F7+PERPLIXITY!F7+GEMINI!F7)/4</f>
-        <v>4350.75</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8238,15 +8238,15 @@
       <c r="G8" s="31"/>
       <c r="I8" s="13">
         <f>'התיק העדכני'!I8</f>
-        <v>45190</v>
+        <v>43310</v>
       </c>
       <c r="L8" s="21">
         <f>(E8+CHATGPT!E8+PERPLIXITY!E8+GEMINI!E8)/4</f>
-        <v>40488.25</v>
+        <v>41525</v>
       </c>
       <c r="M8" s="21">
         <f>(F8+CHATGPT!F8+PERPLIXITY!F8+GEMINI!F8)/4</f>
-        <v>47899</v>
+        <v>48125</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8349,15 +8349,15 @@
       <c r="G11" s="31"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+GEMINI!E11)/4</f>
-        <v>980.75</v>
+        <v>981.25</v>
       </c>
       <c r="M11" s="21">
         <f>(F11+CHATGPT!F11+PERPLIXITY!F11+GEMINI!F11)/4</f>
-        <v>1246.25</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8423,7 +8423,7 @@
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>788.6</v>
+        <v>788.2</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
@@ -8454,15 +8454,15 @@
       <c r="G14" s="31"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8253</v>
+        <v>8274</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
-        <v>7564.5</v>
+        <v>7632.5</v>
       </c>
       <c r="M14" s="21">
         <f>(F14+CHATGPT!F14+PERPLIXITY!F14+GEMINI!F14)/4</f>
-        <v>8702.5</v>
+        <v>8700</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8490,15 +8490,15 @@
       </c>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>78.400000000000006</v>
+        <v>77.2</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+PERPLIXITY!E15+GEMINI!E15)/4</f>
-        <v>12492.25</v>
+        <v>12742.5</v>
       </c>
       <c r="M15" s="21">
         <f>(F15+CHATGPT!F15+PERPLIXITY!F15+GEMINI!F15)/4</f>
-        <v>15005.5</v>
+        <v>15095</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8526,11 +8526,11 @@
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>13244</v>
+        <v>13033</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
-        <v>203.5</v>
+        <v>203.75</v>
       </c>
       <c r="M16" s="21">
         <f>(F16+CHATGPT!F16+PERPLIXITY!F16+GEMINI!F16)/4</f>
@@ -8636,15 +8636,15 @@
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+GEMINI!E19)/4</f>
-        <v>64.3</v>
+        <v>63.5</v>
       </c>
       <c r="M19" s="21">
         <f>(F19+CHATGPT!F19+PERPLIXITY!F19+GEMINI!F19)/4</f>
-        <v>94.25</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="I20" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L20" s="21">
         <f>(E20+CHATGPT!E20+PERPLIXITY!E20+GEMINI!E20)/4</f>
@@ -8705,7 +8705,7 @@
       <c r="G21" s="31"/>
       <c r="I21" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>78.400000000000006</v>
+        <v>77.2</v>
       </c>
       <c r="L21" s="21">
         <f>(E21+CHATGPT!E21+PERPLIXITY!E21+GEMINI!E21)/4</f>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\BURSA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/673b1203f7e82b27/מסמכים/GitHub/BURSA/BURSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4181241-0E48-4B5D-963A-71CF514C7A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{C4181241-0E48-4B5D-963A-71CF514C7A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1737FF8C-896E-4A50-B168-AAF6593562C6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
   <sheets>
     <sheet name="התיק העדכני" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="115">
   <si>
     <t>MTF מחקה אינדקס תעשיה ישראל</t>
   </si>
@@ -371,6 +382,9 @@
   </si>
   <si>
     <t>מחיר 09/02/2026</t>
+  </si>
+  <si>
+    <t>מחיר 10/02/2026</t>
   </si>
 </sst>
 </file>
@@ -380,11 +394,11 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₪&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -393,7 +407,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -444,13 +458,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -841,9 +855,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא של Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -881,7 +895,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -987,7 +1001,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1129,7 +1143,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1137,22 +1151,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86B4639-EF9D-4B16-B2C9-0D5E9C5EEC8B}">
-  <dimension ref="A1:CB25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:CC25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="5" width="17.5703125" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="63" width="14.85546875" customWidth="1"/>
-    <col min="64" max="73" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="13" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="11" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="11.5703125" customWidth="1"/>
+    <col min="1" max="5" width="17.59765625" customWidth="1"/>
+    <col min="6" max="6" width="13.296875" customWidth="1"/>
+    <col min="7" max="7" width="11.59765625" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="64" width="14.8984375" customWidth="1"/>
+    <col min="65" max="74" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="13" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="11" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="11.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1181,220 +1195,223 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BK1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BL1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BM1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BN1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BO1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="BO1" s="6" t="s">
+      <c r="BP1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="BP1" s="6" t="s">
+      <c r="BQ1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="BQ1" s="6" t="s">
+      <c r="BR1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="BR1" s="6" t="s">
+      <c r="BS1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="BS1" s="6" t="s">
+      <c r="BT1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BU1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BU1" s="6" t="s">
+      <c r="BV1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BW1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="BX1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="BY1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BY1" s="6" t="s">
+      <c r="BZ1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="BZ1" s="12" t="s">
+      <c r="CA1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="CA1" s="12" t="s">
+      <c r="CB1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="CB1" s="12" t="s">
+      <c r="CC1" s="12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A2" s="1">
         <v>1105907</v>
       </c>
@@ -1423,12 +1440,14 @@
         <v>774.5</v>
       </c>
       <c r="I2" s="13">
-        <v>857.5</v>
+        <v>846.8</v>
       </c>
       <c r="J2" s="13">
+        <v>846.8</v>
+      </c>
+      <c r="K2" s="13">
         <v>799.8</v>
       </c>
-      <c r="K2" s="13"/>
       <c r="L2" s="13"/>
       <c r="M2" s="13"/>
       <c r="N2" s="13"/>
@@ -1442,7 +1461,7 @@
       <c r="V2" s="13"/>
       <c r="W2" s="13"/>
       <c r="X2" s="13"/>
-      <c r="Y2" s="6"/>
+      <c r="Y2" s="13"/>
       <c r="Z2" s="6"/>
       <c r="AA2" s="6"/>
       <c r="AB2" s="6"/>
@@ -1483,30 +1502,31 @@
       <c r="BK2" s="6"/>
       <c r="BL2" s="6"/>
       <c r="BM2" s="6"/>
-      <c r="BN2" s="32"/>
-      <c r="BO2" s="6"/>
+      <c r="BN2" s="6"/>
+      <c r="BO2" s="32"/>
       <c r="BP2" s="6"/>
-      <c r="BQ2" s="32"/>
-      <c r="BR2" s="6"/>
+      <c r="BQ2" s="6"/>
+      <c r="BR2" s="32"/>
       <c r="BS2" s="6"/>
       <c r="BT2" s="6"/>
       <c r="BU2" s="6"/>
-      <c r="BV2" s="13">
-        <f t="shared" ref="BV2:BV20" si="0">(G2*H2)/100-CB2</f>
+      <c r="BV2" s="6"/>
+      <c r="BW2" s="13">
+        <f t="shared" ref="BW2:BW20" si="0">(G2*H2)/100-CC2</f>
         <v>774.5</v>
       </c>
-      <c r="BW2" s="13">
-        <f t="shared" ref="BW2:BW20" si="1">(G2*H2)/100</f>
+      <c r="BX2" s="13">
+        <f t="shared" ref="BX2:BX20" si="1">(G2*H2)/100</f>
         <v>774.5</v>
       </c>
-      <c r="BX2" s="6"/>
       <c r="BY2" s="6"/>
-      <c r="CB2" s="15">
-        <f>(BZ2*CA2-BZ2*H2)/100</f>
+      <c r="BZ2" s="6"/>
+      <c r="CC2" s="15">
+        <f>(CA2*CB2-CA2*H2)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A3" s="1">
         <v>1227552</v>
       </c>
@@ -1535,9 +1555,11 @@
         <v>950</v>
       </c>
       <c r="I3" s="13">
-        <v>881</v>
-      </c>
-      <c r="J3" s="13"/>
+        <v>884</v>
+      </c>
+      <c r="J3" s="13">
+        <v>884</v>
+      </c>
       <c r="K3" s="13"/>
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
@@ -1574,8 +1596,8 @@
       <c r="AR3" s="13"/>
       <c r="AS3" s="13"/>
       <c r="AT3" s="13"/>
-      <c r="AU3" s="14"/>
-      <c r="AV3" s="13"/>
+      <c r="AU3" s="13"/>
+      <c r="AV3" s="14"/>
       <c r="AW3" s="13"/>
       <c r="AX3" s="13"/>
       <c r="AY3" s="13"/>
@@ -1593,36 +1615,37 @@
       <c r="BK3" s="13"/>
       <c r="BL3" s="13"/>
       <c r="BM3" s="13"/>
-      <c r="BN3" s="29"/>
-      <c r="BO3" s="13"/>
+      <c r="BN3" s="13"/>
+      <c r="BO3" s="29"/>
       <c r="BP3" s="13"/>
-      <c r="BQ3" s="29"/>
-      <c r="BR3" s="13"/>
+      <c r="BQ3" s="13"/>
+      <c r="BR3" s="29"/>
       <c r="BS3" s="13"/>
       <c r="BT3" s="13"/>
       <c r="BU3" s="13"/>
-      <c r="BV3" s="13">
+      <c r="BV3" s="13"/>
+      <c r="BW3" s="13">
         <f t="shared" si="0"/>
         <v>285</v>
       </c>
-      <c r="BW3" s="13">
+      <c r="BX3" s="13">
         <f t="shared" si="1"/>
         <v>285</v>
       </c>
-      <c r="BX3" s="13">
-        <f>(BW3-BV3)</f>
+      <c r="BY3" s="13">
+        <f>(BX3-BW3)</f>
         <v>0</v>
       </c>
-      <c r="BY3" s="13">
-        <f>((BM3-H3)/H3)*100</f>
+      <c r="BZ3" s="13">
+        <f>((BN3-H3)/H3)*100</f>
         <v>-100</v>
       </c>
-      <c r="CB3" s="15">
-        <f>(BZ3*CA3-BZ3*H3)/100</f>
+      <c r="CC3" s="15">
+        <f>(CA3*CB3-CA3*H3)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A4" s="1">
         <v>587014</v>
       </c>
@@ -1651,72 +1674,74 @@
         <v>5925</v>
       </c>
       <c r="I4" s="13">
-        <v>6032</v>
+        <v>6011</v>
       </c>
       <c r="J4" s="13">
-        <v>5990</v>
+        <v>6011</v>
       </c>
       <c r="K4" s="13">
         <v>5990</v>
       </c>
       <c r="L4" s="13">
+        <v>5990</v>
+      </c>
+      <c r="M4" s="13">
         <v>5956</v>
       </c>
-      <c r="M4" s="13">
+      <c r="N4" s="13">
         <v>6298</v>
       </c>
-      <c r="N4" s="13">
+      <c r="O4" s="13">
         <v>6295</v>
       </c>
-      <c r="O4" s="13">
+      <c r="P4" s="13">
         <v>6370</v>
       </c>
-      <c r="P4" s="13">
+      <c r="Q4" s="13">
         <v>6140</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="R4" s="13">
         <v>7252</v>
       </c>
-      <c r="R4" s="13">
+      <c r="S4" s="13">
         <v>7120</v>
       </c>
-      <c r="S4" s="13">
+      <c r="T4" s="13">
         <v>7048</v>
       </c>
-      <c r="T4" s="13">
+      <c r="U4" s="13">
         <v>6979</v>
       </c>
-      <c r="U4" s="13">
+      <c r="V4" s="13">
         <v>6680</v>
       </c>
-      <c r="V4" s="13">
+      <c r="W4" s="13">
         <v>6111</v>
       </c>
-      <c r="W4" s="13">
+      <c r="X4" s="13">
         <v>6050</v>
       </c>
-      <c r="X4" s="13">
+      <c r="Y4" s="13">
         <v>6169</v>
       </c>
-      <c r="Y4" s="13">
+      <c r="Z4" s="13">
         <v>6300</v>
-      </c>
-      <c r="Z4" s="13">
-        <v>6335</v>
       </c>
       <c r="AA4" s="13">
         <v>6335</v>
       </c>
       <c r="AB4" s="13">
+        <v>6335</v>
+      </c>
+      <c r="AC4" s="13">
         <v>6444</v>
-      </c>
-      <c r="AC4" s="13">
-        <v>5749</v>
       </c>
       <c r="AD4" s="13">
         <v>5749</v>
       </c>
-      <c r="AE4" s="13"/>
+      <c r="AE4" s="13">
+        <v>5749</v>
+      </c>
       <c r="AF4" s="13"/>
       <c r="AG4" s="13"/>
       <c r="AH4" s="13"/>
@@ -1751,36 +1776,37 @@
       <c r="BK4" s="13"/>
       <c r="BL4" s="13"/>
       <c r="BM4" s="13"/>
-      <c r="BN4" s="29"/>
-      <c r="BO4" s="13"/>
+      <c r="BN4" s="13"/>
+      <c r="BO4" s="29"/>
       <c r="BP4" s="13"/>
-      <c r="BQ4" s="29"/>
-      <c r="BR4" s="13"/>
+      <c r="BQ4" s="13"/>
+      <c r="BR4" s="29"/>
       <c r="BS4" s="13"/>
       <c r="BT4" s="13"/>
       <c r="BU4" s="13"/>
-      <c r="BV4" s="13">
+      <c r="BV4" s="13"/>
+      <c r="BW4" s="13">
         <f t="shared" si="0"/>
         <v>1185</v>
       </c>
-      <c r="BW4" s="13">
+      <c r="BX4" s="13">
         <f t="shared" si="1"/>
         <v>1185</v>
       </c>
-      <c r="BX4" s="13">
-        <f>(BW4-BV4)</f>
+      <c r="BY4" s="13">
+        <f>(BX4-BW4)</f>
         <v>0</v>
       </c>
-      <c r="BY4" s="13">
-        <f>((BM4-H4)/H4)*100</f>
+      <c r="BZ4" s="13">
+        <f>((BN4-H4)/H4)*100</f>
         <v>-100</v>
       </c>
-      <c r="CB4" s="15">
-        <f>(BZ4*CA4-BZ4*H4)/100</f>
+      <c r="CC4" s="15">
+        <f>(CA4*CB4-CA4*H4)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A5" s="1">
         <v>1099787</v>
       </c>
@@ -1809,102 +1835,104 @@
         <v>617.53</v>
       </c>
       <c r="I5" s="13">
-        <v>649.6</v>
+        <v>642.20000000000005</v>
       </c>
       <c r="J5" s="13">
+        <v>642.20000000000005</v>
+      </c>
+      <c r="K5" s="13">
         <v>656.2</v>
       </c>
-      <c r="K5" s="13">
+      <c r="L5" s="13">
         <v>622.4</v>
       </c>
-      <c r="L5" s="13">
+      <c r="M5" s="13">
         <v>594.9</v>
       </c>
-      <c r="M5" s="13">
+      <c r="N5" s="13">
         <v>638</v>
       </c>
-      <c r="N5" s="13">
+      <c r="O5" s="13">
         <v>587.5</v>
       </c>
-      <c r="O5" s="13">
+      <c r="P5" s="13">
         <v>577.9</v>
       </c>
-      <c r="P5" s="13">
+      <c r="Q5" s="13">
         <v>559</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="R5" s="13">
         <v>570</v>
       </c>
-      <c r="R5" s="13">
+      <c r="S5" s="13">
         <v>575.70000000000005</v>
       </c>
-      <c r="S5" s="13">
+      <c r="T5" s="13">
         <v>612.6</v>
       </c>
-      <c r="T5" s="13">
+      <c r="U5" s="13">
         <v>638.29999999999995</v>
       </c>
-      <c r="U5" s="13">
+      <c r="V5" s="13">
         <v>630.29999999999995</v>
       </c>
-      <c r="V5" s="13">
+      <c r="W5" s="13">
         <v>626</v>
       </c>
-      <c r="W5" s="13">
+      <c r="X5" s="13">
         <v>595.4</v>
       </c>
-      <c r="X5" s="13">
+      <c r="Y5" s="13">
         <v>667.1</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="Z5" s="13">
         <v>651</v>
-      </c>
-      <c r="Z5" s="13">
-        <v>641.1</v>
       </c>
       <c r="AA5" s="13">
         <v>641.1</v>
       </c>
       <c r="AB5" s="13">
+        <v>641.1</v>
+      </c>
+      <c r="AC5" s="13">
         <v>607.1</v>
       </c>
-      <c r="AC5" s="13">
+      <c r="AD5" s="13">
         <v>583</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AE5" s="13">
         <v>581.6</v>
       </c>
-      <c r="AE5" s="13">
+      <c r="AF5" s="13">
         <v>578.70000000000005</v>
       </c>
-      <c r="AF5" s="13">
+      <c r="AG5" s="13">
         <v>590</v>
       </c>
-      <c r="AG5" s="13">
+      <c r="AH5" s="13">
         <v>554.70000000000005</v>
       </c>
-      <c r="AH5" s="13">
+      <c r="AI5" s="13">
         <v>511.8</v>
       </c>
-      <c r="AI5" s="13">
+      <c r="AJ5" s="13">
         <v>487</v>
       </c>
-      <c r="AJ5" s="13">
+      <c r="AK5" s="13">
         <v>478.8</v>
       </c>
-      <c r="AK5" s="13">
+      <c r="AL5" s="13">
         <v>485.5</v>
       </c>
-      <c r="AL5" s="13">
+      <c r="AM5" s="13">
         <v>453.4</v>
       </c>
-      <c r="AM5" s="13">
+      <c r="AN5" s="13">
         <v>426.1</v>
       </c>
-      <c r="AN5" s="13">
+      <c r="AO5" s="13">
         <v>423.2</v>
       </c>
-      <c r="AO5" s="13"/>
       <c r="AP5" s="13"/>
       <c r="AQ5" s="13"/>
       <c r="AR5" s="13"/>
@@ -1929,27 +1957,28 @@
       <c r="BK5" s="13"/>
       <c r="BL5" s="13"/>
       <c r="BM5" s="13"/>
-      <c r="BN5" s="29"/>
-      <c r="BO5" s="13"/>
+      <c r="BN5" s="13"/>
+      <c r="BO5" s="29"/>
       <c r="BP5" s="13"/>
-      <c r="BQ5" s="29"/>
-      <c r="BR5" s="13"/>
+      <c r="BQ5" s="13"/>
+      <c r="BR5" s="29"/>
       <c r="BS5" s="13"/>
       <c r="BT5" s="13"/>
       <c r="BU5" s="13"/>
-      <c r="BV5" s="13">
+      <c r="BV5" s="13"/>
+      <c r="BW5" s="13">
         <f t="shared" si="0"/>
         <v>975.6973999999999</v>
       </c>
-      <c r="BW5" s="13">
+      <c r="BX5" s="13">
         <f t="shared" si="1"/>
         <v>975.6973999999999</v>
       </c>
-      <c r="BX5" s="13"/>
       <c r="BY5" s="13"/>
-      <c r="CB5" s="15"/>
-    </row>
-    <row r="6" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BZ5" s="13"/>
+      <c r="CC5" s="15"/>
+    </row>
+    <row r="6" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A6" s="2">
         <v>1166768</v>
       </c>
@@ -1978,75 +2007,77 @@
         <v>4040</v>
       </c>
       <c r="I6" s="13">
-        <v>5041</v>
+        <v>5059</v>
       </c>
       <c r="J6" s="13">
+        <v>5059</v>
+      </c>
+      <c r="K6" s="13">
         <v>4880</v>
       </c>
-      <c r="K6" s="13">
+      <c r="L6" s="13">
         <v>4647</v>
       </c>
-      <c r="L6" s="13">
+      <c r="M6" s="13">
         <v>4650</v>
       </c>
-      <c r="M6" s="13">
+      <c r="N6" s="13">
         <v>4799</v>
       </c>
-      <c r="N6" s="13">
+      <c r="O6" s="13">
         <v>4740</v>
       </c>
-      <c r="O6" s="13">
+      <c r="P6" s="13">
         <v>4350</v>
       </c>
-      <c r="P6" s="13">
+      <c r="Q6" s="13">
         <v>4355</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="R6" s="13">
         <v>4500</v>
       </c>
-      <c r="R6" s="13">
+      <c r="S6" s="13">
         <v>4424</v>
       </c>
-      <c r="S6" s="13">
+      <c r="T6" s="13">
         <v>4412</v>
       </c>
-      <c r="T6" s="13">
+      <c r="U6" s="13">
         <v>4450</v>
       </c>
-      <c r="U6" s="13">
+      <c r="V6" s="13">
         <v>4238</v>
       </c>
-      <c r="V6" s="13">
+      <c r="W6" s="13">
         <v>3970</v>
       </c>
-      <c r="W6" s="13">
+      <c r="X6" s="13">
         <v>3870</v>
       </c>
-      <c r="X6" s="13">
+      <c r="Y6" s="13">
         <v>3805</v>
       </c>
-      <c r="Y6" s="13">
+      <c r="Z6" s="13">
         <v>3667</v>
-      </c>
-      <c r="Z6" s="13">
-        <v>3582</v>
       </c>
       <c r="AA6" s="13">
         <v>3582</v>
       </c>
       <c r="AB6" s="13">
+        <v>3582</v>
+      </c>
+      <c r="AC6" s="13">
         <v>3570</v>
       </c>
-      <c r="AC6" s="13">
+      <c r="AD6" s="13">
         <v>3619</v>
       </c>
-      <c r="AD6" s="13">
+      <c r="AE6" s="13">
         <v>3650</v>
       </c>
-      <c r="AE6" s="13">
+      <c r="AF6" s="13">
         <v>3720</v>
       </c>
-      <c r="AF6" s="13"/>
       <c r="AG6" s="13"/>
       <c r="AH6" s="13"/>
       <c r="AI6" s="13"/>
@@ -2080,41 +2111,42 @@
       <c r="BK6" s="13"/>
       <c r="BL6" s="13"/>
       <c r="BM6" s="13"/>
-      <c r="BN6" s="29"/>
-      <c r="BO6" s="13"/>
+      <c r="BN6" s="13"/>
+      <c r="BO6" s="29"/>
       <c r="BP6" s="13"/>
-      <c r="BQ6" s="29"/>
-      <c r="BR6" s="13"/>
+      <c r="BQ6" s="13"/>
+      <c r="BR6" s="29"/>
       <c r="BS6" s="13"/>
       <c r="BT6" s="13"/>
-      <c r="BV6" s="13">
+      <c r="BU6" s="13"/>
+      <c r="BW6" s="13">
         <f t="shared" si="0"/>
         <v>1033.7</v>
       </c>
-      <c r="BW6" s="13">
+      <c r="BX6" s="13">
         <f t="shared" si="1"/>
         <v>1010</v>
       </c>
-      <c r="BX6" s="13">
-        <f t="shared" ref="BX6" si="2">(BW6-BV6)</f>
+      <c r="BY6" s="13">
+        <f t="shared" ref="BY6" si="2">(BX6-BW6)</f>
         <v>-23.700000000000045</v>
       </c>
-      <c r="BY6" s="13">
-        <f>((BM6-H6)/H6)*100</f>
+      <c r="BZ6" s="13">
+        <f>((BN6-H6)/H6)*100</f>
         <v>-100</v>
       </c>
-      <c r="BZ6">
+      <c r="CA6">
         <v>5</v>
       </c>
-      <c r="CA6">
+      <c r="CB6">
         <v>3566</v>
       </c>
-      <c r="CB6" s="15">
-        <f>(BZ6*CA6-BZ6*H6)/100</f>
+      <c r="CC6" s="15">
+        <f>(CA6*CB6-CA6*H6)/100</f>
         <v>-23.7</v>
       </c>
     </row>
-    <row r="7" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A7" s="1">
         <v>1148899</v>
       </c>
@@ -2146,99 +2178,101 @@
         <v>4085</v>
       </c>
       <c r="J7" s="13">
+        <v>4085</v>
+      </c>
+      <c r="K7" s="13">
         <v>3996</v>
       </c>
-      <c r="K7" s="13">
+      <c r="L7" s="13">
         <v>3954</v>
       </c>
-      <c r="L7" s="13">
+      <c r="M7" s="13">
         <v>3955</v>
       </c>
-      <c r="M7" s="13">
+      <c r="N7" s="13">
         <v>4022</v>
       </c>
-      <c r="N7" s="13">
+      <c r="O7" s="13">
         <v>4033</v>
       </c>
-      <c r="O7" s="13">
+      <c r="P7" s="13">
         <v>3988</v>
       </c>
-      <c r="P7" s="13">
+      <c r="Q7" s="13">
         <v>3916</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="R7" s="13">
         <v>3954</v>
       </c>
-      <c r="R7" s="13">
+      <c r="S7" s="13">
         <v>3932</v>
       </c>
-      <c r="S7" s="13">
+      <c r="T7" s="13">
         <v>3949</v>
       </c>
-      <c r="T7" s="13">
+      <c r="U7" s="13">
         <v>3943</v>
       </c>
-      <c r="U7" s="13">
+      <c r="V7" s="13">
         <v>3928</v>
       </c>
-      <c r="V7" s="13">
+      <c r="W7" s="13">
         <v>3913</v>
       </c>
-      <c r="W7" s="13">
+      <c r="X7" s="13">
         <v>3860</v>
       </c>
-      <c r="X7" s="13">
+      <c r="Y7" s="13">
         <v>3893</v>
       </c>
-      <c r="Y7" s="13">
+      <c r="Z7" s="13">
         <v>3900</v>
-      </c>
-      <c r="Z7" s="13">
-        <v>3842</v>
       </c>
       <c r="AA7" s="13">
         <v>3842</v>
       </c>
       <c r="AB7" s="13">
+        <v>3842</v>
+      </c>
+      <c r="AC7" s="13">
         <v>3841</v>
       </c>
-      <c r="AC7" s="13">
+      <c r="AD7" s="13">
         <v>3809</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AE7" s="13">
         <v>3810</v>
       </c>
-      <c r="AE7" s="13">
+      <c r="AF7" s="13">
         <v>3798</v>
       </c>
-      <c r="AF7" s="13">
+      <c r="AG7" s="13">
         <v>3713</v>
       </c>
-      <c r="AG7" s="13">
+      <c r="AH7" s="13">
         <v>3657</v>
       </c>
-      <c r="AH7" s="13">
+      <c r="AI7" s="13">
         <v>3592</v>
       </c>
-      <c r="AI7" s="13">
+      <c r="AJ7" s="13">
         <v>3621</v>
       </c>
-      <c r="AJ7" s="13">
+      <c r="AK7" s="13">
         <v>3572</v>
       </c>
-      <c r="AK7" s="13">
+      <c r="AL7" s="13">
         <v>3580</v>
       </c>
-      <c r="AL7" s="13">
+      <c r="AM7" s="13">
         <v>3569</v>
       </c>
-      <c r="AM7" s="13">
+      <c r="AN7" s="13">
         <v>3659</v>
       </c>
-      <c r="AN7" s="13">
+      <c r="AO7" s="13">
         <v>3656</v>
       </c>
-      <c r="AO7" s="13"/>
       <c r="AP7" s="13"/>
       <c r="AQ7" s="13"/>
       <c r="AR7" s="13"/>
@@ -2263,27 +2297,28 @@
       <c r="BK7" s="13"/>
       <c r="BL7" s="13"/>
       <c r="BM7" s="13"/>
-      <c r="BN7" s="29"/>
-      <c r="BO7" s="13"/>
+      <c r="BN7" s="13"/>
+      <c r="BO7" s="29"/>
       <c r="BP7" s="13"/>
-      <c r="BQ7" s="29"/>
-      <c r="BR7" s="13"/>
+      <c r="BQ7" s="13"/>
+      <c r="BR7" s="29"/>
       <c r="BS7" s="13"/>
       <c r="BT7" s="13"/>
       <c r="BU7" s="13"/>
-      <c r="BV7" s="13">
+      <c r="BV7" s="13"/>
+      <c r="BW7" s="13">
         <f t="shared" si="0"/>
         <v>2509.5</v>
       </c>
-      <c r="BW7" s="13">
+      <c r="BX7" s="13">
         <f t="shared" si="1"/>
         <v>2509.5</v>
       </c>
-      <c r="BX7" s="13"/>
       <c r="BY7" s="13"/>
-      <c r="CB7" s="15"/>
-    </row>
-    <row r="8" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BZ7" s="13"/>
+      <c r="CC7" s="15"/>
+    </row>
+    <row r="8" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A8" s="1">
         <v>1082379</v>
       </c>
@@ -2315,135 +2350,137 @@
         <v>43310</v>
       </c>
       <c r="J8" s="13">
+        <v>43310</v>
+      </c>
+      <c r="K8" s="13">
         <v>45300</v>
       </c>
-      <c r="K8" s="13">
+      <c r="L8" s="13">
         <v>40740</v>
       </c>
-      <c r="L8" s="13">
+      <c r="M8" s="13">
         <v>39070</v>
       </c>
-      <c r="M8" s="13">
+      <c r="N8" s="13">
         <v>39600</v>
       </c>
-      <c r="N8" s="13">
+      <c r="O8" s="13">
         <v>43640</v>
       </c>
-      <c r="O8" s="13">
+      <c r="P8" s="13">
         <v>42700</v>
       </c>
-      <c r="P8" s="13">
+      <c r="Q8" s="13">
         <v>42140</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="R8" s="13">
         <v>43490</v>
       </c>
-      <c r="R8" s="13">
+      <c r="S8" s="13">
         <v>40750</v>
       </c>
-      <c r="S8" s="13">
+      <c r="T8" s="13">
         <v>40900</v>
       </c>
-      <c r="T8" s="13">
+      <c r="U8" s="13">
         <v>40790</v>
       </c>
-      <c r="U8" s="13">
+      <c r="V8" s="13">
         <v>40820</v>
       </c>
-      <c r="V8" s="13">
+      <c r="W8" s="13">
         <v>41570</v>
       </c>
-      <c r="W8" s="13">
+      <c r="X8" s="13">
         <v>42050</v>
       </c>
-      <c r="X8" s="13">
+      <c r="Y8" s="13">
         <v>39960</v>
       </c>
-      <c r="Y8" s="13">
+      <c r="Z8" s="13">
         <v>39990</v>
-      </c>
-      <c r="Z8" s="13">
-        <v>38680</v>
       </c>
       <c r="AA8" s="13">
         <v>38680</v>
       </c>
       <c r="AB8" s="13">
+        <v>38680</v>
+      </c>
+      <c r="AC8" s="13">
         <v>37770</v>
       </c>
-      <c r="AC8" s="13">
+      <c r="AD8" s="13">
         <v>36330</v>
       </c>
-      <c r="AD8" s="13">
+      <c r="AE8" s="13">
         <v>38680</v>
       </c>
-      <c r="AE8" s="13">
+      <c r="AF8" s="13">
         <v>39090</v>
       </c>
-      <c r="AF8" s="13">
+      <c r="AG8" s="13">
         <v>37300</v>
       </c>
-      <c r="AG8" s="13">
+      <c r="AH8" s="13">
         <v>37650</v>
       </c>
-      <c r="AH8" s="13">
+      <c r="AI8" s="13">
         <v>37300</v>
       </c>
-      <c r="AI8" s="13">
+      <c r="AJ8" s="13">
         <v>39450</v>
       </c>
-      <c r="AJ8" s="13">
+      <c r="AK8" s="13">
         <v>38390</v>
       </c>
-      <c r="AK8" s="13">
+      <c r="AL8" s="13">
         <v>38800</v>
       </c>
-      <c r="AL8" s="13">
+      <c r="AM8" s="13">
         <v>38510</v>
-      </c>
-      <c r="AM8" s="13">
-        <v>38970</v>
       </c>
       <c r="AN8" s="13">
         <v>38970</v>
       </c>
       <c r="AO8" s="13">
-        <v>37700</v>
+        <v>38970</v>
       </c>
       <c r="AP8" s="13">
         <v>37700</v>
       </c>
       <c r="AQ8" s="13">
+        <v>37700</v>
+      </c>
+      <c r="AR8" s="13">
         <v>37750</v>
       </c>
-      <c r="AR8" s="13">
+      <c r="AS8" s="13">
         <v>38430</v>
       </c>
-      <c r="AS8" s="13">
+      <c r="AT8" s="13">
         <v>38250</v>
       </c>
-      <c r="AT8" s="13">
+      <c r="AU8" s="13">
         <v>40110</v>
       </c>
-      <c r="AU8" s="13">
+      <c r="AV8" s="13">
         <v>40820</v>
       </c>
-      <c r="AV8" s="13">
+      <c r="AW8" s="13">
         <v>39320</v>
       </c>
-      <c r="AW8" s="13">
+      <c r="AX8" s="13">
         <v>37800</v>
       </c>
-      <c r="AX8" s="13">
+      <c r="AY8" s="13">
         <v>36620</v>
       </c>
-      <c r="AY8" s="13">
+      <c r="AZ8" s="13">
         <v>37130</v>
       </c>
-      <c r="AZ8" s="13">
+      <c r="BA8" s="13">
         <v>35850</v>
       </c>
-      <c r="BA8" s="13"/>
       <c r="BB8" s="13"/>
       <c r="BC8" s="13"/>
       <c r="BD8" s="13"/>
@@ -2456,39 +2493,40 @@
       <c r="BK8" s="13"/>
       <c r="BL8" s="13"/>
       <c r="BM8" s="13"/>
-      <c r="BN8" s="29"/>
-      <c r="BO8" s="13"/>
+      <c r="BN8" s="13"/>
+      <c r="BO8" s="29"/>
       <c r="BP8" s="13"/>
-      <c r="BQ8" s="29"/>
-      <c r="BR8" s="13"/>
+      <c r="BQ8" s="13"/>
+      <c r="BR8" s="29"/>
       <c r="BS8" s="13"/>
       <c r="BT8" s="13"/>
       <c r="BU8" s="13"/>
-      <c r="BV8" s="13">
+      <c r="BV8" s="13"/>
+      <c r="BW8" s="13">
         <f t="shared" si="0"/>
         <v>806.25</v>
       </c>
-      <c r="BW8" s="13">
+      <c r="BX8" s="13">
         <f t="shared" si="1"/>
         <v>757.5</v>
       </c>
-      <c r="BX8" s="13">
-        <f t="shared" ref="BX8:BX11" si="3">(BW8-BV8)</f>
+      <c r="BY8" s="13">
+        <f t="shared" ref="BY8:BY11" si="3">(BX8-BW8)</f>
         <v>-48.75</v>
       </c>
-      <c r="BY8" s="13"/>
-      <c r="BZ8">
+      <c r="BZ8" s="13"/>
+      <c r="CA8">
         <v>3</v>
       </c>
-      <c r="CA8">
+      <c r="CB8">
         <v>36250</v>
       </c>
-      <c r="CB8" s="15">
-        <f t="shared" ref="CB8:CB18" si="4">(BZ8*CA8-BZ8*H8)/100</f>
+      <c r="CC8" s="15">
+        <f t="shared" ref="CC8:CC18" si="4">(CA8*CB8-CA8*H8)/100</f>
         <v>-48.75</v>
       </c>
     </row>
-    <row r="9" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A9" s="1">
         <v>629014</v>
       </c>
@@ -2520,129 +2558,131 @@
         <v>10640</v>
       </c>
       <c r="J9" s="13">
+        <v>10640</v>
+      </c>
+      <c r="K9" s="13">
         <v>10660</v>
       </c>
-      <c r="K9" s="13">
+      <c r="L9" s="13">
         <v>10820</v>
       </c>
-      <c r="L9" s="13">
+      <c r="M9" s="13">
         <v>10680</v>
       </c>
-      <c r="M9" s="13">
+      <c r="N9" s="13">
         <v>11290</v>
       </c>
-      <c r="N9" s="13">
+      <c r="O9" s="13">
         <v>11020</v>
-      </c>
-      <c r="O9" s="13">
-        <v>10100</v>
       </c>
       <c r="P9" s="13">
         <v>10100</v>
       </c>
       <c r="Q9" s="13">
+        <v>10100</v>
+      </c>
+      <c r="R9" s="13">
         <v>10240</v>
       </c>
-      <c r="R9" s="13">
+      <c r="S9" s="13">
         <v>9891</v>
       </c>
-      <c r="S9" s="13">
+      <c r="T9" s="13">
         <v>9956</v>
       </c>
-      <c r="T9" s="13">
+      <c r="U9" s="13">
         <v>9910</v>
       </c>
-      <c r="U9" s="13">
+      <c r="V9" s="13">
         <v>9960</v>
       </c>
-      <c r="V9" s="13">
+      <c r="W9" s="13">
         <v>9924</v>
       </c>
-      <c r="W9" s="13">
+      <c r="X9" s="13">
         <v>9999</v>
       </c>
-      <c r="X9" s="13">
+      <c r="Y9" s="13">
         <v>9962</v>
       </c>
-      <c r="Y9" s="13">
+      <c r="Z9" s="13">
         <v>9979</v>
-      </c>
-      <c r="Z9" s="13">
-        <v>10130</v>
       </c>
       <c r="AA9" s="13">
         <v>10130</v>
       </c>
       <c r="AB9" s="13">
+        <v>10130</v>
+      </c>
+      <c r="AC9" s="13">
         <v>10400</v>
       </c>
-      <c r="AC9" s="13">
+      <c r="AD9" s="13">
         <v>10320</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AE9" s="13">
         <v>10300</v>
       </c>
-      <c r="AE9" s="13">
+      <c r="AF9" s="13">
         <v>10310</v>
       </c>
-      <c r="AF9" s="13">
+      <c r="AG9" s="13">
         <v>9672</v>
       </c>
-      <c r="AG9" s="13">
+      <c r="AH9" s="13">
         <v>9953</v>
       </c>
-      <c r="AH9" s="13">
+      <c r="AI9" s="13">
         <v>10090</v>
       </c>
-      <c r="AI9" s="13">
+      <c r="AJ9" s="13">
         <v>10070</v>
       </c>
-      <c r="AJ9" s="13">
+      <c r="AK9" s="13">
         <v>10030</v>
       </c>
-      <c r="AK9" s="13">
+      <c r="AL9" s="13">
         <v>10120</v>
       </c>
-      <c r="AL9" s="13">
+      <c r="AM9" s="13">
         <v>10000</v>
       </c>
-      <c r="AM9" s="13">
+      <c r="AN9" s="13">
         <v>10080</v>
       </c>
-      <c r="AN9" s="13">
+      <c r="AO9" s="13">
         <v>10030</v>
-      </c>
-      <c r="AO9" s="13">
-        <v>9726</v>
       </c>
       <c r="AP9" s="13">
         <v>9726</v>
       </c>
       <c r="AQ9" s="13">
+        <v>9726</v>
+      </c>
+      <c r="AR9" s="13">
         <v>9659</v>
       </c>
-      <c r="AR9" s="13">
+      <c r="AS9" s="13">
         <v>9670</v>
       </c>
-      <c r="AS9" s="13">
+      <c r="AT9" s="13">
         <v>9590</v>
       </c>
-      <c r="AT9" s="13">
+      <c r="AU9" s="13">
         <v>9588</v>
       </c>
-      <c r="AU9" s="13">
+      <c r="AV9" s="13">
         <v>9400</v>
       </c>
-      <c r="AV9" s="13">
+      <c r="AW9" s="13">
         <v>9320</v>
       </c>
-      <c r="AW9" s="13">
+      <c r="AX9" s="13">
         <v>9071</v>
       </c>
-      <c r="AX9" s="13">
+      <c r="AY9" s="13">
         <v>9271</v>
       </c>
-      <c r="AY9" s="13"/>
       <c r="AZ9" s="13"/>
       <c r="BA9" s="13"/>
       <c r="BB9" s="13"/>
@@ -2657,39 +2697,40 @@
       <c r="BK9" s="13"/>
       <c r="BL9" s="13"/>
       <c r="BM9" s="13"/>
-      <c r="BN9" s="29"/>
-      <c r="BO9" s="13"/>
+      <c r="BN9" s="13"/>
+      <c r="BO9" s="29"/>
       <c r="BP9" s="13"/>
-      <c r="BQ9" s="29"/>
-      <c r="BR9" s="13"/>
+      <c r="BQ9" s="13"/>
+      <c r="BR9" s="29"/>
       <c r="BS9" s="13"/>
       <c r="BT9" s="13"/>
       <c r="BU9" s="13"/>
-      <c r="BV9" s="13">
+      <c r="BV9" s="13"/>
+      <c r="BW9" s="13">
         <f t="shared" si="0"/>
         <v>-38.65</v>
       </c>
-      <c r="BW9" s="13">
+      <c r="BX9" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BX9" s="13">
+      <c r="BY9" s="13">
         <f t="shared" si="3"/>
         <v>38.65</v>
       </c>
-      <c r="BY9" s="13"/>
-      <c r="BZ9">
+      <c r="BZ9" s="13"/>
+      <c r="CA9">
         <v>5</v>
       </c>
-      <c r="CA9">
+      <c r="CB9">
         <v>10000</v>
       </c>
-      <c r="CB9" s="15">
+      <c r="CC9" s="15">
         <f t="shared" si="4"/>
         <v>38.65</v>
       </c>
     </row>
-    <row r="10" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A10" s="1">
         <v>1141464</v>
       </c>
@@ -2721,211 +2762,214 @@
         <v>4987</v>
       </c>
       <c r="J10" s="13">
+        <v>4987</v>
+      </c>
+      <c r="K10" s="13">
         <v>5027</v>
-      </c>
-      <c r="K10" s="13">
-        <v>5067</v>
       </c>
       <c r="L10" s="13">
         <v>5067</v>
       </c>
       <c r="M10" s="13">
+        <v>5067</v>
+      </c>
+      <c r="N10" s="13">
         <v>5126</v>
       </c>
-      <c r="N10" s="13">
+      <c r="O10" s="13">
         <v>5164</v>
-      </c>
-      <c r="O10" s="13">
-        <v>4809</v>
       </c>
       <c r="P10" s="13">
         <v>4809</v>
       </c>
       <c r="Q10" s="13">
+        <v>4809</v>
+      </c>
+      <c r="R10" s="13">
         <v>4849</v>
       </c>
-      <c r="R10" s="13">
+      <c r="S10" s="13">
         <v>4821</v>
       </c>
-      <c r="S10" s="13">
+      <c r="T10" s="13">
         <v>4925</v>
       </c>
-      <c r="T10" s="13">
+      <c r="U10" s="13">
         <v>5013</v>
-      </c>
-      <c r="U10" s="13">
-        <v>5050</v>
       </c>
       <c r="V10" s="13">
         <v>5050</v>
       </c>
       <c r="W10" s="13">
+        <v>5050</v>
+      </c>
+      <c r="X10" s="13">
         <v>4930</v>
       </c>
-      <c r="X10" s="13">
+      <c r="Y10" s="13">
         <v>5150</v>
       </c>
-      <c r="Y10" s="13">
+      <c r="Z10" s="13">
         <v>5283</v>
-      </c>
-      <c r="Z10" s="13">
-        <v>5253</v>
       </c>
       <c r="AA10" s="13">
         <v>5253</v>
       </c>
       <c r="AB10" s="13">
+        <v>5253</v>
+      </c>
+      <c r="AC10" s="13">
         <v>5400</v>
       </c>
-      <c r="AC10" s="13">
+      <c r="AD10" s="13">
         <v>5522</v>
       </c>
-      <c r="AD10" s="13">
+      <c r="AE10" s="13">
         <v>5690</v>
       </c>
-      <c r="AE10" s="13">
+      <c r="AF10" s="13">
         <v>5749</v>
       </c>
-      <c r="AF10" s="13">
+      <c r="AG10" s="13">
         <v>5840</v>
-      </c>
-      <c r="AG10" s="13">
-        <v>5650</v>
       </c>
       <c r="AH10" s="13">
         <v>5650</v>
       </c>
       <c r="AI10" s="13">
+        <v>5650</v>
+      </c>
+      <c r="AJ10" s="13">
         <v>5841</v>
       </c>
-      <c r="AJ10" s="13">
+      <c r="AK10" s="13">
         <v>5758</v>
       </c>
-      <c r="AK10" s="13">
+      <c r="AL10" s="13">
         <v>5673</v>
       </c>
-      <c r="AL10" s="13">
+      <c r="AM10" s="13">
         <v>5609</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AN10" s="13">
         <v>5750</v>
       </c>
-      <c r="AN10" s="13">
+      <c r="AO10" s="13">
         <v>5841</v>
-      </c>
-      <c r="AO10" s="13">
-        <v>5564</v>
       </c>
       <c r="AP10" s="13">
         <v>5564</v>
       </c>
       <c r="AQ10" s="13">
+        <v>5564</v>
+      </c>
+      <c r="AR10" s="13">
         <v>5557</v>
       </c>
-      <c r="AR10" s="13">
+      <c r="AS10" s="13">
         <v>5501</v>
       </c>
-      <c r="AS10" s="13">
+      <c r="AT10" s="13">
         <v>5250</v>
       </c>
-      <c r="AT10" s="13">
+      <c r="AU10" s="13">
         <v>5270</v>
       </c>
-      <c r="AU10" s="13">
+      <c r="AV10" s="13">
         <v>5149</v>
       </c>
-      <c r="AV10" s="13">
+      <c r="AW10" s="13">
         <v>5092</v>
       </c>
-      <c r="AW10" s="13">
+      <c r="AX10" s="13">
         <v>5228</v>
       </c>
-      <c r="AX10" s="13">
+      <c r="AY10" s="13">
         <v>5301</v>
       </c>
-      <c r="AY10" s="13">
+      <c r="AZ10" s="13">
         <v>5159</v>
       </c>
-      <c r="AZ10" s="13">
+      <c r="BA10" s="13">
         <v>5198</v>
       </c>
-      <c r="BA10" s="13">
+      <c r="BB10" s="13">
         <v>5077</v>
       </c>
-      <c r="BB10" s="13">
+      <c r="BC10" s="13">
         <v>4842</v>
       </c>
-      <c r="BC10" s="13">
+      <c r="BD10" s="13">
         <v>5050</v>
       </c>
-      <c r="BD10" s="13">
+      <c r="BE10" s="13">
         <v>4970</v>
       </c>
-      <c r="BE10" s="13">
+      <c r="BF10" s="13">
         <v>4880</v>
       </c>
-      <c r="BF10" s="13">
+      <c r="BG10" s="13">
         <v>4704</v>
       </c>
-      <c r="BG10" s="13">
+      <c r="BH10" s="13">
         <v>4770</v>
       </c>
-      <c r="BH10" s="13">
+      <c r="BI10" s="13">
         <v>4609</v>
       </c>
-      <c r="BI10" s="13">
+      <c r="BJ10" s="13">
         <v>4674</v>
       </c>
-      <c r="BJ10" s="13">
+      <c r="BK10" s="13">
         <v>4710</v>
       </c>
-      <c r="BK10" s="13">
+      <c r="BL10" s="13">
         <v>4688</v>
       </c>
-      <c r="BL10" s="13">
+      <c r="BM10" s="13">
         <v>4900</v>
       </c>
-      <c r="BM10" s="13">
+      <c r="BN10" s="13">
         <v>5000</v>
       </c>
-      <c r="BN10" s="29">
+      <c r="BO10" s="29">
         <v>4932</v>
       </c>
-      <c r="BO10" s="13"/>
       <c r="BP10" s="13"/>
-      <c r="BQ10" s="29"/>
-      <c r="BR10" s="13"/>
+      <c r="BQ10" s="13"/>
+      <c r="BR10" s="29"/>
       <c r="BS10" s="13"/>
       <c r="BT10" s="13"/>
       <c r="BU10" s="13"/>
-      <c r="BV10" s="13">
+      <c r="BV10" s="13"/>
+      <c r="BW10" s="13">
         <f t="shared" si="0"/>
         <v>-87.859799999999964</v>
       </c>
-      <c r="BW10" s="13">
+      <c r="BX10" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BX10" s="13">
+      <c r="BY10" s="13">
         <f t="shared" si="3"/>
         <v>87.859799999999964</v>
       </c>
-      <c r="BY10" s="13">
-        <f>((BM10-H10)/H10)*100</f>
+      <c r="BZ10" s="13">
+        <f>((BN10-H10)/H10)*100</f>
         <v>3.434009102192801</v>
       </c>
-      <c r="BZ10">
+      <c r="CA10">
         <v>21</v>
       </c>
-      <c r="CA10">
+      <c r="CB10">
         <v>5252.38</v>
       </c>
-      <c r="CB10" s="15">
+      <c r="CC10" s="15">
         <f t="shared" si="4"/>
         <v>87.859799999999964</v>
       </c>
     </row>
-    <row r="11" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A11" s="1">
         <v>1166974</v>
       </c>
@@ -2954,96 +2998,98 @@
         <v>901.87</v>
       </c>
       <c r="I11" s="13">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="J11" s="13">
+        <v>1070</v>
+      </c>
+      <c r="K11" s="13">
         <v>1086</v>
       </c>
-      <c r="K11" s="13">
+      <c r="L11" s="13">
         <v>1054</v>
       </c>
-      <c r="L11" s="13">
+      <c r="M11" s="13">
         <v>1063</v>
       </c>
-      <c r="M11" s="13">
+      <c r="N11" s="13">
         <v>1099</v>
       </c>
-      <c r="N11" s="13">
+      <c r="O11" s="13">
         <v>1173</v>
       </c>
-      <c r="O11" s="13">
+      <c r="P11" s="13">
         <v>1114</v>
       </c>
-      <c r="P11" s="13">
+      <c r="Q11" s="13">
         <v>1075</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="R11" s="13">
         <v>1109</v>
       </c>
-      <c r="R11" s="13">
+      <c r="S11" s="13">
         <v>1090</v>
       </c>
-      <c r="S11" s="13">
+      <c r="T11" s="13">
         <v>1144</v>
       </c>
-      <c r="T11" s="13">
+      <c r="U11" s="13">
         <v>1162</v>
       </c>
-      <c r="U11" s="13">
+      <c r="V11" s="13">
         <v>1109</v>
       </c>
-      <c r="V11" s="13">
+      <c r="W11" s="13">
         <v>1029</v>
       </c>
-      <c r="W11" s="13">
+      <c r="X11" s="13">
         <v>993</v>
       </c>
-      <c r="X11" s="13">
+      <c r="Y11" s="13">
         <v>1017</v>
       </c>
-      <c r="Y11" s="13">
+      <c r="Z11" s="13">
         <v>960</v>
-      </c>
-      <c r="Z11" s="13">
-        <v>965</v>
       </c>
       <c r="AA11" s="13">
         <v>965</v>
       </c>
       <c r="AB11" s="13">
+        <v>965</v>
+      </c>
+      <c r="AC11" s="13">
         <v>951.7</v>
       </c>
-      <c r="AC11" s="13">
+      <c r="AD11" s="13">
         <v>946</v>
       </c>
-      <c r="AD11" s="13">
+      <c r="AE11" s="13">
         <v>869.2</v>
       </c>
-      <c r="AE11" s="13">
+      <c r="AF11" s="13">
         <v>865</v>
       </c>
-      <c r="AF11" s="13">
+      <c r="AG11" s="13">
         <v>851</v>
       </c>
-      <c r="AG11" s="13">
+      <c r="AH11" s="13">
         <v>829.3</v>
       </c>
-      <c r="AH11" s="13">
+      <c r="AI11" s="13">
         <v>830</v>
       </c>
-      <c r="AI11" s="13">
+      <c r="AJ11" s="13">
         <v>810</v>
       </c>
-      <c r="AJ11" s="13">
+      <c r="AK11" s="13">
         <v>812.8</v>
       </c>
-      <c r="AK11" s="13">
+      <c r="AL11" s="13">
         <v>788</v>
       </c>
-      <c r="AL11" s="13">
+      <c r="AM11" s="13">
         <v>772</v>
       </c>
-      <c r="AM11" s="13"/>
       <c r="AN11" s="13"/>
       <c r="AO11" s="13"/>
       <c r="AP11" s="13"/>
@@ -3070,33 +3116,34 @@
       <c r="BK11" s="13"/>
       <c r="BL11" s="13"/>
       <c r="BM11" s="13"/>
-      <c r="BN11" s="29"/>
-      <c r="BO11" s="13"/>
+      <c r="BN11" s="13"/>
+      <c r="BO11" s="29"/>
       <c r="BP11" s="13"/>
-      <c r="BQ11" s="29"/>
-      <c r="BR11" s="13"/>
+      <c r="BQ11" s="13"/>
+      <c r="BR11" s="29"/>
       <c r="BS11" s="13"/>
       <c r="BT11" s="13"/>
       <c r="BU11" s="13"/>
-      <c r="BV11" s="13">
+      <c r="BV11" s="13"/>
+      <c r="BW11" s="13">
         <f t="shared" si="0"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BW11" s="13">
+      <c r="BX11" s="13">
         <f t="shared" si="1"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BX11" s="13">
+      <c r="BY11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BY11" s="13"/>
-      <c r="CB11" s="15">
+      <c r="BZ11" s="13"/>
+      <c r="CC11" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A12" s="1">
         <v>1176593</v>
       </c>
@@ -3128,99 +3175,101 @@
         <v>29670</v>
       </c>
       <c r="J12" s="13">
+        <v>29670</v>
+      </c>
+      <c r="K12" s="13">
         <v>29650</v>
       </c>
-      <c r="K12" s="13">
+      <c r="L12" s="13">
         <v>28730</v>
       </c>
-      <c r="L12" s="13">
+      <c r="M12" s="13">
         <v>28240</v>
       </c>
-      <c r="M12" s="13">
+      <c r="N12" s="13">
         <v>29460</v>
       </c>
-      <c r="N12" s="13">
+      <c r="O12" s="13">
         <v>28720</v>
-      </c>
-      <c r="O12" s="13">
-        <v>27890</v>
       </c>
       <c r="P12" s="13">
         <v>27890</v>
       </c>
       <c r="Q12" s="13">
+        <v>27890</v>
+      </c>
+      <c r="R12" s="13">
         <v>30100</v>
       </c>
-      <c r="R12" s="13">
+      <c r="S12" s="13">
         <v>30500</v>
       </c>
-      <c r="S12" s="13">
+      <c r="T12" s="13">
         <v>28850</v>
       </c>
-      <c r="T12" s="13">
+      <c r="U12" s="13">
         <v>27450</v>
       </c>
-      <c r="U12" s="13">
+      <c r="V12" s="13">
         <v>26940</v>
       </c>
-      <c r="V12" s="13">
+      <c r="W12" s="13">
         <v>26800</v>
       </c>
-      <c r="W12" s="13">
+      <c r="X12" s="13">
         <v>25950</v>
       </c>
-      <c r="X12" s="13">
+      <c r="Y12" s="13">
         <v>26000</v>
       </c>
-      <c r="Y12" s="13">
+      <c r="Z12" s="13">
         <v>26600</v>
-      </c>
-      <c r="Z12" s="13">
-        <v>24630</v>
       </c>
       <c r="AA12" s="13">
         <v>24630</v>
       </c>
       <c r="AB12" s="13">
+        <v>24630</v>
+      </c>
+      <c r="AC12" s="13">
         <v>25230</v>
       </c>
-      <c r="AC12" s="13">
+      <c r="AD12" s="13">
         <v>24700</v>
       </c>
-      <c r="AD12" s="13">
+      <c r="AE12" s="13">
         <v>23780</v>
       </c>
-      <c r="AE12" s="13">
+      <c r="AF12" s="13">
         <v>23920</v>
       </c>
-      <c r="AF12" s="13">
+      <c r="AG12" s="13">
         <v>22390</v>
       </c>
-      <c r="AG12" s="13">
+      <c r="AH12" s="13">
         <v>23000</v>
       </c>
-      <c r="AH12" s="13">
+      <c r="AI12" s="13">
         <v>20990</v>
       </c>
-      <c r="AI12" s="13">
+      <c r="AJ12" s="13">
         <v>20260</v>
       </c>
-      <c r="AJ12" s="13">
+      <c r="AK12" s="13">
         <v>19200</v>
       </c>
-      <c r="AK12" s="13">
+      <c r="AL12" s="13">
         <v>19860</v>
       </c>
-      <c r="AL12" s="13">
+      <c r="AM12" s="13">
         <v>19700</v>
       </c>
-      <c r="AM12" s="13">
+      <c r="AN12" s="13">
         <v>19430</v>
       </c>
-      <c r="AN12" s="13">
+      <c r="AO12" s="13">
         <v>19020</v>
       </c>
-      <c r="AO12" s="13"/>
       <c r="AP12" s="13"/>
       <c r="AQ12" s="13"/>
       <c r="AR12" s="13"/>
@@ -3245,36 +3294,37 @@
       <c r="BK12" s="13"/>
       <c r="BL12" s="13"/>
       <c r="BM12" s="13"/>
-      <c r="BN12" s="29"/>
-      <c r="BO12" s="13"/>
+      <c r="BN12" s="13"/>
+      <c r="BO12" s="29"/>
       <c r="BP12" s="13"/>
-      <c r="BQ12" s="29"/>
-      <c r="BR12" s="13"/>
+      <c r="BQ12" s="13"/>
+      <c r="BR12" s="29"/>
       <c r="BS12" s="13"/>
       <c r="BT12" s="13"/>
       <c r="BU12" s="13"/>
-      <c r="BV12" s="13">
+      <c r="BV12" s="13"/>
+      <c r="BW12" s="13">
         <f t="shared" si="0"/>
         <v>-331.70059999999995</v>
       </c>
-      <c r="BW12" s="13">
+      <c r="BX12" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BX12" s="13"/>
       <c r="BY12" s="13"/>
-      <c r="BZ12">
+      <c r="BZ12" s="13"/>
+      <c r="CA12">
         <v>7</v>
       </c>
-      <c r="CA12">
+      <c r="CB12">
         <v>27320</v>
       </c>
-      <c r="CB12" s="15">
+      <c r="CC12" s="15">
         <f t="shared" si="4"/>
         <v>331.70059999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A13" s="1">
         <v>397018</v>
       </c>
@@ -3303,52 +3353,54 @@
         <v>840</v>
       </c>
       <c r="I13" s="13">
-        <v>788.2</v>
+        <v>790</v>
       </c>
       <c r="J13" s="13">
+        <v>790</v>
+      </c>
+      <c r="K13" s="13">
         <v>840</v>
       </c>
-      <c r="K13" s="13">
+      <c r="L13" s="13">
         <v>837.7</v>
       </c>
-      <c r="L13" s="13">
+      <c r="M13" s="13">
         <v>802</v>
       </c>
-      <c r="M13" s="13">
+      <c r="N13" s="13">
         <v>1009</v>
       </c>
-      <c r="N13" s="13">
+      <c r="O13" s="13">
         <v>1074</v>
-      </c>
-      <c r="O13" s="13">
-        <v>900</v>
       </c>
       <c r="P13" s="13">
         <v>900</v>
       </c>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13">
+      <c r="Q13" s="13">
+        <v>900</v>
+      </c>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13">
         <v>1490</v>
       </c>
-      <c r="S13" s="13">
+      <c r="T13" s="13">
         <v>1210</v>
       </c>
-      <c r="T13" s="13">
+      <c r="U13" s="13">
         <v>1100</v>
       </c>
-      <c r="U13" s="13">
+      <c r="V13" s="13">
         <v>980</v>
       </c>
-      <c r="V13" s="13">
+      <c r="W13" s="13">
         <v>932.1</v>
       </c>
-      <c r="W13" s="13">
+      <c r="X13" s="13">
         <v>822</v>
       </c>
-      <c r="X13" s="13">
+      <c r="Y13" s="13">
         <v>790</v>
       </c>
-      <c r="Y13" s="13"/>
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
       <c r="AB13" s="13"/>
@@ -3389,33 +3441,34 @@
       <c r="BK13" s="13"/>
       <c r="BL13" s="13"/>
       <c r="BM13" s="13"/>
-      <c r="BN13" s="29"/>
-      <c r="BO13" s="13"/>
+      <c r="BN13" s="13"/>
+      <c r="BO13" s="29"/>
       <c r="BP13" s="13"/>
-      <c r="BQ13" s="29"/>
-      <c r="BR13" s="13"/>
+      <c r="BQ13" s="13"/>
+      <c r="BR13" s="29"/>
       <c r="BS13" s="13"/>
       <c r="BT13" s="13"/>
       <c r="BU13" s="13"/>
-      <c r="BV13" s="13">
+      <c r="BV13" s="13"/>
+      <c r="BW13" s="13">
         <f t="shared" si="0"/>
         <v>1369.2</v>
       </c>
-      <c r="BW13" s="13">
+      <c r="BX13" s="13">
         <f t="shared" si="1"/>
         <v>420</v>
       </c>
-      <c r="BX13" s="13"/>
       <c r="BY13" s="13"/>
-      <c r="BZ13">
+      <c r="BZ13" s="13"/>
+      <c r="CA13">
         <v>113</v>
       </c>
-      <c r="CB13" s="15">
+      <c r="CC13" s="15">
         <f t="shared" si="4"/>
         <v>-949.2</v>
       </c>
     </row>
-    <row r="14" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A14" s="1">
         <v>662577</v>
       </c>
@@ -3444,222 +3497,225 @@
         <v>7204.22</v>
       </c>
       <c r="I14" s="13">
-        <v>8274</v>
+        <v>8280</v>
       </c>
       <c r="J14" s="13">
+        <v>8280</v>
+      </c>
+      <c r="K14" s="13">
         <v>8100</v>
       </c>
-      <c r="K14" s="13">
+      <c r="L14" s="13">
         <v>7922</v>
       </c>
-      <c r="L14" s="13">
+      <c r="M14" s="13">
         <v>7884</v>
       </c>
-      <c r="M14" s="13">
+      <c r="N14" s="13">
         <v>8051</v>
       </c>
-      <c r="N14" s="13">
+      <c r="O14" s="13">
         <v>7911</v>
       </c>
-      <c r="O14" s="13">
+      <c r="P14" s="13">
         <v>7833</v>
       </c>
-      <c r="P14" s="13">
+      <c r="Q14" s="13">
         <v>7687</v>
       </c>
-      <c r="Q14" s="13">
+      <c r="R14" s="13">
         <v>7672</v>
       </c>
-      <c r="R14" s="13">
+      <c r="S14" s="13">
         <v>7676</v>
       </c>
-      <c r="S14" s="13">
+      <c r="T14" s="13">
         <v>7844</v>
       </c>
-      <c r="T14" s="13">
+      <c r="U14" s="13">
         <v>7810</v>
       </c>
-      <c r="U14" s="13">
+      <c r="V14" s="13">
         <v>7710</v>
       </c>
-      <c r="V14" s="13">
+      <c r="W14" s="13">
         <v>7735</v>
       </c>
-      <c r="W14" s="13">
+      <c r="X14" s="13">
         <v>7725</v>
       </c>
-      <c r="X14" s="13">
+      <c r="Y14" s="13">
         <v>7787</v>
       </c>
-      <c r="Y14" s="13">
+      <c r="Z14" s="13">
         <v>7955</v>
-      </c>
-      <c r="Z14" s="13">
-        <v>7627</v>
       </c>
       <c r="AA14" s="13">
         <v>7627</v>
       </c>
       <c r="AB14" s="13">
+        <v>7627</v>
+      </c>
+      <c r="AC14" s="13">
         <v>7656</v>
       </c>
-      <c r="AC14" s="13">
+      <c r="AD14" s="13">
         <v>7507</v>
       </c>
-      <c r="AD14" s="13">
+      <c r="AE14" s="13">
         <v>7590</v>
       </c>
-      <c r="AE14" s="13">
+      <c r="AF14" s="13">
         <v>7569</v>
       </c>
-      <c r="AF14" s="13">
+      <c r="AG14" s="13">
         <v>7269</v>
       </c>
-      <c r="AG14" s="13">
+      <c r="AH14" s="13">
         <v>7444</v>
       </c>
-      <c r="AH14" s="13">
+      <c r="AI14" s="13">
         <v>7205</v>
       </c>
-      <c r="AI14" s="13">
+      <c r="AJ14" s="13">
         <v>7298</v>
       </c>
-      <c r="AJ14" s="13">
+      <c r="AK14" s="13">
         <v>7222</v>
       </c>
-      <c r="AK14" s="13">
+      <c r="AL14" s="13">
         <v>7079</v>
       </c>
-      <c r="AL14" s="13">
+      <c r="AM14" s="13">
         <v>7140</v>
       </c>
-      <c r="AM14" s="13">
+      <c r="AN14" s="13">
         <v>7440</v>
       </c>
-      <c r="AN14" s="13">
+      <c r="AO14" s="13">
         <v>7530</v>
-      </c>
-      <c r="AO14" s="13">
-        <v>7535</v>
       </c>
       <c r="AP14" s="13">
         <v>7535</v>
       </c>
       <c r="AQ14" s="13">
+        <v>7535</v>
+      </c>
+      <c r="AR14" s="13">
         <v>7568</v>
       </c>
-      <c r="AR14" s="13">
+      <c r="AS14" s="13">
         <v>7699</v>
       </c>
-      <c r="AS14" s="13">
+      <c r="AT14" s="13">
         <v>7638</v>
       </c>
-      <c r="AT14" s="13">
+      <c r="AU14" s="13">
         <v>7654</v>
       </c>
-      <c r="AU14" s="13">
+      <c r="AV14" s="13">
         <v>7584</v>
       </c>
-      <c r="AV14" s="13">
+      <c r="AW14" s="13">
         <v>7479</v>
       </c>
-      <c r="AW14" s="13">
+      <c r="AX14" s="13">
         <v>7490</v>
       </c>
-      <c r="AX14" s="13">
+      <c r="AY14" s="13">
         <v>7480</v>
       </c>
-      <c r="AY14" s="13">
+      <c r="AZ14" s="13">
         <v>7270</v>
       </c>
-      <c r="AZ14" s="13">
+      <c r="BA14" s="13">
         <v>7163</v>
       </c>
-      <c r="BA14" s="13">
+      <c r="BB14" s="13">
         <v>7231</v>
-      </c>
-      <c r="BB14" s="13">
-        <v>7100</v>
       </c>
       <c r="BC14" s="13">
         <v>7100</v>
       </c>
       <c r="BD14" s="13">
+        <v>7100</v>
+      </c>
+      <c r="BE14" s="13">
         <v>7027</v>
       </c>
-      <c r="BE14" s="13">
+      <c r="BF14" s="13">
         <v>6984</v>
       </c>
-      <c r="BF14" s="13">
+      <c r="BG14" s="13">
         <v>6944</v>
       </c>
-      <c r="BG14" s="13">
+      <c r="BH14" s="13">
         <v>6924</v>
       </c>
-      <c r="BH14" s="13">
+      <c r="BI14" s="13">
         <v>6930</v>
       </c>
-      <c r="BI14" s="13">
+      <c r="BJ14" s="13">
         <v>6938</v>
       </c>
-      <c r="BJ14" s="13">
+      <c r="BK14" s="13">
         <v>6989</v>
       </c>
-      <c r="BK14" s="13">
+      <c r="BL14" s="13">
         <v>6871</v>
       </c>
-      <c r="BL14" s="13">
+      <c r="BM14" s="13">
         <v>6943</v>
       </c>
-      <c r="BM14" s="13">
+      <c r="BN14" s="13">
         <v>7040</v>
       </c>
-      <c r="BN14" s="29">
+      <c r="BO14" s="29">
         <v>6696</v>
       </c>
-      <c r="BO14" s="13">
+      <c r="BP14" s="13">
         <v>6965</v>
       </c>
-      <c r="BP14" s="13">
+      <c r="BQ14" s="13">
         <v>6788</v>
       </c>
-      <c r="BQ14" s="29">
+      <c r="BR14" s="29">
         <v>6696</v>
       </c>
-      <c r="BR14" s="13">
+      <c r="BS14" s="13">
         <v>6625</v>
       </c>
-      <c r="BS14" s="13">
+      <c r="BT14" s="13">
         <v>6660</v>
       </c>
-      <c r="BT14" s="13">
+      <c r="BU14" s="13">
         <v>6791</v>
       </c>
-      <c r="BU14" s="13">
+      <c r="BV14" s="13">
         <v>6610</v>
       </c>
-      <c r="BV14" s="13">
+      <c r="BW14" s="13">
         <f t="shared" si="0"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BW14" s="13">
+      <c r="BX14" s="13">
         <f t="shared" si="1"/>
         <v>648.37980000000005</v>
       </c>
-      <c r="BX14" s="13">
-        <f t="shared" ref="BX14" si="5">(BW14-BV14)</f>
+      <c r="BY14" s="13">
+        <f t="shared" ref="BY14" si="5">(BX14-BW14)</f>
         <v>0</v>
       </c>
-      <c r="BY14" s="13">
-        <f>((BM14-H14)/H14)*100</f>
+      <c r="BZ14" s="13">
+        <f>((BN14-H14)/H14)*100</f>
         <v>-2.2794972946411995</v>
       </c>
-      <c r="CB14" s="15">
+      <c r="CC14" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A15" s="1">
         <v>5137534</v>
       </c>
@@ -3688,90 +3744,92 @@
         <v>11598.87</v>
       </c>
       <c r="I15" s="13">
-        <v>13033</v>
+        <v>12979</v>
       </c>
       <c r="J15" s="13">
+        <v>12979</v>
+      </c>
+      <c r="K15" s="13">
         <v>13244</v>
       </c>
-      <c r="K15" s="13">
+      <c r="L15" s="13">
         <v>12628.12</v>
       </c>
-      <c r="L15" s="13">
+      <c r="M15" s="13">
         <v>11710.62</v>
       </c>
-      <c r="M15" s="13">
+      <c r="N15" s="13">
         <v>12145</v>
       </c>
-      <c r="N15" s="13">
+      <c r="O15" s="13">
         <v>11855.12</v>
-      </c>
-      <c r="O15" s="13">
-        <v>11946.75</v>
       </c>
       <c r="P15" s="13">
         <v>11946.75</v>
       </c>
       <c r="Q15" s="13">
-        <v>14679.12</v>
+        <v>11946.75</v>
       </c>
       <c r="R15" s="13">
         <v>14679.12</v>
       </c>
       <c r="S15" s="13">
+        <v>14679.12</v>
+      </c>
+      <c r="T15" s="13">
         <v>13968</v>
       </c>
-      <c r="T15" s="13">
+      <c r="U15" s="13">
         <v>15528.12</v>
       </c>
-      <c r="U15" s="13">
+      <c r="V15" s="13">
         <v>14358.25</v>
       </c>
-      <c r="V15" s="13">
+      <c r="W15" s="13">
         <v>14385.75</v>
       </c>
-      <c r="W15" s="13">
+      <c r="X15" s="13">
         <v>13880</v>
       </c>
-      <c r="X15" s="13">
+      <c r="Y15" s="13">
         <v>13610.62</v>
       </c>
-      <c r="Y15" s="13">
+      <c r="Z15" s="13">
         <v>13016</v>
       </c>
-      <c r="Z15" s="13">
+      <c r="AA15" s="13">
         <v>12487.37</v>
       </c>
-      <c r="AA15" s="13">
+      <c r="AB15" s="13">
         <v>12638.62</v>
       </c>
-      <c r="AB15" s="13">
+      <c r="AC15" s="13">
         <v>12533.87</v>
       </c>
-      <c r="AC15" s="13">
+      <c r="AD15" s="13">
         <v>11299.5</v>
       </c>
-      <c r="AD15" s="13">
+      <c r="AE15" s="13">
         <v>11193.12</v>
       </c>
-      <c r="AE15" s="13">
+      <c r="AF15" s="13">
         <v>11548.62</v>
       </c>
-      <c r="AF15" s="13">
+      <c r="AG15" s="13">
         <v>11125.62</v>
       </c>
-      <c r="AG15" s="13">
+      <c r="AH15" s="13">
         <v>10932.12</v>
       </c>
-      <c r="AH15" s="13">
+      <c r="AI15" s="13">
         <v>11095.62</v>
       </c>
-      <c r="AI15" s="13">
+      <c r="AJ15" s="13">
         <v>10910.58</v>
       </c>
-      <c r="AJ15" s="13">
+      <c r="AK15" s="13">
         <v>11609.37</v>
       </c>
-      <c r="AK15" s="13"/>
       <c r="AL15" s="13"/>
       <c r="AM15" s="13"/>
       <c r="AN15" s="13"/>
@@ -3781,8 +3839,8 @@
       <c r="AR15" s="13"/>
       <c r="AS15" s="13"/>
       <c r="AT15" s="13"/>
-      <c r="AU15" s="14"/>
-      <c r="AV15" s="13"/>
+      <c r="AU15" s="13"/>
+      <c r="AV15" s="14"/>
       <c r="AW15" s="13"/>
       <c r="AX15" s="13"/>
       <c r="AY15" s="13"/>
@@ -3800,36 +3858,37 @@
       <c r="BK15" s="13"/>
       <c r="BL15" s="13"/>
       <c r="BM15" s="13"/>
-      <c r="BN15" s="29"/>
-      <c r="BO15" s="13"/>
+      <c r="BN15" s="13"/>
+      <c r="BO15" s="29"/>
       <c r="BP15" s="13"/>
-      <c r="BQ15" s="29"/>
-      <c r="BR15" s="13"/>
+      <c r="BQ15" s="13"/>
+      <c r="BR15" s="29"/>
       <c r="BS15" s="13"/>
       <c r="BT15" s="13"/>
       <c r="BU15" s="13"/>
-      <c r="BV15" s="13">
+      <c r="BV15" s="13"/>
+      <c r="BW15" s="13">
         <f t="shared" si="0"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BW15" s="13">
+      <c r="BX15" s="13">
         <f t="shared" si="1"/>
         <v>927.90960000000007</v>
       </c>
-      <c r="BX15" s="13">
-        <f t="shared" ref="BX15:BX18" si="6">(BW15-BV15)</f>
+      <c r="BY15" s="13">
+        <f t="shared" ref="BY15:BY18" si="6">(BX15-BW15)</f>
         <v>0</v>
       </c>
-      <c r="BY15" s="13">
-        <f>((BM15-H15)/H15)*100</f>
+      <c r="BZ15" s="13">
+        <f>((BN15-H15)/H15)*100</f>
         <v>-100</v>
       </c>
-      <c r="CB15" s="15">
+      <c r="CC15" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A16" s="1">
         <v>5135470</v>
       </c>
@@ -3858,228 +3917,231 @@
         <v>199.49</v>
       </c>
       <c r="I16" s="13">
-        <v>216.71</v>
+        <v>219.37</v>
       </c>
       <c r="J16" s="13">
+        <v>219.37</v>
+      </c>
+      <c r="K16" s="13">
         <v>216</v>
-      </c>
-      <c r="K16" s="13">
-        <v>216.57</v>
       </c>
       <c r="L16" s="13">
         <v>216.57</v>
       </c>
       <c r="M16" s="13">
+        <v>216.57</v>
+      </c>
+      <c r="N16" s="13">
         <v>221.02</v>
       </c>
-      <c r="N16" s="13">
+      <c r="O16" s="13">
         <v>218.38</v>
       </c>
-      <c r="O16" s="13">
+      <c r="P16" s="13">
         <v>218.36</v>
       </c>
-      <c r="P16" s="13">
+      <c r="Q16" s="13">
         <v>223.13</v>
       </c>
-      <c r="Q16" s="13">
+      <c r="R16" s="13">
         <v>227.54</v>
       </c>
-      <c r="R16" s="13">
+      <c r="S16" s="13">
         <v>226.96</v>
       </c>
-      <c r="S16" s="13">
+      <c r="T16" s="13">
         <v>225.24</v>
       </c>
-      <c r="T16" s="13">
+      <c r="U16" s="13">
         <v>223.25</v>
-      </c>
-      <c r="U16" s="13">
-        <v>219.14</v>
       </c>
       <c r="V16" s="13">
         <v>219.14</v>
       </c>
       <c r="W16" s="13">
+        <v>219.14</v>
+      </c>
+      <c r="X16" s="13">
         <v>219.3</v>
       </c>
-      <c r="X16" s="13">
+      <c r="Y16" s="13">
         <v>222.79</v>
       </c>
-      <c r="Y16" s="13">
+      <c r="Z16" s="13">
         <v>221.16</v>
       </c>
-      <c r="Z16" s="13">
+      <c r="AA16" s="13">
         <v>220.66</v>
       </c>
-      <c r="AA16" s="13">
+      <c r="AB16" s="13">
         <v>222.06</v>
       </c>
-      <c r="AB16" s="13">
+      <c r="AC16" s="13">
         <v>218.71</v>
       </c>
-      <c r="AC16" s="13">
+      <c r="AD16" s="13">
         <v>216.74</v>
       </c>
-      <c r="AD16" s="13">
+      <c r="AE16" s="13">
         <v>216.04</v>
-      </c>
-      <c r="AE16" s="13">
-        <v>210.69</v>
       </c>
       <c r="AF16" s="13">
         <v>210.69</v>
       </c>
       <c r="AG16" s="13">
+        <v>210.69</v>
+      </c>
+      <c r="AH16" s="13">
         <v>198</v>
       </c>
-      <c r="AH16" s="13">
+      <c r="AI16" s="13">
         <v>196.74</v>
       </c>
-      <c r="AI16" s="13">
+      <c r="AJ16" s="13">
         <v>192.56</v>
       </c>
-      <c r="AJ16" s="13">
+      <c r="AK16" s="13">
         <v>192.23</v>
       </c>
-      <c r="AK16" s="13">
+      <c r="AL16" s="13">
         <v>191.19</v>
       </c>
-      <c r="AL16" s="13">
+      <c r="AM16" s="13">
         <v>193.62</v>
       </c>
-      <c r="AM16" s="13">
+      <c r="AN16" s="13">
         <v>190.75</v>
       </c>
-      <c r="AN16" s="13">
+      <c r="AO16" s="13">
         <v>189.06</v>
-      </c>
-      <c r="AO16" s="13">
-        <v>182.73</v>
       </c>
       <c r="AP16" s="13">
         <v>182.73</v>
       </c>
       <c r="AQ16" s="13">
+        <v>182.73</v>
+      </c>
+      <c r="AR16" s="13">
         <v>177.92</v>
       </c>
-      <c r="AR16" s="13">
+      <c r="AS16" s="13">
         <v>179.16</v>
       </c>
-      <c r="AS16" s="13">
+      <c r="AT16" s="13">
         <v>179.34</v>
-      </c>
-      <c r="AT16" s="13">
-        <v>176.5</v>
       </c>
       <c r="AU16" s="13">
         <v>176.5</v>
       </c>
       <c r="AV16" s="13">
+        <v>176.5</v>
+      </c>
+      <c r="AW16" s="13">
         <v>175.93</v>
       </c>
-      <c r="AW16" s="13">
+      <c r="AX16" s="13">
         <v>174.51</v>
       </c>
-      <c r="AX16" s="13">
+      <c r="AY16" s="13">
         <v>173.91</v>
       </c>
-      <c r="AY16" s="13">
+      <c r="AZ16" s="13">
         <v>177.1</v>
       </c>
-      <c r="AZ16" s="13">
+      <c r="BA16" s="13">
         <v>178.24</v>
       </c>
-      <c r="BA16" s="13">
+      <c r="BB16" s="13">
         <v>176.52</v>
       </c>
-      <c r="BB16" s="13">
+      <c r="BC16" s="13">
         <v>178.27</v>
       </c>
-      <c r="BC16" s="13">
+      <c r="BD16" s="13">
         <v>175.29</v>
       </c>
-      <c r="BD16" s="13">
+      <c r="BE16" s="13">
         <v>175.34</v>
       </c>
-      <c r="BE16" s="13">
+      <c r="BF16" s="13">
         <v>174.41</v>
       </c>
-      <c r="BF16" s="13">
+      <c r="BG16" s="13">
         <v>176.22</v>
       </c>
-      <c r="BG16" s="13">
+      <c r="BH16" s="13">
         <v>174</v>
       </c>
-      <c r="BH16" s="13">
+      <c r="BI16" s="13">
         <v>176.35</v>
       </c>
-      <c r="BI16" s="13">
+      <c r="BJ16" s="13">
         <v>177.71</v>
       </c>
-      <c r="BJ16" s="13">
+      <c r="BK16" s="13">
         <v>180.08</v>
       </c>
-      <c r="BK16" s="13">
+      <c r="BL16" s="13">
         <v>181.96</v>
       </c>
-      <c r="BL16" s="13">
+      <c r="BM16" s="13">
         <v>182.9</v>
       </c>
-      <c r="BM16" s="13">
+      <c r="BN16" s="13">
         <v>181.86</v>
       </c>
-      <c r="BN16" s="29">
+      <c r="BO16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BO16" s="13">
+      <c r="BP16" s="13">
         <v>181.07</v>
       </c>
-      <c r="BP16" s="13">
+      <c r="BQ16" s="13">
         <v>182.56</v>
       </c>
-      <c r="BQ16" s="29">
+      <c r="BR16" s="29">
         <v>182.56</v>
       </c>
-      <c r="BR16" s="13">
+      <c r="BS16" s="13">
         <v>178.86</v>
       </c>
-      <c r="BS16" s="13">
+      <c r="BT16" s="13">
         <v>180.16</v>
       </c>
-      <c r="BT16" s="13">
+      <c r="BU16" s="13">
         <v>179.56</v>
       </c>
-      <c r="BU16" s="13">
+      <c r="BV16" s="13">
         <v>176.55</v>
       </c>
-      <c r="BV16" s="13">
+      <c r="BW16" s="13">
         <f t="shared" si="0"/>
         <v>1413.1220000000008</v>
       </c>
-      <c r="BW16" s="13">
+      <c r="BX16" s="13">
         <f t="shared" si="1"/>
         <v>997.45</v>
       </c>
-      <c r="BX16" s="13">
+      <c r="BY16" s="13">
         <f t="shared" si="6"/>
         <v>-415.67200000000071</v>
       </c>
-      <c r="BY16" s="13">
-        <f>((BM16-H16)/H16)*100</f>
+      <c r="BZ16" s="13">
+        <f>((BN16-H16)/H16)*100</f>
         <v>-8.8375357160759904</v>
       </c>
-      <c r="BZ16">
+      <c r="CA16">
         <v>1864</v>
       </c>
-      <c r="CA16">
+      <c r="CB16">
         <v>177.19</v>
       </c>
-      <c r="CB16" s="15">
+      <c r="CC16" s="15">
         <f t="shared" si="4"/>
         <v>-415.67200000000071</v>
       </c>
     </row>
-    <row r="17" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A17" s="1">
         <v>5134135</v>
       </c>
@@ -4114,13 +4176,13 @@
         <v>181.5</v>
       </c>
       <c r="K17" s="13">
+        <v>181.5</v>
+      </c>
+      <c r="L17" s="13">
         <v>177.17</v>
       </c>
-      <c r="L17" s="13">
+      <c r="M17" s="13">
         <v>186.88</v>
-      </c>
-      <c r="M17" s="13">
-        <v>184.42</v>
       </c>
       <c r="N17" s="13">
         <v>184.42</v>
@@ -4129,13 +4191,13 @@
         <v>184.42</v>
       </c>
       <c r="P17" s="13">
+        <v>184.42</v>
+      </c>
+      <c r="Q17" s="13">
         <v>199.37</v>
       </c>
-      <c r="Q17" s="13">
+      <c r="R17" s="13">
         <v>194.88</v>
-      </c>
-      <c r="R17" s="13">
-        <v>189.51</v>
       </c>
       <c r="S17" s="13">
         <v>189.51</v>
@@ -4144,13 +4206,13 @@
         <v>189.51</v>
       </c>
       <c r="U17" s="13">
-        <v>185.52</v>
+        <v>189.51</v>
       </c>
       <c r="V17" s="13">
         <v>185.52</v>
       </c>
       <c r="W17" s="13">
-        <v>178.98</v>
+        <v>185.52</v>
       </c>
       <c r="X17" s="13">
         <v>178.98</v>
@@ -4159,7 +4221,7 @@
         <v>178.98</v>
       </c>
       <c r="Z17" s="13">
-        <v>170.7</v>
+        <v>178.98</v>
       </c>
       <c r="AA17" s="13">
         <v>170.7</v>
@@ -4168,10 +4230,10 @@
         <v>170.7</v>
       </c>
       <c r="AC17" s="13">
+        <v>170.7</v>
+      </c>
+      <c r="AD17" s="13">
         <v>170.45</v>
-      </c>
-      <c r="AD17" s="13">
-        <v>160.84</v>
       </c>
       <c r="AE17" s="13">
         <v>160.84</v>
@@ -4180,15 +4242,17 @@
         <v>160.84</v>
       </c>
       <c r="AG17" s="13">
+        <v>160.84</v>
+      </c>
+      <c r="AH17" s="13">
         <v>159.02000000000001</v>
-      </c>
-      <c r="AH17" s="13">
-        <v>159.65</v>
       </c>
       <c r="AI17" s="13">
         <v>159.65</v>
       </c>
-      <c r="AJ17" s="13"/>
+      <c r="AJ17" s="13">
+        <v>159.65</v>
+      </c>
       <c r="AK17" s="13"/>
       <c r="AL17" s="13"/>
       <c r="AM17" s="13"/>
@@ -4218,36 +4282,37 @@
       <c r="BK17" s="13"/>
       <c r="BL17" s="13"/>
       <c r="BM17" s="13"/>
-      <c r="BN17" s="29"/>
-      <c r="BO17" s="13"/>
+      <c r="BN17" s="13"/>
+      <c r="BO17" s="29"/>
       <c r="BP17" s="13"/>
-      <c r="BQ17" s="29"/>
-      <c r="BR17" s="13"/>
+      <c r="BQ17" s="13"/>
+      <c r="BR17" s="29"/>
       <c r="BS17" s="13"/>
       <c r="BT17" s="13"/>
       <c r="BU17" s="13"/>
-      <c r="BV17" s="13">
+      <c r="BV17" s="13"/>
+      <c r="BW17" s="13">
         <f t="shared" si="0"/>
         <v>957.9</v>
       </c>
-      <c r="BW17" s="13">
+      <c r="BX17" s="13">
         <f t="shared" si="1"/>
         <v>957.9</v>
       </c>
-      <c r="BX17" s="13">
-        <f t="shared" ref="BX17" si="7">(BW17-BV17)</f>
+      <c r="BY17" s="13">
+        <f t="shared" ref="BY17" si="7">(BX17-BW17)</f>
         <v>0</v>
       </c>
-      <c r="BY17" s="13">
-        <f>((BM17-H17)/H17)*100</f>
+      <c r="BZ17" s="13">
+        <f>((BN17-H17)/H17)*100</f>
         <v>-100</v>
       </c>
-      <c r="CB17" s="15">
+      <c r="CC17" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A18" s="1">
         <v>1168723</v>
       </c>
@@ -4276,93 +4341,95 @@
         <v>1434</v>
       </c>
       <c r="I18" s="13">
-        <v>1894</v>
+        <v>1891</v>
       </c>
       <c r="J18" s="13">
+        <v>1891</v>
+      </c>
+      <c r="K18" s="13">
         <v>1864</v>
       </c>
-      <c r="K18" s="13">
+      <c r="L18" s="13">
         <v>1823</v>
       </c>
-      <c r="L18" s="13">
+      <c r="M18" s="13">
         <v>1819</v>
       </c>
-      <c r="M18" s="13">
+      <c r="N18" s="13">
         <v>1866</v>
       </c>
-      <c r="N18" s="13">
+      <c r="O18" s="13">
         <v>1886</v>
       </c>
-      <c r="O18" s="13">
+      <c r="P18" s="13">
         <v>1818</v>
       </c>
-      <c r="P18" s="13">
+      <c r="Q18" s="13">
         <v>1785</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="R18" s="13">
         <v>1828</v>
       </c>
-      <c r="R18" s="13">
+      <c r="S18" s="13">
         <v>1811</v>
       </c>
-      <c r="S18" s="13">
+      <c r="T18" s="13">
         <v>1825</v>
       </c>
-      <c r="T18" s="13">
+      <c r="U18" s="13">
         <v>1831</v>
       </c>
-      <c r="U18" s="13">
+      <c r="V18" s="13">
         <v>1799</v>
       </c>
-      <c r="V18" s="13">
+      <c r="W18" s="13">
         <v>1757</v>
       </c>
-      <c r="W18" s="13">
+      <c r="X18" s="13">
         <v>1698</v>
       </c>
-      <c r="X18" s="13">
+      <c r="Y18" s="13">
         <v>1694</v>
       </c>
-      <c r="Y18" s="13">
+      <c r="Z18" s="13">
         <v>1671</v>
-      </c>
-      <c r="Z18" s="13">
-        <v>1660</v>
       </c>
       <c r="AA18" s="13">
         <v>1660</v>
       </c>
       <c r="AB18" s="13">
+        <v>1660</v>
+      </c>
+      <c r="AC18" s="13">
         <v>1646</v>
       </c>
-      <c r="AC18" s="13">
+      <c r="AD18" s="13">
         <v>1648</v>
       </c>
-      <c r="AD18" s="13">
+      <c r="AE18" s="13">
         <v>1614</v>
       </c>
-      <c r="AE18" s="13">
+      <c r="AF18" s="13">
         <v>1626</v>
       </c>
-      <c r="AF18" s="13">
+      <c r="AG18" s="13">
         <v>1587</v>
       </c>
-      <c r="AG18" s="13">
+      <c r="AH18" s="13">
         <v>1548</v>
       </c>
-      <c r="AH18" s="13">
+      <c r="AI18" s="13">
         <v>1500</v>
       </c>
-      <c r="AI18" s="13">
+      <c r="AJ18" s="13">
         <v>1491</v>
       </c>
-      <c r="AJ18" s="13">
+      <c r="AK18" s="13">
         <v>1444</v>
       </c>
-      <c r="AK18" s="13">
+      <c r="AL18" s="13">
         <v>1431</v>
       </c>
-      <c r="AL18" s="13"/>
       <c r="AM18" s="13"/>
       <c r="AN18" s="13"/>
       <c r="AO18" s="13"/>
@@ -4388,64 +4455,65 @@
       <c r="BI18" s="13"/>
       <c r="BJ18" s="13"/>
       <c r="BK18" s="13"/>
-      <c r="BL18" s="13">
-        <v>1788</v>
-      </c>
+      <c r="BL18" s="13"/>
       <c r="BM18" s="13">
         <v>1788</v>
       </c>
-      <c r="BN18" s="29">
+      <c r="BN18" s="13">
+        <v>1788</v>
+      </c>
+      <c r="BO18" s="29">
         <v>1780</v>
       </c>
-      <c r="BO18" s="13">
+      <c r="BP18" s="13">
         <v>1814</v>
       </c>
-      <c r="BP18" s="13">
+      <c r="BQ18" s="13">
         <v>1794</v>
       </c>
-      <c r="BQ18" s="29">
+      <c r="BR18" s="29">
         <v>1780</v>
       </c>
-      <c r="BR18" s="13">
+      <c r="BS18" s="13">
         <v>1772</v>
       </c>
-      <c r="BS18" s="13">
+      <c r="BT18" s="13">
         <v>1798</v>
       </c>
-      <c r="BT18" s="13">
+      <c r="BU18" s="13">
         <v>1806</v>
       </c>
-      <c r="BU18" s="13">
+      <c r="BV18" s="13">
         <v>1801</v>
       </c>
-      <c r="BV18" s="13">
+      <c r="BW18" s="13">
         <f t="shared" si="0"/>
         <v>292.79999999999995</v>
       </c>
-      <c r="BW18" s="13">
+      <c r="BX18" s="13">
         <f t="shared" si="1"/>
         <v>645.29999999999995</v>
       </c>
-      <c r="BX18" s="13">
+      <c r="BY18" s="13">
         <f t="shared" si="6"/>
         <v>352.5</v>
       </c>
-      <c r="BY18" s="13">
-        <f>((BM18-H18)/H18)*100</f>
+      <c r="BZ18" s="13">
+        <f>((BN18-H18)/H18)*100</f>
         <v>24.686192468619247</v>
       </c>
-      <c r="BZ18">
+      <c r="CA18">
         <v>100</v>
       </c>
-      <c r="CA18">
+      <c r="CB18">
         <v>1786.5</v>
       </c>
-      <c r="CB18" s="15">
+      <c r="CC18" s="15">
         <f t="shared" si="4"/>
         <v>352.5</v>
       </c>
     </row>
-    <row r="19" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A19" s="1">
         <v>1122654</v>
       </c>
@@ -4474,30 +4542,32 @@
         <v>93.13</v>
       </c>
       <c r="I19" s="13">
-        <v>75</v>
+        <v>74.5</v>
       </c>
       <c r="J19" s="13">
+        <v>74.5</v>
+      </c>
+      <c r="K19" s="13">
         <v>67.900000000000006</v>
       </c>
-      <c r="K19" s="13">
+      <c r="L19" s="13">
         <v>71.3</v>
       </c>
-      <c r="L19" s="13">
+      <c r="M19" s="13">
         <v>72.099999999999994</v>
       </c>
-      <c r="M19" s="13">
+      <c r="N19" s="13">
         <v>86.7</v>
-      </c>
-      <c r="N19" s="13">
-        <v>91.5</v>
       </c>
       <c r="O19" s="13">
         <v>91.5</v>
       </c>
       <c r="P19" s="13">
+        <v>91.5</v>
+      </c>
+      <c r="Q19" s="13">
         <v>132.6</v>
       </c>
-      <c r="Q19" s="13"/>
       <c r="R19" s="13"/>
       <c r="S19" s="13"/>
       <c r="T19" s="13"/>
@@ -4513,22 +4583,22 @@
       <c r="AD19" s="13"/>
       <c r="AE19" s="13"/>
       <c r="AF19" s="13"/>
-      <c r="AG19" s="13">
+      <c r="AG19" s="13"/>
+      <c r="AH19" s="13">
         <v>6461</v>
       </c>
-      <c r="AH19" s="13">
+      <c r="AI19" s="13">
         <v>6503</v>
       </c>
-      <c r="AI19" s="13">
+      <c r="AJ19" s="13">
         <v>6535</v>
       </c>
-      <c r="AJ19" s="13">
+      <c r="AK19" s="13">
         <v>6532</v>
       </c>
-      <c r="AK19" s="13">
+      <c r="AL19" s="13">
         <v>6515</v>
       </c>
-      <c r="AL19" s="13"/>
       <c r="AM19" s="13"/>
       <c r="AN19" s="13"/>
       <c r="AO19" s="13"/>
@@ -4556,33 +4626,34 @@
       <c r="BK19" s="13"/>
       <c r="BL19" s="13"/>
       <c r="BM19" s="13"/>
-      <c r="BN19" s="29"/>
-      <c r="BO19" s="13"/>
+      <c r="BN19" s="13"/>
+      <c r="BO19" s="29"/>
       <c r="BP19" s="13"/>
-      <c r="BQ19" s="29"/>
-      <c r="BR19" s="13"/>
+      <c r="BQ19" s="13"/>
+      <c r="BR19" s="29"/>
       <c r="BS19" s="13"/>
       <c r="BT19" s="13"/>
       <c r="BU19" s="13"/>
-      <c r="BV19" s="13">
+      <c r="BV19" s="13"/>
+      <c r="BW19" s="13">
         <f t="shared" si="0"/>
         <v>279.39</v>
       </c>
-      <c r="BW19" s="13">
+      <c r="BX19" s="13">
         <f t="shared" si="1"/>
         <v>279.39</v>
       </c>
-      <c r="BX19" s="13"/>
       <c r="BY19" s="13"/>
-      <c r="BZ19">
+      <c r="BZ19" s="13"/>
+      <c r="CA19">
         <v>7</v>
       </c>
-      <c r="CA19">
+      <c r="CB19">
         <v>6461</v>
       </c>
-      <c r="CB19" s="15"/>
-    </row>
-    <row r="20" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="CC19" s="15"/>
+    </row>
+    <row r="20" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A20" s="1">
         <v>363010</v>
       </c>
@@ -4611,24 +4682,26 @@
         <v>74.900000000000006</v>
       </c>
       <c r="I20" s="13">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="J20" s="13">
+        <v>77.3</v>
+      </c>
+      <c r="K20" s="13">
         <v>82.3</v>
       </c>
-      <c r="K20" s="13">
+      <c r="L20" s="13">
         <v>75.2</v>
       </c>
-      <c r="L20" s="13">
+      <c r="M20" s="13">
         <v>68.8</v>
       </c>
-      <c r="M20" s="13">
+      <c r="N20" s="13">
         <v>89</v>
       </c>
-      <c r="N20" s="13">
+      <c r="O20" s="13">
         <v>87.5</v>
       </c>
-      <c r="O20" s="13"/>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
@@ -4679,28 +4752,29 @@
       <c r="BK20" s="13"/>
       <c r="BL20" s="13"/>
       <c r="BM20" s="13"/>
-      <c r="BN20" s="29"/>
-      <c r="BO20" s="13"/>
+      <c r="BN20" s="13"/>
+      <c r="BO20" s="29"/>
       <c r="BP20" s="13"/>
-      <c r="BQ20" s="29"/>
-      <c r="BR20" s="13"/>
+      <c r="BQ20" s="13"/>
+      <c r="BR20" s="29"/>
       <c r="BS20" s="13"/>
       <c r="BT20" s="13"/>
       <c r="BU20" s="13"/>
-      <c r="BV20" s="13">
+      <c r="BV20" s="13"/>
+      <c r="BW20" s="13">
         <f t="shared" si="0"/>
         <v>449.4</v>
       </c>
-      <c r="BW20" s="13">
+      <c r="BX20" s="13">
         <f t="shared" si="1"/>
         <v>449.4</v>
       </c>
-      <c r="BX20" s="13"/>
       <c r="BY20" s="13"/>
-      <c r="CB20" s="15"/>
-    </row>
-    <row r="21" spans="1:80" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="1:80" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BZ20" s="13"/>
+      <c r="CC20" s="15"/>
+    </row>
+    <row r="21" spans="1:81" ht="14.4" thickBot="1"/>
+    <row r="22" spans="1:81" ht="45" customHeight="1" thickBot="1">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -4766,11 +4840,11 @@
       <c r="BK22" s="13"/>
       <c r="BL22" s="13"/>
       <c r="BM22" s="13"/>
-      <c r="BN22" s="29"/>
-      <c r="BO22" s="13"/>
+      <c r="BN22" s="13"/>
+      <c r="BO22" s="29"/>
       <c r="BP22" s="13"/>
-      <c r="BQ22" s="29"/>
-      <c r="BR22" s="13"/>
+      <c r="BQ22" s="13"/>
+      <c r="BR22" s="29"/>
       <c r="BS22" s="13"/>
       <c r="BT22" s="13"/>
       <c r="BU22" s="13"/>
@@ -4778,9 +4852,10 @@
       <c r="BW22" s="13"/>
       <c r="BX22" s="13"/>
       <c r="BY22" s="13"/>
-      <c r="CB22" s="15"/>
-    </row>
-    <row r="23" spans="1:80" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BZ22" s="13"/>
+      <c r="CC22" s="15"/>
+    </row>
+    <row r="23" spans="1:81" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -4793,103 +4868,103 @@
       <c r="H23" s="13"/>
       <c r="I23" s="23">
         <f>(G2*I2+G3*I3+G4*I4+G5*I5+G6*I6+G7*I7+G8*I8+I9*G9+G10*I10+I11*G11+G12*I12+G13*I13+G14*I14+I15*G15+I16*G16+G17*I17+G18*I18+G19*I19+G20*I20)/100</f>
-        <v>15091.768</v>
+        <v>15077.946000000002</v>
       </c>
       <c r="J23" s="23">
         <f>(J2*G2+G3*J3+J4*G4+G5*J5+G6*J6+G7*J7+G8*J8+G9*J9+G10*J10+G11*J11+G12*J12+J13*G13+G14*J14+J15*G15+G16*J16+G17*J17+J18*G18+G19*J19+G20*J20)/100</f>
-        <v>14740.416000000001</v>
+        <v>15077.946000000002</v>
       </c>
       <c r="K23" s="23">
         <f>(K2*G2+G3*K3+K4*G4+G5*K5+G6*K6+G7*K7+G8*K8+G9*K9+G10*K10+G11*K11+G12*K12+K13*G13+G14*K14+K15*G15+G16*K16+G17*K17+K18*G18+G19*K19+G20*K20)/100</f>
-        <v>13542.3416</v>
+        <v>14740.416000000001</v>
       </c>
       <c r="L23" s="23">
         <f>(L2*G2+G3*L3+L4*G4+G5*L5+G6*L6+G7*L7+G8*L8+G9*L9+G10*L10+G11*L11+G12*L12+L13*G13+G14*L14+L15*G15+G16*L16+G17*L17+L18*G18+G19*L19+G20*L20)/100</f>
-        <v>13393.131599999999</v>
+        <v>13542.3416</v>
       </c>
       <c r="M23" s="23">
         <f>(M2*G2+G3*M3+M4*G4+G5*M5+G6*M6+G7*M7+G8*M8+G9*M9+G10*M10+G11*M11+G12*M12+M13*G13+G14*M14+M15*G15+G16*M16+G17*M17+M18*G18+G19*M19+G20*M20)/100</f>
-        <v>14000.1</v>
+        <v>13393.131599999999</v>
       </c>
       <c r="N23" s="23">
         <f>(N2*G2+G3*N3+N4*G4+G5*N5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+N13*G13+G14*N14+N15*G15+G16*N16+G17*N17+N18*G18+G19*N19+G20*N20)/100</f>
-        <v>14050.569599999999</v>
+        <v>14000.1</v>
       </c>
       <c r="O23" s="23">
         <f>(O2*G2+G3*O3+O4*G4+G5*O5+G6*O6+G7*O7+G8*O8+G9*O9+G10*O10+G11*O11+G12*O12+O13*G13+G14*O14+O15*G15+G16*O16+G17*O17+O18*G18+G19*O19+G20*O20)/100</f>
+        <v>14050.569599999999</v>
+      </c>
+      <c r="P23" s="23">
+        <f>(P2*G2+G3*P3+P4*G4+G5*P5+G6*P6+G7*P7+G8*P8+G9*P9+G10*P10+G11*P11+G12*P12+P13*G13+G14*P14+P15*G15+G16*P16+G17*P17+P18*G18+G19*P19+G20*P20)/100</f>
         <v>13213.011999999999</v>
-      </c>
-      <c r="P23" s="23">
-        <f>(P2*G2+G3*P3+P4*G4+G5*P5+G6*P6+G7*P7+G8*P8+G9*P9+G10*P10+G11*P11+G12*P12+P13*G13+G14*P14+P15*G15+G16*P16+G17*P17+P18*G18+G19*P19)/100</f>
-        <v>13254.46</v>
       </c>
       <c r="Q23" s="23">
         <f>(Q2*G2+G3*Q3+Q4*G4+G5*Q5+G6*Q6+G7*Q7+G8*Q8+G9*Q9+G10*Q10+G11*Q11+G12*Q12+Q13*G13+G14*Q14+Q15*G15+G16*Q16+G17*Q17+Q18*G18+G19*Q19)/100</f>
-        <v>12995.1896</v>
+        <v>13254.46</v>
       </c>
       <c r="R23" s="23">
         <f>(R2*G2+G3*R3+R4*G4+G5*R5+G6*R6+G7*R7+G8*R8+G9*R9+G10*R10+G11*R11+G12*R12+R13*G13+G14*R14+R15*G15+G16*R16+G17*R17+R18*G18+G19*R19)/100</f>
-        <v>13575.9856</v>
+        <v>12995.1896</v>
       </c>
       <c r="S23" s="23">
         <f>(S2*G2+G3*S3+S4*G4+G5*S5+G6*S6+G7*S7+G8*S8+G9*S9+G10*S10+G11*S11+G12*S12+S13*G13+G14*S14+S15*G15+G16*S16+G17*S17+S18*G18+G19*S19)/100</f>
-        <v>13490.918</v>
+        <v>13575.9856</v>
       </c>
       <c r="T23" s="23">
         <f>(T2*G2+G3*T3+T4*G4+G5*T5+G6*T6+G7*T7+G8*T8+G9*T9+G10*T10+G11*T11+G12*T12+T13*G13+G14*T14+T15*G15+G16*T16+G17*T17+T18*G18+G19*T19)/100</f>
-        <v>13594.723600000001</v>
+        <v>13490.918</v>
       </c>
       <c r="U23" s="23">
         <f>(U2*G2+G3*U3+U4*G4+G5*U5+G6*U6+G7*U7+G8*U8+G9*U9+G10*U10+G11*U11+G12*U12+U13*G13+G14*U14+U15*G15+G16*U16+G17*U17+U18*G18+G19*U19)/100</f>
-        <v>13195.503999999999</v>
+        <v>13594.723600000001</v>
       </c>
       <c r="V23" s="23">
         <f>(V2*G2+G3*V3+V4*G4+G5*V5+G6*V6+G7*V7+G8*V8+G9*V9+G10*V10+G11*V11+G12*V12+V13*G13+G14*V14+V15*G15+G16*V16+G17*V17+V18*G18+G19*V19)/100</f>
-        <v>12910.01</v>
+        <v>13195.503999999999</v>
       </c>
       <c r="W23" s="23">
         <f>(W2*G2+G3*W3+W4*G4+G5*W5+G6*W6+G7*W7+G8*W8+G9*W9+G10*W10+G11*W11+G12*W12+W13*G13+G14*W14+W15*G15+G16*W16+G17*W17+W18*G18+G19*W19)/100</f>
-        <v>12606.761999999999</v>
+        <v>12910.01</v>
       </c>
       <c r="X23" s="23">
         <f>(X2*G2+G3*X3+X4*G4+G5*X5+G6*X6+G7*X7+G8*X8+G9*X9+G10*X10+G11*X11+G12*X12+X13*G13+G14*X14+X15*G15+G16*X16+G17*X17+X18*G18+G19*X19)/100</f>
+        <v>12606.761999999999</v>
+      </c>
+      <c r="Y23" s="23">
+        <f>(Y2*G2+G3*Y3+Y4*G4+G5*Y5+G6*Y6+G7*Y7+G8*Y8+G9*Y9+G10*Y10+G11*Y11+G12*Y12+Y13*G13+G14*Y14+Y15*G15+G16*Y16+G17*Y17+Y18*G18+G19*Y19)/100</f>
         <v>12711.777599999999</v>
-      </c>
-      <c r="Y23" s="23">
-        <f>(Y3*G3+G4*Y4+Y5*G5+G6*Y6+G7*Y7+G8*Y8+G9*Y9+G10*Y10+G11*Y11+G12*Y12+G14*Y14+Y15*G15+G16*Y16+Y17*G17+G18*Y18+G19*Y19)/100</f>
-        <v>12191.99</v>
       </c>
       <c r="Z23" s="23">
         <f>(Z3*G3+G4*Z4+Z5*G5+G6*Z6+G7*Z7+G8*Z8+G9*Z9+G10*Z10+G11*Z11+G12*Z12+G14*Z14+Z15*G15+G16*Z16+Z17*G17+G18*Z18+G19*Z19)/100</f>
-        <v>11970.357599999999</v>
+        <v>12191.99</v>
       </c>
       <c r="AA23" s="23">
         <f>(AA3*G3+G4*AA4+AA5*G5+G6*AA6+G7*AA7+G8*AA8+G9*AA9+G10*AA10+G11*AA11+G12*AA12+G14*AA14+AA15*G15+G16*AA16+AA17*G17+G18*AA18+G19*AA19)/100</f>
-        <v>11989.4576</v>
+        <v>11970.357599999999</v>
       </c>
       <c r="AB23" s="23">
         <f>(AB3*G3+G4*AB4+AB5*G5+G6*AB6+G7*AB7+G8*AB8+G9*AB9+G10*AB10+G11*AB11+G12*AB12+G14*AB14+AB15*G15+G16*AB16+AB17*G17+G18*AB18+G19*AB19)/100</f>
-        <v>11896.177600000001</v>
+        <v>11989.4576</v>
       </c>
       <c r="AC23" s="23">
         <f>(AC3*G3+G4*AC4+AC5*G5+G6*AC6+G7*AC7+G8*AC8+G9*AC9+G10*AC10+G11*AC11+G12*AC12+G14*AC14+AC15*G15+G16*AC16+AC17*G17+G18*AC18+G19*AC19)/100</f>
-        <v>11552.98</v>
+        <v>11896.177600000001</v>
       </c>
       <c r="AD23" s="23">
         <f>(AD3*G3+G4*AD4+AD5*G5+G6*AD6+G7*AD7+G8*AD8+G9*AD9+G10*AD10+G11*AD11+G12*AD12+G14*AD14+AD15*G15+G16*AD16+AD17*G17+G18*AD18+G19*AD19)/100</f>
-        <v>11467.277599999999</v>
+        <v>11552.98</v>
       </c>
       <c r="AE23" s="23">
         <f>(AE3*G3+G4*AE4+AE5*G5+G6*AE6+G7*AE7+G8*AE8+G9*AE9+G10*AE10+G11*AE11+G12*AE12+G14*AE14+AE15*G15+G16*AE16+AE17*G17+G18*AE18+G19*AE19)/100</f>
+        <v>11467.277599999999</v>
+      </c>
+      <c r="AF23" s="23">
+        <f>(AF3*G3+G4*AF4+AF5*G5+G6*AF6+G7*AF7+G8*AF8+G9*AF9+G10*AF10+G11*AF11+G12*AF12+G14*AF14+AF15*G15+G16*AF16+AF17*G17+G18*AF18+G19*AF19)/100</f>
         <v>10332.035599999999</v>
       </c>
-      <c r="AF23" s="23">
-        <f>(AF5*G5+G6*AF6+AF7*G7+G8*AF8+G9*AF9+G10*AF10+G11*AF11+G12*AF12+G14*AF14+G20*AF20+G15*AF15+AF16*G16+G17*AF17+AF18*G18+G19*AF19)/100</f>
+      <c r="AG23" s="23">
+        <f>(AG5*G5+G6*AG6+AG7*G7+G8*AG8+G9*AG9+G10*AG10+G11*AG11+G12*AG12+G14*AG14+G20*AG20+G15*AG15+AG16*G16+G17*AG17+AG18*G18+G19*AG19)/100</f>
         <v>9234.9995999999992</v>
-      </c>
-      <c r="AG23" s="23" t="e">
-        <f>(AG5*G5+G7*AG7+AG8*G8+G9*AG9+#REF!*#REF!+G10*AG10+G11*AG11+G12*AG12+G14*AG14+G19*AG19+G20*AG20+AG6*G6+G15*AG15+#REF!*#REF!+G16*AG16+G17*AG17+AG18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AG3+#REF!*#REF!)/100</f>
-        <v>#REF!</v>
       </c>
       <c r="AH23" s="23" t="e">
         <f>(AH5*G5+G7*AH7+AH8*G8+G9*AH9+#REF!*#REF!+G10*AH10+G11*AH11+G12*AH12+G14*AH14+G19*AH19+G20*AH20+AH6*G6+G15*AH15+#REF!*#REF!+G16*AH16+G17*AH17+AH18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AH3+#REF!*#REF!)/100</f>
@@ -4900,11 +4975,11 @@
         <v>#REF!</v>
       </c>
       <c r="AJ23" s="23" t="e">
-        <f>(AJ5*G5+G7*AJ7+AJ8*G8+G9*AJ9+#REF!*#REF!+G10*AJ10+G11*AJ11+G12*AJ12+G14*AJ14+G19*AJ19+G20*AJ20+AJ6*G6+G15*AJ15+#REF!*#REF!+G16*AJ16+G18*AJ18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AJ3+#REF!*#REF!+G4*AJ4)/100</f>
+        <f>(AJ5*G5+G7*AJ7+AJ8*G8+G9*AJ9+#REF!*#REF!+G10*AJ10+G11*AJ11+G12*AJ12+G14*AJ14+G19*AJ19+G20*AJ20+AJ6*G6+G15*AJ15+#REF!*#REF!+G16*AJ16+G17*AJ17+AJ18*G18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AJ3+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AK23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AK3*G3+#REF!*#REF!+G4*AK4+G5*AK5+G7*AK7+G8*AK8+G9*AK9+#REF!*#REF!+G10*AK10+AK11*G11+G12*AK12+AK14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AK20+AK6*G6+#REF!*#REF!+G16*AK16+G18*AK18+G19*AK19)/100</f>
+        <f>(AK5*G5+G7*AK7+AK8*G8+G9*AK9+#REF!*#REF!+G10*AK10+G11*AK11+G12*AK12+G14*AK14+G19*AK19+G20*AK20+AK6*G6+G15*AK15+#REF!*#REF!+G16*AK16+G18*AK18+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G3*AK3+#REF!*#REF!+G4*AK4)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AL23" s="23" t="e">
@@ -4912,7 +4987,7 @@
         <v>#REF!</v>
       </c>
       <c r="AM23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AM3*G3+#REF!*#REF!+G4*AM4+G5*AM5+AM7*G7+AM8*G8+AM9*G9+#REF!*#REF!+G10*AM10+AM11*G11+G12*AM12+AM14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AM20+G6*AM6+#REF!*#REF!+G16*AM16+G18*AM18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AM3*G3+#REF!*#REF!+G4*AM4+G5*AM5+G7*AM7+G8*AM8+G9*AM9+#REF!*#REF!+G10*AM10+AM11*G11+G12*AM12+AM14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AM20+AM6*G6+#REF!*#REF!+G16*AM16+G18*AM18+G19*AM19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AN23" s="23" t="e">
@@ -4920,19 +4995,19 @@
         <v>#REF!</v>
       </c>
       <c r="AO23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G8*AO8+AO9*G9+#REF!*#REF!+AO10*G10+G11*AO11+G14*AO14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AO6+#REF!*#REF!+G16*AO16+G18*AO18+G7*AO7+G5*AO5+G12*AO12+G20*AO20)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AO3*G3+#REF!*#REF!+G4*AO4+G5*AO5+AO7*G7+AO8*G8+AO9*G9+#REF!*#REF!+G10*AO10+AO11*G11+G12*AO12+AO14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G20*AO20+G6*AO6+#REF!*#REF!+G16*AO16+G18*AO18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AP23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+AP9*G9+#REF!*#REF!+AP10*G10+G11*AP11+G14*AP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AP6+#REF!*#REF!+G16*AP16+G18*AP18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AP3*G3+#REF!*#REF!+G4*AP4+G8*AP8+AP9*G9+#REF!*#REF!+AP10*G10+G11*AP11+G14*AP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AP6+#REF!*#REF!+G16*AP16+G18*AP18+G7*AP7+G5*AP5+G12*AP12+G20*AP20)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AQ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AQ3*G3+#REF!*#REF!+G4*AQ4+G8*AQ8+G9*AQ9+#REF!*#REF!+G10*AQ10+AQ11*G11+AQ14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AQ6*G6+#REF!*#REF!+G16*AQ16+G18*AQ18+G19*AQ19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AQ3*G3+#REF!*#REF!+G4*AQ4+G8*AQ8+AQ9*G9+#REF!*#REF!+AQ10*G10+G11*AQ11+G14*AQ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AQ6+#REF!*#REF!+G16*AQ16+G18*AQ18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AR23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AR3*G3+#REF!*#REF!+G4*AR4+G8*AR8+AR9*G9+#REF!*#REF!+AR10*G10+G11*AR11+G14*AR14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AR6+#REF!*#REF!+G16*AR16+G18*AR18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AR3*G3+#REF!*#REF!+G4*AR4+G8*AR8+G9*AR9+#REF!*#REF!+G10*AR10+AR11*G11+AR14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+AR6*G6+#REF!*#REF!+G16*AR16+G18*AR18+G19*AR19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AS23" s="23" t="e">
@@ -4940,7 +5015,7 @@
         <v>#REF!</v>
       </c>
       <c r="AT23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AT3*G3+#REF!*#REF!+G4*AT4+G8*AT8+AT9*G9+AT10*G10+AT11*G11+G14*AT14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AT6+#REF!*#REF!+G16*AT16+G18*AT18+G19*AT19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AT3*G3+#REF!*#REF!+G4*AT4+G8*AT8+AT9*G9+#REF!*#REF!+AT10*G10+G11*AT11+G14*AT14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AT6+#REF!*#REF!+G16*AT16+G18*AT18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AU23" s="23" t="e">
@@ -4960,19 +5035,19 @@
         <v>#REF!</v>
       </c>
       <c r="AY23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AY3*G3+#REF!*#REF!+G4*AY4+G8*AY8+AY9*G9+AY10*G10+AY11*G11+G14*AY14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AY6+#REF!*#REF!+G16*AY16+G18*AY18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AY3*G3+#REF!*#REF!+G4*AY4+G8*AY8+AY9*G9+AY10*G10+AY11*G11+G14*AY14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AY6+#REF!*#REF!+G16*AY16+G18*AY18+G19*AY19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="AZ23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+AZ3*G3+#REF!*#REF!+G4*AZ4+G8*AZ8+AZ10*G10+AZ11*G11+G14*AZ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AZ6+#REF!*#REF!+G16*AZ16+G18*AZ18)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+AZ3*G3+#REF!*#REF!+G4*AZ4+G8*AZ8+AZ9*G9+AZ10*G10+AZ11*G11+G14*AZ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*AZ6+#REF!*#REF!+G16*AZ16+G18*AZ18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BA23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BA3*G3+#REF!*#REF!+G4*BA4+G8*BA8+G10*BA10+BA11*G11+BA14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BA6*G6+#REF!*#REF!+G16*BA16+G18*BA18+G19*BA19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BA3*G3+#REF!*#REF!+G4*BA4+G8*BA8+BA10*G10+BA11*G11+G14*BA14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BA6+#REF!*#REF!+G16*BA16+G18*BA18)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BB23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BB3*G3+#REF!*#REF!+G4*BB4+G10*BB10+BB11*G11+BB14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BB6*G6+#REF!*#REF!+G16*BB16+G18*BB18+G19*BB19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BB3*G3+#REF!*#REF!+G4*BB4+G8*BB8+G10*BB10+BB11*G11+BB14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BB6*G6+#REF!*#REF!+G16*BB16+G18*BB18+G19*BB19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BC23" s="23" t="e">
@@ -4984,7 +5059,7 @@
         <v>#REF!</v>
       </c>
       <c r="BE23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BE3*G3+#REF!*#REF!+G4*BE4+G10*BE10+BE11*G11+BE14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BE6*G6+G16*BE16+G18*BE18+G19*BE19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BE3*G3+#REF!*#REF!+G4*BE4+G10*BE10+BE11*G11+BE14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BE6*G6+#REF!*#REF!+G16*BE16+G18*BE18+G19*BE19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BF23" s="23" t="e">
@@ -5012,15 +5087,15 @@
         <v>#REF!</v>
       </c>
       <c r="BL23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BL3*G3+#REF!*#REF!+G4*BL4+G10*BL10+G11*BL11+G14*BL14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BL6+BL16*G16+G18*BL18+G19*BL19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BL3*G3+#REF!*#REF!+G4*BL4+G10*BL10+BL11*G11+BL14*G14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+BL6*G6+G16*BL16+G18*BL18+G19*BL19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BM23" s="23" t="e">
-        <f>(#REF!*#REF!+#REF!*#REF!+BM3*G3+#REF!*#REF!+G4*BM4+G10*BM10+G14*BM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BM6+BM16*G16+G18*BM18+G19*BM19)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BM3*G3+#REF!*#REF!+G4*BM4+G10*BM10+G11*BM11+G14*BM14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BM6+BM16*G16+G18*BM18+G19*BM19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BN23" s="23" t="e">
-        <f>(#REF!*#REF!+BN3*G3+G4*BN4+G14*BN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BN6+BN16*G16+G18*BN18+G19*BN19+G22*BN22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+#REF!*#REF!+BN3*G3+#REF!*#REF!+G4*BN4+G10*BN10+G14*BN14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BN6+BN16*G16+G18*BN18+G19*BN19)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BO23" s="23" t="e">
@@ -5031,16 +5106,16 @@
         <f>(#REF!*#REF!+BP3*G3+G4*BP4+G14*BP14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BP6+BP16*G16+G18*BP18+G19*BP19+G22*BP22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BQ23" s="30" t="e">
+      <c r="BQ23" s="23" t="e">
         <f>(#REF!*#REF!+BQ3*G3+G4*BQ4+G14*BQ14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BQ6+BQ16*G16+G18*BQ18+G19*BQ19+G22*BQ22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BR23" s="23" t="e">
+      <c r="BR23" s="30" t="e">
         <f>(#REF!*#REF!+BR3*G3+G4*BR4+G14*BR14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BR6+BR16*G16+G18*BR18+G19*BR19+G22*BR22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BS23" s="23" t="e">
-        <f>(#REF!*#REF!+BS3*G3+G14*BS14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BS6+BS16*G16+G18*BS18+G19*BS19+G22*BS22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <f>(#REF!*#REF!+BS3*G3+G4*BS4+G14*BS14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BS6+BS16*G16+G18*BS18+G19*BS19+G22*BS22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
       <c r="BT23" s="23" t="e">
@@ -5051,15 +5126,19 @@
         <f>(#REF!*#REF!+BU3*G3+G14*BU14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BU6+BU16*G16+G18*BU18+G19*BU19+G22*BU22+#REF!*#REF!+#REF!*#REF!)/100</f>
         <v>#REF!</v>
       </c>
-      <c r="BV23" s="13"/>
+      <c r="BV23" s="23" t="e">
+        <f>(#REF!*#REF!+BV3*G3+G14*BV14+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+#REF!*#REF!+G6*BV6+BV16*G16+G18*BV18+G19*BV19+G22*BV22+#REF!*#REF!+#REF!*#REF!)/100</f>
+        <v>#REF!</v>
+      </c>
       <c r="BW23" s="13"/>
       <c r="BX23" s="13"/>
       <c r="BY23" s="13"/>
-      <c r="CB23" s="15">
+      <c r="BZ23" s="13"/>
+      <c r="CC23" s="15">
         <v>1414.68</v>
       </c>
     </row>
-    <row r="24" spans="1:80" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:81" ht="44.25" customHeight="1" thickBot="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -5133,29 +5212,30 @@
       <c r="BS24" s="14"/>
       <c r="BT24" s="14"/>
       <c r="BU24" s="14"/>
-      <c r="BV24" s="23">
-        <f>SUM(BV2:BV20)</f>
-        <v>14171.0344</v>
-      </c>
+      <c r="BV24" s="14"/>
       <c r="BW24" s="23">
         <f>SUM(BW2:BW20)</f>
+        <v>14171.0344</v>
+      </c>
+      <c r="BX24" s="23">
+        <f>SUM(BX2:BX20)</f>
         <v>13544.4228</v>
       </c>
-      <c r="BX24" s="24">
-        <f>BW24-BV24</f>
+      <c r="BY24" s="24">
+        <f>BX24-BW24</f>
         <v>-626.61160000000018</v>
       </c>
-      <c r="BY24" s="13">
-        <f>((BW24-BV24)/BV24)*100</f>
+      <c r="BZ24" s="13">
+        <f>((BX24-BW24)/BW24)*100</f>
         <v>-4.4217774250833815</v>
       </c>
-      <c r="CB24" s="15">
-        <f>SUM(CB5:CB23)</f>
+      <c r="CC24" s="15">
+        <f>SUM(CC5:CC23)</f>
         <v>788.0683999999992</v>
       </c>
     </row>
-    <row r="25" spans="1:80" x14ac:dyDescent="0.25">
-      <c r="BV25" s="15">
+    <row r="25" spans="1:81">
+      <c r="BW25" s="15">
         <v>12034.32</v>
       </c>
     </row>
@@ -5213,17 +5293,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DECD697-7590-4F64-9E15-0FA62A69A078}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="7" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="1" width="17.59765625" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="7" width="17.59765625" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="10" max="10" width="9.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>11</v>
       </c>
@@ -5256,7 +5336,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אייראנג'י טק</v>
@@ -5282,7 +5362,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>857.5</v>
+        <v>846.8</v>
       </c>
       <c r="J2" s="25"/>
       <c r="L2" s="21">
@@ -5294,7 +5374,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -5320,7 +5400,7 @@
       <c r="G3" s="17"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="J3" s="26"/>
       <c r="L3" s="21">
@@ -5332,7 +5412,7 @@
         <v>1151.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -5358,7 +5438,7 @@
       <c r="G4" s="17"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6032</v>
+        <v>6011</v>
       </c>
       <c r="J4" s="26"/>
       <c r="L4" s="21">
@@ -5370,7 +5450,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -5395,7 +5475,7 @@
       </c>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>649.6</v>
+        <v>642.20000000000005</v>
       </c>
       <c r="J5" s="26"/>
       <c r="L5" s="21">
@@ -5407,7 +5487,7 @@
         <v>741.25</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -5432,7 +5512,7 @@
       </c>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>5041</v>
+        <v>5059</v>
       </c>
       <c r="J6" s="26"/>
       <c r="L6" s="21">
@@ -5444,7 +5524,7 @@
         <v>5480</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -5482,7 +5562,7 @@
         <v>4350</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -5519,7 +5599,7 @@
         <v>48125</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -5556,7 +5636,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -5593,7 +5673,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -5619,7 +5699,7 @@
       <c r="G11" s="18"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -5630,7 +5710,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -5668,7 +5748,7 @@
         <v>28871.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -5694,7 +5774,7 @@
       <c r="G13" s="18"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>788.2</v>
+        <v>790</v>
       </c>
       <c r="J13" s="26"/>
       <c r="L13" s="21">
@@ -5706,7 +5786,7 @@
         <v>1002.5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -5732,7 +5812,7 @@
       <c r="G14" s="17"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8274</v>
+        <v>8280</v>
       </c>
       <c r="J14" s="26"/>
       <c r="L14" s="21">
@@ -5744,7 +5824,7 @@
         <v>8700</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -5770,7 +5850,7 @@
       <c r="G15" s="17"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>13033</v>
+        <v>12979</v>
       </c>
       <c r="J15" s="26"/>
       <c r="L15" s="21">
@@ -5782,7 +5862,7 @@
         <v>15095</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -5808,7 +5888,7 @@
       <c r="G16" s="17"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216.71</v>
+        <v>219.37</v>
       </c>
       <c r="J16" s="26"/>
       <c r="L16" s="21">
@@ -5820,7 +5900,7 @@
         <v>243.25</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -5858,7 +5938,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -5884,7 +5964,7 @@
       <c r="G18" s="18"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1894</v>
+        <v>1891</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -5895,7 +5975,7 @@
         <v>2053.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -5921,7 +6001,7 @@
       <c r="G19" s="18"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>75</v>
+        <v>74.5</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -5932,7 +6012,7 @@
         <v>93.25</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17" t="str">
         <f>'התיק העדכני'!E20</f>
         <v>אירודרום קבוצה</v>
@@ -5958,7 +6038,7 @@
       <c r="G20" s="19"/>
       <c r="I20" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="L20" s="21">
         <f>(E20+CHATGPT!E20+PERPLIXITY!E20+DEEPSEEK!E20)/4</f>
@@ -5969,7 +6049,7 @@
         <v>96.75</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17">
         <f>'התיק העדכני'!E21</f>
         <v>0</v>
@@ -6003,7 +6083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17">
         <f>'התיק העדכני'!E22</f>
         <v>0</v>
@@ -6037,7 +6117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17">
         <f>'התיק העדכני'!A23</f>
@@ -6068,7 +6148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17">
         <f>'התיק העדכני'!E24</f>
         <v>0</v>
@@ -6102,7 +6182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6136,7 +6216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6170,7 +6250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17" t="e">
         <f>'התיק העדכני'!#REF!</f>
         <v>#REF!</v>
@@ -6204,7 +6284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17" t="str">
         <f>'התיק העדכני'!E20</f>
         <v>אירודרום קבוצה</v>
@@ -6226,7 +6306,7 @@
       <c r="G28" s="19"/>
       <c r="I28" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="J28" s="26"/>
       <c r="L28" s="21">
@@ -6246,15 +6326,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7390F3B9-AE45-44AE-B4DF-D92B58EB94BD}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="7" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="7" width="17.59765625" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -6284,7 +6364,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אייראנג'י טק</v>
@@ -6310,7 +6390,7 @@
       <c r="G2" s="17"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>857.5</v>
+        <v>846.8</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+GEMINI!E2+PERPLIXITY!E2+DEEPSEEK!E2)/4</f>
@@ -6321,7 +6401,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -6347,7 +6427,7 @@
       <c r="G3" s="7"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+GEMINI!E3+PERPLIXITY!E3+DEEPSEEK!E3)/4</f>
@@ -6358,7 +6438,7 @@
         <v>1151.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -6384,7 +6464,7 @@
       <c r="G4" s="7"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6032</v>
+        <v>6011</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+GEMINI!E4+PERPLIXITY!E4+DEEPSEEK!E4)/4</f>
@@ -6395,7 +6475,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -6421,7 +6501,7 @@
       <c r="G5" s="7"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>649.6</v>
+        <v>642.20000000000005</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+GEMINI!E5+PERPLIXITY!E5+DEEPSEEK!E5)/4</f>
@@ -6432,7 +6512,7 @@
         <v>741.25</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -6458,7 +6538,7 @@
       <c r="G6" s="7"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>5041</v>
+        <v>5059</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+GEMINI!E6+PERPLIXITY!E6+DEEPSEEK!E6)/4</f>
@@ -6469,7 +6549,7 @@
         <v>5480</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -6506,7 +6586,7 @@
         <v>4350</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -6543,7 +6623,7 @@
         <v>48125</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -6580,7 +6660,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -6617,7 +6697,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -6643,7 +6723,7 @@
       <c r="G11" s="8"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+GEMINI!E11+PERPLIXITY!E11+DEEPSEEK!E11)/4</f>
@@ -6654,7 +6734,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -6691,7 +6771,7 @@
         <v>28871.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -6717,7 +6797,7 @@
       <c r="G13" s="8"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>788.2</v>
+        <v>790</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+GEMINI!E13+PERPLIXITY!E13+DEEPSEEK!E13)/4</f>
@@ -6728,7 +6808,7 @@
         <v>1002.5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -6754,7 +6834,7 @@
       <c r="G14" s="7"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8274</v>
+        <v>8280</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+GEMINI!E14+PERPLIXITY!E14+DEEPSEEK!E14)/4</f>
@@ -6765,7 +6845,7 @@
         <v>8700</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -6791,7 +6871,7 @@
       <c r="G15" s="7"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>13033</v>
+        <v>12979</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+GEMINI!E15+PERPLIXITY!E15+DEEPSEEK!E15)/4</f>
@@ -6802,7 +6882,7 @@
         <v>15095</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -6828,7 +6908,7 @@
       <c r="G16" s="7"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216.71</v>
+        <v>219.37</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+GEMINI!E16+PERPLIXITY!E16+DEEPSEEK!E16)/4</f>
@@ -6839,7 +6919,7 @@
         <v>243.25</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -6876,7 +6956,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -6902,7 +6982,7 @@
       <c r="G18" s="8"/>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1894</v>
+        <v>1891</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+GEMINI!E18+PERPLIXITY!E18+DEEPSEEK!E18)/4</f>
@@ -6913,7 +6993,7 @@
         <v>2053.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -6939,7 +7019,7 @@
       <c r="G19" s="8"/>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>75</v>
+        <v>74.5</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+GEMINI!E19+PERPLIXITY!E19+DEEPSEEK!E19)/4</f>
@@ -6950,7 +7030,7 @@
         <v>93.25</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17" t="str">
         <f>'התיק העדכני'!E20</f>
         <v>אירודרום קבוצה</v>
@@ -6976,7 +7056,7 @@
       <c r="G20" s="8"/>
       <c r="I20" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="L20" s="21">
         <f>(E20+GEMINI!E20+PERPLIXITY!E20+DEEPSEEK!E20)/4</f>
@@ -6987,7 +7067,7 @@
         <v>96.75</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17">
         <f>'התיק העדכני'!E21</f>
         <v>0</v>
@@ -7011,7 +7091,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -7023,7 +7103,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -7035,7 +7115,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -7047,7 +7127,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -7059,7 +7139,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -7071,7 +7151,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -7083,7 +7163,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -7103,15 +7183,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E88497C0-21A8-47C7-B959-3D6DF74EF6E2}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="6" width="17.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="6" width="17.59765625" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -7141,7 +7221,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אייראנג'י טק</v>
@@ -7167,7 +7247,7 @@
       <c r="G2" s="10"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>857.5</v>
+        <v>846.8</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+GEMINI!E2+DEEPSEEK!E2)/4</f>
@@ -7178,7 +7258,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -7204,7 +7284,7 @@
       <c r="G3" s="10"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+GEMINI!E3+DEEPSEEK!E3)/4</f>
@@ -7215,7 +7295,7 @@
         <v>1151.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -7241,7 +7321,7 @@
       <c r="G4" s="10"/>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6032</v>
+        <v>6011</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+GEMINI!E4+DEEPSEEK!E4)/4</f>
@@ -7252,7 +7332,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -7278,7 +7358,7 @@
       <c r="G5" s="10"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>649.6</v>
+        <v>642.20000000000005</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+GEMINI!E5+DEEPSEEK!E5)/4</f>
@@ -7289,7 +7369,7 @@
         <v>741.25</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -7315,7 +7395,7 @@
       <c r="G6" s="10"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>5041</v>
+        <v>5059</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+GEMINI!E6+DEEPSEEK!E6)/4</f>
@@ -7326,7 +7406,7 @@
         <v>5480</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -7363,7 +7443,7 @@
         <v>4350</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -7399,7 +7479,7 @@
         <v>48125</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -7435,7 +7515,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -7471,7 +7551,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -7496,7 +7576,7 @@
       </c>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+GEMINI!E11+DEEPSEEK!E11)/4</f>
@@ -7507,7 +7587,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -7544,7 +7624,7 @@
         <v>28871.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -7570,7 +7650,7 @@
       <c r="G13" s="10"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>788.2</v>
+        <v>790</v>
       </c>
       <c r="L13" s="21">
         <f>(E13+CHATGPT!E13+GEMINI!E13+DEEPSEEK!E13)/4</f>
@@ -7581,7 +7661,7 @@
         <v>1002.5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -7607,7 +7687,7 @@
       <c r="G14" s="10"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8274</v>
+        <v>8280</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+GEMINI!E14+DEEPSEEK!E14)/4</f>
@@ -7618,7 +7698,7 @@
         <v>8700</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -7644,7 +7724,7 @@
       <c r="G15" s="10"/>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>13033</v>
+        <v>12979</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+GEMINI!E15+DEEPSEEK!E15)/4</f>
@@ -7655,7 +7735,7 @@
         <v>15095</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -7681,7 +7761,7 @@
       <c r="G16" s="10"/>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216.71</v>
+        <v>219.37</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+GEMINI!E16+DEEPSEEK!E16)/4</f>
@@ -7692,7 +7772,7 @@
         <v>243.25</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -7729,7 +7809,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -7754,7 +7834,7 @@
       </c>
       <c r="I18" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1894</v>
+        <v>1891</v>
       </c>
       <c r="L18" s="21">
         <f>(E18+CHATGPT!E18+GEMINI!E18+DEEPSEEK!E18)/4</f>
@@ -7765,7 +7845,7 @@
         <v>2053.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -7790,7 +7870,7 @@
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>75</v>
+        <v>74.5</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+GEMINI!E19+DEEPSEEK!E19)/4</f>
@@ -7801,7 +7881,7 @@
         <v>93.25</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17" t="str">
         <f>'התיק העדכני'!E20</f>
         <v>אירודרום קבוצה</v>
@@ -7827,7 +7907,7 @@
       <c r="G20" s="10"/>
       <c r="I20" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="L20" s="21">
         <f>(E20+CHATGPT!E20+GEMINI!E20+DEEPSEEK!E20)/4</f>
@@ -7838,7 +7918,7 @@
         <v>96.75</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17">
         <f>'התיק העדכני'!E21</f>
         <v>0</v>
@@ -7862,7 +7942,7 @@
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -7874,7 +7954,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -7886,7 +7966,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -7898,7 +7978,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -7910,7 +7990,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -7922,7 +8002,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -7934,7 +8014,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -7954,16 +8034,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D354D65C-237D-4544-BBD1-8A37190947C4}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="2" width="17.5703125" style="20" customWidth="1"/>
-    <col min="3" max="5" width="17.5703125" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" customWidth="1"/>
-    <col min="12" max="13" width="17.5703125" style="20" customWidth="1"/>
+    <col min="1" max="2" width="17.59765625" style="20" customWidth="1"/>
+    <col min="3" max="5" width="17.59765625" customWidth="1"/>
+    <col min="6" max="6" width="20.3984375" customWidth="1"/>
+    <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="12" max="13" width="17.59765625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -7992,7 +8072,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A2" s="17" t="str">
         <f>'התיק העדכני'!E2</f>
         <v>אייראנג'י טק</v>
@@ -8018,7 +8098,7 @@
       <c r="G2" s="31"/>
       <c r="I2" s="13">
         <f>'התיק העדכני'!I2</f>
-        <v>857.5</v>
+        <v>846.8</v>
       </c>
       <c r="L2" s="21">
         <f>(E2+CHATGPT!E2+PERPLIXITY!E2+GEMINI!E2)/4</f>
@@ -8029,7 +8109,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A3" s="17" t="str">
         <f>'התיק העדכני'!E3</f>
         <v>אקסון ויז'ן</v>
@@ -8055,7 +8135,7 @@
       <c r="G3" s="31"/>
       <c r="I3" s="13">
         <f>'התיק העדכני'!I3</f>
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="L3" s="21">
         <f>(E3+CHATGPT!E3+PERPLIXITY!E3+GEMINI!E3)/4</f>
@@ -8066,7 +8146,7 @@
         <v>1151.25</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A4" s="17" t="str">
         <f>'התיק העדכני'!E4</f>
         <v>ארית תעשיות</v>
@@ -8091,7 +8171,7 @@
       </c>
       <c r="I4" s="13">
         <f>'התיק העדכני'!I4</f>
-        <v>6032</v>
+        <v>6011</v>
       </c>
       <c r="L4" s="21">
         <f>(E4+CHATGPT!E4+PERPLIXITY!E4+GEMINI!E4)/4</f>
@@ -8102,7 +8182,7 @@
         <v>7050</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A5" s="17" t="str">
         <f>'התיק העדכני'!E5</f>
         <v>ג'ין טכנולוגיות</v>
@@ -8128,7 +8208,7 @@
       <c r="G5" s="31"/>
       <c r="I5" s="13">
         <f>'התיק העדכני'!I5</f>
-        <v>649.6</v>
+        <v>642.20000000000005</v>
       </c>
       <c r="L5" s="21">
         <f>(E5+CHATGPT!E5+PERPLIXITY!E5+GEMINI!E5)/4</f>
@@ -8139,7 +8219,7 @@
         <v>741.25</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A6" s="17" t="str">
         <f>'התיק העדכני'!E6</f>
         <v>דוראל אנרגיה</v>
@@ -8165,7 +8245,7 @@
       <c r="G6" s="31"/>
       <c r="I6" s="13">
         <f>'התיק העדכני'!I6</f>
-        <v>5041</v>
+        <v>5059</v>
       </c>
       <c r="L6" s="21">
         <f>(E6+CHATGPT!E6+PERPLIXITY!E6+GEMINI!E6)/4</f>
@@ -8176,7 +8256,7 @@
         <v>5480</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A7" s="17" t="str">
         <f>'התיק העדכני'!E7</f>
         <v>הראל סל ת"א 125</v>
@@ -8212,7 +8292,7 @@
         <v>4350</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A8" s="17" t="str">
         <f>'התיק העדכני'!E8</f>
         <v>טאואר</v>
@@ -8249,7 +8329,7 @@
         <v>48125</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="str">
         <f>'התיק העדכני'!E9</f>
         <v>טבע</v>
@@ -8286,7 +8366,7 @@
         <v>11139.75</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A10" s="17" t="str">
         <f>'התיק העדכני'!E10</f>
         <v>מור השקעות</v>
@@ -8323,7 +8403,7 @@
         <v>6091.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A11" s="17" t="str">
         <f>'התיק העדכני'!E11</f>
         <v>משק אנרגיה</v>
@@ -8349,7 +8429,7 @@
       <c r="G11" s="31"/>
       <c r="I11" s="13">
         <f>'התיק העדכני'!I11</f>
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="L11" s="21">
         <f>(E11+CHATGPT!E11+PERPLIXITY!E11+GEMINI!E11)/4</f>
@@ -8360,7 +8440,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A12" s="17" t="str">
         <f>'התיק העדכני'!E12</f>
         <v>נקסט ויז'ן</v>
@@ -8397,7 +8477,7 @@
         <v>28871.25</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A13" s="17" t="str">
         <f>'התיק העדכני'!E13</f>
         <v>עין השלישית</v>
@@ -8423,12 +8503,12 @@
       <c r="G13" s="31"/>
       <c r="I13" s="13">
         <f>'התיק העדכני'!I13</f>
-        <v>788.2</v>
+        <v>790</v>
       </c>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
     </row>
-    <row r="14" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A14" s="17" t="str">
         <f>'התיק העדכני'!E14</f>
         <v>פועלים</v>
@@ -8454,7 +8534,7 @@
       <c r="G14" s="31"/>
       <c r="I14" s="13">
         <f>'התיק העדכני'!I14</f>
-        <v>8274</v>
+        <v>8280</v>
       </c>
       <c r="L14" s="21">
         <f>(E14+CHATGPT!E14+PERPLIXITY!E14+GEMINI!E14)/4</f>
@@ -8465,7 +8545,7 @@
         <v>8700</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A15" s="17" t="str">
         <f>'התיק העדכני'!E15</f>
         <v>ISHARES MSCI GLOBAL SILVER M</v>
@@ -8490,7 +8570,7 @@
       </c>
       <c r="I15" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="L15" s="21">
         <f>(E15+CHATGPT!E15+PERPLIXITY!E15+GEMINI!E15)/4</f>
@@ -8501,7 +8581,7 @@
         <v>15095</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A16" s="17" t="str">
         <f>'התיק העדכני'!E16</f>
         <v>MTF מחקה אינדקס תעשיה ישראל</v>
@@ -8526,7 +8606,7 @@
       </c>
       <c r="I16" s="13">
         <f>'התיק העדכני'!I15</f>
-        <v>13033</v>
+        <v>12979</v>
       </c>
       <c r="L16" s="21">
         <f>(E16+CHATGPT!E16+PERPLIXITY!E16+GEMINI!E16)/4</f>
@@ -8537,7 +8617,7 @@
         <v>243.25</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A17" s="17" t="str">
         <f>'התיק העדכני'!E17</f>
         <v>MTF מחקה אינדקס Global Metals &amp; Minerals producers מנוטרלת דולר</v>
@@ -8563,7 +8643,7 @@
       <c r="G17" s="31"/>
       <c r="I17" s="13">
         <f>'התיק העדכני'!I16</f>
-        <v>216.71</v>
+        <v>219.37</v>
       </c>
       <c r="L17" s="21">
         <f>(E17+CHATGPT!E17+PERPLIXITY!E17+GEMINI!E17)/4</f>
@@ -8574,7 +8654,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A18" s="17" t="str">
         <f>'התיק העדכני'!E18</f>
         <v>MTF סל אינדקס אנרגיה מתחדשת</v>
@@ -8611,7 +8691,7 @@
         <v>2053.25</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A19" s="17" t="str">
         <f>'התיק העדכני'!E19</f>
         <v>סטורג' דרופ</v>
@@ -8636,7 +8716,7 @@
       </c>
       <c r="I19" s="13">
         <f>'התיק העדכני'!I18</f>
-        <v>1894</v>
+        <v>1891</v>
       </c>
       <c r="L19" s="21">
         <f>(E19+CHATGPT!E19+PERPLIXITY!E19+GEMINI!E19)/4</f>
@@ -8647,7 +8727,7 @@
         <v>93.25</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A20" s="17" t="str">
         <f>'התיק העדכני'!E20</f>
         <v>אירודרום קבוצה</v>
@@ -8672,7 +8752,7 @@
       </c>
       <c r="I20" s="13">
         <f>'התיק העדכני'!I19</f>
-        <v>75</v>
+        <v>74.5</v>
       </c>
       <c r="L20" s="21">
         <f>(E20+CHATGPT!E20+PERPLIXITY!E20+GEMINI!E20)/4</f>
@@ -8683,7 +8763,7 @@
         <v>96.75</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A21" s="17">
         <f>'התיק העדכני'!E21</f>
         <v>0</v>
@@ -8705,7 +8785,7 @@
       <c r="G21" s="31"/>
       <c r="I21" s="13">
         <f>'התיק העדכני'!I20</f>
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="L21" s="21">
         <f>(E21+CHATGPT!E21+PERPLIXITY!E21+GEMINI!E21)/4</f>
@@ -8716,7 +8796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A22" s="17"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -8728,7 +8808,7 @@
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
     </row>
-    <row r="23" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
@@ -8740,7 +8820,7 @@
       <c r="L23" s="21"/>
       <c r="M23" s="21"/>
     </row>
-    <row r="24" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A24" s="17"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -8752,7 +8832,7 @@
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
     </row>
-    <row r="25" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A25" s="17"/>
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
@@ -8764,7 +8844,7 @@
       <c r="L25" s="21"/>
       <c r="M25" s="21"/>
     </row>
-    <row r="26" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A26" s="17"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -8776,7 +8856,7 @@
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
     </row>
-    <row r="27" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A27" s="17"/>
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
@@ -8788,7 +8868,7 @@
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
     </row>
-    <row r="28" spans="1:13" ht="54.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="54.9" customHeight="1" thickBot="1">
       <c r="A28" s="17"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>

--- a/תיק_השקעה.xlsx
+++ b/תיק_השקעה.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/673b1203f7e82b27/מסמכים/GitHub/BURSA/BURSA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Philippe\Downloads\BURSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{C4181241-0E48-4B5D-963A-71CF514C7A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1737FF8C-896E-4A50-B168-AAF6593562C6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FDB72FA-D83B-4026-AE05-899EF001125B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FEADB7F-661E-4DDD-A848-BDAD78678BF0}"/>
   </bookViews>
   <sheets>
     <sheet name="התיק העדכני" sheetId="1" r:id="rId1"/>
@@ -24,23 +24,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="116">
   <si>
     <t>MTF מחקה אינדקס תעשיה ישראל</t>
   </si>
@@ -385,6 +374,9 @@
   </si>
   <si>
     <t>מחיר 10/02/2026</t>
+  </si>
+  <si>
+    <t>מחיר 11/02/2026</t>
   </si>
 </sst>
 </file>
@@ -394,11 +386,11 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;₪&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -407,7 +399,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -458,13 +450,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -855,9 +847,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא של Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -895,7 +887,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1001,7 +993,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1143,7 +1135,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1151,22 +1143,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86B4639-EF9D-4B16-B2C9-0D5E9C5EEC8B}">
-  <dimension ref="A1:CC25"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:CD25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="17.59765625" customWidth="1"/>
-    <col min="6" max="6" width="13.296875" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="64" width="14.8984375" customWidth="1"/>
-    <col min="65" max="74" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="13" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="13.09765625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="11" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="7.09765625" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="11.59765625" customWidth="1"/>
+    <col min="1" max="5" width="17.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="65" width="14.85546875" customWidth="1"/>
+    <col min="66" max="75" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="13" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="11" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:81" ht="45" customHeight="1" thickBot="1">
+    <row r="1" spans="1:82" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -1195,223 +1187,226 @@
         <v>6</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AM1" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="AM1" s="6" t="s">
+      <c r="AN1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AO1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AP1" s="6" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="AU1" s="6" t="s">
+      <c r="AV1" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="AV1" s="6" t="s">
+      <c r="AW1" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="AW1" s="6" t="s">
+      <c r="AX1" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="BE1" s="6" t="s">
+      <c r="BF1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="BF1" s="6" t="s">
+      <c r="BG1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="BG1" s="6" t="s">
+      <c r="BH1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="BH1" s="6" t="s">
+      <c r="BI1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="BI1" s="6" t="s">
+      <c r="BJ1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="BJ1" s="6" t="s">
+      <c r="BK1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="BK1" s="6" t="s">
+      <c r="BL1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="BL1" s="6" t="s">
+      <c r="BM1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="BM1" s="6" t="s">
+      <c r="BN1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BN1" s="6" t="s">
+      <c r="BO1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BO1" s="6" t="s">
+      <c r="BP1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="BP1" s="6" t="s">
+      <c r="BQ1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="BQ1" s="6" t="s">
+      <c r="BR1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="BR1" s="6" t="s">
+      <c r="BS1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="BS1" s="6" t="s">
+      <c r="BT1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BU1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="BU1" s="6" t="s">
+      <c r="BV1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="BV1" s="6" t="s">
+      <c r="BW1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="BW1" s="6" t="s">
+      <c r="BX1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="BX1" s="6" t="s">
+      <c r="BY1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="BY1" s="6" t="s">
+      <c r="BZ1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BZ1" s="6" t="s">
+      <c r="CA1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="CA1" s="12" t="s">
+      <c r="CB1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="CB1" s="12" t="s">
+      <c r="CC1" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="CC1" s="12" t="s">
+      <c r="CD1" s="12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:81" ht="45" customHeight="1" thickBot="1">
+    <row r="2" spans="1:82" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1105907</v>
       </c>
@@ -1440,15 +1435,17 @@
         <v>774.5</v>
       </c>
       <c r="I2" s="13">
+        <v>854.6</v>
+      </c>
+      <c r="J2" s="13">
+        <v>854.6</v>
+      </c>
+      <c r="K2" s="13">
         <v>846.8</v>
       </c>
-      <c r="J2" s="13">
-        <v>846.8</v>
-      </c>
-      <c r="K2" s="13">
+      <c r="L2" s="13">
         <v>799.8</v>
       </c>
-      <c r="L2" s="13"/>
       <c r="M2" s="13"/>
       <c r="N2" s="13"/>
       <c r="O2" s="13"/>
@@ -1462,7 +1459,7 @@
       <c r="W2" s="13"/>
       <c r="X2" s="13"/>
       <c r="Y2" s="13"/>
-      <c r="Z2" s="6"/>
+      <c r="Z2" s="13"/>
       <c r="AA2" s="6"/>
       <c r="AB2" s="6"/>
       <c r="AC2" s="6"/>
@@ -1503,30 +1500,31 @@
       <c r="BL2" s="6"/>
       <c r="BM2" s="6"/>
       <c r="BN2" s="6"/>
-      <c r="BO2" s="32"/>
-      <c r="BP2" s="6"/>
+      <c r="BO2" s="6"/>
+      <c r="BP2" s="32"/>
       <c r="BQ2" s="6"/>
-      <c r="BR2" s="32"/>
-      <c r="BS2" s="6"/>
+      <c r="BR2" s="6"/>
+      <c r="BS2" s="32"/>
       <c r="BT2" s="6"/>
       <c r="BU2" s="6"/>
       <c r="BV2" s="6"/>
-      <c r="BW2" s="13">
-        <f t="shared" ref="BW2:BW20" si="0">(G2*H2)/100-CC2</f>
+      <c r="BW2" s="6"/>
+      <c r="BX2" s="13">
+        <f t="shared" ref="BX2:BX20" si="0">(G2*H2)/100-CD2</f>
         <v>774.5</v>
       </c>
-      <c r="BX2" s="13">
-        <f t="shared" ref="BX2:BX20" si="1">(G2*H2)/100</f>
+      <c r="BY2" s="13">
+        <f t="shared" ref="BY2:BY20" si="1">(G2*H2)/100</f>
         <v>774.5</v>
       </c>
-      <c r="BY2" s="6"/>
       <c r="BZ2" s="6"/>
-      <c r="CC2" s="15">
-        <f>(CA2*CB2-CA2*H2)/100</f>
+      <c r="CA2" s="6"/>
+      <c r="CD2" s="15">
+        <f>(CB2*CC2-CB2*H2)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:81" ht="45" customHeight="1" thickBot="1">
+    <row r="3" spans="1:82" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1227552</v>
       </c>
@@ -1555,12 +1553,14 @@
         <v>950</v>
       </c>
       <c r="I3" s="13">
+        <v>871.9</v>
+      </c>
+      <c r="J3" s="13">
+        <v>871.9</v>
+      </c>
+      <c r="K3" s="13">
         <v>884</v>
       </c>
-      <c r="J3" s="13">
-        <v>884</v>
-      </c>
-      <c r="K3" s="13"/>
       <c r="L3" s="13"/>
       <c r="M3" s="13"/>
       <c r="N3" s="13"/>
@@ -1597,8 +1597,8 @@
       <c r="AS3" s="13"/>
       <c r="AT3" s="13"/>
       <c r="AU3" s="13"/>
-      <c r="AV3" s="14"/>
-      <c r="AW3" s="13"/>
+      <c r="AV3" s="13"/>
+      <c r="AW3" s="14"/>
       <c r="AX3" s="13"/>
       <c r="AY3" s="13"/>
       <c r="AZ3" s="13"/>
@@ -1616,36 +1616,37 @@
       <c r="BL3" s="13"/>
       <c r="BM3" s="13"/>
       <c r="BN3" s="13"/>
-      <c r="BO3" s="29"/>
-      <c r="BP3" s="13"/>
+      <c r="BO3" s="13"/>
+      <c r="BP3" s="29"/>
       <c r="BQ3" s="13"/>
-      <c r="BR3" s="29"/>
-      <c r="BS3" s="13"/>
+      <c r="BR3" s="13"/>
+      <c r="BS3" s="29"/>
       <c r="BT3" s="13"/>
       <c r="BU3" s="13"/>
       <c r="BV3" s="13"/>
-      <c r="BW3" s="13">
+      <c r="BW3" s="13"/>
+      <c r="BX3" s="13">
         <f t="shared" si="0"/>
         <v>285</v>
       </c>
-      <c r="BX3" s="13">
+      <c r="BY3" s="13">
         <f t="shared" si="1"/>
         <v>285</v>
       </c>
-      <c r="BY3" s="13">
-        <f>(BX3-BW3)</f>
+      <c r="BZ3" s="13">
+        <f>(BY3-BX3)</f>
         <v>0</v>
       </c>
-      <c r="BZ3" s="13">
-        <f>((BN3-H3)/H3)*100</f>
+      <c r="CA3" s="13">
+        <f>((BO3-H3)/H3)*100</f>
         <v>-100</v>
       </c>
-      <c r="CC3" s="15">
-        <f>(CA3*CB3-CA3*H3)/100</f>
+      <c r="CD3" s="15">
+        <f>(CB3*CC3-CB3*H3)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:81" ht="45" customHeight="1" thickBot="1">
+    <row r="4" spans="1:82" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>587014</v>
       </c>
@@ -1674,75 +1675,77 @@
         <v>5925</v>
       </c>
       <c r="I4" s="13">
+        <v>5891</v>
+      </c>
+      <c r="J4" s="13">
+        <v>5891</v>
+      </c>
+      <c r="K4" s="13">
         <v>6011</v>
-      </c>
-      <c r="J4" s="13">
-        <v>6011</v>
-      </c>
-      <c r="K4" s="13">
-        <v>5990</v>
       </c>
       <c r="L4" s="13">
         <v>5990</v>
       </c>
       <c r="M4" s="13">
+        <v>5990</v>
+      </c>
+      <c r="N4" s="13">
         <v>5956</v>
       </c>
-      <c r="N4" s="13">
+      <c r="O4" s="13">
         <v>6298</v>
       </c>
-      <c r="O4" s="13">
+      <c r="P4" s="13">
         <v>6295</v>
       </c>
-      <c r="P4" s="13">
+      <c r="Q4" s="13">
         <v>6370</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="R4" s="13">
         <v>6140</v>
       </c>
-      <c r="R4" s="13">
+      <c r="S4" s="13">
         <v>7252</v>
       </c>
-      <c r="S4" s="13">
+      <c r="T4" s="13">
         <v>7120</v>
       </c>
-      <c r="T4" s="13">
+      <c r="U4" s="13">
         <v>7048</v>
       </c>
-      <c r="U4" s="13">
+      <c r="V4" s="13">
         <v>6979</v>
       </c>
-      <c r="V4" s="13">
+      <c r="W4" s="13">
         <v>6680</v>
       </c>
-      <c r="W4" s="13">
+      <c r="X4" s="13">
         <v>6111</v>
       </c>
-      <c r="X4" s="13">
+      <c r="Y4" s="13">
         <v>6050</v>
       </c>
-      <c r="Y4" s="13">
+      <c r="Z4" s="13">
         <v>6169</v>
       </c>
-      <c r="Z4" s="13">
+      <c r="AA4" s="13">
         <v>6300</v>
-      </c>
-      <c r="AA4" s="13">
-        <v>6335</v>
       </c>
       <c r="AB4" s="13">
         <v>6335</v>
       </c>
       <c r="AC4" s="13">
+        <v>6335</v>
+      </c>
+      <c r="AD4" s="13">
         <v>6444</v>
-      </c>
-      <c r="AD4" s="13">
-        <v>5749</v>
       </c>
       <c r="AE4" s="13">
         <v>5749</v>
       </c>
-      <c r="AF4" s="13"/>
+      <c r="AF4" s="13">
+        <v>5749</v>
+      </c>
       <c r="AG4" s="13"/>
       <c r="AH4" s="13"/>
       <c r="AI4" s="13"/>
@@ -1777,36 +1780,37 @@
       <c r="BL4" s="13"/>
       <c r="BM4" s="13"/>
       <c r="BN4" s="13"/>
-      <c r="BO4" s="29"/>
-      <c r="BP4" s="13"/>
+      <c r="BO4" s="13"/>
+      <c r="BP4" s="29"/>
       <c r="BQ4" s="13"/>
-      <c r="BR4" s="29"/>
-      <c r="BS4" s="13"/>
+      <c r="BR4" s="13"/>
+      <c r="BS4" s="29"/>
       <c r="BT4" s="13"/>
       <c r="BU4" s="13"/>
       <c r="BV4" s="13"/>
-      <c r="BW4" s="13">
+      <c r="BW4" s="13"/>
+      <c r="BX4" s="13">
         <f t="shared" si="0"/>
         <v>1185</v>
       </c>
-      <c r="BX4" s="13">
+      <c r="BY4" s="13">
         <f t="shared" si="1"/>
         <v>1185</v>
       </c>
-      <c r="BY4" s="13">
-        <f>(BX4-BW4)</f>
+      <c r="BZ4" s="13">
+        <f>(BY4-BX4)</f>
         <v>0</v>
       </c>
-      <c r="BZ4" s="13">
-        <f>((BN4-H4)/H4)*100</f>
+      <c r="CA4" s="13">
+        <f>((BO4-H4)/H4)*100</f>
         <v>-100</v>
       </c>
-      <c r="CC4" s="15">
-        <f>(CA4*CB4-CA4*H4)/100</f>
+      <c r="CD4" s="15">
+        <f>(CB4*CC4-CB4*H4)/100</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:81" ht="45" customHeight="1" thickBot="1">
+    <row r="5" spans="1:82" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1099787</v>
       </c>
@@ -1835,105 +1839,107 @@
         <v>617.53</v>
       </c>
       <c r="I5" s="13">
+        <v>614.5</v>
+      </c>
+      <c r="J5" s="13">
+        <v>614.5</v>
+      </c>
+      <c r="K5" s="13">
         <v>642.20000000000005</v>
       </c>
-      <c r="J5" s="13">
-        <v>642.20000000000005</v>
-      </c>
-      <c r="K5" s="13">
+      <c r="L5" s="13">
         <v>656.2</v>
       </c>
-      <c r="L5" s="13">
+      <c r="M5" s="13">
         <v>622.4</v>
       </c>
-      <c r="M5" s="13">
+      <c r="N5" s="13">
         <v>594.9</v>
       </c>
-      <c r="N5" s="13">
+      <c r="O5" s="13">
         <v>638</v>
       </c>
-      <c r="O5" s="13">
+      <c r="P5" s="13">
         <v>587.5</v>
       </c>
-      <c r="P5" s="13">
+      <c r="Q5" s="13">
         <v>577.9</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="R5" s="13">
         <v>559</v>
       </c>
-      <c r="R5" s="13">
+      <c r="S5" s="13">
         <v>570</v>
       </c>
-      <c r="S5" s="13">
+      <c r="T5" s="13">
         <v>575.70000000000005</v>
       </c>
-      <c r="T5" s="13">
+      <c r="U5" s="13">
         <v>612.6</v>
       </c>
-      <c r="U5" s="13">
+      <c r="V5" s="13">
         <v>638.29999999999995</v>
       </c>
-      <c r="V5" s="13">
+      <c r="W5" s="13">
         <v>630.29999999999995</v>
       </c>
-      <c r="W5" s="13">
+      <c r="X5" s="13">
         <v>626</v>
       </c>
-      <c r="X5" s="13">
+      <c r="Y5" s="13">
         <v>595.4</v>
       </c>
-      <c r="Y5" s="13">
+      <c r="Z5" s="13">
         <v>667.1</v>
       </c>
-      <c r="Z5" s="13">
+      <c r="AA5" s="13">
         <v>651</v>
-      </c>
-      <c r="AA5" s="13">
-        <v>641.1</v>
       </c>
       <c r="AB5" s="13">
         <v>641.1</v>
       </c>
       <c r="AC5" s="13">
+        <v>641.1</v>
+      </c>
+      <c r="AD5" s="13">
         <v>607.1</v>
       </c>
-      <c r="AD5" s="13">
+      <c r="AE5" s="13">
         <v>583</v>
       </c>
-      <c r="AE5" s="13">
+      <c r="AF5" s="13">
         <v>581.6</v>
       </c>
-      <c r="AF5" s="13">
+      <c r="AG5" s="13">
         <v>578.70000000000005</v>
       </c>
-      <c r="AG5" s="13">
+      <c r="AH5" s="13">
         <v>590</v>
       </c>
-      <c r="AH5" s="13">
+      <c r="AI5" s="13">
         <v>554.70000000000005</v>
       </c>
-      <c r="AI5" s="13">
+      <c r="AJ5" s="13">
         <v>511.8</v>
       </c>
-      <c r="AJ5" s="13">
+      <c r="AK5" s="13">
         <v>487</v>
       </c>
-      <c r="AK5" s="13">
+      <c r="AL5" s="13">
         <v>478.8</v>
       </c>
-      <c r="AL5" s="13">
+      <c r="AM5" s="13">
         <v>485.5</v>
       </c>
-      <c r="AM5" s="13">
+      <c r="AN5" s="13">
         <v>453.4</v>
       </c>
-      <c r="AN5" s="13">
+      <c r="AO5" s="13">
         <v>426.1</v>
       </c>
-      <c r="AO5" s="13">
+      <c r="AP5" s="13">
         <v>423.2</v>
       </c>
-      <c r="AP5" s="13"/>
       <c r="AQ5" s="13"/>
       <c r="AR5" s="13"/>
       <c r="AS5" s="13"/>
@@ -1958,27 +1964,28 @@
       <c r="BL5" s="13"/>
       <c r="BM5" s="13"/>
       <c r="BN5" s="13"/>
-      <c r="BO5" s="29"/>
-      <c r="BP5" s="13"/>
+      <c r="BO5" s="13"/>
+      <c r="BP5" s="29"/>
       <c r="BQ5" s="13"/>
-      <c r="BR5" s="29"/>
-      <c r="BS5" s="13"/>
+      <c r="BR5" s="13"/>
+      <c r="BS5" s="29"/>
       <c r="BT5" s="13"/>
       <c r="BU5" s="13"/>
       <c r="BV5" s="13"/>
-      <c r="BW5" s="13">
+      <c r="BW5" s="13"/>
+      <c r="BX5" s="13">
         <f t="shared" si="0"/>
         <v>975.6973999999999</v>
       </c>
-      <c r="BX5" s="13">
+      <c r="BY5" s="13">
         <f t="shared" si="1"/>
         <v>975.6973999999999</v>
       </c>
-      <c r="BY5" s="13"/>
       <c r="BZ5" s="13"/>
-      <c r="CC5" s="15"/>
-    </row>
-    <row r="6" spans="1:81" ht="45" customHeight="1" thickBot="1">
+      <c r="CA5" s="13"/>
+      <c r="CD5" s="15"/>
+    </row>
+    <row r="6" spans="1:82" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1166768</v>
       </c>
@@ -2007,78 +2014,80 @@
         <v>4040</v>
       </c>
       <c r="I6" s="13">
+        <v>5170</v>
+      </c>
+      <c r="J6" s="13">
+        <v>5170</v>
+      </c>
+      <c r="K6" s="13">
         <v>5059</v>
       </c>
-      <c r="J6" s="13">
-        <v>5059</v>
-      </c>
-      <c r="K6" s="13">
+      <c r="L6" s="13">
         <v>4880</v>
       </c>
-      <c r="L6" s="13">
+      <c r="M6" s="13">
         <v>4647</v>
       </c>
-      <c r="M6" s="13">
+      <c r="N6" s="13">
         <v>4650</v>
       </c>
-      <c r="N6" s="13">
+      <c r="O6" s="13">
         <v>4799</v>
       </c>
-      <c r="O6" s="13">
+      <c r="P6" s="13">
         <v>4740</v>
       </c>
-      <c r="P6" s="13">
+      <c r="Q6" s="13">
         <v>4350</v>
       </c>
-      <c r="Q6" s="13">
+      <c r="R6" s="13">
         <v>4355</v>
       </c>
-      <c r="R6" s="13">
+      <c r="S6" s="13">
         <v>4500</v>
       </c>
-      <c r="S6" s="13">
+      <c r="T6" s="13">
         <v>4424</v>
       </c>
-      <c r="T6" s="13">
+      <c r="U6" s="13">
         <v>4412</v>
       </c>
-      <c r="U6" s="13">
+      <c r="V6" s="13">
         <v>4450</v>
       </c>
-      <c r="V6" s="13">
+      <c r="W6" s="13">
         <v>4238</v>
       </c>
-      <c r="W6" s="13">
+      <c r="X6" s="13">
         <v>3970</v>
       </c>
-      <c r="X6" s="13">
+      <c r="Y6" s="13">
         <v>3870</v>
       </c>
-      <c r="Y6" s="13">
+      <c r="Z6" s="13">
         <v>3805</v>
       </c>
-      <c r="Z6" s="13">
+      <c r="AA6" s="13">
         <v>3667</v>
-      </c>
-      <c r="AA6" s="13">
-        <v>3582</v>
       </c>
       <c r="AB6" s="13">
         <v>3582</v>
       </c>
       <c r="AC6" s="13">
+        <v>3582</v>
+      </c>
+      <c r="AD6" s="13">
         <v>3570</v>
       </c>
-      <c r="AD6" s="13">
+      <c r="AE6" s="13">
         <v>3619</v>
       </c>
-      <c r="AE6" s="13">
+      <c r="AF6" s="13">
         <v>3650</v>
       </c>
-      <c r="AF6" s="13">
+      <c r="AG6" s="13">
         <v>3720</v>
       </c>
-      <c r="AG6" s="13"/>
       <c r="AH6" s="13"/>
       <c r="AI6" s="13"/>
       <c r="AJ6" s="13"/>
@@ -2112,41 +2121,42 @@
       <c r="BL6" s="13"/>
       <c r="BM6" s="13"/>
       <c r="BN6" s="13"/>
-      <c r="BO6" s="29"/>
-      <c r="BP6" s="13"/>
+      <c r="BO6" s="13"/>
+      <c r="BP6" s="29"/>
       <c r="BQ6" s="13"/>
-      <c r="BR6" s="29"/>
-      <c r="BS6" s="13"/>
+      <c r="BR6" s="13"/>
+      <c r="BS6" s="29"/>
       <c r="BT6" s="13"/>
       <c r="BU6" s="13"/>
-      <c r="BW6" s="13">
+      <c r="BV6" s="13"/>
+      <c r="BX6" s="13">
         <f t="shared" si="0"/>
         <v>1033.7</v>
       </c>
-      <c r="BX6" s="13">
+      <c r="BY6" s="13">
         <f t="shared" si="1"/>
         <v>1010</v>
       </c>
-      <c r="BY6" s="13">
-        <f t="shared" ref="BY6" si="2">(BX6-BW6)</f>
+      <c r="BZ6" s="13">
+        <f t="shared" ref="BZ6" si="2">(BY6-BX6)</f>
         <v>-23.700000000000045</v>
       </c>
-      <c r="BZ6" s="13">
-        <f>((BN6-H6)/H6)*100</f>
+      <c r="CA6" s="13">
+        <f>((BO6-H6)/H6)*100</f>
         <v>-100</v>
       </c>
-      <c r="CA6">
+      <c r="CB6">
         <v>5</v>
       </c>
-      <c r="CB6">
+      <c r="CC6">
         <v>3566</v>
       </c>
-      <c r="CC6" s="15">
-        <f>(CA6*CB6-CA6*H6)/100</f>
+      <c r="CD6" s="15">
+        <f>(CB6*CC6-CB6*H6)/100</f>
         <v>-23.7</v>
       </c>
     </row>
-    <row r="7" spans="1:81" ht="45" customHeight="1" thickBot="1">
+    <row r="7" spans="1:82" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1148899</v>
       </c>
@@ -2175,105 +2185,107 @@
         <v>3585</v>
       </c>
       <c r="I7" s="13">
+        <v>4069</v>
+      </c>
+      <c r="J7" s="13">
+        <v>4069</v>
+      </c>
+      <c r="K7" s="13">
         <v>4085</v>
       </c>
-      <c r="J7" s="13">
-        <v>4085</v>
-      </c>
-      <c r="K7" s="13">
+      <c r="L7" s="13">
         <v>3996</v>
       </c>
-      <c r="L7" s="13">
+      <c r="M7" s="13">
         <v>3954</v>
       </c>
-      <c r="M7" s="13">
+      <c r="N7" s="13">
         <v>3955</v>
       </c>
-      <c r="N7" s="13">
+      <c r="O7" s="13">
         <v>4022</v>
       </c>
-      <c r="O7" s="13">
+      <c r="P7" s="13">
         <v>4033</v>
       </c>
-      <c r="P7" s="13">
+      <c r="Q7" s="13">
         <v>3988</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="R7" s="13">
         <v>3916</v>
       </c>
-      <c r="R7" s="13">
+      <c r="S7" s="13">
         <v>3954</v>
       </c>
-      <c r="S7" s="13">
+      <c r="T7" s="13">
         <v>3932</v>
       </c>
-      <c r="T7" s="13">
+      <c r="U7" s="13">
         <v>3949</v>
       </c>
-      <c r="U7" s="13">
+      <c r="V7" s="13">
         <v>3943</v>
       </c>
-      <c r="V7" s="13">
+      <c r="W7" s="13">
         <v>3928</v>
       </c>
-      <c r="W7" s="13">
+      <c r="X7" s="13">
         <v>3913</v>
       </c>
-      <c r="X7" s="13">
+      <c r="Y7" s="13">
         <v>3860</v>
       </c>
-      <c r="Y7" s="13">
+      <c r="Z7" s="13">
         <v>3893</v>
       </c>
-      <c r="Z7" s="13">
+      <c r="AA7" s="13">
         <v>3900</v>
-      </c>
-      <c r="AA7" s="13">
-        <v>3842</v>
       </c>
       <c r="AB7" s="13">
         <v>3842</v>
       </c>
       <c r="AC7" s="13">
+        <v>3842</v>
+      </c>
+      <c r="AD7" s="13">
         <v>3841</v>
       </c>
-      <c r="AD7" s="13">
+      <c r="AE7" s="13">
         <v>3809</v>
       </c>
-      <c r="AE7" s="13">
+      <c r="AF7" s="13">
         <v>3810</v>
       </c>
-      <c r="AF7" s="13">
+      <c r="AG7" s="13">
         <v>3798</v>
       </c>
-      <c r="AG7" s="13">
+      <c r="AH7" s="13">
         <v>3713</v>
       </c>
-      <c r="AH7" s="13">
+      <c r="AI7" s="13">
         <v>3657</v>
       </c>
-      <c r="AI7" s="13">
+      <c r="AJ7" s="13">
         <v>3592</v>
       </c>
-      <c r="AJ7" s="13">
+      <c r="AK7" s="13">
         <v>3621</v>
       </c>
-      <c r="AK7" s="13">
+      <c r="AL7" s="13">
         <v>3572</v>
       </c>
-      <c r="AL7" s="13">
+      <c r="AM7" s="13">
         <v>3580</v>
       </c>
-      <c r="AM7" s="13">
+      <c r="AN7" s="13">
         <v>3569</v>
       </c>
-      <c r="AN7" s="13">
+      <c r="AO7" s="13">
         <v>3659</v>
       </c>
-      <c r="AO7" s="13">
+      <c r="AP7" s="13">
         <v>3656</v>
       </c>
-      <c r="AP7" s="13"/>
       <c r="AQ7" s="13"/>
       <c r="AR7" s="13"/>
       <c r="AS7" s="13"/>
@@ -2298,27 +2310,28 @@
       <c r="BL7" s="13"/>
       <c r="BM7" s="13"/>
       <c r="BN7" s="13"/>
-      <c r="BO7" s="29"/>
-      <c r="BP7" s="13"/>
+      <c r="BO7" s="13"/>
+      <c r="BP7" s="29"/>
       <c r="BQ7" s="13"/>
-      <c r="BR7" s="29"/>
-      <c r="BS7" s="13"/>
+      <c r="BR7" s="13"/>
+      <c r="BS7" s="29"/>
       <c r="BT7" s="13"/>
       <c r="BU7" s="13"/>
       <c r="BV7" s="13"/>
-      <c r="BW7" s="13">
+      <c r="BW7" s="13"/>
+      <c r="BX7" s="13">
         <f t="shared" si="0"/>
         <v>2509.5</v>
       </c>
-      <c r="BX7" s="13">
+      <c r="BY7" s="13">
         <f t="shared" si="1"/>
         <v>2509.5</v>
       </c>
-      <c r="BY7" s="13"/>
       <c r="BZ7" s="13"/>
-      <c r="CC7" s="15"/>
-    </row>
-    <row r="8" spans="1:81" ht="45" customHeight="1" thickBot="1">
+      <c r="CA7" s="13"/>
+      <c r="CD7" s="15"/>
+    </row>
+    <row r="8" spans="1:82" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1082379</v>
       </c>
@@ -2332,7 +2345,7 @@
       </c>
       <c r="D8" s="6" t="str">
         <f>IF(I8&lt;GEMINI!L8,"למכור בהפסד",IF(I8&gt;GEMINI!M8,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור בהפסד</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>52</v>
@@ -2347,141 +2360,143 @@
         <v>37875</v>
       </c>
       <c r="I8" s="13">
+        <v>41140</v>
+      </c>
+      <c r="J8" s="13">
+        <v>41140</v>
+      </c>
+      <c r="K8" s="13">
         <v>43310</v>
       </c>
-      <c r="J8" s="13">
-        <v>43310</v>
-      </c>
-      <c r="K8" s="13">
+      <c r="L8" s="13">
         <v>45300</v>
       </c>
-      <c r="L8" s="13">
+      <c r="M8" s="13">
         <v>40740</v>
       </c>
-      <c r="M8" s="13">
+      <c r="N8" s="13">
         <v>39070</v>
       </c>
-      <c r="N8" s="13">
+      <c r="O8" s="13">
         <v>39600</v>
       </c>
-      <c r="O8" s="13">
+      <c r="P8" s="13">
         <v>43640</v>
       </c>
-      <c r="P8" s="13">
+      <c r="Q8" s="13">
         <v>42700</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="R8" s="13">
         <v>42140</v>
       </c>
-      <c r="R8" s="13">
+      <c r="S8" s="13">
         <v>43490</v>
       </c>
-      <c r="S8" s="13">
+      <c r="T8" s="13">
         <v>40750</v>
       </c>
-      <c r="T8" s="13">
+      <c r="U8" s="13">
         <v>40900</v>
       </c>
-      <c r="U8" s="13">
+      <c r="V8" s="13">
         <v>40790</v>
       </c>
-      <c r="V8" s="13">
+      <c r="W8" s="13">
         <v>40820</v>
       </c>
-      <c r="W8" s="13">
+      <c r="X8" s="13">
         <v>41570</v>
       </c>
-      <c r="X8" s="13">
+      <c r="Y8" s="13">
         <v>42050</v>
       </c>
-      <c r="Y8" s="13">
+      <c r="Z8" s="13">
         <v>39960</v>
       </c>
-      <c r="Z8" s="13">
+      <c r="AA8" s="13">
         <v>39990</v>
-      </c>
-      <c r="AA8" s="13">
-        <v>38680</v>
       </c>
       <c r="AB8" s="13">
         <v>38680</v>
       </c>
       <c r="AC8" s="13">
+        <v>38680</v>
+      </c>
+      <c r="AD8" s="13">
         <v>37770</v>
       </c>
-      <c r="AD8" s="13">
+      <c r="AE8" s="13">
         <v>36330</v>
       </c>
-      <c r="AE8" s="13">
+      <c r="AF8" s="13">
         <v>38680</v>
       </c>
-      <c r="AF8" s="13">
+      <c r="AG8" s="13">
         <v>39090</v>
       </c>
-      <c r="AG8" s="13">
+      <c r="AH8" s="13">
         <v>37300</v>
       </c>
-      <c r="AH8" s="13">
+      <c r="AI8" s="13">
         <v>37650</v>
       </c>
-      <c r="AI8" s="13">
+      <c r="AJ8" s="13">
         <v>37300</v>
       </c>
-      <c r="AJ8" s="13">
+      <c r="AK8" s="13">
         <v>39450</v>
       </c>
-      <c r="AK8" s="13">
+      <c r="AL8" s="13">
         <v>38390</v>
       </c>
-      <c r="AL8" s="13">
+      <c r="AM8" s="13">
         <v>38800</v>
       </c>
-      <c r="AM8" s="13">
+      <c r="AN8" s="13">
         <v>38510</v>
-      </c>
-      <c r="AN8" s="13">
-        <v>38970</v>
       </c>
       <c r="AO8" s="13">
         <v>38970</v>
       </c>
       <c r="AP8" s="13">
-        <v>37700</v>
+        <v>38970</v>
       </c>
       <c r="AQ8" s="13">
         <v>37700</v>
       </c>
       <c r="AR8" s="13">
+        <v>37700</v>
+      </c>
+      <c r="AS8" s="13">
         <v>37750</v>
       </c>
-      <c r="AS8" s="13">
+      <c r="AT8" s="13">
         <v>38430</v>
       </c>
-      <c r="AT8" s="13">
+      <c r="AU8" s="13">
         <v>38250</v>
       </c>
-      <c r="AU8" s="13">
+      <c r="AV8" s="13">
         <v>40110</v>
       </c>
-      <c r="AV8" s="13">
+      <c r="AW8" s="13">
         <v>40820</v>
       </c>
-      <c r="AW8" s="13">
+      <c r="AX8" s="13">
         <v>39320</v>
       </c>
-      <c r="AX8" s="13">
+      <c r="AY8" s="13">
         <v>37800</v>
       </c>
-      <c r="AY8" s="13">
+      <c r="AZ8" s="13">
         <v>36620</v>
       </c>
-      <c r="AZ8" s="13">
+      <c r="BA8" s="13">
         <v>37130</v>
       </c>
-      <c r="BA8" s="13">
+      <c r="BB8" s="13">
         <v>35850</v>
       </c>
-      <c r="BB8" s="13"/>
       <c r="BC8" s="13"/>
       <c r="BD8" s="13"/>
       <c r="BE8" s="13"/>
@@ -2494,39 +2509,40 @@
       <c r="BL8" s="13"/>
       <c r="BM8" s="13"/>
       <c r="BN8" s="13"/>
-      <c r="BO8" s="29"/>
-      <c r="BP8" s="13"/>
+      <c r="BO8" s="13"/>
+      <c r="BP8" s="29"/>
       <c r="BQ8" s="13"/>
-      <c r="BR8" s="29"/>
-      <c r="BS8" s="13"/>
+      <c r="BR8" s="13"/>
+      <c r="BS8" s="29"/>
       <c r="BT8" s="13"/>
       <c r="BU8" s="13"/>
       <c r="BV8" s="13"/>
-      <c r="BW8" s="13">
+      <c r="BW8" s="13"/>
+      <c r="BX8" s="13">
         <f t="shared" si="0"/>
         <v>806.25</v>
       </c>
-      <c r="BX8" s="13">
+      <c r="BY8" s="13">
         <f t="shared" si="1"/>
         <v>757.5</v>
       </c>
-      <c r="BY8" s="13">
-        <f t="shared" ref="BY8:BY11" si="3">(BX8-BW8)</f>
+      <c r="BZ8" s="13">
+        <f t="shared" ref="BZ8:BZ11" si="3">(BY8-BX8)</f>
         <v>-48.75</v>
       </c>
-      <c r="BZ8" s="13"/>
-      <c r="CA8">
+      <c r="CA8" s="13"/>
+      <c r="CB8">
         <v>3</v>
       </c>
-      <c r="CB8">
+      <c r="CC8">
         <v>36250</v>
       </c>
-      <c r="CC8" s="15">
-        <f t="shared" ref="CC8:CC18" si="4">(CA8*CB8-CA8*H8)/100</f>
+      <c r="CD8" s="15">
+        <f t="shared" ref="CD8:CD18" si="4">(CB8*CC8-CB8*H8)/100</f>
         <v>-48.75</v>
       </c>
     </row>
-    <row r="9" spans="1:81" ht="45" customHeight="1" thickBot="1">
+    <row r="9" spans="1:82" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>629014</v>
       </c>
@@ -2555,135 +2571,137 @@
         <v>9227</v>
       </c>
       <c r="I9" s="13">
+        <v>10500</v>
+      </c>
+      <c r="J9" s="13">
+        <v>10500</v>
+      </c>
+      <c r="K9" s="13">
         <v>10640</v>
       </c>
-      <c r="J9" s="13">
-        <v>10640</v>
-      </c>
-      <c r="K9" s="13">
+      <c r="L9" s="13">
         <v>10660</v>
       </c>
-      <c r="L9" s="13">
+      <c r="M9" s="13">
         <v>10820</v>
       </c>
-      <c r="M9" s="13">
+      <c r="N9" s="13">
         <v>10680</v>
       </c>
-      <c r="N9" s="13">
+      <c r="O9" s="13">
         <v>11290</v>
       </c>
-      <c r="O9" s="13">
+      <c r="P9" s="13">
         <v>11020</v>
-      </c>
-      <c r="P9" s="13">
-        <v>10100</v>
       </c>
       <c r="Q9" s="13">
         <v>10100</v>
       </c>
       <c r="R9" s="13">
+        <v>10100</v>
+      </c>
+      <c r="S9" s="13">
         <v>10240</v>
       </c>
-      <c r="S9" s="13">
+      <c r="T9" s="13">
         <v>9891</v>
       </c>
-      <c r="T9" s="13">
+      <c r="U9" s="13">
         <v>9956</v>
       </c>
-      <c r="U9" s="13">
+      <c r="V9" s="13">
         <v>9910</v>
       </c>
-      <c r="V9" s="13">
+      <c r="W9" s="13">
         <v>9960</v>
       </c>
-      <c r="W9" s="13">
+      <c r="X9" s="13">
         <v>9924</v>
       </c>
-      <c r="X9" s="13">
+      <c r="Y9" s="13">
         <v>9999</v>
       </c>
-      <c r="Y9" s="13">
+      <c r="Z9" s="13">
         <v>9962</v>
       </c>
-      <c r="Z9" s="13">
+      <c r="AA9" s="13">
         <v>9979</v>
-      </c>
-      <c r="AA9" s="13">
-        <v>10130</v>
       </c>
       <c r="AB9" s="13">
         <v>10130</v>
       </c>
       <c r="AC9" s="13">
+        <v>10130</v>
+      </c>
+      <c r="AD9" s="13">
         <v>10400</v>
       </c>
-      <c r="AD9" s="13">
+      <c r="AE9" s="13">
         <v>10320</v>
       </c>
-      <c r="AE9" s="13">
+      <c r="AF9" s="13">
         <v>10300</v>
       </c>
-      <c r="AF9" s="13">
+      <c r="AG9" s="13">
         <v>10310</v>
       </c>
-      <c r="AG9" s="13">
+      <c r="AH9" s="13">
         <v>9672</v>
       </c>
-      <c r="AH9" s="13">
+      <c r="AI9" s="13">
         <v>9953</v>
       </c>
-      <c r="AI9" s="13">
+      <c r="AJ9" s="13">
         <v>10090</v>
       </c>
-      <c r="AJ9" s="13">
+      <c r="AK9" s="13">
         <v>10070</v>
       </c>
-      <c r="AK9" s="13">
+      <c r="AL9" s="13">
         <v>10030</v>
       </c>
-      <c r="AL9" s="13">
+      <c r="AM9" s="13">
         <v>10120</v>
       </c>
-      <c r="AM9" s="13">
+      <c r="AN9" s="13">
         <v>10000</v>
       </c>
-      <c r="AN9" s="13">
+      <c r="AO9" s="13">
         <v>10080</v>
       </c>
-      <c r="AO9" s="13">
+      <c r="AP9" s="13">
         <v>10030</v>
-      </c>
-      <c r="AP9" s="13">
-        <v>9726</v>
       </c>
       <c r="AQ9" s="13">
         <v>9726</v>
       </c>
       <c r="AR9" s="13">
+        <v>9726</v>
+      </c>
+      <c r="AS9" s="13">
         <v>9659</v>
       </c>
-      <c r="AS9" s="13">
+      <c r="AT9" s="13">
         <v>9670</v>
       </c>
-      <c r="AT9" s="13">
+      <c r="AU9" s="13">
         <v>9590</v>
       </c>
-      <c r="AU9" s="13">
+      <c r="AV9" s="13">
         <v>9588</v>
       </c>
-      <c r="AV9" s="13">
+      <c r="AW9" s="13">
         <v>9400</v>
       </c>
-      <c r="AW9" s="13">
+      <c r="AX9" s="13">
         <v>9320</v>
       </c>
-      <c r="AX9" s="13">
+      <c r="AY9" s="13">
         <v>9071</v>
       </c>
-      <c r="AY9" s="13">
+      <c r="AZ9" s="13">
         <v>9271</v>
       </c>
-      <c r="AZ9" s="13"/>
       <c r="BA9" s="13"/>
       <c r="BB9" s="13"/>
       <c r="BC9" s="13"/>
@@ -2698,39 +2716,40 @@
       <c r="BL9" s="13"/>
       <c r="BM9" s="13"/>
       <c r="BN9" s="13"/>
-      <c r="BO9" s="29"/>
-      <c r="BP9" s="13"/>
+      <c r="BO9" s="13"/>
+      <c r="BP9" s="29"/>
       <c r="BQ9" s="13"/>
-      <c r="BR9" s="29"/>
-      <c r="BS9" s="13"/>
+      <c r="BR9" s="13"/>
+      <c r="BS9" s="29"/>
       <c r="BT9" s="13"/>
       <c r="BU9" s="13"/>
       <c r="BV9" s="13"/>
-      <c r="BW9" s="13">
+      <c r="BW9" s="13"/>
+      <c r="BX9" s="13">
         <f t="shared" si="0"/>
         <v>-38.65</v>
       </c>
-      <c r="BX9" s="13">
+      <c r="BY9" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BY9" s="13">
+      <c r="BZ9" s="13">
         <f t="shared" si="3"/>
         <v>38.65</v>
       </c>
-      <c r="BZ9" s="13"/>
-      <c r="CA9">
+      <c r="CA9" s="13"/>
+      <c r="CB9">
         <v>5</v>
       </c>
-      <c r="CB9">
+      <c r="CC9">
         <v>10000</v>
       </c>
-      <c r="CC9" s="15">
+      <c r="CD9" s="15">
         <f t="shared" si="4"/>
         <v>38.65</v>
       </c>
     </row>
-    <row r="10" spans="1:81" ht="45" customHeight="1" thickBot="1">
+    <row r="10" spans="1:82" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1141464</v>
       </c>
@@ -2744,7 +2763,7 @@
       </c>
       <c r="D10" s="6" t="str">
         <f>IF(I10&lt;GEMINI!L10,"למכור בהפסד",IF(I10&gt;GEMINI!M10,"למכור ברווח","לשמור"))</f>
-        <v>לשמור</v>
+        <v>למכור בהפסד</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>39</v>
@@ -2759,217 +2778,220 @@
         <v>4834</v>
       </c>
       <c r="I10" s="13">
+        <v>4777</v>
+      </c>
+      <c r="J10" s="13">
+        <v>4777</v>
+      </c>
+      <c r="K10" s="13">
         <v>4987</v>
       </c>
-      <c r="J10" s="13">
-        <v>4987</v>
-      </c>
-      <c r="K10" s="13">
+      <c r="L10" s="13">
         <v>5027</v>
-      </c>
-      <c r="L10" s="13">
-        <v>5067</v>
       </c>
       <c r="M10" s="13">
         <v>5067</v>
       </c>
       <c r="N10" s="13">
+        <v>5067</v>
+      </c>
+      <c r="O10" s="13">
         <v>5126</v>
       </c>
-      <c r="O10" s="13">
+      <c r="P10" s="13">
         <v>5164</v>
-      </c>
-      <c r="P10" s="13">
-        <v>4809</v>
       </c>
       <c r="Q10" s="13">
         <v>4809</v>
       </c>
       <c r="R10" s="13">
+        <v>4809</v>
+      </c>
+      <c r="S10" s="13">
         <v>4849</v>
       </c>
-      <c r="S10" s="13">
+      <c r="T10" s="13">
         <v>4821</v>
       </c>
-      <c r="T10" s="13">
+      <c r="U10" s="13">
         <v>4925</v>
       </c>
-      <c r="U10" s="13">
+      <c r="V10" s="13">
         <v>5013</v>
-      </c>
-      <c r="V10" s="13">
-        <v>5050</v>
       </c>
       <c r="W10" s="13">
         <v>5050</v>
       </c>
       <c r="X10" s="13">
+        <v>5050</v>
+      </c>
+      <c r="Y10" s="13">
         <v>4930</v>
       </c>
-      <c r="Y10" s="13">
+      <c r="Z10" s="13">
         <v>5150</v>
       </c>
-      <c r="Z10" s="13">
+      <c r="AA10" s="13">
         <v>5283</v>
-      </c>
-      <c r="AA10" s="13">
-        <v>5253</v>
       </c>
       <c r="AB10" s="13">
         <v>5253</v>
       </c>
       <c r="AC10" s="13">
+        <v>5253</v>
+      </c>
+      <c r="AD10" s="13">
         <v>5400</v>
       </c>
-      <c r="AD10" s="13">
+      <c r="AE10" s="13">
         <v>5522</v>
       </c>
-      <c r="AE10" s="13">
+      <c r="AF10" s="13">
         <v>5690</v>
       </c>
-      <c r="AF10" s="13">
+      <c r="AG10" s="13">
         <v>5749</v>
       </c>
-      <c r="AG10" s="13">
+      <c r="AH10" s="13">
         <v>5840</v>
-      </c>
-      <c r="AH10" s="13">
-        <v>5650</v>
       </c>
       <c r="AI10" s="13">
         <v>5650</v>
       </c>
       <c r="AJ10" s="13">
+        <v>5650</v>
+      </c>
+      <c r="AK10" s="13">
         <v>5841</v>
       </c>
-      <c r="AK10" s="13">
+      <c r="AL10" s="13">
         <v>5758</v>
       </c>
-      <c r="AL10" s="13">
+      <c r="AM10" s="13">
         <v>5673</v>
       </c>
-      <c r="AM10" s="13">
+      <c r="AN10" s="13">
         <v>5609</v>
       </c>
-      <c r="AN10" s="13">
+      <c r="AO10" s="13">
         <v>5750</v>
       </c>
-      <c r="AO10" s="13">
+      <c r="AP10" s="13">
         <v>5841</v>
-      </c>
-      <c r="AP10" s="13">
-        <v>5564</v>
       </c>
       <c r="AQ10" s="13">
         <v>5564</v>
       </c>
       <c r="AR10" s="13">
+        <v>5564</v>
+      </c>
+      <c r="AS10" s="13">
         <v>5557</v>
       </c>
-      <c r="AS10" s="13">
+      <c r="AT10" s="13">
         <v>5501</v>
       </c>
-      <c r="AT10" s="13">
+      <c r="AU10" s="13">
         <v>5250</v>
       </c>
-      <c r="AU10" s="13">
+      <c r="AV10" s="13">
         <v>5270</v>
       </c>
-      <c r="AV10" s="13">
+      <c r="AW10" s="13">
         <v>5149</v>
       </c>
-      <c r="AW10" s="13">
+      <c r="AX10" s="13">
         <v>5092</v>
       </c>
-      <c r="AX10" s="13">
+      <c r="AY10" s="13">
         <v>5228</v>
       </c>
-      <c r="AY10" s="13">
+      <c r="AZ10" s="13">
         <v>5301</v>
       </c>
-      <c r="AZ10" s="13">
+      <c r="BA10" s="13">
         <v>5159</v>
       </c>
-      <c r="BA10" s="13">
+      <c r="BB10" s="13">
         <v>5198</v>
       </c>
-      <c r="BB10" s="13">
+      <c r="BC10" s="13">
         <v>5077</v>
       </c>
-      <c r="BC10" s="13">
+      <c r="BD10" s="13">
         <v>4842</v>
       </c>
-      <c r="BD10" s="13">
+      <c r="BE10" s="13">
         <v>5050</v>
       </c>
-      <c r="BE10" s="13">
+      <c r="BF10" s="13">
         <v>4970</v>
       </c>
-      <c r="BF10" s="13">
+      <c r="BG10" s="13">
         <v>4880</v>
       </c>
-      <c r="BG10" s="13">
+      <c r="BH10" s="13">
         <v>4704</v>
       </c>
-      <c r="BH10" s="13">
+      <c r="BI10" s="13">
         <v>4770</v>
       </c>
-      <c r="BI10" s="13">
+      <c r="BJ10" s="13">
         <v>4609</v>
       </c>
-      <c r="BJ10" s="13">
+      <c r="BK10" s="13">
         <v>4674</v>
       </c>
-      <c r="BK10" s="13">
+      <c r="BL10" s="13">
         <v>4710</v>
       </c>
-      <c r="BL10" s="13">
+      <c r="BM10" s="13">
         <v>4688</v>
       </c>
-      <c r="BM10" s="13">
+      <c r="BN10" s="13">
         <v>4900</v>
       </c>
-      <c r="BN10" s="13">
+      <c r="BO10" s="13">
         <v>5000</v>
       </c>
-      <c r="BO10" s="29">
+      <c r="BP10" s="29">
         <v>4932</v>
       </c>
-      <c r="BP10" s="13"/>
       <c r="BQ10" s="13"/>
-      <c r="BR10" s="29"/>
-      <c r="BS10" s="13"/>
+      <c r="BR10" s="13"/>
+      <c r="BS10" s="29"/>
       <c r="BT10" s="13"/>
       <c r="BU10" s="13"/>
       <c r="BV10" s="13"/>
-      <c r="BW10" s="13">
+      <c r="BW10" s="13"/>
+      <c r="BX10" s="13">
         <f t="shared" si="0"/>
         <v>-87.859799999999964</v>
       </c>
-      <c r="BX10" s="13">
+      <c r="BY10" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BY10" s="13">
+      <c r="BZ10" s="13">
         <f t="shared" si="3"/>
         <v>87.859799999999964</v>
       </c>
-      <c r="BZ10" s="13">
-        <f>((BN10-H10)/H10)*100</f>
+      <c r="CA10" s="13">
+        <f>((BO10-H10)/H10)*100</f>
         <v>3.434009102192801</v>
       </c>
-      <c r="CA10">
+      <c r="CB10">
         <v>21</v>
       </c>
-      <c r="CB10">
+      <c r="CC10">
         <v>5252.38</v>
       </c>
-      <c r="CC10" s="15">
+      <c r="CD10" s="15">
         <f t="shared" si="4"/>
         <v>87.859799999999964</v>
       </c>
     </row>
-    <row r="11" spans="1:81" ht="45" customHeight="1" thickBot="1">
+    <row r="11" spans="1:82" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1166974</v>
       </c>
@@ -2998,99 +3020,101 @@
         <v>901.87</v>
       </c>
       <c r="I11" s="13">
+        <v>1074</v>
+      </c>
+      <c r="J11" s="13">
+        <v>1074</v>
+      </c>
+      <c r="K11" s="13">
         <v>1070</v>
       </c>
-      <c r="J11" s="13">
-        <v>1070</v>
-      </c>
-      <c r="K11" s="13">
+      <c r="L11" s="13">
         <v>1086</v>
       </c>
-      <c r="L11" s="13">
+      <c r="M11" s="13">
         <v>1054</v>
       </c>
-      <c r="M11" s="13">
+      <c r="N11" s="13">
         <v>1063</v>
       </c>
-      <c r="N11" s="13">
+      <c r="O11" s="13">
         <v>1099</v>
       </c>
-      <c r="O11" s="13">
+      <c r="P11" s="13">
         <v>1173</v>
       </c>
-      <c r="P11" s="13">
+      <c r="Q11" s="13">
         <v>1114</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="R11" s="13">
         <v>1075</v>
       </c>
-      <c r="R11" s="13">
+      <c r="S11" s="13">
         <v>1109</v>
       </c>
-      <c r="S11" s="13">
+      <c r="T11" s="13">
         <v>1090</v>
       </c>
-      <c r="T11" s="13">
+      <c r="U11" s="13">
         <v>1144</v>
       </c>
-      <c r="U11" s="13">
+      <c r="V11" s="13">
         <v>1162</v>
       </c>
-      <c r="V11" s="13">
+      <c r="W11" s="13">
         <v>1109</v>
       </c>
-      <c r="W11" s="13">
+      <c r="X11" s="13">
         <v>1029</v>
       </c>
-      <c r="X11" s="13">
+      <c r="Y11" s="13">
         <v>993</v>
       </c>
-      <c r="Y11" s="13">
+      <c r="Z11" s="13">
         <v>1017</v>
       </c>
-      <c r="Z11" s="13">
+      <c r="AA11" s="13">
         <v>960</v>
-      </c>
-      <c r="AA11" s="13">
-        <v>965</v>
       </c>
       <c r="AB11" s="13">
         <v>965</v>
       </c>
       <c r="AC11" s="13">
+        <v>965</v>
+      </c>
+      <c r="AD11" s="13">
         <v>951.7</v>
       </c>
-      <c r="AD11" s="13">
+      <c r="AE11" s="13">
         <v>946</v>
       </c>
-      <c r="AE11" s="13">
+      <c r="AF11" s="13">
         <v>869.2</v>
       </c>
-      <c r="AF11" s="13">
+      <c r="AG11" s="13">
         <v>865</v>
       </c>
-      <c r="AG11" s="13">
+      <c r="AH11" s="13">
         <v>851</v>
       </c>
-      <c r="AH11" s="13">
+      <c r="AI11" s="13">
         <v>829.3</v>
       </c>
-      <c r="AI11" s="13">
+      <c r="AJ11" s="13">
         <v>830</v>
       </c>
-      <c r="AJ11" s="13">
+      <c r="AK11" s="13">
         <v>810</v>
       </c>
-      <c r="AK11" s="13">
+      <c r="AL11" s="13">
         <v>812.8</v>
       </c>
-      <c r="AL11" s="13">
+      <c r="AM11" s="13">
         <v>788</v>
       </c>
-      <c r="AM11" s="13">
+      <c r="AN11" s="13">
         <v>772</v>
       </c>
-      <c r="AN11" s="13"/>
       <c r="AO11" s="13"/>
       <c r="AP11" s="13"/>
       <c r="AQ11" s="13"/>
@@ -3117,33 +3141,34 @@
       <c r="BL11" s="13"/>
       <c r="BM11" s="13"/>
       <c r="BN11" s="13"/>
-      <c r="BO11" s="29"/>
-      <c r="BP11" s="13"/>
+      <c r="BO11" s="13"/>
+      <c r="BP11" s="29"/>
       <c r="BQ11" s="13"/>
-      <c r="BR11" s="29"/>
-      <c r="BS11" s="13"/>
+      <c r="BR11" s="13"/>
+      <c r="BS11" s="29"/>
       <c r="BT11" s="13"/>
       <c r="BU11" s="13"/>
       <c r="BV11" s="13"/>
-      <c r="BW11" s="13">
+      <c r="BW11" s="13"/>
+      <c r="BX11" s="13">
         <f t="shared" si="0"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BX11" s="13">
+      <c r="BY11" s="13">
         <f t="shared" si="1"/>
         <v>721.49600000000009</v>
       </c>
-      <c r="BY11" s="13">
+      <c r="BZ11" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="BZ11" s="13"/>
-      <c r="CC11" s="15">
+      <c r="CA11" s="13"/>
+      <c r="CD11" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:81" ht="45" customHeight="1" thickBot="1">
+    <row r="12" spans="1:82" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1176593</v>
       </c>
@@ -3172,105 +3197,107 @@
         <v>22581.42</v>
       </c>
       <c r="I12" s="13">
-        <v>29670</v>
+        <v>29910</v>
       </c>
       <c r="J12" s="13">
-        <v>29670</v>
+        <v>29910</v>
       </c>
       <c r="K12" s="13">
+        <v>30240</v>
+      </c>
+      <c r="L12" s="13">
         <v>29650</v>
       </c>
-      <c r="L12" s="13">
+      <c r="M12" s="13">
         <v>28730</v>
       </c>
-      <c r="M12" s="13">
+      <c r="N12" s="13">
         <v>28240</v>
       </c>
-      <c r="N12" s="13">
+      <c r="O12" s="13">
         <v>29460</v>
       </c>
-      <c r="O12" s="13">
+      <c r="P12" s="13">
         <v>28720</v>
-      </c>
-      <c r="P12" s="13">
-        <v>27890</v>
       </c>
       <c r="Q12" s="13">
         <v>27890</v>
       </c>
       <c r="R12" s="13">
+        <v>27890</v>
+      </c>
+      <c r="S12" s="13">
         <v>30100</v>
       </c>
-      <c r="S12" s="13">
+      <c r="T12" s="13">
         <v>30500</v>
       </c>
-      <c r="T12" s="13">
+      <c r="U12" s="13">
         <v>28850</v>
       </c>
-      <c r="U12" s="13">
+      <c r="V12" s="13">
         <v>27450</v>
       </c>
-      <c r="V12" s="13">
+      <c r="W12" s="13">
         <v>26940</v>
       </c>
-      <c r="W12" s="13">
+      <c r="X12" s="13">
         <v>26800</v>
       </c>
-      <c r="X12" s="13">
+      <c r="Y12" s="13">
         <v>25950</v>
       </c>
-      <c r="Y12" s="13">
+      <c r="Z12" s="13">
         <v>26000</v>
       </c>
-      <c r="Z12" s="13">
+      <c r="AA12" s="13">
         <v>26600</v>
-      </c>
-      <c r="AA12" s="13">
-        <v>24630</v>
       </c>
       <c r="AB12" s="13">
         <v>24630</v>
       </c>
       <c r="AC12" s="13">
+        <v>24630</v>
+      </c>
+      <c r="AD12" s="13">
         <v>25230</v>
       </c>
-      <c r="AD12" s="13">
+      <c r="AE12" s="13">
         <v>24700</v>
       </c>
-      <c r="AE12" s="13">
+      <c r="AF12" s="13">
         <v>23780</v>
       </c>
-      <c r="AF12" s="13">
+      <c r="AG12" s="13">
         <v>23920</v>
       </c>
-      <c r="AG12" s="13">
+      <c r="AH12" s="13">
         <v>22390</v>
       </c>
-      <c r="AH12" s="13">
+      <c r="AI12" s="13">
         <v>23000</v>
       </c>
-      <c r="AI12" s="13">
+      <c r="AJ12" s="13">
         <v>20990</v>
       </c>
-      <c r="AJ12" s="13">
+      <c r="AK12" s="13">
         <v>20260</v>
       </c>
-      <c r="AK12" s="13">
+      <c r="AL12" s="13">
         <v>19200</v>
       </c>
-      <c r="AL12" s="13">
+      <c r="AM12" s="13">
         <v>19860</v>
       </c>
-      <c r="AM12" s="13">
+      <c r="AN12" s="13">
         <v>19700</v>
       </c>
-      <c r="AN12" s="13">
+      <c r="AO12" s="13">
         <v>19430</v>
       </c>
-      <c r="AO12" s="13">
+      <c r="AP12" s="13">
         <v>19020</v>
       </c>
-      <c r="AP12" s="13"/>
       <c r="AQ12" s="13"/>
       <c r="AR12" s="13"/>
       <c r="AS12" s="13"/>
@@ -3295,36 +3322,37 @@
       <c r="BL12" s="13"/>
       <c r="BM12" s="13"/>
       <c r="BN12" s="13"/>
-      <c r="BO12" s="29"/>
-      <c r="BP12" s="13"/>
+      <c r="BO12" s="13"/>
+      <c r="BP12" s="29"/>
       <c r="BQ12" s="13"/>
-      <c r="BR12" s="29"/>
-      <c r="BS12" s="13"/>
+      <c r="BR12" s="13"/>
+      <c r="BS12" s="29"/>
       <c r="BT12" s="13"/>
       <c r="BU12" s="13"/>
       <c r="BV12" s="13"/>
-      <c r="BW12" s="13">
+      <c r="BW12" s="13"/>
+      <c r="BX12" s="13">
         <f t="shared" si="0"/>
         <v>-331.70059999999995</v>
       </c>
-      <c r="BX12" s="13">
+      <c r="BY12" s="13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="BY12" s="13"/>
       <c r="BZ12" s="13"/>
-      <c r="CA12">
+      <c r="CA12" s="13"/>
+      <c r="CB12">
         <v>7</v>
       </c>
-      <c r="CB12">
+      <c r="CC12">
         <v>27320</v>
       </c>
-      <c r="CC12" s="15">
+      <c r="CD12" s="15">
         <f t="shared" si="4"/>
         <v>331.70059999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:81" ht="45" customHeight="1" thickBot="1">
+    <row r="13" spans="1:82" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>397018</v>
       </c>
@@ -3353,55 +3381,57 @@
         <v>840</v>
       </c>
       <c r="I13" s="13">
+        <v>741</v>
+      </c>
+      <c r="J13" s="13">
+        <v>741</v>
+      </c>
+      <c r="K13" s="13">
         <v>790</v>
       </c>
-      <c r="J13" s="13">
-        <v>790</v>
-      </c>
-      <c r="K13" s="13">
+      <c r="L13" s="13">
         <v>840</v>
       </c>
-      <c r="L13" s="13">
+      <c r="M13" s="13">
         <v>837.7</v>
       </c>
-      <c r="M13" s="13">
+      <c r="N13" s="13">
         <v>802</v>
       </c>
-      <c r="N13" s="13">
+      <c r="O13" s="13">
         <v>1009</v>
       </c>
-      <c r="O13" s="13">
+      <c r="P13" s="13">
         <v>1074</v>
-      </c>
-      <c r="P13" s="13">
-        <v>900</v>
       </c>
       <c r="Q13" s="13">
         <v>900</v>
       </c>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13">
+      <c r="R13" s="13">
+        <v>900</v>
+      </c>
+      <c r="S13" s="13"/>
+      <c r="T13" s="13">
         <v>1490</v>
       </c>
-      <c r="T13" s="13">
+      <c r="U13" s="13">
         <v>1210</v>
       </c>
-      <c r="U13" s="13">
+      <c r="V13" s="13">
         <v>110